--- a/financial_models/opportunities/1913.HK_Valuation.xlsx
+++ b/financial_models/opportunities/1913.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25570E71-94A8-4613-9D06-EB51AEB063E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF9B74A1-019A-4E5C-BB8E-878BA4CD7D16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2409,9 +2409,6 @@
     <t>Valuation Method</t>
   </si>
   <si>
-    <t>DDM</t>
-  </si>
-  <si>
     <t>Dividend</t>
   </si>
   <si>
@@ -2470,6 +2467,9 @@
   </si>
   <si>
     <t>CNS_04</t>
+  </si>
+  <si>
+    <t>DCF</t>
   </si>
 </sst>
 </file>
@@ -3888,29 +3888,29 @@
     </xf>
     <xf numFmtId="181" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="181" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4232,7 +4232,7 @@
         <v>45797</v>
       </c>
       <c r="D1" s="316" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="E1" s="292" t="s">
         <v>355</v>
@@ -4269,7 +4269,7 @@
         <v>316</v>
       </c>
       <c r="C5" s="294" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -4277,7 +4277,7 @@
         <v>0</v>
       </c>
       <c r="C6" s="51">
-        <v>2558820096</v>
+        <v>2558824000</v>
       </c>
       <c r="E6" s="48"/>
     </row>
@@ -4316,7 +4316,7 @@
         <v>419</v>
       </c>
       <c r="C11" s="49" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="D11" s="49"/>
       <c r="E11" s="34"/>
@@ -4347,7 +4347,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>127685.1227904</v>
+        <v>127685.31759999999</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4384,13 +4384,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="356" t="s">
+      <c r="B18" s="358" t="s">
         <v>362</v>
       </c>
-      <c r="C18" s="356"/>
-      <c r="D18" s="356"/>
-      <c r="E18" s="356"/>
-      <c r="F18" s="356"/>
+      <c r="C18" s="358"/>
+      <c r="D18" s="358"/>
+      <c r="E18" s="358"/>
+      <c r="F18" s="358"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4411,7 +4411,7 @@
         <v>441</v>
       </c>
       <c r="E21" s="308" t="s">
-        <v>442</v>
+        <v>462</v>
       </c>
     </row>
     <row r="22" spans="2:6">
@@ -4419,15 +4419,13 @@
         <v>56</v>
       </c>
       <c r="C22" s="48" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="D22" s="1" t="str">
         <f>IF(valuation_method="DDM","DDM Terminal Value","")</f>
-        <v>DDM Terminal Value</v>
-      </c>
-      <c r="E22" s="313">
-        <v>0.02</v>
-      </c>
+        <v/>
+      </c>
+      <c r="E22" s="313"/>
     </row>
     <row r="23" spans="2:6">
       <c r="B23" s="1" t="s">
@@ -4450,7 +4448,7 @@
         <v>349</v>
       </c>
       <c r="C25" s="48" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="D25" s="32" t="str">
         <f>IF(D11="","",Market_currency&amp;"/"&amp;D13&amp;":")</f>
@@ -4468,14 +4466,14 @@
       </c>
       <c r="C26" s="304">
         <f>C132</f>
-        <v>182.47610718562294</v>
+        <v>30.533856751256884</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>402</v>
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.56101689335785077</v>
+        <v>-0.11622199457788085</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4507,7 +4505,7 @@
       </c>
       <c r="C29" s="310">
         <f>C149</f>
-        <v>68.832257720708085</v>
+        <v>13.459717474947846</v>
       </c>
       <c r="D29" s="310" t="str">
         <f>D149</f>
@@ -4526,7 +4524,7 @@
       </c>
       <c r="C30" s="311">
         <f>C157</f>
-        <v>103.4884509637497</v>
+        <v>19.812807168472737</v>
       </c>
       <c r="D30" s="311" t="str">
         <f>D157</f>
@@ -4545,7 +4543,7 @@
       </c>
       <c r="C31" s="311">
         <f>C165</f>
-        <v>148.63808005768217</v>
+        <v>28.021422889721528</v>
       </c>
       <c r="D31" s="311" t="str">
         <f>D165</f>
@@ -4564,7 +4562,7 @@
       </c>
       <c r="C32" s="311">
         <f>C173</f>
-        <v>133.40829672810483</v>
+        <v>25.258804060604444</v>
       </c>
       <c r="D32" s="311" t="str">
         <f>D173</f>
@@ -4592,22 +4590,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="356" t="s">
+      <c r="B36" s="358" t="s">
         <v>363</v>
       </c>
-      <c r="C36" s="356"/>
-      <c r="D36" s="356"/>
-      <c r="E36" s="356"/>
-      <c r="F36" s="356"/>
+      <c r="C36" s="358"/>
+      <c r="D36" s="358"/>
+      <c r="E36" s="358"/>
+      <c r="F36" s="358"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="358" t="s">
+      <c r="B37" s="361" t="s">
         <v>341</v>
       </c>
-      <c r="C37" s="358"/>
-      <c r="D37" s="358"/>
-      <c r="E37" s="358"/>
-      <c r="F37" s="358"/>
+      <c r="C37" s="361"/>
+      <c r="D37" s="361"/>
+      <c r="E37" s="361"/>
+      <c r="F37" s="361"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4619,13 +4617,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="357" t="s">
+      <c r="B40" s="359" t="s">
         <v>231</v>
       </c>
-      <c r="C40" s="357"/>
-      <c r="D40" s="357"/>
-      <c r="E40" s="357"/>
-      <c r="F40" s="357"/>
+      <c r="C40" s="359"/>
+      <c r="D40" s="359"/>
+      <c r="E40" s="359"/>
+      <c r="F40" s="359"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4645,13 +4643,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="357" t="s">
+      <c r="B43" s="359" t="s">
         <v>233</v>
       </c>
-      <c r="C43" s="357"/>
-      <c r="D43" s="357"/>
-      <c r="E43" s="357"/>
-      <c r="F43" s="357"/>
+      <c r="C43" s="359"/>
+      <c r="D43" s="359"/>
+      <c r="E43" s="359"/>
+      <c r="F43" s="359"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4680,13 +4678,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="357" t="s">
+      <c r="B47" s="359" t="s">
         <v>236</v>
       </c>
-      <c r="C47" s="357"/>
-      <c r="D47" s="357"/>
-      <c r="E47" s="357"/>
-      <c r="F47" s="357"/>
+      <c r="C47" s="359"/>
+      <c r="D47" s="359"/>
+      <c r="E47" s="359"/>
+      <c r="F47" s="359"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4702,13 +4700,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="357" t="s">
+      <c r="B50" s="359" t="s">
         <v>240</v>
       </c>
-      <c r="C50" s="357"/>
-      <c r="D50" s="357"/>
-      <c r="E50" s="357"/>
-      <c r="F50" s="357"/>
+      <c r="C50" s="359"/>
+      <c r="D50" s="359"/>
+      <c r="E50" s="359"/>
+      <c r="F50" s="359"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4731,7 +4729,7 @@
       </c>
       <c r="C52" s="350">
         <f>Normalized_FCF!C47</f>
-        <v>0</v>
+        <v>-90938</v>
       </c>
       <c r="D52" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4746,7 +4744,7 @@
       </c>
       <c r="C53" s="349">
         <f>Normalized_FCF!C12</f>
-        <v>0</v>
+        <v>-90938</v>
       </c>
       <c r="D53" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4764,7 +4762,7 @@
       </c>
       <c r="C56" s="349">
         <f>Normalized_FCF!C15</f>
-        <v>0</v>
+        <v>-4167.7471308175782</v>
       </c>
       <c r="D56" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4772,13 +4770,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="357" t="s">
+      <c r="B58" s="359" t="s">
         <v>241</v>
       </c>
-      <c r="C58" s="357"/>
-      <c r="D58" s="357"/>
-      <c r="E58" s="357"/>
-      <c r="F58" s="357"/>
+      <c r="C58" s="359"/>
+      <c r="D58" s="359"/>
+      <c r="E58" s="359"/>
+      <c r="F58" s="359"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4786,7 +4784,7 @@
       </c>
       <c r="C59" s="349">
         <f>Normalized_FCF!C14</f>
-        <v>-255194.61026540946</v>
+        <v>-232460.11026540946</v>
       </c>
       <c r="D59" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4794,7 +4792,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="357" t="s">
+      <c r="B61" s="359" t="s">
         <v>340</v>
       </c>
       <c r="C61" s="360"/>
@@ -4816,22 +4814,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="356" t="s">
+      <c r="B64" s="358" t="s">
         <v>345</v>
       </c>
-      <c r="C64" s="356"/>
-      <c r="D64" s="356"/>
-      <c r="E64" s="356"/>
-      <c r="F64" s="356"/>
+      <c r="C64" s="358"/>
+      <c r="D64" s="358"/>
+      <c r="E64" s="358"/>
+      <c r="F64" s="358"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="356" t="s">
+      <c r="B65" s="358" t="s">
         <v>364</v>
       </c>
-      <c r="C65" s="356"/>
-      <c r="D65" s="356"/>
-      <c r="E65" s="356"/>
-      <c r="F65" s="356"/>
+      <c r="C65" s="358"/>
+      <c r="D65" s="358"/>
+      <c r="E65" s="358"/>
+      <c r="F65" s="358"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4852,7 +4850,7 @@
       </c>
       <c r="C68" s="349">
         <f>Normalized_FCF!C19</f>
-        <v>765583.83079622837</v>
+        <v>693212.58366541076</v>
       </c>
       <c r="D68" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4865,7 +4863,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>5.3663066893658573E-2</v>
+        <v>4.8590180456311333E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4878,35 +4876,35 @@
         <v>2.9414829659318638E-2</v>
       </c>
       <c r="E70" s="47" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="F70" s="315">
         <f>Normalized_FCF!C92</f>
-        <v>4.905845690344095</v>
+        <v>5.4180232091874609</v>
       </c>
     </row>
     <row r="72" spans="1:6">
       <c r="B72" s="210" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="C72" s="323" t="s">
+        <v>455</v>
+      </c>
+      <c r="D72" s="323" t="s">
         <v>456</v>
-      </c>
-      <c r="D72" s="323" t="s">
-        <v>457</v>
       </c>
     </row>
     <row r="73" spans="1:6">
       <c r="B73" s="47" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="C73" s="92">
         <f>Normalized_FCF!C120</f>
-        <v>340259.48035387928</v>
+        <v>0.21039827332068567</v>
       </c>
       <c r="D73" s="92">
         <f>Normalized_FCF!G120</f>
-        <v>448898.66666666669</v>
+        <v>0.3047216496244991</v>
       </c>
     </row>
     <row r="74" spans="1:6">
@@ -4916,11 +4914,11 @@
       </c>
       <c r="C74" s="322">
         <f>Normalized_FCF!C117</f>
-        <v>0.2310072554650987</v>
+        <v>0.21042753223383909</v>
       </c>
       <c r="D74" s="322">
         <f>Normalized_FCF!G117</f>
-        <v>0.25216103226985487</v>
+        <v>0.24793921890168877</v>
       </c>
     </row>
     <row r="75" spans="1:6">
@@ -4930,11 +4928,11 @@
       </c>
       <c r="C75" s="324">
         <f>Normalized_FCF!C118</f>
-        <v>1104703.875</v>
+        <v>0.51682300464832642</v>
       </c>
       <c r="D75" s="324">
         <f>Normalized_FCF!G118</f>
-        <v>1335154.75</v>
+        <v>0.63527287089914697</v>
       </c>
     </row>
     <row r="76" spans="1:6">
@@ -4944,11 +4942,11 @@
       </c>
       <c r="C76" s="324">
         <f>Normalized_FCF!C119</f>
-        <v>1.3333333333333333</v>
+        <v>1.9346293526540752</v>
       </c>
       <c r="D76" s="324">
         <f>Normalized_FCF!G119</f>
-        <v>1.3333333333333333</v>
+        <v>1.9346293526540752</v>
       </c>
     </row>
     <row r="78" spans="1:6" ht="13.9">
@@ -4966,22 +4964,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.6" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="356" t="s">
+      <c r="B80" s="358" t="s">
         <v>365</v>
       </c>
-      <c r="C80" s="356"/>
-      <c r="D80" s="356"/>
-      <c r="E80" s="356"/>
-      <c r="F80" s="356"/>
+      <c r="C80" s="358"/>
+      <c r="D80" s="358"/>
+      <c r="E80" s="358"/>
+      <c r="F80" s="358"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="358" t="s">
+      <c r="B81" s="361" t="s">
         <v>252</v>
       </c>
-      <c r="C81" s="358"/>
-      <c r="D81" s="358"/>
-      <c r="E81" s="358"/>
-      <c r="F81" s="358"/>
+      <c r="C81" s="361"/>
+      <c r="D81" s="361"/>
+      <c r="E81" s="361"/>
+      <c r="F81" s="361"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5025,22 +5023,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="356" t="s">
+      <c r="B89" s="358" t="s">
         <v>366</v>
       </c>
-      <c r="C89" s="356"/>
-      <c r="D89" s="356"/>
-      <c r="E89" s="356"/>
-      <c r="F89" s="356"/>
+      <c r="C89" s="358"/>
+      <c r="D89" s="358"/>
+      <c r="E89" s="358"/>
+      <c r="F89" s="358"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="356" t="s">
+      <c r="B90" s="358" t="s">
         <v>367</v>
       </c>
-      <c r="C90" s="356"/>
-      <c r="D90" s="356"/>
-      <c r="E90" s="356"/>
-      <c r="F90" s="356"/>
+      <c r="C90" s="358"/>
+      <c r="D90" s="358"/>
+      <c r="E90" s="358"/>
+      <c r="F90" s="358"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5056,7 +5054,7 @@
       </c>
       <c r="C93" s="223">
         <f>DCF!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>33.472337974919526</v>
+        <v>30.308125059624196</v>
       </c>
       <c r="D93" s="1" t="str">
         <f>Market_currency</f>
@@ -5077,13 +5075,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="356" t="s">
+      <c r="B97" s="358" t="s">
         <v>368</v>
       </c>
-      <c r="C97" s="356"/>
-      <c r="D97" s="356"/>
-      <c r="E97" s="356"/>
-      <c r="F97" s="356"/>
+      <c r="C97" s="358"/>
+      <c r="D97" s="358"/>
+      <c r="E97" s="358"/>
+      <c r="F97" s="358"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5096,13 +5094,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="356" t="s">
+      <c r="B101" s="358" t="s">
         <v>346</v>
       </c>
-      <c r="C101" s="356"/>
-      <c r="D101" s="356"/>
-      <c r="E101" s="356"/>
-      <c r="F101" s="356"/>
+      <c r="C101" s="358"/>
+      <c r="D101" s="358"/>
+      <c r="E101" s="358"/>
+      <c r="F101" s="358"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5110,7 +5108,7 @@
       </c>
       <c r="C102" s="349">
         <f>DCF!C7</f>
-        <v>0</v>
+        <v>866500</v>
       </c>
       <c r="D102" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5123,7 +5121,7 @@
       </c>
       <c r="C103" s="223">
         <f>C102*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>0</v>
+        <v>3.0307574885963238</v>
       </c>
       <c r="D103" s="1" t="str">
         <f>Market_currency</f>
@@ -5136,7 +5134,7 @@
       </c>
       <c r="C104" s="325">
         <f>IF(BS!G31/BS!G27&gt;300%,"nm",BS!G31/BS!G27)</f>
-        <v>0</v>
+        <v>0.19606600851240996</v>
       </c>
     </row>
     <row r="105" spans="2:6">
@@ -5145,7 +5143,7 @@
       </c>
       <c r="C105" s="326">
         <f>IF(BS!C50&gt;30,"nm",BS!C50)</f>
-        <v>0</v>
+        <v>0.84886197155458731</v>
       </c>
     </row>
     <row r="107" spans="2:6">
@@ -5159,7 +5157,7 @@
       </c>
       <c r="C108" s="349">
         <f>BS!C66</f>
-        <v>2</v>
+        <v>1011563</v>
       </c>
       <c r="D108" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5172,7 +5170,7 @@
       </c>
       <c r="C109" s="349">
         <f>DCF!C8</f>
-        <v>0</v>
+        <v>415406.42282180313</v>
       </c>
       <c r="D109" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5185,7 +5183,7 @@
       </c>
       <c r="C110" s="223">
         <f>C109*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>0</v>
+        <v>1.452967255370099</v>
       </c>
       <c r="D110" s="1" t="str">
         <f>Market_currency</f>
@@ -5203,7 +5201,7 @@
       </c>
       <c r="C113" s="349">
         <f>DCF!C9</f>
-        <v>0</v>
+        <v>3762.4</v>
       </c>
       <c r="D113" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5216,7 +5214,7 @@
       </c>
       <c r="C114" s="223">
         <f>C113*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>0</v>
+        <v>1.315974838441409E-2</v>
       </c>
       <c r="D114" s="1" t="str">
         <f>Market_currency</f>
@@ -5224,21 +5222,21 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="356" t="s">
+      <c r="B116" s="358" t="s">
         <v>369</v>
       </c>
-      <c r="C116" s="356"/>
-      <c r="D116" s="356"/>
-      <c r="E116" s="356"/>
-      <c r="F116" s="356"/>
+      <c r="C116" s="358"/>
+      <c r="D116" s="358"/>
+      <c r="E116" s="358"/>
+      <c r="F116" s="358"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="C118" s="223">
         <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
-        <v>164.21012499999998</v>
+        <v>28.743494574782385</v>
       </c>
       <c r="D118" s="1" t="str">
         <f>Market_currency</f>
@@ -5251,7 +5249,7 @@
       </c>
       <c r="C119" s="223">
         <f>BS!D47</f>
-        <v>3.1479352583605787E-6</v>
+        <v>-5.8165293881095375</v>
       </c>
       <c r="D119" s="1" t="str">
         <f>Market_currency</f>
@@ -5269,13 +5267,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B123" s="357" t="s">
+      <c r="B123" s="359" t="s">
         <v>370</v>
       </c>
-      <c r="C123" s="357"/>
-      <c r="D123" s="357"/>
-      <c r="E123" s="357"/>
-      <c r="F123" s="357"/>
+      <c r="C123" s="359"/>
+      <c r="D123" s="359"/>
+      <c r="E123" s="359"/>
+      <c r="F123" s="359"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5301,7 +5299,7 @@
       </c>
       <c r="C126" s="229">
         <f>DCF!C74</f>
-        <v>0.04</v>
+        <v>0.08</v>
       </c>
       <c r="D126" s="230">
         <f>DCF!D74</f>
@@ -5309,7 +5307,7 @@
       </c>
       <c r="E126" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E74,DDM!E69),2)&amp;" "&amp;Market_currency</f>
-        <v>203.8 HKD</v>
+        <v>37.84 HKD</v>
       </c>
       <c r="F126" s="232">
         <f>DCF!F74</f>
@@ -5323,7 +5321,7 @@
       </c>
       <c r="C127" s="219">
         <f>DCF!C75</f>
-        <v>0.03</v>
+        <v>0.05</v>
       </c>
       <c r="D127" s="220">
         <f>DCF!D75</f>
@@ -5331,7 +5329,7 @@
       </c>
       <c r="E127" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E75,DDM!E70),2)&amp;" "&amp;Market_currency</f>
-        <v>184.2 HKD</v>
+        <v>31.24 HKD</v>
       </c>
       <c r="F127" s="221">
         <f>DCF!F75</f>
@@ -5345,7 +5343,7 @@
       </c>
       <c r="C128" s="219">
         <f>DCF!C76</f>
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="D128" s="220">
         <f>DCF!D76</f>
@@ -5353,7 +5351,7 @@
       </c>
       <c r="E128" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E76,DDM!E71),2)&amp;" "&amp;Market_currency</f>
-        <v>181.37 HKD</v>
+        <v>30.22 HKD</v>
       </c>
       <c r="F128" s="221">
         <f>DCF!F76</f>
@@ -5375,7 +5373,7 @@
       </c>
       <c r="E129" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E77,DDM!E72),2)&amp;" "&amp;Market_currency</f>
-        <v>178.59 HKD</v>
+        <v>29.23 HKD</v>
       </c>
       <c r="F129" s="221">
         <f>DCF!F77</f>
@@ -5397,7 +5395,7 @@
       </c>
       <c r="E130" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E78,DDM!E73),2)&amp;" "&amp;Market_currency</f>
-        <v>180.87 HKD</v>
+        <v>28.74 HKD</v>
       </c>
       <c r="F130" s="221">
         <f>DCF!F78</f>
@@ -5410,7 +5408,7 @@
       </c>
       <c r="C132" s="217">
         <f>Scenarios!C60</f>
-        <v>182.47610718562294</v>
+        <v>30.533856751256884</v>
       </c>
       <c r="D132" s="212" t="str">
         <f>Market_currency</f>
@@ -5418,13 +5416,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="361" t="s">
+      <c r="B134" s="362" t="s">
         <v>373</v>
       </c>
-      <c r="C134" s="361"/>
-      <c r="D134" s="361"/>
-      <c r="E134" s="361"/>
-      <c r="F134" s="361"/>
+      <c r="C134" s="362"/>
+      <c r="D134" s="362"/>
+      <c r="E134" s="362"/>
+      <c r="F134" s="362"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5437,22 +5435,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="359" t="s">
+      <c r="B138" s="363" t="s">
         <v>371</v>
       </c>
-      <c r="C138" s="359"/>
-      <c r="D138" s="359"/>
-      <c r="E138" s="359"/>
-      <c r="F138" s="359"/>
+      <c r="C138" s="363"/>
+      <c r="D138" s="363"/>
+      <c r="E138" s="363"/>
+      <c r="F138" s="363"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="356" t="s">
+      <c r="B139" s="358" t="s">
         <v>372</v>
       </c>
-      <c r="C139" s="356"/>
-      <c r="D139" s="356"/>
-      <c r="E139" s="356"/>
-      <c r="F139" s="356"/>
+      <c r="C139" s="358"/>
+      <c r="D139" s="358"/>
+      <c r="E139" s="358"/>
+      <c r="F139" s="358"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5529,7 +5527,7 @@
       </c>
       <c r="C148" s="216">
         <f>Scenarios!C82</f>
-        <v>66.500039061815954</v>
+        <v>11.127498816055718</v>
       </c>
     </row>
     <row r="149" spans="2:4">
@@ -5538,7 +5536,7 @@
       </c>
       <c r="C149" s="215">
         <f>Scenarios!C83</f>
-        <v>68.832257720708085</v>
+        <v>13.459717474947846</v>
       </c>
       <c r="D149" s="300" t="str">
         <f>IF($D$11="","",C149*$E$25)</f>
@@ -5564,7 +5562,7 @@
       </c>
       <c r="C151" s="92">
         <f>Scenarios!F83</f>
-        <v>0.622787559520388</v>
+        <v>0.55918711531933174</v>
       </c>
     </row>
     <row r="153" spans="2:4">
@@ -5598,7 +5596,7 @@
       </c>
       <c r="C156" s="216">
         <f>Scenarios!C92</f>
-        <v>100.49084900587657</v>
+        <v>16.815205210599611</v>
       </c>
     </row>
     <row r="157" spans="2:4">
@@ -5607,7 +5605,7 @@
       </c>
       <c r="C157" s="215">
         <f>Scenarios!C93</f>
-        <v>103.4884509637497</v>
+        <v>19.812807168472737</v>
       </c>
       <c r="D157" s="300" t="str">
         <f>IF($D$11="","",C157*$E$25)</f>
@@ -5633,7 +5631,7 @@
       </c>
       <c r="C159" s="92">
         <f>Scenarios!F93</f>
-        <v>0.4328657457686963</v>
+        <v>0.35112005896021736</v>
       </c>
     </row>
     <row r="161" spans="2:4">
@@ -5667,7 +5665,7 @@
       </c>
       <c r="C164" s="216">
         <f>Scenarios!C98</f>
-        <v>144.85541709979972</v>
+        <v>24.238759931839088</v>
       </c>
     </row>
     <row r="165" spans="2:4">
@@ -5676,7 +5674,7 @@
       </c>
       <c r="C165" s="215">
         <f>Scenarios!C99</f>
-        <v>148.63808005768217</v>
+        <v>28.021422889721528</v>
       </c>
       <c r="D165" s="300" t="str">
         <f>IF($D$11="","",C165*$E$25)</f>
@@ -5702,7 +5700,7 @@
       </c>
       <c r="C167" s="92">
         <f>Scenarios!F99</f>
-        <v>0.18543812474867838</v>
+        <v>8.2283541250711356E-2</v>
       </c>
     </row>
     <row r="169" spans="2:4">
@@ -5736,7 +5734,7 @@
       </c>
       <c r="C172" s="216">
         <f>Scenarios!C104</f>
-        <v>129.88288879260921</v>
+        <v>21.733396125108815</v>
       </c>
     </row>
     <row r="173" spans="2:4">
@@ -5745,7 +5743,7 @@
       </c>
       <c r="C173" s="215">
         <f>Scenarios!C105</f>
-        <v>133.40829672810483</v>
+        <v>25.258804060604444</v>
       </c>
       <c r="D173" s="300" t="str">
         <f>IF($D$11="","",C173*$E$25)</f>
@@ -5771,7 +5769,7 @@
       </c>
       <c r="C175" s="92">
         <f>Scenarios!F105</f>
-        <v>-5.5450634831928003</v>
+        <v>0.15545280182445731</v>
       </c>
     </row>
     <row r="177" spans="1:6" ht="13.9">
@@ -5785,13 +5783,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="363" t="s">
+      <c r="B179" s="357" t="s">
         <v>379</v>
       </c>
-      <c r="C179" s="356"/>
-      <c r="D179" s="356"/>
-      <c r="E179" s="356"/>
-      <c r="F179" s="356"/>
+      <c r="C179" s="358"/>
+      <c r="D179" s="358"/>
+      <c r="E179" s="358"/>
+      <c r="F179" s="358"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5828,13 +5826,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="357" t="s">
+      <c r="B188" s="359" t="s">
         <v>384</v>
       </c>
-      <c r="C188" s="357"/>
-      <c r="D188" s="357"/>
-      <c r="E188" s="357"/>
-      <c r="F188" s="357"/>
+      <c r="C188" s="359"/>
+      <c r="D188" s="359"/>
+      <c r="E188" s="359"/>
+      <c r="F188" s="359"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5842,22 +5840,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="362" t="s">
+      <c r="B191" s="356" t="s">
         <v>385</v>
       </c>
-      <c r="C191" s="362"/>
-      <c r="D191" s="362"/>
-      <c r="E191" s="362"/>
-      <c r="F191" s="362"/>
+      <c r="C191" s="356"/>
+      <c r="D191" s="356"/>
+      <c r="E191" s="356"/>
+      <c r="F191" s="356"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="362" t="s">
+      <c r="B192" s="356" t="s">
         <v>386</v>
       </c>
-      <c r="C192" s="362"/>
-      <c r="D192" s="362"/>
-      <c r="E192" s="362"/>
-      <c r="F192" s="362"/>
+      <c r="C192" s="356"/>
+      <c r="D192" s="356"/>
+      <c r="E192" s="356"/>
+      <c r="F192" s="356"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5881,17 +5879,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5908,6 +5895,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -6513,7 +6511,7 @@
       </c>
       <c r="C28" s="333">
         <f>BS!C4</f>
-        <v>0</v>
+        <v>423874</v>
       </c>
       <c r="D28" s="351">
         <v>405151</v>
@@ -6550,7 +6548,7 @@
       </c>
       <c r="C29" s="333">
         <f>BS!C6</f>
-        <v>0</v>
+        <v>866160</v>
       </c>
       <c r="D29" s="351">
         <v>782978</v>
@@ -6587,7 +6585,7 @@
       </c>
       <c r="C30" s="334">
         <f>BS!C33+BS!C42</f>
-        <v>1</v>
+        <v>4130529</v>
       </c>
       <c r="D30" s="353">
         <v>3738242</v>
@@ -6624,7 +6622,7 @@
       </c>
       <c r="C31" s="334">
         <f>BS!G27</f>
-        <v>3</v>
+        <v>4419430</v>
       </c>
       <c r="D31" s="353">
         <v>3876809</v>
@@ -6661,7 +6659,7 @@
       </c>
       <c r="C32" s="333">
         <f>BS!G28</f>
-        <v>0</v>
+        <v>20065</v>
       </c>
       <c r="D32" s="351">
         <v>23014</v>
@@ -8186,7 +8184,7 @@
       </c>
       <c r="C76" s="76">
         <f>IF(C$4="","",C79+C80)</f>
-        <v>4</v>
+        <v>8549959</v>
       </c>
       <c r="D76" s="349">
         <f t="shared" ref="D76:M76" si="39">IF(D$4="","",D79+D80)</f>
@@ -8235,7 +8233,7 @@
       </c>
       <c r="C77" s="318">
         <f t="shared" ref="C77:H78" si="40">IF(C$4="","",C28)</f>
-        <v>0</v>
+        <v>423874</v>
       </c>
       <c r="D77" s="346">
         <f t="shared" si="40"/>
@@ -8269,7 +8267,7 @@
       </c>
       <c r="C78" s="318">
         <f t="shared" si="40"/>
-        <v>0</v>
+        <v>866160</v>
       </c>
       <c r="D78" s="346">
         <f t="shared" si="40"/>
@@ -8303,7 +8301,7 @@
       </c>
       <c r="C79" s="317">
         <f t="shared" ref="C79:M79" si="41">IF(C$4="","",C30)</f>
-        <v>1</v>
+        <v>4130529</v>
       </c>
       <c r="D79" s="333">
         <f t="shared" si="41"/>
@@ -8352,7 +8350,7 @@
       </c>
       <c r="C80" s="317">
         <f t="shared" ref="C80:M80" si="42">IF(C$4="","",C31)</f>
-        <v>3</v>
+        <v>4419430</v>
       </c>
       <c r="D80" s="333">
         <f t="shared" si="42"/>
@@ -8490,7 +8488,8 @@
         <v>24</v>
       </c>
       <c r="C4" s="19">
-        <v>0</v>
+        <f>423733+141</f>
+        <v>423874</v>
       </c>
       <c r="D4" s="261">
         <v>0.6</v>
@@ -8500,7 +8499,7 @@
         <v>77</v>
       </c>
       <c r="G4" s="19">
-        <v>1</v>
+        <v>1011563</v>
       </c>
       <c r="H4" s="261">
         <v>0.9</v>
@@ -8511,7 +8510,7 @@
         <v>33</v>
       </c>
       <c r="C5" s="19">
-        <v>0</v>
+        <v>12487</v>
       </c>
       <c r="D5" s="261">
         <v>0.6</v>
@@ -8532,7 +8531,7 @@
         <v>10</v>
       </c>
       <c r="C6" s="19">
-        <v>0</v>
+        <v>866160</v>
       </c>
       <c r="D6" s="261">
         <v>0.5</v>
@@ -8595,7 +8594,7 @@
         <v>25</v>
       </c>
       <c r="C9" s="19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D9" s="261">
         <v>0.1</v>
@@ -8628,7 +8627,7 @@
         <v>12</v>
       </c>
       <c r="C11" s="19">
-        <v>0</v>
+        <v>245324</v>
       </c>
       <c r="D11" s="261">
         <v>0.05</v>
@@ -8641,22 +8640,22 @@
       </c>
       <c r="C12" s="81">
         <f>SUM(C4:C11)</f>
-        <v>1</v>
+        <v>1547845</v>
       </c>
       <c r="D12" s="20">
         <f>C4*D4+C5*D5+C9*D9+C6*D6+C8*D8+C7*D7+C10*D10+C11*D11</f>
-        <v>0.1</v>
+        <v>707162.79999999993</v>
       </c>
       <c r="F12" s="80" t="s">
         <v>70</v>
       </c>
       <c r="G12" s="81">
         <f>SUM(G4:G9)</f>
-        <v>1</v>
+        <v>1011563</v>
       </c>
       <c r="H12" s="20">
         <f>G4*H4+G5*H5+G6*H6+G7*H7+G8*H8+G9*H9</f>
-        <v>0.9</v>
+        <v>910406.70000000007</v>
       </c>
     </row>
     <row r="13" spans="2:8" ht="15" customHeight="1">
@@ -8686,10 +8685,10 @@
     </row>
     <row r="15" spans="2:8" ht="15" customHeight="1">
       <c r="B15" s="4" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="C15" s="19">
-        <v>0</v>
+        <v>369</v>
       </c>
       <c r="D15" s="261">
         <v>0.4</v>
@@ -8698,7 +8697,7 @@
         <v>78</v>
       </c>
       <c r="G15" s="19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H15" s="261">
         <v>0.8</v>
@@ -8709,7 +8708,7 @@
         <v>34</v>
       </c>
       <c r="C16" s="19">
-        <v>0</v>
+        <v>2571</v>
       </c>
       <c r="D16" s="261">
         <v>0.5</v>
@@ -8769,7 +8768,8 @@
         <v>26</v>
       </c>
       <c r="C19" s="19">
-        <v>1</v>
+        <f>2255055+2278955</f>
+        <v>4534010</v>
       </c>
       <c r="D19" s="261">
         <v>0.1</v>
@@ -8778,7 +8778,7 @@
         <v>182</v>
       </c>
       <c r="G19" s="19">
-        <v>0</v>
+        <v>37624</v>
       </c>
       <c r="H19" s="261">
         <v>0.1</v>
@@ -8809,7 +8809,7 @@
         <v>19</v>
       </c>
       <c r="C21" s="19">
-        <v>0</v>
+        <v>867920</v>
       </c>
       <c r="D21" s="261">
         <v>0.05</v>
@@ -8829,7 +8829,7 @@
         <v>20</v>
       </c>
       <c r="C22" s="19">
-        <v>0</v>
+        <v>408971</v>
       </c>
       <c r="D22" s="261">
         <v>0.9</v>
@@ -8841,7 +8841,7 @@
         <v>21</v>
       </c>
       <c r="C23" s="19">
-        <v>0</v>
+        <v>139086</v>
       </c>
       <c r="D23" s="261">
         <v>0</v>
@@ -8854,22 +8854,22 @@
       </c>
       <c r="C24" s="81">
         <f>SUM(C15:C23)</f>
-        <v>1</v>
+        <v>5952927</v>
       </c>
       <c r="D24" s="20">
         <f>C15*D15+C16*D16+C18*D18+C17*D17+C19*D19+C20*D20+C21*D21+C22*D22+C23*D23</f>
-        <v>0.1</v>
+        <v>866304</v>
       </c>
       <c r="F24" s="80" t="s">
         <v>71</v>
       </c>
       <c r="G24" s="81">
         <f>SUM(G15:G21)</f>
-        <v>1</v>
+        <v>37624</v>
       </c>
       <c r="H24" s="20">
         <f>G15*H15+G16*H16+G17*H17+G18*H18+G19*H19+G20*H20+G21*H21</f>
-        <v>0.8</v>
+        <v>3762.4</v>
       </c>
     </row>
     <row r="26" spans="2:8" ht="15" customHeight="1">
@@ -8894,18 +8894,18 @@
         <v>5</v>
       </c>
       <c r="C27" s="19">
-        <v>0</v>
+        <v>183247</v>
       </c>
       <c r="F27" s="187" t="s">
         <v>30</v>
       </c>
       <c r="G27" s="85">
         <f>G32-G30</f>
-        <v>3</v>
+        <v>4419430</v>
       </c>
       <c r="H27" s="188">
         <f>H32-G30</f>
-        <v>0.90000000000000013</v>
+        <v>-1642893.1</v>
       </c>
     </row>
     <row r="28" spans="2:8" ht="15" customHeight="1">
@@ -8913,13 +8913,13 @@
         <v>6</v>
       </c>
       <c r="C28" s="19">
-        <v>0</v>
+        <v>434135</v>
       </c>
       <c r="F28" s="189" t="s">
         <v>244</v>
       </c>
       <c r="G28" s="12">
-        <v>0</v>
+        <v>20065</v>
       </c>
       <c r="H28" s="188"/>
     </row>
@@ -8935,11 +8935,11 @@
       </c>
       <c r="G29" s="14">
         <f>G27-G28</f>
-        <v>3</v>
+        <v>4399365</v>
       </c>
       <c r="H29" s="188">
         <f>H27-G28</f>
-        <v>0.90000000000000013</v>
+        <v>-1662958.1</v>
       </c>
     </row>
     <row r="30" spans="2:8" ht="15" customHeight="1">
@@ -8947,14 +8947,14 @@
         <v>8</v>
       </c>
       <c r="C30" s="19">
-        <v>0</v>
+        <v>27778</v>
       </c>
       <c r="F30" s="187" t="s">
         <v>23</v>
       </c>
       <c r="G30" s="85">
         <f>C33+C42</f>
-        <v>1</v>
+        <v>4130529</v>
       </c>
       <c r="H30" s="188"/>
     </row>
@@ -8964,14 +8964,14 @@
       </c>
       <c r="C31" s="81">
         <f>SUM(C27:C30)</f>
-        <v>0</v>
+        <v>645160</v>
       </c>
       <c r="F31" s="190" t="s">
         <v>76</v>
       </c>
       <c r="G31" s="191">
         <f>C31+C40</f>
-        <v>0</v>
+        <v>866500</v>
       </c>
       <c r="H31" s="188"/>
     </row>
@@ -8981,18 +8981,18 @@
       </c>
       <c r="C32" s="21">
         <f>C33-C31</f>
-        <v>1</v>
+        <v>1038292</v>
       </c>
       <c r="F32" s="192" t="s">
         <v>74</v>
       </c>
       <c r="G32" s="193">
         <f>G35+G40</f>
-        <v>4</v>
+        <v>8549959</v>
       </c>
       <c r="H32" s="188">
         <f>H35+H40</f>
-        <v>1.9000000000000001</v>
+        <v>2487635.9</v>
       </c>
     </row>
     <row r="33" spans="2:8" ht="15" customHeight="1">
@@ -9000,7 +9000,7 @@
         <v>4</v>
       </c>
       <c r="C33" s="84">
-        <v>1</v>
+        <v>1683452</v>
       </c>
       <c r="F33" s="194"/>
       <c r="G33" s="2"/>
@@ -9031,11 +9031,11 @@
       </c>
       <c r="G35" s="193">
         <f>C12+C24</f>
-        <v>2</v>
+        <v>7500772</v>
       </c>
       <c r="H35" s="200">
         <f>D12+D24</f>
-        <v>0.2</v>
+        <v>1573466.7999999998</v>
       </c>
     </row>
     <row r="36" spans="2:8" ht="15" customHeight="1">
@@ -9043,14 +9043,14 @@
         <v>13</v>
       </c>
       <c r="C36" s="19">
-        <v>0</v>
+        <v>220941</v>
       </c>
       <c r="F36" s="190" t="s">
         <v>197</v>
       </c>
       <c r="G36" s="191">
         <f>C4+C15</f>
-        <v>0</v>
+        <v>424243</v>
       </c>
       <c r="H36" s="195"/>
     </row>
@@ -9066,7 +9066,7 @@
       </c>
       <c r="G37" s="191">
         <f>C6</f>
-        <v>0</v>
+        <v>866160</v>
       </c>
       <c r="H37" s="195"/>
     </row>
@@ -9091,18 +9091,18 @@
         <v>16</v>
       </c>
       <c r="C39" s="19">
-        <v>0</v>
+        <v>399</v>
       </c>
       <c r="F39" s="190" t="s">
         <v>79</v>
       </c>
       <c r="G39" s="191">
         <f>C7+C17+C19+C20</f>
-        <v>1</v>
+        <v>4534010</v>
       </c>
       <c r="H39" s="188">
         <f>C7*D7+C17*D17+C19*D19+C20*D20</f>
-        <v>0.1</v>
+        <v>453401</v>
       </c>
     </row>
     <row r="40" spans="2:8" ht="15" customHeight="1">
@@ -9111,18 +9111,18 @@
       </c>
       <c r="C40" s="81">
         <f>SUM(C36:C39)</f>
-        <v>0</v>
+        <v>221340</v>
       </c>
       <c r="F40" s="199" t="s">
         <v>138</v>
       </c>
       <c r="G40" s="193">
         <f>G12+G24</f>
-        <v>2</v>
+        <v>1049187</v>
       </c>
       <c r="H40" s="200">
         <f>H12+H24</f>
-        <v>1.7000000000000002</v>
+        <v>914169.10000000009</v>
       </c>
     </row>
     <row r="41" spans="2:8" ht="15" customHeight="1">
@@ -9131,18 +9131,18 @@
       </c>
       <c r="C41" s="21">
         <f>C42-C40</f>
-        <v>0</v>
+        <v>2225737</v>
       </c>
       <c r="F41" s="190" t="s">
         <v>191</v>
       </c>
       <c r="G41" s="191">
         <f>C70</f>
-        <v>2</v>
+        <v>1011563</v>
       </c>
       <c r="H41" s="200">
         <f>H40-H42</f>
-        <v>1.7000000000000002</v>
+        <v>910406.70000000007</v>
       </c>
     </row>
     <row r="42" spans="2:8" ht="15" customHeight="1">
@@ -9150,18 +9150,18 @@
         <v>22</v>
       </c>
       <c r="C42" s="84">
-        <v>0</v>
+        <v>2447077</v>
       </c>
       <c r="F42" s="201" t="s">
         <v>192</v>
       </c>
       <c r="G42" s="202">
         <f>C82</f>
-        <v>0</v>
+        <v>37624</v>
       </c>
       <c r="H42" s="203">
         <f>D82</f>
-        <v>0</v>
+        <v>3762.4</v>
       </c>
     </row>
     <row r="44" spans="2:8" ht="15" customHeight="1">
@@ -9195,11 +9195,11 @@
       </c>
       <c r="C46" s="76">
         <f>G29</f>
-        <v>3</v>
+        <v>4399365</v>
       </c>
       <c r="D46" s="76">
         <f>H29</f>
-        <v>0.90000000000000013</v>
+        <v>-1662958.1</v>
       </c>
       <c r="F46" s="253"/>
     </row>
@@ -9210,11 +9210,11 @@
       </c>
       <c r="C47" s="147">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>1.0493117527868593E-5</v>
+        <v>15.387661187326676</v>
       </c>
       <c r="D47" s="147">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>3.1479352583605787E-6</v>
+        <v>-5.8165293881095375</v>
       </c>
       <c r="F47" s="253"/>
     </row>
@@ -9240,11 +9240,11 @@
       </c>
       <c r="C50" s="95">
         <f>G31/Normalized_FCF!C8</f>
-        <v>0</v>
+        <v>0.84886197155458731</v>
       </c>
       <c r="D50" s="95">
         <f>G31/Normalized_FCF!G8</f>
-        <v>0</v>
+        <v>0.60272642411072641</v>
       </c>
       <c r="F50" s="253"/>
     </row>
@@ -9255,7 +9255,7 @@
       <c r="C51" s="181"/>
       <c r="D51" s="92">
         <f>G29/G32</f>
-        <v>0.75</v>
+        <v>0.51454808145863629</v>
       </c>
       <c r="F51" s="253"/>
     </row>
@@ -9280,11 +9280,11 @@
       </c>
       <c r="C54" s="92">
         <f>Normalized_FCF!C8/G35</f>
-        <v>510389.22053081891</v>
+        <v>0.13608978396645544</v>
       </c>
       <c r="D54" s="92">
         <f>Normalized_FCF!G8/G35</f>
-        <v>718817</v>
+        <v>0.19166480463610946</v>
       </c>
       <c r="F54" s="253"/>
     </row>
@@ -9335,7 +9335,7 @@
       <c r="C59" s="98"/>
       <c r="D59" s="92">
         <f>G39/G32</f>
-        <v>0.25</v>
+        <v>0.53029611019187339</v>
       </c>
       <c r="F59" s="253"/>
     </row>
@@ -9360,11 +9360,11 @@
       </c>
       <c r="C62" s="92">
         <f>IF(G28&lt;=0,0,G28/G29)</f>
-        <v>0</v>
+        <v>4.5608854914288765E-3</v>
       </c>
       <c r="D62" s="92">
         <f>G28/G29</f>
-        <v>0</v>
+        <v>4.5608854914288765E-3</v>
       </c>
       <c r="F62" s="253" t="s">
         <v>272</v>
@@ -9401,11 +9401,11 @@
       </c>
       <c r="C66" s="20">
         <f>G4+G5+G15</f>
-        <v>2</v>
+        <v>1011563</v>
       </c>
       <c r="D66" s="76">
         <f>C66-D75</f>
-        <v>0</v>
+        <v>415406.42282180313</v>
       </c>
       <c r="F66" s="5" t="s">
         <v>226</v>
@@ -9447,7 +9447,7 @@
       </c>
       <c r="C70" s="81">
         <f>SUM(C66:C69)</f>
-        <v>2</v>
+        <v>1011563</v>
       </c>
       <c r="F70" s="253"/>
     </row>
@@ -9472,11 +9472,11 @@
       </c>
       <c r="C73" s="349">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35-Normalized_FCF!G91)/12</f>
-        <v>-645813.26140906673</v>
+        <v>-645813.73893333331</v>
       </c>
       <c r="D73" s="349">
         <f>(Normalized_FCF!C25+Normalized_FCF!C35-Normalized_FCF!C91)/12</f>
-        <v>-596156.09965393029</v>
+        <v>-596156.57717819687</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>353</v>
@@ -9488,11 +9488,11 @@
       </c>
       <c r="C74" s="258">
         <f>-$C$66/C73</f>
-        <v>3.0968704415209792E-6</v>
+        <v>1.5663386190432573</v>
       </c>
       <c r="D74" s="258">
         <f>-$C$66/D73</f>
-        <v>3.3548260282181191E-6</v>
+        <v>1.6968075816391341</v>
       </c>
       <c r="F74" s="253" t="s">
         <v>320</v>
@@ -9505,7 +9505,7 @@
       <c r="C75" s="320"/>
       <c r="D75" s="321">
         <f>MAX(-D73*D76,G5)</f>
-        <v>2</v>
+        <v>596156.57717819687</v>
       </c>
       <c r="F75" s="253" t="s">
         <v>354</v>
@@ -9518,7 +9518,7 @@
       <c r="C76" s="260"/>
       <c r="D76" s="290">
         <f>IF(valuation_method="DCF",IF(D74&lt;=3,1,IF(D74&gt;18,6,2)),-C66/D73)</f>
-        <v>3.3548260282181191E-6</v>
+        <v>1</v>
       </c>
       <c r="F76" s="253" t="s">
         <v>325</v>
@@ -9559,11 +9559,11 @@
       </c>
       <c r="C80" s="20">
         <f>G19</f>
-        <v>0</v>
+        <v>37624</v>
       </c>
       <c r="D80" s="76">
         <f>G19*H19</f>
-        <v>0</v>
+        <v>3762.4</v>
       </c>
       <c r="F80" s="253"/>
     </row>
@@ -9587,11 +9587,11 @@
       </c>
       <c r="C82" s="81">
         <f>SUM(C79:C81)</f>
-        <v>0</v>
+        <v>37624</v>
       </c>
       <c r="D82" s="81">
         <f>SUM(D79:D81)</f>
-        <v>0</v>
+        <v>3762.4</v>
       </c>
       <c r="F82" s="253"/>
     </row>
@@ -9620,11 +9620,11 @@
       </c>
       <c r="C86" s="76">
         <f>-DCF!C7*Exchange_Rate</f>
-        <v>0</v>
+        <v>-7755174.9999999991</v>
       </c>
       <c r="D86" s="223">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>0</v>
+        <v>-3.0307574885963238</v>
       </c>
       <c r="E86" s="240" t="str">
         <f>Market_currency</f>
@@ -9637,11 +9637,11 @@
       </c>
       <c r="C87" s="76">
         <f>DCF!C8*Exchange_Rate</f>
-        <v>0</v>
+        <v>3717887.4842551379</v>
       </c>
       <c r="D87" s="223">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>0</v>
+        <v>1.452967255370099</v>
       </c>
       <c r="E87" s="240" t="str">
         <f>Market_currency</f>
@@ -9654,11 +9654,11 @@
       </c>
       <c r="C88" s="76">
         <f>DCF!C9*Exchange_Rate</f>
-        <v>0</v>
+        <v>33673.479999999996</v>
       </c>
       <c r="D88" s="223">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>0</v>
+        <v>1.3159748384414088E-2</v>
       </c>
       <c r="E88" s="240" t="str">
         <f>Market_currency</f>
@@ -9671,11 +9671,11 @@
       </c>
       <c r="C89" s="180">
         <f>SUM(C86:C88)</f>
-        <v>0</v>
+        <v>-4003614.0357448612</v>
       </c>
       <c r="D89" s="242">
         <f>SUM(D86:D88)</f>
-        <v>0</v>
+        <v>-1.5646304848418107</v>
       </c>
       <c r="E89" s="240" t="str">
         <f>Market_currency</f>
@@ -10255,7 +10255,7 @@
       </c>
       <c r="C12" s="328">
         <f>C50</f>
-        <v>0</v>
+        <v>-90938</v>
       </c>
       <c r="E12" s="268"/>
       <c r="G12" s="328">
@@ -10310,7 +10310,7 @@
       </c>
       <c r="C13" s="329">
         <f>SUM(C8:C12)</f>
-        <v>1020778.4410616378</v>
+        <v>929840.44106163783</v>
       </c>
       <c r="E13" s="268"/>
       <c r="G13" s="329">
@@ -10365,7 +10365,7 @@
       </c>
       <c r="C14" s="328">
         <f>-SUM(C8+C11,C12)*C43</f>
-        <v>-255194.61026540946</v>
+        <v>-232460.11026540946</v>
       </c>
       <c r="E14" s="268"/>
       <c r="G14" s="328">
@@ -10420,7 +10420,7 @@
       </c>
       <c r="C15" s="328">
         <f>-C4*C83</f>
-        <v>0</v>
+        <v>-4167.7471308175782</v>
       </c>
       <c r="D15" s="60"/>
       <c r="E15" s="275"/>
@@ -10477,7 +10477,7 @@
       </c>
       <c r="C16" s="332">
         <f>SUM(C13:C15)</f>
-        <v>765583.83079622837</v>
+        <v>693212.58366541076</v>
       </c>
       <c r="D16" s="61"/>
       <c r="E16" s="276"/>
@@ -10585,7 +10585,7 @@
       </c>
       <c r="C19" s="329">
         <f>C16+C17</f>
-        <v>765583.83079622837</v>
+        <v>693212.58366541076</v>
       </c>
       <c r="D19" s="27"/>
       <c r="E19" s="265"/>
@@ -11529,7 +11529,7 @@
       </c>
       <c r="C47" s="328">
         <f>-BS!G31*Normalized_FCF!C54</f>
-        <v>0</v>
+        <v>-90938</v>
       </c>
       <c r="E47" s="268"/>
       <c r="G47" s="328">
@@ -11696,7 +11696,7 @@
       </c>
       <c r="C50" s="329">
         <f>C47+C48</f>
-        <v>0</v>
+        <v>-90938</v>
       </c>
       <c r="E50" s="268"/>
       <c r="G50" s="329">
@@ -11771,7 +11771,7 @@
       </c>
       <c r="G53" s="6">
         <f>IF(Normalized_FCF!G4="","",Normalized_FCF!G49/BS!$C$66)</f>
-        <v>55.5</v>
+        <v>1.0973117838434185E-4</v>
       </c>
       <c r="H53" s="169"/>
       <c r="I53" s="169"/>
@@ -11791,14 +11791,14 @@
       </c>
       <c r="C54" s="82">
         <f>G54</f>
-        <v>0</v>
+        <v>0.10494864396999423</v>
       </c>
       <c r="E54" s="265" t="s">
         <v>338</v>
       </c>
       <c r="G54" s="23">
         <f>IFERROR(ABS(Normalized_FCF!G47/BS!$G$31),0)</f>
-        <v>0</v>
+        <v>0.10494864396999423</v>
       </c>
       <c r="H54" s="169"/>
       <c r="I54" s="169"/>
@@ -11816,9 +11816,9 @@
       <c r="B55" s="26" t="s">
         <v>90</v>
       </c>
-      <c r="C55" s="42" t="e">
+      <c r="C55" s="42">
         <f>-C8/C47</f>
-        <v>#DIV/0!</v>
+        <v>11.224993303807405</v>
       </c>
       <c r="E55" s="268"/>
       <c r="G55" s="42">
@@ -12782,7 +12782,7 @@
       </c>
       <c r="C80" s="77">
         <f>ABS(C12/C$4)</f>
-        <v>0</v>
+        <v>2.0579723231259599E-2</v>
       </c>
       <c r="D80" s="27"/>
       <c r="E80" s="265"/>
@@ -12839,7 +12839,7 @@
       </c>
       <c r="C81" s="78">
         <f>C13/C4</f>
-        <v>0.2310072554650987</v>
+        <v>0.21042753223383909</v>
       </c>
       <c r="D81" s="27"/>
       <c r="E81" s="265"/>
@@ -12896,7 +12896,7 @@
       </c>
       <c r="C82" s="77">
         <f>ABS(C14/C$4)</f>
-        <v>5.7751813866274676E-2</v>
+        <v>5.2606883058459772E-2</v>
       </c>
       <c r="D82" s="27"/>
       <c r="E82" s="265"/>
@@ -12954,7 +12954,7 @@
       </c>
       <c r="C83" s="264">
         <f>MIN(BS!C62,MAX(G83:K83))</f>
-        <v>0</v>
+        <v>9.4318197508304617E-4</v>
       </c>
       <c r="D83" s="27"/>
       <c r="E83" s="265"/>
@@ -13011,7 +13011,7 @@
       </c>
       <c r="C84" s="78">
         <f>ABS(C16/C$4)</f>
-        <v>0.17325544159882403</v>
+        <v>0.15687746720029627</v>
       </c>
       <c r="D84" s="27"/>
       <c r="E84" s="265"/>
@@ -13118,7 +13118,7 @@
       </c>
       <c r="C87" s="78">
         <f>ABS(C19/C$4)</f>
-        <v>0.17325544159882403</v>
+        <v>0.15687746720029627</v>
       </c>
       <c r="D87" s="75"/>
       <c r="E87" s="265"/>
@@ -13243,20 +13243,20 @@
       </c>
       <c r="C91" s="74">
         <f>C90*Common_Shares/scaling_factor</f>
-        <v>3755836.1369088003</v>
+        <v>3755841.8671999997</v>
       </c>
       <c r="E91" s="268"/>
       <c r="G91" s="74">
         <f t="shared" ref="G91:Q91" si="37">IF(G$4="","",G90*Common_Shares/scaling_factor)</f>
-        <v>3755836.1369088003</v>
+        <v>3755841.8671999997</v>
       </c>
       <c r="H91" s="74">
         <f t="shared" si="37"/>
-        <v>3137497.2607104001</v>
+        <v>3137502.0476000002</v>
       </c>
       <c r="I91" s="74">
         <f t="shared" si="37"/>
-        <v>2519158.3845119998</v>
+        <v>2519162.2280000001</v>
       </c>
       <c r="J91" s="74">
         <f t="shared" si="37"/>
@@ -13298,20 +13298,20 @@
       </c>
       <c r="C92" s="23">
         <f>C90/(C19*scaling_factor/Common_Shares)</f>
-        <v>4.905845690344095</v>
+        <v>5.4180232091874609</v>
       </c>
       <c r="E92" s="268"/>
       <c r="G92" s="170">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",G90/(G19*scaling_factor/Common_Shares))</f>
-        <v>3.7675910208939891</v>
+        <v>3.767596769119653</v>
       </c>
       <c r="H92" s="170">
         <f t="shared" si="38"/>
-        <v>3.82148591768774</v>
+        <v>3.8214917481410211</v>
       </c>
       <c r="I92" s="170">
         <f t="shared" si="38"/>
-        <v>3.7495957188411659</v>
+        <v>3.7496014396113404</v>
       </c>
       <c r="J92" s="170">
         <f t="shared" si="38"/>
@@ -13490,7 +13490,7 @@
       </c>
       <c r="C97" s="77">
         <f>C13/G13-1</f>
-        <v>-0.242012717746516</v>
+        <v>-0.30953946468866189</v>
       </c>
       <c r="D97" s="27"/>
       <c r="E97" s="265"/>
@@ -13583,14 +13583,14 @@
       </c>
       <c r="C101" s="344">
         <f>BS!G32</f>
-        <v>4</v>
+        <v>8549959</v>
       </c>
       <c r="D101" s="26"/>
       <c r="E101" s="269"/>
       <c r="F101" s="26"/>
       <c r="G101" s="333">
         <f t="shared" ref="G101:Q101" si="42">IF(G$4="","",G105+G104)</f>
-        <v>4</v>
+        <v>8549959</v>
       </c>
       <c r="H101" s="333">
         <f t="shared" si="42"/>
@@ -13640,7 +13640,7 @@
       </c>
       <c r="C102" s="345">
         <f>BS!C4</f>
-        <v>0</v>
+        <v>423874</v>
       </c>
       <c r="D102" s="89"/>
       <c r="E102" s="270"/>
@@ -13697,7 +13697,7 @@
       </c>
       <c r="C103" s="345">
         <f>BS!C6+BS!C7</f>
-        <v>0</v>
+        <v>866160</v>
       </c>
       <c r="D103" s="89"/>
       <c r="E103" s="270"/>
@@ -13754,14 +13754,14 @@
       </c>
       <c r="C104" s="344">
         <f>BS!G30</f>
-        <v>1</v>
+        <v>4130529</v>
       </c>
       <c r="D104" s="26"/>
       <c r="E104" s="269"/>
       <c r="F104" s="26"/>
       <c r="G104" s="333">
         <f>Data!C79</f>
-        <v>1</v>
+        <v>4130529</v>
       </c>
       <c r="H104" s="333">
         <f>Data!D79</f>
@@ -13811,14 +13811,14 @@
       </c>
       <c r="C105" s="344">
         <f>BS!G27</f>
-        <v>3</v>
+        <v>4419430</v>
       </c>
       <c r="D105" s="26"/>
       <c r="E105" s="269"/>
       <c r="F105" s="26"/>
       <c r="G105" s="333">
         <f>Data!C80</f>
-        <v>3</v>
+        <v>4419430</v>
       </c>
       <c r="H105" s="333">
         <f>Data!D80</f>
@@ -13895,7 +13895,7 @@
       </c>
       <c r="C108" s="94">
         <f>C102/C$4</f>
-        <v>0</v>
+        <v>9.5924801567297838E-2</v>
       </c>
       <c r="D108" s="26"/>
       <c r="E108" s="269"/>
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C109" s="94">
         <f>C103/C$4</f>
-        <v>0</v>
+        <v>0.19601633062072857</v>
       </c>
       <c r="D109" s="26"/>
       <c r="E109" s="269"/>
@@ -14209,24 +14209,24 @@
       </c>
       <c r="C117" s="23">
         <f>IF(valuation_method="DDM",C13/(C4+C12),C81)</f>
-        <v>0.2310072554650987</v>
+        <v>0.21042753223383909</v>
       </c>
       <c r="E117" s="268"/>
       <c r="G117" s="23">
         <f t="shared" ref="G117:Q117" si="45">IF(G4="","",IF(valuation_method="DDM",G13/(G4+G12),G81))</f>
-        <v>0.25216103226985487</v>
+        <v>0.24793921890168877</v>
       </c>
       <c r="H117" s="23">
         <f t="shared" si="45"/>
-        <v>0.2419239983130391</v>
+        <v>0.23727348298740841</v>
       </c>
       <c r="I117" s="23">
         <f t="shared" si="45"/>
-        <v>0.22188241341948164</v>
+        <v>0.21844827758593025</v>
       </c>
       <c r="J117" s="23">
         <f t="shared" si="45"/>
-        <v>0.15014539970836946</v>
+        <v>0.14706749642708541</v>
       </c>
       <c r="K117" s="23">
         <f t="shared" si="45"/>
@@ -14263,24 +14263,24 @@
       </c>
       <c r="C118" s="42">
         <f>IF(valuation_method="DDM",(C4+C12)/C101,C4/C101)</f>
-        <v>1104703.875</v>
+        <v>0.51682300464832642</v>
       </c>
       <c r="E118" s="268"/>
       <c r="G118" s="42">
         <f t="shared" ref="G118:Q118" si="46">IF(G4="","",IF(valuation_method="DDM",(G4+G12)/G101,G4/G101))</f>
-        <v>1335154.75</v>
+        <v>0.63527287089914697</v>
       </c>
       <c r="H118" s="42">
         <f t="shared" si="46"/>
-        <v>0.60873590997617744</v>
+        <v>0.6206670185137303</v>
       </c>
       <c r="I118" s="42">
         <f t="shared" si="46"/>
-        <v>0.56057136908616889</v>
+        <v>0.56938388181053456</v>
       </c>
       <c r="J118" s="42">
         <f t="shared" si="46"/>
-        <v>0.46682366215544135</v>
+        <v>0.47659358492176546</v>
       </c>
       <c r="K118" s="42">
         <f t="shared" si="46"/>
@@ -14317,14 +14317,14 @@
       </c>
       <c r="C119" s="15">
         <f>C101/C105</f>
-        <v>1.3333333333333333</v>
+        <v>1.9346293526540752</v>
       </c>
       <c r="D119" s="11"/>
       <c r="E119" s="272"/>
       <c r="F119" s="11"/>
       <c r="G119" s="15">
         <f t="shared" ref="G119:Q119" si="47">IF(G$4="","",G101/G105)</f>
-        <v>1.3333333333333333</v>
+        <v>1.9346293526540752</v>
       </c>
       <c r="H119" s="15">
         <f t="shared" si="47"/>
@@ -14374,14 +14374,14 @@
       </c>
       <c r="C120" s="102">
         <f>C13/C105</f>
-        <v>340259.48035387928</v>
+        <v>0.21039827332068567</v>
       </c>
       <c r="D120" s="103"/>
       <c r="E120" s="271"/>
       <c r="F120" s="103"/>
       <c r="G120" s="102">
         <f>IF(G$4="","",G13/G105)</f>
-        <v>448898.66666666669</v>
+        <v>0.3047216496244991</v>
       </c>
       <c r="H120" s="102">
         <f t="shared" ref="H120:Q120" si="48">IF(H$4="","",H13/H105)</f>
@@ -14495,38 +14495,38 @@
       </c>
       <c r="C124" s="177">
         <f>C16*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>2.6777870379935629</v>
+        <v>2.4246500047699358</v>
       </c>
       <c r="D124" s="27"/>
       <c r="E124" s="265"/>
       <c r="F124" s="27"/>
       <c r="G124" s="177">
         <f t="shared" ref="G124:Q124" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>3.4867930003938814</v>
+        <v>3.4867876805907714</v>
       </c>
       <c r="H124" s="177">
         <f t="shared" si="49"/>
-        <v>2.8716689623810114</v>
+        <v>2.8716645810731802</v>
       </c>
       <c r="I124" s="177">
         <f t="shared" si="49"/>
-        <v>2.3499266749544865</v>
+        <v>2.3499230896693168</v>
       </c>
       <c r="J124" s="177">
         <f t="shared" si="49"/>
-        <v>1.260454263682631</v>
+        <v>1.260452340606466</v>
       </c>
       <c r="K124" s="177">
         <f t="shared" si="49"/>
-        <v>6.0888832803664208</v>
+        <v>6.0888739905519094</v>
       </c>
       <c r="L124" s="177">
         <f t="shared" si="49"/>
-        <v>8.1868702034767811</v>
+        <v>8.1868577127617996</v>
       </c>
       <c r="M124" s="177">
         <f t="shared" si="49"/>
-        <v>7.5742785044939707</v>
+        <v>7.5742669484106759</v>
       </c>
       <c r="N124" s="177" t="str">
         <f t="shared" si="49"/>
@@ -14552,38 +14552,38 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>5.3663066893658573E-2</v>
+        <v>4.8590180456311333E-2</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="265"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>6.9875611230338308E-2</v>
+        <v>6.9875504621057544E-2</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>5.7548476200020272E-2</v>
+        <v>5.7548388398260125E-2</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>4.7092718936963658E-2</v>
+        <v>4.7092647087561459E-2</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>2.5259604482617857E-2</v>
+        <v>2.5259565944017355E-2</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>0.12202170902537918</v>
+        <v>0.12202152285675169</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>0.16406553513981526</v>
+        <v>0.16406528482488578</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>0.15178914838665272</v>
+        <v>0.15178891680181716</v>
       </c>
       <c r="N125" s="77" t="str">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
@@ -14609,31 +14609,31 @@
       <c r="C126" s="169"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.6053114221025838E-3</v>
+        <v>6.605301344373208E-3</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.2738485524691757E-3</v>
+        <v>5.2738405061538568E-3</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.6743121653266988E-3</v>
+        <v>3.6743065594254352E-3</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.3111776340962046E-3</v>
+        <v>2.3111741079304797E-3</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-4.2579745245064412E-4</v>
+        <v>-4.2579680281110095E-4</v>
       </c>
       <c r="L126" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.018434053770413E-3</v>
+        <v>2.0184309742438235E-3</v>
       </c>
       <c r="M126" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.6304327039081813E-3</v>
+        <v>1.6304302163555882E-3</v>
       </c>
       <c r="N126" s="23" t="str">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -15395,7 +15395,7 @@
       </c>
       <c r="C4" s="338">
         <f>Normalized_FCF!C19</f>
-        <v>765583.83079622837</v>
+        <v>693212.58366541076</v>
       </c>
       <c r="D4" t="str">
         <f>Reporting_currency</f>
@@ -15427,7 +15427,7 @@
       </c>
       <c r="C6" s="347">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
-        <v>9569797.8849528544</v>
+        <v>8665157.2958176341</v>
       </c>
       <c r="D6" t="str">
         <f>Reporting_currency</f>
@@ -15445,7 +15445,7 @@
       </c>
       <c r="C7" s="338">
         <f>BS!G31</f>
-        <v>0</v>
+        <v>866500</v>
       </c>
       <c r="D7" t="str">
         <f>Reporting_currency</f>
@@ -15461,7 +15461,7 @@
       </c>
       <c r="C8" s="338">
         <f>BS!D66</f>
-        <v>0</v>
+        <v>415406.42282180313</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
@@ -15477,7 +15477,7 @@
       </c>
       <c r="C9" s="348">
         <f>BS!H42</f>
-        <v>0</v>
+        <v>3762.4</v>
       </c>
       <c r="D9" t="str">
         <f>Reporting_currency</f>
@@ -15493,7 +15493,7 @@
       </c>
       <c r="C10" s="347">
         <f>C6-C7+C8+C9</f>
-        <v>9569797.8849528544</v>
+        <v>8217826.1186394375</v>
       </c>
       <c r="D10" t="str">
         <f>Reporting_currency</f>
@@ -15521,7 +15521,7 @@
       </c>
       <c r="C12" s="111">
         <f>(C10*scaling_factor)/Common_Shares*Exchange_Rate</f>
-        <v>33.472337974919526</v>
+        <v>28.743494574782385</v>
       </c>
       <c r="D12" t="str">
         <f>Market_currency</f>
@@ -15574,7 +15574,7 @@
       </c>
       <c r="C18" s="140">
         <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>34.758532541674811</v>
+        <v>29.908102371508068</v>
       </c>
       <c r="D18" t="str">
         <f>Market_currency</f>
@@ -15609,7 +15609,7 @@
       </c>
       <c r="C21" s="123">
         <f>C4*(1+D21)</f>
-        <v>783768.45206779265</v>
+        <v>709678.19825594837</v>
       </c>
       <c r="D21" s="138">
         <f>IF($C$17&lt;B21,0,DCF!$C$16)</f>
@@ -15621,7 +15621,7 @@
       </c>
       <c r="F21" s="125">
         <f t="shared" ref="F21:F51" si="1">C21*E21</f>
-        <v>725711.52969240048</v>
+        <v>657109.44282958179</v>
       </c>
       <c r="H21" s="120"/>
     </row>
@@ -15631,7 +15631,7 @@
       </c>
       <c r="C22" s="123">
         <f t="shared" ref="C22:C50" si="2">IF(ROW()-ROW($C$21)&lt;$C$17, $C$21*(1+D22)^(ROW()-ROW($C$21)), 0)</f>
-        <v>802385.00572545012</v>
+        <v>726534.91432131862</v>
       </c>
       <c r="D22" s="138">
         <f>IF($C$17&lt;B22,0,DCF!$C$16)</f>
@@ -15643,7 +15643,7 @@
       </c>
       <c r="F22" s="125">
         <f t="shared" si="1"/>
-        <v>687915.81423649692</v>
+        <v>622886.58635229641</v>
       </c>
       <c r="H22" s="120"/>
     </row>
@@ -15653,7 +15653,7 @@
       </c>
       <c r="C23" s="123">
         <f t="shared" si="2"/>
-        <v>821443.75129472918</v>
+        <v>743792.02154595929</v>
       </c>
       <c r="D23" s="138">
         <f>IF($C$17&lt;B23,0,DCF!$C$16)</f>
@@ -15665,7 +15665,7 @@
       </c>
       <c r="F23" s="125">
         <f t="shared" si="1"/>
-        <v>652088.53396230971</v>
+        <v>590446.08731675113</v>
       </c>
       <c r="G23" s="338"/>
       <c r="H23" s="339"/>
@@ -15685,7 +15685,7 @@
       </c>
       <c r="C24" s="123">
         <f t="shared" si="2"/>
-        <v>840955.19199176179</v>
+        <v>761459.03026864538</v>
       </c>
       <c r="D24" s="138">
         <f>IF($C$17&lt;B24,0,DCF!$C$16)</f>
@@ -15697,7 +15697,7 @@
       </c>
       <c r="F24" s="125">
         <f t="shared" si="1"/>
-        <v>618127.17097811773</v>
+        <v>559695.11892889242</v>
       </c>
       <c r="G24" s="338"/>
       <c r="H24" s="339"/>
@@ -15717,7 +15717,7 @@
       </c>
       <c r="C25" s="123">
         <f t="shared" si="2"/>
-        <v>860930.08051157452</v>
+        <v>779545.67672360886</v>
       </c>
       <c r="D25" s="138">
         <f>IF($C$17&lt;B25,0,DCF!$C$16)</f>
@@ -15729,7 +15729,7 @@
       </c>
       <c r="F25" s="125">
         <f t="shared" si="1"/>
-        <v>585934.54661709373</v>
+        <v>530545.68889839423</v>
       </c>
       <c r="G25" s="338"/>
       <c r="H25" s="339"/>
@@ -16369,7 +16369,7 @@
       </c>
       <c r="C51" s="123">
         <f>C$21*(1+Terminal_Growth)^$C$17/Equity_Cost</f>
-        <v>9797105.6508474071</v>
+        <v>8870977.4781993553</v>
       </c>
       <c r="D51" s="139">
         <f>Terminal_Growth</f>
@@ -16381,7 +16381,7 @@
       </c>
       <c r="F51" s="125">
         <f t="shared" si="1"/>
-        <v>6667745.4855311764</v>
+        <v>6037438.2129273377</v>
       </c>
       <c r="H51" s="120"/>
     </row>
@@ -16392,7 +16392,7 @@
       </c>
       <c r="F52" s="137">
         <f>SUM(F21:F51)</f>
-        <v>9937523.0810175948</v>
+        <v>8998121.1372532547</v>
       </c>
       <c r="H52" s="120"/>
     </row>
@@ -16413,7 +16413,7 @@
     <row r="55" spans="1:17" ht="13.15">
       <c r="A55" s="133">
         <f>F52</f>
-        <v>9937523.0810175948</v>
+        <v>8998121.1372532547</v>
       </c>
       <c r="B55" s="131">
         <f>C78</f>
@@ -16425,15 +16425,15 @@
       </c>
       <c r="D55" s="131">
         <f>C76</f>
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="E55" s="131">
         <f>C75</f>
-        <v>0.03</v>
+        <v>0.05</v>
       </c>
       <c r="F55" s="131">
         <f>C74</f>
-        <v>0.04</v>
+        <v>0.08</v>
       </c>
       <c r="H55" s="120"/>
     </row>
@@ -16443,19 +16443,19 @@
       </c>
       <c r="B56" s="123">
         <f t="dataTable" ref="B56:F61" dt2D="1" dtr="1" r1="C16" r2="C17"/>
-        <v>9569797.8849528525</v>
+        <v>8665157.2958176322</v>
       </c>
       <c r="C56" s="123">
-        <v>9723052.7030127402</v>
+        <v>8803924.8142956235</v>
       </c>
       <c r="D56" s="123">
-        <v>9878569.6600468941</v>
+        <v>9087649.620388709</v>
       </c>
       <c r="E56" s="123">
-        <v>10036398.318858489</v>
+        <v>9379930.1403924413</v>
       </c>
       <c r="F56" s="123">
-        <v>10196589.015062407</v>
+        <v>9835212.2099300027</v>
       </c>
       <c r="H56" s="120"/>
     </row>
@@ -16464,19 +16464,19 @@
         <v>10</v>
       </c>
       <c r="B57" s="123">
-        <v>9569797.8849528506</v>
+        <v>8665157.2958176304</v>
       </c>
       <c r="C57" s="123">
-        <v>9871404.3604671881</v>
+        <v>8938252.6718316022</v>
       </c>
       <c r="D57" s="123">
-        <v>10187625.765152168</v>
+        <v>9524916.8791843541</v>
       </c>
       <c r="E57" s="123">
-        <v>10519316.186997069</v>
+        <v>10170916.302175496</v>
       </c>
       <c r="F57" s="123">
-        <v>10867376.727276832</v>
+        <v>11266861.823918507</v>
       </c>
       <c r="H57" s="120"/>
     </row>
@@ -16485,19 +16485,19 @@
         <v>15</v>
       </c>
       <c r="B58" s="123">
-        <v>9569797.8849528506</v>
+        <v>8665157.2958176285</v>
       </c>
       <c r="C58" s="341">
-        <v>10050466.035063189</v>
+        <v>9100387.5042157359</v>
       </c>
       <c r="D58" s="123">
-        <v>10570168.388447896</v>
+        <v>10080232.297878651</v>
       </c>
       <c r="E58" s="123">
-        <v>11132606.417962337</v>
+        <v>11229889.3697685</v>
       </c>
       <c r="F58" s="123">
-        <v>11741833.576186236</v>
+        <v>13348337.231490824</v>
       </c>
       <c r="G58" s="338"/>
       <c r="H58" s="339"/>
@@ -16516,19 +16516,19 @@
         <v>20</v>
       </c>
       <c r="B59" s="123">
-        <v>9569797.8849528506</v>
+        <v>8665157.2958176285</v>
       </c>
       <c r="C59" s="341">
-        <v>10228194.474590007</v>
+        <v>9261315.1332998965</v>
       </c>
       <c r="D59" s="123">
-        <v>10959917.974165445</v>
+        <v>10661506.149837431</v>
       </c>
       <c r="E59" s="123">
-        <v>11774565.137135092</v>
+        <v>12402845.790754531</v>
       </c>
       <c r="F59" s="123">
-        <v>12683034.266582098</v>
+        <v>15872073.155175414</v>
       </c>
       <c r="G59" s="338"/>
       <c r="H59" s="339"/>
@@ -16547,19 +16547,19 @@
         <v>25</v>
       </c>
       <c r="B60" s="123">
-        <v>9569797.8849528488</v>
+        <v>8665157.2958176285</v>
       </c>
       <c r="C60" s="341">
-        <v>10389111.592383051</v>
+        <v>9407020.6282360852</v>
       </c>
       <c r="D60" s="123">
-        <v>11322406.716091026</v>
+        <v>11217539.515536647</v>
       </c>
       <c r="E60" s="123">
-        <v>12388648.268620763</v>
+        <v>13593960.545009606</v>
       </c>
       <c r="F60" s="123">
-        <v>13610148.965593254</v>
+        <v>18696804.154837489</v>
       </c>
       <c r="G60" s="338"/>
       <c r="H60" s="339"/>
@@ -16578,19 +16578,19 @@
         <v>30</v>
       </c>
       <c r="B61" s="123">
-        <v>9569797.8849528506</v>
+        <v>8665157.2958176285</v>
       </c>
       <c r="C61" s="341">
-        <v>10527211.119190726</v>
+        <v>9532065.497171931</v>
       </c>
       <c r="D61" s="123">
-        <v>11642172.211618342</v>
+        <v>11722541.476329962</v>
       </c>
       <c r="E61" s="123">
-        <v>12946372.327320715</v>
+        <v>14745823.166404199</v>
       </c>
       <c r="F61" s="123">
-        <v>14478400.09751598</v>
+        <v>21726387.345599752</v>
       </c>
       <c r="G61" s="338"/>
       <c r="H61" s="339"/>
@@ -16652,15 +16652,15 @@
       </c>
       <c r="D64" s="132">
         <f>D55</f>
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="E64" s="132">
         <f>E55</f>
-        <v>0.03</v>
+        <v>0.05</v>
       </c>
       <c r="F64" s="132">
         <f>F55</f>
-        <v>0.04</v>
+        <v>0.08</v>
       </c>
       <c r="H64" s="120"/>
     </row>
@@ -16670,23 +16670,23 @@
       </c>
       <c r="B65" s="124">
         <f>C12</f>
-        <v>33.472337974919526</v>
+        <v>28.743494574782385</v>
       </c>
       <c r="C65" s="124">
         <f>C12</f>
-        <v>33.472337974919526</v>
+        <v>28.743494574782385</v>
       </c>
       <c r="D65" s="124">
         <f>C12</f>
-        <v>33.472337974919526</v>
+        <v>28.743494574782385</v>
       </c>
       <c r="E65" s="141">
         <f>C12</f>
-        <v>33.472337974919526</v>
+        <v>28.743494574782385</v>
       </c>
       <c r="F65" s="124">
         <f>C12</f>
-        <v>33.472337974919526</v>
+        <v>28.743494574782385</v>
       </c>
       <c r="H65" s="120"/>
     </row>
@@ -16697,23 +16697,23 @@
       </c>
       <c r="B66" s="124">
         <f t="shared" ref="B66:F71" si="4">(B56-$C$7+$C$8+$C$9)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>33.472337974919526</v>
+        <v>28.743494574782378</v>
       </c>
       <c r="C66" s="124">
         <f t="shared" si="4"/>
-        <v>34.008378247457699</v>
+        <v>29.228861794402807</v>
       </c>
       <c r="D66" s="124">
         <f t="shared" si="4"/>
-        <v>34.552330816702991</v>
+        <v>30.221246192287584</v>
       </c>
       <c r="E66" s="124">
         <f t="shared" si="4"/>
-        <v>35.104369038761632</v>
+        <v>31.243555915048276</v>
       </c>
       <c r="F66" s="124">
         <f t="shared" si="4"/>
-        <v>35.664668972807902</v>
+        <v>32.83599624011994</v>
       </c>
       <c r="H66" s="120"/>
     </row>
@@ -16724,23 +16724,23 @@
       </c>
       <c r="B67" s="124">
         <f t="shared" si="4"/>
-        <v>33.472337974919519</v>
+        <v>28.743494574782375</v>
       </c>
       <c r="C67" s="124">
         <f t="shared" si="4"/>
-        <v>34.527268706498909</v>
+        <v>29.698700409699136</v>
       </c>
       <c r="D67" s="124">
         <f t="shared" si="4"/>
-        <v>35.633318161227969</v>
+        <v>31.750676104708692</v>
       </c>
       <c r="E67" s="124">
         <f t="shared" si="4"/>
-        <v>36.793473687656927</v>
+        <v>34.010188613490342</v>
       </c>
       <c r="F67" s="124">
         <f t="shared" si="4"/>
-        <v>38.010887072979919</v>
+        <v>37.84347781962564</v>
       </c>
       <c r="H67" s="120"/>
     </row>
@@ -16751,23 +16751,23 @@
       </c>
       <c r="B68" s="124">
         <f t="shared" si="4"/>
-        <v>33.472337974919519</v>
+        <v>28.743494574782368</v>
       </c>
       <c r="C68" s="124">
         <f t="shared" si="4"/>
-        <v>35.153573771923178</v>
+        <v>30.265799494996905</v>
       </c>
       <c r="D68" s="124">
         <f t="shared" si="4"/>
-        <v>36.971339729781718</v>
+        <v>33.693003125759745</v>
       </c>
       <c r="E68" s="124">
         <f t="shared" si="4"/>
-        <v>38.938582511727667</v>
+        <v>37.714159248030818</v>
       </c>
       <c r="F68" s="124">
         <f t="shared" si="4"/>
-        <v>41.069479902531917</v>
+        <v>45.123855406271794</v>
       </c>
       <c r="H68" s="120"/>
     </row>
@@ -16778,23 +16778,23 @@
       </c>
       <c r="B69" s="124">
         <f t="shared" si="4"/>
-        <v>33.472337974919519</v>
+        <v>28.743494574782368</v>
       </c>
       <c r="C69" s="124">
         <f t="shared" si="4"/>
-        <v>35.775215573256368</v>
+        <v>30.828676144701319</v>
       </c>
       <c r="D69" s="124">
         <f t="shared" si="4"/>
-        <v>38.334569132905834</v>
+        <v>35.726124971979374</v>
       </c>
       <c r="E69" s="124">
         <f t="shared" si="4"/>
-        <v>41.183965274500906</v>
+        <v>41.816809515429036</v>
       </c>
       <c r="F69" s="124">
         <f t="shared" si="4"/>
-        <v>44.361523056410199</v>
+        <v>53.951127823982851</v>
       </c>
       <c r="H69" s="120"/>
     </row>
@@ -16805,23 +16805,23 @@
       </c>
       <c r="B70" s="124">
         <f t="shared" si="4"/>
-        <v>33.472337974919512</v>
+        <v>28.743494574782368</v>
       </c>
       <c r="C70" s="124">
         <f t="shared" si="4"/>
-        <v>36.338056316339134</v>
+        <v>31.338310328091382</v>
       </c>
       <c r="D70" s="124">
         <f t="shared" si="4"/>
-        <v>39.60244812342394</v>
+        <v>37.670963156632943</v>
       </c>
       <c r="E70" s="124">
         <f t="shared" si="4"/>
-        <v>43.331847431354475</v>
+        <v>45.982972194293588</v>
       </c>
       <c r="F70" s="124">
         <f t="shared" si="4"/>
-        <v>47.604297555923061</v>
+        <v>63.831190871295036</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="13.15">
@@ -16831,23 +16831,23 @@
       </c>
       <c r="B71" s="124">
         <f t="shared" si="4"/>
-        <v>33.472337974919519</v>
+        <v>28.743494574782368</v>
       </c>
       <c r="C71" s="124">
         <f t="shared" si="4"/>
-        <v>36.821087838117791</v>
+        <v>31.775679829462252</v>
       </c>
       <c r="D71" s="124">
         <f t="shared" si="4"/>
-        <v>40.720893765399033</v>
+        <v>39.437308770516573</v>
       </c>
       <c r="E71" s="124">
         <f t="shared" si="4"/>
-        <v>45.282602130040644</v>
+        <v>50.011842668183782</v>
       </c>
       <c r="F71" s="124">
         <f t="shared" si="4"/>
-        <v>50.641184612913094</v>
+        <v>74.427765531108392</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="13.15">
@@ -16874,7 +16874,7 @@
       </c>
       <c r="C74" s="142">
         <f>Scenarios!C56</f>
-        <v>0.04</v>
+        <v>0.08</v>
       </c>
       <c r="D74" s="145">
         <f>Scenarios!C55</f>
@@ -16882,7 +16882,7 @@
       </c>
       <c r="E74" s="135">
         <f>INDEX(B$65:F$71, MATCH(D74, A$65:A$71, 0), MATCH(C74, B$64:F$64, 0))</f>
-        <v>38.010887072979919</v>
+        <v>37.84347781962564</v>
       </c>
       <c r="F74" s="142">
         <f>Scenarios!C58</f>
@@ -16896,7 +16896,7 @@
       </c>
       <c r="C75" s="142">
         <f>Scenarios!C38</f>
-        <v>0.03</v>
+        <v>0.05</v>
       </c>
       <c r="D75" s="145">
         <f>Scenarios!C37</f>
@@ -16904,7 +16904,7 @@
       </c>
       <c r="E75" s="135">
         <f>INDEX(B$65:F$71, MATCH(D75, A$65:A$71, 0), MATCH(C75, B$64:F$64, 0))</f>
-        <v>35.104369038761632</v>
+        <v>31.243555915048276</v>
       </c>
       <c r="F75" s="142">
         <f>Scenarios!C40*(1-F$74-F$78)</f>
@@ -16919,7 +16919,7 @@
       </c>
       <c r="C76" s="142">
         <f>Scenarios!C26</f>
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="D76" s="145">
         <f>Scenarios!C25</f>
@@ -16927,7 +16927,7 @@
       </c>
       <c r="E76" s="135">
         <f>INDEX(B$65:F$71, MATCH(D76, A$65:A$71, 0), MATCH(C76, B$64:F$64, 0))</f>
-        <v>34.552330816702991</v>
+        <v>30.221246192287584</v>
       </c>
       <c r="F76" s="142">
         <f>Scenarios!C28*(1-F$74-F$78)</f>
@@ -16950,7 +16950,7 @@
       </c>
       <c r="E77" s="135">
         <f>INDEX(B$65:F$71, MATCH(D77, A$65:A$71, 0), MATCH(C77, B$64:F$64, 0))</f>
-        <v>34.008378247457699</v>
+        <v>29.228861794402807</v>
       </c>
       <c r="F77" s="142">
         <f>Scenarios!C34*(1-F$74-F$78)</f>
@@ -16973,7 +16973,7 @@
       </c>
       <c r="E78" s="135">
         <f>INDEX(B$65:F$71, MATCH(D78, A$65:A$71, 0), MATCH(C78, B$64:F$64, 0))</f>
-        <v>33.472337974919519</v>
+        <v>28.743494574782375</v>
       </c>
       <c r="F78" s="142">
         <f>Scenarios!C52</f>
@@ -17126,7 +17126,7 @@
   <sheetData>
     <row r="2" spans="2:8" ht="13.9">
       <c r="B2" s="36" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C2" s="37"/>
       <c r="D2" s="37"/>
@@ -17138,7 +17138,7 @@
     </row>
     <row r="3" spans="2:8" ht="13.15">
       <c r="B3" s="109" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="C3" s="107">
         <f>scaling_factor</f>
@@ -17151,11 +17151,11 @@
     </row>
     <row r="4" spans="2:8">
       <c r="B4" s="100" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C4" s="114">
         <f>Normalized_FCF!C91</f>
-        <v>3755836.1369088003</v>
+        <v>3755841.8671999997</v>
       </c>
       <c r="D4" t="str">
         <f>Market_currency</f>
@@ -17166,7 +17166,7 @@
       </c>
       <c r="F4" s="134">
         <f>Thesis!E22</f>
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="H4" s="120"/>
     </row>
@@ -17183,11 +17183,11 @@
     </row>
     <row r="6" spans="2:8" ht="13.35" customHeight="1">
       <c r="B6" s="149" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="C6" s="319">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
-        <v>46947951.71136</v>
+        <v>46948023.339999996</v>
       </c>
       <c r="D6" t="str">
         <f>Reporting_currency</f>
@@ -17199,11 +17199,11 @@
     </row>
     <row r="7" spans="2:8" ht="13.15">
       <c r="B7" s="149" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="C7" s="111">
         <f>(C6*scaling_factor)/Common_Shares*Exchange_Rate</f>
-        <v>164.21012499999998</v>
+        <v>164.21012499999995</v>
       </c>
       <c r="D7" t="str">
         <f>Market_currency</f>
@@ -17256,7 +17256,7 @@
       </c>
       <c r="C13" s="140">
         <f>F47/Common_Shares*scaling_factor</f>
-        <v>20.383040908722531</v>
+        <v>19.052513639358704</v>
       </c>
       <c r="D13" t="str">
         <f>Market_currency</f>
@@ -17272,7 +17272,7 @@
         <v>107</v>
       </c>
       <c r="C15" s="128" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="D15" s="128" t="s">
         <v>118</v>
@@ -17281,7 +17281,7 @@
         <v>109</v>
       </c>
       <c r="F15" s="129" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="H15" s="120"/>
     </row>
@@ -17291,7 +17291,7 @@
       </c>
       <c r="C16" s="123">
         <f>C4*(1+D16)</f>
-        <v>3845047.0828044433</v>
+        <v>3845052.9492050684</v>
       </c>
       <c r="D16" s="138">
         <f>IF($C$12&lt;B16,0,DDM!$C$11)</f>
@@ -17303,7 +17303,7 @@
       </c>
       <c r="F16" s="125">
         <f t="shared" ref="F16:F46" si="1">C16*E16</f>
-        <v>3560228.7803744841</v>
+        <v>3560234.2122269147</v>
       </c>
       <c r="H16" s="120"/>
     </row>
@@ -17313,7 +17313,7 @@
       </c>
       <c r="C17" s="123">
         <f t="shared" ref="C17:C45" si="2">IF(ROW()-ROW($C$16)&lt;$C$12, $C$16*(1+D17)^(ROW()-ROW($C$16)), 0)</f>
-        <v>3936377.0223349221</v>
+        <v>3936383.0280779279</v>
       </c>
       <c r="D17" s="138">
         <f>IF($C$12&lt;B17,0,DDM!$C$11)</f>
@@ -17325,7 +17325,7 @@
       </c>
       <c r="F17" s="125">
         <f t="shared" si="1"/>
-        <v>3374808.8325916682</v>
+        <v>3374813.9815482921</v>
       </c>
       <c r="H17" s="120"/>
     </row>
@@ -17335,7 +17335,7 @@
       </c>
       <c r="C18" s="123">
         <f t="shared" si="2"/>
-        <v>4029876.2871493343</v>
+        <v>4029882.4355444671</v>
       </c>
       <c r="D18" s="138">
         <f>IF($C$12&lt;B18,0,DDM!$C$11)</f>
@@ -17347,7 +17347,7 @@
       </c>
       <c r="F18" s="125">
         <f t="shared" si="1"/>
-        <v>3199045.7240617964</v>
+        <v>3199050.6048560832</v>
       </c>
       <c r="H18" s="120"/>
     </row>
@@ -17357,7 +17357,7 @@
       </c>
       <c r="C19" s="123">
         <f t="shared" si="2"/>
-        <v>4125596.4044052763</v>
+        <v>4125602.698840898</v>
       </c>
       <c r="D19" s="138">
         <f>IF($C$12&lt;B19,0,DDM!$C$11)</f>
@@ -17369,7 +17369,7 @@
       </c>
       <c r="F19" s="125">
         <f t="shared" si="1"/>
-        <v>3032436.5178275872</v>
+        <v>3032441.1444256757</v>
       </c>
       <c r="H19" s="120"/>
     </row>
@@ -17379,7 +17379,7 @@
       </c>
       <c r="C20" s="123">
         <f t="shared" si="2"/>
-        <v>4223590.1251653032</v>
+        <v>4223596.5691102576</v>
       </c>
       <c r="D20" s="138">
         <f>IF($C$12&lt;B20,0,DDM!$C$11)</f>
@@ -17391,7 +17391,7 @@
       </c>
       <c r="F20" s="125">
         <f t="shared" si="1"/>
-        <v>2874504.4703451912</v>
+        <v>2874508.8559858496</v>
       </c>
       <c r="H20" s="120"/>
     </row>
@@ -17951,7 +17951,7 @@
       </c>
       <c r="C46" s="123">
         <f>C$16*(1+F4)^$C$12/Equity_Cost</f>
-        <v>53065533.394056834</v>
+        <v>48063161.865063354</v>
       </c>
       <c r="D46" s="139">
         <f>Terminal_Growth</f>
@@ -17963,7 +17963,7 @@
       </c>
       <c r="F46" s="125">
         <f t="shared" si="1"/>
-        <v>36115510.369628586</v>
+        <v>32710980.361675579</v>
       </c>
       <c r="H46" s="120"/>
     </row>
@@ -17974,7 +17974,7 @@
       </c>
       <c r="F47" s="137">
         <f>SUM(F16:F46)</f>
-        <v>52156534.694829315</v>
+        <v>48752029.160718396</v>
       </c>
       <c r="H47" s="120"/>
     </row>
@@ -17995,7 +17995,7 @@
     <row r="50" spans="1:8" ht="13.15">
       <c r="A50" s="133">
         <f>F47</f>
-        <v>52156534.694829315</v>
+        <v>48752029.160718396</v>
       </c>
       <c r="B50" s="131">
         <f>C73</f>
@@ -18007,15 +18007,15 @@
       </c>
       <c r="D50" s="131">
         <f>C71</f>
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="E50" s="131">
         <f>C70</f>
-        <v>0.03</v>
+        <v>0.05</v>
       </c>
       <c r="F50" s="131">
         <f>C69</f>
-        <v>0.04</v>
+        <v>0.08</v>
       </c>
       <c r="H50" s="120"/>
     </row>
@@ -18025,19 +18025,19 @@
       </c>
       <c r="B51" s="123">
         <f t="dataTable" ref="B51:F56" dt2D="1" dtr="1" r1="C11" r2="C12"/>
-        <v>50273540.189431578</v>
+        <v>46948023.339999989</v>
       </c>
       <c r="C51" s="123">
-        <v>51058640.562915869</v>
+        <v>47699868.975795098</v>
       </c>
       <c r="D51" s="123">
-        <v>51854838.641138017</v>
+        <v>49237096.560229637</v>
       </c>
       <c r="E51" s="123">
-        <v>52662377.571562372</v>
+        <v>50820679.201203234</v>
       </c>
       <c r="F51" s="123">
-        <v>53481504.292948306</v>
+        <v>53287408.020684652</v>
       </c>
       <c r="H51" s="120"/>
     </row>
@@ -18046,19 +18046,19 @@
         <v>10</v>
       </c>
       <c r="B52" s="123">
-        <v>51710201.195690759</v>
+        <v>46948023.339999989</v>
       </c>
       <c r="C52" s="123">
-        <v>53237458.518615946</v>
+        <v>48427660.425565451</v>
       </c>
       <c r="D52" s="123">
-        <v>54836414.428827628</v>
+        <v>51606220.717002235</v>
       </c>
       <c r="E52" s="123">
-        <v>56511258.950207151</v>
+        <v>55106260.583889931</v>
       </c>
       <c r="F52" s="123">
-        <v>58266412.746560767</v>
+        <v>61044118.856698632</v>
       </c>
       <c r="H52" s="120"/>
     </row>
@@ -18067,19 +18067,19 @@
         <v>15</v>
       </c>
       <c r="B53" s="123">
-        <v>52066786.635214113</v>
+        <v>46948023.339999981</v>
       </c>
       <c r="C53" s="123">
-        <v>54476058.757157139</v>
+        <v>49306110.710440405</v>
       </c>
       <c r="D53" s="123">
-        <v>57076826.657009721</v>
+        <v>54614932.543907583</v>
       </c>
       <c r="E53" s="123">
-        <v>59887249.189427316</v>
+        <v>60843801.242013268</v>
       </c>
       <c r="F53" s="123">
-        <v>62927211.967279136</v>
+        <v>72321600.924278408</v>
       </c>
       <c r="H53" s="120"/>
     </row>
@@ -18088,19 +18088,19 @@
         <v>20</v>
       </c>
       <c r="B54" s="123">
-        <v>51842704.90829917</v>
+        <v>46948023.339999974</v>
       </c>
       <c r="C54" s="123">
-        <v>55121644.512077264</v>
+        <v>50178020.339817904</v>
       </c>
       <c r="D54" s="123">
-        <v>58760314.620962307</v>
+        <v>57764287.764714047</v>
       </c>
       <c r="E54" s="123">
-        <v>62805795.426537372</v>
+        <v>67198906.354281053</v>
       </c>
       <c r="F54" s="123">
-        <v>67311552.322015017</v>
+        <v>85995260.732661694</v>
       </c>
       <c r="H54" s="120"/>
     </row>
@@ -18109,19 +18109,19 @@
         <v>25</v>
       </c>
       <c r="B55" s="123">
-        <v>51339460.54105404</v>
+        <v>46948023.339999974</v>
       </c>
       <c r="C55" s="123">
-        <v>55402802.249987274</v>
+        <v>50967456.093088314</v>
       </c>
       <c r="D55" s="123">
-        <v>60025319.198746137</v>
+        <v>60776889.445155039</v>
       </c>
       <c r="E55" s="123">
-        <v>65300050.81238687</v>
+        <v>73652393.737640664</v>
       </c>
       <c r="F55" s="123">
-        <v>71336459.830678657</v>
+        <v>101299718.84854215</v>
       </c>
       <c r="H55" s="120"/>
     </row>
@@ -18130,19 +18130,19 @@
         <v>30</v>
       </c>
       <c r="B56" s="123">
-        <v>50733409.656596974</v>
+        <v>46948023.339999974</v>
       </c>
       <c r="C56" s="123">
-        <v>55468185.825113632</v>
+        <v>51644952.095172547</v>
       </c>
       <c r="D56" s="123">
-        <v>60975867.474753365</v>
+        <v>63513001.789418392</v>
       </c>
       <c r="E56" s="123">
-        <v>67411926.571170464</v>
+        <v>79893212.15415208</v>
       </c>
       <c r="F56" s="123">
-        <v>74965672.98452279</v>
+        <v>117714070.89025626</v>
       </c>
       <c r="H56" s="120"/>
     </row>
@@ -18174,15 +18174,15 @@
       </c>
       <c r="D59" s="132">
         <f>D50</f>
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="E59" s="132">
         <f>E50</f>
-        <v>0.03</v>
+        <v>0.05</v>
       </c>
       <c r="F59" s="132">
         <f>F50</f>
-        <v>0.04</v>
+        <v>0.08</v>
       </c>
       <c r="H59" s="120"/>
     </row>
@@ -18192,23 +18192,23 @@
       </c>
       <c r="B60" s="124">
         <f>C7</f>
-        <v>164.21012499999998</v>
+        <v>164.21012499999995</v>
       </c>
       <c r="C60" s="124">
         <f>C7</f>
-        <v>164.21012499999998</v>
+        <v>164.21012499999995</v>
       </c>
       <c r="D60" s="124">
         <f>C7</f>
-        <v>164.21012499999998</v>
+        <v>164.21012499999995</v>
       </c>
       <c r="E60" s="141">
         <f>C7</f>
-        <v>164.21012499999998</v>
+        <v>164.21012499999995</v>
       </c>
       <c r="F60" s="124">
         <f>C7</f>
-        <v>164.21012499999998</v>
+        <v>164.21012499999995</v>
       </c>
       <c r="H60" s="120"/>
     </row>
@@ -18219,23 +18219,23 @@
       </c>
       <c r="B61" s="124">
         <f t="shared" ref="B61:F66" si="4">B51/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>175.84205524991023</v>
+        <v>164.21012499999995</v>
       </c>
       <c r="C61" s="124">
         <f t="shared" si="4"/>
-        <v>178.58810541329163</v>
+        <v>166.83985586088221</v>
       </c>
       <c r="D61" s="124">
         <f t="shared" si="4"/>
-        <v>181.37297208337429</v>
+        <v>172.21661756105743</v>
       </c>
       <c r="E61" s="124">
         <f t="shared" si="4"/>
-        <v>184.19750571846498</v>
+        <v>177.75551536595285</v>
       </c>
       <c r="F61" s="124">
         <f t="shared" si="4"/>
-        <v>187.06257003770511</v>
+        <v>186.38339400643719</v>
       </c>
       <c r="H61" s="120"/>
     </row>
@@ -18246,23 +18246,23 @@
       </c>
       <c r="B62" s="124">
         <f t="shared" si="4"/>
-        <v>180.86707284537138</v>
+        <v>164.21012499999995</v>
       </c>
       <c r="C62" s="124">
         <f t="shared" si="4"/>
-        <v>186.2089697069554</v>
+        <v>169.3854523831302</v>
       </c>
       <c r="D62" s="124">
         <f t="shared" si="4"/>
-        <v>191.80164713619914</v>
+        <v>180.50310432338054</v>
       </c>
       <c r="E62" s="124">
         <f t="shared" si="4"/>
-        <v>197.65976060411322</v>
+        <v>192.7451955374089</v>
       </c>
       <c r="F62" s="124">
         <f t="shared" si="4"/>
-        <v>203.79877229232093</v>
+        <v>213.51404542377779</v>
       </c>
       <c r="H62" s="120"/>
     </row>
@@ -18273,23 +18273,23 @@
       </c>
       <c r="B63" s="124">
         <f t="shared" si="4"/>
-        <v>182.11430382058649</v>
+        <v>164.21012499999992</v>
       </c>
       <c r="C63" s="124">
         <f t="shared" si="4"/>
-        <v>190.54122899797503</v>
+        <v>172.45800838918254</v>
       </c>
       <c r="D63" s="124">
         <f t="shared" si="4"/>
-        <v>199.63795007659539</v>
+        <v>191.02667720326716</v>
       </c>
       <c r="E63" s="124">
         <f t="shared" si="4"/>
-        <v>209.46798138847132</v>
+        <v>212.81339440149802</v>
       </c>
       <c r="F63" s="124">
         <f t="shared" si="4"/>
-        <v>220.10087695791967</v>
+        <v>252.95930015987491</v>
       </c>
       <c r="H63" s="120"/>
     </row>
@@ -18300,23 +18300,23 @@
       </c>
       <c r="B64" s="124">
         <f t="shared" si="4"/>
-        <v>181.33053185513106</v>
+        <v>164.21012499999989</v>
       </c>
       <c r="C64" s="124">
         <f t="shared" si="4"/>
-        <v>192.79929806487323</v>
+        <v>175.50768714119076</v>
       </c>
       <c r="D64" s="124">
         <f t="shared" si="4"/>
-        <v>205.5262957640976</v>
+        <v>202.04217855319109</v>
       </c>
       <c r="E64" s="124">
         <f t="shared" si="4"/>
-        <v>219.67619761397617</v>
+        <v>235.04164876944071</v>
       </c>
       <c r="F64" s="124">
         <f t="shared" si="4"/>
-        <v>235.4360098327266</v>
+        <v>300.78566699285375</v>
       </c>
       <c r="H64" s="120"/>
     </row>
@@ -18327,23 +18327,23 @@
       </c>
       <c r="B65" s="124">
         <f t="shared" si="4"/>
-        <v>179.57033109155074</v>
+        <v>164.21012499999989</v>
       </c>
       <c r="C65" s="124">
         <f t="shared" si="4"/>
-        <v>193.78270512745968</v>
+        <v>178.26889697499334</v>
       </c>
       <c r="D65" s="124">
         <f t="shared" si="4"/>
-        <v>209.95090966675679</v>
+        <v>212.5793569757582</v>
       </c>
       <c r="E65" s="124">
         <f t="shared" si="4"/>
-        <v>228.40036925005549</v>
+        <v>257.61401485677948</v>
       </c>
       <c r="F65" s="124">
         <f t="shared" si="4"/>
-        <v>249.513952341796</v>
+        <v>354.31607789142674</v>
       </c>
     </row>
     <row r="66" spans="1:8" ht="13.15">
@@ -18353,23 +18353,23 @@
       </c>
       <c r="B66" s="124">
         <f t="shared" si="4"/>
-        <v>177.45054337205849</v>
+        <v>164.21012499999989</v>
       </c>
       <c r="C66" s="124">
         <f t="shared" si="4"/>
-        <v>194.01139764019069</v>
+        <v>180.63857508441154</v>
       </c>
       <c r="D66" s="124">
         <f t="shared" si="4"/>
-        <v>213.27564792544237</v>
+        <v>222.1494585072262</v>
       </c>
       <c r="E66" s="124">
         <f t="shared" si="4"/>
-        <v>235.78708943044649</v>
+        <v>279.44252859112663</v>
       </c>
       <c r="F66" s="124">
         <f t="shared" si="4"/>
-        <v>262.20787239412039</v>
+        <v>411.72856533618312</v>
       </c>
     </row>
     <row r="68" spans="1:8" ht="13.15">
@@ -18396,7 +18396,7 @@
       </c>
       <c r="C69" s="142">
         <f>Scenarios!C56</f>
-        <v>0.04</v>
+        <v>0.08</v>
       </c>
       <c r="D69" s="145">
         <f>Scenarios!C55</f>
@@ -18404,7 +18404,7 @@
       </c>
       <c r="E69" s="135">
         <f>INDEX(B$60:F$66, MATCH(D69, A$60:A$66, 0), MATCH(C69, B$59:F$59, 0))</f>
-        <v>203.79877229232093</v>
+        <v>213.51404542377779</v>
       </c>
       <c r="F69" s="142">
         <f>Scenarios!C58</f>
@@ -18418,7 +18418,7 @@
       </c>
       <c r="C70" s="142">
         <f>Scenarios!C38</f>
-        <v>0.03</v>
+        <v>0.05</v>
       </c>
       <c r="D70" s="145">
         <f>Scenarios!C37</f>
@@ -18426,7 +18426,7 @@
       </c>
       <c r="E70" s="135">
         <f>INDEX(B$60:F$66, MATCH(D70, A$60:A$66, 0), MATCH(C70, B$59:F$59, 0))</f>
-        <v>184.19750571846498</v>
+        <v>177.75551536595285</v>
       </c>
       <c r="F70" s="142">
         <f>Scenarios!C40*(1-F$69-F$73)</f>
@@ -18441,7 +18441,7 @@
       </c>
       <c r="C71" s="142">
         <f>Scenarios!C26</f>
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="D71" s="145">
         <f>Scenarios!C25</f>
@@ -18449,7 +18449,7 @@
       </c>
       <c r="E71" s="135">
         <f>INDEX(B$60:F$66, MATCH(D71, A$60:A$66, 0), MATCH(C71, B$59:F$59, 0))</f>
-        <v>181.37297208337429</v>
+        <v>172.21661756105743</v>
       </c>
       <c r="F71" s="142">
         <f>Scenarios!C28*(1-F$69-F$73)</f>
@@ -18472,7 +18472,7 @@
       </c>
       <c r="E72" s="135">
         <f>INDEX(B$60:F$66, MATCH(D72, A$60:A$66, 0), MATCH(C72, B$59:F$59, 0))</f>
-        <v>178.58810541329163</v>
+        <v>166.83985586088221</v>
       </c>
       <c r="F72" s="142">
         <f>Scenarios!C34*(1-F$69-F$73)</f>
@@ -18495,7 +18495,7 @@
       </c>
       <c r="E73" s="135">
         <f>INDEX(B$60:F$66, MATCH(D73, A$60:A$66, 0), MATCH(C73, B$59:F$59, 0))</f>
-        <v>180.86707284537138</v>
+        <v>164.21012499999995</v>
       </c>
       <c r="F73" s="142">
         <f>Scenarios!C52</f>
@@ -18644,7 +18644,7 @@
       </c>
       <c r="I6" s="124">
         <f t="shared" si="0"/>
-        <v>183.94390718562295</v>
+        <v>32.001656751256881</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1">
@@ -18700,7 +18700,7 @@
       </c>
       <c r="C9" s="338">
         <f>Normalized_FCF!C19</f>
-        <v>765583.83079622837</v>
+        <v>693212.58366541076</v>
       </c>
       <c r="D9" t="str">
         <f>Reporting_currency</f>
@@ -18729,7 +18729,7 @@
     </row>
     <row r="11" spans="2:9" ht="13.15">
       <c r="B11" s="159" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="E11" s="366"/>
       <c r="F11" s="366"/>
@@ -18850,7 +18850,7 @@
       </c>
       <c r="C22" s="160">
         <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
-        <v>164.21012499999998</v>
+        <v>28.743494574782385</v>
       </c>
       <c r="D22" t="str">
         <f>Market_currency</f>
@@ -18885,7 +18885,7 @@
         <v>134</v>
       </c>
       <c r="C26" s="164">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="D26" s="164"/>
       <c r="E26" s="365"/>
@@ -18897,7 +18897,7 @@
       </c>
       <c r="C27" s="160">
         <f>IF(valuation_method="DCF",DCF!E76,DDM!E71)</f>
-        <v>181.37297208337429</v>
+        <v>30.221246192287584</v>
       </c>
       <c r="D27" s="160" t="str">
         <f>Market_currency</f>
@@ -18955,7 +18955,7 @@
       </c>
       <c r="C33" s="160">
         <f>IF(valuation_method="DCF",DCF!E77,DDM!E72)</f>
-        <v>178.58810541329163</v>
+        <v>29.228861794402807</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
@@ -19001,7 +19001,7 @@
         <v>134</v>
       </c>
       <c r="C38" s="164">
-        <v>0.03</v>
+        <v>0.05</v>
       </c>
       <c r="D38" s="164"/>
       <c r="E38" s="365"/>
@@ -19013,7 +19013,7 @@
       </c>
       <c r="C39" s="160">
         <f>IF(valuation_method="DCF",DCF!E75,DDM!E70)</f>
-        <v>184.19750571846498</v>
+        <v>31.243555915048276</v>
       </c>
       <c r="D39" t="str">
         <f>Market_currency</f>
@@ -19040,7 +19040,7 @@
       </c>
       <c r="C42" s="154">
         <f>C27*C28+C33*C34+C39*C40</f>
-        <v>181.38090547637591</v>
+        <v>30.227231257262765</v>
       </c>
       <c r="D42" t="str">
         <f>Market_currency</f>
@@ -19114,7 +19114,7 @@
       </c>
       <c r="C51" s="160">
         <f>IF(valuation_method="DCF",DCF!E78,DDM!E73)</f>
-        <v>180.86707284537138</v>
+        <v>28.743494574782375</v>
       </c>
       <c r="D51" t="str">
         <f>Market_currency</f>
@@ -19160,7 +19160,7 @@
         <v>134</v>
       </c>
       <c r="C56" s="164">
-        <v>0.04</v>
+        <v>0.08</v>
       </c>
       <c r="D56" s="164"/>
       <c r="E56" s="365"/>
@@ -19172,7 +19172,7 @@
       </c>
       <c r="C57" s="160">
         <f>IF(valuation_method="DCF",DCF!E74,DDM!E69)</f>
-        <v>203.79877229232093</v>
+        <v>37.84347781962564</v>
       </c>
       <c r="D57" t="str">
         <f>Market_currency</f>
@@ -19198,7 +19198,7 @@
       </c>
       <c r="C60" s="154">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
-        <v>182.47610718562294</v>
+        <v>30.533856751256884</v>
       </c>
       <c r="D60" t="str">
         <f>Market_currency</f>
@@ -19260,7 +19260,7 @@
       </c>
       <c r="C66" s="160">
         <f>IF(valuation_method="DCF",DCF!C18,DDM!C13)</f>
-        <v>20.383040908722531</v>
+        <v>29.908102371508068</v>
       </c>
       <c r="D66" s="160" t="str">
         <f>Market_currency</f>
@@ -19323,7 +19323,7 @@
       </c>
       <c r="F72" s="291">
         <f>BS!D89/C60</f>
-        <v>0</v>
+        <v>-5.1242478065840952E-2</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="13.9">
@@ -19395,7 +19395,7 @@
       </c>
       <c r="C82" s="116">
         <f>C60/(1+C80)^C76</f>
-        <v>66.500039061815954</v>
+        <v>11.127498816055718</v>
       </c>
       <c r="D82" s="116"/>
     </row>
@@ -19405,7 +19405,7 @@
       </c>
       <c r="C83" s="111">
         <f>C81+C82</f>
-        <v>68.832257720708085</v>
+        <v>13.459717474947846</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -19416,7 +19416,7 @@
       </c>
       <c r="F83" s="291">
         <f>(1-C83/C60)</f>
-        <v>0.622787559520388</v>
+        <v>0.55918711531933174</v>
       </c>
     </row>
     <row r="84" spans="2:8">
@@ -19446,7 +19446,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.56101689335785077</v>
+        <v>-0.11622199457788085</v>
       </c>
     </row>
     <row r="88" spans="2:8">
@@ -19484,7 +19484,7 @@
       </c>
       <c r="C92" s="116">
         <f>C60/(1+C90)^C76</f>
-        <v>100.49084900587657</v>
+        <v>16.815205210599611</v>
       </c>
       <c r="D92" s="116"/>
     </row>
@@ -19494,7 +19494,7 @@
       </c>
       <c r="C93" s="111">
         <f>C91+C92</f>
-        <v>103.4884509637497</v>
+        <v>19.812807168472737</v>
       </c>
       <c r="D93" t="str">
         <f>Market_currency</f>
@@ -19505,7 +19505,7 @@
       </c>
       <c r="F93" s="291">
         <f>(1-C93/C60)</f>
-        <v>0.4328657457686963</v>
+        <v>0.35112005896021736</v>
       </c>
     </row>
     <row r="95" spans="2:8" ht="13.15">
@@ -19544,7 +19544,7 @@
       </c>
       <c r="C98" s="116">
         <f>C60/(1+C96)^C76</f>
-        <v>144.85541709979972</v>
+        <v>24.238759931839088</v>
       </c>
       <c r="D98" s="116"/>
       <c r="G98" s="2"/>
@@ -19556,7 +19556,7 @@
       </c>
       <c r="C99" s="111">
         <f>C97+C98</f>
-        <v>148.63808005768217</v>
+        <v>28.021422889721528</v>
       </c>
       <c r="D99" t="s">
         <v>399</v>
@@ -19566,7 +19566,7 @@
       </c>
       <c r="F99" s="291">
         <f>(1-C99/C60)</f>
-        <v>0.18543812474867838</v>
+        <v>8.2283541250711356E-2</v>
       </c>
     </row>
     <row r="100" spans="2:8">
@@ -19602,7 +19602,7 @@
       </c>
       <c r="C104" s="116">
         <f>C60/(1+C102)^C76</f>
-        <v>129.88288879260921</v>
+        <v>21.733396125108815</v>
       </c>
       <c r="D104" s="116"/>
     </row>
@@ -19612,7 +19612,7 @@
       </c>
       <c r="C105" s="111">
         <f>C103+C104</f>
-        <v>133.40829672810483</v>
+        <v>25.258804060604444</v>
       </c>
       <c r="D105" t="s">
         <v>399</v>
@@ -19622,7 +19622,7 @@
       </c>
       <c r="F105" s="291">
         <f>(1-C105/C66)</f>
-        <v>-5.5450634831928003</v>
+        <v>0.15545280182445731</v>
       </c>
     </row>
     <row r="106" spans="2:8">

--- a/financial_models/opportunities/1913.HK_Valuation.xlsx
+++ b/financial_models/opportunities/1913.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF9B74A1-019A-4E5C-BB8E-878BA4CD7D16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDA2D04D-AA98-4611-A559-929E7338DFC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3888,29 +3888,29 @@
     </xf>
     <xf numFmtId="181" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="181" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4326,7 +4326,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>49.9</v>
+        <v>50.15</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4347,7 +4347,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>127685.31759999999</v>
+        <v>128325.0236</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4374,7 +4374,7 @@
         <v>1</v>
       </c>
       <c r="C16" s="50">
-        <v>8.9499999999999993</v>
+        <v>8.97755598</v>
       </c>
       <c r="D16" s="50"/>
       <c r="E16" s="5"/>
@@ -4384,13 +4384,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="358" t="s">
+      <c r="B18" s="356" t="s">
         <v>362</v>
       </c>
-      <c r="C18" s="358"/>
-      <c r="D18" s="358"/>
-      <c r="E18" s="358"/>
-      <c r="F18" s="358"/>
+      <c r="C18" s="356"/>
+      <c r="D18" s="356"/>
+      <c r="E18" s="356"/>
+      <c r="F18" s="356"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4466,14 +4466,14 @@
       </c>
       <c r="C26" s="304">
         <f>C132</f>
-        <v>30.533856751256884</v>
+        <v>32.734974170923991</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>402</v>
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>-0.11622199457788085</v>
+        <v>-9.8595701784031209E-2</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4505,7 +4505,7 @@
       </c>
       <c r="C29" s="310">
         <f>C149</f>
-        <v>13.459717474947846</v>
+        <v>15.243413565733329</v>
       </c>
       <c r="D29" s="310" t="str">
         <f>D149</f>
@@ -4515,7 +4515,7 @@
         <v>426</v>
       </c>
       <c r="F29" s="302">
-        <v>0.4</v>
+        <v>0.3674</v>
       </c>
     </row>
     <row r="30" spans="2:6">
@@ -4524,7 +4524,7 @@
       </c>
       <c r="C30" s="311">
         <f>C157</f>
-        <v>19.812807168472737</v>
+        <v>21.161970196851307</v>
       </c>
       <c r="D30" s="311" t="str">
         <f>D157</f>
@@ -4534,7 +4534,7 @@
         <v>439</v>
       </c>
       <c r="F30" s="312">
-        <v>0.22</v>
+        <v>0.21740000000000001</v>
       </c>
     </row>
     <row r="31" spans="2:6">
@@ -4543,7 +4543,7 @@
       </c>
       <c r="C31" s="311">
         <f>C165</f>
-        <v>28.021422889721528</v>
+        <v>30.179167378278677</v>
       </c>
       <c r="D31" s="311" t="str">
         <f>D165</f>
@@ -4553,7 +4553,7 @@
         <v>438</v>
       </c>
       <c r="F31" s="312">
-        <v>0.08</v>
+        <v>7.4999999999999997E-2</v>
       </c>
     </row>
     <row r="32" spans="2:6">
@@ -4562,7 +4562,7 @@
       </c>
       <c r="C32" s="311">
         <f>C173</f>
-        <v>25.258804060604444</v>
+        <v>27.015254809865393</v>
       </c>
       <c r="D32" s="311" t="str">
         <f>D173</f>
@@ -4572,7 +4572,7 @@
         <v>440</v>
       </c>
       <c r="F32" s="312">
-        <v>0.12</v>
+        <v>0.1174</v>
       </c>
     </row>
     <row r="33" spans="1:6">
@@ -4590,22 +4590,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="358" t="s">
+      <c r="B36" s="356" t="s">
         <v>363</v>
       </c>
-      <c r="C36" s="358"/>
-      <c r="D36" s="358"/>
-      <c r="E36" s="358"/>
-      <c r="F36" s="358"/>
+      <c r="C36" s="356"/>
+      <c r="D36" s="356"/>
+      <c r="E36" s="356"/>
+      <c r="F36" s="356"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="361" t="s">
+      <c r="B37" s="358" t="s">
         <v>341</v>
       </c>
-      <c r="C37" s="361"/>
-      <c r="D37" s="361"/>
-      <c r="E37" s="361"/>
-      <c r="F37" s="361"/>
+      <c r="C37" s="358"/>
+      <c r="D37" s="358"/>
+      <c r="E37" s="358"/>
+      <c r="F37" s="358"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4617,13 +4617,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="359" t="s">
+      <c r="B40" s="357" t="s">
         <v>231</v>
       </c>
-      <c r="C40" s="359"/>
-      <c r="D40" s="359"/>
-      <c r="E40" s="359"/>
-      <c r="F40" s="359"/>
+      <c r="C40" s="357"/>
+      <c r="D40" s="357"/>
+      <c r="E40" s="357"/>
+      <c r="F40" s="357"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4643,13 +4643,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="359" t="s">
+      <c r="B43" s="357" t="s">
         <v>233</v>
       </c>
-      <c r="C43" s="359"/>
-      <c r="D43" s="359"/>
-      <c r="E43" s="359"/>
-      <c r="F43" s="359"/>
+      <c r="C43" s="357"/>
+      <c r="D43" s="357"/>
+      <c r="E43" s="357"/>
+      <c r="F43" s="357"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4678,13 +4678,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="359" t="s">
+      <c r="B47" s="357" t="s">
         <v>236</v>
       </c>
-      <c r="C47" s="359"/>
-      <c r="D47" s="359"/>
-      <c r="E47" s="359"/>
-      <c r="F47" s="359"/>
+      <c r="C47" s="357"/>
+      <c r="D47" s="357"/>
+      <c r="E47" s="357"/>
+      <c r="F47" s="357"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4700,13 +4700,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="359" t="s">
+      <c r="B50" s="357" t="s">
         <v>240</v>
       </c>
-      <c r="C50" s="359"/>
-      <c r="D50" s="359"/>
-      <c r="E50" s="359"/>
-      <c r="F50" s="359"/>
+      <c r="C50" s="357"/>
+      <c r="D50" s="357"/>
+      <c r="E50" s="357"/>
+      <c r="F50" s="357"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4770,13 +4770,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="359" t="s">
+      <c r="B58" s="357" t="s">
         <v>241</v>
       </c>
-      <c r="C58" s="359"/>
-      <c r="D58" s="359"/>
-      <c r="E58" s="359"/>
-      <c r="F58" s="359"/>
+      <c r="C58" s="357"/>
+      <c r="D58" s="357"/>
+      <c r="E58" s="357"/>
+      <c r="F58" s="357"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4792,7 +4792,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="359" t="s">
+      <c r="B61" s="357" t="s">
         <v>340</v>
       </c>
       <c r="C61" s="360"/>
@@ -4814,22 +4814,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="358" t="s">
+      <c r="B64" s="356" t="s">
         <v>345</v>
       </c>
-      <c r="C64" s="358"/>
-      <c r="D64" s="358"/>
-      <c r="E64" s="358"/>
-      <c r="F64" s="358"/>
+      <c r="C64" s="356"/>
+      <c r="D64" s="356"/>
+      <c r="E64" s="356"/>
+      <c r="F64" s="356"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="358" t="s">
+      <c r="B65" s="356" t="s">
         <v>364</v>
       </c>
-      <c r="C65" s="358"/>
-      <c r="D65" s="358"/>
-      <c r="E65" s="358"/>
-      <c r="F65" s="358"/>
+      <c r="C65" s="356"/>
+      <c r="D65" s="356"/>
+      <c r="E65" s="356"/>
+      <c r="F65" s="356"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4863,7 +4863,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>4.8590180456311333E-2</v>
+        <v>4.8496813803793899E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4873,14 +4873,14 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>2.9414829659318638E-2</v>
+        <v>2.9358308688334996E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>450</v>
       </c>
       <c r="F70" s="315">
         <f>Normalized_FCF!C92</f>
-        <v>5.4180232091874609</v>
+        <v>5.4347046549072271</v>
       </c>
     </row>
     <row r="72" spans="1:6">
@@ -4964,22 +4964,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.6" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="358" t="s">
+      <c r="B80" s="356" t="s">
         <v>365</v>
       </c>
-      <c r="C80" s="358"/>
-      <c r="D80" s="358"/>
-      <c r="E80" s="358"/>
-      <c r="F80" s="358"/>
+      <c r="C80" s="356"/>
+      <c r="D80" s="356"/>
+      <c r="E80" s="356"/>
+      <c r="F80" s="356"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="361" t="s">
+      <c r="B81" s="358" t="s">
         <v>252</v>
       </c>
-      <c r="C81" s="361"/>
-      <c r="D81" s="361"/>
-      <c r="E81" s="361"/>
-      <c r="F81" s="361"/>
+      <c r="C81" s="358"/>
+      <c r="D81" s="358"/>
+      <c r="E81" s="358"/>
+      <c r="F81" s="358"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -4992,7 +4992,7 @@
       </c>
       <c r="C84" s="92">
         <f>F31</f>
-        <v>0.08</v>
+        <v>7.4999999999999997E-2</v>
       </c>
     </row>
     <row r="85" spans="1:6">
@@ -5010,7 +5010,7 @@
       </c>
       <c r="C86" s="236">
         <f>F31+C85</f>
-        <v>0.08</v>
+        <v>7.4999999999999997E-2</v>
       </c>
     </row>
     <row r="87" spans="1:6">
@@ -5023,22 +5023,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="358" t="s">
+      <c r="B89" s="356" t="s">
         <v>366</v>
       </c>
-      <c r="C89" s="358"/>
-      <c r="D89" s="358"/>
-      <c r="E89" s="358"/>
-      <c r="F89" s="358"/>
+      <c r="C89" s="356"/>
+      <c r="D89" s="356"/>
+      <c r="E89" s="356"/>
+      <c r="F89" s="356"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="358" t="s">
+      <c r="B90" s="356" t="s">
         <v>367</v>
       </c>
-      <c r="C90" s="358"/>
-      <c r="D90" s="358"/>
-      <c r="E90" s="358"/>
-      <c r="F90" s="358"/>
+      <c r="C90" s="356"/>
+      <c r="D90" s="356"/>
+      <c r="E90" s="356"/>
+      <c r="F90" s="356"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5054,7 +5054,7 @@
       </c>
       <c r="C93" s="223">
         <f>DCF!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>30.308125059624196</v>
+        <v>32.428202830136861</v>
       </c>
       <c r="D93" s="1" t="str">
         <f>Market_currency</f>
@@ -5075,13 +5075,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="358" t="s">
+      <c r="B97" s="356" t="s">
         <v>368</v>
       </c>
-      <c r="C97" s="358"/>
-      <c r="D97" s="358"/>
-      <c r="E97" s="358"/>
-      <c r="F97" s="358"/>
+      <c r="C97" s="356"/>
+      <c r="D97" s="356"/>
+      <c r="E97" s="356"/>
+      <c r="F97" s="356"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5094,13 +5094,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="358" t="s">
+      <c r="B101" s="356" t="s">
         <v>346</v>
       </c>
-      <c r="C101" s="358"/>
-      <c r="D101" s="358"/>
-      <c r="E101" s="358"/>
-      <c r="F101" s="358"/>
+      <c r="C101" s="356"/>
+      <c r="D101" s="356"/>
+      <c r="E101" s="356"/>
+      <c r="F101" s="356"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5121,7 +5121,7 @@
       </c>
       <c r="C103" s="223">
         <f>C102*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>3.0307574885963238</v>
+        <v>3.0400888285673417</v>
       </c>
       <c r="D103" s="1" t="str">
         <f>Market_currency</f>
@@ -5170,7 +5170,7 @@
       </c>
       <c r="C109" s="349">
         <f>DCF!C8</f>
-        <v>415406.42282180313</v>
+        <v>414442.7738145804</v>
       </c>
       <c r="D109" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5183,7 +5183,7 @@
       </c>
       <c r="C110" s="223">
         <f>C109*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>1.452967255370099</v>
+        <v>1.4540598346845557</v>
       </c>
       <c r="D110" s="1" t="str">
         <f>Market_currency</f>
@@ -5214,7 +5214,7 @@
       </c>
       <c r="C114" s="223">
         <f>C113*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>1.315974838441409E-2</v>
+        <v>1.3200265676401347E-2</v>
       </c>
       <c r="D114" s="1" t="str">
         <f>Market_currency</f>
@@ -5222,13 +5222,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="358" t="s">
+      <c r="B116" s="356" t="s">
         <v>369</v>
       </c>
-      <c r="C116" s="358"/>
-      <c r="D116" s="358"/>
-      <c r="E116" s="358"/>
-      <c r="F116" s="358"/>
+      <c r="C116" s="356"/>
+      <c r="D116" s="356"/>
+      <c r="E116" s="356"/>
+      <c r="F116" s="356"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5236,7 +5236,7 @@
       </c>
       <c r="C118" s="223">
         <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
-        <v>28.743494574782385</v>
+        <v>30.855374101930472</v>
       </c>
       <c r="D118" s="1" t="str">
         <f>Market_currency</f>
@@ -5249,7 +5249,7 @@
       </c>
       <c r="C119" s="223">
         <f>BS!D47</f>
-        <v>-5.8165293881095375</v>
+        <v>-5.8344377867115664</v>
       </c>
       <c r="D119" s="1" t="str">
         <f>Market_currency</f>
@@ -5267,13 +5267,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B123" s="359" t="s">
+      <c r="B123" s="357" t="s">
         <v>370</v>
       </c>
-      <c r="C123" s="359"/>
-      <c r="D123" s="359"/>
-      <c r="E123" s="359"/>
-      <c r="F123" s="359"/>
+      <c r="C123" s="357"/>
+      <c r="D123" s="357"/>
+      <c r="E123" s="357"/>
+      <c r="F123" s="357"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5307,7 +5307,7 @@
       </c>
       <c r="E126" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E74,DDM!E69),2)&amp;" "&amp;Market_currency</f>
-        <v>37.84 HKD</v>
+        <v>40.37 HKD</v>
       </c>
       <c r="F126" s="232">
         <f>DCF!F74</f>
@@ -5329,7 +5329,7 @@
       </c>
       <c r="E127" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E75,DDM!E70),2)&amp;" "&amp;Market_currency</f>
-        <v>31.24 HKD</v>
+        <v>33.48 HKD</v>
       </c>
       <c r="F127" s="221">
         <f>DCF!F75</f>
@@ -5351,7 +5351,7 @@
       </c>
       <c r="E128" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E76,DDM!E71),2)&amp;" "&amp;Market_currency</f>
-        <v>30.22 HKD</v>
+        <v>32.41 HKD</v>
       </c>
       <c r="F128" s="221">
         <f>DCF!F76</f>
@@ -5373,7 +5373,7 @@
       </c>
       <c r="E129" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E77,DDM!E72),2)&amp;" "&amp;Market_currency</f>
-        <v>29.23 HKD</v>
+        <v>31.37 HKD</v>
       </c>
       <c r="F129" s="221">
         <f>DCF!F77</f>
@@ -5395,7 +5395,7 @@
       </c>
       <c r="E130" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E78,DDM!E73),2)&amp;" "&amp;Market_currency</f>
-        <v>28.74 HKD</v>
+        <v>30.86 HKD</v>
       </c>
       <c r="F130" s="221">
         <f>DCF!F78</f>
@@ -5408,7 +5408,7 @@
       </c>
       <c r="C132" s="217">
         <f>Scenarios!C60</f>
-        <v>30.533856751256884</v>
+        <v>32.734974170923991</v>
       </c>
       <c r="D132" s="212" t="str">
         <f>Market_currency</f>
@@ -5416,13 +5416,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="362" t="s">
+      <c r="B134" s="361" t="s">
         <v>373</v>
       </c>
-      <c r="C134" s="362"/>
-      <c r="D134" s="362"/>
-      <c r="E134" s="362"/>
-      <c r="F134" s="362"/>
+      <c r="C134" s="361"/>
+      <c r="D134" s="361"/>
+      <c r="E134" s="361"/>
+      <c r="F134" s="361"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5435,22 +5435,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="363" t="s">
+      <c r="B138" s="359" t="s">
         <v>371</v>
       </c>
-      <c r="C138" s="363"/>
-      <c r="D138" s="363"/>
-      <c r="E138" s="363"/>
-      <c r="F138" s="363"/>
+      <c r="C138" s="359"/>
+      <c r="D138" s="359"/>
+      <c r="E138" s="359"/>
+      <c r="F138" s="359"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="358" t="s">
+      <c r="B139" s="356" t="s">
         <v>372</v>
       </c>
-      <c r="C139" s="358"/>
-      <c r="D139" s="358"/>
-      <c r="E139" s="358"/>
-      <c r="F139" s="358"/>
+      <c r="C139" s="356"/>
+      <c r="D139" s="356"/>
+      <c r="E139" s="356"/>
+      <c r="F139" s="356"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5472,7 +5472,7 @@
       </c>
       <c r="C142" s="224">
         <f>F29</f>
-        <v>0.4</v>
+        <v>0.3674</v>
       </c>
     </row>
     <row r="143" spans="1:6">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C143" s="213">
         <f>Scenarios!C77</f>
-        <v>1.4678</v>
+        <v>1.47231918072</v>
       </c>
       <c r="D143" s="212" t="str">
         <f>Market_currency</f>
@@ -5507,7 +5507,7 @@
       </c>
       <c r="C146" s="297">
         <f>F29</f>
-        <v>0.4</v>
+        <v>0.3674</v>
       </c>
     </row>
     <row r="147" spans="2:4">
@@ -5517,7 +5517,7 @@
       </c>
       <c r="C147" s="216">
         <f>Scenarios!C81</f>
-        <v>2.3322186588921276</v>
+        <v>2.440014683327854</v>
       </c>
     </row>
     <row r="148" spans="2:4">
@@ -5527,7 +5527,7 @@
       </c>
       <c r="C148" s="216">
         <f>Scenarios!C82</f>
-        <v>11.127498816055718</v>
+        <v>12.803398882405475</v>
       </c>
     </row>
     <row r="149" spans="2:4">
@@ -5536,7 +5536,7 @@
       </c>
       <c r="C149" s="215">
         <f>Scenarios!C83</f>
-        <v>13.459717474947846</v>
+        <v>15.243413565733329</v>
       </c>
       <c r="D149" s="300" t="str">
         <f>IF($D$11="","",C149*$E$25)</f>
@@ -5562,7 +5562,7 @@
       </c>
       <c r="C151" s="92">
         <f>Scenarios!F83</f>
-        <v>0.55918711531933174</v>
+        <v>0.53433861025395579</v>
       </c>
     </row>
     <row r="153" spans="2:4">
@@ -5576,7 +5576,7 @@
       </c>
       <c r="C154" s="297">
         <f>Scenarios!C90</f>
-        <v>0.22</v>
+        <v>0.21740000000000001</v>
       </c>
     </row>
     <row r="155" spans="2:4">
@@ -5586,7 +5586,7 @@
       </c>
       <c r="C155" s="216">
         <f>Scenarios!C91</f>
-        <v>2.9976019578731261</v>
+        <v>3.018844461140437</v>
       </c>
     </row>
     <row r="156" spans="2:4">
@@ -5596,7 +5596,7 @@
       </c>
       <c r="C156" s="216">
         <f>Scenarios!C92</f>
-        <v>16.815205210599611</v>
+        <v>18.143125735710871</v>
       </c>
     </row>
     <row r="157" spans="2:4">
@@ -5605,7 +5605,7 @@
       </c>
       <c r="C157" s="215">
         <f>Scenarios!C93</f>
-        <v>19.812807168472737</v>
+        <v>21.161970196851307</v>
       </c>
       <c r="D157" s="300" t="str">
         <f>IF($D$11="","",C157*$E$25)</f>
@@ -5631,7 +5631,7 @@
       </c>
       <c r="C159" s="92">
         <f>Scenarios!F93</f>
-        <v>0.35112005896021736</v>
+        <v>0.353536371027661</v>
       </c>
     </row>
     <row r="161" spans="2:4">
@@ -5645,7 +5645,7 @@
       </c>
       <c r="C162" s="92">
         <f>Scenarios!C96</f>
-        <v>0.08</v>
+        <v>7.4999999999999997E-2</v>
       </c>
     </row>
     <row r="163" spans="2:4">
@@ -5655,7 +5655,7 @@
       </c>
       <c r="C163" s="216">
         <f>Scenarios!C97</f>
-        <v>3.7826629578824384</v>
+        <v>3.8288039267695555</v>
       </c>
     </row>
     <row r="164" spans="2:4">
@@ -5665,7 +5665,7 @@
       </c>
       <c r="C164" s="216">
         <f>Scenarios!C98</f>
-        <v>24.238759931839088</v>
+        <v>26.350363451509121</v>
       </c>
     </row>
     <row r="165" spans="2:4">
@@ -5674,7 +5674,7 @@
       </c>
       <c r="C165" s="215">
         <f>Scenarios!C99</f>
-        <v>28.021422889721528</v>
+        <v>30.179167378278677</v>
       </c>
       <c r="D165" s="300" t="str">
         <f>IF($D$11="","",C165*$E$25)</f>
@@ -5700,7 +5700,7 @@
       </c>
       <c r="C167" s="92">
         <f>Scenarios!F99</f>
-        <v>8.2283541250711356E-2</v>
+        <v>7.807572351517067E-2</v>
       </c>
     </row>
     <row r="169" spans="2:4">
@@ -5714,7 +5714,7 @@
       </c>
       <c r="C170" s="92">
         <f>F32</f>
-        <v>0.12</v>
+        <v>0.1174</v>
       </c>
     </row>
     <row r="171" spans="2:4">
@@ -5724,7 +5724,7 @@
       </c>
       <c r="C171" s="216">
         <f>Scenarios!C103</f>
-        <v>3.5254079354956298</v>
+        <v>3.5521218577845026</v>
       </c>
     </row>
     <row r="172" spans="2:4">
@@ -5734,7 +5734,7 @@
       </c>
       <c r="C172" s="216">
         <f>Scenarios!C104</f>
-        <v>21.733396125108815</v>
+        <v>23.46313295208089</v>
       </c>
     </row>
     <row r="173" spans="2:4">
@@ -5743,7 +5743,7 @@
       </c>
       <c r="C173" s="215">
         <f>Scenarios!C105</f>
-        <v>25.258804060604444</v>
+        <v>27.015254809865393</v>
       </c>
       <c r="D173" s="300" t="str">
         <f>IF($D$11="","",C173*$E$25)</f>
@@ -5769,7 +5769,7 @@
       </c>
       <c r="C175" s="92">
         <f>Scenarios!F105</f>
-        <v>0.15545280182445731</v>
+        <v>0.15787677826395219</v>
       </c>
     </row>
     <row r="177" spans="1:6" ht="13.9">
@@ -5783,13 +5783,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="357" t="s">
+      <c r="B179" s="363" t="s">
         <v>379</v>
       </c>
-      <c r="C179" s="358"/>
-      <c r="D179" s="358"/>
-      <c r="E179" s="358"/>
-      <c r="F179" s="358"/>
+      <c r="C179" s="356"/>
+      <c r="D179" s="356"/>
+      <c r="E179" s="356"/>
+      <c r="F179" s="356"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5826,13 +5826,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="359" t="s">
+      <c r="B188" s="357" t="s">
         <v>384</v>
       </c>
-      <c r="C188" s="359"/>
-      <c r="D188" s="359"/>
-      <c r="E188" s="359"/>
-      <c r="F188" s="359"/>
+      <c r="C188" s="357"/>
+      <c r="D188" s="357"/>
+      <c r="E188" s="357"/>
+      <c r="F188" s="357"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5840,22 +5840,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="356" t="s">
+      <c r="B191" s="362" t="s">
         <v>385</v>
       </c>
-      <c r="C191" s="356"/>
-      <c r="D191" s="356"/>
-      <c r="E191" s="356"/>
-      <c r="F191" s="356"/>
+      <c r="C191" s="362"/>
+      <c r="D191" s="362"/>
+      <c r="E191" s="362"/>
+      <c r="F191" s="362"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="356" t="s">
+      <c r="B192" s="362" t="s">
         <v>386</v>
       </c>
-      <c r="C192" s="356"/>
-      <c r="D192" s="356"/>
-      <c r="E192" s="356"/>
-      <c r="F192" s="356"/>
+      <c r="C192" s="362"/>
+      <c r="D192" s="362"/>
+      <c r="E192" s="362"/>
+      <c r="F192" s="362"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5879,6 +5879,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5895,17 +5906,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -6478,15 +6478,15 @@
       </c>
       <c r="C25" s="39">
         <f>0.164*Exchange_Rate</f>
-        <v>1.4678</v>
+        <v>1.47231918072</v>
       </c>
       <c r="D25" s="39">
         <f>0.137*Exchange_Rate</f>
-        <v>1.2261500000000001</v>
+        <v>1.2299251692600002</v>
       </c>
       <c r="E25" s="39">
         <f>0.11*Exchange_Rate</f>
-        <v>0.98449999999999993</v>
+        <v>0.9875311578</v>
       </c>
       <c r="F25" s="39"/>
       <c r="G25" s="39"/>
@@ -7860,15 +7860,15 @@
       </c>
       <c r="C65" s="73">
         <f>IF(C$4="","",C25)</f>
-        <v>1.4678</v>
+        <v>1.47231918072</v>
       </c>
       <c r="D65" s="73">
         <f t="shared" ref="D65:M65" si="33">IF(D$4="","",D25)</f>
-        <v>1.2261500000000001</v>
+        <v>1.2299251692600002</v>
       </c>
       <c r="E65" s="73">
         <f t="shared" si="33"/>
-        <v>0.98449999999999993</v>
+        <v>0.9875311578</v>
       </c>
       <c r="F65" s="73">
         <f t="shared" si="33"/>
@@ -9210,11 +9210,11 @@
       </c>
       <c r="C47" s="147">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>15.387661187326676</v>
+        <v>15.435037956480281</v>
       </c>
       <c r="D47" s="147">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>-5.8165293881095375</v>
+        <v>-5.8344377867115664</v>
       </c>
       <c r="F47" s="253"/>
     </row>
@@ -9405,7 +9405,7 @@
       </c>
       <c r="D66" s="76">
         <f>C66-D75</f>
-        <v>415406.42282180313</v>
+        <v>414442.7738145804</v>
       </c>
       <c r="F66" s="5" t="s">
         <v>226</v>
@@ -9472,11 +9472,11 @@
       </c>
       <c r="C73" s="349">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35-Normalized_FCF!G91)/12</f>
-        <v>-645813.73893333331</v>
+        <v>-646777.38794055616</v>
       </c>
       <c r="D73" s="349">
         <f>(Normalized_FCF!C25+Normalized_FCF!C35-Normalized_FCF!C91)/12</f>
-        <v>-596156.57717819687</v>
+        <v>-597120.2261854196</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>353</v>
@@ -9488,11 +9488,11 @@
       </c>
       <c r="C74" s="258">
         <f>-$C$66/C73</f>
-        <v>1.5663386190432573</v>
+        <v>1.5640048938955338</v>
       </c>
       <c r="D74" s="258">
         <f>-$C$66/D73</f>
-        <v>1.6968075816391341</v>
+        <v>1.6940692270000017</v>
       </c>
       <c r="F74" s="253" t="s">
         <v>320</v>
@@ -9505,7 +9505,7 @@
       <c r="C75" s="320"/>
       <c r="D75" s="321">
         <f>MAX(-D73*D76,G5)</f>
-        <v>596156.57717819687</v>
+        <v>597120.2261854196</v>
       </c>
       <c r="F75" s="253" t="s">
         <v>354</v>
@@ -9620,11 +9620,11 @@
       </c>
       <c r="C86" s="76">
         <f>-DCF!C7*Exchange_Rate</f>
-        <v>-7755174.9999999991</v>
+        <v>-7779052.25667</v>
       </c>
       <c r="D86" s="223">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>-3.0307574885963238</v>
+        <v>-3.0400888285673417</v>
       </c>
       <c r="E86" s="240" t="str">
         <f>Market_currency</f>
@@ -9637,11 +9637,11 @@
       </c>
       <c r="C87" s="76">
         <f>DCF!C8*Exchange_Rate</f>
-        <v>3717887.4842551379</v>
+        <v>3720683.2024268736</v>
       </c>
       <c r="D87" s="223">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>1.452967255370099</v>
+        <v>1.4540598346845557</v>
       </c>
       <c r="E87" s="240" t="str">
         <f>Market_currency</f>
@@ -9654,11 +9654,11 @@
       </c>
       <c r="C88" s="76">
         <f>DCF!C9*Exchange_Rate</f>
-        <v>33673.479999999996</v>
+        <v>33777.156619152003</v>
       </c>
       <c r="D88" s="223">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>1.3159748384414088E-2</v>
+        <v>1.3200265676401347E-2</v>
       </c>
       <c r="E88" s="240" t="str">
         <f>Market_currency</f>
@@ -9671,11 +9671,11 @@
       </c>
       <c r="C89" s="180">
         <f>SUM(C86:C88)</f>
-        <v>-4003614.0357448612</v>
+        <v>-4024591.8976239744</v>
       </c>
       <c r="D89" s="242">
         <f>SUM(D86:D88)</f>
-        <v>-1.5646304848418107</v>
+        <v>-1.5728287282063846</v>
       </c>
       <c r="E89" s="240" t="str">
         <f>Market_currency</f>
@@ -13187,20 +13187,20 @@
       </c>
       <c r="C90" s="113">
         <f>G90</f>
-        <v>1.4678</v>
+        <v>1.47231918072</v>
       </c>
       <c r="E90" s="268"/>
       <c r="G90" s="112">
         <f>Data!C65</f>
-        <v>1.4678</v>
+        <v>1.47231918072</v>
       </c>
       <c r="H90" s="112">
         <f>Data!D65</f>
-        <v>1.2261500000000001</v>
+        <v>1.2299251692600002</v>
       </c>
       <c r="I90" s="112">
         <f>Data!E65</f>
-        <v>0.98449999999999993</v>
+        <v>0.9875311578</v>
       </c>
       <c r="J90" s="112">
         <f>Data!F65</f>
@@ -13243,20 +13243,20 @@
       </c>
       <c r="C91" s="74">
         <f>C90*Common_Shares/scaling_factor</f>
-        <v>3755841.8671999997</v>
+        <v>3767405.655286673</v>
       </c>
       <c r="E91" s="268"/>
       <c r="G91" s="74">
         <f t="shared" ref="G91:Q91" si="37">IF(G$4="","",G90*Common_Shares/scaling_factor)</f>
-        <v>3755841.8671999997</v>
+        <v>3767405.655286673</v>
       </c>
       <c r="H91" s="74">
         <f t="shared" si="37"/>
-        <v>3137502.0476000002</v>
+        <v>3147162.0413065506</v>
       </c>
       <c r="I91" s="74">
         <f t="shared" si="37"/>
-        <v>2519162.2280000001</v>
+        <v>2526918.4273264268</v>
       </c>
       <c r="J91" s="74">
         <f t="shared" si="37"/>
@@ -13298,20 +13298,20 @@
       </c>
       <c r="C92" s="23">
         <f>C90/(C19*scaling_factor/Common_Shares)</f>
-        <v>5.4180232091874609</v>
+        <v>5.4347046549072271</v>
       </c>
       <c r="E92" s="268"/>
       <c r="G92" s="170">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",G90/(G19*scaling_factor/Common_Shares))</f>
-        <v>3.767596769119653</v>
+        <v>3.7791967491440022</v>
       </c>
       <c r="H92" s="170">
         <f t="shared" si="38"/>
-        <v>3.8214917481410211</v>
+        <v>3.833257664362467</v>
       </c>
       <c r="I92" s="170">
         <f t="shared" si="38"/>
-        <v>3.7496014396113404</v>
+        <v>3.7611460141675304</v>
       </c>
       <c r="J92" s="170">
         <f t="shared" si="38"/>
@@ -13353,20 +13353,20 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>2.9414829659318638E-2</v>
+        <v>2.9358308688334996E-2</v>
       </c>
       <c r="E93" s="268"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>2.9414829659318638E-2</v>
+        <v>2.9358308688334996E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
-        <v>2.4572144288577156E-2</v>
+        <v>2.45249285994018E-2</v>
       </c>
       <c r="I93" s="23">
         <f t="shared" si="39"/>
-        <v>1.972945891783567E-2</v>
+        <v>1.9691548510468594E-2</v>
       </c>
       <c r="J93" s="23">
         <f t="shared" si="39"/>
@@ -14495,38 +14495,38 @@
       </c>
       <c r="C124" s="177">
         <f>C16*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>2.4246500047699358</v>
+        <v>2.4321152122602645</v>
       </c>
       <c r="D124" s="27"/>
       <c r="E124" s="265"/>
       <c r="F124" s="27"/>
       <c r="G124" s="177">
         <f t="shared" ref="G124:Q124" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>3.4867876805907714</v>
+        <v>3.4975230830031299</v>
       </c>
       <c r="H124" s="177">
         <f t="shared" si="49"/>
-        <v>2.8716645810731802</v>
+        <v>2.8805060930019804</v>
       </c>
       <c r="I124" s="177">
         <f t="shared" si="49"/>
-        <v>2.3499230896693168</v>
+        <v>2.3571582219218832</v>
       </c>
       <c r="J124" s="177">
         <f t="shared" si="49"/>
-        <v>1.260452340606466</v>
+        <v>1.2643331226722432</v>
       </c>
       <c r="K124" s="177">
         <f t="shared" si="49"/>
-        <v>6.0888739905519094</v>
+        <v>6.1076209056252253</v>
       </c>
       <c r="L124" s="177">
         <f t="shared" si="49"/>
-        <v>8.1868577127617996</v>
+        <v>8.2120640688953994</v>
       </c>
       <c r="M124" s="177">
         <f t="shared" si="49"/>
-        <v>7.5742669484106759</v>
+        <v>7.5975872108179461</v>
       </c>
       <c r="N124" s="177" t="str">
         <f t="shared" si="49"/>
@@ -14552,38 +14552,38 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>4.8590180456311333E-2</v>
+        <v>4.8496813803793899E-2</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="265"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>6.9875504621057544E-2</v>
+        <v>6.974123794622393E-2</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>5.7548388398260125E-2</v>
+        <v>5.74378084347354E-2</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>4.7092647087561459E-2</v>
+        <v>4.7002157964544031E-2</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>2.5259565944017355E-2</v>
+        <v>2.5211029365348817E-2</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>0.12202152285675169</v>
+        <v>0.12178705694167948</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>0.16406528482488578</v>
+        <v>0.16375003128405582</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>0.15178891680181716</v>
+        <v>0.15149725245898199</v>
       </c>
       <c r="N125" s="77" t="str">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
@@ -14609,31 +14609,31 @@
       <c r="C126" s="169"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.605301344373208E-3</v>
+        <v>6.5723736208219957E-3</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.2738405061538568E-3</v>
+        <v>5.2475501746176963E-3</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.6743065594254352E-3</v>
+        <v>3.6559899763774521E-3</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.3111741079304797E-3</v>
+        <v>2.2996528013106868E-3</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-4.2579680281110095E-4</v>
+        <v>-4.2367418664554214E-4</v>
       </c>
       <c r="L126" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.0184309742438235E-3</v>
+        <v>2.0083690052794972E-3</v>
       </c>
       <c r="M126" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.6304302163555882E-3</v>
+        <v>1.6223024485771456E-3</v>
       </c>
       <c r="N126" s="23" t="str">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -15416,7 +15416,7 @@
       </c>
       <c r="C5" s="206">
         <f>Equity_Cost</f>
-        <v>0.08</v>
+        <v>7.4999999999999997E-2</v>
       </c>
       <c r="E5" s="148"/>
       <c r="H5" s="120"/>
@@ -15427,7 +15427,7 @@
       </c>
       <c r="C6" s="347">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
-        <v>8665157.2958176341</v>
+        <v>9242834.4488721434</v>
       </c>
       <c r="D6" t="str">
         <f>Reporting_currency</f>
@@ -15461,7 +15461,7 @@
       </c>
       <c r="C8" s="338">
         <f>BS!D66</f>
-        <v>415406.42282180313</v>
+        <v>414442.7738145804</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
@@ -15493,7 +15493,7 @@
       </c>
       <c r="C10" s="347">
         <f>C6-C7+C8+C9</f>
-        <v>8217826.1186394375</v>
+        <v>8794539.6226867232</v>
       </c>
       <c r="D10" t="str">
         <f>Reporting_currency</f>
@@ -15507,7 +15507,7 @@
       </c>
       <c r="C11" s="208">
         <f>Exchange_Rate</f>
-        <v>8.9499999999999993</v>
+        <v>8.97755598</v>
       </c>
       <c r="D11" t="str">
         <f>Thesis!C15</f>
@@ -15521,7 +15521,7 @@
       </c>
       <c r="C12" s="111">
         <f>(C10*scaling_factor)/Common_Shares*Exchange_Rate</f>
-        <v>28.743494574782385</v>
+        <v>30.855374101930472</v>
       </c>
       <c r="D12" t="str">
         <f>Market_currency</f>
@@ -15574,7 +15574,7 @@
       </c>
       <c r="C18" s="140">
         <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>29.908102371508068</v>
+        <v>32.079930956152829</v>
       </c>
       <c r="D18" t="str">
         <f>Market_currency</f>
@@ -15617,11 +15617,11 @@
       </c>
       <c r="E21" s="124">
         <f t="shared" ref="E21:E50" si="0">IF($C$17&lt;B21,0,1/(1+Equity_Cost)^B21)</f>
-        <v>0.92592592592592582</v>
+        <v>0.93023255813953487</v>
       </c>
       <c r="F21" s="125">
         <f t="shared" ref="F21:F51" si="1">C21*E21</f>
-        <v>657109.44282958179</v>
+        <v>660165.76581948681</v>
       </c>
       <c r="H21" s="120"/>
     </row>
@@ -15639,11 +15639,11 @@
       </c>
       <c r="E22" s="124">
         <f t="shared" si="0"/>
-        <v>0.85733882030178321</v>
+        <v>0.86533261222282321</v>
       </c>
       <c r="F22" s="125">
         <f t="shared" si="1"/>
-        <v>622886.58635229641</v>
+        <v>628694.35528075171</v>
       </c>
       <c r="H22" s="120"/>
     </row>
@@ -15661,11 +15661,11 @@
       </c>
       <c r="E23" s="124">
         <f t="shared" si="0"/>
-        <v>0.79383224102016958</v>
+        <v>0.80496056950960304</v>
       </c>
       <c r="F23" s="125">
         <f t="shared" si="1"/>
-        <v>590446.08731675113</v>
+        <v>598723.2492603343</v>
       </c>
       <c r="G23" s="338"/>
       <c r="H23" s="339"/>
@@ -15693,11 +15693,11 @@
       </c>
       <c r="E24" s="124">
         <f t="shared" si="0"/>
-        <v>0.73502985279645328</v>
+        <v>0.7488005297763749</v>
       </c>
       <c r="F24" s="125">
         <f t="shared" si="1"/>
-        <v>559695.11892889242</v>
+        <v>570180.92526816635</v>
       </c>
       <c r="G24" s="338"/>
       <c r="H24" s="339"/>
@@ -15725,11 +15725,11 @@
       </c>
       <c r="E25" s="124">
         <f t="shared" si="0"/>
-        <v>0.68058319703375303</v>
+        <v>0.69655863235011617</v>
       </c>
       <c r="F25" s="125">
         <f t="shared" si="1"/>
-        <v>530545.68889839423</v>
+        <v>542999.27043304278</v>
       </c>
       <c r="G25" s="338"/>
       <c r="H25" s="339"/>
@@ -16369,7 +16369,7 @@
       </c>
       <c r="C51" s="123">
         <f>C$21*(1+Terminal_Growth)^$C$17/Equity_Cost</f>
-        <v>8870977.4781993553</v>
+        <v>9462375.976745978</v>
       </c>
       <c r="D51" s="139">
         <f>Terminal_Growth</f>
@@ -16377,11 +16377,11 @@
       </c>
       <c r="E51" s="124">
         <f>1/(1+Equity_Cost)^C17</f>
-        <v>0.68058319703375303</v>
+        <v>0.69655863235011617</v>
       </c>
       <c r="F51" s="125">
         <f t="shared" si="1"/>
-        <v>6037438.2129273377</v>
+        <v>6591099.6691447729</v>
       </c>
       <c r="H51" s="120"/>
     </row>
@@ -16392,7 +16392,7 @@
       </c>
       <c r="F52" s="137">
         <f>SUM(F21:F51)</f>
-        <v>8998121.1372532547</v>
+        <v>9591863.2352065556</v>
       </c>
       <c r="H52" s="120"/>
     </row>
@@ -16413,7 +16413,7 @@
     <row r="55" spans="1:17" ht="13.15">
       <c r="A55" s="133">
         <f>F52</f>
-        <v>8998121.1372532547</v>
+        <v>9591863.2352065556</v>
       </c>
       <c r="B55" s="131">
         <f>C78</f>
@@ -16443,19 +16443,19 @@
       </c>
       <c r="B56" s="123">
         <f t="dataTable" ref="B56:F61" dt2D="1" dtr="1" r1="C16" r2="C17"/>
-        <v>8665157.2958176322</v>
+        <v>9242834.4488721434</v>
       </c>
       <c r="C56" s="123">
-        <v>8803924.8142956235</v>
+        <v>9388337.6216057334</v>
       </c>
       <c r="D56" s="123">
-        <v>9087649.620388709</v>
+        <v>9685655.5689548738</v>
       </c>
       <c r="E56" s="123">
-        <v>9379930.1403924413</v>
+        <v>9991698.1758301258</v>
       </c>
       <c r="F56" s="123">
-        <v>9835212.2099300027</v>
+        <v>10467957.777461857</v>
       </c>
       <c r="H56" s="120"/>
     </row>
@@ -16464,19 +16464,19 @@
         <v>10</v>
       </c>
       <c r="B57" s="123">
-        <v>8665157.2958176304</v>
+        <v>9242834.4488721453</v>
       </c>
       <c r="C57" s="123">
-        <v>8938252.6718316022</v>
+        <v>9527843.4073876105</v>
       </c>
       <c r="D57" s="123">
-        <v>9524916.8791843541</v>
+        <v>10139820.387874126</v>
       </c>
       <c r="E57" s="123">
-        <v>10170916.302175496</v>
+        <v>10813328.899216197</v>
       </c>
       <c r="F57" s="123">
-        <v>11266861.823918507</v>
+        <v>11955289.404270325</v>
       </c>
       <c r="H57" s="120"/>
     </row>
@@ -16485,19 +16485,19 @@
         <v>15</v>
       </c>
       <c r="B58" s="123">
-        <v>8665157.2958176285</v>
+        <v>9242834.4488721453</v>
       </c>
       <c r="C58" s="341">
-        <v>9100387.5042157359</v>
+        <v>9700083.0005997624</v>
       </c>
       <c r="D58" s="123">
-        <v>10080232.297878651</v>
+        <v>10729802.441241121</v>
       </c>
       <c r="E58" s="123">
-        <v>11229889.3697685</v>
+        <v>11938525.744288776</v>
       </c>
       <c r="F58" s="123">
-        <v>13348337.231490824</v>
+        <v>14167289.593852498</v>
       </c>
       <c r="G58" s="338"/>
       <c r="H58" s="339"/>
@@ -16516,19 +16516,19 @@
         <v>20</v>
       </c>
       <c r="B59" s="123">
-        <v>8665157.2958176285</v>
+        <v>9242834.4488721471</v>
       </c>
       <c r="C59" s="341">
-        <v>9261315.1332998965</v>
+        <v>9875012.7852182947</v>
       </c>
       <c r="D59" s="123">
-        <v>10661506.149837431</v>
+        <v>11361716.105030598</v>
       </c>
       <c r="E59" s="123">
-        <v>12402845.790754531</v>
+        <v>13213806.924166916</v>
       </c>
       <c r="F59" s="123">
-        <v>15872073.155175414</v>
+        <v>16911668.040718824</v>
       </c>
       <c r="G59" s="338"/>
       <c r="H59" s="339"/>
@@ -16547,19 +16547,19 @@
         <v>25</v>
       </c>
       <c r="B60" s="123">
-        <v>8665157.2958176285</v>
+        <v>9242834.4488721471</v>
       </c>
       <c r="C60" s="341">
-        <v>9407020.6282360852</v>
+        <v>10037093.509732543</v>
       </c>
       <c r="D60" s="123">
-        <v>11217539.515536647</v>
+        <v>11980303.976276074</v>
       </c>
       <c r="E60" s="123">
-        <v>13593960.545009606</v>
+        <v>14539074.838875804</v>
       </c>
       <c r="F60" s="123">
-        <v>18696804.154837489</v>
+        <v>20055131.228334628</v>
       </c>
       <c r="G60" s="338"/>
       <c r="H60" s="339"/>
@@ -16578,19 +16578,19 @@
         <v>30</v>
       </c>
       <c r="B61" s="123">
-        <v>8665157.2958176285</v>
+        <v>9242834.4488721453</v>
       </c>
       <c r="C61" s="341">
-        <v>9532065.497171931</v>
+        <v>10179445.594374567</v>
       </c>
       <c r="D61" s="123">
-        <v>11722541.476329962</v>
+        <v>12555263.654819999</v>
       </c>
       <c r="E61" s="123">
-        <v>14745823.166404199</v>
+        <v>15850661.065849466</v>
       </c>
       <c r="F61" s="123">
-        <v>21726387.345599752</v>
+        <v>23505495.572357047</v>
       </c>
       <c r="G61" s="338"/>
       <c r="H61" s="339"/>
@@ -16670,23 +16670,23 @@
       </c>
       <c r="B65" s="124">
         <f>C12</f>
-        <v>28.743494574782385</v>
+        <v>30.855374101930472</v>
       </c>
       <c r="C65" s="124">
         <f>C12</f>
-        <v>28.743494574782385</v>
+        <v>30.855374101930472</v>
       </c>
       <c r="D65" s="124">
         <f>C12</f>
-        <v>28.743494574782385</v>
+        <v>30.855374101930472</v>
       </c>
       <c r="E65" s="141">
         <f>C12</f>
-        <v>28.743494574782385</v>
+        <v>30.855374101930472</v>
       </c>
       <c r="F65" s="124">
         <f>C12</f>
-        <v>28.743494574782385</v>
+        <v>30.855374101930472</v>
       </c>
       <c r="H65" s="120"/>
     </row>
@@ -16697,23 +16697,23 @@
       </c>
       <c r="B66" s="124">
         <f t="shared" ref="B66:F71" si="4">(B56-$C$7+$C$8+$C$9)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>28.743494574782378</v>
+        <v>30.855374101930472</v>
       </c>
       <c r="C66" s="124">
         <f t="shared" si="4"/>
-        <v>29.228861794402807</v>
+        <v>31.365867546764274</v>
       </c>
       <c r="D66" s="124">
         <f t="shared" si="4"/>
-        <v>30.221246192287584</v>
+        <v>32.408998499180548</v>
       </c>
       <c r="E66" s="124">
         <f t="shared" si="4"/>
-        <v>31.243555915048276</v>
+        <v>33.482739653510706</v>
       </c>
       <c r="F66" s="124">
         <f t="shared" si="4"/>
-        <v>32.83599624011994</v>
+        <v>35.153681943664836</v>
       </c>
       <c r="H66" s="120"/>
     </row>
@@ -16724,23 +16724,23 @@
       </c>
       <c r="B67" s="124">
         <f t="shared" si="4"/>
-        <v>28.743494574782375</v>
+        <v>30.855374101930487</v>
       </c>
       <c r="C67" s="124">
         <f t="shared" si="4"/>
-        <v>29.698700409699136</v>
+        <v>31.85531934235112</v>
       </c>
       <c r="D67" s="124">
         <f t="shared" si="4"/>
-        <v>31.750676104708692</v>
+        <v>34.002421917904989</v>
       </c>
       <c r="E67" s="124">
         <f t="shared" si="4"/>
-        <v>34.010188613490342</v>
+        <v>36.365405993237999</v>
       </c>
       <c r="F67" s="124">
         <f t="shared" si="4"/>
-        <v>37.84347781962564</v>
+        <v>40.371939604409576</v>
       </c>
       <c r="H67" s="120"/>
     </row>
@@ -16751,23 +16751,23 @@
       </c>
       <c r="B68" s="124">
         <f t="shared" si="4"/>
-        <v>28.743494574782368</v>
+        <v>30.855374101930487</v>
       </c>
       <c r="C68" s="124">
         <f t="shared" si="4"/>
-        <v>30.265799494996905</v>
+        <v>32.459616703183478</v>
       </c>
       <c r="D68" s="124">
         <f t="shared" si="4"/>
-        <v>33.693003125759745</v>
+        <v>36.072355962332246</v>
       </c>
       <c r="E68" s="124">
         <f t="shared" si="4"/>
-        <v>37.714159248030818</v>
+        <v>40.313124814524045</v>
       </c>
       <c r="F68" s="124">
         <f t="shared" si="4"/>
-        <v>45.123855406271794</v>
+        <v>48.132674820956154</v>
       </c>
       <c r="H68" s="120"/>
     </row>
@@ -16778,23 +16778,23 @@
       </c>
       <c r="B69" s="124">
         <f t="shared" si="4"/>
-        <v>28.743494574782368</v>
+        <v>30.855374101930487</v>
       </c>
       <c r="C69" s="124">
         <f t="shared" si="4"/>
-        <v>30.828676144701319</v>
+        <v>33.073352518535465</v>
       </c>
       <c r="D69" s="124">
         <f t="shared" si="4"/>
-        <v>35.726124971979374</v>
+        <v>38.289405783342573</v>
       </c>
       <c r="E69" s="124">
         <f t="shared" si="4"/>
-        <v>41.816809515429036</v>
+        <v>44.787409948084012</v>
       </c>
       <c r="F69" s="124">
         <f t="shared" si="4"/>
-        <v>53.951127823982851</v>
+        <v>57.761242919835908</v>
       </c>
       <c r="H69" s="120"/>
     </row>
@@ -16805,23 +16805,23 @@
       </c>
       <c r="B70" s="124">
         <f t="shared" si="4"/>
-        <v>28.743494574782368</v>
+        <v>30.855374101930487</v>
       </c>
       <c r="C70" s="124">
         <f t="shared" si="4"/>
-        <v>31.338310328091382</v>
+        <v>33.6420077983068</v>
       </c>
       <c r="D70" s="124">
         <f t="shared" si="4"/>
-        <v>37.670963156632943</v>
+        <v>40.459702467544105</v>
       </c>
       <c r="E70" s="124">
         <f t="shared" si="4"/>
-        <v>45.982972194293588</v>
+        <v>49.437072016595536</v>
       </c>
       <c r="F70" s="124">
         <f t="shared" si="4"/>
-        <v>63.831190871295036</v>
+        <v>68.789987662690478</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="13.15">
@@ -16831,23 +16831,23 @@
       </c>
       <c r="B71" s="124">
         <f t="shared" si="4"/>
-        <v>28.743494574782368</v>
+        <v>30.855374101930487</v>
       </c>
       <c r="C71" s="124">
         <f t="shared" si="4"/>
-        <v>31.775679829462252</v>
+        <v>34.141445746654746</v>
       </c>
       <c r="D71" s="124">
         <f t="shared" si="4"/>
-        <v>39.437308770516573</v>
+        <v>42.476930967968869</v>
       </c>
       <c r="E71" s="124">
         <f t="shared" si="4"/>
-        <v>50.011842668183782</v>
+        <v>54.038732300871835</v>
       </c>
       <c r="F71" s="124">
         <f t="shared" si="4"/>
-        <v>74.427765531108392</v>
+        <v>80.895485754726991</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="13.15">
@@ -16882,7 +16882,7 @@
       </c>
       <c r="E74" s="135">
         <f>INDEX(B$65:F$71, MATCH(D74, A$65:A$71, 0), MATCH(C74, B$64:F$64, 0))</f>
-        <v>37.84347781962564</v>
+        <v>40.371939604409576</v>
       </c>
       <c r="F74" s="142">
         <f>Scenarios!C58</f>
@@ -16904,7 +16904,7 @@
       </c>
       <c r="E75" s="135">
         <f>INDEX(B$65:F$71, MATCH(D75, A$65:A$71, 0), MATCH(C75, B$64:F$64, 0))</f>
-        <v>31.243555915048276</v>
+        <v>33.482739653510706</v>
       </c>
       <c r="F75" s="142">
         <f>Scenarios!C40*(1-F$74-F$78)</f>
@@ -16927,7 +16927,7 @@
       </c>
       <c r="E76" s="135">
         <f>INDEX(B$65:F$71, MATCH(D76, A$65:A$71, 0), MATCH(C76, B$64:F$64, 0))</f>
-        <v>30.221246192287584</v>
+        <v>32.408998499180548</v>
       </c>
       <c r="F76" s="142">
         <f>Scenarios!C28*(1-F$74-F$78)</f>
@@ -16950,7 +16950,7 @@
       </c>
       <c r="E77" s="135">
         <f>INDEX(B$65:F$71, MATCH(D77, A$65:A$71, 0), MATCH(C77, B$64:F$64, 0))</f>
-        <v>29.228861794402807</v>
+        <v>31.365867546764274</v>
       </c>
       <c r="F77" s="142">
         <f>Scenarios!C34*(1-F$74-F$78)</f>
@@ -16973,7 +16973,7 @@
       </c>
       <c r="E78" s="135">
         <f>INDEX(B$65:F$71, MATCH(D78, A$65:A$71, 0), MATCH(C78, B$64:F$64, 0))</f>
-        <v>28.743494574782375</v>
+        <v>30.855374101930487</v>
       </c>
       <c r="F78" s="142">
         <f>Scenarios!C52</f>
@@ -17155,7 +17155,7 @@
       </c>
       <c r="C4" s="114">
         <f>Normalized_FCF!C91</f>
-        <v>3755841.8671999997</v>
+        <v>3767405.655286673</v>
       </c>
       <c r="D4" t="str">
         <f>Market_currency</f>
@@ -17176,7 +17176,7 @@
       </c>
       <c r="C5" s="206">
         <f>Equity_Cost</f>
-        <v>0.08</v>
+        <v>7.4999999999999997E-2</v>
       </c>
       <c r="E5" s="148"/>
       <c r="H5" s="120"/>
@@ -17187,7 +17187,7 @@
       </c>
       <c r="C6" s="319">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
-        <v>46948023.339999996</v>
+        <v>50232075.40382231</v>
       </c>
       <c r="D6" t="str">
         <f>Reporting_currency</f>
@@ -17203,7 +17203,7 @@
       </c>
       <c r="C7" s="111">
         <f>(C6*scaling_factor)/Common_Shares*Exchange_Rate</f>
-        <v>164.21012499999995</v>
+        <v>176.2377048712205</v>
       </c>
       <c r="D7" t="str">
         <f>Market_currency</f>
@@ -17256,7 +17256,7 @@
       </c>
       <c r="C13" s="140">
         <f>F47/Common_Shares*scaling_factor</f>
-        <v>19.052513639358704</v>
+        <v>20.372227153415224</v>
       </c>
       <c r="D13" t="str">
         <f>Market_currency</f>
@@ -17291,7 +17291,7 @@
       </c>
       <c r="C16" s="123">
         <f>C4*(1+D16)</f>
-        <v>3845052.9492050684</v>
+        <v>3856891.4075477761</v>
       </c>
       <c r="D16" s="138">
         <f>IF($C$12&lt;B16,0,DDM!$C$11)</f>
@@ -17299,11 +17299,11 @@
       </c>
       <c r="E16" s="124">
         <f t="shared" ref="E16:E45" si="0">IF($C$12&lt;B16,0,1/(1+Equity_Cost)^B16)</f>
-        <v>0.92592592592592582</v>
+        <v>0.93023255813953487</v>
       </c>
       <c r="F16" s="125">
         <f t="shared" ref="F16:F46" si="1">C16*E16</f>
-        <v>3560234.2122269147</v>
+        <v>3587805.9605095591</v>
       </c>
       <c r="H16" s="120"/>
     </row>
@@ -17313,7 +17313,7 @@
       </c>
       <c r="C17" s="123">
         <f t="shared" ref="C17:C45" si="2">IF(ROW()-ROW($C$16)&lt;$C$12, $C$16*(1+D17)^(ROW()-ROW($C$16)), 0)</f>
-        <v>3936383.0280779279</v>
+        <v>3948502.6808146937</v>
       </c>
       <c r="D17" s="138">
         <f>IF($C$12&lt;B17,0,DDM!$C$11)</f>
@@ -17321,11 +17321,11 @@
       </c>
       <c r="E17" s="124">
         <f t="shared" si="0"/>
-        <v>0.85733882030178321</v>
+        <v>0.86533261222282321</v>
       </c>
       <c r="F17" s="125">
         <f t="shared" si="1"/>
-        <v>3374813.9815482921</v>
+        <v>3416768.1391581991</v>
       </c>
       <c r="H17" s="120"/>
     </row>
@@ -17335,7 +17335,7 @@
       </c>
       <c r="C18" s="123">
         <f t="shared" si="2"/>
-        <v>4029882.4355444671</v>
+        <v>4042289.9617786808</v>
       </c>
       <c r="D18" s="138">
         <f>IF($C$12&lt;B18,0,DDM!$C$11)</f>
@@ -17343,11 +17343,11 @@
       </c>
       <c r="E18" s="124">
         <f t="shared" si="0"/>
-        <v>0.79383224102016958</v>
+        <v>0.80496056950960304</v>
       </c>
       <c r="F18" s="125">
         <f t="shared" si="1"/>
-        <v>3199050.6048560832</v>
+        <v>3253884.0297563183</v>
       </c>
       <c r="H18" s="120"/>
     </row>
@@ -17357,7 +17357,7 @@
       </c>
       <c r="C19" s="123">
         <f t="shared" si="2"/>
-        <v>4125602.698840898</v>
+        <v>4138304.9363221498</v>
       </c>
       <c r="D19" s="138">
         <f>IF($C$12&lt;B19,0,DDM!$C$11)</f>
@@ -17365,11 +17365,11 @@
       </c>
       <c r="E19" s="124">
         <f t="shared" si="0"/>
-        <v>0.73502985279645328</v>
+        <v>0.7488005297763749</v>
       </c>
       <c r="F19" s="125">
         <f t="shared" si="1"/>
-        <v>3032441.1444256757</v>
+        <v>3098764.9286942133</v>
       </c>
       <c r="H19" s="120"/>
     </row>
@@ -17379,7 +17379,7 @@
       </c>
       <c r="C20" s="123">
         <f t="shared" si="2"/>
-        <v>4223596.5691102576</v>
+        <v>4236600.5180026004</v>
       </c>
       <c r="D20" s="138">
         <f>IF($C$12&lt;B20,0,DDM!$C$11)</f>
@@ -17387,11 +17387,11 @@
       </c>
       <c r="E20" s="124">
         <f t="shared" si="0"/>
-        <v>0.68058319703375303</v>
+        <v>0.69655863235011617</v>
       </c>
       <c r="F20" s="125">
         <f t="shared" si="1"/>
-        <v>2874508.8559858496</v>
+        <v>2951040.6626336849</v>
       </c>
       <c r="H20" s="120"/>
     </row>
@@ -17951,7 +17951,7 @@
       </c>
       <c r="C46" s="123">
         <f>C$16*(1+F4)^$C$12/Equity_Cost</f>
-        <v>48063161.865063354</v>
+        <v>51425218.767303683</v>
       </c>
       <c r="D46" s="139">
         <f>Terminal_Growth</f>
@@ -17959,11 +17959,11 @@
       </c>
       <c r="E46" s="124">
         <f>1/(1+Equity_Cost)^C12</f>
-        <v>0.68058319703375303</v>
+        <v>0.69655863235011617</v>
       </c>
       <c r="F46" s="125">
         <f t="shared" si="1"/>
-        <v>32710980.361675579</v>
+        <v>35820680.052858584</v>
       </c>
       <c r="H46" s="120"/>
     </row>
@@ -17974,7 +17974,7 @@
       </c>
       <c r="F47" s="137">
         <f>SUM(F16:F46)</f>
-        <v>48752029.160718396</v>
+        <v>52128943.773610562</v>
       </c>
       <c r="H47" s="120"/>
     </row>
@@ -17995,7 +17995,7 @@
     <row r="50" spans="1:8" ht="13.15">
       <c r="A50" s="133">
         <f>F47</f>
-        <v>48752029.160718396</v>
+        <v>52128943.773610562</v>
       </c>
       <c r="B50" s="131">
         <f>C73</f>
@@ -18025,19 +18025,19 @@
       </c>
       <c r="B51" s="123">
         <f t="dataTable" ref="B51:F56" dt2D="1" dtr="1" r1="C11" r2="C12"/>
-        <v>46948023.339999989</v>
+        <v>50232075.40382231</v>
       </c>
       <c r="C51" s="123">
-        <v>47699868.975795098</v>
+        <v>51022842.173981324</v>
       </c>
       <c r="D51" s="123">
-        <v>49237096.560229637</v>
+        <v>52638677.40642716</v>
       </c>
       <c r="E51" s="123">
-        <v>50820679.201203234</v>
+        <v>54301928.586612023</v>
       </c>
       <c r="F51" s="123">
-        <v>53287408.020684652</v>
+        <v>56890258.860544249</v>
       </c>
       <c r="H51" s="120"/>
     </row>
@@ -18046,19 +18046,19 @@
         <v>10</v>
       </c>
       <c r="B52" s="123">
-        <v>46948023.339999989</v>
+        <v>50232075.403822318</v>
       </c>
       <c r="C52" s="123">
-        <v>48427660.425565451</v>
+        <v>51781014.91735658</v>
       </c>
       <c r="D52" s="123">
-        <v>51606220.717002235</v>
+        <v>55106929.061902717</v>
       </c>
       <c r="E52" s="123">
-        <v>55106260.583889931</v>
+        <v>58767248.903613091</v>
       </c>
       <c r="F52" s="123">
-        <v>61044118.856698632</v>
+        <v>64973466.976150982</v>
       </c>
       <c r="H52" s="120"/>
     </row>
@@ -18067,19 +18067,19 @@
         <v>15</v>
       </c>
       <c r="B53" s="123">
-        <v>46948023.339999981</v>
+        <v>50232075.403822318</v>
       </c>
       <c r="C53" s="123">
-        <v>49306110.710440405</v>
+        <v>52717086.236345999</v>
       </c>
       <c r="D53" s="123">
-        <v>54614932.543907583</v>
+        <v>58313307.273648046</v>
       </c>
       <c r="E53" s="123">
-        <v>60843801.242013268</v>
+        <v>64882361.435215972</v>
       </c>
       <c r="F53" s="123">
-        <v>72321600.924278408</v>
+        <v>76995034.703128889</v>
       </c>
       <c r="H53" s="120"/>
     </row>
@@ -18088,19 +18088,19 @@
         <v>20</v>
       </c>
       <c r="B54" s="123">
-        <v>46948023.339999974</v>
+        <v>50232075.403822325</v>
       </c>
       <c r="C54" s="123">
-        <v>50178020.339817904</v>
+        <v>53667777.951094262</v>
       </c>
       <c r="D54" s="123">
-        <v>57764287.764714047</v>
+        <v>61747571.403744191</v>
       </c>
       <c r="E54" s="123">
-        <v>67198906.354281053</v>
+        <v>71813137.99981527</v>
       </c>
       <c r="F54" s="123">
-        <v>85995260.732661694</v>
+        <v>91909921.023140371</v>
       </c>
       <c r="H54" s="120"/>
     </row>
@@ -18109,19 +18109,19 @@
         <v>25</v>
       </c>
       <c r="B55" s="123">
-        <v>46948023.339999974</v>
+        <v>50232075.403822333</v>
       </c>
       <c r="C55" s="123">
-        <v>50967456.093088314</v>
+        <v>54548638.819082573</v>
       </c>
       <c r="D55" s="123">
-        <v>60776889.445155039</v>
+        <v>65109413.787071124</v>
       </c>
       <c r="E55" s="123">
-        <v>73652393.737640664</v>
+        <v>79015577.70488286</v>
       </c>
       <c r="F55" s="123">
-        <v>101299718.84854215</v>
+        <v>108993715.0414055</v>
       </c>
       <c r="H55" s="120"/>
     </row>
@@ -18130,19 +18130,19 @@
         <v>30</v>
       </c>
       <c r="B56" s="123">
-        <v>46948023.339999974</v>
+        <v>50232075.403822333</v>
       </c>
       <c r="C56" s="123">
-        <v>51644952.095172547</v>
+        <v>55322280.356122322</v>
       </c>
       <c r="D56" s="123">
-        <v>63513001.789418392</v>
+        <v>68234149.82843776</v>
       </c>
       <c r="E56" s="123">
-        <v>79893212.15415208</v>
+        <v>86143661.477928832</v>
       </c>
       <c r="F56" s="123">
-        <v>117714070.89025626</v>
+        <v>127745426.20299007</v>
       </c>
       <c r="H56" s="120"/>
     </row>
@@ -18192,23 +18192,23 @@
       </c>
       <c r="B60" s="124">
         <f>C7</f>
-        <v>164.21012499999995</v>
+        <v>176.2377048712205</v>
       </c>
       <c r="C60" s="124">
         <f>C7</f>
-        <v>164.21012499999995</v>
+        <v>176.2377048712205</v>
       </c>
       <c r="D60" s="124">
         <f>C7</f>
-        <v>164.21012499999995</v>
+        <v>176.2377048712205</v>
       </c>
       <c r="E60" s="141">
         <f>C7</f>
-        <v>164.21012499999995</v>
+        <v>176.2377048712205</v>
       </c>
       <c r="F60" s="124">
         <f>C7</f>
-        <v>164.21012499999995</v>
+        <v>176.2377048712205</v>
       </c>
       <c r="H60" s="120"/>
     </row>
@@ -18219,23 +18219,23 @@
       </c>
       <c r="B61" s="124">
         <f t="shared" ref="B61:F66" si="4">B51/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>164.21012499999995</v>
+        <v>176.23770487122047</v>
       </c>
       <c r="C61" s="124">
         <f t="shared" si="4"/>
-        <v>166.83985586088221</v>
+        <v>179.01208597215839</v>
       </c>
       <c r="D61" s="124">
         <f t="shared" si="4"/>
-        <v>172.21661756105743</v>
+        <v>184.68119461493291</v>
       </c>
       <c r="E61" s="124">
         <f t="shared" si="4"/>
-        <v>177.75551536595285</v>
+        <v>190.51666066453643</v>
       </c>
       <c r="F61" s="124">
         <f t="shared" si="4"/>
-        <v>186.38339400643719</v>
+        <v>199.5977385069184</v>
       </c>
       <c r="H61" s="120"/>
     </row>
@@ -18246,23 +18246,23 @@
       </c>
       <c r="B62" s="124">
         <f t="shared" si="4"/>
-        <v>164.21012499999995</v>
+        <v>176.2377048712205</v>
       </c>
       <c r="C62" s="124">
         <f t="shared" si="4"/>
-        <v>169.3854523831302</v>
+        <v>181.67211192398688</v>
       </c>
       <c r="D62" s="124">
         <f t="shared" si="4"/>
-        <v>180.50310432338054</v>
+        <v>193.34098028591279</v>
       </c>
       <c r="E62" s="124">
         <f t="shared" si="4"/>
-        <v>192.7451955374089</v>
+        <v>206.18310083959668</v>
       </c>
       <c r="F62" s="124">
         <f t="shared" si="4"/>
-        <v>213.51404542377779</v>
+        <v>227.95742770627319</v>
       </c>
       <c r="H62" s="120"/>
     </row>
@@ -18273,23 +18273,23 @@
       </c>
       <c r="B63" s="124">
         <f t="shared" si="4"/>
-        <v>164.21012499999992</v>
+        <v>176.2377048712205</v>
       </c>
       <c r="C63" s="124">
         <f t="shared" si="4"/>
-        <v>172.45800838918254</v>
+        <v>184.95628960385071</v>
       </c>
       <c r="D63" s="124">
         <f t="shared" si="4"/>
-        <v>191.02667720326716</v>
+        <v>204.59046047251258</v>
       </c>
       <c r="E63" s="124">
         <f t="shared" si="4"/>
-        <v>212.81339440149802</v>
+        <v>227.6377866939049</v>
       </c>
       <c r="F63" s="124">
         <f t="shared" si="4"/>
-        <v>252.95930015987491</v>
+        <v>270.13473151314133</v>
       </c>
       <c r="H63" s="120"/>
     </row>
@@ -18300,23 +18300,23 @@
       </c>
       <c r="B64" s="124">
         <f t="shared" si="4"/>
-        <v>164.21012499999989</v>
+        <v>176.23770487122053</v>
       </c>
       <c r="C64" s="124">
         <f t="shared" si="4"/>
-        <v>175.50768714119076</v>
+        <v>188.29176249642745</v>
       </c>
       <c r="D64" s="124">
         <f t="shared" si="4"/>
-        <v>202.04217855319109</v>
+        <v>216.63947145491861</v>
       </c>
       <c r="E64" s="124">
         <f t="shared" si="4"/>
-        <v>235.04164876944071</v>
+        <v>251.95420493664545</v>
       </c>
       <c r="F64" s="124">
         <f t="shared" si="4"/>
-        <v>300.78566699285375</v>
+        <v>322.46315538021435</v>
       </c>
       <c r="H64" s="120"/>
     </row>
@@ -18327,23 +18327,23 @@
       </c>
       <c r="B65" s="124">
         <f t="shared" si="4"/>
-        <v>164.21012499999989</v>
+        <v>176.23770487122056</v>
       </c>
       <c r="C65" s="124">
         <f t="shared" si="4"/>
-        <v>178.26889697499334</v>
+        <v>191.3822359924383</v>
       </c>
       <c r="D65" s="124">
         <f t="shared" si="4"/>
-        <v>212.5793569757582</v>
+        <v>228.43439294707832</v>
       </c>
       <c r="E65" s="124">
         <f t="shared" si="4"/>
-        <v>257.61401485677948</v>
+        <v>277.22374502413055</v>
       </c>
       <c r="F65" s="124">
         <f t="shared" si="4"/>
-        <v>354.31607789142674</v>
+        <v>382.40112577198971</v>
       </c>
     </row>
     <row r="66" spans="1:8" ht="13.15">
@@ -18353,23 +18353,23 @@
       </c>
       <c r="B66" s="124">
         <f t="shared" si="4"/>
-        <v>164.21012499999989</v>
+        <v>176.23770487122056</v>
       </c>
       <c r="C66" s="124">
         <f t="shared" si="4"/>
-        <v>180.63857508441154</v>
+        <v>194.09653373516213</v>
       </c>
       <c r="D66" s="124">
         <f t="shared" si="4"/>
-        <v>222.1494585072262</v>
+        <v>239.39743406834833</v>
       </c>
       <c r="E66" s="124">
         <f t="shared" si="4"/>
-        <v>279.44252859112663</v>
+        <v>302.23240959138872</v>
       </c>
       <c r="F66" s="124">
         <f t="shared" si="4"/>
-        <v>411.72856533618312</v>
+        <v>448.19093260275116</v>
       </c>
     </row>
     <row r="68" spans="1:8" ht="13.15">
@@ -18404,7 +18404,7 @@
       </c>
       <c r="E69" s="135">
         <f>INDEX(B$60:F$66, MATCH(D69, A$60:A$66, 0), MATCH(C69, B$59:F$59, 0))</f>
-        <v>213.51404542377779</v>
+        <v>227.95742770627319</v>
       </c>
       <c r="F69" s="142">
         <f>Scenarios!C58</f>
@@ -18426,7 +18426,7 @@
       </c>
       <c r="E70" s="135">
         <f>INDEX(B$60:F$66, MATCH(D70, A$60:A$66, 0), MATCH(C70, B$59:F$59, 0))</f>
-        <v>177.75551536595285</v>
+        <v>190.51666066453643</v>
       </c>
       <c r="F70" s="142">
         <f>Scenarios!C40*(1-F$69-F$73)</f>
@@ -18449,7 +18449,7 @@
       </c>
       <c r="E71" s="135">
         <f>INDEX(B$60:F$66, MATCH(D71, A$60:A$66, 0), MATCH(C71, B$59:F$59, 0))</f>
-        <v>172.21661756105743</v>
+        <v>184.68119461493291</v>
       </c>
       <c r="F71" s="142">
         <f>Scenarios!C28*(1-F$69-F$73)</f>
@@ -18472,7 +18472,7 @@
       </c>
       <c r="E72" s="135">
         <f>INDEX(B$60:F$66, MATCH(D72, A$60:A$66, 0), MATCH(C72, B$59:F$59, 0))</f>
-        <v>166.83985586088221</v>
+        <v>179.01208597215839</v>
       </c>
       <c r="F72" s="142">
         <f>Scenarios!C34*(1-F$69-F$73)</f>
@@ -18495,7 +18495,7 @@
       </c>
       <c r="E73" s="135">
         <f>INDEX(B$60:F$66, MATCH(D73, A$60:A$66, 0), MATCH(C73, B$59:F$59, 0))</f>
-        <v>164.21012499999995</v>
+        <v>176.2377048712205</v>
       </c>
       <c r="F73" s="142">
         <f>Scenarios!C52</f>
@@ -18595,7 +18595,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-49.9</v>
+        <v>-50.15</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18615,7 +18615,7 @@
       </c>
       <c r="I4" s="124">
         <f t="shared" ref="I4:I13" si="0">IF(ROW()-3 &lt; $C$76, $C$77, IF(ROW()-3 = $C$76, $C$77 + $C$60, ""))</f>
-        <v>1.4678</v>
+        <v>1.47231918072</v>
       </c>
     </row>
     <row r="5" spans="2:9">
@@ -18624,7 +18624,7 @@
       </c>
       <c r="I5" s="124">
         <f t="shared" si="0"/>
-        <v>1.4678</v>
+        <v>1.47231918072</v>
       </c>
     </row>
     <row r="6" spans="2:9" ht="13.15">
@@ -18644,7 +18644,7 @@
       </c>
       <c r="I6" s="124">
         <f t="shared" si="0"/>
-        <v>32.001656751256881</v>
+        <v>34.20729335164399</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1">
@@ -18835,7 +18835,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>49.9</v>
+        <v>50.15</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -18850,7 +18850,7 @@
       </c>
       <c r="C22" s="160">
         <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
-        <v>28.743494574782385</v>
+        <v>30.855374101930472</v>
       </c>
       <c r="D22" t="str">
         <f>Market_currency</f>
@@ -18897,7 +18897,7 @@
       </c>
       <c r="C27" s="160">
         <f>IF(valuation_method="DCF",DCF!E76,DDM!E71)</f>
-        <v>30.221246192287584</v>
+        <v>32.408998499180548</v>
       </c>
       <c r="D27" s="160" t="str">
         <f>Market_currency</f>
@@ -18955,7 +18955,7 @@
       </c>
       <c r="C33" s="160">
         <f>IF(valuation_method="DCF",DCF!E77,DDM!E72)</f>
-        <v>29.228861794402807</v>
+        <v>31.365867546764274</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
@@ -19013,7 +19013,7 @@
       </c>
       <c r="C39" s="160">
         <f>IF(valuation_method="DCF",DCF!E75,DDM!E70)</f>
-        <v>31.243555915048276</v>
+        <v>33.482739653510706</v>
       </c>
       <c r="D39" t="str">
         <f>Market_currency</f>
@@ -19040,7 +19040,7 @@
       </c>
       <c r="C42" s="154">
         <f>C27*C28+C33*C34+C39*C40</f>
-        <v>30.227231257262765</v>
+        <v>32.415120539563326</v>
       </c>
       <c r="D42" t="str">
         <f>Market_currency</f>
@@ -19114,7 +19114,7 @@
       </c>
       <c r="C51" s="160">
         <f>IF(valuation_method="DCF",DCF!E78,DDM!E73)</f>
-        <v>28.743494574782375</v>
+        <v>30.855374101930487</v>
       </c>
       <c r="D51" t="str">
         <f>Market_currency</f>
@@ -19172,7 +19172,7 @@
       </c>
       <c r="C57" s="160">
         <f>IF(valuation_method="DCF",DCF!E74,DDM!E69)</f>
-        <v>37.84347781962564</v>
+        <v>40.371939604409576</v>
       </c>
       <c r="D57" t="str">
         <f>Market_currency</f>
@@ -19198,7 +19198,7 @@
       </c>
       <c r="C60" s="154">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
-        <v>30.533856751256884</v>
+        <v>32.734974170923991</v>
       </c>
       <c r="D60" t="str">
         <f>Market_currency</f>
@@ -19260,7 +19260,7 @@
       </c>
       <c r="C66" s="160">
         <f>IF(valuation_method="DCF",DCF!C18,DDM!C13)</f>
-        <v>29.908102371508068</v>
+        <v>32.079930956152829</v>
       </c>
       <c r="D66" s="160" t="str">
         <f>Market_currency</f>
@@ -19323,7 +19323,7 @@
       </c>
       <c r="F72" s="291">
         <f>BS!D89/C60</f>
-        <v>-5.1242478065840952E-2</v>
+        <v>-4.8047348991141402E-2</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="13.9">
@@ -19356,7 +19356,7 @@
       </c>
       <c r="C77" s="173">
         <f>Normalized_FCF!C90</f>
-        <v>1.4678</v>
+        <v>1.47231918072</v>
       </c>
       <c r="D77" t="str">
         <f>Market_currency</f>
@@ -19374,7 +19374,7 @@
       </c>
       <c r="C80" s="167">
         <f>Thesis!F29</f>
-        <v>0.4</v>
+        <v>0.3674</v>
       </c>
     </row>
     <row r="81" spans="2:8">
@@ -19383,7 +19383,7 @@
       </c>
       <c r="C81" s="116">
         <f>PV(C80, C76, -C77, 0)</f>
-        <v>2.3322186588921276</v>
+        <v>2.440014683327854</v>
       </c>
       <c r="D81" s="116"/>
       <c r="E81" s="100"/>
@@ -19395,7 +19395,7 @@
       </c>
       <c r="C82" s="116">
         <f>C60/(1+C80)^C76</f>
-        <v>11.127498816055718</v>
+        <v>12.803398882405475</v>
       </c>
       <c r="D82" s="116"/>
     </row>
@@ -19405,7 +19405,7 @@
       </c>
       <c r="C83" s="111">
         <f>C81+C82</f>
-        <v>13.459717474947846</v>
+        <v>15.243413565733329</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -19416,7 +19416,7 @@
       </c>
       <c r="F83" s="291">
         <f>(1-C83/C60)</f>
-        <v>0.55918711531933174</v>
+        <v>0.53433861025395579</v>
       </c>
     </row>
     <row r="84" spans="2:8">
@@ -19433,7 +19433,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>49.9</v>
+        <v>50.15</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19446,7 +19446,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>-0.11622199457788085</v>
+        <v>-9.8595701784031209E-2</v>
       </c>
     </row>
     <row r="88" spans="2:8">
@@ -19463,7 +19463,7 @@
       </c>
       <c r="C90" s="167">
         <f>Thesis!F30</f>
-        <v>0.22</v>
+        <v>0.21740000000000001</v>
       </c>
     </row>
     <row r="91" spans="2:8">
@@ -19472,7 +19472,7 @@
       </c>
       <c r="C91" s="116">
         <f>PV(C90, C76, -C77, 0)</f>
-        <v>2.9976019578731261</v>
+        <v>3.018844461140437</v>
       </c>
       <c r="D91" s="116"/>
       <c r="E91" s="100"/>
@@ -19484,7 +19484,7 @@
       </c>
       <c r="C92" s="116">
         <f>C60/(1+C90)^C76</f>
-        <v>16.815205210599611</v>
+        <v>18.143125735710871</v>
       </c>
       <c r="D92" s="116"/>
     </row>
@@ -19494,7 +19494,7 @@
       </c>
       <c r="C93" s="111">
         <f>C91+C92</f>
-        <v>19.812807168472737</v>
+        <v>21.161970196851307</v>
       </c>
       <c r="D93" t="str">
         <f>Market_currency</f>
@@ -19505,7 +19505,7 @@
       </c>
       <c r="F93" s="291">
         <f>(1-C93/C60)</f>
-        <v>0.35112005896021736</v>
+        <v>0.353536371027661</v>
       </c>
     </row>
     <row r="95" spans="2:8" ht="13.15">
@@ -19521,7 +19521,7 @@
       </c>
       <c r="C96" s="134">
         <f>Thesis!F31</f>
-        <v>0.08</v>
+        <v>7.4999999999999997E-2</v>
       </c>
       <c r="G96" s="2"/>
       <c r="H96" s="281"/>
@@ -19532,7 +19532,7 @@
       </c>
       <c r="C97" s="116">
         <f>PV(C96, C76, -C77, 0)</f>
-        <v>3.7826629578824384</v>
+        <v>3.8288039267695555</v>
       </c>
       <c r="D97" s="116"/>
       <c r="G97" s="2"/>
@@ -19544,7 +19544,7 @@
       </c>
       <c r="C98" s="116">
         <f>C60/(1+C96)^C76</f>
-        <v>24.238759931839088</v>
+        <v>26.350363451509121</v>
       </c>
       <c r="D98" s="116"/>
       <c r="G98" s="2"/>
@@ -19556,7 +19556,7 @@
       </c>
       <c r="C99" s="111">
         <f>C97+C98</f>
-        <v>28.021422889721528</v>
+        <v>30.179167378278677</v>
       </c>
       <c r="D99" t="s">
         <v>399</v>
@@ -19566,7 +19566,7 @@
       </c>
       <c r="F99" s="291">
         <f>(1-C99/C60)</f>
-        <v>8.2283541250711356E-2</v>
+        <v>7.807572351517067E-2</v>
       </c>
     </row>
     <row r="100" spans="2:8">
@@ -19583,7 +19583,7 @@
       </c>
       <c r="C102" s="134">
         <f>Thesis!F32</f>
-        <v>0.12</v>
+        <v>0.1174</v>
       </c>
     </row>
     <row r="103" spans="2:8">
@@ -19592,7 +19592,7 @@
       </c>
       <c r="C103" s="116">
         <f>PV(C102, C76, -C77, 0)</f>
-        <v>3.5254079354956298</v>
+        <v>3.5521218577845026</v>
       </c>
       <c r="D103" s="116"/>
     </row>
@@ -19602,7 +19602,7 @@
       </c>
       <c r="C104" s="116">
         <f>C60/(1+C102)^C76</f>
-        <v>21.733396125108815</v>
+        <v>23.46313295208089</v>
       </c>
       <c r="D104" s="116"/>
     </row>
@@ -19612,7 +19612,7 @@
       </c>
       <c r="C105" s="111">
         <f>C103+C104</f>
-        <v>25.258804060604444</v>
+        <v>27.015254809865393</v>
       </c>
       <c r="D105" t="s">
         <v>399</v>
@@ -19622,7 +19622,7 @@
       </c>
       <c r="F105" s="291">
         <f>(1-C105/C66)</f>
-        <v>0.15545280182445731</v>
+        <v>0.15787677826395219</v>
       </c>
     </row>
     <row r="106" spans="2:8">

--- a/financial_models/opportunities/1913.HK_Valuation.xlsx
+++ b/financial_models/opportunities/1913.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDA2D04D-AA98-4611-A559-929E7338DFC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFEF12AE-0E50-4144-A9DE-2A16BD191F73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -25,6 +25,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">DCF!$B$73:$H$73</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">DDM!$B$68:$H$68</definedName>
     <definedName name="Common_Shares">Thesis!$C$6</definedName>
+    <definedName name="dividend_tax_rate">Normalized_FCF!$C$93</definedName>
     <definedName name="Equity_Cost">Thesis!$C$86</definedName>
     <definedName name="Exchange_Rate">Thesis!$C$16</definedName>
     <definedName name="Market_currency">Thesis!$C$13</definedName>
@@ -47,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="684" uniqueCount="463">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="686" uniqueCount="466">
   <si>
     <t>Number of Shares:</t>
   </si>
@@ -465,10 +466,6 @@
   <si>
     <t>PV of FCFE</t>
     <phoneticPr fontId="28" type="noConversion"/>
-  </si>
-  <si>
-    <t>Annual Dividend per share</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>HGP</t>
@@ -1401,10 +1398,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Y</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Asset Play</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -1501,14 +1494,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Dividend/Market Cap =</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Dividend Yield</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Note of the formulas:</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -1550,10 +1535,6 @@
   </si>
   <si>
     <t>Operating Cash Requirement</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>N</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -1761,10 +1742,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Historical Average or D&amp;A</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Step 1: Establishing the Company’s Sustainable Earning Power (Calculating Normalized FCFE)</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -2457,19 +2434,46 @@
     <t>LT AR and Prepayments</t>
   </si>
   <si>
+    <t>Dividend after tax Yield</t>
+  </si>
+  <si>
+    <t>Dividend tax rate</t>
+  </si>
+  <si>
+    <t>After tax Dividend/Market Cap =</t>
+  </si>
+  <si>
+    <t>After-tax Dividend per share</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
     <t>PRADA</t>
   </si>
   <si>
     <t>1913.HK</t>
   </si>
   <si>
+    <t/>
+  </si>
+  <si>
+    <t>CNS_04</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
     <t>EUR</t>
   </si>
   <si>
-    <t>CNS_04</t>
-  </si>
-  <si>
     <t>DCF</t>
+  </si>
+  <si>
+    <t>Latest Asset Value</t>
+  </si>
+  <si>
+    <t>Historical Average or D&amp;A</t>
   </si>
 </sst>
 </file>
@@ -3143,7 +3147,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="368">
+  <cellXfs count="370">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -3888,29 +3892,33 @@
     </xf>
     <xf numFmtId="181" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="181" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="10" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4232,18 +4240,18 @@
         <v>45797</v>
       </c>
       <c r="D1" s="316" t="s">
-        <v>452</v>
+        <v>446</v>
       </c>
       <c r="E1" s="292" t="s">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="F1" s="254" t="s">
-        <v>284</v>
+        <v>456</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="13.9">
       <c r="A2" s="222" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B2" s="36"/>
       <c r="C2" s="36"/>
@@ -4257,7 +4265,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="B4" s="45" t="s">
-        <v>417</v>
+        <v>411</v>
       </c>
       <c r="C4" s="46"/>
       <c r="D4" s="5"/>
@@ -4266,10 +4274,10 @@
     </row>
     <row r="5" spans="1:10" ht="12.4">
       <c r="B5" s="4" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="C5" s="294" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -4283,7 +4291,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="B7" s="2" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="C7" s="250">
         <v>6</v>
@@ -4293,7 +4301,7 @@
     </row>
     <row r="8" spans="1:10">
       <c r="B8" s="1" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C8" s="33">
         <f>EOMONTH(EDATE(BS!C1,C7+2),0)</f>
@@ -4306,19 +4314,21 @@
     </row>
     <row r="10" spans="1:10">
       <c r="B10" s="45" t="s">
-        <v>420</v>
+        <v>414</v>
       </c>
       <c r="C10" s="46"/>
       <c r="E10" s="34"/>
     </row>
     <row r="11" spans="1:10">
       <c r="B11" s="1" t="s">
-        <v>419</v>
+        <v>413</v>
       </c>
       <c r="C11" s="49" t="s">
+        <v>458</v>
+      </c>
+      <c r="D11" s="49" t="s">
         <v>459</v>
       </c>
-      <c r="D11" s="49"/>
       <c r="E11" s="34"/>
     </row>
     <row r="12" spans="1:10">
@@ -4333,17 +4343,17 @@
     </row>
     <row r="13" spans="1:10">
       <c r="B13" s="1" t="s">
-        <v>418</v>
+        <v>412</v>
       </c>
       <c r="C13" s="48" t="s">
-        <v>399</v>
+        <v>393</v>
       </c>
       <c r="D13" s="48"/>
       <c r="E13" s="5"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="4" t="s">
-        <v>422</v>
+        <v>416</v>
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
@@ -4357,7 +4367,7 @@
     </row>
     <row r="15" spans="1:10">
       <c r="B15" s="4" t="s">
-        <v>421</v>
+        <v>415</v>
       </c>
       <c r="C15" s="32" t="str">
         <f>IF(C25=C13,C13,C25&amp;"/"&amp;C13)</f>
@@ -4384,34 +4394,34 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="356" t="s">
-        <v>362</v>
-      </c>
-      <c r="C18" s="356"/>
-      <c r="D18" s="356"/>
-      <c r="E18" s="356"/>
-      <c r="F18" s="356"/>
+      <c r="B18" s="360" t="s">
+        <v>356</v>
+      </c>
+      <c r="C18" s="360"/>
+      <c r="D18" s="360"/>
+      <c r="E18" s="360"/>
+      <c r="F18" s="360"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="C20" s="46"/>
       <c r="D20" s="5"/>
     </row>
     <row r="21" spans="2:6">
       <c r="B21" s="2" t="s">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="C21" s="32" t="str">
         <f>IF(Scenarios!C69="Y",Scenarios!B69,"")&amp;IF(Scenarios!C70="Y",Scenarios!B70,"")&amp;IF(Scenarios!C71="Y",Scenarios!B71,"")&amp;" "&amp;IF(Scenarios!C72="Y",Scenarios!B72,"")</f>
         <v xml:space="preserve">Low Growth </v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>441</v>
+        <v>435</v>
       </c>
       <c r="E21" s="308" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="22" spans="2:6">
@@ -4419,7 +4429,7 @@
         <v>56</v>
       </c>
       <c r="C22" s="48" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="D22" s="1" t="str">
         <f>IF(valuation_method="DDM","DDM Terminal Value","")</f>
@@ -4429,26 +4439,26 @@
     </row>
     <row r="23" spans="2:6">
       <c r="B23" s="1" t="s">
-        <v>436</v>
+        <v>430</v>
       </c>
       <c r="C23" s="262" t="s">
-        <v>322</v>
+        <v>461</v>
       </c>
     </row>
     <row r="24" spans="2:6">
       <c r="B24" s="1" t="s">
-        <v>437</v>
+        <v>431</v>
       </c>
       <c r="C24" s="262" t="s">
-        <v>322</v>
+        <v>461</v>
       </c>
     </row>
     <row r="25" spans="2:6">
       <c r="B25" s="4" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="C25" s="48" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="D25" s="32" t="str">
         <f>IF(D11="","",Market_currency&amp;"/"&amp;D13&amp;":")</f>
@@ -4469,7 +4479,7 @@
         <v>32.734974170923991</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>402</v>
+        <v>396</v>
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
@@ -4482,7 +4492,7 @@
     </row>
     <row r="28" spans="2:6">
       <c r="B28" s="45" t="s">
-        <v>435</v>
+        <v>429</v>
       </c>
       <c r="C28" s="309" t="str">
         <f>C145&amp;" ("&amp;Market_currency&amp;")"</f>
@@ -4493,7 +4503,7 @@
         <v/>
       </c>
       <c r="E28" s="305" t="s">
-        <v>431</v>
+        <v>425</v>
       </c>
       <c r="F28" s="303">
         <v>3</v>
@@ -4501,7 +4511,7 @@
     </row>
     <row r="29" spans="2:6">
       <c r="B29" s="1" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="C29" s="310">
         <f>C149</f>
@@ -4512,7 +4522,7 @@
         <v/>
       </c>
       <c r="E29" s="306" t="s">
-        <v>426</v>
+        <v>420</v>
       </c>
       <c r="F29" s="302">
         <v>0.3674</v>
@@ -4520,7 +4530,7 @@
     </row>
     <row r="30" spans="2:6">
       <c r="B30" s="1" t="s">
-        <v>428</v>
+        <v>422</v>
       </c>
       <c r="C30" s="311">
         <f>C157</f>
@@ -4531,7 +4541,7 @@
         <v/>
       </c>
       <c r="E30" s="307" t="s">
-        <v>439</v>
+        <v>433</v>
       </c>
       <c r="F30" s="312">
         <v>0.21740000000000001</v>
@@ -4539,7 +4549,7 @@
     </row>
     <row r="31" spans="2:6">
       <c r="B31" s="1" t="s">
-        <v>429</v>
+        <v>423</v>
       </c>
       <c r="C31" s="311">
         <f>C165</f>
@@ -4550,7 +4560,7 @@
         <v/>
       </c>
       <c r="E31" s="307" t="s">
-        <v>438</v>
+        <v>432</v>
       </c>
       <c r="F31" s="312">
         <v>7.4999999999999997E-2</v>
@@ -4558,7 +4568,7 @@
     </row>
     <row r="32" spans="2:6">
       <c r="B32" s="1" t="s">
-        <v>430</v>
+        <v>424</v>
       </c>
       <c r="C32" s="311">
         <f>C173</f>
@@ -4569,7 +4579,7 @@
         <v/>
       </c>
       <c r="E32" s="307" t="s">
-        <v>440</v>
+        <v>434</v>
       </c>
       <c r="F32" s="312">
         <v>0.1174</v>
@@ -4581,7 +4591,7 @@
     </row>
     <row r="34" spans="1:6" ht="13.9">
       <c r="A34" s="222" t="s">
-        <v>357</v>
+        <v>351</v>
       </c>
       <c r="B34" s="36"/>
       <c r="C34" s="36"/>
@@ -4590,26 +4600,26 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="356" t="s">
-        <v>363</v>
-      </c>
-      <c r="C36" s="356"/>
-      <c r="D36" s="356"/>
-      <c r="E36" s="356"/>
-      <c r="F36" s="356"/>
+      <c r="B36" s="360" t="s">
+        <v>357</v>
+      </c>
+      <c r="C36" s="360"/>
+      <c r="D36" s="360"/>
+      <c r="E36" s="360"/>
+      <c r="F36" s="360"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="358" t="s">
-        <v>341</v>
-      </c>
-      <c r="C37" s="358"/>
-      <c r="D37" s="358"/>
-      <c r="E37" s="358"/>
-      <c r="F37" s="358"/>
+      <c r="B37" s="363" t="s">
+        <v>336</v>
+      </c>
+      <c r="C37" s="363"/>
+      <c r="D37" s="363"/>
+      <c r="E37" s="363"/>
+      <c r="F37" s="363"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C39" s="108">
         <f>scaling_factor</f>
@@ -4617,17 +4627,17 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="357" t="s">
-        <v>231</v>
-      </c>
-      <c r="C40" s="357"/>
-      <c r="D40" s="357"/>
-      <c r="E40" s="357"/>
-      <c r="F40" s="357"/>
+      <c r="B40" s="361" t="s">
+        <v>230</v>
+      </c>
+      <c r="C40" s="361"/>
+      <c r="D40" s="361"/>
+      <c r="E40" s="361"/>
+      <c r="F40" s="361"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C41" s="349">
         <f>Normalized_FCF!C8</f>
@@ -4643,17 +4653,17 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="357" t="s">
-        <v>233</v>
-      </c>
-      <c r="C43" s="357"/>
-      <c r="D43" s="357"/>
-      <c r="E43" s="357"/>
-      <c r="F43" s="357"/>
+      <c r="B43" s="361" t="s">
+        <v>232</v>
+      </c>
+      <c r="C43" s="361"/>
+      <c r="D43" s="361"/>
+      <c r="E43" s="361"/>
+      <c r="F43" s="361"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C44" s="349">
         <f>Normalized_FCF!C9</f>
@@ -4666,7 +4676,7 @@
     </row>
     <row r="45" spans="1:6">
       <c r="B45" s="52" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C45" s="349">
         <f>Normalized_FCF!C10</f>
@@ -4678,17 +4688,17 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="357" t="s">
-        <v>236</v>
-      </c>
-      <c r="C47" s="357"/>
-      <c r="D47" s="357"/>
-      <c r="E47" s="357"/>
-      <c r="F47" s="357"/>
+      <c r="B47" s="361" t="s">
+        <v>235</v>
+      </c>
+      <c r="C47" s="361"/>
+      <c r="D47" s="361"/>
+      <c r="E47" s="361"/>
+      <c r="F47" s="361"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C48" s="349">
         <f>Normalized_FCF!C11</f>
@@ -4700,17 +4710,17 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="357" t="s">
-        <v>240</v>
-      </c>
-      <c r="C50" s="357"/>
-      <c r="D50" s="357"/>
-      <c r="E50" s="357"/>
-      <c r="F50" s="357"/>
+      <c r="B50" s="361" t="s">
+        <v>239</v>
+      </c>
+      <c r="C50" s="361"/>
+      <c r="D50" s="361"/>
+      <c r="E50" s="361"/>
+      <c r="F50" s="361"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="C51" s="350">
         <f>Normalized_FCF!C48</f>
@@ -4725,7 +4735,7 @@
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="47" t="s">
-        <v>343</v>
+        <v>338</v>
       </c>
       <c r="C52" s="350">
         <f>Normalized_FCF!C47</f>
@@ -4740,7 +4750,7 @@
     </row>
     <row r="53" spans="2:6">
       <c r="B53" s="47" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C53" s="349">
         <f>Normalized_FCF!C12</f>
@@ -4753,12 +4763,12 @@
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="1" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="56" spans="2:6">
       <c r="B56" s="47" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C56" s="349">
         <f>Normalized_FCF!C15</f>
@@ -4770,17 +4780,17 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="357" t="s">
-        <v>241</v>
-      </c>
-      <c r="C58" s="357"/>
-      <c r="D58" s="357"/>
-      <c r="E58" s="357"/>
-      <c r="F58" s="357"/>
+      <c r="B58" s="361" t="s">
+        <v>240</v>
+      </c>
+      <c r="C58" s="361"/>
+      <c r="D58" s="361"/>
+      <c r="E58" s="361"/>
+      <c r="F58" s="361"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C59" s="349">
         <f>Normalized_FCF!C14</f>
@@ -4792,17 +4802,17 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="357" t="s">
-        <v>340</v>
-      </c>
-      <c r="C61" s="360"/>
-      <c r="D61" s="360"/>
-      <c r="E61" s="360"/>
-      <c r="F61" s="360"/>
+      <c r="B61" s="361" t="s">
+        <v>335</v>
+      </c>
+      <c r="C61" s="362"/>
+      <c r="D61" s="362"/>
+      <c r="E61" s="362"/>
+      <c r="F61" s="362"/>
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C62" s="349">
         <f>Normalized_FCF!C17</f>
@@ -4814,26 +4824,26 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="356" t="s">
-        <v>345</v>
-      </c>
-      <c r="C64" s="356"/>
-      <c r="D64" s="356"/>
-      <c r="E64" s="356"/>
-      <c r="F64" s="356"/>
+      <c r="B64" s="360" t="s">
+        <v>340</v>
+      </c>
+      <c r="C64" s="360"/>
+      <c r="D64" s="360"/>
+      <c r="E64" s="360"/>
+      <c r="F64" s="360"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="356" t="s">
-        <v>364</v>
-      </c>
-      <c r="C65" s="356"/>
-      <c r="D65" s="356"/>
-      <c r="E65" s="356"/>
-      <c r="F65" s="356"/>
+      <c r="B65" s="360" t="s">
+        <v>358</v>
+      </c>
+      <c r="C65" s="360"/>
+      <c r="D65" s="360"/>
+      <c r="E65" s="360"/>
+      <c r="F65" s="360"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C67" s="349">
         <f>Normalized_FCF!G19</f>
@@ -4846,7 +4856,7 @@
     </row>
     <row r="68" spans="1:6">
       <c r="B68" s="47" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C68" s="349">
         <f>Normalized_FCF!C19</f>
@@ -4859,24 +4869,24 @@
     </row>
     <row r="69" spans="1:6">
       <c r="B69" s="227" t="s">
-        <v>393</v>
+        <v>387</v>
       </c>
       <c r="C69" s="92">
-        <f>Normalized_FCF!C125</f>
+        <f>Normalized_FCF!C126</f>
         <v>4.8496813803793899E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
     <row r="70" spans="1:6">
       <c r="B70" s="227" t="s">
-        <v>309</v>
+        <v>454</v>
       </c>
       <c r="C70" s="92">
-        <f>Normalized_FCF!C93</f>
+        <f>Normalized_FCF!C94</f>
         <v>2.9358308688334996E-2</v>
       </c>
       <c r="E70" s="47" t="s">
-        <v>450</v>
+        <v>444</v>
       </c>
       <c r="F70" s="315">
         <f>Normalized_FCF!C92</f>
@@ -4885,73 +4895,73 @@
     </row>
     <row r="72" spans="1:6">
       <c r="B72" s="210" t="s">
-        <v>453</v>
+        <v>447</v>
       </c>
       <c r="C72" s="323" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="D72" s="323" t="s">
-        <v>456</v>
+        <v>450</v>
       </c>
     </row>
     <row r="73" spans="1:6">
       <c r="B73" s="47" t="s">
-        <v>454</v>
+        <v>448</v>
       </c>
       <c r="C73" s="92">
-        <f>Normalized_FCF!C120</f>
+        <f>Normalized_FCF!C121</f>
         <v>0.21039827332068567</v>
       </c>
       <c r="D73" s="92">
-        <f>Normalized_FCF!G120</f>
+        <f>Normalized_FCF!G121</f>
         <v>0.3047216496244991</v>
       </c>
     </row>
     <row r="74" spans="1:6">
       <c r="B74" s="259" t="str">
-        <f>Normalized_FCF!B117</f>
+        <f>Normalized_FCF!B118</f>
         <v>Pre-tax Profit/Sales</v>
       </c>
       <c r="C74" s="322">
-        <f>Normalized_FCF!C117</f>
+        <f>Normalized_FCF!C118</f>
         <v>0.21042753223383909</v>
       </c>
       <c r="D74" s="322">
-        <f>Normalized_FCF!G117</f>
+        <f>Normalized_FCF!G118</f>
         <v>0.24793921890168877</v>
       </c>
     </row>
     <row r="75" spans="1:6">
       <c r="B75" s="259" t="str">
-        <f>Normalized_FCF!B118</f>
+        <f>Normalized_FCF!B119</f>
         <v>Sales/Total Assets</v>
       </c>
       <c r="C75" s="324">
-        <f>Normalized_FCF!C118</f>
+        <f>Normalized_FCF!C119</f>
         <v>0.51682300464832642</v>
       </c>
       <c r="D75" s="324">
-        <f>Normalized_FCF!G118</f>
+        <f>Normalized_FCF!G119</f>
         <v>0.63527287089914697</v>
       </c>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="259" t="str">
-        <f>Normalized_FCF!B119</f>
+        <f>Normalized_FCF!B120</f>
         <v>Total Assets/Equity</v>
       </c>
       <c r="C76" s="324">
-        <f>Normalized_FCF!C119</f>
+        <f>Normalized_FCF!C120</f>
         <v>1.9346293526540752</v>
       </c>
       <c r="D76" s="324">
-        <f>Normalized_FCF!G119</f>
+        <f>Normalized_FCF!G120</f>
         <v>1.9346293526540752</v>
       </c>
     </row>
     <row r="78" spans="1:6" ht="13.9">
       <c r="A78" s="222" t="s">
-        <v>358</v>
+        <v>352</v>
       </c>
       <c r="B78" s="36"/>
       <c r="C78" s="36"/>
@@ -4964,31 +4974,31 @@
     </row>
     <row r="80" spans="1:6" ht="24.6" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="356" t="s">
-        <v>365</v>
-      </c>
-      <c r="C80" s="356"/>
-      <c r="D80" s="356"/>
-      <c r="E80" s="356"/>
-      <c r="F80" s="356"/>
+      <c r="B80" s="360" t="s">
+        <v>359</v>
+      </c>
+      <c r="C80" s="360"/>
+      <c r="D80" s="360"/>
+      <c r="E80" s="360"/>
+      <c r="F80" s="360"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="358" t="s">
-        <v>252</v>
-      </c>
-      <c r="C81" s="358"/>
-      <c r="D81" s="358"/>
-      <c r="E81" s="358"/>
-      <c r="F81" s="358"/>
+      <c r="B81" s="363" t="s">
+        <v>251</v>
+      </c>
+      <c r="C81" s="363"/>
+      <c r="D81" s="363"/>
+      <c r="E81" s="363"/>
+      <c r="F81" s="363"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="84" spans="1:6">
       <c r="B84" s="1" t="s">
-        <v>433</v>
+        <v>427</v>
       </c>
       <c r="C84" s="92">
         <f>F31</f>
@@ -4997,7 +5007,7 @@
     </row>
     <row r="85" spans="1:6">
       <c r="B85" s="1" t="s">
-        <v>432</v>
+        <v>426</v>
       </c>
       <c r="C85" s="92">
         <f>IF(C23="Y",1%,0)+IF(C24="Y",1%,0)</f>
@@ -5006,7 +5016,7 @@
     </row>
     <row r="86" spans="1:6">
       <c r="B86" s="80" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C86" s="236">
         <f>F31+C85</f>
@@ -5018,31 +5028,31 @@
     </row>
     <row r="88" spans="1:6">
       <c r="B88" s="293" t="s">
-        <v>359</v>
+        <v>353</v>
       </c>
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="356" t="s">
-        <v>366</v>
-      </c>
-      <c r="C89" s="356"/>
-      <c r="D89" s="356"/>
-      <c r="E89" s="356"/>
-      <c r="F89" s="356"/>
+      <c r="B89" s="360" t="s">
+        <v>360</v>
+      </c>
+      <c r="C89" s="360"/>
+      <c r="D89" s="360"/>
+      <c r="E89" s="360"/>
+      <c r="F89" s="360"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="356" t="s">
-        <v>367</v>
-      </c>
-      <c r="C90" s="356"/>
-      <c r="D90" s="356"/>
-      <c r="E90" s="356"/>
-      <c r="F90" s="356"/>
+      <c r="B90" s="360" t="s">
+        <v>361</v>
+      </c>
+      <c r="C90" s="360"/>
+      <c r="D90" s="360"/>
+      <c r="E90" s="360"/>
+      <c r="F90" s="360"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C92" s="236">
         <v>0</v>
@@ -5050,7 +5060,7 @@
     </row>
     <row r="93" spans="1:6">
       <c r="B93" s="47" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C93" s="223">
         <f>DCF!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
@@ -5063,7 +5073,7 @@
     </row>
     <row r="95" spans="1:6" ht="13.9">
       <c r="A95" s="222" t="s">
-        <v>360</v>
+        <v>354</v>
       </c>
       <c r="B95" s="36"/>
       <c r="C95" s="36"/>
@@ -5075,36 +5085,36 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="356" t="s">
-        <v>368</v>
-      </c>
-      <c r="C97" s="356"/>
-      <c r="D97" s="356"/>
-      <c r="E97" s="356"/>
-      <c r="F97" s="356"/>
+      <c r="B97" s="360" t="s">
+        <v>362</v>
+      </c>
+      <c r="C97" s="360"/>
+      <c r="D97" s="360"/>
+      <c r="E97" s="360"/>
+      <c r="F97" s="360"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="210" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="356" t="s">
-        <v>346</v>
-      </c>
-      <c r="C101" s="356"/>
-      <c r="D101" s="356"/>
-      <c r="E101" s="356"/>
-      <c r="F101" s="356"/>
+      <c r="B101" s="360" t="s">
+        <v>341</v>
+      </c>
+      <c r="C101" s="360"/>
+      <c r="D101" s="360"/>
+      <c r="E101" s="360"/>
+      <c r="F101" s="360"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C102" s="349">
         <f>DCF!C7</f>
@@ -5117,7 +5127,7 @@
     </row>
     <row r="103" spans="2:6">
       <c r="B103" s="47" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C103" s="223">
         <f>C102*scaling_factor*Exchange_Rate/Common_Shares</f>
@@ -5130,7 +5140,7 @@
     </row>
     <row r="104" spans="2:6">
       <c r="B104" s="296" t="s">
-        <v>407</v>
+        <v>401</v>
       </c>
       <c r="C104" s="325">
         <f>IF(BS!G31/BS!G27&gt;300%,"nm",BS!G31/BS!G27)</f>
@@ -5139,7 +5149,7 @@
     </row>
     <row r="105" spans="2:6">
       <c r="B105" s="296" t="s">
-        <v>409</v>
+        <v>403</v>
       </c>
       <c r="C105" s="326">
         <f>IF(BS!C50&gt;30,"nm",BS!C50)</f>
@@ -5148,12 +5158,12 @@
     </row>
     <row r="107" spans="2:6">
       <c r="B107" s="1" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="108" spans="2:6">
       <c r="B108" s="47" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C108" s="349">
         <f>BS!C66</f>
@@ -5166,7 +5176,7 @@
     </row>
     <row r="109" spans="2:6">
       <c r="B109" s="47" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C109" s="349">
         <f>DCF!C8</f>
@@ -5179,7 +5189,7 @@
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="47" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C110" s="223">
         <f>C109*scaling_factor*Exchange_Rate/Common_Shares</f>
@@ -5192,12 +5202,12 @@
     </row>
     <row r="112" spans="2:6">
       <c r="B112" s="1" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="113" spans="1:6">
       <c r="B113" s="47" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C113" s="349">
         <f>DCF!C9</f>
@@ -5210,7 +5220,7 @@
     </row>
     <row r="114" spans="1:6">
       <c r="B114" s="47" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C114" s="223">
         <f>C113*scaling_factor*Exchange_Rate/Common_Shares</f>
@@ -5222,17 +5232,17 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="356" t="s">
-        <v>369</v>
-      </c>
-      <c r="C116" s="356"/>
-      <c r="D116" s="356"/>
-      <c r="E116" s="356"/>
-      <c r="F116" s="356"/>
+      <c r="B116" s="360" t="s">
+        <v>363</v>
+      </c>
+      <c r="C116" s="360"/>
+      <c r="D116" s="360"/>
+      <c r="E116" s="360"/>
+      <c r="F116" s="360"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
-        <v>451</v>
+        <v>445</v>
       </c>
       <c r="C118" s="223">
         <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
@@ -5245,7 +5255,7 @@
     </row>
     <row r="119" spans="1:6">
       <c r="B119" s="296" t="s">
-        <v>408</v>
+        <v>402</v>
       </c>
       <c r="C119" s="223">
         <f>BS!D47</f>
@@ -5258,7 +5268,7 @@
     </row>
     <row r="121" spans="1:6" ht="13.9">
       <c r="A121" s="222" t="s">
-        <v>361</v>
+        <v>355</v>
       </c>
       <c r="B121" s="36"/>
       <c r="C121" s="36"/>
@@ -5267,29 +5277,29 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B123" s="357" t="s">
-        <v>370</v>
-      </c>
-      <c r="C123" s="357"/>
-      <c r="D123" s="357"/>
-      <c r="E123" s="357"/>
-      <c r="F123" s="357"/>
+      <c r="B123" s="361" t="s">
+        <v>364</v>
+      </c>
+      <c r="C123" s="361"/>
+      <c r="D123" s="361"/>
+      <c r="E123" s="361"/>
+      <c r="F123" s="361"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C125" s="233" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D125" s="233" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E125" s="233" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="F125" s="233" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="126" spans="1:6">
@@ -5404,7 +5414,7 @@
     </row>
     <row r="132" spans="1:6">
       <c r="B132" s="211" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C132" s="217">
         <f>Scenarios!C60</f>
@@ -5416,17 +5426,17 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="361" t="s">
-        <v>373</v>
-      </c>
-      <c r="C134" s="361"/>
-      <c r="D134" s="361"/>
-      <c r="E134" s="361"/>
-      <c r="F134" s="361"/>
+      <c r="B134" s="364" t="s">
+        <v>367</v>
+      </c>
+      <c r="C134" s="364"/>
+      <c r="D134" s="364"/>
+      <c r="E134" s="364"/>
+      <c r="F134" s="364"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
-        <v>405</v>
+        <v>399</v>
       </c>
       <c r="B136" s="36"/>
       <c r="C136" s="36"/>
@@ -5435,31 +5445,31 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="359" t="s">
-        <v>371</v>
-      </c>
-      <c r="C138" s="359"/>
-      <c r="D138" s="359"/>
-      <c r="E138" s="359"/>
-      <c r="F138" s="359"/>
+      <c r="B138" s="365" t="s">
+        <v>365</v>
+      </c>
+      <c r="C138" s="365"/>
+      <c r="D138" s="365"/>
+      <c r="E138" s="365"/>
+      <c r="F138" s="365"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="356" t="s">
-        <v>372</v>
-      </c>
-      <c r="C139" s="356"/>
-      <c r="D139" s="356"/>
-      <c r="E139" s="356"/>
-      <c r="F139" s="356"/>
+      <c r="B139" s="360" t="s">
+        <v>366</v>
+      </c>
+      <c r="C139" s="360"/>
+      <c r="D139" s="360"/>
+      <c r="E139" s="360"/>
+      <c r="F139" s="360"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="141" spans="1:6">
       <c r="B141" s="1" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C141" s="225">
         <f>F28</f>
@@ -5468,7 +5478,7 @@
     </row>
     <row r="142" spans="1:6">
       <c r="B142" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C142" s="224">
         <f>F29</f>
@@ -5477,7 +5487,7 @@
     </row>
     <row r="143" spans="1:6">
       <c r="B143" s="212" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C143" s="213">
         <f>Scenarios!C77</f>
@@ -5490,7 +5500,7 @@
     </row>
     <row r="145" spans="2:4">
       <c r="B145" s="210" t="s">
-        <v>411</v>
+        <v>405</v>
       </c>
       <c r="C145" s="241" t="str">
         <f>C11</f>
@@ -5503,7 +5513,7 @@
     </row>
     <row r="146" spans="2:4">
       <c r="B146" s="1" t="s">
-        <v>410</v>
+        <v>404</v>
       </c>
       <c r="C146" s="297">
         <f>F29</f>
@@ -5532,7 +5542,7 @@
     </row>
     <row r="149" spans="2:4">
       <c r="B149" s="80" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C149" s="215">
         <f>Scenarios!C83</f>
@@ -5545,7 +5555,7 @@
     </row>
     <row r="150" spans="2:4">
       <c r="B150" s="259" t="s">
-        <v>418</v>
+        <v>412</v>
       </c>
       <c r="C150" s="298" t="str">
         <f>Market_currency</f>
@@ -5558,7 +5568,7 @@
     </row>
     <row r="151" spans="2:4">
       <c r="B151" s="214" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C151" s="92">
         <f>Scenarios!F83</f>
@@ -5567,12 +5577,12 @@
     </row>
     <row r="153" spans="2:4">
       <c r="B153" s="210" t="s">
-        <v>414</v>
+        <v>408</v>
       </c>
     </row>
     <row r="154" spans="2:4">
       <c r="B154" s="1" t="s">
-        <v>413</v>
+        <v>407</v>
       </c>
       <c r="C154" s="297">
         <f>Scenarios!C90</f>
@@ -5601,7 +5611,7 @@
     </row>
     <row r="157" spans="2:4">
       <c r="B157" s="80" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C157" s="215">
         <f>Scenarios!C93</f>
@@ -5614,7 +5624,7 @@
     </row>
     <row r="158" spans="2:4">
       <c r="B158" s="259" t="s">
-        <v>418</v>
+        <v>412</v>
       </c>
       <c r="C158" s="298" t="str">
         <f>Market_currency</f>
@@ -5627,7 +5637,7 @@
     </row>
     <row r="159" spans="2:4">
       <c r="B159" s="214" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C159" s="92">
         <f>Scenarios!F93</f>
@@ -5636,12 +5646,12 @@
     </row>
     <row r="161" spans="2:4">
       <c r="B161" s="210" t="s">
-        <v>403</v>
+        <v>397</v>
       </c>
     </row>
     <row r="162" spans="2:4">
       <c r="B162" s="1" t="s">
-        <v>412</v>
+        <v>406</v>
       </c>
       <c r="C162" s="92">
         <f>Scenarios!C96</f>
@@ -5670,7 +5680,7 @@
     </row>
     <row r="165" spans="2:4">
       <c r="B165" s="80" t="s">
-        <v>404</v>
+        <v>398</v>
       </c>
       <c r="C165" s="215">
         <f>Scenarios!C99</f>
@@ -5683,7 +5693,7 @@
     </row>
     <row r="166" spans="2:4">
       <c r="B166" s="259" t="s">
-        <v>418</v>
+        <v>412</v>
       </c>
       <c r="C166" s="298" t="str">
         <f>Market_currency</f>
@@ -5696,7 +5706,7 @@
     </row>
     <row r="167" spans="2:4">
       <c r="B167" s="214" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C167" s="92">
         <f>Scenarios!F99</f>
@@ -5705,12 +5715,12 @@
     </row>
     <row r="169" spans="2:4">
       <c r="B169" s="210" t="s">
-        <v>434</v>
+        <v>428</v>
       </c>
     </row>
     <row r="170" spans="2:4">
       <c r="B170" s="1" t="s">
-        <v>425</v>
+        <v>419</v>
       </c>
       <c r="C170" s="92">
         <f>F32</f>
@@ -5739,7 +5749,7 @@
     </row>
     <row r="173" spans="2:4">
       <c r="B173" s="80" t="s">
-        <v>404</v>
+        <v>398</v>
       </c>
       <c r="C173" s="215">
         <f>Scenarios!C105</f>
@@ -5752,7 +5762,7 @@
     </row>
     <row r="174" spans="2:4">
       <c r="B174" s="259" t="s">
-        <v>418</v>
+        <v>412</v>
       </c>
       <c r="C174" s="298" t="str">
         <f>Market_currency</f>
@@ -5765,7 +5775,7 @@
     </row>
     <row r="175" spans="2:4">
       <c r="B175" s="214" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C175" s="92">
         <f>Scenarios!F105</f>
@@ -5774,7 +5784,7 @@
     </row>
     <row r="177" spans="1:6" ht="13.9">
       <c r="A177" s="222" t="s">
-        <v>377</v>
+        <v>371</v>
       </c>
       <c r="B177" s="36"/>
       <c r="C177" s="36"/>
@@ -5783,113 +5793,102 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="363" t="s">
-        <v>379</v>
-      </c>
-      <c r="C179" s="356"/>
-      <c r="D179" s="356"/>
-      <c r="E179" s="356"/>
-      <c r="F179" s="356"/>
+      <c r="B179" s="359" t="s">
+        <v>373</v>
+      </c>
+      <c r="C179" s="360"/>
+      <c r="D179" s="360"/>
+      <c r="E179" s="360"/>
+      <c r="F179" s="360"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
-        <v>378</v>
+        <v>372</v>
       </c>
     </row>
     <row r="182" spans="1:6">
-      <c r="B182" s="360" t="s">
-        <v>383</v>
-      </c>
-      <c r="C182" s="360"/>
-      <c r="D182" s="360"/>
-      <c r="E182" s="360"/>
-      <c r="F182" s="360"/>
+      <c r="B182" s="362" t="s">
+        <v>377</v>
+      </c>
+      <c r="C182" s="362"/>
+      <c r="D182" s="362"/>
+      <c r="E182" s="362"/>
+      <c r="F182" s="362"/>
     </row>
     <row r="183" spans="1:6">
       <c r="B183" s="214" t="s">
-        <v>380</v>
+        <v>374</v>
       </c>
     </row>
     <row r="184" spans="1:6">
       <c r="B184" s="214" t="s">
-        <v>381</v>
+        <v>375</v>
       </c>
     </row>
     <row r="185" spans="1:6">
       <c r="B185" s="214" t="s">
-        <v>382</v>
+        <v>376</v>
       </c>
     </row>
     <row r="187" spans="1:6">
       <c r="B187" s="1" t="s">
-        <v>387</v>
+        <v>381</v>
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="357" t="s">
-        <v>384</v>
-      </c>
-      <c r="C188" s="357"/>
-      <c r="D188" s="357"/>
-      <c r="E188" s="357"/>
-      <c r="F188" s="357"/>
+      <c r="B188" s="361" t="s">
+        <v>378</v>
+      </c>
+      <c r="C188" s="361"/>
+      <c r="D188" s="361"/>
+      <c r="E188" s="361"/>
+      <c r="F188" s="361"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
-        <v>388</v>
+        <v>382</v>
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="362" t="s">
-        <v>385</v>
-      </c>
-      <c r="C191" s="362"/>
-      <c r="D191" s="362"/>
-      <c r="E191" s="362"/>
-      <c r="F191" s="362"/>
+      <c r="B191" s="358" t="s">
+        <v>379</v>
+      </c>
+      <c r="C191" s="358"/>
+      <c r="D191" s="358"/>
+      <c r="E191" s="358"/>
+      <c r="F191" s="358"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="362" t="s">
-        <v>386</v>
-      </c>
-      <c r="C192" s="362"/>
-      <c r="D192" s="362"/>
-      <c r="E192" s="362"/>
-      <c r="F192" s="362"/>
+      <c r="B192" s="358" t="s">
+        <v>380</v>
+      </c>
+      <c r="C192" s="358"/>
+      <c r="D192" s="358"/>
+      <c r="E192" s="358"/>
+      <c r="F192" s="358"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
-        <v>392</v>
+        <v>386</v>
       </c>
     </row>
     <row r="195" spans="2:2">
       <c r="B195" s="214" t="s">
-        <v>389</v>
+        <v>383</v>
       </c>
     </row>
     <row r="196" spans="2:2">
       <c r="B196" s="214" t="s">
-        <v>390</v>
+        <v>384</v>
       </c>
     </row>
     <row r="197" spans="2:2">
       <c r="B197" s="214" t="s">
-        <v>391</v>
+        <v>385</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5906,6 +5905,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -6143,7 +6153,7 @@
     </row>
     <row r="9" spans="2:13">
       <c r="B9" s="40" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C9" s="351"/>
       <c r="D9" s="351"/>
@@ -6159,7 +6169,7 @@
     </row>
     <row r="10" spans="2:13">
       <c r="B10" s="40" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C10" s="351"/>
       <c r="D10" s="351"/>
@@ -6175,7 +6185,7 @@
     </row>
     <row r="11" spans="2:13">
       <c r="B11" s="40" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C11" s="351"/>
       <c r="D11" s="351"/>
@@ -6383,7 +6393,7 @@
     </row>
     <row r="22" spans="2:13">
       <c r="B22" s="27" t="s">
-        <v>374</v>
+        <v>368</v>
       </c>
       <c r="C22" s="351">
         <v>1651617</v>
@@ -6413,7 +6423,7 @@
     </row>
     <row r="23" spans="2:13">
       <c r="B23" s="27" t="s">
-        <v>376</v>
+        <v>370</v>
       </c>
       <c r="C23" s="351">
         <v>-462453</v>
@@ -6443,7 +6453,7 @@
     </row>
     <row r="24" spans="2:13">
       <c r="B24" s="27" t="s">
-        <v>375</v>
+        <v>369</v>
       </c>
       <c r="C24" s="351">
         <v>-875470</v>
@@ -6502,7 +6512,7 @@
         <v>28</v>
       </c>
       <c r="C27" s="97" t="s">
-        <v>219</v>
+        <v>464</v>
       </c>
     </row>
     <row r="28" spans="2:13">
@@ -6655,7 +6665,7 @@
     </row>
     <row r="32" spans="2:13">
       <c r="B32" s="26" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C32" s="333">
         <f>BS!G28</f>
@@ -7056,7 +7066,7 @@
     </row>
     <row r="43" spans="2:13">
       <c r="B43" s="43" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C43" s="334">
         <f>IF(C$4="","",C38+C39+C42)</f>
@@ -7105,7 +7115,7 @@
     </row>
     <row r="44" spans="2:13">
       <c r="B44" s="43" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C44" s="354">
         <f t="shared" ref="C44:M44" si="18">IF(C$4="","",C47-C46-C45-C43)</f>
@@ -7453,12 +7463,12 @@
     </row>
     <row r="54" spans="2:13">
       <c r="B54" s="174" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="55" spans="2:13">
       <c r="B55" s="40" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C55" s="349">
         <f t="shared" ref="C55:M55" si="25">IF(C$4="","",C9)</f>
@@ -7507,7 +7517,7 @@
     </row>
     <row r="56" spans="2:13">
       <c r="B56" s="40" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C56" s="349">
         <f t="shared" ref="C56:M56" si="26">IF(C$4="","",C10)</f>
@@ -7556,7 +7566,7 @@
     </row>
     <row r="57" spans="2:13">
       <c r="B57" s="40" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C57" s="349">
         <f t="shared" ref="C57:M57" si="27">IF(C$4="","",C11)</f>
@@ -7605,7 +7615,7 @@
     </row>
     <row r="58" spans="2:13">
       <c r="B58" s="40" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C58" s="349">
         <f>IF(C$4="","",C44-C55-C56-C57)</f>
@@ -7807,7 +7817,7 @@
     </row>
     <row r="64" spans="2:13">
       <c r="B64" s="27" t="s">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="C64" s="333">
         <f>IF(C$4="","",C22+C23+C24)</f>
@@ -8059,7 +8069,7 @@
     </row>
     <row r="71" spans="2:13">
       <c r="B71" s="43" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C71" s="101">
         <f>IF(D$36="","",C44/D44-1)</f>
@@ -8454,7 +8464,7 @@
     </row>
     <row r="2" spans="2:8" ht="15" customHeight="1">
       <c r="B2" s="79" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C2" s="37"/>
       <c r="D2" s="37"/>
@@ -8465,19 +8475,19 @@
     </row>
     <row r="3" spans="2:8" ht="15" customHeight="1">
       <c r="B3" s="16" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C3" s="182" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D3" s="183" t="s">
         <v>35</v>
       </c>
       <c r="F3" s="16" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="G3" s="182" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H3" s="183" t="s">
         <v>35</v>
@@ -8538,7 +8548,7 @@
       </c>
       <c r="E6" s="25"/>
       <c r="F6" s="4" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="G6" s="19">
         <v>0</v>
@@ -8559,7 +8569,7 @@
       </c>
       <c r="E7" s="25"/>
       <c r="F7" s="4" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="G7" s="19">
         <v>0</v>
@@ -8570,7 +8580,7 @@
     </row>
     <row r="8" spans="2:8" ht="15" customHeight="1">
       <c r="B8" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C8" s="19">
         <v>0</v>
@@ -8580,7 +8590,7 @@
       </c>
       <c r="E8" s="25"/>
       <c r="F8" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="G8" s="19">
         <v>0</v>
@@ -8601,7 +8611,7 @@
       </c>
       <c r="E9" s="25"/>
       <c r="F9" s="4" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G9" s="19">
         <v>0</v>
@@ -8665,19 +8675,19 @@
     </row>
     <row r="14" spans="2:8" ht="15" customHeight="1">
       <c r="B14" s="16" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C14" s="182" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D14" s="183" t="s">
         <v>35</v>
       </c>
       <c r="F14" s="16" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="G14" s="182" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H14" s="183" t="s">
         <v>35</v>
@@ -8685,7 +8695,7 @@
     </row>
     <row r="15" spans="2:8" ht="15" customHeight="1">
       <c r="B15" s="4" t="s">
-        <v>457</v>
+        <v>451</v>
       </c>
       <c r="C15" s="19">
         <v>369</v>
@@ -8714,7 +8724,7 @@
         <v>0.5</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="G16" s="19">
         <v>0</v>
@@ -8734,7 +8744,7 @@
         <v>0.6</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="G17" s="19">
         <v>0</v>
@@ -8745,7 +8755,7 @@
     </row>
     <row r="18" spans="2:8" ht="15" customHeight="1">
       <c r="B18" s="4" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C18" s="19">
         <v>0</v>
@@ -8754,7 +8764,7 @@
         <v>0.6</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="G18" s="19">
         <v>0</v>
@@ -8775,7 +8785,7 @@
         <v>0.1</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G19" s="19">
         <v>37624</v>
@@ -8795,7 +8805,7 @@
         <v>0.05</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="G20" s="19">
         <v>0</v>
@@ -8815,7 +8825,7 @@
         <v>0.05</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G21" s="19">
         <v>0</v>
@@ -8874,16 +8884,16 @@
     </row>
     <row r="26" spans="2:8" ht="15" customHeight="1">
       <c r="B26" s="16" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C26" s="182" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F26" s="184" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G26" s="185" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H26" s="186" t="s">
         <v>35</v>
@@ -8916,7 +8926,7 @@
         <v>434135</v>
       </c>
       <c r="F28" s="189" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="G28" s="12">
         <v>20065</v>
@@ -8960,7 +8970,7 @@
     </row>
     <row r="31" spans="2:8" ht="15" customHeight="1">
       <c r="B31" s="80" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C31" s="81">
         <f>SUM(C27:C30)</f>
@@ -9010,10 +9020,10 @@
       <c r="B34" s="83"/>
       <c r="C34" s="84"/>
       <c r="F34" s="196" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="G34" s="197" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H34" s="198" t="s">
         <v>35</v>
@@ -9021,10 +9031,10 @@
     </row>
     <row r="35" spans="2:8" ht="15" customHeight="1">
       <c r="B35" s="16" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C35" s="182" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F35" s="199" t="s">
         <v>31</v>
@@ -9046,7 +9056,7 @@
         <v>220941</v>
       </c>
       <c r="F36" s="190" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="G36" s="191">
         <f>C4+C15</f>
@@ -9062,7 +9072,7 @@
         <v>0</v>
       </c>
       <c r="F37" s="190" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G37" s="191">
         <f>C6</f>
@@ -9078,7 +9088,7 @@
         <v>0</v>
       </c>
       <c r="F38" s="190" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G38" s="191">
         <f>C7+C17</f>
@@ -9107,14 +9117,14 @@
     </row>
     <row r="40" spans="2:8" ht="15" customHeight="1">
       <c r="B40" s="80" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C40" s="81">
         <f>SUM(C36:C39)</f>
         <v>221340</v>
       </c>
       <c r="F40" s="199" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="G40" s="193">
         <f>G12+G24</f>
@@ -9134,7 +9144,7 @@
         <v>2225737</v>
       </c>
       <c r="F41" s="190" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="G41" s="191">
         <f>C70</f>
@@ -9153,7 +9163,7 @@
         <v>2447077</v>
       </c>
       <c r="F42" s="201" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="G42" s="202">
         <f>C82</f>
@@ -9177,13 +9187,13 @@
     </row>
     <row r="45" spans="2:8" ht="15" customHeight="1">
       <c r="B45" s="16" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C45" s="234" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D45" s="182" t="s">
-        <v>408</v>
+        <v>402</v>
       </c>
       <c r="F45" s="256" t="s">
         <v>59</v>
@@ -9191,7 +9201,7 @@
     </row>
     <row r="46" spans="2:8" ht="15" customHeight="1">
       <c r="B46" s="1" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C46" s="76">
         <f>G29</f>
@@ -9223,7 +9233,7 @@
     </row>
     <row r="49" spans="2:8" ht="15" customHeight="1">
       <c r="B49" s="157" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C49" s="235" t="s">
         <v>57</v>
@@ -9250,7 +9260,7 @@
     </row>
     <row r="51" spans="2:8" ht="15" customHeight="1">
       <c r="B51" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C51" s="181"/>
       <c r="D51" s="92">
@@ -9264,7 +9274,7 @@
     </row>
     <row r="53" spans="2:8" ht="15" customHeight="1">
       <c r="B53" s="157" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C53" s="235" t="s">
         <v>57</v>
@@ -9276,7 +9286,7 @@
     </row>
     <row r="54" spans="2:8" ht="15" customHeight="1">
       <c r="B54" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C54" s="92">
         <f>Normalized_FCF!C8/G35</f>
@@ -9290,7 +9300,7 @@
     </row>
     <row r="55" spans="2:8" ht="15" customHeight="1">
       <c r="B55" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C55" s="92">
         <f>Normalized_FCF!C11/G40</f>
@@ -9307,7 +9317,7 @@
     </row>
     <row r="57" spans="2:8" ht="15" customHeight="1">
       <c r="B57" s="157" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C57" s="235" t="s">
         <v>57</v>
@@ -9344,10 +9354,10 @@
     </row>
     <row r="61" spans="2:8" ht="15" customHeight="1">
       <c r="B61" s="157" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C61" s="235" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D61" s="197" t="s">
         <v>95</v>
@@ -9356,7 +9366,7 @@
     </row>
     <row r="62" spans="2:8" ht="15" customHeight="1">
       <c r="B62" s="1" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C62" s="92">
         <f>IF(G28&lt;=0,0,G28/G29)</f>
@@ -9367,12 +9377,12 @@
         <v>4.5608854914288765E-3</v>
       </c>
       <c r="F62" s="253" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="64" spans="2:8" ht="15" customHeight="1">
       <c r="B64" s="79" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C64" s="37"/>
       <c r="D64" s="37"/>
@@ -9383,13 +9393,13 @@
     </row>
     <row r="65" spans="2:6" ht="15" customHeight="1">
       <c r="B65" s="16" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C65" s="234" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D65" s="183" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="F65" s="256" t="s">
         <v>59</v>
@@ -9397,7 +9407,7 @@
     </row>
     <row r="66" spans="2:6" ht="15" customHeight="1">
       <c r="B66" s="105" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C66" s="20">
         <f>G4+G5+G15</f>
@@ -9408,12 +9418,12 @@
         <v>414442.7738145804</v>
       </c>
       <c r="F66" s="5" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="67" spans="2:6" ht="15" customHeight="1">
       <c r="B67" s="105" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C67" s="20">
         <f>G6+G16</f>
@@ -9423,7 +9433,7 @@
     </row>
     <row r="68" spans="2:6" ht="15" customHeight="1">
       <c r="B68" s="105" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C68" s="20">
         <f>G18</f>
@@ -9433,7 +9443,7 @@
     </row>
     <row r="69" spans="2:6" ht="15" customHeight="1">
       <c r="B69" s="105" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C69" s="20">
         <f>G8+G20</f>
@@ -9443,7 +9453,7 @@
     </row>
     <row r="70" spans="2:6" ht="15" customHeight="1">
       <c r="B70" s="80" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C70" s="81">
         <f>SUM(C66:C69)</f>
@@ -9456,7 +9466,7 @@
     </row>
     <row r="72" spans="2:6" ht="15" customHeight="1">
       <c r="B72" s="255" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="C72" s="234" t="s">
         <v>95</v>
@@ -9468,7 +9478,7 @@
     </row>
     <row r="73" spans="2:6" ht="15" customHeight="1">
       <c r="B73" s="105" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="C73" s="349">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35-Normalized_FCF!G91)/12</f>
@@ -9479,12 +9489,12 @@
         <v>-597120.2261854196</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>353</v>
+        <v>348</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="15" customHeight="1">
       <c r="B74" s="257" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="C74" s="258">
         <f>-$C$66/C73</f>
@@ -9495,12 +9505,12 @@
         <v>1.6940692270000017</v>
       </c>
       <c r="F74" s="253" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
     </row>
     <row r="75" spans="2:6" ht="15" customHeight="1">
       <c r="B75" s="80" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="C75" s="320"/>
       <c r="D75" s="321">
@@ -9508,12 +9518,12 @@
         <v>597120.2261854196</v>
       </c>
       <c r="F75" s="253" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
     </row>
     <row r="76" spans="2:6" ht="15" customHeight="1">
       <c r="B76" s="259" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="C76" s="260"/>
       <c r="D76" s="290">
@@ -9521,7 +9531,7 @@
         <v>1</v>
       </c>
       <c r="F76" s="253" t="s">
-        <v>325</v>
+        <v>320</v>
       </c>
     </row>
     <row r="77" spans="2:6" ht="15" customHeight="1">
@@ -9529,10 +9539,10 @@
     </row>
     <row r="78" spans="2:6" ht="15" customHeight="1">
       <c r="B78" s="16" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C78" s="234" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D78" s="183" t="s">
         <v>35</v>
@@ -9541,7 +9551,7 @@
     </row>
     <row r="79" spans="2:6" ht="15" customHeight="1">
       <c r="B79" s="105" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C79" s="20">
         <f>G7+G17</f>
@@ -9555,7 +9565,7 @@
     </row>
     <row r="80" spans="2:6" ht="15" customHeight="1">
       <c r="B80" s="105" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C80" s="20">
         <f>G19</f>
@@ -9569,7 +9579,7 @@
     </row>
     <row r="81" spans="2:8" ht="15" customHeight="1">
       <c r="B81" s="105" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C81" s="20">
         <f>G9+G21</f>
@@ -9583,7 +9593,7 @@
     </row>
     <row r="82" spans="2:8" ht="15" customHeight="1">
       <c r="B82" s="80" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C82" s="81">
         <f>SUM(C79:C81)</f>
@@ -9597,7 +9607,7 @@
     </row>
     <row r="84" spans="2:8" ht="15" customHeight="1">
       <c r="B84" s="79" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="C84" s="37"/>
       <c r="D84" s="37"/>
@@ -9608,15 +9618,15 @@
     </row>
     <row r="85" spans="2:8" ht="15" customHeight="1">
       <c r="B85" s="16" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="D85" s="241" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
     </row>
     <row r="86" spans="2:8" ht="15" customHeight="1">
       <c r="B86" s="238" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="C86" s="76">
         <f>-DCF!C7*Exchange_Rate</f>
@@ -9633,7 +9643,7 @@
     </row>
     <row r="87" spans="2:8" ht="15" customHeight="1">
       <c r="B87" s="238" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="C87" s="76">
         <f>DCF!C8*Exchange_Rate</f>
@@ -9650,7 +9660,7 @@
     </row>
     <row r="88" spans="2:8" ht="15" customHeight="1">
       <c r="B88" s="239" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C88" s="76">
         <f>DCF!C9*Exchange_Rate</f>
@@ -9667,7 +9677,7 @@
     </row>
     <row r="89" spans="2:8" ht="15" customHeight="1">
       <c r="B89" s="80" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C89" s="180">
         <f>SUM(C86:C88)</f>
@@ -9695,7 +9705,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q808"/>
+  <dimension ref="A1:Q809"/>
   <sheetFormatPr defaultColWidth="12.265625" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="1.265625" style="2" customWidth="1"/>
@@ -10027,7 +10037,7 @@
     <row r="8" spans="1:17" ht="15.75" customHeight="1">
       <c r="A8" s="10"/>
       <c r="B8" s="29" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C8" s="330">
         <f>C6+C7</f>
@@ -10194,7 +10204,7 @@
     <row r="11" spans="1:17" ht="15.75" customHeight="1">
       <c r="A11" s="10"/>
       <c r="B11" s="31" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C11" s="331">
         <f>C63</f>
@@ -10306,7 +10316,7 @@
     <row r="13" spans="1:17" ht="15.75" customHeight="1">
       <c r="A13" s="10"/>
       <c r="B13" s="70" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C13" s="329">
         <f>SUM(C8:C12)</f>
@@ -10416,7 +10426,7 @@
     <row r="15" spans="1:17" ht="15.75" customHeight="1">
       <c r="A15" s="10"/>
       <c r="B15" s="40" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C15" s="328">
         <f>-C4*C83</f>
@@ -10473,7 +10483,7 @@
     <row r="16" spans="1:17" ht="15.75" customHeight="1">
       <c r="A16" s="10"/>
       <c r="B16" s="41" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C16" s="332">
         <f>SUM(C13:C15)</f>
@@ -10538,7 +10548,7 @@
       </c>
       <c r="D17" s="58"/>
       <c r="E17" s="267" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="F17" s="58"/>
       <c r="G17" s="335"/>
@@ -10563,7 +10573,7 @@
       </c>
       <c r="D18" s="58"/>
       <c r="E18" s="267" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="F18" s="58"/>
       <c r="G18" s="336"/>
@@ -10657,7 +10667,7 @@
     <row r="21" spans="1:17" ht="15.75" customHeight="1">
       <c r="A21" s="10"/>
       <c r="B21" s="54" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C21" s="54"/>
       <c r="D21" s="56"/>
@@ -10876,7 +10886,7 @@
     <row r="27" spans="1:17" ht="15.75" customHeight="1">
       <c r="A27" s="10"/>
       <c r="B27" s="64" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E27" s="268"/>
     </row>
@@ -10891,7 +10901,7 @@
       </c>
       <c r="D28" s="26"/>
       <c r="E28" s="266" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="F28" s="26"/>
       <c r="G28" s="13">
@@ -10951,7 +10961,7 @@
       </c>
       <c r="D29" s="26"/>
       <c r="E29" s="266" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="F29" s="26"/>
       <c r="G29" s="13">
@@ -11068,14 +11078,14 @@
     <row r="33" spans="1:17" ht="15.75" customHeight="1">
       <c r="A33" s="10"/>
       <c r="B33" s="8" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C33" s="340">
         <f>AVERAGE(G33:J33)</f>
         <v>-283216.75</v>
       </c>
       <c r="E33" s="266" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="G33" s="328">
         <f>Data!C41</f>
@@ -11133,7 +11143,7 @@
       </c>
       <c r="D34" s="58"/>
       <c r="E34" s="266" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="F34" s="58"/>
       <c r="G34" s="333">
@@ -11245,7 +11255,7 @@
     <row r="37" spans="1:17" ht="15.75" customHeight="1">
       <c r="A37" s="10"/>
       <c r="B37" s="64" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E37" s="268"/>
     </row>
@@ -11427,21 +11437,21 @@
     <row r="42" spans="1:17" ht="15.75" customHeight="1">
       <c r="A42" s="10"/>
       <c r="B42" s="64" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E42" s="268"/>
     </row>
     <row r="43" spans="1:17" ht="15.75" customHeight="1">
       <c r="A43" s="10"/>
       <c r="B43" s="27" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C43" s="263">
         <v>0.25</v>
       </c>
       <c r="D43" s="27"/>
       <c r="E43" s="265" t="s">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="F43" s="27"/>
       <c r="G43" s="6">
@@ -11495,7 +11505,7 @@
     <row r="45" spans="1:17" ht="15.75" customHeight="1">
       <c r="A45" s="10"/>
       <c r="B45" s="54" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C45" s="54"/>
       <c r="D45" s="56"/>
@@ -11580,7 +11590,7 @@
     <row r="48" spans="1:17" ht="15.75" customHeight="1">
       <c r="A48" s="10"/>
       <c r="B48" s="2" t="s">
-        <v>347</v>
+        <v>342</v>
       </c>
       <c r="C48" s="328">
         <f>BS!D75*C53</f>
@@ -11635,7 +11645,7 @@
     <row r="49" spans="1:17" ht="15.75" customHeight="1">
       <c r="A49" s="10"/>
       <c r="B49" s="287" t="s">
-        <v>344</v>
+        <v>339</v>
       </c>
       <c r="C49" s="342">
         <f>BS!$C$66*C53</f>
@@ -11751,11 +11761,11 @@
     <row r="52" spans="1:17" ht="15.75" customHeight="1">
       <c r="A52" s="10"/>
       <c r="B52" s="72" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E52" s="268"/>
       <c r="G52" s="97" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="53" spans="1:17" ht="15.75" customHeight="1">
@@ -11767,7 +11777,7 @@
         <v>0</v>
       </c>
       <c r="E53" s="265" t="s">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="G53" s="6">
         <f>IF(Normalized_FCF!G4="","",Normalized_FCF!G49/BS!$C$66)</f>
@@ -11794,7 +11804,7 @@
         <v>0.10494864396999423</v>
       </c>
       <c r="E54" s="265" t="s">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="G54" s="23">
         <f>IFERROR(ABS(Normalized_FCF!G47/BS!$G$31),0)</f>
@@ -11873,17 +11883,17 @@
     <row r="57" spans="1:17" ht="15.75" customHeight="1">
       <c r="A57" s="10"/>
       <c r="B57" s="64" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E57" s="268"/>
       <c r="G57" s="97" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="58" spans="1:17" ht="15.75" customHeight="1">
       <c r="A58" s="10"/>
       <c r="B58" s="40" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C58" s="328">
         <f>BS!$C67*C66</f>
@@ -11938,7 +11948,7 @@
     <row r="59" spans="1:17" ht="15.75" customHeight="1">
       <c r="A59" s="10"/>
       <c r="B59" s="40" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C59" s="328">
         <f>BS!$C68*C67</f>
@@ -11993,7 +12003,7 @@
     <row r="60" spans="1:17" ht="15.75" customHeight="1">
       <c r="A60" s="10"/>
       <c r="B60" s="40" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C60" s="328">
         <f>BS!$C69*C68</f>
@@ -12048,7 +12058,7 @@
     <row r="61" spans="1:17" ht="15.75" customHeight="1">
       <c r="A61" s="10"/>
       <c r="B61" s="31" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C61" s="329">
         <f>SUM(C58:C60)</f>
@@ -12103,13 +12113,13 @@
     <row r="62" spans="1:17" ht="15.75" customHeight="1">
       <c r="A62" s="10"/>
       <c r="B62" s="40" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C62" s="343">
         <v>0</v>
       </c>
       <c r="E62" s="266" t="s">
-        <v>339</v>
+        <v>334</v>
       </c>
       <c r="G62" s="328">
         <f>Data!C58</f>
@@ -12159,7 +12169,7 @@
     <row r="63" spans="1:17" ht="15.75" customHeight="1">
       <c r="A63" s="10"/>
       <c r="B63" s="31" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C63" s="329">
         <f>C61+C62</f>
@@ -12218,17 +12228,17 @@
     <row r="65" spans="1:17" ht="15.75" customHeight="1">
       <c r="A65" s="10"/>
       <c r="B65" s="96" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E65" s="268"/>
       <c r="G65" s="97" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="66" spans="1:17" ht="15.75" customHeight="1">
       <c r="A66" s="10"/>
       <c r="B66" s="40" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C66" s="176">
         <f>G66</f>
@@ -12253,7 +12263,7 @@
     <row r="67" spans="1:17" ht="15.75" customHeight="1">
       <c r="A67" s="10"/>
       <c r="B67" s="105" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C67" s="176">
         <f>G67</f>
@@ -12278,7 +12288,7 @@
     <row r="68" spans="1:17" ht="15.75" customHeight="1">
       <c r="A68" s="10"/>
       <c r="B68" s="105" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C68" s="176">
         <f>G68</f>
@@ -12303,7 +12313,7 @@
     <row r="69" spans="1:17" ht="15.75" customHeight="1">
       <c r="A69" s="10"/>
       <c r="B69" s="31" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C69" s="71">
         <f>C61/BS!C70</f>
@@ -12333,7 +12343,7 @@
     <row r="71" spans="1:17" ht="15.75" customHeight="1">
       <c r="A71" s="10"/>
       <c r="B71" s="54" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C71" s="54"/>
       <c r="D71" s="56"/>
@@ -12356,7 +12366,7 @@
     <row r="72" spans="1:17" ht="15.75" customHeight="1">
       <c r="A72" s="10"/>
       <c r="B72" s="72" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C72" s="62"/>
       <c r="D72" s="27"/>
@@ -12548,7 +12558,7 @@
     <row r="76" spans="1:17" ht="15.75" customHeight="1">
       <c r="A76" s="10"/>
       <c r="B76" s="29" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C76" s="78">
         <f>ABS(C8/C$4)</f>
@@ -12670,7 +12680,7 @@
       </c>
       <c r="D78" s="27"/>
       <c r="E78" s="266" t="s">
-        <v>356</v>
+        <v>465</v>
       </c>
       <c r="F78" s="27"/>
       <c r="G78" s="6">
@@ -12721,7 +12731,7 @@
     <row r="79" spans="1:17" ht="15.75" customHeight="1">
       <c r="A79" s="10"/>
       <c r="B79" s="31" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C79" s="78">
         <f>ABS(C11/C$4)</f>
@@ -12835,7 +12845,7 @@
     <row r="81" spans="1:17" ht="15.75" customHeight="1">
       <c r="A81" s="10"/>
       <c r="B81" s="70" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C81" s="78">
         <f>C13/C4</f>
@@ -13007,7 +13017,7 @@
     <row r="84" spans="1:17" ht="15.75" customHeight="1">
       <c r="A84" s="10"/>
       <c r="B84" s="41" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C84" s="78">
         <f>ABS(C16/C$4)</f>
@@ -13114,7 +13124,7 @@
     <row r="87" spans="1:17" ht="15.75" customHeight="1">
       <c r="A87" s="10"/>
       <c r="B87" s="31" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C87" s="78">
         <f>ABS(C19/C$4)</f>
@@ -13175,7 +13185,7 @@
     <row r="89" spans="1:17" ht="15.75" customHeight="1">
       <c r="A89" s="10"/>
       <c r="B89" s="64" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="E89" s="268"/>
     </row>
@@ -13294,7 +13304,7 @@
     <row r="92" spans="1:17" ht="15.75" customHeight="1">
       <c r="A92" s="10"/>
       <c r="B92" s="2" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C92" s="23">
         <f>C90/(C19*scaling_factor/Common_Shares)</f>
@@ -13349,1310 +13359,1330 @@
     <row r="93" spans="1:17" ht="15.75" customHeight="1">
       <c r="A93" s="10"/>
       <c r="B93" s="2" t="s">
-        <v>310</v>
-      </c>
-      <c r="C93" s="23">
-        <f>C90/Market_Price</f>
+        <v>453</v>
+      </c>
+      <c r="C93" s="356">
+        <v>0</v>
+      </c>
+      <c r="E93" s="268"/>
+      <c r="G93" s="357"/>
+      <c r="H93" s="357"/>
+      <c r="I93" s="357"/>
+      <c r="J93" s="357"/>
+      <c r="K93" s="357"/>
+      <c r="L93" s="357"/>
+      <c r="M93" s="357"/>
+      <c r="N93" s="357"/>
+      <c r="O93" s="357"/>
+      <c r="P93" s="357"/>
+      <c r="Q93" s="357"/>
+    </row>
+    <row r="94" spans="1:17" ht="15.75" customHeight="1">
+      <c r="A94" s="10"/>
+      <c r="B94" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="C94" s="23">
+        <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
         <v>2.9358308688334996E-2</v>
       </c>
-      <c r="E93" s="268"/>
-      <c r="G93" s="23">
-        <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
+      <c r="E94" s="268"/>
+      <c r="G94" s="23">
+        <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
         <v>2.9358308688334996E-2</v>
       </c>
-      <c r="H93" s="23">
+      <c r="H94" s="23">
         <f t="shared" si="39"/>
         <v>2.45249285994018E-2</v>
       </c>
-      <c r="I93" s="23">
+      <c r="I94" s="23">
         <f t="shared" si="39"/>
         <v>1.9691548510468594E-2</v>
       </c>
-      <c r="J93" s="23">
+      <c r="J94" s="23">
         <f t="shared" si="39"/>
         <v>0</v>
       </c>
-      <c r="K93" s="23">
+      <c r="K94" s="23">
         <f t="shared" si="39"/>
         <v>0</v>
       </c>
-      <c r="L93" s="23">
+      <c r="L94" s="23">
         <f t="shared" si="39"/>
         <v>0</v>
       </c>
-      <c r="M93" s="23">
+      <c r="M94" s="23">
         <f t="shared" si="39"/>
         <v>0</v>
       </c>
-      <c r="N93" s="23" t="str">
+      <c r="N94" s="23" t="str">
         <f t="shared" si="39"/>
         <v/>
       </c>
-      <c r="O93" s="23" t="str">
+      <c r="O94" s="23" t="str">
         <f t="shared" si="39"/>
         <v/>
       </c>
-      <c r="P93" s="23" t="str">
+      <c r="P94" s="23" t="str">
         <f t="shared" si="39"/>
         <v/>
       </c>
-      <c r="Q93" s="23" t="str">
+      <c r="Q94" s="23" t="str">
         <f t="shared" si="39"/>
         <v/>
       </c>
-    </row>
-    <row r="94" spans="1:17" ht="15.75" customHeight="1">
-      <c r="A94" s="10"/>
-      <c r="E94" s="268"/>
     </row>
     <row r="95" spans="1:17" ht="15.75" customHeight="1">
       <c r="A95" s="10"/>
-      <c r="B95" s="157" t="s">
-        <v>84</v>
-      </c>
-      <c r="C95" s="62"/>
-      <c r="D95" s="27"/>
-      <c r="E95" s="265"/>
-      <c r="F95" s="27"/>
-      <c r="G95" s="12"/>
-      <c r="H95" s="12"/>
-      <c r="I95" s="12"/>
-      <c r="J95" s="12"/>
-      <c r="K95" s="12"/>
-      <c r="L95" s="12"/>
-      <c r="M95" s="12"/>
-      <c r="N95" s="12"/>
-      <c r="O95" s="12"/>
-      <c r="P95" s="12"/>
-      <c r="Q95" s="12"/>
+      <c r="E95" s="268"/>
     </row>
     <row r="96" spans="1:17" ht="15.75" customHeight="1">
       <c r="A96" s="10"/>
-      <c r="B96" s="27" t="s">
-        <v>144</v>
-      </c>
-      <c r="C96" s="77">
-        <f>C4/G4-1</f>
-        <v>-0.18645509933891879</v>
-      </c>
+      <c r="B96" s="157" t="s">
+        <v>84</v>
+      </c>
+      <c r="C96" s="62"/>
       <c r="D96" s="27"/>
       <c r="E96" s="265"/>
       <c r="F96" s="27"/>
-      <c r="G96" s="6">
-        <f t="shared" ref="G96:Q96" si="40">IF(H4="","",G4/H4-1)</f>
-        <v>0.14919269610704622</v>
-      </c>
-      <c r="H96" s="6">
-        <f t="shared" si="40"/>
-        <v>0.1251553917299939</v>
-      </c>
-      <c r="I96" s="6">
-        <f t="shared" si="40"/>
-        <v>0.26655269521380198</v>
-      </c>
-      <c r="J96" s="6">
-        <f t="shared" si="40"/>
-        <v>0.36895472438426102</v>
-      </c>
-      <c r="K96" s="6">
-        <f t="shared" si="40"/>
-        <v>-0.24890144264901282</v>
-      </c>
-      <c r="L96" s="6">
-        <f t="shared" si="40"/>
-        <v>2.655699222315433E-2</v>
-      </c>
-      <c r="M96" s="6" t="str">
-        <f t="shared" si="40"/>
-        <v/>
-      </c>
-      <c r="N96" s="6" t="str">
-        <f t="shared" si="40"/>
-        <v/>
-      </c>
-      <c r="O96" s="6" t="str">
-        <f t="shared" si="40"/>
-        <v/>
-      </c>
-      <c r="P96" s="6" t="str">
-        <f t="shared" si="40"/>
-        <v/>
-      </c>
-      <c r="Q96" s="6" t="str">
-        <f t="shared" si="40"/>
-        <v/>
-      </c>
+      <c r="G96" s="12"/>
+      <c r="H96" s="12"/>
+      <c r="I96" s="12"/>
+      <c r="J96" s="12"/>
+      <c r="K96" s="12"/>
+      <c r="L96" s="12"/>
+      <c r="M96" s="12"/>
+      <c r="N96" s="12"/>
+      <c r="O96" s="12"/>
+      <c r="P96" s="12"/>
+      <c r="Q96" s="12"/>
     </row>
     <row r="97" spans="1:17" ht="15.75" customHeight="1">
       <c r="A97" s="10"/>
-      <c r="B97" s="70" t="s">
-        <v>164</v>
+      <c r="B97" s="27" t="s">
+        <v>143</v>
       </c>
       <c r="C97" s="77">
-        <f>C13/G13-1</f>
-        <v>-0.30953946468866189</v>
+        <f>C4/G4-1</f>
+        <v>-0.18645509933891879</v>
       </c>
       <c r="D97" s="27"/>
       <c r="E97" s="265"/>
       <c r="F97" s="27"/>
       <c r="G97" s="6">
-        <f t="shared" ref="G97:Q97" si="41">IF(H5="","",G13/H13-1)</f>
+        <f t="shared" ref="G97:Q97" si="40">IF(H4="","",G4/H4-1)</f>
+        <v>0.14919269610704622</v>
+      </c>
+      <c r="H97" s="6">
+        <f t="shared" si="40"/>
+        <v>0.1251553917299939</v>
+      </c>
+      <c r="I97" s="6">
+        <f t="shared" si="40"/>
+        <v>0.26655269521380198</v>
+      </c>
+      <c r="J97" s="6">
+        <f t="shared" si="40"/>
+        <v>0.36895472438426102</v>
+      </c>
+      <c r="K97" s="6">
+        <f t="shared" si="40"/>
+        <v>-0.24890144264901282</v>
+      </c>
+      <c r="L97" s="6">
+        <f t="shared" si="40"/>
+        <v>2.655699222315433E-2</v>
+      </c>
+      <c r="M97" s="6" t="str">
+        <f t="shared" si="40"/>
+        <v/>
+      </c>
+      <c r="N97" s="6" t="str">
+        <f t="shared" si="40"/>
+        <v/>
+      </c>
+      <c r="O97" s="6" t="str">
+        <f t="shared" si="40"/>
+        <v/>
+      </c>
+      <c r="P97" s="6" t="str">
+        <f t="shared" si="40"/>
+        <v/>
+      </c>
+      <c r="Q97" s="6" t="str">
+        <f t="shared" si="40"/>
+        <v/>
+      </c>
+    </row>
+    <row r="98" spans="1:17" ht="15.75" customHeight="1">
+      <c r="A98" s="10"/>
+      <c r="B98" s="70" t="s">
+        <v>163</v>
+      </c>
+      <c r="C98" s="77">
+        <f>C13/G13-1</f>
+        <v>-0.30953946468866189</v>
+      </c>
+      <c r="D98" s="27"/>
+      <c r="E98" s="265"/>
+      <c r="F98" s="27"/>
+      <c r="G98" s="6">
+        <f t="shared" ref="G98:Q98" si="41">IF(H5="","",G13/H13-1)</f>
         <v>0.20085032618426824</v>
       </c>
-      <c r="H97" s="6">
+      <c r="H98" s="6">
         <f t="shared" si="41"/>
         <v>0.22211784706254156</v>
       </c>
-      <c r="I97" s="6">
+      <c r="I98" s="6">
         <f t="shared" si="41"/>
         <v>0.88128758198074086</v>
       </c>
-      <c r="J97" s="6">
+      <c r="J98" s="6">
         <f t="shared" si="41"/>
         <v>-0.72021730227179648</v>
       </c>
-      <c r="K97" s="6">
+      <c r="K98" s="6">
         <f t="shared" si="41"/>
         <v>-0.24841826995204375</v>
       </c>
-      <c r="L97" s="6">
+      <c r="L98" s="6">
         <f t="shared" si="41"/>
         <v>2.5200278971835077E-2</v>
       </c>
-      <c r="M97" s="6" t="str">
+      <c r="M98" s="6" t="str">
         <f t="shared" si="41"/>
         <v/>
       </c>
-      <c r="N97" s="6" t="str">
+      <c r="N98" s="6" t="str">
         <f t="shared" si="41"/>
         <v/>
       </c>
-      <c r="O97" s="6" t="str">
+      <c r="O98" s="6" t="str">
         <f t="shared" si="41"/>
         <v/>
       </c>
-      <c r="P97" s="6" t="str">
+      <c r="P98" s="6" t="str">
         <f t="shared" si="41"/>
         <v/>
       </c>
-      <c r="Q97" s="6" t="str">
+      <c r="Q98" s="6" t="str">
         <f t="shared" si="41"/>
         <v/>
       </c>
     </row>
-    <row r="98" spans="1:17" ht="15.75" customHeight="1">
-      <c r="A98" s="10"/>
-    </row>
     <row r="99" spans="1:17" ht="15.75" customHeight="1">
-      <c r="A99" s="3"/>
-      <c r="B99" s="54" t="s">
-        <v>215</v>
-      </c>
-      <c r="C99" s="54"/>
-      <c r="D99" s="56"/>
-      <c r="E99" s="66" t="s">
+      <c r="A99" s="10"/>
+    </row>
+    <row r="100" spans="1:17" ht="15.75" customHeight="1">
+      <c r="A100" s="3"/>
+      <c r="B100" s="54" t="s">
+        <v>214</v>
+      </c>
+      <c r="C100" s="54"/>
+      <c r="D100" s="56"/>
+      <c r="E100" s="66" t="s">
         <v>59</v>
       </c>
-      <c r="F99" s="56"/>
-      <c r="G99" s="37"/>
-      <c r="H99" s="37"/>
-      <c r="I99" s="37"/>
-      <c r="J99" s="37"/>
-      <c r="K99" s="37"/>
-      <c r="L99" s="37"/>
-      <c r="M99" s="37"/>
-      <c r="N99" s="37"/>
-      <c r="O99" s="37"/>
-      <c r="P99" s="37"/>
-      <c r="Q99" s="37"/>
-    </row>
-    <row r="100" spans="1:17" ht="15.75" customHeight="1">
-      <c r="A100" s="10"/>
-      <c r="B100" s="64" t="s">
-        <v>28</v>
-      </c>
-      <c r="E100" s="268"/>
-      <c r="G100" s="97" t="s">
-        <v>219</v>
-      </c>
+      <c r="F100" s="56"/>
+      <c r="G100" s="37"/>
+      <c r="H100" s="37"/>
+      <c r="I100" s="37"/>
+      <c r="J100" s="37"/>
+      <c r="K100" s="37"/>
+      <c r="L100" s="37"/>
+      <c r="M100" s="37"/>
+      <c r="N100" s="37"/>
+      <c r="O100" s="37"/>
+      <c r="P100" s="37"/>
+      <c r="Q100" s="37"/>
     </row>
     <row r="101" spans="1:17" ht="15.75" customHeight="1">
       <c r="A101" s="10"/>
-      <c r="B101" s="26" t="s">
+      <c r="B101" s="64" t="s">
+        <v>28</v>
+      </c>
+      <c r="E101" s="268"/>
+      <c r="G101" s="97" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="102" spans="1:17" ht="15.75" customHeight="1">
+      <c r="A102" s="10"/>
+      <c r="B102" s="26" t="s">
         <v>3</v>
       </c>
-      <c r="C101" s="344">
+      <c r="C102" s="344">
         <f>BS!G32</f>
         <v>8549959</v>
       </c>
-      <c r="D101" s="26"/>
-      <c r="E101" s="269"/>
-      <c r="F101" s="26"/>
-      <c r="G101" s="333">
-        <f t="shared" ref="G101:Q101" si="42">IF(G$4="","",G105+G104)</f>
+      <c r="D102" s="26"/>
+      <c r="E102" s="269"/>
+      <c r="F102" s="26"/>
+      <c r="G102" s="333">
+        <f t="shared" ref="G102:Q102" si="42">IF(G$4="","",G106+G105)</f>
         <v>8549959</v>
       </c>
-      <c r="H101" s="333">
+      <c r="H102" s="333">
         <f t="shared" si="42"/>
         <v>7615051</v>
       </c>
-      <c r="I101" s="333">
+      <c r="I102" s="333">
         <f t="shared" si="42"/>
         <v>7377578</v>
       </c>
-      <c r="J101" s="333">
+      <c r="J102" s="333">
         <f t="shared" si="42"/>
         <v>6959011</v>
       </c>
-      <c r="K101" s="333">
+      <c r="K102" s="333">
         <f t="shared" si="42"/>
         <v>6527927</v>
       </c>
-      <c r="L101" s="333">
+      <c r="L102" s="333">
         <f t="shared" si="42"/>
         <v>7038439</v>
       </c>
-      <c r="M101" s="333">
+      <c r="M102" s="333">
         <f t="shared" si="42"/>
         <v>4678812</v>
       </c>
-      <c r="N101" s="333" t="str">
+      <c r="N102" s="333" t="str">
         <f t="shared" si="42"/>
         <v/>
       </c>
-      <c r="O101" s="333" t="str">
+      <c r="O102" s="333" t="str">
         <f t="shared" si="42"/>
         <v/>
       </c>
-      <c r="P101" s="333" t="str">
+      <c r="P102" s="333" t="str">
         <f t="shared" si="42"/>
         <v/>
       </c>
-      <c r="Q101" s="333" t="str">
+      <c r="Q102" s="333" t="str">
         <f t="shared" si="42"/>
-        <v/>
-      </c>
-    </row>
-    <row r="102" spans="1:17" ht="15.75" customHeight="1">
-      <c r="A102" s="10"/>
-      <c r="B102" s="93" t="s">
-        <v>210</v>
-      </c>
-      <c r="C102" s="345">
-        <f>BS!C4</f>
-        <v>423874</v>
-      </c>
-      <c r="D102" s="89"/>
-      <c r="E102" s="270"/>
-      <c r="F102" s="89"/>
-      <c r="G102" s="346">
-        <f>IF(G$4="","",Data!D77)</f>
-        <v>405151</v>
-      </c>
-      <c r="H102" s="346">
-        <f>IF(H$4="","",Data!E77)</f>
-        <v>331915</v>
-      </c>
-      <c r="I102" s="346">
-        <f>IF(I$4="","",Data!F77)</f>
-        <v>329547</v>
-      </c>
-      <c r="J102" s="346">
-        <f>IF(J$4="","",Data!G77)</f>
-        <v>290380</v>
-      </c>
-      <c r="K102" s="346">
-        <f>IF(K$4="","",Data!H77)</f>
-        <v>317554</v>
-      </c>
-      <c r="L102" s="346">
-        <f>IF(L$4="","",Data!I77)</f>
-        <v>0</v>
-      </c>
-      <c r="M102" s="346">
-        <f>IF(M$4="","",Data!J77)</f>
-        <v>0</v>
-      </c>
-      <c r="N102" s="346" t="str">
-        <f>IF(N$4="","",Data!K77)</f>
-        <v/>
-      </c>
-      <c r="O102" s="346" t="str">
-        <f>IF(O$4="","",Data!L77)</f>
-        <v/>
-      </c>
-      <c r="P102" s="346" t="str">
-        <f>IF(P$4="","",Data!M77)</f>
-        <v/>
-      </c>
-      <c r="Q102" s="346" t="str">
-        <f>IF(Q$4="","",Data!N77)</f>
         <v/>
       </c>
     </row>
     <row r="103" spans="1:17" ht="15.75" customHeight="1">
       <c r="A103" s="10"/>
       <c r="B103" s="93" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C103" s="345">
-        <f>BS!C6+BS!C7</f>
-        <v>866160</v>
+        <f>BS!C4</f>
+        <v>423874</v>
       </c>
       <c r="D103" s="89"/>
       <c r="E103" s="270"/>
       <c r="F103" s="89"/>
       <c r="G103" s="346">
+        <f>IF(G$4="","",Data!D77)</f>
+        <v>405151</v>
+      </c>
+      <c r="H103" s="346">
+        <f>IF(H$4="","",Data!E77)</f>
+        <v>331915</v>
+      </c>
+      <c r="I103" s="346">
+        <f>IF(I$4="","",Data!F77)</f>
+        <v>329547</v>
+      </c>
+      <c r="J103" s="346">
+        <f>IF(J$4="","",Data!G77)</f>
+        <v>290380</v>
+      </c>
+      <c r="K103" s="346">
+        <f>IF(K$4="","",Data!H77)</f>
+        <v>317554</v>
+      </c>
+      <c r="L103" s="346">
+        <f>IF(L$4="","",Data!I77)</f>
+        <v>0</v>
+      </c>
+      <c r="M103" s="346">
+        <f>IF(M$4="","",Data!J77)</f>
+        <v>0</v>
+      </c>
+      <c r="N103" s="346" t="str">
+        <f>IF(N$4="","",Data!K77)</f>
+        <v/>
+      </c>
+      <c r="O103" s="346" t="str">
+        <f>IF(O$4="","",Data!L77)</f>
+        <v/>
+      </c>
+      <c r="P103" s="346" t="str">
+        <f>IF(P$4="","",Data!M77)</f>
+        <v/>
+      </c>
+      <c r="Q103" s="346" t="str">
+        <f>IF(Q$4="","",Data!N77)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="104" spans="1:17" ht="15.75" customHeight="1">
+      <c r="A104" s="10"/>
+      <c r="B104" s="93" t="s">
+        <v>210</v>
+      </c>
+      <c r="C104" s="345">
+        <f>BS!C6+BS!C7</f>
+        <v>866160</v>
+      </c>
+      <c r="D104" s="89"/>
+      <c r="E104" s="270"/>
+      <c r="F104" s="89"/>
+      <c r="G104" s="346">
         <f>IF(G$4="","",Data!D78)</f>
         <v>782978</v>
       </c>
-      <c r="H103" s="346">
+      <c r="H104" s="346">
         <f>IF(H$4="","",Data!E78)</f>
         <v>760457</v>
       </c>
-      <c r="I103" s="346">
+      <c r="I104" s="346">
         <f>IF(I$4="","",Data!F78)</f>
         <v>662654</v>
       </c>
-      <c r="J103" s="346">
+      <c r="J104" s="346">
         <f>IF(J$4="","",Data!G78)</f>
         <v>666222</v>
       </c>
-      <c r="K103" s="346">
+      <c r="K104" s="346">
         <f>IF(K$4="","",Data!H78)</f>
         <v>712611</v>
       </c>
-      <c r="L103" s="346">
+      <c r="L104" s="346">
         <f>IF(L$4="","",Data!I78)</f>
         <v>0</v>
       </c>
-      <c r="M103" s="346">
+      <c r="M104" s="346">
         <f>IF(M$4="","",Data!J78)</f>
         <v>0</v>
       </c>
-      <c r="N103" s="346" t="str">
+      <c r="N104" s="346" t="str">
         <f>IF(N$4="","",Data!K78)</f>
         <v/>
       </c>
-      <c r="O103" s="346" t="str">
+      <c r="O104" s="346" t="str">
         <f>IF(O$4="","",Data!L78)</f>
         <v/>
       </c>
-      <c r="P103" s="346" t="str">
+      <c r="P104" s="346" t="str">
         <f>IF(P$4="","",Data!M78)</f>
         <v/>
       </c>
-      <c r="Q103" s="346" t="str">
+      <c r="Q104" s="346" t="str">
         <f>IF(Q$4="","",Data!N78)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="104" spans="1:17" ht="15.75" customHeight="1">
-      <c r="A104" s="10"/>
-      <c r="B104" s="26" t="s">
-        <v>40</v>
-      </c>
-      <c r="C104" s="344">
-        <f>BS!G30</f>
-        <v>4130529</v>
-      </c>
-      <c r="D104" s="26"/>
-      <c r="E104" s="269"/>
-      <c r="F104" s="26"/>
-      <c r="G104" s="333">
-        <f>Data!C79</f>
-        <v>4130529</v>
-      </c>
-      <c r="H104" s="333">
-        <f>Data!D79</f>
-        <v>3738242</v>
-      </c>
-      <c r="I104" s="333">
-        <f>Data!E79</f>
-        <v>3876556</v>
-      </c>
-      <c r="J104" s="333">
-        <f>Data!F79</f>
-        <v>3830368</v>
-      </c>
-      <c r="K104" s="333">
-        <f>Data!G79</f>
-        <v>3676207</v>
-      </c>
-      <c r="L104" s="333">
-        <f>Data!H79</f>
-        <v>4049864</v>
-      </c>
-      <c r="M104" s="333">
-        <f>Data!I79</f>
-        <v>1781743</v>
-      </c>
-      <c r="N104" s="333" t="str">
-        <f>Data!J79</f>
-        <v/>
-      </c>
-      <c r="O104" s="333" t="str">
-        <f>Data!K79</f>
-        <v/>
-      </c>
-      <c r="P104" s="333" t="str">
-        <f>Data!L79</f>
-        <v/>
-      </c>
-      <c r="Q104" s="333" t="str">
-        <f>Data!M79</f>
         <v/>
       </c>
     </row>
     <row r="105" spans="1:17" ht="15.75" customHeight="1">
       <c r="A105" s="10"/>
       <c r="B105" s="26" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="C105" s="344">
-        <f>BS!G27</f>
-        <v>4419430</v>
+        <f>BS!G30</f>
+        <v>4130529</v>
       </c>
       <c r="D105" s="26"/>
       <c r="E105" s="269"/>
       <c r="F105" s="26"/>
       <c r="G105" s="333">
+        <f>Data!C79</f>
+        <v>4130529</v>
+      </c>
+      <c r="H105" s="333">
+        <f>Data!D79</f>
+        <v>3738242</v>
+      </c>
+      <c r="I105" s="333">
+        <f>Data!E79</f>
+        <v>3876556</v>
+      </c>
+      <c r="J105" s="333">
+        <f>Data!F79</f>
+        <v>3830368</v>
+      </c>
+      <c r="K105" s="333">
+        <f>Data!G79</f>
+        <v>3676207</v>
+      </c>
+      <c r="L105" s="333">
+        <f>Data!H79</f>
+        <v>4049864</v>
+      </c>
+      <c r="M105" s="333">
+        <f>Data!I79</f>
+        <v>1781743</v>
+      </c>
+      <c r="N105" s="333" t="str">
+        <f>Data!J79</f>
+        <v/>
+      </c>
+      <c r="O105" s="333" t="str">
+        <f>Data!K79</f>
+        <v/>
+      </c>
+      <c r="P105" s="333" t="str">
+        <f>Data!L79</f>
+        <v/>
+      </c>
+      <c r="Q105" s="333" t="str">
+        <f>Data!M79</f>
+        <v/>
+      </c>
+    </row>
+    <row r="106" spans="1:17" ht="15.75" customHeight="1">
+      <c r="A106" s="10"/>
+      <c r="B106" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="C106" s="344">
+        <f>BS!G27</f>
+        <v>4419430</v>
+      </c>
+      <c r="D106" s="26"/>
+      <c r="E106" s="269"/>
+      <c r="F106" s="26"/>
+      <c r="G106" s="333">
         <f>Data!C80</f>
         <v>4419430</v>
       </c>
-      <c r="H105" s="333">
+      <c r="H106" s="333">
         <f>Data!D80</f>
         <v>3876809</v>
       </c>
-      <c r="I105" s="333">
+      <c r="I106" s="333">
         <f>Data!E80</f>
         <v>3501022</v>
       </c>
-      <c r="J105" s="333">
+      <c r="J106" s="333">
         <f>Data!F80</f>
         <v>3128643</v>
       </c>
-      <c r="K105" s="333">
+      <c r="K106" s="333">
         <f>Data!G80</f>
         <v>2851720</v>
       </c>
-      <c r="L105" s="333">
+      <c r="L106" s="333">
         <f>Data!H80</f>
         <v>2988575</v>
       </c>
-      <c r="M105" s="333">
+      <c r="M106" s="333">
         <f>Data!I80</f>
         <v>2897069</v>
       </c>
-      <c r="N105" s="333" t="str">
+      <c r="N106" s="333" t="str">
         <f>Data!J80</f>
         <v/>
       </c>
-      <c r="O105" s="333" t="str">
+      <c r="O106" s="333" t="str">
         <f>Data!K80</f>
         <v/>
       </c>
-      <c r="P105" s="333" t="str">
+      <c r="P106" s="333" t="str">
         <f>Data!L80</f>
         <v/>
       </c>
-      <c r="Q105" s="333" t="str">
+      <c r="Q106" s="333" t="str">
         <f>Data!M80</f>
         <v/>
       </c>
-    </row>
-    <row r="106" spans="1:17" ht="15.75" customHeight="1">
-      <c r="A106" s="10"/>
-      <c r="E106" s="268"/>
     </row>
     <row r="107" spans="1:17" ht="15.75" customHeight="1">
       <c r="A107" s="10"/>
-      <c r="B107" s="91" t="s">
-        <v>220</v>
-      </c>
-      <c r="C107" s="26"/>
-      <c r="D107" s="26"/>
-      <c r="E107" s="269"/>
-      <c r="F107" s="26"/>
-      <c r="G107" s="97" t="s">
-        <v>219</v>
-      </c>
-      <c r="H107" s="12"/>
-      <c r="I107" s="12"/>
-      <c r="J107" s="12"/>
-      <c r="K107" s="12"/>
-      <c r="L107" s="12"/>
-      <c r="M107" s="12"/>
-      <c r="N107" s="12"/>
-      <c r="O107" s="12"/>
-      <c r="P107" s="12"/>
-      <c r="Q107" s="12"/>
+      <c r="E107" s="268"/>
     </row>
     <row r="108" spans="1:17" ht="15.75" customHeight="1">
       <c r="A108" s="10"/>
-      <c r="B108" s="26" t="s">
-        <v>217</v>
-      </c>
-      <c r="C108" s="94">
-        <f>C102/C$4</f>
-        <v>9.5924801567297838E-2</v>
-      </c>
+      <c r="B108" s="91" t="s">
+        <v>219</v>
+      </c>
+      <c r="C108" s="26"/>
       <c r="D108" s="26"/>
       <c r="E108" s="269"/>
       <c r="F108" s="26"/>
-      <c r="G108" s="94">
-        <f t="shared" ref="G108:Q108" si="43">IF(G$4="","",G102/G$4)</f>
-        <v>7.4592055279913291E-2</v>
-      </c>
-      <c r="H108" s="94">
-        <f t="shared" si="43"/>
-        <v>7.0225589776259409E-2</v>
-      </c>
-      <c r="I108" s="94">
-        <f t="shared" si="43"/>
-        <v>7.8450981913854773E-2</v>
-      </c>
-      <c r="J108" s="94">
-        <f t="shared" si="43"/>
-        <v>8.7552990695346472E-2</v>
-      </c>
-      <c r="K108" s="94">
-        <f t="shared" si="43"/>
-        <v>0.13107231113215248</v>
-      </c>
-      <c r="L108" s="94">
-        <f t="shared" si="43"/>
-        <v>0</v>
-      </c>
-      <c r="M108" s="94">
-        <f t="shared" si="43"/>
-        <v>0</v>
-      </c>
-      <c r="N108" s="94" t="str">
-        <f t="shared" si="43"/>
-        <v/>
-      </c>
-      <c r="O108" s="94" t="str">
-        <f t="shared" si="43"/>
-        <v/>
-      </c>
-      <c r="P108" s="94" t="str">
-        <f t="shared" si="43"/>
-        <v/>
-      </c>
-      <c r="Q108" s="94" t="str">
-        <f t="shared" si="43"/>
-        <v/>
-      </c>
+      <c r="G108" s="97" t="s">
+        <v>218</v>
+      </c>
+      <c r="H108" s="12"/>
+      <c r="I108" s="12"/>
+      <c r="J108" s="12"/>
+      <c r="K108" s="12"/>
+      <c r="L108" s="12"/>
+      <c r="M108" s="12"/>
+      <c r="N108" s="12"/>
+      <c r="O108" s="12"/>
+      <c r="P108" s="12"/>
+      <c r="Q108" s="12"/>
     </row>
     <row r="109" spans="1:17" ht="15.75" customHeight="1">
       <c r="A109" s="10"/>
       <c r="B109" s="26" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C109" s="94">
         <f>C103/C$4</f>
-        <v>0.19601633062072857</v>
+        <v>9.5924801567297838E-2</v>
       </c>
       <c r="D109" s="26"/>
       <c r="E109" s="269"/>
       <c r="F109" s="26"/>
       <c r="G109" s="94">
-        <f t="shared" ref="G109:Q109" si="44">IF(G$4="","",G103/G$4)</f>
-        <v>0.14415350883733707</v>
+        <f t="shared" ref="G109:Q109" si="43">IF(G$4="","",G103/G$4)</f>
+        <v>7.4592055279913291E-2</v>
       </c>
       <c r="H109" s="94">
-        <f t="shared" si="44"/>
-        <v>0.16089523319068105</v>
+        <f t="shared" si="43"/>
+        <v>7.0225589776259409E-2</v>
       </c>
       <c r="I109" s="94">
-        <f t="shared" si="44"/>
-        <v>0.15774944687447776</v>
+        <f t="shared" si="43"/>
+        <v>7.8450981913854773E-2</v>
       </c>
       <c r="J109" s="94">
-        <f t="shared" si="44"/>
-        <v>0.20087378113862908</v>
+        <f t="shared" si="43"/>
+        <v>8.7552990695346472E-2</v>
       </c>
       <c r="K109" s="94">
-        <f t="shared" si="44"/>
-        <v>0.29413444865501404</v>
+        <f t="shared" si="43"/>
+        <v>0.13107231113215248</v>
       </c>
       <c r="L109" s="94">
-        <f t="shared" si="44"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="M109" s="94">
-        <f t="shared" si="44"/>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="N109" s="94" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="O109" s="94" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="P109" s="94" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="Q109" s="94" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
     </row>
     <row r="110" spans="1:17" ht="15.75" customHeight="1">
       <c r="A110" s="10"/>
       <c r="B110" s="26" t="s">
-        <v>69</v>
+        <v>217</v>
       </c>
       <c r="C110" s="94">
-        <f>BS!$G$38/C$4</f>
-        <v>0</v>
+        <f>C104/C$4</f>
+        <v>0.19601633062072857</v>
       </c>
       <c r="D110" s="26"/>
       <c r="E110" s="269"/>
       <c r="F110" s="26"/>
       <c r="G110" s="94">
-        <f>BS!$G$38/G$4</f>
-        <v>0</v>
-      </c>
-      <c r="H110" s="204"/>
-      <c r="I110" s="204"/>
-      <c r="J110" s="204"/>
-      <c r="K110" s="204"/>
-      <c r="L110" s="204"/>
-      <c r="M110" s="204"/>
-      <c r="N110" s="204"/>
-      <c r="O110" s="204"/>
-      <c r="P110" s="204"/>
-      <c r="Q110" s="204"/>
+        <f t="shared" ref="G110:Q110" si="44">IF(G$4="","",G104/G$4)</f>
+        <v>0.14415350883733707</v>
+      </c>
+      <c r="H110" s="94">
+        <f t="shared" si="44"/>
+        <v>0.16089523319068105</v>
+      </c>
+      <c r="I110" s="94">
+        <f t="shared" si="44"/>
+        <v>0.15774944687447776</v>
+      </c>
+      <c r="J110" s="94">
+        <f t="shared" si="44"/>
+        <v>0.20087378113862908</v>
+      </c>
+      <c r="K110" s="94">
+        <f t="shared" si="44"/>
+        <v>0.29413444865501404</v>
+      </c>
+      <c r="L110" s="94">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+      <c r="M110" s="94">
+        <f t="shared" si="44"/>
+        <v>0</v>
+      </c>
+      <c r="N110" s="94" t="str">
+        <f t="shared" si="44"/>
+        <v/>
+      </c>
+      <c r="O110" s="94" t="str">
+        <f t="shared" si="44"/>
+        <v/>
+      </c>
+      <c r="P110" s="94" t="str">
+        <f t="shared" si="44"/>
+        <v/>
+      </c>
+      <c r="Q110" s="94" t="str">
+        <f t="shared" si="44"/>
+        <v/>
+      </c>
     </row>
     <row r="111" spans="1:17" ht="15.75" customHeight="1">
       <c r="A111" s="10"/>
-      <c r="E111" s="268"/>
+      <c r="B111" s="26" t="s">
+        <v>69</v>
+      </c>
+      <c r="C111" s="94">
+        <f>BS!$G$38/C$4</f>
+        <v>0</v>
+      </c>
+      <c r="D111" s="26"/>
+      <c r="E111" s="269"/>
+      <c r="F111" s="26"/>
+      <c r="G111" s="94">
+        <f>BS!$G$38/G$4</f>
+        <v>0</v>
+      </c>
+      <c r="H111" s="204"/>
+      <c r="I111" s="204"/>
+      <c r="J111" s="204"/>
+      <c r="K111" s="204"/>
+      <c r="L111" s="204"/>
+      <c r="M111" s="204"/>
+      <c r="N111" s="204"/>
+      <c r="O111" s="204"/>
+      <c r="P111" s="204"/>
+      <c r="Q111" s="204"/>
     </row>
     <row r="112" spans="1:17" ht="15.75" customHeight="1">
       <c r="A112" s="10"/>
-      <c r="B112" s="64" t="s">
-        <v>51</v>
-      </c>
       <c r="E112" s="268"/>
     </row>
     <row r="113" spans="1:17" ht="15.75" customHeight="1">
       <c r="A113" s="10"/>
-      <c r="B113" s="2" t="s">
-        <v>394</v>
-      </c>
-      <c r="C113" s="169"/>
+      <c r="B113" s="64" t="s">
+        <v>51</v>
+      </c>
       <c r="E113" s="268"/>
-      <c r="G113" s="295">
-        <f>IF(G$4="","",Data!C$22/Data!C15)</f>
-        <v>1.9582843253497748</v>
-      </c>
-      <c r="H113" s="295">
-        <f>IF(H$4="","",Data!D$22/Data!D15)</f>
-        <v>1.7156143821132417</v>
-      </c>
-      <c r="I113" s="295">
-        <f>IF(I$4="","",Data!E$22/Data!E15)</f>
-        <v>2.3951508563268002</v>
-      </c>
-      <c r="J113" s="295">
-        <f>IF(J$4="","",Data!F$22/Data!F15)</f>
-        <v>3.8750131310084952</v>
-      </c>
-      <c r="K113" s="295">
-        <f>IF(K$4="","",Data!G$22/Data!G15)</f>
-        <v>-10.896464832254267</v>
-      </c>
-      <c r="L113" s="295">
-        <f>IF(L$4="","",Data!H$22/Data!H15)</f>
-        <v>3.1424896400800857</v>
-      </c>
-      <c r="M113" s="295">
-        <f>IF(M$4="","",Data!I$22/Data!I15)</f>
-        <v>1.7537923547665024</v>
-      </c>
-      <c r="N113" s="295" t="str">
-        <f>IF(N$4="","",Data!J$22/Data!J15)</f>
-        <v/>
-      </c>
-      <c r="O113" s="295" t="str">
-        <f>IF(O$4="","",Data!K$22/Data!K15)</f>
-        <v/>
-      </c>
-      <c r="P113" s="295" t="str">
-        <f>IF(P$4="","",Data!L$22/Data!L15)</f>
-        <v/>
-      </c>
-      <c r="Q113" s="295" t="str">
-        <f>IF(Q$4="","",Data!M$22/Data!M15)</f>
-        <v/>
-      </c>
     </row>
     <row r="114" spans="1:17" ht="15.75" customHeight="1">
       <c r="A114" s="10"/>
       <c r="B114" s="2" t="s">
-        <v>395</v>
+        <v>388</v>
       </c>
       <c r="C114" s="169"/>
       <c r="E114" s="268"/>
       <c r="G114" s="295">
+        <f>IF(G$4="","",Data!C$22/Data!C15)</f>
+        <v>1.9582843253497748</v>
+      </c>
+      <c r="H114" s="295">
+        <f>IF(H$4="","",Data!D$22/Data!D15)</f>
+        <v>1.7156143821132417</v>
+      </c>
+      <c r="I114" s="295">
+        <f>IF(I$4="","",Data!E$22/Data!E15)</f>
+        <v>2.3951508563268002</v>
+      </c>
+      <c r="J114" s="295">
+        <f>IF(J$4="","",Data!F$22/Data!F15)</f>
+        <v>3.8750131310084952</v>
+      </c>
+      <c r="K114" s="295">
+        <f>IF(K$4="","",Data!G$22/Data!G15)</f>
+        <v>-10.896464832254267</v>
+      </c>
+      <c r="L114" s="295">
+        <f>IF(L$4="","",Data!H$22/Data!H15)</f>
+        <v>3.1424896400800857</v>
+      </c>
+      <c r="M114" s="295">
+        <f>IF(M$4="","",Data!I$22/Data!I15)</f>
+        <v>1.7537923547665024</v>
+      </c>
+      <c r="N114" s="295" t="str">
+        <f>IF(N$4="","",Data!J$22/Data!J15)</f>
+        <v/>
+      </c>
+      <c r="O114" s="295" t="str">
+        <f>IF(O$4="","",Data!K$22/Data!K15)</f>
+        <v/>
+      </c>
+      <c r="P114" s="295" t="str">
+        <f>IF(P$4="","",Data!L$22/Data!L15)</f>
+        <v/>
+      </c>
+      <c r="Q114" s="295" t="str">
+        <f>IF(Q$4="","",Data!M$22/Data!M15)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="115" spans="1:17" ht="15.75" customHeight="1">
+      <c r="A115" s="10"/>
+      <c r="B115" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="C115" s="169"/>
+      <c r="E115" s="268"/>
+      <c r="G115" s="295">
         <f>IF(G$4="","",Data!C$22/G19)</f>
         <v>1.6567861728593212</v>
       </c>
-      <c r="H114" s="295">
+      <c r="H115" s="295">
         <f>IF(H$4="","",Data!D$22/H19)</f>
         <v>1.4071375066228997</v>
       </c>
-      <c r="I114" s="295">
+      <c r="I115" s="295">
         <f>IF(I$4="","",Data!E$22/I19)</f>
         <v>1.6725464688441434</v>
       </c>
-      <c r="J114" s="295">
+      <c r="J115" s="295">
         <f>IF(J$4="","",Data!F$22/J19)</f>
         <v>3.173240538785568</v>
       </c>
-      <c r="K114" s="295">
+      <c r="K115" s="295">
         <f>IF(K$4="","",Data!G$22/K19)</f>
         <v>0.34030992255382803</v>
       </c>
-      <c r="L114" s="295">
+      <c r="L115" s="295">
         <f>IF(L$4="","",Data!H$22/L19)</f>
         <v>0.34601433795884884</v>
       </c>
-      <c r="M114" s="295">
+      <c r="M115" s="295">
         <f>IF(M$4="","",Data!I$22/M19)</f>
         <v>0.16860224825779185</v>
       </c>
-      <c r="N114" s="295" t="str">
+      <c r="N115" s="295" t="str">
         <f>IF(N$4="","",Data!J$22/N19)</f>
         <v/>
       </c>
-      <c r="O114" s="295" t="str">
+      <c r="O115" s="295" t="str">
         <f>IF(O$4="","",Data!K$22/O19)</f>
         <v/>
       </c>
-      <c r="P114" s="295" t="str">
+      <c r="P115" s="295" t="str">
         <f>IF(P$4="","",Data!L$22/P19)</f>
         <v/>
       </c>
-      <c r="Q114" s="295" t="str">
+      <c r="Q115" s="295" t="str">
         <f>IF(Q$4="","",Data!M$22/Q19)</f>
         <v/>
       </c>
-    </row>
-    <row r="115" spans="1:17" ht="15.75" customHeight="1">
-      <c r="A115" s="10"/>
-      <c r="E115" s="268"/>
     </row>
     <row r="116" spans="1:17" ht="15.75" customHeight="1">
       <c r="A116" s="10"/>
-      <c r="B116" s="91" t="s">
-        <v>38</v>
-      </c>
-      <c r="C116" s="55"/>
-      <c r="D116" s="55"/>
-      <c r="E116" s="271"/>
-      <c r="F116" s="55"/>
-      <c r="G116" s="23" t="str">
-        <f>IFERROR(IF(#REF!*G118*(1/#REF!)=G120,"","Error"),"")</f>
-        <v/>
-      </c>
-      <c r="H116" s="23" t="str">
-        <f>IFERROR(IF(#REF!*H118*(1/#REF!)=H120,"","Error"),"")</f>
-        <v/>
-      </c>
-      <c r="I116" s="23" t="str">
-        <f>IFERROR(IF(#REF!*I118*(1/#REF!)=I120,"","Error"),"")</f>
-        <v/>
-      </c>
-      <c r="J116" s="23" t="str">
-        <f>IFERROR(IF(#REF!*J118*(1/#REF!)=J120,"","Error"),"")</f>
-        <v/>
-      </c>
-      <c r="K116" s="23" t="str">
-        <f>IFERROR(IF(#REF!*K118*(1/#REF!)=K120,"","Error"),"")</f>
-        <v/>
-      </c>
-      <c r="L116" s="23" t="str">
-        <f>IFERROR(IF(#REF!*L118*(1/#REF!)=L120,"","Error"),"")</f>
-        <v/>
-      </c>
-      <c r="M116" s="23" t="str">
-        <f>IFERROR(IF(#REF!*M118*(1/#REF!)=M120,"","Error"),"")</f>
-        <v/>
-      </c>
-      <c r="N116" s="23" t="str">
-        <f>IFERROR(IF(#REF!*N118*(1/#REF!)=N120,"","Error"),"")</f>
-        <v/>
-      </c>
-      <c r="O116" s="23" t="str">
-        <f>IFERROR(IF(#REF!*O118*(1/#REF!)=O120,"","Error"),"")</f>
-        <v/>
-      </c>
-      <c r="P116" s="23" t="str">
-        <f>IFERROR(IF(#REF!*P118*(1/#REF!)=P120,"","Error"),"")</f>
-        <v/>
-      </c>
-      <c r="Q116" s="23" t="str">
-        <f>IFERROR(IF(#REF!*Q118*(1/#REF!)=Q120,"","Error"),"")</f>
-        <v/>
-      </c>
+      <c r="E116" s="268"/>
     </row>
     <row r="117" spans="1:17" ht="15.75" customHeight="1">
       <c r="A117" s="10"/>
-      <c r="B117" s="7" t="s">
-        <v>221</v>
-      </c>
-      <c r="C117" s="23">
+      <c r="B117" s="91" t="s">
+        <v>38</v>
+      </c>
+      <c r="C117" s="55"/>
+      <c r="D117" s="55"/>
+      <c r="E117" s="271"/>
+      <c r="F117" s="55"/>
+      <c r="G117" s="23" t="str">
+        <f>IFERROR(IF(#REF!*G119*(1/#REF!)=G121,"","Error"),"")</f>
+        <v/>
+      </c>
+      <c r="H117" s="23" t="str">
+        <f>IFERROR(IF(#REF!*H119*(1/#REF!)=H121,"","Error"),"")</f>
+        <v/>
+      </c>
+      <c r="I117" s="23" t="str">
+        <f>IFERROR(IF(#REF!*I119*(1/#REF!)=I121,"","Error"),"")</f>
+        <v/>
+      </c>
+      <c r="J117" s="23" t="str">
+        <f>IFERROR(IF(#REF!*J119*(1/#REF!)=J121,"","Error"),"")</f>
+        <v/>
+      </c>
+      <c r="K117" s="23" t="str">
+        <f>IFERROR(IF(#REF!*K119*(1/#REF!)=K121,"","Error"),"")</f>
+        <v/>
+      </c>
+      <c r="L117" s="23" t="str">
+        <f>IFERROR(IF(#REF!*L119*(1/#REF!)=L121,"","Error"),"")</f>
+        <v/>
+      </c>
+      <c r="M117" s="23" t="str">
+        <f>IFERROR(IF(#REF!*M119*(1/#REF!)=M121,"","Error"),"")</f>
+        <v/>
+      </c>
+      <c r="N117" s="23" t="str">
+        <f>IFERROR(IF(#REF!*N119*(1/#REF!)=N121,"","Error"),"")</f>
+        <v/>
+      </c>
+      <c r="O117" s="23" t="str">
+        <f>IFERROR(IF(#REF!*O119*(1/#REF!)=O121,"","Error"),"")</f>
+        <v/>
+      </c>
+      <c r="P117" s="23" t="str">
+        <f>IFERROR(IF(#REF!*P119*(1/#REF!)=P121,"","Error"),"")</f>
+        <v/>
+      </c>
+      <c r="Q117" s="23" t="str">
+        <f>IFERROR(IF(#REF!*Q119*(1/#REF!)=Q121,"","Error"),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="118" spans="1:17" ht="15.75" customHeight="1">
+      <c r="A118" s="10"/>
+      <c r="B118" s="7" t="s">
+        <v>220</v>
+      </c>
+      <c r="C118" s="23">
         <f>IF(valuation_method="DDM",C13/(C4+C12),C81)</f>
         <v>0.21042753223383909</v>
       </c>
-      <c r="E117" s="268"/>
-      <c r="G117" s="23">
-        <f t="shared" ref="G117:Q117" si="45">IF(G4="","",IF(valuation_method="DDM",G13/(G4+G12),G81))</f>
+      <c r="E118" s="268"/>
+      <c r="G118" s="23">
+        <f t="shared" ref="G118:Q118" si="45">IF(G4="","",IF(valuation_method="DDM",G13/(G4+G12),G81))</f>
         <v>0.24793921890168877</v>
       </c>
-      <c r="H117" s="23">
+      <c r="H118" s="23">
         <f t="shared" si="45"/>
         <v>0.23727348298740841</v>
       </c>
-      <c r="I117" s="23">
+      <c r="I118" s="23">
         <f t="shared" si="45"/>
         <v>0.21844827758593025</v>
       </c>
-      <c r="J117" s="23">
+      <c r="J118" s="23">
         <f t="shared" si="45"/>
         <v>0.14706749642708541</v>
       </c>
-      <c r="K117" s="23">
+      <c r="K118" s="23">
         <f t="shared" si="45"/>
         <v>0.71958968753959873</v>
       </c>
-      <c r="L117" s="23">
+      <c r="L118" s="23">
         <f t="shared" si="45"/>
         <v>0.71912708170960138</v>
       </c>
-      <c r="M117" s="23">
+      <c r="M118" s="23">
         <f t="shared" si="45"/>
         <v>0.7200787486776562</v>
       </c>
-      <c r="N117" s="23" t="str">
+      <c r="N118" s="23" t="str">
         <f t="shared" si="45"/>
         <v/>
       </c>
-      <c r="O117" s="23" t="str">
+      <c r="O118" s="23" t="str">
         <f t="shared" si="45"/>
         <v/>
       </c>
-      <c r="P117" s="23" t="str">
+      <c r="P118" s="23" t="str">
         <f t="shared" si="45"/>
         <v/>
       </c>
-      <c r="Q117" s="23" t="str">
+      <c r="Q118" s="23" t="str">
         <f t="shared" si="45"/>
         <v/>
       </c>
     </row>
-    <row r="118" spans="1:17" ht="15.75" customHeight="1">
-      <c r="B118" s="7" t="s">
+    <row r="119" spans="1:17" ht="15.75" customHeight="1">
+      <c r="B119" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="C118" s="42">
-        <f>IF(valuation_method="DDM",(C4+C12)/C101,C4/C101)</f>
+      <c r="C119" s="42">
+        <f>IF(valuation_method="DDM",(C4+C12)/C102,C4/C102)</f>
         <v>0.51682300464832642</v>
       </c>
-      <c r="E118" s="268"/>
-      <c r="G118" s="42">
-        <f t="shared" ref="G118:Q118" si="46">IF(G4="","",IF(valuation_method="DDM",(G4+G12)/G101,G4/G101))</f>
+      <c r="E119" s="268"/>
+      <c r="G119" s="42">
+        <f t="shared" ref="G119:Q119" si="46">IF(G4="","",IF(valuation_method="DDM",(G4+G12)/G102,G4/G102))</f>
         <v>0.63527287089914697</v>
       </c>
-      <c r="H118" s="42">
+      <c r="H119" s="42">
         <f t="shared" si="46"/>
         <v>0.6206670185137303</v>
       </c>
-      <c r="I118" s="42">
+      <c r="I119" s="42">
         <f t="shared" si="46"/>
         <v>0.56938388181053456</v>
       </c>
-      <c r="J118" s="42">
+      <c r="J119" s="42">
         <f t="shared" si="46"/>
         <v>0.47659358492176546</v>
       </c>
-      <c r="K118" s="42">
+      <c r="K119" s="42">
         <f t="shared" si="46"/>
         <v>0.37113451176767143</v>
       </c>
-      <c r="L118" s="42">
+      <c r="L119" s="42">
         <f t="shared" si="46"/>
         <v>0.45828258226007218</v>
       </c>
-      <c r="M118" s="42">
+      <c r="M119" s="42">
         <f t="shared" si="46"/>
         <v>0.67156962066439085</v>
       </c>
-      <c r="N118" s="42" t="str">
+      <c r="N119" s="42" t="str">
         <f t="shared" si="46"/>
         <v/>
       </c>
-      <c r="O118" s="42" t="str">
+      <c r="O119" s="42" t="str">
         <f t="shared" si="46"/>
         <v/>
       </c>
-      <c r="P118" s="42" t="str">
+      <c r="P119" s="42" t="str">
         <f t="shared" si="46"/>
         <v/>
       </c>
-      <c r="Q118" s="42" t="str">
+      <c r="Q119" s="42" t="str">
         <f t="shared" si="46"/>
         <v/>
       </c>
     </row>
-    <row r="119" spans="1:17" ht="15.75" customHeight="1">
-      <c r="B119" s="7" t="s">
+    <row r="120" spans="1:17" ht="15.75" customHeight="1">
+      <c r="B120" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="C119" s="15">
-        <f>C101/C105</f>
+      <c r="C120" s="15">
+        <f>C102/C106</f>
         <v>1.9346293526540752</v>
       </c>
-      <c r="D119" s="11"/>
-      <c r="E119" s="272"/>
-      <c r="F119" s="11"/>
-      <c r="G119" s="15">
-        <f t="shared" ref="G119:Q119" si="47">IF(G$4="","",G101/G105)</f>
+      <c r="D120" s="11"/>
+      <c r="E120" s="272"/>
+      <c r="F120" s="11"/>
+      <c r="G120" s="15">
+        <f t="shared" ref="G120:Q120" si="47">IF(G$4="","",G102/G106)</f>
         <v>1.9346293526540752</v>
       </c>
-      <c r="H119" s="15">
+      <c r="H120" s="15">
         <f t="shared" si="47"/>
         <v>1.9642574601947116</v>
       </c>
-      <c r="I119" s="15">
+      <c r="I120" s="15">
         <f t="shared" si="47"/>
         <v>2.1072641074520524</v>
       </c>
-      <c r="J119" s="15">
+      <c r="J120" s="15">
         <f t="shared" si="47"/>
         <v>2.2242905310704995</v>
       </c>
-      <c r="K119" s="15">
+      <c r="K120" s="15">
         <f t="shared" si="47"/>
         <v>2.2891191982382564</v>
       </c>
-      <c r="L119" s="15">
+      <c r="L120" s="15">
         <f t="shared" si="47"/>
         <v>2.3551153978066468</v>
       </c>
-      <c r="M119" s="15">
+      <c r="M120" s="15">
         <f t="shared" si="47"/>
         <v>1.615015727965057</v>
       </c>
-      <c r="N119" s="15" t="str">
+      <c r="N120" s="15" t="str">
         <f t="shared" si="47"/>
         <v/>
       </c>
-      <c r="O119" s="15" t="str">
+      <c r="O120" s="15" t="str">
         <f t="shared" si="47"/>
         <v/>
       </c>
-      <c r="P119" s="15" t="str">
+      <c r="P120" s="15" t="str">
         <f t="shared" si="47"/>
         <v/>
       </c>
-      <c r="Q119" s="15" t="str">
+      <c r="Q120" s="15" t="str">
         <f t="shared" si="47"/>
         <v/>
       </c>
     </row>
-    <row r="120" spans="1:17" ht="15.75" customHeight="1">
-      <c r="A120" s="10"/>
-      <c r="B120" s="70" t="s">
-        <v>222</v>
-      </c>
-      <c r="C120" s="102">
-        <f>C13/C105</f>
+    <row r="121" spans="1:17" ht="15.75" customHeight="1">
+      <c r="A121" s="10"/>
+      <c r="B121" s="70" t="s">
+        <v>221</v>
+      </c>
+      <c r="C121" s="102">
+        <f>C13/C106</f>
         <v>0.21039827332068567</v>
       </c>
-      <c r="D120" s="103"/>
-      <c r="E120" s="271"/>
-      <c r="F120" s="103"/>
-      <c r="G120" s="102">
-        <f>IF(G$4="","",G13/G105)</f>
+      <c r="D121" s="103"/>
+      <c r="E121" s="271"/>
+      <c r="F121" s="103"/>
+      <c r="G121" s="102">
+        <f t="shared" ref="G121:Q121" si="48">IF(G$4="","",G13/G106)</f>
         <v>0.3047216496244991</v>
       </c>
-      <c r="H120" s="102">
-        <f t="shared" ref="H120:Q120" si="48">IF(H$4="","",H13/H105)</f>
+      <c r="H121" s="102">
+        <f t="shared" si="48"/>
         <v>0.28927192440999799</v>
       </c>
-      <c r="I120" s="102">
+      <c r="I121" s="102">
         <f t="shared" si="48"/>
         <v>0.26210346578798993</v>
       </c>
-      <c r="J120" s="102">
+      <c r="J121" s="102">
         <f t="shared" si="48"/>
         <v>0.15590369371002061</v>
       </c>
-      <c r="K120" s="102">
+      <c r="K121" s="102">
         <f t="shared" si="48"/>
         <v>0.61134262830852959</v>
       </c>
-      <c r="L120" s="102">
+      <c r="L121" s="102">
         <f t="shared" si="48"/>
         <v>0.77615987552596133</v>
       </c>
-      <c r="M120" s="102">
+      <c r="M121" s="102">
         <f t="shared" si="48"/>
         <v>0.78099417031489415</v>
       </c>
-      <c r="N120" s="102" t="str">
+      <c r="N121" s="102" t="str">
         <f t="shared" si="48"/>
         <v/>
       </c>
-      <c r="O120" s="102" t="str">
+      <c r="O121" s="102" t="str">
         <f t="shared" si="48"/>
         <v/>
       </c>
-      <c r="P120" s="102" t="str">
+      <c r="P121" s="102" t="str">
         <f t="shared" si="48"/>
         <v/>
       </c>
-      <c r="Q120" s="102" t="str">
+      <c r="Q121" s="102" t="str">
         <f t="shared" si="48"/>
         <v/>
       </c>
-    </row>
-    <row r="121" spans="1:17" ht="15.75" customHeight="1">
-      <c r="A121" s="10"/>
-      <c r="B121" s="27"/>
-      <c r="C121" s="62"/>
-      <c r="D121" s="27"/>
-      <c r="E121" s="67"/>
-      <c r="F121" s="27"/>
-      <c r="G121" s="12"/>
-      <c r="H121" s="12"/>
-      <c r="I121" s="12"/>
-      <c r="J121" s="12"/>
-      <c r="K121" s="12"/>
-      <c r="L121" s="12"/>
-      <c r="M121" s="12"/>
-      <c r="N121" s="12"/>
-      <c r="O121" s="12"/>
-      <c r="P121" s="12"/>
-      <c r="Q121" s="12"/>
     </row>
     <row r="122" spans="1:17" ht="15.75" customHeight="1">
       <c r="A122" s="10"/>
-      <c r="B122" s="54" t="s">
-        <v>223</v>
-      </c>
-      <c r="C122" s="54"/>
-      <c r="D122" s="56"/>
-      <c r="E122" s="66" t="s">
-        <v>59</v>
-      </c>
-      <c r="F122" s="56"/>
-      <c r="G122" s="37"/>
-      <c r="H122" s="37"/>
-      <c r="I122" s="37"/>
-      <c r="J122" s="37"/>
-      <c r="K122" s="37"/>
-      <c r="L122" s="37"/>
-      <c r="M122" s="37"/>
-      <c r="N122" s="37"/>
-      <c r="O122" s="37"/>
-      <c r="P122" s="37"/>
-      <c r="Q122" s="37"/>
+      <c r="B122" s="27"/>
+      <c r="C122" s="62"/>
+      <c r="D122" s="27"/>
+      <c r="E122" s="67"/>
+      <c r="F122" s="27"/>
+      <c r="G122" s="12"/>
+      <c r="H122" s="12"/>
+      <c r="I122" s="12"/>
+      <c r="J122" s="12"/>
+      <c r="K122" s="12"/>
+      <c r="L122" s="12"/>
+      <c r="M122" s="12"/>
+      <c r="N122" s="12"/>
+      <c r="O122" s="12"/>
+      <c r="P122" s="12"/>
+      <c r="Q122" s="12"/>
     </row>
     <row r="123" spans="1:17" ht="15.75" customHeight="1">
       <c r="A123" s="10"/>
-      <c r="B123" s="178" t="s">
-        <v>170</v>
-      </c>
-      <c r="C123" s="179"/>
-      <c r="D123" s="27"/>
-      <c r="E123" s="265"/>
-      <c r="F123" s="27"/>
-      <c r="G123" s="12"/>
-      <c r="H123" s="12"/>
-      <c r="I123" s="12"/>
-      <c r="J123" s="12"/>
-      <c r="K123" s="12"/>
-      <c r="L123" s="12"/>
-      <c r="M123" s="12"/>
-      <c r="N123" s="12"/>
-      <c r="O123" s="12"/>
-      <c r="P123" s="12"/>
-      <c r="Q123" s="12"/>
+      <c r="B123" s="54" t="s">
+        <v>222</v>
+      </c>
+      <c r="C123" s="54"/>
+      <c r="D123" s="56"/>
+      <c r="E123" s="66" t="s">
+        <v>59</v>
+      </c>
+      <c r="F123" s="56"/>
+      <c r="G123" s="37"/>
+      <c r="H123" s="37"/>
+      <c r="I123" s="37"/>
+      <c r="J123" s="37"/>
+      <c r="K123" s="37"/>
+      <c r="L123" s="37"/>
+      <c r="M123" s="37"/>
+      <c r="N123" s="37"/>
+      <c r="O123" s="37"/>
+      <c r="P123" s="37"/>
+      <c r="Q123" s="37"/>
     </row>
     <row r="124" spans="1:17" ht="15.75" customHeight="1">
       <c r="A124" s="10"/>
-      <c r="B124" s="27" t="str">
-        <f>"FCFE per share ("&amp;Market_currency&amp;")"</f>
-        <v>FCFE per share (HKD)</v>
-      </c>
-      <c r="C124" s="177">
-        <f>C16*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>2.4321152122602645</v>
-      </c>
+      <c r="B124" s="178" t="s">
+        <v>169</v>
+      </c>
+      <c r="C124" s="179"/>
       <c r="D124" s="27"/>
       <c r="E124" s="265"/>
       <c r="F124" s="27"/>
-      <c r="G124" s="177">
-        <f t="shared" ref="G124:Q124" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>3.4975230830031299</v>
-      </c>
-      <c r="H124" s="177">
-        <f t="shared" si="49"/>
-        <v>2.8805060930019804</v>
-      </c>
-      <c r="I124" s="177">
-        <f t="shared" si="49"/>
-        <v>2.3571582219218832</v>
-      </c>
-      <c r="J124" s="177">
-        <f t="shared" si="49"/>
-        <v>1.2643331226722432</v>
-      </c>
-      <c r="K124" s="177">
-        <f t="shared" si="49"/>
-        <v>6.1076209056252253</v>
-      </c>
-      <c r="L124" s="177">
-        <f t="shared" si="49"/>
-        <v>8.2120640688953994</v>
-      </c>
-      <c r="M124" s="177">
-        <f t="shared" si="49"/>
-        <v>7.5975872108179461</v>
-      </c>
-      <c r="N124" s="177" t="str">
-        <f t="shared" si="49"/>
-        <v/>
-      </c>
-      <c r="O124" s="177" t="str">
-        <f t="shared" si="49"/>
-        <v/>
-      </c>
-      <c r="P124" s="177" t="str">
-        <f t="shared" si="49"/>
-        <v/>
-      </c>
-      <c r="Q124" s="177" t="str">
-        <f t="shared" si="49"/>
-        <v/>
-      </c>
+      <c r="G124" s="12"/>
+      <c r="H124" s="12"/>
+      <c r="I124" s="12"/>
+      <c r="J124" s="12"/>
+      <c r="K124" s="12"/>
+      <c r="L124" s="12"/>
+      <c r="M124" s="12"/>
+      <c r="N124" s="12"/>
+      <c r="O124" s="12"/>
+      <c r="P124" s="12"/>
+      <c r="Q124" s="12"/>
     </row>
     <row r="125" spans="1:17" ht="15.75" customHeight="1">
       <c r="A125" s="10"/>
-      <c r="B125" s="27" t="s">
-        <v>269</v>
-      </c>
-      <c r="C125" s="77">
-        <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>4.8496813803793899E-2</v>
+      <c r="B125" s="27" t="str">
+        <f>"FCFE per share ("&amp;Market_currency&amp;")"</f>
+        <v>FCFE per share (HKD)</v>
+      </c>
+      <c r="C125" s="177">
+        <f>C16*$C$3/Common_Shares*Exchange_Rate</f>
+        <v>2.4321152122602645</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="265"/>
       <c r="F125" s="27"/>
-      <c r="G125" s="77">
-        <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
+      <c r="G125" s="177">
+        <f t="shared" ref="G125:Q125" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
+        <v>3.4975230830031299</v>
+      </c>
+      <c r="H125" s="177">
+        <f t="shared" si="49"/>
+        <v>2.8805060930019804</v>
+      </c>
+      <c r="I125" s="177">
+        <f t="shared" si="49"/>
+        <v>2.3571582219218832</v>
+      </c>
+      <c r="J125" s="177">
+        <f t="shared" si="49"/>
+        <v>1.2643331226722432</v>
+      </c>
+      <c r="K125" s="177">
+        <f t="shared" si="49"/>
+        <v>6.1076209056252253</v>
+      </c>
+      <c r="L125" s="177">
+        <f t="shared" si="49"/>
+        <v>8.2120640688953994</v>
+      </c>
+      <c r="M125" s="177">
+        <f t="shared" si="49"/>
+        <v>7.5975872108179461</v>
+      </c>
+      <c r="N125" s="177" t="str">
+        <f t="shared" si="49"/>
+        <v/>
+      </c>
+      <c r="O125" s="177" t="str">
+        <f t="shared" si="49"/>
+        <v/>
+      </c>
+      <c r="P125" s="177" t="str">
+        <f t="shared" si="49"/>
+        <v/>
+      </c>
+      <c r="Q125" s="177" t="str">
+        <f t="shared" si="49"/>
+        <v/>
+      </c>
+    </row>
+    <row r="126" spans="1:17" ht="15.75" customHeight="1">
+      <c r="A126" s="10"/>
+      <c r="B126" s="27" t="s">
+        <v>268</v>
+      </c>
+      <c r="C126" s="77">
+        <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
+        <v>4.8496813803793899E-2</v>
+      </c>
+      <c r="D126" s="27"/>
+      <c r="E126" s="265"/>
+      <c r="F126" s="27"/>
+      <c r="G126" s="77">
+        <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
         <v>6.974123794622393E-2</v>
       </c>
-      <c r="H125" s="77">
-        <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
+      <c r="H126" s="77">
+        <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
         <v>5.74378084347354E-2</v>
       </c>
-      <c r="I125" s="77">
-        <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
+      <c r="I126" s="77">
+        <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
         <v>4.7002157964544031E-2</v>
       </c>
-      <c r="J125" s="77">
-        <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
+      <c r="J126" s="77">
+        <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
         <v>2.5211029365348817E-2</v>
       </c>
-      <c r="K125" s="77">
-        <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
+      <c r="K126" s="77">
+        <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
         <v>0.12178705694167948</v>
       </c>
-      <c r="L125" s="77">
-        <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
+      <c r="L126" s="77">
+        <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
         <v>0.16375003128405582</v>
       </c>
-      <c r="M125" s="77">
-        <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
+      <c r="M126" s="77">
+        <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
         <v>0.15149725245898199</v>
       </c>
-      <c r="N125" s="77" t="str">
-        <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v/>
-      </c>
-      <c r="O125" s="77" t="str">
-        <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v/>
-      </c>
-      <c r="P125" s="77" t="str">
-        <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
-        <v/>
-      </c>
-      <c r="Q125" s="77" t="str">
-        <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="126" spans="1:17" ht="15.75" customHeight="1">
-      <c r="B126" s="2" t="s">
-        <v>397</v>
-      </c>
-      <c r="C126" s="169"/>
-      <c r="G126" s="23">
+      <c r="N126" s="77" t="str">
+        <f t="shared" ref="N126" si="57">IF(N$4="","",N125/Market_Price)</f>
+        <v/>
+      </c>
+      <c r="O126" s="77" t="str">
+        <f t="shared" ref="O126" si="58">IF(O$4="","",O125/Market_Price)</f>
+        <v/>
+      </c>
+      <c r="P126" s="77" t="str">
+        <f t="shared" ref="P126" si="59">IF(P$4="","",P125/Market_Price)</f>
+        <v/>
+      </c>
+      <c r="Q126" s="77" t="str">
+        <f t="shared" ref="Q126" si="60">IF(Q$4="","",Q125/Market_Price)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="127" spans="1:17" ht="15.75" customHeight="1">
+      <c r="B127" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="C127" s="169"/>
+      <c r="G127" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
         <v>6.5723736208219957E-3</v>
       </c>
-      <c r="H126" s="23">
+      <c r="H127" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
         <v>5.2475501746176963E-3</v>
       </c>
-      <c r="I126" s="23">
+      <c r="I127" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
         <v>3.6559899763774521E-3</v>
       </c>
-      <c r="J126" s="23">
+      <c r="J127" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
         <v>2.2996528013106868E-3</v>
       </c>
-      <c r="K126" s="23">
+      <c r="K127" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
         <v>-4.2367418664554214E-4</v>
       </c>
-      <c r="L126" s="23">
+      <c r="L127" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
         <v>2.0083690052794972E-3</v>
       </c>
-      <c r="M126" s="23">
+      <c r="M127" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
         <v>1.6223024485771456E-3</v>
       </c>
-      <c r="N126" s="23" t="str">
+      <c r="N127" s="23" t="str">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
         <v/>
       </c>
-      <c r="O126" s="23" t="str">
+      <c r="O127" s="23" t="str">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
         <v/>
       </c>
-      <c r="P126" s="23" t="str">
+      <c r="P127" s="23" t="str">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
         <v/>
       </c>
-      <c r="Q126" s="23" t="str">
+      <c r="Q127" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
         <v/>
       </c>
     </row>
-    <row r="127" spans="1:17" ht="15.75" customHeight="1"/>
     <row r="128" spans="1:17" ht="15.75" customHeight="1"/>
     <row r="129" ht="15.75" customHeight="1"/>
     <row r="130" ht="15.75" customHeight="1"/>
@@ -15334,6 +15364,7 @@
     <row r="806" ht="15.75" customHeight="1"/>
     <row r="807" ht="15.75" customHeight="1"/>
     <row r="808" ht="15.75" customHeight="1"/>
+    <row r="809" ht="15.75" customHeight="1"/>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="G4:Q13 G15:Q16 G23:Q24 G34:Q34">
@@ -15378,20 +15409,20 @@
     </row>
     <row r="3" spans="2:8" ht="13.15">
       <c r="B3" s="109" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C3" s="107">
         <f>scaling_factor</f>
         <v>1000</v>
       </c>
       <c r="E3" s="109" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H3" s="120"/>
     </row>
     <row r="4" spans="2:8">
       <c r="B4" s="100" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C4" s="338">
         <f>Normalized_FCF!C19</f>
@@ -15402,7 +15433,7 @@
         <v>EUR</v>
       </c>
       <c r="E4" s="100" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F4" s="134">
         <f>Terminal_Growth</f>
@@ -15412,7 +15443,7 @@
     </row>
     <row r="5" spans="2:8">
       <c r="B5" s="205" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C5" s="206">
         <f>Equity_Cost</f>
@@ -15423,7 +15454,7 @@
     </row>
     <row r="6" spans="2:8" ht="13.35" customHeight="1">
       <c r="B6" s="149" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C6" s="347">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
@@ -15433,15 +15464,15 @@
         <f>Reporting_currency</f>
         <v>EUR</v>
       </c>
-      <c r="E6" s="364" t="s">
-        <v>249</v>
-      </c>
-      <c r="F6" s="364"/>
+      <c r="E6" s="366" t="s">
+        <v>248</v>
+      </c>
+      <c r="F6" s="366"/>
       <c r="H6" s="120"/>
     </row>
     <row r="7" spans="2:8">
       <c r="B7" s="148" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C7" s="338">
         <f>BS!G31</f>
@@ -15451,13 +15482,13 @@
         <f>Reporting_currency</f>
         <v>EUR</v>
       </c>
-      <c r="E7" s="364"/>
-      <c r="F7" s="364"/>
+      <c r="E7" s="366"/>
+      <c r="F7" s="366"/>
       <c r="H7" s="120"/>
     </row>
     <row r="8" spans="2:8">
       <c r="B8" s="148" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C8" s="338">
         <f>BS!D66</f>
@@ -15467,13 +15498,13 @@
         <f>Reporting_currency</f>
         <v>EUR</v>
       </c>
-      <c r="E8" s="364"/>
-      <c r="F8" s="364"/>
+      <c r="E8" s="366"/>
+      <c r="F8" s="366"/>
       <c r="H8" s="120"/>
     </row>
     <row r="9" spans="2:8">
       <c r="B9" s="205" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C9" s="348">
         <f>BS!H42</f>
@@ -15483,13 +15514,13 @@
         <f>Reporting_currency</f>
         <v>EUR</v>
       </c>
-      <c r="E9" s="364"/>
-      <c r="F9" s="364"/>
+      <c r="E9" s="366"/>
+      <c r="F9" s="366"/>
       <c r="H9" s="120"/>
     </row>
     <row r="10" spans="2:8" ht="13.15">
       <c r="B10" s="149" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C10" s="347">
         <f>C6-C7+C8+C9</f>
@@ -15503,7 +15534,7 @@
     </row>
     <row r="11" spans="2:8" ht="13.15" thickBot="1">
       <c r="B11" s="207" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C11" s="208">
         <f>Exchange_Rate</f>
@@ -15534,7 +15565,7 @@
     </row>
     <row r="14" spans="2:8" ht="13.9">
       <c r="B14" s="36" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C14" s="37"/>
       <c r="D14" s="37"/>
@@ -15544,23 +15575,23 @@
     </row>
     <row r="15" spans="2:8" ht="13.15">
       <c r="B15" s="119" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H15" s="120"/>
     </row>
     <row r="16" spans="2:8" ht="13.35" customHeight="1">
       <c r="B16" s="152" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C16" s="161">
         <f>Scenarios!C65</f>
-        <v>2.3752619295331442E-2</v>
+        <v>2.3752619295331401E-2</v>
       </c>
       <c r="H16" s="120"/>
     </row>
     <row r="17" spans="2:17" ht="13.35" customHeight="1">
       <c r="B17" s="118" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C17" s="162">
         <f>Scenarios!C64</f>
@@ -15593,7 +15624,7 @@
         <v>108</v>
       </c>
       <c r="D20" s="128" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E20" s="128" t="s">
         <v>109</v>
@@ -15613,7 +15644,7 @@
       </c>
       <c r="D21" s="138">
         <f>IF($C$17&lt;B21,0,DCF!$C$16)</f>
-        <v>2.3752619295331442E-2</v>
+        <v>2.3752619295331401E-2</v>
       </c>
       <c r="E21" s="124">
         <f t="shared" ref="E21:E50" si="0">IF($C$17&lt;B21,0,1/(1+Equity_Cost)^B21)</f>
@@ -15635,7 +15666,7 @@
       </c>
       <c r="D22" s="138">
         <f>IF($C$17&lt;B22,0,DCF!$C$16)</f>
-        <v>2.3752619295331442E-2</v>
+        <v>2.3752619295331401E-2</v>
       </c>
       <c r="E22" s="124">
         <f t="shared" si="0"/>
@@ -15657,7 +15688,7 @@
       </c>
       <c r="D23" s="138">
         <f>IF($C$17&lt;B23,0,DCF!$C$16)</f>
-        <v>2.3752619295331442E-2</v>
+        <v>2.3752619295331401E-2</v>
       </c>
       <c r="E23" s="124">
         <f t="shared" si="0"/>
@@ -15689,7 +15720,7 @@
       </c>
       <c r="D24" s="138">
         <f>IF($C$17&lt;B24,0,DCF!$C$16)</f>
-        <v>2.3752619295331442E-2</v>
+        <v>2.3752619295331401E-2</v>
       </c>
       <c r="E24" s="124">
         <f t="shared" si="0"/>
@@ -15721,7 +15752,7 @@
       </c>
       <c r="D25" s="138">
         <f>IF($C$17&lt;B25,0,DCF!$C$16)</f>
-        <v>2.3752619295331442E-2</v>
+        <v>2.3752619295331401E-2</v>
       </c>
       <c r="E25" s="124">
         <f t="shared" si="0"/>
@@ -16365,7 +16396,7 @@
     </row>
     <row r="51" spans="1:17">
       <c r="B51" s="126" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C51" s="123">
         <f>C$21*(1+Terminal_Growth)^$C$17/Equity_Cost</f>
@@ -16402,7 +16433,7 @@
     </row>
     <row r="54" spans="1:17" ht="13.15">
       <c r="B54" s="119" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C54" s="136"/>
       <c r="D54" s="136"/>
@@ -16623,7 +16654,7 @@
     </row>
     <row r="63" spans="1:17" ht="13.15">
       <c r="B63" s="119" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C63" s="338"/>
       <c r="D63" s="114"/>
@@ -16852,19 +16883,19 @@
     </row>
     <row r="73" spans="1:8" ht="13.15">
       <c r="B73" s="171" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C73" s="171" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D73" s="171" t="s">
+        <v>111</v>
+      </c>
+      <c r="E73" s="172" t="s">
         <v>112</v>
       </c>
-      <c r="E73" s="172" t="s">
-        <v>113</v>
-      </c>
       <c r="F73" s="172" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="74" spans="1:8">
@@ -16989,7 +17020,7 @@
     </row>
     <row r="80" spans="1:8">
       <c r="B80" s="155" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="C80" s="155" t="s">
         <v>105</v>
@@ -17126,7 +17157,7 @@
   <sheetData>
     <row r="2" spans="2:8" ht="13.9">
       <c r="B2" s="36" t="s">
-        <v>445</v>
+        <v>439</v>
       </c>
       <c r="C2" s="37"/>
       <c r="D2" s="37"/>
@@ -17138,23 +17169,23 @@
     </row>
     <row r="3" spans="2:8" ht="13.15">
       <c r="B3" s="109" t="s">
-        <v>444</v>
+        <v>438</v>
       </c>
       <c r="C3" s="107">
         <f>scaling_factor</f>
         <v>1000</v>
       </c>
       <c r="E3" s="109" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H3" s="120"/>
     </row>
     <row r="4" spans="2:8">
       <c r="B4" s="100" t="s">
-        <v>442</v>
+        <v>436</v>
       </c>
       <c r="C4" s="114">
-        <f>Normalized_FCF!C91</f>
+        <f>Normalized_FCF!C91*(1-dividend_tax_rate)</f>
         <v>3767405.655286673</v>
       </c>
       <c r="D4" t="str">
@@ -17162,7 +17193,7 @@
         <v>HKD</v>
       </c>
       <c r="E4" s="100" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F4" s="134">
         <f>Thesis!E22</f>
@@ -17172,7 +17203,7 @@
     </row>
     <row r="5" spans="2:8">
       <c r="B5" s="205" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C5" s="206">
         <f>Equity_Cost</f>
@@ -17183,7 +17214,7 @@
     </row>
     <row r="6" spans="2:8" ht="13.35" customHeight="1">
       <c r="B6" s="149" t="s">
-        <v>443</v>
+        <v>437</v>
       </c>
       <c r="C6" s="319">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
@@ -17193,13 +17224,13 @@
         <f>Reporting_currency</f>
         <v>EUR</v>
       </c>
-      <c r="E6" s="364"/>
-      <c r="F6" s="364"/>
+      <c r="E6" s="366"/>
+      <c r="F6" s="366"/>
       <c r="H6" s="120"/>
     </row>
     <row r="7" spans="2:8" ht="13.15">
       <c r="B7" s="149" t="s">
-        <v>446</v>
+        <v>440</v>
       </c>
       <c r="C7" s="111">
         <f>(C6*scaling_factor)/Common_Shares*Exchange_Rate</f>
@@ -17216,7 +17247,7 @@
     </row>
     <row r="9" spans="2:8" ht="13.9">
       <c r="B9" s="36" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C9" s="37"/>
       <c r="D9" s="37"/>
@@ -17226,23 +17257,23 @@
     </row>
     <row r="10" spans="2:8" ht="13.15">
       <c r="B10" s="119" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H10" s="120"/>
     </row>
     <row r="11" spans="2:8" ht="13.35" customHeight="1">
       <c r="B11" s="152" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C11" s="161">
         <f>Scenarios!C65</f>
-        <v>2.3752619295331442E-2</v>
+        <v>2.3752619295331401E-2</v>
       </c>
       <c r="H11" s="120"/>
     </row>
     <row r="12" spans="2:8" ht="13.35" customHeight="1">
       <c r="B12" s="118" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C12" s="162">
         <f>Scenarios!C64</f>
@@ -17272,16 +17303,16 @@
         <v>107</v>
       </c>
       <c r="C15" s="128" t="s">
-        <v>448</v>
+        <v>442</v>
       </c>
       <c r="D15" s="128" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E15" s="128" t="s">
         <v>109</v>
       </c>
       <c r="F15" s="129" t="s">
-        <v>447</v>
+        <v>441</v>
       </c>
       <c r="H15" s="120"/>
     </row>
@@ -17295,7 +17326,7 @@
       </c>
       <c r="D16" s="138">
         <f>IF($C$12&lt;B16,0,DDM!$C$11)</f>
-        <v>2.3752619295331442E-2</v>
+        <v>2.3752619295331401E-2</v>
       </c>
       <c r="E16" s="124">
         <f t="shared" ref="E16:E45" si="0">IF($C$12&lt;B16,0,1/(1+Equity_Cost)^B16)</f>
@@ -17317,7 +17348,7 @@
       </c>
       <c r="D17" s="138">
         <f>IF($C$12&lt;B17,0,DDM!$C$11)</f>
-        <v>2.3752619295331442E-2</v>
+        <v>2.3752619295331401E-2</v>
       </c>
       <c r="E17" s="124">
         <f t="shared" si="0"/>
@@ -17339,7 +17370,7 @@
       </c>
       <c r="D18" s="138">
         <f>IF($C$12&lt;B18,0,DDM!$C$11)</f>
-        <v>2.3752619295331442E-2</v>
+        <v>2.3752619295331401E-2</v>
       </c>
       <c r="E18" s="124">
         <f t="shared" si="0"/>
@@ -17361,7 +17392,7 @@
       </c>
       <c r="D19" s="138">
         <f>IF($C$12&lt;B19,0,DDM!$C$11)</f>
-        <v>2.3752619295331442E-2</v>
+        <v>2.3752619295331401E-2</v>
       </c>
       <c r="E19" s="124">
         <f t="shared" si="0"/>
@@ -17383,7 +17414,7 @@
       </c>
       <c r="D20" s="138">
         <f>IF($C$12&lt;B20,0,DDM!$C$11)</f>
-        <v>2.3752619295331442E-2</v>
+        <v>2.3752619295331401E-2</v>
       </c>
       <c r="E20" s="124">
         <f t="shared" si="0"/>
@@ -17947,7 +17978,7 @@
     </row>
     <row r="46" spans="2:8">
       <c r="B46" s="126" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C46" s="123">
         <f>C$16*(1+F4)^$C$12/Equity_Cost</f>
@@ -17984,7 +18015,7 @@
     </row>
     <row r="49" spans="1:8" ht="13.15">
       <c r="B49" s="119" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C49" s="136"/>
       <c r="D49" s="136"/>
@@ -18155,7 +18186,7 @@
     </row>
     <row r="58" spans="1:8" ht="13.15">
       <c r="B58" s="119" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C58" s="114"/>
       <c r="D58" s="114"/>
@@ -18374,19 +18405,19 @@
     </row>
     <row r="68" spans="1:8" ht="13.15">
       <c r="B68" s="171" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C68" s="171" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D68" s="171" t="s">
+        <v>111</v>
+      </c>
+      <c r="E68" s="172" t="s">
         <v>112</v>
       </c>
-      <c r="E68" s="172" t="s">
-        <v>113</v>
-      </c>
       <c r="F68" s="172" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="69" spans="1:8">
@@ -18511,7 +18542,7 @@
     </row>
     <row r="75" spans="1:8">
       <c r="B75" s="155" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="C75" s="155" t="s">
         <v>105</v>
@@ -18575,20 +18606,20 @@
   <sheetData>
     <row r="2" spans="2:9" ht="13.9">
       <c r="B2" s="36" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C2" s="37"/>
       <c r="D2" s="37"/>
       <c r="E2" s="37"/>
       <c r="F2" s="37"/>
       <c r="H2" s="248" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="I2" s="249"/>
     </row>
     <row r="3" spans="2:9" ht="13.15">
       <c r="B3" s="159" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="H3" s="247">
         <v>0</v>
@@ -18600,14 +18631,14 @@
     </row>
     <row r="4" spans="2:9">
       <c r="B4" s="152" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C4" s="120">
         <v>3</v>
       </c>
       <c r="D4" s="120"/>
       <c r="E4" s="155" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F4" s="155"/>
       <c r="H4" s="247">
@@ -18636,7 +18667,7 @@
         <v>1000</v>
       </c>
       <c r="E6" s="100" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="F6" s="100"/>
       <c r="H6" s="247">
@@ -18649,7 +18680,7 @@
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1">
       <c r="B7" s="100" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C7" s="338">
         <f>Normalized_FCF!G8</f>
@@ -18659,11 +18690,11 @@
         <f>Reporting_currency</f>
         <v>EUR</v>
       </c>
-      <c r="E7" s="366" t="str">
+      <c r="E7" s="368" t="str">
         <f>"Please develop three logical "&amp;C18&amp;"-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme "&amp;C46&amp;"-year scenarios (Success Scenario, Devil’s Advocate Scenario) for "&amp;Thesis!C5&amp;"("&amp;Thesis!C11&amp;"). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative."</f>
         <v>Please develop three logical 5-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme 10-year scenarios (Success Scenario, Devil’s Advocate Scenario) for PRADA(1913.HK). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative.</v>
       </c>
-      <c r="F7" s="366"/>
+      <c r="F7" s="368"/>
       <c r="H7" s="247">
         <v>4</v>
       </c>
@@ -18684,8 +18715,8 @@
         <f>Reporting_currency</f>
         <v>EUR</v>
       </c>
-      <c r="E8" s="366"/>
-      <c r="F8" s="366"/>
+      <c r="E8" s="368"/>
+      <c r="F8" s="368"/>
       <c r="H8" s="247">
         <v>5</v>
       </c>
@@ -18706,8 +18737,8 @@
         <f>Reporting_currency</f>
         <v>EUR</v>
       </c>
-      <c r="E9" s="366"/>
-      <c r="F9" s="366"/>
+      <c r="E9" s="368"/>
+      <c r="F9" s="368"/>
       <c r="H9" s="247">
         <v>6</v>
       </c>
@@ -18717,8 +18748,8 @@
       </c>
     </row>
     <row r="10" spans="2:9">
-      <c r="E10" s="366"/>
-      <c r="F10" s="366"/>
+      <c r="E10" s="368"/>
+      <c r="F10" s="368"/>
       <c r="H10" s="247">
         <v>7</v>
       </c>
@@ -18729,10 +18760,10 @@
     </row>
     <row r="11" spans="2:9" ht="13.15">
       <c r="B11" s="159" t="s">
-        <v>449</v>
-      </c>
-      <c r="E11" s="366"/>
-      <c r="F11" s="366"/>
+        <v>443</v>
+      </c>
+      <c r="E11" s="368"/>
+      <c r="F11" s="368"/>
       <c r="H11" s="247">
         <v>8</v>
       </c>
@@ -18743,15 +18774,15 @@
     </row>
     <row r="12" spans="2:9">
       <c r="B12" s="118" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C12" s="158">
         <f ca="1">(Normalized_FCF!G4/OFFSET(Normalized_FCF!G4, 0, $C$4))^(1/$C$4) - 1</f>
         <v>0.17871698612149922</v>
       </c>
       <c r="D12" s="158"/>
-      <c r="E12" s="366"/>
-      <c r="F12" s="366"/>
+      <c r="E12" s="368"/>
+      <c r="F12" s="368"/>
       <c r="H12" s="247">
         <v>9</v>
       </c>
@@ -18762,14 +18793,14 @@
     </row>
     <row r="13" spans="2:9">
       <c r="B13" s="148" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C13" s="158">
         <f ca="1">(Normalized_FCF!G8/OFFSET(Normalized_FCF!G8, 0, $C$4))^(1/$C$4) - 1</f>
         <v>0.37273927208324187</v>
       </c>
-      <c r="E13" s="366"/>
-      <c r="F13" s="366"/>
+      <c r="E13" s="368"/>
+      <c r="F13" s="368"/>
       <c r="H13" s="247">
         <v>10</v>
       </c>
@@ -18786,12 +18817,12 @@
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
         <v>0.40378207079529949</v>
       </c>
-      <c r="E14" s="366"/>
-      <c r="F14" s="366"/>
+      <c r="E14" s="368"/>
+      <c r="F14" s="368"/>
     </row>
     <row r="16" spans="2:9" ht="13.9">
       <c r="B16" s="36" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C16" s="37"/>
       <c r="D16" s="37"/>
@@ -18800,38 +18831,38 @@
     </row>
     <row r="17" spans="2:6" ht="13.15">
       <c r="B17" s="109" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E17" s="159" t="s">
-        <v>331</v>
+        <v>326</v>
       </c>
     </row>
     <row r="18" spans="2:6">
       <c r="B18" s="152" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C18" s="150">
         <v>5</v>
       </c>
-      <c r="E18" s="366" t="s">
-        <v>332</v>
-      </c>
-      <c r="F18" s="367"/>
+      <c r="E18" s="368" t="s">
+        <v>327</v>
+      </c>
+      <c r="F18" s="369"/>
     </row>
     <row r="19" spans="2:6">
-      <c r="E19" s="367"/>
-      <c r="F19" s="367"/>
+      <c r="E19" s="369"/>
+      <c r="F19" s="369"/>
     </row>
     <row r="20" spans="2:6" ht="13.15">
       <c r="B20" s="159" t="s">
-        <v>304</v>
-      </c>
-      <c r="E20" s="367"/>
-      <c r="F20" s="367"/>
+        <v>302</v>
+      </c>
+      <c r="E20" s="369"/>
+      <c r="F20" s="369"/>
     </row>
     <row r="21" spans="2:6">
       <c r="B21" s="100" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
@@ -18841,12 +18872,12 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E21" s="367"/>
-      <c r="F21" s="367"/>
+      <c r="E21" s="369"/>
+      <c r="F21" s="369"/>
     </row>
     <row r="22" spans="2:6">
       <c r="B22" s="100" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C22" s="160">
         <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
@@ -18856,44 +18887,44 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E22" s="367"/>
-      <c r="F22" s="367"/>
+      <c r="E22" s="369"/>
+      <c r="F22" s="369"/>
     </row>
     <row r="24" spans="2:6" ht="13.15">
       <c r="B24" s="159" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E24" s="159" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F24" s="159"/>
     </row>
     <row r="25" spans="2:6">
       <c r="B25" s="152" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C25" s="166">
         <f>C18</f>
         <v>5</v>
       </c>
       <c r="D25" s="163"/>
-      <c r="E25" s="365"/>
-      <c r="F25" s="365"/>
+      <c r="E25" s="367"/>
+      <c r="F25" s="367"/>
     </row>
     <row r="26" spans="2:6">
       <c r="B26" s="118" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C26" s="164">
         <v>0.03</v>
       </c>
       <c r="D26" s="164"/>
-      <c r="E26" s="365"/>
-      <c r="F26" s="365"/>
+      <c r="E26" s="367"/>
+      <c r="F26" s="367"/>
     </row>
     <row r="27" spans="2:6">
       <c r="B27" s="100" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C27" s="160">
         <f>IF(valuation_method="DCF",DCF!E76,DDM!E71)</f>
@@ -18903,55 +18934,55 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E27" s="365"/>
-      <c r="F27" s="365"/>
+      <c r="E27" s="367"/>
+      <c r="F27" s="367"/>
     </row>
     <row r="28" spans="2:6">
       <c r="B28" s="100" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C28" s="165">
         <v>0.6</v>
       </c>
       <c r="D28" s="165"/>
-      <c r="E28" s="365"/>
-      <c r="F28" s="365"/>
+      <c r="E28" s="367"/>
+      <c r="F28" s="367"/>
     </row>
     <row r="30" spans="2:6" ht="13.15">
       <c r="B30" s="159" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E30" s="159" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F30" s="159"/>
     </row>
     <row r="31" spans="2:6">
       <c r="B31" s="152" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C31" s="166">
         <f>C18</f>
         <v>5</v>
       </c>
       <c r="D31" s="163"/>
-      <c r="E31" s="365"/>
-      <c r="F31" s="365"/>
+      <c r="E31" s="367"/>
+      <c r="F31" s="367"/>
     </row>
     <row r="32" spans="2:6">
       <c r="B32" s="118" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C32" s="164">
         <v>0.01</v>
       </c>
       <c r="D32" s="164"/>
-      <c r="E32" s="365"/>
-      <c r="F32" s="365"/>
+      <c r="E32" s="367"/>
+      <c r="F32" s="367"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="100" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C33" s="160">
         <f>IF(valuation_method="DCF",DCF!E77,DDM!E72)</f>
@@ -18961,55 +18992,55 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E33" s="365"/>
-      <c r="F33" s="365"/>
+      <c r="E33" s="367"/>
+      <c r="F33" s="367"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="100" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C34" s="165">
         <v>0.2</v>
       </c>
       <c r="D34" s="165"/>
-      <c r="E34" s="365"/>
-      <c r="F34" s="365"/>
+      <c r="E34" s="367"/>
+      <c r="F34" s="367"/>
     </row>
     <row r="36" spans="2:6" ht="13.15">
       <c r="B36" s="159" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E36" s="159" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F36" s="159"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="152" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C37" s="166">
         <f>C18</f>
         <v>5</v>
       </c>
       <c r="D37" s="163"/>
-      <c r="E37" s="365"/>
-      <c r="F37" s="365"/>
+      <c r="E37" s="367"/>
+      <c r="F37" s="367"/>
     </row>
     <row r="38" spans="2:6">
       <c r="B38" s="118" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C38" s="164">
         <v>0.05</v>
       </c>
       <c r="D38" s="164"/>
-      <c r="E38" s="365"/>
-      <c r="F38" s="365"/>
+      <c r="E38" s="367"/>
+      <c r="F38" s="367"/>
     </row>
     <row r="39" spans="2:6">
       <c r="B39" s="100" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C39" s="160">
         <f>IF(valuation_method="DCF",DCF!E75,DDM!E70)</f>
@@ -19019,24 +19050,24 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E39" s="365"/>
-      <c r="F39" s="365"/>
+      <c r="E39" s="367"/>
+      <c r="F39" s="367"/>
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="100" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C40" s="167">
         <f>1-C28-C34</f>
         <v>0.2</v>
       </c>
       <c r="D40" s="165"/>
-      <c r="E40" s="365"/>
-      <c r="F40" s="365"/>
+      <c r="E40" s="367"/>
+      <c r="F40" s="367"/>
     </row>
     <row r="42" spans="2:6" ht="13.15">
       <c r="B42" s="100" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C42" s="154">
         <f>C27*C28+C33*C34+C39*C40</f>
@@ -19049,7 +19080,7 @@
     </row>
     <row r="44" spans="2:6" ht="13.9">
       <c r="B44" s="36" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C44" s="37"/>
       <c r="D44" s="37"/>
@@ -19058,12 +19089,12 @@
     </row>
     <row r="45" spans="2:6" ht="13.15">
       <c r="B45" s="109" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="46" spans="2:6">
       <c r="B46" s="152" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C46" s="150">
         <v>10</v>
@@ -19078,39 +19109,39 @@
     </row>
     <row r="48" spans="2:6" ht="13.15">
       <c r="B48" s="159" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E48" s="159" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F48" s="159"/>
     </row>
     <row r="49" spans="2:6" ht="12.75" customHeight="1">
       <c r="B49" s="152" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C49" s="166">
         <f>C46</f>
         <v>10</v>
       </c>
       <c r="D49" s="163"/>
-      <c r="E49" s="365"/>
-      <c r="F49" s="365"/>
+      <c r="E49" s="367"/>
+      <c r="F49" s="367"/>
     </row>
     <row r="50" spans="2:6">
       <c r="B50" s="118" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C50" s="164">
         <v>0</v>
       </c>
       <c r="D50" s="164"/>
-      <c r="E50" s="365"/>
-      <c r="F50" s="365"/>
+      <c r="E50" s="367"/>
+      <c r="F50" s="367"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="100" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C51" s="160">
         <f>IF(valuation_method="DCF",DCF!E78,DDM!E73)</f>
@@ -19120,55 +19151,55 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E51" s="365"/>
-      <c r="F51" s="365"/>
+      <c r="E51" s="367"/>
+      <c r="F51" s="367"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="100" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C52" s="165">
         <v>0.05</v>
       </c>
       <c r="D52" s="165"/>
-      <c r="E52" s="365"/>
-      <c r="F52" s="365"/>
+      <c r="E52" s="367"/>
+      <c r="F52" s="367"/>
     </row>
     <row r="54" spans="2:6" ht="13.15">
       <c r="B54" s="159" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="E54" s="159" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F54" s="159"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="152" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C55" s="166">
         <f>C46</f>
         <v>10</v>
       </c>
       <c r="D55" s="163"/>
-      <c r="E55" s="365"/>
-      <c r="F55" s="365"/>
+      <c r="E55" s="367"/>
+      <c r="F55" s="367"/>
     </row>
     <row r="56" spans="2:6">
       <c r="B56" s="118" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C56" s="164">
         <v>0.08</v>
       </c>
       <c r="D56" s="164"/>
-      <c r="E56" s="365"/>
-      <c r="F56" s="365"/>
+      <c r="E56" s="367"/>
+      <c r="F56" s="367"/>
     </row>
     <row r="57" spans="2:6">
       <c r="B57" s="100" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C57" s="160">
         <f>IF(valuation_method="DCF",DCF!E74,DDM!E69)</f>
@@ -19178,23 +19209,23 @@
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
-      <c r="E57" s="365"/>
-      <c r="F57" s="365"/>
+      <c r="E57" s="367"/>
+      <c r="F57" s="367"/>
     </row>
     <row r="58" spans="2:6">
       <c r="B58" s="100" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C58" s="165">
         <v>0.05</v>
       </c>
       <c r="D58" s="165"/>
-      <c r="E58" s="365"/>
-      <c r="F58" s="365"/>
+      <c r="E58" s="367"/>
+      <c r="F58" s="367"/>
     </row>
     <row r="60" spans="2:6" ht="13.15">
       <c r="B60" s="100" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C60" s="154">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
@@ -19205,7 +19236,7 @@
         <v>HKD</v>
       </c>
       <c r="E60" s="100" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="F60" s="277">
         <f>Thesis!F28</f>
@@ -19214,7 +19245,7 @@
     </row>
     <row r="62" spans="2:6" ht="13.9">
       <c r="B62" s="36" t="s">
-        <v>351</v>
+        <v>346</v>
       </c>
       <c r="C62" s="37"/>
       <c r="D62" s="37"/>
@@ -19223,15 +19254,15 @@
     </row>
     <row r="63" spans="2:6" ht="13.15">
       <c r="B63" s="109" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="E63" s="252" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
     </row>
     <row r="64" spans="2:6">
       <c r="B64" s="152" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C64" s="166">
         <f>C18</f>
@@ -19239,19 +19270,19 @@
       </c>
       <c r="D64" s="150"/>
       <c r="E64" s="251" t="s">
-        <v>398</v>
+        <v>392</v>
       </c>
     </row>
     <row r="65" spans="2:6">
       <c r="B65" s="118" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C65" s="151">
-        <v>2.3752619295331442E-2</v>
+        <v>2.3752619295331401E-2</v>
       </c>
       <c r="D65" s="151"/>
       <c r="E65" s="251" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
     </row>
     <row r="66" spans="2:6">
@@ -19267,20 +19298,20 @@
         <v>HKD</v>
       </c>
       <c r="E66" s="251" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
     </row>
     <row r="68" spans="2:6" ht="13.15">
       <c r="B68" s="109" t="s">
-        <v>352</v>
+        <v>347</v>
       </c>
       <c r="E68" s="252" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
     </row>
     <row r="69" spans="2:6">
       <c r="B69" s="100" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="C69" s="244" t="str">
         <f>IF(C60&lt;C22,"Y","N")</f>
@@ -19290,19 +19321,19 @@
     </row>
     <row r="70" spans="2:6">
       <c r="B70" s="100" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="C70" s="244" t="str">
         <f>IF(C69="Y","N",IF(C65&gt;8%,"N","Y"))</f>
         <v>Y</v>
       </c>
       <c r="E70" s="251" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
     </row>
     <row r="71" spans="2:6">
       <c r="B71" s="100" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="C71" s="244" t="str">
         <f>IF(C65&gt;8%,"Y","N")</f>
@@ -19312,14 +19343,14 @@
     </row>
     <row r="72" spans="2:6">
       <c r="B72" s="100" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="C72" s="243" t="str">
         <f>IF(F72&gt;50%,"Y","N")</f>
         <v>N</v>
       </c>
       <c r="E72" s="134" t="s">
-        <v>348</v>
+        <v>343</v>
       </c>
       <c r="F72" s="291">
         <f>BS!D89/C60</f>
@@ -19328,7 +19359,7 @@
     </row>
     <row r="74" spans="2:6" ht="13.9">
       <c r="B74" s="36" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C74" s="37"/>
       <c r="D74" s="37"/>
@@ -19337,12 +19368,12 @@
     </row>
     <row r="75" spans="2:6" ht="13.15">
       <c r="B75" s="109" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="76" spans="2:6">
       <c r="B76" s="246" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C76" s="245">
         <f>F60</f>
@@ -19352,10 +19383,10 @@
     </row>
     <row r="77" spans="2:6">
       <c r="B77" s="100" t="s">
-        <v>111</v>
+        <v>455</v>
       </c>
       <c r="C77" s="173">
-        <f>Normalized_FCF!C90</f>
+        <f>Normalized_FCF!C90*(1-dividend_tax_rate)</f>
         <v>1.47231918072</v>
       </c>
       <c r="D77" t="str">
@@ -19365,12 +19396,12 @@
     </row>
     <row r="79" spans="2:6" ht="13.15">
       <c r="B79" s="109" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="80" spans="2:6">
       <c r="B80" s="148" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="C80" s="167">
         <f>Thesis!F29</f>
@@ -19379,7 +19410,7 @@
     </row>
     <row r="81" spans="2:8">
       <c r="B81" s="100" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C81" s="116">
         <f>PV(C80, C76, -C77, 0)</f>
@@ -19391,7 +19422,7 @@
     </row>
     <row r="82" spans="2:8">
       <c r="B82" s="100" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C82" s="116">
         <f>C60/(1+C80)^C76</f>
@@ -19412,7 +19443,7 @@
         <v>HKD</v>
       </c>
       <c r="E83" s="146" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F83" s="291">
         <f>(1-C83/C60)</f>
@@ -19424,12 +19455,12 @@
     </row>
     <row r="85" spans="2:8" ht="13.15">
       <c r="B85" s="109" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
     </row>
     <row r="86" spans="2:8">
       <c r="B86" s="148" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
@@ -19442,7 +19473,7 @@
     </row>
     <row r="87" spans="2:8" ht="13.15">
       <c r="B87" s="100" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
@@ -19454,12 +19485,12 @@
     </row>
     <row r="89" spans="2:8" ht="13.15">
       <c r="B89" s="109" t="s">
-        <v>415</v>
+        <v>409</v>
       </c>
     </row>
     <row r="90" spans="2:8">
       <c r="B90" s="148" t="s">
-        <v>416</v>
+        <v>410</v>
       </c>
       <c r="C90" s="167">
         <f>Thesis!F30</f>
@@ -19468,7 +19499,7 @@
     </row>
     <row r="91" spans="2:8">
       <c r="B91" s="100" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C91" s="116">
         <f>PV(C90, C76, -C77, 0)</f>
@@ -19480,7 +19511,7 @@
     </row>
     <row r="92" spans="2:8">
       <c r="B92" s="100" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C92" s="116">
         <f>C60/(1+C90)^C76</f>
@@ -19501,7 +19532,7 @@
         <v>HKD</v>
       </c>
       <c r="E93" s="146" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F93" s="291">
         <f>(1-C93/C60)</f>
@@ -19510,14 +19541,14 @@
     </row>
     <row r="95" spans="2:8" ht="13.15">
       <c r="B95" s="109" t="s">
-        <v>400</v>
+        <v>394</v>
       </c>
       <c r="G95" s="2"/>
       <c r="H95" s="281"/>
     </row>
     <row r="96" spans="2:8">
       <c r="B96" s="148" t="s">
-        <v>406</v>
+        <v>400</v>
       </c>
       <c r="C96" s="134">
         <f>Thesis!F31</f>
@@ -19528,7 +19559,7 @@
     </row>
     <row r="97" spans="2:8">
       <c r="B97" s="100" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C97" s="116">
         <f>PV(C96, C76, -C77, 0)</f>
@@ -19540,7 +19571,7 @@
     </row>
     <row r="98" spans="2:8">
       <c r="B98" s="100" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C98" s="116">
         <f>C60/(1+C96)^C76</f>
@@ -19552,17 +19583,17 @@
     </row>
     <row r="99" spans="2:8" ht="13.15">
       <c r="B99" s="110" t="s">
-        <v>401</v>
+        <v>395</v>
       </c>
       <c r="C99" s="111">
         <f>C97+C98</f>
         <v>30.179167378278677</v>
       </c>
       <c r="D99" t="s">
-        <v>399</v>
+        <v>393</v>
       </c>
       <c r="E99" s="146" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F99" s="291">
         <f>(1-C99/C60)</f>
@@ -19574,12 +19605,12 @@
     </row>
     <row r="101" spans="2:8" ht="13.15">
       <c r="B101" s="109" t="s">
-        <v>424</v>
+        <v>418</v>
       </c>
     </row>
     <row r="102" spans="2:8">
       <c r="B102" s="148" t="s">
-        <v>423</v>
+        <v>417</v>
       </c>
       <c r="C102" s="134">
         <f>Thesis!F32</f>
@@ -19588,7 +19619,7 @@
     </row>
     <row r="103" spans="2:8">
       <c r="B103" s="100" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C103" s="116">
         <f>PV(C102, C76, -C77, 0)</f>
@@ -19598,7 +19629,7 @@
     </row>
     <row r="104" spans="2:8">
       <c r="B104" s="100" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C104" s="116">
         <f>C60/(1+C102)^C76</f>
@@ -19608,17 +19639,17 @@
     </row>
     <row r="105" spans="2:8" ht="13.15">
       <c r="B105" s="110" t="s">
-        <v>401</v>
+        <v>395</v>
       </c>
       <c r="C105" s="111">
         <f>C103+C104</f>
         <v>27.015254809865393</v>
       </c>
       <c r="D105" t="s">
-        <v>399</v>
+        <v>393</v>
       </c>
       <c r="E105" s="146" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F105" s="291">
         <f>(1-C105/C66)</f>
@@ -19630,32 +19661,32 @@
     </row>
     <row r="107" spans="2:8" ht="14.65">
       <c r="E107" s="285" t="s">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="F107" s="282"/>
     </row>
     <row r="108" spans="2:8" ht="13.9">
       <c r="E108" s="278" t="s">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="F108" s="283" t="s">
-        <v>328</v>
+        <v>323</v>
       </c>
     </row>
     <row r="109" spans="2:8" ht="13.9">
       <c r="E109" s="279" t="s">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="F109" s="283" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
     </row>
     <row r="110" spans="2:8" ht="13.9">
       <c r="E110" s="280" t="s">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="F110" s="284" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
     </row>
   </sheetData>

--- a/financial_models/opportunities/1913.HK_Valuation.xlsx
+++ b/financial_models/opportunities/1913.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFEF12AE-0E50-4144-A9DE-2A16BD191F73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FE3584E-DEAA-4D24-A51E-DC3E56DCA077}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3896,29 +3896,29 @@
     <xf numFmtId="10" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4336,7 +4336,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>50.15</v>
+        <v>50.65</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4357,7 +4357,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>128325.0236</v>
+        <v>129604.4356</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4384,7 +4384,7 @@
         <v>1</v>
       </c>
       <c r="C16" s="50">
-        <v>8.97755598</v>
+        <v>8.9818395600000009</v>
       </c>
       <c r="D16" s="50"/>
       <c r="E16" s="5"/>
@@ -4394,13 +4394,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="360" t="s">
+      <c r="B18" s="358" t="s">
         <v>356</v>
       </c>
-      <c r="C18" s="360"/>
-      <c r="D18" s="360"/>
-      <c r="E18" s="360"/>
-      <c r="F18" s="360"/>
+      <c r="C18" s="358"/>
+      <c r="D18" s="358"/>
+      <c r="E18" s="358"/>
+      <c r="F18" s="358"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4476,14 +4476,14 @@
       </c>
       <c r="C26" s="304">
         <f>C132</f>
-        <v>32.734974170923991</v>
+        <v>32.750067624836312</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>396</v>
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>-9.8595701784031209E-2</v>
+        <v>-0.10153176218238202</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4515,7 +4515,7 @@
       </c>
       <c r="C29" s="310">
         <f>C149</f>
-        <v>15.243413565733329</v>
+        <v>15.250481198063488</v>
       </c>
       <c r="D29" s="310" t="str">
         <f>D149</f>
@@ -4534,7 +4534,7 @@
       </c>
       <c r="C30" s="311">
         <f>C157</f>
-        <v>21.161970196851307</v>
+        <v>21.17177605710603</v>
       </c>
       <c r="D30" s="311" t="str">
         <f>D157</f>
@@ -4553,7 +4553,7 @@
       </c>
       <c r="C31" s="311">
         <f>C165</f>
-        <v>30.179167378278677</v>
+        <v>30.193143901383809</v>
       </c>
       <c r="D31" s="311" t="str">
         <f>D165</f>
@@ -4572,7 +4572,7 @@
       </c>
       <c r="C32" s="311">
         <f>C173</f>
-        <v>27.015254809865393</v>
+        <v>27.027768070697245</v>
       </c>
       <c r="D32" s="311" t="str">
         <f>D173</f>
@@ -4600,22 +4600,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="360" t="s">
+      <c r="B36" s="358" t="s">
         <v>357</v>
       </c>
-      <c r="C36" s="360"/>
-      <c r="D36" s="360"/>
-      <c r="E36" s="360"/>
-      <c r="F36" s="360"/>
+      <c r="C36" s="358"/>
+      <c r="D36" s="358"/>
+      <c r="E36" s="358"/>
+      <c r="F36" s="358"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="363" t="s">
+      <c r="B37" s="360" t="s">
         <v>336</v>
       </c>
-      <c r="C37" s="363"/>
-      <c r="D37" s="363"/>
-      <c r="E37" s="363"/>
-      <c r="F37" s="363"/>
+      <c r="C37" s="360"/>
+      <c r="D37" s="360"/>
+      <c r="E37" s="360"/>
+      <c r="F37" s="360"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4627,13 +4627,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="361" t="s">
+      <c r="B40" s="359" t="s">
         <v>230</v>
       </c>
-      <c r="C40" s="361"/>
-      <c r="D40" s="361"/>
-      <c r="E40" s="361"/>
-      <c r="F40" s="361"/>
+      <c r="C40" s="359"/>
+      <c r="D40" s="359"/>
+      <c r="E40" s="359"/>
+      <c r="F40" s="359"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4653,13 +4653,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="361" t="s">
+      <c r="B43" s="359" t="s">
         <v>232</v>
       </c>
-      <c r="C43" s="361"/>
-      <c r="D43" s="361"/>
-      <c r="E43" s="361"/>
-      <c r="F43" s="361"/>
+      <c r="C43" s="359"/>
+      <c r="D43" s="359"/>
+      <c r="E43" s="359"/>
+      <c r="F43" s="359"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4688,13 +4688,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="361" t="s">
+      <c r="B47" s="359" t="s">
         <v>235</v>
       </c>
-      <c r="C47" s="361"/>
-      <c r="D47" s="361"/>
-      <c r="E47" s="361"/>
-      <c r="F47" s="361"/>
+      <c r="C47" s="359"/>
+      <c r="D47" s="359"/>
+      <c r="E47" s="359"/>
+      <c r="F47" s="359"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4710,13 +4710,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="361" t="s">
+      <c r="B50" s="359" t="s">
         <v>239</v>
       </c>
-      <c r="C50" s="361"/>
-      <c r="D50" s="361"/>
-      <c r="E50" s="361"/>
-      <c r="F50" s="361"/>
+      <c r="C50" s="359"/>
+      <c r="D50" s="359"/>
+      <c r="E50" s="359"/>
+      <c r="F50" s="359"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4780,13 +4780,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="361" t="s">
+      <c r="B58" s="359" t="s">
         <v>240</v>
       </c>
-      <c r="C58" s="361"/>
-      <c r="D58" s="361"/>
-      <c r="E58" s="361"/>
-      <c r="F58" s="361"/>
+      <c r="C58" s="359"/>
+      <c r="D58" s="359"/>
+      <c r="E58" s="359"/>
+      <c r="F58" s="359"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4802,7 +4802,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="361" t="s">
+      <c r="B61" s="359" t="s">
         <v>335</v>
       </c>
       <c r="C61" s="362"/>
@@ -4824,22 +4824,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="360" t="s">
+      <c r="B64" s="358" t="s">
         <v>340</v>
       </c>
-      <c r="C64" s="360"/>
-      <c r="D64" s="360"/>
-      <c r="E64" s="360"/>
-      <c r="F64" s="360"/>
+      <c r="C64" s="358"/>
+      <c r="D64" s="358"/>
+      <c r="E64" s="358"/>
+      <c r="F64" s="358"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="360" t="s">
+      <c r="B65" s="358" t="s">
         <v>358</v>
       </c>
-      <c r="C65" s="360"/>
-      <c r="D65" s="360"/>
-      <c r="E65" s="360"/>
-      <c r="F65" s="360"/>
+      <c r="C65" s="358"/>
+      <c r="D65" s="358"/>
+      <c r="E65" s="358"/>
+      <c r="F65" s="358"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4873,7 +4873,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>4.8496813803793899E-2</v>
+        <v>4.8040980840132586E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4883,14 +4883,14 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>2.9358308688334996E-2</v>
+        <v>2.9082363037314912E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>444</v>
       </c>
       <c r="F70" s="315">
         <f>Normalized_FCF!C92</f>
-        <v>5.4347046549072271</v>
+        <v>5.4372977874053738</v>
       </c>
     </row>
     <row r="72" spans="1:6">
@@ -4974,22 +4974,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.6" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="360" t="s">
+      <c r="B80" s="358" t="s">
         <v>359</v>
       </c>
-      <c r="C80" s="360"/>
-      <c r="D80" s="360"/>
-      <c r="E80" s="360"/>
-      <c r="F80" s="360"/>
+      <c r="C80" s="358"/>
+      <c r="D80" s="358"/>
+      <c r="E80" s="358"/>
+      <c r="F80" s="358"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="363" t="s">
+      <c r="B81" s="360" t="s">
         <v>251</v>
       </c>
-      <c r="C81" s="363"/>
-      <c r="D81" s="363"/>
-      <c r="E81" s="363"/>
-      <c r="F81" s="363"/>
+      <c r="C81" s="360"/>
+      <c r="D81" s="360"/>
+      <c r="E81" s="360"/>
+      <c r="F81" s="360"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5033,22 +5033,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="360" t="s">
+      <c r="B89" s="358" t="s">
         <v>360</v>
       </c>
-      <c r="C89" s="360"/>
-      <c r="D89" s="360"/>
-      <c r="E89" s="360"/>
-      <c r="F89" s="360"/>
+      <c r="C89" s="358"/>
+      <c r="D89" s="358"/>
+      <c r="E89" s="358"/>
+      <c r="F89" s="358"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="360" t="s">
+      <c r="B90" s="358" t="s">
         <v>361</v>
       </c>
-      <c r="C90" s="360"/>
-      <c r="D90" s="360"/>
-      <c r="E90" s="360"/>
-      <c r="F90" s="360"/>
+      <c r="C90" s="358"/>
+      <c r="D90" s="358"/>
+      <c r="E90" s="358"/>
+      <c r="F90" s="358"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5064,7 +5064,7 @@
       </c>
       <c r="C93" s="223">
         <f>DCF!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>32.428202830136861</v>
+        <v>32.443675727369531</v>
       </c>
       <c r="D93" s="1" t="str">
         <f>Market_currency</f>
@@ -5085,13 +5085,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="360" t="s">
+      <c r="B97" s="358" t="s">
         <v>362</v>
       </c>
-      <c r="C97" s="360"/>
-      <c r="D97" s="360"/>
-      <c r="E97" s="360"/>
-      <c r="F97" s="360"/>
+      <c r="C97" s="358"/>
+      <c r="D97" s="358"/>
+      <c r="E97" s="358"/>
+      <c r="F97" s="358"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5104,13 +5104,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="360" t="s">
+      <c r="B101" s="358" t="s">
         <v>341</v>
       </c>
-      <c r="C101" s="360"/>
-      <c r="D101" s="360"/>
-      <c r="E101" s="360"/>
-      <c r="F101" s="360"/>
+      <c r="C101" s="358"/>
+      <c r="D101" s="358"/>
+      <c r="E101" s="358"/>
+      <c r="F101" s="358"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="C103" s="223">
         <f>C102*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>3.0400888285673417</v>
+        <v>3.0415393863509177</v>
       </c>
       <c r="D103" s="1" t="str">
         <f>Market_currency</f>
@@ -5180,7 +5180,7 @@
       </c>
       <c r="C109" s="349">
         <f>DCF!C8</f>
-        <v>414442.7738145804</v>
+        <v>414292.97447467817</v>
       </c>
       <c r="D109" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5193,7 +5193,7 @@
       </c>
       <c r="C110" s="223">
         <f>C109*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>1.4540598346845557</v>
+        <v>1.4542278122945285</v>
       </c>
       <c r="D110" s="1" t="str">
         <f>Market_currency</f>
@@ -5224,7 +5224,7 @@
       </c>
       <c r="C114" s="223">
         <f>C113*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>1.3200265676401347E-2</v>
+        <v>1.3206564093718051E-2</v>
       </c>
       <c r="D114" s="1" t="str">
         <f>Market_currency</f>
@@ -5232,13 +5232,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="360" t="s">
+      <c r="B116" s="358" t="s">
         <v>363</v>
       </c>
-      <c r="C116" s="360"/>
-      <c r="D116" s="360"/>
-      <c r="E116" s="360"/>
-      <c r="F116" s="360"/>
+      <c r="C116" s="358"/>
+      <c r="D116" s="358"/>
+      <c r="E116" s="358"/>
+      <c r="F116" s="358"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="C118" s="223">
         <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
-        <v>30.855374101930472</v>
+        <v>30.869570717406862</v>
       </c>
       <c r="D118" s="1" t="str">
         <f>Market_currency</f>
@@ -5259,7 +5259,7 @@
       </c>
       <c r="C119" s="223">
         <f>BS!D47</f>
-        <v>-5.8344377867115664</v>
+        <v>-5.8372216491647873</v>
       </c>
       <c r="D119" s="1" t="str">
         <f>Market_currency</f>
@@ -5277,13 +5277,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B123" s="361" t="s">
+      <c r="B123" s="359" t="s">
         <v>364</v>
       </c>
-      <c r="C123" s="361"/>
-      <c r="D123" s="361"/>
-      <c r="E123" s="361"/>
-      <c r="F123" s="361"/>
+      <c r="C123" s="359"/>
+      <c r="D123" s="359"/>
+      <c r="E123" s="359"/>
+      <c r="F123" s="359"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5317,7 +5317,7 @@
       </c>
       <c r="E126" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E74,DDM!E69),2)&amp;" "&amp;Market_currency</f>
-        <v>40.37 HKD</v>
+        <v>40.39 HKD</v>
       </c>
       <c r="F126" s="232">
         <f>DCF!F74</f>
@@ -5339,7 +5339,7 @@
       </c>
       <c r="E127" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E75,DDM!E70),2)&amp;" "&amp;Market_currency</f>
-        <v>33.48 HKD</v>
+        <v>33.5 HKD</v>
       </c>
       <c r="F127" s="221">
         <f>DCF!F75</f>
@@ -5361,7 +5361,7 @@
       </c>
       <c r="E128" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E76,DDM!E71),2)&amp;" "&amp;Market_currency</f>
-        <v>32.41 HKD</v>
+        <v>32.42 HKD</v>
       </c>
       <c r="F128" s="221">
         <f>DCF!F76</f>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="E129" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E77,DDM!E72),2)&amp;" "&amp;Market_currency</f>
-        <v>31.37 HKD</v>
+        <v>31.38 HKD</v>
       </c>
       <c r="F129" s="221">
         <f>DCF!F77</f>
@@ -5405,7 +5405,7 @@
       </c>
       <c r="E130" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E78,DDM!E73),2)&amp;" "&amp;Market_currency</f>
-        <v>30.86 HKD</v>
+        <v>30.87 HKD</v>
       </c>
       <c r="F130" s="221">
         <f>DCF!F78</f>
@@ -5418,7 +5418,7 @@
       </c>
       <c r="C132" s="217">
         <f>Scenarios!C60</f>
-        <v>32.734974170923991</v>
+        <v>32.750067624836312</v>
       </c>
       <c r="D132" s="212" t="str">
         <f>Market_currency</f>
@@ -5426,13 +5426,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="364" t="s">
+      <c r="B134" s="363" t="s">
         <v>367</v>
       </c>
-      <c r="C134" s="364"/>
-      <c r="D134" s="364"/>
-      <c r="E134" s="364"/>
-      <c r="F134" s="364"/>
+      <c r="C134" s="363"/>
+      <c r="D134" s="363"/>
+      <c r="E134" s="363"/>
+      <c r="F134" s="363"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5445,22 +5445,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="365" t="s">
+      <c r="B138" s="361" t="s">
         <v>365</v>
       </c>
-      <c r="C138" s="365"/>
-      <c r="D138" s="365"/>
-      <c r="E138" s="365"/>
-      <c r="F138" s="365"/>
+      <c r="C138" s="361"/>
+      <c r="D138" s="361"/>
+      <c r="E138" s="361"/>
+      <c r="F138" s="361"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="360" t="s">
+      <c r="B139" s="358" t="s">
         <v>366</v>
       </c>
-      <c r="C139" s="360"/>
-      <c r="D139" s="360"/>
-      <c r="E139" s="360"/>
-      <c r="F139" s="360"/>
+      <c r="C139" s="358"/>
+      <c r="D139" s="358"/>
+      <c r="E139" s="358"/>
+      <c r="F139" s="358"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5491,7 +5491,7 @@
       </c>
       <c r="C143" s="213">
         <f>Scenarios!C77</f>
-        <v>1.47231918072</v>
+        <v>1.4730216878400002</v>
       </c>
       <c r="D143" s="212" t="str">
         <f>Market_currency</f>
@@ -5527,7 +5527,7 @@
       </c>
       <c r="C147" s="216">
         <f>Scenarios!C81</f>
-        <v>2.440014683327854</v>
+        <v>2.4411789197993943</v>
       </c>
     </row>
     <row r="148" spans="2:4">
@@ -5537,7 +5537,7 @@
       </c>
       <c r="C148" s="216">
         <f>Scenarios!C82</f>
-        <v>12.803398882405475</v>
+        <v>12.809302278264093</v>
       </c>
     </row>
     <row r="149" spans="2:4">
@@ -5546,7 +5546,7 @@
       </c>
       <c r="C149" s="215">
         <f>Scenarios!C83</f>
-        <v>15.243413565733329</v>
+        <v>15.250481198063488</v>
       </c>
       <c r="D149" s="300" t="str">
         <f>IF($D$11="","",C149*$E$25)</f>
@@ -5572,7 +5572,7 @@
       </c>
       <c r="C151" s="92">
         <f>Scenarios!F83</f>
-        <v>0.53433861025395579</v>
+        <v>0.53433741350512065</v>
       </c>
     </row>
     <row r="153" spans="2:4">
@@ -5596,7 +5596,7 @@
       </c>
       <c r="C155" s="216">
         <f>Scenarios!C91</f>
-        <v>3.018844461140437</v>
+        <v>3.0202848823180561</v>
       </c>
     </row>
     <row r="156" spans="2:4">
@@ -5606,7 +5606,7 @@
       </c>
       <c r="C156" s="216">
         <f>Scenarios!C92</f>
-        <v>18.143125735710871</v>
+        <v>18.151491174787974</v>
       </c>
     </row>
     <row r="157" spans="2:4">
@@ -5615,7 +5615,7 @@
       </c>
       <c r="C157" s="215">
         <f>Scenarios!C93</f>
-        <v>21.161970196851307</v>
+        <v>21.17177605710603</v>
       </c>
       <c r="D157" s="300" t="str">
         <f>IF($D$11="","",C157*$E$25)</f>
@@ -5641,7 +5641,7 @@
       </c>
       <c r="C159" s="92">
         <f>Scenarios!F93</f>
-        <v>0.353536371027661</v>
+        <v>0.35353489038141039</v>
       </c>
     </row>
     <row r="161" spans="2:4">
@@ -5665,7 +5665,7 @@
       </c>
       <c r="C163" s="216">
         <f>Scenarios!C97</f>
-        <v>3.8288039267695555</v>
+        <v>3.8306308146175594</v>
       </c>
     </row>
     <row r="164" spans="2:4">
@@ -5675,7 +5675,7 @@
       </c>
       <c r="C164" s="216">
         <f>Scenarios!C98</f>
-        <v>26.350363451509121</v>
+        <v>26.362513086766249</v>
       </c>
     </row>
     <row r="165" spans="2:4">
@@ -5684,7 +5684,7 @@
       </c>
       <c r="C165" s="215">
         <f>Scenarios!C99</f>
-        <v>30.179167378278677</v>
+        <v>30.193143901383809</v>
       </c>
       <c r="D165" s="300" t="str">
         <f>IF($D$11="","",C165*$E$25)</f>
@@ -5710,7 +5710,7 @@
       </c>
       <c r="C167" s="92">
         <f>Scenarios!F99</f>
-        <v>7.807572351517067E-2</v>
+        <v>7.8073845609816006E-2</v>
       </c>
     </row>
     <row r="169" spans="2:4">
@@ -5734,7 +5734,7 @@
       </c>
       <c r="C171" s="216">
         <f>Scenarios!C103</f>
-        <v>3.5521218577845026</v>
+        <v>3.5538167286582092</v>
       </c>
     </row>
     <row r="172" spans="2:4">
@@ -5744,7 +5744,7 @@
       </c>
       <c r="C172" s="216">
         <f>Scenarios!C104</f>
-        <v>23.46313295208089</v>
+        <v>23.473951342039037</v>
       </c>
     </row>
     <row r="173" spans="2:4">
@@ -5753,7 +5753,7 @@
       </c>
       <c r="C173" s="215">
         <f>Scenarios!C105</f>
-        <v>27.015254809865393</v>
+        <v>27.027768070697245</v>
       </c>
       <c r="D173" s="300" t="str">
         <f>IF($D$11="","",C173*$E$25)</f>
@@ -5779,7 +5779,7 @@
       </c>
       <c r="C175" s="92">
         <f>Scenarios!F105</f>
-        <v>0.15787677826395219</v>
+        <v>0.15787472440753425</v>
       </c>
     </row>
     <row r="177" spans="1:6" ht="13.9">
@@ -5793,13 +5793,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="359" t="s">
+      <c r="B179" s="365" t="s">
         <v>373</v>
       </c>
-      <c r="C179" s="360"/>
-      <c r="D179" s="360"/>
-      <c r="E179" s="360"/>
-      <c r="F179" s="360"/>
+      <c r="C179" s="358"/>
+      <c r="D179" s="358"/>
+      <c r="E179" s="358"/>
+      <c r="F179" s="358"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5836,13 +5836,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="361" t="s">
+      <c r="B188" s="359" t="s">
         <v>378</v>
       </c>
-      <c r="C188" s="361"/>
-      <c r="D188" s="361"/>
-      <c r="E188" s="361"/>
-      <c r="F188" s="361"/>
+      <c r="C188" s="359"/>
+      <c r="D188" s="359"/>
+      <c r="E188" s="359"/>
+      <c r="F188" s="359"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5850,22 +5850,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="358" t="s">
+      <c r="B191" s="364" t="s">
         <v>379</v>
       </c>
-      <c r="C191" s="358"/>
-      <c r="D191" s="358"/>
-      <c r="E191" s="358"/>
-      <c r="F191" s="358"/>
+      <c r="C191" s="364"/>
+      <c r="D191" s="364"/>
+      <c r="E191" s="364"/>
+      <c r="F191" s="364"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="358" t="s">
+      <c r="B192" s="364" t="s">
         <v>380</v>
       </c>
-      <c r="C192" s="358"/>
-      <c r="D192" s="358"/>
-      <c r="E192" s="358"/>
-      <c r="F192" s="358"/>
+      <c r="C192" s="364"/>
+      <c r="D192" s="364"/>
+      <c r="E192" s="364"/>
+      <c r="F192" s="364"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5889,6 +5889,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5905,17 +5916,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -6488,15 +6488,15 @@
       </c>
       <c r="C25" s="39">
         <f>0.164*Exchange_Rate</f>
-        <v>1.47231918072</v>
+        <v>1.4730216878400002</v>
       </c>
       <c r="D25" s="39">
         <f>0.137*Exchange_Rate</f>
-        <v>1.2299251692600002</v>
+        <v>1.2305120197200001</v>
       </c>
       <c r="E25" s="39">
         <f>0.11*Exchange_Rate</f>
-        <v>0.9875311578</v>
+        <v>0.98800235160000016</v>
       </c>
       <c r="F25" s="39"/>
       <c r="G25" s="39"/>
@@ -7870,15 +7870,15 @@
       </c>
       <c r="C65" s="73">
         <f>IF(C$4="","",C25)</f>
-        <v>1.47231918072</v>
+        <v>1.4730216878400002</v>
       </c>
       <c r="D65" s="73">
         <f t="shared" ref="D65:M65" si="33">IF(D$4="","",D25)</f>
-        <v>1.2299251692600002</v>
+        <v>1.2305120197200001</v>
       </c>
       <c r="E65" s="73">
         <f t="shared" si="33"/>
-        <v>0.9875311578</v>
+        <v>0.98800235160000016</v>
       </c>
       <c r="F65" s="73">
         <f t="shared" si="33"/>
@@ -9220,11 +9220,11 @@
       </c>
       <c r="C47" s="147">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>15.435037956480281</v>
+        <v>15.44240268024663</v>
       </c>
       <c r="D47" s="147">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>-5.8344377867115664</v>
+        <v>-5.8372216491647873</v>
       </c>
       <c r="F47" s="253"/>
     </row>
@@ -9415,7 +9415,7 @@
       </c>
       <c r="D66" s="76">
         <f>C66-D75</f>
-        <v>414442.7738145804</v>
+        <v>414292.97447467817</v>
       </c>
       <c r="F66" s="5" t="s">
         <v>225</v>
@@ -9482,11 +9482,11 @@
       </c>
       <c r="C73" s="349">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35-Normalized_FCF!G91)/12</f>
-        <v>-646777.38794055616</v>
+        <v>-646927.1872804584</v>
       </c>
       <c r="D73" s="349">
         <f>(Normalized_FCF!C25+Normalized_FCF!C35-Normalized_FCF!C91)/12</f>
-        <v>-597120.2261854196</v>
+        <v>-597270.02552532183</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>348</v>
@@ -9498,11 +9498,11 @@
       </c>
       <c r="C74" s="258">
         <f>-$C$66/C73</f>
-        <v>1.5640048938955338</v>
+        <v>1.5636427404641804</v>
       </c>
       <c r="D74" s="258">
         <f>-$C$66/D73</f>
-        <v>1.6940692270000017</v>
+        <v>1.6936443430428165</v>
       </c>
       <c r="F74" s="253" t="s">
         <v>316</v>
@@ -9515,7 +9515,7 @@
       <c r="C75" s="320"/>
       <c r="D75" s="321">
         <f>MAX(-D73*D76,G5)</f>
-        <v>597120.2261854196</v>
+        <v>597270.02552532183</v>
       </c>
       <c r="F75" s="253" t="s">
         <v>349</v>
@@ -9630,11 +9630,11 @@
       </c>
       <c r="C86" s="76">
         <f>-DCF!C7*Exchange_Rate</f>
-        <v>-7779052.25667</v>
+        <v>-7782763.9787400011</v>
       </c>
       <c r="D86" s="223">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>-3.0400888285673417</v>
+        <v>-3.0415393863509177</v>
       </c>
       <c r="E86" s="240" t="str">
         <f>Market_currency</f>
@@ -9647,11 +9647,11 @@
       </c>
       <c r="C87" s="76">
         <f>DCF!C8*Exchange_Rate</f>
-        <v>3720683.2024268736</v>
+        <v>3721113.0275667352</v>
       </c>
       <c r="D87" s="223">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>1.4540598346845557</v>
+        <v>1.4542278122945287</v>
       </c>
       <c r="E87" s="240" t="str">
         <f>Market_currency</f>
@@ -9664,11 +9664,11 @@
       </c>
       <c r="C88" s="76">
         <f>DCF!C9*Exchange_Rate</f>
-        <v>33777.156619152003</v>
+        <v>33793.273160544006</v>
       </c>
       <c r="D88" s="223">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>1.3200265676401347E-2</v>
+        <v>1.3206564093718055E-2</v>
       </c>
       <c r="E88" s="240" t="str">
         <f>Market_currency</f>
@@ -9681,11 +9681,11 @@
       </c>
       <c r="C89" s="180">
         <f>SUM(C86:C88)</f>
-        <v>-4024591.8976239744</v>
+        <v>-4027857.6780127217</v>
       </c>
       <c r="D89" s="242">
         <f>SUM(D86:D88)</f>
-        <v>-1.5728287282063846</v>
+        <v>-1.574105009962671</v>
       </c>
       <c r="E89" s="240" t="str">
         <f>Market_currency</f>
@@ -13197,20 +13197,20 @@
       </c>
       <c r="C90" s="113">
         <f>G90</f>
-        <v>1.47231918072</v>
+        <v>1.4730216878400002</v>
       </c>
       <c r="E90" s="268"/>
       <c r="G90" s="112">
         <f>Data!C65</f>
-        <v>1.47231918072</v>
+        <v>1.4730216878400002</v>
       </c>
       <c r="H90" s="112">
         <f>Data!D65</f>
-        <v>1.2299251692600002</v>
+        <v>1.2305120197200001</v>
       </c>
       <c r="I90" s="112">
         <f>Data!E65</f>
-        <v>0.9875311578</v>
+        <v>0.98800235160000016</v>
       </c>
       <c r="J90" s="112">
         <f>Data!F65</f>
@@ -13253,20 +13253,20 @@
       </c>
       <c r="C91" s="74">
         <f>C90*Common_Shares/scaling_factor</f>
-        <v>3767405.655286673</v>
+        <v>3769203.2473655003</v>
       </c>
       <c r="E91" s="268"/>
       <c r="G91" s="74">
         <f t="shared" ref="G91:Q91" si="37">IF(G$4="","",G90*Common_Shares/scaling_factor)</f>
-        <v>3767405.655286673</v>
+        <v>3769203.2473655003</v>
       </c>
       <c r="H91" s="74">
         <f t="shared" si="37"/>
-        <v>3147162.0413065506</v>
+        <v>3148663.6883480097</v>
       </c>
       <c r="I91" s="74">
         <f t="shared" si="37"/>
-        <v>2526918.4273264268</v>
+        <v>2528124.1293305187</v>
       </c>
       <c r="J91" s="74">
         <f t="shared" si="37"/>
@@ -13308,20 +13308,20 @@
       </c>
       <c r="C92" s="23">
         <f>C90/(C19*scaling_factor/Common_Shares)</f>
-        <v>5.4347046549072271</v>
+        <v>5.4372977874053738</v>
       </c>
       <c r="E92" s="268"/>
       <c r="G92" s="170">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",G90/(G19*scaling_factor/Common_Shares))</f>
-        <v>3.7791967491440022</v>
+        <v>3.7809999672633623</v>
       </c>
       <c r="H92" s="170">
         <f t="shared" si="38"/>
-        <v>3.833257664362467</v>
+        <v>3.8350866772811822</v>
       </c>
       <c r="I92" s="170">
         <f t="shared" si="38"/>
-        <v>3.7611460141675304</v>
+        <v>3.7629406195010162</v>
       </c>
       <c r="J92" s="170">
         <f t="shared" si="38"/>
@@ -13384,20 +13384,20 @@
       </c>
       <c r="C94" s="23">
         <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
-        <v>2.9358308688334996E-2</v>
+        <v>2.9082363037314912E-2</v>
       </c>
       <c r="E94" s="268"/>
       <c r="G94" s="23">
         <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>2.9358308688334996E-2</v>
+        <v>2.9082363037314912E-2</v>
       </c>
       <c r="H94" s="23">
         <f t="shared" si="39"/>
-        <v>2.45249285994018E-2</v>
+        <v>2.4294413025074041E-2</v>
       </c>
       <c r="I94" s="23">
         <f t="shared" si="39"/>
-        <v>1.9691548510468594E-2</v>
+        <v>1.9506463012833174E-2</v>
       </c>
       <c r="J94" s="23">
         <f t="shared" si="39"/>
@@ -14526,38 +14526,38 @@
       </c>
       <c r="C125" s="177">
         <f>C16*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>2.4321152122602645</v>
+        <v>2.4332756795527151</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="265"/>
       <c r="F125" s="27"/>
       <c r="G125" s="177">
         <f t="shared" ref="G125:Q125" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>3.4975230830031299</v>
+        <v>3.4991919024414346</v>
       </c>
       <c r="H125" s="177">
         <f t="shared" si="49"/>
-        <v>2.8805060930019804</v>
+        <v>2.8818805069646838</v>
       </c>
       <c r="I125" s="177">
         <f t="shared" si="49"/>
-        <v>2.3571582219218832</v>
+        <v>2.3582829239943353</v>
       </c>
       <c r="J125" s="177">
         <f t="shared" si="49"/>
-        <v>1.2643331226722432</v>
+        <v>1.2649363906540505</v>
       </c>
       <c r="K125" s="177">
         <f t="shared" si="49"/>
-        <v>6.1076209056252253</v>
+        <v>6.1105351155524268</v>
       </c>
       <c r="L125" s="177">
         <f t="shared" si="49"/>
-        <v>8.2120640688953994</v>
+        <v>8.2159823996173245</v>
       </c>
       <c r="M125" s="177">
         <f t="shared" si="49"/>
-        <v>7.5975872108179461</v>
+        <v>7.6012123480710052</v>
       </c>
       <c r="N125" s="177" t="str">
         <f t="shared" si="49"/>
@@ -14583,38 +14583,38 @@
       </c>
       <c r="C126" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>4.8496813803793899E-2</v>
+        <v>4.8040980840132586E-2</v>
       </c>
       <c r="D126" s="27"/>
       <c r="E126" s="265"/>
       <c r="F126" s="27"/>
       <c r="G126" s="77">
         <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
-        <v>6.974123794622393E-2</v>
+        <v>6.9085723641489336E-2</v>
       </c>
       <c r="H126" s="77">
         <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
-        <v>5.74378084347354E-2</v>
+        <v>5.6897936958828901E-2</v>
       </c>
       <c r="I126" s="77">
         <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
-        <v>4.7002157964544031E-2</v>
+        <v>4.6560373622790432E-2</v>
       </c>
       <c r="J126" s="77">
         <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
-        <v>2.5211029365348817E-2</v>
+        <v>2.4974064968490632E-2</v>
       </c>
       <c r="K126" s="77">
         <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
-        <v>0.12178705694167948</v>
+        <v>0.1206423517384487</v>
       </c>
       <c r="L126" s="77">
         <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
-        <v>0.16375003128405582</v>
+        <v>0.16221090621159576</v>
       </c>
       <c r="M126" s="77">
         <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
-        <v>0.15149725245898199</v>
+        <v>0.1500732941376309</v>
       </c>
       <c r="N126" s="77" t="str">
         <f t="shared" ref="N126" si="57">IF(N$4="","",N125/Market_Price)</f>
@@ -14640,31 +14640,31 @@
       <c r="C127" s="169"/>
       <c r="G127" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.5723736208219957E-3</v>
+        <v>6.5074933284150656E-3</v>
       </c>
       <c r="H127" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.2475501746176963E-3</v>
+        <v>5.1957480998435831E-3</v>
       </c>
       <c r="I127" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.6559899763774521E-3</v>
+        <v>3.6198992559788594E-3</v>
       </c>
       <c r="J127" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.2996528013106868E-3</v>
+        <v>2.2769513916235133E-3</v>
       </c>
       <c r="K127" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-4.2367418664554214E-4</v>
+        <v>-4.1949181560264437E-4</v>
       </c>
       <c r="L127" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.0083690052794972E-3</v>
+        <v>1.9885430526113876E-3</v>
       </c>
       <c r="M127" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.6223024485771456E-3</v>
+        <v>1.6062876169031363E-3</v>
       </c>
       <c r="N127" s="23" t="str">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -15492,7 +15492,7 @@
       </c>
       <c r="C8" s="338">
         <f>BS!D66</f>
-        <v>414442.7738145804</v>
+        <v>414292.97447467817</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
@@ -15524,7 +15524,7 @@
       </c>
       <c r="C10" s="347">
         <f>C6-C7+C8+C9</f>
-        <v>8794539.6226867232</v>
+        <v>8794389.8233468216</v>
       </c>
       <c r="D10" t="str">
         <f>Reporting_currency</f>
@@ -15538,7 +15538,7 @@
       </c>
       <c r="C11" s="208">
         <f>Exchange_Rate</f>
-        <v>8.97755598</v>
+        <v>8.9818395600000009</v>
       </c>
       <c r="D11" t="str">
         <f>Thesis!C15</f>
@@ -15552,7 +15552,7 @@
       </c>
       <c r="C12" s="111">
         <f>(C10*scaling_factor)/Common_Shares*Exchange_Rate</f>
-        <v>30.855374101930472</v>
+        <v>30.869570717406862</v>
       </c>
       <c r="D12" t="str">
         <f>Market_currency</f>
@@ -15605,7 +15605,7 @@
       </c>
       <c r="C18" s="140">
         <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>32.079930956152829</v>
+        <v>32.094711860634071</v>
       </c>
       <c r="D18" t="str">
         <f>Market_currency</f>
@@ -16701,23 +16701,23 @@
       </c>
       <c r="B65" s="124">
         <f>C12</f>
-        <v>30.855374101930472</v>
+        <v>30.869570717406862</v>
       </c>
       <c r="C65" s="124">
         <f>C12</f>
-        <v>30.855374101930472</v>
+        <v>30.869570717406862</v>
       </c>
       <c r="D65" s="124">
         <f>C12</f>
-        <v>30.855374101930472</v>
+        <v>30.869570717406862</v>
       </c>
       <c r="E65" s="141">
         <f>C12</f>
-        <v>30.855374101930472</v>
+        <v>30.869570717406862</v>
       </c>
       <c r="F65" s="124">
         <f>C12</f>
-        <v>30.855374101930472</v>
+        <v>30.869570717406862</v>
       </c>
       <c r="H65" s="120"/>
     </row>
@@ -16728,23 +16728,23 @@
       </c>
       <c r="B66" s="124">
         <f t="shared" ref="B66:F71" si="4">(B56-$C$7+$C$8+$C$9)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>30.855374101930472</v>
+        <v>30.869570717406866</v>
       </c>
       <c r="C66" s="124">
         <f t="shared" si="4"/>
-        <v>31.365867546764274</v>
+        <v>31.380307740728544</v>
       </c>
       <c r="D66" s="124">
         <f t="shared" si="4"/>
-        <v>32.408998499180548</v>
+        <v>32.423936416010044</v>
       </c>
       <c r="E66" s="124">
         <f t="shared" si="4"/>
-        <v>33.482739653510706</v>
+        <v>33.498189898655845</v>
       </c>
       <c r="F66" s="124">
         <f t="shared" si="4"/>
-        <v>35.153681943664836</v>
+        <v>35.169929467600689</v>
       </c>
       <c r="H66" s="120"/>
     </row>
@@ -16755,23 +16755,23 @@
       </c>
       <c r="B67" s="124">
         <f t="shared" si="4"/>
-        <v>30.855374101930487</v>
+        <v>30.869570717406869</v>
       </c>
       <c r="C67" s="124">
         <f t="shared" si="4"/>
-        <v>31.85531934235112</v>
+        <v>31.869993074922903</v>
       </c>
       <c r="D67" s="124">
         <f t="shared" si="4"/>
-        <v>34.002421917904989</v>
+        <v>34.018120125920994</v>
       </c>
       <c r="E67" s="124">
         <f t="shared" si="4"/>
-        <v>36.365405993237999</v>
+        <v>36.382231683092932</v>
       </c>
       <c r="F67" s="124">
         <f t="shared" si="4"/>
-        <v>40.371939604409576</v>
+        <v>40.390676984627049</v>
       </c>
       <c r="H67" s="120"/>
     </row>
@@ -16782,23 +16782,23 @@
       </c>
       <c r="B68" s="124">
         <f t="shared" si="4"/>
-        <v>30.855374101930487</v>
+        <v>30.869570717406869</v>
       </c>
       <c r="C68" s="124">
         <f t="shared" si="4"/>
-        <v>32.459616703183478</v>
+        <v>32.47457877214601</v>
       </c>
       <c r="D68" s="124">
         <f t="shared" si="4"/>
-        <v>36.072355962332246</v>
+        <v>36.089041825350769</v>
       </c>
       <c r="E68" s="124">
         <f t="shared" si="4"/>
-        <v>40.313124814524045</v>
+        <v>40.331834131663079</v>
       </c>
       <c r="F68" s="124">
         <f t="shared" si="4"/>
-        <v>48.132674820956154</v>
+        <v>48.155115183392056</v>
       </c>
       <c r="H68" s="120"/>
     </row>
@@ -16809,23 +16809,23 @@
       </c>
       <c r="B69" s="124">
         <f t="shared" si="4"/>
-        <v>30.855374101930487</v>
+        <v>30.869570717406877</v>
       </c>
       <c r="C69" s="124">
         <f t="shared" si="4"/>
-        <v>33.073352518535465</v>
+        <v>33.088607427383344</v>
       </c>
       <c r="D69" s="124">
         <f t="shared" si="4"/>
-        <v>38.289405783342573</v>
+        <v>38.307149496659498</v>
       </c>
       <c r="E69" s="124">
         <f t="shared" si="4"/>
-        <v>44.787409948084012</v>
+        <v>44.808254140054814</v>
       </c>
       <c r="F69" s="124">
         <f t="shared" si="4"/>
-        <v>57.761242919835908</v>
+        <v>57.788277488292792</v>
       </c>
       <c r="H69" s="120"/>
     </row>
@@ -16836,23 +16836,23 @@
       </c>
       <c r="B70" s="124">
         <f t="shared" si="4"/>
-        <v>30.855374101930487</v>
+        <v>30.869570717406877</v>
       </c>
       <c r="C70" s="124">
         <f t="shared" si="4"/>
-        <v>33.6420077983068</v>
+        <v>33.65753403716797</v>
       </c>
       <c r="D70" s="124">
         <f t="shared" si="4"/>
-        <v>40.459702467544105</v>
+        <v>40.478481723217008</v>
       </c>
       <c r="E70" s="124">
         <f t="shared" si="4"/>
-        <v>49.437072016595536</v>
+        <v>49.460134763314159</v>
       </c>
       <c r="F70" s="124">
         <f t="shared" si="4"/>
-        <v>68.789987662690478</v>
+        <v>68.822284521965813</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="13.15">
@@ -16862,23 +16862,23 @@
       </c>
       <c r="B71" s="124">
         <f t="shared" si="4"/>
-        <v>30.855374101930487</v>
+        <v>30.869570717406869</v>
       </c>
       <c r="C71" s="124">
         <f t="shared" si="4"/>
-        <v>34.141445746654746</v>
+        <v>34.157210288948555</v>
       </c>
       <c r="D71" s="124">
         <f t="shared" si="4"/>
-        <v>42.476930967968869</v>
+        <v>42.496672730551118</v>
       </c>
       <c r="E71" s="124">
         <f t="shared" si="4"/>
-        <v>54.038732300871835</v>
+        <v>54.063990698612258</v>
       </c>
       <c r="F71" s="124">
         <f t="shared" si="4"/>
-        <v>80.895485754726991</v>
+        <v>80.93355867038477</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="13.15">
@@ -16913,7 +16913,7 @@
       </c>
       <c r="E74" s="135">
         <f>INDEX(B$65:F$71, MATCH(D74, A$65:A$71, 0), MATCH(C74, B$64:F$64, 0))</f>
-        <v>40.371939604409576</v>
+        <v>40.390676984627049</v>
       </c>
       <c r="F74" s="142">
         <f>Scenarios!C58</f>
@@ -16935,7 +16935,7 @@
       </c>
       <c r="E75" s="135">
         <f>INDEX(B$65:F$71, MATCH(D75, A$65:A$71, 0), MATCH(C75, B$64:F$64, 0))</f>
-        <v>33.482739653510706</v>
+        <v>33.498189898655845</v>
       </c>
       <c r="F75" s="142">
         <f>Scenarios!C40*(1-F$74-F$78)</f>
@@ -16958,7 +16958,7 @@
       </c>
       <c r="E76" s="135">
         <f>INDEX(B$65:F$71, MATCH(D76, A$65:A$71, 0), MATCH(C76, B$64:F$64, 0))</f>
-        <v>32.408998499180548</v>
+        <v>32.423936416010044</v>
       </c>
       <c r="F76" s="142">
         <f>Scenarios!C28*(1-F$74-F$78)</f>
@@ -16981,7 +16981,7 @@
       </c>
       <c r="E77" s="135">
         <f>INDEX(B$65:F$71, MATCH(D77, A$65:A$71, 0), MATCH(C77, B$64:F$64, 0))</f>
-        <v>31.365867546764274</v>
+        <v>31.380307740728544</v>
       </c>
       <c r="F77" s="142">
         <f>Scenarios!C34*(1-F$74-F$78)</f>
@@ -17004,7 +17004,7 @@
       </c>
       <c r="E78" s="135">
         <f>INDEX(B$65:F$71, MATCH(D78, A$65:A$71, 0), MATCH(C78, B$64:F$64, 0))</f>
-        <v>30.855374101930487</v>
+        <v>30.869570717406869</v>
       </c>
       <c r="F78" s="142">
         <f>Scenarios!C52</f>
@@ -17186,7 +17186,7 @@
       </c>
       <c r="C4" s="114">
         <f>Normalized_FCF!C91*(1-dividend_tax_rate)</f>
-        <v>3767405.655286673</v>
+        <v>3769203.2473655003</v>
       </c>
       <c r="D4" t="str">
         <f>Market_currency</f>
@@ -17218,7 +17218,7 @@
       </c>
       <c r="C6" s="319">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
-        <v>50232075.40382231</v>
+        <v>50256043.298206672</v>
       </c>
       <c r="D6" t="str">
         <f>Reporting_currency</f>
@@ -17234,7 +17234,7 @@
       </c>
       <c r="C7" s="111">
         <f>(C6*scaling_factor)/Common_Shares*Exchange_Rate</f>
-        <v>176.2377048712205</v>
+        <v>176.40592624772381</v>
       </c>
       <c r="D7" t="str">
         <f>Market_currency</f>
@@ -17287,7 +17287,7 @@
       </c>
       <c r="C13" s="140">
         <f>F47/Common_Shares*scaling_factor</f>
-        <v>20.372227153415224</v>
+        <v>20.381947623550332</v>
       </c>
       <c r="D13" t="str">
         <f>Market_currency</f>
@@ -17322,7 +17322,7 @@
       </c>
       <c r="C16" s="123">
         <f>C4*(1+D16)</f>
-        <v>3856891.4075477761</v>
+        <v>3858731.6971469</v>
       </c>
       <c r="D16" s="138">
         <f>IF($C$12&lt;B16,0,DDM!$C$11)</f>
@@ -17334,7 +17334,7 @@
       </c>
       <c r="F16" s="125">
         <f t="shared" ref="F16:F46" si="1">C16*E16</f>
-        <v>3587805.9605095591</v>
+        <v>3589517.8578110696</v>
       </c>
       <c r="H16" s="120"/>
     </row>
@@ -17344,7 +17344,7 @@
       </c>
       <c r="C17" s="123">
         <f t="shared" ref="C17:C45" si="2">IF(ROW()-ROW($C$16)&lt;$C$12, $C$16*(1+D17)^(ROW()-ROW($C$16)), 0)</f>
-        <v>3948502.6808146937</v>
+        <v>3950386.6821120586</v>
       </c>
       <c r="D17" s="138">
         <f>IF($C$12&lt;B17,0,DDM!$C$11)</f>
@@ -17356,7 +17356,7 @@
       </c>
       <c r="F17" s="125">
         <f t="shared" si="1"/>
-        <v>3416768.1391581991</v>
+        <v>3418398.4269222794</v>
       </c>
       <c r="H17" s="120"/>
     </row>
@@ -17366,7 +17366,7 @@
       </c>
       <c r="C18" s="123">
         <f t="shared" si="2"/>
-        <v>4042289.9617786808</v>
+        <v>4044218.7130416138</v>
       </c>
       <c r="D18" s="138">
         <f>IF($C$12&lt;B18,0,DDM!$C$11)</f>
@@ -17378,7 +17378,7 @@
       </c>
       <c r="F18" s="125">
         <f t="shared" si="1"/>
-        <v>3253884.0297563183</v>
+        <v>3255436.5984713715</v>
       </c>
       <c r="H18" s="120"/>
     </row>
@@ -17388,7 +17388,7 @@
       </c>
       <c r="C19" s="123">
         <f t="shared" si="2"/>
-        <v>4138304.9363221498</v>
+        <v>4140279.5004795468</v>
       </c>
       <c r="D19" s="138">
         <f>IF($C$12&lt;B19,0,DDM!$C$11)</f>
@@ -17400,7 +17400,7 @@
       </c>
       <c r="F19" s="125">
         <f t="shared" si="1"/>
-        <v>3098764.9286942133</v>
+        <v>3100243.4833813496</v>
       </c>
       <c r="H19" s="120"/>
     </row>
@@ -17410,7 +17410,7 @@
       </c>
       <c r="C20" s="123">
         <f t="shared" si="2"/>
-        <v>4236600.5180026004</v>
+        <v>4238621.9832307026</v>
       </c>
       <c r="D20" s="138">
         <f>IF($C$12&lt;B20,0,DDM!$C$11)</f>
@@ -17422,7 +17422,7 @@
       </c>
       <c r="F20" s="125">
         <f t="shared" si="1"/>
-        <v>2951040.6626336849</v>
+        <v>2952448.731688315</v>
       </c>
       <c r="H20" s="120"/>
     </row>
@@ -17982,7 +17982,7 @@
       </c>
       <c r="C46" s="123">
         <f>C$16*(1+F4)^$C$12/Equity_Cost</f>
-        <v>51425218.767303683</v>
+        <v>51449755.961958669</v>
       </c>
       <c r="D46" s="139">
         <f>Terminal_Growth</f>
@@ -17994,7 +17994,7 @@
       </c>
       <c r="F46" s="125">
         <f t="shared" si="1"/>
-        <v>35820680.052858584</v>
+        <v>35837771.647609167</v>
       </c>
       <c r="H46" s="120"/>
     </row>
@@ -18005,7 +18005,7 @@
       </c>
       <c r="F47" s="137">
         <f>SUM(F16:F46)</f>
-        <v>52128943.773610562</v>
+        <v>52153816.745883554</v>
       </c>
       <c r="H47" s="120"/>
     </row>
@@ -18026,7 +18026,7 @@
     <row r="50" spans="1:8" ht="13.15">
       <c r="A50" s="133">
         <f>F47</f>
-        <v>52128943.773610562</v>
+        <v>52153816.745883554</v>
       </c>
       <c r="B50" s="131">
         <f>C73</f>
@@ -18056,19 +18056,19 @@
       </c>
       <c r="B51" s="123">
         <f t="dataTable" ref="B51:F56" dt2D="1" dtr="1" r1="C11" r2="C12"/>
-        <v>50232075.40382231</v>
+        <v>50256043.29820668</v>
       </c>
       <c r="C51" s="123">
-        <v>51022842.173981324</v>
+        <v>51047187.377371483</v>
       </c>
       <c r="D51" s="123">
-        <v>52638677.40642716</v>
+        <v>52663793.594648868</v>
       </c>
       <c r="E51" s="123">
-        <v>54301928.586612023</v>
+        <v>54327838.383863449</v>
       </c>
       <c r="F51" s="123">
-        <v>56890258.860544249</v>
+        <v>56917403.662046216</v>
       </c>
       <c r="H51" s="120"/>
     </row>
@@ -18077,19 +18077,19 @@
         <v>10</v>
       </c>
       <c r="B52" s="123">
-        <v>50232075.403822318</v>
+        <v>50256043.298206687</v>
       </c>
       <c r="C52" s="123">
-        <v>51781014.91735658</v>
+        <v>51805721.877733529</v>
       </c>
       <c r="D52" s="123">
-        <v>55106929.061902717</v>
+        <v>55133222.959675893</v>
       </c>
       <c r="E52" s="123">
-        <v>58767248.903613091</v>
+        <v>58795289.298194811</v>
       </c>
       <c r="F52" s="123">
-        <v>64973466.976150982</v>
+        <v>65004468.625629947</v>
       </c>
       <c r="H52" s="120"/>
     </row>
@@ -18098,19 +18098,19 @@
         <v>15</v>
       </c>
       <c r="B53" s="123">
-        <v>50232075.403822318</v>
+        <v>50256043.29820668</v>
       </c>
       <c r="C53" s="123">
-        <v>52717086.236345999</v>
+        <v>52742239.836809561</v>
       </c>
       <c r="D53" s="123">
-        <v>58313307.273648046</v>
+        <v>58341131.073057123</v>
       </c>
       <c r="E53" s="123">
-        <v>64882361.435215972</v>
+        <v>64913319.614303447</v>
       </c>
       <c r="F53" s="123">
-        <v>76995034.703128889</v>
+        <v>77031772.362185359</v>
       </c>
       <c r="H53" s="120"/>
     </row>
@@ -18119,19 +18119,19 @@
         <v>20</v>
       </c>
       <c r="B54" s="123">
-        <v>50232075.403822325</v>
+        <v>50256043.298206672</v>
       </c>
       <c r="C54" s="123">
-        <v>53667777.951094262</v>
+        <v>53693385.167667225</v>
       </c>
       <c r="D54" s="123">
-        <v>61747571.403744191</v>
+        <v>61777033.839010872</v>
       </c>
       <c r="E54" s="123">
-        <v>71813137.99981527</v>
+        <v>71847403.151974574</v>
       </c>
       <c r="F54" s="123">
-        <v>91909921.023140371</v>
+        <v>91953775.219134629</v>
       </c>
       <c r="H54" s="120"/>
     </row>
@@ -18140,19 +18140,19 @@
         <v>25</v>
       </c>
       <c r="B55" s="123">
-        <v>50232075.403822333</v>
+        <v>50256043.298206665</v>
       </c>
       <c r="C55" s="123">
-        <v>54548638.819082573</v>
+        <v>54574666.332449585</v>
       </c>
       <c r="D55" s="123">
-        <v>65109413.787071124</v>
+        <v>65140480.302649699</v>
       </c>
       <c r="E55" s="123">
-        <v>79015577.70488286</v>
+        <v>79053279.452340543</v>
       </c>
       <c r="F55" s="123">
-        <v>108993715.0414055</v>
+        <v>109045720.65394828</v>
       </c>
       <c r="H55" s="120"/>
     </row>
@@ -18161,19 +18161,19 @@
         <v>30</v>
       </c>
       <c r="B56" s="123">
-        <v>50232075.403822333</v>
+        <v>50256043.298206665</v>
       </c>
       <c r="C56" s="123">
-        <v>55322280.356122322</v>
+        <v>55348677.007306211</v>
       </c>
       <c r="D56" s="123">
-        <v>68234149.82843776</v>
+        <v>68266707.290643886</v>
       </c>
       <c r="E56" s="123">
-        <v>86143661.477928832</v>
+        <v>86184764.342255801</v>
       </c>
       <c r="F56" s="123">
-        <v>127745426.20299007</v>
+        <v>127806379.06744374</v>
       </c>
       <c r="H56" s="120"/>
     </row>
@@ -18223,23 +18223,23 @@
       </c>
       <c r="B60" s="124">
         <f>C7</f>
-        <v>176.2377048712205</v>
+        <v>176.40592624772381</v>
       </c>
       <c r="C60" s="124">
         <f>C7</f>
-        <v>176.2377048712205</v>
+        <v>176.40592624772381</v>
       </c>
       <c r="D60" s="124">
         <f>C7</f>
-        <v>176.2377048712205</v>
+        <v>176.40592624772381</v>
       </c>
       <c r="E60" s="141">
         <f>C7</f>
-        <v>176.2377048712205</v>
+        <v>176.40592624772381</v>
       </c>
       <c r="F60" s="124">
         <f>C7</f>
-        <v>176.2377048712205</v>
+        <v>176.40592624772381</v>
       </c>
       <c r="H60" s="120"/>
     </row>
@@ -18250,23 +18250,23 @@
       </c>
       <c r="B61" s="124">
         <f t="shared" ref="B61:F66" si="4">B51/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>176.23770487122047</v>
+        <v>176.40592624772381</v>
       </c>
       <c r="C61" s="124">
         <f t="shared" si="4"/>
-        <v>179.01208597215839</v>
+        <v>179.18295553457676</v>
       </c>
       <c r="D61" s="124">
         <f t="shared" si="4"/>
-        <v>184.68119461493291</v>
+        <v>184.85747542155767</v>
       </c>
       <c r="E61" s="124">
         <f t="shared" si="4"/>
-        <v>190.51666066453643</v>
+        <v>190.69851150586021</v>
       </c>
       <c r="F61" s="124">
         <f t="shared" si="4"/>
-        <v>199.5977385069184</v>
+        <v>199.78825736520199</v>
       </c>
       <c r="H61" s="120"/>
     </row>
@@ -18277,23 +18277,23 @@
       </c>
       <c r="B62" s="124">
         <f t="shared" si="4"/>
-        <v>176.2377048712205</v>
+        <v>176.40592624772384</v>
       </c>
       <c r="C62" s="124">
         <f t="shared" si="4"/>
-        <v>181.67211192398688</v>
+        <v>181.8455205187166</v>
       </c>
       <c r="D62" s="124">
         <f t="shared" si="4"/>
-        <v>193.34098028591279</v>
+        <v>193.52552698017419</v>
       </c>
       <c r="E62" s="124">
         <f t="shared" si="4"/>
-        <v>206.18310083959668</v>
+        <v>206.37990551916459</v>
       </c>
       <c r="F62" s="124">
         <f t="shared" si="4"/>
-        <v>227.95742770627319</v>
+        <v>228.17501628813156</v>
       </c>
       <c r="H62" s="120"/>
     </row>
@@ -18304,23 +18304,23 @@
       </c>
       <c r="B63" s="124">
         <f t="shared" si="4"/>
-        <v>176.2377048712205</v>
+        <v>176.40592624772381</v>
       </c>
       <c r="C63" s="124">
         <f t="shared" si="4"/>
-        <v>184.95628960385071</v>
+        <v>185.13283299252473</v>
       </c>
       <c r="D63" s="124">
         <f t="shared" si="4"/>
-        <v>204.59046047251258</v>
+        <v>204.78574495437348</v>
       </c>
       <c r="E63" s="124">
         <f t="shared" si="4"/>
-        <v>227.6377866939049</v>
+        <v>227.85507017390591</v>
       </c>
       <c r="F63" s="124">
         <f t="shared" si="4"/>
-        <v>270.13473151314133</v>
+        <v>270.39257892672225</v>
       </c>
       <c r="H63" s="120"/>
     </row>
@@ -18331,23 +18331,23 @@
       </c>
       <c r="B64" s="124">
         <f t="shared" si="4"/>
-        <v>176.23770487122053</v>
+        <v>176.40592624772378</v>
       </c>
       <c r="C64" s="124">
         <f t="shared" si="4"/>
-        <v>188.29176249642745</v>
+        <v>188.47148964105025</v>
       </c>
       <c r="D64" s="124">
         <f t="shared" si="4"/>
-        <v>216.63947145491861</v>
+        <v>216.8462568878073</v>
       </c>
       <c r="E64" s="124">
         <f t="shared" si="4"/>
-        <v>251.95420493664545</v>
+        <v>252.19469878103143</v>
       </c>
       <c r="F64" s="124">
         <f t="shared" si="4"/>
-        <v>322.46315538021435</v>
+        <v>322.77095101287586</v>
       </c>
       <c r="H64" s="120"/>
     </row>
@@ -18358,23 +18358,23 @@
       </c>
       <c r="B65" s="124">
         <f t="shared" si="4"/>
-        <v>176.23770487122056</v>
+        <v>176.40592624772376</v>
       </c>
       <c r="C65" s="124">
         <f t="shared" si="4"/>
-        <v>191.3822359924383</v>
+        <v>191.56491303762817</v>
       </c>
       <c r="D65" s="124">
         <f t="shared" si="4"/>
-        <v>228.43439294707832</v>
+        <v>228.65243679899041</v>
       </c>
       <c r="E65" s="124">
         <f t="shared" si="4"/>
-        <v>277.22374502413055</v>
+        <v>277.48835900115347</v>
       </c>
       <c r="F65" s="124">
         <f t="shared" si="4"/>
-        <v>382.40112577198971</v>
+        <v>382.76613304328151</v>
       </c>
     </row>
     <row r="66" spans="1:8" ht="13.15">
@@ -18384,23 +18384,23 @@
       </c>
       <c r="B66" s="124">
         <f t="shared" si="4"/>
-        <v>176.23770487122056</v>
+        <v>176.40592624772376</v>
       </c>
       <c r="C66" s="124">
         <f t="shared" si="4"/>
-        <v>194.09653373516213</v>
+        <v>194.28180161585377</v>
       </c>
       <c r="D66" s="124">
         <f t="shared" si="4"/>
-        <v>239.39743406834833</v>
+        <v>239.62594229772961</v>
       </c>
       <c r="E66" s="124">
         <f t="shared" si="4"/>
-        <v>302.23240959138872</v>
+        <v>302.52089469168283</v>
       </c>
       <c r="F66" s="124">
         <f t="shared" si="4"/>
-        <v>448.19093260275116</v>
+        <v>448.61873717313978</v>
       </c>
     </row>
     <row r="68" spans="1:8" ht="13.15">
@@ -18435,7 +18435,7 @@
       </c>
       <c r="E69" s="135">
         <f>INDEX(B$60:F$66, MATCH(D69, A$60:A$66, 0), MATCH(C69, B$59:F$59, 0))</f>
-        <v>227.95742770627319</v>
+        <v>228.17501628813156</v>
       </c>
       <c r="F69" s="142">
         <f>Scenarios!C58</f>
@@ -18457,7 +18457,7 @@
       </c>
       <c r="E70" s="135">
         <f>INDEX(B$60:F$66, MATCH(D70, A$60:A$66, 0), MATCH(C70, B$59:F$59, 0))</f>
-        <v>190.51666066453643</v>
+        <v>190.69851150586021</v>
       </c>
       <c r="F70" s="142">
         <f>Scenarios!C40*(1-F$69-F$73)</f>
@@ -18480,7 +18480,7 @@
       </c>
       <c r="E71" s="135">
         <f>INDEX(B$60:F$66, MATCH(D71, A$60:A$66, 0), MATCH(C71, B$59:F$59, 0))</f>
-        <v>184.68119461493291</v>
+        <v>184.85747542155767</v>
       </c>
       <c r="F71" s="142">
         <f>Scenarios!C28*(1-F$69-F$73)</f>
@@ -18503,7 +18503,7 @@
       </c>
       <c r="E72" s="135">
         <f>INDEX(B$60:F$66, MATCH(D72, A$60:A$66, 0), MATCH(C72, B$59:F$59, 0))</f>
-        <v>179.01208597215839</v>
+        <v>179.18295553457676</v>
       </c>
       <c r="F72" s="142">
         <f>Scenarios!C34*(1-F$69-F$73)</f>
@@ -18526,7 +18526,7 @@
       </c>
       <c r="E73" s="135">
         <f>INDEX(B$60:F$66, MATCH(D73, A$60:A$66, 0), MATCH(C73, B$59:F$59, 0))</f>
-        <v>176.2377048712205</v>
+        <v>176.40592624772384</v>
       </c>
       <c r="F73" s="142">
         <f>Scenarios!C52</f>
@@ -18626,7 +18626,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-50.15</v>
+        <v>-50.65</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18646,7 +18646,7 @@
       </c>
       <c r="I4" s="124">
         <f t="shared" ref="I4:I13" si="0">IF(ROW()-3 &lt; $C$76, $C$77, IF(ROW()-3 = $C$76, $C$77 + $C$60, ""))</f>
-        <v>1.47231918072</v>
+        <v>1.4730216878400002</v>
       </c>
     </row>
     <row r="5" spans="2:9">
@@ -18655,7 +18655,7 @@
       </c>
       <c r="I5" s="124">
         <f t="shared" si="0"/>
-        <v>1.47231918072</v>
+        <v>1.4730216878400002</v>
       </c>
     </row>
     <row r="6" spans="2:9" ht="13.15">
@@ -18675,7 +18675,7 @@
       </c>
       <c r="I6" s="124">
         <f t="shared" si="0"/>
-        <v>34.20729335164399</v>
+        <v>34.223089312676315</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1">
@@ -18866,7 +18866,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>50.15</v>
+        <v>50.65</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -18881,7 +18881,7 @@
       </c>
       <c r="C22" s="160">
         <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
-        <v>30.855374101930472</v>
+        <v>30.869570717406862</v>
       </c>
       <c r="D22" t="str">
         <f>Market_currency</f>
@@ -18928,7 +18928,7 @@
       </c>
       <c r="C27" s="160">
         <f>IF(valuation_method="DCF",DCF!E76,DDM!E71)</f>
-        <v>32.408998499180548</v>
+        <v>32.423936416010044</v>
       </c>
       <c r="D27" s="160" t="str">
         <f>Market_currency</f>
@@ -18986,7 +18986,7 @@
       </c>
       <c r="C33" s="160">
         <f>IF(valuation_method="DCF",DCF!E77,DDM!E72)</f>
-        <v>31.365867546764274</v>
+        <v>31.380307740728544</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
@@ -19044,7 +19044,7 @@
       </c>
       <c r="C39" s="160">
         <f>IF(valuation_method="DCF",DCF!E75,DDM!E70)</f>
-        <v>33.482739653510706</v>
+        <v>33.498189898655845</v>
       </c>
       <c r="D39" t="str">
         <f>Market_currency</f>
@@ -19071,7 +19071,7 @@
       </c>
       <c r="C42" s="154">
         <f>C27*C28+C33*C34+C39*C40</f>
-        <v>32.415120539563326</v>
+        <v>32.430061377482907</v>
       </c>
       <c r="D42" t="str">
         <f>Market_currency</f>
@@ -19145,7 +19145,7 @@
       </c>
       <c r="C51" s="160">
         <f>IF(valuation_method="DCF",DCF!E78,DDM!E73)</f>
-        <v>30.855374101930487</v>
+        <v>30.869570717406869</v>
       </c>
       <c r="D51" t="str">
         <f>Market_currency</f>
@@ -19203,7 +19203,7 @@
       </c>
       <c r="C57" s="160">
         <f>IF(valuation_method="DCF",DCF!E74,DDM!E69)</f>
-        <v>40.371939604409576</v>
+        <v>40.390676984627049</v>
       </c>
       <c r="D57" t="str">
         <f>Market_currency</f>
@@ -19229,7 +19229,7 @@
       </c>
       <c r="C60" s="154">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
-        <v>32.734974170923991</v>
+        <v>32.750067624836312</v>
       </c>
       <c r="D60" t="str">
         <f>Market_currency</f>
@@ -19291,7 +19291,7 @@
       </c>
       <c r="C66" s="160">
         <f>IF(valuation_method="DCF",DCF!C18,DDM!C13)</f>
-        <v>32.079930956152829</v>
+        <v>32.094711860634071</v>
       </c>
       <c r="D66" s="160" t="str">
         <f>Market_currency</f>
@@ -19354,7 +19354,7 @@
       </c>
       <c r="F72" s="291">
         <f>BS!D89/C60</f>
-        <v>-4.8047348991141402E-2</v>
+        <v>-4.8064175866584596E-2</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="13.9">
@@ -19387,7 +19387,7 @@
       </c>
       <c r="C77" s="173">
         <f>Normalized_FCF!C90*(1-dividend_tax_rate)</f>
-        <v>1.47231918072</v>
+        <v>1.4730216878400002</v>
       </c>
       <c r="D77" t="str">
         <f>Market_currency</f>
@@ -19414,7 +19414,7 @@
       </c>
       <c r="C81" s="116">
         <f>PV(C80, C76, -C77, 0)</f>
-        <v>2.440014683327854</v>
+        <v>2.4411789197993943</v>
       </c>
       <c r="D81" s="116"/>
       <c r="E81" s="100"/>
@@ -19426,7 +19426,7 @@
       </c>
       <c r="C82" s="116">
         <f>C60/(1+C80)^C76</f>
-        <v>12.803398882405475</v>
+        <v>12.809302278264093</v>
       </c>
       <c r="D82" s="116"/>
     </row>
@@ -19436,7 +19436,7 @@
       </c>
       <c r="C83" s="111">
         <f>C81+C82</f>
-        <v>15.243413565733329</v>
+        <v>15.250481198063488</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -19447,7 +19447,7 @@
       </c>
       <c r="F83" s="291">
         <f>(1-C83/C60)</f>
-        <v>0.53433861025395579</v>
+        <v>0.53433741350512065</v>
       </c>
     </row>
     <row r="84" spans="2:8">
@@ -19464,7 +19464,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>50.15</v>
+        <v>50.65</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19477,7 +19477,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>-9.8595701784031209E-2</v>
+        <v>-0.10153176218238202</v>
       </c>
     </row>
     <row r="88" spans="2:8">
@@ -19503,7 +19503,7 @@
       </c>
       <c r="C91" s="116">
         <f>PV(C90, C76, -C77, 0)</f>
-        <v>3.018844461140437</v>
+        <v>3.0202848823180561</v>
       </c>
       <c r="D91" s="116"/>
       <c r="E91" s="100"/>
@@ -19515,7 +19515,7 @@
       </c>
       <c r="C92" s="116">
         <f>C60/(1+C90)^C76</f>
-        <v>18.143125735710871</v>
+        <v>18.151491174787974</v>
       </c>
       <c r="D92" s="116"/>
     </row>
@@ -19525,7 +19525,7 @@
       </c>
       <c r="C93" s="111">
         <f>C91+C92</f>
-        <v>21.161970196851307</v>
+        <v>21.17177605710603</v>
       </c>
       <c r="D93" t="str">
         <f>Market_currency</f>
@@ -19536,7 +19536,7 @@
       </c>
       <c r="F93" s="291">
         <f>(1-C93/C60)</f>
-        <v>0.353536371027661</v>
+        <v>0.35353489038141039</v>
       </c>
     </row>
     <row r="95" spans="2:8" ht="13.15">
@@ -19563,7 +19563,7 @@
       </c>
       <c r="C97" s="116">
         <f>PV(C96, C76, -C77, 0)</f>
-        <v>3.8288039267695555</v>
+        <v>3.8306308146175594</v>
       </c>
       <c r="D97" s="116"/>
       <c r="G97" s="2"/>
@@ -19575,7 +19575,7 @@
       </c>
       <c r="C98" s="116">
         <f>C60/(1+C96)^C76</f>
-        <v>26.350363451509121</v>
+        <v>26.362513086766249</v>
       </c>
       <c r="D98" s="116"/>
       <c r="G98" s="2"/>
@@ -19587,7 +19587,7 @@
       </c>
       <c r="C99" s="111">
         <f>C97+C98</f>
-        <v>30.179167378278677</v>
+        <v>30.193143901383809</v>
       </c>
       <c r="D99" t="s">
         <v>393</v>
@@ -19597,7 +19597,7 @@
       </c>
       <c r="F99" s="291">
         <f>(1-C99/C60)</f>
-        <v>7.807572351517067E-2</v>
+        <v>7.8073845609816006E-2</v>
       </c>
     </row>
     <row r="100" spans="2:8">
@@ -19623,7 +19623,7 @@
       </c>
       <c r="C103" s="116">
         <f>PV(C102, C76, -C77, 0)</f>
-        <v>3.5521218577845026</v>
+        <v>3.5538167286582092</v>
       </c>
       <c r="D103" s="116"/>
     </row>
@@ -19633,7 +19633,7 @@
       </c>
       <c r="C104" s="116">
         <f>C60/(1+C102)^C76</f>
-        <v>23.46313295208089</v>
+        <v>23.473951342039037</v>
       </c>
       <c r="D104" s="116"/>
     </row>
@@ -19643,7 +19643,7 @@
       </c>
       <c r="C105" s="111">
         <f>C103+C104</f>
-        <v>27.015254809865393</v>
+        <v>27.027768070697245</v>
       </c>
       <c r="D105" t="s">
         <v>393</v>
@@ -19653,7 +19653,7 @@
       </c>
       <c r="F105" s="291">
         <f>(1-C105/C66)</f>
-        <v>0.15787677826395219</v>
+        <v>0.15787472440753425</v>
       </c>
     </row>
     <row r="106" spans="2:8">

--- a/financial_models/opportunities/1913.HK_Valuation.xlsx
+++ b/financial_models/opportunities/1913.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FE3584E-DEAA-4D24-A51E-DC3E56DCA077}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CEE1C5E-2914-451F-82DC-4087CA2A7F9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2205" yWindow="2205" windowWidth="12690" windowHeight="7642" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -3896,29 +3896,29 @@
     <xf numFmtId="10" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4336,7 +4336,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>50.65</v>
+        <v>47.6</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4357,7 +4357,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>129604.4356</v>
+        <v>121800.0224</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4384,7 +4384,7 @@
         <v>1</v>
       </c>
       <c r="C16" s="50">
-        <v>8.9818395600000009</v>
+        <v>9.0663799000000012</v>
       </c>
       <c r="D16" s="50"/>
       <c r="E16" s="5"/>
@@ -4394,13 +4394,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="358" t="s">
+      <c r="B18" s="360" t="s">
         <v>356</v>
       </c>
-      <c r="C18" s="358"/>
-      <c r="D18" s="358"/>
-      <c r="E18" s="358"/>
-      <c r="F18" s="358"/>
+      <c r="C18" s="360"/>
+      <c r="D18" s="360"/>
+      <c r="E18" s="360"/>
+      <c r="F18" s="360"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4476,14 +4476,14 @@
       </c>
       <c r="C26" s="304">
         <f>C132</f>
-        <v>32.750067624836312</v>
+        <v>33.047848014072677</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>396</v>
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>-0.10153176218238202</v>
+        <v>-7.9180969336304363E-2</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4515,7 +4515,7 @@
       </c>
       <c r="C29" s="310">
         <f>C149</f>
-        <v>15.250481198063488</v>
+        <v>15.389927198904168</v>
       </c>
       <c r="D29" s="310" t="str">
         <f>D149</f>
@@ -4534,7 +4534,7 @@
       </c>
       <c r="C30" s="311">
         <f>C157</f>
-        <v>21.17177605710603</v>
+        <v>21.365246731530732</v>
       </c>
       <c r="D30" s="311" t="str">
         <f>D157</f>
@@ -4553,7 +4553,7 @@
       </c>
       <c r="C31" s="311">
         <f>C165</f>
-        <v>30.193143901383809</v>
+        <v>30.46890066324962</v>
       </c>
       <c r="D31" s="311" t="str">
         <f>D165</f>
@@ -4572,7 +4572,7 @@
       </c>
       <c r="C32" s="311">
         <f>C173</f>
-        <v>27.027768070697245</v>
+        <v>27.274655074840922</v>
       </c>
       <c r="D32" s="311" t="str">
         <f>D173</f>
@@ -4600,22 +4600,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="358" t="s">
+      <c r="B36" s="360" t="s">
         <v>357</v>
       </c>
-      <c r="C36" s="358"/>
-      <c r="D36" s="358"/>
-      <c r="E36" s="358"/>
-      <c r="F36" s="358"/>
+      <c r="C36" s="360"/>
+      <c r="D36" s="360"/>
+      <c r="E36" s="360"/>
+      <c r="F36" s="360"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="360" t="s">
+      <c r="B37" s="363" t="s">
         <v>336</v>
       </c>
-      <c r="C37" s="360"/>
-      <c r="D37" s="360"/>
-      <c r="E37" s="360"/>
-      <c r="F37" s="360"/>
+      <c r="C37" s="363"/>
+      <c r="D37" s="363"/>
+      <c r="E37" s="363"/>
+      <c r="F37" s="363"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4627,13 +4627,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="359" t="s">
+      <c r="B40" s="361" t="s">
         <v>230</v>
       </c>
-      <c r="C40" s="359"/>
-      <c r="D40" s="359"/>
-      <c r="E40" s="359"/>
-      <c r="F40" s="359"/>
+      <c r="C40" s="361"/>
+      <c r="D40" s="361"/>
+      <c r="E40" s="361"/>
+      <c r="F40" s="361"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4653,13 +4653,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="359" t="s">
+      <c r="B43" s="361" t="s">
         <v>232</v>
       </c>
-      <c r="C43" s="359"/>
-      <c r="D43" s="359"/>
-      <c r="E43" s="359"/>
-      <c r="F43" s="359"/>
+      <c r="C43" s="361"/>
+      <c r="D43" s="361"/>
+      <c r="E43" s="361"/>
+      <c r="F43" s="361"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4688,13 +4688,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="359" t="s">
+      <c r="B47" s="361" t="s">
         <v>235</v>
       </c>
-      <c r="C47" s="359"/>
-      <c r="D47" s="359"/>
-      <c r="E47" s="359"/>
-      <c r="F47" s="359"/>
+      <c r="C47" s="361"/>
+      <c r="D47" s="361"/>
+      <c r="E47" s="361"/>
+      <c r="F47" s="361"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4710,13 +4710,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="359" t="s">
+      <c r="B50" s="361" t="s">
         <v>239</v>
       </c>
-      <c r="C50" s="359"/>
-      <c r="D50" s="359"/>
-      <c r="E50" s="359"/>
-      <c r="F50" s="359"/>
+      <c r="C50" s="361"/>
+      <c r="D50" s="361"/>
+      <c r="E50" s="361"/>
+      <c r="F50" s="361"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4780,13 +4780,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="359" t="s">
+      <c r="B58" s="361" t="s">
         <v>240</v>
       </c>
-      <c r="C58" s="359"/>
-      <c r="D58" s="359"/>
-      <c r="E58" s="359"/>
-      <c r="F58" s="359"/>
+      <c r="C58" s="361"/>
+      <c r="D58" s="361"/>
+      <c r="E58" s="361"/>
+      <c r="F58" s="361"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4802,7 +4802,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="359" t="s">
+      <c r="B61" s="361" t="s">
         <v>335</v>
       </c>
       <c r="C61" s="362"/>
@@ -4824,22 +4824,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="358" t="s">
+      <c r="B64" s="360" t="s">
         <v>340</v>
       </c>
-      <c r="C64" s="358"/>
-      <c r="D64" s="358"/>
-      <c r="E64" s="358"/>
-      <c r="F64" s="358"/>
+      <c r="C64" s="360"/>
+      <c r="D64" s="360"/>
+      <c r="E64" s="360"/>
+      <c r="F64" s="360"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="358" t="s">
+      <c r="B65" s="360" t="s">
         <v>358</v>
       </c>
-      <c r="C65" s="358"/>
-      <c r="D65" s="358"/>
-      <c r="E65" s="358"/>
-      <c r="F65" s="358"/>
+      <c r="C65" s="360"/>
+      <c r="D65" s="360"/>
+      <c r="E65" s="360"/>
+      <c r="F65" s="360"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4873,7 +4873,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>4.8040980840132586E-2</v>
+        <v>5.1600389812170917E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4883,14 +4883,14 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>2.9082363037314912E-2</v>
+        <v>3.1237107218487398E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>444</v>
       </c>
       <c r="F70" s="315">
         <f>Normalized_FCF!C92</f>
-        <v>5.4372977874053738</v>
+        <v>5.4884756113419773</v>
       </c>
     </row>
     <row r="72" spans="1:6">
@@ -4974,22 +4974,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.6" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="358" t="s">
+      <c r="B80" s="360" t="s">
         <v>359</v>
       </c>
-      <c r="C80" s="358"/>
-      <c r="D80" s="358"/>
-      <c r="E80" s="358"/>
-      <c r="F80" s="358"/>
+      <c r="C80" s="360"/>
+      <c r="D80" s="360"/>
+      <c r="E80" s="360"/>
+      <c r="F80" s="360"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="360" t="s">
+      <c r="B81" s="363" t="s">
         <v>251</v>
       </c>
-      <c r="C81" s="360"/>
-      <c r="D81" s="360"/>
-      <c r="E81" s="360"/>
-      <c r="F81" s="360"/>
+      <c r="C81" s="363"/>
+      <c r="D81" s="363"/>
+      <c r="E81" s="363"/>
+      <c r="F81" s="363"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5033,22 +5033,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="358" t="s">
+      <c r="B89" s="360" t="s">
         <v>360</v>
       </c>
-      <c r="C89" s="358"/>
-      <c r="D89" s="358"/>
-      <c r="E89" s="358"/>
-      <c r="F89" s="358"/>
+      <c r="C89" s="360"/>
+      <c r="D89" s="360"/>
+      <c r="E89" s="360"/>
+      <c r="F89" s="360"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="358" t="s">
+      <c r="B90" s="360" t="s">
         <v>361</v>
       </c>
-      <c r="C90" s="358"/>
-      <c r="D90" s="358"/>
-      <c r="E90" s="358"/>
-      <c r="F90" s="358"/>
+      <c r="C90" s="360"/>
+      <c r="D90" s="360"/>
+      <c r="E90" s="360"/>
+      <c r="F90" s="360"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5064,7 +5064,7 @@
       </c>
       <c r="C93" s="223">
         <f>DCF!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>32.443675727369531</v>
+        <v>32.749047400791135</v>
       </c>
       <c r="D93" s="1" t="str">
         <f>Market_currency</f>
@@ -5085,13 +5085,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="358" t="s">
+      <c r="B97" s="360" t="s">
         <v>362</v>
       </c>
-      <c r="C97" s="358"/>
-      <c r="D97" s="358"/>
-      <c r="E97" s="358"/>
-      <c r="F97" s="358"/>
+      <c r="C97" s="360"/>
+      <c r="D97" s="360"/>
+      <c r="E97" s="360"/>
+      <c r="F97" s="360"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5104,13 +5104,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="358" t="s">
+      <c r="B101" s="360" t="s">
         <v>341</v>
       </c>
-      <c r="C101" s="358"/>
-      <c r="D101" s="358"/>
-      <c r="E101" s="358"/>
-      <c r="F101" s="358"/>
+      <c r="C101" s="360"/>
+      <c r="D101" s="360"/>
+      <c r="E101" s="360"/>
+      <c r="F101" s="360"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="C103" s="223">
         <f>C102*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>3.0415393863509177</v>
+        <v>3.0701674610485132</v>
       </c>
       <c r="D103" s="1" t="str">
         <f>Market_currency</f>
@@ -5180,7 +5180,7 @@
       </c>
       <c r="C109" s="349">
         <f>DCF!C8</f>
-        <v>414292.97447467817</v>
+        <v>411336.54851155588</v>
       </c>
       <c r="D109" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5193,7 +5193,7 @@
       </c>
       <c r="C110" s="223">
         <f>C109*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>1.4542278122945285</v>
+        <v>1.4574403771265807</v>
       </c>
       <c r="D110" s="1" t="str">
         <f>Market_currency</f>
@@ -5224,7 +5224,7 @@
       </c>
       <c r="C114" s="223">
         <f>C113*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>1.3206564093718051E-2</v>
+        <v>1.333086907726362E-2</v>
       </c>
       <c r="D114" s="1" t="str">
         <f>Market_currency</f>
@@ -5232,13 +5232,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="358" t="s">
+      <c r="B116" s="360" t="s">
         <v>363</v>
       </c>
-      <c r="C116" s="358"/>
-      <c r="D116" s="358"/>
-      <c r="E116" s="358"/>
-      <c r="F116" s="358"/>
+      <c r="C116" s="360"/>
+      <c r="D116" s="360"/>
+      <c r="E116" s="360"/>
+      <c r="F116" s="360"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="C118" s="223">
         <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
-        <v>30.869570717406862</v>
+        <v>31.149651185946471</v>
       </c>
       <c r="D118" s="1" t="str">
         <f>Market_currency</f>
@@ -5259,7 +5259,7 @@
       </c>
       <c r="C119" s="223">
         <f>BS!D47</f>
-        <v>-5.8372216491647873</v>
+        <v>-5.8921637019123594</v>
       </c>
       <c r="D119" s="1" t="str">
         <f>Market_currency</f>
@@ -5277,13 +5277,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B123" s="359" t="s">
+      <c r="B123" s="361" t="s">
         <v>364</v>
       </c>
-      <c r="C123" s="359"/>
-      <c r="D123" s="359"/>
-      <c r="E123" s="359"/>
-      <c r="F123" s="359"/>
+      <c r="C123" s="361"/>
+      <c r="D123" s="361"/>
+      <c r="E123" s="361"/>
+      <c r="F123" s="361"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5317,7 +5317,7 @@
       </c>
       <c r="E126" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E74,DDM!E69),2)&amp;" "&amp;Market_currency</f>
-        <v>40.39 HKD</v>
+        <v>40.76 HKD</v>
       </c>
       <c r="F126" s="232">
         <f>DCF!F74</f>
@@ -5339,7 +5339,7 @@
       </c>
       <c r="E127" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E75,DDM!E70),2)&amp;" "&amp;Market_currency</f>
-        <v>33.5 HKD</v>
+        <v>33.8 HKD</v>
       </c>
       <c r="F127" s="221">
         <f>DCF!F75</f>
@@ -5361,7 +5361,7 @@
       </c>
       <c r="E128" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E76,DDM!E71),2)&amp;" "&amp;Market_currency</f>
-        <v>32.42 HKD</v>
+        <v>32.72 HKD</v>
       </c>
       <c r="F128" s="221">
         <f>DCF!F76</f>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="E129" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E77,DDM!E72),2)&amp;" "&amp;Market_currency</f>
-        <v>31.38 HKD</v>
+        <v>31.67 HKD</v>
       </c>
       <c r="F129" s="221">
         <f>DCF!F77</f>
@@ -5405,7 +5405,7 @@
       </c>
       <c r="E130" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E78,DDM!E73),2)&amp;" "&amp;Market_currency</f>
-        <v>30.87 HKD</v>
+        <v>31.15 HKD</v>
       </c>
       <c r="F130" s="221">
         <f>DCF!F78</f>
@@ -5418,7 +5418,7 @@
       </c>
       <c r="C132" s="217">
         <f>Scenarios!C60</f>
-        <v>32.750067624836312</v>
+        <v>33.047848014072677</v>
       </c>
       <c r="D132" s="212" t="str">
         <f>Market_currency</f>
@@ -5426,13 +5426,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="363" t="s">
+      <c r="B134" s="364" t="s">
         <v>367</v>
       </c>
-      <c r="C134" s="363"/>
-      <c r="D134" s="363"/>
-      <c r="E134" s="363"/>
-      <c r="F134" s="363"/>
+      <c r="C134" s="364"/>
+      <c r="D134" s="364"/>
+      <c r="E134" s="364"/>
+      <c r="F134" s="364"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5445,22 +5445,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="361" t="s">
+      <c r="B138" s="365" t="s">
         <v>365</v>
       </c>
-      <c r="C138" s="361"/>
-      <c r="D138" s="361"/>
-      <c r="E138" s="361"/>
-      <c r="F138" s="361"/>
+      <c r="C138" s="365"/>
+      <c r="D138" s="365"/>
+      <c r="E138" s="365"/>
+      <c r="F138" s="365"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="358" t="s">
+      <c r="B139" s="360" t="s">
         <v>366</v>
       </c>
-      <c r="C139" s="358"/>
-      <c r="D139" s="358"/>
-      <c r="E139" s="358"/>
-      <c r="F139" s="358"/>
+      <c r="C139" s="360"/>
+      <c r="D139" s="360"/>
+      <c r="E139" s="360"/>
+      <c r="F139" s="360"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5491,7 +5491,7 @@
       </c>
       <c r="C143" s="213">
         <f>Scenarios!C77</f>
-        <v>1.4730216878400002</v>
+        <v>1.4868863036000002</v>
       </c>
       <c r="D143" s="212" t="str">
         <f>Market_currency</f>
@@ -5527,7 +5527,7 @@
       </c>
       <c r="C147" s="216">
         <f>Scenarios!C81</f>
-        <v>2.4411789197993943</v>
+        <v>2.4641561834770669</v>
       </c>
     </row>
     <row r="148" spans="2:4">
@@ -5537,7 +5537,7 @@
       </c>
       <c r="C148" s="216">
         <f>Scenarios!C82</f>
-        <v>12.809302278264093</v>
+        <v>12.925771015427101</v>
       </c>
     </row>
     <row r="149" spans="2:4">
@@ -5546,7 +5546,7 @@
       </c>
       <c r="C149" s="215">
         <f>Scenarios!C83</f>
-        <v>15.250481198063488</v>
+        <v>15.389927198904168</v>
       </c>
       <c r="D149" s="300" t="str">
         <f>IF($D$11="","",C149*$E$25)</f>
@@ -5572,7 +5572,7 @@
       </c>
       <c r="C151" s="92">
         <f>Scenarios!F83</f>
-        <v>0.53433741350512065</v>
+        <v>0.53431378671462304</v>
       </c>
     </row>
     <row r="153" spans="2:4">
@@ -5596,7 +5596,7 @@
       </c>
       <c r="C155" s="216">
         <f>Scenarios!C91</f>
-        <v>3.0202848823180561</v>
+        <v>3.0487129018949313</v>
       </c>
     </row>
     <row r="156" spans="2:4">
@@ -5606,7 +5606,7 @@
       </c>
       <c r="C156" s="216">
         <f>Scenarios!C92</f>
-        <v>18.151491174787974</v>
+        <v>18.316533829635802</v>
       </c>
     </row>
     <row r="157" spans="2:4">
@@ -5615,7 +5615,7 @@
       </c>
       <c r="C157" s="215">
         <f>Scenarios!C93</f>
-        <v>21.17177605710603</v>
+        <v>21.365246731530732</v>
       </c>
       <c r="D157" s="300" t="str">
         <f>IF($D$11="","",C157*$E$25)</f>
@@ -5641,7 +5641,7 @@
       </c>
       <c r="C159" s="92">
         <f>Scenarios!F93</f>
-        <v>0.35353489038141039</v>
+        <v>0.35350565875173401</v>
       </c>
     </row>
     <row r="161" spans="2:4">
@@ -5665,7 +5665,7 @@
       </c>
       <c r="C163" s="216">
         <f>Scenarios!C97</f>
-        <v>3.8306308146175594</v>
+        <v>3.8666861047748737</v>
       </c>
     </row>
     <row r="164" spans="2:4">
@@ -5675,7 +5675,7 @@
       </c>
       <c r="C164" s="216">
         <f>Scenarios!C98</f>
-        <v>26.362513086766249</v>
+        <v>26.602214558474746</v>
       </c>
     </row>
     <row r="165" spans="2:4">
@@ -5684,7 +5684,7 @@
       </c>
       <c r="C165" s="215">
         <f>Scenarios!C99</f>
-        <v>30.193143901383809</v>
+        <v>30.46890066324962</v>
       </c>
       <c r="D165" s="300" t="str">
         <f>IF($D$11="","",C165*$E$25)</f>
@@ -5710,7 +5710,7 @@
       </c>
       <c r="C167" s="92">
         <f>Scenarios!F99</f>
-        <v>7.8073845609816006E-2</v>
+        <v>7.8036771100038704E-2</v>
       </c>
     </row>
     <row r="169" spans="2:4">
@@ -5734,7 +5734,7 @@
       </c>
       <c r="C171" s="216">
         <f>Scenarios!C103</f>
-        <v>3.5538167286582092</v>
+        <v>3.5872665439807236</v>
       </c>
     </row>
     <row r="172" spans="2:4">
@@ -5744,7 +5744,7 @@
       </c>
       <c r="C172" s="216">
         <f>Scenarios!C104</f>
-        <v>23.473951342039037</v>
+        <v>23.687388530860197</v>
       </c>
     </row>
     <row r="173" spans="2:4">
@@ -5753,7 +5753,7 @@
       </c>
       <c r="C173" s="215">
         <f>Scenarios!C105</f>
-        <v>27.027768070697245</v>
+        <v>27.274655074840922</v>
       </c>
       <c r="D173" s="300" t="str">
         <f>IF($D$11="","",C173*$E$25)</f>
@@ -5779,7 +5779,7 @@
       </c>
       <c r="C175" s="92">
         <f>Scenarios!F105</f>
-        <v>0.15787472440753425</v>
+        <v>0.15783417591159743</v>
       </c>
     </row>
     <row r="177" spans="1:6" ht="13.9">
@@ -5793,13 +5793,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="365" t="s">
+      <c r="B179" s="359" t="s">
         <v>373</v>
       </c>
-      <c r="C179" s="358"/>
-      <c r="D179" s="358"/>
-      <c r="E179" s="358"/>
-      <c r="F179" s="358"/>
+      <c r="C179" s="360"/>
+      <c r="D179" s="360"/>
+      <c r="E179" s="360"/>
+      <c r="F179" s="360"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5836,13 +5836,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="359" t="s">
+      <c r="B188" s="361" t="s">
         <v>378</v>
       </c>
-      <c r="C188" s="359"/>
-      <c r="D188" s="359"/>
-      <c r="E188" s="359"/>
-      <c r="F188" s="359"/>
+      <c r="C188" s="361"/>
+      <c r="D188" s="361"/>
+      <c r="E188" s="361"/>
+      <c r="F188" s="361"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5850,22 +5850,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="364" t="s">
+      <c r="B191" s="358" t="s">
         <v>379</v>
       </c>
-      <c r="C191" s="364"/>
-      <c r="D191" s="364"/>
-      <c r="E191" s="364"/>
-      <c r="F191" s="364"/>
+      <c r="C191" s="358"/>
+      <c r="D191" s="358"/>
+      <c r="E191" s="358"/>
+      <c r="F191" s="358"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="364" t="s">
+      <c r="B192" s="358" t="s">
         <v>380</v>
       </c>
-      <c r="C192" s="364"/>
-      <c r="D192" s="364"/>
-      <c r="E192" s="364"/>
-      <c r="F192" s="364"/>
+      <c r="C192" s="358"/>
+      <c r="D192" s="358"/>
+      <c r="E192" s="358"/>
+      <c r="F192" s="358"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5889,17 +5889,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5916,6 +5905,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -6488,15 +6488,15 @@
       </c>
       <c r="C25" s="39">
         <f>0.164*Exchange_Rate</f>
-        <v>1.4730216878400002</v>
+        <v>1.4868863036000002</v>
       </c>
       <c r="D25" s="39">
         <f>0.137*Exchange_Rate</f>
-        <v>1.2305120197200001</v>
+        <v>1.2420940463000003</v>
       </c>
       <c r="E25" s="39">
         <f>0.11*Exchange_Rate</f>
-        <v>0.98800235160000016</v>
+        <v>0.99730178900000011</v>
       </c>
       <c r="F25" s="39"/>
       <c r="G25" s="39"/>
@@ -7870,15 +7870,15 @@
       </c>
       <c r="C65" s="73">
         <f>IF(C$4="","",C25)</f>
-        <v>1.4730216878400002</v>
+        <v>1.4868863036000002</v>
       </c>
       <c r="D65" s="73">
         <f t="shared" ref="D65:M65" si="33">IF(D$4="","",D25)</f>
-        <v>1.2305120197200001</v>
+        <v>1.2420940463000003</v>
       </c>
       <c r="E65" s="73">
         <f t="shared" si="33"/>
-        <v>0.98800235160000016</v>
+        <v>0.99730178900000011</v>
       </c>
       <c r="F65" s="73">
         <f t="shared" si="33"/>
@@ -9220,11 +9220,11 @@
       </c>
       <c r="C47" s="147">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>15.44240268024663</v>
+        <v>15.587752189585334</v>
       </c>
       <c r="D47" s="147">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>-5.8372216491647873</v>
+        <v>-5.8921637019123594</v>
       </c>
       <c r="F47" s="253"/>
     </row>
@@ -9415,7 +9415,7 @@
       </c>
       <c r="D66" s="76">
         <f>C66-D75</f>
-        <v>414292.97447467817</v>
+        <v>411336.54851155588</v>
       </c>
       <c r="F66" s="5" t="s">
         <v>225</v>
@@ -9482,11 +9482,11 @@
       </c>
       <c r="C73" s="349">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35-Normalized_FCF!G91)/12</f>
-        <v>-646927.1872804584</v>
+        <v>-649883.61324358056</v>
       </c>
       <c r="D73" s="349">
         <f>(Normalized_FCF!C25+Normalized_FCF!C35-Normalized_FCF!C91)/12</f>
-        <v>-597270.02552532183</v>
+        <v>-600226.45148844412</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>348</v>
@@ -9498,11 +9498,11 @@
       </c>
       <c r="C74" s="258">
         <f>-$C$66/C73</f>
-        <v>1.5636427404641804</v>
+        <v>1.5565294760261321</v>
       </c>
       <c r="D74" s="258">
         <f>-$C$66/D73</f>
-        <v>1.6936443430428165</v>
+        <v>1.6853022679882264</v>
       </c>
       <c r="F74" s="253" t="s">
         <v>316</v>
@@ -9515,7 +9515,7 @@
       <c r="C75" s="320"/>
       <c r="D75" s="321">
         <f>MAX(-D73*D76,G5)</f>
-        <v>597270.02552532183</v>
+        <v>600226.45148844412</v>
       </c>
       <c r="F75" s="253" t="s">
         <v>349</v>
@@ -9630,11 +9630,11 @@
       </c>
       <c r="C86" s="76">
         <f>-DCF!C7*Exchange_Rate</f>
-        <v>-7782763.9787400011</v>
+        <v>-7856018.1833500015</v>
       </c>
       <c r="D86" s="223">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>-3.0415393863509177</v>
+        <v>-3.0701674610485132</v>
       </c>
       <c r="E86" s="240" t="str">
         <f>Market_currency</f>
@@ -9647,11 +9647,11 @@
       </c>
       <c r="C87" s="76">
         <f>DCF!C8*Exchange_Rate</f>
-        <v>3721113.0275667352</v>
+        <v>3729333.4155605459</v>
       </c>
       <c r="D87" s="223">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>1.4542278122945287</v>
+        <v>1.4574403771265807</v>
       </c>
       <c r="E87" s="240" t="str">
         <f>Market_currency</f>
@@ -9664,11 +9664,11 @@
       </c>
       <c r="C88" s="76">
         <f>DCF!C9*Exchange_Rate</f>
-        <v>33793.273160544006</v>
+        <v>34111.347735760006</v>
       </c>
       <c r="D88" s="223">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>1.3206564093718055E-2</v>
+        <v>1.333086907726362E-2</v>
       </c>
       <c r="E88" s="240" t="str">
         <f>Market_currency</f>
@@ -9681,11 +9681,11 @@
       </c>
       <c r="C89" s="180">
         <f>SUM(C86:C88)</f>
-        <v>-4027857.6780127217</v>
+        <v>-4092573.4200536958</v>
       </c>
       <c r="D89" s="242">
         <f>SUM(D86:D88)</f>
-        <v>-1.574105009962671</v>
+        <v>-1.599396214844669</v>
       </c>
       <c r="E89" s="240" t="str">
         <f>Market_currency</f>
@@ -13197,20 +13197,20 @@
       </c>
       <c r="C90" s="113">
         <f>G90</f>
-        <v>1.4730216878400002</v>
+        <v>1.4868863036000002</v>
       </c>
       <c r="E90" s="268"/>
       <c r="G90" s="112">
         <f>Data!C65</f>
-        <v>1.4730216878400002</v>
+        <v>1.4868863036000002</v>
       </c>
       <c r="H90" s="112">
         <f>Data!D65</f>
-        <v>1.2305120197200001</v>
+        <v>1.2420940463000003</v>
       </c>
       <c r="I90" s="112">
         <f>Data!E65</f>
-        <v>0.98800235160000016</v>
+        <v>0.99730178900000011</v>
       </c>
       <c r="J90" s="112">
         <f>Data!F65</f>
@@ -13253,20 +13253,20 @@
       </c>
       <c r="C91" s="74">
         <f>C90*Common_Shares/scaling_factor</f>
-        <v>3769203.2473655003</v>
+        <v>3804680.3589229668</v>
       </c>
       <c r="E91" s="268"/>
       <c r="G91" s="74">
         <f t="shared" ref="G91:Q91" si="37">IF(G$4="","",G90*Common_Shares/scaling_factor)</f>
-        <v>3769203.2473655003</v>
+        <v>3804680.3589229668</v>
       </c>
       <c r="H91" s="74">
         <f t="shared" si="37"/>
-        <v>3148663.6883480097</v>
+        <v>3178300.0559295523</v>
       </c>
       <c r="I91" s="74">
         <f t="shared" si="37"/>
-        <v>2528124.1293305187</v>
+        <v>2551919.7529361364</v>
       </c>
       <c r="J91" s="74">
         <f t="shared" si="37"/>
@@ -13308,20 +13308,20 @@
       </c>
       <c r="C92" s="23">
         <f>C90/(C19*scaling_factor/Common_Shares)</f>
-        <v>5.4372977874053738</v>
+        <v>5.4884756113419773</v>
       </c>
       <c r="E92" s="268"/>
       <c r="G92" s="170">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",G90/(G19*scaling_factor/Common_Shares))</f>
-        <v>3.7809999672633623</v>
+        <v>3.8165881138381414</v>
       </c>
       <c r="H92" s="170">
         <f t="shared" si="38"/>
-        <v>3.8350866772811822</v>
+        <v>3.8711839076381702</v>
       </c>
       <c r="I92" s="170">
         <f t="shared" si="38"/>
-        <v>3.7629406195010162</v>
+        <v>3.7983587849277458</v>
       </c>
       <c r="J92" s="170">
         <f t="shared" si="38"/>
@@ -13384,20 +13384,20 @@
       </c>
       <c r="C94" s="23">
         <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
-        <v>2.9082363037314912E-2</v>
+        <v>3.1237107218487398E-2</v>
       </c>
       <c r="E94" s="268"/>
       <c r="G94" s="23">
         <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>2.9082363037314912E-2</v>
+        <v>3.1237107218487398E-2</v>
       </c>
       <c r="H94" s="23">
         <f t="shared" si="39"/>
-        <v>2.4294413025074041E-2</v>
+        <v>2.6094412737394965E-2</v>
       </c>
       <c r="I94" s="23">
         <f t="shared" si="39"/>
-        <v>1.9506463012833174E-2</v>
+        <v>2.0951718256302522E-2</v>
       </c>
       <c r="J94" s="23">
         <f t="shared" si="39"/>
@@ -14526,38 +14526,38 @@
       </c>
       <c r="C125" s="177">
         <f>C16*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>2.4332756795527151</v>
+        <v>2.4561785550593354</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="265"/>
       <c r="F125" s="27"/>
       <c r="G125" s="177">
         <f t="shared" ref="G125:Q125" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>3.4991919024414346</v>
+        <v>3.532127569036402</v>
       </c>
       <c r="H125" s="177">
         <f t="shared" si="49"/>
-        <v>2.8818805069646838</v>
+        <v>2.9090058142328274</v>
       </c>
       <c r="I125" s="177">
         <f t="shared" si="49"/>
-        <v>2.3582829239943353</v>
+        <v>2.3804799404160666</v>
       </c>
       <c r="J125" s="177">
         <f t="shared" si="49"/>
-        <v>1.2649363906540505</v>
+        <v>1.2768424319309966</v>
       </c>
       <c r="K125" s="177">
         <f t="shared" si="49"/>
-        <v>6.1105351155524268</v>
+        <v>6.1680496940304623</v>
       </c>
       <c r="L125" s="177">
         <f t="shared" si="49"/>
-        <v>8.2159823996173245</v>
+        <v>8.2933142135355933</v>
       </c>
       <c r="M125" s="177">
         <f t="shared" si="49"/>
-        <v>7.6012123480710052</v>
+        <v>7.6727577227156312</v>
       </c>
       <c r="N125" s="177" t="str">
         <f t="shared" si="49"/>
@@ -14583,38 +14583,38 @@
       </c>
       <c r="C126" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>4.8040980840132586E-2</v>
+        <v>5.1600389812170917E-2</v>
       </c>
       <c r="D126" s="27"/>
       <c r="E126" s="265"/>
       <c r="F126" s="27"/>
       <c r="G126" s="77">
         <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
-        <v>6.9085723641489336E-2</v>
+        <v>7.4204360694042057E-2</v>
       </c>
       <c r="H126" s="77">
         <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
-        <v>5.6897936958828901E-2</v>
+        <v>6.1113567525899734E-2</v>
       </c>
       <c r="I126" s="77">
         <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
-        <v>4.6560373622790432E-2</v>
+        <v>5.0010082781850138E-2</v>
       </c>
       <c r="J126" s="77">
         <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
-        <v>2.4974064968490632E-2</v>
+        <v>2.6824420838886483E-2</v>
       </c>
       <c r="K126" s="77">
         <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
-        <v>0.1206423517384487</v>
+        <v>0.12958087592500972</v>
       </c>
       <c r="L126" s="77">
         <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
-        <v>0.16221090621159576</v>
+        <v>0.1742292902003276</v>
       </c>
       <c r="M126" s="77">
         <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
-        <v>0.1500732941376309</v>
+        <v>0.16119238913268133</v>
       </c>
       <c r="N126" s="77" t="str">
         <f t="shared" ref="N126" si="57">IF(N$4="","",N125/Market_Price)</f>
@@ -14640,31 +14640,31 @@
       <c r="C127" s="169"/>
       <c r="G127" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.5074933284150656E-3</v>
+        <v>6.9244650647946023E-3</v>
       </c>
       <c r="H127" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.1957480998435831E-3</v>
+        <v>5.528668933972216E-3</v>
       </c>
       <c r="I127" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.6198992559788594E-3</v>
+        <v>3.8518465822548159E-3</v>
       </c>
       <c r="J127" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.2769513916235133E-3</v>
+        <v>2.422848487095188E-3</v>
       </c>
       <c r="K127" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-4.1949181560264437E-4</v>
+        <v>-4.463710180729819E-4</v>
       </c>
       <c r="L127" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.9885430526113876E-3</v>
+        <v>2.1159602019908989E-3</v>
       </c>
       <c r="M127" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.6062876169031363E-3</v>
+        <v>1.7092115083223499E-3</v>
       </c>
       <c r="N127" s="23" t="str">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -15492,7 +15492,7 @@
       </c>
       <c r="C8" s="338">
         <f>BS!D66</f>
-        <v>414292.97447467817</v>
+        <v>411336.54851155588</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
@@ -15524,7 +15524,7 @@
       </c>
       <c r="C10" s="347">
         <f>C6-C7+C8+C9</f>
-        <v>8794389.8233468216</v>
+        <v>8791433.3973836992</v>
       </c>
       <c r="D10" t="str">
         <f>Reporting_currency</f>
@@ -15538,7 +15538,7 @@
       </c>
       <c r="C11" s="208">
         <f>Exchange_Rate</f>
-        <v>8.9818395600000009</v>
+        <v>9.0663799000000012</v>
       </c>
       <c r="D11" t="str">
         <f>Thesis!C15</f>
@@ -15552,7 +15552,7 @@
       </c>
       <c r="C12" s="111">
         <f>(C10*scaling_factor)/Common_Shares*Exchange_Rate</f>
-        <v>30.869570717406862</v>
+        <v>31.149651185946471</v>
       </c>
       <c r="D12" t="str">
         <f>Market_currency</f>
@@ -15605,7 +15605,7 @@
       </c>
       <c r="C18" s="140">
         <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>32.094711860634071</v>
+        <v>32.386323803111118</v>
       </c>
       <c r="D18" t="str">
         <f>Market_currency</f>
@@ -16701,23 +16701,23 @@
       </c>
       <c r="B65" s="124">
         <f>C12</f>
-        <v>30.869570717406862</v>
+        <v>31.149651185946471</v>
       </c>
       <c r="C65" s="124">
         <f>C12</f>
-        <v>30.869570717406862</v>
+        <v>31.149651185946471</v>
       </c>
       <c r="D65" s="124">
         <f>C12</f>
-        <v>30.869570717406862</v>
+        <v>31.149651185946471</v>
       </c>
       <c r="E65" s="141">
         <f>C12</f>
-        <v>30.869570717406862</v>
+        <v>31.149651185946471</v>
       </c>
       <c r="F65" s="124">
         <f>C12</f>
-        <v>30.869570717406862</v>
+        <v>31.149651185946471</v>
       </c>
       <c r="H65" s="120"/>
     </row>
@@ -16728,23 +16728,23 @@
       </c>
       <c r="B66" s="124">
         <f t="shared" ref="B66:F71" si="4">(B56-$C$7+$C$8+$C$9)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>30.869570717406866</v>
+        <v>31.149651185946471</v>
       </c>
       <c r="C66" s="124">
         <f t="shared" si="4"/>
-        <v>31.380307740728544</v>
+        <v>31.665195451850668</v>
       </c>
       <c r="D66" s="124">
         <f t="shared" si="4"/>
-        <v>32.423936416010044</v>
+        <v>32.71864713971803</v>
       </c>
       <c r="E66" s="124">
         <f t="shared" si="4"/>
-        <v>33.498189898655845</v>
+        <v>33.803011886772687</v>
       </c>
       <c r="F66" s="124">
         <f t="shared" si="4"/>
-        <v>35.169929467600689</v>
+        <v>35.490486476434164</v>
       </c>
       <c r="H66" s="120"/>
     </row>
@@ -16755,23 +16755,23 @@
       </c>
       <c r="B67" s="124">
         <f t="shared" si="4"/>
-        <v>30.869570717406869</v>
+        <v>31.149651185946482</v>
       </c>
       <c r="C67" s="124">
         <f t="shared" si="4"/>
-        <v>31.869993074922903</v>
+        <v>32.159489882474467</v>
       </c>
       <c r="D67" s="124">
         <f t="shared" si="4"/>
-        <v>34.018120125920994</v>
+        <v>34.327835886398788</v>
       </c>
       <c r="E67" s="124">
         <f t="shared" si="4"/>
-        <v>36.382231683092932</v>
+        <v>36.714199321207381</v>
       </c>
       <c r="F67" s="124">
         <f t="shared" si="4"/>
-        <v>40.390676984627049</v>
+        <v>40.760373567508267</v>
       </c>
       <c r="H67" s="120"/>
     </row>
@@ -16782,23 +16782,23 @@
       </c>
       <c r="B68" s="124">
         <f t="shared" si="4"/>
-        <v>30.869570717406869</v>
+        <v>31.149651185946482</v>
       </c>
       <c r="C68" s="124">
         <f t="shared" si="4"/>
-        <v>32.47457877214601</v>
+        <v>32.769766160124995</v>
       </c>
       <c r="D68" s="124">
         <f t="shared" si="4"/>
-        <v>36.089041825350769</v>
+        <v>36.418249853911703</v>
       </c>
       <c r="E68" s="124">
         <f t="shared" si="4"/>
-        <v>40.331834131663079</v>
+        <v>40.700976864215214</v>
       </c>
       <c r="F68" s="124">
         <f t="shared" si="4"/>
-        <v>48.155115183392056</v>
+        <v>48.597893481978346</v>
       </c>
       <c r="H68" s="120"/>
     </row>
@@ -16809,23 +16809,23 @@
       </c>
       <c r="B69" s="124">
         <f t="shared" si="4"/>
-        <v>30.869570717406877</v>
+        <v>31.149651185946485</v>
       </c>
       <c r="C69" s="124">
         <f t="shared" si="4"/>
-        <v>33.088607427383344</v>
+        <v>33.38957427634432</v>
       </c>
       <c r="D69" s="124">
         <f t="shared" si="4"/>
-        <v>38.307149496659498</v>
+        <v>38.65723516119202</v>
       </c>
       <c r="E69" s="124">
         <f t="shared" si="4"/>
-        <v>44.808254140054814</v>
+        <v>45.219530565484014</v>
       </c>
       <c r="F69" s="124">
         <f t="shared" si="4"/>
-        <v>57.788277488292792</v>
+        <v>58.321726613394212</v>
       </c>
       <c r="H69" s="120"/>
     </row>
@@ -16836,23 +16836,23 @@
       </c>
       <c r="B70" s="124">
         <f t="shared" si="4"/>
-        <v>30.869570717406877</v>
+        <v>31.149651185946485</v>
       </c>
       <c r="C70" s="124">
         <f t="shared" si="4"/>
-        <v>33.65753403716797</v>
+        <v>33.963855830258701</v>
       </c>
       <c r="D70" s="124">
         <f t="shared" si="4"/>
-        <v>40.478481723217008</v>
+        <v>40.849004756226215</v>
       </c>
       <c r="E70" s="124">
         <f t="shared" si="4"/>
-        <v>49.460134763314159</v>
+        <v>49.915196380730237</v>
       </c>
       <c r="F70" s="124">
         <f t="shared" si="4"/>
-        <v>68.822284521965813</v>
+        <v>69.459589733557962</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="13.15">
@@ -16862,23 +16862,23 @@
       </c>
       <c r="B71" s="124">
         <f t="shared" si="4"/>
-        <v>30.869570717406869</v>
+        <v>31.149651185946482</v>
       </c>
       <c r="C71" s="124">
         <f t="shared" si="4"/>
-        <v>34.157210288948555</v>
+        <v>34.468235216618041</v>
       </c>
       <c r="D71" s="124">
         <f t="shared" si="4"/>
-        <v>42.496672730551118</v>
+        <v>42.886191711195025</v>
       </c>
       <c r="E71" s="124">
         <f t="shared" si="4"/>
-        <v>54.063990698612258</v>
+        <v>54.562385482188887</v>
       </c>
       <c r="F71" s="124">
         <f t="shared" si="4"/>
-        <v>80.93355867038477</v>
+        <v>81.684859598277669</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="13.15">
@@ -16913,7 +16913,7 @@
       </c>
       <c r="E74" s="135">
         <f>INDEX(B$65:F$71, MATCH(D74, A$65:A$71, 0), MATCH(C74, B$64:F$64, 0))</f>
-        <v>40.390676984627049</v>
+        <v>40.760373567508267</v>
       </c>
       <c r="F74" s="142">
         <f>Scenarios!C58</f>
@@ -16935,7 +16935,7 @@
       </c>
       <c r="E75" s="135">
         <f>INDEX(B$65:F$71, MATCH(D75, A$65:A$71, 0), MATCH(C75, B$64:F$64, 0))</f>
-        <v>33.498189898655845</v>
+        <v>33.803011886772687</v>
       </c>
       <c r="F75" s="142">
         <f>Scenarios!C40*(1-F$74-F$78)</f>
@@ -16958,7 +16958,7 @@
       </c>
       <c r="E76" s="135">
         <f>INDEX(B$65:F$71, MATCH(D76, A$65:A$71, 0), MATCH(C76, B$64:F$64, 0))</f>
-        <v>32.423936416010044</v>
+        <v>32.71864713971803</v>
       </c>
       <c r="F76" s="142">
         <f>Scenarios!C28*(1-F$74-F$78)</f>
@@ -16981,7 +16981,7 @@
       </c>
       <c r="E77" s="135">
         <f>INDEX(B$65:F$71, MATCH(D77, A$65:A$71, 0), MATCH(C77, B$64:F$64, 0))</f>
-        <v>31.380307740728544</v>
+        <v>31.665195451850668</v>
       </c>
       <c r="F77" s="142">
         <f>Scenarios!C34*(1-F$74-F$78)</f>
@@ -17004,7 +17004,7 @@
       </c>
       <c r="E78" s="135">
         <f>INDEX(B$65:F$71, MATCH(D78, A$65:A$71, 0), MATCH(C78, B$64:F$64, 0))</f>
-        <v>30.869570717406869</v>
+        <v>31.149651185946482</v>
       </c>
       <c r="F78" s="142">
         <f>Scenarios!C52</f>
@@ -17186,7 +17186,7 @@
       </c>
       <c r="C4" s="114">
         <f>Normalized_FCF!C91*(1-dividend_tax_rate)</f>
-        <v>3769203.2473655003</v>
+        <v>3804680.3589229668</v>
       </c>
       <c r="D4" t="str">
         <f>Market_currency</f>
@@ -17218,7 +17218,7 @@
       </c>
       <c r="C6" s="319">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
-        <v>50256043.298206672</v>
+        <v>50729071.452306226</v>
       </c>
       <c r="D6" t="str">
         <f>Reporting_currency</f>
@@ -17234,7 +17234,7 @@
       </c>
       <c r="C7" s="111">
         <f>(C6*scaling_factor)/Common_Shares*Exchange_Rate</f>
-        <v>176.40592624772381</v>
+        <v>179.74234795392456</v>
       </c>
       <c r="D7" t="str">
         <f>Market_currency</f>
@@ -17287,7 +17287,7 @@
       </c>
       <c r="C13" s="140">
         <f>F47/Common_Shares*scaling_factor</f>
-        <v>20.381947623550332</v>
+        <v>20.573789926059366</v>
       </c>
       <c r="D13" t="str">
         <f>Market_currency</f>
@@ -17322,7 +17322,7 @@
       </c>
       <c r="C16" s="123">
         <f>C4*(1+D16)</f>
-        <v>3858731.6971469</v>
+        <v>3895051.4830288892</v>
       </c>
       <c r="D16" s="138">
         <f>IF($C$12&lt;B16,0,DDM!$C$11)</f>
@@ -17334,7 +17334,7 @@
       </c>
       <c r="F16" s="125">
         <f t="shared" ref="F16:F46" si="1">C16*E16</f>
-        <v>3589517.8578110696</v>
+        <v>3623303.7051431527</v>
       </c>
       <c r="H16" s="120"/>
     </row>
@@ -17344,7 +17344,7 @@
       </c>
       <c r="C17" s="123">
         <f t="shared" ref="C17:C45" si="2">IF(ROW()-ROW($C$16)&lt;$C$12, $C$16*(1+D17)^(ROW()-ROW($C$16)), 0)</f>
-        <v>3950386.6821120586</v>
+        <v>3987569.1580409906</v>
       </c>
       <c r="D17" s="138">
         <f>IF($C$12&lt;B17,0,DDM!$C$11)</f>
@@ -17356,7 +17356,7 @@
       </c>
       <c r="F17" s="125">
         <f t="shared" si="1"/>
-        <v>3418398.4269222794</v>
+        <v>3450573.6359467739</v>
       </c>
       <c r="H17" s="120"/>
     </row>
@@ -17366,7 +17366,7 @@
       </c>
       <c r="C18" s="123">
         <f t="shared" si="2"/>
-        <v>4044218.7130416138</v>
+        <v>4082284.3701657439</v>
       </c>
       <c r="D18" s="138">
         <f>IF($C$12&lt;B18,0,DDM!$C$11)</f>
@@ -17378,7 +17378,7 @@
       </c>
       <c r="F18" s="125">
         <f t="shared" si="1"/>
-        <v>3255436.5984713715</v>
+        <v>3286077.9515087684</v>
       </c>
       <c r="H18" s="120"/>
     </row>
@@ -17388,7 +17388,7 @@
       </c>
       <c r="C19" s="123">
         <f t="shared" si="2"/>
-        <v>4140279.5004795468</v>
+        <v>4179249.3166655726</v>
       </c>
       <c r="D19" s="138">
         <f>IF($C$12&lt;B19,0,DDM!$C$11)</f>
@@ -17400,7 +17400,7 @@
       </c>
       <c r="F19" s="125">
         <f t="shared" si="1"/>
-        <v>3100243.4833813496</v>
+        <v>3129424.1023867335</v>
       </c>
       <c r="H19" s="120"/>
     </row>
@@ -17410,7 +17410,7 @@
       </c>
       <c r="C20" s="123">
         <f t="shared" si="2"/>
-        <v>4238621.9832307026</v>
+        <v>4278517.4346246039</v>
       </c>
       <c r="D20" s="138">
         <f>IF($C$12&lt;B20,0,DDM!$C$11)</f>
@@ -17422,7 +17422,7 @@
       </c>
       <c r="F20" s="125">
         <f t="shared" si="1"/>
-        <v>2952448.731688315</v>
+        <v>2980238.2527482416</v>
       </c>
       <c r="H20" s="120"/>
     </row>
@@ -17982,7 +17982,7 @@
       </c>
       <c r="C46" s="123">
         <f>C$16*(1+F4)^$C$12/Equity_Cost</f>
-        <v>51449755.961958669</v>
+        <v>51934019.773718521</v>
       </c>
       <c r="D46" s="139">
         <f>Terminal_Growth</f>
@@ -17994,7 +17994,7 @@
       </c>
       <c r="F46" s="125">
         <f t="shared" si="1"/>
-        <v>35837771.647609167</v>
+        <v>36175089.786025263</v>
       </c>
       <c r="H46" s="120"/>
     </row>
@@ -18005,7 +18005,7 @@
       </c>
       <c r="F47" s="137">
         <f>SUM(F16:F46)</f>
-        <v>52153816.745883554</v>
+        <v>52644707.433758929</v>
       </c>
       <c r="H47" s="120"/>
     </row>
@@ -18026,7 +18026,7 @@
     <row r="50" spans="1:8" ht="13.15">
       <c r="A50" s="133">
         <f>F47</f>
-        <v>52153816.745883554</v>
+        <v>52644707.433758929</v>
       </c>
       <c r="B50" s="131">
         <f>C73</f>
@@ -18056,19 +18056,19 @@
       </c>
       <c r="B51" s="123">
         <f t="dataTable" ref="B51:F56" dt2D="1" dtr="1" r1="C11" r2="C12"/>
-        <v>50256043.29820668</v>
+        <v>50729071.452306226</v>
       </c>
       <c r="C51" s="123">
-        <v>51047187.377371483</v>
+        <v>51527662.067227416</v>
       </c>
       <c r="D51" s="123">
-        <v>52663793.594648868</v>
+        <v>53159484.370067433</v>
       </c>
       <c r="E51" s="123">
-        <v>54327838.383863449</v>
+        <v>54839191.753933758</v>
       </c>
       <c r="F51" s="123">
-        <v>56917403.662046216</v>
+        <v>57453130.962156966</v>
       </c>
       <c r="H51" s="120"/>
     </row>
@@ -18077,19 +18077,19 @@
         <v>10</v>
       </c>
       <c r="B52" s="123">
-        <v>50256043.298206687</v>
+        <v>50729071.452306241</v>
       </c>
       <c r="C52" s="123">
-        <v>51805721.877733529</v>
+        <v>52293336.170132339</v>
       </c>
       <c r="D52" s="123">
-        <v>55133222.959675893</v>
+        <v>55652156.902235284</v>
       </c>
       <c r="E52" s="123">
-        <v>58795289.298194811</v>
+        <v>59348691.940767482</v>
       </c>
       <c r="F52" s="123">
-        <v>65004468.625629947</v>
+        <v>65616314.321872845</v>
       </c>
       <c r="H52" s="120"/>
     </row>
@@ -18098,19 +18098,19 @@
         <v>15</v>
       </c>
       <c r="B53" s="123">
-        <v>50256043.29820668</v>
+        <v>50729071.452306233</v>
       </c>
       <c r="C53" s="123">
-        <v>52742239.836809561</v>
+        <v>53238668.976784706</v>
       </c>
       <c r="D53" s="123">
-        <v>58341131.073057123</v>
+        <v>58890259.013269499</v>
       </c>
       <c r="E53" s="123">
-        <v>64913319.614303447</v>
+        <v>65524307.382907271</v>
       </c>
       <c r="F53" s="123">
-        <v>77031772.362185359</v>
+        <v>77756823.414678425</v>
       </c>
       <c r="H53" s="120"/>
     </row>
@@ -18119,19 +18119,19 @@
         <v>20</v>
       </c>
       <c r="B54" s="123">
-        <v>50256043.298206672</v>
+        <v>50729071.452306241</v>
       </c>
       <c r="C54" s="123">
-        <v>53693385.167667225</v>
+        <v>54198766.833360828</v>
       </c>
       <c r="D54" s="123">
-        <v>61777033.839010872</v>
+        <v>62358501.745451801</v>
       </c>
       <c r="E54" s="123">
-        <v>71847403.151974574</v>
+        <v>72523657.036271855</v>
       </c>
       <c r="F54" s="123">
-        <v>91953775.219134629</v>
+        <v>92819277.588596806</v>
       </c>
       <c r="H54" s="120"/>
     </row>
@@ -18140,19 +18140,19 @@
         <v>25</v>
       </c>
       <c r="B55" s="123">
-        <v>50256043.298206665</v>
+        <v>50729071.452306241</v>
       </c>
       <c r="C55" s="123">
-        <v>54574666.332449585</v>
+        <v>55088342.936925903</v>
       </c>
       <c r="D55" s="123">
-        <v>65140480.302649699</v>
+        <v>65753606.190254539</v>
       </c>
       <c r="E55" s="123">
-        <v>79053279.452340543</v>
+        <v>79797357.664645627</v>
       </c>
       <c r="F55" s="123">
-        <v>109045720.65394828</v>
+        <v>110072098.62897746</v>
       </c>
       <c r="H55" s="120"/>
     </row>
@@ -18161,19 +18161,19 @@
         <v>30</v>
       </c>
       <c r="B56" s="123">
-        <v>50256043.298206665</v>
+        <v>50729071.452306233</v>
       </c>
       <c r="C56" s="123">
-        <v>55348677.007306211</v>
+        <v>55869638.88170734</v>
       </c>
       <c r="D56" s="123">
-        <v>68266707.290643886</v>
+        <v>68909258.36344789</v>
       </c>
       <c r="E56" s="123">
-        <v>86184764.342255801</v>
+        <v>86995966.683562607</v>
       </c>
       <c r="F56" s="123">
-        <v>127806379.06744374</v>
+        <v>129009339.18138848</v>
       </c>
       <c r="H56" s="120"/>
     </row>
@@ -18223,23 +18223,23 @@
       </c>
       <c r="B60" s="124">
         <f>C7</f>
-        <v>176.40592624772381</v>
+        <v>179.74234795392456</v>
       </c>
       <c r="C60" s="124">
         <f>C7</f>
-        <v>176.40592624772381</v>
+        <v>179.74234795392456</v>
       </c>
       <c r="D60" s="124">
         <f>C7</f>
-        <v>176.40592624772381</v>
+        <v>179.74234795392456</v>
       </c>
       <c r="E60" s="141">
         <f>C7</f>
-        <v>176.40592624772381</v>
+        <v>179.74234795392456</v>
       </c>
       <c r="F60" s="124">
         <f>C7</f>
-        <v>176.40592624772381</v>
+        <v>179.74234795392456</v>
       </c>
       <c r="H60" s="120"/>
     </row>
@@ -18250,23 +18250,23 @@
       </c>
       <c r="B61" s="124">
         <f t="shared" ref="B61:F66" si="4">B51/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>176.40592624772381</v>
+        <v>179.74234795392456</v>
       </c>
       <c r="C61" s="124">
         <f t="shared" si="4"/>
-        <v>179.18295553457676</v>
+        <v>182.57190008390697</v>
       </c>
       <c r="D61" s="124">
         <f t="shared" si="4"/>
-        <v>184.85747542155767</v>
+        <v>188.35374398049402</v>
       </c>
       <c r="E61" s="124">
         <f t="shared" si="4"/>
-        <v>190.69851150586021</v>
+        <v>194.30525344850244</v>
       </c>
       <c r="F61" s="124">
         <f t="shared" si="4"/>
-        <v>199.78825736520199</v>
+        <v>203.56691657861879</v>
       </c>
       <c r="H61" s="120"/>
     </row>
@@ -18277,23 +18277,23 @@
       </c>
       <c r="B62" s="124">
         <f t="shared" si="4"/>
-        <v>176.40592624772384</v>
+        <v>179.74234795392462</v>
       </c>
       <c r="C62" s="124">
         <f t="shared" si="4"/>
-        <v>181.8455205187166</v>
+        <v>185.28482301120783</v>
       </c>
       <c r="D62" s="124">
         <f t="shared" si="4"/>
-        <v>193.52552698017419</v>
+        <v>197.18573717069731</v>
       </c>
       <c r="E62" s="124">
         <f t="shared" si="4"/>
-        <v>206.37990551916459</v>
+        <v>210.28323468244253</v>
       </c>
       <c r="F62" s="124">
         <f t="shared" si="4"/>
-        <v>228.17501628813156</v>
+        <v>232.49056335250495</v>
       </c>
       <c r="H62" s="120"/>
     </row>
@@ -18304,23 +18304,23 @@
       </c>
       <c r="B63" s="124">
         <f t="shared" si="4"/>
-        <v>176.40592624772381</v>
+        <v>179.74234795392459</v>
       </c>
       <c r="C63" s="124">
         <f t="shared" si="4"/>
-        <v>185.13283299252473</v>
+        <v>188.63430947727335</v>
       </c>
       <c r="D63" s="124">
         <f t="shared" si="4"/>
-        <v>204.78574495437348</v>
+        <v>208.65892324900054</v>
       </c>
       <c r="E63" s="124">
         <f t="shared" si="4"/>
-        <v>227.85507017390591</v>
+        <v>232.16456599508686</v>
       </c>
       <c r="F63" s="124">
         <f t="shared" si="4"/>
-        <v>270.39257892672225</v>
+        <v>275.50660025648108</v>
       </c>
       <c r="H63" s="120"/>
     </row>
@@ -18331,23 +18331,23 @@
       </c>
       <c r="B64" s="124">
         <f t="shared" si="4"/>
-        <v>176.40592624772378</v>
+        <v>179.74234795392462</v>
       </c>
       <c r="C64" s="124">
         <f t="shared" si="4"/>
-        <v>188.47148964105025</v>
+        <v>192.03611120685491</v>
       </c>
       <c r="D64" s="124">
         <f t="shared" si="4"/>
-        <v>216.8462568878073</v>
+        <v>220.94753950216165</v>
       </c>
       <c r="E64" s="124">
         <f t="shared" si="4"/>
-        <v>252.19469878103143</v>
+        <v>256.9645377830397</v>
       </c>
       <c r="F64" s="124">
         <f t="shared" si="4"/>
-        <v>322.77095101287586</v>
+        <v>328.87562124701611</v>
       </c>
       <c r="H64" s="120"/>
     </row>
@@ -18358,23 +18358,23 @@
       </c>
       <c r="B65" s="124">
         <f t="shared" si="4"/>
-        <v>176.40592624772376</v>
+        <v>179.74234795392462</v>
       </c>
       <c r="C65" s="124">
         <f t="shared" si="4"/>
-        <v>191.56491303762817</v>
+        <v>195.18804150955754</v>
       </c>
       <c r="D65" s="124">
         <f t="shared" si="4"/>
-        <v>228.65243679899041</v>
+        <v>232.97701347018764</v>
       </c>
       <c r="E65" s="124">
         <f t="shared" si="4"/>
-        <v>277.48835900115347</v>
+        <v>282.73658508903083</v>
       </c>
       <c r="F65" s="124">
         <f t="shared" si="4"/>
-        <v>382.76613304328151</v>
+        <v>390.00551134450001</v>
       </c>
     </row>
     <row r="66" spans="1:8" ht="13.15">
@@ -18384,23 +18384,23 @@
       </c>
       <c r="B66" s="124">
         <f t="shared" si="4"/>
-        <v>176.40592624772376</v>
+        <v>179.74234795392459</v>
       </c>
       <c r="C66" s="124">
         <f t="shared" si="4"/>
-        <v>194.28180161585377</v>
+        <v>197.9563154704544</v>
       </c>
       <c r="D66" s="124">
         <f t="shared" si="4"/>
-        <v>239.62594229772961</v>
+        <v>244.15806438827795</v>
       </c>
       <c r="E66" s="124">
         <f t="shared" si="4"/>
-        <v>302.52089469168283</v>
+        <v>308.24256913368083</v>
       </c>
       <c r="F66" s="124">
         <f t="shared" si="4"/>
-        <v>448.61873717313978</v>
+        <v>457.10360683908823</v>
       </c>
     </row>
     <row r="68" spans="1:8" ht="13.15">
@@ -18435,7 +18435,7 @@
       </c>
       <c r="E69" s="135">
         <f>INDEX(B$60:F$66, MATCH(D69, A$60:A$66, 0), MATCH(C69, B$59:F$59, 0))</f>
-        <v>228.17501628813156</v>
+        <v>232.49056335250495</v>
       </c>
       <c r="F69" s="142">
         <f>Scenarios!C58</f>
@@ -18457,7 +18457,7 @@
       </c>
       <c r="E70" s="135">
         <f>INDEX(B$60:F$66, MATCH(D70, A$60:A$66, 0), MATCH(C70, B$59:F$59, 0))</f>
-        <v>190.69851150586021</v>
+        <v>194.30525344850244</v>
       </c>
       <c r="F70" s="142">
         <f>Scenarios!C40*(1-F$69-F$73)</f>
@@ -18480,7 +18480,7 @@
       </c>
       <c r="E71" s="135">
         <f>INDEX(B$60:F$66, MATCH(D71, A$60:A$66, 0), MATCH(C71, B$59:F$59, 0))</f>
-        <v>184.85747542155767</v>
+        <v>188.35374398049402</v>
       </c>
       <c r="F71" s="142">
         <f>Scenarios!C28*(1-F$69-F$73)</f>
@@ -18503,7 +18503,7 @@
       </c>
       <c r="E72" s="135">
         <f>INDEX(B$60:F$66, MATCH(D72, A$60:A$66, 0), MATCH(C72, B$59:F$59, 0))</f>
-        <v>179.18295553457676</v>
+        <v>182.57190008390697</v>
       </c>
       <c r="F72" s="142">
         <f>Scenarios!C34*(1-F$69-F$73)</f>
@@ -18526,7 +18526,7 @@
       </c>
       <c r="E73" s="135">
         <f>INDEX(B$60:F$66, MATCH(D73, A$60:A$66, 0), MATCH(C73, B$59:F$59, 0))</f>
-        <v>176.40592624772384</v>
+        <v>179.74234795392462</v>
       </c>
       <c r="F73" s="142">
         <f>Scenarios!C52</f>
@@ -18626,7 +18626,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-50.65</v>
+        <v>-47.6</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18646,7 +18646,7 @@
       </c>
       <c r="I4" s="124">
         <f t="shared" ref="I4:I13" si="0">IF(ROW()-3 &lt; $C$76, $C$77, IF(ROW()-3 = $C$76, $C$77 + $C$60, ""))</f>
-        <v>1.4730216878400002</v>
+        <v>1.4868863036000002</v>
       </c>
     </row>
     <row r="5" spans="2:9">
@@ -18655,7 +18655,7 @@
       </c>
       <c r="I5" s="124">
         <f t="shared" si="0"/>
-        <v>1.4730216878400002</v>
+        <v>1.4868863036000002</v>
       </c>
     </row>
     <row r="6" spans="2:9" ht="13.15">
@@ -18675,7 +18675,7 @@
       </c>
       <c r="I6" s="124">
         <f t="shared" si="0"/>
-        <v>34.223089312676315</v>
+        <v>34.53473431767268</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1">
@@ -18866,7 +18866,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>50.65</v>
+        <v>47.6</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -18881,7 +18881,7 @@
       </c>
       <c r="C22" s="160">
         <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
-        <v>30.869570717406862</v>
+        <v>31.149651185946471</v>
       </c>
       <c r="D22" t="str">
         <f>Market_currency</f>
@@ -18928,7 +18928,7 @@
       </c>
       <c r="C27" s="160">
         <f>IF(valuation_method="DCF",DCF!E76,DDM!E71)</f>
-        <v>32.423936416010044</v>
+        <v>32.71864713971803</v>
       </c>
       <c r="D27" s="160" t="str">
         <f>Market_currency</f>
@@ -18986,7 +18986,7 @@
       </c>
       <c r="C33" s="160">
         <f>IF(valuation_method="DCF",DCF!E77,DDM!E72)</f>
-        <v>31.380307740728544</v>
+        <v>31.665195451850668</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
@@ -19044,7 +19044,7 @@
       </c>
       <c r="C39" s="160">
         <f>IF(valuation_method="DCF",DCF!E75,DDM!E70)</f>
-        <v>33.498189898655845</v>
+        <v>33.803011886772687</v>
       </c>
       <c r="D39" t="str">
         <f>Market_currency</f>
@@ -19071,7 +19071,7 @@
       </c>
       <c r="C42" s="154">
         <f>C27*C28+C33*C34+C39*C40</f>
-        <v>32.430061377482907</v>
+        <v>32.72482975155549</v>
       </c>
       <c r="D42" t="str">
         <f>Market_currency</f>
@@ -19145,7 +19145,7 @@
       </c>
       <c r="C51" s="160">
         <f>IF(valuation_method="DCF",DCF!E78,DDM!E73)</f>
-        <v>30.869570717406869</v>
+        <v>31.149651185946482</v>
       </c>
       <c r="D51" t="str">
         <f>Market_currency</f>
@@ -19203,7 +19203,7 @@
       </c>
       <c r="C57" s="160">
         <f>IF(valuation_method="DCF",DCF!E74,DDM!E69)</f>
-        <v>40.390676984627049</v>
+        <v>40.760373567508267</v>
       </c>
       <c r="D57" t="str">
         <f>Market_currency</f>
@@ -19229,7 +19229,7 @@
       </c>
       <c r="C60" s="154">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
-        <v>32.750067624836312</v>
+        <v>33.047848014072677</v>
       </c>
       <c r="D60" t="str">
         <f>Market_currency</f>
@@ -19291,7 +19291,7 @@
       </c>
       <c r="C66" s="160">
         <f>IF(valuation_method="DCF",DCF!C18,DDM!C13)</f>
-        <v>32.094711860634071</v>
+        <v>32.386323803111118</v>
       </c>
       <c r="D66" s="160" t="str">
         <f>Market_currency</f>
@@ -19354,7 +19354,7 @@
       </c>
       <c r="F72" s="291">
         <f>BS!D89/C60</f>
-        <v>-4.8064175866584596E-2</v>
+        <v>-4.8396380126282425E-2</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="13.9">
@@ -19387,7 +19387,7 @@
       </c>
       <c r="C77" s="173">
         <f>Normalized_FCF!C90*(1-dividend_tax_rate)</f>
-        <v>1.4730216878400002</v>
+        <v>1.4868863036000002</v>
       </c>
       <c r="D77" t="str">
         <f>Market_currency</f>
@@ -19414,7 +19414,7 @@
       </c>
       <c r="C81" s="116">
         <f>PV(C80, C76, -C77, 0)</f>
-        <v>2.4411789197993943</v>
+        <v>2.4641561834770669</v>
       </c>
       <c r="D81" s="116"/>
       <c r="E81" s="100"/>
@@ -19426,7 +19426,7 @@
       </c>
       <c r="C82" s="116">
         <f>C60/(1+C80)^C76</f>
-        <v>12.809302278264093</v>
+        <v>12.925771015427101</v>
       </c>
       <c r="D82" s="116"/>
     </row>
@@ -19436,7 +19436,7 @@
       </c>
       <c r="C83" s="111">
         <f>C81+C82</f>
-        <v>15.250481198063488</v>
+        <v>15.389927198904168</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -19447,7 +19447,7 @@
       </c>
       <c r="F83" s="291">
         <f>(1-C83/C60)</f>
-        <v>0.53433741350512065</v>
+        <v>0.53431378671462304</v>
       </c>
     </row>
     <row r="84" spans="2:8">
@@ -19464,7 +19464,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>50.65</v>
+        <v>47.6</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19477,7 +19477,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>-0.10153176218238202</v>
+        <v>-7.9180969336304363E-2</v>
       </c>
     </row>
     <row r="88" spans="2:8">
@@ -19503,7 +19503,7 @@
       </c>
       <c r="C91" s="116">
         <f>PV(C90, C76, -C77, 0)</f>
-        <v>3.0202848823180561</v>
+        <v>3.0487129018949313</v>
       </c>
       <c r="D91" s="116"/>
       <c r="E91" s="100"/>
@@ -19515,7 +19515,7 @@
       </c>
       <c r="C92" s="116">
         <f>C60/(1+C90)^C76</f>
-        <v>18.151491174787974</v>
+        <v>18.316533829635802</v>
       </c>
       <c r="D92" s="116"/>
     </row>
@@ -19525,7 +19525,7 @@
       </c>
       <c r="C93" s="111">
         <f>C91+C92</f>
-        <v>21.17177605710603</v>
+        <v>21.365246731530732</v>
       </c>
       <c r="D93" t="str">
         <f>Market_currency</f>
@@ -19536,7 +19536,7 @@
       </c>
       <c r="F93" s="291">
         <f>(1-C93/C60)</f>
-        <v>0.35353489038141039</v>
+        <v>0.35350565875173401</v>
       </c>
     </row>
     <row r="95" spans="2:8" ht="13.15">
@@ -19563,7 +19563,7 @@
       </c>
       <c r="C97" s="116">
         <f>PV(C96, C76, -C77, 0)</f>
-        <v>3.8306308146175594</v>
+        <v>3.8666861047748737</v>
       </c>
       <c r="D97" s="116"/>
       <c r="G97" s="2"/>
@@ -19575,7 +19575,7 @@
       </c>
       <c r="C98" s="116">
         <f>C60/(1+C96)^C76</f>
-        <v>26.362513086766249</v>
+        <v>26.602214558474746</v>
       </c>
       <c r="D98" s="116"/>
       <c r="G98" s="2"/>
@@ -19587,7 +19587,7 @@
       </c>
       <c r="C99" s="111">
         <f>C97+C98</f>
-        <v>30.193143901383809</v>
+        <v>30.46890066324962</v>
       </c>
       <c r="D99" t="s">
         <v>393</v>
@@ -19597,7 +19597,7 @@
       </c>
       <c r="F99" s="291">
         <f>(1-C99/C60)</f>
-        <v>7.8073845609816006E-2</v>
+        <v>7.8036771100038704E-2</v>
       </c>
     </row>
     <row r="100" spans="2:8">
@@ -19623,7 +19623,7 @@
       </c>
       <c r="C103" s="116">
         <f>PV(C102, C76, -C77, 0)</f>
-        <v>3.5538167286582092</v>
+        <v>3.5872665439807236</v>
       </c>
       <c r="D103" s="116"/>
     </row>
@@ -19633,7 +19633,7 @@
       </c>
       <c r="C104" s="116">
         <f>C60/(1+C102)^C76</f>
-        <v>23.473951342039037</v>
+        <v>23.687388530860197</v>
       </c>
       <c r="D104" s="116"/>
     </row>
@@ -19643,7 +19643,7 @@
       </c>
       <c r="C105" s="111">
         <f>C103+C104</f>
-        <v>27.027768070697245</v>
+        <v>27.274655074840922</v>
       </c>
       <c r="D105" t="s">
         <v>393</v>
@@ -19653,7 +19653,7 @@
       </c>
       <c r="F105" s="291">
         <f>(1-C105/C66)</f>
-        <v>0.15787472440753425</v>
+        <v>0.15783417591159743</v>
       </c>
     </row>
     <row r="106" spans="2:8">

--- a/financial_models/opportunities/1913.HK_Valuation.xlsx
+++ b/financial_models/opportunities/1913.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CEE1C5E-2914-451F-82DC-4087CA2A7F9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F372674F-0F75-4C0D-BE94-5272F7359FA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2205" yWindow="2205" windowWidth="12690" windowHeight="7642" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3896,29 +3896,29 @@
     <xf numFmtId="10" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4336,7 +4336,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>47.6</v>
+        <v>47.5</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4357,7 +4357,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>121800.0224</v>
+        <v>121544.14</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4384,7 +4384,7 @@
         <v>1</v>
       </c>
       <c r="C16" s="50">
-        <v>9.0663799000000012</v>
+        <v>8.9955269999999992</v>
       </c>
       <c r="D16" s="50"/>
       <c r="E16" s="5"/>
@@ -4394,13 +4394,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="360" t="s">
+      <c r="B18" s="358" t="s">
         <v>356</v>
       </c>
-      <c r="C18" s="360"/>
-      <c r="D18" s="360"/>
-      <c r="E18" s="360"/>
-      <c r="F18" s="360"/>
+      <c r="C18" s="358"/>
+      <c r="D18" s="358"/>
+      <c r="E18" s="358"/>
+      <c r="F18" s="358"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4476,14 +4476,14 @@
       </c>
       <c r="C26" s="304">
         <f>C132</f>
-        <v>33.047848014072677</v>
+        <v>32.798292788076616</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>396</v>
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>-7.9180969336304363E-2</v>
+        <v>-8.0930426518360243E-2</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4515,7 +4515,7 @@
       </c>
       <c r="C29" s="310">
         <f>C149</f>
-        <v>15.389927198904168</v>
+        <v>15.273063281569726</v>
       </c>
       <c r="D29" s="310" t="str">
         <f>D149</f>
@@ -4534,7 +4534,7 @@
       </c>
       <c r="C30" s="311">
         <f>C157</f>
-        <v>21.365246731530732</v>
+        <v>21.203107126620736</v>
       </c>
       <c r="D30" s="311" t="str">
         <f>D157</f>
@@ -4553,7 +4553,7 @@
       </c>
       <c r="C31" s="311">
         <f>C165</f>
-        <v>30.46890066324962</v>
+        <v>30.237800760815819</v>
       </c>
       <c r="D31" s="311" t="str">
         <f>D165</f>
@@ -4572,7 +4572,7 @@
       </c>
       <c r="C32" s="311">
         <f>C173</f>
-        <v>27.274655074840922</v>
+        <v>27.067749624781506</v>
       </c>
       <c r="D32" s="311" t="str">
         <f>D173</f>
@@ -4600,22 +4600,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="360" t="s">
+      <c r="B36" s="358" t="s">
         <v>357</v>
       </c>
-      <c r="C36" s="360"/>
-      <c r="D36" s="360"/>
-      <c r="E36" s="360"/>
-      <c r="F36" s="360"/>
+      <c r="C36" s="358"/>
+      <c r="D36" s="358"/>
+      <c r="E36" s="358"/>
+      <c r="F36" s="358"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="363" t="s">
+      <c r="B37" s="360" t="s">
         <v>336</v>
       </c>
-      <c r="C37" s="363"/>
-      <c r="D37" s="363"/>
-      <c r="E37" s="363"/>
-      <c r="F37" s="363"/>
+      <c r="C37" s="360"/>
+      <c r="D37" s="360"/>
+      <c r="E37" s="360"/>
+      <c r="F37" s="360"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4627,13 +4627,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="361" t="s">
+      <c r="B40" s="359" t="s">
         <v>230</v>
       </c>
-      <c r="C40" s="361"/>
-      <c r="D40" s="361"/>
-      <c r="E40" s="361"/>
-      <c r="F40" s="361"/>
+      <c r="C40" s="359"/>
+      <c r="D40" s="359"/>
+      <c r="E40" s="359"/>
+      <c r="F40" s="359"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4653,13 +4653,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="361" t="s">
+      <c r="B43" s="359" t="s">
         <v>232</v>
       </c>
-      <c r="C43" s="361"/>
-      <c r="D43" s="361"/>
-      <c r="E43" s="361"/>
-      <c r="F43" s="361"/>
+      <c r="C43" s="359"/>
+      <c r="D43" s="359"/>
+      <c r="E43" s="359"/>
+      <c r="F43" s="359"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4688,13 +4688,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="361" t="s">
+      <c r="B47" s="359" t="s">
         <v>235</v>
       </c>
-      <c r="C47" s="361"/>
-      <c r="D47" s="361"/>
-      <c r="E47" s="361"/>
-      <c r="F47" s="361"/>
+      <c r="C47" s="359"/>
+      <c r="D47" s="359"/>
+      <c r="E47" s="359"/>
+      <c r="F47" s="359"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4710,13 +4710,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="361" t="s">
+      <c r="B50" s="359" t="s">
         <v>239</v>
       </c>
-      <c r="C50" s="361"/>
-      <c r="D50" s="361"/>
-      <c r="E50" s="361"/>
-      <c r="F50" s="361"/>
+      <c r="C50" s="359"/>
+      <c r="D50" s="359"/>
+      <c r="E50" s="359"/>
+      <c r="F50" s="359"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4780,13 +4780,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="361" t="s">
+      <c r="B58" s="359" t="s">
         <v>240</v>
       </c>
-      <c r="C58" s="361"/>
-      <c r="D58" s="361"/>
-      <c r="E58" s="361"/>
-      <c r="F58" s="361"/>
+      <c r="C58" s="359"/>
+      <c r="D58" s="359"/>
+      <c r="E58" s="359"/>
+      <c r="F58" s="359"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4802,7 +4802,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="361" t="s">
+      <c r="B61" s="359" t="s">
         <v>335</v>
       </c>
       <c r="C61" s="362"/>
@@ -4824,22 +4824,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="360" t="s">
+      <c r="B64" s="358" t="s">
         <v>340</v>
       </c>
-      <c r="C64" s="360"/>
-      <c r="D64" s="360"/>
-      <c r="E64" s="360"/>
-      <c r="F64" s="360"/>
+      <c r="C64" s="358"/>
+      <c r="D64" s="358"/>
+      <c r="E64" s="358"/>
+      <c r="F64" s="358"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="360" t="s">
+      <c r="B65" s="358" t="s">
         <v>358</v>
       </c>
-      <c r="C65" s="360"/>
-      <c r="D65" s="360"/>
-      <c r="E65" s="360"/>
-      <c r="F65" s="360"/>
+      <c r="C65" s="358"/>
+      <c r="D65" s="358"/>
+      <c r="E65" s="358"/>
+      <c r="F65" s="358"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4873,7 +4873,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>5.1600389812170917E-2</v>
+        <v>5.1304921101930211E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4883,14 +4883,14 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>3.1237107218487398E-2</v>
+        <v>3.1058240589473683E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>444</v>
       </c>
       <c r="F70" s="315">
         <f>Normalized_FCF!C92</f>
-        <v>5.4884756113419773</v>
+        <v>5.445583694399156</v>
       </c>
     </row>
     <row r="72" spans="1:6">
@@ -4974,22 +4974,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.6" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="360" t="s">
+      <c r="B80" s="358" t="s">
         <v>359</v>
       </c>
-      <c r="C80" s="360"/>
-      <c r="D80" s="360"/>
-      <c r="E80" s="360"/>
-      <c r="F80" s="360"/>
+      <c r="C80" s="358"/>
+      <c r="D80" s="358"/>
+      <c r="E80" s="358"/>
+      <c r="F80" s="358"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="363" t="s">
+      <c r="B81" s="360" t="s">
         <v>251</v>
       </c>
-      <c r="C81" s="363"/>
-      <c r="D81" s="363"/>
-      <c r="E81" s="363"/>
-      <c r="F81" s="363"/>
+      <c r="C81" s="360"/>
+      <c r="D81" s="360"/>
+      <c r="E81" s="360"/>
+      <c r="F81" s="360"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5033,22 +5033,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="360" t="s">
+      <c r="B89" s="358" t="s">
         <v>360</v>
       </c>
-      <c r="C89" s="360"/>
-      <c r="D89" s="360"/>
-      <c r="E89" s="360"/>
-      <c r="F89" s="360"/>
+      <c r="C89" s="358"/>
+      <c r="D89" s="358"/>
+      <c r="E89" s="358"/>
+      <c r="F89" s="358"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="360" t="s">
+      <c r="B90" s="358" t="s">
         <v>361</v>
       </c>
-      <c r="C90" s="360"/>
-      <c r="D90" s="360"/>
-      <c r="E90" s="360"/>
-      <c r="F90" s="360"/>
+      <c r="C90" s="358"/>
+      <c r="D90" s="358"/>
+      <c r="E90" s="358"/>
+      <c r="F90" s="358"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5064,7 +5064,7 @@
       </c>
       <c r="C93" s="223">
         <f>DCF!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>32.749047400791135</v>
+        <v>32.493116697889135</v>
       </c>
       <c r="D93" s="1" t="str">
         <f>Market_currency</f>
@@ -5085,13 +5085,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="360" t="s">
+      <c r="B97" s="358" t="s">
         <v>362</v>
       </c>
-      <c r="C97" s="360"/>
-      <c r="D97" s="360"/>
-      <c r="E97" s="360"/>
-      <c r="F97" s="360"/>
+      <c r="C97" s="358"/>
+      <c r="D97" s="358"/>
+      <c r="E97" s="358"/>
+      <c r="F97" s="358"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5104,13 +5104,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="360" t="s">
+      <c r="B101" s="358" t="s">
         <v>341</v>
       </c>
-      <c r="C101" s="360"/>
-      <c r="D101" s="360"/>
-      <c r="E101" s="360"/>
-      <c r="F101" s="360"/>
+      <c r="C101" s="358"/>
+      <c r="D101" s="358"/>
+      <c r="E101" s="358"/>
+      <c r="F101" s="358"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="C103" s="223">
         <f>C102*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>3.0701674610485132</v>
+        <v>3.0461743931978122</v>
       </c>
       <c r="D103" s="1" t="str">
         <f>Market_currency</f>
@@ -5180,7 +5180,7 @@
       </c>
       <c r="C109" s="349">
         <f>DCF!C8</f>
-        <v>411336.54851155588</v>
+        <v>413814.31655841379</v>
       </c>
       <c r="D109" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5193,7 +5193,7 @@
       </c>
       <c r="C110" s="223">
         <f>C109*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>1.4574403771265807</v>
+        <v>1.4547611940437319</v>
       </c>
       <c r="D110" s="1" t="str">
         <f>Market_currency</f>
@@ -5224,7 +5224,7 @@
       </c>
       <c r="C114" s="223">
         <f>C113*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>1.333086907726362E-2</v>
+        <v>1.322668959834674E-2</v>
       </c>
       <c r="D114" s="1" t="str">
         <f>Market_currency</f>
@@ -5232,13 +5232,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="360" t="s">
+      <c r="B116" s="358" t="s">
         <v>363</v>
       </c>
-      <c r="C116" s="360"/>
-      <c r="D116" s="360"/>
-      <c r="E116" s="360"/>
-      <c r="F116" s="360"/>
+      <c r="C116" s="358"/>
+      <c r="D116" s="358"/>
+      <c r="E116" s="358"/>
+      <c r="F116" s="358"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="C118" s="223">
         <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
-        <v>31.149651185946471</v>
+        <v>30.914930188333404</v>
       </c>
       <c r="D118" s="1" t="str">
         <f>Market_currency</f>
@@ -5259,7 +5259,7 @@
       </c>
       <c r="C119" s="223">
         <f>BS!D47</f>
-        <v>-5.8921637019123594</v>
+        <v>-5.8461170007857897</v>
       </c>
       <c r="D119" s="1" t="str">
         <f>Market_currency</f>
@@ -5277,13 +5277,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B123" s="361" t="s">
+      <c r="B123" s="359" t="s">
         <v>364</v>
       </c>
-      <c r="C123" s="361"/>
-      <c r="D123" s="361"/>
-      <c r="E123" s="361"/>
-      <c r="F123" s="361"/>
+      <c r="C123" s="359"/>
+      <c r="D123" s="359"/>
+      <c r="E123" s="359"/>
+      <c r="F123" s="359"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5317,7 +5317,7 @@
       </c>
       <c r="E126" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E74,DDM!E69),2)&amp;" "&amp;Market_currency</f>
-        <v>40.76 HKD</v>
+        <v>40.45 HKD</v>
       </c>
       <c r="F126" s="232">
         <f>DCF!F74</f>
@@ -5339,7 +5339,7 @@
       </c>
       <c r="E127" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E75,DDM!E70),2)&amp;" "&amp;Market_currency</f>
-        <v>33.8 HKD</v>
+        <v>33.55 HKD</v>
       </c>
       <c r="F127" s="221">
         <f>DCF!F75</f>
@@ -5361,7 +5361,7 @@
       </c>
       <c r="E128" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E76,DDM!E71),2)&amp;" "&amp;Market_currency</f>
-        <v>32.72 HKD</v>
+        <v>32.47 HKD</v>
       </c>
       <c r="F128" s="221">
         <f>DCF!F76</f>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="E129" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E77,DDM!E72),2)&amp;" "&amp;Market_currency</f>
-        <v>31.67 HKD</v>
+        <v>31.43 HKD</v>
       </c>
       <c r="F129" s="221">
         <f>DCF!F77</f>
@@ -5405,7 +5405,7 @@
       </c>
       <c r="E130" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E78,DDM!E73),2)&amp;" "&amp;Market_currency</f>
-        <v>31.15 HKD</v>
+        <v>30.91 HKD</v>
       </c>
       <c r="F130" s="221">
         <f>DCF!F78</f>
@@ -5418,7 +5418,7 @@
       </c>
       <c r="C132" s="217">
         <f>Scenarios!C60</f>
-        <v>33.047848014072677</v>
+        <v>32.798292788076616</v>
       </c>
       <c r="D132" s="212" t="str">
         <f>Market_currency</f>
@@ -5426,13 +5426,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="364" t="s">
+      <c r="B134" s="363" t="s">
         <v>367</v>
       </c>
-      <c r="C134" s="364"/>
-      <c r="D134" s="364"/>
-      <c r="E134" s="364"/>
-      <c r="F134" s="364"/>
+      <c r="C134" s="363"/>
+      <c r="D134" s="363"/>
+      <c r="E134" s="363"/>
+      <c r="F134" s="363"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5445,22 +5445,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="365" t="s">
+      <c r="B138" s="361" t="s">
         <v>365</v>
       </c>
-      <c r="C138" s="365"/>
-      <c r="D138" s="365"/>
-      <c r="E138" s="365"/>
-      <c r="F138" s="365"/>
+      <c r="C138" s="361"/>
+      <c r="D138" s="361"/>
+      <c r="E138" s="361"/>
+      <c r="F138" s="361"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="360" t="s">
+      <c r="B139" s="358" t="s">
         <v>366</v>
       </c>
-      <c r="C139" s="360"/>
-      <c r="D139" s="360"/>
-      <c r="E139" s="360"/>
-      <c r="F139" s="360"/>
+      <c r="C139" s="358"/>
+      <c r="D139" s="358"/>
+      <c r="E139" s="358"/>
+      <c r="F139" s="358"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5491,7 +5491,7 @@
       </c>
       <c r="C143" s="213">
         <f>Scenarios!C77</f>
-        <v>1.4868863036000002</v>
+        <v>1.4752664279999999</v>
       </c>
       <c r="D143" s="212" t="str">
         <f>Market_currency</f>
@@ -5527,7 +5527,7 @@
       </c>
       <c r="C147" s="216">
         <f>Scenarios!C81</f>
-        <v>2.4641561834770669</v>
+        <v>2.4448990363491063</v>
       </c>
     </row>
     <row r="148" spans="2:4">
@@ -5537,7 +5537,7 @@
       </c>
       <c r="C148" s="216">
         <f>Scenarios!C82</f>
-        <v>12.925771015427101</v>
+        <v>12.82816424522062</v>
       </c>
     </row>
     <row r="149" spans="2:4">
@@ -5546,7 +5546,7 @@
       </c>
       <c r="C149" s="215">
         <f>Scenarios!C83</f>
-        <v>15.389927198904168</v>
+        <v>15.273063281569726</v>
       </c>
       <c r="D149" s="300" t="str">
         <f>IF($D$11="","",C149*$E$25)</f>
@@ -5572,7 +5572,7 @@
       </c>
       <c r="C151" s="92">
         <f>Scenarios!F83</f>
-        <v>0.53431378671462304</v>
+        <v>0.53433358924333874</v>
       </c>
     </row>
     <row r="153" spans="2:4">
@@ -5596,7 +5596,7 @@
       </c>
       <c r="C155" s="216">
         <f>Scenarios!C91</f>
-        <v>3.0487129018949313</v>
+        <v>3.024887499391482</v>
       </c>
     </row>
     <row r="156" spans="2:4">
@@ -5606,7 +5606,7 @@
       </c>
       <c r="C156" s="216">
         <f>Scenarios!C92</f>
-        <v>18.316533829635802</v>
+        <v>18.178219627229254</v>
       </c>
     </row>
     <row r="157" spans="2:4">
@@ -5615,7 +5615,7 @@
       </c>
       <c r="C157" s="215">
         <f>Scenarios!C93</f>
-        <v>21.365246731530732</v>
+        <v>21.203107126620736</v>
       </c>
       <c r="D157" s="300" t="str">
         <f>IF($D$11="","",C157*$E$25)</f>
@@ -5641,7 +5641,7 @@
       </c>
       <c r="C159" s="92">
         <f>Scenarios!F93</f>
-        <v>0.35350565875173401</v>
+        <v>0.35353015891336748</v>
       </c>
     </row>
     <row r="161" spans="2:4">
@@ -5665,7 +5665,7 @@
       </c>
       <c r="C163" s="216">
         <f>Scenarios!C97</f>
-        <v>3.8666861047748737</v>
+        <v>3.8364683191829627</v>
       </c>
     </row>
     <row r="164" spans="2:4">
@@ -5675,7 +5675,7 @@
       </c>
       <c r="C164" s="216">
         <f>Scenarios!C98</f>
-        <v>26.602214558474746</v>
+        <v>26.401332441632857</v>
       </c>
     </row>
     <row r="165" spans="2:4">
@@ -5684,7 +5684,7 @@
       </c>
       <c r="C165" s="215">
         <f>Scenarios!C99</f>
-        <v>30.46890066324962</v>
+        <v>30.237800760815819</v>
       </c>
       <c r="D165" s="300" t="str">
         <f>IF($D$11="","",C165*$E$25)</f>
@@ -5710,7 +5710,7 @@
       </c>
       <c r="C167" s="92">
         <f>Scenarios!F99</f>
-        <v>7.8036771100038704E-2</v>
+        <v>7.8067844683416876E-2</v>
       </c>
     </row>
     <row r="169" spans="2:4">
@@ -5734,7 +5734,7 @@
       </c>
       <c r="C171" s="216">
         <f>Scenarios!C103</f>
-        <v>3.5872665439807236</v>
+        <v>3.5592323957851444</v>
       </c>
     </row>
     <row r="172" spans="2:4">
@@ -5744,7 +5744,7 @@
       </c>
       <c r="C172" s="216">
         <f>Scenarios!C104</f>
-        <v>23.687388530860197</v>
+        <v>23.508517228996361</v>
       </c>
     </row>
     <row r="173" spans="2:4">
@@ -5753,7 +5753,7 @@
       </c>
       <c r="C173" s="215">
         <f>Scenarios!C105</f>
-        <v>27.274655074840922</v>
+        <v>27.067749624781506</v>
       </c>
       <c r="D173" s="300" t="str">
         <f>IF($D$11="","",C173*$E$25)</f>
@@ -5779,7 +5779,7 @@
       </c>
       <c r="C175" s="92">
         <f>Scenarios!F105</f>
-        <v>0.15783417591159743</v>
+        <v>0.15786816121300562</v>
       </c>
     </row>
     <row r="177" spans="1:6" ht="13.9">
@@ -5793,13 +5793,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="359" t="s">
+      <c r="B179" s="365" t="s">
         <v>373</v>
       </c>
-      <c r="C179" s="360"/>
-      <c r="D179" s="360"/>
-      <c r="E179" s="360"/>
-      <c r="F179" s="360"/>
+      <c r="C179" s="358"/>
+      <c r="D179" s="358"/>
+      <c r="E179" s="358"/>
+      <c r="F179" s="358"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5836,13 +5836,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="361" t="s">
+      <c r="B188" s="359" t="s">
         <v>378</v>
       </c>
-      <c r="C188" s="361"/>
-      <c r="D188" s="361"/>
-      <c r="E188" s="361"/>
-      <c r="F188" s="361"/>
+      <c r="C188" s="359"/>
+      <c r="D188" s="359"/>
+      <c r="E188" s="359"/>
+      <c r="F188" s="359"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5850,22 +5850,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="358" t="s">
+      <c r="B191" s="364" t="s">
         <v>379</v>
       </c>
-      <c r="C191" s="358"/>
-      <c r="D191" s="358"/>
-      <c r="E191" s="358"/>
-      <c r="F191" s="358"/>
+      <c r="C191" s="364"/>
+      <c r="D191" s="364"/>
+      <c r="E191" s="364"/>
+      <c r="F191" s="364"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="358" t="s">
+      <c r="B192" s="364" t="s">
         <v>380</v>
       </c>
-      <c r="C192" s="358"/>
-      <c r="D192" s="358"/>
-      <c r="E192" s="358"/>
-      <c r="F192" s="358"/>
+      <c r="C192" s="364"/>
+      <c r="D192" s="364"/>
+      <c r="E192" s="364"/>
+      <c r="F192" s="364"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5889,6 +5889,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5905,17 +5916,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -6488,15 +6488,15 @@
       </c>
       <c r="C25" s="39">
         <f>0.164*Exchange_Rate</f>
-        <v>1.4868863036000002</v>
+        <v>1.4752664279999999</v>
       </c>
       <c r="D25" s="39">
         <f>0.137*Exchange_Rate</f>
-        <v>1.2420940463000003</v>
+        <v>1.2323871989999999</v>
       </c>
       <c r="E25" s="39">
         <f>0.11*Exchange_Rate</f>
-        <v>0.99730178900000011</v>
+        <v>0.9895079699999999</v>
       </c>
       <c r="F25" s="39"/>
       <c r="G25" s="39"/>
@@ -7870,15 +7870,15 @@
       </c>
       <c r="C65" s="73">
         <f>IF(C$4="","",C25)</f>
-        <v>1.4868863036000002</v>
+        <v>1.4752664279999999</v>
       </c>
       <c r="D65" s="73">
         <f t="shared" ref="D65:M65" si="33">IF(D$4="","",D25)</f>
-        <v>1.2420940463000003</v>
+        <v>1.2323871989999999</v>
       </c>
       <c r="E65" s="73">
         <f t="shared" si="33"/>
-        <v>0.99730178900000011</v>
+        <v>0.9895079699999999</v>
       </c>
       <c r="F65" s="73">
         <f t="shared" si="33"/>
@@ -9220,11 +9220,11 @@
       </c>
       <c r="C47" s="147">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>15.587752189585334</v>
+        <v>15.465935382955214</v>
       </c>
       <c r="D47" s="147">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>-5.8921637019123594</v>
+        <v>-5.8461170007857897</v>
       </c>
       <c r="F47" s="253"/>
     </row>
@@ -9415,7 +9415,7 @@
       </c>
       <c r="D66" s="76">
         <f>C66-D75</f>
-        <v>411336.54851155588</v>
+        <v>413814.31655841379</v>
       </c>
       <c r="F66" s="5" t="s">
         <v>225</v>
@@ -9482,11 +9482,11 @@
       </c>
       <c r="C73" s="349">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35-Normalized_FCF!G91)/12</f>
-        <v>-649883.61324358056</v>
+        <v>-647405.84519672266</v>
       </c>
       <c r="D73" s="349">
         <f>(Normalized_FCF!C25+Normalized_FCF!C35-Normalized_FCF!C91)/12</f>
-        <v>-600226.45148844412</v>
+        <v>-597748.68344158621</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>348</v>
@@ -9498,11 +9498,11 @@
       </c>
       <c r="C74" s="258">
         <f>-$C$66/C73</f>
-        <v>1.5565294760261321</v>
+        <v>1.562486665057254</v>
       </c>
       <c r="D74" s="258">
         <f>-$C$66/D73</f>
-        <v>1.6853022679882264</v>
+        <v>1.6922881271370511</v>
       </c>
       <c r="F74" s="253" t="s">
         <v>316</v>
@@ -9515,7 +9515,7 @@
       <c r="C75" s="320"/>
       <c r="D75" s="321">
         <f>MAX(-D73*D76,G5)</f>
-        <v>600226.45148844412</v>
+        <v>597748.68344158621</v>
       </c>
       <c r="F75" s="253" t="s">
         <v>349</v>
@@ -9630,11 +9630,11 @@
       </c>
       <c r="C86" s="76">
         <f>-DCF!C7*Exchange_Rate</f>
-        <v>-7856018.1833500015</v>
+        <v>-7794624.1454999996</v>
       </c>
       <c r="D86" s="223">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>-3.0701674610485132</v>
+        <v>-3.0461743931978127</v>
       </c>
       <c r="E86" s="240" t="str">
         <f>Market_currency</f>
@@ -9647,11 +9647,11 @@
       </c>
       <c r="C87" s="76">
         <f>DCF!C8*Exchange_Rate</f>
-        <v>3729333.4155605459</v>
+        <v>3722477.857587758</v>
       </c>
       <c r="D87" s="223">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>1.4574403771265807</v>
+        <v>1.4547611940437319</v>
       </c>
       <c r="E87" s="240" t="str">
         <f>Market_currency</f>
@@ -9664,11 +9664,11 @@
       </c>
       <c r="C88" s="76">
         <f>DCF!C9*Exchange_Rate</f>
-        <v>34111.347735760006</v>
+        <v>33844.770784799999</v>
       </c>
       <c r="D88" s="223">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>1.333086907726362E-2</v>
+        <v>1.322668959834674E-2</v>
       </c>
       <c r="E88" s="240" t="str">
         <f>Market_currency</f>
@@ -9681,11 +9681,11 @@
       </c>
       <c r="C89" s="180">
         <f>SUM(C86:C88)</f>
-        <v>-4092573.4200536958</v>
+        <v>-4038301.5171274417</v>
       </c>
       <c r="D89" s="242">
         <f>SUM(D86:D88)</f>
-        <v>-1.599396214844669</v>
+        <v>-1.5781865095557339</v>
       </c>
       <c r="E89" s="240" t="str">
         <f>Market_currency</f>
@@ -13197,20 +13197,20 @@
       </c>
       <c r="C90" s="113">
         <f>G90</f>
-        <v>1.4868863036000002</v>
+        <v>1.4752664279999999</v>
       </c>
       <c r="E90" s="268"/>
       <c r="G90" s="112">
         <f>Data!C65</f>
-        <v>1.4868863036000002</v>
+        <v>1.4752664279999999</v>
       </c>
       <c r="H90" s="112">
         <f>Data!D65</f>
-        <v>1.2420940463000003</v>
+        <v>1.2323871989999999</v>
       </c>
       <c r="I90" s="112">
         <f>Data!E65</f>
-        <v>0.99730178900000011</v>
+        <v>0.9895079699999999</v>
       </c>
       <c r="J90" s="112">
         <f>Data!F65</f>
@@ -13253,20 +13253,20 @@
       </c>
       <c r="C91" s="74">
         <f>C90*Common_Shares/scaling_factor</f>
-        <v>3804680.3589229668</v>
+        <v>3774947.1423606714</v>
       </c>
       <c r="E91" s="268"/>
       <c r="G91" s="74">
         <f t="shared" ref="G91:Q91" si="37">IF(G$4="","",G90*Common_Shares/scaling_factor)</f>
-        <v>3804680.3589229668</v>
+        <v>3774947.1423606714</v>
       </c>
       <c r="H91" s="74">
         <f t="shared" si="37"/>
-        <v>3178300.0559295523</v>
+        <v>3153461.9420939758</v>
       </c>
       <c r="I91" s="74">
         <f t="shared" si="37"/>
-        <v>2551919.7529361364</v>
+        <v>2531976.7418272798</v>
       </c>
       <c r="J91" s="74">
         <f t="shared" si="37"/>
@@ -13308,20 +13308,20 @@
       </c>
       <c r="C92" s="23">
         <f>C90/(C19*scaling_factor/Common_Shares)</f>
-        <v>5.4884756113419773</v>
+        <v>5.445583694399156</v>
       </c>
       <c r="E92" s="268"/>
       <c r="G92" s="170">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",G90/(G19*scaling_factor/Common_Shares))</f>
-        <v>3.8165881138381414</v>
+        <v>3.786761839299285</v>
       </c>
       <c r="H92" s="170">
         <f t="shared" si="38"/>
-        <v>3.8711839076381702</v>
+        <v>3.840930972142989</v>
       </c>
       <c r="I92" s="170">
         <f t="shared" si="38"/>
-        <v>3.7983587849277458</v>
+        <v>3.7686749708673384</v>
       </c>
       <c r="J92" s="170">
         <f t="shared" si="38"/>
@@ -13384,20 +13384,20 @@
       </c>
       <c r="C94" s="23">
         <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
-        <v>3.1237107218487398E-2</v>
+        <v>3.1058240589473683E-2</v>
       </c>
       <c r="E94" s="268"/>
       <c r="G94" s="23">
         <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>3.1237107218487398E-2</v>
+        <v>3.1058240589473683E-2</v>
       </c>
       <c r="H94" s="23">
         <f t="shared" si="39"/>
-        <v>2.6094412737394965E-2</v>
+        <v>2.5944993663157893E-2</v>
       </c>
       <c r="I94" s="23">
         <f t="shared" si="39"/>
-        <v>2.0951718256302522E-2</v>
+        <v>2.0831746736842103E-2</v>
       </c>
       <c r="J94" s="23">
         <f t="shared" si="39"/>
@@ -14526,38 +14526,38 @@
       </c>
       <c r="C125" s="177">
         <f>C16*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>2.4561785550593354</v>
+        <v>2.4369837523416855</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="265"/>
       <c r="F125" s="27"/>
       <c r="G125" s="177">
         <f t="shared" ref="G125:Q125" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>3.532127569036402</v>
+        <v>3.5045243267063309</v>
       </c>
       <c r="H125" s="177">
         <f t="shared" si="49"/>
-        <v>2.9090058142328274</v>
+        <v>2.8862722093840758</v>
       </c>
       <c r="I125" s="177">
         <f t="shared" si="49"/>
-        <v>2.3804799404160666</v>
+        <v>2.3618767152004203</v>
       </c>
       <c r="J125" s="177">
         <f t="shared" si="49"/>
-        <v>1.2768424319309966</v>
+        <v>1.2668640292892359</v>
       </c>
       <c r="K125" s="177">
         <f t="shared" si="49"/>
-        <v>6.1680496940304623</v>
+        <v>6.1198469700120048</v>
       </c>
       <c r="L125" s="177">
         <f t="shared" si="49"/>
-        <v>8.2933142135355933</v>
+        <v>8.2285027486376539</v>
       </c>
       <c r="M125" s="177">
         <f t="shared" si="49"/>
-        <v>7.6727577227156312</v>
+        <v>7.6127958480040041</v>
       </c>
       <c r="N125" s="177" t="str">
         <f t="shared" si="49"/>
@@ -14583,38 +14583,38 @@
       </c>
       <c r="C126" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>5.1600389812170917E-2</v>
+        <v>5.1304921101930211E-2</v>
       </c>
       <c r="D126" s="27"/>
       <c r="E126" s="265"/>
       <c r="F126" s="27"/>
       <c r="G126" s="77">
         <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
-        <v>7.4204360694042057E-2</v>
+        <v>7.3779459509606959E-2</v>
       </c>
       <c r="H126" s="77">
         <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
-        <v>6.1113567525899734E-2</v>
+        <v>6.0763625460717383E-2</v>
       </c>
       <c r="I126" s="77">
         <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
-        <v>5.0010082781850138E-2</v>
+        <v>4.9723720320008852E-2</v>
       </c>
       <c r="J126" s="77">
         <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
-        <v>2.6824420838886483E-2</v>
+        <v>2.6670821669247072E-2</v>
       </c>
       <c r="K126" s="77">
         <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
-        <v>0.12958087592500972</v>
+        <v>0.12883888357920009</v>
       </c>
       <c r="L126" s="77">
         <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
-        <v>0.1742292902003276</v>
+        <v>0.17323163681342429</v>
       </c>
       <c r="M126" s="77">
         <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
-        <v>0.16119238913268133</v>
+        <v>0.16026938627376849</v>
       </c>
       <c r="N126" s="77" t="str">
         <f t="shared" ref="N126" si="57">IF(N$4="","",N125/Market_Price)</f>
@@ -14640,31 +14640,31 @@
       <c r="C127" s="169"/>
       <c r="G127" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.9244650647946023E-3</v>
+        <v>6.9390428859836435E-3</v>
       </c>
       <c r="H127" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.528668933972216E-3</v>
+        <v>5.5403082369911046E-3</v>
       </c>
       <c r="I127" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.8518465822548159E-3</v>
+        <v>3.8599557329542997E-3</v>
       </c>
       <c r="J127" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.422848487095188E-3</v>
+        <v>2.4279492207522303E-3</v>
       </c>
       <c r="K127" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-4.463710180729819E-4</v>
+        <v>-4.4731074653208292E-4</v>
       </c>
       <c r="L127" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.1159602019908989E-3</v>
+        <v>2.1204148550477216E-3</v>
       </c>
       <c r="M127" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.7092115083223499E-3</v>
+        <v>1.7128098483398706E-3</v>
       </c>
       <c r="N127" s="23" t="str">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -15492,7 +15492,7 @@
       </c>
       <c r="C8" s="338">
         <f>BS!D66</f>
-        <v>411336.54851155588</v>
+        <v>413814.31655841379</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
@@ -15524,7 +15524,7 @@
       </c>
       <c r="C10" s="347">
         <f>C6-C7+C8+C9</f>
-        <v>8791433.3973836992</v>
+        <v>8793911.165430557</v>
       </c>
       <c r="D10" t="str">
         <f>Reporting_currency</f>
@@ -15538,7 +15538,7 @@
       </c>
       <c r="C11" s="208">
         <f>Exchange_Rate</f>
-        <v>9.0663799000000012</v>
+        <v>8.9955269999999992</v>
       </c>
       <c r="D11" t="str">
         <f>Thesis!C15</f>
@@ -15552,7 +15552,7 @@
       </c>
       <c r="C12" s="111">
         <f>(C10*scaling_factor)/Common_Shares*Exchange_Rate</f>
-        <v>31.149651185946471</v>
+        <v>30.914930188333404</v>
       </c>
       <c r="D12" t="str">
         <f>Market_currency</f>
@@ -15605,7 +15605,7 @@
       </c>
       <c r="C18" s="140">
         <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>32.386323803111118</v>
+        <v>32.141938326153131</v>
       </c>
       <c r="D18" t="str">
         <f>Market_currency</f>
@@ -16701,23 +16701,23 @@
       </c>
       <c r="B65" s="124">
         <f>C12</f>
-        <v>31.149651185946471</v>
+        <v>30.914930188333404</v>
       </c>
       <c r="C65" s="124">
         <f>C12</f>
-        <v>31.149651185946471</v>
+        <v>30.914930188333404</v>
       </c>
       <c r="D65" s="124">
         <f>C12</f>
-        <v>31.149651185946471</v>
+        <v>30.914930188333404</v>
       </c>
       <c r="E65" s="141">
         <f>C12</f>
-        <v>31.149651185946471</v>
+        <v>30.914930188333404</v>
       </c>
       <c r="F65" s="124">
         <f>C12</f>
-        <v>31.149651185946471</v>
+        <v>30.914930188333404</v>
       </c>
       <c r="H65" s="120"/>
     </row>
@@ -16728,23 +16728,23 @@
       </c>
       <c r="B66" s="124">
         <f t="shared" ref="B66:F71" si="4">(B56-$C$7+$C$8+$C$9)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>31.149651185946471</v>
+        <v>30.914930188333404</v>
       </c>
       <c r="C66" s="124">
         <f t="shared" si="4"/>
-        <v>31.665195451850668</v>
+        <v>31.426445524640503</v>
       </c>
       <c r="D66" s="124">
         <f t="shared" si="4"/>
-        <v>32.71864713971803</v>
+        <v>32.471664587367663</v>
       </c>
       <c r="E66" s="124">
         <f t="shared" si="4"/>
-        <v>33.803011886772687</v>
+        <v>33.54755512665318</v>
       </c>
       <c r="F66" s="124">
         <f t="shared" si="4"/>
-        <v>35.490486476434164</v>
+        <v>35.221842262262143</v>
       </c>
       <c r="H66" s="120"/>
     </row>
@@ -16755,23 +16755,23 @@
       </c>
       <c r="B67" s="124">
         <f t="shared" si="4"/>
-        <v>31.149651185946482</v>
+        <v>30.914930188333415</v>
       </c>
       <c r="C67" s="124">
         <f t="shared" si="4"/>
-        <v>32.159489882474467</v>
+        <v>31.916877091116778</v>
       </c>
       <c r="D67" s="124">
         <f t="shared" si="4"/>
-        <v>34.327835886398788</v>
+        <v>34.068277676442278</v>
       </c>
       <c r="E67" s="124">
         <f t="shared" si="4"/>
-        <v>36.714199321207381</v>
+        <v>36.435991907083931</v>
       </c>
       <c r="F67" s="124">
         <f t="shared" si="4"/>
-        <v>40.760373567508267</v>
+        <v>40.450545684970969</v>
       </c>
       <c r="H67" s="120"/>
     </row>
@@ -16782,23 +16782,23 @@
       </c>
       <c r="B68" s="124">
         <f t="shared" si="4"/>
-        <v>31.149651185946482</v>
+        <v>30.914930188333415</v>
       </c>
       <c r="C68" s="124">
         <f t="shared" si="4"/>
-        <v>32.769766160124995</v>
+        <v>32.522384117473003</v>
       </c>
       <c r="D68" s="124">
         <f t="shared" si="4"/>
-        <v>36.418249853911703</v>
+        <v>36.142355256837888</v>
       </c>
       <c r="E68" s="124">
         <f t="shared" si="4"/>
-        <v>40.700976864215214</v>
+        <v>40.391613161287104</v>
       </c>
       <c r="F68" s="124">
         <f t="shared" si="4"/>
-        <v>48.597893481978346</v>
+        <v>48.22681612380989</v>
       </c>
       <c r="H68" s="120"/>
     </row>
@@ -16809,23 +16809,23 @@
       </c>
       <c r="B69" s="124">
         <f t="shared" si="4"/>
-        <v>31.149651185946485</v>
+        <v>30.914930188333422</v>
       </c>
       <c r="C69" s="124">
         <f t="shared" si="4"/>
-        <v>33.38957427634432</v>
+        <v>33.137348491982614</v>
       </c>
       <c r="D69" s="124">
         <f t="shared" si="4"/>
-        <v>38.65723516119202</v>
+        <v>38.363843106055803</v>
       </c>
       <c r="E69" s="124">
         <f t="shared" si="4"/>
-        <v>45.219530565484014</v>
+        <v>44.87485479345316</v>
       </c>
       <c r="F69" s="124">
         <f t="shared" si="4"/>
-        <v>58.321726613394212</v>
+        <v>57.87465842050716</v>
       </c>
       <c r="H69" s="120"/>
     </row>
@@ -16836,23 +16836,23 @@
       </c>
       <c r="B70" s="124">
         <f t="shared" si="4"/>
-        <v>31.149651185946485</v>
+        <v>30.914930188333422</v>
       </c>
       <c r="C70" s="124">
         <f t="shared" si="4"/>
-        <v>33.963855830258701</v>
+        <v>33.707142089958673</v>
       </c>
       <c r="D70" s="124">
         <f t="shared" si="4"/>
-        <v>40.849004756226215</v>
+        <v>40.53848422934572</v>
       </c>
       <c r="E70" s="124">
         <f t="shared" si="4"/>
-        <v>49.915196380730237</v>
+        <v>49.533824425204898</v>
       </c>
       <c r="F70" s="124">
         <f t="shared" si="4"/>
-        <v>69.459589733557962</v>
+        <v>68.925480195550691</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="13.15">
@@ -16862,23 +16862,23 @@
       </c>
       <c r="B71" s="124">
         <f t="shared" si="4"/>
-        <v>31.149651185946482</v>
+        <v>30.914930188333415</v>
       </c>
       <c r="C71" s="124">
         <f t="shared" si="4"/>
-        <v>34.468235216618041</v>
+        <v>34.207579799196822</v>
       </c>
       <c r="D71" s="124">
         <f t="shared" si="4"/>
-        <v>42.886191711195025</v>
+        <v>42.559750761257717</v>
       </c>
       <c r="E71" s="124">
         <f t="shared" si="4"/>
-        <v>54.562385482188887</v>
+        <v>54.144696184094805</v>
       </c>
       <c r="F71" s="124">
         <f t="shared" si="4"/>
-        <v>81.684859598277669</v>
+        <v>81.055210734458797</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="13.15">
@@ -16913,7 +16913,7 @@
       </c>
       <c r="E74" s="135">
         <f>INDEX(B$65:F$71, MATCH(D74, A$65:A$71, 0), MATCH(C74, B$64:F$64, 0))</f>
-        <v>40.760373567508267</v>
+        <v>40.450545684970969</v>
       </c>
       <c r="F74" s="142">
         <f>Scenarios!C58</f>
@@ -16935,7 +16935,7 @@
       </c>
       <c r="E75" s="135">
         <f>INDEX(B$65:F$71, MATCH(D75, A$65:A$71, 0), MATCH(C75, B$64:F$64, 0))</f>
-        <v>33.803011886772687</v>
+        <v>33.54755512665318</v>
       </c>
       <c r="F75" s="142">
         <f>Scenarios!C40*(1-F$74-F$78)</f>
@@ -16958,7 +16958,7 @@
       </c>
       <c r="E76" s="135">
         <f>INDEX(B$65:F$71, MATCH(D76, A$65:A$71, 0), MATCH(C76, B$64:F$64, 0))</f>
-        <v>32.71864713971803</v>
+        <v>32.471664587367663</v>
       </c>
       <c r="F76" s="142">
         <f>Scenarios!C28*(1-F$74-F$78)</f>
@@ -16981,7 +16981,7 @@
       </c>
       <c r="E77" s="135">
         <f>INDEX(B$65:F$71, MATCH(D77, A$65:A$71, 0), MATCH(C77, B$64:F$64, 0))</f>
-        <v>31.665195451850668</v>
+        <v>31.426445524640503</v>
       </c>
       <c r="F77" s="142">
         <f>Scenarios!C34*(1-F$74-F$78)</f>
@@ -17004,7 +17004,7 @@
       </c>
       <c r="E78" s="135">
         <f>INDEX(B$65:F$71, MATCH(D78, A$65:A$71, 0), MATCH(C78, B$64:F$64, 0))</f>
-        <v>31.149651185946482</v>
+        <v>30.914930188333415</v>
       </c>
       <c r="F78" s="142">
         <f>Scenarios!C52</f>
@@ -17186,7 +17186,7 @@
       </c>
       <c r="C4" s="114">
         <f>Normalized_FCF!C91*(1-dividend_tax_rate)</f>
-        <v>3804680.3589229668</v>
+        <v>3774947.1423606714</v>
       </c>
       <c r="D4" t="str">
         <f>Market_currency</f>
@@ -17218,7 +17218,7 @@
       </c>
       <c r="C6" s="319">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
-        <v>50729071.452306226</v>
+        <v>50332628.564808957</v>
       </c>
       <c r="D6" t="str">
         <f>Reporting_currency</f>
@@ -17234,7 +17234,7 @@
       </c>
       <c r="C7" s="111">
         <f>(C6*scaling_factor)/Common_Shares*Exchange_Rate</f>
-        <v>179.74234795392456</v>
+        <v>176.94398647023405</v>
       </c>
       <c r="D7" t="str">
         <f>Market_currency</f>
@@ -17287,7 +17287,7 @@
       </c>
       <c r="C13" s="140">
         <f>F47/Common_Shares*scaling_factor</f>
-        <v>20.573789926059366</v>
+        <v>20.413007706879238</v>
       </c>
       <c r="D13" t="str">
         <f>Market_currency</f>
@@ -17322,7 +17322,7 @@
       </c>
       <c r="C16" s="123">
         <f>C4*(1+D16)</f>
-        <v>3895051.4830288892</v>
+        <v>3864612.024693164</v>
       </c>
       <c r="D16" s="138">
         <f>IF($C$12&lt;B16,0,DDM!$C$11)</f>
@@ -17334,7 +17334,7 @@
       </c>
       <c r="F16" s="125">
         <f t="shared" ref="F16:F46" si="1">C16*E16</f>
-        <v>3623303.7051431527</v>
+        <v>3594987.9299471295</v>
       </c>
       <c r="H16" s="120"/>
     </row>
@@ -17344,7 +17344,7 @@
       </c>
       <c r="C17" s="123">
         <f t="shared" ref="C17:C45" si="2">IF(ROW()-ROW($C$16)&lt;$C$12, $C$16*(1+D17)^(ROW()-ROW($C$16)), 0)</f>
-        <v>3987569.1580409906</v>
+        <v>3956406.6828398607</v>
       </c>
       <c r="D17" s="138">
         <f>IF($C$12&lt;B17,0,DDM!$C$11)</f>
@@ -17356,7 +17356,7 @@
       </c>
       <c r="F17" s="125">
         <f t="shared" si="1"/>
-        <v>3450573.6359467739</v>
+        <v>3423607.7298776512</v>
       </c>
       <c r="H17" s="120"/>
     </row>
@@ -17366,7 +17366,7 @@
       </c>
       <c r="C18" s="123">
         <f t="shared" si="2"/>
-        <v>4082284.3701657439</v>
+        <v>4050381.7045548614</v>
       </c>
       <c r="D18" s="138">
         <f>IF($C$12&lt;B18,0,DDM!$C$11)</f>
@@ -17378,7 +17378,7 @@
       </c>
       <c r="F18" s="125">
         <f t="shared" si="1"/>
-        <v>3286077.9515087684</v>
+        <v>3260397.5636297581</v>
       </c>
       <c r="H18" s="120"/>
     </row>
@@ -17388,7 +17388,7 @@
       </c>
       <c r="C19" s="123">
         <f t="shared" si="2"/>
-        <v>4179249.3166655726</v>
+        <v>4146588.8791839289</v>
       </c>
       <c r="D19" s="138">
         <f>IF($C$12&lt;B19,0,DDM!$C$11)</f>
@@ -17400,7 +17400,7 @@
       </c>
       <c r="F19" s="125">
         <f t="shared" si="1"/>
-        <v>3129424.1023867335</v>
+        <v>3104967.9494977505</v>
       </c>
       <c r="H19" s="120"/>
     </row>
@@ -17410,7 +17410,7 @@
       </c>
       <c r="C20" s="123">
         <f t="shared" si="2"/>
-        <v>4278517.4346246039</v>
+        <v>4245081.2262054402</v>
       </c>
       <c r="D20" s="138">
         <f>IF($C$12&lt;B20,0,DDM!$C$11)</f>
@@ -17422,7 +17422,7 @@
       </c>
       <c r="F20" s="125">
         <f t="shared" si="1"/>
-        <v>2980238.2527482416</v>
+        <v>2956947.9731408157</v>
       </c>
       <c r="H20" s="120"/>
     </row>
@@ -17982,7 +17982,7 @@
       </c>
       <c r="C46" s="123">
         <f>C$16*(1+F4)^$C$12/Equity_Cost</f>
-        <v>51934019.773718521</v>
+        <v>51528160.329242192</v>
       </c>
       <c r="D46" s="139">
         <f>Terminal_Growth</f>
@@ -17994,7 +17994,7 @@
       </c>
       <c r="F46" s="125">
         <f t="shared" si="1"/>
-        <v>36175089.786025263</v>
+        <v>35892384.886454456</v>
       </c>
       <c r="H46" s="120"/>
     </row>
@@ -18005,7 +18005,7 @@
       </c>
       <c r="F47" s="137">
         <f>SUM(F16:F46)</f>
-        <v>52644707.433758929</v>
+        <v>52233294.032547563</v>
       </c>
       <c r="H47" s="120"/>
     </row>
@@ -18026,7 +18026,7 @@
     <row r="50" spans="1:8" ht="13.15">
       <c r="A50" s="133">
         <f>F47</f>
-        <v>52644707.433758929</v>
+        <v>52233294.032547563</v>
       </c>
       <c r="B50" s="131">
         <f>C73</f>
@@ -18056,19 +18056,19 @@
       </c>
       <c r="B51" s="123">
         <f t="dataTable" ref="B51:F56" dt2D="1" dtr="1" r1="C11" r2="C12"/>
-        <v>50729071.452306226</v>
+        <v>50332628.564808957</v>
       </c>
       <c r="C51" s="123">
-        <v>51527662.067227416</v>
+        <v>51124978.269730337</v>
       </c>
       <c r="D51" s="123">
-        <v>53159484.370067433</v>
+        <v>52744048.035867043</v>
       </c>
       <c r="E51" s="123">
-        <v>54839191.753933758</v>
+        <v>54410628.665658325</v>
       </c>
       <c r="F51" s="123">
-        <v>57453130.962156966</v>
+        <v>57004140.186605111</v>
       </c>
       <c r="H51" s="120"/>
     </row>
@@ -18077,19 +18077,19 @@
         <v>10</v>
       </c>
       <c r="B52" s="123">
-        <v>50729071.452306241</v>
+        <v>50332628.564808965</v>
       </c>
       <c r="C52" s="123">
-        <v>52293336.170132339</v>
+        <v>51884668.702058464</v>
       </c>
       <c r="D52" s="123">
-        <v>55652156.902235284</v>
+        <v>55217240.568343468</v>
       </c>
       <c r="E52" s="123">
-        <v>59348691.940767482</v>
+        <v>58884887.535746887</v>
       </c>
       <c r="F52" s="123">
-        <v>65616314.321872845</v>
+        <v>65103529.041717485</v>
       </c>
       <c r="H52" s="120"/>
     </row>
@@ -18098,19 +18098,19 @@
         <v>15</v>
       </c>
       <c r="B53" s="123">
-        <v>50729071.452306233</v>
+        <v>50332628.564808965</v>
       </c>
       <c r="C53" s="123">
-        <v>53238668.976784706</v>
+        <v>52822613.822384506</v>
       </c>
       <c r="D53" s="123">
-        <v>58890259.013269499</v>
+        <v>58430037.218146905</v>
       </c>
       <c r="E53" s="123">
-        <v>65524307.382907271</v>
+        <v>65012241.128263503</v>
       </c>
       <c r="F53" s="123">
-        <v>77756823.414678425</v>
+        <v>77149161.206114009</v>
       </c>
       <c r="H53" s="120"/>
     </row>
@@ -18119,19 +18119,19 @@
         <v>20</v>
       </c>
       <c r="B54" s="123">
-        <v>50729071.452306241</v>
+        <v>50332628.564808972</v>
       </c>
       <c r="C54" s="123">
-        <v>54198766.833360828</v>
+        <v>53775208.605167955</v>
       </c>
       <c r="D54" s="123">
-        <v>62358501.745451801</v>
+        <v>61871175.96194692</v>
       </c>
       <c r="E54" s="123">
-        <v>72523657.036271855</v>
+        <v>71956891.527182013</v>
       </c>
       <c r="F54" s="123">
-        <v>92819277.588596806</v>
+        <v>92093903.727629751</v>
       </c>
       <c r="H54" s="120"/>
     </row>
@@ -18140,19 +18140,19 @@
         <v>25</v>
       </c>
       <c r="B55" s="123">
-        <v>50729071.452306241</v>
+        <v>50332628.564808972</v>
       </c>
       <c r="C55" s="123">
-        <v>55088342.936925903</v>
+        <v>54657832.755759142</v>
       </c>
       <c r="D55" s="123">
-        <v>65753606.190254539</v>
+        <v>65239747.987154357</v>
       </c>
       <c r="E55" s="123">
-        <v>79797357.664645627</v>
+        <v>79173748.8742311</v>
       </c>
       <c r="F55" s="123">
-        <v>110072098.62897746</v>
+        <v>109211895.60605437</v>
       </c>
       <c r="H55" s="120"/>
     </row>
@@ -18161,19 +18161,19 @@
         <v>30</v>
       </c>
       <c r="B56" s="123">
-        <v>50729071.452306233</v>
+        <v>50332628.564808972</v>
       </c>
       <c r="C56" s="123">
-        <v>55869638.88170734</v>
+        <v>55433022.946749471</v>
       </c>
       <c r="D56" s="123">
-        <v>68909258.36344789</v>
+        <v>68370739.037570134</v>
       </c>
       <c r="E56" s="123">
-        <v>86995966.683562607</v>
+        <v>86316101.44563736</v>
       </c>
       <c r="F56" s="123">
-        <v>129009339.18138848</v>
+        <v>128001143.4175991</v>
       </c>
       <c r="H56" s="120"/>
     </row>
@@ -18223,23 +18223,23 @@
       </c>
       <c r="B60" s="124">
         <f>C7</f>
-        <v>179.74234795392456</v>
+        <v>176.94398647023405</v>
       </c>
       <c r="C60" s="124">
         <f>C7</f>
-        <v>179.74234795392456</v>
+        <v>176.94398647023405</v>
       </c>
       <c r="D60" s="124">
         <f>C7</f>
-        <v>179.74234795392456</v>
+        <v>176.94398647023405</v>
       </c>
       <c r="E60" s="141">
         <f>C7</f>
-        <v>179.74234795392456</v>
+        <v>176.94398647023405</v>
       </c>
       <c r="F60" s="124">
         <f>C7</f>
-        <v>179.74234795392456</v>
+        <v>176.94398647023405</v>
       </c>
       <c r="H60" s="120"/>
     </row>
@@ -18250,23 +18250,23 @@
       </c>
       <c r="B61" s="124">
         <f t="shared" ref="B61:F66" si="4">B51/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>179.74234795392456</v>
+        <v>176.94398647023405</v>
       </c>
       <c r="C61" s="124">
         <f t="shared" si="4"/>
-        <v>182.57190008390697</v>
+        <v>179.72948604506308</v>
       </c>
       <c r="D61" s="124">
         <f t="shared" si="4"/>
-        <v>188.35374398049402</v>
+        <v>185.42131393012528</v>
       </c>
       <c r="E61" s="124">
         <f t="shared" si="4"/>
-        <v>194.30525344850244</v>
+        <v>191.28016590781681</v>
       </c>
       <c r="F61" s="124">
         <f t="shared" si="4"/>
-        <v>203.56691657861879</v>
+        <v>200.39763663323123</v>
       </c>
       <c r="H61" s="120"/>
     </row>
@@ -18277,23 +18277,23 @@
       </c>
       <c r="B62" s="124">
         <f t="shared" si="4"/>
-        <v>179.74234795392462</v>
+        <v>176.94398647023408</v>
       </c>
       <c r="C62" s="124">
         <f t="shared" si="4"/>
-        <v>185.28482301120783</v>
+        <v>182.40017218668493</v>
       </c>
       <c r="D62" s="124">
         <f t="shared" si="4"/>
-        <v>197.18573717069731</v>
+        <v>194.11580413425423</v>
       </c>
       <c r="E62" s="124">
         <f t="shared" si="4"/>
-        <v>210.28323468244253</v>
+        <v>207.00939014163325</v>
       </c>
       <c r="F62" s="124">
         <f t="shared" si="4"/>
-        <v>232.49056335250495</v>
+        <v>228.87097873478353</v>
       </c>
       <c r="H62" s="120"/>
     </row>
@@ -18304,23 +18304,23 @@
       </c>
       <c r="B63" s="124">
         <f t="shared" si="4"/>
-        <v>179.74234795392459</v>
+        <v>176.94398647023408</v>
       </c>
       <c r="C63" s="124">
         <f t="shared" si="4"/>
-        <v>188.63430947727335</v>
+        <v>185.69751137625451</v>
       </c>
       <c r="D63" s="124">
         <f t="shared" si="4"/>
-        <v>208.65892324900054</v>
+        <v>205.41036718697549</v>
       </c>
       <c r="E63" s="124">
         <f t="shared" si="4"/>
-        <v>232.16456599508686</v>
+        <v>228.55005674474086</v>
       </c>
       <c r="F63" s="124">
         <f t="shared" si="4"/>
-        <v>275.50660025648108</v>
+        <v>271.21731023976292</v>
       </c>
       <c r="H63" s="120"/>
     </row>
@@ -18331,23 +18331,23 @@
       </c>
       <c r="B64" s="124">
         <f t="shared" si="4"/>
-        <v>179.74234795392462</v>
+        <v>176.94398647023411</v>
       </c>
       <c r="C64" s="124">
         <f t="shared" si="4"/>
-        <v>192.03611120685491</v>
+        <v>189.04635134672046</v>
       </c>
       <c r="D64" s="124">
         <f t="shared" si="4"/>
-        <v>220.94753950216165</v>
+        <v>217.50766519598238</v>
       </c>
       <c r="E64" s="124">
         <f t="shared" si="4"/>
-        <v>256.9645377830397</v>
+        <v>252.96392427491574</v>
       </c>
       <c r="F64" s="124">
         <f t="shared" si="4"/>
-        <v>328.87562124701611</v>
+        <v>323.75544293679201</v>
       </c>
       <c r="H64" s="120"/>
     </row>
@@ -18358,23 +18358,23 @@
       </c>
       <c r="B65" s="124">
         <f t="shared" si="4"/>
-        <v>179.74234795392462</v>
+        <v>176.94398647023411</v>
       </c>
       <c r="C65" s="124">
         <f t="shared" si="4"/>
-        <v>195.18804150955754</v>
+        <v>192.1492100730319</v>
       </c>
       <c r="D65" s="124">
         <f t="shared" si="4"/>
-        <v>232.97701347018764</v>
+        <v>229.3498554381398</v>
       </c>
       <c r="E65" s="124">
         <f t="shared" si="4"/>
-        <v>282.73658508903083</v>
+        <v>278.33473333428384</v>
       </c>
       <c r="F65" s="124">
         <f t="shared" si="4"/>
-        <v>390.00551134450001</v>
+        <v>383.9336178046803</v>
       </c>
     </row>
     <row r="66" spans="1:8" ht="13.15">
@@ -18384,23 +18384,23 @@
       </c>
       <c r="B66" s="124">
         <f t="shared" si="4"/>
-        <v>179.74234795392459</v>
+        <v>176.94398647023411</v>
       </c>
       <c r="C66" s="124">
         <f t="shared" si="4"/>
-        <v>197.9563154704544</v>
+        <v>194.87438550252162</v>
       </c>
       <c r="D66" s="124">
         <f t="shared" si="4"/>
-        <v>244.15806438827795</v>
+        <v>240.3568315063545</v>
       </c>
       <c r="E66" s="124">
         <f t="shared" si="4"/>
-        <v>308.24256913368083</v>
+        <v>303.44362140146012</v>
       </c>
       <c r="F66" s="124">
         <f t="shared" si="4"/>
-        <v>457.10360683908823</v>
+        <v>449.98708064481372</v>
       </c>
     </row>
     <row r="68" spans="1:8" ht="13.15">
@@ -18435,7 +18435,7 @@
       </c>
       <c r="E69" s="135">
         <f>INDEX(B$60:F$66, MATCH(D69, A$60:A$66, 0), MATCH(C69, B$59:F$59, 0))</f>
-        <v>232.49056335250495</v>
+        <v>228.87097873478353</v>
       </c>
       <c r="F69" s="142">
         <f>Scenarios!C58</f>
@@ -18457,7 +18457,7 @@
       </c>
       <c r="E70" s="135">
         <f>INDEX(B$60:F$66, MATCH(D70, A$60:A$66, 0), MATCH(C70, B$59:F$59, 0))</f>
-        <v>194.30525344850244</v>
+        <v>191.28016590781681</v>
       </c>
       <c r="F70" s="142">
         <f>Scenarios!C40*(1-F$69-F$73)</f>
@@ -18480,7 +18480,7 @@
       </c>
       <c r="E71" s="135">
         <f>INDEX(B$60:F$66, MATCH(D71, A$60:A$66, 0), MATCH(C71, B$59:F$59, 0))</f>
-        <v>188.35374398049402</v>
+        <v>185.42131393012528</v>
       </c>
       <c r="F71" s="142">
         <f>Scenarios!C28*(1-F$69-F$73)</f>
@@ -18503,7 +18503,7 @@
       </c>
       <c r="E72" s="135">
         <f>INDEX(B$60:F$66, MATCH(D72, A$60:A$66, 0), MATCH(C72, B$59:F$59, 0))</f>
-        <v>182.57190008390697</v>
+        <v>179.72948604506308</v>
       </c>
       <c r="F72" s="142">
         <f>Scenarios!C34*(1-F$69-F$73)</f>
@@ -18526,7 +18526,7 @@
       </c>
       <c r="E73" s="135">
         <f>INDEX(B$60:F$66, MATCH(D73, A$60:A$66, 0), MATCH(C73, B$59:F$59, 0))</f>
-        <v>179.74234795392462</v>
+        <v>176.94398647023408</v>
       </c>
       <c r="F73" s="142">
         <f>Scenarios!C52</f>
@@ -18626,7 +18626,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-47.6</v>
+        <v>-47.5</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18646,7 +18646,7 @@
       </c>
       <c r="I4" s="124">
         <f t="shared" ref="I4:I13" si="0">IF(ROW()-3 &lt; $C$76, $C$77, IF(ROW()-3 = $C$76, $C$77 + $C$60, ""))</f>
-        <v>1.4868863036000002</v>
+        <v>1.4752664279999999</v>
       </c>
     </row>
     <row r="5" spans="2:9">
@@ -18655,7 +18655,7 @@
       </c>
       <c r="I5" s="124">
         <f t="shared" si="0"/>
-        <v>1.4868863036000002</v>
+        <v>1.4752664279999999</v>
       </c>
     </row>
     <row r="6" spans="2:9" ht="13.15">
@@ -18675,7 +18675,7 @@
       </c>
       <c r="I6" s="124">
         <f t="shared" si="0"/>
-        <v>34.53473431767268</v>
+        <v>34.273559216076613</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1">
@@ -18866,7 +18866,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>47.6</v>
+        <v>47.5</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -18881,7 +18881,7 @@
       </c>
       <c r="C22" s="160">
         <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
-        <v>31.149651185946471</v>
+        <v>30.914930188333404</v>
       </c>
       <c r="D22" t="str">
         <f>Market_currency</f>
@@ -18928,7 +18928,7 @@
       </c>
       <c r="C27" s="160">
         <f>IF(valuation_method="DCF",DCF!E76,DDM!E71)</f>
-        <v>32.71864713971803</v>
+        <v>32.471664587367663</v>
       </c>
       <c r="D27" s="160" t="str">
         <f>Market_currency</f>
@@ -18986,7 +18986,7 @@
       </c>
       <c r="C33" s="160">
         <f>IF(valuation_method="DCF",DCF!E77,DDM!E72)</f>
-        <v>31.665195451850668</v>
+        <v>31.426445524640503</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
@@ -19044,7 +19044,7 @@
       </c>
       <c r="C39" s="160">
         <f>IF(valuation_method="DCF",DCF!E75,DDM!E70)</f>
-        <v>33.803011886772687</v>
+        <v>33.54755512665318</v>
       </c>
       <c r="D39" t="str">
         <f>Market_currency</f>
@@ -19071,7 +19071,7 @@
       </c>
       <c r="C42" s="154">
         <f>C27*C28+C33*C34+C39*C40</f>
-        <v>32.72482975155549</v>
+        <v>32.47779888267933</v>
       </c>
       <c r="D42" t="str">
         <f>Market_currency</f>
@@ -19145,7 +19145,7 @@
       </c>
       <c r="C51" s="160">
         <f>IF(valuation_method="DCF",DCF!E78,DDM!E73)</f>
-        <v>31.149651185946482</v>
+        <v>30.914930188333415</v>
       </c>
       <c r="D51" t="str">
         <f>Market_currency</f>
@@ -19203,7 +19203,7 @@
       </c>
       <c r="C57" s="160">
         <f>IF(valuation_method="DCF",DCF!E74,DDM!E69)</f>
-        <v>40.760373567508267</v>
+        <v>40.450545684970969</v>
       </c>
       <c r="D57" t="str">
         <f>Market_currency</f>
@@ -19229,7 +19229,7 @@
       </c>
       <c r="C60" s="154">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
-        <v>33.047848014072677</v>
+        <v>32.798292788076616</v>
       </c>
       <c r="D60" t="str">
         <f>Market_currency</f>
@@ -19291,7 +19291,7 @@
       </c>
       <c r="C66" s="160">
         <f>IF(valuation_method="DCF",DCF!C18,DDM!C13)</f>
-        <v>32.386323803111118</v>
+        <v>32.141938326153131</v>
       </c>
       <c r="D66" s="160" t="str">
         <f>Market_currency</f>
@@ -19354,7 +19354,7 @@
       </c>
       <c r="F72" s="291">
         <f>BS!D89/C60</f>
-        <v>-4.8396380126282425E-2</v>
+        <v>-4.8117946862449579E-2</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="13.9">
@@ -19387,7 +19387,7 @@
       </c>
       <c r="C77" s="173">
         <f>Normalized_FCF!C90*(1-dividend_tax_rate)</f>
-        <v>1.4868863036000002</v>
+        <v>1.4752664279999999</v>
       </c>
       <c r="D77" t="str">
         <f>Market_currency</f>
@@ -19414,7 +19414,7 @@
       </c>
       <c r="C81" s="116">
         <f>PV(C80, C76, -C77, 0)</f>
-        <v>2.4641561834770669</v>
+        <v>2.4448990363491063</v>
       </c>
       <c r="D81" s="116"/>
       <c r="E81" s="100"/>
@@ -19426,7 +19426,7 @@
       </c>
       <c r="C82" s="116">
         <f>C60/(1+C80)^C76</f>
-        <v>12.925771015427101</v>
+        <v>12.82816424522062</v>
       </c>
       <c r="D82" s="116"/>
     </row>
@@ -19436,7 +19436,7 @@
       </c>
       <c r="C83" s="111">
         <f>C81+C82</f>
-        <v>15.389927198904168</v>
+        <v>15.273063281569726</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -19447,7 +19447,7 @@
       </c>
       <c r="F83" s="291">
         <f>(1-C83/C60)</f>
-        <v>0.53431378671462304</v>
+        <v>0.53433358924333874</v>
       </c>
     </row>
     <row r="84" spans="2:8">
@@ -19464,7 +19464,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>47.6</v>
+        <v>47.5</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19477,7 +19477,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>-7.9180969336304363E-2</v>
+        <v>-8.0930426518360243E-2</v>
       </c>
     </row>
     <row r="88" spans="2:8">
@@ -19503,7 +19503,7 @@
       </c>
       <c r="C91" s="116">
         <f>PV(C90, C76, -C77, 0)</f>
-        <v>3.0487129018949313</v>
+        <v>3.024887499391482</v>
       </c>
       <c r="D91" s="116"/>
       <c r="E91" s="100"/>
@@ -19515,7 +19515,7 @@
       </c>
       <c r="C92" s="116">
         <f>C60/(1+C90)^C76</f>
-        <v>18.316533829635802</v>
+        <v>18.178219627229254</v>
       </c>
       <c r="D92" s="116"/>
     </row>
@@ -19525,7 +19525,7 @@
       </c>
       <c r="C93" s="111">
         <f>C91+C92</f>
-        <v>21.365246731530732</v>
+        <v>21.203107126620736</v>
       </c>
       <c r="D93" t="str">
         <f>Market_currency</f>
@@ -19536,7 +19536,7 @@
       </c>
       <c r="F93" s="291">
         <f>(1-C93/C60)</f>
-        <v>0.35350565875173401</v>
+        <v>0.35353015891336748</v>
       </c>
     </row>
     <row r="95" spans="2:8" ht="13.15">
@@ -19563,7 +19563,7 @@
       </c>
       <c r="C97" s="116">
         <f>PV(C96, C76, -C77, 0)</f>
-        <v>3.8666861047748737</v>
+        <v>3.8364683191829627</v>
       </c>
       <c r="D97" s="116"/>
       <c r="G97" s="2"/>
@@ -19575,7 +19575,7 @@
       </c>
       <c r="C98" s="116">
         <f>C60/(1+C96)^C76</f>
-        <v>26.602214558474746</v>
+        <v>26.401332441632857</v>
       </c>
       <c r="D98" s="116"/>
       <c r="G98" s="2"/>
@@ -19587,7 +19587,7 @@
       </c>
       <c r="C99" s="111">
         <f>C97+C98</f>
-        <v>30.46890066324962</v>
+        <v>30.237800760815819</v>
       </c>
       <c r="D99" t="s">
         <v>393</v>
@@ -19597,7 +19597,7 @@
       </c>
       <c r="F99" s="291">
         <f>(1-C99/C60)</f>
-        <v>7.8036771100038704E-2</v>
+        <v>7.8067844683416876E-2</v>
       </c>
     </row>
     <row r="100" spans="2:8">
@@ -19623,7 +19623,7 @@
       </c>
       <c r="C103" s="116">
         <f>PV(C102, C76, -C77, 0)</f>
-        <v>3.5872665439807236</v>
+        <v>3.5592323957851444</v>
       </c>
       <c r="D103" s="116"/>
     </row>
@@ -19633,7 +19633,7 @@
       </c>
       <c r="C104" s="116">
         <f>C60/(1+C102)^C76</f>
-        <v>23.687388530860197</v>
+        <v>23.508517228996361</v>
       </c>
       <c r="D104" s="116"/>
     </row>
@@ -19643,7 +19643,7 @@
       </c>
       <c r="C105" s="111">
         <f>C103+C104</f>
-        <v>27.274655074840922</v>
+        <v>27.067749624781506</v>
       </c>
       <c r="D105" t="s">
         <v>393</v>
@@ -19653,7 +19653,7 @@
       </c>
       <c r="F105" s="291">
         <f>(1-C105/C66)</f>
-        <v>0.15783417591159743</v>
+        <v>0.15786816121300562</v>
       </c>
     </row>
     <row r="106" spans="2:8">

--- a/financial_models/opportunities/1913.HK_Valuation.xlsx
+++ b/financial_models/opportunities/1913.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F372674F-0F75-4C0D-BE94-5272F7359FA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AEC366E-1ED0-4FA8-83CA-91F786C96E53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2205" yWindow="2205" windowWidth="12690" windowHeight="7642" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -3896,29 +3896,29 @@
     <xf numFmtId="10" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4336,7 +4336,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>47.5</v>
+        <v>47.7</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4357,7 +4357,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>121544.14</v>
+        <v>122055.9048</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4384,7 +4384,7 @@
         <v>1</v>
       </c>
       <c r="C16" s="50">
-        <v>8.9955269999999992</v>
+        <v>9.0468945000000005</v>
       </c>
       <c r="D16" s="50"/>
       <c r="E16" s="5"/>
@@ -4394,13 +4394,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="358" t="s">
+      <c r="B18" s="360" t="s">
         <v>356</v>
       </c>
-      <c r="C18" s="358"/>
-      <c r="D18" s="358"/>
-      <c r="E18" s="358"/>
-      <c r="F18" s="358"/>
+      <c r="C18" s="360"/>
+      <c r="D18" s="360"/>
+      <c r="E18" s="360"/>
+      <c r="F18" s="360"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4476,14 +4476,14 @@
       </c>
       <c r="C26" s="304">
         <f>C132</f>
-        <v>32.798292788076616</v>
+        <v>32.979231003471874</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>396</v>
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>-8.0930426518360243E-2</v>
+        <v>-8.0510996454183692E-2</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4515,7 +4515,7 @@
       </c>
       <c r="C29" s="310">
         <f>C149</f>
-        <v>15.273063281569726</v>
+        <v>15.357793565778509</v>
       </c>
       <c r="D29" s="310" t="str">
         <f>D149</f>
@@ -4534,7 +4534,7 @@
       </c>
       <c r="C30" s="311">
         <f>C157</f>
-        <v>21.203107126620736</v>
+        <v>21.320663970914513</v>
       </c>
       <c r="D30" s="311" t="str">
         <f>D157</f>
@@ -4553,7 +4553,7 @@
       </c>
       <c r="C31" s="311">
         <f>C165</f>
-        <v>30.237800760815819</v>
+        <v>30.405356420701072</v>
       </c>
       <c r="D31" s="311" t="str">
         <f>D165</f>
@@ -4572,7 +4572,7 @@
       </c>
       <c r="C32" s="311">
         <f>C173</f>
-        <v>27.067749624781506</v>
+        <v>27.21776339129536</v>
       </c>
       <c r="D32" s="311" t="str">
         <f>D173</f>
@@ -4600,22 +4600,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="358" t="s">
+      <c r="B36" s="360" t="s">
         <v>357</v>
       </c>
-      <c r="C36" s="358"/>
-      <c r="D36" s="358"/>
-      <c r="E36" s="358"/>
-      <c r="F36" s="358"/>
+      <c r="C36" s="360"/>
+      <c r="D36" s="360"/>
+      <c r="E36" s="360"/>
+      <c r="F36" s="360"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="360" t="s">
+      <c r="B37" s="363" t="s">
         <v>336</v>
       </c>
-      <c r="C37" s="360"/>
-      <c r="D37" s="360"/>
-      <c r="E37" s="360"/>
-      <c r="F37" s="360"/>
+      <c r="C37" s="363"/>
+      <c r="D37" s="363"/>
+      <c r="E37" s="363"/>
+      <c r="F37" s="363"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4627,13 +4627,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="359" t="s">
+      <c r="B40" s="361" t="s">
         <v>230</v>
       </c>
-      <c r="C40" s="359"/>
-      <c r="D40" s="359"/>
-      <c r="E40" s="359"/>
-      <c r="F40" s="359"/>
+      <c r="C40" s="361"/>
+      <c r="D40" s="361"/>
+      <c r="E40" s="361"/>
+      <c r="F40" s="361"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4653,13 +4653,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="359" t="s">
+      <c r="B43" s="361" t="s">
         <v>232</v>
       </c>
-      <c r="C43" s="359"/>
-      <c r="D43" s="359"/>
-      <c r="E43" s="359"/>
-      <c r="F43" s="359"/>
+      <c r="C43" s="361"/>
+      <c r="D43" s="361"/>
+      <c r="E43" s="361"/>
+      <c r="F43" s="361"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4688,13 +4688,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="359" t="s">
+      <c r="B47" s="361" t="s">
         <v>235</v>
       </c>
-      <c r="C47" s="359"/>
-      <c r="D47" s="359"/>
-      <c r="E47" s="359"/>
-      <c r="F47" s="359"/>
+      <c r="C47" s="361"/>
+      <c r="D47" s="361"/>
+      <c r="E47" s="361"/>
+      <c r="F47" s="361"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4710,13 +4710,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="359" t="s">
+      <c r="B50" s="361" t="s">
         <v>239</v>
       </c>
-      <c r="C50" s="359"/>
-      <c r="D50" s="359"/>
-      <c r="E50" s="359"/>
-      <c r="F50" s="359"/>
+      <c r="C50" s="361"/>
+      <c r="D50" s="361"/>
+      <c r="E50" s="361"/>
+      <c r="F50" s="361"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4780,13 +4780,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="359" t="s">
+      <c r="B58" s="361" t="s">
         <v>240</v>
       </c>
-      <c r="C58" s="359"/>
-      <c r="D58" s="359"/>
-      <c r="E58" s="359"/>
-      <c r="F58" s="359"/>
+      <c r="C58" s="361"/>
+      <c r="D58" s="361"/>
+      <c r="E58" s="361"/>
+      <c r="F58" s="361"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4802,7 +4802,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="359" t="s">
+      <c r="B61" s="361" t="s">
         <v>335</v>
       </c>
       <c r="C61" s="362"/>
@@ -4824,22 +4824,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="358" t="s">
+      <c r="B64" s="360" t="s">
         <v>340</v>
       </c>
-      <c r="C64" s="358"/>
-      <c r="D64" s="358"/>
-      <c r="E64" s="358"/>
-      <c r="F64" s="358"/>
+      <c r="C64" s="360"/>
+      <c r="D64" s="360"/>
+      <c r="E64" s="360"/>
+      <c r="F64" s="360"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="358" t="s">
+      <c r="B65" s="360" t="s">
         <v>358</v>
       </c>
-      <c r="C65" s="358"/>
-      <c r="D65" s="358"/>
-      <c r="E65" s="358"/>
-      <c r="F65" s="358"/>
+      <c r="C65" s="360"/>
+      <c r="D65" s="360"/>
+      <c r="E65" s="360"/>
+      <c r="F65" s="360"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4873,7 +4873,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>5.1304921101930211E-2</v>
+        <v>5.138154619204785E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4883,14 +4883,14 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>3.1058240589473683E-2</v>
+        <v>3.1104626792452832E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>444</v>
       </c>
       <c r="F70" s="315">
         <f>Normalized_FCF!C92</f>
-        <v>5.445583694399156</v>
+        <v>5.4766798181084244</v>
       </c>
     </row>
     <row r="72" spans="1:6">
@@ -4974,22 +4974,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.6" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="358" t="s">
+      <c r="B80" s="360" t="s">
         <v>359</v>
       </c>
-      <c r="C80" s="358"/>
-      <c r="D80" s="358"/>
-      <c r="E80" s="358"/>
-      <c r="F80" s="358"/>
+      <c r="C80" s="360"/>
+      <c r="D80" s="360"/>
+      <c r="E80" s="360"/>
+      <c r="F80" s="360"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="360" t="s">
+      <c r="B81" s="363" t="s">
         <v>251</v>
       </c>
-      <c r="C81" s="360"/>
-      <c r="D81" s="360"/>
-      <c r="E81" s="360"/>
-      <c r="F81" s="360"/>
+      <c r="C81" s="363"/>
+      <c r="D81" s="363"/>
+      <c r="E81" s="363"/>
+      <c r="F81" s="363"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5033,22 +5033,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="358" t="s">
+      <c r="B89" s="360" t="s">
         <v>360</v>
       </c>
-      <c r="C89" s="358"/>
-      <c r="D89" s="358"/>
-      <c r="E89" s="358"/>
-      <c r="F89" s="358"/>
+      <c r="C89" s="360"/>
+      <c r="D89" s="360"/>
+      <c r="E89" s="360"/>
+      <c r="F89" s="360"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="358" t="s">
+      <c r="B90" s="360" t="s">
         <v>361</v>
       </c>
-      <c r="C90" s="358"/>
-      <c r="D90" s="358"/>
-      <c r="E90" s="358"/>
-      <c r="F90" s="358"/>
+      <c r="C90" s="360"/>
+      <c r="D90" s="360"/>
+      <c r="E90" s="360"/>
+      <c r="F90" s="360"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5064,7 +5064,7 @@
       </c>
       <c r="C93" s="223">
         <f>DCF!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>32.493116697889135</v>
+        <v>32.678663378142431</v>
       </c>
       <c r="D93" s="1" t="str">
         <f>Market_currency</f>
@@ -5085,13 +5085,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="358" t="s">
+      <c r="B97" s="360" t="s">
         <v>362</v>
       </c>
-      <c r="C97" s="358"/>
-      <c r="D97" s="358"/>
-      <c r="E97" s="358"/>
-      <c r="F97" s="358"/>
+      <c r="C97" s="360"/>
+      <c r="D97" s="360"/>
+      <c r="E97" s="360"/>
+      <c r="F97" s="360"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5104,13 +5104,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="358" t="s">
+      <c r="B101" s="360" t="s">
         <v>341</v>
       </c>
-      <c r="C101" s="358"/>
-      <c r="D101" s="358"/>
-      <c r="E101" s="358"/>
-      <c r="F101" s="358"/>
+      <c r="C101" s="360"/>
+      <c r="D101" s="360"/>
+      <c r="E101" s="360"/>
+      <c r="F101" s="360"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="C103" s="223">
         <f>C102*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>3.0461743931978122</v>
+        <v>3.0635690787056866</v>
       </c>
       <c r="D103" s="1" t="str">
         <f>Market_currency</f>
@@ -5180,7 +5180,7 @@
       </c>
       <c r="C109" s="349">
         <f>DCF!C8</f>
-        <v>413814.31655841379</v>
+        <v>412017.96453687374</v>
       </c>
       <c r="D109" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5193,7 +5193,7 @@
       </c>
       <c r="C110" s="223">
         <f>C109*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>1.4547611940437319</v>
+        <v>1.4567172487321669</v>
       </c>
       <c r="D110" s="1" t="str">
         <f>Market_currency</f>
@@ -5224,7 +5224,7 @@
       </c>
       <c r="C114" s="223">
         <f>C113*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>1.322668959834674E-2</v>
+        <v>1.3302218467077064E-2</v>
       </c>
       <c r="D114" s="1" t="str">
         <f>Market_currency</f>
@@ -5232,13 +5232,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="358" t="s">
+      <c r="B116" s="360" t="s">
         <v>363</v>
       </c>
-      <c r="C116" s="358"/>
-      <c r="D116" s="358"/>
-      <c r="E116" s="358"/>
-      <c r="F116" s="358"/>
+      <c r="C116" s="360"/>
+      <c r="D116" s="360"/>
+      <c r="E116" s="360"/>
+      <c r="F116" s="360"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="C118" s="223">
         <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
-        <v>30.914930188333404</v>
+        <v>31.085113766635988</v>
       </c>
       <c r="D118" s="1" t="str">
         <f>Market_currency</f>
@@ -5259,7 +5259,7 @@
       </c>
       <c r="C119" s="223">
         <f>BS!D47</f>
-        <v>-5.8461170007857897</v>
+        <v>-5.879500305070005</v>
       </c>
       <c r="D119" s="1" t="str">
         <f>Market_currency</f>
@@ -5277,13 +5277,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B123" s="359" t="s">
+      <c r="B123" s="361" t="s">
         <v>364</v>
       </c>
-      <c r="C123" s="359"/>
-      <c r="D123" s="359"/>
-      <c r="E123" s="359"/>
-      <c r="F123" s="359"/>
+      <c r="C123" s="361"/>
+      <c r="D123" s="361"/>
+      <c r="E123" s="361"/>
+      <c r="F123" s="361"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5317,7 +5317,7 @@
       </c>
       <c r="E126" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E74,DDM!E69),2)&amp;" "&amp;Market_currency</f>
-        <v>40.45 HKD</v>
+        <v>40.68 HKD</v>
       </c>
       <c r="F126" s="232">
         <f>DCF!F74</f>
@@ -5339,7 +5339,7 @@
       </c>
       <c r="E127" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E75,DDM!E70),2)&amp;" "&amp;Market_currency</f>
-        <v>33.55 HKD</v>
+        <v>33.73 HKD</v>
       </c>
       <c r="F127" s="221">
         <f>DCF!F75</f>
@@ -5361,7 +5361,7 @@
       </c>
       <c r="E128" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E76,DDM!E71),2)&amp;" "&amp;Market_currency</f>
-        <v>32.47 HKD</v>
+        <v>32.65 HKD</v>
       </c>
       <c r="F128" s="221">
         <f>DCF!F76</f>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="E129" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E77,DDM!E72),2)&amp;" "&amp;Market_currency</f>
-        <v>31.43 HKD</v>
+        <v>31.6 HKD</v>
       </c>
       <c r="F129" s="221">
         <f>DCF!F77</f>
@@ -5405,7 +5405,7 @@
       </c>
       <c r="E130" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E78,DDM!E73),2)&amp;" "&amp;Market_currency</f>
-        <v>30.91 HKD</v>
+        <v>31.09 HKD</v>
       </c>
       <c r="F130" s="221">
         <f>DCF!F78</f>
@@ -5418,7 +5418,7 @@
       </c>
       <c r="C132" s="217">
         <f>Scenarios!C60</f>
-        <v>32.798292788076616</v>
+        <v>32.979231003471874</v>
       </c>
       <c r="D132" s="212" t="str">
         <f>Market_currency</f>
@@ -5426,13 +5426,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="363" t="s">
+      <c r="B134" s="364" t="s">
         <v>367</v>
       </c>
-      <c r="C134" s="363"/>
-      <c r="D134" s="363"/>
-      <c r="E134" s="363"/>
-      <c r="F134" s="363"/>
+      <c r="C134" s="364"/>
+      <c r="D134" s="364"/>
+      <c r="E134" s="364"/>
+      <c r="F134" s="364"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5445,22 +5445,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="361" t="s">
+      <c r="B138" s="365" t="s">
         <v>365</v>
       </c>
-      <c r="C138" s="361"/>
-      <c r="D138" s="361"/>
-      <c r="E138" s="361"/>
-      <c r="F138" s="361"/>
+      <c r="C138" s="365"/>
+      <c r="D138" s="365"/>
+      <c r="E138" s="365"/>
+      <c r="F138" s="365"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="358" t="s">
+      <c r="B139" s="360" t="s">
         <v>366</v>
       </c>
-      <c r="C139" s="358"/>
-      <c r="D139" s="358"/>
-      <c r="E139" s="358"/>
-      <c r="F139" s="358"/>
+      <c r="C139" s="360"/>
+      <c r="D139" s="360"/>
+      <c r="E139" s="360"/>
+      <c r="F139" s="360"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5491,7 +5491,7 @@
       </c>
       <c r="C143" s="213">
         <f>Scenarios!C77</f>
-        <v>1.4752664279999999</v>
+        <v>1.4836906980000002</v>
       </c>
       <c r="D143" s="212" t="str">
         <f>Market_currency</f>
@@ -5527,7 +5527,7 @@
       </c>
       <c r="C147" s="216">
         <f>Scenarios!C81</f>
-        <v>2.4448990363491063</v>
+        <v>2.4588602363154526</v>
       </c>
     </row>
     <row r="148" spans="2:4">
@@ -5537,7 +5537,7 @@
       </c>
       <c r="C148" s="216">
         <f>Scenarios!C82</f>
-        <v>12.82816424522062</v>
+        <v>12.898933329463057</v>
       </c>
     </row>
     <row r="149" spans="2:4">
@@ -5546,7 +5546,7 @@
       </c>
       <c r="C149" s="215">
         <f>Scenarios!C83</f>
-        <v>15.273063281569726</v>
+        <v>15.357793565778509</v>
       </c>
       <c r="D149" s="300" t="str">
         <f>IF($D$11="","",C149*$E$25)</f>
@@ -5572,7 +5572,7 @@
       </c>
       <c r="C151" s="92">
         <f>Scenarios!F83</f>
-        <v>0.53433358924333874</v>
+        <v>0.53431923369705847</v>
       </c>
     </row>
     <row r="153" spans="2:4">
@@ -5596,7 +5596,7 @@
       </c>
       <c r="C155" s="216">
         <f>Scenarios!C91</f>
-        <v>3.024887499391482</v>
+        <v>3.0421606295399433</v>
       </c>
     </row>
     <row r="156" spans="2:4">
@@ -5606,7 +5606,7 @@
       </c>
       <c r="C156" s="216">
         <f>Scenarios!C92</f>
-        <v>18.178219627229254</v>
+        <v>18.27850334137457</v>
       </c>
     </row>
     <row r="157" spans="2:4">
@@ -5615,7 +5615,7 @@
       </c>
       <c r="C157" s="215">
         <f>Scenarios!C93</f>
-        <v>21.203107126620736</v>
+        <v>21.320663970914513</v>
       </c>
       <c r="D157" s="300" t="str">
         <f>IF($D$11="","",C157*$E$25)</f>
@@ -5641,7 +5641,7 @@
       </c>
       <c r="C159" s="92">
         <f>Scenarios!F93</f>
-        <v>0.35353015891336748</v>
+        <v>0.35351239788853805</v>
       </c>
     </row>
     <row r="161" spans="2:4">
@@ -5665,7 +5665,7 @@
       </c>
       <c r="C163" s="216">
         <f>Scenarios!C97</f>
-        <v>3.8364683191829627</v>
+        <v>3.8583758501575951</v>
       </c>
     </row>
     <row r="164" spans="2:4">
@@ -5675,7 +5675,7 @@
       </c>
       <c r="C164" s="216">
         <f>Scenarios!C98</f>
-        <v>26.401332441632857</v>
+        <v>26.546980570543475</v>
       </c>
     </row>
     <row r="165" spans="2:4">
@@ -5684,7 +5684,7 @@
       </c>
       <c r="C165" s="215">
         <f>Scenarios!C99</f>
-        <v>30.237800760815819</v>
+        <v>30.405356420701072</v>
       </c>
       <c r="D165" s="300" t="str">
         <f>IF($D$11="","",C165*$E$25)</f>
@@ -5710,7 +5710,7 @@
       </c>
       <c r="C167" s="92">
         <f>Scenarios!F99</f>
-        <v>7.8067844683416876E-2</v>
+        <v>7.8045318355053128E-2</v>
       </c>
     </row>
     <row r="169" spans="2:4">
@@ -5734,7 +5734,7 @@
       </c>
       <c r="C171" s="216">
         <f>Scenarios!C103</f>
-        <v>3.5592323957851444</v>
+        <v>3.5795568159208964</v>
       </c>
     </row>
     <row r="172" spans="2:4">
@@ -5744,7 +5744,7 @@
       </c>
       <c r="C172" s="216">
         <f>Scenarios!C104</f>
-        <v>23.508517228996361</v>
+        <v>23.638206575374465</v>
       </c>
     </row>
     <row r="173" spans="2:4">
@@ -5753,7 +5753,7 @@
       </c>
       <c r="C173" s="215">
         <f>Scenarios!C105</f>
-        <v>27.067749624781506</v>
+        <v>27.21776339129536</v>
       </c>
       <c r="D173" s="300" t="str">
         <f>IF($D$11="","",C173*$E$25)</f>
@@ -5779,7 +5779,7 @@
       </c>
       <c r="C175" s="92">
         <f>Scenarios!F105</f>
-        <v>0.15786816121300562</v>
+        <v>0.15784352411507596</v>
       </c>
     </row>
     <row r="177" spans="1:6" ht="13.9">
@@ -5793,13 +5793,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="365" t="s">
+      <c r="B179" s="359" t="s">
         <v>373</v>
       </c>
-      <c r="C179" s="358"/>
-      <c r="D179" s="358"/>
-      <c r="E179" s="358"/>
-      <c r="F179" s="358"/>
+      <c r="C179" s="360"/>
+      <c r="D179" s="360"/>
+      <c r="E179" s="360"/>
+      <c r="F179" s="360"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5836,13 +5836,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="359" t="s">
+      <c r="B188" s="361" t="s">
         <v>378</v>
       </c>
-      <c r="C188" s="359"/>
-      <c r="D188" s="359"/>
-      <c r="E188" s="359"/>
-      <c r="F188" s="359"/>
+      <c r="C188" s="361"/>
+      <c r="D188" s="361"/>
+      <c r="E188" s="361"/>
+      <c r="F188" s="361"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5850,22 +5850,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="364" t="s">
+      <c r="B191" s="358" t="s">
         <v>379</v>
       </c>
-      <c r="C191" s="364"/>
-      <c r="D191" s="364"/>
-      <c r="E191" s="364"/>
-      <c r="F191" s="364"/>
+      <c r="C191" s="358"/>
+      <c r="D191" s="358"/>
+      <c r="E191" s="358"/>
+      <c r="F191" s="358"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="364" t="s">
+      <c r="B192" s="358" t="s">
         <v>380</v>
       </c>
-      <c r="C192" s="364"/>
-      <c r="D192" s="364"/>
-      <c r="E192" s="364"/>
-      <c r="F192" s="364"/>
+      <c r="C192" s="358"/>
+      <c r="D192" s="358"/>
+      <c r="E192" s="358"/>
+      <c r="F192" s="358"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5889,17 +5889,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5916,6 +5905,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -6488,15 +6488,15 @@
       </c>
       <c r="C25" s="39">
         <f>0.164*Exchange_Rate</f>
-        <v>1.4752664279999999</v>
+        <v>1.4836906980000002</v>
       </c>
       <c r="D25" s="39">
         <f>0.137*Exchange_Rate</f>
-        <v>1.2323871989999999</v>
+        <v>1.2394245465000002</v>
       </c>
       <c r="E25" s="39">
         <f>0.11*Exchange_Rate</f>
-        <v>0.9895079699999999</v>
+        <v>0.99515839500000003</v>
       </c>
       <c r="F25" s="39"/>
       <c r="G25" s="39"/>
@@ -7870,15 +7870,15 @@
       </c>
       <c r="C65" s="73">
         <f>IF(C$4="","",C25)</f>
-        <v>1.4752664279999999</v>
+        <v>1.4836906980000002</v>
       </c>
       <c r="D65" s="73">
         <f t="shared" ref="D65:M65" si="33">IF(D$4="","",D25)</f>
-        <v>1.2323871989999999</v>
+        <v>1.2394245465000002</v>
       </c>
       <c r="E65" s="73">
         <f t="shared" si="33"/>
-        <v>0.9895079699999999</v>
+        <v>0.99515839500000003</v>
       </c>
       <c r="F65" s="73">
         <f t="shared" si="33"/>
@@ -9220,11 +9220,11 @@
       </c>
       <c r="C47" s="147">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>15.465935382955214</v>
+        <v>15.554251102065832</v>
       </c>
       <c r="D47" s="147">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>-5.8461170007857897</v>
+        <v>-5.879500305070005</v>
       </c>
       <c r="F47" s="253"/>
     </row>
@@ -9415,7 +9415,7 @@
       </c>
       <c r="D66" s="76">
         <f>C66-D75</f>
-        <v>413814.31655841379</v>
+        <v>412017.96453687374</v>
       </c>
       <c r="F66" s="5" t="s">
         <v>225</v>
@@ -9482,11 +9482,11 @@
       </c>
       <c r="C73" s="349">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35-Normalized_FCF!G91)/12</f>
-        <v>-647405.84519672266</v>
+        <v>-649202.19721826271</v>
       </c>
       <c r="D73" s="349">
         <f>(Normalized_FCF!C25+Normalized_FCF!C35-Normalized_FCF!C91)/12</f>
-        <v>-597748.68344158621</v>
+        <v>-599545.03546312626</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>348</v>
@@ -9498,11 +9498,11 @@
       </c>
       <c r="C74" s="258">
         <f>-$C$66/C73</f>
-        <v>1.562486665057254</v>
+        <v>1.5581632414899407</v>
       </c>
       <c r="D74" s="258">
         <f>-$C$66/D73</f>
-        <v>1.6922881271370511</v>
+        <v>1.6872177070378127</v>
       </c>
       <c r="F74" s="253" t="s">
         <v>316</v>
@@ -9515,7 +9515,7 @@
       <c r="C75" s="320"/>
       <c r="D75" s="321">
         <f>MAX(-D73*D76,G5)</f>
-        <v>597748.68344158621</v>
+        <v>599545.03546312626</v>
       </c>
       <c r="F75" s="253" t="s">
         <v>349</v>
@@ -9630,11 +9630,11 @@
       </c>
       <c r="C86" s="76">
         <f>-DCF!C7*Exchange_Rate</f>
-        <v>-7794624.1454999996</v>
+        <v>-7839134.0842500003</v>
       </c>
       <c r="D86" s="223">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>-3.0461743931978127</v>
+        <v>-3.0635690787056866</v>
       </c>
       <c r="E86" s="240" t="str">
         <f>Market_currency</f>
@@ -9647,11 +9647,11 @@
       </c>
       <c r="C87" s="76">
         <f>DCF!C8*Exchange_Rate</f>
-        <v>3722477.857587758</v>
+        <v>3727483.0572698382</v>
       </c>
       <c r="D87" s="223">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>1.4547611940437319</v>
+        <v>1.4567172487321669</v>
       </c>
       <c r="E87" s="240" t="str">
         <f>Market_currency</f>
@@ -9664,11 +9664,11 @@
       </c>
       <c r="C88" s="76">
         <f>DCF!C9*Exchange_Rate</f>
-        <v>33844.770784799999</v>
+        <v>34038.035866800004</v>
       </c>
       <c r="D88" s="223">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>1.322668959834674E-2</v>
+        <v>1.3302218467077064E-2</v>
       </c>
       <c r="E88" s="240" t="str">
         <f>Market_currency</f>
@@ -9681,11 +9681,11 @@
       </c>
       <c r="C89" s="180">
         <f>SUM(C86:C88)</f>
-        <v>-4038301.5171274417</v>
+        <v>-4077612.9911133619</v>
       </c>
       <c r="D89" s="242">
         <f>SUM(D86:D88)</f>
-        <v>-1.5781865095557339</v>
+        <v>-1.5935496115064427</v>
       </c>
       <c r="E89" s="240" t="str">
         <f>Market_currency</f>
@@ -13197,20 +13197,20 @@
       </c>
       <c r="C90" s="113">
         <f>G90</f>
-        <v>1.4752664279999999</v>
+        <v>1.4836906980000002</v>
       </c>
       <c r="E90" s="268"/>
       <c r="G90" s="112">
         <f>Data!C65</f>
-        <v>1.4752664279999999</v>
+        <v>1.4836906980000002</v>
       </c>
       <c r="H90" s="112">
         <f>Data!D65</f>
-        <v>1.2323871989999999</v>
+        <v>1.2394245465000002</v>
       </c>
       <c r="I90" s="112">
         <f>Data!E65</f>
-        <v>0.9895079699999999</v>
+        <v>0.99515839500000003</v>
       </c>
       <c r="J90" s="112">
         <f>Data!F65</f>
@@ -13253,20 +13253,20 @@
       </c>
       <c r="C91" s="74">
         <f>C90*Common_Shares/scaling_factor</f>
-        <v>3774947.1423606714</v>
+        <v>3796503.3666191525</v>
       </c>
       <c r="E91" s="268"/>
       <c r="G91" s="74">
         <f t="shared" ref="G91:Q91" si="37">IF(G$4="","",G90*Common_Shares/scaling_factor)</f>
-        <v>3774947.1423606714</v>
+        <v>3796503.3666191525</v>
       </c>
       <c r="H91" s="74">
         <f t="shared" si="37"/>
-        <v>3153461.9420939758</v>
+        <v>3171469.2757733162</v>
       </c>
       <c r="I91" s="74">
         <f t="shared" si="37"/>
-        <v>2531976.7418272798</v>
+        <v>2546435.1849274803</v>
       </c>
       <c r="J91" s="74">
         <f t="shared" si="37"/>
@@ -13308,20 +13308,20 @@
       </c>
       <c r="C92" s="23">
         <f>C90/(C19*scaling_factor/Common_Shares)</f>
-        <v>5.445583694399156</v>
+        <v>5.4766798181084244</v>
       </c>
       <c r="E92" s="268"/>
       <c r="G92" s="170">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",G90/(G19*scaling_factor/Common_Shares))</f>
-        <v>3.786761839299285</v>
+        <v>3.808385529471102</v>
       </c>
       <c r="H92" s="170">
         <f t="shared" si="38"/>
-        <v>3.840930972142989</v>
+        <v>3.8628639863745691</v>
       </c>
       <c r="I92" s="170">
         <f t="shared" si="38"/>
-        <v>3.7686749708673384</v>
+        <v>3.7901953789063598</v>
       </c>
       <c r="J92" s="170">
         <f t="shared" si="38"/>
@@ -13384,20 +13384,20 @@
       </c>
       <c r="C94" s="23">
         <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
-        <v>3.1058240589473683E-2</v>
+        <v>3.1104626792452832E-2</v>
       </c>
       <c r="E94" s="268"/>
       <c r="G94" s="23">
         <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>3.1058240589473683E-2</v>
+        <v>3.1104626792452832E-2</v>
       </c>
       <c r="H94" s="23">
         <f t="shared" si="39"/>
-        <v>2.5944993663157893E-2</v>
+        <v>2.5983743113207551E-2</v>
       </c>
       <c r="I94" s="23">
         <f t="shared" si="39"/>
-        <v>2.0831746736842103E-2</v>
+        <v>2.0862859433962263E-2</v>
       </c>
       <c r="J94" s="23">
         <f t="shared" si="39"/>
@@ -14526,38 +14526,38 @@
       </c>
       <c r="C125" s="177">
         <f>C16*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>2.4369837523416855</v>
+        <v>2.4508997533606824</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="265"/>
       <c r="F125" s="27"/>
       <c r="G125" s="177">
         <f t="shared" ref="G125:Q125" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>3.5045243267063309</v>
+        <v>3.5245363452742358</v>
       </c>
       <c r="H125" s="177">
         <f t="shared" si="49"/>
-        <v>2.8862722093840758</v>
+        <v>2.9027537993693588</v>
       </c>
       <c r="I125" s="177">
         <f t="shared" si="49"/>
-        <v>2.3618767152004203</v>
+        <v>2.3753638296483075</v>
       </c>
       <c r="J125" s="177">
         <f t="shared" si="49"/>
-        <v>1.2668640292892359</v>
+        <v>1.2740982511446666</v>
       </c>
       <c r="K125" s="177">
         <f t="shared" si="49"/>
-        <v>6.1198469700120048</v>
+        <v>6.1547933649516349</v>
       </c>
       <c r="L125" s="177">
         <f t="shared" si="49"/>
-        <v>8.2285027486376539</v>
+        <v>8.2754902808790298</v>
       </c>
       <c r="M125" s="177">
         <f t="shared" si="49"/>
-        <v>7.6127958480040041</v>
+        <v>7.6562674857104289</v>
       </c>
       <c r="N125" s="177" t="str">
         <f t="shared" si="49"/>
@@ -14583,38 +14583,38 @@
       </c>
       <c r="C126" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>5.1304921101930211E-2</v>
+        <v>5.138154619204785E-2</v>
       </c>
       <c r="D126" s="27"/>
       <c r="E126" s="265"/>
       <c r="F126" s="27"/>
       <c r="G126" s="77">
         <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
-        <v>7.3779459509606959E-2</v>
+        <v>7.3889650844323598E-2</v>
       </c>
       <c r="H126" s="77">
         <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
-        <v>6.0763625460717383E-2</v>
+        <v>6.0854377345269571E-2</v>
       </c>
       <c r="I126" s="77">
         <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
-        <v>4.9723720320008852E-2</v>
+        <v>4.9797983850069338E-2</v>
       </c>
       <c r="J126" s="77">
         <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
-        <v>2.6670821669247072E-2</v>
+        <v>2.6710655160265544E-2</v>
       </c>
       <c r="K126" s="77">
         <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
-        <v>0.12883888357920009</v>
+        <v>0.12903130744133406</v>
       </c>
       <c r="L126" s="77">
         <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
-        <v>0.17323163681342429</v>
+        <v>0.17349036228257922</v>
       </c>
       <c r="M126" s="77">
         <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
-        <v>0.16026938627376849</v>
+        <v>0.16050875232097334</v>
       </c>
       <c r="N126" s="77" t="str">
         <f t="shared" ref="N126" si="57">IF(N$4="","",N125/Market_Price)</f>
@@ -14640,31 +14640,31 @@
       <c r="C127" s="169"/>
       <c r="G127" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.9390428859836435E-3</v>
+        <v>6.9099483665455569E-3</v>
       </c>
       <c r="H127" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.5403082369911046E-3</v>
+        <v>5.5170784330624209E-3</v>
       </c>
       <c r="I127" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.8599557329542997E-3</v>
+        <v>3.8437714321871955E-3</v>
       </c>
       <c r="J127" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.4279492207522303E-3</v>
+        <v>2.4177691401620744E-3</v>
       </c>
       <c r="K127" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-4.4731074653208292E-4</v>
+        <v>-4.45435229775135E-4</v>
       </c>
       <c r="L127" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.1204148550477216E-3</v>
+        <v>2.1115242267246703E-3</v>
       </c>
       <c r="M127" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.7128098483398706E-3</v>
+        <v>1.7056282556843574E-3</v>
       </c>
       <c r="N127" s="23" t="str">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -15492,7 +15492,7 @@
       </c>
       <c r="C8" s="338">
         <f>BS!D66</f>
-        <v>413814.31655841379</v>
+        <v>412017.96453687374</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
@@ -15524,7 +15524,7 @@
       </c>
       <c r="C10" s="347">
         <f>C6-C7+C8+C9</f>
-        <v>8793911.165430557</v>
+        <v>8792114.8134090174</v>
       </c>
       <c r="D10" t="str">
         <f>Reporting_currency</f>
@@ -15538,7 +15538,7 @@
       </c>
       <c r="C11" s="208">
         <f>Exchange_Rate</f>
-        <v>8.9955269999999992</v>
+        <v>9.0468945000000005</v>
       </c>
       <c r="D11" t="str">
         <f>Thesis!C15</f>
@@ -15552,7 +15552,7 @@
       </c>
       <c r="C12" s="111">
         <f>(C10*scaling_factor)/Common_Shares*Exchange_Rate</f>
-        <v>30.914930188333404</v>
+        <v>31.085113766635988</v>
       </c>
       <c r="D12" t="str">
         <f>Market_currency</f>
@@ -15605,7 +15605,7 @@
       </c>
       <c r="C18" s="140">
         <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>32.141938326153131</v>
+        <v>32.319128535698056</v>
       </c>
       <c r="D18" t="str">
         <f>Market_currency</f>
@@ -16701,23 +16701,23 @@
       </c>
       <c r="B65" s="124">
         <f>C12</f>
-        <v>30.914930188333404</v>
+        <v>31.085113766635988</v>
       </c>
       <c r="C65" s="124">
         <f>C12</f>
-        <v>30.914930188333404</v>
+        <v>31.085113766635988</v>
       </c>
       <c r="D65" s="124">
         <f>C12</f>
-        <v>30.914930188333404</v>
+        <v>31.085113766635988</v>
       </c>
       <c r="E65" s="141">
         <f>C12</f>
-        <v>30.914930188333404</v>
+        <v>31.085113766635988</v>
       </c>
       <c r="F65" s="124">
         <f>C12</f>
-        <v>30.914930188333404</v>
+        <v>31.085113766635988</v>
       </c>
       <c r="H65" s="120"/>
     </row>
@@ -16728,23 +16728,23 @@
       </c>
       <c r="B66" s="124">
         <f t="shared" ref="B66:F71" si="4">(B56-$C$7+$C$8+$C$9)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>30.914930188333404</v>
+        <v>31.085113766635988</v>
       </c>
       <c r="C66" s="124">
         <f t="shared" si="4"/>
-        <v>31.426445524640503</v>
+        <v>31.599550028425025</v>
       </c>
       <c r="D66" s="124">
         <f t="shared" si="4"/>
-        <v>32.471664587367663</v>
+        <v>32.650737645324128</v>
       </c>
       <c r="E66" s="124">
         <f t="shared" si="4"/>
-        <v>33.54755512665318</v>
+        <v>33.732771883280854</v>
       </c>
       <c r="F66" s="124">
         <f t="shared" si="4"/>
-        <v>35.221842262262143</v>
+        <v>35.416619764406832</v>
       </c>
       <c r="H66" s="120"/>
     </row>
@@ -16755,23 +16755,23 @@
       </c>
       <c r="B67" s="124">
         <f t="shared" si="4"/>
-        <v>30.914930188333415</v>
+        <v>31.085113766635995</v>
       </c>
       <c r="C67" s="124">
         <f t="shared" si="4"/>
-        <v>31.916877091116778</v>
+        <v>32.092782124930388</v>
       </c>
       <c r="D67" s="124">
         <f t="shared" si="4"/>
-        <v>34.068277676442278</v>
+        <v>34.256467934853255</v>
       </c>
       <c r="E67" s="124">
         <f t="shared" si="4"/>
-        <v>36.435991907083931</v>
+        <v>36.637702614129275</v>
       </c>
       <c r="F67" s="124">
         <f t="shared" si="4"/>
-        <v>40.450545684970969</v>
+        <v>40.675180851159801</v>
       </c>
       <c r="H67" s="120"/>
     </row>
@@ -16782,23 +16782,23 @@
       </c>
       <c r="B68" s="124">
         <f t="shared" si="4"/>
-        <v>30.914930188333415</v>
+        <v>31.085113766635995</v>
       </c>
       <c r="C68" s="124">
         <f t="shared" si="4"/>
-        <v>32.522384117473003</v>
+        <v>32.701746801091488</v>
       </c>
       <c r="D68" s="124">
         <f t="shared" si="4"/>
-        <v>36.142355256837888</v>
+        <v>36.342389199349981</v>
       </c>
       <c r="E68" s="124">
         <f t="shared" si="4"/>
-        <v>40.391613161287104</v>
+        <v>40.615911802844273</v>
       </c>
       <c r="F68" s="124">
         <f t="shared" si="4"/>
-        <v>48.22681612380989</v>
+        <v>48.495856422879427</v>
       </c>
       <c r="H68" s="120"/>
     </row>
@@ -16809,23 +16809,23 @@
       </c>
       <c r="B69" s="124">
         <f t="shared" si="4"/>
-        <v>30.914930188333422</v>
+        <v>31.085113766635999</v>
       </c>
       <c r="C69" s="124">
         <f t="shared" si="4"/>
-        <v>33.137348491982614</v>
+        <v>33.320222830060885</v>
       </c>
       <c r="D69" s="124">
         <f t="shared" si="4"/>
-        <v>38.363843106055803</v>
+        <v>38.576562495134247</v>
       </c>
       <c r="E69" s="124">
         <f t="shared" si="4"/>
-        <v>44.87485479345316</v>
+        <v>45.124754260236038</v>
       </c>
       <c r="F69" s="124">
         <f t="shared" si="4"/>
-        <v>57.87465842050716</v>
+        <v>58.198791160428208</v>
       </c>
       <c r="H69" s="120"/>
     </row>
@@ -16836,23 +16836,23 @@
       </c>
       <c r="B70" s="124">
         <f t="shared" si="4"/>
-        <v>30.914930188333422</v>
+        <v>31.085113766635999</v>
       </c>
       <c r="C70" s="124">
         <f t="shared" si="4"/>
-        <v>33.707142089958673</v>
+        <v>33.893270142093272</v>
       </c>
       <c r="D70" s="124">
         <f t="shared" si="4"/>
-        <v>40.53848422934572</v>
+        <v>40.763621554349498</v>
       </c>
       <c r="E70" s="124">
         <f t="shared" si="4"/>
-        <v>49.533824425204898</v>
+        <v>49.81032818349388</v>
       </c>
       <c r="F70" s="124">
         <f t="shared" si="4"/>
-        <v>68.925480195550691</v>
+        <v>69.312716863405001</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="13.15">
@@ -16862,23 +16862,23 @@
       </c>
       <c r="B71" s="124">
         <f t="shared" si="4"/>
-        <v>30.914930188333415</v>
+        <v>31.085113766635995</v>
       </c>
       <c r="C71" s="124">
         <f t="shared" si="4"/>
-        <v>34.207579799196822</v>
+        <v>34.396565519818147</v>
       </c>
       <c r="D71" s="124">
         <f t="shared" si="4"/>
-        <v>42.559750761257717</v>
+        <v>42.796430201423618</v>
       </c>
       <c r="E71" s="124">
         <f t="shared" si="4"/>
-        <v>54.144696184094805</v>
+        <v>54.447529578776937</v>
       </c>
       <c r="F71" s="124">
         <f t="shared" si="4"/>
-        <v>81.055210734458797</v>
+        <v>81.511712264000181</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="13.15">
@@ -16913,7 +16913,7 @@
       </c>
       <c r="E74" s="135">
         <f>INDEX(B$65:F$71, MATCH(D74, A$65:A$71, 0), MATCH(C74, B$64:F$64, 0))</f>
-        <v>40.450545684970969</v>
+        <v>40.675180851159801</v>
       </c>
       <c r="F74" s="142">
         <f>Scenarios!C58</f>
@@ -16935,7 +16935,7 @@
       </c>
       <c r="E75" s="135">
         <f>INDEX(B$65:F$71, MATCH(D75, A$65:A$71, 0), MATCH(C75, B$64:F$64, 0))</f>
-        <v>33.54755512665318</v>
+        <v>33.732771883280854</v>
       </c>
       <c r="F75" s="142">
         <f>Scenarios!C40*(1-F$74-F$78)</f>
@@ -16958,7 +16958,7 @@
       </c>
       <c r="E76" s="135">
         <f>INDEX(B$65:F$71, MATCH(D76, A$65:A$71, 0), MATCH(C76, B$64:F$64, 0))</f>
-        <v>32.471664587367663</v>
+        <v>32.650737645324128</v>
       </c>
       <c r="F76" s="142">
         <f>Scenarios!C28*(1-F$74-F$78)</f>
@@ -16981,7 +16981,7 @@
       </c>
       <c r="E77" s="135">
         <f>INDEX(B$65:F$71, MATCH(D77, A$65:A$71, 0), MATCH(C77, B$64:F$64, 0))</f>
-        <v>31.426445524640503</v>
+        <v>31.599550028425025</v>
       </c>
       <c r="F77" s="142">
         <f>Scenarios!C34*(1-F$74-F$78)</f>
@@ -17004,7 +17004,7 @@
       </c>
       <c r="E78" s="135">
         <f>INDEX(B$65:F$71, MATCH(D78, A$65:A$71, 0), MATCH(C78, B$64:F$64, 0))</f>
-        <v>30.914930188333415</v>
+        <v>31.085113766635995</v>
       </c>
       <c r="F78" s="142">
         <f>Scenarios!C52</f>
@@ -17186,7 +17186,7 @@
       </c>
       <c r="C4" s="114">
         <f>Normalized_FCF!C91*(1-dividend_tax_rate)</f>
-        <v>3774947.1423606714</v>
+        <v>3796503.3666191525</v>
       </c>
       <c r="D4" t="str">
         <f>Market_currency</f>
@@ -17218,7 +17218,7 @@
       </c>
       <c r="C6" s="319">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
-        <v>50332628.564808957</v>
+        <v>50620044.888255365</v>
       </c>
       <c r="D6" t="str">
         <f>Reporting_currency</f>
@@ -17234,7 +17234,7 @@
       </c>
       <c r="C7" s="111">
         <f>(C6*scaling_factor)/Common_Shares*Exchange_Rate</f>
-        <v>176.94398647023405</v>
+        <v>178.97057620583152</v>
       </c>
       <c r="D7" t="str">
         <f>Market_currency</f>
@@ -17287,7 +17287,7 @@
       </c>
       <c r="C13" s="140">
         <f>F47/Common_Shares*scaling_factor</f>
-        <v>20.413007706879238</v>
+        <v>20.52957288125792</v>
       </c>
       <c r="D13" t="str">
         <f>Market_currency</f>
@@ -17322,7 +17322,7 @@
       </c>
       <c r="C16" s="123">
         <f>C4*(1+D16)</f>
-        <v>3864612.024693164</v>
+        <v>3886680.2657399015</v>
       </c>
       <c r="D16" s="138">
         <f>IF($C$12&lt;B16,0,DDM!$C$11)</f>
@@ -17334,7 +17334,7 @@
       </c>
       <c r="F16" s="125">
         <f t="shared" ref="F16:F46" si="1">C16*E16</f>
-        <v>3594987.9299471295</v>
+        <v>3615516.5262696757</v>
       </c>
       <c r="H16" s="120"/>
     </row>
@@ -17344,7 +17344,7 @@
       </c>
       <c r="C17" s="123">
         <f t="shared" ref="C17:C45" si="2">IF(ROW()-ROW($C$16)&lt;$C$12, $C$16*(1+D17)^(ROW()-ROW($C$16)), 0)</f>
-        <v>3956406.6828398607</v>
+        <v>3978999.1024146988</v>
       </c>
       <c r="D17" s="138">
         <f>IF($C$12&lt;B17,0,DDM!$C$11)</f>
@@ -17356,7 +17356,7 @@
       </c>
       <c r="F17" s="125">
         <f t="shared" si="1"/>
-        <v>3423607.7298776512</v>
+        <v>3443157.68732478</v>
       </c>
       <c r="H17" s="120"/>
     </row>
@@ -17366,7 +17366,7 @@
       </c>
       <c r="C18" s="123">
         <f t="shared" si="2"/>
-        <v>4050381.7045548614</v>
+        <v>4073510.7532708212</v>
       </c>
       <c r="D18" s="138">
         <f>IF($C$12&lt;B18,0,DDM!$C$11)</f>
@@ -17378,7 +17378,7 @@
       </c>
       <c r="F18" s="125">
         <f t="shared" si="1"/>
-        <v>3260397.5636297581</v>
+        <v>3279015.5358563722</v>
       </c>
       <c r="H18" s="120"/>
     </row>
@@ -17388,7 +17388,7 @@
       </c>
       <c r="C19" s="123">
         <f t="shared" si="2"/>
-        <v>4146588.8791839289</v>
+        <v>4170267.3033887018</v>
       </c>
       <c r="D19" s="138">
         <f>IF($C$12&lt;B19,0,DDM!$C$11)</f>
@@ -17400,7 +17400,7 @@
       </c>
       <c r="F19" s="125">
         <f t="shared" si="1"/>
-        <v>3104967.9494977505</v>
+        <v>3122698.3660865542</v>
       </c>
       <c r="H19" s="120"/>
     </row>
@@ -17410,7 +17410,7 @@
       </c>
       <c r="C20" s="123">
         <f t="shared" si="2"/>
-        <v>4245081.2262054402</v>
+        <v>4269322.0750058619</v>
       </c>
       <c r="D20" s="138">
         <f>IF($C$12&lt;B20,0,DDM!$C$11)</f>
@@ -17422,7 +17422,7 @@
       </c>
       <c r="F20" s="125">
         <f t="shared" si="1"/>
-        <v>2956947.9731408157</v>
+        <v>2973833.1456282432</v>
       </c>
       <c r="H20" s="120"/>
     </row>
@@ -17982,7 +17982,7 @@
       </c>
       <c r="C46" s="123">
         <f>C$16*(1+F4)^$C$12/Equity_Cost</f>
-        <v>51528160.329242192</v>
+        <v>51822403.54319869</v>
       </c>
       <c r="D46" s="139">
         <f>Terminal_Growth</f>
@@ -17994,7 +17994,7 @@
       </c>
       <c r="F46" s="125">
         <f t="shared" si="1"/>
-        <v>35892384.886454456</v>
+        <v>36097342.537146293</v>
       </c>
       <c r="H46" s="120"/>
     </row>
@@ -18005,7 +18005,7 @@
       </c>
       <c r="F47" s="137">
         <f>SUM(F16:F46)</f>
-        <v>52233294.032547563</v>
+        <v>52531563.798311919</v>
       </c>
       <c r="H47" s="120"/>
     </row>
@@ -18026,7 +18026,7 @@
     <row r="50" spans="1:8" ht="13.15">
       <c r="A50" s="133">
         <f>F47</f>
-        <v>52233294.032547563</v>
+        <v>52531563.798311919</v>
       </c>
       <c r="B50" s="131">
         <f>C73</f>
@@ -18056,19 +18056,19 @@
       </c>
       <c r="B51" s="123">
         <f t="dataTable" ref="B51:F56" dt2D="1" dtr="1" r1="C11" r2="C12"/>
-        <v>50332628.564808957</v>
+        <v>50620044.888255373</v>
       </c>
       <c r="C51" s="123">
-        <v>51124978.269730337</v>
+        <v>51416919.177836165</v>
       </c>
       <c r="D51" s="123">
-        <v>52744048.035867043</v>
+        <v>53045234.379644617</v>
       </c>
       <c r="E51" s="123">
-        <v>54410628.665658325</v>
+        <v>54721331.748199597</v>
       </c>
       <c r="F51" s="123">
-        <v>57004140.186605111</v>
+        <v>57329653.096636467</v>
       </c>
       <c r="H51" s="120"/>
     </row>
@@ -18077,19 +18077,19 @@
         <v>10</v>
       </c>
       <c r="B52" s="123">
-        <v>50332628.564808965</v>
+        <v>50620044.88825538</v>
       </c>
       <c r="C52" s="123">
-        <v>51884668.702058464</v>
+        <v>52180947.699337125</v>
       </c>
       <c r="D52" s="123">
-        <v>55217240.568343468</v>
+        <v>55532549.677514568</v>
       </c>
       <c r="E52" s="123">
-        <v>58884887.535746887</v>
+        <v>59221140.148905918</v>
       </c>
       <c r="F52" s="123">
-        <v>65103529.041717485</v>
+        <v>65475292.200012781</v>
       </c>
       <c r="H52" s="120"/>
     </row>
@@ -18098,19 +18098,19 @@
         <v>15</v>
       </c>
       <c r="B53" s="123">
-        <v>50332628.564808965</v>
+        <v>50620044.888255373</v>
       </c>
       <c r="C53" s="123">
-        <v>52822613.822384506</v>
+        <v>53124248.803361326</v>
       </c>
       <c r="D53" s="123">
-        <v>58430037.218146905</v>
+        <v>58763692.482235752</v>
       </c>
       <c r="E53" s="123">
-        <v>65012241.128263503</v>
+        <v>65383483.001714185</v>
       </c>
       <c r="F53" s="123">
-        <v>77149161.206114009</v>
+        <v>77589708.995949477</v>
       </c>
       <c r="H53" s="120"/>
     </row>
@@ -18119,19 +18119,19 @@
         <v>20</v>
       </c>
       <c r="B54" s="123">
-        <v>50332628.564808972</v>
+        <v>50620044.888255373</v>
       </c>
       <c r="C54" s="123">
-        <v>53775208.605167955</v>
+        <v>54082283.224367708</v>
       </c>
       <c r="D54" s="123">
-        <v>61871175.96194692</v>
+        <v>62224481.291498534</v>
       </c>
       <c r="E54" s="123">
-        <v>71956891.527182013</v>
+        <v>72367789.701966286</v>
       </c>
       <c r="F54" s="123">
-        <v>92093903.727629751</v>
+        <v>92619791.049154013</v>
       </c>
       <c r="H54" s="120"/>
     </row>
@@ -18140,19 +18140,19 @@
         <v>25</v>
       </c>
       <c r="B55" s="123">
-        <v>50332628.564808972</v>
+        <v>50620044.888255388</v>
       </c>
       <c r="C55" s="123">
-        <v>54657832.755759142</v>
+        <v>54969947.457219273</v>
       </c>
       <c r="D55" s="123">
-        <v>65239747.987154357</v>
+        <v>65612289.001675293</v>
       </c>
       <c r="E55" s="123">
-        <v>79173748.8742311</v>
+        <v>79625857.744039088</v>
       </c>
       <c r="F55" s="123">
-        <v>109211895.60605437</v>
+        <v>109835532.44773628</v>
       </c>
       <c r="H55" s="120"/>
     </row>
@@ -18161,19 +18161,19 @@
         <v>30</v>
       </c>
       <c r="B56" s="123">
-        <v>50332628.564808972</v>
+        <v>50620044.88825538</v>
       </c>
       <c r="C56" s="123">
-        <v>55433022.946749471</v>
+        <v>55749564.246243894</v>
       </c>
       <c r="D56" s="123">
-        <v>68370739.037570134</v>
+        <v>68761159.069382921</v>
       </c>
       <c r="E56" s="123">
-        <v>86316101.44563736</v>
+        <v>86808995.563014716</v>
       </c>
       <c r="F56" s="123">
-        <v>128001143.4175991</v>
+        <v>128732073.21576476</v>
       </c>
       <c r="H56" s="120"/>
     </row>
@@ -18223,23 +18223,23 @@
       </c>
       <c r="B60" s="124">
         <f>C7</f>
-        <v>176.94398647023405</v>
+        <v>178.97057620583152</v>
       </c>
       <c r="C60" s="124">
         <f>C7</f>
-        <v>176.94398647023405</v>
+        <v>178.97057620583152</v>
       </c>
       <c r="D60" s="124">
         <f>C7</f>
-        <v>176.94398647023405</v>
+        <v>178.97057620583152</v>
       </c>
       <c r="E60" s="141">
         <f>C7</f>
-        <v>176.94398647023405</v>
+        <v>178.97057620583152</v>
       </c>
       <c r="F60" s="124">
         <f>C7</f>
-        <v>176.94398647023405</v>
+        <v>178.97057620583152</v>
       </c>
       <c r="H60" s="120"/>
     </row>
@@ -18250,23 +18250,23 @@
       </c>
       <c r="B61" s="124">
         <f t="shared" ref="B61:F66" si="4">B51/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>176.94398647023405</v>
+        <v>178.97057620583155</v>
       </c>
       <c r="C61" s="124">
         <f t="shared" si="4"/>
-        <v>179.72948604506308</v>
+        <v>181.78797889847468</v>
       </c>
       <c r="D61" s="124">
         <f t="shared" si="4"/>
-        <v>185.42131393012528</v>
+        <v>187.54499690499142</v>
       </c>
       <c r="E61" s="124">
         <f t="shared" si="4"/>
-        <v>191.28016590781681</v>
+        <v>193.47095197851135</v>
       </c>
       <c r="F61" s="124">
         <f t="shared" si="4"/>
-        <v>200.39763663323123</v>
+        <v>202.69284768583867</v>
       </c>
       <c r="H61" s="120"/>
     </row>
@@ -18277,23 +18277,23 @@
       </c>
       <c r="B62" s="124">
         <f t="shared" si="4"/>
-        <v>176.94398647023408</v>
+        <v>178.97057620583158</v>
       </c>
       <c r="C62" s="124">
         <f t="shared" si="4"/>
-        <v>182.40017218668493</v>
+        <v>184.48925316704887</v>
       </c>
       <c r="D62" s="124">
         <f t="shared" si="4"/>
-        <v>194.11580413425423</v>
+        <v>196.33906757498104</v>
       </c>
       <c r="E62" s="124">
         <f t="shared" si="4"/>
-        <v>207.00939014163325</v>
+        <v>209.38032748515181</v>
       </c>
       <c r="F62" s="124">
         <f t="shared" si="4"/>
-        <v>228.87097873478353</v>
+        <v>231.49230306194897</v>
       </c>
       <c r="H62" s="120"/>
     </row>
@@ -18304,23 +18304,23 @@
       </c>
       <c r="B63" s="124">
         <f t="shared" si="4"/>
-        <v>176.94398647023408</v>
+        <v>178.97057620583155</v>
       </c>
       <c r="C63" s="124">
         <f t="shared" si="4"/>
-        <v>185.69751137625451</v>
+        <v>187.82435771892136</v>
       </c>
       <c r="D63" s="124">
         <f t="shared" si="4"/>
-        <v>205.41036718697549</v>
+        <v>207.76299046641347</v>
       </c>
       <c r="E63" s="124">
         <f t="shared" si="4"/>
-        <v>228.55005674474086</v>
+        <v>231.16770546120077</v>
       </c>
       <c r="F63" s="124">
         <f t="shared" si="4"/>
-        <v>271.21731023976292</v>
+        <v>274.32363912955947</v>
       </c>
       <c r="H63" s="120"/>
     </row>
@@ -18331,23 +18331,23 @@
       </c>
       <c r="B64" s="124">
         <f t="shared" si="4"/>
-        <v>176.94398647023411</v>
+        <v>178.97057620583155</v>
       </c>
       <c r="C64" s="124">
         <f t="shared" si="4"/>
-        <v>189.04635134672046</v>
+        <v>191.21155290476193</v>
       </c>
       <c r="D64" s="124">
         <f t="shared" si="4"/>
-        <v>217.50766519598238</v>
+        <v>219.99884226559192</v>
       </c>
       <c r="E64" s="124">
         <f t="shared" si="4"/>
-        <v>252.96392427491574</v>
+        <v>255.86119195062867</v>
       </c>
       <c r="F64" s="124">
         <f t="shared" si="4"/>
-        <v>323.75544293679201</v>
+        <v>327.46350598311591</v>
       </c>
       <c r="H64" s="120"/>
     </row>
@@ -18358,23 +18358,23 @@
       </c>
       <c r="B65" s="124">
         <f t="shared" si="4"/>
-        <v>176.94398647023411</v>
+        <v>178.97057620583158</v>
       </c>
       <c r="C65" s="124">
         <f t="shared" si="4"/>
-        <v>192.1492100730319</v>
+        <v>194.34994955339099</v>
       </c>
       <c r="D65" s="124">
         <f t="shared" si="4"/>
-        <v>229.3498554381398</v>
+        <v>231.9766644762073</v>
       </c>
       <c r="E65" s="124">
         <f t="shared" si="4"/>
-        <v>278.33473333428384</v>
+        <v>281.52258009239</v>
       </c>
       <c r="F65" s="124">
         <f t="shared" si="4"/>
-        <v>383.9336178046803</v>
+        <v>388.33091858056548</v>
       </c>
     </row>
     <row r="66" spans="1:8" ht="13.15">
@@ -18384,23 +18384,23 @@
       </c>
       <c r="B66" s="124">
         <f t="shared" si="4"/>
-        <v>176.94398647023411</v>
+        <v>178.97057620583158</v>
       </c>
       <c r="C66" s="124">
         <f t="shared" si="4"/>
-        <v>194.87438550252162</v>
+        <v>197.10633719112397</v>
       </c>
       <c r="D66" s="124">
         <f t="shared" si="4"/>
-        <v>240.3568315063545</v>
+        <v>243.10970656771451</v>
       </c>
       <c r="E66" s="124">
         <f t="shared" si="4"/>
-        <v>303.44362140146012</v>
+        <v>306.91904738644087</v>
       </c>
       <c r="F66" s="124">
         <f t="shared" si="4"/>
-        <v>449.98708064481372</v>
+        <v>455.14091049220247</v>
       </c>
     </row>
     <row r="68" spans="1:8" ht="13.15">
@@ -18435,7 +18435,7 @@
       </c>
       <c r="E69" s="135">
         <f>INDEX(B$60:F$66, MATCH(D69, A$60:A$66, 0), MATCH(C69, B$59:F$59, 0))</f>
-        <v>228.87097873478353</v>
+        <v>231.49230306194897</v>
       </c>
       <c r="F69" s="142">
         <f>Scenarios!C58</f>
@@ -18457,7 +18457,7 @@
       </c>
       <c r="E70" s="135">
         <f>INDEX(B$60:F$66, MATCH(D70, A$60:A$66, 0), MATCH(C70, B$59:F$59, 0))</f>
-        <v>191.28016590781681</v>
+        <v>193.47095197851135</v>
       </c>
       <c r="F70" s="142">
         <f>Scenarios!C40*(1-F$69-F$73)</f>
@@ -18480,7 +18480,7 @@
       </c>
       <c r="E71" s="135">
         <f>INDEX(B$60:F$66, MATCH(D71, A$60:A$66, 0), MATCH(C71, B$59:F$59, 0))</f>
-        <v>185.42131393012528</v>
+        <v>187.54499690499142</v>
       </c>
       <c r="F71" s="142">
         <f>Scenarios!C28*(1-F$69-F$73)</f>
@@ -18503,7 +18503,7 @@
       </c>
       <c r="E72" s="135">
         <f>INDEX(B$60:F$66, MATCH(D72, A$60:A$66, 0), MATCH(C72, B$59:F$59, 0))</f>
-        <v>179.72948604506308</v>
+        <v>181.78797889847468</v>
       </c>
       <c r="F72" s="142">
         <f>Scenarios!C34*(1-F$69-F$73)</f>
@@ -18526,7 +18526,7 @@
       </c>
       <c r="E73" s="135">
         <f>INDEX(B$60:F$66, MATCH(D73, A$60:A$66, 0), MATCH(C73, B$59:F$59, 0))</f>
-        <v>176.94398647023408</v>
+        <v>178.97057620583158</v>
       </c>
       <c r="F73" s="142">
         <f>Scenarios!C52</f>
@@ -18626,7 +18626,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-47.5</v>
+        <v>-47.7</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18646,7 +18646,7 @@
       </c>
       <c r="I4" s="124">
         <f t="shared" ref="I4:I13" si="0">IF(ROW()-3 &lt; $C$76, $C$77, IF(ROW()-3 = $C$76, $C$77 + $C$60, ""))</f>
-        <v>1.4752664279999999</v>
+        <v>1.4836906980000002</v>
       </c>
     </row>
     <row r="5" spans="2:9">
@@ -18655,7 +18655,7 @@
       </c>
       <c r="I5" s="124">
         <f t="shared" si="0"/>
-        <v>1.4752664279999999</v>
+        <v>1.4836906980000002</v>
       </c>
     </row>
     <row r="6" spans="2:9" ht="13.15">
@@ -18675,7 +18675,7 @@
       </c>
       <c r="I6" s="124">
         <f t="shared" si="0"/>
-        <v>34.273559216076613</v>
+        <v>34.462921701471871</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1">
@@ -18866,7 +18866,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>47.5</v>
+        <v>47.7</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -18881,7 +18881,7 @@
       </c>
       <c r="C22" s="160">
         <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
-        <v>30.914930188333404</v>
+        <v>31.085113766635988</v>
       </c>
       <c r="D22" t="str">
         <f>Market_currency</f>
@@ -18928,7 +18928,7 @@
       </c>
       <c r="C27" s="160">
         <f>IF(valuation_method="DCF",DCF!E76,DDM!E71)</f>
-        <v>32.471664587367663</v>
+        <v>32.650737645324128</v>
       </c>
       <c r="D27" s="160" t="str">
         <f>Market_currency</f>
@@ -18986,7 +18986,7 @@
       </c>
       <c r="C33" s="160">
         <f>IF(valuation_method="DCF",DCF!E77,DDM!E72)</f>
-        <v>31.426445524640503</v>
+        <v>31.599550028425025</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
@@ -19044,7 +19044,7 @@
       </c>
       <c r="C39" s="160">
         <f>IF(valuation_method="DCF",DCF!E75,DDM!E70)</f>
-        <v>33.54755512665318</v>
+        <v>33.732771883280854</v>
       </c>
       <c r="D39" t="str">
         <f>Market_currency</f>
@@ -19071,7 +19071,7 @@
       </c>
       <c r="C42" s="154">
         <f>C27*C28+C33*C34+C39*C40</f>
-        <v>32.47779888267933</v>
+        <v>32.656906969535655</v>
       </c>
       <c r="D42" t="str">
         <f>Market_currency</f>
@@ -19145,7 +19145,7 @@
       </c>
       <c r="C51" s="160">
         <f>IF(valuation_method="DCF",DCF!E78,DDM!E73)</f>
-        <v>30.914930188333415</v>
+        <v>31.085113766635995</v>
       </c>
       <c r="D51" t="str">
         <f>Market_currency</f>
@@ -19203,7 +19203,7 @@
       </c>
       <c r="C57" s="160">
         <f>IF(valuation_method="DCF",DCF!E74,DDM!E69)</f>
-        <v>40.450545684970969</v>
+        <v>40.675180851159801</v>
       </c>
       <c r="D57" t="str">
         <f>Market_currency</f>
@@ -19229,7 +19229,7 @@
       </c>
       <c r="C60" s="154">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
-        <v>32.798292788076616</v>
+        <v>32.979231003471874</v>
       </c>
       <c r="D60" t="str">
         <f>Market_currency</f>
@@ -19291,7 +19291,7 @@
       </c>
       <c r="C66" s="160">
         <f>IF(valuation_method="DCF",DCF!C18,DDM!C13)</f>
-        <v>32.141938326153131</v>
+        <v>32.319128535698056</v>
       </c>
       <c r="D66" s="160" t="str">
         <f>Market_currency</f>
@@ -19354,7 +19354,7 @@
       </c>
       <c r="F72" s="291">
         <f>BS!D89/C60</f>
-        <v>-4.8117946862449579E-2</v>
+        <v>-4.8319792882335018E-2</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="13.9">
@@ -19387,7 +19387,7 @@
       </c>
       <c r="C77" s="173">
         <f>Normalized_FCF!C90*(1-dividend_tax_rate)</f>
-        <v>1.4752664279999999</v>
+        <v>1.4836906980000002</v>
       </c>
       <c r="D77" t="str">
         <f>Market_currency</f>
@@ -19414,7 +19414,7 @@
       </c>
       <c r="C81" s="116">
         <f>PV(C80, C76, -C77, 0)</f>
-        <v>2.4448990363491063</v>
+        <v>2.4588602363154526</v>
       </c>
       <c r="D81" s="116"/>
       <c r="E81" s="100"/>
@@ -19426,7 +19426,7 @@
       </c>
       <c r="C82" s="116">
         <f>C60/(1+C80)^C76</f>
-        <v>12.82816424522062</v>
+        <v>12.898933329463057</v>
       </c>
       <c r="D82" s="116"/>
     </row>
@@ -19436,7 +19436,7 @@
       </c>
       <c r="C83" s="111">
         <f>C81+C82</f>
-        <v>15.273063281569726</v>
+        <v>15.357793565778509</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -19447,7 +19447,7 @@
       </c>
       <c r="F83" s="291">
         <f>(1-C83/C60)</f>
-        <v>0.53433358924333874</v>
+        <v>0.53431923369705847</v>
       </c>
     </row>
     <row r="84" spans="2:8">
@@ -19464,7 +19464,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>47.5</v>
+        <v>47.7</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19477,7 +19477,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>-8.0930426518360243E-2</v>
+        <v>-8.0510996454183692E-2</v>
       </c>
     </row>
     <row r="88" spans="2:8">
@@ -19503,7 +19503,7 @@
       </c>
       <c r="C91" s="116">
         <f>PV(C90, C76, -C77, 0)</f>
-        <v>3.024887499391482</v>
+        <v>3.0421606295399433</v>
       </c>
       <c r="D91" s="116"/>
       <c r="E91" s="100"/>
@@ -19515,7 +19515,7 @@
       </c>
       <c r="C92" s="116">
         <f>C60/(1+C90)^C76</f>
-        <v>18.178219627229254</v>
+        <v>18.27850334137457</v>
       </c>
       <c r="D92" s="116"/>
     </row>
@@ -19525,7 +19525,7 @@
       </c>
       <c r="C93" s="111">
         <f>C91+C92</f>
-        <v>21.203107126620736</v>
+        <v>21.320663970914513</v>
       </c>
       <c r="D93" t="str">
         <f>Market_currency</f>
@@ -19536,7 +19536,7 @@
       </c>
       <c r="F93" s="291">
         <f>(1-C93/C60)</f>
-        <v>0.35353015891336748</v>
+        <v>0.35351239788853805</v>
       </c>
     </row>
     <row r="95" spans="2:8" ht="13.15">
@@ -19563,7 +19563,7 @@
       </c>
       <c r="C97" s="116">
         <f>PV(C96, C76, -C77, 0)</f>
-        <v>3.8364683191829627</v>
+        <v>3.8583758501575951</v>
       </c>
       <c r="D97" s="116"/>
       <c r="G97" s="2"/>
@@ -19575,7 +19575,7 @@
       </c>
       <c r="C98" s="116">
         <f>C60/(1+C96)^C76</f>
-        <v>26.401332441632857</v>
+        <v>26.546980570543475</v>
       </c>
       <c r="D98" s="116"/>
       <c r="G98" s="2"/>
@@ -19587,7 +19587,7 @@
       </c>
       <c r="C99" s="111">
         <f>C97+C98</f>
-        <v>30.237800760815819</v>
+        <v>30.405356420701072</v>
       </c>
       <c r="D99" t="s">
         <v>393</v>
@@ -19597,7 +19597,7 @@
       </c>
       <c r="F99" s="291">
         <f>(1-C99/C60)</f>
-        <v>7.8067844683416876E-2</v>
+        <v>7.8045318355053128E-2</v>
       </c>
     </row>
     <row r="100" spans="2:8">
@@ -19623,7 +19623,7 @@
       </c>
       <c r="C103" s="116">
         <f>PV(C102, C76, -C77, 0)</f>
-        <v>3.5592323957851444</v>
+        <v>3.5795568159208964</v>
       </c>
       <c r="D103" s="116"/>
     </row>
@@ -19633,7 +19633,7 @@
       </c>
       <c r="C104" s="116">
         <f>C60/(1+C102)^C76</f>
-        <v>23.508517228996361</v>
+        <v>23.638206575374465</v>
       </c>
       <c r="D104" s="116"/>
     </row>
@@ -19643,7 +19643,7 @@
       </c>
       <c r="C105" s="111">
         <f>C103+C104</f>
-        <v>27.067749624781506</v>
+        <v>27.21776339129536</v>
       </c>
       <c r="D105" t="s">
         <v>393</v>
@@ -19653,7 +19653,7 @@
       </c>
       <c r="F105" s="291">
         <f>(1-C105/C66)</f>
-        <v>0.15786816121300562</v>
+        <v>0.15784352411507596</v>
       </c>
     </row>
     <row r="106" spans="2:8">

--- a/financial_models/opportunities/1913.HK_Valuation.xlsx
+++ b/financial_models/opportunities/1913.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AEC366E-1ED0-4FA8-83CA-91F786C96E53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1352F6C0-7BC7-4DF4-81BD-10EECF1D943F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3896,29 +3896,29 @@
     <xf numFmtId="10" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4336,7 +4336,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>47.7</v>
+        <v>47.8</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4357,7 +4357,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>122055.9048</v>
+        <v>122311.78720000001</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4384,7 +4384,7 @@
         <v>1</v>
       </c>
       <c r="C16" s="50">
-        <v>9.0468945000000005</v>
+        <v>9.1121639200000004</v>
       </c>
       <c r="D16" s="50"/>
       <c r="E16" s="5"/>
@@ -4394,13 +4394,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="360" t="s">
+      <c r="B18" s="358" t="s">
         <v>356</v>
       </c>
-      <c r="C18" s="360"/>
-      <c r="D18" s="360"/>
-      <c r="E18" s="360"/>
-      <c r="F18" s="360"/>
+      <c r="C18" s="358"/>
+      <c r="D18" s="358"/>
+      <c r="E18" s="358"/>
+      <c r="F18" s="358"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4476,14 +4476,14 @@
       </c>
       <c r="C26" s="304">
         <f>C132</f>
-        <v>32.979231003471874</v>
+        <v>33.20903366081091</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>396</v>
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>-8.0510996454183692E-2</v>
+        <v>-7.8960977262645282E-2</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4515,7 +4515,7 @@
       </c>
       <c r="C29" s="310">
         <f>C149</f>
-        <v>15.357793565778509</v>
+        <v>15.46541426368313</v>
       </c>
       <c r="D29" s="310" t="str">
         <f>D149</f>
@@ -4534,7 +4534,7 @@
       </c>
       <c r="C30" s="311">
         <f>C157</f>
-        <v>21.320663970914513</v>
+        <v>21.469978322655386</v>
       </c>
       <c r="D30" s="311" t="str">
         <f>D157</f>
@@ -4553,7 +4553,7 @@
       </c>
       <c r="C31" s="311">
         <f>C165</f>
-        <v>30.405356420701072</v>
+        <v>30.618175006932312</v>
       </c>
       <c r="D31" s="311" t="str">
         <f>D165</f>
@@ -4572,7 +4572,7 @@
       </c>
       <c r="C32" s="311">
         <f>C173</f>
-        <v>27.21776339129536</v>
+        <v>27.40830178418765</v>
       </c>
       <c r="D32" s="311" t="str">
         <f>D173</f>
@@ -4600,22 +4600,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="360" t="s">
+      <c r="B36" s="358" t="s">
         <v>357</v>
       </c>
-      <c r="C36" s="360"/>
-      <c r="D36" s="360"/>
-      <c r="E36" s="360"/>
-      <c r="F36" s="360"/>
+      <c r="C36" s="358"/>
+      <c r="D36" s="358"/>
+      <c r="E36" s="358"/>
+      <c r="F36" s="358"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="363" t="s">
+      <c r="B37" s="360" t="s">
         <v>336</v>
       </c>
-      <c r="C37" s="363"/>
-      <c r="D37" s="363"/>
-      <c r="E37" s="363"/>
-      <c r="F37" s="363"/>
+      <c r="C37" s="360"/>
+      <c r="D37" s="360"/>
+      <c r="E37" s="360"/>
+      <c r="F37" s="360"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4627,13 +4627,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="361" t="s">
+      <c r="B40" s="359" t="s">
         <v>230</v>
       </c>
-      <c r="C40" s="361"/>
-      <c r="D40" s="361"/>
-      <c r="E40" s="361"/>
-      <c r="F40" s="361"/>
+      <c r="C40" s="359"/>
+      <c r="D40" s="359"/>
+      <c r="E40" s="359"/>
+      <c r="F40" s="359"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4653,13 +4653,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="361" t="s">
+      <c r="B43" s="359" t="s">
         <v>232</v>
       </c>
-      <c r="C43" s="361"/>
-      <c r="D43" s="361"/>
-      <c r="E43" s="361"/>
-      <c r="F43" s="361"/>
+      <c r="C43" s="359"/>
+      <c r="D43" s="359"/>
+      <c r="E43" s="359"/>
+      <c r="F43" s="359"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4688,13 +4688,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="361" t="s">
+      <c r="B47" s="359" t="s">
         <v>235</v>
       </c>
-      <c r="C47" s="361"/>
-      <c r="D47" s="361"/>
-      <c r="E47" s="361"/>
-      <c r="F47" s="361"/>
+      <c r="C47" s="359"/>
+      <c r="D47" s="359"/>
+      <c r="E47" s="359"/>
+      <c r="F47" s="359"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4710,13 +4710,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="361" t="s">
+      <c r="B50" s="359" t="s">
         <v>239</v>
       </c>
-      <c r="C50" s="361"/>
-      <c r="D50" s="361"/>
-      <c r="E50" s="361"/>
-      <c r="F50" s="361"/>
+      <c r="C50" s="359"/>
+      <c r="D50" s="359"/>
+      <c r="E50" s="359"/>
+      <c r="F50" s="359"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4780,13 +4780,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="361" t="s">
+      <c r="B58" s="359" t="s">
         <v>240</v>
       </c>
-      <c r="C58" s="361"/>
-      <c r="D58" s="361"/>
-      <c r="E58" s="361"/>
-      <c r="F58" s="361"/>
+      <c r="C58" s="359"/>
+      <c r="D58" s="359"/>
+      <c r="E58" s="359"/>
+      <c r="F58" s="359"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4802,7 +4802,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="361" t="s">
+      <c r="B61" s="359" t="s">
         <v>335</v>
       </c>
       <c r="C61" s="362"/>
@@ -4824,22 +4824,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="360" t="s">
+      <c r="B64" s="358" t="s">
         <v>340</v>
       </c>
-      <c r="C64" s="360"/>
-      <c r="D64" s="360"/>
-      <c r="E64" s="360"/>
-      <c r="F64" s="360"/>
+      <c r="C64" s="358"/>
+      <c r="D64" s="358"/>
+      <c r="E64" s="358"/>
+      <c r="F64" s="358"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="360" t="s">
+      <c r="B65" s="358" t="s">
         <v>358</v>
       </c>
-      <c r="C65" s="360"/>
-      <c r="D65" s="360"/>
-      <c r="E65" s="360"/>
-      <c r="F65" s="360"/>
+      <c r="C65" s="358"/>
+      <c r="D65" s="358"/>
+      <c r="E65" s="358"/>
+      <c r="F65" s="358"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4873,7 +4873,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>5.138154619204785E-2</v>
+        <v>5.1643973474421914E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4883,14 +4883,14 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>3.1104626792452832E-2</v>
+        <v>3.126349127364017E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>444</v>
       </c>
       <c r="F70" s="315">
         <f>Normalized_FCF!C92</f>
-        <v>5.4766798181084244</v>
+        <v>5.5161916876514638</v>
       </c>
     </row>
     <row r="72" spans="1:6">
@@ -4974,22 +4974,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.6" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="360" t="s">
+      <c r="B80" s="358" t="s">
         <v>359</v>
       </c>
-      <c r="C80" s="360"/>
-      <c r="D80" s="360"/>
-      <c r="E80" s="360"/>
-      <c r="F80" s="360"/>
+      <c r="C80" s="358"/>
+      <c r="D80" s="358"/>
+      <c r="E80" s="358"/>
+      <c r="F80" s="358"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="363" t="s">
+      <c r="B81" s="360" t="s">
         <v>251</v>
       </c>
-      <c r="C81" s="363"/>
-      <c r="D81" s="363"/>
-      <c r="E81" s="363"/>
-      <c r="F81" s="363"/>
+      <c r="C81" s="360"/>
+      <c r="D81" s="360"/>
+      <c r="E81" s="360"/>
+      <c r="F81" s="360"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5033,22 +5033,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="360" t="s">
+      <c r="B89" s="358" t="s">
         <v>360</v>
       </c>
-      <c r="C89" s="360"/>
-      <c r="D89" s="360"/>
-      <c r="E89" s="360"/>
-      <c r="F89" s="360"/>
+      <c r="C89" s="358"/>
+      <c r="D89" s="358"/>
+      <c r="E89" s="358"/>
+      <c r="F89" s="358"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="360" t="s">
+      <c r="B90" s="358" t="s">
         <v>361</v>
       </c>
-      <c r="C90" s="360"/>
-      <c r="D90" s="360"/>
-      <c r="E90" s="360"/>
-      <c r="F90" s="360"/>
+      <c r="C90" s="358"/>
+      <c r="D90" s="358"/>
+      <c r="E90" s="358"/>
+      <c r="F90" s="358"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5064,7 +5064,7 @@
       </c>
       <c r="C93" s="223">
         <f>DCF!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>32.678663378142431</v>
+        <v>32.914425761031559</v>
       </c>
       <c r="D93" s="1" t="str">
         <f>Market_currency</f>
@@ -5085,13 +5085,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="360" t="s">
+      <c r="B97" s="358" t="s">
         <v>362</v>
       </c>
-      <c r="C97" s="360"/>
-      <c r="D97" s="360"/>
-      <c r="E97" s="360"/>
-      <c r="F97" s="360"/>
+      <c r="C97" s="358"/>
+      <c r="D97" s="358"/>
+      <c r="E97" s="358"/>
+      <c r="F97" s="358"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5104,13 +5104,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="360" t="s">
+      <c r="B101" s="358" t="s">
         <v>341</v>
       </c>
-      <c r="C101" s="360"/>
-      <c r="D101" s="360"/>
-      <c r="E101" s="360"/>
-      <c r="F101" s="360"/>
+      <c r="C101" s="358"/>
+      <c r="D101" s="358"/>
+      <c r="E101" s="358"/>
+      <c r="F101" s="358"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="C103" s="223">
         <f>C102*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>3.0635690787056866</v>
+        <v>3.0856714008779034</v>
       </c>
       <c r="D103" s="1" t="str">
         <f>Market_currency</f>
@@ -5180,7 +5180,7 @@
       </c>
       <c r="C109" s="349">
         <f>DCF!C8</f>
-        <v>412017.96453687374</v>
+        <v>409735.4541059254</v>
       </c>
       <c r="D109" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5193,7 +5193,7 @@
       </c>
       <c r="C110" s="223">
         <f>C109*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>1.4567172487321669</v>
+        <v>1.4590986412699074</v>
       </c>
       <c r="D110" s="1" t="str">
         <f>Market_currency</f>
@@ -5224,7 +5224,7 @@
       </c>
       <c r="C114" s="223">
         <f>C113*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>1.3302218467077064E-2</v>
+        <v>1.3398188203881159E-2</v>
       </c>
       <c r="D114" s="1" t="str">
         <f>Market_currency</f>
@@ -5232,13 +5232,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="360" t="s">
+      <c r="B116" s="358" t="s">
         <v>363</v>
       </c>
-      <c r="C116" s="360"/>
-      <c r="D116" s="360"/>
-      <c r="E116" s="360"/>
-      <c r="F116" s="360"/>
+      <c r="C116" s="358"/>
+      <c r="D116" s="358"/>
+      <c r="E116" s="358"/>
+      <c r="F116" s="358"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="C118" s="223">
         <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
-        <v>31.085113766635988</v>
+        <v>31.30125118962745</v>
       </c>
       <c r="D118" s="1" t="str">
         <f>Market_currency</f>
@@ -5259,7 +5259,7 @@
       </c>
       <c r="C119" s="223">
         <f>BS!D47</f>
-        <v>-5.879500305070005</v>
+        <v>-5.9219183497152414</v>
       </c>
       <c r="D119" s="1" t="str">
         <f>Market_currency</f>
@@ -5277,13 +5277,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B123" s="361" t="s">
+      <c r="B123" s="359" t="s">
         <v>364</v>
       </c>
-      <c r="C123" s="361"/>
-      <c r="D123" s="361"/>
-      <c r="E123" s="361"/>
-      <c r="F123" s="361"/>
+      <c r="C123" s="359"/>
+      <c r="D123" s="359"/>
+      <c r="E123" s="359"/>
+      <c r="F123" s="359"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5317,7 +5317,7 @@
       </c>
       <c r="E126" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E74,DDM!E69),2)&amp;" "&amp;Market_currency</f>
-        <v>40.68 HKD</v>
+        <v>40.96 HKD</v>
       </c>
       <c r="F126" s="232">
         <f>DCF!F74</f>
@@ -5339,7 +5339,7 @@
       </c>
       <c r="E127" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E75,DDM!E70),2)&amp;" "&amp;Market_currency</f>
-        <v>33.73 HKD</v>
+        <v>33.97 HKD</v>
       </c>
       <c r="F127" s="221">
         <f>DCF!F75</f>
@@ -5361,7 +5361,7 @@
       </c>
       <c r="E128" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E76,DDM!E71),2)&amp;" "&amp;Market_currency</f>
-        <v>32.65 HKD</v>
+        <v>32.88 HKD</v>
       </c>
       <c r="F128" s="221">
         <f>DCF!F76</f>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="E129" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E77,DDM!E72),2)&amp;" "&amp;Market_currency</f>
-        <v>31.6 HKD</v>
+        <v>31.82 HKD</v>
       </c>
       <c r="F129" s="221">
         <f>DCF!F77</f>
@@ -5405,7 +5405,7 @@
       </c>
       <c r="E130" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E78,DDM!E73),2)&amp;" "&amp;Market_currency</f>
-        <v>31.09 HKD</v>
+        <v>31.3 HKD</v>
       </c>
       <c r="F130" s="221">
         <f>DCF!F78</f>
@@ -5418,7 +5418,7 @@
       </c>
       <c r="C132" s="217">
         <f>Scenarios!C60</f>
-        <v>32.979231003471874</v>
+        <v>33.20903366081091</v>
       </c>
       <c r="D132" s="212" t="str">
         <f>Market_currency</f>
@@ -5426,13 +5426,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="364" t="s">
+      <c r="B134" s="363" t="s">
         <v>367</v>
       </c>
-      <c r="C134" s="364"/>
-      <c r="D134" s="364"/>
-      <c r="E134" s="364"/>
-      <c r="F134" s="364"/>
+      <c r="C134" s="363"/>
+      <c r="D134" s="363"/>
+      <c r="E134" s="363"/>
+      <c r="F134" s="363"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5445,22 +5445,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="365" t="s">
+      <c r="B138" s="361" t="s">
         <v>365</v>
       </c>
-      <c r="C138" s="365"/>
-      <c r="D138" s="365"/>
-      <c r="E138" s="365"/>
-      <c r="F138" s="365"/>
+      <c r="C138" s="361"/>
+      <c r="D138" s="361"/>
+      <c r="E138" s="361"/>
+      <c r="F138" s="361"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="360" t="s">
+      <c r="B139" s="358" t="s">
         <v>366</v>
       </c>
-      <c r="C139" s="360"/>
-      <c r="D139" s="360"/>
-      <c r="E139" s="360"/>
-      <c r="F139" s="360"/>
+      <c r="C139" s="358"/>
+      <c r="D139" s="358"/>
+      <c r="E139" s="358"/>
+      <c r="F139" s="358"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5491,7 +5491,7 @@
       </c>
       <c r="C143" s="213">
         <f>Scenarios!C77</f>
-        <v>1.4836906980000002</v>
+        <v>1.4943948828800002</v>
       </c>
       <c r="D143" s="212" t="str">
         <f>Market_currency</f>
@@ -5527,7 +5527,7 @@
       </c>
       <c r="C147" s="216">
         <f>Scenarios!C81</f>
-        <v>2.4588602363154526</v>
+        <v>2.4765998464640369</v>
       </c>
     </row>
     <row r="148" spans="2:4">
@@ -5537,7 +5537,7 @@
       </c>
       <c r="C148" s="216">
         <f>Scenarios!C82</f>
-        <v>12.898933329463057</v>
+        <v>12.988814417219093</v>
       </c>
     </row>
     <row r="149" spans="2:4">
@@ -5546,7 +5546,7 @@
       </c>
       <c r="C149" s="215">
         <f>Scenarios!C83</f>
-        <v>15.357793565778509</v>
+        <v>15.46541426368313</v>
       </c>
       <c r="D149" s="300" t="str">
         <f>IF($D$11="","",C149*$E$25)</f>
@@ -5572,7 +5572,7 @@
       </c>
       <c r="C151" s="92">
         <f>Scenarios!F83</f>
-        <v>0.53431923369705847</v>
+        <v>0.53430098503789192</v>
       </c>
     </row>
     <row r="153" spans="2:4">
@@ -5596,7 +5596,7 @@
       </c>
       <c r="C155" s="216">
         <f>Scenarios!C91</f>
-        <v>3.0421606295399433</v>
+        <v>3.0641084990366978</v>
       </c>
     </row>
     <row r="156" spans="2:4">
@@ -5606,7 +5606,7 @@
       </c>
       <c r="C156" s="216">
         <f>Scenarios!C92</f>
-        <v>18.27850334137457</v>
+        <v>18.405869823618687</v>
       </c>
     </row>
     <row r="157" spans="2:4">
@@ -5615,7 +5615,7 @@
       </c>
       <c r="C157" s="215">
         <f>Scenarios!C93</f>
-        <v>21.320663970914513</v>
+        <v>21.469978322655386</v>
       </c>
       <c r="D157" s="300" t="str">
         <f>IF($D$11="","",C157*$E$25)</f>
@@ -5641,7 +5641,7 @@
       </c>
       <c r="C159" s="92">
         <f>Scenarios!F93</f>
-        <v>0.35351239788853805</v>
+        <v>0.35348982021143449</v>
       </c>
     </row>
     <row r="161" spans="2:4">
@@ -5665,7 +5665,7 @@
       </c>
       <c r="C163" s="216">
         <f>Scenarios!C97</f>
-        <v>3.8583758501575951</v>
+        <v>3.8862123584623829</v>
       </c>
     </row>
     <row r="164" spans="2:4">
@@ -5675,7 +5675,7 @@
       </c>
       <c r="C164" s="216">
         <f>Scenarios!C98</f>
-        <v>26.546980570543475</v>
+        <v>26.731962648469928</v>
       </c>
     </row>
     <row r="165" spans="2:4">
@@ -5684,7 +5684,7 @@
       </c>
       <c r="C165" s="215">
         <f>Scenarios!C99</f>
-        <v>30.405356420701072</v>
+        <v>30.618175006932312</v>
       </c>
       <c r="D165" s="300" t="str">
         <f>IF($D$11="","",C165*$E$25)</f>
@@ -5710,7 +5710,7 @@
       </c>
       <c r="C167" s="92">
         <f>Scenarios!F99</f>
-        <v>7.8045318355053128E-2</v>
+        <v>7.8016683061031156E-2</v>
       </c>
     </row>
     <row r="169" spans="2:4">
@@ -5734,7 +5734,7 @@
       </c>
       <c r="C171" s="216">
         <f>Scenarios!C103</f>
-        <v>3.5795568159208964</v>
+        <v>3.6053817658230098</v>
       </c>
     </row>
     <row r="172" spans="2:4">
@@ -5744,7 +5744,7 @@
       </c>
       <c r="C172" s="216">
         <f>Scenarios!C104</f>
-        <v>23.638206575374465</v>
+        <v>23.802920018364638</v>
       </c>
     </row>
     <row r="173" spans="2:4">
@@ -5753,7 +5753,7 @@
       </c>
       <c r="C173" s="215">
         <f>Scenarios!C105</f>
-        <v>27.21776339129536</v>
+        <v>27.40830178418765</v>
       </c>
       <c r="D173" s="300" t="str">
         <f>IF($D$11="","",C173*$E$25)</f>
@@ -5779,7 +5779,7 @@
       </c>
       <c r="C175" s="92">
         <f>Scenarios!F105</f>
-        <v>0.15784352411507596</v>
+        <v>0.15781220534741391</v>
       </c>
     </row>
     <row r="177" spans="1:6" ht="13.9">
@@ -5793,13 +5793,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="359" t="s">
+      <c r="B179" s="365" t="s">
         <v>373</v>
       </c>
-      <c r="C179" s="360"/>
-      <c r="D179" s="360"/>
-      <c r="E179" s="360"/>
-      <c r="F179" s="360"/>
+      <c r="C179" s="358"/>
+      <c r="D179" s="358"/>
+      <c r="E179" s="358"/>
+      <c r="F179" s="358"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5836,13 +5836,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="361" t="s">
+      <c r="B188" s="359" t="s">
         <v>378</v>
       </c>
-      <c r="C188" s="361"/>
-      <c r="D188" s="361"/>
-      <c r="E188" s="361"/>
-      <c r="F188" s="361"/>
+      <c r="C188" s="359"/>
+      <c r="D188" s="359"/>
+      <c r="E188" s="359"/>
+      <c r="F188" s="359"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5850,22 +5850,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="358" t="s">
+      <c r="B191" s="364" t="s">
         <v>379</v>
       </c>
-      <c r="C191" s="358"/>
-      <c r="D191" s="358"/>
-      <c r="E191" s="358"/>
-      <c r="F191" s="358"/>
+      <c r="C191" s="364"/>
+      <c r="D191" s="364"/>
+      <c r="E191" s="364"/>
+      <c r="F191" s="364"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="358" t="s">
+      <c r="B192" s="364" t="s">
         <v>380</v>
       </c>
-      <c r="C192" s="358"/>
-      <c r="D192" s="358"/>
-      <c r="E192" s="358"/>
-      <c r="F192" s="358"/>
+      <c r="C192" s="364"/>
+      <c r="D192" s="364"/>
+      <c r="E192" s="364"/>
+      <c r="F192" s="364"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5889,6 +5889,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5905,17 +5916,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -6488,15 +6488,15 @@
       </c>
       <c r="C25" s="39">
         <f>0.164*Exchange_Rate</f>
-        <v>1.4836906980000002</v>
+        <v>1.4943948828800002</v>
       </c>
       <c r="D25" s="39">
         <f>0.137*Exchange_Rate</f>
-        <v>1.2394245465000002</v>
+        <v>1.2483664570400002</v>
       </c>
       <c r="E25" s="39">
         <f>0.11*Exchange_Rate</f>
-        <v>0.99515839500000003</v>
+        <v>1.0023380312000001</v>
       </c>
       <c r="F25" s="39"/>
       <c r="G25" s="39"/>
@@ -7870,15 +7870,15 @@
       </c>
       <c r="C65" s="73">
         <f>IF(C$4="","",C25)</f>
-        <v>1.4836906980000002</v>
+        <v>1.4943948828800002</v>
       </c>
       <c r="D65" s="73">
         <f t="shared" ref="D65:M65" si="33">IF(D$4="","",D25)</f>
-        <v>1.2394245465000002</v>
+        <v>1.2483664570400002</v>
       </c>
       <c r="E65" s="73">
         <f t="shared" si="33"/>
-        <v>0.99515839500000003</v>
+        <v>1.0023380312000001</v>
       </c>
       <c r="F65" s="73">
         <f t="shared" si="33"/>
@@ -9220,11 +9220,11 @@
       </c>
       <c r="C47" s="147">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>15.554251102065832</v>
+        <v>15.666468277580169</v>
       </c>
       <c r="D47" s="147">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>-5.879500305070005</v>
+        <v>-5.9219183497152414</v>
       </c>
       <c r="F47" s="253"/>
     </row>
@@ -9415,7 +9415,7 @@
       </c>
       <c r="D66" s="76">
         <f>C66-D75</f>
-        <v>412017.96453687374</v>
+        <v>409735.4541059254</v>
       </c>
       <c r="F66" s="5" t="s">
         <v>225</v>
@@ -9482,11 +9482,11 @@
       </c>
       <c r="C73" s="349">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35-Normalized_FCF!G91)/12</f>
-        <v>-649202.19721826271</v>
+        <v>-651484.70764921105</v>
       </c>
       <c r="D73" s="349">
         <f>(Normalized_FCF!C25+Normalized_FCF!C35-Normalized_FCF!C91)/12</f>
-        <v>-599545.03546312626</v>
+        <v>-601827.5458940746</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>348</v>
@@ -9498,11 +9498,11 @@
       </c>
       <c r="C74" s="258">
         <f>-$C$66/C73</f>
-        <v>1.5581632414899407</v>
+        <v>1.5527041358347147</v>
       </c>
       <c r="D74" s="258">
         <f>-$C$66/D73</f>
-        <v>1.6872177070378127</v>
+        <v>1.6808187111097128</v>
       </c>
       <c r="F74" s="253" t="s">
         <v>316</v>
@@ -9515,7 +9515,7 @@
       <c r="C75" s="320"/>
       <c r="D75" s="321">
         <f>MAX(-D73*D76,G5)</f>
-        <v>599545.03546312626</v>
+        <v>601827.5458940746</v>
       </c>
       <c r="F75" s="253" t="s">
         <v>349</v>
@@ -9630,11 +9630,11 @@
       </c>
       <c r="C86" s="76">
         <f>-DCF!C7*Exchange_Rate</f>
-        <v>-7839134.0842500003</v>
+        <v>-7895690.0366799999</v>
       </c>
       <c r="D86" s="223">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>-3.0635690787056866</v>
+        <v>-3.0856714008779034</v>
       </c>
       <c r="E86" s="240" t="str">
         <f>Market_currency</f>
@@ -9647,11 +9647,11 @@
       </c>
       <c r="C87" s="76">
         <f>DCF!C8*Exchange_Rate</f>
-        <v>3727483.0572698382</v>
+        <v>3733576.6216488294</v>
       </c>
       <c r="D87" s="223">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>1.4567172487321669</v>
+        <v>1.4590986412699074</v>
       </c>
       <c r="E87" s="240" t="str">
         <f>Market_currency</f>
@@ -9664,11 +9664,11 @@
       </c>
       <c r="C88" s="76">
         <f>DCF!C9*Exchange_Rate</f>
-        <v>34038.035866800004</v>
+        <v>34283.605532608002</v>
       </c>
       <c r="D88" s="223">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>1.3302218467077064E-2</v>
+        <v>1.3398188203881159E-2</v>
       </c>
       <c r="E88" s="240" t="str">
         <f>Market_currency</f>
@@ -9681,11 +9681,11 @@
       </c>
       <c r="C89" s="180">
         <f>SUM(C86:C88)</f>
-        <v>-4077612.9911133619</v>
+        <v>-4127829.8094985625</v>
       </c>
       <c r="D89" s="242">
         <f>SUM(D86:D88)</f>
-        <v>-1.5935496115064427</v>
+        <v>-1.6131745714041148</v>
       </c>
       <c r="E89" s="240" t="str">
         <f>Market_currency</f>
@@ -13197,20 +13197,20 @@
       </c>
       <c r="C90" s="113">
         <f>G90</f>
-        <v>1.4836906980000002</v>
+        <v>1.4943948828800002</v>
       </c>
       <c r="E90" s="268"/>
       <c r="G90" s="112">
         <f>Data!C65</f>
-        <v>1.4836906980000002</v>
+        <v>1.4943948828800002</v>
       </c>
       <c r="H90" s="112">
         <f>Data!D65</f>
-        <v>1.2394245465000002</v>
+        <v>1.2483664570400002</v>
       </c>
       <c r="I90" s="112">
         <f>Data!E65</f>
-        <v>0.99515839500000003</v>
+        <v>1.0023380312000001</v>
       </c>
       <c r="J90" s="112">
         <f>Data!F65</f>
@@ -13253,20 +13253,20 @@
       </c>
       <c r="C91" s="74">
         <f>C90*Common_Shares/scaling_factor</f>
-        <v>3796503.3666191525</v>
+        <v>3823893.4917905335</v>
       </c>
       <c r="E91" s="268"/>
       <c r="G91" s="74">
         <f t="shared" ref="G91:Q91" si="37">IF(G$4="","",G90*Common_Shares/scaling_factor)</f>
-        <v>3796503.3666191525</v>
+        <v>3823893.4917905335</v>
       </c>
       <c r="H91" s="74">
         <f t="shared" si="37"/>
-        <v>3171469.2757733162</v>
+        <v>3194350.0510689216</v>
       </c>
       <c r="I91" s="74">
         <f t="shared" si="37"/>
-        <v>2546435.1849274803</v>
+        <v>2564806.6103473091</v>
       </c>
       <c r="J91" s="74">
         <f t="shared" si="37"/>
@@ -13308,20 +13308,20 @@
       </c>
       <c r="C92" s="23">
         <f>C90/(C19*scaling_factor/Common_Shares)</f>
-        <v>5.4766798181084244</v>
+        <v>5.5161916876514638</v>
       </c>
       <c r="E92" s="268"/>
       <c r="G92" s="170">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",G90/(G19*scaling_factor/Common_Shares))</f>
-        <v>3.808385529471102</v>
+        <v>3.8358613792939305</v>
       </c>
       <c r="H92" s="170">
         <f t="shared" si="38"/>
-        <v>3.8628639863745691</v>
+        <v>3.8907328746355687</v>
       </c>
       <c r="I92" s="170">
         <f t="shared" si="38"/>
-        <v>3.7901953789063598</v>
+        <v>3.8175399946822925</v>
       </c>
       <c r="J92" s="170">
         <f t="shared" si="38"/>
@@ -13384,20 +13384,20 @@
       </c>
       <c r="C94" s="23">
         <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
-        <v>3.1104626792452832E-2</v>
+        <v>3.126349127364017E-2</v>
       </c>
       <c r="E94" s="268"/>
       <c r="G94" s="23">
         <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>3.1104626792452832E-2</v>
+        <v>3.126349127364017E-2</v>
       </c>
       <c r="H94" s="23">
         <f t="shared" si="39"/>
-        <v>2.5983743113207551E-2</v>
+        <v>2.6116453076150632E-2</v>
       </c>
       <c r="I94" s="23">
         <f t="shared" si="39"/>
-        <v>2.0862859433962263E-2</v>
+        <v>2.0969414878661091E-2</v>
       </c>
       <c r="J94" s="23">
         <f t="shared" si="39"/>
@@ -14526,38 +14526,38 @@
       </c>
       <c r="C125" s="177">
         <f>C16*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>2.4508997533606824</v>
+        <v>2.4685819320773672</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="265"/>
       <c r="F125" s="27"/>
       <c r="G125" s="177">
         <f t="shared" ref="G125:Q125" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>3.5245363452742358</v>
+        <v>3.5499643463441024</v>
       </c>
       <c r="H125" s="177">
         <f t="shared" si="49"/>
-        <v>2.9027537993693588</v>
+        <v>2.9236959090499384</v>
       </c>
       <c r="I125" s="177">
         <f t="shared" si="49"/>
-        <v>2.3753638296483075</v>
+        <v>2.3925010494368353</v>
       </c>
       <c r="J125" s="177">
         <f t="shared" si="49"/>
-        <v>1.2740982511446666</v>
+        <v>1.2832903174250045</v>
       </c>
       <c r="K125" s="177">
         <f t="shared" si="49"/>
-        <v>6.1547933649516349</v>
+        <v>6.1991975296238593</v>
       </c>
       <c r="L125" s="177">
         <f t="shared" si="49"/>
-        <v>8.2754902808790298</v>
+        <v>8.3351943540113744</v>
       </c>
       <c r="M125" s="177">
         <f t="shared" si="49"/>
-        <v>7.6562674857104289</v>
+        <v>7.7115041349448346</v>
       </c>
       <c r="N125" s="177" t="str">
         <f t="shared" si="49"/>
@@ -14583,38 +14583,38 @@
       </c>
       <c r="C126" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>5.138154619204785E-2</v>
+        <v>5.1643973474421914E-2</v>
       </c>
       <c r="D126" s="27"/>
       <c r="E126" s="265"/>
       <c r="F126" s="27"/>
       <c r="G126" s="77">
         <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
-        <v>7.3889650844323598E-2</v>
+        <v>7.4267036534395453E-2</v>
       </c>
       <c r="H126" s="77">
         <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
-        <v>6.0854377345269571E-2</v>
+        <v>6.1165186381797874E-2</v>
       </c>
       <c r="I126" s="77">
         <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
-        <v>4.9797983850069338E-2</v>
+        <v>5.0052323209975637E-2</v>
       </c>
       <c r="J126" s="77">
         <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
-        <v>2.6710655160265544E-2</v>
+        <v>2.6847077770397586E-2</v>
       </c>
       <c r="K126" s="77">
         <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
-        <v>0.12903130744133406</v>
+        <v>0.12969032488752844</v>
       </c>
       <c r="L126" s="77">
         <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
-        <v>0.17349036228257922</v>
+        <v>0.17437645092074006</v>
       </c>
       <c r="M126" s="77">
         <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
-        <v>0.16050875232097334</v>
+        <v>0.16132853838796726</v>
       </c>
       <c r="N126" s="77" t="str">
         <f t="shared" ref="N126" si="57">IF(N$4="","",N125/Market_Price)</f>
@@ -14640,31 +14640,31 @@
       <c r="C127" s="169"/>
       <c r="G127" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.9099483665455569E-3</v>
+        <v>6.8954924076197292E-3</v>
       </c>
       <c r="H127" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.5170784330624209E-3</v>
+        <v>5.5055364279723322E-3</v>
       </c>
       <c r="I127" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.8437714321871955E-3</v>
+        <v>3.8357300693583523E-3</v>
       </c>
       <c r="J127" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.4177691401620744E-3</v>
+        <v>2.4127110457265889E-3</v>
       </c>
       <c r="K127" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-4.45435229775135E-4</v>
+        <v>-4.445033569094966E-4</v>
       </c>
       <c r="L127" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.1115242267246703E-3</v>
+        <v>2.1071068120244096E-3</v>
       </c>
       <c r="M127" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.7056282556843574E-3</v>
+        <v>1.702059995735227E-3</v>
       </c>
       <c r="N127" s="23" t="str">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -15492,7 +15492,7 @@
       </c>
       <c r="C8" s="338">
         <f>BS!D66</f>
-        <v>412017.96453687374</v>
+        <v>409735.4541059254</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
@@ -15524,7 +15524,7 @@
       </c>
       <c r="C10" s="347">
         <f>C6-C7+C8+C9</f>
-        <v>8792114.8134090174</v>
+        <v>8789832.3029780686</v>
       </c>
       <c r="D10" t="str">
         <f>Reporting_currency</f>
@@ -15538,7 +15538,7 @@
       </c>
       <c r="C11" s="208">
         <f>Exchange_Rate</f>
-        <v>9.0468945000000005</v>
+        <v>9.1121639200000004</v>
       </c>
       <c r="D11" t="str">
         <f>Thesis!C15</f>
@@ -15552,7 +15552,7 @@
       </c>
       <c r="C12" s="111">
         <f>(C10*scaling_factor)/Common_Shares*Exchange_Rate</f>
-        <v>31.085113766635988</v>
+        <v>31.30125118962745</v>
       </c>
       <c r="D12" t="str">
         <f>Market_currency</f>
@@ -15605,7 +15605,7 @@
       </c>
       <c r="C18" s="140">
         <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>32.319128535698056</v>
+        <v>32.544168840031631</v>
       </c>
       <c r="D18" t="str">
         <f>Market_currency</f>
@@ -16701,23 +16701,23 @@
       </c>
       <c r="B65" s="124">
         <f>C12</f>
-        <v>31.085113766635988</v>
+        <v>31.30125118962745</v>
       </c>
       <c r="C65" s="124">
         <f>C12</f>
-        <v>31.085113766635988</v>
+        <v>31.30125118962745</v>
       </c>
       <c r="D65" s="124">
         <f>C12</f>
-        <v>31.085113766635988</v>
+        <v>31.30125118962745</v>
       </c>
       <c r="E65" s="141">
         <f>C12</f>
-        <v>31.085113766635988</v>
+        <v>31.30125118962745</v>
       </c>
       <c r="F65" s="124">
         <f>C12</f>
-        <v>31.085113766635988</v>
+        <v>31.30125118962745</v>
       </c>
       <c r="H65" s="120"/>
     </row>
@@ -16728,23 +16728,23 @@
       </c>
       <c r="B66" s="124">
         <f t="shared" ref="B66:F71" si="4">(B56-$C$7+$C$8+$C$9)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>31.085113766635988</v>
+        <v>31.301251189627447</v>
       </c>
       <c r="C66" s="124">
         <f t="shared" si="4"/>
-        <v>31.599550028425025</v>
+        <v>31.819398885924087</v>
       </c>
       <c r="D66" s="124">
         <f t="shared" si="4"/>
-        <v>32.650737645324128</v>
+        <v>32.878170365558205</v>
       </c>
       <c r="E66" s="124">
         <f t="shared" si="4"/>
-        <v>33.732771883280854</v>
+        <v>33.968011011242091</v>
       </c>
       <c r="F66" s="124">
         <f t="shared" si="4"/>
-        <v>35.416619764406832</v>
+        <v>35.664007124512182</v>
       </c>
       <c r="H66" s="120"/>
     </row>
@@ -16755,23 +16755,23 @@
       </c>
       <c r="B67" s="124">
         <f t="shared" si="4"/>
-        <v>31.085113766635995</v>
+        <v>31.301251189627454</v>
       </c>
       <c r="C67" s="124">
         <f t="shared" si="4"/>
-        <v>32.092782124930388</v>
+        <v>32.316189438081196</v>
       </c>
       <c r="D67" s="124">
         <f t="shared" si="4"/>
-        <v>34.256467934853255</v>
+        <v>34.495485302689225</v>
       </c>
       <c r="E67" s="124">
         <f t="shared" si="4"/>
-        <v>36.637702614129275</v>
+        <v>36.893899557387527</v>
       </c>
       <c r="F67" s="124">
         <f t="shared" si="4"/>
-        <v>40.675180851159801</v>
+        <v>40.960506448763873</v>
       </c>
       <c r="H67" s="120"/>
     </row>
@@ -16782,23 +16782,23 @@
       </c>
       <c r="B68" s="124">
         <f t="shared" si="4"/>
-        <v>31.085113766635995</v>
+        <v>31.301251189627454</v>
       </c>
       <c r="C68" s="124">
         <f t="shared" si="4"/>
-        <v>32.701746801091488</v>
+        <v>32.929547530260749</v>
       </c>
       <c r="D68" s="124">
         <f t="shared" si="4"/>
-        <v>36.342389199349981</v>
+        <v>36.596455584403891</v>
       </c>
       <c r="E68" s="124">
         <f t="shared" si="4"/>
-        <v>40.615911802844273</v>
+        <v>40.900809799970915</v>
       </c>
       <c r="F68" s="124">
         <f t="shared" si="4"/>
-        <v>48.495856422879427</v>
+        <v>48.837604802751429</v>
       </c>
       <c r="H68" s="120"/>
     </row>
@@ -16809,23 +16809,23 @@
       </c>
       <c r="B69" s="124">
         <f t="shared" si="4"/>
-        <v>31.085113766635999</v>
+        <v>31.301251189627465</v>
       </c>
       <c r="C69" s="124">
         <f t="shared" si="4"/>
-        <v>33.320222830060885</v>
+        <v>33.552485595533845</v>
       </c>
       <c r="D69" s="124">
         <f t="shared" si="4"/>
-        <v>38.576562495134247</v>
+        <v>38.846747471511982</v>
       </c>
       <c r="E69" s="124">
         <f t="shared" si="4"/>
-        <v>45.124754260236038</v>
+        <v>45.44218160011841</v>
       </c>
       <c r="F69" s="124">
         <f t="shared" si="4"/>
-        <v>58.198791160428208</v>
+        <v>58.610542006076464</v>
       </c>
       <c r="H69" s="120"/>
     </row>
@@ -16836,23 +16836,23 @@
       </c>
       <c r="B70" s="124">
         <f t="shared" si="4"/>
-        <v>31.085113766635999</v>
+        <v>31.301251189627465</v>
       </c>
       <c r="C70" s="124">
         <f t="shared" si="4"/>
-        <v>33.893270142093272</v>
+        <v>34.129667195380563</v>
       </c>
       <c r="D70" s="124">
         <f t="shared" si="4"/>
-        <v>40.763621554349498</v>
+        <v>41.0495852132686</v>
       </c>
       <c r="E70" s="124">
         <f t="shared" si="4"/>
-        <v>49.81032818349388</v>
+        <v>50.161559907006243</v>
       </c>
       <c r="F70" s="124">
         <f t="shared" si="4"/>
-        <v>69.312716863405001</v>
+        <v>69.804649862670317</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="13.15">
@@ -16862,23 +16862,23 @@
       </c>
       <c r="B71" s="124">
         <f t="shared" si="4"/>
-        <v>31.085113766635995</v>
+        <v>31.301251189627454</v>
       </c>
       <c r="C71" s="124">
         <f t="shared" si="4"/>
-        <v>34.396565519818147</v>
+        <v>34.636593630966537</v>
       </c>
       <c r="D71" s="124">
         <f t="shared" si="4"/>
-        <v>42.796430201423618</v>
+        <v>43.097059693061958</v>
       </c>
       <c r="E71" s="124">
         <f t="shared" si="4"/>
-        <v>54.447529578776937</v>
+        <v>54.832216699110099</v>
       </c>
       <c r="F71" s="124">
         <f t="shared" si="4"/>
-        <v>81.511712264000181</v>
+        <v>82.091655724134625</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="13.15">
@@ -16913,7 +16913,7 @@
       </c>
       <c r="E74" s="135">
         <f>INDEX(B$65:F$71, MATCH(D74, A$65:A$71, 0), MATCH(C74, B$64:F$64, 0))</f>
-        <v>40.675180851159801</v>
+        <v>40.960506448763873</v>
       </c>
       <c r="F74" s="142">
         <f>Scenarios!C58</f>
@@ -16935,7 +16935,7 @@
       </c>
       <c r="E75" s="135">
         <f>INDEX(B$65:F$71, MATCH(D75, A$65:A$71, 0), MATCH(C75, B$64:F$64, 0))</f>
-        <v>33.732771883280854</v>
+        <v>33.968011011242091</v>
       </c>
       <c r="F75" s="142">
         <f>Scenarios!C40*(1-F$74-F$78)</f>
@@ -16958,7 +16958,7 @@
       </c>
       <c r="E76" s="135">
         <f>INDEX(B$65:F$71, MATCH(D76, A$65:A$71, 0), MATCH(C76, B$64:F$64, 0))</f>
-        <v>32.650737645324128</v>
+        <v>32.878170365558205</v>
       </c>
       <c r="F76" s="142">
         <f>Scenarios!C28*(1-F$74-F$78)</f>
@@ -16981,7 +16981,7 @@
       </c>
       <c r="E77" s="135">
         <f>INDEX(B$65:F$71, MATCH(D77, A$65:A$71, 0), MATCH(C77, B$64:F$64, 0))</f>
-        <v>31.599550028425025</v>
+        <v>31.819398885924087</v>
       </c>
       <c r="F77" s="142">
         <f>Scenarios!C34*(1-F$74-F$78)</f>
@@ -17004,7 +17004,7 @@
       </c>
       <c r="E78" s="135">
         <f>INDEX(B$65:F$71, MATCH(D78, A$65:A$71, 0), MATCH(C78, B$64:F$64, 0))</f>
-        <v>31.085113766635995</v>
+        <v>31.301251189627454</v>
       </c>
       <c r="F78" s="142">
         <f>Scenarios!C52</f>
@@ -17186,7 +17186,7 @@
       </c>
       <c r="C4" s="114">
         <f>Normalized_FCF!C91*(1-dividend_tax_rate)</f>
-        <v>3796503.3666191525</v>
+        <v>3823893.4917905335</v>
       </c>
       <c r="D4" t="str">
         <f>Market_currency</f>
@@ -17218,7 +17218,7 @@
       </c>
       <c r="C6" s="319">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
-        <v>50620044.888255365</v>
+        <v>50985246.557207115</v>
       </c>
       <c r="D6" t="str">
         <f>Reporting_currency</f>
@@ -17234,7 +17234,7 @@
       </c>
       <c r="C7" s="111">
         <f>(C6*scaling_factor)/Common_Shares*Exchange_Rate</f>
-        <v>178.97057620583152</v>
+        <v>181.56228178682352</v>
       </c>
       <c r="D7" t="str">
         <f>Market_currency</f>
@@ -17287,7 +17287,7 @@
       </c>
       <c r="C13" s="140">
         <f>F47/Common_Shares*scaling_factor</f>
-        <v>20.52957288125792</v>
+        <v>20.677684845513436</v>
       </c>
       <c r="D13" t="str">
         <f>Market_currency</f>
@@ -17322,7 +17322,7 @@
       </c>
       <c r="C16" s="123">
         <f>C4*(1+D16)</f>
-        <v>3886680.2657399015</v>
+        <v>3914720.9781269296</v>
       </c>
       <c r="D16" s="138">
         <f>IF($C$12&lt;B16,0,DDM!$C$11)</f>
@@ -17334,7 +17334,7 @@
       </c>
       <c r="F16" s="125">
         <f t="shared" ref="F16:F46" si="1">C16*E16</f>
-        <v>3615516.5262696757</v>
+        <v>3641600.9098855159</v>
       </c>
       <c r="H16" s="120"/>
     </row>
@@ -17344,7 +17344,7 @@
       </c>
       <c r="C17" s="123">
         <f t="shared" ref="C17:C45" si="2">IF(ROW()-ROW($C$16)&lt;$C$12, $C$16*(1+D17)^(ROW()-ROW($C$16)), 0)</f>
-        <v>3978999.1024146988</v>
+        <v>4007705.8551678262</v>
       </c>
       <c r="D17" s="138">
         <f>IF($C$12&lt;B17,0,DDM!$C$11)</f>
@@ -17356,7 +17356,7 @@
       </c>
       <c r="F17" s="125">
         <f t="shared" si="1"/>
-        <v>3443157.68732478</v>
+        <v>3467998.5766730788</v>
       </c>
       <c r="H17" s="120"/>
     </row>
@@ -17366,7 +17366,7 @@
       </c>
       <c r="C18" s="123">
         <f t="shared" si="2"/>
-        <v>4073510.7532708212</v>
+        <v>4102899.3665932985</v>
       </c>
       <c r="D18" s="138">
         <f>IF($C$12&lt;B18,0,DDM!$C$11)</f>
@@ -17378,7 +17378,7 @@
       </c>
       <c r="F18" s="125">
         <f t="shared" si="1"/>
-        <v>3279015.5358563722</v>
+        <v>3302672.2107735313</v>
       </c>
       <c r="H18" s="120"/>
     </row>
@@ -17388,7 +17388,7 @@
       </c>
       <c r="C19" s="123">
         <f t="shared" si="2"/>
-        <v>4170267.3033887018</v>
+        <v>4200353.9732550457</v>
       </c>
       <c r="D19" s="138">
         <f>IF($C$12&lt;B19,0,DDM!$C$11)</f>
@@ -17400,7 +17400,7 @@
       </c>
       <c r="F19" s="125">
         <f t="shared" si="1"/>
-        <v>3122698.3660865542</v>
+        <v>3145227.2804216794</v>
       </c>
       <c r="H19" s="120"/>
     </row>
@@ -17410,7 +17410,7 @@
       </c>
       <c r="C20" s="123">
         <f t="shared" si="2"/>
-        <v>4269322.0750058619</v>
+        <v>4300123.3820874058</v>
       </c>
       <c r="D20" s="138">
         <f>IF($C$12&lt;B20,0,DDM!$C$11)</f>
@@ -17422,7 +17422,7 @@
       </c>
       <c r="F20" s="125">
         <f t="shared" si="1"/>
-        <v>2973833.1456282432</v>
+        <v>2995288.0619635596</v>
       </c>
       <c r="H20" s="120"/>
     </row>
@@ -17982,7 +17982,7 @@
       </c>
       <c r="C46" s="123">
         <f>C$16*(1+F4)^$C$12/Equity_Cost</f>
-        <v>51822403.54319869</v>
+        <v>52196279.708359063</v>
       </c>
       <c r="D46" s="139">
         <f>Terminal_Growth</f>
@@ -17994,7 +17994,7 @@
       </c>
       <c r="F46" s="125">
         <f t="shared" si="1"/>
-        <v>36097342.537146293</v>
+        <v>36357769.20741871</v>
       </c>
       <c r="H46" s="120"/>
     </row>
@@ -18005,7 +18005,7 @@
       </c>
       <c r="F47" s="137">
         <f>SUM(F16:F46)</f>
-        <v>52531563.798311919</v>
+        <v>52910556.247136071</v>
       </c>
       <c r="H47" s="120"/>
     </row>
@@ -18026,7 +18026,7 @@
     <row r="50" spans="1:8" ht="13.15">
       <c r="A50" s="133">
         <f>F47</f>
-        <v>52531563.798311919</v>
+        <v>52910556.247136071</v>
       </c>
       <c r="B50" s="131">
         <f>C73</f>
@@ -18056,19 +18056,19 @@
       </c>
       <c r="B51" s="123">
         <f t="dataTable" ref="B51:F56" dt2D="1" dtr="1" r1="C11" r2="C12"/>
-        <v>50620044.888255373</v>
+        <v>50985246.557207122</v>
       </c>
       <c r="C51" s="123">
-        <v>51416919.177836165</v>
+        <v>51787869.949167058</v>
       </c>
       <c r="D51" s="123">
-        <v>53045234.379644617</v>
+        <v>53427932.738923989</v>
       </c>
       <c r="E51" s="123">
-        <v>54721331.748199597</v>
+        <v>55116122.423036419</v>
       </c>
       <c r="F51" s="123">
-        <v>57329653.096636467</v>
+        <v>57743261.678721577</v>
       </c>
       <c r="H51" s="120"/>
     </row>
@@ -18077,19 +18077,19 @@
         <v>10</v>
       </c>
       <c r="B52" s="123">
-        <v>50620044.88825538</v>
+        <v>50985246.557207122</v>
       </c>
       <c r="C52" s="123">
-        <v>52180947.699337125</v>
+        <v>52557410.605076328</v>
       </c>
       <c r="D52" s="123">
-        <v>55532549.677514568</v>
+        <v>55933192.9378701</v>
       </c>
       <c r="E52" s="123">
-        <v>59221140.148905918</v>
+        <v>59648394.989697725</v>
       </c>
       <c r="F52" s="123">
-        <v>65475292.200012781</v>
+        <v>65947668.035303585</v>
       </c>
       <c r="H52" s="120"/>
     </row>
@@ -18098,19 +18098,19 @@
         <v>15</v>
       </c>
       <c r="B53" s="123">
-        <v>50620044.888255373</v>
+        <v>50985246.557207122</v>
       </c>
       <c r="C53" s="123">
-        <v>53124248.803361326</v>
+        <v>53507517.217437685</v>
       </c>
       <c r="D53" s="123">
-        <v>58763692.482235752</v>
+        <v>59187647.036516652</v>
       </c>
       <c r="E53" s="123">
-        <v>65383483.001714185</v>
+        <v>65855196.473458737</v>
       </c>
       <c r="F53" s="123">
-        <v>77589708.995949477</v>
+        <v>78149485.094160229</v>
       </c>
       <c r="H53" s="120"/>
     </row>
@@ -18119,19 +18119,19 @@
         <v>20</v>
       </c>
       <c r="B54" s="123">
-        <v>50620044.888255373</v>
+        <v>50985246.55720713</v>
       </c>
       <c r="C54" s="123">
-        <v>54082283.224367708</v>
+        <v>54472463.441273101</v>
       </c>
       <c r="D54" s="123">
-        <v>62224481.291498534</v>
+        <v>62673403.936025545</v>
       </c>
       <c r="E54" s="123">
-        <v>72367789.701966286</v>
+        <v>72889891.917320892</v>
       </c>
       <c r="F54" s="123">
-        <v>92619791.049154013</v>
+        <v>93288002.670534074</v>
       </c>
       <c r="H54" s="120"/>
     </row>
@@ -18140,19 +18140,19 @@
         <v>25</v>
       </c>
       <c r="B55" s="123">
-        <v>50620044.888255388</v>
+        <v>50985246.55720713</v>
       </c>
       <c r="C55" s="123">
-        <v>54969947.457219273</v>
+        <v>55366531.786567114</v>
       </c>
       <c r="D55" s="123">
-        <v>65612289.001675293</v>
+        <v>66085653.209471852</v>
       </c>
       <c r="E55" s="123">
-        <v>79625857.744039088</v>
+        <v>80200323.772349238</v>
       </c>
       <c r="F55" s="123">
-        <v>109835532.44773628</v>
+        <v>110627948.17649877</v>
       </c>
       <c r="H55" s="120"/>
     </row>
@@ -18161,19 +18161,19 @@
         <v>30</v>
       </c>
       <c r="B56" s="123">
-        <v>50620044.88825538</v>
+        <v>50985246.55720713</v>
       </c>
       <c r="C56" s="123">
-        <v>55749564.246243894</v>
+        <v>56151773.172589302</v>
       </c>
       <c r="D56" s="123">
-        <v>68761159.069382921</v>
+        <v>69257241.008990616</v>
       </c>
       <c r="E56" s="123">
-        <v>86808995.563014716</v>
+        <v>87435284.815219507</v>
       </c>
       <c r="F56" s="123">
-        <v>128732073.21576476</v>
+        <v>129660819.29036422</v>
       </c>
       <c r="H56" s="120"/>
     </row>
@@ -18223,23 +18223,23 @@
       </c>
       <c r="B60" s="124">
         <f>C7</f>
-        <v>178.97057620583152</v>
+        <v>181.56228178682352</v>
       </c>
       <c r="C60" s="124">
         <f>C7</f>
-        <v>178.97057620583152</v>
+        <v>181.56228178682352</v>
       </c>
       <c r="D60" s="124">
         <f>C7</f>
-        <v>178.97057620583152</v>
+        <v>181.56228178682352</v>
       </c>
       <c r="E60" s="141">
         <f>C7</f>
-        <v>178.97057620583152</v>
+        <v>181.56228178682352</v>
       </c>
       <c r="F60" s="124">
         <f>C7</f>
-        <v>178.97057620583152</v>
+        <v>181.56228178682352</v>
       </c>
       <c r="H60" s="120"/>
     </row>
@@ -18250,23 +18250,23 @@
       </c>
       <c r="B61" s="124">
         <f t="shared" ref="B61:F66" si="4">B51/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>178.97057620583155</v>
+        <v>181.56228178682355</v>
       </c>
       <c r="C61" s="124">
         <f t="shared" si="4"/>
-        <v>181.78797889847468</v>
+        <v>184.42048380211077</v>
       </c>
       <c r="D61" s="124">
         <f t="shared" si="4"/>
-        <v>187.54499690499142</v>
+        <v>190.260870237191</v>
       </c>
       <c r="E61" s="124">
         <f t="shared" si="4"/>
-        <v>193.47095197851135</v>
+        <v>196.27264014777705</v>
       </c>
       <c r="F61" s="124">
         <f t="shared" si="4"/>
-        <v>202.69284768583867</v>
+        <v>205.62807981008675</v>
       </c>
       <c r="H61" s="120"/>
     </row>
@@ -18277,23 +18277,23 @@
       </c>
       <c r="B62" s="124">
         <f t="shared" si="4"/>
-        <v>178.97057620583158</v>
+        <v>181.56228178682355</v>
       </c>
       <c r="C62" s="124">
         <f t="shared" si="4"/>
-        <v>184.48925316704887</v>
+        <v>187.16087571642359</v>
       </c>
       <c r="D62" s="124">
         <f t="shared" si="4"/>
-        <v>196.33906757498104</v>
+        <v>199.18228944970767</v>
       </c>
       <c r="E62" s="124">
         <f t="shared" si="4"/>
-        <v>209.38032748515181</v>
+        <v>212.41240222501915</v>
       </c>
       <c r="F62" s="124">
         <f t="shared" si="4"/>
-        <v>231.49230306194897</v>
+        <v>234.84458535617557</v>
       </c>
       <c r="H62" s="120"/>
     </row>
@@ -18304,23 +18304,23 @@
       </c>
       <c r="B63" s="124">
         <f t="shared" si="4"/>
-        <v>178.97057620583155</v>
+        <v>181.56228178682355</v>
       </c>
       <c r="C63" s="124">
         <f t="shared" si="4"/>
-        <v>187.82435771892136</v>
+        <v>190.54427652605827</v>
       </c>
       <c r="D63" s="124">
         <f t="shared" si="4"/>
-        <v>207.76299046641347</v>
+        <v>210.77164425370481</v>
       </c>
       <c r="E63" s="124">
         <f t="shared" si="4"/>
-        <v>231.16770546120077</v>
+        <v>234.51528719832314</v>
       </c>
       <c r="F63" s="124">
         <f t="shared" si="4"/>
-        <v>274.32363912955947</v>
+        <v>278.29616981925471</v>
       </c>
       <c r="H63" s="120"/>
     </row>
@@ -18331,23 +18331,23 @@
       </c>
       <c r="B64" s="124">
         <f t="shared" si="4"/>
-        <v>178.97057620583155</v>
+        <v>181.56228178682358</v>
       </c>
       <c r="C64" s="124">
         <f t="shared" si="4"/>
-        <v>191.21155290476193</v>
+        <v>193.98052230363942</v>
       </c>
       <c r="D64" s="124">
         <f t="shared" si="4"/>
-        <v>219.99884226559192</v>
+        <v>223.18468565616001</v>
       </c>
       <c r="E64" s="124">
         <f t="shared" si="4"/>
-        <v>255.86119195062867</v>
+        <v>259.5663645728315</v>
       </c>
       <c r="F64" s="124">
         <f t="shared" si="4"/>
-        <v>327.46350598311591</v>
+        <v>332.20556478417598</v>
       </c>
       <c r="H64" s="120"/>
     </row>
@@ -18358,23 +18358,23 @@
       </c>
       <c r="B65" s="124">
         <f t="shared" si="4"/>
-        <v>178.97057620583158</v>
+        <v>181.56228178682358</v>
       </c>
       <c r="C65" s="124">
         <f t="shared" si="4"/>
-        <v>194.34994955339099</v>
+        <v>197.16436664697926</v>
       </c>
       <c r="D65" s="124">
         <f t="shared" si="4"/>
-        <v>231.9766644762073</v>
+        <v>235.33596089648276</v>
       </c>
       <c r="E65" s="124">
         <f t="shared" si="4"/>
-        <v>281.52258009239</v>
+        <v>285.59935996016884</v>
       </c>
       <c r="F65" s="124">
         <f t="shared" si="4"/>
-        <v>388.33091858056548</v>
+        <v>393.95440949339303</v>
       </c>
     </row>
     <row r="66" spans="1:8" ht="13.15">
@@ -18384,23 +18384,23 @@
       </c>
       <c r="B66" s="124">
         <f t="shared" si="4"/>
-        <v>178.97057620583158</v>
+        <v>181.56228178682358</v>
       </c>
       <c r="C66" s="124">
         <f t="shared" si="4"/>
-        <v>197.10633719112397</v>
+        <v>199.96067003720935</v>
       </c>
       <c r="D66" s="124">
         <f t="shared" si="4"/>
-        <v>243.10970656771451</v>
+        <v>246.6302226025974</v>
       </c>
       <c r="E66" s="124">
         <f t="shared" si="4"/>
-        <v>306.91904738644087</v>
+        <v>311.36359813264494</v>
       </c>
       <c r="F66" s="124">
         <f t="shared" si="4"/>
-        <v>455.14091049220247</v>
+        <v>461.73188909252724</v>
       </c>
     </row>
     <row r="68" spans="1:8" ht="13.15">
@@ -18435,7 +18435,7 @@
       </c>
       <c r="E69" s="135">
         <f>INDEX(B$60:F$66, MATCH(D69, A$60:A$66, 0), MATCH(C69, B$59:F$59, 0))</f>
-        <v>231.49230306194897</v>
+        <v>234.84458535617557</v>
       </c>
       <c r="F69" s="142">
         <f>Scenarios!C58</f>
@@ -18457,7 +18457,7 @@
       </c>
       <c r="E70" s="135">
         <f>INDEX(B$60:F$66, MATCH(D70, A$60:A$66, 0), MATCH(C70, B$59:F$59, 0))</f>
-        <v>193.47095197851135</v>
+        <v>196.27264014777705</v>
       </c>
       <c r="F70" s="142">
         <f>Scenarios!C40*(1-F$69-F$73)</f>
@@ -18480,7 +18480,7 @@
       </c>
       <c r="E71" s="135">
         <f>INDEX(B$60:F$66, MATCH(D71, A$60:A$66, 0), MATCH(C71, B$59:F$59, 0))</f>
-        <v>187.54499690499142</v>
+        <v>190.260870237191</v>
       </c>
       <c r="F71" s="142">
         <f>Scenarios!C28*(1-F$69-F$73)</f>
@@ -18503,7 +18503,7 @@
       </c>
       <c r="E72" s="135">
         <f>INDEX(B$60:F$66, MATCH(D72, A$60:A$66, 0), MATCH(C72, B$59:F$59, 0))</f>
-        <v>181.78797889847468</v>
+        <v>184.42048380211077</v>
       </c>
       <c r="F72" s="142">
         <f>Scenarios!C34*(1-F$69-F$73)</f>
@@ -18526,7 +18526,7 @@
       </c>
       <c r="E73" s="135">
         <f>INDEX(B$60:F$66, MATCH(D73, A$60:A$66, 0), MATCH(C73, B$59:F$59, 0))</f>
-        <v>178.97057620583158</v>
+        <v>181.56228178682355</v>
       </c>
       <c r="F73" s="142">
         <f>Scenarios!C52</f>
@@ -18626,7 +18626,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-47.7</v>
+        <v>-47.8</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18646,7 +18646,7 @@
       </c>
       <c r="I4" s="124">
         <f t="shared" ref="I4:I13" si="0">IF(ROW()-3 &lt; $C$76, $C$77, IF(ROW()-3 = $C$76, $C$77 + $C$60, ""))</f>
-        <v>1.4836906980000002</v>
+        <v>1.4943948828800002</v>
       </c>
     </row>
     <row r="5" spans="2:9">
@@ -18655,7 +18655,7 @@
       </c>
       <c r="I5" s="124">
         <f t="shared" si="0"/>
-        <v>1.4836906980000002</v>
+        <v>1.4943948828800002</v>
       </c>
     </row>
     <row r="6" spans="2:9" ht="13.15">
@@ -18675,7 +18675,7 @@
       </c>
       <c r="I6" s="124">
         <f t="shared" si="0"/>
-        <v>34.462921701471871</v>
+        <v>34.703428543690912</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1">
@@ -18866,7 +18866,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>47.7</v>
+        <v>47.8</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -18881,7 +18881,7 @@
       </c>
       <c r="C22" s="160">
         <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
-        <v>31.085113766635988</v>
+        <v>31.30125118962745</v>
       </c>
       <c r="D22" t="str">
         <f>Market_currency</f>
@@ -18928,7 +18928,7 @@
       </c>
       <c r="C27" s="160">
         <f>IF(valuation_method="DCF",DCF!E76,DDM!E71)</f>
-        <v>32.650737645324128</v>
+        <v>32.878170365558205</v>
       </c>
       <c r="D27" s="160" t="str">
         <f>Market_currency</f>
@@ -18986,7 +18986,7 @@
       </c>
       <c r="C33" s="160">
         <f>IF(valuation_method="DCF",DCF!E77,DDM!E72)</f>
-        <v>31.599550028425025</v>
+        <v>31.819398885924087</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
@@ -19044,7 +19044,7 @@
       </c>
       <c r="C39" s="160">
         <f>IF(valuation_method="DCF",DCF!E75,DDM!E70)</f>
-        <v>33.732771883280854</v>
+        <v>33.968011011242091</v>
       </c>
       <c r="D39" t="str">
         <f>Market_currency</f>
@@ -19071,7 +19071,7 @@
       </c>
       <c r="C42" s="154">
         <f>C27*C28+C33*C34+C39*C40</f>
-        <v>32.656906969535655</v>
+        <v>32.88438419876816</v>
       </c>
       <c r="D42" t="str">
         <f>Market_currency</f>
@@ -19145,7 +19145,7 @@
       </c>
       <c r="C51" s="160">
         <f>IF(valuation_method="DCF",DCF!E78,DDM!E73)</f>
-        <v>31.085113766635995</v>
+        <v>31.301251189627454</v>
       </c>
       <c r="D51" t="str">
         <f>Market_currency</f>
@@ -19203,7 +19203,7 @@
       </c>
       <c r="C57" s="160">
         <f>IF(valuation_method="DCF",DCF!E74,DDM!E69)</f>
-        <v>40.675180851159801</v>
+        <v>40.960506448763873</v>
       </c>
       <c r="D57" t="str">
         <f>Market_currency</f>
@@ -19229,7 +19229,7 @@
       </c>
       <c r="C60" s="154">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
-        <v>32.979231003471874</v>
+        <v>33.20903366081091</v>
       </c>
       <c r="D60" t="str">
         <f>Market_currency</f>
@@ -19291,7 +19291,7 @@
       </c>
       <c r="C66" s="160">
         <f>IF(valuation_method="DCF",DCF!C18,DDM!C13)</f>
-        <v>32.319128535698056</v>
+        <v>32.544168840031631</v>
       </c>
       <c r="D66" s="160" t="str">
         <f>Market_currency</f>
@@ -19354,7 +19354,7 @@
       </c>
       <c r="F72" s="291">
         <f>BS!D89/C60</f>
-        <v>-4.8319792882335018E-2</v>
+        <v>-4.8576377978374566E-2</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="13.9">
@@ -19387,7 +19387,7 @@
       </c>
       <c r="C77" s="173">
         <f>Normalized_FCF!C90*(1-dividend_tax_rate)</f>
-        <v>1.4836906980000002</v>
+        <v>1.4943948828800002</v>
       </c>
       <c r="D77" t="str">
         <f>Market_currency</f>
@@ -19414,7 +19414,7 @@
       </c>
       <c r="C81" s="116">
         <f>PV(C80, C76, -C77, 0)</f>
-        <v>2.4588602363154526</v>
+        <v>2.4765998464640369</v>
       </c>
       <c r="D81" s="116"/>
       <c r="E81" s="100"/>
@@ -19426,7 +19426,7 @@
       </c>
       <c r="C82" s="116">
         <f>C60/(1+C80)^C76</f>
-        <v>12.898933329463057</v>
+        <v>12.988814417219093</v>
       </c>
       <c r="D82" s="116"/>
     </row>
@@ -19436,7 +19436,7 @@
       </c>
       <c r="C83" s="111">
         <f>C81+C82</f>
-        <v>15.357793565778509</v>
+        <v>15.46541426368313</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -19447,7 +19447,7 @@
       </c>
       <c r="F83" s="291">
         <f>(1-C83/C60)</f>
-        <v>0.53431923369705847</v>
+        <v>0.53430098503789192</v>
       </c>
     </row>
     <row r="84" spans="2:8">
@@ -19464,7 +19464,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>47.7</v>
+        <v>47.8</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19477,7 +19477,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>-8.0510996454183692E-2</v>
+        <v>-7.8960977262645282E-2</v>
       </c>
     </row>
     <row r="88" spans="2:8">
@@ -19503,7 +19503,7 @@
       </c>
       <c r="C91" s="116">
         <f>PV(C90, C76, -C77, 0)</f>
-        <v>3.0421606295399433</v>
+        <v>3.0641084990366978</v>
       </c>
       <c r="D91" s="116"/>
       <c r="E91" s="100"/>
@@ -19515,7 +19515,7 @@
       </c>
       <c r="C92" s="116">
         <f>C60/(1+C90)^C76</f>
-        <v>18.27850334137457</v>
+        <v>18.405869823618687</v>
       </c>
       <c r="D92" s="116"/>
     </row>
@@ -19525,7 +19525,7 @@
       </c>
       <c r="C93" s="111">
         <f>C91+C92</f>
-        <v>21.320663970914513</v>
+        <v>21.469978322655386</v>
       </c>
       <c r="D93" t="str">
         <f>Market_currency</f>
@@ -19536,7 +19536,7 @@
       </c>
       <c r="F93" s="291">
         <f>(1-C93/C60)</f>
-        <v>0.35351239788853805</v>
+        <v>0.35348982021143449</v>
       </c>
     </row>
     <row r="95" spans="2:8" ht="13.15">
@@ -19563,7 +19563,7 @@
       </c>
       <c r="C97" s="116">
         <f>PV(C96, C76, -C77, 0)</f>
-        <v>3.8583758501575951</v>
+        <v>3.8862123584623829</v>
       </c>
       <c r="D97" s="116"/>
       <c r="G97" s="2"/>
@@ -19575,7 +19575,7 @@
       </c>
       <c r="C98" s="116">
         <f>C60/(1+C96)^C76</f>
-        <v>26.546980570543475</v>
+        <v>26.731962648469928</v>
       </c>
       <c r="D98" s="116"/>
       <c r="G98" s="2"/>
@@ -19587,7 +19587,7 @@
       </c>
       <c r="C99" s="111">
         <f>C97+C98</f>
-        <v>30.405356420701072</v>
+        <v>30.618175006932312</v>
       </c>
       <c r="D99" t="s">
         <v>393</v>
@@ -19597,7 +19597,7 @@
       </c>
       <c r="F99" s="291">
         <f>(1-C99/C60)</f>
-        <v>7.8045318355053128E-2</v>
+        <v>7.8016683061031156E-2</v>
       </c>
     </row>
     <row r="100" spans="2:8">
@@ -19623,7 +19623,7 @@
       </c>
       <c r="C103" s="116">
         <f>PV(C102, C76, -C77, 0)</f>
-        <v>3.5795568159208964</v>
+        <v>3.6053817658230098</v>
       </c>
       <c r="D103" s="116"/>
     </row>
@@ -19633,7 +19633,7 @@
       </c>
       <c r="C104" s="116">
         <f>C60/(1+C102)^C76</f>
-        <v>23.638206575374465</v>
+        <v>23.802920018364638</v>
       </c>
       <c r="D104" s="116"/>
     </row>
@@ -19643,7 +19643,7 @@
       </c>
       <c r="C105" s="111">
         <f>C103+C104</f>
-        <v>27.21776339129536</v>
+        <v>27.40830178418765</v>
       </c>
       <c r="D105" t="s">
         <v>393</v>
@@ -19653,7 +19653,7 @@
       </c>
       <c r="F105" s="291">
         <f>(1-C105/C66)</f>
-        <v>0.15784352411507596</v>
+        <v>0.15781220534741391</v>
       </c>
     </row>
     <row r="106" spans="2:8">

--- a/financial_models/opportunities/1913.HK_Valuation.xlsx
+++ b/financial_models/opportunities/1913.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1352F6C0-7BC7-4DF4-81BD-10EECF1D943F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61A7A5F8-2839-4BDB-A79B-FBA488625559}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3896,29 +3896,29 @@
     <xf numFmtId="10" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4336,7 +4336,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>47.8</v>
+        <v>48.55</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4357,7 +4357,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>122311.78720000001</v>
+        <v>124230.90519999999</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4384,7 +4384,7 @@
         <v>1</v>
       </c>
       <c r="C16" s="50">
-        <v>9.1121639200000004</v>
+        <v>9.1025121200000001</v>
       </c>
       <c r="D16" s="50"/>
       <c r="E16" s="5"/>
@@ -4394,13 +4394,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="358" t="s">
+      <c r="B18" s="360" t="s">
         <v>356</v>
       </c>
-      <c r="C18" s="358"/>
-      <c r="D18" s="358"/>
-      <c r="E18" s="358"/>
-      <c r="F18" s="358"/>
+      <c r="C18" s="360"/>
+      <c r="D18" s="360"/>
+      <c r="E18" s="360"/>
+      <c r="F18" s="360"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4476,14 +4476,14 @@
       </c>
       <c r="C26" s="304">
         <f>C132</f>
-        <v>33.20903366081091</v>
+        <v>33.175058631690291</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>396</v>
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>-7.8960977262645282E-2</v>
+        <v>-8.4224595913299005E-2</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4515,7 +4515,7 @@
       </c>
       <c r="C29" s="310">
         <f>C149</f>
-        <v>15.46541426368313</v>
+        <v>15.449502583058539</v>
       </c>
       <c r="D29" s="310" t="str">
         <f>D149</f>
@@ -4534,7 +4534,7 @@
       </c>
       <c r="C30" s="311">
         <f>C157</f>
-        <v>21.469978322655386</v>
+        <v>21.447902335694522</v>
       </c>
       <c r="D30" s="311" t="str">
         <f>D157</f>
@@ -4553,7 +4553,7 @@
       </c>
       <c r="C31" s="311">
         <f>C165</f>
-        <v>30.618175006932312</v>
+        <v>30.586710088431154</v>
       </c>
       <c r="D31" s="311" t="str">
         <f>D165</f>
@@ -4572,7 +4572,7 @@
       </c>
       <c r="C32" s="311">
         <f>C173</f>
-        <v>27.40830178418765</v>
+        <v>27.380130931054907</v>
       </c>
       <c r="D32" s="311" t="str">
         <f>D173</f>
@@ -4600,22 +4600,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="358" t="s">
+      <c r="B36" s="360" t="s">
         <v>357</v>
       </c>
-      <c r="C36" s="358"/>
-      <c r="D36" s="358"/>
-      <c r="E36" s="358"/>
-      <c r="F36" s="358"/>
+      <c r="C36" s="360"/>
+      <c r="D36" s="360"/>
+      <c r="E36" s="360"/>
+      <c r="F36" s="360"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="360" t="s">
+      <c r="B37" s="363" t="s">
         <v>336</v>
       </c>
-      <c r="C37" s="360"/>
-      <c r="D37" s="360"/>
-      <c r="E37" s="360"/>
-      <c r="F37" s="360"/>
+      <c r="C37" s="363"/>
+      <c r="D37" s="363"/>
+      <c r="E37" s="363"/>
+      <c r="F37" s="363"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4627,13 +4627,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="359" t="s">
+      <c r="B40" s="361" t="s">
         <v>230</v>
       </c>
-      <c r="C40" s="359"/>
-      <c r="D40" s="359"/>
-      <c r="E40" s="359"/>
-      <c r="F40" s="359"/>
+      <c r="C40" s="361"/>
+      <c r="D40" s="361"/>
+      <c r="E40" s="361"/>
+      <c r="F40" s="361"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4653,13 +4653,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="359" t="s">
+      <c r="B43" s="361" t="s">
         <v>232</v>
       </c>
-      <c r="C43" s="359"/>
-      <c r="D43" s="359"/>
-      <c r="E43" s="359"/>
-      <c r="F43" s="359"/>
+      <c r="C43" s="361"/>
+      <c r="D43" s="361"/>
+      <c r="E43" s="361"/>
+      <c r="F43" s="361"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4688,13 +4688,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="359" t="s">
+      <c r="B47" s="361" t="s">
         <v>235</v>
       </c>
-      <c r="C47" s="359"/>
-      <c r="D47" s="359"/>
-      <c r="E47" s="359"/>
-      <c r="F47" s="359"/>
+      <c r="C47" s="361"/>
+      <c r="D47" s="361"/>
+      <c r="E47" s="361"/>
+      <c r="F47" s="361"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4710,13 +4710,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="359" t="s">
+      <c r="B50" s="361" t="s">
         <v>239</v>
       </c>
-      <c r="C50" s="359"/>
-      <c r="D50" s="359"/>
-      <c r="E50" s="359"/>
-      <c r="F50" s="359"/>
+      <c r="C50" s="361"/>
+      <c r="D50" s="361"/>
+      <c r="E50" s="361"/>
+      <c r="F50" s="361"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4780,13 +4780,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="359" t="s">
+      <c r="B58" s="361" t="s">
         <v>240</v>
       </c>
-      <c r="C58" s="359"/>
-      <c r="D58" s="359"/>
-      <c r="E58" s="359"/>
-      <c r="F58" s="359"/>
+      <c r="C58" s="361"/>
+      <c r="D58" s="361"/>
+      <c r="E58" s="361"/>
+      <c r="F58" s="361"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4802,7 +4802,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="359" t="s">
+      <c r="B61" s="361" t="s">
         <v>335</v>
       </c>
       <c r="C61" s="362"/>
@@ -4824,22 +4824,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="358" t="s">
+      <c r="B64" s="360" t="s">
         <v>340</v>
       </c>
-      <c r="C64" s="358"/>
-      <c r="D64" s="358"/>
-      <c r="E64" s="358"/>
-      <c r="F64" s="358"/>
+      <c r="C64" s="360"/>
+      <c r="D64" s="360"/>
+      <c r="E64" s="360"/>
+      <c r="F64" s="360"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="358" t="s">
+      <c r="B65" s="360" t="s">
         <v>358</v>
       </c>
-      <c r="C65" s="358"/>
-      <c r="D65" s="358"/>
-      <c r="E65" s="358"/>
-      <c r="F65" s="358"/>
+      <c r="C65" s="360"/>
+      <c r="D65" s="360"/>
+      <c r="E65" s="360"/>
+      <c r="F65" s="360"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4873,7 +4873,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>5.1643973474421914E-2</v>
+        <v>5.0792320432604524E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4883,14 +4883,14 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>3.126349127364017E-2</v>
+        <v>3.0747929715345009E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>444</v>
       </c>
       <c r="F70" s="315">
         <f>Normalized_FCF!C92</f>
-        <v>5.5161916876514638</v>
+        <v>5.5103488187787892</v>
       </c>
     </row>
     <row r="72" spans="1:6">
@@ -4974,22 +4974,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.6" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="358" t="s">
+      <c r="B80" s="360" t="s">
         <v>359</v>
       </c>
-      <c r="C80" s="358"/>
-      <c r="D80" s="358"/>
-      <c r="E80" s="358"/>
-      <c r="F80" s="358"/>
+      <c r="C80" s="360"/>
+      <c r="D80" s="360"/>
+      <c r="E80" s="360"/>
+      <c r="F80" s="360"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="360" t="s">
+      <c r="B81" s="363" t="s">
         <v>251</v>
       </c>
-      <c r="C81" s="360"/>
-      <c r="D81" s="360"/>
-      <c r="E81" s="360"/>
-      <c r="F81" s="360"/>
+      <c r="C81" s="363"/>
+      <c r="D81" s="363"/>
+      <c r="E81" s="363"/>
+      <c r="F81" s="363"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5033,22 +5033,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="358" t="s">
+      <c r="B89" s="360" t="s">
         <v>360</v>
       </c>
-      <c r="C89" s="358"/>
-      <c r="D89" s="358"/>
-      <c r="E89" s="358"/>
-      <c r="F89" s="358"/>
+      <c r="C89" s="360"/>
+      <c r="D89" s="360"/>
+      <c r="E89" s="360"/>
+      <c r="F89" s="360"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="358" t="s">
+      <c r="B90" s="360" t="s">
         <v>361</v>
       </c>
-      <c r="C90" s="358"/>
-      <c r="D90" s="358"/>
-      <c r="E90" s="358"/>
-      <c r="F90" s="358"/>
+      <c r="C90" s="360"/>
+      <c r="D90" s="360"/>
+      <c r="E90" s="360"/>
+      <c r="F90" s="360"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5064,7 +5064,7 @@
       </c>
       <c r="C93" s="223">
         <f>DCF!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>32.914425761031559</v>
+        <v>32.879562093372662</v>
       </c>
       <c r="D93" s="1" t="str">
         <f>Market_currency</f>
@@ -5085,13 +5085,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="358" t="s">
+      <c r="B97" s="360" t="s">
         <v>362</v>
       </c>
-      <c r="C97" s="358"/>
-      <c r="D97" s="358"/>
-      <c r="E97" s="358"/>
-      <c r="F97" s="358"/>
+      <c r="C97" s="360"/>
+      <c r="D97" s="360"/>
+      <c r="E97" s="360"/>
+      <c r="F97" s="360"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5104,13 +5104,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="358" t="s">
+      <c r="B101" s="360" t="s">
         <v>341</v>
       </c>
-      <c r="C101" s="358"/>
-      <c r="D101" s="358"/>
-      <c r="E101" s="358"/>
-      <c r="F101" s="358"/>
+      <c r="C101" s="360"/>
+      <c r="D101" s="360"/>
+      <c r="E101" s="360"/>
+      <c r="F101" s="360"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="C103" s="223">
         <f>C102*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>3.0856714008779034</v>
+        <v>3.0824029913663464</v>
       </c>
       <c r="D103" s="1" t="str">
         <f>Market_currency</f>
@@ -5180,7 +5180,7 @@
       </c>
       <c r="C109" s="349">
         <f>DCF!C8</f>
-        <v>409735.4541059254</v>
+        <v>410072.98329152912</v>
       </c>
       <c r="D109" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5193,7 +5193,7 @@
       </c>
       <c r="C110" s="223">
         <f>C109*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>1.4590986412699074</v>
+        <v>1.4587538261700301</v>
       </c>
       <c r="D110" s="1" t="str">
         <f>Market_currency</f>
@@ -5224,7 +5224,7 @@
       </c>
       <c r="C114" s="223">
         <f>C113*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>1.3398188203881159E-2</v>
+        <v>1.3383996554779853E-2</v>
       </c>
       <c r="D114" s="1" t="str">
         <f>Market_currency</f>
@@ -5232,13 +5232,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="358" t="s">
+      <c r="B116" s="360" t="s">
         <v>363</v>
       </c>
-      <c r="C116" s="358"/>
-      <c r="D116" s="358"/>
-      <c r="E116" s="358"/>
-      <c r="F116" s="358"/>
+      <c r="C116" s="360"/>
+      <c r="D116" s="360"/>
+      <c r="E116" s="360"/>
+      <c r="F116" s="360"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="C118" s="223">
         <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
-        <v>31.30125118962745</v>
+        <v>31.269296924731126</v>
       </c>
       <c r="D118" s="1" t="str">
         <f>Market_currency</f>
@@ -5259,7 +5259,7 @@
       </c>
       <c r="C119" s="223">
         <f>BS!D47</f>
-        <v>-5.9219183497152414</v>
+        <v>-5.9156457264361171</v>
       </c>
       <c r="D119" s="1" t="str">
         <f>Market_currency</f>
@@ -5277,13 +5277,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B123" s="359" t="s">
+      <c r="B123" s="361" t="s">
         <v>364</v>
       </c>
-      <c r="C123" s="359"/>
-      <c r="D123" s="359"/>
-      <c r="E123" s="359"/>
-      <c r="F123" s="359"/>
+      <c r="C123" s="361"/>
+      <c r="D123" s="361"/>
+      <c r="E123" s="361"/>
+      <c r="F123" s="361"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5317,7 +5317,7 @@
       </c>
       <c r="E126" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E74,DDM!E69),2)&amp;" "&amp;Market_currency</f>
-        <v>40.96 HKD</v>
+        <v>40.92 HKD</v>
       </c>
       <c r="F126" s="232">
         <f>DCF!F74</f>
@@ -5339,7 +5339,7 @@
       </c>
       <c r="E127" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E75,DDM!E70),2)&amp;" "&amp;Market_currency</f>
-        <v>33.97 HKD</v>
+        <v>33.93 HKD</v>
       </c>
       <c r="F127" s="221">
         <f>DCF!F75</f>
@@ -5361,7 +5361,7 @@
       </c>
       <c r="E128" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E76,DDM!E71),2)&amp;" "&amp;Market_currency</f>
-        <v>32.88 HKD</v>
+        <v>32.84 HKD</v>
       </c>
       <c r="F128" s="221">
         <f>DCF!F76</f>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="E129" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E77,DDM!E72),2)&amp;" "&amp;Market_currency</f>
-        <v>31.82 HKD</v>
+        <v>31.79 HKD</v>
       </c>
       <c r="F129" s="221">
         <f>DCF!F77</f>
@@ -5405,7 +5405,7 @@
       </c>
       <c r="E130" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E78,DDM!E73),2)&amp;" "&amp;Market_currency</f>
-        <v>31.3 HKD</v>
+        <v>31.27 HKD</v>
       </c>
       <c r="F130" s="221">
         <f>DCF!F78</f>
@@ -5418,7 +5418,7 @@
       </c>
       <c r="C132" s="217">
         <f>Scenarios!C60</f>
-        <v>33.20903366081091</v>
+        <v>33.175058631690291</v>
       </c>
       <c r="D132" s="212" t="str">
         <f>Market_currency</f>
@@ -5426,13 +5426,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="363" t="s">
+      <c r="B134" s="364" t="s">
         <v>367</v>
       </c>
-      <c r="C134" s="363"/>
-      <c r="D134" s="363"/>
-      <c r="E134" s="363"/>
-      <c r="F134" s="363"/>
+      <c r="C134" s="364"/>
+      <c r="D134" s="364"/>
+      <c r="E134" s="364"/>
+      <c r="F134" s="364"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5445,22 +5445,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="361" t="s">
+      <c r="B138" s="365" t="s">
         <v>365</v>
       </c>
-      <c r="C138" s="361"/>
-      <c r="D138" s="361"/>
-      <c r="E138" s="361"/>
-      <c r="F138" s="361"/>
+      <c r="C138" s="365"/>
+      <c r="D138" s="365"/>
+      <c r="E138" s="365"/>
+      <c r="F138" s="365"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="358" t="s">
+      <c r="B139" s="360" t="s">
         <v>366</v>
       </c>
-      <c r="C139" s="358"/>
-      <c r="D139" s="358"/>
-      <c r="E139" s="358"/>
-      <c r="F139" s="358"/>
+      <c r="C139" s="360"/>
+      <c r="D139" s="360"/>
+      <c r="E139" s="360"/>
+      <c r="F139" s="360"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5491,7 +5491,7 @@
       </c>
       <c r="C143" s="213">
         <f>Scenarios!C77</f>
-        <v>1.4943948828800002</v>
+        <v>1.4928119876800001</v>
       </c>
       <c r="D143" s="212" t="str">
         <f>Market_currency</f>
@@ -5527,7 +5527,7 @@
       </c>
       <c r="C147" s="216">
         <f>Scenarios!C81</f>
-        <v>2.4765998464640369</v>
+        <v>2.4739765786422589</v>
       </c>
     </row>
     <row r="148" spans="2:4">
@@ -5537,7 +5537,7 @@
       </c>
       <c r="C148" s="216">
         <f>Scenarios!C82</f>
-        <v>12.988814417219093</v>
+        <v>12.975526004416281</v>
       </c>
     </row>
     <row r="149" spans="2:4">
@@ -5546,7 +5546,7 @@
       </c>
       <c r="C149" s="215">
         <f>Scenarios!C83</f>
-        <v>15.46541426368313</v>
+        <v>15.449502583058539</v>
       </c>
       <c r="D149" s="300" t="str">
         <f>IF($D$11="","",C149*$E$25)</f>
@@ -5572,7 +5572,7 @@
       </c>
       <c r="C151" s="92">
         <f>Scenarios!F83</f>
-        <v>0.53430098503789192</v>
+        <v>0.53430368414479645</v>
       </c>
     </row>
     <row r="153" spans="2:4">
@@ -5596,7 +5596,7 @@
       </c>
       <c r="C155" s="216">
         <f>Scenarios!C91</f>
-        <v>3.0641084990366978</v>
+        <v>3.060862929414526</v>
       </c>
     </row>
     <row r="156" spans="2:4">
@@ -5606,7 +5606,7 @@
       </c>
       <c r="C156" s="216">
         <f>Scenarios!C92</f>
-        <v>18.405869823618687</v>
+        <v>18.387039406279996</v>
       </c>
     </row>
     <row r="157" spans="2:4">
@@ -5615,7 +5615,7 @@
       </c>
       <c r="C157" s="215">
         <f>Scenarios!C93</f>
-        <v>21.469978322655386</v>
+        <v>21.447902335694522</v>
       </c>
       <c r="D157" s="300" t="str">
         <f>IF($D$11="","",C157*$E$25)</f>
@@ -5641,7 +5641,7 @@
       </c>
       <c r="C159" s="92">
         <f>Scenarios!F93</f>
-        <v>0.35348982021143449</v>
+        <v>0.3534931596109816</v>
       </c>
     </row>
     <row r="161" spans="2:4">
@@ -5665,7 +5665,7 @@
       </c>
       <c r="C163" s="216">
         <f>Scenarios!C97</f>
-        <v>3.8862123584623829</v>
+        <v>3.8820959987512631</v>
       </c>
     </row>
     <row r="164" spans="2:4">
@@ -5675,7 +5675,7 @@
       </c>
       <c r="C164" s="216">
         <f>Scenarios!C98</f>
-        <v>26.731962648469928</v>
+        <v>26.70461408967989</v>
       </c>
     </row>
     <row r="165" spans="2:4">
@@ -5684,7 +5684,7 @@
       </c>
       <c r="C165" s="215">
         <f>Scenarios!C99</f>
-        <v>30.618175006932312</v>
+        <v>30.586710088431154</v>
       </c>
       <c r="D165" s="300" t="str">
         <f>IF($D$11="","",C165*$E$25)</f>
@@ -5710,7 +5710,7 @@
       </c>
       <c r="C167" s="92">
         <f>Scenarios!F99</f>
-        <v>7.8016683061031156E-2</v>
+        <v>7.8020918425344754E-2</v>
       </c>
     </row>
     <row r="169" spans="2:4">
@@ -5734,7 +5734,7 @@
       </c>
       <c r="C171" s="216">
         <f>Scenarios!C103</f>
-        <v>3.6053817658230098</v>
+        <v>3.6015628679154563</v>
       </c>
     </row>
     <row r="172" spans="2:4">
@@ -5744,7 +5744,7 @@
       </c>
       <c r="C172" s="216">
         <f>Scenarios!C104</f>
-        <v>23.802920018364638</v>
+        <v>23.778568063139453</v>
       </c>
     </row>
     <row r="173" spans="2:4">
@@ -5753,7 +5753,7 @@
       </c>
       <c r="C173" s="215">
         <f>Scenarios!C105</f>
-        <v>27.40830178418765</v>
+        <v>27.380130931054907</v>
       </c>
       <c r="D173" s="300" t="str">
         <f>IF($D$11="","",C173*$E$25)</f>
@@ -5779,7 +5779,7 @@
       </c>
       <c r="C175" s="92">
         <f>Scenarios!F105</f>
-        <v>0.15781220534741391</v>
+        <v>0.15781683763635923</v>
       </c>
     </row>
     <row r="177" spans="1:6" ht="13.9">
@@ -5793,13 +5793,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="365" t="s">
+      <c r="B179" s="359" t="s">
         <v>373</v>
       </c>
-      <c r="C179" s="358"/>
-      <c r="D179" s="358"/>
-      <c r="E179" s="358"/>
-      <c r="F179" s="358"/>
+      <c r="C179" s="360"/>
+      <c r="D179" s="360"/>
+      <c r="E179" s="360"/>
+      <c r="F179" s="360"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5836,13 +5836,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="359" t="s">
+      <c r="B188" s="361" t="s">
         <v>378</v>
       </c>
-      <c r="C188" s="359"/>
-      <c r="D188" s="359"/>
-      <c r="E188" s="359"/>
-      <c r="F188" s="359"/>
+      <c r="C188" s="361"/>
+      <c r="D188" s="361"/>
+      <c r="E188" s="361"/>
+      <c r="F188" s="361"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5850,22 +5850,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="364" t="s">
+      <c r="B191" s="358" t="s">
         <v>379</v>
       </c>
-      <c r="C191" s="364"/>
-      <c r="D191" s="364"/>
-      <c r="E191" s="364"/>
-      <c r="F191" s="364"/>
+      <c r="C191" s="358"/>
+      <c r="D191" s="358"/>
+      <c r="E191" s="358"/>
+      <c r="F191" s="358"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="364" t="s">
+      <c r="B192" s="358" t="s">
         <v>380</v>
       </c>
-      <c r="C192" s="364"/>
-      <c r="D192" s="364"/>
-      <c r="E192" s="364"/>
-      <c r="F192" s="364"/>
+      <c r="C192" s="358"/>
+      <c r="D192" s="358"/>
+      <c r="E192" s="358"/>
+      <c r="F192" s="358"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5889,17 +5889,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5916,6 +5905,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -6488,15 +6488,15 @@
       </c>
       <c r="C25" s="39">
         <f>0.164*Exchange_Rate</f>
-        <v>1.4943948828800002</v>
+        <v>1.4928119876800001</v>
       </c>
       <c r="D25" s="39">
         <f>0.137*Exchange_Rate</f>
-        <v>1.2483664570400002</v>
+        <v>1.2470441604400002</v>
       </c>
       <c r="E25" s="39">
         <f>0.11*Exchange_Rate</f>
-        <v>1.0023380312000001</v>
+        <v>1.0012763332000001</v>
       </c>
       <c r="F25" s="39"/>
       <c r="G25" s="39"/>
@@ -7870,15 +7870,15 @@
       </c>
       <c r="C65" s="73">
         <f>IF(C$4="","",C25)</f>
-        <v>1.4943948828800002</v>
+        <v>1.4928119876800001</v>
       </c>
       <c r="D65" s="73">
         <f t="shared" ref="D65:M65" si="33">IF(D$4="","",D25)</f>
-        <v>1.2483664570400002</v>
+        <v>1.2470441604400002</v>
       </c>
       <c r="E65" s="73">
         <f t="shared" si="33"/>
-        <v>1.0023380312000001</v>
+        <v>1.0012763332000001</v>
       </c>
       <c r="F65" s="73">
         <f t="shared" si="33"/>
@@ -9220,11 +9220,11 @@
       </c>
       <c r="C47" s="147">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>15.666468277580169</v>
+        <v>15.649874017440746</v>
       </c>
       <c r="D47" s="147">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>-5.9219183497152414</v>
+        <v>-5.9156457264361171</v>
       </c>
       <c r="F47" s="253"/>
     </row>
@@ -9415,7 +9415,7 @@
       </c>
       <c r="D66" s="76">
         <f>C66-D75</f>
-        <v>409735.4541059254</v>
+        <v>410072.98329152912</v>
       </c>
       <c r="F66" s="5" t="s">
         <v>225</v>
@@ -9482,11 +9482,11 @@
       </c>
       <c r="C73" s="349">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35-Normalized_FCF!G91)/12</f>
-        <v>-651484.70764921105</v>
+        <v>-651147.17846360744</v>
       </c>
       <c r="D73" s="349">
         <f>(Normalized_FCF!C25+Normalized_FCF!C35-Normalized_FCF!C91)/12</f>
-        <v>-601827.5458940746</v>
+        <v>-601490.01670847088</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>348</v>
@@ -9498,11 +9498,11 @@
       </c>
       <c r="C74" s="258">
         <f>-$C$66/C73</f>
-        <v>1.5527041358347147</v>
+        <v>1.5535089968243427</v>
       </c>
       <c r="D74" s="258">
         <f>-$C$66/D73</f>
-        <v>1.6808187111097128</v>
+        <v>1.6817619110880149</v>
       </c>
       <c r="F74" s="253" t="s">
         <v>316</v>
@@ -9515,7 +9515,7 @@
       <c r="C75" s="320"/>
       <c r="D75" s="321">
         <f>MAX(-D73*D76,G5)</f>
-        <v>601827.5458940746</v>
+        <v>601490.01670847088</v>
       </c>
       <c r="F75" s="253" t="s">
         <v>349</v>
@@ -9630,11 +9630,11 @@
       </c>
       <c r="C86" s="76">
         <f>-DCF!C7*Exchange_Rate</f>
-        <v>-7895690.0366799999</v>
+        <v>-7887326.7519800002</v>
       </c>
       <c r="D86" s="223">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>-3.0856714008779034</v>
+        <v>-3.0824029913663464</v>
       </c>
       <c r="E86" s="240" t="str">
         <f>Market_currency</f>
@@ -9647,11 +9647,11 @@
       </c>
       <c r="C87" s="76">
         <f>DCF!C8*Exchange_Rate</f>
-        <v>3733576.6216488294</v>
+        <v>3732694.3004957014</v>
       </c>
       <c r="D87" s="223">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>1.4590986412699074</v>
+        <v>1.4587538261700301</v>
       </c>
       <c r="E87" s="240" t="str">
         <f>Market_currency</f>
@@ -9664,11 +9664,11 @@
       </c>
       <c r="C88" s="76">
         <f>DCF!C9*Exchange_Rate</f>
-        <v>34283.605532608002</v>
+        <v>34247.291600288001</v>
       </c>
       <c r="D88" s="223">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>1.3398188203881159E-2</v>
+        <v>1.3383996554779853E-2</v>
       </c>
       <c r="E88" s="240" t="str">
         <f>Market_currency</f>
@@ -9681,11 +9681,11 @@
       </c>
       <c r="C89" s="180">
         <f>SUM(C86:C88)</f>
-        <v>-4127829.8094985625</v>
+        <v>-4120385.1598840109</v>
       </c>
       <c r="D89" s="242">
         <f>SUM(D86:D88)</f>
-        <v>-1.6131745714041148</v>
+        <v>-1.6102651686415363</v>
       </c>
       <c r="E89" s="240" t="str">
         <f>Market_currency</f>
@@ -13197,20 +13197,20 @@
       </c>
       <c r="C90" s="113">
         <f>G90</f>
-        <v>1.4943948828800002</v>
+        <v>1.4928119876800001</v>
       </c>
       <c r="E90" s="268"/>
       <c r="G90" s="112">
         <f>Data!C65</f>
-        <v>1.4943948828800002</v>
+        <v>1.4928119876800001</v>
       </c>
       <c r="H90" s="112">
         <f>Data!D65</f>
-        <v>1.2483664570400002</v>
+        <v>1.2470441604400002</v>
       </c>
       <c r="I90" s="112">
         <f>Data!E65</f>
-        <v>1.0023380312000001</v>
+        <v>1.0012763332000001</v>
       </c>
       <c r="J90" s="112">
         <f>Data!F65</f>
@@ -13253,20 +13253,20 @@
       </c>
       <c r="C91" s="74">
         <f>C90*Common_Shares/scaling_factor</f>
-        <v>3823893.4917905335</v>
+        <v>3819843.1415632889</v>
       </c>
       <c r="E91" s="268"/>
       <c r="G91" s="74">
         <f t="shared" ref="G91:Q91" si="37">IF(G$4="","",G90*Common_Shares/scaling_factor)</f>
-        <v>3823893.4917905335</v>
+        <v>3819843.1415632889</v>
       </c>
       <c r="H91" s="74">
         <f t="shared" si="37"/>
-        <v>3194350.0510689216</v>
+        <v>3190966.526793723</v>
       </c>
       <c r="I91" s="74">
         <f t="shared" si="37"/>
-        <v>2564806.6103473091</v>
+        <v>2562089.9120241571</v>
       </c>
       <c r="J91" s="74">
         <f t="shared" si="37"/>
@@ -13308,20 +13308,20 @@
       </c>
       <c r="C92" s="23">
         <f>C90/(C19*scaling_factor/Common_Shares)</f>
-        <v>5.5161916876514638</v>
+        <v>5.5103488187787892</v>
       </c>
       <c r="E92" s="268"/>
       <c r="G92" s="170">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",G90/(G19*scaling_factor/Common_Shares))</f>
-        <v>3.8358613792939305</v>
+        <v>3.8317983524228478</v>
       </c>
       <c r="H92" s="170">
         <f t="shared" si="38"/>
-        <v>3.8907328746355687</v>
+        <v>3.8866117266964957</v>
       </c>
       <c r="I92" s="170">
         <f t="shared" si="38"/>
-        <v>3.8175399946822925</v>
+        <v>3.8134963742158301</v>
       </c>
       <c r="J92" s="170">
         <f t="shared" si="38"/>
@@ -13384,20 +13384,20 @@
       </c>
       <c r="C94" s="23">
         <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
-        <v>3.126349127364017E-2</v>
+        <v>3.0747929715345009E-2</v>
       </c>
       <c r="E94" s="268"/>
       <c r="G94" s="23">
         <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>3.126349127364017E-2</v>
+        <v>3.0747929715345009E-2</v>
       </c>
       <c r="H94" s="23">
         <f t="shared" si="39"/>
-        <v>2.6116453076150632E-2</v>
+        <v>2.5685770554891869E-2</v>
       </c>
       <c r="I94" s="23">
         <f t="shared" si="39"/>
-        <v>2.0969414878661091E-2</v>
+        <v>2.0623611394438725E-2</v>
       </c>
       <c r="J94" s="23">
         <f t="shared" si="39"/>
@@ -14526,38 +14526,38 @@
       </c>
       <c r="C125" s="177">
         <f>C16*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>2.4685819320773672</v>
+        <v>2.4659671570029498</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="265"/>
       <c r="F125" s="27"/>
       <c r="G125" s="177">
         <f t="shared" ref="G125:Q125" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>3.5499643463441024</v>
+        <v>3.5462041477591271</v>
       </c>
       <c r="H125" s="177">
         <f t="shared" si="49"/>
-        <v>2.9236959090499384</v>
+        <v>2.9205990674629438</v>
       </c>
       <c r="I125" s="177">
         <f t="shared" si="49"/>
-        <v>2.3925010494368353</v>
+        <v>2.389966860869587</v>
       </c>
       <c r="J125" s="177">
         <f t="shared" si="49"/>
-        <v>1.2832903174250045</v>
+        <v>1.2819310287209749</v>
       </c>
       <c r="K125" s="177">
         <f t="shared" si="49"/>
-        <v>6.1991975296238593</v>
+        <v>6.1926312062739139</v>
       </c>
       <c r="L125" s="177">
         <f t="shared" si="49"/>
-        <v>8.3351943540113744</v>
+        <v>8.3263655368860068</v>
       </c>
       <c r="M125" s="177">
         <f t="shared" si="49"/>
-        <v>7.7115041349448346</v>
+        <v>7.7033359439132507</v>
       </c>
       <c r="N125" s="177" t="str">
         <f t="shared" si="49"/>
@@ -14583,38 +14583,38 @@
       </c>
       <c r="C126" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>5.1643973474421914E-2</v>
+        <v>5.0792320432604524E-2</v>
       </c>
       <c r="D126" s="27"/>
       <c r="E126" s="265"/>
       <c r="F126" s="27"/>
       <c r="G126" s="77">
         <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
-        <v>7.4267036534395453E-2</v>
+        <v>7.3042309943545367E-2</v>
       </c>
       <c r="H126" s="77">
         <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
-        <v>6.1165186381797874E-2</v>
+        <v>6.0156520442079177E-2</v>
       </c>
       <c r="I126" s="77">
         <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
-        <v>5.0052323209975637E-2</v>
+        <v>4.9226917834594999E-2</v>
       </c>
       <c r="J126" s="77">
         <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
-        <v>2.6847077770397586E-2</v>
+        <v>2.6404346626590625E-2</v>
       </c>
       <c r="K126" s="77">
         <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
-        <v>0.12969032488752844</v>
+        <v>0.12755162113849464</v>
       </c>
       <c r="L126" s="77">
         <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
-        <v>0.17437645092074006</v>
+        <v>0.17150083495130808</v>
       </c>
       <c r="M126" s="77">
         <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
-        <v>0.16132853838796726</v>
+        <v>0.15866809359244596</v>
       </c>
       <c r="N126" s="77" t="str">
         <f t="shared" ref="N126" si="57">IF(N$4="","",N125/Market_Price)</f>
@@ -14640,31 +14640,31 @@
       <c r="C127" s="169"/>
       <c r="G127" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.8954924076197292E-3</v>
+        <v>6.7889708977182921E-3</v>
       </c>
       <c r="H127" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.5055364279723322E-3</v>
+        <v>5.4204869465927386E-3</v>
       </c>
       <c r="I127" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.8357300693583523E-3</v>
+        <v>3.7764757428492119E-3</v>
       </c>
       <c r="J127" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.4127110457265889E-3</v>
+        <v>2.3754395053703593E-3</v>
       </c>
       <c r="K127" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-4.445033569094966E-4</v>
+        <v>-4.3763667271419027E-4</v>
       </c>
       <c r="L127" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.1071068120244096E-3</v>
+        <v>2.0745562433525599E-3</v>
       </c>
       <c r="M127" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.702059995735227E-3</v>
+        <v>1.6757665869442605E-3</v>
       </c>
       <c r="N127" s="23" t="str">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -15492,7 +15492,7 @@
       </c>
       <c r="C8" s="338">
         <f>BS!D66</f>
-        <v>409735.4541059254</v>
+        <v>410072.98329152912</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
@@ -15524,7 +15524,7 @@
       </c>
       <c r="C10" s="347">
         <f>C6-C7+C8+C9</f>
-        <v>8789832.3029780686</v>
+        <v>8790169.8321636729</v>
       </c>
       <c r="D10" t="str">
         <f>Reporting_currency</f>
@@ -15538,7 +15538,7 @@
       </c>
       <c r="C11" s="208">
         <f>Exchange_Rate</f>
-        <v>9.1121639200000004</v>
+        <v>9.1025121200000001</v>
       </c>
       <c r="D11" t="str">
         <f>Thesis!C15</f>
@@ -15552,7 +15552,7 @@
       </c>
       <c r="C12" s="111">
         <f>(C10*scaling_factor)/Common_Shares*Exchange_Rate</f>
-        <v>31.30125118962745</v>
+        <v>31.269296924731126</v>
       </c>
       <c r="D12" t="str">
         <f>Market_currency</f>
@@ -15605,7 +15605,7 @@
       </c>
       <c r="C18" s="140">
         <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>32.544168840031631</v>
+        <v>32.51089805002848</v>
       </c>
       <c r="D18" t="str">
         <f>Market_currency</f>
@@ -16701,23 +16701,23 @@
       </c>
       <c r="B65" s="124">
         <f>C12</f>
-        <v>31.30125118962745</v>
+        <v>31.269296924731126</v>
       </c>
       <c r="C65" s="124">
         <f>C12</f>
-        <v>31.30125118962745</v>
+        <v>31.269296924731126</v>
       </c>
       <c r="D65" s="124">
         <f>C12</f>
-        <v>31.30125118962745</v>
+        <v>31.269296924731126</v>
       </c>
       <c r="E65" s="141">
         <f>C12</f>
-        <v>31.30125118962745</v>
+        <v>31.269296924731126</v>
       </c>
       <c r="F65" s="124">
         <f>C12</f>
-        <v>31.30125118962745</v>
+        <v>31.269296924731126</v>
       </c>
       <c r="H65" s="120"/>
     </row>
@@ -16728,23 +16728,23 @@
       </c>
       <c r="B66" s="124">
         <f t="shared" ref="B66:F71" si="4">(B56-$C$7+$C$8+$C$9)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>31.301251189627447</v>
+        <v>31.269296924731123</v>
       </c>
       <c r="C66" s="124">
         <f t="shared" si="4"/>
-        <v>31.819398885924087</v>
+        <v>31.78689578784401</v>
       </c>
       <c r="D66" s="124">
         <f t="shared" si="4"/>
-        <v>32.878170365558205</v>
+        <v>32.844545793955824</v>
       </c>
       <c r="E66" s="124">
         <f t="shared" si="4"/>
-        <v>33.968011011242091</v>
+        <v>33.933232056988523</v>
       </c>
       <c r="F66" s="124">
         <f t="shared" si="4"/>
-        <v>35.664007124512182</v>
+        <v>35.627431734699535</v>
       </c>
       <c r="H66" s="120"/>
     </row>
@@ -16755,23 +16755,23 @@
       </c>
       <c r="B67" s="124">
         <f t="shared" si="4"/>
-        <v>31.301251189627454</v>
+        <v>31.26929692473113</v>
       </c>
       <c r="C67" s="124">
         <f t="shared" si="4"/>
-        <v>32.316189438081196</v>
+        <v>32.283160128763768</v>
       </c>
       <c r="D67" s="124">
         <f t="shared" si="4"/>
-        <v>34.495485302689225</v>
+        <v>34.460147636321736</v>
       </c>
       <c r="E67" s="124">
         <f t="shared" si="4"/>
-        <v>36.893899557387527</v>
+        <v>36.856021439058608</v>
       </c>
       <c r="F67" s="124">
         <f t="shared" si="4"/>
-        <v>40.960506448763873</v>
+        <v>40.918320892954817</v>
       </c>
       <c r="H67" s="120"/>
     </row>
@@ -16782,23 +16782,23 @@
       </c>
       <c r="B68" s="124">
         <f t="shared" si="4"/>
-        <v>31.301251189627454</v>
+        <v>31.26929692473113</v>
       </c>
       <c r="C68" s="124">
         <f t="shared" si="4"/>
-        <v>32.929547530260749</v>
+        <v>32.895868538860547</v>
       </c>
       <c r="D68" s="124">
         <f t="shared" si="4"/>
-        <v>36.596455584403891</v>
+        <v>36.558892525128293</v>
       </c>
       <c r="E68" s="124">
         <f t="shared" si="4"/>
-        <v>40.900809799970915</v>
+        <v>40.858687476136147</v>
       </c>
       <c r="F68" s="124">
         <f t="shared" si="4"/>
-        <v>48.837604802751429</v>
+        <v>48.787075654952517</v>
       </c>
       <c r="H68" s="120"/>
     </row>
@@ -16809,23 +16809,23 @@
       </c>
       <c r="B69" s="124">
         <f t="shared" si="4"/>
-        <v>31.301251189627465</v>
+        <v>31.26929692473114</v>
       </c>
       <c r="C69" s="124">
         <f t="shared" si="4"/>
-        <v>33.552485595533845</v>
+        <v>33.518146774737332</v>
       </c>
       <c r="D69" s="124">
         <f t="shared" si="4"/>
-        <v>38.846747471511982</v>
+        <v>38.806800854672389</v>
       </c>
       <c r="E69" s="124">
         <f t="shared" si="4"/>
-        <v>45.44218160011841</v>
+        <v>45.395248957601332</v>
       </c>
       <c r="F69" s="124">
         <f t="shared" si="4"/>
-        <v>58.610542006076464</v>
+        <v>58.549661153004557</v>
       </c>
       <c r="H69" s="120"/>
     </row>
@@ -16836,23 +16836,23 @@
       </c>
       <c r="B70" s="124">
         <f t="shared" si="4"/>
-        <v>31.301251189627465</v>
+        <v>31.26929692473114</v>
       </c>
       <c r="C70" s="124">
         <f t="shared" si="4"/>
-        <v>34.129667195380563</v>
+        <v>34.094717011420016</v>
       </c>
       <c r="D70" s="124">
         <f t="shared" si="4"/>
-        <v>41.0495852132686</v>
+        <v>41.00730530331635</v>
       </c>
       <c r="E70" s="124">
         <f t="shared" si="4"/>
-        <v>50.161559907006243</v>
+        <v>50.109628397486517</v>
       </c>
       <c r="F70" s="124">
         <f t="shared" si="4"/>
-        <v>69.804649862670317</v>
+        <v>69.731911969804258</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="13.15">
@@ -16862,23 +16862,23 @@
       </c>
       <c r="B71" s="124">
         <f t="shared" si="4"/>
-        <v>31.301251189627454</v>
+        <v>31.26929692473113</v>
       </c>
       <c r="C71" s="124">
         <f t="shared" si="4"/>
-        <v>34.636593630966537</v>
+        <v>34.601106499622908</v>
       </c>
       <c r="D71" s="124">
         <f t="shared" si="4"/>
-        <v>43.097059693061958</v>
+        <v>43.052611054105526</v>
       </c>
       <c r="E71" s="124">
         <f t="shared" si="4"/>
-        <v>54.832216699110099</v>
+        <v>54.775337929464037</v>
       </c>
       <c r="F71" s="124">
         <f t="shared" si="4"/>
-        <v>82.091655724134625</v>
+        <v>82.005903170402632</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="13.15">
@@ -16913,7 +16913,7 @@
       </c>
       <c r="E74" s="135">
         <f>INDEX(B$65:F$71, MATCH(D74, A$65:A$71, 0), MATCH(C74, B$64:F$64, 0))</f>
-        <v>40.960506448763873</v>
+        <v>40.918320892954817</v>
       </c>
       <c r="F74" s="142">
         <f>Scenarios!C58</f>
@@ -16935,7 +16935,7 @@
       </c>
       <c r="E75" s="135">
         <f>INDEX(B$65:F$71, MATCH(D75, A$65:A$71, 0), MATCH(C75, B$64:F$64, 0))</f>
-        <v>33.968011011242091</v>
+        <v>33.933232056988523</v>
       </c>
       <c r="F75" s="142">
         <f>Scenarios!C40*(1-F$74-F$78)</f>
@@ -16958,7 +16958,7 @@
       </c>
       <c r="E76" s="135">
         <f>INDEX(B$65:F$71, MATCH(D76, A$65:A$71, 0), MATCH(C76, B$64:F$64, 0))</f>
-        <v>32.878170365558205</v>
+        <v>32.844545793955824</v>
       </c>
       <c r="F76" s="142">
         <f>Scenarios!C28*(1-F$74-F$78)</f>
@@ -16981,7 +16981,7 @@
       </c>
       <c r="E77" s="135">
         <f>INDEX(B$65:F$71, MATCH(D77, A$65:A$71, 0), MATCH(C77, B$64:F$64, 0))</f>
-        <v>31.819398885924087</v>
+        <v>31.78689578784401</v>
       </c>
       <c r="F77" s="142">
         <f>Scenarios!C34*(1-F$74-F$78)</f>
@@ -17004,7 +17004,7 @@
       </c>
       <c r="E78" s="135">
         <f>INDEX(B$65:F$71, MATCH(D78, A$65:A$71, 0), MATCH(C78, B$64:F$64, 0))</f>
-        <v>31.301251189627454</v>
+        <v>31.26929692473113</v>
       </c>
       <c r="F78" s="142">
         <f>Scenarios!C52</f>
@@ -17186,7 +17186,7 @@
       </c>
       <c r="C4" s="114">
         <f>Normalized_FCF!C91*(1-dividend_tax_rate)</f>
-        <v>3823893.4917905335</v>
+        <v>3819843.1415632889</v>
       </c>
       <c r="D4" t="str">
         <f>Market_currency</f>
@@ -17218,7 +17218,7 @@
       </c>
       <c r="C6" s="319">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
-        <v>50985246.557207115</v>
+        <v>50931241.887510523</v>
       </c>
       <c r="D6" t="str">
         <f>Reporting_currency</f>
@@ -17234,7 +17234,7 @@
       </c>
       <c r="C7" s="111">
         <f>(C6*scaling_factor)/Common_Shares*Exchange_Rate</f>
-        <v>181.56228178682352</v>
+        <v>181.17785614317992</v>
       </c>
       <c r="D7" t="str">
         <f>Market_currency</f>
@@ -17287,7 +17287,7 @@
       </c>
       <c r="C13" s="140">
         <f>F47/Common_Shares*scaling_factor</f>
-        <v>20.677684845513436</v>
+        <v>20.655782597008681</v>
       </c>
       <c r="D13" t="str">
         <f>Market_currency</f>
@@ -17322,7 +17322,7 @@
       </c>
       <c r="C16" s="123">
         <f>C4*(1+D16)</f>
-        <v>3914720.9781269296</v>
+        <v>3910574.4214727245</v>
       </c>
       <c r="D16" s="138">
         <f>IF($C$12&lt;B16,0,DDM!$C$11)</f>
@@ -17334,7 +17334,7 @@
       </c>
       <c r="F16" s="125">
         <f t="shared" ref="F16:F46" si="1">C16*E16</f>
-        <v>3641600.9098855159</v>
+        <v>3637743.6478816043</v>
       </c>
       <c r="H16" s="120"/>
     </row>
@@ -17344,7 +17344,7 @@
       </c>
       <c r="C17" s="123">
         <f t="shared" ref="C17:C45" si="2">IF(ROW()-ROW($C$16)&lt;$C$12, $C$16*(1+D17)^(ROW()-ROW($C$16)), 0)</f>
-        <v>4007705.8551678262</v>
+        <v>4003460.806932027</v>
       </c>
       <c r="D17" s="138">
         <f>IF($C$12&lt;B17,0,DDM!$C$11)</f>
@@ -17356,7 +17356,7 @@
       </c>
       <c r="F17" s="125">
         <f t="shared" si="1"/>
-        <v>3467998.5766730788</v>
+        <v>3464325.1979941828</v>
       </c>
       <c r="H17" s="120"/>
     </row>
@@ -17366,7 +17366,7 @@
       </c>
       <c r="C18" s="123">
         <f t="shared" si="2"/>
-        <v>4102899.3665932985</v>
+        <v>4098553.4873428643</v>
       </c>
       <c r="D18" s="138">
         <f>IF($C$12&lt;B18,0,DDM!$C$11)</f>
@@ -17378,7 +17378,7 @@
       </c>
       <c r="F18" s="125">
         <f t="shared" si="1"/>
-        <v>3302672.2107735313</v>
+        <v>3299173.9493370815</v>
       </c>
       <c r="H18" s="120"/>
     </row>
@@ -17388,7 +17388,7 @@
       </c>
       <c r="C19" s="123">
         <f t="shared" si="2"/>
-        <v>4200353.9732550457</v>
+        <v>4195904.8679892728</v>
       </c>
       <c r="D19" s="138">
         <f>IF($C$12&lt;B19,0,DDM!$C$11)</f>
@@ -17400,7 +17400,7 @@
       </c>
       <c r="F19" s="125">
         <f t="shared" si="1"/>
-        <v>3145227.2804216794</v>
+        <v>3141895.7880416377</v>
       </c>
       <c r="H19" s="120"/>
     </row>
@@ -17410,7 +17410,7 @@
       </c>
       <c r="C20" s="123">
         <f t="shared" si="2"/>
-        <v>4300123.3820874058</v>
+        <v>4295568.5989180496</v>
       </c>
       <c r="D20" s="138">
         <f>IF($C$12&lt;B20,0,DDM!$C$11)</f>
@@ -17422,7 +17422,7 @@
       </c>
       <c r="F20" s="125">
         <f t="shared" si="1"/>
-        <v>2995288.0619635596</v>
+        <v>2992115.3884284613</v>
       </c>
       <c r="H20" s="120"/>
     </row>
@@ -17982,7 +17982,7 @@
       </c>
       <c r="C46" s="123">
         <f>C$16*(1+F4)^$C$12/Equity_Cost</f>
-        <v>52196279.708359063</v>
+        <v>52140992.286302999</v>
       </c>
       <c r="D46" s="139">
         <f>Terminal_Growth</f>
@@ -17994,7 +17994,7 @@
       </c>
       <c r="F46" s="125">
         <f t="shared" si="1"/>
-        <v>36357769.20741871</v>
+        <v>36319258.276325174</v>
       </c>
       <c r="H46" s="120"/>
     </row>
@@ -18005,7 +18005,7 @@
       </c>
       <c r="F47" s="137">
         <f>SUM(F16:F46)</f>
-        <v>52910556.247136071</v>
+        <v>52854512.248008139</v>
       </c>
       <c r="H47" s="120"/>
     </row>
@@ -18026,7 +18026,7 @@
     <row r="50" spans="1:8" ht="13.15">
       <c r="A50" s="133">
         <f>F47</f>
-        <v>52910556.247136071</v>
+        <v>52854512.248008139</v>
       </c>
       <c r="B50" s="131">
         <f>C73</f>
@@ -18056,19 +18056,19 @@
       </c>
       <c r="B51" s="123">
         <f t="dataTable" ref="B51:F56" dt2D="1" dtr="1" r1="C11" r2="C12"/>
-        <v>50985246.557207122</v>
+        <v>50931241.887510523</v>
       </c>
       <c r="C51" s="123">
-        <v>51787869.949167058</v>
+        <v>51733015.123511627</v>
       </c>
       <c r="D51" s="123">
-        <v>53427932.738923989</v>
+        <v>53371340.723488696</v>
       </c>
       <c r="E51" s="123">
-        <v>55116122.423036419</v>
+        <v>55057742.240779713</v>
       </c>
       <c r="F51" s="123">
-        <v>57743261.678721577</v>
+        <v>57682098.774063192</v>
       </c>
       <c r="H51" s="120"/>
     </row>
@@ -18077,19 +18077,19 @@
         <v>10</v>
       </c>
       <c r="B52" s="123">
-        <v>50985246.557207122</v>
+        <v>50931241.887510538</v>
       </c>
       <c r="C52" s="123">
-        <v>52557410.605076328</v>
+        <v>52501740.665407598</v>
       </c>
       <c r="D52" s="123">
-        <v>55933192.9378701</v>
+        <v>55873947.296951286</v>
       </c>
       <c r="E52" s="123">
-        <v>59648394.989697725</v>
+        <v>59585214.126862511</v>
       </c>
       <c r="F52" s="123">
-        <v>65947668.035303585</v>
+        <v>65877814.846979573</v>
       </c>
       <c r="H52" s="120"/>
     </row>
@@ -18098,19 +18098,19 @@
         <v>15</v>
       </c>
       <c r="B53" s="123">
-        <v>50985246.557207122</v>
+        <v>50931241.887510538</v>
       </c>
       <c r="C53" s="123">
-        <v>53507517.217437685</v>
+        <v>53450840.904411122</v>
       </c>
       <c r="D53" s="123">
-        <v>59187647.036516652</v>
+        <v>59124954.207822785</v>
       </c>
       <c r="E53" s="123">
-        <v>65855196.473458737</v>
+        <v>65785441.233001813</v>
       </c>
       <c r="F53" s="123">
-        <v>78149485.094160229</v>
+        <v>78066707.478782162</v>
       </c>
       <c r="H53" s="120"/>
     </row>
@@ -18119,19 +18119,19 @@
         <v>20</v>
       </c>
       <c r="B54" s="123">
-        <v>50985246.55720713</v>
+        <v>50931241.887510538</v>
       </c>
       <c r="C54" s="123">
-        <v>54472463.441273101</v>
+        <v>54414765.036453098</v>
       </c>
       <c r="D54" s="123">
-        <v>62673403.936025545</v>
+        <v>62607018.918655314</v>
       </c>
       <c r="E54" s="123">
-        <v>72889891.917320892</v>
+        <v>72812685.37615414</v>
       </c>
       <c r="F54" s="123">
-        <v>93288002.670534074</v>
+        <v>93189190.011754006</v>
       </c>
       <c r="H54" s="120"/>
     </row>
@@ -18140,19 +18140,19 @@
         <v>25</v>
       </c>
       <c r="B55" s="123">
-        <v>50985246.55720713</v>
+        <v>50931241.887510546</v>
       </c>
       <c r="C55" s="123">
-        <v>55366531.786567114</v>
+        <v>55307886.365326986</v>
       </c>
       <c r="D55" s="123">
-        <v>66085653.209471852</v>
+        <v>66015653.864283703</v>
       </c>
       <c r="E55" s="123">
-        <v>80200323.772349238</v>
+        <v>80115373.864535704</v>
       </c>
       <c r="F55" s="123">
-        <v>110627948.17649877</v>
+        <v>110510768.67450738</v>
       </c>
       <c r="H55" s="120"/>
     </row>
@@ -18161,19 +18161,19 @@
         <v>30</v>
       </c>
       <c r="B56" s="123">
-        <v>50985246.55720713</v>
+        <v>50931241.887510538</v>
       </c>
       <c r="C56" s="123">
-        <v>56151773.172589302</v>
+        <v>56092296.006784864</v>
       </c>
       <c r="D56" s="123">
-        <v>69257241.008990616</v>
+        <v>69183882.249793664</v>
       </c>
       <c r="E56" s="123">
-        <v>87435284.815219507</v>
+        <v>87342671.48106654</v>
       </c>
       <c r="F56" s="123">
-        <v>129660819.29036422</v>
+        <v>129523479.76194777</v>
       </c>
       <c r="H56" s="120"/>
     </row>
@@ -18223,23 +18223,23 @@
       </c>
       <c r="B60" s="124">
         <f>C7</f>
-        <v>181.56228178682352</v>
+        <v>181.17785614317992</v>
       </c>
       <c r="C60" s="124">
         <f>C7</f>
-        <v>181.56228178682352</v>
+        <v>181.17785614317992</v>
       </c>
       <c r="D60" s="124">
         <f>C7</f>
-        <v>181.56228178682352</v>
+        <v>181.17785614317992</v>
       </c>
       <c r="E60" s="141">
         <f>C7</f>
-        <v>181.56228178682352</v>
+        <v>181.17785614317992</v>
       </c>
       <c r="F60" s="124">
         <f>C7</f>
-        <v>181.56228178682352</v>
+        <v>181.17785614317992</v>
       </c>
       <c r="H60" s="120"/>
     </row>
@@ -18250,23 +18250,23 @@
       </c>
       <c r="B61" s="124">
         <f t="shared" ref="B61:F66" si="4">B51/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>181.56228178682355</v>
+        <v>181.17785614317992</v>
       </c>
       <c r="C61" s="124">
         <f t="shared" si="4"/>
-        <v>184.42048380211077</v>
+        <v>184.03000642713525</v>
       </c>
       <c r="D61" s="124">
         <f t="shared" si="4"/>
-        <v>190.260870237191</v>
+        <v>189.85802688899489</v>
       </c>
       <c r="E61" s="124">
         <f t="shared" si="4"/>
-        <v>196.27264014777705</v>
+        <v>195.85706795251775</v>
       </c>
       <c r="F61" s="124">
         <f t="shared" si="4"/>
-        <v>205.62807981008675</v>
+        <v>205.19269914536807</v>
       </c>
       <c r="H61" s="120"/>
     </row>
@@ -18277,23 +18277,23 @@
       </c>
       <c r="B62" s="124">
         <f t="shared" si="4"/>
-        <v>181.56228178682355</v>
+        <v>181.17785614317998</v>
       </c>
       <c r="C62" s="124">
         <f t="shared" si="4"/>
-        <v>187.16087571642359</v>
+        <v>186.76459605192446</v>
       </c>
       <c r="D62" s="124">
         <f t="shared" si="4"/>
-        <v>199.18228944970767</v>
+        <v>198.76055659269269</v>
       </c>
       <c r="E62" s="124">
         <f t="shared" si="4"/>
-        <v>212.41240222501915</v>
+        <v>211.96265697154678</v>
       </c>
       <c r="F62" s="124">
         <f t="shared" si="4"/>
-        <v>234.84458535617557</v>
+        <v>234.34734396884957</v>
       </c>
       <c r="H62" s="120"/>
     </row>
@@ -18304,23 +18304,23 @@
       </c>
       <c r="B63" s="124">
         <f t="shared" si="4"/>
-        <v>181.56228178682355</v>
+        <v>181.17785614317998</v>
       </c>
       <c r="C63" s="124">
         <f t="shared" si="4"/>
-        <v>190.54427652605827</v>
+        <v>190.14083311575709</v>
       </c>
       <c r="D63" s="124">
         <f t="shared" si="4"/>
-        <v>210.77164425370481</v>
+        <v>210.32537301164592</v>
       </c>
       <c r="E63" s="124">
         <f t="shared" si="4"/>
-        <v>234.51528719832314</v>
+        <v>234.01874304092303</v>
       </c>
       <c r="F63" s="124">
         <f t="shared" si="4"/>
-        <v>278.29616981925471</v>
+        <v>277.70692747688361</v>
       </c>
       <c r="H63" s="120"/>
     </row>
@@ -18331,23 +18331,23 @@
       </c>
       <c r="B64" s="124">
         <f t="shared" si="4"/>
-        <v>181.56228178682358</v>
+        <v>181.17785614317998</v>
       </c>
       <c r="C64" s="124">
         <f t="shared" si="4"/>
-        <v>193.98052230363942</v>
+        <v>193.56980325777255</v>
       </c>
       <c r="D64" s="124">
         <f t="shared" si="4"/>
-        <v>223.18468565616001</v>
+        <v>222.71213202007223</v>
       </c>
       <c r="E64" s="124">
         <f t="shared" si="4"/>
-        <v>259.5663645728315</v>
+        <v>259.01677924163204</v>
       </c>
       <c r="F64" s="124">
         <f t="shared" si="4"/>
-        <v>332.20556478417598</v>
+        <v>331.5021789443017</v>
       </c>
       <c r="H64" s="120"/>
     </row>
@@ -18358,23 +18358,23 @@
       </c>
       <c r="B65" s="124">
         <f t="shared" si="4"/>
-        <v>181.56228178682358</v>
+        <v>181.17785614318001</v>
       </c>
       <c r="C65" s="124">
         <f t="shared" si="4"/>
-        <v>197.16436664697926</v>
+        <v>196.74690638041992</v>
       </c>
       <c r="D65" s="124">
         <f t="shared" si="4"/>
-        <v>235.33596089648276</v>
+        <v>234.83767910937496</v>
       </c>
       <c r="E65" s="124">
         <f t="shared" si="4"/>
-        <v>285.59935996016884</v>
+        <v>284.99465441947842</v>
       </c>
       <c r="F65" s="124">
         <f t="shared" si="4"/>
-        <v>393.95440949339303</v>
+        <v>393.12028152394214</v>
       </c>
     </row>
     <row r="66" spans="1:8" ht="13.15">
@@ -18384,23 +18384,23 @@
       </c>
       <c r="B66" s="124">
         <f t="shared" si="4"/>
-        <v>181.56228178682358</v>
+        <v>181.17785614317998</v>
       </c>
       <c r="C66" s="124">
         <f t="shared" si="4"/>
-        <v>199.96067003720935</v>
+        <v>199.53728909858074</v>
       </c>
       <c r="D66" s="124">
         <f t="shared" si="4"/>
-        <v>246.6302226025974</v>
+        <v>246.10802723727764</v>
       </c>
       <c r="E66" s="124">
         <f t="shared" si="4"/>
-        <v>311.36359813264494</v>
+        <v>310.7043414277756</v>
       </c>
       <c r="F66" s="124">
         <f t="shared" si="4"/>
-        <v>461.73188909252724</v>
+        <v>460.7542544378606</v>
       </c>
     </row>
     <row r="68" spans="1:8" ht="13.15">
@@ -18435,7 +18435,7 @@
       </c>
       <c r="E69" s="135">
         <f>INDEX(B$60:F$66, MATCH(D69, A$60:A$66, 0), MATCH(C69, B$59:F$59, 0))</f>
-        <v>234.84458535617557</v>
+        <v>234.34734396884957</v>
       </c>
       <c r="F69" s="142">
         <f>Scenarios!C58</f>
@@ -18457,7 +18457,7 @@
       </c>
       <c r="E70" s="135">
         <f>INDEX(B$60:F$66, MATCH(D70, A$60:A$66, 0), MATCH(C70, B$59:F$59, 0))</f>
-        <v>196.27264014777705</v>
+        <v>195.85706795251775</v>
       </c>
       <c r="F70" s="142">
         <f>Scenarios!C40*(1-F$69-F$73)</f>
@@ -18480,7 +18480,7 @@
       </c>
       <c r="E71" s="135">
         <f>INDEX(B$60:F$66, MATCH(D71, A$60:A$66, 0), MATCH(C71, B$59:F$59, 0))</f>
-        <v>190.260870237191</v>
+        <v>189.85802688899489</v>
       </c>
       <c r="F71" s="142">
         <f>Scenarios!C28*(1-F$69-F$73)</f>
@@ -18503,7 +18503,7 @@
       </c>
       <c r="E72" s="135">
         <f>INDEX(B$60:F$66, MATCH(D72, A$60:A$66, 0), MATCH(C72, B$59:F$59, 0))</f>
-        <v>184.42048380211077</v>
+        <v>184.03000642713525</v>
       </c>
       <c r="F72" s="142">
         <f>Scenarios!C34*(1-F$69-F$73)</f>
@@ -18526,7 +18526,7 @@
       </c>
       <c r="E73" s="135">
         <f>INDEX(B$60:F$66, MATCH(D73, A$60:A$66, 0), MATCH(C73, B$59:F$59, 0))</f>
-        <v>181.56228178682355</v>
+        <v>181.17785614317998</v>
       </c>
       <c r="F73" s="142">
         <f>Scenarios!C52</f>
@@ -18626,7 +18626,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-47.8</v>
+        <v>-48.55</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18646,7 +18646,7 @@
       </c>
       <c r="I4" s="124">
         <f t="shared" ref="I4:I13" si="0">IF(ROW()-3 &lt; $C$76, $C$77, IF(ROW()-3 = $C$76, $C$77 + $C$60, ""))</f>
-        <v>1.4943948828800002</v>
+        <v>1.4928119876800001</v>
       </c>
     </row>
     <row r="5" spans="2:9">
@@ -18655,7 +18655,7 @@
       </c>
       <c r="I5" s="124">
         <f t="shared" si="0"/>
-        <v>1.4943948828800002</v>
+        <v>1.4928119876800001</v>
       </c>
     </row>
     <row r="6" spans="2:9" ht="13.15">
@@ -18675,7 +18675,7 @@
       </c>
       <c r="I6" s="124">
         <f t="shared" si="0"/>
-        <v>34.703428543690912</v>
+        <v>34.667870619370291</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1">
@@ -18866,7 +18866,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>47.8</v>
+        <v>48.55</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -18881,7 +18881,7 @@
       </c>
       <c r="C22" s="160">
         <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
-        <v>31.30125118962745</v>
+        <v>31.269296924731126</v>
       </c>
       <c r="D22" t="str">
         <f>Market_currency</f>
@@ -18928,7 +18928,7 @@
       </c>
       <c r="C27" s="160">
         <f>IF(valuation_method="DCF",DCF!E76,DDM!E71)</f>
-        <v>32.878170365558205</v>
+        <v>32.844545793955824</v>
       </c>
       <c r="D27" s="160" t="str">
         <f>Market_currency</f>
@@ -18986,7 +18986,7 @@
       </c>
       <c r="C33" s="160">
         <f>IF(valuation_method="DCF",DCF!E77,DDM!E72)</f>
-        <v>31.819398885924087</v>
+        <v>31.78689578784401</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
@@ -19044,7 +19044,7 @@
       </c>
       <c r="C39" s="160">
         <f>IF(valuation_method="DCF",DCF!E75,DDM!E70)</f>
-        <v>33.968011011242091</v>
+        <v>33.933232056988523</v>
       </c>
       <c r="D39" t="str">
         <f>Market_currency</f>
@@ -19071,7 +19071,7 @@
       </c>
       <c r="C42" s="154">
         <f>C27*C28+C33*C34+C39*C40</f>
-        <v>32.88438419876816</v>
+        <v>32.850753045339999</v>
       </c>
       <c r="D42" t="str">
         <f>Market_currency</f>
@@ -19145,7 +19145,7 @@
       </c>
       <c r="C51" s="160">
         <f>IF(valuation_method="DCF",DCF!E78,DDM!E73)</f>
-        <v>31.301251189627454</v>
+        <v>31.26929692473113</v>
       </c>
       <c r="D51" t="str">
         <f>Market_currency</f>
@@ -19203,7 +19203,7 @@
       </c>
       <c r="C57" s="160">
         <f>IF(valuation_method="DCF",DCF!E74,DDM!E69)</f>
-        <v>40.960506448763873</v>
+        <v>40.918320892954817</v>
       </c>
       <c r="D57" t="str">
         <f>Market_currency</f>
@@ -19229,7 +19229,7 @@
       </c>
       <c r="C60" s="154">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
-        <v>33.20903366081091</v>
+        <v>33.175058631690291</v>
       </c>
       <c r="D60" t="str">
         <f>Market_currency</f>
@@ -19291,7 +19291,7 @@
       </c>
       <c r="C66" s="160">
         <f>IF(valuation_method="DCF",DCF!C18,DDM!C13)</f>
-        <v>32.544168840031631</v>
+        <v>32.51089805002848</v>
       </c>
       <c r="D66" s="160" t="str">
         <f>Market_currency</f>
@@ -19354,7 +19354,7 @@
       </c>
       <c r="F72" s="291">
         <f>BS!D89/C60</f>
-        <v>-4.8576377978374566E-2</v>
+        <v>-4.8538427211801204E-2</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="13.9">
@@ -19387,7 +19387,7 @@
       </c>
       <c r="C77" s="173">
         <f>Normalized_FCF!C90*(1-dividend_tax_rate)</f>
-        <v>1.4943948828800002</v>
+        <v>1.4928119876800001</v>
       </c>
       <c r="D77" t="str">
         <f>Market_currency</f>
@@ -19414,7 +19414,7 @@
       </c>
       <c r="C81" s="116">
         <f>PV(C80, C76, -C77, 0)</f>
-        <v>2.4765998464640369</v>
+        <v>2.4739765786422589</v>
       </c>
       <c r="D81" s="116"/>
       <c r="E81" s="100"/>
@@ -19426,7 +19426,7 @@
       </c>
       <c r="C82" s="116">
         <f>C60/(1+C80)^C76</f>
-        <v>12.988814417219093</v>
+        <v>12.975526004416281</v>
       </c>
       <c r="D82" s="116"/>
     </row>
@@ -19436,7 +19436,7 @@
       </c>
       <c r="C83" s="111">
         <f>C81+C82</f>
-        <v>15.46541426368313</v>
+        <v>15.449502583058539</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -19447,7 +19447,7 @@
       </c>
       <c r="F83" s="291">
         <f>(1-C83/C60)</f>
-        <v>0.53430098503789192</v>
+        <v>0.53430368414479645</v>
       </c>
     </row>
     <row r="84" spans="2:8">
@@ -19464,7 +19464,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>47.8</v>
+        <v>48.55</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19477,7 +19477,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>-7.8960977262645282E-2</v>
+        <v>-8.4224595913299005E-2</v>
       </c>
     </row>
     <row r="88" spans="2:8">
@@ -19503,7 +19503,7 @@
       </c>
       <c r="C91" s="116">
         <f>PV(C90, C76, -C77, 0)</f>
-        <v>3.0641084990366978</v>
+        <v>3.060862929414526</v>
       </c>
       <c r="D91" s="116"/>
       <c r="E91" s="100"/>
@@ -19515,7 +19515,7 @@
       </c>
       <c r="C92" s="116">
         <f>C60/(1+C90)^C76</f>
-        <v>18.405869823618687</v>
+        <v>18.387039406279996</v>
       </c>
       <c r="D92" s="116"/>
     </row>
@@ -19525,7 +19525,7 @@
       </c>
       <c r="C93" s="111">
         <f>C91+C92</f>
-        <v>21.469978322655386</v>
+        <v>21.447902335694522</v>
       </c>
       <c r="D93" t="str">
         <f>Market_currency</f>
@@ -19536,7 +19536,7 @@
       </c>
       <c r="F93" s="291">
         <f>(1-C93/C60)</f>
-        <v>0.35348982021143449</v>
+        <v>0.3534931596109816</v>
       </c>
     </row>
     <row r="95" spans="2:8" ht="13.15">
@@ -19563,7 +19563,7 @@
       </c>
       <c r="C97" s="116">
         <f>PV(C96, C76, -C77, 0)</f>
-        <v>3.8862123584623829</v>
+        <v>3.8820959987512631</v>
       </c>
       <c r="D97" s="116"/>
       <c r="G97" s="2"/>
@@ -19575,7 +19575,7 @@
       </c>
       <c r="C98" s="116">
         <f>C60/(1+C96)^C76</f>
-        <v>26.731962648469928</v>
+        <v>26.70461408967989</v>
       </c>
       <c r="D98" s="116"/>
       <c r="G98" s="2"/>
@@ -19587,7 +19587,7 @@
       </c>
       <c r="C99" s="111">
         <f>C97+C98</f>
-        <v>30.618175006932312</v>
+        <v>30.586710088431154</v>
       </c>
       <c r="D99" t="s">
         <v>393</v>
@@ -19597,7 +19597,7 @@
       </c>
       <c r="F99" s="291">
         <f>(1-C99/C60)</f>
-        <v>7.8016683061031156E-2</v>
+        <v>7.8020918425344754E-2</v>
       </c>
     </row>
     <row r="100" spans="2:8">
@@ -19623,7 +19623,7 @@
       </c>
       <c r="C103" s="116">
         <f>PV(C102, C76, -C77, 0)</f>
-        <v>3.6053817658230098</v>
+        <v>3.6015628679154563</v>
       </c>
       <c r="D103" s="116"/>
     </row>
@@ -19633,7 +19633,7 @@
       </c>
       <c r="C104" s="116">
         <f>C60/(1+C102)^C76</f>
-        <v>23.802920018364638</v>
+        <v>23.778568063139453</v>
       </c>
       <c r="D104" s="116"/>
     </row>
@@ -19643,7 +19643,7 @@
       </c>
       <c r="C105" s="111">
         <f>C103+C104</f>
-        <v>27.40830178418765</v>
+        <v>27.380130931054907</v>
       </c>
       <c r="D105" t="s">
         <v>393</v>
@@ -19653,7 +19653,7 @@
       </c>
       <c r="F105" s="291">
         <f>(1-C105/C66)</f>
-        <v>0.15781220534741391</v>
+        <v>0.15781683763635923</v>
       </c>
     </row>
     <row r="106" spans="2:8">

--- a/financial_models/opportunities/1913.HK_Valuation.xlsx
+++ b/financial_models/opportunities/1913.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61A7A5F8-2839-4BDB-A79B-FBA488625559}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{427AF2C6-DDDF-424A-9CFB-80DF3B91F653}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3896,29 +3896,29 @@
     <xf numFmtId="10" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4336,7 +4336,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>48.55</v>
+        <v>48.9</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4357,7 +4357,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>124230.90519999999</v>
+        <v>125126.4936</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4384,7 +4384,7 @@
         <v>1</v>
       </c>
       <c r="C16" s="50">
-        <v>9.1025121200000001</v>
+        <v>9.1115835199999999</v>
       </c>
       <c r="D16" s="50"/>
       <c r="E16" s="5"/>
@@ -4394,13 +4394,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="360" t="s">
+      <c r="B18" s="358" t="s">
         <v>356</v>
       </c>
-      <c r="C18" s="360"/>
-      <c r="D18" s="360"/>
-      <c r="E18" s="360"/>
-      <c r="F18" s="360"/>
+      <c r="C18" s="358"/>
+      <c r="D18" s="358"/>
+      <c r="E18" s="358"/>
+      <c r="F18" s="358"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4476,14 +4476,14 @@
       </c>
       <c r="C26" s="304">
         <f>C132</f>
-        <v>33.175058631690291</v>
+        <v>33.206990683086438</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>396</v>
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>-8.4224595913299005E-2</v>
+        <v>-8.6188313093982005E-2</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4515,7 +4515,7 @@
       </c>
       <c r="C29" s="310">
         <f>C149</f>
-        <v>15.449502583058539</v>
+        <v>15.464457461034979</v>
       </c>
       <c r="D29" s="310" t="str">
         <f>D149</f>
@@ -4534,7 +4534,7 @@
       </c>
       <c r="C30" s="311">
         <f>C157</f>
-        <v>21.447902335694522</v>
+        <v>21.468650848203975</v>
       </c>
       <c r="D30" s="311" t="str">
         <f>D157</f>
@@ -4553,7 +4553,7 @@
       </c>
       <c r="C31" s="311">
         <f>C165</f>
-        <v>30.586710088431154</v>
+        <v>30.616282957816857</v>
       </c>
       <c r="D31" s="311" t="str">
         <f>D165</f>
@@ -4572,7 +4572,7 @@
       </c>
       <c r="C32" s="311">
         <f>C173</f>
-        <v>27.380130931054907</v>
+        <v>27.406607813594828</v>
       </c>
       <c r="D32" s="311" t="str">
         <f>D173</f>
@@ -4600,22 +4600,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="360" t="s">
+      <c r="B36" s="358" t="s">
         <v>357</v>
       </c>
-      <c r="C36" s="360"/>
-      <c r="D36" s="360"/>
-      <c r="E36" s="360"/>
-      <c r="F36" s="360"/>
+      <c r="C36" s="358"/>
+      <c r="D36" s="358"/>
+      <c r="E36" s="358"/>
+      <c r="F36" s="358"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="363" t="s">
+      <c r="B37" s="360" t="s">
         <v>336</v>
       </c>
-      <c r="C37" s="363"/>
-      <c r="D37" s="363"/>
-      <c r="E37" s="363"/>
-      <c r="F37" s="363"/>
+      <c r="C37" s="360"/>
+      <c r="D37" s="360"/>
+      <c r="E37" s="360"/>
+      <c r="F37" s="360"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4627,13 +4627,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="361" t="s">
+      <c r="B40" s="359" t="s">
         <v>230</v>
       </c>
-      <c r="C40" s="361"/>
-      <c r="D40" s="361"/>
-      <c r="E40" s="361"/>
-      <c r="F40" s="361"/>
+      <c r="C40" s="359"/>
+      <c r="D40" s="359"/>
+      <c r="E40" s="359"/>
+      <c r="F40" s="359"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4653,13 +4653,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="361" t="s">
+      <c r="B43" s="359" t="s">
         <v>232</v>
       </c>
-      <c r="C43" s="361"/>
-      <c r="D43" s="361"/>
-      <c r="E43" s="361"/>
-      <c r="F43" s="361"/>
+      <c r="C43" s="359"/>
+      <c r="D43" s="359"/>
+      <c r="E43" s="359"/>
+      <c r="F43" s="359"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4688,13 +4688,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="361" t="s">
+      <c r="B47" s="359" t="s">
         <v>235</v>
       </c>
-      <c r="C47" s="361"/>
-      <c r="D47" s="361"/>
-      <c r="E47" s="361"/>
-      <c r="F47" s="361"/>
+      <c r="C47" s="359"/>
+      <c r="D47" s="359"/>
+      <c r="E47" s="359"/>
+      <c r="F47" s="359"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4710,13 +4710,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="361" t="s">
+      <c r="B50" s="359" t="s">
         <v>239</v>
       </c>
-      <c r="C50" s="361"/>
-      <c r="D50" s="361"/>
-      <c r="E50" s="361"/>
-      <c r="F50" s="361"/>
+      <c r="C50" s="359"/>
+      <c r="D50" s="359"/>
+      <c r="E50" s="359"/>
+      <c r="F50" s="359"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4780,13 +4780,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="361" t="s">
+      <c r="B58" s="359" t="s">
         <v>240</v>
       </c>
-      <c r="C58" s="361"/>
-      <c r="D58" s="361"/>
-      <c r="E58" s="361"/>
-      <c r="F58" s="361"/>
+      <c r="C58" s="359"/>
+      <c r="D58" s="359"/>
+      <c r="E58" s="359"/>
+      <c r="F58" s="359"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4802,7 +4802,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="361" t="s">
+      <c r="B61" s="359" t="s">
         <v>335</v>
       </c>
       <c r="C61" s="362"/>
@@ -4824,22 +4824,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="360" t="s">
+      <c r="B64" s="358" t="s">
         <v>340</v>
       </c>
-      <c r="C64" s="360"/>
-      <c r="D64" s="360"/>
-      <c r="E64" s="360"/>
-      <c r="F64" s="360"/>
+      <c r="C64" s="358"/>
+      <c r="D64" s="358"/>
+      <c r="E64" s="358"/>
+      <c r="F64" s="358"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="360" t="s">
+      <c r="B65" s="358" t="s">
         <v>358</v>
       </c>
-      <c r="C65" s="360"/>
-      <c r="D65" s="360"/>
-      <c r="E65" s="360"/>
-      <c r="F65" s="360"/>
+      <c r="C65" s="358"/>
+      <c r="D65" s="358"/>
+      <c r="E65" s="358"/>
+      <c r="F65" s="358"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4873,7 +4873,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>5.0792320432604524E-2</v>
+        <v>5.0479032628964977E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4883,14 +4883,14 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>3.0747929715345009E-2</v>
+        <v>3.0558276017995913E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>444</v>
       </c>
       <c r="F70" s="315">
         <f>Normalized_FCF!C92</f>
-        <v>5.5103488187787892</v>
+        <v>5.5158403333865902</v>
       </c>
     </row>
     <row r="72" spans="1:6">
@@ -4974,22 +4974,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.6" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="360" t="s">
+      <c r="B80" s="358" t="s">
         <v>359</v>
       </c>
-      <c r="C80" s="360"/>
-      <c r="D80" s="360"/>
-      <c r="E80" s="360"/>
-      <c r="F80" s="360"/>
+      <c r="C80" s="358"/>
+      <c r="D80" s="358"/>
+      <c r="E80" s="358"/>
+      <c r="F80" s="358"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="363" t="s">
+      <c r="B81" s="360" t="s">
         <v>251</v>
       </c>
-      <c r="C81" s="363"/>
-      <c r="D81" s="363"/>
-      <c r="E81" s="363"/>
-      <c r="F81" s="363"/>
+      <c r="C81" s="360"/>
+      <c r="D81" s="360"/>
+      <c r="E81" s="360"/>
+      <c r="F81" s="360"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5033,22 +5033,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="360" t="s">
+      <c r="B89" s="358" t="s">
         <v>360</v>
       </c>
-      <c r="C89" s="360"/>
-      <c r="D89" s="360"/>
-      <c r="E89" s="360"/>
-      <c r="F89" s="360"/>
+      <c r="C89" s="358"/>
+      <c r="D89" s="358"/>
+      <c r="E89" s="358"/>
+      <c r="F89" s="358"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="360" t="s">
+      <c r="B90" s="358" t="s">
         <v>361</v>
       </c>
-      <c r="C90" s="360"/>
-      <c r="D90" s="360"/>
-      <c r="E90" s="360"/>
-      <c r="F90" s="360"/>
+      <c r="C90" s="358"/>
+      <c r="D90" s="358"/>
+      <c r="E90" s="358"/>
+      <c r="F90" s="358"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5064,7 +5064,7 @@
       </c>
       <c r="C93" s="223">
         <f>DCF!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>32.879562093372662</v>
+        <v>32.912329274085167</v>
       </c>
       <c r="D93" s="1" t="str">
         <f>Market_currency</f>
@@ -5085,13 +5085,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="360" t="s">
+      <c r="B97" s="358" t="s">
         <v>362</v>
       </c>
-      <c r="C97" s="360"/>
-      <c r="D97" s="360"/>
-      <c r="E97" s="360"/>
-      <c r="F97" s="360"/>
+      <c r="C97" s="358"/>
+      <c r="D97" s="358"/>
+      <c r="E97" s="358"/>
+      <c r="F97" s="358"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5104,13 +5104,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="360" t="s">
+      <c r="B101" s="358" t="s">
         <v>341</v>
       </c>
-      <c r="C101" s="360"/>
-      <c r="D101" s="360"/>
-      <c r="E101" s="360"/>
-      <c r="F101" s="360"/>
+      <c r="C101" s="358"/>
+      <c r="D101" s="358"/>
+      <c r="E101" s="358"/>
+      <c r="F101" s="358"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="C103" s="223">
         <f>C102*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>3.0824029913663464</v>
+        <v>3.0854748587945089</v>
       </c>
       <c r="D103" s="1" t="str">
         <f>Market_currency</f>
@@ -5180,7 +5180,7 @@
       </c>
       <c r="C109" s="349">
         <f>DCF!C8</f>
-        <v>410072.98329152912</v>
+        <v>409755.75103906996</v>
       </c>
       <c r="D109" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5193,7 +5193,7 @@
       </c>
       <c r="C110" s="223">
         <f>C109*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>1.4587538261700301</v>
+        <v>1.4590779781621608</v>
       </c>
       <c r="D110" s="1" t="str">
         <f>Market_currency</f>
@@ -5224,7 +5224,7 @@
       </c>
       <c r="C114" s="223">
         <f>C113*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>1.3383996554779853E-2</v>
+        <v>1.3397334805226152E-2</v>
       </c>
       <c r="D114" s="1" t="str">
         <f>Market_currency</f>
@@ -5232,13 +5232,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="360" t="s">
+      <c r="B116" s="358" t="s">
         <v>363</v>
       </c>
-      <c r="C116" s="360"/>
-      <c r="D116" s="360"/>
-      <c r="E116" s="360"/>
-      <c r="F116" s="360"/>
+      <c r="C116" s="358"/>
+      <c r="D116" s="358"/>
+      <c r="E116" s="358"/>
+      <c r="F116" s="358"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="C118" s="223">
         <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
-        <v>31.269296924731126</v>
+        <v>31.299329728258044</v>
       </c>
       <c r="D118" s="1" t="str">
         <f>Market_currency</f>
@@ -5259,7 +5259,7 @@
       </c>
       <c r="C119" s="223">
         <f>BS!D47</f>
-        <v>-5.9156457264361171</v>
+        <v>-5.9215411526586088</v>
       </c>
       <c r="D119" s="1" t="str">
         <f>Market_currency</f>
@@ -5277,13 +5277,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B123" s="361" t="s">
+      <c r="B123" s="359" t="s">
         <v>364</v>
       </c>
-      <c r="C123" s="361"/>
-      <c r="D123" s="361"/>
-      <c r="E123" s="361"/>
-      <c r="F123" s="361"/>
+      <c r="C123" s="359"/>
+      <c r="D123" s="359"/>
+      <c r="E123" s="359"/>
+      <c r="F123" s="359"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5317,7 +5317,7 @@
       </c>
       <c r="E126" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E74,DDM!E69),2)&amp;" "&amp;Market_currency</f>
-        <v>40.92 HKD</v>
+        <v>40.96 HKD</v>
       </c>
       <c r="F126" s="232">
         <f>DCF!F74</f>
@@ -5339,7 +5339,7 @@
       </c>
       <c r="E127" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E75,DDM!E70),2)&amp;" "&amp;Market_currency</f>
-        <v>33.93 HKD</v>
+        <v>33.97 HKD</v>
       </c>
       <c r="F127" s="221">
         <f>DCF!F75</f>
@@ -5361,7 +5361,7 @@
       </c>
       <c r="E128" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E76,DDM!E71),2)&amp;" "&amp;Market_currency</f>
-        <v>32.84 HKD</v>
+        <v>32.88 HKD</v>
       </c>
       <c r="F128" s="221">
         <f>DCF!F76</f>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="E129" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E77,DDM!E72),2)&amp;" "&amp;Market_currency</f>
-        <v>31.79 HKD</v>
+        <v>31.82 HKD</v>
       </c>
       <c r="F129" s="221">
         <f>DCF!F77</f>
@@ -5405,7 +5405,7 @@
       </c>
       <c r="E130" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E78,DDM!E73),2)&amp;" "&amp;Market_currency</f>
-        <v>31.27 HKD</v>
+        <v>31.3 HKD</v>
       </c>
       <c r="F130" s="221">
         <f>DCF!F78</f>
@@ -5418,7 +5418,7 @@
       </c>
       <c r="C132" s="217">
         <f>Scenarios!C60</f>
-        <v>33.175058631690291</v>
+        <v>33.206990683086438</v>
       </c>
       <c r="D132" s="212" t="str">
         <f>Market_currency</f>
@@ -5426,13 +5426,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="364" t="s">
+      <c r="B134" s="363" t="s">
         <v>367</v>
       </c>
-      <c r="C134" s="364"/>
-      <c r="D134" s="364"/>
-      <c r="E134" s="364"/>
-      <c r="F134" s="364"/>
+      <c r="C134" s="363"/>
+      <c r="D134" s="363"/>
+      <c r="E134" s="363"/>
+      <c r="F134" s="363"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5445,22 +5445,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="365" t="s">
+      <c r="B138" s="361" t="s">
         <v>365</v>
       </c>
-      <c r="C138" s="365"/>
-      <c r="D138" s="365"/>
-      <c r="E138" s="365"/>
-      <c r="F138" s="365"/>
+      <c r="C138" s="361"/>
+      <c r="D138" s="361"/>
+      <c r="E138" s="361"/>
+      <c r="F138" s="361"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="360" t="s">
+      <c r="B139" s="358" t="s">
         <v>366</v>
       </c>
-      <c r="C139" s="360"/>
-      <c r="D139" s="360"/>
-      <c r="E139" s="360"/>
-      <c r="F139" s="360"/>
+      <c r="C139" s="358"/>
+      <c r="D139" s="358"/>
+      <c r="E139" s="358"/>
+      <c r="F139" s="358"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5491,7 +5491,7 @@
       </c>
       <c r="C143" s="213">
         <f>Scenarios!C77</f>
-        <v>1.4928119876800001</v>
+        <v>1.49429969728</v>
       </c>
       <c r="D143" s="212" t="str">
         <f>Market_currency</f>
@@ -5527,7 +5527,7 @@
       </c>
       <c r="C147" s="216">
         <f>Scenarios!C81</f>
-        <v>2.4739765786422589</v>
+        <v>2.4764420992413672</v>
       </c>
     </row>
     <row r="148" spans="2:4">
@@ -5537,7 +5537,7 @@
       </c>
       <c r="C148" s="216">
         <f>Scenarios!C82</f>
-        <v>12.975526004416281</v>
+        <v>12.988015361793611</v>
       </c>
     </row>
     <row r="149" spans="2:4">
@@ -5546,7 +5546,7 @@
       </c>
       <c r="C149" s="215">
         <f>Scenarios!C83</f>
-        <v>15.449502583058539</v>
+        <v>15.464457461034979</v>
       </c>
       <c r="D149" s="300" t="str">
         <f>IF($D$11="","",C149*$E$25)</f>
@@ -5572,7 +5572,7 @@
       </c>
       <c r="C151" s="92">
         <f>Scenarios!F83</f>
-        <v>0.53430368414479645</v>
+        <v>0.53430114735113277</v>
       </c>
     </row>
     <row r="153" spans="2:4">
@@ -5596,7 +5596,7 @@
       </c>
       <c r="C155" s="216">
         <f>Scenarios!C91</f>
-        <v>3.060862929414526</v>
+        <v>3.0639133304040378</v>
       </c>
     </row>
     <row r="156" spans="2:4">
@@ -5606,7 +5606,7 @@
       </c>
       <c r="C156" s="216">
         <f>Scenarios!C92</f>
-        <v>18.387039406279996</v>
+        <v>18.404737517799937</v>
       </c>
     </row>
     <row r="157" spans="2:4">
@@ -5615,7 +5615,7 @@
       </c>
       <c r="C157" s="215">
         <f>Scenarios!C93</f>
-        <v>21.447902335694522</v>
+        <v>21.468650848203975</v>
       </c>
       <c r="D157" s="300" t="str">
         <f>IF($D$11="","",C157*$E$25)</f>
@@ -5641,7 +5641,7 @@
       </c>
       <c r="C159" s="92">
         <f>Scenarios!F93</f>
-        <v>0.3534931596109816</v>
+        <v>0.35349002102925386</v>
       </c>
     </row>
     <row r="161" spans="2:4">
@@ -5665,7 +5665,7 @@
       </c>
       <c r="C163" s="216">
         <f>Scenarios!C97</f>
-        <v>3.8820959987512631</v>
+        <v>3.8859648258595172</v>
       </c>
     </row>
     <row r="164" spans="2:4">
@@ -5675,7 +5675,7 @@
       </c>
       <c r="C164" s="216">
         <f>Scenarios!C98</f>
-        <v>26.70461408967989</v>
+        <v>26.73031813195734</v>
       </c>
     </row>
     <row r="165" spans="2:4">
@@ -5684,7 +5684,7 @@
       </c>
       <c r="C165" s="215">
         <f>Scenarios!C99</f>
-        <v>30.586710088431154</v>
+        <v>30.616282957816857</v>
       </c>
       <c r="D165" s="300" t="str">
         <f>IF($D$11="","",C165*$E$25)</f>
@@ -5710,7 +5710,7 @@
       </c>
       <c r="C167" s="92">
         <f>Scenarios!F99</f>
-        <v>7.8020918425344754E-2</v>
+        <v>7.8016937758504157E-2</v>
       </c>
     </row>
     <row r="169" spans="2:4">
@@ -5734,7 +5734,7 @@
       </c>
       <c r="C171" s="216">
         <f>Scenarios!C103</f>
-        <v>3.6015628679154563</v>
+        <v>3.6051521207469053</v>
       </c>
     </row>
     <row r="172" spans="2:4">
@@ -5744,7 +5744,7 @@
       </c>
       <c r="C172" s="216">
         <f>Scenarios!C104</f>
-        <v>23.778568063139453</v>
+        <v>23.801455692847924</v>
       </c>
     </row>
     <row r="173" spans="2:4">
@@ -5753,7 +5753,7 @@
       </c>
       <c r="C173" s="215">
         <f>Scenarios!C105</f>
-        <v>27.380130931054907</v>
+        <v>27.406607813594828</v>
       </c>
       <c r="D173" s="300" t="str">
         <f>IF($D$11="","",C173*$E$25)</f>
@@ -5779,7 +5779,7 @@
       </c>
       <c r="C175" s="92">
         <f>Scenarios!F105</f>
-        <v>0.15781683763635923</v>
+        <v>0.15781248391450331</v>
       </c>
     </row>
     <row r="177" spans="1:6" ht="13.9">
@@ -5793,13 +5793,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="359" t="s">
+      <c r="B179" s="365" t="s">
         <v>373</v>
       </c>
-      <c r="C179" s="360"/>
-      <c r="D179" s="360"/>
-      <c r="E179" s="360"/>
-      <c r="F179" s="360"/>
+      <c r="C179" s="358"/>
+      <c r="D179" s="358"/>
+      <c r="E179" s="358"/>
+      <c r="F179" s="358"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5836,13 +5836,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="361" t="s">
+      <c r="B188" s="359" t="s">
         <v>378</v>
       </c>
-      <c r="C188" s="361"/>
-      <c r="D188" s="361"/>
-      <c r="E188" s="361"/>
-      <c r="F188" s="361"/>
+      <c r="C188" s="359"/>
+      <c r="D188" s="359"/>
+      <c r="E188" s="359"/>
+      <c r="F188" s="359"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5850,22 +5850,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="358" t="s">
+      <c r="B191" s="364" t="s">
         <v>379</v>
       </c>
-      <c r="C191" s="358"/>
-      <c r="D191" s="358"/>
-      <c r="E191" s="358"/>
-      <c r="F191" s="358"/>
+      <c r="C191" s="364"/>
+      <c r="D191" s="364"/>
+      <c r="E191" s="364"/>
+      <c r="F191" s="364"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="358" t="s">
+      <c r="B192" s="364" t="s">
         <v>380</v>
       </c>
-      <c r="C192" s="358"/>
-      <c r="D192" s="358"/>
-      <c r="E192" s="358"/>
-      <c r="F192" s="358"/>
+      <c r="C192" s="364"/>
+      <c r="D192" s="364"/>
+      <c r="E192" s="364"/>
+      <c r="F192" s="364"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5889,6 +5889,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5905,17 +5916,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -6488,15 +6488,15 @@
       </c>
       <c r="C25" s="39">
         <f>0.164*Exchange_Rate</f>
-        <v>1.4928119876800001</v>
+        <v>1.49429969728</v>
       </c>
       <c r="D25" s="39">
         <f>0.137*Exchange_Rate</f>
-        <v>1.2470441604400002</v>
+        <v>1.24828694224</v>
       </c>
       <c r="E25" s="39">
         <f>0.11*Exchange_Rate</f>
-        <v>1.0012763332000001</v>
+        <v>1.0022741872000001</v>
       </c>
       <c r="F25" s="39"/>
       <c r="G25" s="39"/>
@@ -7870,15 +7870,15 @@
       </c>
       <c r="C65" s="73">
         <f>IF(C$4="","",C25)</f>
-        <v>1.4928119876800001</v>
+        <v>1.49429969728</v>
       </c>
       <c r="D65" s="73">
         <f t="shared" ref="D65:M65" si="33">IF(D$4="","",D25)</f>
-        <v>1.2470441604400002</v>
+        <v>1.24828694224</v>
       </c>
       <c r="E65" s="73">
         <f t="shared" si="33"/>
-        <v>1.0012763332000001</v>
+        <v>1.0022741872000001</v>
       </c>
       <c r="F65" s="73">
         <f t="shared" si="33"/>
@@ -9220,11 +9220,11 @@
       </c>
       <c r="C47" s="147">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>15.649874017440746</v>
+        <v>15.665470400646859</v>
       </c>
       <c r="D47" s="147">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>-5.9156457264361171</v>
+        <v>-5.9215411526586088</v>
       </c>
       <c r="F47" s="253"/>
     </row>
@@ -9415,7 +9415,7 @@
       </c>
       <c r="D66" s="76">
         <f>C66-D75</f>
-        <v>410072.98329152912</v>
+        <v>409755.75103906996</v>
       </c>
       <c r="F66" s="5" t="s">
         <v>225</v>
@@ -9482,11 +9482,11 @@
       </c>
       <c r="C73" s="349">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35-Normalized_FCF!G91)/12</f>
-        <v>-651147.17846360744</v>
+        <v>-651464.4107160666</v>
       </c>
       <c r="D73" s="349">
         <f>(Normalized_FCF!C25+Normalized_FCF!C35-Normalized_FCF!C91)/12</f>
-        <v>-601490.01670847088</v>
+        <v>-601807.24896093004</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>348</v>
@@ -9498,11 +9498,11 @@
       </c>
       <c r="C74" s="258">
         <f>-$C$66/C73</f>
-        <v>1.5535089968243427</v>
+        <v>1.5527525116654119</v>
       </c>
       <c r="D74" s="258">
         <f>-$C$66/D73</f>
-        <v>1.6817619110880149</v>
+        <v>1.6808753994680974</v>
       </c>
       <c r="F74" s="253" t="s">
         <v>316</v>
@@ -9515,7 +9515,7 @@
       <c r="C75" s="320"/>
       <c r="D75" s="321">
         <f>MAX(-D73*D76,G5)</f>
-        <v>601490.01670847088</v>
+        <v>601807.24896093004</v>
       </c>
       <c r="F75" s="253" t="s">
         <v>349</v>
@@ -9630,11 +9630,11 @@
       </c>
       <c r="C86" s="76">
         <f>-DCF!C7*Exchange_Rate</f>
-        <v>-7887326.7519800002</v>
+        <v>-7895187.1200799998</v>
       </c>
       <c r="D86" s="223">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>-3.0824029913663464</v>
+        <v>-3.0854748587945089</v>
       </c>
       <c r="E86" s="240" t="str">
         <f>Market_currency</f>
@@ -9647,11 +9647,11 @@
       </c>
       <c r="C87" s="76">
         <f>DCF!C8*Exchange_Rate</f>
-        <v>3732694.3004957014</v>
+        <v>3733523.7483928129</v>
       </c>
       <c r="D87" s="223">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>1.4587538261700301</v>
+        <v>1.4590779781621608</v>
       </c>
       <c r="E87" s="240" t="str">
         <f>Market_currency</f>
@@ -9664,11 +9664,11 @@
       </c>
       <c r="C88" s="76">
         <f>DCF!C9*Exchange_Rate</f>
-        <v>34247.291600288001</v>
+        <v>34281.421835647998</v>
       </c>
       <c r="D88" s="223">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>1.3383996554779853E-2</v>
+        <v>1.3397334805226152E-2</v>
       </c>
       <c r="E88" s="240" t="str">
         <f>Market_currency</f>
@@ -9681,11 +9681,11 @@
       </c>
       <c r="C89" s="180">
         <f>SUM(C86:C88)</f>
-        <v>-4120385.1598840109</v>
+        <v>-4127381.949851539</v>
       </c>
       <c r="D89" s="242">
         <f>SUM(D86:D88)</f>
-        <v>-1.6102651686415363</v>
+        <v>-1.612999545827122</v>
       </c>
       <c r="E89" s="240" t="str">
         <f>Market_currency</f>
@@ -13197,20 +13197,20 @@
       </c>
       <c r="C90" s="113">
         <f>G90</f>
-        <v>1.4928119876800001</v>
+        <v>1.49429969728</v>
       </c>
       <c r="E90" s="268"/>
       <c r="G90" s="112">
         <f>Data!C65</f>
-        <v>1.4928119876800001</v>
+        <v>1.49429969728</v>
       </c>
       <c r="H90" s="112">
         <f>Data!D65</f>
-        <v>1.2470441604400002</v>
+        <v>1.24828694224</v>
       </c>
       <c r="I90" s="112">
         <f>Data!E65</f>
-        <v>1.0012763332000001</v>
+        <v>1.0022741872000001</v>
       </c>
       <c r="J90" s="112">
         <f>Data!F65</f>
@@ -13253,20 +13253,20 @@
       </c>
       <c r="C91" s="74">
         <f>C90*Common_Shares/scaling_factor</f>
-        <v>3819843.1415632889</v>
+        <v>3823649.9285927988</v>
       </c>
       <c r="E91" s="268"/>
       <c r="G91" s="74">
         <f t="shared" ref="G91:Q91" si="37">IF(G$4="","",G90*Common_Shares/scaling_factor)</f>
-        <v>3819843.1415632889</v>
+        <v>3823649.9285927988</v>
       </c>
       <c r="H91" s="74">
         <f t="shared" si="37"/>
-        <v>3190966.526793723</v>
+        <v>3194146.5866903258</v>
       </c>
       <c r="I91" s="74">
         <f t="shared" si="37"/>
-        <v>2562089.9120241571</v>
+        <v>2564643.2447878527</v>
       </c>
       <c r="J91" s="74">
         <f t="shared" si="37"/>
@@ -13308,20 +13308,20 @@
       </c>
       <c r="C92" s="23">
         <f>C90/(C19*scaling_factor/Common_Shares)</f>
-        <v>5.5103488187787892</v>
+        <v>5.5158403333865902</v>
       </c>
       <c r="E92" s="268"/>
       <c r="G92" s="170">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",G90/(G19*scaling_factor/Common_Shares))</f>
-        <v>3.8317983524228478</v>
+        <v>3.8356170538006564</v>
       </c>
       <c r="H92" s="170">
         <f t="shared" si="38"/>
-        <v>3.8866117266964957</v>
+        <v>3.8904850540980687</v>
       </c>
       <c r="I92" s="170">
         <f t="shared" si="38"/>
-        <v>3.8134963742158301</v>
+        <v>3.8172968361710575</v>
       </c>
       <c r="J92" s="170">
         <f t="shared" si="38"/>
@@ -13384,20 +13384,20 @@
       </c>
       <c r="C94" s="23">
         <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
-        <v>3.0747929715345009E-2</v>
+        <v>3.0558276017995913E-2</v>
       </c>
       <c r="E94" s="268"/>
       <c r="G94" s="23">
         <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>3.0747929715345009E-2</v>
+        <v>3.0558276017995913E-2</v>
       </c>
       <c r="H94" s="23">
         <f t="shared" si="39"/>
-        <v>2.5685770554891869E-2</v>
+        <v>2.5527340332106341E-2</v>
       </c>
       <c r="I94" s="23">
         <f t="shared" si="39"/>
-        <v>2.0623611394438725E-2</v>
+        <v>2.049640464621677E-2</v>
       </c>
       <c r="J94" s="23">
         <f t="shared" si="39"/>
@@ -14526,38 +14526,38 @@
       </c>
       <c r="C125" s="177">
         <f>C16*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>2.4659671570029498</v>
+        <v>2.4684246955563873</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="265"/>
       <c r="F125" s="27"/>
       <c r="G125" s="177">
         <f t="shared" ref="G125:Q125" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>3.5462041477591271</v>
+        <v>3.549738231084905</v>
       </c>
       <c r="H125" s="177">
         <f t="shared" si="49"/>
-        <v>2.9205990674629438</v>
+        <v>2.9235096840082786</v>
       </c>
       <c r="I125" s="177">
         <f t="shared" si="49"/>
-        <v>2.389966860869587</v>
+        <v>2.3923486588936793</v>
       </c>
       <c r="J125" s="177">
         <f t="shared" si="49"/>
-        <v>1.2819310287209749</v>
+        <v>1.2832085781469611</v>
       </c>
       <c r="K125" s="177">
         <f t="shared" si="49"/>
-        <v>6.1926312062739139</v>
+        <v>6.1988026712479796</v>
       </c>
       <c r="L125" s="177">
         <f t="shared" si="49"/>
-        <v>8.3263655368860068</v>
+        <v>8.3346634431491964</v>
       </c>
       <c r="M125" s="177">
         <f t="shared" si="49"/>
-        <v>7.7033359439132507</v>
+        <v>7.7110129500803808</v>
       </c>
       <c r="N125" s="177" t="str">
         <f t="shared" si="49"/>
@@ -14583,38 +14583,38 @@
       </c>
       <c r="C126" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>5.0792320432604524E-2</v>
+        <v>5.0479032628964977E-2</v>
       </c>
       <c r="D126" s="27"/>
       <c r="E126" s="265"/>
       <c r="F126" s="27"/>
       <c r="G126" s="77">
         <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
-        <v>7.3042309943545367E-2</v>
+        <v>7.2591783866766971E-2</v>
       </c>
       <c r="H126" s="77">
         <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
-        <v>6.0156520442079177E-2</v>
+        <v>5.9785474110598744E-2</v>
       </c>
       <c r="I126" s="77">
         <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
-        <v>4.9226917834594999E-2</v>
+        <v>4.8923285457948454E-2</v>
       </c>
       <c r="J126" s="77">
         <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
-        <v>2.6404346626590625E-2</v>
+        <v>2.6241484215684278E-2</v>
       </c>
       <c r="K126" s="77">
         <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
-        <v>0.12755162113849464</v>
+        <v>0.12676488080261716</v>
       </c>
       <c r="L126" s="77">
         <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
-        <v>0.17150083495130808</v>
+        <v>0.17044301519732508</v>
       </c>
       <c r="M126" s="77">
         <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
-        <v>0.15866809359244596</v>
+        <v>0.15768942638201189</v>
       </c>
       <c r="N126" s="77" t="str">
         <f t="shared" ref="N126" si="57">IF(N$4="","",N125/Market_Price)</f>
@@ -14640,31 +14640,31 @@
       <c r="C127" s="169"/>
       <c r="G127" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.7889708977182921E-3</v>
+        <v>6.740379081476954E-3</v>
       </c>
       <c r="H127" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.4204869465927386E-3</v>
+        <v>5.3816900052572076E-3</v>
       </c>
       <c r="I127" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.7764757428492119E-3</v>
+        <v>3.7494457528697185E-3</v>
       </c>
       <c r="J127" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.3754395053703593E-3</v>
+        <v>2.3584373821212874E-3</v>
       </c>
       <c r="K127" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-4.3763667271419027E-4</v>
+        <v>-4.345043038910826E-4</v>
       </c>
       <c r="L127" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.0745562433525599E-3</v>
+        <v>2.0597076812835743E-3</v>
       </c>
       <c r="M127" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.6757665869442605E-3</v>
+        <v>1.663772347569404E-3</v>
       </c>
       <c r="N127" s="23" t="str">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -15492,7 +15492,7 @@
       </c>
       <c r="C8" s="338">
         <f>BS!D66</f>
-        <v>410072.98329152912</v>
+        <v>409755.75103906996</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
@@ -15524,7 +15524,7 @@
       </c>
       <c r="C10" s="347">
         <f>C6-C7+C8+C9</f>
-        <v>8790169.8321636729</v>
+        <v>8789852.5999112129</v>
       </c>
       <c r="D10" t="str">
         <f>Reporting_currency</f>
@@ -15538,7 +15538,7 @@
       </c>
       <c r="C11" s="208">
         <f>Exchange_Rate</f>
-        <v>9.1025121200000001</v>
+        <v>9.1115835199999999</v>
       </c>
       <c r="D11" t="str">
         <f>Thesis!C15</f>
@@ -15552,7 +15552,7 @@
       </c>
       <c r="C12" s="111">
         <f>(C10*scaling_factor)/Common_Shares*Exchange_Rate</f>
-        <v>31.269296924731126</v>
+        <v>31.299329728258044</v>
       </c>
       <c r="D12" t="str">
         <f>Market_currency</f>
@@ -15605,7 +15605,7 @@
       </c>
       <c r="C18" s="140">
         <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>32.51089805002848</v>
+        <v>32.542168210924395</v>
       </c>
       <c r="D18" t="str">
         <f>Market_currency</f>
@@ -16701,23 +16701,23 @@
       </c>
       <c r="B65" s="124">
         <f>C12</f>
-        <v>31.269296924731126</v>
+        <v>31.299329728258044</v>
       </c>
       <c r="C65" s="124">
         <f>C12</f>
-        <v>31.269296924731126</v>
+        <v>31.299329728258044</v>
       </c>
       <c r="D65" s="124">
         <f>C12</f>
-        <v>31.269296924731126</v>
+        <v>31.299329728258044</v>
       </c>
       <c r="E65" s="141">
         <f>C12</f>
-        <v>31.269296924731126</v>
+        <v>31.299329728258044</v>
       </c>
       <c r="F65" s="124">
         <f>C12</f>
-        <v>31.269296924731126</v>
+        <v>31.299329728258044</v>
       </c>
       <c r="H65" s="120"/>
     </row>
@@ -16728,23 +16728,23 @@
       </c>
       <c r="B66" s="124">
         <f t="shared" ref="B66:F71" si="4">(B56-$C$7+$C$8+$C$9)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>31.269296924731123</v>
+        <v>31.299329728258044</v>
       </c>
       <c r="C66" s="124">
         <f t="shared" si="4"/>
-        <v>31.78689578784401</v>
+        <v>31.817444421096273</v>
       </c>
       <c r="D66" s="124">
         <f t="shared" si="4"/>
-        <v>32.844545793955824</v>
+        <v>32.876148462197442</v>
       </c>
       <c r="E66" s="124">
         <f t="shared" si="4"/>
-        <v>33.933232056988523</v>
+        <v>33.965919690395395</v>
       </c>
       <c r="F66" s="124">
         <f t="shared" si="4"/>
-        <v>35.627431734699535</v>
+        <v>35.661807777059202</v>
       </c>
       <c r="H66" s="120"/>
     </row>
@@ -16755,23 +16755,23 @@
       </c>
       <c r="B67" s="124">
         <f t="shared" si="4"/>
-        <v>31.26929692473113</v>
+        <v>31.299329728258055</v>
       </c>
       <c r="C67" s="124">
         <f t="shared" si="4"/>
-        <v>32.283160128763768</v>
+        <v>32.314203330139961</v>
       </c>
       <c r="D67" s="124">
         <f t="shared" si="4"/>
-        <v>34.460147636321736</v>
+        <v>34.493360384325904</v>
       </c>
       <c r="E67" s="124">
         <f t="shared" si="4"/>
-        <v>36.856021439058608</v>
+        <v>36.891621871838986</v>
       </c>
       <c r="F67" s="124">
         <f t="shared" si="4"/>
-        <v>40.918320892954817</v>
+        <v>40.957969740368455</v>
       </c>
       <c r="H67" s="120"/>
     </row>
@@ -16782,23 +16782,23 @@
       </c>
       <c r="B68" s="124">
         <f t="shared" si="4"/>
-        <v>31.26929692473113</v>
+        <v>31.299329728258055</v>
       </c>
       <c r="C68" s="124">
         <f t="shared" si="4"/>
-        <v>32.895868538860547</v>
+        <v>32.927522354427424</v>
       </c>
       <c r="D68" s="124">
         <f t="shared" si="4"/>
-        <v>36.558892525128293</v>
+        <v>36.594196844572664</v>
       </c>
       <c r="E68" s="124">
         <f t="shared" si="4"/>
-        <v>40.858687476136147</v>
+        <v>40.89827689395824</v>
       </c>
       <c r="F68" s="124">
         <f t="shared" si="4"/>
-        <v>48.787075654952517</v>
+        <v>48.8345663619547</v>
       </c>
       <c r="H68" s="120"/>
     </row>
@@ -16809,23 +16809,23 @@
       </c>
       <c r="B69" s="124">
         <f t="shared" si="4"/>
-        <v>31.26929692473114</v>
+        <v>31.299329728258058</v>
       </c>
       <c r="C69" s="124">
         <f t="shared" si="4"/>
-        <v>33.518146774737332</v>
+        <v>33.550420741611291</v>
       </c>
       <c r="D69" s="124">
         <f t="shared" si="4"/>
-        <v>38.806800854672389</v>
+        <v>38.844345399161426</v>
       </c>
       <c r="E69" s="124">
         <f t="shared" si="4"/>
-        <v>45.395248957601332</v>
+        <v>45.439359431070528</v>
       </c>
       <c r="F69" s="124">
         <f t="shared" si="4"/>
-        <v>58.549661153004557</v>
+        <v>58.606881077273307</v>
       </c>
       <c r="H69" s="120"/>
     </row>
@@ -16836,23 +16836,23 @@
       </c>
       <c r="B70" s="124">
         <f t="shared" si="4"/>
-        <v>31.26929692473114</v>
+        <v>31.299329728258058</v>
       </c>
       <c r="C70" s="124">
         <f t="shared" si="4"/>
-        <v>34.094717011420016</v>
+        <v>34.12756557783046</v>
       </c>
       <c r="D70" s="124">
         <f t="shared" si="4"/>
-        <v>41.00730530331635</v>
+        <v>41.047042830994243</v>
       </c>
       <c r="E70" s="124">
         <f t="shared" si="4"/>
-        <v>50.109628397486517</v>
+        <v>50.158437136784663</v>
       </c>
       <c r="F70" s="124">
         <f t="shared" si="4"/>
-        <v>69.731911969804258</v>
+        <v>69.80027592428381</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="13.15">
@@ -16862,23 +16862,23 @@
       </c>
       <c r="B71" s="124">
         <f t="shared" si="4"/>
-        <v>31.26929692473113</v>
+        <v>31.299329728258055</v>
       </c>
       <c r="C71" s="124">
         <f t="shared" si="4"/>
-        <v>34.601106499622908</v>
+        <v>34.634459724697116</v>
       </c>
       <c r="D71" s="124">
         <f t="shared" si="4"/>
-        <v>43.052611054105526</v>
+        <v>43.094386896739024</v>
       </c>
       <c r="E71" s="124">
         <f t="shared" si="4"/>
-        <v>54.775337929464037</v>
+        <v>54.828796431035542</v>
       </c>
       <c r="F71" s="124">
         <f t="shared" si="4"/>
-        <v>82.005903170402632</v>
+        <v>82.08649916394009</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="13.15">
@@ -16913,7 +16913,7 @@
       </c>
       <c r="E74" s="135">
         <f>INDEX(B$65:F$71, MATCH(D74, A$65:A$71, 0), MATCH(C74, B$64:F$64, 0))</f>
-        <v>40.918320892954817</v>
+        <v>40.957969740368455</v>
       </c>
       <c r="F74" s="142">
         <f>Scenarios!C58</f>
@@ -16935,7 +16935,7 @@
       </c>
       <c r="E75" s="135">
         <f>INDEX(B$65:F$71, MATCH(D75, A$65:A$71, 0), MATCH(C75, B$64:F$64, 0))</f>
-        <v>33.933232056988523</v>
+        <v>33.965919690395395</v>
       </c>
       <c r="F75" s="142">
         <f>Scenarios!C40*(1-F$74-F$78)</f>
@@ -16958,7 +16958,7 @@
       </c>
       <c r="E76" s="135">
         <f>INDEX(B$65:F$71, MATCH(D76, A$65:A$71, 0), MATCH(C76, B$64:F$64, 0))</f>
-        <v>32.844545793955824</v>
+        <v>32.876148462197442</v>
       </c>
       <c r="F76" s="142">
         <f>Scenarios!C28*(1-F$74-F$78)</f>
@@ -16981,7 +16981,7 @@
       </c>
       <c r="E77" s="135">
         <f>INDEX(B$65:F$71, MATCH(D77, A$65:A$71, 0), MATCH(C77, B$64:F$64, 0))</f>
-        <v>31.78689578784401</v>
+        <v>31.817444421096273</v>
       </c>
       <c r="F77" s="142">
         <f>Scenarios!C34*(1-F$74-F$78)</f>
@@ -17004,7 +17004,7 @@
       </c>
       <c r="E78" s="135">
         <f>INDEX(B$65:F$71, MATCH(D78, A$65:A$71, 0), MATCH(C78, B$64:F$64, 0))</f>
-        <v>31.26929692473113</v>
+        <v>31.299329728258055</v>
       </c>
       <c r="F78" s="142">
         <f>Scenarios!C52</f>
@@ -17186,7 +17186,7 @@
       </c>
       <c r="C4" s="114">
         <f>Normalized_FCF!C91*(1-dividend_tax_rate)</f>
-        <v>3819843.1415632889</v>
+        <v>3823649.9285927988</v>
       </c>
       <c r="D4" t="str">
         <f>Market_currency</f>
@@ -17218,7 +17218,7 @@
       </c>
       <c r="C6" s="319">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
-        <v>50931241.887510523</v>
+        <v>50981999.047903985</v>
       </c>
       <c r="D6" t="str">
         <f>Reporting_currency</f>
@@ -17234,7 +17234,7 @@
       </c>
       <c r="C7" s="111">
         <f>(C6*scaling_factor)/Common_Shares*Exchange_Rate</f>
-        <v>181.17785614317992</v>
+        <v>181.53915327569916</v>
       </c>
       <c r="D7" t="str">
         <f>Market_currency</f>
@@ -17287,7 +17287,7 @@
       </c>
       <c r="C13" s="140">
         <f>F47/Common_Shares*scaling_factor</f>
-        <v>20.655782597008681</v>
+        <v>20.676367778745359</v>
       </c>
       <c r="D13" t="str">
         <f>Market_currency</f>
@@ -17322,7 +17322,7 @@
       </c>
       <c r="C16" s="123">
         <f>C4*(1+D16)</f>
-        <v>3910574.4214727245</v>
+        <v>3914471.6296652849</v>
       </c>
       <c r="D16" s="138">
         <f>IF($C$12&lt;B16,0,DDM!$C$11)</f>
@@ -17334,7 +17334,7 @@
       </c>
       <c r="F16" s="125">
         <f t="shared" ref="F16:F46" si="1">C16*E16</f>
-        <v>3637743.6478816043</v>
+        <v>3641368.957828172</v>
       </c>
       <c r="H16" s="120"/>
     </row>
@@ -17344,7 +17344,7 @@
       </c>
       <c r="C17" s="123">
         <f t="shared" ref="C17:C45" si="2">IF(ROW()-ROW($C$16)&lt;$C$12, $C$16*(1+D17)^(ROW()-ROW($C$16)), 0)</f>
-        <v>4003460.806932027</v>
+        <v>4007450.5840270999</v>
       </c>
       <c r="D17" s="138">
         <f>IF($C$12&lt;B17,0,DDM!$C$11)</f>
@@ -17356,7 +17356,7 @@
       </c>
       <c r="F17" s="125">
         <f t="shared" si="1"/>
-        <v>3464325.1979941828</v>
+        <v>3467777.6822300488</v>
       </c>
       <c r="H17" s="120"/>
     </row>
@@ -17366,7 +17366,7 @@
       </c>
       <c r="C18" s="123">
         <f t="shared" si="2"/>
-        <v>4098553.4873428643</v>
+        <v>4102638.0320943496</v>
       </c>
       <c r="D18" s="138">
         <f>IF($C$12&lt;B18,0,DDM!$C$11)</f>
@@ -17378,7 +17378,7 @@
       </c>
       <c r="F18" s="125">
         <f t="shared" si="1"/>
-        <v>3299173.9493370815</v>
+        <v>3302461.8468064247</v>
       </c>
       <c r="H18" s="120"/>
     </row>
@@ -17388,7 +17388,7 @@
       </c>
       <c r="C19" s="123">
         <f t="shared" si="2"/>
-        <v>4195904.8679892728</v>
+        <v>4200086.4313772349</v>
       </c>
       <c r="D19" s="138">
         <f>IF($C$12&lt;B19,0,DDM!$C$11)</f>
@@ -17400,7 +17400,7 @@
       </c>
       <c r="F19" s="125">
         <f t="shared" si="1"/>
-        <v>3141895.7880416377</v>
+        <v>3145026.9449218372</v>
       </c>
       <c r="H19" s="120"/>
     </row>
@@ -17410,7 +17410,7 @@
       </c>
       <c r="C20" s="123">
         <f t="shared" si="2"/>
-        <v>4295568.5989180496</v>
+        <v>4299849.4853892252</v>
       </c>
       <c r="D20" s="138">
         <f>IF($C$12&lt;B20,0,DDM!$C$11)</f>
@@ -17422,7 +17422,7 @@
       </c>
       <c r="F20" s="125">
         <f t="shared" si="1"/>
-        <v>2992115.3884284613</v>
+        <v>2995097.2768540694</v>
       </c>
       <c r="H20" s="120"/>
     </row>
@@ -17982,7 +17982,7 @@
       </c>
       <c r="C46" s="123">
         <f>C$16*(1+F4)^$C$12/Equity_Cost</f>
-        <v>52140992.286302999</v>
+        <v>52192955.062203802</v>
       </c>
       <c r="D46" s="139">
         <f>Terminal_Growth</f>
@@ -17994,7 +17994,7 @@
       </c>
       <c r="F46" s="125">
         <f t="shared" si="1"/>
-        <v>36319258.276325174</v>
+        <v>36355453.396439753</v>
       </c>
       <c r="H46" s="120"/>
     </row>
@@ -18005,7 +18005,7 @@
       </c>
       <c r="F47" s="137">
         <f>SUM(F16:F46)</f>
-        <v>52854512.248008139</v>
+        <v>52907186.105080307</v>
       </c>
       <c r="H47" s="120"/>
     </row>
@@ -18026,7 +18026,7 @@
     <row r="50" spans="1:8" ht="13.15">
       <c r="A50" s="133">
         <f>F47</f>
-        <v>52854512.248008139</v>
+        <v>52907186.105080307</v>
       </c>
       <c r="B50" s="131">
         <f>C73</f>
@@ -18056,19 +18056,19 @@
       </c>
       <c r="B51" s="123">
         <f t="dataTable" ref="B51:F56" dt2D="1" dtr="1" r1="C11" r2="C12"/>
-        <v>50931241.887510523</v>
+        <v>50981999.047903985</v>
       </c>
       <c r="C51" s="123">
-        <v>51733015.123511627</v>
+        <v>51784571.316703632</v>
       </c>
       <c r="D51" s="123">
-        <v>53371340.723488696</v>
+        <v>53424529.642531738</v>
       </c>
       <c r="E51" s="123">
-        <v>55057742.240779713</v>
+        <v>55112611.797269031</v>
       </c>
       <c r="F51" s="123">
-        <v>57682098.774063192</v>
+        <v>57739583.71711196</v>
       </c>
       <c r="H51" s="120"/>
     </row>
@@ -18077,19 +18077,19 @@
         <v>10</v>
       </c>
       <c r="B52" s="123">
-        <v>50931241.887510538</v>
+        <v>50981999.047904</v>
       </c>
       <c r="C52" s="123">
-        <v>52501740.665407598</v>
+        <v>52554062.956660099</v>
       </c>
       <c r="D52" s="123">
-        <v>55873947.296951286</v>
+        <v>55929630.268731765</v>
       </c>
       <c r="E52" s="123">
-        <v>59585214.126862511</v>
+        <v>59644595.680471517</v>
       </c>
       <c r="F52" s="123">
-        <v>65877814.846979573</v>
+        <v>65943467.493383601</v>
       </c>
       <c r="H52" s="120"/>
     </row>
@@ -18098,19 +18098,19 @@
         <v>15</v>
       </c>
       <c r="B53" s="123">
-        <v>50931241.887510538</v>
+        <v>50981999.047904</v>
       </c>
       <c r="C53" s="123">
-        <v>53450840.904411122</v>
+        <v>53504109.051905796</v>
       </c>
       <c r="D53" s="123">
-        <v>59124954.207822785</v>
+        <v>59183877.074667662</v>
       </c>
       <c r="E53" s="123">
-        <v>65785441.233001813</v>
+        <v>65851001.821522191</v>
       </c>
       <c r="F53" s="123">
-        <v>78066707.478782162</v>
+        <v>78144507.356539741</v>
       </c>
       <c r="H53" s="120"/>
     </row>
@@ -18119,19 +18119,19 @@
         <v>20</v>
       </c>
       <c r="B54" s="123">
-        <v>50931241.887510538</v>
+        <v>50981999.047904</v>
       </c>
       <c r="C54" s="123">
-        <v>54414765.036453098</v>
+        <v>54468993.813415334</v>
       </c>
       <c r="D54" s="123">
-        <v>62607018.918655314</v>
+        <v>62669411.94861576</v>
       </c>
       <c r="E54" s="123">
-        <v>72812685.37615414</v>
+        <v>72885249.189902872</v>
       </c>
       <c r="F54" s="123">
-        <v>93189190.011754006</v>
+        <v>93282060.683841854</v>
       </c>
       <c r="H54" s="120"/>
     </row>
@@ -18140,19 +18140,19 @@
         <v>25</v>
       </c>
       <c r="B55" s="123">
-        <v>50931241.887510546</v>
+        <v>50981999.047904</v>
       </c>
       <c r="C55" s="123">
-        <v>55307886.365326986</v>
+        <v>55363005.21095553</v>
       </c>
       <c r="D55" s="123">
-        <v>66015653.864283703</v>
+        <v>66081443.878575303</v>
       </c>
       <c r="E55" s="123">
-        <v>80115373.864535704</v>
+        <v>80195215.406397298</v>
       </c>
       <c r="F55" s="123">
-        <v>110510768.67450738</v>
+        <v>110620901.72060908</v>
       </c>
       <c r="H55" s="120"/>
     </row>
@@ -18161,19 +18161,19 @@
         <v>30</v>
       </c>
       <c r="B56" s="123">
-        <v>50931241.887510538</v>
+        <v>50981999.047903985</v>
       </c>
       <c r="C56" s="123">
-        <v>56092296.006784864</v>
+        <v>56148196.580965668</v>
       </c>
       <c r="D56" s="123">
-        <v>69183882.249793664</v>
+        <v>69252829.663558871</v>
       </c>
       <c r="E56" s="123">
-        <v>87342671.48106654</v>
+        <v>87429715.617852971</v>
       </c>
       <c r="F56" s="123">
-        <v>129523479.76194777</v>
+        <v>129652560.53424691</v>
       </c>
       <c r="H56" s="120"/>
     </row>
@@ -18223,23 +18223,23 @@
       </c>
       <c r="B60" s="124">
         <f>C7</f>
-        <v>181.17785614317992</v>
+        <v>181.53915327569916</v>
       </c>
       <c r="C60" s="124">
         <f>C7</f>
-        <v>181.17785614317992</v>
+        <v>181.53915327569916</v>
       </c>
       <c r="D60" s="124">
         <f>C7</f>
-        <v>181.17785614317992</v>
+        <v>181.53915327569916</v>
       </c>
       <c r="E60" s="141">
         <f>C7</f>
-        <v>181.17785614317992</v>
+        <v>181.53915327569916</v>
       </c>
       <c r="F60" s="124">
         <f>C7</f>
-        <v>181.17785614317992</v>
+        <v>181.53915327569916</v>
       </c>
       <c r="H60" s="120"/>
     </row>
@@ -18250,23 +18250,23 @@
       </c>
       <c r="B61" s="124">
         <f t="shared" ref="B61:F66" si="4">B51/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>181.17785614317992</v>
+        <v>181.53915327569916</v>
       </c>
       <c r="C61" s="124">
         <f t="shared" si="4"/>
-        <v>184.03000642713525</v>
+        <v>184.39699119577648</v>
       </c>
       <c r="D61" s="124">
         <f t="shared" si="4"/>
-        <v>189.85802688899489</v>
+        <v>190.23663364680169</v>
       </c>
       <c r="E61" s="124">
         <f t="shared" si="4"/>
-        <v>195.85706795251775</v>
+        <v>196.24763774146018</v>
       </c>
       <c r="F61" s="124">
         <f t="shared" si="4"/>
-        <v>205.19269914536807</v>
+        <v>205.60188565079025</v>
       </c>
       <c r="H61" s="120"/>
     </row>
@@ -18277,23 +18277,23 @@
       </c>
       <c r="B62" s="124">
         <f t="shared" si="4"/>
-        <v>181.17785614317998</v>
+        <v>181.53915327569922</v>
       </c>
       <c r="C62" s="124">
         <f t="shared" si="4"/>
-        <v>186.76459605192446</v>
+        <v>187.13703402224874</v>
       </c>
       <c r="D62" s="124">
         <f t="shared" si="4"/>
-        <v>198.76055659269269</v>
+        <v>199.15691639451151</v>
       </c>
       <c r="E62" s="124">
         <f t="shared" si="4"/>
-        <v>211.96265697154678</v>
+        <v>212.38534383734381</v>
       </c>
       <c r="F62" s="124">
         <f t="shared" si="4"/>
-        <v>234.34734396884957</v>
+        <v>234.81466942015933</v>
       </c>
       <c r="H62" s="120"/>
     </row>
@@ -18304,23 +18304,23 @@
       </c>
       <c r="B63" s="124">
         <f t="shared" si="4"/>
-        <v>181.17785614317998</v>
+        <v>181.53915327569922</v>
       </c>
       <c r="C63" s="124">
         <f t="shared" si="4"/>
-        <v>190.14083311575709</v>
+        <v>190.52000383364688</v>
       </c>
       <c r="D63" s="124">
         <f t="shared" si="4"/>
-        <v>210.32537301164592</v>
+        <v>210.74479487578969</v>
       </c>
       <c r="E63" s="124">
         <f t="shared" si="4"/>
-        <v>234.01874304092303</v>
+        <v>234.48541321031522</v>
       </c>
       <c r="F63" s="124">
         <f t="shared" si="4"/>
-        <v>277.70692747688361</v>
+        <v>278.26071875532131</v>
       </c>
       <c r="H63" s="120"/>
     </row>
@@ -18331,23 +18331,23 @@
       </c>
       <c r="B64" s="124">
         <f t="shared" si="4"/>
-        <v>181.17785614317998</v>
+        <v>181.53915327569922</v>
       </c>
       <c r="C64" s="124">
         <f t="shared" si="4"/>
-        <v>193.56980325777255</v>
+        <v>193.95581188127716</v>
       </c>
       <c r="D64" s="124">
         <f t="shared" si="4"/>
-        <v>222.71213202007223</v>
+        <v>223.15625502930192</v>
       </c>
       <c r="E64" s="124">
         <f t="shared" si="4"/>
-        <v>259.01677924163204</v>
+        <v>259.53329942575664</v>
       </c>
       <c r="F64" s="124">
         <f t="shared" si="4"/>
-        <v>331.5021789443017</v>
+        <v>332.16324641262287</v>
       </c>
       <c r="H64" s="120"/>
     </row>
@@ -18358,23 +18358,23 @@
       </c>
       <c r="B65" s="124">
         <f t="shared" si="4"/>
-        <v>181.17785614318001</v>
+        <v>181.53915327569922</v>
       </c>
       <c r="C65" s="124">
         <f t="shared" si="4"/>
-        <v>196.74690638041992</v>
+        <v>197.13925064710057</v>
       </c>
       <c r="D65" s="124">
         <f t="shared" si="4"/>
-        <v>234.83767910937496</v>
+        <v>235.30598236605238</v>
       </c>
       <c r="E65" s="124">
         <f t="shared" si="4"/>
-        <v>284.99465441947842</v>
+        <v>285.56297857132012</v>
       </c>
       <c r="F65" s="124">
         <f t="shared" si="4"/>
-        <v>393.12028152394214</v>
+        <v>393.90422517728507</v>
       </c>
     </row>
     <row r="66" spans="1:8" ht="13.15">
@@ -18384,23 +18384,23 @@
       </c>
       <c r="B66" s="124">
         <f t="shared" si="4"/>
-        <v>181.17785614317998</v>
+        <v>181.53915327569916</v>
       </c>
       <c r="C66" s="124">
         <f t="shared" si="4"/>
-        <v>199.53728909858074</v>
+        <v>199.93519782714523</v>
       </c>
       <c r="D66" s="124">
         <f t="shared" si="4"/>
-        <v>246.10802723727764</v>
+        <v>246.59880534020709</v>
       </c>
       <c r="E66" s="124">
         <f t="shared" si="4"/>
-        <v>310.7043414277756</v>
+        <v>311.32393473795605</v>
       </c>
       <c r="F66" s="124">
         <f t="shared" si="4"/>
-        <v>460.7542544378606</v>
+        <v>461.67307086757296</v>
       </c>
     </row>
     <row r="68" spans="1:8" ht="13.15">
@@ -18435,7 +18435,7 @@
       </c>
       <c r="E69" s="135">
         <f>INDEX(B$60:F$66, MATCH(D69, A$60:A$66, 0), MATCH(C69, B$59:F$59, 0))</f>
-        <v>234.34734396884957</v>
+        <v>234.81466942015933</v>
       </c>
       <c r="F69" s="142">
         <f>Scenarios!C58</f>
@@ -18457,7 +18457,7 @@
       </c>
       <c r="E70" s="135">
         <f>INDEX(B$60:F$66, MATCH(D70, A$60:A$66, 0), MATCH(C70, B$59:F$59, 0))</f>
-        <v>195.85706795251775</v>
+        <v>196.24763774146018</v>
       </c>
       <c r="F70" s="142">
         <f>Scenarios!C40*(1-F$69-F$73)</f>
@@ -18480,7 +18480,7 @@
       </c>
       <c r="E71" s="135">
         <f>INDEX(B$60:F$66, MATCH(D71, A$60:A$66, 0), MATCH(C71, B$59:F$59, 0))</f>
-        <v>189.85802688899489</v>
+        <v>190.23663364680169</v>
       </c>
       <c r="F71" s="142">
         <f>Scenarios!C28*(1-F$69-F$73)</f>
@@ -18503,7 +18503,7 @@
       </c>
       <c r="E72" s="135">
         <f>INDEX(B$60:F$66, MATCH(D72, A$60:A$66, 0), MATCH(C72, B$59:F$59, 0))</f>
-        <v>184.03000642713525</v>
+        <v>184.39699119577648</v>
       </c>
       <c r="F72" s="142">
         <f>Scenarios!C34*(1-F$69-F$73)</f>
@@ -18526,7 +18526,7 @@
       </c>
       <c r="E73" s="135">
         <f>INDEX(B$60:F$66, MATCH(D73, A$60:A$66, 0), MATCH(C73, B$59:F$59, 0))</f>
-        <v>181.17785614317998</v>
+        <v>181.53915327569922</v>
       </c>
       <c r="F73" s="142">
         <f>Scenarios!C52</f>
@@ -18626,7 +18626,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-48.55</v>
+        <v>-48.9</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18646,7 +18646,7 @@
       </c>
       <c r="I4" s="124">
         <f t="shared" ref="I4:I13" si="0">IF(ROW()-3 &lt; $C$76, $C$77, IF(ROW()-3 = $C$76, $C$77 + $C$60, ""))</f>
-        <v>1.4928119876800001</v>
+        <v>1.49429969728</v>
       </c>
     </row>
     <row r="5" spans="2:9">
@@ -18655,7 +18655,7 @@
       </c>
       <c r="I5" s="124">
         <f t="shared" si="0"/>
-        <v>1.4928119876800001</v>
+        <v>1.49429969728</v>
       </c>
     </row>
     <row r="6" spans="2:9" ht="13.15">
@@ -18675,7 +18675,7 @@
       </c>
       <c r="I6" s="124">
         <f t="shared" si="0"/>
-        <v>34.667870619370291</v>
+        <v>34.701290380366437</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1">
@@ -18866,7 +18866,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>48.55</v>
+        <v>48.9</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -18881,7 +18881,7 @@
       </c>
       <c r="C22" s="160">
         <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
-        <v>31.269296924731126</v>
+        <v>31.299329728258044</v>
       </c>
       <c r="D22" t="str">
         <f>Market_currency</f>
@@ -18928,7 +18928,7 @@
       </c>
       <c r="C27" s="160">
         <f>IF(valuation_method="DCF",DCF!E76,DDM!E71)</f>
-        <v>32.844545793955824</v>
+        <v>32.876148462197442</v>
       </c>
       <c r="D27" s="160" t="str">
         <f>Market_currency</f>
@@ -18986,7 +18986,7 @@
       </c>
       <c r="C33" s="160">
         <f>IF(valuation_method="DCF",DCF!E77,DDM!E72)</f>
-        <v>31.78689578784401</v>
+        <v>31.817444421096273</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
@@ -19044,7 +19044,7 @@
       </c>
       <c r="C39" s="160">
         <f>IF(valuation_method="DCF",DCF!E75,DDM!E70)</f>
-        <v>33.933232056988523</v>
+        <v>33.965919690395395</v>
       </c>
       <c r="D39" t="str">
         <f>Market_currency</f>
@@ -19071,7 +19071,7 @@
       </c>
       <c r="C42" s="154">
         <f>C27*C28+C33*C34+C39*C40</f>
-        <v>32.850753045339999</v>
+        <v>32.882361899616797</v>
       </c>
       <c r="D42" t="str">
         <f>Market_currency</f>
@@ -19145,7 +19145,7 @@
       </c>
       <c r="C51" s="160">
         <f>IF(valuation_method="DCF",DCF!E78,DDM!E73)</f>
-        <v>31.26929692473113</v>
+        <v>31.299329728258055</v>
       </c>
       <c r="D51" t="str">
         <f>Market_currency</f>
@@ -19203,7 +19203,7 @@
       </c>
       <c r="C57" s="160">
         <f>IF(valuation_method="DCF",DCF!E74,DDM!E69)</f>
-        <v>40.918320892954817</v>
+        <v>40.957969740368455</v>
       </c>
       <c r="D57" t="str">
         <f>Market_currency</f>
@@ -19229,7 +19229,7 @@
       </c>
       <c r="C60" s="154">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
-        <v>33.175058631690291</v>
+        <v>33.206990683086438</v>
       </c>
       <c r="D60" t="str">
         <f>Market_currency</f>
@@ -19291,7 +19291,7 @@
       </c>
       <c r="C66" s="160">
         <f>IF(valuation_method="DCF",DCF!C18,DDM!C13)</f>
-        <v>32.51089805002848</v>
+        <v>32.542168210924395</v>
       </c>
       <c r="D66" s="160" t="str">
         <f>Market_currency</f>
@@ -19354,7 +19354,7 @@
       </c>
       <c r="F72" s="291">
         <f>BS!D89/C60</f>
-        <v>-4.8538427211801204E-2</v>
+        <v>-4.8574095774619019E-2</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="13.9">
@@ -19387,7 +19387,7 @@
       </c>
       <c r="C77" s="173">
         <f>Normalized_FCF!C90*(1-dividend_tax_rate)</f>
-        <v>1.4928119876800001</v>
+        <v>1.49429969728</v>
       </c>
       <c r="D77" t="str">
         <f>Market_currency</f>
@@ -19414,7 +19414,7 @@
       </c>
       <c r="C81" s="116">
         <f>PV(C80, C76, -C77, 0)</f>
-        <v>2.4739765786422589</v>
+        <v>2.4764420992413672</v>
       </c>
       <c r="D81" s="116"/>
       <c r="E81" s="100"/>
@@ -19426,7 +19426,7 @@
       </c>
       <c r="C82" s="116">
         <f>C60/(1+C80)^C76</f>
-        <v>12.975526004416281</v>
+        <v>12.988015361793611</v>
       </c>
       <c r="D82" s="116"/>
     </row>
@@ -19436,7 +19436,7 @@
       </c>
       <c r="C83" s="111">
         <f>C81+C82</f>
-        <v>15.449502583058539</v>
+        <v>15.464457461034979</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -19447,7 +19447,7 @@
       </c>
       <c r="F83" s="291">
         <f>(1-C83/C60)</f>
-        <v>0.53430368414479645</v>
+        <v>0.53430114735113277</v>
       </c>
     </row>
     <row r="84" spans="2:8">
@@ -19464,7 +19464,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>48.55</v>
+        <v>48.9</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19477,7 +19477,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>-8.4224595913299005E-2</v>
+        <v>-8.6188313093982005E-2</v>
       </c>
     </row>
     <row r="88" spans="2:8">
@@ -19503,7 +19503,7 @@
       </c>
       <c r="C91" s="116">
         <f>PV(C90, C76, -C77, 0)</f>
-        <v>3.060862929414526</v>
+        <v>3.0639133304040378</v>
       </c>
       <c r="D91" s="116"/>
       <c r="E91" s="100"/>
@@ -19515,7 +19515,7 @@
       </c>
       <c r="C92" s="116">
         <f>C60/(1+C90)^C76</f>
-        <v>18.387039406279996</v>
+        <v>18.404737517799937</v>
       </c>
       <c r="D92" s="116"/>
     </row>
@@ -19525,7 +19525,7 @@
       </c>
       <c r="C93" s="111">
         <f>C91+C92</f>
-        <v>21.447902335694522</v>
+        <v>21.468650848203975</v>
       </c>
       <c r="D93" t="str">
         <f>Market_currency</f>
@@ -19536,7 +19536,7 @@
       </c>
       <c r="F93" s="291">
         <f>(1-C93/C60)</f>
-        <v>0.3534931596109816</v>
+        <v>0.35349002102925386</v>
       </c>
     </row>
     <row r="95" spans="2:8" ht="13.15">
@@ -19563,7 +19563,7 @@
       </c>
       <c r="C97" s="116">
         <f>PV(C96, C76, -C77, 0)</f>
-        <v>3.8820959987512631</v>
+        <v>3.8859648258595172</v>
       </c>
       <c r="D97" s="116"/>
       <c r="G97" s="2"/>
@@ -19575,7 +19575,7 @@
       </c>
       <c r="C98" s="116">
         <f>C60/(1+C96)^C76</f>
-        <v>26.70461408967989</v>
+        <v>26.73031813195734</v>
       </c>
       <c r="D98" s="116"/>
       <c r="G98" s="2"/>
@@ -19587,7 +19587,7 @@
       </c>
       <c r="C99" s="111">
         <f>C97+C98</f>
-        <v>30.586710088431154</v>
+        <v>30.616282957816857</v>
       </c>
       <c r="D99" t="s">
         <v>393</v>
@@ -19597,7 +19597,7 @@
       </c>
       <c r="F99" s="291">
         <f>(1-C99/C60)</f>
-        <v>7.8020918425344754E-2</v>
+        <v>7.8016937758504157E-2</v>
       </c>
     </row>
     <row r="100" spans="2:8">
@@ -19623,7 +19623,7 @@
       </c>
       <c r="C103" s="116">
         <f>PV(C102, C76, -C77, 0)</f>
-        <v>3.6015628679154563</v>
+        <v>3.6051521207469053</v>
       </c>
       <c r="D103" s="116"/>
     </row>
@@ -19633,7 +19633,7 @@
       </c>
       <c r="C104" s="116">
         <f>C60/(1+C102)^C76</f>
-        <v>23.778568063139453</v>
+        <v>23.801455692847924</v>
       </c>
       <c r="D104" s="116"/>
     </row>
@@ -19643,7 +19643,7 @@
       </c>
       <c r="C105" s="111">
         <f>C103+C104</f>
-        <v>27.380130931054907</v>
+        <v>27.406607813594828</v>
       </c>
       <c r="D105" t="s">
         <v>393</v>
@@ -19653,7 +19653,7 @@
       </c>
       <c r="F105" s="291">
         <f>(1-C105/C66)</f>
-        <v>0.15781683763635923</v>
+        <v>0.15781248391450331</v>
       </c>
     </row>
     <row r="106" spans="2:8">

--- a/financial_models/opportunities/1913.HK_Valuation.xlsx
+++ b/financial_models/opportunities/1913.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{427AF2C6-DDDF-424A-9CFB-80DF3B91F653}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E6E4CFA-D4D7-4C94-9AEE-CDBB73443B2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3896,29 +3896,29 @@
     <xf numFmtId="10" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4336,7 +4336,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>48.9</v>
+        <v>50</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4357,7 +4357,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>125126.4936</v>
+        <v>127941.2</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4384,7 +4384,7 @@
         <v>1</v>
       </c>
       <c r="C16" s="50">
-        <v>9.1115835199999999</v>
+        <v>9.2629589299999999</v>
       </c>
       <c r="D16" s="50"/>
       <c r="E16" s="5"/>
@@ -4394,13 +4394,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="358" t="s">
+      <c r="B18" s="360" t="s">
         <v>356</v>
       </c>
-      <c r="C18" s="358"/>
-      <c r="D18" s="358"/>
-      <c r="E18" s="358"/>
-      <c r="F18" s="358"/>
+      <c r="C18" s="360"/>
+      <c r="D18" s="360"/>
+      <c r="E18" s="360"/>
+      <c r="F18" s="360"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4476,14 +4476,14 @@
       </c>
       <c r="C26" s="304">
         <f>C132</f>
-        <v>33.206990683086438</v>
+        <v>33.739512265751841</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>396</v>
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>-8.6188313093982005E-2</v>
+        <v>-8.8165408338003126E-2</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4515,7 +4515,7 @@
       </c>
       <c r="C29" s="310">
         <f>C149</f>
-        <v>15.464457461034979</v>
+        <v>15.713881263307032</v>
       </c>
       <c r="D29" s="310" t="str">
         <f>D149</f>
@@ -4534,7 +4534,7 @@
       </c>
       <c r="C30" s="311">
         <f>C157</f>
-        <v>21.468650848203975</v>
+        <v>21.814699497188869</v>
       </c>
       <c r="D30" s="311" t="str">
         <f>D157</f>
@@ -4553,7 +4553,7 @@
       </c>
       <c r="C31" s="311">
         <f>C165</f>
-        <v>30.616282957816857</v>
+        <v>31.109501360889897</v>
       </c>
       <c r="D31" s="311" t="str">
         <f>D165</f>
@@ -4572,7 +4572,7 @@
       </c>
       <c r="C32" s="311">
         <f>C173</f>
-        <v>27.406607813594828</v>
+        <v>27.848192433601373</v>
       </c>
       <c r="D32" s="311" t="str">
         <f>D173</f>
@@ -4600,22 +4600,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="358" t="s">
+      <c r="B36" s="360" t="s">
         <v>357</v>
       </c>
-      <c r="C36" s="358"/>
-      <c r="D36" s="358"/>
-      <c r="E36" s="358"/>
-      <c r="F36" s="358"/>
+      <c r="C36" s="360"/>
+      <c r="D36" s="360"/>
+      <c r="E36" s="360"/>
+      <c r="F36" s="360"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="360" t="s">
+      <c r="B37" s="363" t="s">
         <v>336</v>
       </c>
-      <c r="C37" s="360"/>
-      <c r="D37" s="360"/>
-      <c r="E37" s="360"/>
-      <c r="F37" s="360"/>
+      <c r="C37" s="363"/>
+      <c r="D37" s="363"/>
+      <c r="E37" s="363"/>
+      <c r="F37" s="363"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4627,13 +4627,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="359" t="s">
+      <c r="B40" s="361" t="s">
         <v>230</v>
       </c>
-      <c r="C40" s="359"/>
-      <c r="D40" s="359"/>
-      <c r="E40" s="359"/>
-      <c r="F40" s="359"/>
+      <c r="C40" s="361"/>
+      <c r="D40" s="361"/>
+      <c r="E40" s="361"/>
+      <c r="F40" s="361"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4653,13 +4653,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="359" t="s">
+      <c r="B43" s="361" t="s">
         <v>232</v>
       </c>
-      <c r="C43" s="359"/>
-      <c r="D43" s="359"/>
-      <c r="E43" s="359"/>
-      <c r="F43" s="359"/>
+      <c r="C43" s="361"/>
+      <c r="D43" s="361"/>
+      <c r="E43" s="361"/>
+      <c r="F43" s="361"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4688,13 +4688,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="359" t="s">
+      <c r="B47" s="361" t="s">
         <v>235</v>
       </c>
-      <c r="C47" s="359"/>
-      <c r="D47" s="359"/>
-      <c r="E47" s="359"/>
-      <c r="F47" s="359"/>
+      <c r="C47" s="361"/>
+      <c r="D47" s="361"/>
+      <c r="E47" s="361"/>
+      <c r="F47" s="361"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4710,13 +4710,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="359" t="s">
+      <c r="B50" s="361" t="s">
         <v>239</v>
       </c>
-      <c r="C50" s="359"/>
-      <c r="D50" s="359"/>
-      <c r="E50" s="359"/>
-      <c r="F50" s="359"/>
+      <c r="C50" s="361"/>
+      <c r="D50" s="361"/>
+      <c r="E50" s="361"/>
+      <c r="F50" s="361"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4780,13 +4780,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="359" t="s">
+      <c r="B58" s="361" t="s">
         <v>240</v>
       </c>
-      <c r="C58" s="359"/>
-      <c r="D58" s="359"/>
-      <c r="E58" s="359"/>
-      <c r="F58" s="359"/>
+      <c r="C58" s="361"/>
+      <c r="D58" s="361"/>
+      <c r="E58" s="361"/>
+      <c r="F58" s="361"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4802,7 +4802,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="359" t="s">
+      <c r="B61" s="361" t="s">
         <v>335</v>
       </c>
       <c r="C61" s="362"/>
@@ -4824,22 +4824,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="358" t="s">
+      <c r="B64" s="360" t="s">
         <v>340</v>
       </c>
-      <c r="C64" s="358"/>
-      <c r="D64" s="358"/>
-      <c r="E64" s="358"/>
-      <c r="F64" s="358"/>
+      <c r="C64" s="360"/>
+      <c r="D64" s="360"/>
+      <c r="E64" s="360"/>
+      <c r="F64" s="360"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="358" t="s">
+      <c r="B65" s="360" t="s">
         <v>358</v>
       </c>
-      <c r="C65" s="358"/>
-      <c r="D65" s="358"/>
-      <c r="E65" s="358"/>
-      <c r="F65" s="358"/>
+      <c r="C65" s="360"/>
+      <c r="D65" s="360"/>
+      <c r="E65" s="360"/>
+      <c r="F65" s="360"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4873,7 +4873,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>5.0479032628964977E-2</v>
+        <v>5.0188678019683179E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4883,14 +4883,14 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>3.0558276017995913E-2</v>
+        <v>3.03825052904E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>444</v>
       </c>
       <c r="F70" s="315">
         <f>Normalized_FCF!C92</f>
-        <v>5.5158403333865902</v>
+        <v>5.6074778177084079</v>
       </c>
     </row>
     <row r="72" spans="1:6">
@@ -4974,22 +4974,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.6" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="358" t="s">
+      <c r="B80" s="360" t="s">
         <v>359</v>
       </c>
-      <c r="C80" s="358"/>
-      <c r="D80" s="358"/>
-      <c r="E80" s="358"/>
-      <c r="F80" s="358"/>
+      <c r="C80" s="360"/>
+      <c r="D80" s="360"/>
+      <c r="E80" s="360"/>
+      <c r="F80" s="360"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="360" t="s">
+      <c r="B81" s="363" t="s">
         <v>251</v>
       </c>
-      <c r="C81" s="360"/>
-      <c r="D81" s="360"/>
-      <c r="E81" s="360"/>
-      <c r="F81" s="360"/>
+      <c r="C81" s="363"/>
+      <c r="D81" s="363"/>
+      <c r="E81" s="363"/>
+      <c r="F81" s="363"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5033,22 +5033,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="358" t="s">
+      <c r="B89" s="360" t="s">
         <v>360</v>
       </c>
-      <c r="C89" s="358"/>
-      <c r="D89" s="358"/>
-      <c r="E89" s="358"/>
-      <c r="F89" s="358"/>
+      <c r="C89" s="360"/>
+      <c r="D89" s="360"/>
+      <c r="E89" s="360"/>
+      <c r="F89" s="360"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="358" t="s">
+      <c r="B90" s="360" t="s">
         <v>361</v>
       </c>
-      <c r="C90" s="358"/>
-      <c r="D90" s="358"/>
-      <c r="E90" s="358"/>
-      <c r="F90" s="358"/>
+      <c r="C90" s="360"/>
+      <c r="D90" s="360"/>
+      <c r="E90" s="360"/>
+      <c r="F90" s="360"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5064,7 +5064,7 @@
       </c>
       <c r="C93" s="223">
         <f>DCF!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>32.912329274085167</v>
+        <v>33.45911867978878</v>
       </c>
       <c r="D93" s="1" t="str">
         <f>Market_currency</f>
@@ -5085,13 +5085,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="358" t="s">
+      <c r="B97" s="360" t="s">
         <v>362</v>
       </c>
-      <c r="C97" s="358"/>
-      <c r="D97" s="358"/>
-      <c r="E97" s="358"/>
-      <c r="F97" s="358"/>
+      <c r="C97" s="360"/>
+      <c r="D97" s="360"/>
+      <c r="E97" s="360"/>
+      <c r="F97" s="360"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5104,13 +5104,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="358" t="s">
+      <c r="B101" s="360" t="s">
         <v>341</v>
       </c>
-      <c r="C101" s="358"/>
-      <c r="D101" s="358"/>
-      <c r="E101" s="358"/>
-      <c r="F101" s="358"/>
+      <c r="C101" s="360"/>
+      <c r="D101" s="360"/>
+      <c r="E101" s="360"/>
+      <c r="F101" s="360"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="C103" s="223">
         <f>C102*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>3.0854748587945089</v>
+        <v>3.1367354350455523</v>
       </c>
       <c r="D103" s="1" t="str">
         <f>Market_currency</f>
@@ -5180,7 +5180,7 @@
       </c>
       <c r="C109" s="349">
         <f>DCF!C8</f>
-        <v>409755.75103906996</v>
+        <v>404462.06293345941</v>
       </c>
       <c r="D109" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5193,7 +5193,7 @@
       </c>
       <c r="C110" s="223">
         <f>C109*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>1.4590779781621608</v>
+        <v>1.4641552047720787</v>
       </c>
       <c r="D110" s="1" t="str">
         <f>Market_currency</f>
@@ -5224,7 +5224,7 @@
       </c>
       <c r="C114" s="223">
         <f>C113*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>1.3397334805226152E-2</v>
+        <v>1.3619911599325315E-2</v>
       </c>
       <c r="D114" s="1" t="str">
         <f>Market_currency</f>
@@ -5232,13 +5232,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="358" t="s">
+      <c r="B116" s="360" t="s">
         <v>363</v>
       </c>
-      <c r="C116" s="358"/>
-      <c r="D116" s="358"/>
-      <c r="E116" s="358"/>
-      <c r="F116" s="358"/>
+      <c r="C116" s="360"/>
+      <c r="D116" s="360"/>
+      <c r="E116" s="360"/>
+      <c r="F116" s="360"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="C118" s="223">
         <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
-        <v>31.299329728258044</v>
+        <v>31.800158361114637</v>
       </c>
       <c r="D118" s="1" t="str">
         <f>Market_currency</f>
@@ -5259,7 +5259,7 @@
       </c>
       <c r="C119" s="223">
         <f>BS!D47</f>
-        <v>-5.9215411526586088</v>
+        <v>-6.0199187527594056</v>
       </c>
       <c r="D119" s="1" t="str">
         <f>Market_currency</f>
@@ -5277,13 +5277,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B123" s="359" t="s">
+      <c r="B123" s="361" t="s">
         <v>364</v>
       </c>
-      <c r="C123" s="359"/>
-      <c r="D123" s="359"/>
-      <c r="E123" s="359"/>
-      <c r="F123" s="359"/>
+      <c r="C123" s="361"/>
+      <c r="D123" s="361"/>
+      <c r="E123" s="361"/>
+      <c r="F123" s="361"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5317,7 +5317,7 @@
       </c>
       <c r="E126" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E74,DDM!E69),2)&amp;" "&amp;Market_currency</f>
-        <v>40.96 HKD</v>
+        <v>41.62 HKD</v>
       </c>
       <c r="F126" s="232">
         <f>DCF!F74</f>
@@ -5339,7 +5339,7 @@
       </c>
       <c r="E127" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E75,DDM!E70),2)&amp;" "&amp;Market_currency</f>
-        <v>33.97 HKD</v>
+        <v>34.51 HKD</v>
       </c>
       <c r="F127" s="221">
         <f>DCF!F75</f>
@@ -5361,7 +5361,7 @@
       </c>
       <c r="E128" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E76,DDM!E71),2)&amp;" "&amp;Market_currency</f>
-        <v>32.88 HKD</v>
+        <v>33.4 HKD</v>
       </c>
       <c r="F128" s="221">
         <f>DCF!F76</f>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="E129" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E77,DDM!E72),2)&amp;" "&amp;Market_currency</f>
-        <v>31.82 HKD</v>
+        <v>32.33 HKD</v>
       </c>
       <c r="F129" s="221">
         <f>DCF!F77</f>
@@ -5405,7 +5405,7 @@
       </c>
       <c r="E130" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E78,DDM!E73),2)&amp;" "&amp;Market_currency</f>
-        <v>31.3 HKD</v>
+        <v>31.8 HKD</v>
       </c>
       <c r="F130" s="221">
         <f>DCF!F78</f>
@@ -5418,7 +5418,7 @@
       </c>
       <c r="C132" s="217">
         <f>Scenarios!C60</f>
-        <v>33.206990683086438</v>
+        <v>33.739512265751841</v>
       </c>
       <c r="D132" s="212" t="str">
         <f>Market_currency</f>
@@ -5426,13 +5426,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="363" t="s">
+      <c r="B134" s="364" t="s">
         <v>367</v>
       </c>
-      <c r="C134" s="363"/>
-      <c r="D134" s="363"/>
-      <c r="E134" s="363"/>
-      <c r="F134" s="363"/>
+      <c r="C134" s="364"/>
+      <c r="D134" s="364"/>
+      <c r="E134" s="364"/>
+      <c r="F134" s="364"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5445,22 +5445,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="361" t="s">
+      <c r="B138" s="365" t="s">
         <v>365</v>
       </c>
-      <c r="C138" s="361"/>
-      <c r="D138" s="361"/>
-      <c r="E138" s="361"/>
-      <c r="F138" s="361"/>
+      <c r="C138" s="365"/>
+      <c r="D138" s="365"/>
+      <c r="E138" s="365"/>
+      <c r="F138" s="365"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="358" t="s">
+      <c r="B139" s="360" t="s">
         <v>366</v>
       </c>
-      <c r="C139" s="358"/>
-      <c r="D139" s="358"/>
-      <c r="E139" s="358"/>
-      <c r="F139" s="358"/>
+      <c r="C139" s="360"/>
+      <c r="D139" s="360"/>
+      <c r="E139" s="360"/>
+      <c r="F139" s="360"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5491,7 +5491,7 @@
       </c>
       <c r="C143" s="213">
         <f>Scenarios!C77</f>
-        <v>1.49429969728</v>
+        <v>1.51912526452</v>
       </c>
       <c r="D143" s="212" t="str">
         <f>Market_currency</f>
@@ -5527,7 +5527,7 @@
       </c>
       <c r="C147" s="216">
         <f>Scenarios!C81</f>
-        <v>2.4764420992413672</v>
+        <v>2.517584501908376</v>
       </c>
     </row>
     <row r="148" spans="2:4">
@@ -5537,7 +5537,7 @@
       </c>
       <c r="C148" s="216">
         <f>Scenarios!C82</f>
-        <v>12.988015361793611</v>
+        <v>13.196296761398656</v>
       </c>
     </row>
     <row r="149" spans="2:4">
@@ -5546,7 +5546,7 @@
       </c>
       <c r="C149" s="215">
         <f>Scenarios!C83</f>
-        <v>15.464457461034979</v>
+        <v>15.713881263307032</v>
       </c>
       <c r="D149" s="300" t="str">
         <f>IF($D$11="","",C149*$E$25)</f>
@@ -5572,7 +5572,7 @@
       </c>
       <c r="C151" s="92">
         <f>Scenarios!F83</f>
-        <v>0.53430114735113277</v>
+        <v>0.53425879012312194</v>
       </c>
     </row>
     <row r="153" spans="2:4">
@@ -5596,7 +5596,7 @@
       </c>
       <c r="C155" s="216">
         <f>Scenarios!C91</f>
-        <v>3.0639133304040378</v>
+        <v>3.114815693925848</v>
       </c>
     </row>
     <row r="156" spans="2:4">
@@ -5606,7 +5606,7 @@
       </c>
       <c r="C156" s="216">
         <f>Scenarios!C92</f>
-        <v>18.404737517799937</v>
+        <v>18.69988380326302</v>
       </c>
     </row>
     <row r="157" spans="2:4">
@@ -5615,7 +5615,7 @@
       </c>
       <c r="C157" s="215">
         <f>Scenarios!C93</f>
-        <v>21.468650848203975</v>
+        <v>21.814699497188869</v>
       </c>
       <c r="D157" s="300" t="str">
         <f>IF($D$11="","",C157*$E$25)</f>
@@ -5641,7 +5641,7 @@
       </c>
       <c r="C159" s="92">
         <f>Scenarios!F93</f>
-        <v>0.35349002102925386</v>
+        <v>0.35343761565479292</v>
       </c>
     </row>
     <row r="161" spans="2:4">
@@ -5665,7 +5665,7 @@
       </c>
       <c r="C163" s="216">
         <f>Scenarios!C97</f>
-        <v>3.8859648258595172</v>
+        <v>3.9505243524740594</v>
       </c>
     </row>
     <row r="164" spans="2:4">
@@ -5675,7 +5675,7 @@
       </c>
       <c r="C164" s="216">
         <f>Scenarios!C98</f>
-        <v>26.73031813195734</v>
+        <v>27.158977008415839</v>
       </c>
     </row>
     <row r="165" spans="2:4">
@@ -5684,7 +5684,7 @@
       </c>
       <c r="C165" s="215">
         <f>Scenarios!C99</f>
-        <v>30.616282957816857</v>
+        <v>31.109501360889897</v>
       </c>
       <c r="D165" s="300" t="str">
         <f>IF($D$11="","",C165*$E$25)</f>
@@ -5710,7 +5710,7 @@
       </c>
       <c r="C167" s="92">
         <f>Scenarios!F99</f>
-        <v>7.8016937758504157E-2</v>
+        <v>7.7950471961374612E-2</v>
       </c>
     </row>
     <row r="169" spans="2:4">
@@ -5734,7 +5734,7 @@
       </c>
       <c r="C171" s="216">
         <f>Scenarios!C103</f>
-        <v>3.6051521207469053</v>
+        <v>3.6650463618733289</v>
       </c>
     </row>
     <row r="172" spans="2:4">
@@ -5744,7 +5744,7 @@
       </c>
       <c r="C172" s="216">
         <f>Scenarios!C104</f>
-        <v>23.801455692847924</v>
+        <v>24.183146071728043</v>
       </c>
     </row>
     <row r="173" spans="2:4">
@@ -5753,7 +5753,7 @@
       </c>
       <c r="C173" s="215">
         <f>Scenarios!C105</f>
-        <v>27.406607813594828</v>
+        <v>27.848192433601373</v>
       </c>
       <c r="D173" s="300" t="str">
         <f>IF($D$11="","",C173*$E$25)</f>
@@ -5779,7 +5779,7 @@
       </c>
       <c r="C175" s="92">
         <f>Scenarios!F105</f>
-        <v>0.15781248391450331</v>
+        <v>0.15773978826724333</v>
       </c>
     </row>
     <row r="177" spans="1:6" ht="13.9">
@@ -5793,13 +5793,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="365" t="s">
+      <c r="B179" s="359" t="s">
         <v>373</v>
       </c>
-      <c r="C179" s="358"/>
-      <c r="D179" s="358"/>
-      <c r="E179" s="358"/>
-      <c r="F179" s="358"/>
+      <c r="C179" s="360"/>
+      <c r="D179" s="360"/>
+      <c r="E179" s="360"/>
+      <c r="F179" s="360"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5836,13 +5836,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="359" t="s">
+      <c r="B188" s="361" t="s">
         <v>378</v>
       </c>
-      <c r="C188" s="359"/>
-      <c r="D188" s="359"/>
-      <c r="E188" s="359"/>
-      <c r="F188" s="359"/>
+      <c r="C188" s="361"/>
+      <c r="D188" s="361"/>
+      <c r="E188" s="361"/>
+      <c r="F188" s="361"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5850,22 +5850,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="364" t="s">
+      <c r="B191" s="358" t="s">
         <v>379</v>
       </c>
-      <c r="C191" s="364"/>
-      <c r="D191" s="364"/>
-      <c r="E191" s="364"/>
-      <c r="F191" s="364"/>
+      <c r="C191" s="358"/>
+      <c r="D191" s="358"/>
+      <c r="E191" s="358"/>
+      <c r="F191" s="358"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="364" t="s">
+      <c r="B192" s="358" t="s">
         <v>380</v>
       </c>
-      <c r="C192" s="364"/>
-      <c r="D192" s="364"/>
-      <c r="E192" s="364"/>
-      <c r="F192" s="364"/>
+      <c r="C192" s="358"/>
+      <c r="D192" s="358"/>
+      <c r="E192" s="358"/>
+      <c r="F192" s="358"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5889,17 +5889,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5916,6 +5905,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -6488,15 +6488,15 @@
       </c>
       <c r="C25" s="39">
         <f>0.164*Exchange_Rate</f>
-        <v>1.49429969728</v>
+        <v>1.51912526452</v>
       </c>
       <c r="D25" s="39">
         <f>0.137*Exchange_Rate</f>
-        <v>1.24828694224</v>
+        <v>1.2690253734100001</v>
       </c>
       <c r="E25" s="39">
         <f>0.11*Exchange_Rate</f>
-        <v>1.0022741872000001</v>
+        <v>1.0189254823</v>
       </c>
       <c r="F25" s="39"/>
       <c r="G25" s="39"/>
@@ -7870,15 +7870,15 @@
       </c>
       <c r="C65" s="73">
         <f>IF(C$4="","",C25)</f>
-        <v>1.49429969728</v>
+        <v>1.51912526452</v>
       </c>
       <c r="D65" s="73">
         <f t="shared" ref="D65:M65" si="33">IF(D$4="","",D25)</f>
-        <v>1.24828694224</v>
+        <v>1.2690253734100001</v>
       </c>
       <c r="E65" s="73">
         <f t="shared" si="33"/>
-        <v>1.0022741872000001</v>
+        <v>1.0189254823</v>
       </c>
       <c r="F65" s="73">
         <f t="shared" si="33"/>
@@ -9220,11 +9220,11 @@
       </c>
       <c r="C47" s="147">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>15.665470400646859</v>
+        <v>15.925728894632631</v>
       </c>
       <c r="D47" s="147">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>-5.9215411526586088</v>
+        <v>-6.0199187527594056</v>
       </c>
       <c r="F47" s="253"/>
     </row>
@@ -9415,7 +9415,7 @@
       </c>
       <c r="D66" s="76">
         <f>C66-D75</f>
-        <v>409755.75103906996</v>
+        <v>404462.06293345941</v>
       </c>
       <c r="F66" s="5" t="s">
         <v>225</v>
@@ -9482,11 +9482,11 @@
       </c>
       <c r="C73" s="349">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35-Normalized_FCF!G91)/12</f>
-        <v>-651464.4107160666</v>
+        <v>-656758.09882167703</v>
       </c>
       <c r="D73" s="349">
         <f>(Normalized_FCF!C25+Normalized_FCF!C35-Normalized_FCF!C91)/12</f>
-        <v>-601807.24896093004</v>
+        <v>-607100.93706654059</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>348</v>
@@ -9498,11 +9498,11 @@
       </c>
       <c r="C74" s="258">
         <f>-$C$66/C73</f>
-        <v>1.5527525116654119</v>
+        <v>1.5402368114148823</v>
       </c>
       <c r="D74" s="258">
         <f>-$C$66/D73</f>
-        <v>1.6808753994680974</v>
+        <v>1.6662188085028913</v>
       </c>
       <c r="F74" s="253" t="s">
         <v>316</v>
@@ -9515,7 +9515,7 @@
       <c r="C75" s="320"/>
       <c r="D75" s="321">
         <f>MAX(-D73*D76,G5)</f>
-        <v>601807.24896093004</v>
+        <v>607100.93706654059</v>
       </c>
       <c r="F75" s="253" t="s">
         <v>349</v>
@@ -9630,11 +9630,11 @@
       </c>
       <c r="C86" s="76">
         <f>-DCF!C7*Exchange_Rate</f>
-        <v>-7895187.1200799998</v>
+        <v>-8026353.9128449997</v>
       </c>
       <c r="D86" s="223">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>-3.0854748587945089</v>
+        <v>-3.1367354350455519</v>
       </c>
       <c r="E86" s="240" t="str">
         <f>Market_currency</f>
@@ -9647,11 +9647,11 @@
       </c>
       <c r="C87" s="76">
         <f>DCF!C8*Exchange_Rate</f>
-        <v>3733523.7483928129</v>
+        <v>3746515.47769571</v>
       </c>
       <c r="D87" s="223">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>1.4590779781621608</v>
+        <v>1.4641552047720789</v>
       </c>
       <c r="E87" s="240" t="str">
         <f>Market_currency</f>
@@ -9664,11 +9664,11 @@
       </c>
       <c r="C88" s="76">
         <f>DCF!C9*Exchange_Rate</f>
-        <v>34281.421835647998</v>
+        <v>34850.956678232003</v>
       </c>
       <c r="D88" s="223">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>1.3397334805226152E-2</v>
+        <v>1.3619911599325317E-2</v>
       </c>
       <c r="E88" s="240" t="str">
         <f>Market_currency</f>
@@ -9681,11 +9681,11 @@
       </c>
       <c r="C89" s="180">
         <f>SUM(C86:C88)</f>
-        <v>-4127381.949851539</v>
+        <v>-4244987.4784710575</v>
       </c>
       <c r="D89" s="242">
         <f>SUM(D86:D88)</f>
-        <v>-1.612999545827122</v>
+        <v>-1.6589603186741475</v>
       </c>
       <c r="E89" s="240" t="str">
         <f>Market_currency</f>
@@ -13197,20 +13197,20 @@
       </c>
       <c r="C90" s="113">
         <f>G90</f>
-        <v>1.49429969728</v>
+        <v>1.51912526452</v>
       </c>
       <c r="E90" s="268"/>
       <c r="G90" s="112">
         <f>Data!C65</f>
-        <v>1.49429969728</v>
+        <v>1.51912526452</v>
       </c>
       <c r="H90" s="112">
         <f>Data!D65</f>
-        <v>1.24828694224</v>
+        <v>1.2690253734100001</v>
       </c>
       <c r="I90" s="112">
         <f>Data!E65</f>
-        <v>1.0022741872000001</v>
+        <v>1.0189254823</v>
       </c>
       <c r="J90" s="112">
         <f>Data!F65</f>
@@ -13253,20 +13253,20 @@
       </c>
       <c r="C91" s="74">
         <f>C90*Common_Shares/scaling_factor</f>
-        <v>3823649.9285927988</v>
+        <v>3887174.1858601244</v>
       </c>
       <c r="E91" s="268"/>
       <c r="G91" s="74">
         <f t="shared" ref="G91:Q91" si="37">IF(G$4="","",G90*Common_Shares/scaling_factor)</f>
-        <v>3823649.9285927988</v>
+        <v>3887174.1858601244</v>
       </c>
       <c r="H91" s="74">
         <f t="shared" si="37"/>
-        <v>3194146.5866903258</v>
+        <v>3247212.5820904705</v>
       </c>
       <c r="I91" s="74">
         <f t="shared" si="37"/>
-        <v>2564643.2447878527</v>
+        <v>2607250.9783208151</v>
       </c>
       <c r="J91" s="74">
         <f t="shared" si="37"/>
@@ -13308,20 +13308,20 @@
       </c>
       <c r="C92" s="23">
         <f>C90/(C19*scaling_factor/Common_Shares)</f>
-        <v>5.5158403333865902</v>
+        <v>5.6074778177084079</v>
       </c>
       <c r="E92" s="268"/>
       <c r="G92" s="170">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",G90/(G19*scaling_factor/Common_Shares))</f>
-        <v>3.8356170538006564</v>
+        <v>3.8993401270565404</v>
       </c>
       <c r="H92" s="170">
         <f t="shared" si="38"/>
-        <v>3.8904850540980687</v>
+        <v>3.9551196775825903</v>
       </c>
       <c r="I92" s="170">
         <f t="shared" si="38"/>
-        <v>3.8172968361710575</v>
+        <v>3.8807155462557232</v>
       </c>
       <c r="J92" s="170">
         <f t="shared" si="38"/>
@@ -13384,20 +13384,20 @@
       </c>
       <c r="C94" s="23">
         <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
-        <v>3.0558276017995913E-2</v>
+        <v>3.03825052904E-2</v>
       </c>
       <c r="E94" s="268"/>
       <c r="G94" s="23">
         <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>3.0558276017995913E-2</v>
+        <v>3.03825052904E-2</v>
       </c>
       <c r="H94" s="23">
         <f t="shared" si="39"/>
-        <v>2.5527340332106341E-2</v>
+        <v>2.5380507468200003E-2</v>
       </c>
       <c r="I94" s="23">
         <f t="shared" si="39"/>
-        <v>2.049640464621677E-2</v>
+        <v>2.0378509646E-2</v>
       </c>
       <c r="J94" s="23">
         <f t="shared" si="39"/>
@@ -14526,38 +14526,38 @@
       </c>
       <c r="C125" s="177">
         <f>C16*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>2.4684246955563873</v>
+        <v>2.5094339009841584</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="265"/>
       <c r="F125" s="27"/>
       <c r="G125" s="177">
         <f t="shared" ref="G125:Q125" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>3.549738231084905</v>
+        <v>3.6087118528427125</v>
       </c>
       <c r="H125" s="177">
         <f t="shared" si="49"/>
-        <v>2.9235096840082786</v>
+        <v>2.972079449744863</v>
       </c>
       <c r="I125" s="177">
         <f t="shared" si="49"/>
-        <v>2.3923486588936793</v>
+        <v>2.4320939741078873</v>
       </c>
       <c r="J125" s="177">
         <f t="shared" si="49"/>
-        <v>1.2832085781469611</v>
+        <v>1.3045271803642533</v>
       </c>
       <c r="K125" s="177">
         <f t="shared" si="49"/>
-        <v>6.1988026712479796</v>
+        <v>6.3017865591539159</v>
       </c>
       <c r="L125" s="177">
         <f t="shared" si="49"/>
-        <v>8.3346634431491964</v>
+        <v>8.4731314814599212</v>
       </c>
       <c r="M125" s="177">
         <f t="shared" si="49"/>
-        <v>7.7110129500803808</v>
+        <v>7.8391199629032986</v>
       </c>
       <c r="N125" s="177" t="str">
         <f t="shared" si="49"/>
@@ -14583,38 +14583,38 @@
       </c>
       <c r="C126" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>5.0479032628964977E-2</v>
+        <v>5.0188678019683179E-2</v>
       </c>
       <c r="D126" s="27"/>
       <c r="E126" s="265"/>
       <c r="F126" s="27"/>
       <c r="G126" s="77">
         <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
-        <v>7.2591783866766971E-2</v>
+        <v>7.2174237056854246E-2</v>
       </c>
       <c r="H126" s="77">
         <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
-        <v>5.9785474110598744E-2</v>
+        <v>5.9441588994897258E-2</v>
       </c>
       <c r="I126" s="77">
         <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
-        <v>4.8923285457948454E-2</v>
+        <v>4.8641879482157743E-2</v>
       </c>
       <c r="J126" s="77">
         <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
-        <v>2.6241484215684278E-2</v>
+        <v>2.6090543607285067E-2</v>
       </c>
       <c r="K126" s="77">
         <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
-        <v>0.12676488080261716</v>
+        <v>0.12603573118307831</v>
       </c>
       <c r="L126" s="77">
         <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
-        <v>0.17044301519732508</v>
+        <v>0.16946262962919842</v>
       </c>
       <c r="M126" s="77">
         <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
-        <v>0.15768942638201189</v>
+        <v>0.15678239925806597</v>
       </c>
       <c r="N126" s="77" t="str">
         <f t="shared" ref="N126" si="57">IF(N$4="","",N125/Market_Price)</f>
@@ -14640,31 +14640,31 @@
       <c r="C127" s="169"/>
       <c r="G127" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.740379081476954E-3</v>
+        <v>6.5920907416844613E-3</v>
       </c>
       <c r="H127" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.3816900052572076E-3</v>
+        <v>5.263292825141549E-3</v>
       </c>
       <c r="I127" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.7494457528697185E-3</v>
+        <v>3.6669579463065845E-3</v>
       </c>
       <c r="J127" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.3584373821212874E-3</v>
+        <v>2.3065517597146189E-3</v>
       </c>
       <c r="K127" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-4.345043038910826E-4</v>
+        <v>-4.2494520920547876E-4</v>
       </c>
       <c r="L127" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.0597076812835743E-3</v>
+        <v>2.0143941122953359E-3</v>
       </c>
       <c r="M127" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.663772347569404E-3</v>
+        <v>1.627169355922877E-3</v>
       </c>
       <c r="N127" s="23" t="str">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -15492,7 +15492,7 @@
       </c>
       <c r="C8" s="338">
         <f>BS!D66</f>
-        <v>409755.75103906996</v>
+        <v>404462.06293345941</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
@@ -15524,7 +15524,7 @@
       </c>
       <c r="C10" s="347">
         <f>C6-C7+C8+C9</f>
-        <v>8789852.5999112129</v>
+        <v>8784558.9118056037</v>
       </c>
       <c r="D10" t="str">
         <f>Reporting_currency</f>
@@ -15538,7 +15538,7 @@
       </c>
       <c r="C11" s="208">
         <f>Exchange_Rate</f>
-        <v>9.1115835199999999</v>
+        <v>9.2629589299999999</v>
       </c>
       <c r="D11" t="str">
         <f>Thesis!C15</f>
@@ -15552,7 +15552,7 @@
       </c>
       <c r="C12" s="111">
         <f>(C10*scaling_factor)/Common_Shares*Exchange_Rate</f>
-        <v>31.299329728258044</v>
+        <v>31.800158361114637</v>
       </c>
       <c r="D12" t="str">
         <f>Market_currency</f>
@@ -15605,7 +15605,7 @@
       </c>
       <c r="C18" s="140">
         <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>32.542168210924395</v>
+        <v>33.06364475689778</v>
       </c>
       <c r="D18" t="str">
         <f>Market_currency</f>
@@ -16701,23 +16701,23 @@
       </c>
       <c r="B65" s="124">
         <f>C12</f>
-        <v>31.299329728258044</v>
+        <v>31.800158361114637</v>
       </c>
       <c r="C65" s="124">
         <f>C12</f>
-        <v>31.299329728258044</v>
+        <v>31.800158361114637</v>
       </c>
       <c r="D65" s="124">
         <f>C12</f>
-        <v>31.299329728258044</v>
+        <v>31.800158361114637</v>
       </c>
       <c r="E65" s="141">
         <f>C12</f>
-        <v>31.299329728258044</v>
+        <v>31.800158361114637</v>
       </c>
       <c r="F65" s="124">
         <f>C12</f>
-        <v>31.299329728258044</v>
+        <v>31.800158361114637</v>
       </c>
       <c r="H65" s="120"/>
     </row>
@@ -16728,23 +16728,23 @@
       </c>
       <c r="B66" s="124">
         <f t="shared" ref="B66:F71" si="4">(B56-$C$7+$C$8+$C$9)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>31.299329728258044</v>
+        <v>31.800158361114637</v>
       </c>
       <c r="C66" s="124">
         <f t="shared" si="4"/>
-        <v>31.817444421096273</v>
+        <v>32.326880759066171</v>
       </c>
       <c r="D66" s="124">
         <f t="shared" si="4"/>
-        <v>32.876148462197442</v>
+        <v>33.403173593370909</v>
       </c>
       <c r="E66" s="124">
         <f t="shared" si="4"/>
-        <v>33.965919690395395</v>
+        <v>34.51104974988484</v>
       </c>
       <c r="F66" s="124">
         <f t="shared" si="4"/>
-        <v>35.661807777059202</v>
+        <v>36.235112495088451</v>
       </c>
       <c r="H66" s="120"/>
     </row>
@@ -16755,23 +16755,23 @@
       </c>
       <c r="B67" s="124">
         <f t="shared" si="4"/>
-        <v>31.299329728258055</v>
+        <v>31.800158361114644</v>
       </c>
       <c r="C67" s="124">
         <f t="shared" si="4"/>
-        <v>32.314203330139961</v>
+        <v>32.831892578634424</v>
       </c>
       <c r="D67" s="124">
         <f t="shared" si="4"/>
-        <v>34.493360384325904</v>
+        <v>35.047253086567757</v>
       </c>
       <c r="E67" s="124">
         <f t="shared" si="4"/>
-        <v>36.891621871838986</v>
+        <v>37.48535812214935</v>
       </c>
       <c r="F67" s="124">
         <f t="shared" si="4"/>
-        <v>40.957969740368455</v>
+        <v>41.619262313292801</v>
       </c>
       <c r="H67" s="120"/>
     </row>
@@ -16782,23 +16782,23 @@
       </c>
       <c r="B68" s="124">
         <f t="shared" si="4"/>
-        <v>31.299329728258055</v>
+        <v>31.800158361114644</v>
       </c>
       <c r="C68" s="124">
         <f t="shared" si="4"/>
-        <v>32.927522354427424</v>
+        <v>33.455400986420216</v>
       </c>
       <c r="D68" s="124">
         <f t="shared" si="4"/>
-        <v>36.594196844572664</v>
+        <v>37.182991820367164</v>
       </c>
       <c r="E68" s="124">
         <f t="shared" si="4"/>
-        <v>40.89827689395824</v>
+        <v>41.558577759011008</v>
       </c>
       <c r="F68" s="124">
         <f t="shared" si="4"/>
-        <v>48.8345663619547</v>
+        <v>49.626716874158213</v>
       </c>
       <c r="H68" s="120"/>
     </row>
@@ -16809,23 +16809,23 @@
       </c>
       <c r="B69" s="124">
         <f t="shared" si="4"/>
-        <v>31.299329728258058</v>
+        <v>31.800158361114647</v>
       </c>
       <c r="C69" s="124">
         <f t="shared" si="4"/>
-        <v>33.550420741611291</v>
+        <v>34.088647903971086</v>
       </c>
       <c r="D69" s="124">
         <f t="shared" si="4"/>
-        <v>38.844345399161426</v>
+        <v>39.470523246908321</v>
       </c>
       <c r="E69" s="124">
         <f t="shared" si="4"/>
-        <v>45.439359431070528</v>
+        <v>46.175103629259652</v>
       </c>
       <c r="F69" s="124">
         <f t="shared" si="4"/>
-        <v>58.606881077273307</v>
+        <v>59.561384065688372</v>
       </c>
       <c r="H69" s="120"/>
     </row>
@@ -16836,23 +16836,23 @@
       </c>
       <c r="B70" s="124">
         <f t="shared" si="4"/>
-        <v>31.299329728258058</v>
+        <v>31.800158361114647</v>
       </c>
       <c r="C70" s="124">
         <f t="shared" si="4"/>
-        <v>34.12756557783046</v>
+        <v>34.675381143349853</v>
       </c>
       <c r="D70" s="124">
         <f t="shared" si="4"/>
-        <v>41.047042830994243</v>
+        <v>41.709815220855326</v>
       </c>
       <c r="E70" s="124">
         <f t="shared" si="4"/>
-        <v>50.158437136784663</v>
+        <v>50.972581793133052</v>
       </c>
       <c r="F70" s="124">
         <f t="shared" si="4"/>
-        <v>69.80027592428381</v>
+        <v>70.940740521955817</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="13.15">
@@ -16862,23 +16862,23 @@
       </c>
       <c r="B71" s="124">
         <f t="shared" si="4"/>
-        <v>31.299329728258055</v>
+        <v>31.800158361114644</v>
       </c>
       <c r="C71" s="124">
         <f t="shared" si="4"/>
-        <v>34.634459724697116</v>
+        <v>35.190696582644996</v>
       </c>
       <c r="D71" s="124">
         <f t="shared" si="4"/>
-        <v>43.094386896739024</v>
+        <v>43.79117286356869</v>
       </c>
       <c r="E71" s="124">
         <f t="shared" si="4"/>
-        <v>54.828796431035542</v>
+        <v>55.720532161587734</v>
       </c>
       <c r="F71" s="124">
         <f t="shared" si="4"/>
-        <v>82.08649916394009</v>
+        <v>83.431081089425874</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="13.15">
@@ -16913,7 +16913,7 @@
       </c>
       <c r="E74" s="135">
         <f>INDEX(B$65:F$71, MATCH(D74, A$65:A$71, 0), MATCH(C74, B$64:F$64, 0))</f>
-        <v>40.957969740368455</v>
+        <v>41.619262313292801</v>
       </c>
       <c r="F74" s="142">
         <f>Scenarios!C58</f>
@@ -16935,7 +16935,7 @@
       </c>
       <c r="E75" s="135">
         <f>INDEX(B$65:F$71, MATCH(D75, A$65:A$71, 0), MATCH(C75, B$64:F$64, 0))</f>
-        <v>33.965919690395395</v>
+        <v>34.51104974988484</v>
       </c>
       <c r="F75" s="142">
         <f>Scenarios!C40*(1-F$74-F$78)</f>
@@ -16958,7 +16958,7 @@
       </c>
       <c r="E76" s="135">
         <f>INDEX(B$65:F$71, MATCH(D76, A$65:A$71, 0), MATCH(C76, B$64:F$64, 0))</f>
-        <v>32.876148462197442</v>
+        <v>33.403173593370909</v>
       </c>
       <c r="F76" s="142">
         <f>Scenarios!C28*(1-F$74-F$78)</f>
@@ -16981,7 +16981,7 @@
       </c>
       <c r="E77" s="135">
         <f>INDEX(B$65:F$71, MATCH(D77, A$65:A$71, 0), MATCH(C77, B$64:F$64, 0))</f>
-        <v>31.817444421096273</v>
+        <v>32.326880759066171</v>
       </c>
       <c r="F77" s="142">
         <f>Scenarios!C34*(1-F$74-F$78)</f>
@@ -17004,7 +17004,7 @@
       </c>
       <c r="E78" s="135">
         <f>INDEX(B$65:F$71, MATCH(D78, A$65:A$71, 0), MATCH(C78, B$64:F$64, 0))</f>
-        <v>31.299329728258055</v>
+        <v>31.800158361114644</v>
       </c>
       <c r="F78" s="142">
         <f>Scenarios!C52</f>
@@ -17186,7 +17186,7 @@
       </c>
       <c r="C4" s="114">
         <f>Normalized_FCF!C91*(1-dividend_tax_rate)</f>
-        <v>3823649.9285927988</v>
+        <v>3887174.1858601244</v>
       </c>
       <c r="D4" t="str">
         <f>Market_currency</f>
@@ -17218,7 +17218,7 @@
       </c>
       <c r="C6" s="319">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
-        <v>50981999.047903985</v>
+        <v>51828989.144801661</v>
       </c>
       <c r="D6" t="str">
         <f>Reporting_currency</f>
@@ -17234,7 +17234,7 @@
       </c>
       <c r="C7" s="111">
         <f>(C6*scaling_factor)/Common_Shares*Exchange_Rate</f>
-        <v>181.53915327569916</v>
+        <v>187.62126579698861</v>
       </c>
       <c r="D7" t="str">
         <f>Market_currency</f>
@@ -17287,7 +17287,7 @@
       </c>
       <c r="C13" s="140">
         <f>F47/Common_Shares*scaling_factor</f>
-        <v>20.676367778745359</v>
+        <v>21.019874880770839</v>
       </c>
       <c r="D13" t="str">
         <f>Market_currency</f>
@@ -17322,7 +17322,7 @@
       </c>
       <c r="C16" s="123">
         <f>C4*(1+D16)</f>
-        <v>3914471.6296652849</v>
+        <v>3979504.7544315001</v>
       </c>
       <c r="D16" s="138">
         <f>IF($C$12&lt;B16,0,DDM!$C$11)</f>
@@ -17334,7 +17334,7 @@
       </c>
       <c r="F16" s="125">
         <f t="shared" ref="F16:F46" si="1">C16*E16</f>
-        <v>3641368.957828172</v>
+        <v>3701864.8878432559</v>
       </c>
       <c r="H16" s="120"/>
     </row>
@@ -17344,7 +17344,7 @@
       </c>
       <c r="C17" s="123">
         <f t="shared" ref="C17:C45" si="2">IF(ROW()-ROW($C$16)&lt;$C$12, $C$16*(1+D17)^(ROW()-ROW($C$16)), 0)</f>
-        <v>4007450.5840270999</v>
+        <v>4074028.4158474728</v>
       </c>
       <c r="D17" s="138">
         <f>IF($C$12&lt;B17,0,DDM!$C$11)</f>
@@ -17356,7 +17356,7 @@
       </c>
       <c r="F17" s="125">
         <f t="shared" si="1"/>
-        <v>3467777.6822300488</v>
+        <v>3525389.6513553038</v>
       </c>
       <c r="H17" s="120"/>
     </row>
@@ -17366,7 +17366,7 @@
       </c>
       <c r="C18" s="123">
         <f t="shared" si="2"/>
-        <v>4102638.0320943496</v>
+        <v>4170797.2618074603</v>
       </c>
       <c r="D18" s="138">
         <f>IF($C$12&lt;B18,0,DDM!$C$11)</f>
@@ -17378,7 +17378,7 @@
       </c>
       <c r="F18" s="125">
         <f t="shared" si="1"/>
-        <v>3302461.8468064247</v>
+        <v>3357327.3391736262</v>
       </c>
       <c r="H18" s="120"/>
     </row>
@@ -17388,7 +17388,7 @@
       </c>
       <c r="C19" s="123">
         <f t="shared" si="2"/>
-        <v>4200086.4313772349</v>
+        <v>4269864.6213251837</v>
       </c>
       <c r="D19" s="138">
         <f>IF($C$12&lt;B19,0,DDM!$C$11)</f>
@@ -17400,7 +17400,7 @@
       </c>
       <c r="F19" s="125">
         <f t="shared" si="1"/>
-        <v>3145026.9449218372</v>
+        <v>3197276.8905216977</v>
       </c>
       <c r="H19" s="120"/>
     </row>
@@ -17410,7 +17410,7 @@
       </c>
       <c r="C20" s="123">
         <f t="shared" si="2"/>
-        <v>4299849.4853892252</v>
+        <v>4371285.090118126</v>
       </c>
       <c r="D20" s="138">
         <f>IF($C$12&lt;B20,0,DDM!$C$11)</f>
@@ -17422,7 +17422,7 @@
       </c>
       <c r="F20" s="125">
         <f t="shared" si="1"/>
-        <v>2995097.2768540694</v>
+        <v>3044856.3639851362</v>
       </c>
       <c r="H20" s="120"/>
     </row>
@@ -17982,7 +17982,7 @@
       </c>
       <c r="C46" s="123">
         <f>C$16*(1+F4)^$C$12/Equity_Cost</f>
-        <v>52192955.062203802</v>
+        <v>53060063.392420001</v>
       </c>
       <c r="D46" s="139">
         <f>Terminal_Growth</f>
@@ -17994,7 +17994,7 @@
       </c>
       <c r="F46" s="125">
         <f t="shared" si="1"/>
-        <v>36355453.396439753</v>
+        <v>36959445.189034544</v>
       </c>
       <c r="H46" s="120"/>
     </row>
@@ -18005,7 +18005,7 @@
       </c>
       <c r="F47" s="137">
         <f>SUM(F16:F46)</f>
-        <v>52907186.105080307</v>
+        <v>53786160.321913563</v>
       </c>
       <c r="H47" s="120"/>
     </row>
@@ -18026,7 +18026,7 @@
     <row r="50" spans="1:8" ht="13.15">
       <c r="A50" s="133">
         <f>F47</f>
-        <v>52907186.105080307</v>
+        <v>53786160.321913563</v>
       </c>
       <c r="B50" s="131">
         <f>C73</f>
@@ -18056,19 +18056,19 @@
       </c>
       <c r="B51" s="123">
         <f t="dataTable" ref="B51:F56" dt2D="1" dtr="1" r1="C11" r2="C12"/>
-        <v>50981999.047903985</v>
+        <v>51828989.144801661</v>
       </c>
       <c r="C51" s="123">
-        <v>51784571.316703632</v>
+        <v>52644894.958311461</v>
       </c>
       <c r="D51" s="123">
-        <v>53424529.642531738</v>
+        <v>54312098.752878368</v>
       </c>
       <c r="E51" s="123">
-        <v>55112611.797269031</v>
+        <v>56028225.88220498</v>
       </c>
       <c r="F51" s="123">
-        <v>57739583.71711196</v>
+        <v>58698841.033825554</v>
       </c>
       <c r="H51" s="120"/>
     </row>
@@ -18077,19 +18077,19 @@
         <v>10</v>
       </c>
       <c r="B52" s="123">
-        <v>50981999.047904</v>
+        <v>51828989.144801676</v>
       </c>
       <c r="C52" s="123">
-        <v>52554062.956660099</v>
+        <v>53427170.557525307</v>
       </c>
       <c r="D52" s="123">
-        <v>55929630.268731765</v>
+        <v>56858817.900551625</v>
       </c>
       <c r="E52" s="123">
-        <v>59644595.680471517</v>
+        <v>60635501.937940091</v>
       </c>
       <c r="F52" s="123">
-        <v>65943467.493383601</v>
+        <v>67039020.138730198</v>
       </c>
       <c r="H52" s="120"/>
     </row>
@@ -18098,19 +18098,19 @@
         <v>15</v>
       </c>
       <c r="B53" s="123">
-        <v>50981999.047904</v>
+        <v>51828989.144801676</v>
       </c>
       <c r="C53" s="123">
-        <v>53504109.051905796</v>
+        <v>54393000.255793579</v>
       </c>
       <c r="D53" s="123">
-        <v>59183877.074667662</v>
+        <v>60167129.177653104</v>
       </c>
       <c r="E53" s="123">
-        <v>65851001.821522191</v>
+        <v>66945018.287240066</v>
       </c>
       <c r="F53" s="123">
-        <v>78144507.356539741</v>
+        <v>79442762.134579033</v>
       </c>
       <c r="H53" s="120"/>
     </row>
@@ -18119,19 +18119,19 @@
         <v>20</v>
       </c>
       <c r="B54" s="123">
-        <v>50981999.047904</v>
+        <v>51828989.144801676</v>
       </c>
       <c r="C54" s="123">
-        <v>54468993.813415334</v>
+        <v>55373915.142698519</v>
       </c>
       <c r="D54" s="123">
-        <v>62669411.94861576</v>
+        <v>63710571.030059457</v>
       </c>
       <c r="E54" s="123">
-        <v>72885249.189902872</v>
+        <v>74096129.214747742</v>
       </c>
       <c r="F54" s="123">
-        <v>93282060.683841854</v>
+        <v>94831803.398779005</v>
       </c>
       <c r="H54" s="120"/>
     </row>
@@ -18140,19 +18140,19 @@
         <v>25</v>
       </c>
       <c r="B55" s="123">
-        <v>50981999.047904</v>
+        <v>51828989.144801676</v>
       </c>
       <c r="C55" s="123">
-        <v>55363005.21095553</v>
+        <v>56282779.210090257</v>
       </c>
       <c r="D55" s="123">
-        <v>66081443.878575303</v>
+        <v>67179288.796371922</v>
       </c>
       <c r="E55" s="123">
-        <v>80195215.406397298</v>
+        <v>81527539.648998499</v>
       </c>
       <c r="F55" s="123">
-        <v>110620901.72060908</v>
+        <v>112458703.4941176</v>
       </c>
       <c r="H55" s="120"/>
     </row>
@@ -18161,19 +18161,19 @@
         <v>30</v>
       </c>
       <c r="B56" s="123">
-        <v>50981999.047903985</v>
+        <v>51828989.144801669</v>
       </c>
       <c r="C56" s="123">
-        <v>56148196.580965668</v>
+        <v>57081015.367024951</v>
       </c>
       <c r="D56" s="123">
-        <v>69252829.663558871</v>
+        <v>70403362.439883739</v>
       </c>
       <c r="E56" s="123">
-        <v>87429715.617852971</v>
+        <v>88882230.322765172</v>
       </c>
       <c r="F56" s="123">
-        <v>129652560.53424691</v>
+        <v>131806545.01623532</v>
       </c>
       <c r="H56" s="120"/>
     </row>
@@ -18223,23 +18223,23 @@
       </c>
       <c r="B60" s="124">
         <f>C7</f>
-        <v>181.53915327569916</v>
+        <v>187.62126579698861</v>
       </c>
       <c r="C60" s="124">
         <f>C7</f>
-        <v>181.53915327569916</v>
+        <v>187.62126579698861</v>
       </c>
       <c r="D60" s="124">
         <f>C7</f>
-        <v>181.53915327569916</v>
+        <v>187.62126579698861</v>
       </c>
       <c r="E60" s="141">
         <f>C7</f>
-        <v>181.53915327569916</v>
+        <v>187.62126579698861</v>
       </c>
       <c r="F60" s="124">
         <f>C7</f>
-        <v>181.53915327569916</v>
+        <v>187.62126579698861</v>
       </c>
       <c r="H60" s="120"/>
     </row>
@@ -18250,23 +18250,23 @@
       </c>
       <c r="B61" s="124">
         <f t="shared" ref="B61:F66" si="4">B51/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>181.53915327569916</v>
+        <v>187.62126579698861</v>
       </c>
       <c r="C61" s="124">
         <f t="shared" si="4"/>
-        <v>184.39699119577648</v>
+        <v>190.57484995959203</v>
       </c>
       <c r="D61" s="124">
         <f t="shared" si="4"/>
-        <v>190.23663364680169</v>
+        <v>196.61013815331435</v>
       </c>
       <c r="E61" s="124">
         <f t="shared" si="4"/>
-        <v>196.24763774146018</v>
+        <v>202.82252912573423</v>
       </c>
       <c r="F61" s="124">
         <f t="shared" si="4"/>
-        <v>205.60188565079025</v>
+        <v>212.49017272580096</v>
       </c>
       <c r="H61" s="120"/>
     </row>
@@ -18277,23 +18277,23 @@
       </c>
       <c r="B62" s="124">
         <f t="shared" si="4"/>
-        <v>181.53915327569922</v>
+        <v>187.62126579698867</v>
       </c>
       <c r="C62" s="124">
         <f t="shared" si="4"/>
-        <v>187.13703402224874</v>
+        <v>193.40669253550149</v>
       </c>
       <c r="D62" s="124">
         <f t="shared" si="4"/>
-        <v>199.15691639451151</v>
+        <v>205.82927744196496</v>
       </c>
       <c r="E62" s="124">
         <f t="shared" si="4"/>
-        <v>212.38534383734381</v>
+        <v>219.50089734623191</v>
       </c>
       <c r="F62" s="124">
         <f t="shared" si="4"/>
-        <v>234.81466942015933</v>
+        <v>242.68167339860059</v>
       </c>
       <c r="H62" s="120"/>
     </row>
@@ -18304,23 +18304,23 @@
       </c>
       <c r="B63" s="124">
         <f t="shared" si="4"/>
-        <v>181.53915327569922</v>
+        <v>187.62126579698867</v>
       </c>
       <c r="C63" s="124">
         <f t="shared" si="4"/>
-        <v>190.52000383364688</v>
+        <v>196.90300210131502</v>
       </c>
       <c r="D63" s="124">
         <f t="shared" si="4"/>
-        <v>210.74479487578969</v>
+        <v>217.80538501616576</v>
       </c>
       <c r="E63" s="124">
         <f t="shared" si="4"/>
-        <v>234.48541321031522</v>
+        <v>242.34138610658789</v>
       </c>
       <c r="F63" s="124">
         <f t="shared" si="4"/>
-        <v>278.26071875532131</v>
+        <v>287.58329722496143</v>
       </c>
       <c r="H63" s="120"/>
     </row>
@@ -18331,23 +18331,23 @@
       </c>
       <c r="B64" s="124">
         <f t="shared" si="4"/>
-        <v>181.53915327569922</v>
+        <v>187.62126579698867</v>
       </c>
       <c r="C64" s="124">
         <f t="shared" si="4"/>
-        <v>193.95581188127716</v>
+        <v>200.45392014461385</v>
       </c>
       <c r="D64" s="124">
         <f t="shared" si="4"/>
-        <v>223.15625502930192</v>
+        <v>230.63266674780621</v>
       </c>
       <c r="E64" s="124">
         <f t="shared" si="4"/>
-        <v>259.53329942575664</v>
+        <v>268.22845251888424</v>
       </c>
       <c r="F64" s="124">
         <f t="shared" si="4"/>
-        <v>332.16324641262287</v>
+        <v>343.29172312778229</v>
       </c>
       <c r="H64" s="120"/>
     </row>
@@ -18358,23 +18358,23 @@
       </c>
       <c r="B65" s="124">
         <f t="shared" si="4"/>
-        <v>181.53915327569922</v>
+        <v>187.62126579698867</v>
       </c>
       <c r="C65" s="124">
         <f t="shared" si="4"/>
-        <v>197.13925064710057</v>
+        <v>203.74401376934242</v>
       </c>
       <c r="D65" s="124">
         <f t="shared" si="4"/>
-        <v>235.30598236605238</v>
+        <v>243.18944681908653</v>
       </c>
       <c r="E65" s="124">
         <f t="shared" si="4"/>
-        <v>285.56297857132012</v>
+        <v>295.13020490374475</v>
       </c>
       <c r="F65" s="124">
         <f t="shared" si="4"/>
-        <v>393.90422517728507</v>
+        <v>407.10121203609896</v>
       </c>
     </row>
     <row r="66" spans="1:8" ht="13.15">
@@ -18384,23 +18384,23 @@
       </c>
       <c r="B66" s="124">
         <f t="shared" si="4"/>
-        <v>181.53915327569916</v>
+        <v>187.62126579698864</v>
       </c>
       <c r="C66" s="124">
         <f t="shared" si="4"/>
-        <v>199.93519782714523</v>
+        <v>206.63363366431258</v>
       </c>
       <c r="D66" s="124">
         <f t="shared" si="4"/>
-        <v>246.59880534020709</v>
+        <v>254.86061363131958</v>
       </c>
       <c r="E66" s="124">
         <f t="shared" si="4"/>
-        <v>311.32393473795605</v>
+        <v>321.75423127443474</v>
       </c>
       <c r="F66" s="124">
         <f t="shared" si="4"/>
-        <v>461.67307086757296</v>
+        <v>477.14051970381081</v>
       </c>
     </row>
     <row r="68" spans="1:8" ht="13.15">
@@ -18435,7 +18435,7 @@
       </c>
       <c r="E69" s="135">
         <f>INDEX(B$60:F$66, MATCH(D69, A$60:A$66, 0), MATCH(C69, B$59:F$59, 0))</f>
-        <v>234.81466942015933</v>
+        <v>242.68167339860059</v>
       </c>
       <c r="F69" s="142">
         <f>Scenarios!C58</f>
@@ -18457,7 +18457,7 @@
       </c>
       <c r="E70" s="135">
         <f>INDEX(B$60:F$66, MATCH(D70, A$60:A$66, 0), MATCH(C70, B$59:F$59, 0))</f>
-        <v>196.24763774146018</v>
+        <v>202.82252912573423</v>
       </c>
       <c r="F70" s="142">
         <f>Scenarios!C40*(1-F$69-F$73)</f>
@@ -18480,7 +18480,7 @@
       </c>
       <c r="E71" s="135">
         <f>INDEX(B$60:F$66, MATCH(D71, A$60:A$66, 0), MATCH(C71, B$59:F$59, 0))</f>
-        <v>190.23663364680169</v>
+        <v>196.61013815331435</v>
       </c>
       <c r="F71" s="142">
         <f>Scenarios!C28*(1-F$69-F$73)</f>
@@ -18503,7 +18503,7 @@
       </c>
       <c r="E72" s="135">
         <f>INDEX(B$60:F$66, MATCH(D72, A$60:A$66, 0), MATCH(C72, B$59:F$59, 0))</f>
-        <v>184.39699119577648</v>
+        <v>190.57484995959203</v>
       </c>
       <c r="F72" s="142">
         <f>Scenarios!C34*(1-F$69-F$73)</f>
@@ -18526,7 +18526,7 @@
       </c>
       <c r="E73" s="135">
         <f>INDEX(B$60:F$66, MATCH(D73, A$60:A$66, 0), MATCH(C73, B$59:F$59, 0))</f>
-        <v>181.53915327569922</v>
+        <v>187.62126579698867</v>
       </c>
       <c r="F73" s="142">
         <f>Scenarios!C52</f>
@@ -18626,7 +18626,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-48.9</v>
+        <v>-50</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18646,7 +18646,7 @@
       </c>
       <c r="I4" s="124">
         <f t="shared" ref="I4:I13" si="0">IF(ROW()-3 &lt; $C$76, $C$77, IF(ROW()-3 = $C$76, $C$77 + $C$60, ""))</f>
-        <v>1.49429969728</v>
+        <v>1.51912526452</v>
       </c>
     </row>
     <row r="5" spans="2:9">
@@ -18655,7 +18655,7 @@
       </c>
       <c r="I5" s="124">
         <f t="shared" si="0"/>
-        <v>1.49429969728</v>
+        <v>1.51912526452</v>
       </c>
     </row>
     <row r="6" spans="2:9" ht="13.15">
@@ -18675,7 +18675,7 @@
       </c>
       <c r="I6" s="124">
         <f t="shared" si="0"/>
-        <v>34.701290380366437</v>
+        <v>35.258637530271841</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1">
@@ -18866,7 +18866,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>48.9</v>
+        <v>50</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -18881,7 +18881,7 @@
       </c>
       <c r="C22" s="160">
         <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
-        <v>31.299329728258044</v>
+        <v>31.800158361114637</v>
       </c>
       <c r="D22" t="str">
         <f>Market_currency</f>
@@ -18928,7 +18928,7 @@
       </c>
       <c r="C27" s="160">
         <f>IF(valuation_method="DCF",DCF!E76,DDM!E71)</f>
-        <v>32.876148462197442</v>
+        <v>33.403173593370909</v>
       </c>
       <c r="D27" s="160" t="str">
         <f>Market_currency</f>
@@ -18986,7 +18986,7 @@
       </c>
       <c r="C33" s="160">
         <f>IF(valuation_method="DCF",DCF!E77,DDM!E72)</f>
-        <v>31.817444421096273</v>
+        <v>32.326880759066171</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
@@ -19044,7 +19044,7 @@
       </c>
       <c r="C39" s="160">
         <f>IF(valuation_method="DCF",DCF!E75,DDM!E70)</f>
-        <v>33.965919690395395</v>
+        <v>34.51104974988484</v>
       </c>
       <c r="D39" t="str">
         <f>Market_currency</f>
@@ -19071,7 +19071,7 @@
       </c>
       <c r="C42" s="154">
         <f>C27*C28+C33*C34+C39*C40</f>
-        <v>32.882361899616797</v>
+        <v>33.409490257812749</v>
       </c>
       <c r="D42" t="str">
         <f>Market_currency</f>
@@ -19145,7 +19145,7 @@
       </c>
       <c r="C51" s="160">
         <f>IF(valuation_method="DCF",DCF!E78,DDM!E73)</f>
-        <v>31.299329728258055</v>
+        <v>31.800158361114644</v>
       </c>
       <c r="D51" t="str">
         <f>Market_currency</f>
@@ -19203,7 +19203,7 @@
       </c>
       <c r="C57" s="160">
         <f>IF(valuation_method="DCF",DCF!E74,DDM!E69)</f>
-        <v>40.957969740368455</v>
+        <v>41.619262313292801</v>
       </c>
       <c r="D57" t="str">
         <f>Market_currency</f>
@@ -19229,7 +19229,7 @@
       </c>
       <c r="C60" s="154">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
-        <v>33.206990683086438</v>
+        <v>33.739512265751841</v>
       </c>
       <c r="D60" t="str">
         <f>Market_currency</f>
@@ -19291,7 +19291,7 @@
       </c>
       <c r="C66" s="160">
         <f>IF(valuation_method="DCF",DCF!C18,DDM!C13)</f>
-        <v>32.542168210924395</v>
+        <v>33.06364475689778</v>
       </c>
       <c r="D66" s="160" t="str">
         <f>Market_currency</f>
@@ -19354,7 +19354,7 @@
       </c>
       <c r="F72" s="291">
         <f>BS!D89/C60</f>
-        <v>-4.8574095774619019E-2</v>
+        <v>-4.9169659170151009E-2</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="13.9">
@@ -19387,7 +19387,7 @@
       </c>
       <c r="C77" s="173">
         <f>Normalized_FCF!C90*(1-dividend_tax_rate)</f>
-        <v>1.49429969728</v>
+        <v>1.51912526452</v>
       </c>
       <c r="D77" t="str">
         <f>Market_currency</f>
@@ -19414,7 +19414,7 @@
       </c>
       <c r="C81" s="116">
         <f>PV(C80, C76, -C77, 0)</f>
-        <v>2.4764420992413672</v>
+        <v>2.517584501908376</v>
       </c>
       <c r="D81" s="116"/>
       <c r="E81" s="100"/>
@@ -19426,7 +19426,7 @@
       </c>
       <c r="C82" s="116">
         <f>C60/(1+C80)^C76</f>
-        <v>12.988015361793611</v>
+        <v>13.196296761398656</v>
       </c>
       <c r="D82" s="116"/>
     </row>
@@ -19436,7 +19436,7 @@
       </c>
       <c r="C83" s="111">
         <f>C81+C82</f>
-        <v>15.464457461034979</v>
+        <v>15.713881263307032</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -19447,7 +19447,7 @@
       </c>
       <c r="F83" s="291">
         <f>(1-C83/C60)</f>
-        <v>0.53430114735113277</v>
+        <v>0.53425879012312194</v>
       </c>
     </row>
     <row r="84" spans="2:8">
@@ -19464,7 +19464,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>48.9</v>
+        <v>50</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19477,7 +19477,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>-8.6188313093982005E-2</v>
+        <v>-8.8165408338003126E-2</v>
       </c>
     </row>
     <row r="88" spans="2:8">
@@ -19503,7 +19503,7 @@
       </c>
       <c r="C91" s="116">
         <f>PV(C90, C76, -C77, 0)</f>
-        <v>3.0639133304040378</v>
+        <v>3.114815693925848</v>
       </c>
       <c r="D91" s="116"/>
       <c r="E91" s="100"/>
@@ -19515,7 +19515,7 @@
       </c>
       <c r="C92" s="116">
         <f>C60/(1+C90)^C76</f>
-        <v>18.404737517799937</v>
+        <v>18.69988380326302</v>
       </c>
       <c r="D92" s="116"/>
     </row>
@@ -19525,7 +19525,7 @@
       </c>
       <c r="C93" s="111">
         <f>C91+C92</f>
-        <v>21.468650848203975</v>
+        <v>21.814699497188869</v>
       </c>
       <c r="D93" t="str">
         <f>Market_currency</f>
@@ -19536,7 +19536,7 @@
       </c>
       <c r="F93" s="291">
         <f>(1-C93/C60)</f>
-        <v>0.35349002102925386</v>
+        <v>0.35343761565479292</v>
       </c>
     </row>
     <row r="95" spans="2:8" ht="13.15">
@@ -19563,7 +19563,7 @@
       </c>
       <c r="C97" s="116">
         <f>PV(C96, C76, -C77, 0)</f>
-        <v>3.8859648258595172</v>
+        <v>3.9505243524740594</v>
       </c>
       <c r="D97" s="116"/>
       <c r="G97" s="2"/>
@@ -19575,7 +19575,7 @@
       </c>
       <c r="C98" s="116">
         <f>C60/(1+C96)^C76</f>
-        <v>26.73031813195734</v>
+        <v>27.158977008415839</v>
       </c>
       <c r="D98" s="116"/>
       <c r="G98" s="2"/>
@@ -19587,7 +19587,7 @@
       </c>
       <c r="C99" s="111">
         <f>C97+C98</f>
-        <v>30.616282957816857</v>
+        <v>31.109501360889897</v>
       </c>
       <c r="D99" t="s">
         <v>393</v>
@@ -19597,7 +19597,7 @@
       </c>
       <c r="F99" s="291">
         <f>(1-C99/C60)</f>
-        <v>7.8016937758504157E-2</v>
+        <v>7.7950471961374612E-2</v>
       </c>
     </row>
     <row r="100" spans="2:8">
@@ -19623,7 +19623,7 @@
       </c>
       <c r="C103" s="116">
         <f>PV(C102, C76, -C77, 0)</f>
-        <v>3.6051521207469053</v>
+        <v>3.6650463618733289</v>
       </c>
       <c r="D103" s="116"/>
     </row>
@@ -19633,7 +19633,7 @@
       </c>
       <c r="C104" s="116">
         <f>C60/(1+C102)^C76</f>
-        <v>23.801455692847924</v>
+        <v>24.183146071728043</v>
       </c>
       <c r="D104" s="116"/>
     </row>
@@ -19643,7 +19643,7 @@
       </c>
       <c r="C105" s="111">
         <f>C103+C104</f>
-        <v>27.406607813594828</v>
+        <v>27.848192433601373</v>
       </c>
       <c r="D105" t="s">
         <v>393</v>
@@ -19653,7 +19653,7 @@
       </c>
       <c r="F105" s="291">
         <f>(1-C105/C66)</f>
-        <v>0.15781248391450331</v>
+        <v>0.15773978826724333</v>
       </c>
     </row>
     <row r="106" spans="2:8">

--- a/financial_models/opportunities/1913.HK_Valuation.xlsx
+++ b/financial_models/opportunities/1913.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E6E4CFA-D4D7-4C94-9AEE-CDBB73443B2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64FAAA38-9DDD-4DDD-A05D-109611CA6BCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3896,29 +3896,29 @@
     <xf numFmtId="10" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4336,7 +4336,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>50</v>
+        <v>50.5</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4357,7 +4357,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>127941.2</v>
+        <v>129220.61199999999</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4384,7 +4384,7 @@
         <v>1</v>
       </c>
       <c r="C16" s="50">
-        <v>9.2629589299999999</v>
+        <v>9.2581720599999997</v>
       </c>
       <c r="D16" s="50"/>
       <c r="E16" s="5"/>
@@ -4394,13 +4394,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="360" t="s">
+      <c r="B18" s="358" t="s">
         <v>356</v>
       </c>
-      <c r="C18" s="360"/>
-      <c r="D18" s="360"/>
-      <c r="E18" s="360"/>
-      <c r="F18" s="360"/>
+      <c r="C18" s="358"/>
+      <c r="D18" s="358"/>
+      <c r="E18" s="358"/>
+      <c r="F18" s="358"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4476,14 +4476,14 @@
       </c>
       <c r="C26" s="304">
         <f>C132</f>
-        <v>33.739512265751841</v>
+        <v>33.722682188047798</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>396</v>
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>-8.8165408338003126E-2</v>
+        <v>-9.1448907953051495E-2</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4515,7 +4515,7 @@
       </c>
       <c r="C29" s="310">
         <f>C149</f>
-        <v>15.713881263307032</v>
+        <v>15.705997608142953</v>
       </c>
       <c r="D29" s="310" t="str">
         <f>D149</f>
@@ -4534,7 +4534,7 @@
       </c>
       <c r="C30" s="311">
         <f>C157</f>
-        <v>21.814699497188869</v>
+        <v>21.803761886413703</v>
       </c>
       <c r="D30" s="311" t="str">
         <f>D157</f>
@@ -4553,7 +4553,7 @@
       </c>
       <c r="C31" s="311">
         <f>C165</f>
-        <v>31.109501360889897</v>
+        <v>31.093912277858021</v>
       </c>
       <c r="D31" s="311" t="str">
         <f>D165</f>
@@ -4572,7 +4572,7 @@
       </c>
       <c r="C32" s="311">
         <f>C173</f>
-        <v>27.848192433601373</v>
+        <v>27.834235294417574</v>
       </c>
       <c r="D32" s="311" t="str">
         <f>D173</f>
@@ -4600,22 +4600,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="360" t="s">
+      <c r="B36" s="358" t="s">
         <v>357</v>
       </c>
-      <c r="C36" s="360"/>
-      <c r="D36" s="360"/>
-      <c r="E36" s="360"/>
-      <c r="F36" s="360"/>
+      <c r="C36" s="358"/>
+      <c r="D36" s="358"/>
+      <c r="E36" s="358"/>
+      <c r="F36" s="358"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="363" t="s">
+      <c r="B37" s="360" t="s">
         <v>336</v>
       </c>
-      <c r="C37" s="363"/>
-      <c r="D37" s="363"/>
-      <c r="E37" s="363"/>
-      <c r="F37" s="363"/>
+      <c r="C37" s="360"/>
+      <c r="D37" s="360"/>
+      <c r="E37" s="360"/>
+      <c r="F37" s="360"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4627,13 +4627,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="361" t="s">
+      <c r="B40" s="359" t="s">
         <v>230</v>
       </c>
-      <c r="C40" s="361"/>
-      <c r="D40" s="361"/>
-      <c r="E40" s="361"/>
-      <c r="F40" s="361"/>
+      <c r="C40" s="359"/>
+      <c r="D40" s="359"/>
+      <c r="E40" s="359"/>
+      <c r="F40" s="359"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4653,13 +4653,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="361" t="s">
+      <c r="B43" s="359" t="s">
         <v>232</v>
       </c>
-      <c r="C43" s="361"/>
-      <c r="D43" s="361"/>
-      <c r="E43" s="361"/>
-      <c r="F43" s="361"/>
+      <c r="C43" s="359"/>
+      <c r="D43" s="359"/>
+      <c r="E43" s="359"/>
+      <c r="F43" s="359"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4688,13 +4688,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="361" t="s">
+      <c r="B47" s="359" t="s">
         <v>235</v>
       </c>
-      <c r="C47" s="361"/>
-      <c r="D47" s="361"/>
-      <c r="E47" s="361"/>
-      <c r="F47" s="361"/>
+      <c r="C47" s="359"/>
+      <c r="D47" s="359"/>
+      <c r="E47" s="359"/>
+      <c r="F47" s="359"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4710,13 +4710,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="361" t="s">
+      <c r="B50" s="359" t="s">
         <v>239</v>
       </c>
-      <c r="C50" s="361"/>
-      <c r="D50" s="361"/>
-      <c r="E50" s="361"/>
-      <c r="F50" s="361"/>
+      <c r="C50" s="359"/>
+      <c r="D50" s="359"/>
+      <c r="E50" s="359"/>
+      <c r="F50" s="359"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4780,13 +4780,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="361" t="s">
+      <c r="B58" s="359" t="s">
         <v>240</v>
       </c>
-      <c r="C58" s="361"/>
-      <c r="D58" s="361"/>
-      <c r="E58" s="361"/>
-      <c r="F58" s="361"/>
+      <c r="C58" s="359"/>
+      <c r="D58" s="359"/>
+      <c r="E58" s="359"/>
+      <c r="F58" s="359"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4802,7 +4802,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="361" t="s">
+      <c r="B61" s="359" t="s">
         <v>335</v>
       </c>
       <c r="C61" s="362"/>
@@ -4824,22 +4824,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="360" t="s">
+      <c r="B64" s="358" t="s">
         <v>340</v>
       </c>
-      <c r="C64" s="360"/>
-      <c r="D64" s="360"/>
-      <c r="E64" s="360"/>
-      <c r="F64" s="360"/>
+      <c r="C64" s="358"/>
+      <c r="D64" s="358"/>
+      <c r="E64" s="358"/>
+      <c r="F64" s="358"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="360" t="s">
+      <c r="B65" s="358" t="s">
         <v>358</v>
       </c>
-      <c r="C65" s="360"/>
-      <c r="D65" s="360"/>
-      <c r="E65" s="360"/>
-      <c r="F65" s="360"/>
+      <c r="C65" s="358"/>
+      <c r="D65" s="358"/>
+      <c r="E65" s="358"/>
+      <c r="F65" s="358"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4873,7 +4873,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>5.0188678019683179E-2</v>
+        <v>4.9666080932440702E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4883,14 +4883,14 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>3.03825052904E-2</v>
+        <v>3.0066142927524752E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>444</v>
       </c>
       <c r="F70" s="315">
         <f>Normalized_FCF!C92</f>
-        <v>5.6074778177084079</v>
+        <v>5.6045800106961883</v>
       </c>
     </row>
     <row r="72" spans="1:6">
@@ -4974,22 +4974,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.6" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="360" t="s">
+      <c r="B80" s="358" t="s">
         <v>359</v>
       </c>
-      <c r="C80" s="360"/>
-      <c r="D80" s="360"/>
-      <c r="E80" s="360"/>
-      <c r="F80" s="360"/>
+      <c r="C80" s="358"/>
+      <c r="D80" s="358"/>
+      <c r="E80" s="358"/>
+      <c r="F80" s="358"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="363" t="s">
+      <c r="B81" s="360" t="s">
         <v>251</v>
       </c>
-      <c r="C81" s="363"/>
-      <c r="D81" s="363"/>
-      <c r="E81" s="363"/>
-      <c r="F81" s="363"/>
+      <c r="C81" s="360"/>
+      <c r="D81" s="360"/>
+      <c r="E81" s="360"/>
+      <c r="F81" s="360"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5033,22 +5033,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="360" t="s">
+      <c r="B89" s="358" t="s">
         <v>360</v>
       </c>
-      <c r="C89" s="360"/>
-      <c r="D89" s="360"/>
-      <c r="E89" s="360"/>
-      <c r="F89" s="360"/>
+      <c r="C89" s="358"/>
+      <c r="D89" s="358"/>
+      <c r="E89" s="358"/>
+      <c r="F89" s="358"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="360" t="s">
+      <c r="B90" s="358" t="s">
         <v>361</v>
       </c>
-      <c r="C90" s="360"/>
-      <c r="D90" s="360"/>
-      <c r="E90" s="360"/>
-      <c r="F90" s="360"/>
+      <c r="C90" s="358"/>
+      <c r="D90" s="358"/>
+      <c r="E90" s="358"/>
+      <c r="F90" s="358"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5064,7 +5064,7 @@
       </c>
       <c r="C93" s="223">
         <f>DCF!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>33.45911867978878</v>
+        <v>33.441827827843404</v>
       </c>
       <c r="D93" s="1" t="str">
         <f>Market_currency</f>
@@ -5085,13 +5085,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="360" t="s">
+      <c r="B97" s="358" t="s">
         <v>362</v>
       </c>
-      <c r="C97" s="360"/>
-      <c r="D97" s="360"/>
-      <c r="E97" s="360"/>
-      <c r="F97" s="360"/>
+      <c r="C97" s="358"/>
+      <c r="D97" s="358"/>
+      <c r="E97" s="358"/>
+      <c r="F97" s="358"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5104,13 +5104,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="360" t="s">
+      <c r="B101" s="358" t="s">
         <v>341</v>
       </c>
-      <c r="C101" s="360"/>
-      <c r="D101" s="360"/>
-      <c r="E101" s="360"/>
-      <c r="F101" s="360"/>
+      <c r="C101" s="358"/>
+      <c r="D101" s="358"/>
+      <c r="E101" s="358"/>
+      <c r="F101" s="358"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="C103" s="223">
         <f>C102*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>3.1367354350455523</v>
+        <v>3.1351144471014809</v>
       </c>
       <c r="D103" s="1" t="str">
         <f>Market_currency</f>
@@ -5180,7 +5180,7 @@
       </c>
       <c r="C109" s="349">
         <f>DCF!C8</f>
-        <v>404462.06293345941</v>
+        <v>404629.46262395149</v>
       </c>
       <c r="D109" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5193,7 +5193,7 @@
       </c>
       <c r="C110" s="223">
         <f>C109*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>1.4641552047720787</v>
+        <v>1.4640042400406914</v>
       </c>
       <c r="D110" s="1" t="str">
         <f>Market_currency</f>
@@ -5224,7 +5224,7 @@
       </c>
       <c r="C114" s="223">
         <f>C113*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>1.3619911599325315E-2</v>
+        <v>1.3612873163040523E-2</v>
       </c>
       <c r="D114" s="1" t="str">
         <f>Market_currency</f>
@@ -5232,13 +5232,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="360" t="s">
+      <c r="B116" s="358" t="s">
         <v>363</v>
       </c>
-      <c r="C116" s="360"/>
-      <c r="D116" s="360"/>
-      <c r="E116" s="360"/>
-      <c r="F116" s="360"/>
+      <c r="C116" s="358"/>
+      <c r="D116" s="358"/>
+      <c r="E116" s="358"/>
+      <c r="F116" s="358"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="C118" s="223">
         <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
-        <v>31.800158361114637</v>
+        <v>31.784330493945657</v>
       </c>
       <c r="D118" s="1" t="str">
         <f>Market_currency</f>
@@ -5259,7 +5259,7 @@
       </c>
       <c r="C119" s="223">
         <f>BS!D47</f>
-        <v>-6.0199187527594056</v>
+        <v>-6.0168078063871082</v>
       </c>
       <c r="D119" s="1" t="str">
         <f>Market_currency</f>
@@ -5277,13 +5277,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B123" s="361" t="s">
+      <c r="B123" s="359" t="s">
         <v>364</v>
       </c>
-      <c r="C123" s="361"/>
-      <c r="D123" s="361"/>
-      <c r="E123" s="361"/>
-      <c r="F123" s="361"/>
+      <c r="C123" s="359"/>
+      <c r="D123" s="359"/>
+      <c r="E123" s="359"/>
+      <c r="F123" s="359"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5317,7 +5317,7 @@
       </c>
       <c r="E126" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E74,DDM!E69),2)&amp;" "&amp;Market_currency</f>
-        <v>41.62 HKD</v>
+        <v>41.6 HKD</v>
       </c>
       <c r="F126" s="232">
         <f>DCF!F74</f>
@@ -5339,7 +5339,7 @@
       </c>
       <c r="E127" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E75,DDM!E70),2)&amp;" "&amp;Market_currency</f>
-        <v>34.51 HKD</v>
+        <v>34.49 HKD</v>
       </c>
       <c r="F127" s="221">
         <f>DCF!F75</f>
@@ -5361,7 +5361,7 @@
       </c>
       <c r="E128" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E76,DDM!E71),2)&amp;" "&amp;Market_currency</f>
-        <v>33.4 HKD</v>
+        <v>33.39 HKD</v>
       </c>
       <c r="F128" s="221">
         <f>DCF!F76</f>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="E129" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E77,DDM!E72),2)&amp;" "&amp;Market_currency</f>
-        <v>32.33 HKD</v>
+        <v>32.31 HKD</v>
       </c>
       <c r="F129" s="221">
         <f>DCF!F77</f>
@@ -5405,7 +5405,7 @@
       </c>
       <c r="E130" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E78,DDM!E73),2)&amp;" "&amp;Market_currency</f>
-        <v>31.8 HKD</v>
+        <v>31.78 HKD</v>
       </c>
       <c r="F130" s="221">
         <f>DCF!F78</f>
@@ -5418,7 +5418,7 @@
       </c>
       <c r="C132" s="217">
         <f>Scenarios!C60</f>
-        <v>33.739512265751841</v>
+        <v>33.722682188047798</v>
       </c>
       <c r="D132" s="212" t="str">
         <f>Market_currency</f>
@@ -5426,13 +5426,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="364" t="s">
+      <c r="B134" s="363" t="s">
         <v>367</v>
       </c>
-      <c r="C134" s="364"/>
-      <c r="D134" s="364"/>
-      <c r="E134" s="364"/>
-      <c r="F134" s="364"/>
+      <c r="C134" s="363"/>
+      <c r="D134" s="363"/>
+      <c r="E134" s="363"/>
+      <c r="F134" s="363"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5445,22 +5445,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="365" t="s">
+      <c r="B138" s="361" t="s">
         <v>365</v>
       </c>
-      <c r="C138" s="365"/>
-      <c r="D138" s="365"/>
-      <c r="E138" s="365"/>
-      <c r="F138" s="365"/>
+      <c r="C138" s="361"/>
+      <c r="D138" s="361"/>
+      <c r="E138" s="361"/>
+      <c r="F138" s="361"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="360" t="s">
+      <c r="B139" s="358" t="s">
         <v>366</v>
       </c>
-      <c r="C139" s="360"/>
-      <c r="D139" s="360"/>
-      <c r="E139" s="360"/>
-      <c r="F139" s="360"/>
+      <c r="C139" s="358"/>
+      <c r="D139" s="358"/>
+      <c r="E139" s="358"/>
+      <c r="F139" s="358"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5491,7 +5491,7 @@
       </c>
       <c r="C143" s="213">
         <f>Scenarios!C77</f>
-        <v>1.51912526452</v>
+        <v>1.5183402178400001</v>
       </c>
       <c r="D143" s="212" t="str">
         <f>Market_currency</f>
@@ -5527,7 +5527,7 @@
       </c>
       <c r="C147" s="216">
         <f>Scenarios!C81</f>
-        <v>2.517584501908376</v>
+        <v>2.51628347598181</v>
       </c>
     </row>
     <row r="148" spans="2:4">
@@ -5537,7 +5537,7 @@
       </c>
       <c r="C148" s="216">
         <f>Scenarios!C82</f>
-        <v>13.196296761398656</v>
+        <v>13.189714132161143</v>
       </c>
     </row>
     <row r="149" spans="2:4">
@@ -5546,7 +5546,7 @@
       </c>
       <c r="C149" s="215">
         <f>Scenarios!C83</f>
-        <v>15.713881263307032</v>
+        <v>15.705997608142953</v>
       </c>
       <c r="D149" s="300" t="str">
         <f>IF($D$11="","",C149*$E$25)</f>
@@ -5572,7 +5572,7 @@
       </c>
       <c r="C151" s="92">
         <f>Scenarios!F83</f>
-        <v>0.53425879012312194</v>
+        <v>0.53426013030156994</v>
       </c>
     </row>
     <row r="153" spans="2:4">
@@ -5596,7 +5596,7 @@
       </c>
       <c r="C155" s="216">
         <f>Scenarios!C91</f>
-        <v>3.114815693925848</v>
+        <v>3.1132060335664034</v>
       </c>
     </row>
     <row r="156" spans="2:4">
@@ -5606,7 +5606,7 @@
       </c>
       <c r="C156" s="216">
         <f>Scenarios!C92</f>
-        <v>18.69988380326302</v>
+        <v>18.6905558528473</v>
       </c>
     </row>
     <row r="157" spans="2:4">
@@ -5615,7 +5615,7 @@
       </c>
       <c r="C157" s="215">
         <f>Scenarios!C93</f>
-        <v>21.814699497188869</v>
+        <v>21.803761886413703</v>
       </c>
       <c r="D157" s="300" t="str">
         <f>IF($D$11="","",C157*$E$25)</f>
@@ -5641,7 +5641,7 @@
       </c>
       <c r="C159" s="92">
         <f>Scenarios!F93</f>
-        <v>0.35343761565479292</v>
+        <v>0.35343927375558737</v>
       </c>
     </row>
     <row r="161" spans="2:4">
@@ -5665,7 +5665,7 @@
       </c>
       <c r="C163" s="216">
         <f>Scenarios!C97</f>
-        <v>3.9505243524740594</v>
+        <v>3.948482818375719</v>
       </c>
     </row>
     <row r="164" spans="2:4">
@@ -5675,7 +5675,7 @@
       </c>
       <c r="C164" s="216">
         <f>Scenarios!C98</f>
-        <v>27.158977008415839</v>
+        <v>27.145429459482301</v>
       </c>
     </row>
     <row r="165" spans="2:4">
@@ -5684,7 +5684,7 @@
       </c>
       <c r="C165" s="215">
         <f>Scenarios!C99</f>
-        <v>31.109501360889897</v>
+        <v>31.093912277858021</v>
       </c>
       <c r="D165" s="300" t="str">
         <f>IF($D$11="","",C165*$E$25)</f>
@@ -5710,7 +5710,7 @@
       </c>
       <c r="C167" s="92">
         <f>Scenarios!F99</f>
-        <v>7.7950471961374612E-2</v>
+        <v>7.7952574932532603E-2</v>
       </c>
     </row>
     <row r="169" spans="2:4">
@@ -5734,7 +5734,7 @@
       </c>
       <c r="C171" s="216">
         <f>Scenarios!C103</f>
-        <v>3.6650463618733289</v>
+        <v>3.6631523557991534</v>
       </c>
     </row>
     <row r="172" spans="2:4">
@@ -5744,7 +5744,7 @@
       </c>
       <c r="C172" s="216">
         <f>Scenarios!C104</f>
-        <v>24.183146071728043</v>
+        <v>24.171082938618422</v>
       </c>
     </row>
     <row r="173" spans="2:4">
@@ -5753,7 +5753,7 @@
       </c>
       <c r="C173" s="215">
         <f>Scenarios!C105</f>
-        <v>27.848192433601373</v>
+        <v>27.834235294417574</v>
       </c>
       <c r="D173" s="300" t="str">
         <f>IF($D$11="","",C173*$E$25)</f>
@@ -5779,7 +5779,7 @@
       </c>
       <c r="C175" s="92">
         <f>Scenarios!F105</f>
-        <v>0.15773978826724333</v>
+        <v>0.15774208837607995</v>
       </c>
     </row>
     <row r="177" spans="1:6" ht="13.9">
@@ -5793,13 +5793,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="359" t="s">
+      <c r="B179" s="365" t="s">
         <v>373</v>
       </c>
-      <c r="C179" s="360"/>
-      <c r="D179" s="360"/>
-      <c r="E179" s="360"/>
-      <c r="F179" s="360"/>
+      <c r="C179" s="358"/>
+      <c r="D179" s="358"/>
+      <c r="E179" s="358"/>
+      <c r="F179" s="358"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5836,13 +5836,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="361" t="s">
+      <c r="B188" s="359" t="s">
         <v>378</v>
       </c>
-      <c r="C188" s="361"/>
-      <c r="D188" s="361"/>
-      <c r="E188" s="361"/>
-      <c r="F188" s="361"/>
+      <c r="C188" s="359"/>
+      <c r="D188" s="359"/>
+      <c r="E188" s="359"/>
+      <c r="F188" s="359"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5850,22 +5850,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="358" t="s">
+      <c r="B191" s="364" t="s">
         <v>379</v>
       </c>
-      <c r="C191" s="358"/>
-      <c r="D191" s="358"/>
-      <c r="E191" s="358"/>
-      <c r="F191" s="358"/>
+      <c r="C191" s="364"/>
+      <c r="D191" s="364"/>
+      <c r="E191" s="364"/>
+      <c r="F191" s="364"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="358" t="s">
+      <c r="B192" s="364" t="s">
         <v>380</v>
       </c>
-      <c r="C192" s="358"/>
-      <c r="D192" s="358"/>
-      <c r="E192" s="358"/>
-      <c r="F192" s="358"/>
+      <c r="C192" s="364"/>
+      <c r="D192" s="364"/>
+      <c r="E192" s="364"/>
+      <c r="F192" s="364"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5889,6 +5889,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5905,17 +5916,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -6488,15 +6488,15 @@
       </c>
       <c r="C25" s="39">
         <f>0.164*Exchange_Rate</f>
-        <v>1.51912526452</v>
+        <v>1.5183402178400001</v>
       </c>
       <c r="D25" s="39">
         <f>0.137*Exchange_Rate</f>
-        <v>1.2690253734100001</v>
+        <v>1.2683695722200001</v>
       </c>
       <c r="E25" s="39">
         <f>0.11*Exchange_Rate</f>
-        <v>1.0189254823</v>
+        <v>1.0183989266</v>
       </c>
       <c r="F25" s="39"/>
       <c r="G25" s="39"/>
@@ -7870,15 +7870,15 @@
       </c>
       <c r="C65" s="73">
         <f>IF(C$4="","",C25)</f>
-        <v>1.51912526452</v>
+        <v>1.5183402178400001</v>
       </c>
       <c r="D65" s="73">
         <f t="shared" ref="D65:M65" si="33">IF(D$4="","",D25)</f>
-        <v>1.2690253734100001</v>
+        <v>1.2683695722200001</v>
       </c>
       <c r="E65" s="73">
         <f t="shared" si="33"/>
-        <v>1.0189254823</v>
+        <v>1.0183989266</v>
       </c>
       <c r="F65" s="73">
         <f t="shared" si="33"/>
@@ -9220,11 +9220,11 @@
       </c>
       <c r="C47" s="147">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>15.925728894632631</v>
+        <v>15.917498868520029</v>
       </c>
       <c r="D47" s="147">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>-6.0199187527594056</v>
+        <v>-6.0168078063871082</v>
       </c>
       <c r="F47" s="253"/>
     </row>
@@ -9415,7 +9415,7 @@
       </c>
       <c r="D66" s="76">
         <f>C66-D75</f>
-        <v>404462.06293345941</v>
+        <v>404629.46262395149</v>
       </c>
       <c r="F66" s="5" t="s">
         <v>225</v>
@@ -9482,11 +9482,11 @@
       </c>
       <c r="C73" s="349">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35-Normalized_FCF!G91)/12</f>
-        <v>-656758.09882167703</v>
+        <v>-656590.69913118507</v>
       </c>
       <c r="D73" s="349">
         <f>(Normalized_FCF!C25+Normalized_FCF!C35-Normalized_FCF!C91)/12</f>
-        <v>-607100.93706654059</v>
+        <v>-606933.53737604851</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>348</v>
@@ -9498,11 +9498,11 @@
       </c>
       <c r="C74" s="258">
         <f>-$C$66/C73</f>
-        <v>1.5402368114148823</v>
+        <v>1.5406294992276344</v>
       </c>
       <c r="D74" s="258">
         <f>-$C$66/D73</f>
-        <v>1.6662188085028913</v>
+        <v>1.6666783720228795</v>
       </c>
       <c r="F74" s="253" t="s">
         <v>316</v>
@@ -9515,7 +9515,7 @@
       <c r="C75" s="320"/>
       <c r="D75" s="321">
         <f>MAX(-D73*D76,G5)</f>
-        <v>607100.93706654059</v>
+        <v>606933.53737604851</v>
       </c>
       <c r="F75" s="253" t="s">
         <v>349</v>
@@ -9630,11 +9630,11 @@
       </c>
       <c r="C86" s="76">
         <f>-DCF!C7*Exchange_Rate</f>
-        <v>-8026353.9128449997</v>
+        <v>-8022206.0899899993</v>
       </c>
       <c r="D86" s="223">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>-3.1367354350455519</v>
+        <v>-3.1351144471014809</v>
       </c>
       <c r="E86" s="240" t="str">
         <f>Market_currency</f>
@@ -9647,11 +9647,11 @@
       </c>
       <c r="C87" s="76">
         <f>DCF!C8*Exchange_Rate</f>
-        <v>3746515.47769571</v>
+        <v>3746129.185517882</v>
       </c>
       <c r="D87" s="223">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>1.4641552047720789</v>
+        <v>1.4640042400406914</v>
       </c>
       <c r="E87" s="240" t="str">
         <f>Market_currency</f>
@@ -9664,11 +9664,11 @@
       </c>
       <c r="C88" s="76">
         <f>DCF!C9*Exchange_Rate</f>
-        <v>34850.956678232003</v>
+        <v>34832.946558543998</v>
       </c>
       <c r="D88" s="223">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>1.3619911599325317E-2</v>
+        <v>1.361287316304052E-2</v>
       </c>
       <c r="E88" s="240" t="str">
         <f>Market_currency</f>
@@ -9681,11 +9681,11 @@
       </c>
       <c r="C89" s="180">
         <f>SUM(C86:C88)</f>
-        <v>-4244987.4784710575</v>
+        <v>-4241243.9579135729</v>
       </c>
       <c r="D89" s="242">
         <f>SUM(D86:D88)</f>
-        <v>-1.6589603186741475</v>
+        <v>-1.657497333897749</v>
       </c>
       <c r="E89" s="240" t="str">
         <f>Market_currency</f>
@@ -13197,20 +13197,20 @@
       </c>
       <c r="C90" s="113">
         <f>G90</f>
-        <v>1.51912526452</v>
+        <v>1.5183402178400001</v>
       </c>
       <c r="E90" s="268"/>
       <c r="G90" s="112">
         <f>Data!C65</f>
-        <v>1.51912526452</v>
+        <v>1.5183402178400001</v>
       </c>
       <c r="H90" s="112">
         <f>Data!D65</f>
-        <v>1.2690253734100001</v>
+        <v>1.2683695722200001</v>
       </c>
       <c r="I90" s="112">
         <f>Data!E65</f>
-        <v>1.0189254823</v>
+        <v>1.0183989266</v>
       </c>
       <c r="J90" s="112">
         <f>Data!F65</f>
@@ -13253,20 +13253,20 @@
       </c>
       <c r="C91" s="74">
         <f>C90*Common_Shares/scaling_factor</f>
-        <v>3887174.1858601244</v>
+        <v>3885165.3895742204</v>
       </c>
       <c r="E91" s="268"/>
       <c r="G91" s="74">
         <f t="shared" ref="G91:Q91" si="37">IF(G$4="","",G90*Common_Shares/scaling_factor)</f>
-        <v>3887174.1858601244</v>
+        <v>3885165.3895742204</v>
       </c>
       <c r="H91" s="74">
         <f t="shared" si="37"/>
-        <v>3247212.5820904705</v>
+        <v>3245534.5022662696</v>
       </c>
       <c r="I91" s="74">
         <f t="shared" si="37"/>
-        <v>2607250.9783208151</v>
+        <v>2605903.6149583184</v>
       </c>
       <c r="J91" s="74">
         <f t="shared" si="37"/>
@@ -13308,20 +13308,20 @@
       </c>
       <c r="C92" s="23">
         <f>C90/(C19*scaling_factor/Common_Shares)</f>
-        <v>5.6074778177084079</v>
+        <v>5.6045800106961883</v>
       </c>
       <c r="E92" s="268"/>
       <c r="G92" s="170">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",G90/(G19*scaling_factor/Common_Shares))</f>
-        <v>3.8993401270565404</v>
+        <v>3.8973250437105973</v>
       </c>
       <c r="H92" s="170">
         <f t="shared" si="38"/>
-        <v>3.9551196775825903</v>
+        <v>3.9530757687329339</v>
       </c>
       <c r="I92" s="170">
         <f t="shared" si="38"/>
-        <v>3.8807155462557232</v>
+        <v>3.8787100876363674</v>
       </c>
       <c r="J92" s="170">
         <f t="shared" si="38"/>
@@ -13384,20 +13384,20 @@
       </c>
       <c r="C94" s="23">
         <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
-        <v>3.03825052904E-2</v>
+        <v>3.0066142927524752E-2</v>
       </c>
       <c r="E94" s="268"/>
       <c r="G94" s="23">
         <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>3.03825052904E-2</v>
+        <v>3.0066142927524752E-2</v>
       </c>
       <c r="H94" s="23">
         <f t="shared" si="39"/>
-        <v>2.5380507468200003E-2</v>
+        <v>2.5116229152871289E-2</v>
       </c>
       <c r="I94" s="23">
         <f t="shared" si="39"/>
-        <v>2.0378509646E-2</v>
+        <v>2.0166315378217822E-2</v>
       </c>
       <c r="J94" s="23">
         <f t="shared" si="39"/>
@@ -14526,38 +14526,38 @@
       </c>
       <c r="C125" s="177">
         <f>C16*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>2.5094339009841584</v>
+        <v>2.5081370870882553</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="265"/>
       <c r="F125" s="27"/>
       <c r="G125" s="177">
         <f t="shared" ref="G125:Q125" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>3.6087118528427125</v>
+        <v>3.606846959061194</v>
       </c>
       <c r="H125" s="177">
         <f t="shared" si="49"/>
-        <v>2.972079449744863</v>
+        <v>2.9705435519757901</v>
       </c>
       <c r="I125" s="177">
         <f t="shared" si="49"/>
-        <v>2.4320939741078873</v>
+        <v>2.4308371275894238</v>
       </c>
       <c r="J125" s="177">
         <f t="shared" si="49"/>
-        <v>1.3045271803642533</v>
+        <v>1.3038530327111046</v>
       </c>
       <c r="K125" s="177">
         <f t="shared" si="49"/>
-        <v>6.3017865591539159</v>
+        <v>6.2985299504121111</v>
       </c>
       <c r="L125" s="177">
         <f t="shared" si="49"/>
-        <v>8.4731314814599212</v>
+        <v>8.4687527749147264</v>
       </c>
       <c r="M125" s="177">
         <f t="shared" si="49"/>
-        <v>7.8391199629032986</v>
+        <v>7.8350688979616967</v>
       </c>
       <c r="N125" s="177" t="str">
         <f t="shared" si="49"/>
@@ -14583,38 +14583,38 @@
       </c>
       <c r="C126" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>5.0188678019683179E-2</v>
+        <v>4.9666080932440702E-2</v>
       </c>
       <c r="D126" s="27"/>
       <c r="E126" s="265"/>
       <c r="F126" s="27"/>
       <c r="G126" s="77">
         <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
-        <v>7.2174237056854246E-2</v>
+        <v>7.1422712060617705E-2</v>
       </c>
       <c r="H126" s="77">
         <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
-        <v>5.9441588994897258E-2</v>
+        <v>5.8822644593580005E-2</v>
       </c>
       <c r="I126" s="77">
         <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
-        <v>4.8641879482157743E-2</v>
+        <v>4.8135388665137106E-2</v>
       </c>
       <c r="J126" s="77">
         <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
-        <v>2.6090543607285067E-2</v>
+        <v>2.5818871934873359E-2</v>
       </c>
       <c r="K126" s="77">
         <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
-        <v>0.12603573118307831</v>
+        <v>0.12472336535469526</v>
       </c>
       <c r="L126" s="77">
         <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
-        <v>0.16946262962919842</v>
+        <v>0.16769807475078666</v>
       </c>
       <c r="M126" s="77">
         <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
-        <v>0.15678239925806597</v>
+        <v>0.15514987916755835</v>
       </c>
       <c r="N126" s="77" t="str">
         <f t="shared" ref="N126" si="57">IF(N$4="","",N125/Market_Price)</f>
@@ -14640,31 +14640,31 @@
       <c r="C127" s="169"/>
       <c r="G127" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.5920907416844613E-3</v>
+        <v>6.526822516519269E-3</v>
       </c>
       <c r="H127" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.263292825141549E-3</v>
+        <v>5.2111810149916334E-3</v>
       </c>
       <c r="I127" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.6669579463065845E-3</v>
+        <v>3.6306514319867176E-3</v>
       </c>
       <c r="J127" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.3065517597146189E-3</v>
+        <v>2.2837146135788306E-3</v>
       </c>
       <c r="K127" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-4.2494520920547876E-4</v>
+        <v>-4.2073783089651361E-4</v>
       </c>
       <c r="L127" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.0143941122953359E-3</v>
+        <v>1.9944496161339955E-3</v>
       </c>
       <c r="M127" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.627169355922877E-3</v>
+        <v>1.6110587682404724E-3</v>
       </c>
       <c r="N127" s="23" t="str">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -15492,7 +15492,7 @@
       </c>
       <c r="C8" s="338">
         <f>BS!D66</f>
-        <v>404462.06293345941</v>
+        <v>404629.46262395149</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
@@ -15524,7 +15524,7 @@
       </c>
       <c r="C10" s="347">
         <f>C6-C7+C8+C9</f>
-        <v>8784558.9118056037</v>
+        <v>8784726.3114960957</v>
       </c>
       <c r="D10" t="str">
         <f>Reporting_currency</f>
@@ -15538,7 +15538,7 @@
       </c>
       <c r="C11" s="208">
         <f>Exchange_Rate</f>
-        <v>9.2629589299999999</v>
+        <v>9.2581720599999997</v>
       </c>
       <c r="D11" t="str">
         <f>Thesis!C15</f>
@@ -15552,7 +15552,7 @@
       </c>
       <c r="C12" s="111">
         <f>(C10*scaling_factor)/Common_Shares*Exchange_Rate</f>
-        <v>31.800158361114637</v>
+        <v>31.784330493945657</v>
       </c>
       <c r="D12" t="str">
         <f>Market_currency</f>
@@ -15605,7 +15605,7 @@
       </c>
       <c r="C18" s="140">
         <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>33.06364475689778</v>
+        <v>33.047163950946597</v>
       </c>
       <c r="D18" t="str">
         <f>Market_currency</f>
@@ -16701,23 +16701,23 @@
       </c>
       <c r="B65" s="124">
         <f>C12</f>
-        <v>31.800158361114637</v>
+        <v>31.784330493945657</v>
       </c>
       <c r="C65" s="124">
         <f>C12</f>
-        <v>31.800158361114637</v>
+        <v>31.784330493945657</v>
       </c>
       <c r="D65" s="124">
         <f>C12</f>
-        <v>31.800158361114637</v>
+        <v>31.784330493945657</v>
       </c>
       <c r="E65" s="141">
         <f>C12</f>
-        <v>31.800158361114637</v>
+        <v>31.784330493945657</v>
       </c>
       <c r="F65" s="124">
         <f>C12</f>
-        <v>31.800158361114637</v>
+        <v>31.784330493945657</v>
       </c>
       <c r="H65" s="120"/>
     </row>
@@ -16728,23 +16728,23 @@
       </c>
       <c r="B66" s="124">
         <f t="shared" ref="B66:F71" si="4">(B56-$C$7+$C$8+$C$9)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>31.800158361114637</v>
+        <v>31.784330493945657</v>
       </c>
       <c r="C66" s="124">
         <f t="shared" si="4"/>
-        <v>32.326880759066171</v>
+        <v>32.310780694679856</v>
       </c>
       <c r="D66" s="124">
         <f t="shared" si="4"/>
-        <v>33.403173593370909</v>
+        <v>33.386517327244015</v>
       </c>
       <c r="E66" s="124">
         <f t="shared" si="4"/>
-        <v>34.51104974988484</v>
+        <v>34.493820960531032</v>
       </c>
       <c r="F66" s="124">
         <f t="shared" si="4"/>
-        <v>36.235112495088451</v>
+        <v>36.216992752390738</v>
       </c>
       <c r="H66" s="120"/>
     </row>
@@ -16755,23 +16755,23 @@
       </c>
       <c r="B67" s="124">
         <f t="shared" si="4"/>
-        <v>31.800158361114644</v>
+        <v>31.784330493945667</v>
       </c>
       <c r="C67" s="124">
         <f t="shared" si="4"/>
-        <v>32.831892578634424</v>
+        <v>32.815531536525214</v>
       </c>
       <c r="D67" s="124">
         <f t="shared" si="4"/>
-        <v>35.047253086567757</v>
+        <v>35.029747200479996</v>
       </c>
       <c r="E67" s="124">
         <f t="shared" si="4"/>
-        <v>37.48535812214935</v>
+        <v>37.466592283173988</v>
       </c>
       <c r="F67" s="124">
         <f t="shared" si="4"/>
-        <v>41.619262313292801</v>
+        <v>41.59836017401588</v>
       </c>
       <c r="H67" s="120"/>
     </row>
@@ -16782,23 +16782,23 @@
       </c>
       <c r="B68" s="124">
         <f t="shared" si="4"/>
-        <v>31.800158361114644</v>
+        <v>31.784330493945667</v>
       </c>
       <c r="C68" s="124">
         <f t="shared" si="4"/>
-        <v>33.455400986420216</v>
+        <v>33.438717730457476</v>
       </c>
       <c r="D68" s="124">
         <f t="shared" si="4"/>
-        <v>37.182991820367164</v>
+        <v>37.164382236880989</v>
       </c>
       <c r="E68" s="124">
         <f t="shared" si="4"/>
-        <v>41.558577759011008</v>
+        <v>41.537706980023437</v>
       </c>
       <c r="F68" s="124">
         <f t="shared" si="4"/>
-        <v>49.626716874158213</v>
+        <v>49.601676678747879</v>
       </c>
       <c r="H68" s="120"/>
     </row>
@@ -16809,23 +16809,23 @@
       </c>
       <c r="B69" s="124">
         <f t="shared" si="4"/>
-        <v>31.800158361114647</v>
+        <v>31.784330493945671</v>
       </c>
       <c r="C69" s="124">
         <f t="shared" si="4"/>
-        <v>34.088647903971086</v>
+        <v>34.07163740153181</v>
       </c>
       <c r="D69" s="124">
         <f t="shared" si="4"/>
-        <v>39.470523246908321</v>
+        <v>39.450731523282862</v>
       </c>
       <c r="E69" s="124">
         <f t="shared" si="4"/>
-        <v>46.175103629259652</v>
+        <v>46.151847142923117</v>
       </c>
       <c r="F69" s="124">
         <f t="shared" si="4"/>
-        <v>59.561384065688372</v>
+        <v>59.531209877922194</v>
       </c>
       <c r="H69" s="120"/>
     </row>
@@ -16836,23 +16836,23 @@
       </c>
       <c r="B70" s="124">
         <f t="shared" si="4"/>
-        <v>31.800158361114647</v>
+        <v>31.784330493945671</v>
       </c>
       <c r="C70" s="124">
         <f t="shared" si="4"/>
-        <v>34.675381143349853</v>
+        <v>34.658067431562152</v>
       </c>
       <c r="D70" s="124">
         <f t="shared" si="4"/>
-        <v>41.709815220855326</v>
+        <v>41.688866286056601</v>
       </c>
       <c r="E70" s="124">
         <f t="shared" si="4"/>
-        <v>50.972581793133052</v>
+        <v>50.94684608774007</v>
       </c>
       <c r="F70" s="124">
         <f t="shared" si="4"/>
-        <v>70.940740521955817</v>
+        <v>70.904685761852917</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="13.15">
@@ -16862,23 +16862,23 @@
       </c>
       <c r="B71" s="124">
         <f t="shared" si="4"/>
-        <v>31.800158361114644</v>
+        <v>31.784330493945667</v>
       </c>
       <c r="C71" s="124">
         <f t="shared" si="4"/>
-        <v>35.190696582644996</v>
+        <v>35.173116568476438</v>
       </c>
       <c r="D71" s="124">
         <f t="shared" si="4"/>
-        <v>43.79117286356869</v>
+        <v>43.769148334185708</v>
       </c>
       <c r="E71" s="124">
         <f t="shared" si="4"/>
-        <v>55.720532161587734</v>
+        <v>55.692342831888311</v>
       </c>
       <c r="F71" s="124">
         <f t="shared" si="4"/>
-        <v>83.431081089425874</v>
+        <v>83.388571627644609</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="13.15">
@@ -16913,7 +16913,7 @@
       </c>
       <c r="E74" s="135">
         <f>INDEX(B$65:F$71, MATCH(D74, A$65:A$71, 0), MATCH(C74, B$64:F$64, 0))</f>
-        <v>41.619262313292801</v>
+        <v>41.59836017401588</v>
       </c>
       <c r="F74" s="142">
         <f>Scenarios!C58</f>
@@ -16935,7 +16935,7 @@
       </c>
       <c r="E75" s="135">
         <f>INDEX(B$65:F$71, MATCH(D75, A$65:A$71, 0), MATCH(C75, B$64:F$64, 0))</f>
-        <v>34.51104974988484</v>
+        <v>34.493820960531032</v>
       </c>
       <c r="F75" s="142">
         <f>Scenarios!C40*(1-F$74-F$78)</f>
@@ -16958,7 +16958,7 @@
       </c>
       <c r="E76" s="135">
         <f>INDEX(B$65:F$71, MATCH(D76, A$65:A$71, 0), MATCH(C76, B$64:F$64, 0))</f>
-        <v>33.403173593370909</v>
+        <v>33.386517327244015</v>
       </c>
       <c r="F76" s="142">
         <f>Scenarios!C28*(1-F$74-F$78)</f>
@@ -16981,7 +16981,7 @@
       </c>
       <c r="E77" s="135">
         <f>INDEX(B$65:F$71, MATCH(D77, A$65:A$71, 0), MATCH(C77, B$64:F$64, 0))</f>
-        <v>32.326880759066171</v>
+        <v>32.310780694679856</v>
       </c>
       <c r="F77" s="142">
         <f>Scenarios!C34*(1-F$74-F$78)</f>
@@ -17004,7 +17004,7 @@
       </c>
       <c r="E78" s="135">
         <f>INDEX(B$65:F$71, MATCH(D78, A$65:A$71, 0), MATCH(C78, B$64:F$64, 0))</f>
-        <v>31.800158361114644</v>
+        <v>31.784330493945667</v>
       </c>
       <c r="F78" s="142">
         <f>Scenarios!C52</f>
@@ -17186,7 +17186,7 @@
       </c>
       <c r="C4" s="114">
         <f>Normalized_FCF!C91*(1-dividend_tax_rate)</f>
-        <v>3887174.1858601244</v>
+        <v>3885165.3895742204</v>
       </c>
       <c r="D4" t="str">
         <f>Market_currency</f>
@@ -17218,7 +17218,7 @@
       </c>
       <c r="C6" s="319">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
-        <v>51828989.144801661</v>
+        <v>51802205.194322944</v>
       </c>
       <c r="D6" t="str">
         <f>Reporting_currency</f>
@@ -17234,7 +17234,7 @@
       </c>
       <c r="C7" s="111">
         <f>(C6*scaling_factor)/Common_Shares*Exchange_Rate</f>
-        <v>187.62126579698861</v>
+        <v>187.42739976507471</v>
       </c>
       <c r="D7" t="str">
         <f>Market_currency</f>
@@ -17287,7 +17287,7 @@
       </c>
       <c r="C13" s="140">
         <f>F47/Common_Shares*scaling_factor</f>
-        <v>21.019874880770839</v>
+        <v>21.009012324947058</v>
       </c>
       <c r="D13" t="str">
         <f>Market_currency</f>
@@ -17322,7 +17322,7 @@
       </c>
       <c r="C16" s="123">
         <f>C4*(1+D16)</f>
-        <v>3979504.7544315001</v>
+        <v>3977448.2439721748</v>
       </c>
       <c r="D16" s="138">
         <f>IF($C$12&lt;B16,0,DDM!$C$11)</f>
@@ -17334,7 +17334,7 @@
       </c>
       <c r="F16" s="125">
         <f t="shared" ref="F16:F46" si="1">C16*E16</f>
-        <v>3701864.8878432559</v>
+        <v>3699951.8548578368</v>
       </c>
       <c r="H16" s="120"/>
     </row>
@@ -17344,7 +17344,7 @@
       </c>
       <c r="C17" s="123">
         <f t="shared" ref="C17:C45" si="2">IF(ROW()-ROW($C$16)&lt;$C$12, $C$16*(1+D17)^(ROW()-ROW($C$16)), 0)</f>
-        <v>4074028.4158474728</v>
+        <v>4071923.0578781306</v>
       </c>
       <c r="D17" s="138">
         <f>IF($C$12&lt;B17,0,DDM!$C$11)</f>
@@ -17356,7 +17356,7 @@
       </c>
       <c r="F17" s="125">
         <f t="shared" si="1"/>
-        <v>3525389.6513553038</v>
+        <v>3523567.8164440286</v>
       </c>
       <c r="H17" s="120"/>
     </row>
@@ -17366,7 +17366,7 @@
       </c>
       <c r="C18" s="123">
         <f t="shared" si="2"/>
-        <v>4170797.2618074603</v>
+        <v>4168641.8960717916</v>
       </c>
       <c r="D18" s="138">
         <f>IF($C$12&lt;B18,0,DDM!$C$11)</f>
@@ -17378,7 +17378,7 @@
       </c>
       <c r="F18" s="125">
         <f t="shared" si="1"/>
-        <v>3357327.3391736262</v>
+        <v>3355592.3547435408</v>
       </c>
       <c r="H18" s="120"/>
     </row>
@@ -17388,7 +17388,7 @@
       </c>
       <c r="C19" s="123">
         <f t="shared" si="2"/>
-        <v>4269864.6213251837</v>
+        <v>4267658.0600077538</v>
       </c>
       <c r="D19" s="138">
         <f>IF($C$12&lt;B19,0,DDM!$C$11)</f>
@@ -17400,7 +17400,7 @@
       </c>
       <c r="F19" s="125">
         <f t="shared" si="1"/>
-        <v>3197276.8905216977</v>
+        <v>3195624.6162382225</v>
       </c>
       <c r="H19" s="120"/>
     </row>
@@ -17410,7 +17410,7 @@
       </c>
       <c r="C20" s="123">
         <f t="shared" si="2"/>
-        <v>4371285.090118126</v>
+        <v>4369026.1171897706</v>
       </c>
       <c r="D20" s="138">
         <f>IF($C$12&lt;B20,0,DDM!$C$11)</f>
@@ -17422,7 +17422,7 @@
       </c>
       <c r="F20" s="125">
         <f t="shared" si="1"/>
-        <v>3044856.3639851362</v>
+        <v>3043282.8568916451</v>
       </c>
       <c r="H20" s="120"/>
     </row>
@@ -17982,7 +17982,7 @@
       </c>
       <c r="C46" s="123">
         <f>C$16*(1+F4)^$C$12/Equity_Cost</f>
-        <v>53060063.392420001</v>
+        <v>53032643.252962336</v>
       </c>
       <c r="D46" s="139">
         <f>Terminal_Growth</f>
@@ -17994,7 +17994,7 @@
       </c>
       <c r="F46" s="125">
         <f t="shared" si="1"/>
-        <v>36959445.189034544</v>
+        <v>36940345.45419506</v>
       </c>
       <c r="H46" s="120"/>
     </row>
@@ -18005,7 +18005,7 @@
       </c>
       <c r="F47" s="137">
         <f>SUM(F16:F46)</f>
-        <v>53786160.321913563</v>
+        <v>53758364.953370333</v>
       </c>
       <c r="H47" s="120"/>
     </row>
@@ -18026,7 +18026,7 @@
     <row r="50" spans="1:8" ht="13.15">
       <c r="A50" s="133">
         <f>F47</f>
-        <v>53786160.321913563</v>
+        <v>53758364.953370333</v>
       </c>
       <c r="B50" s="131">
         <f>C73</f>
@@ -18056,19 +18056,19 @@
       </c>
       <c r="B51" s="123">
         <f t="dataTable" ref="B51:F56" dt2D="1" dtr="1" r1="C11" r2="C12"/>
-        <v>51828989.144801661</v>
+        <v>51802205.194322944</v>
       </c>
       <c r="C51" s="123">
-        <v>52644894.958311461</v>
+        <v>52617689.367718488</v>
       </c>
       <c r="D51" s="123">
-        <v>54312098.752878368</v>
+        <v>54284031.592252709</v>
       </c>
       <c r="E51" s="123">
-        <v>56028225.88220498</v>
+        <v>55999271.869167089</v>
       </c>
       <c r="F51" s="123">
-        <v>58698841.033825554</v>
+        <v>58668506.912374422</v>
       </c>
       <c r="H51" s="120"/>
     </row>
@@ -18077,19 +18077,19 @@
         <v>10</v>
       </c>
       <c r="B52" s="123">
-        <v>51828989.144801676</v>
+        <v>51802205.194322944</v>
       </c>
       <c r="C52" s="123">
-        <v>53427170.557525307</v>
+        <v>53399560.706088059</v>
       </c>
       <c r="D52" s="123">
-        <v>56858817.900551625</v>
+        <v>56829434.657929003</v>
       </c>
       <c r="E52" s="123">
-        <v>60635501.937940091</v>
+        <v>60604166.997630522</v>
       </c>
       <c r="F52" s="123">
-        <v>67039020.138730198</v>
+        <v>67004376.017261416</v>
       </c>
       <c r="H52" s="120"/>
     </row>
@@ -18098,19 +18098,19 @@
         <v>15</v>
       </c>
       <c r="B53" s="123">
-        <v>51828989.144801676</v>
+        <v>51802205.194322944</v>
       </c>
       <c r="C53" s="123">
-        <v>54393000.255793579</v>
+        <v>54364891.287255332</v>
       </c>
       <c r="D53" s="123">
-        <v>60167129.177653104</v>
+        <v>60136036.280899152</v>
       </c>
       <c r="E53" s="123">
-        <v>66945018.287240066</v>
+        <v>66910422.743622713</v>
       </c>
       <c r="F53" s="123">
-        <v>79442762.134579033</v>
+        <v>79401708.063449845</v>
       </c>
       <c r="H53" s="120"/>
     </row>
@@ -18119,19 +18119,19 @@
         <v>20</v>
       </c>
       <c r="B54" s="123">
-        <v>51828989.144801676</v>
+        <v>51802205.194322951</v>
       </c>
       <c r="C54" s="123">
-        <v>55373915.142698519</v>
+        <v>55345299.261403762</v>
       </c>
       <c r="D54" s="123">
-        <v>63710571.030059457</v>
+        <v>63677646.969459444</v>
       </c>
       <c r="E54" s="123">
-        <v>74096129.214747742</v>
+        <v>74057838.152384788</v>
       </c>
       <c r="F54" s="123">
-        <v>94831803.398779005</v>
+        <v>94782796.648542315</v>
       </c>
       <c r="H54" s="120"/>
     </row>
@@ -18140,19 +18140,19 @@
         <v>25</v>
       </c>
       <c r="B55" s="123">
-        <v>51828989.144801676</v>
+        <v>51802205.194322944</v>
       </c>
       <c r="C55" s="123">
-        <v>56282779.210090257</v>
+        <v>56253693.650135458</v>
       </c>
       <c r="D55" s="123">
-        <v>67179288.796371922</v>
+        <v>67144572.187500939</v>
       </c>
       <c r="E55" s="123">
-        <v>81527539.648998499</v>
+        <v>81485408.215979248</v>
       </c>
       <c r="F55" s="123">
-        <v>112458703.4941176</v>
+        <v>112400587.5942132</v>
       </c>
       <c r="H55" s="120"/>
     </row>
@@ -18161,19 +18161,19 @@
         <v>30</v>
       </c>
       <c r="B56" s="123">
-        <v>51828989.144801669</v>
+        <v>51802205.194322944</v>
       </c>
       <c r="C56" s="123">
-        <v>57081015.367024951</v>
+        <v>57051517.298201077</v>
       </c>
       <c r="D56" s="123">
-        <v>70403362.439883739</v>
+        <v>70366979.70882453</v>
       </c>
       <c r="E56" s="123">
-        <v>88882230.322765172</v>
+        <v>88836298.165980265</v>
       </c>
       <c r="F56" s="123">
-        <v>131806545.01623532</v>
+        <v>131738430.62634011</v>
       </c>
       <c r="H56" s="120"/>
     </row>
@@ -18223,23 +18223,23 @@
       </c>
       <c r="B60" s="124">
         <f>C7</f>
-        <v>187.62126579698861</v>
+        <v>187.42739976507471</v>
       </c>
       <c r="C60" s="124">
         <f>C7</f>
-        <v>187.62126579698861</v>
+        <v>187.42739976507471</v>
       </c>
       <c r="D60" s="124">
         <f>C7</f>
-        <v>187.62126579698861</v>
+        <v>187.42739976507471</v>
       </c>
       <c r="E60" s="141">
         <f>C7</f>
-        <v>187.62126579698861</v>
+        <v>187.42739976507471</v>
       </c>
       <c r="F60" s="124">
         <f>C7</f>
-        <v>187.62126579698861</v>
+        <v>187.42739976507471</v>
       </c>
       <c r="H60" s="120"/>
     </row>
@@ -18250,23 +18250,23 @@
       </c>
       <c r="B61" s="124">
         <f t="shared" ref="B61:F66" si="4">B51/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>187.62126579698861</v>
+        <v>187.42739976507474</v>
       </c>
       <c r="C61" s="124">
         <f t="shared" si="4"/>
-        <v>190.57484995959203</v>
+        <v>190.37793203673655</v>
       </c>
       <c r="D61" s="124">
         <f t="shared" si="4"/>
-        <v>196.61013815331435</v>
+        <v>196.40698406437932</v>
       </c>
       <c r="E61" s="124">
         <f t="shared" si="4"/>
-        <v>202.82252912573423</v>
+        <v>202.61295587327095</v>
       </c>
       <c r="F61" s="124">
         <f t="shared" si="4"/>
-        <v>212.49017272580096</v>
+        <v>212.27061005292342</v>
       </c>
       <c r="H61" s="120"/>
     </row>
@@ -18277,23 +18277,23 @@
       </c>
       <c r="B62" s="124">
         <f t="shared" si="4"/>
-        <v>187.62126579698867</v>
+        <v>187.42739976507474</v>
       </c>
       <c r="C62" s="124">
         <f t="shared" si="4"/>
-        <v>193.40669253550149</v>
+        <v>193.20684851532511</v>
       </c>
       <c r="D62" s="124">
         <f t="shared" si="4"/>
-        <v>205.82927744196496</v>
+        <v>205.61659736489653</v>
       </c>
       <c r="E62" s="124">
         <f t="shared" si="4"/>
-        <v>219.50089734623191</v>
+        <v>219.27409060452652</v>
       </c>
       <c r="F62" s="124">
         <f t="shared" si="4"/>
-        <v>242.68167339860059</v>
+        <v>242.43091433437536</v>
       </c>
       <c r="H62" s="120"/>
     </row>
@@ -18304,23 +18304,23 @@
       </c>
       <c r="B63" s="124">
         <f t="shared" si="4"/>
-        <v>187.62126579698867</v>
+        <v>187.42739976507474</v>
       </c>
       <c r="C63" s="124">
         <f t="shared" si="4"/>
-        <v>196.90300210131502</v>
+        <v>196.6995454007797</v>
       </c>
       <c r="D63" s="124">
         <f t="shared" si="4"/>
-        <v>217.80538501616576</v>
+        <v>217.58033022004125</v>
       </c>
       <c r="E63" s="124">
         <f t="shared" si="4"/>
-        <v>242.34138610658789</v>
+        <v>242.0909786557404</v>
       </c>
       <c r="F63" s="124">
         <f t="shared" si="4"/>
-        <v>287.58329722496143</v>
+        <v>287.28614203607128</v>
       </c>
       <c r="H63" s="120"/>
     </row>
@@ -18331,23 +18331,23 @@
       </c>
       <c r="B64" s="124">
         <f t="shared" si="4"/>
-        <v>187.62126579698867</v>
+        <v>187.42739976507474</v>
       </c>
       <c r="C64" s="124">
         <f t="shared" si="4"/>
-        <v>200.45392014461385</v>
+        <v>200.24679433765937</v>
       </c>
       <c r="D64" s="124">
         <f t="shared" si="4"/>
-        <v>230.63266674780621</v>
+        <v>230.39435772807866</v>
       </c>
       <c r="E64" s="124">
         <f t="shared" si="4"/>
-        <v>268.22845251888424</v>
+        <v>267.95129637927846</v>
       </c>
       <c r="F64" s="124">
         <f t="shared" si="4"/>
-        <v>343.29172312778229</v>
+        <v>342.93700531970785</v>
       </c>
       <c r="H64" s="120"/>
     </row>
@@ -18358,23 +18358,23 @@
       </c>
       <c r="B65" s="124">
         <f t="shared" si="4"/>
-        <v>187.62126579698867</v>
+        <v>187.42739976507474</v>
       </c>
       <c r="C65" s="124">
         <f t="shared" si="4"/>
-        <v>203.74401376934242</v>
+        <v>203.53348836163934</v>
       </c>
       <c r="D65" s="124">
         <f t="shared" si="4"/>
-        <v>243.18944681908653</v>
+        <v>242.93816308076455</v>
       </c>
       <c r="E65" s="124">
         <f t="shared" si="4"/>
-        <v>295.13020490374475</v>
+        <v>294.8252516167089</v>
       </c>
       <c r="F65" s="124">
         <f t="shared" si="4"/>
-        <v>407.10121203609896</v>
+        <v>406.68056091092132</v>
       </c>
     </row>
     <row r="66" spans="1:8" ht="13.15">
@@ -18384,23 +18384,23 @@
       </c>
       <c r="B66" s="124">
         <f t="shared" si="4"/>
-        <v>187.62126579698864</v>
+        <v>187.42739976507474</v>
       </c>
       <c r="C66" s="124">
         <f t="shared" si="4"/>
-        <v>206.63363366431258</v>
+        <v>206.42012245891544</v>
       </c>
       <c r="D66" s="124">
         <f t="shared" si="4"/>
-        <v>254.86061363131958</v>
+        <v>254.59727026431912</v>
       </c>
       <c r="E66" s="124">
         <f t="shared" si="4"/>
-        <v>321.75423127443474</v>
+        <v>321.42176780978593</v>
       </c>
       <c r="F66" s="124">
         <f t="shared" si="4"/>
-        <v>477.14051970381081</v>
+        <v>476.64749809015018</v>
       </c>
     </row>
     <row r="68" spans="1:8" ht="13.15">
@@ -18435,7 +18435,7 @@
       </c>
       <c r="E69" s="135">
         <f>INDEX(B$60:F$66, MATCH(D69, A$60:A$66, 0), MATCH(C69, B$59:F$59, 0))</f>
-        <v>242.68167339860059</v>
+        <v>242.43091433437536</v>
       </c>
       <c r="F69" s="142">
         <f>Scenarios!C58</f>
@@ -18457,7 +18457,7 @@
       </c>
       <c r="E70" s="135">
         <f>INDEX(B$60:F$66, MATCH(D70, A$60:A$66, 0), MATCH(C70, B$59:F$59, 0))</f>
-        <v>202.82252912573423</v>
+        <v>202.61295587327095</v>
       </c>
       <c r="F70" s="142">
         <f>Scenarios!C40*(1-F$69-F$73)</f>
@@ -18480,7 +18480,7 @@
       </c>
       <c r="E71" s="135">
         <f>INDEX(B$60:F$66, MATCH(D71, A$60:A$66, 0), MATCH(C71, B$59:F$59, 0))</f>
-        <v>196.61013815331435</v>
+        <v>196.40698406437932</v>
       </c>
       <c r="F71" s="142">
         <f>Scenarios!C28*(1-F$69-F$73)</f>
@@ -18503,7 +18503,7 @@
       </c>
       <c r="E72" s="135">
         <f>INDEX(B$60:F$66, MATCH(D72, A$60:A$66, 0), MATCH(C72, B$59:F$59, 0))</f>
-        <v>190.57484995959203</v>
+        <v>190.37793203673655</v>
       </c>
       <c r="F72" s="142">
         <f>Scenarios!C34*(1-F$69-F$73)</f>
@@ -18526,7 +18526,7 @@
       </c>
       <c r="E73" s="135">
         <f>INDEX(B$60:F$66, MATCH(D73, A$60:A$66, 0), MATCH(C73, B$59:F$59, 0))</f>
-        <v>187.62126579698867</v>
+        <v>187.42739976507474</v>
       </c>
       <c r="F73" s="142">
         <f>Scenarios!C52</f>
@@ -18626,7 +18626,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-50</v>
+        <v>-50.5</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18646,7 +18646,7 @@
       </c>
       <c r="I4" s="124">
         <f t="shared" ref="I4:I13" si="0">IF(ROW()-3 &lt; $C$76, $C$77, IF(ROW()-3 = $C$76, $C$77 + $C$60, ""))</f>
-        <v>1.51912526452</v>
+        <v>1.5183402178400001</v>
       </c>
     </row>
     <row r="5" spans="2:9">
@@ -18655,7 +18655,7 @@
       </c>
       <c r="I5" s="124">
         <f t="shared" si="0"/>
-        <v>1.51912526452</v>
+        <v>1.5183402178400001</v>
       </c>
     </row>
     <row r="6" spans="2:9" ht="13.15">
@@ -18675,7 +18675,7 @@
       </c>
       <c r="I6" s="124">
         <f t="shared" si="0"/>
-        <v>35.258637530271841</v>
+        <v>35.241022405887797</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1">
@@ -18866,7 +18866,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>50</v>
+        <v>50.5</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -18881,7 +18881,7 @@
       </c>
       <c r="C22" s="160">
         <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
-        <v>31.800158361114637</v>
+        <v>31.784330493945657</v>
       </c>
       <c r="D22" t="str">
         <f>Market_currency</f>
@@ -18928,7 +18928,7 @@
       </c>
       <c r="C27" s="160">
         <f>IF(valuation_method="DCF",DCF!E76,DDM!E71)</f>
-        <v>33.403173593370909</v>
+        <v>33.386517327244015</v>
       </c>
       <c r="D27" s="160" t="str">
         <f>Market_currency</f>
@@ -18986,7 +18986,7 @@
       </c>
       <c r="C33" s="160">
         <f>IF(valuation_method="DCF",DCF!E77,DDM!E72)</f>
-        <v>32.326880759066171</v>
+        <v>32.310780694679856</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
@@ -19044,7 +19044,7 @@
       </c>
       <c r="C39" s="160">
         <f>IF(valuation_method="DCF",DCF!E75,DDM!E70)</f>
-        <v>34.51104974988484</v>
+        <v>34.493820960531032</v>
       </c>
       <c r="D39" t="str">
         <f>Market_currency</f>
@@ -19071,7 +19071,7 @@
       </c>
       <c r="C42" s="154">
         <f>C27*C28+C33*C34+C39*C40</f>
-        <v>33.409490257812749</v>
+        <v>33.392830727388585</v>
       </c>
       <c r="D42" t="str">
         <f>Market_currency</f>
@@ -19145,7 +19145,7 @@
       </c>
       <c r="C51" s="160">
         <f>IF(valuation_method="DCF",DCF!E78,DDM!E73)</f>
-        <v>31.800158361114644</v>
+        <v>31.784330493945667</v>
       </c>
       <c r="D51" t="str">
         <f>Market_currency</f>
@@ -19203,7 +19203,7 @@
       </c>
       <c r="C57" s="160">
         <f>IF(valuation_method="DCF",DCF!E74,DDM!E69)</f>
-        <v>41.619262313292801</v>
+        <v>41.59836017401588</v>
       </c>
       <c r="D57" t="str">
         <f>Market_currency</f>
@@ -19229,7 +19229,7 @@
       </c>
       <c r="C60" s="154">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
-        <v>33.739512265751841</v>
+        <v>33.722682188047798</v>
       </c>
       <c r="D60" t="str">
         <f>Market_currency</f>
@@ -19291,7 +19291,7 @@
       </c>
       <c r="C66" s="160">
         <f>IF(valuation_method="DCF",DCF!C18,DDM!C13)</f>
-        <v>33.06364475689778</v>
+        <v>33.047163950946597</v>
       </c>
       <c r="D66" s="160" t="str">
         <f>Market_currency</f>
@@ -19354,7 +19354,7 @@
       </c>
       <c r="F72" s="291">
         <f>BS!D89/C60</f>
-        <v>-4.9169659170151009E-2</v>
+        <v>-4.9150815604021243E-2</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="13.9">
@@ -19387,7 +19387,7 @@
       </c>
       <c r="C77" s="173">
         <f>Normalized_FCF!C90*(1-dividend_tax_rate)</f>
-        <v>1.51912526452</v>
+        <v>1.5183402178400001</v>
       </c>
       <c r="D77" t="str">
         <f>Market_currency</f>
@@ -19414,7 +19414,7 @@
       </c>
       <c r="C81" s="116">
         <f>PV(C80, C76, -C77, 0)</f>
-        <v>2.517584501908376</v>
+        <v>2.51628347598181</v>
       </c>
       <c r="D81" s="116"/>
       <c r="E81" s="100"/>
@@ -19426,7 +19426,7 @@
       </c>
       <c r="C82" s="116">
         <f>C60/(1+C80)^C76</f>
-        <v>13.196296761398656</v>
+        <v>13.189714132161143</v>
       </c>
       <c r="D82" s="116"/>
     </row>
@@ -19436,7 +19436,7 @@
       </c>
       <c r="C83" s="111">
         <f>C81+C82</f>
-        <v>15.713881263307032</v>
+        <v>15.705997608142953</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -19447,7 +19447,7 @@
       </c>
       <c r="F83" s="291">
         <f>(1-C83/C60)</f>
-        <v>0.53425879012312194</v>
+        <v>0.53426013030156994</v>
       </c>
     </row>
     <row r="84" spans="2:8">
@@ -19464,7 +19464,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>50</v>
+        <v>50.5</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19477,7 +19477,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>-8.8165408338003126E-2</v>
+        <v>-9.1448907953051495E-2</v>
       </c>
     </row>
     <row r="88" spans="2:8">
@@ -19503,7 +19503,7 @@
       </c>
       <c r="C91" s="116">
         <f>PV(C90, C76, -C77, 0)</f>
-        <v>3.114815693925848</v>
+        <v>3.1132060335664034</v>
       </c>
       <c r="D91" s="116"/>
       <c r="E91" s="100"/>
@@ -19515,7 +19515,7 @@
       </c>
       <c r="C92" s="116">
         <f>C60/(1+C90)^C76</f>
-        <v>18.69988380326302</v>
+        <v>18.6905558528473</v>
       </c>
       <c r="D92" s="116"/>
     </row>
@@ -19525,7 +19525,7 @@
       </c>
       <c r="C93" s="111">
         <f>C91+C92</f>
-        <v>21.814699497188869</v>
+        <v>21.803761886413703</v>
       </c>
       <c r="D93" t="str">
         <f>Market_currency</f>
@@ -19536,7 +19536,7 @@
       </c>
       <c r="F93" s="291">
         <f>(1-C93/C60)</f>
-        <v>0.35343761565479292</v>
+        <v>0.35343927375558737</v>
       </c>
     </row>
     <row r="95" spans="2:8" ht="13.15">
@@ -19563,7 +19563,7 @@
       </c>
       <c r="C97" s="116">
         <f>PV(C96, C76, -C77, 0)</f>
-        <v>3.9505243524740594</v>
+        <v>3.948482818375719</v>
       </c>
       <c r="D97" s="116"/>
       <c r="G97" s="2"/>
@@ -19575,7 +19575,7 @@
       </c>
       <c r="C98" s="116">
         <f>C60/(1+C96)^C76</f>
-        <v>27.158977008415839</v>
+        <v>27.145429459482301</v>
       </c>
       <c r="D98" s="116"/>
       <c r="G98" s="2"/>
@@ -19587,7 +19587,7 @@
       </c>
       <c r="C99" s="111">
         <f>C97+C98</f>
-        <v>31.109501360889897</v>
+        <v>31.093912277858021</v>
       </c>
       <c r="D99" t="s">
         <v>393</v>
@@ -19597,7 +19597,7 @@
       </c>
       <c r="F99" s="291">
         <f>(1-C99/C60)</f>
-        <v>7.7950471961374612E-2</v>
+        <v>7.7952574932532603E-2</v>
       </c>
     </row>
     <row r="100" spans="2:8">
@@ -19623,7 +19623,7 @@
       </c>
       <c r="C103" s="116">
         <f>PV(C102, C76, -C77, 0)</f>
-        <v>3.6650463618733289</v>
+        <v>3.6631523557991534</v>
       </c>
       <c r="D103" s="116"/>
     </row>
@@ -19633,7 +19633,7 @@
       </c>
       <c r="C104" s="116">
         <f>C60/(1+C102)^C76</f>
-        <v>24.183146071728043</v>
+        <v>24.171082938618422</v>
       </c>
       <c r="D104" s="116"/>
     </row>
@@ -19643,7 +19643,7 @@
       </c>
       <c r="C105" s="111">
         <f>C103+C104</f>
-        <v>27.848192433601373</v>
+        <v>27.834235294417574</v>
       </c>
       <c r="D105" t="s">
         <v>393</v>
@@ -19653,7 +19653,7 @@
       </c>
       <c r="F105" s="291">
         <f>(1-C105/C66)</f>
-        <v>0.15773978826724333</v>
+        <v>0.15774208837607995</v>
       </c>
     </row>
     <row r="106" spans="2:8">

--- a/financial_models/opportunities/1913.HK_Valuation.xlsx
+++ b/financial_models/opportunities/1913.HK_Valuation.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr showObjects="none" codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64FAAA38-9DDD-4DDD-A05D-109611CA6BCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5103535-173A-4940-BF32-9C42B9D67B12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3896,29 +3896,29 @@
     <xf numFmtId="10" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4384,7 +4384,7 @@
         <v>1</v>
       </c>
       <c r="C16" s="50">
-        <v>9.2581720599999997</v>
+        <v>9.2476137599999984</v>
       </c>
       <c r="D16" s="50"/>
       <c r="E16" s="5"/>
@@ -4394,13 +4394,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="358" t="s">
+      <c r="B18" s="360" t="s">
         <v>356</v>
       </c>
-      <c r="C18" s="358"/>
-      <c r="D18" s="358"/>
-      <c r="E18" s="358"/>
-      <c r="F18" s="358"/>
+      <c r="C18" s="360"/>
+      <c r="D18" s="360"/>
+      <c r="E18" s="360"/>
+      <c r="F18" s="360"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4476,14 +4476,14 @@
       </c>
       <c r="C26" s="304">
         <f>C132</f>
-        <v>33.722682188047798</v>
+        <v>33.685558220029087</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>396</v>
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>-9.1448907953051495E-2</v>
+        <v>-9.1795592256709635E-2</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4515,7 +4515,7 @@
       </c>
       <c r="C29" s="310">
         <f>C149</f>
-        <v>15.705997608142953</v>
+        <v>16.263215095202757</v>
       </c>
       <c r="D29" s="310" t="str">
         <f>D149</f>
@@ -4525,7 +4525,7 @@
         <v>420</v>
       </c>
       <c r="F29" s="302">
-        <v>0.3674</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="30" spans="2:6">
@@ -4534,7 +4534,7 @@
       </c>
       <c r="C30" s="311">
         <f>C157</f>
-        <v>21.803761886413703</v>
+        <v>20.207425906416173</v>
       </c>
       <c r="D30" s="311" t="str">
         <f>D157</f>
@@ -4544,7 +4544,7 @@
         <v>433</v>
       </c>
       <c r="F30" s="312">
-        <v>0.21740000000000001</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="31" spans="2:6">
@@ -4553,7 +4553,7 @@
       </c>
       <c r="C31" s="311">
         <f>C165</f>
-        <v>31.093912277858021</v>
+        <v>31.059525977948461</v>
       </c>
       <c r="D31" s="311" t="str">
         <f>D165</f>
@@ -4572,7 +4572,7 @@
       </c>
       <c r="C32" s="311">
         <f>C173</f>
-        <v>27.834235294417574</v>
+        <v>27.803448734546343</v>
       </c>
       <c r="D32" s="311" t="str">
         <f>D173</f>
@@ -4600,22 +4600,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="358" t="s">
+      <c r="B36" s="360" t="s">
         <v>357</v>
       </c>
-      <c r="C36" s="358"/>
-      <c r="D36" s="358"/>
-      <c r="E36" s="358"/>
-      <c r="F36" s="358"/>
+      <c r="C36" s="360"/>
+      <c r="D36" s="360"/>
+      <c r="E36" s="360"/>
+      <c r="F36" s="360"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="360" t="s">
+      <c r="B37" s="363" t="s">
         <v>336</v>
       </c>
-      <c r="C37" s="360"/>
-      <c r="D37" s="360"/>
-      <c r="E37" s="360"/>
-      <c r="F37" s="360"/>
+      <c r="C37" s="363"/>
+      <c r="D37" s="363"/>
+      <c r="E37" s="363"/>
+      <c r="F37" s="363"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4627,13 +4627,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="359" t="s">
+      <c r="B40" s="361" t="s">
         <v>230</v>
       </c>
-      <c r="C40" s="359"/>
-      <c r="D40" s="359"/>
-      <c r="E40" s="359"/>
-      <c r="F40" s="359"/>
+      <c r="C40" s="361"/>
+      <c r="D40" s="361"/>
+      <c r="E40" s="361"/>
+      <c r="F40" s="361"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4653,13 +4653,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="359" t="s">
+      <c r="B43" s="361" t="s">
         <v>232</v>
       </c>
-      <c r="C43" s="359"/>
-      <c r="D43" s="359"/>
-      <c r="E43" s="359"/>
-      <c r="F43" s="359"/>
+      <c r="C43" s="361"/>
+      <c r="D43" s="361"/>
+      <c r="E43" s="361"/>
+      <c r="F43" s="361"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4688,13 +4688,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="359" t="s">
+      <c r="B47" s="361" t="s">
         <v>235</v>
       </c>
-      <c r="C47" s="359"/>
-      <c r="D47" s="359"/>
-      <c r="E47" s="359"/>
-      <c r="F47" s="359"/>
+      <c r="C47" s="361"/>
+      <c r="D47" s="361"/>
+      <c r="E47" s="361"/>
+      <c r="F47" s="361"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4710,13 +4710,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="359" t="s">
+      <c r="B50" s="361" t="s">
         <v>239</v>
       </c>
-      <c r="C50" s="359"/>
-      <c r="D50" s="359"/>
-      <c r="E50" s="359"/>
-      <c r="F50" s="359"/>
+      <c r="C50" s="361"/>
+      <c r="D50" s="361"/>
+      <c r="E50" s="361"/>
+      <c r="F50" s="361"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4780,13 +4780,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="359" t="s">
+      <c r="B58" s="361" t="s">
         <v>240</v>
       </c>
-      <c r="C58" s="359"/>
-      <c r="D58" s="359"/>
-      <c r="E58" s="359"/>
-      <c r="F58" s="359"/>
+      <c r="C58" s="361"/>
+      <c r="D58" s="361"/>
+      <c r="E58" s="361"/>
+      <c r="F58" s="361"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4802,7 +4802,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="359" t="s">
+      <c r="B61" s="361" t="s">
         <v>335</v>
       </c>
       <c r="C61" s="362"/>
@@ -4824,22 +4824,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="358" t="s">
+      <c r="B64" s="360" t="s">
         <v>340</v>
       </c>
-      <c r="C64" s="358"/>
-      <c r="D64" s="358"/>
-      <c r="E64" s="358"/>
-      <c r="F64" s="358"/>
+      <c r="C64" s="360"/>
+      <c r="D64" s="360"/>
+      <c r="E64" s="360"/>
+      <c r="F64" s="360"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="358" t="s">
+      <c r="B65" s="360" t="s">
         <v>358</v>
       </c>
-      <c r="C65" s="358"/>
-      <c r="D65" s="358"/>
-      <c r="E65" s="358"/>
-      <c r="F65" s="358"/>
+      <c r="C65" s="360"/>
+      <c r="D65" s="360"/>
+      <c r="E65" s="360"/>
+      <c r="F65" s="360"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4873,7 +4873,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>4.9666080932440702E-2</v>
+        <v>4.9609440228540344E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4883,14 +4883,14 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>3.0066142927524752E-2</v>
+        <v>3.0031854586930692E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>444</v>
       </c>
       <c r="F70" s="315">
         <f>Normalized_FCF!C92</f>
-        <v>5.6045800106961883</v>
+        <v>5.5981883777967951</v>
       </c>
     </row>
     <row r="72" spans="1:6">
@@ -4974,22 +4974,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.6" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="358" t="s">
+      <c r="B80" s="360" t="s">
         <v>359</v>
       </c>
-      <c r="C80" s="358"/>
-      <c r="D80" s="358"/>
-      <c r="E80" s="358"/>
-      <c r="F80" s="358"/>
+      <c r="C80" s="360"/>
+      <c r="D80" s="360"/>
+      <c r="E80" s="360"/>
+      <c r="F80" s="360"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="360" t="s">
+      <c r="B81" s="363" t="s">
         <v>251</v>
       </c>
-      <c r="C81" s="360"/>
-      <c r="D81" s="360"/>
-      <c r="E81" s="360"/>
-      <c r="F81" s="360"/>
+      <c r="C81" s="363"/>
+      <c r="D81" s="363"/>
+      <c r="E81" s="363"/>
+      <c r="F81" s="363"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5033,22 +5033,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="358" t="s">
+      <c r="B89" s="360" t="s">
         <v>360</v>
       </c>
-      <c r="C89" s="358"/>
-      <c r="D89" s="358"/>
-      <c r="E89" s="358"/>
-      <c r="F89" s="358"/>
+      <c r="C89" s="360"/>
+      <c r="D89" s="360"/>
+      <c r="E89" s="360"/>
+      <c r="F89" s="360"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="358" t="s">
+      <c r="B90" s="360" t="s">
         <v>361</v>
       </c>
-      <c r="C90" s="358"/>
-      <c r="D90" s="358"/>
-      <c r="E90" s="358"/>
-      <c r="F90" s="358"/>
+      <c r="C90" s="360"/>
+      <c r="D90" s="360"/>
+      <c r="E90" s="360"/>
+      <c r="F90" s="360"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5064,7 +5064,7 @@
       </c>
       <c r="C93" s="223">
         <f>DCF!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>33.441827827843404</v>
+        <v>33.403689753883825</v>
       </c>
       <c r="D93" s="1" t="str">
         <f>Market_currency</f>
@@ -5085,13 +5085,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="358" t="s">
+      <c r="B97" s="360" t="s">
         <v>362</v>
       </c>
-      <c r="C97" s="358"/>
-      <c r="D97" s="358"/>
-      <c r="E97" s="358"/>
-      <c r="F97" s="358"/>
+      <c r="C97" s="360"/>
+      <c r="D97" s="360"/>
+      <c r="E97" s="360"/>
+      <c r="F97" s="360"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5104,13 +5104,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="358" t="s">
+      <c r="B101" s="360" t="s">
         <v>341</v>
       </c>
-      <c r="C101" s="358"/>
-      <c r="D101" s="358"/>
-      <c r="E101" s="358"/>
-      <c r="F101" s="358"/>
+      <c r="C101" s="360"/>
+      <c r="D101" s="360"/>
+      <c r="E101" s="360"/>
+      <c r="F101" s="360"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="C103" s="223">
         <f>C102*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>3.1351144471014809</v>
+        <v>3.1315390675716652</v>
       </c>
       <c r="D103" s="1" t="str">
         <f>Market_currency</f>
@@ -5180,7 +5180,7 @@
       </c>
       <c r="C109" s="349">
         <f>DCF!C8</f>
-        <v>404629.46262395149</v>
+        <v>404998.6926536205</v>
       </c>
       <c r="D109" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5193,7 +5193,7 @@
       </c>
       <c r="C110" s="223">
         <f>C109*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>1.4640042400406914</v>
+        <v>1.4636690460014565</v>
       </c>
       <c r="D110" s="1" t="str">
         <f>Market_currency</f>
@@ -5224,7 +5224,7 @@
       </c>
       <c r="C114" s="223">
         <f>C113*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>1.3612873163040523E-2</v>
+        <v>1.359734862992687E-2</v>
       </c>
       <c r="D114" s="1" t="str">
         <f>Market_currency</f>
@@ -5232,13 +5232,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="358" t="s">
+      <c r="B116" s="360" t="s">
         <v>363</v>
       </c>
-      <c r="C116" s="358"/>
-      <c r="D116" s="358"/>
-      <c r="E116" s="358"/>
-      <c r="F116" s="358"/>
+      <c r="C116" s="360"/>
+      <c r="D116" s="360"/>
+      <c r="E116" s="360"/>
+      <c r="F116" s="360"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="C118" s="223">
         <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
-        <v>31.784330493945657</v>
+        <v>31.749417080943548</v>
       </c>
       <c r="D118" s="1" t="str">
         <f>Market_currency</f>
@@ -5259,7 +5259,7 @@
       </c>
       <c r="C119" s="223">
         <f>BS!D47</f>
-        <v>-6.0168078063871082</v>
+        <v>-6.0099460564163278</v>
       </c>
       <c r="D119" s="1" t="str">
         <f>Market_currency</f>
@@ -5277,13 +5277,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B123" s="359" t="s">
+      <c r="B123" s="361" t="s">
         <v>364</v>
       </c>
-      <c r="C123" s="359"/>
-      <c r="D123" s="359"/>
-      <c r="E123" s="359"/>
-      <c r="F123" s="359"/>
+      <c r="C123" s="361"/>
+      <c r="D123" s="361"/>
+      <c r="E123" s="361"/>
+      <c r="F123" s="361"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5317,7 +5317,7 @@
       </c>
       <c r="E126" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E74,DDM!E69),2)&amp;" "&amp;Market_currency</f>
-        <v>41.6 HKD</v>
+        <v>41.55 HKD</v>
       </c>
       <c r="F126" s="232">
         <f>DCF!F74</f>
@@ -5339,7 +5339,7 @@
       </c>
       <c r="E127" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E75,DDM!E70),2)&amp;" "&amp;Market_currency</f>
-        <v>34.49 HKD</v>
+        <v>34.46 HKD</v>
       </c>
       <c r="F127" s="221">
         <f>DCF!F75</f>
@@ -5361,7 +5361,7 @@
       </c>
       <c r="E128" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E76,DDM!E71),2)&amp;" "&amp;Market_currency</f>
-        <v>33.39 HKD</v>
+        <v>33.35 HKD</v>
       </c>
       <c r="F128" s="221">
         <f>DCF!F76</f>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="E129" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E77,DDM!E72),2)&amp;" "&amp;Market_currency</f>
-        <v>32.31 HKD</v>
+        <v>32.28 HKD</v>
       </c>
       <c r="F129" s="221">
         <f>DCF!F77</f>
@@ -5405,7 +5405,7 @@
       </c>
       <c r="E130" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E78,DDM!E73),2)&amp;" "&amp;Market_currency</f>
-        <v>31.78 HKD</v>
+        <v>31.75 HKD</v>
       </c>
       <c r="F130" s="221">
         <f>DCF!F78</f>
@@ -5418,7 +5418,7 @@
       </c>
       <c r="C132" s="217">
         <f>Scenarios!C60</f>
-        <v>33.722682188047798</v>
+        <v>33.685558220029087</v>
       </c>
       <c r="D132" s="212" t="str">
         <f>Market_currency</f>
@@ -5426,13 +5426,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="363" t="s">
+      <c r="B134" s="364" t="s">
         <v>367</v>
       </c>
-      <c r="C134" s="363"/>
-      <c r="D134" s="363"/>
-      <c r="E134" s="363"/>
-      <c r="F134" s="363"/>
+      <c r="C134" s="364"/>
+      <c r="D134" s="364"/>
+      <c r="E134" s="364"/>
+      <c r="F134" s="364"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5445,22 +5445,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="361" t="s">
+      <c r="B138" s="365" t="s">
         <v>365</v>
       </c>
-      <c r="C138" s="361"/>
-      <c r="D138" s="361"/>
-      <c r="E138" s="361"/>
-      <c r="F138" s="361"/>
+      <c r="C138" s="365"/>
+      <c r="D138" s="365"/>
+      <c r="E138" s="365"/>
+      <c r="F138" s="365"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="358" t="s">
+      <c r="B139" s="360" t="s">
         <v>366</v>
       </c>
-      <c r="C139" s="358"/>
-      <c r="D139" s="358"/>
-      <c r="E139" s="358"/>
-      <c r="F139" s="358"/>
+      <c r="C139" s="360"/>
+      <c r="D139" s="360"/>
+      <c r="E139" s="360"/>
+      <c r="F139" s="360"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5482,7 +5482,7 @@
       </c>
       <c r="C142" s="224">
         <f>F29</f>
-        <v>0.3674</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="143" spans="1:6">
@@ -5491,7 +5491,7 @@
       </c>
       <c r="C143" s="213">
         <f>Scenarios!C77</f>
-        <v>1.5183402178400001</v>
+        <v>1.5166086566399999</v>
       </c>
       <c r="D143" s="212" t="str">
         <f>Market_currency</f>
@@ -5517,7 +5517,7 @@
       </c>
       <c r="C146" s="297">
         <f>F29</f>
-        <v>0.3674</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="147" spans="2:4">
@@ -5527,7 +5527,7 @@
       </c>
       <c r="C147" s="216">
         <f>Scenarios!C81</f>
-        <v>2.51628347598181</v>
+        <v>2.5719858232303614</v>
       </c>
     </row>
     <row r="148" spans="2:4">
@@ -5537,7 +5537,7 @@
       </c>
       <c r="C148" s="216">
         <f>Scenarios!C82</f>
-        <v>13.189714132161143</v>
+        <v>13.691229271972395</v>
       </c>
     </row>
     <row r="149" spans="2:4">
@@ -5546,7 +5546,7 @@
       </c>
       <c r="C149" s="215">
         <f>Scenarios!C83</f>
-        <v>15.705997608142953</v>
+        <v>16.263215095202757</v>
       </c>
       <c r="D149" s="300" t="str">
         <f>IF($D$11="","",C149*$E$25)</f>
@@ -5572,7 +5572,7 @@
       </c>
       <c r="C151" s="92">
         <f>Scenarios!F83</f>
-        <v>0.53426013030156994</v>
+        <v>0.51720511831884042</v>
       </c>
     </row>
     <row r="153" spans="2:4">
@@ -5586,7 +5586,7 @@
       </c>
       <c r="C154" s="297">
         <f>Scenarios!C90</f>
-        <v>0.21740000000000001</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="155" spans="2:4">
@@ -5596,7 +5596,7 @@
       </c>
       <c r="C155" s="216">
         <f>Scenarios!C91</f>
-        <v>3.1132060335664034</v>
+        <v>2.96042009776128</v>
       </c>
     </row>
     <row r="156" spans="2:4">
@@ -5606,7 +5606,7 @@
       </c>
       <c r="C156" s="216">
         <f>Scenarios!C92</f>
-        <v>18.6905558528473</v>
+        <v>17.247005808654894</v>
       </c>
     </row>
     <row r="157" spans="2:4">
@@ -5615,7 +5615,7 @@
       </c>
       <c r="C157" s="215">
         <f>Scenarios!C93</f>
-        <v>21.803761886413703</v>
+        <v>20.207425906416173</v>
       </c>
       <c r="D157" s="300" t="str">
         <f>IF($D$11="","",C157*$E$25)</f>
@@ -5641,7 +5641,7 @@
       </c>
       <c r="C159" s="92">
         <f>Scenarios!F93</f>
-        <v>0.35343927375558737</v>
+        <v>0.40011604455463512</v>
       </c>
     </row>
     <row r="161" spans="2:4">
@@ -5665,7 +5665,7 @@
       </c>
       <c r="C163" s="216">
         <f>Scenarios!C97</f>
-        <v>3.948482818375719</v>
+        <v>3.9439798489049545</v>
       </c>
     </row>
     <row r="164" spans="2:4">
@@ -5675,7 +5675,7 @@
       </c>
       <c r="C164" s="216">
         <f>Scenarios!C98</f>
-        <v>27.145429459482301</v>
+        <v>27.115546129043505</v>
       </c>
     </row>
     <row r="165" spans="2:4">
@@ -5684,7 +5684,7 @@
       </c>
       <c r="C165" s="215">
         <f>Scenarios!C99</f>
-        <v>31.093912277858021</v>
+        <v>31.059525977948461</v>
       </c>
       <c r="D165" s="300" t="str">
         <f>IF($D$11="","",C165*$E$25)</f>
@@ -5710,7 +5710,7 @@
       </c>
       <c r="C167" s="92">
         <f>Scenarios!F99</f>
-        <v>7.7952574932532603E-2</v>
+        <v>7.7957213145401161E-2</v>
       </c>
     </row>
     <row r="169" spans="2:4">
@@ -5734,7 +5734,7 @@
       </c>
       <c r="C171" s="216">
         <f>Scenarios!C103</f>
-        <v>3.6631523557991534</v>
+        <v>3.6589747858352792</v>
       </c>
     </row>
     <row r="172" spans="2:4">
@@ -5744,7 +5744,7 @@
       </c>
       <c r="C172" s="216">
         <f>Scenarios!C104</f>
-        <v>24.171082938618422</v>
+        <v>24.144473948711063</v>
       </c>
     </row>
     <row r="173" spans="2:4">
@@ -5753,7 +5753,7 @@
       </c>
       <c r="C173" s="215">
         <f>Scenarios!C105</f>
-        <v>27.834235294417574</v>
+        <v>27.803448734546343</v>
       </c>
       <c r="D173" s="300" t="str">
         <f>IF($D$11="","",C173*$E$25)</f>
@@ -5779,7 +5779,7 @@
       </c>
       <c r="C175" s="92">
         <f>Scenarios!F105</f>
-        <v>0.15774208837607995</v>
+        <v>0.15774716138043743</v>
       </c>
     </row>
     <row r="177" spans="1:6" ht="13.9">
@@ -5793,13 +5793,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="365" t="s">
+      <c r="B179" s="359" t="s">
         <v>373</v>
       </c>
-      <c r="C179" s="358"/>
-      <c r="D179" s="358"/>
-      <c r="E179" s="358"/>
-      <c r="F179" s="358"/>
+      <c r="C179" s="360"/>
+      <c r="D179" s="360"/>
+      <c r="E179" s="360"/>
+      <c r="F179" s="360"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5836,13 +5836,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="359" t="s">
+      <c r="B188" s="361" t="s">
         <v>378</v>
       </c>
-      <c r="C188" s="359"/>
-      <c r="D188" s="359"/>
-      <c r="E188" s="359"/>
-      <c r="F188" s="359"/>
+      <c r="C188" s="361"/>
+      <c r="D188" s="361"/>
+      <c r="E188" s="361"/>
+      <c r="F188" s="361"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5850,22 +5850,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="364" t="s">
+      <c r="B191" s="358" t="s">
         <v>379</v>
       </c>
-      <c r="C191" s="364"/>
-      <c r="D191" s="364"/>
-      <c r="E191" s="364"/>
-      <c r="F191" s="364"/>
+      <c r="C191" s="358"/>
+      <c r="D191" s="358"/>
+      <c r="E191" s="358"/>
+      <c r="F191" s="358"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="364" t="s">
+      <c r="B192" s="358" t="s">
         <v>380</v>
       </c>
-      <c r="C192" s="364"/>
-      <c r="D192" s="364"/>
-      <c r="E192" s="364"/>
-      <c r="F192" s="364"/>
+      <c r="C192" s="358"/>
+      <c r="D192" s="358"/>
+      <c r="E192" s="358"/>
+      <c r="F192" s="358"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5889,17 +5889,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5916,6 +5905,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -6488,15 +6488,15 @@
       </c>
       <c r="C25" s="39">
         <f>0.164*Exchange_Rate</f>
-        <v>1.5183402178400001</v>
+        <v>1.5166086566399999</v>
       </c>
       <c r="D25" s="39">
         <f>0.137*Exchange_Rate</f>
-        <v>1.2683695722200001</v>
+        <v>1.26692308512</v>
       </c>
       <c r="E25" s="39">
         <f>0.11*Exchange_Rate</f>
-        <v>1.0183989266</v>
+        <v>1.0172375135999998</v>
       </c>
       <c r="F25" s="39"/>
       <c r="G25" s="39"/>
@@ -7870,15 +7870,15 @@
       </c>
       <c r="C65" s="73">
         <f>IF(C$4="","",C25)</f>
-        <v>1.5183402178400001</v>
+        <v>1.5166086566399999</v>
       </c>
       <c r="D65" s="73">
         <f t="shared" ref="D65:M65" si="33">IF(D$4="","",D25)</f>
-        <v>1.2683695722200001</v>
+        <v>1.26692308512</v>
       </c>
       <c r="E65" s="73">
         <f t="shared" si="33"/>
-        <v>1.0183989266</v>
+        <v>1.0172375135999998</v>
       </c>
       <c r="F65" s="73">
         <f t="shared" si="33"/>
@@ -9220,11 +9220,11 @@
       </c>
       <c r="C47" s="147">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>15.917498868520029</v>
+        <v>15.899346070406715</v>
       </c>
       <c r="D47" s="147">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>-6.0168078063871082</v>
+        <v>-6.0099460564163278</v>
       </c>
       <c r="F47" s="253"/>
     </row>
@@ -9415,7 +9415,7 @@
       </c>
       <c r="D66" s="76">
         <f>C66-D75</f>
-        <v>404629.46262395149</v>
+        <v>404998.6926536205</v>
       </c>
       <c r="F66" s="5" t="s">
         <v>225</v>
@@ -9482,11 +9482,11 @@
       </c>
       <c r="C73" s="349">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35-Normalized_FCF!G91)/12</f>
-        <v>-656590.69913118507</v>
+        <v>-656221.46910151595</v>
       </c>
       <c r="D73" s="349">
         <f>(Normalized_FCF!C25+Normalized_FCF!C35-Normalized_FCF!C91)/12</f>
-        <v>-606933.53737604851</v>
+        <v>-606564.3073463795</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>348</v>
@@ -9498,11 +9498,11 @@
       </c>
       <c r="C74" s="258">
         <f>-$C$66/C73</f>
-        <v>1.5406294992276344</v>
+        <v>1.5414963508966111</v>
       </c>
       <c r="D74" s="258">
         <f>-$C$66/D73</f>
-        <v>1.6666783720228795</v>
+        <v>1.6676929185388836</v>
       </c>
       <c r="F74" s="253" t="s">
         <v>316</v>
@@ -9515,7 +9515,7 @@
       <c r="C75" s="320"/>
       <c r="D75" s="321">
         <f>MAX(-D73*D76,G5)</f>
-        <v>606933.53737604851</v>
+        <v>606564.3073463795</v>
       </c>
       <c r="F75" s="253" t="s">
         <v>349</v>
@@ -9630,11 +9630,11 @@
       </c>
       <c r="C86" s="76">
         <f>-DCF!C7*Exchange_Rate</f>
-        <v>-8022206.0899899993</v>
+        <v>-8013057.3230399983</v>
       </c>
       <c r="D86" s="223">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>-3.1351144471014809</v>
+        <v>-3.1315390675716648</v>
       </c>
       <c r="E86" s="240" t="str">
         <f>Market_currency</f>
@@ -9647,11 +9647,11 @@
       </c>
       <c r="C87" s="76">
         <f>DCF!C8*Exchange_Rate</f>
-        <v>3746129.185517882</v>
+        <v>3745271.4829656309</v>
       </c>
       <c r="D87" s="223">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>1.4640042400406914</v>
+        <v>1.4636690460014565</v>
       </c>
       <c r="E87" s="240" t="str">
         <f>Market_currency</f>
@@ -9664,11 +9664,11 @@
       </c>
       <c r="C88" s="76">
         <f>DCF!C9*Exchange_Rate</f>
-        <v>34832.946558543998</v>
+        <v>34793.222010623991</v>
       </c>
       <c r="D88" s="223">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>1.361287316304052E-2</v>
+        <v>1.359734862992687E-2</v>
       </c>
       <c r="E88" s="240" t="str">
         <f>Market_currency</f>
@@ -9681,11 +9681,11 @@
       </c>
       <c r="C89" s="180">
         <f>SUM(C86:C88)</f>
-        <v>-4241243.9579135729</v>
+        <v>-4232992.6180637442</v>
       </c>
       <c r="D89" s="242">
         <f>SUM(D86:D88)</f>
-        <v>-1.657497333897749</v>
+        <v>-1.6542726729402815</v>
       </c>
       <c r="E89" s="240" t="str">
         <f>Market_currency</f>
@@ -13197,20 +13197,20 @@
       </c>
       <c r="C90" s="113">
         <f>G90</f>
-        <v>1.5183402178400001</v>
+        <v>1.5166086566399999</v>
       </c>
       <c r="E90" s="268"/>
       <c r="G90" s="112">
         <f>Data!C65</f>
-        <v>1.5183402178400001</v>
+        <v>1.5166086566399999</v>
       </c>
       <c r="H90" s="112">
         <f>Data!D65</f>
-        <v>1.2683695722200001</v>
+        <v>1.26692308512</v>
       </c>
       <c r="I90" s="112">
         <f>Data!E65</f>
-        <v>1.0183989266</v>
+        <v>1.0172375135999998</v>
       </c>
       <c r="J90" s="112">
         <f>Data!F65</f>
@@ -13253,20 +13253,20 @@
       </c>
       <c r="C91" s="74">
         <f>C90*Common_Shares/scaling_factor</f>
-        <v>3885165.3895742204</v>
+        <v>3880734.6292181914</v>
       </c>
       <c r="E91" s="268"/>
       <c r="G91" s="74">
         <f t="shared" ref="G91:Q91" si="37">IF(G$4="","",G90*Common_Shares/scaling_factor)</f>
-        <v>3885165.3895742204</v>
+        <v>3880734.6292181914</v>
       </c>
       <c r="H91" s="74">
         <f t="shared" si="37"/>
-        <v>3245534.5022662696</v>
+        <v>3241833.1963590989</v>
       </c>
       <c r="I91" s="74">
         <f t="shared" si="37"/>
-        <v>2605903.6149583184</v>
+        <v>2602931.7635000059</v>
       </c>
       <c r="J91" s="74">
         <f t="shared" si="37"/>
@@ -13308,20 +13308,20 @@
       </c>
       <c r="C92" s="23">
         <f>C90/(C19*scaling_factor/Common_Shares)</f>
-        <v>5.6045800106961883</v>
+        <v>5.5981883777967951</v>
       </c>
       <c r="E92" s="268"/>
       <c r="G92" s="170">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",G90/(G19*scaling_factor/Common_Shares))</f>
-        <v>3.8973250437105973</v>
+        <v>3.8928804161164741</v>
       </c>
       <c r="H92" s="170">
         <f t="shared" si="38"/>
-        <v>3.9530757687329339</v>
+        <v>3.9485675613223861</v>
       </c>
       <c r="I92" s="170">
         <f t="shared" si="38"/>
-        <v>3.8787100876363674</v>
+        <v>3.8742866891023056</v>
       </c>
       <c r="J92" s="170">
         <f t="shared" si="38"/>
@@ -13384,20 +13384,20 @@
       </c>
       <c r="C94" s="23">
         <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
-        <v>3.0066142927524752E-2</v>
+        <v>3.0031854586930692E-2</v>
       </c>
       <c r="E94" s="268"/>
       <c r="G94" s="23">
         <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>3.0066142927524752E-2</v>
+        <v>3.0031854586930692E-2</v>
       </c>
       <c r="H94" s="23">
         <f t="shared" si="39"/>
-        <v>2.5116229152871289E-2</v>
+        <v>2.5087585843960394E-2</v>
       </c>
       <c r="I94" s="23">
         <f t="shared" si="39"/>
-        <v>2.0166315378217822E-2</v>
+        <v>2.0143317100990096E-2</v>
       </c>
       <c r="J94" s="23">
         <f t="shared" si="39"/>
@@ -14526,38 +14526,38 @@
       </c>
       <c r="C125" s="177">
         <f>C16*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>2.5081370870882553</v>
+        <v>2.5052767315412869</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="265"/>
       <c r="F125" s="27"/>
       <c r="G125" s="177">
         <f t="shared" ref="G125:Q125" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>3.606846959061194</v>
+        <v>3.6027336014781786</v>
       </c>
       <c r="H125" s="177">
         <f t="shared" si="49"/>
-        <v>2.9705435519757901</v>
+        <v>2.9671558540823435</v>
       </c>
       <c r="I125" s="177">
         <f t="shared" si="49"/>
-        <v>2.4308371275894238</v>
+        <v>2.4280649272589594</v>
       </c>
       <c r="J125" s="177">
         <f t="shared" si="49"/>
-        <v>1.3038530327111046</v>
+        <v>1.302366079197381</v>
       </c>
       <c r="K125" s="177">
         <f t="shared" si="49"/>
-        <v>6.2985299504121111</v>
+        <v>6.2913469159702728</v>
       </c>
       <c r="L125" s="177">
         <f t="shared" si="49"/>
-        <v>8.4687527749147264</v>
+        <v>8.4590947525919713</v>
       </c>
       <c r="M125" s="177">
         <f t="shared" si="49"/>
-        <v>7.8350688979616967</v>
+        <v>7.8261335479369576</v>
       </c>
       <c r="N125" s="177" t="str">
         <f t="shared" si="49"/>
@@ -14583,38 +14583,38 @@
       </c>
       <c r="C126" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>4.9666080932440702E-2</v>
+        <v>4.9609440228540344E-2</v>
       </c>
       <c r="D126" s="27"/>
       <c r="E126" s="265"/>
       <c r="F126" s="27"/>
       <c r="G126" s="77">
         <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
-        <v>7.1422712060617705E-2</v>
+        <v>7.1341259435211454E-2</v>
       </c>
       <c r="H126" s="77">
         <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
-        <v>5.8822644593580005E-2</v>
+        <v>5.8755561466977101E-2</v>
       </c>
       <c r="I126" s="77">
         <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
-        <v>4.8135388665137106E-2</v>
+        <v>4.8080493609088303E-2</v>
       </c>
       <c r="J126" s="77">
         <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
-        <v>2.5818871934873359E-2</v>
+        <v>2.578942731083923E-2</v>
       </c>
       <c r="K126" s="77">
         <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
-        <v>0.12472336535469526</v>
+        <v>0.12458112704891629</v>
       </c>
       <c r="L126" s="77">
         <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
-        <v>0.16769807475078666</v>
+        <v>0.16750682678399942</v>
       </c>
       <c r="M126" s="77">
         <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
-        <v>0.15514987916755835</v>
+        <v>0.1549729415433061</v>
       </c>
       <c r="N126" s="77" t="str">
         <f t="shared" ref="N126" si="57">IF(N$4="","",N125/Market_Price)</f>
@@ -15492,7 +15492,7 @@
       </c>
       <c r="C8" s="338">
         <f>BS!D66</f>
-        <v>404629.46262395149</v>
+        <v>404998.6926536205</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
@@ -15524,7 +15524,7 @@
       </c>
       <c r="C10" s="347">
         <f>C6-C7+C8+C9</f>
-        <v>8784726.3114960957</v>
+        <v>8785095.5415257644</v>
       </c>
       <c r="D10" t="str">
         <f>Reporting_currency</f>
@@ -15538,7 +15538,7 @@
       </c>
       <c r="C11" s="208">
         <f>Exchange_Rate</f>
-        <v>9.2581720599999997</v>
+        <v>9.2476137599999984</v>
       </c>
       <c r="D11" t="str">
         <f>Thesis!C15</f>
@@ -15552,7 +15552,7 @@
       </c>
       <c r="C12" s="111">
         <f>(C10*scaling_factor)/Common_Shares*Exchange_Rate</f>
-        <v>31.784330493945657</v>
+        <v>31.749417080943548</v>
       </c>
       <c r="D12" t="str">
         <f>Market_currency</f>
@@ -15605,7 +15605,7 @@
       </c>
       <c r="C18" s="140">
         <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>33.047163950946597</v>
+        <v>33.010810364398061</v>
       </c>
       <c r="D18" t="str">
         <f>Market_currency</f>
@@ -16701,23 +16701,23 @@
       </c>
       <c r="B65" s="124">
         <f>C12</f>
-        <v>31.784330493945657</v>
+        <v>31.749417080943548</v>
       </c>
       <c r="C65" s="124">
         <f>C12</f>
-        <v>31.784330493945657</v>
+        <v>31.749417080943548</v>
       </c>
       <c r="D65" s="124">
         <f>C12</f>
-        <v>31.784330493945657</v>
+        <v>31.749417080943548</v>
       </c>
       <c r="E65" s="141">
         <f>C12</f>
-        <v>31.784330493945657</v>
+        <v>31.749417080943548</v>
       </c>
       <c r="F65" s="124">
         <f>C12</f>
-        <v>31.784330493945657</v>
+        <v>31.749417080943548</v>
       </c>
       <c r="H65" s="120"/>
     </row>
@@ -16728,23 +16728,23 @@
       </c>
       <c r="B66" s="124">
         <f t="shared" ref="B66:F71" si="4">(B56-$C$7+$C$8+$C$9)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>31.784330493945657</v>
+        <v>31.749417080943548</v>
       </c>
       <c r="C66" s="124">
         <f t="shared" si="4"/>
-        <v>32.310780694679856</v>
+        <v>32.275266901913966</v>
       </c>
       <c r="D66" s="124">
         <f t="shared" si="4"/>
-        <v>33.386517327244015</v>
+        <v>33.34977673182054</v>
       </c>
       <c r="E66" s="124">
         <f t="shared" si="4"/>
-        <v>34.493820960531032</v>
+        <v>34.455817562485663</v>
       </c>
       <c r="F66" s="124">
         <f t="shared" si="4"/>
-        <v>36.216992752390738</v>
+        <v>36.177024197010624</v>
       </c>
       <c r="H66" s="120"/>
     </row>
@@ -16755,23 +16755,23 @@
       </c>
       <c r="B67" s="124">
         <f t="shared" si="4"/>
-        <v>31.784330493945667</v>
+        <v>31.749417080943555</v>
       </c>
       <c r="C67" s="124">
         <f t="shared" si="4"/>
-        <v>32.815531536525214</v>
+        <v>32.779442110602062</v>
       </c>
       <c r="D67" s="124">
         <f t="shared" si="4"/>
-        <v>35.029747200479996</v>
+        <v>34.991132615908533</v>
       </c>
       <c r="E67" s="124">
         <f t="shared" si="4"/>
-        <v>37.466592283173988</v>
+        <v>37.425198646617979</v>
       </c>
       <c r="F67" s="124">
         <f t="shared" si="4"/>
-        <v>41.59836017401588</v>
+        <v>41.552254544137739</v>
       </c>
       <c r="H67" s="120"/>
     </row>
@@ -16782,23 +16782,23 @@
       </c>
       <c r="B68" s="124">
         <f t="shared" si="4"/>
-        <v>31.784330493945667</v>
+        <v>31.749417080943555</v>
       </c>
       <c r="C68" s="124">
         <f t="shared" si="4"/>
-        <v>33.438717730457476</v>
+        <v>33.401917604112164</v>
       </c>
       <c r="D68" s="124">
         <f t="shared" si="4"/>
-        <v>37.164382236880989</v>
+        <v>37.12333324982071</v>
       </c>
       <c r="E68" s="124">
         <f t="shared" si="4"/>
-        <v>41.537706980023437</v>
+        <v>41.491670520885904</v>
       </c>
       <c r="F68" s="124">
         <f t="shared" si="4"/>
-        <v>49.601676678747879</v>
+        <v>49.546443824175256</v>
       </c>
       <c r="H68" s="120"/>
     </row>
@@ -16809,23 +16809,23 @@
       </c>
       <c r="B69" s="124">
         <f t="shared" si="4"/>
-        <v>31.784330493945671</v>
+        <v>31.749417080943559</v>
       </c>
       <c r="C69" s="124">
         <f t="shared" si="4"/>
-        <v>34.07163740153181</v>
+        <v>34.034115474412026</v>
       </c>
       <c r="D69" s="124">
         <f t="shared" si="4"/>
-        <v>39.450731523282862</v>
+        <v>39.407075114205121</v>
       </c>
       <c r="E69" s="124">
         <f t="shared" si="4"/>
-        <v>46.151847142923117</v>
+        <v>46.100548578505396</v>
       </c>
       <c r="F69" s="124">
         <f t="shared" si="4"/>
-        <v>59.531209877922194</v>
+        <v>59.464653082759838</v>
       </c>
       <c r="H69" s="120"/>
     </row>
@@ -16836,23 +16836,23 @@
       </c>
       <c r="B70" s="124">
         <f t="shared" si="4"/>
-        <v>31.784330493945671</v>
+        <v>31.749417080943559</v>
       </c>
       <c r="C70" s="124">
         <f t="shared" si="4"/>
-        <v>34.658067431562152</v>
+        <v>34.619876721863477</v>
       </c>
       <c r="D70" s="124">
         <f t="shared" si="4"/>
-        <v>41.688866286056601</v>
+        <v>41.642657440265367</v>
       </c>
       <c r="E70" s="124">
         <f t="shared" si="4"/>
-        <v>50.94684608774007</v>
+        <v>50.890079161206046</v>
       </c>
       <c r="F70" s="124">
         <f t="shared" si="4"/>
-        <v>70.904685761852917</v>
+        <v>70.825158310102296</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="13.15">
@@ -16862,23 +16862,23 @@
       </c>
       <c r="B71" s="124">
         <f t="shared" si="4"/>
-        <v>31.784330493945667</v>
+        <v>31.749417080943555</v>
       </c>
       <c r="C71" s="124">
         <f t="shared" si="4"/>
-        <v>35.173116568476438</v>
+        <v>35.134338481132687</v>
       </c>
       <c r="D71" s="124">
         <f t="shared" si="4"/>
-        <v>43.769148334185708</v>
+        <v>43.720567071700728</v>
       </c>
       <c r="E71" s="124">
         <f t="shared" si="4"/>
-        <v>55.692342831888311</v>
+        <v>55.63016399704788</v>
       </c>
       <c r="F71" s="124">
         <f t="shared" si="4"/>
-        <v>83.388571627644609</v>
+        <v>83.294807174109778</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="13.15">
@@ -16913,7 +16913,7 @@
       </c>
       <c r="E74" s="135">
         <f>INDEX(B$65:F$71, MATCH(D74, A$65:A$71, 0), MATCH(C74, B$64:F$64, 0))</f>
-        <v>41.59836017401588</v>
+        <v>41.552254544137739</v>
       </c>
       <c r="F74" s="142">
         <f>Scenarios!C58</f>
@@ -16935,7 +16935,7 @@
       </c>
       <c r="E75" s="135">
         <f>INDEX(B$65:F$71, MATCH(D75, A$65:A$71, 0), MATCH(C75, B$64:F$64, 0))</f>
-        <v>34.493820960531032</v>
+        <v>34.455817562485663</v>
       </c>
       <c r="F75" s="142">
         <f>Scenarios!C40*(1-F$74-F$78)</f>
@@ -16958,7 +16958,7 @@
       </c>
       <c r="E76" s="135">
         <f>INDEX(B$65:F$71, MATCH(D76, A$65:A$71, 0), MATCH(C76, B$64:F$64, 0))</f>
-        <v>33.386517327244015</v>
+        <v>33.34977673182054</v>
       </c>
       <c r="F76" s="142">
         <f>Scenarios!C28*(1-F$74-F$78)</f>
@@ -16981,7 +16981,7 @@
       </c>
       <c r="E77" s="135">
         <f>INDEX(B$65:F$71, MATCH(D77, A$65:A$71, 0), MATCH(C77, B$64:F$64, 0))</f>
-        <v>32.310780694679856</v>
+        <v>32.275266901913966</v>
       </c>
       <c r="F77" s="142">
         <f>Scenarios!C34*(1-F$74-F$78)</f>
@@ -17004,7 +17004,7 @@
       </c>
       <c r="E78" s="135">
         <f>INDEX(B$65:F$71, MATCH(D78, A$65:A$71, 0), MATCH(C78, B$64:F$64, 0))</f>
-        <v>31.784330493945667</v>
+        <v>31.749417080943555</v>
       </c>
       <c r="F78" s="142">
         <f>Scenarios!C52</f>
@@ -17186,7 +17186,7 @@
       </c>
       <c r="C4" s="114">
         <f>Normalized_FCF!C91*(1-dividend_tax_rate)</f>
-        <v>3885165.3895742204</v>
+        <v>3880734.6292181914</v>
       </c>
       <c r="D4" t="str">
         <f>Market_currency</f>
@@ -17218,7 +17218,7 @@
       </c>
       <c r="C6" s="319">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
-        <v>51802205.194322944</v>
+        <v>51743128.389575884</v>
       </c>
       <c r="D6" t="str">
         <f>Reporting_currency</f>
@@ -17234,7 +17234,7 @@
       </c>
       <c r="C7" s="111">
         <f>(C6*scaling_factor)/Common_Shares*Exchange_Rate</f>
-        <v>187.42739976507471</v>
+        <v>187.00014775572234</v>
       </c>
       <c r="D7" t="str">
         <f>Market_currency</f>
@@ -17287,7 +17287,7 @@
       </c>
       <c r="C13" s="140">
         <f>F47/Common_Shares*scaling_factor</f>
-        <v>21.009012324947058</v>
+        <v>20.985053010582089</v>
       </c>
       <c r="D13" t="str">
         <f>Market_currency</f>
@@ -17322,7 +17322,7 @@
       </c>
       <c r="C16" s="123">
         <f>C4*(1+D16)</f>
-        <v>3977448.2439721748</v>
+        <v>3972912.2414522204</v>
       </c>
       <c r="D16" s="138">
         <f>IF($C$12&lt;B16,0,DDM!$C$11)</f>
@@ -17334,7 +17334,7 @@
       </c>
       <c r="F16" s="125">
         <f t="shared" ref="F16:F46" si="1">C16*E16</f>
-        <v>3699951.8548578368</v>
+        <v>3695732.3176299725</v>
       </c>
       <c r="H16" s="120"/>
     </row>
@@ -17344,7 +17344,7 @@
       </c>
       <c r="C17" s="123">
         <f t="shared" ref="C17:C45" si="2">IF(ROW()-ROW($C$16)&lt;$C$12, $C$16*(1+D17)^(ROW()-ROW($C$16)), 0)</f>
-        <v>4071923.0578781306</v>
+        <v>4067279.3134171967</v>
       </c>
       <c r="D17" s="138">
         <f>IF($C$12&lt;B17,0,DDM!$C$11)</f>
@@ -17356,7 +17356,7 @@
       </c>
       <c r="F17" s="125">
         <f t="shared" si="1"/>
-        <v>3523567.8164440286</v>
+        <v>3519549.4329191539</v>
       </c>
       <c r="H17" s="120"/>
     </row>
@@ -17366,7 +17366,7 @@
       </c>
       <c r="C18" s="123">
         <f t="shared" si="2"/>
-        <v>4168641.8960717916</v>
+        <v>4163887.8505165731</v>
       </c>
       <c r="D18" s="138">
         <f>IF($C$12&lt;B18,0,DDM!$C$11)</f>
@@ -17378,7 +17378,7 @@
       </c>
       <c r="F18" s="125">
         <f t="shared" si="1"/>
-        <v>3355592.3547435408</v>
+        <v>3351765.5355259376</v>
       </c>
       <c r="H18" s="120"/>
     </row>
@@ -17388,7 +17388,7 @@
       </c>
       <c r="C19" s="123">
         <f t="shared" si="2"/>
-        <v>4267658.0600077538</v>
+        <v>4262791.0934183495</v>
       </c>
       <c r="D19" s="138">
         <f>IF($C$12&lt;B19,0,DDM!$C$11)</f>
@@ -17400,7 +17400,7 @@
       </c>
       <c r="F19" s="125">
         <f t="shared" si="1"/>
-        <v>3195624.6162382225</v>
+        <v>3191980.2290776726</v>
       </c>
       <c r="H19" s="120"/>
     </row>
@@ -17410,7 +17410,7 @@
       </c>
       <c r="C20" s="123">
         <f t="shared" si="2"/>
-        <v>4369026.1171897706</v>
+        <v>4364043.5473958449</v>
       </c>
       <c r="D20" s="138">
         <f>IF($C$12&lt;B20,0,DDM!$C$11)</f>
@@ -17422,7 +17422,7 @@
       </c>
       <c r="F20" s="125">
         <f t="shared" si="1"/>
-        <v>3043282.8568916451</v>
+        <v>3039812.2048903992</v>
       </c>
       <c r="H20" s="120"/>
     </row>
@@ -17982,7 +17982,7 @@
       </c>
       <c r="C46" s="123">
         <f>C$16*(1+F4)^$C$12/Equity_Cost</f>
-        <v>53032643.252962336</v>
+        <v>52972163.219362937</v>
       </c>
       <c r="D46" s="139">
         <f>Terminal_Growth</f>
@@ -17994,7 +17994,7 @@
       </c>
       <c r="F46" s="125">
         <f t="shared" si="1"/>
-        <v>36940345.45419506</v>
+        <v>36898217.564706571</v>
       </c>
       <c r="H46" s="120"/>
     </row>
@@ -18005,7 +18005,7 @@
       </c>
       <c r="F47" s="137">
         <f>SUM(F16:F46)</f>
-        <v>53758364.953370333</v>
+        <v>53697057.284749702</v>
       </c>
       <c r="H47" s="120"/>
     </row>
@@ -18026,7 +18026,7 @@
     <row r="50" spans="1:8" ht="13.15">
       <c r="A50" s="133">
         <f>F47</f>
-        <v>53758364.953370333</v>
+        <v>53697057.284749702</v>
       </c>
       <c r="B50" s="131">
         <f>C73</f>
@@ -18056,19 +18056,19 @@
       </c>
       <c r="B51" s="123">
         <f t="dataTable" ref="B51:F56" dt2D="1" dtr="1" r1="C11" r2="C12"/>
-        <v>51802205.194322944</v>
+        <v>51743128.389575884</v>
       </c>
       <c r="C51" s="123">
-        <v>52617689.367718488</v>
+        <v>52557682.560105629</v>
       </c>
       <c r="D51" s="123">
-        <v>54284031.592252709</v>
+        <v>54222124.437465981</v>
       </c>
       <c r="E51" s="123">
-        <v>55999271.869167089</v>
+        <v>55935408.602385655</v>
       </c>
       <c r="F51" s="123">
-        <v>58668506.912374422</v>
+        <v>58601599.569054544</v>
       </c>
       <c r="H51" s="120"/>
     </row>
@@ -18077,19 +18077,19 @@
         <v>10</v>
       </c>
       <c r="B52" s="123">
-        <v>51802205.194322944</v>
+        <v>51743128.389575899</v>
       </c>
       <c r="C52" s="123">
-        <v>53399560.706088059</v>
+        <v>53338662.228705138</v>
       </c>
       <c r="D52" s="123">
-        <v>56829434.657929003</v>
+        <v>56764624.648343928</v>
       </c>
       <c r="E52" s="123">
-        <v>60604166.997630522</v>
+        <v>60535052.168886326</v>
       </c>
       <c r="F52" s="123">
-        <v>67004376.017261416</v>
+        <v>66927962.196183309</v>
       </c>
       <c r="H52" s="120"/>
     </row>
@@ -18098,19 +18098,19 @@
         <v>15</v>
       </c>
       <c r="B53" s="123">
-        <v>51802205.194322944</v>
+        <v>51743128.389575899</v>
       </c>
       <c r="C53" s="123">
-        <v>54364891.287255332</v>
+        <v>54302891.917621866</v>
       </c>
       <c r="D53" s="123">
-        <v>60136036.280899152</v>
+        <v>60067455.322611719</v>
       </c>
       <c r="E53" s="123">
-        <v>66910422.743622713</v>
+        <v>66834116.069705263</v>
       </c>
       <c r="F53" s="123">
-        <v>79401708.063449845</v>
+        <v>79311155.949186534</v>
       </c>
       <c r="H53" s="120"/>
     </row>
@@ -18119,19 +18119,19 @@
         <v>20</v>
       </c>
       <c r="B54" s="123">
-        <v>51802205.194322951</v>
+        <v>51743128.389575899</v>
       </c>
       <c r="C54" s="123">
-        <v>55345299.261403762</v>
+        <v>55282181.804803833</v>
       </c>
       <c r="D54" s="123">
-        <v>63677646.969459444</v>
+        <v>63605027.051008962</v>
       </c>
       <c r="E54" s="123">
-        <v>74057838.152384788</v>
+        <v>73973380.349322051</v>
       </c>
       <c r="F54" s="123">
-        <v>94782796.648542315</v>
+        <v>94674703.474709615</v>
       </c>
       <c r="H54" s="120"/>
     </row>
@@ -18140,19 +18140,19 @@
         <v>25</v>
       </c>
       <c r="B55" s="123">
-        <v>51802205.194322944</v>
+        <v>51743128.389575899</v>
       </c>
       <c r="C55" s="123">
-        <v>56253693.650135458</v>
+        <v>56189540.233044356</v>
       </c>
       <c r="D55" s="123">
-        <v>67144572.187500939</v>
+        <v>67067998.482461445</v>
       </c>
       <c r="E55" s="123">
-        <v>81485408.215979248</v>
+        <v>81392479.786912352</v>
       </c>
       <c r="F55" s="123">
-        <v>112400587.5942132</v>
+        <v>112272402.5576525</v>
       </c>
       <c r="H55" s="120"/>
     </row>
@@ -18161,19 +18161,19 @@
         <v>30</v>
       </c>
       <c r="B56" s="123">
-        <v>51802205.194322944</v>
+        <v>51743128.389575899</v>
       </c>
       <c r="C56" s="123">
-        <v>57051517.298201077</v>
+        <v>56986454.018842474</v>
       </c>
       <c r="D56" s="123">
-        <v>70366979.70882453</v>
+        <v>70286731.072587833</v>
       </c>
       <c r="E56" s="123">
-        <v>88836298.165980265</v>
+        <v>88734986.559234679</v>
       </c>
       <c r="F56" s="123">
-        <v>131738430.62634011</v>
+        <v>131588192.12752329</v>
       </c>
       <c r="H56" s="120"/>
     </row>
@@ -18223,23 +18223,23 @@
       </c>
       <c r="B60" s="124">
         <f>C7</f>
-        <v>187.42739976507471</v>
+        <v>187.00014775572234</v>
       </c>
       <c r="C60" s="124">
         <f>C7</f>
-        <v>187.42739976507471</v>
+        <v>187.00014775572234</v>
       </c>
       <c r="D60" s="124">
         <f>C7</f>
-        <v>187.42739976507471</v>
+        <v>187.00014775572234</v>
       </c>
       <c r="E60" s="141">
         <f>C7</f>
-        <v>187.42739976507471</v>
+        <v>187.00014775572234</v>
       </c>
       <c r="F60" s="124">
         <f>C7</f>
-        <v>187.42739976507471</v>
+        <v>187.00014775572234</v>
       </c>
       <c r="H60" s="120"/>
     </row>
@@ -18250,23 +18250,23 @@
       </c>
       <c r="B61" s="124">
         <f t="shared" ref="B61:F66" si="4">B51/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>187.42739976507474</v>
+        <v>187.00014775572237</v>
       </c>
       <c r="C61" s="124">
         <f t="shared" si="4"/>
-        <v>190.37793203673655</v>
+        <v>189.94395411194549</v>
       </c>
       <c r="D61" s="124">
         <f t="shared" si="4"/>
-        <v>196.40698406437932</v>
+        <v>195.95926255355687</v>
       </c>
       <c r="E61" s="124">
         <f t="shared" si="4"/>
-        <v>202.61295587327095</v>
+        <v>202.1510874771551</v>
       </c>
       <c r="F61" s="124">
         <f t="shared" si="4"/>
-        <v>212.27061005292342</v>
+        <v>211.78672645433946</v>
       </c>
       <c r="H61" s="120"/>
     </row>
@@ -18277,23 +18277,23 @@
       </c>
       <c r="B62" s="124">
         <f t="shared" si="4"/>
-        <v>187.42739976507474</v>
+        <v>187.00014775572242</v>
       </c>
       <c r="C62" s="124">
         <f t="shared" si="4"/>
-        <v>193.20684851532511</v>
+        <v>192.76642190559639</v>
       </c>
       <c r="D62" s="124">
         <f t="shared" si="4"/>
-        <v>205.61659736489653</v>
+        <v>205.14788198768667</v>
       </c>
       <c r="E62" s="124">
         <f t="shared" si="4"/>
-        <v>219.27409060452652</v>
+        <v>218.77424215159422</v>
       </c>
       <c r="F62" s="124">
         <f t="shared" si="4"/>
-        <v>242.43091433437536</v>
+        <v>241.87827851160705</v>
       </c>
       <c r="H62" s="120"/>
     </row>
@@ -18304,23 +18304,23 @@
       </c>
       <c r="B63" s="124">
         <f t="shared" si="4"/>
-        <v>187.42739976507474</v>
+        <v>187.00014775572242</v>
       </c>
       <c r="C63" s="124">
         <f t="shared" si="4"/>
-        <v>196.6995454007797</v>
+        <v>196.25115697882805</v>
       </c>
       <c r="D63" s="124">
         <f t="shared" si="4"/>
-        <v>217.58033022004125</v>
+        <v>217.08434279558472</v>
       </c>
       <c r="E63" s="124">
         <f t="shared" si="4"/>
-        <v>242.0909786557404</v>
+        <v>241.53911773675853</v>
       </c>
       <c r="F63" s="124">
         <f t="shared" si="4"/>
-        <v>287.28614203607128</v>
+        <v>286.63125602902079</v>
       </c>
       <c r="H63" s="120"/>
     </row>
@@ -18331,23 +18331,23 @@
       </c>
       <c r="B64" s="124">
         <f t="shared" si="4"/>
-        <v>187.42739976507474</v>
+        <v>187.00014775572242</v>
       </c>
       <c r="C64" s="124">
         <f t="shared" si="4"/>
-        <v>200.24679433765937</v>
+        <v>199.79031974880863</v>
       </c>
       <c r="D64" s="124">
         <f t="shared" si="4"/>
-        <v>230.39435772807866</v>
+        <v>229.86915995866957</v>
       </c>
       <c r="E64" s="124">
         <f t="shared" si="4"/>
-        <v>267.95129637927846</v>
+        <v>267.34048531360656</v>
       </c>
       <c r="F64" s="124">
         <f t="shared" si="4"/>
-        <v>342.93700531970785</v>
+        <v>342.15525982898555</v>
       </c>
       <c r="H64" s="120"/>
     </row>
@@ -18358,23 +18358,23 @@
       </c>
       <c r="B65" s="124">
         <f t="shared" si="4"/>
-        <v>187.42739976507474</v>
+        <v>187.00014775572242</v>
       </c>
       <c r="C65" s="124">
         <f t="shared" si="4"/>
-        <v>203.53348836163934</v>
+        <v>203.06952155645502</v>
       </c>
       <c r="D65" s="124">
         <f t="shared" si="4"/>
-        <v>242.93816308076455</v>
+        <v>242.3843709540279</v>
       </c>
       <c r="E65" s="124">
         <f t="shared" si="4"/>
-        <v>294.8252516167089</v>
+        <v>294.15317975678374</v>
       </c>
       <c r="F65" s="124">
         <f t="shared" si="4"/>
-        <v>406.68056091092132</v>
+        <v>405.75350815859412</v>
       </c>
     </row>
     <row r="66" spans="1:8" ht="13.15">
@@ -18384,23 +18384,23 @@
       </c>
       <c r="B66" s="124">
         <f t="shared" si="4"/>
-        <v>187.42739976507474</v>
+        <v>187.00014775572242</v>
       </c>
       <c r="C66" s="124">
         <f t="shared" si="4"/>
-        <v>206.42012245891544</v>
+        <v>205.94957539801678</v>
       </c>
       <c r="D66" s="124">
         <f t="shared" si="4"/>
-        <v>254.59727026431912</v>
+        <v>254.01690050284139</v>
       </c>
       <c r="E66" s="124">
         <f t="shared" si="4"/>
-        <v>321.42176780978593</v>
+        <v>320.68906759456434</v>
       </c>
       <c r="F66" s="124">
         <f t="shared" si="4"/>
-        <v>476.64749809015018</v>
+        <v>475.56095150428786</v>
       </c>
     </row>
     <row r="68" spans="1:8" ht="13.15">
@@ -18435,7 +18435,7 @@
       </c>
       <c r="E69" s="135">
         <f>INDEX(B$60:F$66, MATCH(D69, A$60:A$66, 0), MATCH(C69, B$59:F$59, 0))</f>
-        <v>242.43091433437536</v>
+        <v>241.87827851160705</v>
       </c>
       <c r="F69" s="142">
         <f>Scenarios!C58</f>
@@ -18457,7 +18457,7 @@
       </c>
       <c r="E70" s="135">
         <f>INDEX(B$60:F$66, MATCH(D70, A$60:A$66, 0), MATCH(C70, B$59:F$59, 0))</f>
-        <v>202.61295587327095</v>
+        <v>202.1510874771551</v>
       </c>
       <c r="F70" s="142">
         <f>Scenarios!C40*(1-F$69-F$73)</f>
@@ -18480,7 +18480,7 @@
       </c>
       <c r="E71" s="135">
         <f>INDEX(B$60:F$66, MATCH(D71, A$60:A$66, 0), MATCH(C71, B$59:F$59, 0))</f>
-        <v>196.40698406437932</v>
+        <v>195.95926255355687</v>
       </c>
       <c r="F71" s="142">
         <f>Scenarios!C28*(1-F$69-F$73)</f>
@@ -18503,7 +18503,7 @@
       </c>
       <c r="E72" s="135">
         <f>INDEX(B$60:F$66, MATCH(D72, A$60:A$66, 0), MATCH(C72, B$59:F$59, 0))</f>
-        <v>190.37793203673655</v>
+        <v>189.94395411194549</v>
       </c>
       <c r="F72" s="142">
         <f>Scenarios!C34*(1-F$69-F$73)</f>
@@ -18526,7 +18526,7 @@
       </c>
       <c r="E73" s="135">
         <f>INDEX(B$60:F$66, MATCH(D73, A$60:A$66, 0), MATCH(C73, B$59:F$59, 0))</f>
-        <v>187.42739976507474</v>
+        <v>187.00014775572242</v>
       </c>
       <c r="F73" s="142">
         <f>Scenarios!C52</f>
@@ -18646,7 +18646,7 @@
       </c>
       <c r="I4" s="124">
         <f t="shared" ref="I4:I13" si="0">IF(ROW()-3 &lt; $C$76, $C$77, IF(ROW()-3 = $C$76, $C$77 + $C$60, ""))</f>
-        <v>1.5183402178400001</v>
+        <v>1.5166086566399999</v>
       </c>
     </row>
     <row r="5" spans="2:9">
@@ -18655,7 +18655,7 @@
       </c>
       <c r="I5" s="124">
         <f t="shared" si="0"/>
-        <v>1.5183402178400001</v>
+        <v>1.5166086566399999</v>
       </c>
     </row>
     <row r="6" spans="2:9" ht="13.15">
@@ -18675,7 +18675,7 @@
       </c>
       <c r="I6" s="124">
         <f t="shared" si="0"/>
-        <v>35.241022405887797</v>
+        <v>35.202166876669089</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1">
@@ -18881,7 +18881,7 @@
       </c>
       <c r="C22" s="160">
         <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
-        <v>31.784330493945657</v>
+        <v>31.749417080943548</v>
       </c>
       <c r="D22" t="str">
         <f>Market_currency</f>
@@ -18928,7 +18928,7 @@
       </c>
       <c r="C27" s="160">
         <f>IF(valuation_method="DCF",DCF!E76,DDM!E71)</f>
-        <v>33.386517327244015</v>
+        <v>33.34977673182054</v>
       </c>
       <c r="D27" s="160" t="str">
         <f>Market_currency</f>
@@ -18986,7 +18986,7 @@
       </c>
       <c r="C33" s="160">
         <f>IF(valuation_method="DCF",DCF!E77,DDM!E72)</f>
-        <v>32.310780694679856</v>
+        <v>32.275266901913966</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
@@ -19044,7 +19044,7 @@
       </c>
       <c r="C39" s="160">
         <f>IF(valuation_method="DCF",DCF!E75,DDM!E70)</f>
-        <v>34.493820960531032</v>
+        <v>34.455817562485663</v>
       </c>
       <c r="D39" t="str">
         <f>Market_currency</f>
@@ -19071,7 +19071,7 @@
       </c>
       <c r="C42" s="154">
         <f>C27*C28+C33*C34+C39*C40</f>
-        <v>33.392830727388585</v>
+        <v>33.356082931972253</v>
       </c>
       <c r="D42" t="str">
         <f>Market_currency</f>
@@ -19145,7 +19145,7 @@
       </c>
       <c r="C51" s="160">
         <f>IF(valuation_method="DCF",DCF!E78,DDM!E73)</f>
-        <v>31.784330493945667</v>
+        <v>31.749417080943555</v>
       </c>
       <c r="D51" t="str">
         <f>Market_currency</f>
@@ -19203,7 +19203,7 @@
       </c>
       <c r="C57" s="160">
         <f>IF(valuation_method="DCF",DCF!E74,DDM!E69)</f>
-        <v>41.59836017401588</v>
+        <v>41.552254544137739</v>
       </c>
       <c r="D57" t="str">
         <f>Market_currency</f>
@@ -19229,7 +19229,7 @@
       </c>
       <c r="C60" s="154">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
-        <v>33.722682188047798</v>
+        <v>33.685558220029087</v>
       </c>
       <c r="D60" t="str">
         <f>Market_currency</f>
@@ -19291,7 +19291,7 @@
       </c>
       <c r="C66" s="160">
         <f>IF(valuation_method="DCF",DCF!C18,DDM!C13)</f>
-        <v>33.047163950946597</v>
+        <v>33.010810364398061</v>
       </c>
       <c r="D66" s="160" t="str">
         <f>Market_currency</f>
@@ -19354,7 +19354,7 @@
       </c>
       <c r="F72" s="291">
         <f>BS!D89/C60</f>
-        <v>-4.9150815604021243E-2</v>
+        <v>-4.9109255133455619E-2</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="13.9">
@@ -19387,7 +19387,7 @@
       </c>
       <c r="C77" s="173">
         <f>Normalized_FCF!C90*(1-dividend_tax_rate)</f>
-        <v>1.5183402178400001</v>
+        <v>1.5166086566399999</v>
       </c>
       <c r="D77" t="str">
         <f>Market_currency</f>
@@ -19405,7 +19405,7 @@
       </c>
       <c r="C80" s="167">
         <f>Thesis!F29</f>
-        <v>0.3674</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="81" spans="2:8">
@@ -19414,7 +19414,7 @@
       </c>
       <c r="C81" s="116">
         <f>PV(C80, C76, -C77, 0)</f>
-        <v>2.51628347598181</v>
+        <v>2.5719858232303614</v>
       </c>
       <c r="D81" s="116"/>
       <c r="E81" s="100"/>
@@ -19426,7 +19426,7 @@
       </c>
       <c r="C82" s="116">
         <f>C60/(1+C80)^C76</f>
-        <v>13.189714132161143</v>
+        <v>13.691229271972395</v>
       </c>
       <c r="D82" s="116"/>
     </row>
@@ -19436,7 +19436,7 @@
       </c>
       <c r="C83" s="111">
         <f>C81+C82</f>
-        <v>15.705997608142953</v>
+        <v>16.263215095202757</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -19447,7 +19447,7 @@
       </c>
       <c r="F83" s="291">
         <f>(1-C83/C60)</f>
-        <v>0.53426013030156994</v>
+        <v>0.51720511831884042</v>
       </c>
     </row>
     <row r="84" spans="2:8">
@@ -19477,7 +19477,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>-9.1448907953051495E-2</v>
+        <v>-9.1795592256709635E-2</v>
       </c>
     </row>
     <row r="88" spans="2:8">
@@ -19494,7 +19494,7 @@
       </c>
       <c r="C90" s="167">
         <f>Thesis!F30</f>
-        <v>0.21740000000000001</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="91" spans="2:8">
@@ -19503,7 +19503,7 @@
       </c>
       <c r="C91" s="116">
         <f>PV(C90, C76, -C77, 0)</f>
-        <v>3.1132060335664034</v>
+        <v>2.96042009776128</v>
       </c>
       <c r="D91" s="116"/>
       <c r="E91" s="100"/>
@@ -19515,7 +19515,7 @@
       </c>
       <c r="C92" s="116">
         <f>C60/(1+C90)^C76</f>
-        <v>18.6905558528473</v>
+        <v>17.247005808654894</v>
       </c>
       <c r="D92" s="116"/>
     </row>
@@ -19525,7 +19525,7 @@
       </c>
       <c r="C93" s="111">
         <f>C91+C92</f>
-        <v>21.803761886413703</v>
+        <v>20.207425906416173</v>
       </c>
       <c r="D93" t="str">
         <f>Market_currency</f>
@@ -19536,7 +19536,7 @@
       </c>
       <c r="F93" s="291">
         <f>(1-C93/C60)</f>
-        <v>0.35343927375558737</v>
+        <v>0.40011604455463512</v>
       </c>
     </row>
     <row r="95" spans="2:8" ht="13.15">
@@ -19563,7 +19563,7 @@
       </c>
       <c r="C97" s="116">
         <f>PV(C96, C76, -C77, 0)</f>
-        <v>3.948482818375719</v>
+        <v>3.9439798489049545</v>
       </c>
       <c r="D97" s="116"/>
       <c r="G97" s="2"/>
@@ -19575,7 +19575,7 @@
       </c>
       <c r="C98" s="116">
         <f>C60/(1+C96)^C76</f>
-        <v>27.145429459482301</v>
+        <v>27.115546129043505</v>
       </c>
       <c r="D98" s="116"/>
       <c r="G98" s="2"/>
@@ -19587,7 +19587,7 @@
       </c>
       <c r="C99" s="111">
         <f>C97+C98</f>
-        <v>31.093912277858021</v>
+        <v>31.059525977948461</v>
       </c>
       <c r="D99" t="s">
         <v>393</v>
@@ -19597,7 +19597,7 @@
       </c>
       <c r="F99" s="291">
         <f>(1-C99/C60)</f>
-        <v>7.7952574932532603E-2</v>
+        <v>7.7957213145401161E-2</v>
       </c>
     </row>
     <row r="100" spans="2:8">
@@ -19623,7 +19623,7 @@
       </c>
       <c r="C103" s="116">
         <f>PV(C102, C76, -C77, 0)</f>
-        <v>3.6631523557991534</v>
+        <v>3.6589747858352792</v>
       </c>
       <c r="D103" s="116"/>
     </row>
@@ -19633,7 +19633,7 @@
       </c>
       <c r="C104" s="116">
         <f>C60/(1+C102)^C76</f>
-        <v>24.171082938618422</v>
+        <v>24.144473948711063</v>
       </c>
       <c r="D104" s="116"/>
     </row>
@@ -19643,7 +19643,7 @@
       </c>
       <c r="C105" s="111">
         <f>C103+C104</f>
-        <v>27.834235294417574</v>
+        <v>27.803448734546343</v>
       </c>
       <c r="D105" t="s">
         <v>393</v>
@@ -19653,7 +19653,7 @@
       </c>
       <c r="F105" s="291">
         <f>(1-C105/C66)</f>
-        <v>0.15774208837607995</v>
+        <v>0.15774716138043743</v>
       </c>
     </row>
     <row r="106" spans="2:8">

--- a/financial_models/opportunities/1913.HK_Valuation.xlsx
+++ b/financial_models/opportunities/1913.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5103535-173A-4940-BF32-9C42B9D67B12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82945DBC-FF26-4930-AEF6-0A671AD19A6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3896,29 +3896,29 @@
     <xf numFmtId="10" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4336,7 +4336,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>50.5</v>
+        <v>49.5</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4357,7 +4357,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>129220.61199999999</v>
+        <v>126661.788</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4384,7 +4384,7 @@
         <v>1</v>
       </c>
       <c r="C16" s="50">
-        <v>9.2476137599999984</v>
+        <v>9.2078154000000012</v>
       </c>
       <c r="D16" s="50"/>
       <c r="E16" s="5"/>
@@ -4394,13 +4394,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="360" t="s">
+      <c r="B18" s="358" t="s">
         <v>356</v>
       </c>
-      <c r="C18" s="360"/>
-      <c r="D18" s="360"/>
-      <c r="E18" s="360"/>
-      <c r="F18" s="360"/>
+      <c r="C18" s="358"/>
+      <c r="D18" s="358"/>
+      <c r="E18" s="358"/>
+      <c r="F18" s="358"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4476,14 +4476,14 @@
       </c>
       <c r="C26" s="304">
         <f>C132</f>
-        <v>33.685558220029087</v>
+        <v>33.545596083057383</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>396</v>
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>-9.1795592256709635E-2</v>
+        <v>-8.6822328085409906E-2</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4515,7 +4515,7 @@
       </c>
       <c r="C29" s="310">
         <f>C149</f>
-        <v>16.263215095202757</v>
+        <v>16.195259699486208</v>
       </c>
       <c r="D29" s="310" t="str">
         <f>D149</f>
@@ -4534,7 +4534,7 @@
       </c>
       <c r="C30" s="311">
         <f>C157</f>
-        <v>20.207425906416173</v>
+        <v>20.123024722896581</v>
       </c>
       <c r="D30" s="311" t="str">
         <f>D157</f>
@@ -4553,7 +4553,7 @@
       </c>
       <c r="C31" s="311">
         <f>C165</f>
-        <v>31.059525977948461</v>
+        <v>30.929888524290046</v>
       </c>
       <c r="D31" s="311" t="str">
         <f>D165</f>
@@ -4572,7 +4572,7 @@
       </c>
       <c r="C32" s="311">
         <f>C173</f>
-        <v>27.803448734546343</v>
+        <v>27.687382524013426</v>
       </c>
       <c r="D32" s="311" t="str">
         <f>D173</f>
@@ -4600,22 +4600,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="360" t="s">
+      <c r="B36" s="358" t="s">
         <v>357</v>
       </c>
-      <c r="C36" s="360"/>
-      <c r="D36" s="360"/>
-      <c r="E36" s="360"/>
-      <c r="F36" s="360"/>
+      <c r="C36" s="358"/>
+      <c r="D36" s="358"/>
+      <c r="E36" s="358"/>
+      <c r="F36" s="358"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="363" t="s">
+      <c r="B37" s="360" t="s">
         <v>336</v>
       </c>
-      <c r="C37" s="363"/>
-      <c r="D37" s="363"/>
-      <c r="E37" s="363"/>
-      <c r="F37" s="363"/>
+      <c r="C37" s="360"/>
+      <c r="D37" s="360"/>
+      <c r="E37" s="360"/>
+      <c r="F37" s="360"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4627,13 +4627,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="361" t="s">
+      <c r="B40" s="359" t="s">
         <v>230</v>
       </c>
-      <c r="C40" s="361"/>
-      <c r="D40" s="361"/>
-      <c r="E40" s="361"/>
-      <c r="F40" s="361"/>
+      <c r="C40" s="359"/>
+      <c r="D40" s="359"/>
+      <c r="E40" s="359"/>
+      <c r="F40" s="359"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4653,13 +4653,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="361" t="s">
+      <c r="B43" s="359" t="s">
         <v>232</v>
       </c>
-      <c r="C43" s="361"/>
-      <c r="D43" s="361"/>
-      <c r="E43" s="361"/>
-      <c r="F43" s="361"/>
+      <c r="C43" s="359"/>
+      <c r="D43" s="359"/>
+      <c r="E43" s="359"/>
+      <c r="F43" s="359"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4688,13 +4688,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="361" t="s">
+      <c r="B47" s="359" t="s">
         <v>235</v>
       </c>
-      <c r="C47" s="361"/>
-      <c r="D47" s="361"/>
-      <c r="E47" s="361"/>
-      <c r="F47" s="361"/>
+      <c r="C47" s="359"/>
+      <c r="D47" s="359"/>
+      <c r="E47" s="359"/>
+      <c r="F47" s="359"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4710,13 +4710,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="361" t="s">
+      <c r="B50" s="359" t="s">
         <v>239</v>
       </c>
-      <c r="C50" s="361"/>
-      <c r="D50" s="361"/>
-      <c r="E50" s="361"/>
-      <c r="F50" s="361"/>
+      <c r="C50" s="359"/>
+      <c r="D50" s="359"/>
+      <c r="E50" s="359"/>
+      <c r="F50" s="359"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4780,13 +4780,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="361" t="s">
+      <c r="B58" s="359" t="s">
         <v>240</v>
       </c>
-      <c r="C58" s="361"/>
-      <c r="D58" s="361"/>
-      <c r="E58" s="361"/>
-      <c r="F58" s="361"/>
+      <c r="C58" s="359"/>
+      <c r="D58" s="359"/>
+      <c r="E58" s="359"/>
+      <c r="F58" s="359"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4802,7 +4802,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="361" t="s">
+      <c r="B61" s="359" t="s">
         <v>335</v>
       </c>
       <c r="C61" s="362"/>
@@ -4824,22 +4824,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="360" t="s">
+      <c r="B64" s="358" t="s">
         <v>340</v>
       </c>
-      <c r="C64" s="360"/>
-      <c r="D64" s="360"/>
-      <c r="E64" s="360"/>
-      <c r="F64" s="360"/>
+      <c r="C64" s="358"/>
+      <c r="D64" s="358"/>
+      <c r="E64" s="358"/>
+      <c r="F64" s="358"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="360" t="s">
+      <c r="B65" s="358" t="s">
         <v>358</v>
       </c>
-      <c r="C65" s="360"/>
-      <c r="D65" s="360"/>
-      <c r="E65" s="360"/>
-      <c r="F65" s="360"/>
+      <c r="C65" s="358"/>
+      <c r="D65" s="358"/>
+      <c r="E65" s="358"/>
+      <c r="F65" s="358"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4873,7 +4873,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>4.9609440228540344E-2</v>
+        <v>5.0393837037482521E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4883,14 +4883,14 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>3.0031854586930692E-2</v>
+        <v>3.0506701527272733E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>444</v>
       </c>
       <c r="F70" s="315">
         <f>Normalized_FCF!C92</f>
-        <v>5.5981883777967951</v>
+        <v>5.5740958148730426</v>
       </c>
     </row>
     <row r="72" spans="1:6">
@@ -4974,22 +4974,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.6" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="360" t="s">
+      <c r="B80" s="358" t="s">
         <v>359</v>
       </c>
-      <c r="C80" s="360"/>
-      <c r="D80" s="360"/>
-      <c r="E80" s="360"/>
-      <c r="F80" s="360"/>
+      <c r="C80" s="358"/>
+      <c r="D80" s="358"/>
+      <c r="E80" s="358"/>
+      <c r="F80" s="358"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="363" t="s">
+      <c r="B81" s="360" t="s">
         <v>251</v>
       </c>
-      <c r="C81" s="363"/>
-      <c r="D81" s="363"/>
-      <c r="E81" s="363"/>
-      <c r="F81" s="363"/>
+      <c r="C81" s="360"/>
+      <c r="D81" s="360"/>
+      <c r="E81" s="360"/>
+      <c r="F81" s="360"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5033,22 +5033,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="360" t="s">
+      <c r="B89" s="358" t="s">
         <v>360</v>
       </c>
-      <c r="C89" s="360"/>
-      <c r="D89" s="360"/>
-      <c r="E89" s="360"/>
-      <c r="F89" s="360"/>
+      <c r="C89" s="358"/>
+      <c r="D89" s="358"/>
+      <c r="E89" s="358"/>
+      <c r="F89" s="358"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="360" t="s">
+      <c r="B90" s="358" t="s">
         <v>361</v>
       </c>
-      <c r="C90" s="360"/>
-      <c r="D90" s="360"/>
-      <c r="E90" s="360"/>
-      <c r="F90" s="360"/>
+      <c r="C90" s="358"/>
+      <c r="D90" s="358"/>
+      <c r="E90" s="358"/>
+      <c r="F90" s="358"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5064,7 +5064,7 @@
       </c>
       <c r="C93" s="223">
         <f>DCF!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>33.403689753883825</v>
+        <v>33.259932444738453</v>
       </c>
       <c r="D93" s="1" t="str">
         <f>Market_currency</f>
@@ -5085,13 +5085,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="360" t="s">
+      <c r="B97" s="358" t="s">
         <v>362</v>
       </c>
-      <c r="C97" s="360"/>
-      <c r="D97" s="360"/>
-      <c r="E97" s="360"/>
-      <c r="F97" s="360"/>
+      <c r="C97" s="358"/>
+      <c r="D97" s="358"/>
+      <c r="E97" s="358"/>
+      <c r="F97" s="358"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5104,13 +5104,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="360" t="s">
+      <c r="B101" s="358" t="s">
         <v>341</v>
       </c>
-      <c r="C101" s="360"/>
-      <c r="D101" s="360"/>
-      <c r="E101" s="360"/>
-      <c r="F101" s="360"/>
+      <c r="C101" s="358"/>
+      <c r="D101" s="358"/>
+      <c r="E101" s="358"/>
+      <c r="F101" s="358"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="C103" s="223">
         <f>C102*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>3.1315390675716652</v>
+        <v>3.1180620644874368</v>
       </c>
       <c r="D103" s="1" t="str">
         <f>Market_currency</f>
@@ -5180,7 +5180,7 @@
       </c>
       <c r="C109" s="349">
         <f>DCF!C8</f>
-        <v>404998.6926536205</v>
+        <v>406390.46496957855</v>
       </c>
       <c r="D109" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5193,7 +5193,7 @@
       </c>
       <c r="C110" s="223">
         <f>C109*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>1.4636690460014565</v>
+        <v>1.4623781791010426</v>
       </c>
       <c r="D110" s="1" t="str">
         <f>Market_currency</f>
@@ -5224,7 +5224,7 @@
       </c>
       <c r="C114" s="223">
         <f>C113*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>1.359734862992687E-2</v>
+        <v>1.3538830595992535E-2</v>
       </c>
       <c r="D114" s="1" t="str">
         <f>Market_currency</f>
@@ -5232,13 +5232,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="360" t="s">
+      <c r="B116" s="358" t="s">
         <v>363</v>
       </c>
-      <c r="C116" s="360"/>
-      <c r="D116" s="360"/>
-      <c r="E116" s="360"/>
-      <c r="F116" s="360"/>
+      <c r="C116" s="358"/>
+      <c r="D116" s="358"/>
+      <c r="E116" s="358"/>
+      <c r="F116" s="358"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="C118" s="223">
         <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
-        <v>31.749417080943548</v>
+        <v>31.617787389948063</v>
       </c>
       <c r="D118" s="1" t="str">
         <f>Market_currency</f>
@@ -5259,7 +5259,7 @@
       </c>
       <c r="C119" s="223">
         <f>BS!D47</f>
-        <v>-6.0099460564163278</v>
+        <v>-5.9840814384790599</v>
       </c>
       <c r="D119" s="1" t="str">
         <f>Market_currency</f>
@@ -5277,13 +5277,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B123" s="361" t="s">
+      <c r="B123" s="359" t="s">
         <v>364</v>
       </c>
-      <c r="C123" s="361"/>
-      <c r="D123" s="361"/>
-      <c r="E123" s="361"/>
-      <c r="F123" s="361"/>
+      <c r="C123" s="359"/>
+      <c r="D123" s="359"/>
+      <c r="E123" s="359"/>
+      <c r="F123" s="359"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5317,7 +5317,7 @@
       </c>
       <c r="E126" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E74,DDM!E69),2)&amp;" "&amp;Market_currency</f>
-        <v>41.55 HKD</v>
+        <v>41.38 HKD</v>
       </c>
       <c r="F126" s="232">
         <f>DCF!F74</f>
@@ -5339,7 +5339,7 @@
       </c>
       <c r="E127" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E75,DDM!E70),2)&amp;" "&amp;Market_currency</f>
-        <v>34.46 HKD</v>
+        <v>34.31 HKD</v>
       </c>
       <c r="F127" s="221">
         <f>DCF!F75</f>
@@ -5361,7 +5361,7 @@
       </c>
       <c r="E128" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E76,DDM!E71),2)&amp;" "&amp;Market_currency</f>
-        <v>33.35 HKD</v>
+        <v>33.21 HKD</v>
       </c>
       <c r="F128" s="221">
         <f>DCF!F76</f>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="E129" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E77,DDM!E72),2)&amp;" "&amp;Market_currency</f>
-        <v>32.28 HKD</v>
+        <v>32.14 HKD</v>
       </c>
       <c r="F129" s="221">
         <f>DCF!F77</f>
@@ -5405,7 +5405,7 @@
       </c>
       <c r="E130" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E78,DDM!E73),2)&amp;" "&amp;Market_currency</f>
-        <v>31.75 HKD</v>
+        <v>31.62 HKD</v>
       </c>
       <c r="F130" s="221">
         <f>DCF!F78</f>
@@ -5418,7 +5418,7 @@
       </c>
       <c r="C132" s="217">
         <f>Scenarios!C60</f>
-        <v>33.685558220029087</v>
+        <v>33.545596083057383</v>
       </c>
       <c r="D132" s="212" t="str">
         <f>Market_currency</f>
@@ -5426,13 +5426,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="364" t="s">
+      <c r="B134" s="363" t="s">
         <v>367</v>
       </c>
-      <c r="C134" s="364"/>
-      <c r="D134" s="364"/>
-      <c r="E134" s="364"/>
-      <c r="F134" s="364"/>
+      <c r="C134" s="363"/>
+      <c r="D134" s="363"/>
+      <c r="E134" s="363"/>
+      <c r="F134" s="363"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5445,22 +5445,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="365" t="s">
+      <c r="B138" s="361" t="s">
         <v>365</v>
       </c>
-      <c r="C138" s="365"/>
-      <c r="D138" s="365"/>
-      <c r="E138" s="365"/>
-      <c r="F138" s="365"/>
+      <c r="C138" s="361"/>
+      <c r="D138" s="361"/>
+      <c r="E138" s="361"/>
+      <c r="F138" s="361"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="360" t="s">
+      <c r="B139" s="358" t="s">
         <v>366</v>
       </c>
-      <c r="C139" s="360"/>
-      <c r="D139" s="360"/>
-      <c r="E139" s="360"/>
-      <c r="F139" s="360"/>
+      <c r="C139" s="358"/>
+      <c r="D139" s="358"/>
+      <c r="E139" s="358"/>
+      <c r="F139" s="358"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5491,7 +5491,7 @@
       </c>
       <c r="C143" s="213">
         <f>Scenarios!C77</f>
-        <v>1.5166086566399999</v>
+        <v>1.5100817256000003</v>
       </c>
       <c r="D143" s="212" t="str">
         <f>Market_currency</f>
@@ -5527,7 +5527,7 @@
       </c>
       <c r="C147" s="216">
         <f>Scenarios!C81</f>
-        <v>2.5719858232303614</v>
+        <v>2.5609169334211259</v>
       </c>
     </row>
     <row r="148" spans="2:4">
@@ -5537,7 +5537,7 @@
       </c>
       <c r="C148" s="216">
         <f>Scenarios!C82</f>
-        <v>13.691229271972395</v>
+        <v>13.634342766065082</v>
       </c>
     </row>
     <row r="149" spans="2:4">
@@ -5546,7 +5546,7 @@
       </c>
       <c r="C149" s="215">
         <f>Scenarios!C83</f>
-        <v>16.263215095202757</v>
+        <v>16.195259699486208</v>
       </c>
       <c r="D149" s="300" t="str">
         <f>IF($D$11="","",C149*$E$25)</f>
@@ -5572,7 +5572,7 @@
       </c>
       <c r="C151" s="92">
         <f>Scenarios!F83</f>
-        <v>0.51720511831884042</v>
+        <v>0.51721651750091202</v>
       </c>
     </row>
     <row r="153" spans="2:4">
@@ -5596,7 +5596,7 @@
       </c>
       <c r="C155" s="216">
         <f>Scenarios!C91</f>
-        <v>2.96042009776128</v>
+        <v>2.947679528371201</v>
       </c>
     </row>
     <row r="156" spans="2:4">
@@ -5606,7 +5606,7 @@
       </c>
       <c r="C156" s="216">
         <f>Scenarios!C92</f>
-        <v>17.247005808654894</v>
+        <v>17.175345194525381</v>
       </c>
     </row>
     <row r="157" spans="2:4">
@@ -5615,7 +5615,7 @@
       </c>
       <c r="C157" s="215">
         <f>Scenarios!C93</f>
-        <v>20.207425906416173</v>
+        <v>20.123024722896581</v>
       </c>
       <c r="D157" s="300" t="str">
         <f>IF($D$11="","",C157*$E$25)</f>
@@ -5641,7 +5641,7 @@
       </c>
       <c r="C159" s="92">
         <f>Scenarios!F93</f>
-        <v>0.40011604455463512</v>
+        <v>0.40012916529869136</v>
       </c>
     </row>
     <row r="161" spans="2:4">
@@ -5665,7 +5665,7 @@
       </c>
       <c r="C163" s="216">
         <f>Scenarios!C97</f>
-        <v>3.9439798489049545</v>
+        <v>3.9270063967330664</v>
       </c>
     </row>
     <row r="164" spans="2:4">
@@ -5675,7 +5675,7 @@
       </c>
       <c r="C164" s="216">
         <f>Scenarios!C98</f>
-        <v>27.115546129043505</v>
+        <v>27.00288212755698</v>
       </c>
     </row>
     <row r="165" spans="2:4">
@@ -5684,7 +5684,7 @@
       </c>
       <c r="C165" s="215">
         <f>Scenarios!C99</f>
-        <v>31.059525977948461</v>
+        <v>30.929888524290046</v>
       </c>
       <c r="D165" s="300" t="str">
         <f>IF($D$11="","",C165*$E$25)</f>
@@ -5710,7 +5710,7 @@
       </c>
       <c r="C167" s="92">
         <f>Scenarios!F99</f>
-        <v>7.7957213145401161E-2</v>
+        <v>7.7974693080157587E-2</v>
       </c>
     </row>
     <row r="169" spans="2:4">
@@ -5734,7 +5734,7 @@
       </c>
       <c r="C171" s="216">
         <f>Scenarios!C103</f>
-        <v>3.6589747858352792</v>
+        <v>3.6432278916053904</v>
       </c>
     </row>
     <row r="172" spans="2:4">
@@ -5744,7 +5744,7 @@
       </c>
       <c r="C172" s="216">
         <f>Scenarios!C104</f>
-        <v>24.144473948711063</v>
+        <v>24.044154632408034</v>
       </c>
     </row>
     <row r="173" spans="2:4">
@@ -5753,7 +5753,7 @@
       </c>
       <c r="C173" s="215">
         <f>Scenarios!C105</f>
-        <v>27.803448734546343</v>
+        <v>27.687382524013426</v>
       </c>
       <c r="D173" s="300" t="str">
         <f>IF($D$11="","",C173*$E$25)</f>
@@ -5779,7 +5779,7 @@
       </c>
       <c r="C175" s="92">
         <f>Scenarios!F105</f>
-        <v>0.15774716138043743</v>
+        <v>0.15776627983086078</v>
       </c>
     </row>
     <row r="177" spans="1:6" ht="13.9">
@@ -5793,13 +5793,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="359" t="s">
+      <c r="B179" s="365" t="s">
         <v>373</v>
       </c>
-      <c r="C179" s="360"/>
-      <c r="D179" s="360"/>
-      <c r="E179" s="360"/>
-      <c r="F179" s="360"/>
+      <c r="C179" s="358"/>
+      <c r="D179" s="358"/>
+      <c r="E179" s="358"/>
+      <c r="F179" s="358"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5836,13 +5836,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="361" t="s">
+      <c r="B188" s="359" t="s">
         <v>378</v>
       </c>
-      <c r="C188" s="361"/>
-      <c r="D188" s="361"/>
-      <c r="E188" s="361"/>
-      <c r="F188" s="361"/>
+      <c r="C188" s="359"/>
+      <c r="D188" s="359"/>
+      <c r="E188" s="359"/>
+      <c r="F188" s="359"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5850,22 +5850,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="358" t="s">
+      <c r="B191" s="364" t="s">
         <v>379</v>
       </c>
-      <c r="C191" s="358"/>
-      <c r="D191" s="358"/>
-      <c r="E191" s="358"/>
-      <c r="F191" s="358"/>
+      <c r="C191" s="364"/>
+      <c r="D191" s="364"/>
+      <c r="E191" s="364"/>
+      <c r="F191" s="364"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="358" t="s">
+      <c r="B192" s="364" t="s">
         <v>380</v>
       </c>
-      <c r="C192" s="358"/>
-      <c r="D192" s="358"/>
-      <c r="E192" s="358"/>
-      <c r="F192" s="358"/>
+      <c r="C192" s="364"/>
+      <c r="D192" s="364"/>
+      <c r="E192" s="364"/>
+      <c r="F192" s="364"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5889,6 +5889,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5905,17 +5916,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -6488,15 +6488,15 @@
       </c>
       <c r="C25" s="39">
         <f>0.164*Exchange_Rate</f>
-        <v>1.5166086566399999</v>
+        <v>1.5100817256000003</v>
       </c>
       <c r="D25" s="39">
         <f>0.137*Exchange_Rate</f>
-        <v>1.26692308512</v>
+        <v>1.2614707098000002</v>
       </c>
       <c r="E25" s="39">
         <f>0.11*Exchange_Rate</f>
-        <v>1.0172375135999998</v>
+        <v>1.0128596940000001</v>
       </c>
       <c r="F25" s="39"/>
       <c r="G25" s="39"/>
@@ -7870,15 +7870,15 @@
       </c>
       <c r="C65" s="73">
         <f>IF(C$4="","",C25)</f>
-        <v>1.5166086566399999</v>
+        <v>1.5100817256000003</v>
       </c>
       <c r="D65" s="73">
         <f t="shared" ref="D65:M65" si="33">IF(D$4="","",D25)</f>
-        <v>1.26692308512</v>
+        <v>1.2614707098000002</v>
       </c>
       <c r="E65" s="73">
         <f t="shared" si="33"/>
-        <v>1.0172375135999998</v>
+        <v>1.0128596940000001</v>
       </c>
       <c r="F65" s="73">
         <f t="shared" si="33"/>
@@ -9220,11 +9220,11 @@
       </c>
       <c r="C47" s="147">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>15.899346070406715</v>
+        <v>15.830921078284792</v>
       </c>
       <c r="D47" s="147">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>-6.0099460564163278</v>
+        <v>-5.9840814384790599</v>
       </c>
       <c r="F47" s="253"/>
     </row>
@@ -9415,7 +9415,7 @@
       </c>
       <c r="D66" s="76">
         <f>C66-D75</f>
-        <v>404998.6926536205</v>
+        <v>406390.46496957855</v>
       </c>
       <c r="F66" s="5" t="s">
         <v>225</v>
@@ -9482,11 +9482,11 @@
       </c>
       <c r="C73" s="349">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35-Normalized_FCF!G91)/12</f>
-        <v>-656221.46910151595</v>
+        <v>-654829.6967855579</v>
       </c>
       <c r="D73" s="349">
         <f>(Normalized_FCF!C25+Normalized_FCF!C35-Normalized_FCF!C91)/12</f>
-        <v>-606564.3073463795</v>
+        <v>-605172.53503042145</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>348</v>
@@ -9498,11 +9498,11 @@
       </c>
       <c r="C74" s="258">
         <f>-$C$66/C73</f>
-        <v>1.5414963508966111</v>
+        <v>1.5447726408340705</v>
       </c>
       <c r="D74" s="258">
         <f>-$C$66/D73</f>
-        <v>1.6676929185388836</v>
+        <v>1.6715282691227051</v>
       </c>
       <c r="F74" s="253" t="s">
         <v>316</v>
@@ -9515,7 +9515,7 @@
       <c r="C75" s="320"/>
       <c r="D75" s="321">
         <f>MAX(-D73*D76,G5)</f>
-        <v>606564.3073463795</v>
+        <v>605172.53503042145</v>
       </c>
       <c r="F75" s="253" t="s">
         <v>349</v>
@@ -9630,11 +9630,11 @@
       </c>
       <c r="C86" s="76">
         <f>-DCF!C7*Exchange_Rate</f>
-        <v>-8013057.3230399983</v>
+        <v>-7978572.0441000015</v>
       </c>
       <c r="D86" s="223">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>-3.1315390675716648</v>
+        <v>-3.1180620644874368</v>
       </c>
       <c r="E86" s="240" t="str">
         <f>Market_currency</f>
@@ -9647,11 +9647,11 @@
       </c>
       <c r="C87" s="76">
         <f>DCF!C8*Exchange_Rate</f>
-        <v>3745271.4829656309</v>
+        <v>3741968.3817600464</v>
       </c>
       <c r="D87" s="223">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>1.4636690460014565</v>
+        <v>1.4623781791010426</v>
       </c>
       <c r="E87" s="240" t="str">
         <f>Market_currency</f>
@@ -9664,11 +9664,11 @@
       </c>
       <c r="C88" s="76">
         <f>DCF!C9*Exchange_Rate</f>
-        <v>34793.222010623991</v>
+        <v>34643.484660960006</v>
       </c>
       <c r="D88" s="223">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>1.359734862992687E-2</v>
+        <v>1.3538830595992535E-2</v>
       </c>
       <c r="E88" s="240" t="str">
         <f>Market_currency</f>
@@ -9681,11 +9681,11 @@
       </c>
       <c r="C89" s="180">
         <f>SUM(C86:C88)</f>
-        <v>-4232992.6180637442</v>
+        <v>-4201960.1776789958</v>
       </c>
       <c r="D89" s="242">
         <f>SUM(D86:D88)</f>
-        <v>-1.6542726729402815</v>
+        <v>-1.6421450547904017</v>
       </c>
       <c r="E89" s="240" t="str">
         <f>Market_currency</f>
@@ -13197,20 +13197,20 @@
       </c>
       <c r="C90" s="113">
         <f>G90</f>
-        <v>1.5166086566399999</v>
+        <v>1.5100817256000003</v>
       </c>
       <c r="E90" s="268"/>
       <c r="G90" s="112">
         <f>Data!C65</f>
-        <v>1.5166086566399999</v>
+        <v>1.5100817256000003</v>
       </c>
       <c r="H90" s="112">
         <f>Data!D65</f>
-        <v>1.26692308512</v>
+        <v>1.2614707098000002</v>
       </c>
       <c r="I90" s="112">
         <f>Data!E65</f>
-        <v>1.0172375135999998</v>
+        <v>1.0128596940000001</v>
       </c>
       <c r="J90" s="112">
         <f>Data!F65</f>
@@ -13253,20 +13253,20 @@
       </c>
       <c r="C91" s="74">
         <f>C90*Common_Shares/scaling_factor</f>
-        <v>3880734.6292181914</v>
+        <v>3864033.3614266952</v>
       </c>
       <c r="E91" s="268"/>
       <c r="G91" s="74">
         <f t="shared" ref="G91:Q91" si="37">IF(G$4="","",G90*Common_Shares/scaling_factor)</f>
-        <v>3880734.6292181914</v>
+        <v>3864033.3614266952</v>
       </c>
       <c r="H91" s="74">
         <f t="shared" si="37"/>
-        <v>3241833.1963590989</v>
+        <v>3227881.5275332755</v>
       </c>
       <c r="I91" s="74">
         <f t="shared" si="37"/>
-        <v>2602931.7635000059</v>
+        <v>2591729.6936398563</v>
       </c>
       <c r="J91" s="74">
         <f t="shared" si="37"/>
@@ -13308,20 +13308,20 @@
       </c>
       <c r="C92" s="23">
         <f>C90/(C19*scaling_factor/Common_Shares)</f>
-        <v>5.5981883777967951</v>
+        <v>5.5740958148730426</v>
       </c>
       <c r="E92" s="268"/>
       <c r="G92" s="170">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",G90/(G19*scaling_factor/Common_Shares))</f>
-        <v>3.8928804161164741</v>
+        <v>3.8761268772838204</v>
       </c>
       <c r="H92" s="170">
         <f t="shared" si="38"/>
-        <v>3.9485675613223861</v>
+        <v>3.9315743653079127</v>
       </c>
       <c r="I92" s="170">
         <f t="shared" si="38"/>
-        <v>3.8742866891023056</v>
+        <v>3.8576131708955836</v>
       </c>
       <c r="J92" s="170">
         <f t="shared" si="38"/>
@@ -13384,20 +13384,20 @@
       </c>
       <c r="C94" s="23">
         <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
-        <v>3.0031854586930692E-2</v>
+        <v>3.0506701527272733E-2</v>
       </c>
       <c r="E94" s="268"/>
       <c r="G94" s="23">
         <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>3.0031854586930692E-2</v>
+        <v>3.0506701527272733E-2</v>
       </c>
       <c r="H94" s="23">
         <f t="shared" si="39"/>
-        <v>2.5087585843960394E-2</v>
+        <v>2.5484256763636366E-2</v>
       </c>
       <c r="I94" s="23">
         <f t="shared" si="39"/>
-        <v>2.0143317100990096E-2</v>
+        <v>2.0461812000000003E-2</v>
       </c>
       <c r="J94" s="23">
         <f t="shared" si="39"/>
@@ -14526,38 +14526,38 @@
       </c>
       <c r="C125" s="177">
         <f>C16*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>2.5052767315412869</v>
+        <v>2.4944949333553845</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="265"/>
       <c r="F125" s="27"/>
       <c r="G125" s="177">
         <f t="shared" ref="G125:Q125" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>3.6027336014781786</v>
+        <v>3.5872287488127368</v>
       </c>
       <c r="H125" s="177">
         <f t="shared" si="49"/>
-        <v>2.9671558540823435</v>
+        <v>2.9543862964514171</v>
       </c>
       <c r="I125" s="177">
         <f t="shared" si="49"/>
-        <v>2.4280649272589594</v>
+        <v>2.417615420544438</v>
       </c>
       <c r="J125" s="177">
         <f t="shared" si="49"/>
-        <v>1.302366079197381</v>
+        <v>1.2967611701455044</v>
       </c>
       <c r="K125" s="177">
         <f t="shared" si="49"/>
-        <v>6.2913469159702728</v>
+        <v>6.2642712512696468</v>
       </c>
       <c r="L125" s="177">
         <f t="shared" si="49"/>
-        <v>8.4590947525919713</v>
+        <v>8.422689891081216</v>
       </c>
       <c r="M125" s="177">
         <f t="shared" si="49"/>
-        <v>7.8261335479369576</v>
+        <v>7.7924527208141718</v>
       </c>
       <c r="N125" s="177" t="str">
         <f t="shared" si="49"/>
@@ -14583,38 +14583,38 @@
       </c>
       <c r="C126" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>4.9609440228540344E-2</v>
+        <v>5.0393837037482521E-2</v>
       </c>
       <c r="D126" s="27"/>
       <c r="E126" s="265"/>
       <c r="F126" s="27"/>
       <c r="G126" s="77">
         <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
-        <v>7.1341259435211454E-2</v>
+        <v>7.2469267652782568E-2</v>
       </c>
       <c r="H126" s="77">
         <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
-        <v>5.8755561466977101E-2</v>
+        <v>5.9684571645483173E-2</v>
       </c>
       <c r="I126" s="77">
         <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
-        <v>4.8080493609088303E-2</v>
+        <v>4.8840715566554303E-2</v>
       </c>
       <c r="J126" s="77">
         <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
-        <v>2.578942731083923E-2</v>
+        <v>2.6197195356474835E-2</v>
       </c>
       <c r="K126" s="77">
         <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
-        <v>0.12458112704891629</v>
+        <v>0.12655093436908377</v>
       </c>
       <c r="L126" s="77">
         <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
-        <v>0.16750682678399942</v>
+        <v>0.17015535133497406</v>
       </c>
       <c r="M126" s="77">
         <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
-        <v>0.1549729415433061</v>
+        <v>0.15742328728917518</v>
       </c>
       <c r="N126" s="77" t="str">
         <f t="shared" ref="N126" si="57">IF(N$4="","",N125/Market_Price)</f>
@@ -14640,31 +14640,31 @@
       <c r="C127" s="169"/>
       <c r="G127" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.526822516519269E-3</v>
+        <v>6.658677516852991E-3</v>
       </c>
       <c r="H127" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.2111810149916334E-3</v>
+        <v>5.3164573991328779E-3</v>
       </c>
       <c r="I127" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.6306514319867176E-3</v>
+        <v>3.7039979255622068E-3</v>
       </c>
       <c r="J127" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.2837146135788306E-3</v>
+        <v>2.329850262337999E-3</v>
       </c>
       <c r="K127" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-4.2073783089651361E-4</v>
+        <v>-4.2923758505603916E-4</v>
       </c>
       <c r="L127" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.9944496161339955E-3</v>
+        <v>2.0347415275710459E-3</v>
       </c>
       <c r="M127" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.6110587682404724E-3</v>
+        <v>1.6436054100231082E-3</v>
       </c>
       <c r="N127" s="23" t="str">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -15492,7 +15492,7 @@
       </c>
       <c r="C8" s="338">
         <f>BS!D66</f>
-        <v>404998.6926536205</v>
+        <v>406390.46496957855</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
@@ -15524,7 +15524,7 @@
       </c>
       <c r="C10" s="347">
         <f>C6-C7+C8+C9</f>
-        <v>8785095.5415257644</v>
+        <v>8786487.3138417229</v>
       </c>
       <c r="D10" t="str">
         <f>Reporting_currency</f>
@@ -15538,7 +15538,7 @@
       </c>
       <c r="C11" s="208">
         <f>Exchange_Rate</f>
-        <v>9.2476137599999984</v>
+        <v>9.2078154000000012</v>
       </c>
       <c r="D11" t="str">
         <f>Thesis!C15</f>
@@ -15552,7 +15552,7 @@
       </c>
       <c r="C12" s="111">
         <f>(C10*scaling_factor)/Common_Shares*Exchange_Rate</f>
-        <v>31.749417080943548</v>
+        <v>31.617787389948063</v>
       </c>
       <c r="D12" t="str">
         <f>Market_currency</f>
@@ -15605,7 +15605,7 @@
       </c>
       <c r="C18" s="140">
         <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>33.010810364398061</v>
+        <v>32.873752096334002</v>
       </c>
       <c r="D18" t="str">
         <f>Market_currency</f>
@@ -16701,23 +16701,23 @@
       </c>
       <c r="B65" s="124">
         <f>C12</f>
-        <v>31.749417080943548</v>
+        <v>31.617787389948063</v>
       </c>
       <c r="C65" s="124">
         <f>C12</f>
-        <v>31.749417080943548</v>
+        <v>31.617787389948063</v>
       </c>
       <c r="D65" s="124">
         <f>C12</f>
-        <v>31.749417080943548</v>
+        <v>31.617787389948063</v>
       </c>
       <c r="E65" s="141">
         <f>C12</f>
-        <v>31.749417080943548</v>
+        <v>31.617787389948063</v>
       </c>
       <c r="F65" s="124">
         <f>C12</f>
-        <v>31.749417080943548</v>
+        <v>31.617787389948063</v>
       </c>
       <c r="H65" s="120"/>
     </row>
@@ -16728,23 +16728,23 @@
       </c>
       <c r="B66" s="124">
         <f t="shared" ref="B66:F71" si="4">(B56-$C$7+$C$8+$C$9)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>31.749417080943548</v>
+        <v>31.617787389948063</v>
       </c>
       <c r="C66" s="124">
         <f t="shared" si="4"/>
-        <v>32.275266901913966</v>
+        <v>32.141374144896901</v>
       </c>
       <c r="D66" s="124">
         <f t="shared" si="4"/>
-        <v>33.34977673182054</v>
+        <v>33.211259676022841</v>
       </c>
       <c r="E66" s="124">
         <f t="shared" si="4"/>
-        <v>34.455817562485663</v>
+        <v>34.312540509969253</v>
       </c>
       <c r="F66" s="124">
         <f t="shared" si="4"/>
-        <v>36.177024197010624</v>
+        <v>36.02633969830832</v>
       </c>
       <c r="H66" s="120"/>
     </row>
@@ -16755,23 +16755,23 @@
       </c>
       <c r="B67" s="124">
         <f t="shared" si="4"/>
-        <v>31.749417080943555</v>
+        <v>31.61778738994807</v>
       </c>
       <c r="C67" s="124">
         <f t="shared" si="4"/>
-        <v>32.779442110602062</v>
+        <v>32.643379567196938</v>
       </c>
       <c r="D67" s="124">
         <f t="shared" si="4"/>
-        <v>34.991132615908533</v>
+        <v>34.845551762458996</v>
       </c>
       <c r="E67" s="124">
         <f t="shared" si="4"/>
-        <v>37.425198646617979</v>
+        <v>37.269142459891327</v>
       </c>
       <c r="F67" s="124">
         <f t="shared" si="4"/>
-        <v>41.552254544137739</v>
+        <v>41.37843701263477</v>
       </c>
       <c r="H67" s="120"/>
     </row>
@@ -16782,23 +16782,23 @@
       </c>
       <c r="B68" s="124">
         <f t="shared" si="4"/>
-        <v>31.749417080943555</v>
+        <v>31.61778738994807</v>
       </c>
       <c r="C68" s="124">
         <f t="shared" si="4"/>
-        <v>33.401917604112164</v>
+        <v>33.263176152999087</v>
       </c>
       <c r="D68" s="124">
         <f t="shared" si="4"/>
-        <v>37.12333324982071</v>
+        <v>36.968576181768896</v>
       </c>
       <c r="E68" s="124">
         <f t="shared" si="4"/>
-        <v>41.491670520885904</v>
+        <v>41.318113720943558</v>
       </c>
       <c r="F68" s="124">
         <f t="shared" si="4"/>
-        <v>49.546443824175256</v>
+        <v>49.338222214914275</v>
       </c>
       <c r="H68" s="120"/>
     </row>
@@ -16809,23 +16809,23 @@
       </c>
       <c r="B69" s="124">
         <f t="shared" si="4"/>
-        <v>31.749417080943559</v>
+        <v>31.617787389948077</v>
       </c>
       <c r="C69" s="124">
         <f t="shared" si="4"/>
-        <v>34.034115474412026</v>
+        <v>33.8926532740239</v>
       </c>
       <c r="D69" s="124">
         <f t="shared" si="4"/>
-        <v>39.407075114205121</v>
+        <v>39.242489653313314</v>
       </c>
       <c r="E69" s="124">
         <f t="shared" si="4"/>
-        <v>46.100548578505396</v>
+        <v>45.907156846774839</v>
       </c>
       <c r="F69" s="124">
         <f t="shared" si="4"/>
-        <v>59.464653082759838</v>
+        <v>59.213747114822922</v>
       </c>
       <c r="H69" s="120"/>
     </row>
@@ -16836,23 +16836,23 @@
       </c>
       <c r="B70" s="124">
         <f t="shared" si="4"/>
-        <v>31.749417080943559</v>
+        <v>31.617787389948077</v>
       </c>
       <c r="C70" s="124">
         <f t="shared" si="4"/>
-        <v>34.619876721863477</v>
+        <v>34.475893618504585</v>
       </c>
       <c r="D70" s="124">
         <f t="shared" si="4"/>
-        <v>41.642657440265367</v>
+        <v>41.468450847638245</v>
       </c>
       <c r="E70" s="124">
         <f t="shared" si="4"/>
-        <v>50.890079161206046</v>
+        <v>50.676075035045081</v>
       </c>
       <c r="F70" s="124">
         <f t="shared" si="4"/>
-        <v>70.825158310102296</v>
+        <v>70.525360867180197</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="13.15">
@@ -16862,23 +16862,23 @@
       </c>
       <c r="B71" s="124">
         <f t="shared" si="4"/>
-        <v>31.749417080943555</v>
+        <v>31.61778738994807</v>
       </c>
       <c r="C71" s="124">
         <f t="shared" si="4"/>
-        <v>35.134338481132687</v>
+        <v>34.988141321820223</v>
       </c>
       <c r="D71" s="124">
         <f t="shared" si="4"/>
-        <v>43.720567071700728</v>
+        <v>43.537417913163587</v>
       </c>
       <c r="E71" s="124">
         <f t="shared" si="4"/>
-        <v>55.63016399704788</v>
+        <v>55.395760272934034</v>
       </c>
       <c r="F71" s="124">
         <f t="shared" si="4"/>
-        <v>83.294807174109778</v>
+        <v>82.941344906137374</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="13.15">
@@ -16913,7 +16913,7 @@
       </c>
       <c r="E74" s="135">
         <f>INDEX(B$65:F$71, MATCH(D74, A$65:A$71, 0), MATCH(C74, B$64:F$64, 0))</f>
-        <v>41.552254544137739</v>
+        <v>41.37843701263477</v>
       </c>
       <c r="F74" s="142">
         <f>Scenarios!C58</f>
@@ -16935,7 +16935,7 @@
       </c>
       <c r="E75" s="135">
         <f>INDEX(B$65:F$71, MATCH(D75, A$65:A$71, 0), MATCH(C75, B$64:F$64, 0))</f>
-        <v>34.455817562485663</v>
+        <v>34.312540509969253</v>
       </c>
       <c r="F75" s="142">
         <f>Scenarios!C40*(1-F$74-F$78)</f>
@@ -16958,7 +16958,7 @@
       </c>
       <c r="E76" s="135">
         <f>INDEX(B$65:F$71, MATCH(D76, A$65:A$71, 0), MATCH(C76, B$64:F$64, 0))</f>
-        <v>33.34977673182054</v>
+        <v>33.211259676022841</v>
       </c>
       <c r="F76" s="142">
         <f>Scenarios!C28*(1-F$74-F$78)</f>
@@ -16981,7 +16981,7 @@
       </c>
       <c r="E77" s="135">
         <f>INDEX(B$65:F$71, MATCH(D77, A$65:A$71, 0), MATCH(C77, B$64:F$64, 0))</f>
-        <v>32.275266901913966</v>
+        <v>32.141374144896901</v>
       </c>
       <c r="F77" s="142">
         <f>Scenarios!C34*(1-F$74-F$78)</f>
@@ -17004,7 +17004,7 @@
       </c>
       <c r="E78" s="135">
         <f>INDEX(B$65:F$71, MATCH(D78, A$65:A$71, 0), MATCH(C78, B$64:F$64, 0))</f>
-        <v>31.749417080943555</v>
+        <v>31.61778738994807</v>
       </c>
       <c r="F78" s="142">
         <f>Scenarios!C52</f>
@@ -17186,7 +17186,7 @@
       </c>
       <c r="C4" s="114">
         <f>Normalized_FCF!C91*(1-dividend_tax_rate)</f>
-        <v>3880734.6292181914</v>
+        <v>3864033.3614266952</v>
       </c>
       <c r="D4" t="str">
         <f>Market_currency</f>
@@ -17218,7 +17218,7 @@
       </c>
       <c r="C6" s="319">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
-        <v>51743128.389575884</v>
+        <v>51520444.819022603</v>
       </c>
       <c r="D6" t="str">
         <f>Reporting_currency</f>
@@ -17234,7 +17234,7 @@
       </c>
       <c r="C7" s="111">
         <f>(C6*scaling_factor)/Common_Shares*Exchange_Rate</f>
-        <v>187.00014775572234</v>
+        <v>185.39405024317679</v>
       </c>
       <c r="D7" t="str">
         <f>Market_currency</f>
@@ -17287,7 +17287,7 @@
       </c>
       <c r="C13" s="140">
         <f>F47/Common_Shares*scaling_factor</f>
-        <v>20.985053010582089</v>
+        <v>20.894740988907198</v>
       </c>
       <c r="D13" t="str">
         <f>Market_currency</f>
@@ -17322,7 +17322,7 @@
       </c>
       <c r="C16" s="123">
         <f>C4*(1+D16)</f>
-        <v>3972912.2414522204</v>
+        <v>3955814.2748051235</v>
       </c>
       <c r="D16" s="138">
         <f>IF($C$12&lt;B16,0,DDM!$C$11)</f>
@@ -17334,7 +17334,7 @@
       </c>
       <c r="F16" s="125">
         <f t="shared" ref="F16:F46" si="1">C16*E16</f>
-        <v>3695732.3176299725</v>
+        <v>3679827.2323768591</v>
       </c>
       <c r="H16" s="120"/>
     </row>
@@ -17344,7 +17344,7 @@
       </c>
       <c r="C17" s="123">
         <f t="shared" ref="C17:C45" si="2">IF(ROW()-ROW($C$16)&lt;$C$12, $C$16*(1+D17)^(ROW()-ROW($C$16)), 0)</f>
-        <v>4067279.3134171967</v>
+        <v>4049775.2252776073</v>
       </c>
       <c r="D17" s="138">
         <f>IF($C$12&lt;B17,0,DDM!$C$11)</f>
@@ -17356,7 +17356,7 @@
       </c>
       <c r="F17" s="125">
         <f t="shared" si="1"/>
-        <v>3519549.4329191539</v>
+        <v>3504402.5746047441</v>
       </c>
       <c r="H17" s="120"/>
     </row>
@@ -17366,7 +17366,7 @@
       </c>
       <c r="C18" s="123">
         <f t="shared" si="2"/>
-        <v>4163887.8505165731</v>
+        <v>4145967.9944352917</v>
       </c>
       <c r="D18" s="138">
         <f>IF($C$12&lt;B18,0,DDM!$C$11)</f>
@@ -17378,7 +17378,7 @@
       </c>
       <c r="F18" s="125">
         <f t="shared" si="1"/>
-        <v>3351765.5355259376</v>
+        <v>3337340.7579692192</v>
       </c>
       <c r="H18" s="120"/>
     </row>
@@ -17388,7 +17388,7 @@
       </c>
       <c r="C19" s="123">
         <f t="shared" si="2"/>
-        <v>4262791.0934183495</v>
+        <v>4244445.5938177416</v>
       </c>
       <c r="D19" s="138">
         <f>IF($C$12&lt;B19,0,DDM!$C$11)</f>
@@ -17400,7 +17400,7 @@
       </c>
       <c r="F19" s="125">
         <f t="shared" si="1"/>
-        <v>3191980.2290776726</v>
+        <v>3178243.1092577251</v>
       </c>
       <c r="H19" s="120"/>
     </row>
@@ -17410,7 +17410,7 @@
       </c>
       <c r="C20" s="123">
         <f t="shared" si="2"/>
-        <v>4364043.5473958449</v>
+        <v>4345262.2941274419</v>
       </c>
       <c r="D20" s="138">
         <f>IF($C$12&lt;B20,0,DDM!$C$11)</f>
@@ -17422,7 +17422,7 @@
       </c>
       <c r="F20" s="125">
         <f t="shared" si="1"/>
-        <v>3039812.2048903992</v>
+        <v>3026729.960799939</v>
       </c>
       <c r="H20" s="120"/>
     </row>
@@ -17982,7 +17982,7 @@
       </c>
       <c r="C46" s="123">
         <f>C$16*(1+F4)^$C$12/Equity_Cost</f>
-        <v>52972163.219362937</v>
+        <v>52744190.330734983</v>
       </c>
       <c r="D46" s="139">
         <f>Terminal_Growth</f>
@@ -17994,7 +17994,7 @@
       </c>
       <c r="F46" s="125">
         <f t="shared" si="1"/>
-        <v>36898217.564706571</v>
+        <v>36739421.081190981</v>
       </c>
       <c r="H46" s="120"/>
     </row>
@@ -18005,7 +18005,7 @@
       </c>
       <c r="F47" s="137">
         <f>SUM(F16:F46)</f>
-        <v>53697057.284749702</v>
+        <v>53465964.716199473</v>
       </c>
       <c r="H47" s="120"/>
     </row>
@@ -18026,7 +18026,7 @@
     <row r="50" spans="1:8" ht="13.15">
       <c r="A50" s="133">
         <f>F47</f>
-        <v>53697057.284749702</v>
+        <v>53465964.716199473</v>
       </c>
       <c r="B50" s="131">
         <f>C73</f>
@@ -18056,19 +18056,19 @@
       </c>
       <c r="B51" s="123">
         <f t="dataTable" ref="B51:F56" dt2D="1" dtr="1" r1="C11" r2="C12"/>
-        <v>51743128.389575884</v>
+        <v>51520444.819022611</v>
       </c>
       <c r="C51" s="123">
-        <v>52557682.560105629</v>
+        <v>52331493.445207655</v>
       </c>
       <c r="D51" s="123">
-        <v>54222124.437465981</v>
+        <v>53988772.171213143</v>
       </c>
       <c r="E51" s="123">
-        <v>55935408.602385655</v>
+        <v>55694682.98536931</v>
       </c>
       <c r="F51" s="123">
-        <v>58601599.569054544</v>
+        <v>58349399.637617856</v>
       </c>
       <c r="H51" s="120"/>
     </row>
@@ -18077,19 +18077,19 @@
         <v>10</v>
       </c>
       <c r="B52" s="123">
-        <v>51743128.389575899</v>
+        <v>51520444.819022611</v>
       </c>
       <c r="C52" s="123">
-        <v>53338662.228705138</v>
+        <v>53109112.061884992</v>
       </c>
       <c r="D52" s="123">
-        <v>56764624.648343928</v>
+        <v>56520330.38761352</v>
       </c>
       <c r="E52" s="123">
-        <v>60535052.168886326</v>
+        <v>60274531.361966722</v>
       </c>
       <c r="F52" s="123">
-        <v>66927962.196183309</v>
+        <v>66639928.633939266</v>
       </c>
       <c r="H52" s="120"/>
     </row>
@@ -18098,19 +18098,19 @@
         <v>15</v>
       </c>
       <c r="B53" s="123">
-        <v>51743128.389575899</v>
+        <v>51520444.819022611</v>
       </c>
       <c r="C53" s="123">
-        <v>54302891.917621866</v>
+        <v>54069192.057564288</v>
       </c>
       <c r="D53" s="123">
-        <v>60067455.322611719</v>
+        <v>59808946.88213668</v>
       </c>
       <c r="E53" s="123">
-        <v>66834116.069705263</v>
+        <v>66546486.386994131</v>
       </c>
       <c r="F53" s="123">
-        <v>79311155.949186534</v>
+        <v>78969829.633187622</v>
       </c>
       <c r="H53" s="120"/>
     </row>
@@ -18119,19 +18119,19 @@
         <v>20</v>
       </c>
       <c r="B54" s="123">
-        <v>51743128.389575899</v>
+        <v>51520444.819022618</v>
       </c>
       <c r="C54" s="123">
-        <v>55282181.804803833</v>
+        <v>55044267.437903099</v>
       </c>
       <c r="D54" s="123">
-        <v>63605027.051008962</v>
+        <v>63331294.190826692</v>
       </c>
       <c r="E54" s="123">
-        <v>73973380.349322051</v>
+        <v>73655025.874539226</v>
       </c>
       <c r="F54" s="123">
-        <v>94674703.474709615</v>
+        <v>94267258.048292994</v>
       </c>
       <c r="H54" s="120"/>
     </row>
@@ -18140,19 +18140,19 @@
         <v>25</v>
       </c>
       <c r="B55" s="123">
-        <v>51743128.389575899</v>
+        <v>51520444.819022626</v>
       </c>
       <c r="C55" s="123">
-        <v>56189540.233044356</v>
+        <v>55947720.926089555</v>
       </c>
       <c r="D55" s="123">
-        <v>67067998.482461445</v>
+        <v>66779362.255067326</v>
       </c>
       <c r="E55" s="123">
-        <v>81392479.786912352</v>
+        <v>81042196.211503565</v>
       </c>
       <c r="F55" s="123">
-        <v>112272402.5576525</v>
+        <v>111789223.04658976</v>
       </c>
       <c r="H55" s="120"/>
     </row>
@@ -18161,19 +18161,19 @@
         <v>30</v>
       </c>
       <c r="B56" s="123">
-        <v>51743128.389575899</v>
+        <v>51520444.819022618</v>
       </c>
       <c r="C56" s="123">
-        <v>56986454.018842474</v>
+        <v>56741205.085331112</v>
       </c>
       <c r="D56" s="123">
-        <v>70286731.072587833</v>
+        <v>69984242.592959762</v>
       </c>
       <c r="E56" s="123">
-        <v>88734986.559234679</v>
+        <v>88353103.510122597</v>
       </c>
       <c r="F56" s="123">
-        <v>131588192.12752329</v>
+        <v>131021884.49639229</v>
       </c>
       <c r="H56" s="120"/>
     </row>
@@ -18223,23 +18223,23 @@
       </c>
       <c r="B60" s="124">
         <f>C7</f>
-        <v>187.00014775572234</v>
+        <v>185.39405024317679</v>
       </c>
       <c r="C60" s="124">
         <f>C7</f>
-        <v>187.00014775572234</v>
+        <v>185.39405024317679</v>
       </c>
       <c r="D60" s="124">
         <f>C7</f>
-        <v>187.00014775572234</v>
+        <v>185.39405024317679</v>
       </c>
       <c r="E60" s="141">
         <f>C7</f>
-        <v>187.00014775572234</v>
+        <v>185.39405024317679</v>
       </c>
       <c r="F60" s="124">
         <f>C7</f>
-        <v>187.00014775572234</v>
+        <v>185.39405024317679</v>
       </c>
       <c r="H60" s="120"/>
     </row>
@@ -18250,23 +18250,23 @@
       </c>
       <c r="B61" s="124">
         <f t="shared" ref="B61:F66" si="4">B51/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>187.00014775572237</v>
+        <v>185.39405024317682</v>
       </c>
       <c r="C61" s="124">
         <f t="shared" si="4"/>
-        <v>189.94395411194549</v>
+        <v>188.31257298266007</v>
       </c>
       <c r="D61" s="124">
         <f t="shared" si="4"/>
-        <v>195.95926255355687</v>
+        <v>194.27621744410243</v>
       </c>
       <c r="E61" s="124">
         <f t="shared" si="4"/>
-        <v>202.1510874771551</v>
+        <v>200.41486233160296</v>
       </c>
       <c r="F61" s="124">
         <f t="shared" si="4"/>
-        <v>211.78672645433946</v>
+        <v>209.9677432148566</v>
       </c>
       <c r="H61" s="120"/>
     </row>
@@ -18277,23 +18277,23 @@
       </c>
       <c r="B62" s="124">
         <f t="shared" si="4"/>
-        <v>187.00014775572242</v>
+        <v>185.39405024317682</v>
       </c>
       <c r="C62" s="124">
         <f t="shared" si="4"/>
-        <v>192.76642190559639</v>
+        <v>191.1107993061463</v>
       </c>
       <c r="D62" s="124">
         <f t="shared" si="4"/>
-        <v>205.14788198768667</v>
+        <v>203.38591812338629</v>
       </c>
       <c r="E62" s="124">
         <f t="shared" si="4"/>
-        <v>218.77424215159422</v>
+        <v>216.89524488690907</v>
       </c>
       <c r="F62" s="124">
         <f t="shared" si="4"/>
-        <v>241.87827851160705</v>
+        <v>239.80084645543698</v>
       </c>
       <c r="H62" s="120"/>
     </row>
@@ -18304,23 +18304,23 @@
       </c>
       <c r="B63" s="124">
         <f t="shared" si="4"/>
-        <v>187.00014775572242</v>
+        <v>185.39405024317682</v>
       </c>
       <c r="C63" s="124">
         <f t="shared" si="4"/>
-        <v>196.25115697882805</v>
+        <v>194.56560486113864</v>
       </c>
       <c r="D63" s="124">
         <f t="shared" si="4"/>
-        <v>217.08434279558472</v>
+        <v>215.21985965393486</v>
       </c>
       <c r="E63" s="124">
         <f t="shared" si="4"/>
-        <v>241.53911773675853</v>
+        <v>239.46459864768153</v>
       </c>
       <c r="F63" s="124">
         <f t="shared" si="4"/>
-        <v>286.63125602902079</v>
+        <v>284.16945183875146</v>
       </c>
       <c r="H63" s="120"/>
     </row>
@@ -18331,23 +18331,23 @@
       </c>
       <c r="B64" s="124">
         <f t="shared" si="4"/>
-        <v>187.00014775572242</v>
+        <v>185.39405024317682</v>
       </c>
       <c r="C64" s="124">
         <f t="shared" si="4"/>
-        <v>199.79031974880863</v>
+        <v>198.07437064700139</v>
       </c>
       <c r="D64" s="124">
         <f t="shared" si="4"/>
-        <v>229.86915995866957</v>
+        <v>227.89487121905401</v>
       </c>
       <c r="E64" s="124">
         <f t="shared" si="4"/>
-        <v>267.34048531360656</v>
+        <v>265.0443647296496</v>
       </c>
       <c r="F64" s="124">
         <f t="shared" si="4"/>
-        <v>342.15525982898555</v>
+        <v>339.21657385300682</v>
       </c>
       <c r="H64" s="120"/>
     </row>
@@ -18358,23 +18358,23 @@
       </c>
       <c r="B65" s="124">
         <f t="shared" si="4"/>
-        <v>187.00014775572242</v>
+        <v>185.39405024317688</v>
       </c>
       <c r="C65" s="124">
         <f t="shared" si="4"/>
-        <v>203.06952155645502</v>
+        <v>201.3254082102363</v>
       </c>
       <c r="D65" s="124">
         <f t="shared" si="4"/>
-        <v>242.3843709540279</v>
+        <v>240.30259219641044</v>
       </c>
       <c r="E65" s="124">
         <f t="shared" si="4"/>
-        <v>294.15317975678374</v>
+        <v>291.6267716443586</v>
       </c>
       <c r="F65" s="124">
         <f t="shared" si="4"/>
-        <v>405.75350815859412</v>
+        <v>402.26859272948212</v>
       </c>
     </row>
     <row r="66" spans="1:8" ht="13.15">
@@ -18384,23 +18384,23 @@
       </c>
       <c r="B66" s="124">
         <f t="shared" si="4"/>
-        <v>187.00014775572242</v>
+        <v>185.39405024317682</v>
       </c>
       <c r="C66" s="124">
         <f t="shared" si="4"/>
-        <v>205.94957539801678</v>
+        <v>204.18072598946634</v>
       </c>
       <c r="D66" s="124">
         <f t="shared" si="4"/>
-        <v>254.01690050284139</v>
+        <v>251.83521285746536</v>
       </c>
       <c r="E66" s="124">
         <f t="shared" si="4"/>
-        <v>320.68906759456434</v>
+        <v>317.93474937639365</v>
       </c>
       <c r="F66" s="124">
         <f t="shared" si="4"/>
-        <v>475.56095150428786</v>
+        <v>471.4764773985637</v>
       </c>
     </row>
     <row r="68" spans="1:8" ht="13.15">
@@ -18435,7 +18435,7 @@
       </c>
       <c r="E69" s="135">
         <f>INDEX(B$60:F$66, MATCH(D69, A$60:A$66, 0), MATCH(C69, B$59:F$59, 0))</f>
-        <v>241.87827851160705</v>
+        <v>239.80084645543698</v>
       </c>
       <c r="F69" s="142">
         <f>Scenarios!C58</f>
@@ -18457,7 +18457,7 @@
       </c>
       <c r="E70" s="135">
         <f>INDEX(B$60:F$66, MATCH(D70, A$60:A$66, 0), MATCH(C70, B$59:F$59, 0))</f>
-        <v>202.1510874771551</v>
+        <v>200.41486233160296</v>
       </c>
       <c r="F70" s="142">
         <f>Scenarios!C40*(1-F$69-F$73)</f>
@@ -18480,7 +18480,7 @@
       </c>
       <c r="E71" s="135">
         <f>INDEX(B$60:F$66, MATCH(D71, A$60:A$66, 0), MATCH(C71, B$59:F$59, 0))</f>
-        <v>195.95926255355687</v>
+        <v>194.27621744410243</v>
       </c>
       <c r="F71" s="142">
         <f>Scenarios!C28*(1-F$69-F$73)</f>
@@ -18503,7 +18503,7 @@
       </c>
       <c r="E72" s="135">
         <f>INDEX(B$60:F$66, MATCH(D72, A$60:A$66, 0), MATCH(C72, B$59:F$59, 0))</f>
-        <v>189.94395411194549</v>
+        <v>188.31257298266007</v>
       </c>
       <c r="F72" s="142">
         <f>Scenarios!C34*(1-F$69-F$73)</f>
@@ -18526,7 +18526,7 @@
       </c>
       <c r="E73" s="135">
         <f>INDEX(B$60:F$66, MATCH(D73, A$60:A$66, 0), MATCH(C73, B$59:F$59, 0))</f>
-        <v>187.00014775572242</v>
+        <v>185.39405024317682</v>
       </c>
       <c r="F73" s="142">
         <f>Scenarios!C52</f>
@@ -18626,7 +18626,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-50.5</v>
+        <v>-49.5</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18646,7 +18646,7 @@
       </c>
       <c r="I4" s="124">
         <f t="shared" ref="I4:I13" si="0">IF(ROW()-3 &lt; $C$76, $C$77, IF(ROW()-3 = $C$76, $C$77 + $C$60, ""))</f>
-        <v>1.5166086566399999</v>
+        <v>1.5100817256000003</v>
       </c>
     </row>
     <row r="5" spans="2:9">
@@ -18655,7 +18655,7 @@
       </c>
       <c r="I5" s="124">
         <f t="shared" si="0"/>
-        <v>1.5166086566399999</v>
+        <v>1.5100817256000003</v>
       </c>
     </row>
     <row r="6" spans="2:9" ht="13.15">
@@ -18675,7 +18675,7 @@
       </c>
       <c r="I6" s="124">
         <f t="shared" si="0"/>
-        <v>35.202166876669089</v>
+        <v>35.055677808657386</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1">
@@ -18866,7 +18866,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>50.5</v>
+        <v>49.5</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -18881,7 +18881,7 @@
       </c>
       <c r="C22" s="160">
         <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
-        <v>31.749417080943548</v>
+        <v>31.617787389948063</v>
       </c>
       <c r="D22" t="str">
         <f>Market_currency</f>
@@ -18928,7 +18928,7 @@
       </c>
       <c r="C27" s="160">
         <f>IF(valuation_method="DCF",DCF!E76,DDM!E71)</f>
-        <v>33.34977673182054</v>
+        <v>33.211259676022841</v>
       </c>
       <c r="D27" s="160" t="str">
         <f>Market_currency</f>
@@ -18986,7 +18986,7 @@
       </c>
       <c r="C33" s="160">
         <f>IF(valuation_method="DCF",DCF!E77,DDM!E72)</f>
-        <v>32.275266901913966</v>
+        <v>32.141374144896901</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
@@ -19044,7 +19044,7 @@
       </c>
       <c r="C39" s="160">
         <f>IF(valuation_method="DCF",DCF!E75,DDM!E70)</f>
-        <v>34.455817562485663</v>
+        <v>34.312540509969253</v>
       </c>
       <c r="D39" t="str">
         <f>Market_currency</f>
@@ -19071,7 +19071,7 @@
       </c>
       <c r="C42" s="154">
         <f>C27*C28+C33*C34+C39*C40</f>
-        <v>33.356082931972253</v>
+        <v>33.217538736586938</v>
       </c>
       <c r="D42" t="str">
         <f>Market_currency</f>
@@ -19145,7 +19145,7 @@
       </c>
       <c r="C51" s="160">
         <f>IF(valuation_method="DCF",DCF!E78,DDM!E73)</f>
-        <v>31.749417080943555</v>
+        <v>31.61778738994807</v>
       </c>
       <c r="D51" t="str">
         <f>Market_currency</f>
@@ -19203,7 +19203,7 @@
       </c>
       <c r="C57" s="160">
         <f>IF(valuation_method="DCF",DCF!E74,DDM!E69)</f>
-        <v>41.552254544137739</v>
+        <v>41.37843701263477</v>
       </c>
       <c r="D57" t="str">
         <f>Market_currency</f>
@@ -19229,7 +19229,7 @@
       </c>
       <c r="C60" s="154">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
-        <v>33.685558220029087</v>
+        <v>33.545596083057383</v>
       </c>
       <c r="D60" t="str">
         <f>Market_currency</f>
@@ -19291,7 +19291,7 @@
       </c>
       <c r="C66" s="160">
         <f>IF(valuation_method="DCF",DCF!C18,DDM!C13)</f>
-        <v>33.010810364398061</v>
+        <v>32.873752096334002</v>
       </c>
       <c r="D66" s="160" t="str">
         <f>Market_currency</f>
@@ -19354,7 +19354,7 @@
       </c>
       <c r="F72" s="291">
         <f>BS!D89/C60</f>
-        <v>-4.9109255133455619E-2</v>
+        <v>-4.8952627066889035E-2</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="13.9">
@@ -19387,7 +19387,7 @@
       </c>
       <c r="C77" s="173">
         <f>Normalized_FCF!C90*(1-dividend_tax_rate)</f>
-        <v>1.5166086566399999</v>
+        <v>1.5100817256000003</v>
       </c>
       <c r="D77" t="str">
         <f>Market_currency</f>
@@ -19414,7 +19414,7 @@
       </c>
       <c r="C81" s="116">
         <f>PV(C80, C76, -C77, 0)</f>
-        <v>2.5719858232303614</v>
+        <v>2.5609169334211259</v>
       </c>
       <c r="D81" s="116"/>
       <c r="E81" s="100"/>
@@ -19426,7 +19426,7 @@
       </c>
       <c r="C82" s="116">
         <f>C60/(1+C80)^C76</f>
-        <v>13.691229271972395</v>
+        <v>13.634342766065082</v>
       </c>
       <c r="D82" s="116"/>
     </row>
@@ -19436,7 +19436,7 @@
       </c>
       <c r="C83" s="111">
         <f>C81+C82</f>
-        <v>16.263215095202757</v>
+        <v>16.195259699486208</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -19447,7 +19447,7 @@
       </c>
       <c r="F83" s="291">
         <f>(1-C83/C60)</f>
-        <v>0.51720511831884042</v>
+        <v>0.51721651750091202</v>
       </c>
     </row>
     <row r="84" spans="2:8">
@@ -19464,7 +19464,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>50.5</v>
+        <v>49.5</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19477,7 +19477,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>-9.1795592256709635E-2</v>
+        <v>-8.6822328085409906E-2</v>
       </c>
     </row>
     <row r="88" spans="2:8">
@@ -19503,7 +19503,7 @@
       </c>
       <c r="C91" s="116">
         <f>PV(C90, C76, -C77, 0)</f>
-        <v>2.96042009776128</v>
+        <v>2.947679528371201</v>
       </c>
       <c r="D91" s="116"/>
       <c r="E91" s="100"/>
@@ -19515,7 +19515,7 @@
       </c>
       <c r="C92" s="116">
         <f>C60/(1+C90)^C76</f>
-        <v>17.247005808654894</v>
+        <v>17.175345194525381</v>
       </c>
       <c r="D92" s="116"/>
     </row>
@@ -19525,7 +19525,7 @@
       </c>
       <c r="C93" s="111">
         <f>C91+C92</f>
-        <v>20.207425906416173</v>
+        <v>20.123024722896581</v>
       </c>
       <c r="D93" t="str">
         <f>Market_currency</f>
@@ -19536,7 +19536,7 @@
       </c>
       <c r="F93" s="291">
         <f>(1-C93/C60)</f>
-        <v>0.40011604455463512</v>
+        <v>0.40012916529869136</v>
       </c>
     </row>
     <row r="95" spans="2:8" ht="13.15">
@@ -19563,7 +19563,7 @@
       </c>
       <c r="C97" s="116">
         <f>PV(C96, C76, -C77, 0)</f>
-        <v>3.9439798489049545</v>
+        <v>3.9270063967330664</v>
       </c>
       <c r="D97" s="116"/>
       <c r="G97" s="2"/>
@@ -19575,7 +19575,7 @@
       </c>
       <c r="C98" s="116">
         <f>C60/(1+C96)^C76</f>
-        <v>27.115546129043505</v>
+        <v>27.00288212755698</v>
       </c>
       <c r="D98" s="116"/>
       <c r="G98" s="2"/>
@@ -19587,7 +19587,7 @@
       </c>
       <c r="C99" s="111">
         <f>C97+C98</f>
-        <v>31.059525977948461</v>
+        <v>30.929888524290046</v>
       </c>
       <c r="D99" t="s">
         <v>393</v>
@@ -19597,7 +19597,7 @@
       </c>
       <c r="F99" s="291">
         <f>(1-C99/C60)</f>
-        <v>7.7957213145401161E-2</v>
+        <v>7.7974693080157587E-2</v>
       </c>
     </row>
     <row r="100" spans="2:8">
@@ -19623,7 +19623,7 @@
       </c>
       <c r="C103" s="116">
         <f>PV(C102, C76, -C77, 0)</f>
-        <v>3.6589747858352792</v>
+        <v>3.6432278916053904</v>
       </c>
       <c r="D103" s="116"/>
     </row>
@@ -19633,7 +19633,7 @@
       </c>
       <c r="C104" s="116">
         <f>C60/(1+C102)^C76</f>
-        <v>24.144473948711063</v>
+        <v>24.044154632408034</v>
       </c>
       <c r="D104" s="116"/>
     </row>
@@ -19643,7 +19643,7 @@
       </c>
       <c r="C105" s="111">
         <f>C103+C104</f>
-        <v>27.803448734546343</v>
+        <v>27.687382524013426</v>
       </c>
       <c r="D105" t="s">
         <v>393</v>
@@ -19653,7 +19653,7 @@
       </c>
       <c r="F105" s="291">
         <f>(1-C105/C66)</f>
-        <v>0.15774716138043743</v>
+        <v>0.15776627983086078</v>
       </c>
     </row>
     <row r="106" spans="2:8">

--- a/financial_models/opportunities/1913.HK_Valuation.xlsx
+++ b/financial_models/opportunities/1913.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82945DBC-FF26-4930-AEF6-0A671AD19A6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8B11AF7-60BB-43CA-A93C-62647ACA425B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3896,29 +3896,29 @@
     <xf numFmtId="10" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4336,7 +4336,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>49.5</v>
+        <v>49.75</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4357,7 +4357,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>126661.788</v>
+        <v>127301.49400000001</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4384,7 +4384,7 @@
         <v>1</v>
       </c>
       <c r="C16" s="50">
-        <v>9.2078154000000012</v>
+        <v>9.2242999799999996</v>
       </c>
       <c r="D16" s="50"/>
       <c r="E16" s="5"/>
@@ -4394,13 +4394,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="358" t="s">
+      <c r="B18" s="360" t="s">
         <v>356</v>
       </c>
-      <c r="C18" s="358"/>
-      <c r="D18" s="358"/>
-      <c r="E18" s="358"/>
-      <c r="F18" s="358"/>
+      <c r="C18" s="360"/>
+      <c r="D18" s="360"/>
+      <c r="E18" s="360"/>
+      <c r="F18" s="360"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4476,14 +4476,14 @@
       </c>
       <c r="C26" s="304">
         <f>C132</f>
-        <v>33.545596083057383</v>
+        <v>33.603574001709504</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>396</v>
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>-8.6822328085409906E-2</v>
+        <v>-8.7863363504127934E-2</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4515,7 +4515,7 @@
       </c>
       <c r="C29" s="310">
         <f>C149</f>
-        <v>16.195259699486208</v>
+        <v>16.223409128699366</v>
       </c>
       <c r="D29" s="310" t="str">
         <f>D149</f>
@@ -4534,7 +4534,7 @@
       </c>
       <c r="C30" s="311">
         <f>C157</f>
-        <v>20.123024722896581</v>
+        <v>20.157986592872707</v>
       </c>
       <c r="D30" s="311" t="str">
         <f>D157</f>
@@ -4553,7 +4553,7 @@
       </c>
       <c r="C31" s="311">
         <f>C165</f>
-        <v>30.929888524290046</v>
+        <v>30.983588908941798</v>
       </c>
       <c r="D31" s="311" t="str">
         <f>D165</f>
@@ -4572,7 +4572,7 @@
       </c>
       <c r="C32" s="311">
         <f>C173</f>
-        <v>27.687382524013426</v>
+        <v>27.735461202647695</v>
       </c>
       <c r="D32" s="311" t="str">
         <f>D173</f>
@@ -4600,22 +4600,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="358" t="s">
+      <c r="B36" s="360" t="s">
         <v>357</v>
       </c>
-      <c r="C36" s="358"/>
-      <c r="D36" s="358"/>
-      <c r="E36" s="358"/>
-      <c r="F36" s="358"/>
+      <c r="C36" s="360"/>
+      <c r="D36" s="360"/>
+      <c r="E36" s="360"/>
+      <c r="F36" s="360"/>
     </row>
     <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="360" t="s">
+      <c r="B37" s="363" t="s">
         <v>336</v>
       </c>
-      <c r="C37" s="360"/>
-      <c r="D37" s="360"/>
-      <c r="E37" s="360"/>
-      <c r="F37" s="360"/>
+      <c r="C37" s="363"/>
+      <c r="D37" s="363"/>
+      <c r="E37" s="363"/>
+      <c r="F37" s="363"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4627,13 +4627,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="359" t="s">
+      <c r="B40" s="361" t="s">
         <v>230</v>
       </c>
-      <c r="C40" s="359"/>
-      <c r="D40" s="359"/>
-      <c r="E40" s="359"/>
-      <c r="F40" s="359"/>
+      <c r="C40" s="361"/>
+      <c r="D40" s="361"/>
+      <c r="E40" s="361"/>
+      <c r="F40" s="361"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4653,13 +4653,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="359" t="s">
+      <c r="B43" s="361" t="s">
         <v>232</v>
       </c>
-      <c r="C43" s="359"/>
-      <c r="D43" s="359"/>
-      <c r="E43" s="359"/>
-      <c r="F43" s="359"/>
+      <c r="C43" s="361"/>
+      <c r="D43" s="361"/>
+      <c r="E43" s="361"/>
+      <c r="F43" s="361"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4688,13 +4688,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="359" t="s">
+      <c r="B47" s="361" t="s">
         <v>235</v>
       </c>
-      <c r="C47" s="359"/>
-      <c r="D47" s="359"/>
-      <c r="E47" s="359"/>
-      <c r="F47" s="359"/>
+      <c r="C47" s="361"/>
+      <c r="D47" s="361"/>
+      <c r="E47" s="361"/>
+      <c r="F47" s="361"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4710,13 +4710,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="359" t="s">
+      <c r="B50" s="361" t="s">
         <v>239</v>
       </c>
-      <c r="C50" s="359"/>
-      <c r="D50" s="359"/>
-      <c r="E50" s="359"/>
-      <c r="F50" s="359"/>
+      <c r="C50" s="361"/>
+      <c r="D50" s="361"/>
+      <c r="E50" s="361"/>
+      <c r="F50" s="361"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4780,13 +4780,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="359" t="s">
+      <c r="B58" s="361" t="s">
         <v>240</v>
       </c>
-      <c r="C58" s="359"/>
-      <c r="D58" s="359"/>
-      <c r="E58" s="359"/>
-      <c r="F58" s="359"/>
+      <c r="C58" s="361"/>
+      <c r="D58" s="361"/>
+      <c r="E58" s="361"/>
+      <c r="F58" s="361"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4802,7 +4802,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="359" t="s">
+      <c r="B61" s="361" t="s">
         <v>335</v>
       </c>
       <c r="C61" s="362"/>
@@ -4824,22 +4824,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="358" t="s">
+      <c r="B64" s="360" t="s">
         <v>340</v>
       </c>
-      <c r="C64" s="358"/>
-      <c r="D64" s="358"/>
-      <c r="E64" s="358"/>
-      <c r="F64" s="358"/>
+      <c r="C64" s="360"/>
+      <c r="D64" s="360"/>
+      <c r="E64" s="360"/>
+      <c r="F64" s="360"/>
     </row>
     <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="358" t="s">
+      <c r="B65" s="360" t="s">
         <v>358</v>
       </c>
-      <c r="C65" s="358"/>
-      <c r="D65" s="358"/>
-      <c r="E65" s="358"/>
-      <c r="F65" s="358"/>
+      <c r="C65" s="360"/>
+      <c r="D65" s="360"/>
+      <c r="E65" s="360"/>
+      <c r="F65" s="360"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4873,7 +4873,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C126</f>
-        <v>5.0393837037482521E-2</v>
+        <v>5.0230367458535846E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4883,14 +4883,14 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C94</f>
-        <v>3.0506701527272733E-2</v>
+        <v>3.0407742647638188E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>444</v>
       </c>
       <c r="F70" s="315">
         <f>Normalized_FCF!C92</f>
-        <v>5.5740958148730426</v>
+        <v>5.5840750145416118</v>
       </c>
     </row>
     <row r="72" spans="1:6">
@@ -4974,22 +4974,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.6" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="358" t="s">
+      <c r="B80" s="360" t="s">
         <v>359</v>
       </c>
-      <c r="C80" s="358"/>
-      <c r="D80" s="358"/>
-      <c r="E80" s="358"/>
-      <c r="F80" s="358"/>
+      <c r="C80" s="360"/>
+      <c r="D80" s="360"/>
+      <c r="E80" s="360"/>
+      <c r="F80" s="360"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="360" t="s">
+      <c r="B81" s="363" t="s">
         <v>251</v>
       </c>
-      <c r="C81" s="360"/>
-      <c r="D81" s="360"/>
-      <c r="E81" s="360"/>
-      <c r="F81" s="360"/>
+      <c r="C81" s="363"/>
+      <c r="D81" s="363"/>
+      <c r="E81" s="363"/>
+      <c r="F81" s="363"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5033,22 +5033,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="358" t="s">
+      <c r="B89" s="360" t="s">
         <v>360</v>
       </c>
-      <c r="C89" s="358"/>
-      <c r="D89" s="358"/>
-      <c r="E89" s="358"/>
-      <c r="F89" s="358"/>
+      <c r="C89" s="360"/>
+      <c r="D89" s="360"/>
+      <c r="E89" s="360"/>
+      <c r="F89" s="360"/>
     </row>
     <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="358" t="s">
+      <c r="B90" s="360" t="s">
         <v>361</v>
       </c>
-      <c r="C90" s="358"/>
-      <c r="D90" s="358"/>
-      <c r="E90" s="358"/>
-      <c r="F90" s="358"/>
+      <c r="C90" s="360"/>
+      <c r="D90" s="360"/>
+      <c r="E90" s="360"/>
+      <c r="F90" s="360"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5064,7 +5064,7 @@
       </c>
       <c r="C93" s="223">
         <f>DCF!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>33.259932444738453</v>
+        <v>33.319477080828776</v>
       </c>
       <c r="D93" s="1" t="str">
         <f>Market_currency</f>
@@ -5085,13 +5085,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="358" t="s">
+      <c r="B97" s="360" t="s">
         <v>362</v>
       </c>
-      <c r="C97" s="358"/>
-      <c r="D97" s="358"/>
-      <c r="E97" s="358"/>
-      <c r="F97" s="358"/>
+      <c r="C97" s="360"/>
+      <c r="D97" s="360"/>
+      <c r="E97" s="360"/>
+      <c r="F97" s="360"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5104,13 +5104,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="358" t="s">
+      <c r="B101" s="360" t="s">
         <v>341</v>
       </c>
-      <c r="C101" s="358"/>
-      <c r="D101" s="358"/>
-      <c r="E101" s="358"/>
-      <c r="F101" s="358"/>
+      <c r="C101" s="360"/>
+      <c r="D101" s="360"/>
+      <c r="E101" s="360"/>
+      <c r="F101" s="360"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="C103" s="223">
         <f>C102*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>3.1180620644874368</v>
+        <v>3.1236442727870304</v>
       </c>
       <c r="D103" s="1" t="str">
         <f>Market_currency</f>
@@ -5180,7 +5180,7 @@
       </c>
       <c r="C109" s="349">
         <f>DCF!C8</f>
-        <v>406390.46496957855</v>
+        <v>405813.98940414842</v>
       </c>
       <c r="D109" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5193,7 +5193,7 @@
       </c>
       <c r="C110" s="223">
         <f>C109*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>1.4623781791010426</v>
+        <v>1.4629181117358623</v>
       </c>
       <c r="D110" s="1" t="str">
         <f>Market_currency</f>
@@ -5224,7 +5224,7 @@
       </c>
       <c r="C114" s="223">
         <f>C113*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>1.3538830595992535E-2</v>
+        <v>1.3563068911637532E-2</v>
       </c>
       <c r="D114" s="1" t="str">
         <f>Market_currency</f>
@@ -5232,13 +5232,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="358" t="s">
+      <c r="B116" s="360" t="s">
         <v>363</v>
       </c>
-      <c r="C116" s="358"/>
-      <c r="D116" s="358"/>
-      <c r="E116" s="358"/>
-      <c r="F116" s="358"/>
+      <c r="C116" s="360"/>
+      <c r="D116" s="360"/>
+      <c r="E116" s="360"/>
+      <c r="F116" s="360"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="C118" s="223">
         <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
-        <v>31.617787389948063</v>
+        <v>31.672313988689243</v>
       </c>
       <c r="D118" s="1" t="str">
         <f>Market_currency</f>
@@ -5259,7 +5259,7 @@
       </c>
       <c r="C119" s="223">
         <f>BS!D47</f>
-        <v>-5.9840814384790599</v>
+        <v>-5.9947946277551081</v>
       </c>
       <c r="D119" s="1" t="str">
         <f>Market_currency</f>
@@ -5277,13 +5277,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B123" s="359" t="s">
+      <c r="B123" s="361" t="s">
         <v>364</v>
       </c>
-      <c r="C123" s="359"/>
-      <c r="D123" s="359"/>
-      <c r="E123" s="359"/>
-      <c r="F123" s="359"/>
+      <c r="C123" s="361"/>
+      <c r="D123" s="361"/>
+      <c r="E123" s="361"/>
+      <c r="F123" s="361"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5317,7 +5317,7 @@
       </c>
       <c r="E126" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E74,DDM!E69),2)&amp;" "&amp;Market_currency</f>
-        <v>41.38 HKD</v>
+        <v>41.45 HKD</v>
       </c>
       <c r="F126" s="232">
         <f>DCF!F74</f>
@@ -5339,7 +5339,7 @@
       </c>
       <c r="E127" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E75,DDM!E70),2)&amp;" "&amp;Market_currency</f>
-        <v>34.31 HKD</v>
+        <v>34.37 HKD</v>
       </c>
       <c r="F127" s="221">
         <f>DCF!F75</f>
@@ -5361,7 +5361,7 @@
       </c>
       <c r="E128" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E76,DDM!E71),2)&amp;" "&amp;Market_currency</f>
-        <v>33.21 HKD</v>
+        <v>33.27 HKD</v>
       </c>
       <c r="F128" s="221">
         <f>DCF!F76</f>
@@ -5383,7 +5383,7 @@
       </c>
       <c r="E129" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E77,DDM!E72),2)&amp;" "&amp;Market_currency</f>
-        <v>32.14 HKD</v>
+        <v>32.2 HKD</v>
       </c>
       <c r="F129" s="221">
         <f>DCF!F77</f>
@@ -5405,7 +5405,7 @@
       </c>
       <c r="E130" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E78,DDM!E73),2)&amp;" "&amp;Market_currency</f>
-        <v>31.62 HKD</v>
+        <v>31.67 HKD</v>
       </c>
       <c r="F130" s="221">
         <f>DCF!F78</f>
@@ -5418,7 +5418,7 @@
       </c>
       <c r="C132" s="217">
         <f>Scenarios!C60</f>
-        <v>33.545596083057383</v>
+        <v>33.603574001709504</v>
       </c>
       <c r="D132" s="212" t="str">
         <f>Market_currency</f>
@@ -5426,13 +5426,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="363" t="s">
+      <c r="B134" s="364" t="s">
         <v>367</v>
       </c>
-      <c r="C134" s="363"/>
-      <c r="D134" s="363"/>
-      <c r="E134" s="363"/>
-      <c r="F134" s="363"/>
+      <c r="C134" s="364"/>
+      <c r="D134" s="364"/>
+      <c r="E134" s="364"/>
+      <c r="F134" s="364"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5445,22 +5445,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="361" t="s">
+      <c r="B138" s="365" t="s">
         <v>365</v>
       </c>
-      <c r="C138" s="361"/>
-      <c r="D138" s="361"/>
-      <c r="E138" s="361"/>
-      <c r="F138" s="361"/>
+      <c r="C138" s="365"/>
+      <c r="D138" s="365"/>
+      <c r="E138" s="365"/>
+      <c r="F138" s="365"/>
     </row>
     <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="358" t="s">
+      <c r="B139" s="360" t="s">
         <v>366</v>
       </c>
-      <c r="C139" s="358"/>
-      <c r="D139" s="358"/>
-      <c r="E139" s="358"/>
-      <c r="F139" s="358"/>
+      <c r="C139" s="360"/>
+      <c r="D139" s="360"/>
+      <c r="E139" s="360"/>
+      <c r="F139" s="360"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5491,7 +5491,7 @@
       </c>
       <c r="C143" s="213">
         <f>Scenarios!C77</f>
-        <v>1.5100817256000003</v>
+        <v>1.5127851967199999</v>
       </c>
       <c r="D143" s="212" t="str">
         <f>Market_currency</f>
@@ -5527,7 +5527,7 @@
       </c>
       <c r="C147" s="216">
         <f>Scenarios!C81</f>
-        <v>2.5609169334211259</v>
+        <v>2.5655016951945129</v>
       </c>
     </row>
     <row r="148" spans="2:4">
@@ -5537,7 +5537,7 @@
       </c>
       <c r="C148" s="216">
         <f>Scenarios!C82</f>
-        <v>13.634342766065082</v>
+        <v>13.657907433504851</v>
       </c>
     </row>
     <row r="149" spans="2:4">
@@ -5546,7 +5546,7 @@
       </c>
       <c r="C149" s="215">
         <f>Scenarios!C83</f>
-        <v>16.195259699486208</v>
+        <v>16.223409128699366</v>
       </c>
       <c r="D149" s="300" t="str">
         <f>IF($D$11="","",C149*$E$25)</f>
@@ -5572,7 +5572,7 @@
       </c>
       <c r="C151" s="92">
         <f>Scenarios!F83</f>
-        <v>0.51721651750091202</v>
+        <v>0.5172117963442211</v>
       </c>
     </row>
     <row r="153" spans="2:4">
@@ -5596,7 +5596,7 @@
       </c>
       <c r="C155" s="216">
         <f>Scenarios!C91</f>
-        <v>2.947679528371201</v>
+        <v>2.9529567039974398</v>
       </c>
     </row>
     <row r="156" spans="2:4">
@@ -5606,7 +5606,7 @@
       </c>
       <c r="C156" s="216">
         <f>Scenarios!C92</f>
-        <v>17.175345194525381</v>
+        <v>17.205029888875266</v>
       </c>
     </row>
     <row r="157" spans="2:4">
@@ -5615,7 +5615,7 @@
       </c>
       <c r="C157" s="215">
         <f>Scenarios!C93</f>
-        <v>20.123024722896581</v>
+        <v>20.157986592872707</v>
       </c>
       <c r="D157" s="300" t="str">
         <f>IF($D$11="","",C157*$E$25)</f>
@@ -5641,7 +5641,7 @@
       </c>
       <c r="C159" s="92">
         <f>Scenarios!F93</f>
-        <v>0.40012916529869136</v>
+        <v>0.40012373112909905</v>
       </c>
     </row>
     <row r="161" spans="2:4">
@@ -5665,7 +5665,7 @@
       </c>
       <c r="C163" s="216">
         <f>Scenarios!C97</f>
-        <v>3.9270063967330664</v>
+        <v>3.9340368429676258</v>
       </c>
     </row>
     <row r="164" spans="2:4">
@@ -5675,7 +5675,7 @@
       </c>
       <c r="C164" s="216">
         <f>Scenarios!C98</f>
-        <v>27.00288212755698</v>
+        <v>27.049552065974172</v>
       </c>
     </row>
     <row r="165" spans="2:4">
@@ -5684,7 +5684,7 @@
       </c>
       <c r="C165" s="215">
         <f>Scenarios!C99</f>
-        <v>30.929888524290046</v>
+        <v>30.983588908941798</v>
       </c>
       <c r="D165" s="300" t="str">
         <f>IF($D$11="","",C165*$E$25)</f>
@@ -5710,7 +5710,7 @@
       </c>
       <c r="C167" s="92">
         <f>Scenarios!F99</f>
-        <v>7.7974693080157587E-2</v>
+        <v>7.796745348082379E-2</v>
       </c>
     </row>
     <row r="169" spans="2:4">
@@ -5734,7 +5734,7 @@
       </c>
       <c r="C171" s="216">
         <f>Scenarios!C103</f>
-        <v>3.6432278916053904</v>
+        <v>3.6497502944803863</v>
       </c>
     </row>
     <row r="172" spans="2:4">
@@ -5744,7 +5744,7 @@
       </c>
       <c r="C172" s="216">
         <f>Scenarios!C104</f>
-        <v>24.044154632408034</v>
+        <v>24.085710908167307</v>
       </c>
     </row>
     <row r="173" spans="2:4">
@@ -5753,7 +5753,7 @@
       </c>
       <c r="C173" s="215">
         <f>Scenarios!C105</f>
-        <v>27.687382524013426</v>
+        <v>27.735461202647695</v>
       </c>
       <c r="D173" s="300" t="str">
         <f>IF($D$11="","",C173*$E$25)</f>
@@ -5779,7 +5779,7 @@
       </c>
       <c r="C175" s="92">
         <f>Scenarios!F105</f>
-        <v>0.15776627983086078</v>
+        <v>0.15775836162776513</v>
       </c>
     </row>
     <row r="177" spans="1:6" ht="13.9">
@@ -5793,13 +5793,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="365" t="s">
+      <c r="B179" s="359" t="s">
         <v>373</v>
       </c>
-      <c r="C179" s="358"/>
-      <c r="D179" s="358"/>
-      <c r="E179" s="358"/>
-      <c r="F179" s="358"/>
+      <c r="C179" s="360"/>
+      <c r="D179" s="360"/>
+      <c r="E179" s="360"/>
+      <c r="F179" s="360"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5836,13 +5836,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="359" t="s">
+      <c r="B188" s="361" t="s">
         <v>378</v>
       </c>
-      <c r="C188" s="359"/>
-      <c r="D188" s="359"/>
-      <c r="E188" s="359"/>
-      <c r="F188" s="359"/>
+      <c r="C188" s="361"/>
+      <c r="D188" s="361"/>
+      <c r="E188" s="361"/>
+      <c r="F188" s="361"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5850,22 +5850,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="364" t="s">
+      <c r="B191" s="358" t="s">
         <v>379</v>
       </c>
-      <c r="C191" s="364"/>
-      <c r="D191" s="364"/>
-      <c r="E191" s="364"/>
-      <c r="F191" s="364"/>
+      <c r="C191" s="358"/>
+      <c r="D191" s="358"/>
+      <c r="E191" s="358"/>
+      <c r="F191" s="358"/>
     </row>
     <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="364" t="s">
+      <c r="B192" s="358" t="s">
         <v>380</v>
       </c>
-      <c r="C192" s="364"/>
-      <c r="D192" s="364"/>
-      <c r="E192" s="364"/>
-      <c r="F192" s="364"/>
+      <c r="C192" s="358"/>
+      <c r="D192" s="358"/>
+      <c r="E192" s="358"/>
+      <c r="F192" s="358"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5889,17 +5889,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5916,6 +5905,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -6488,15 +6488,15 @@
       </c>
       <c r="C25" s="39">
         <f>0.164*Exchange_Rate</f>
-        <v>1.5100817256000003</v>
+        <v>1.5127851967199999</v>
       </c>
       <c r="D25" s="39">
         <f>0.137*Exchange_Rate</f>
-        <v>1.2614707098000002</v>
+        <v>1.2637290972600002</v>
       </c>
       <c r="E25" s="39">
         <f>0.11*Exchange_Rate</f>
-        <v>1.0128596940000001</v>
+        <v>1.0146729978</v>
       </c>
       <c r="F25" s="39"/>
       <c r="G25" s="39"/>
@@ -7870,15 +7870,15 @@
       </c>
       <c r="C65" s="73">
         <f>IF(C$4="","",C25)</f>
-        <v>1.5100817256000003</v>
+        <v>1.5127851967199999</v>
       </c>
       <c r="D65" s="73">
         <f t="shared" ref="D65:M65" si="33">IF(D$4="","",D25)</f>
-        <v>1.2614707098000002</v>
+        <v>1.2637290972600002</v>
       </c>
       <c r="E65" s="73">
         <f t="shared" si="33"/>
-        <v>1.0128596940000001</v>
+        <v>1.0146729978</v>
       </c>
       <c r="F65" s="73">
         <f t="shared" si="33"/>
@@ -9220,11 +9220,11 @@
       </c>
       <c r="C47" s="147">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>15.830921078284792</v>
+        <v>15.85926288072673</v>
       </c>
       <c r="D47" s="147">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>-5.9840814384790599</v>
+        <v>-5.9947946277551081</v>
       </c>
       <c r="F47" s="253"/>
     </row>
@@ -9415,7 +9415,7 @@
       </c>
       <c r="D66" s="76">
         <f>C66-D75</f>
-        <v>406390.46496957855</v>
+        <v>405813.98940414842</v>
       </c>
       <c r="F66" s="5" t="s">
         <v>225</v>
@@ -9482,11 +9482,11 @@
       </c>
       <c r="C73" s="349">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35-Normalized_FCF!G91)/12</f>
-        <v>-654829.6967855579</v>
+        <v>-655406.17235098814</v>
       </c>
       <c r="D73" s="349">
         <f>(Normalized_FCF!C25+Normalized_FCF!C35-Normalized_FCF!C91)/12</f>
-        <v>-605172.53503042145</v>
+        <v>-605749.01059585158</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>348</v>
@@ -9498,11 +9498,11 @@
       </c>
       <c r="C74" s="258">
         <f>-$C$66/C73</f>
-        <v>1.5447726408340705</v>
+        <v>1.5434139052603857</v>
       </c>
       <c r="D74" s="258">
         <f>-$C$66/D73</f>
-        <v>1.6715282691227051</v>
+        <v>1.6699375191797097</v>
       </c>
       <c r="F74" s="253" t="s">
         <v>316</v>
@@ -9515,7 +9515,7 @@
       <c r="C75" s="320"/>
       <c r="D75" s="321">
         <f>MAX(-D73*D76,G5)</f>
-        <v>605172.53503042145</v>
+        <v>605749.01059585158</v>
       </c>
       <c r="F75" s="253" t="s">
         <v>349</v>
@@ -9630,11 +9630,11 @@
       </c>
       <c r="C86" s="76">
         <f>-DCF!C7*Exchange_Rate</f>
-        <v>-7978572.0441000015</v>
+        <v>-7992855.93267</v>
       </c>
       <c r="D86" s="223">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>-3.1180620644874368</v>
+        <v>-3.1236442727870304</v>
       </c>
       <c r="E86" s="240" t="str">
         <f>Market_currency</f>
@@ -9647,11 +9647,11 @@
       </c>
       <c r="C87" s="76">
         <f>DCF!C8*Exchange_Rate</f>
-        <v>3741968.3817600464</v>
+        <v>3743349.9743444063</v>
       </c>
       <c r="D87" s="223">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>1.4623781791010426</v>
+        <v>1.4629181117358623</v>
       </c>
       <c r="E87" s="240" t="str">
         <f>Market_currency</f>
@@ -9664,11 +9664,11 @@
       </c>
       <c r="C88" s="76">
         <f>DCF!C9*Exchange_Rate</f>
-        <v>34643.484660960006</v>
+        <v>34705.506244751996</v>
       </c>
       <c r="D88" s="223">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>1.3538830595992535E-2</v>
+        <v>1.3563068911637532E-2</v>
       </c>
       <c r="E88" s="240" t="str">
         <f>Market_currency</f>
@@ -9681,11 +9681,11 @@
       </c>
       <c r="C89" s="180">
         <f>SUM(C86:C88)</f>
-        <v>-4201960.1776789958</v>
+        <v>-4214800.4520808421</v>
       </c>
       <c r="D89" s="242">
         <f>SUM(D86:D88)</f>
-        <v>-1.6421450547904017</v>
+        <v>-1.6471630921395306</v>
       </c>
       <c r="E89" s="240" t="str">
         <f>Market_currency</f>
@@ -13197,20 +13197,20 @@
       </c>
       <c r="C90" s="113">
         <f>G90</f>
-        <v>1.5100817256000003</v>
+        <v>1.5127851967199999</v>
       </c>
       <c r="E90" s="268"/>
       <c r="G90" s="112">
         <f>Data!C65</f>
-        <v>1.5100817256000003</v>
+        <v>1.5127851967199999</v>
       </c>
       <c r="H90" s="112">
         <f>Data!D65</f>
-        <v>1.2614707098000002</v>
+        <v>1.2637290972600002</v>
       </c>
       <c r="I90" s="112">
         <f>Data!E65</f>
-        <v>1.0128596940000001</v>
+        <v>1.0146729978</v>
       </c>
       <c r="J90" s="112">
         <f>Data!F65</f>
@@ -13253,20 +13253,20 @@
       </c>
       <c r="C91" s="74">
         <f>C90*Common_Shares/scaling_factor</f>
-        <v>3864033.3614266952</v>
+        <v>3870951.0682118568</v>
       </c>
       <c r="E91" s="268"/>
       <c r="G91" s="74">
         <f t="shared" ref="G91:Q91" si="37">IF(G$4="","",G90*Common_Shares/scaling_factor)</f>
-        <v>3864033.3614266952</v>
+        <v>3870951.0682118568</v>
       </c>
       <c r="H91" s="74">
         <f t="shared" si="37"/>
-        <v>3227881.5275332755</v>
+        <v>3233660.3435672228</v>
       </c>
       <c r="I91" s="74">
         <f t="shared" si="37"/>
-        <v>2591729.6936398563</v>
+        <v>2596369.618922587</v>
       </c>
       <c r="J91" s="74">
         <f t="shared" si="37"/>
@@ -13308,20 +13308,20 @@
       </c>
       <c r="C92" s="23">
         <f>C90/(C19*scaling_factor/Common_Shares)</f>
-        <v>5.5740958148730426</v>
+        <v>5.5840750145416118</v>
       </c>
       <c r="E92" s="268"/>
       <c r="G92" s="170">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",G90/(G19*scaling_factor/Common_Shares))</f>
-        <v>3.8761268772838204</v>
+        <v>3.8830662348646343</v>
       </c>
       <c r="H92" s="170">
         <f t="shared" si="38"/>
-        <v>3.9315743653079127</v>
+        <v>3.938612989491328</v>
       </c>
       <c r="I92" s="170">
         <f t="shared" si="38"/>
-        <v>3.8576131708955836</v>
+        <v>3.8645193837335037</v>
       </c>
       <c r="J92" s="170">
         <f t="shared" si="38"/>
@@ -13384,20 +13384,20 @@
       </c>
       <c r="C94" s="23">
         <f>(C90*(1-dividend_tax_rate))/Market_Price</f>
-        <v>3.0506701527272733E-2</v>
+        <v>3.0407742647638188E-2</v>
       </c>
       <c r="E94" s="268"/>
       <c r="G94" s="23">
         <f t="shared" ref="G94:Q94" si="39">IF(G$4="","",(G90*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>3.0506701527272733E-2</v>
+        <v>3.0407742647638188E-2</v>
       </c>
       <c r="H94" s="23">
         <f t="shared" si="39"/>
-        <v>2.5484256763636366E-2</v>
+        <v>2.5401589894673369E-2</v>
       </c>
       <c r="I94" s="23">
         <f t="shared" si="39"/>
-        <v>2.0461812000000003E-2</v>
+        <v>2.0395437141708543E-2</v>
       </c>
       <c r="J94" s="23">
         <f t="shared" si="39"/>
@@ -14526,38 +14526,38 @@
       </c>
       <c r="C125" s="177">
         <f>C16*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>2.4944949333553845</v>
+        <v>2.4989607810621584</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="265"/>
       <c r="F125" s="27"/>
       <c r="G125" s="177">
         <f t="shared" ref="G125:Q125" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>3.5872287488127368</v>
+        <v>3.5936508974678993</v>
       </c>
       <c r="H125" s="177">
         <f t="shared" si="49"/>
-        <v>2.9543862964514171</v>
+        <v>2.9596754790793347</v>
       </c>
       <c r="I125" s="177">
         <f t="shared" si="49"/>
-        <v>2.417615420544438</v>
+        <v>2.4219436322947732</v>
       </c>
       <c r="J125" s="177">
         <f t="shared" si="49"/>
-        <v>1.2967611701455044</v>
+        <v>1.2990827374577851</v>
       </c>
       <c r="K125" s="177">
         <f t="shared" si="49"/>
-        <v>6.2642712512696468</v>
+        <v>6.2754860591363686</v>
       </c>
       <c r="L125" s="177">
         <f t="shared" si="49"/>
-        <v>8.422689891081216</v>
+        <v>8.4377688755409519</v>
       </c>
       <c r="M125" s="177">
         <f t="shared" si="49"/>
-        <v>7.7924527208141718</v>
+        <v>7.8064034034345546</v>
       </c>
       <c r="N125" s="177" t="str">
         <f t="shared" si="49"/>
@@ -14583,38 +14583,38 @@
       </c>
       <c r="C126" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>5.0393837037482521E-2</v>
+        <v>5.0230367458535846E-2</v>
       </c>
       <c r="D126" s="27"/>
       <c r="E126" s="265"/>
       <c r="F126" s="27"/>
       <c r="G126" s="77">
         <f t="shared" ref="G126" si="50">IF(G$4="","",G125/Market_Price)</f>
-        <v>7.2469267652782568E-2</v>
+        <v>7.2234188893827128E-2</v>
       </c>
       <c r="H126" s="77">
         <f t="shared" ref="H126" si="51">IF(H$4="","",H125/Market_Price)</f>
-        <v>5.9684571645483173E-2</v>
+        <v>5.9490964403604719E-2</v>
       </c>
       <c r="I126" s="77">
         <f t="shared" ref="I126" si="52">IF(I$4="","",I125/Market_Price)</f>
-        <v>4.8840715566554303E-2</v>
+        <v>4.8682284066226593E-2</v>
       </c>
       <c r="J126" s="77">
         <f t="shared" ref="J126" si="53">IF(J$4="","",J125/Market_Price)</f>
-        <v>2.6197195356474835E-2</v>
+        <v>2.6112215828297189E-2</v>
       </c>
       <c r="K126" s="77">
         <f t="shared" ref="K126" si="54">IF(K$4="","",K125/Market_Price)</f>
-        <v>0.12655093436908377</v>
+        <v>0.12614042329922348</v>
       </c>
       <c r="L126" s="77">
         <f t="shared" ref="L126" si="55">IF(L$4="","",L125/Market_Price)</f>
-        <v>0.17015535133497406</v>
+        <v>0.16960339448323522</v>
       </c>
       <c r="M126" s="77">
         <f t="shared" ref="M126" si="56">IF(M$4="","",M125/Market_Price)</f>
-        <v>0.15742328728917518</v>
+        <v>0.15691263122481516</v>
       </c>
       <c r="N126" s="77" t="str">
         <f t="shared" ref="N126" si="57">IF(N$4="","",N125/Market_Price)</f>
@@ -14640,31 +14640,31 @@
       <c r="C127" s="169"/>
       <c r="G127" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.658677516852991E-3</v>
+        <v>6.6252168258135293E-3</v>
       </c>
       <c r="H127" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.3164573991328779E-3</v>
+        <v>5.2897415328055771E-3</v>
       </c>
       <c r="I127" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.7039979255622068E-3</v>
+        <v>3.6853848706598839E-3</v>
       </c>
       <c r="J127" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.329850262337999E-3</v>
+        <v>2.3181424720749937E-3</v>
       </c>
       <c r="K127" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-4.2923758505603916E-4</v>
+        <v>-4.2708061226681281E-4</v>
       </c>
       <c r="L127" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.0347415275710459E-3</v>
+        <v>2.0245166957742066E-3</v>
       </c>
       <c r="M127" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.6436054100231082E-3</v>
+        <v>1.6353460863546504E-3</v>
       </c>
       <c r="N127" s="23" t="str">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -15492,7 +15492,7 @@
       </c>
       <c r="C8" s="338">
         <f>BS!D66</f>
-        <v>406390.46496957855</v>
+        <v>405813.98940414842</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
@@ -15524,7 +15524,7 @@
       </c>
       <c r="C10" s="347">
         <f>C6-C7+C8+C9</f>
-        <v>8786487.3138417229</v>
+        <v>8785910.8382762913</v>
       </c>
       <c r="D10" t="str">
         <f>Reporting_currency</f>
@@ -15538,7 +15538,7 @@
       </c>
       <c r="C11" s="208">
         <f>Exchange_Rate</f>
-        <v>9.2078154000000012</v>
+        <v>9.2242999799999996</v>
       </c>
       <c r="D11" t="str">
         <f>Thesis!C15</f>
@@ -15552,7 +15552,7 @@
       </c>
       <c r="C12" s="111">
         <f>(C10*scaling_factor)/Common_Shares*Exchange_Rate</f>
-        <v>31.617787389948063</v>
+        <v>31.672313988689243</v>
       </c>
       <c r="D12" t="str">
         <f>Market_currency</f>
@@ -15605,7 +15605,7 @@
       </c>
       <c r="C18" s="140">
         <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>32.873752096334002</v>
+        <v>32.930527225240084</v>
       </c>
       <c r="D18" t="str">
         <f>Market_currency</f>
@@ -16701,23 +16701,23 @@
       </c>
       <c r="B65" s="124">
         <f>C12</f>
-        <v>31.617787389948063</v>
+        <v>31.672313988689243</v>
       </c>
       <c r="C65" s="124">
         <f>C12</f>
-        <v>31.617787389948063</v>
+        <v>31.672313988689243</v>
       </c>
       <c r="D65" s="124">
         <f>C12</f>
-        <v>31.617787389948063</v>
+        <v>31.672313988689243</v>
       </c>
       <c r="E65" s="141">
         <f>C12</f>
-        <v>31.617787389948063</v>
+        <v>31.672313988689243</v>
       </c>
       <c r="F65" s="124">
         <f>C12</f>
-        <v>31.617787389948063</v>
+        <v>31.672313988689243</v>
       </c>
       <c r="H65" s="120"/>
     </row>
@@ -16728,23 +16728,23 @@
       </c>
       <c r="B66" s="124">
         <f t="shared" ref="B66:F71" si="4">(B56-$C$7+$C$8+$C$9)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>31.617787389948063</v>
+        <v>31.672313988689243</v>
       </c>
       <c r="C66" s="124">
         <f t="shared" si="4"/>
-        <v>32.141374144896901</v>
+        <v>32.196838111230072</v>
       </c>
       <c r="D66" s="124">
         <f t="shared" si="4"/>
-        <v>33.211259676022841</v>
+        <v>33.268639038447546</v>
       </c>
       <c r="E66" s="124">
         <f t="shared" si="4"/>
-        <v>34.312540509969253</v>
+        <v>34.371891474909965</v>
       </c>
       <c r="F66" s="124">
         <f t="shared" si="4"/>
-        <v>36.02633969830832</v>
+        <v>36.088758845939154</v>
       </c>
       <c r="H66" s="120"/>
     </row>
@@ -16755,23 +16755,23 @@
       </c>
       <c r="B67" s="124">
         <f t="shared" si="4"/>
-        <v>31.61778738994807</v>
+        <v>31.672313988689261</v>
       </c>
       <c r="C67" s="124">
         <f t="shared" si="4"/>
-        <v>32.643379567196938</v>
+        <v>32.699742264465172</v>
       </c>
       <c r="D67" s="124">
         <f t="shared" si="4"/>
-        <v>34.845551762458996</v>
+        <v>34.905856967493683</v>
       </c>
       <c r="E67" s="124">
         <f t="shared" si="4"/>
-        <v>37.269142459891327</v>
+        <v>37.333786574103016</v>
       </c>
       <c r="F67" s="124">
         <f t="shared" si="4"/>
-        <v>41.37843701263477</v>
+        <v>41.450437920163381</v>
       </c>
       <c r="H67" s="120"/>
     </row>
@@ -16782,23 +16782,23 @@
       </c>
       <c r="B68" s="124">
         <f t="shared" si="4"/>
-        <v>31.61778738994807</v>
+        <v>31.672313988689261</v>
       </c>
       <c r="C68" s="124">
         <f t="shared" si="4"/>
-        <v>33.263176152999087</v>
+        <v>33.320648460523223</v>
       </c>
       <c r="D68" s="124">
         <f t="shared" si="4"/>
-        <v>36.968576181768896</v>
+        <v>37.032682197784439</v>
       </c>
       <c r="E68" s="124">
         <f t="shared" si="4"/>
-        <v>41.318113720943558</v>
+        <v>41.390006632809296</v>
       </c>
       <c r="F68" s="124">
         <f t="shared" si="4"/>
-        <v>49.338222214914275</v>
+        <v>49.424473377280719</v>
       </c>
       <c r="H68" s="120"/>
     </row>
@@ -16809,23 +16809,23 @@
       </c>
       <c r="B69" s="124">
         <f t="shared" si="4"/>
-        <v>31.617787389948077</v>
+        <v>31.672313988689261</v>
       </c>
       <c r="C69" s="124">
         <f t="shared" si="4"/>
-        <v>33.8926532740239</v>
+        <v>33.951252522685429</v>
       </c>
       <c r="D69" s="124">
         <f t="shared" si="4"/>
-        <v>39.242489653313314</v>
+        <v>39.310666614162834</v>
       </c>
       <c r="E69" s="124">
         <f t="shared" si="4"/>
-        <v>45.907156846774839</v>
+        <v>45.987265436870956</v>
       </c>
       <c r="F69" s="124">
         <f t="shared" si="4"/>
-        <v>59.213747114822922</v>
+        <v>59.31767824504086</v>
       </c>
       <c r="H69" s="120"/>
     </row>
@@ -16836,23 +16836,23 @@
       </c>
       <c r="B70" s="124">
         <f t="shared" si="4"/>
-        <v>31.617787389948077</v>
+        <v>31.672313988689261</v>
       </c>
       <c r="C70" s="124">
         <f t="shared" si="4"/>
-        <v>34.475893618504585</v>
+        <v>34.535537031465694</v>
       </c>
       <c r="D70" s="124">
         <f t="shared" si="4"/>
-        <v>41.468450847638245</v>
+        <v>41.540612905255095</v>
       </c>
       <c r="E70" s="124">
         <f t="shared" si="4"/>
-        <v>50.676075035045081</v>
+        <v>50.764721330337586</v>
       </c>
       <c r="F70" s="124">
         <f t="shared" si="4"/>
-        <v>70.525360867180197</v>
+        <v>70.6495429683103</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="13.15">
@@ -16862,23 +16862,23 @@
       </c>
       <c r="B71" s="124">
         <f t="shared" si="4"/>
-        <v>31.61778738994807</v>
+        <v>31.672313988689261</v>
       </c>
       <c r="C71" s="124">
         <f t="shared" si="4"/>
-        <v>34.988141321820223</v>
+        <v>35.048701802280881</v>
       </c>
       <c r="D71" s="124">
         <f t="shared" si="4"/>
-        <v>43.537417913163587</v>
+        <v>43.613284003890065</v>
       </c>
       <c r="E71" s="124">
         <f t="shared" si="4"/>
-        <v>55.395760272934034</v>
+        <v>55.492856132591051</v>
       </c>
       <c r="F71" s="124">
         <f t="shared" si="4"/>
-        <v>82.941344906137374</v>
+        <v>83.087755111685041</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="13.15">
@@ -16913,7 +16913,7 @@
       </c>
       <c r="E74" s="135">
         <f>INDEX(B$65:F$71, MATCH(D74, A$65:A$71, 0), MATCH(C74, B$64:F$64, 0))</f>
-        <v>41.37843701263477</v>
+        <v>41.450437920163381</v>
       </c>
       <c r="F74" s="142">
         <f>Scenarios!C58</f>
@@ -16935,7 +16935,7 @@
       </c>
       <c r="E75" s="135">
         <f>INDEX(B$65:F$71, MATCH(D75, A$65:A$71, 0), MATCH(C75, B$64:F$64, 0))</f>
-        <v>34.312540509969253</v>
+        <v>34.371891474909965</v>
       </c>
       <c r="F75" s="142">
         <f>Scenarios!C40*(1-F$74-F$78)</f>
@@ -16958,7 +16958,7 @@
       </c>
       <c r="E76" s="135">
         <f>INDEX(B$65:F$71, MATCH(D76, A$65:A$71, 0), MATCH(C76, B$64:F$64, 0))</f>
-        <v>33.211259676022841</v>
+        <v>33.268639038447546</v>
       </c>
       <c r="F76" s="142">
         <f>Scenarios!C28*(1-F$74-F$78)</f>
@@ -16981,7 +16981,7 @@
       </c>
       <c r="E77" s="135">
         <f>INDEX(B$65:F$71, MATCH(D77, A$65:A$71, 0), MATCH(C77, B$64:F$64, 0))</f>
-        <v>32.141374144896901</v>
+        <v>32.196838111230072</v>
       </c>
       <c r="F77" s="142">
         <f>Scenarios!C34*(1-F$74-F$78)</f>
@@ -17004,7 +17004,7 @@
       </c>
       <c r="E78" s="135">
         <f>INDEX(B$65:F$71, MATCH(D78, A$65:A$71, 0), MATCH(C78, B$64:F$64, 0))</f>
-        <v>31.61778738994807</v>
+        <v>31.672313988689261</v>
       </c>
       <c r="F78" s="142">
         <f>Scenarios!C52</f>
@@ -17186,7 +17186,7 @@
       </c>
       <c r="C4" s="114">
         <f>Normalized_FCF!C91*(1-dividend_tax_rate)</f>
-        <v>3864033.3614266952</v>
+        <v>3870951.0682118568</v>
       </c>
       <c r="D4" t="str">
         <f>Market_currency</f>
@@ -17218,7 +17218,7 @@
       </c>
       <c r="C6" s="319">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
-        <v>51520444.819022603</v>
+        <v>51612680.909491427</v>
       </c>
       <c r="D6" t="str">
         <f>Reporting_currency</f>
@@ -17234,7 +17234,7 @@
       </c>
       <c r="C7" s="111">
         <f>(C6*scaling_factor)/Common_Shares*Exchange_Rate</f>
-        <v>185.39405024317679</v>
+        <v>186.05845946464785</v>
       </c>
       <c r="D7" t="str">
         <f>Market_currency</f>
@@ -17287,7 +17287,7 @@
       </c>
       <c r="C13" s="140">
         <f>F47/Common_Shares*scaling_factor</f>
-        <v>20.894740988907198</v>
+        <v>20.932148453593214</v>
       </c>
       <c r="D13" t="str">
         <f>Market_currency</f>
@@ -17322,7 +17322,7 @@
       </c>
       <c r="C16" s="123">
         <f>C4*(1+D16)</f>
-        <v>3955814.2748051235</v>
+        <v>3962896.2952459496</v>
       </c>
       <c r="D16" s="138">
         <f>IF($C$12&lt;B16,0,DDM!$C$11)</f>
@@ -17334,7 +17334,7 @@
       </c>
       <c r="F16" s="125">
         <f t="shared" ref="F16:F46" si="1">C16*E16</f>
-        <v>3679827.2323768591</v>
+        <v>3686415.1583683253</v>
       </c>
       <c r="H16" s="120"/>
     </row>
@@ -17344,7 +17344,7 @@
       </c>
       <c r="C17" s="123">
         <f t="shared" ref="C17:C45" si="2">IF(ROW()-ROW($C$16)&lt;$C$12, $C$16*(1+D17)^(ROW()-ROW($C$16)), 0)</f>
-        <v>4049775.2252776073</v>
+        <v>4057025.4622538062</v>
       </c>
       <c r="D17" s="138">
         <f>IF($C$12&lt;B17,0,DDM!$C$11)</f>
@@ -17356,7 +17356,7 @@
       </c>
       <c r="F17" s="125">
         <f t="shared" si="1"/>
-        <v>3504402.5746047441</v>
+        <v>3510676.4411065928</v>
       </c>
       <c r="H17" s="120"/>
     </row>
@@ -17366,7 +17366,7 @@
       </c>
       <c r="C18" s="123">
         <f t="shared" si="2"/>
-        <v>4145967.9944352917</v>
+        <v>4153390.443530187</v>
       </c>
       <c r="D18" s="138">
         <f>IF($C$12&lt;B18,0,DDM!$C$11)</f>
@@ -17378,7 +17378,7 @@
       </c>
       <c r="F18" s="125">
         <f t="shared" si="1"/>
-        <v>3337340.7579692192</v>
+        <v>3343315.5368198021</v>
       </c>
       <c r="H18" s="120"/>
     </row>
@@ -17388,7 +17388,7 @@
       </c>
       <c r="C19" s="123">
         <f t="shared" si="2"/>
-        <v>4244445.5938177416</v>
+        <v>4252044.3455202272</v>
       </c>
       <c r="D19" s="138">
         <f>IF($C$12&lt;B19,0,DDM!$C$11)</f>
@@ -17400,7 +17400,7 @@
       </c>
       <c r="F19" s="125">
         <f t="shared" si="1"/>
-        <v>3178243.1092577251</v>
+        <v>3183933.0585581856</v>
       </c>
       <c r="H19" s="120"/>
     </row>
@@ -17410,7 +17410,7 @@
       </c>
       <c r="C20" s="123">
         <f t="shared" si="2"/>
-        <v>4345262.2941274419</v>
+        <v>4353041.5360862361</v>
       </c>
       <c r="D20" s="138">
         <f>IF($C$12&lt;B20,0,DDM!$C$11)</f>
@@ -17422,7 +17422,7 @@
       </c>
       <c r="F20" s="125">
         <f t="shared" si="1"/>
-        <v>3026729.960799939</v>
+        <v>3032148.6589394775</v>
       </c>
       <c r="H20" s="120"/>
     </row>
@@ -17982,7 +17982,7 @@
       </c>
       <c r="C46" s="123">
         <f>C$16*(1+F4)^$C$12/Equity_Cost</f>
-        <v>52744190.330734983</v>
+        <v>52838617.269945994</v>
       </c>
       <c r="D46" s="139">
         <f>Terminal_Growth</f>
@@ -17994,7 +17994,7 @@
       </c>
       <c r="F46" s="125">
         <f t="shared" si="1"/>
-        <v>36739421.081190981</v>
+        <v>36805194.980824813</v>
       </c>
       <c r="H46" s="120"/>
     </row>
@@ -18005,7 +18005,7 @@
       </c>
       <c r="F47" s="137">
         <f>SUM(F16:F46)</f>
-        <v>53465964.716199473</v>
+        <v>53561683.834617198</v>
       </c>
       <c r="H47" s="120"/>
     </row>
@@ -18026,7 +18026,7 @@
     <row r="50" spans="1:8" ht="13.15">
       <c r="A50" s="133">
         <f>F47</f>
-        <v>53465964.716199473</v>
+        <v>53561683.834617198</v>
       </c>
       <c r="B50" s="131">
         <f>C73</f>
@@ -18056,19 +18056,19 @@
       </c>
       <c r="B51" s="123">
         <f t="dataTable" ref="B51:F56" dt2D="1" dtr="1" r1="C11" r2="C12"/>
-        <v>51520444.819022611</v>
+        <v>51612680.909491435</v>
       </c>
       <c r="C51" s="123">
-        <v>52331493.445207655</v>
+        <v>52425181.540889606</v>
       </c>
       <c r="D51" s="123">
-        <v>53988772.171213143</v>
+        <v>54085427.262056738</v>
       </c>
       <c r="E51" s="123">
-        <v>55694682.98536931</v>
+        <v>55794392.136493996</v>
       </c>
       <c r="F51" s="123">
-        <v>58349399.637617856</v>
+        <v>58453861.478401296</v>
       </c>
       <c r="H51" s="120"/>
     </row>
@@ -18077,19 +18077,19 @@
         <v>10</v>
       </c>
       <c r="B52" s="123">
-        <v>51520444.819022611</v>
+        <v>51612680.909491435</v>
       </c>
       <c r="C52" s="123">
-        <v>53109112.061884992</v>
+        <v>53204192.313658163</v>
       </c>
       <c r="D52" s="123">
-        <v>56520330.38761352</v>
+        <v>56621517.679867543</v>
       </c>
       <c r="E52" s="123">
-        <v>60274531.361966722</v>
+        <v>60382439.730133906</v>
       </c>
       <c r="F52" s="123">
-        <v>66639928.633939266</v>
+        <v>66759232.854000002</v>
       </c>
       <c r="H52" s="120"/>
     </row>
@@ -18098,19 +18098,19 @@
         <v>15</v>
       </c>
       <c r="B53" s="123">
-        <v>51520444.819022611</v>
+        <v>51612680.909491435</v>
       </c>
       <c r="C53" s="123">
-        <v>54069192.057564288</v>
+        <v>54165991.122628957</v>
       </c>
       <c r="D53" s="123">
-        <v>59808946.88213668</v>
+        <v>59916021.72310213</v>
       </c>
       <c r="E53" s="123">
-        <v>66546486.386994131</v>
+        <v>66665623.319144756</v>
       </c>
       <c r="F53" s="123">
-        <v>78969829.633187622</v>
+        <v>79111207.844807118</v>
       </c>
       <c r="H53" s="120"/>
     </row>
@@ -18119,19 +18119,19 @@
         <v>20</v>
       </c>
       <c r="B54" s="123">
-        <v>51520444.819022618</v>
+        <v>51612680.909491442</v>
       </c>
       <c r="C54" s="123">
-        <v>55044267.437903099</v>
+        <v>55142812.16221647</v>
       </c>
       <c r="D54" s="123">
-        <v>63331294.190826692</v>
+        <v>63444675.024416395</v>
       </c>
       <c r="E54" s="123">
-        <v>73655025.874539226</v>
+        <v>73786889.09221743</v>
       </c>
       <c r="F54" s="123">
-        <v>94267258.048292994</v>
+        <v>94436022.960399866</v>
       </c>
       <c r="H54" s="120"/>
     </row>
@@ -18140,19 +18140,19 @@
         <v>25</v>
       </c>
       <c r="B55" s="123">
-        <v>51520444.819022626</v>
+        <v>51612680.909491442</v>
       </c>
       <c r="C55" s="123">
-        <v>55947720.926089555</v>
+        <v>56047883.086315274</v>
       </c>
       <c r="D55" s="123">
-        <v>66779362.255067326</v>
+        <v>66898916.100536741</v>
       </c>
       <c r="E55" s="123">
-        <v>81042196.211503565</v>
+        <v>81187284.542317003</v>
       </c>
       <c r="F55" s="123">
-        <v>111789223.04658976</v>
+        <v>111989357.20549661</v>
       </c>
       <c r="H55" s="120"/>
     </row>
@@ -18161,19 +18161,19 @@
         <v>30</v>
       </c>
       <c r="B56" s="123">
-        <v>51520444.819022618</v>
+        <v>51612680.909491442</v>
       </c>
       <c r="C56" s="123">
-        <v>56741205.085331112</v>
+        <v>56842787.8054327</v>
       </c>
       <c r="D56" s="123">
-        <v>69984242.592959762</v>
+        <v>70109534.07586275</v>
       </c>
       <c r="E56" s="123">
-        <v>88353103.510122597</v>
+        <v>88511280.421777532</v>
       </c>
       <c r="F56" s="123">
-        <v>131021884.49639229</v>
+        <v>131256450.53001744</v>
       </c>
       <c r="H56" s="120"/>
     </row>
@@ -18223,23 +18223,23 @@
       </c>
       <c r="B60" s="124">
         <f>C7</f>
-        <v>185.39405024317679</v>
+        <v>186.05845946464785</v>
       </c>
       <c r="C60" s="124">
         <f>C7</f>
-        <v>185.39405024317679</v>
+        <v>186.05845946464785</v>
       </c>
       <c r="D60" s="124">
         <f>C7</f>
-        <v>185.39405024317679</v>
+        <v>186.05845946464785</v>
       </c>
       <c r="E60" s="141">
         <f>C7</f>
-        <v>185.39405024317679</v>
+        <v>186.05845946464785</v>
       </c>
       <c r="F60" s="124">
         <f>C7</f>
-        <v>185.39405024317679</v>
+        <v>186.05845946464785</v>
       </c>
       <c r="H60" s="120"/>
     </row>
@@ -18250,23 +18250,23 @@
       </c>
       <c r="B61" s="124">
         <f t="shared" ref="B61:F66" si="4">B51/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>185.39405024317682</v>
+        <v>186.05845946464788</v>
       </c>
       <c r="C61" s="124">
         <f t="shared" si="4"/>
-        <v>188.31257298266007</v>
+        <v>188.98744151185244</v>
       </c>
       <c r="D61" s="124">
         <f t="shared" si="4"/>
-        <v>194.27621744410243</v>
+        <v>194.97245829009003</v>
       </c>
       <c r="E61" s="124">
         <f t="shared" si="4"/>
-        <v>200.41486233160296</v>
+        <v>201.13310265527195</v>
       </c>
       <c r="F61" s="124">
         <f t="shared" si="4"/>
-        <v>209.9677432148566</v>
+        <v>210.72021884511784</v>
       </c>
       <c r="H61" s="120"/>
     </row>
@@ -18277,23 +18277,23 @@
       </c>
       <c r="B62" s="124">
         <f t="shared" si="4"/>
-        <v>185.39405024317682</v>
+        <v>186.05845946464788</v>
       </c>
       <c r="C62" s="124">
         <f t="shared" si="4"/>
-        <v>191.1107993061463</v>
+        <v>191.79569602864169</v>
       </c>
       <c r="D62" s="124">
         <f t="shared" si="4"/>
-        <v>203.38591812338629</v>
+        <v>204.11480602103615</v>
       </c>
       <c r="E62" s="124">
         <f t="shared" si="4"/>
-        <v>216.89524488690907</v>
+        <v>217.67254707436905</v>
       </c>
       <c r="F62" s="124">
         <f t="shared" si="4"/>
-        <v>239.80084645543698</v>
+        <v>240.66023699948397</v>
       </c>
       <c r="H62" s="120"/>
     </row>
@@ -18304,23 +18304,23 @@
       </c>
       <c r="B63" s="124">
         <f t="shared" si="4"/>
-        <v>185.39405024317682</v>
+        <v>186.05845946464788</v>
       </c>
       <c r="C63" s="124">
         <f t="shared" si="4"/>
-        <v>194.56560486113864</v>
+        <v>195.26288280442361</v>
       </c>
       <c r="D63" s="124">
         <f t="shared" si="4"/>
-        <v>215.21985965393486</v>
+        <v>215.9911576497995</v>
       </c>
       <c r="E63" s="124">
         <f t="shared" si="4"/>
-        <v>239.46459864768153</v>
+        <v>240.3227841576734</v>
       </c>
       <c r="F63" s="124">
         <f t="shared" si="4"/>
-        <v>284.16945183875146</v>
+        <v>285.1878491606418</v>
       </c>
       <c r="H63" s="120"/>
     </row>
@@ -18331,23 +18331,23 @@
       </c>
       <c r="B64" s="124">
         <f t="shared" si="4"/>
-        <v>185.39405024317682</v>
+        <v>186.05845946464791</v>
       </c>
       <c r="C64" s="124">
         <f t="shared" si="4"/>
-        <v>198.07437064700139</v>
+        <v>198.78422319201206</v>
       </c>
       <c r="D64" s="124">
         <f t="shared" si="4"/>
-        <v>227.89487121905401</v>
+        <v>228.71159351281315</v>
       </c>
       <c r="E64" s="124">
         <f t="shared" si="4"/>
-        <v>265.0443647296496</v>
+        <v>265.99422218081565</v>
       </c>
       <c r="F64" s="124">
         <f t="shared" si="4"/>
-        <v>339.21657385300682</v>
+        <v>340.43224727644258</v>
       </c>
       <c r="H64" s="120"/>
     </row>
@@ -18358,23 +18358,23 @@
       </c>
       <c r="B65" s="124">
         <f t="shared" si="4"/>
-        <v>185.39405024317688</v>
+        <v>186.05845946464791</v>
       </c>
       <c r="C65" s="124">
         <f t="shared" si="4"/>
-        <v>201.3254082102363</v>
+        <v>202.04691171887566</v>
       </c>
       <c r="D65" s="124">
         <f t="shared" si="4"/>
-        <v>240.30259219641044</v>
+        <v>241.16378088067123</v>
       </c>
       <c r="E65" s="124">
         <f t="shared" si="4"/>
-        <v>291.6267716443586</v>
+        <v>292.67189426859721</v>
       </c>
       <c r="F65" s="124">
         <f t="shared" si="4"/>
-        <v>402.26859272948212</v>
+        <v>403.71022994581699</v>
       </c>
     </row>
     <row r="66" spans="1:8" ht="13.15">
@@ -18384,23 +18384,23 @@
       </c>
       <c r="B66" s="124">
         <f t="shared" si="4"/>
-        <v>185.39405024317682</v>
+        <v>186.05845946464791</v>
       </c>
       <c r="C66" s="124">
         <f t="shared" si="4"/>
-        <v>204.18072598946634</v>
+        <v>204.91246229392763</v>
       </c>
       <c r="D66" s="124">
         <f t="shared" si="4"/>
-        <v>251.83521285746536</v>
+        <v>252.7377317759213</v>
       </c>
       <c r="E66" s="124">
         <f t="shared" si="4"/>
-        <v>317.93474937639365</v>
+        <v>319.07415368324541</v>
       </c>
       <c r="F66" s="124">
         <f t="shared" si="4"/>
-        <v>471.4764773985637</v>
+        <v>473.16613960120384</v>
       </c>
     </row>
     <row r="68" spans="1:8" ht="13.15">
@@ -18435,7 +18435,7 @@
       </c>
       <c r="E69" s="135">
         <f>INDEX(B$60:F$66, MATCH(D69, A$60:A$66, 0), MATCH(C69, B$59:F$59, 0))</f>
-        <v>239.80084645543698</v>
+        <v>240.66023699948397</v>
       </c>
       <c r="F69" s="142">
         <f>Scenarios!C58</f>
@@ -18457,7 +18457,7 @@
       </c>
       <c r="E70" s="135">
         <f>INDEX(B$60:F$66, MATCH(D70, A$60:A$66, 0), MATCH(C70, B$59:F$59, 0))</f>
-        <v>200.41486233160296</v>
+        <v>201.13310265527195</v>
       </c>
       <c r="F70" s="142">
         <f>Scenarios!C40*(1-F$69-F$73)</f>
@@ -18480,7 +18480,7 @@
       </c>
       <c r="E71" s="135">
         <f>INDEX(B$60:F$66, MATCH(D71, A$60:A$66, 0), MATCH(C71, B$59:F$59, 0))</f>
-        <v>194.27621744410243</v>
+        <v>194.97245829009003</v>
       </c>
       <c r="F71" s="142">
         <f>Scenarios!C28*(1-F$69-F$73)</f>
@@ -18503,7 +18503,7 @@
       </c>
       <c r="E72" s="135">
         <f>INDEX(B$60:F$66, MATCH(D72, A$60:A$66, 0), MATCH(C72, B$59:F$59, 0))</f>
-        <v>188.31257298266007</v>
+        <v>188.98744151185244</v>
       </c>
       <c r="F72" s="142">
         <f>Scenarios!C34*(1-F$69-F$73)</f>
@@ -18526,7 +18526,7 @@
       </c>
       <c r="E73" s="135">
         <f>INDEX(B$60:F$66, MATCH(D73, A$60:A$66, 0), MATCH(C73, B$59:F$59, 0))</f>
-        <v>185.39405024317682</v>
+        <v>186.05845946464788</v>
       </c>
       <c r="F73" s="142">
         <f>Scenarios!C52</f>
@@ -18626,7 +18626,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-49.5</v>
+        <v>-49.75</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18646,7 +18646,7 @@
       </c>
       <c r="I4" s="124">
         <f t="shared" ref="I4:I13" si="0">IF(ROW()-3 &lt; $C$76, $C$77, IF(ROW()-3 = $C$76, $C$77 + $C$60, ""))</f>
-        <v>1.5100817256000003</v>
+        <v>1.5127851967199999</v>
       </c>
     </row>
     <row r="5" spans="2:9">
@@ -18655,7 +18655,7 @@
       </c>
       <c r="I5" s="124">
         <f t="shared" si="0"/>
-        <v>1.5100817256000003</v>
+        <v>1.5127851967199999</v>
       </c>
     </row>
     <row r="6" spans="2:9" ht="13.15">
@@ -18675,7 +18675,7 @@
       </c>
       <c r="I6" s="124">
         <f t="shared" si="0"/>
-        <v>35.055677808657386</v>
+        <v>35.116359198429507</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1">
@@ -18866,7 +18866,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>49.5</v>
+        <v>49.75</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -18881,7 +18881,7 @@
       </c>
       <c r="C22" s="160">
         <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
-        <v>31.617787389948063</v>
+        <v>31.672313988689243</v>
       </c>
       <c r="D22" t="str">
         <f>Market_currency</f>
@@ -18928,7 +18928,7 @@
       </c>
       <c r="C27" s="160">
         <f>IF(valuation_method="DCF",DCF!E76,DDM!E71)</f>
-        <v>33.211259676022841</v>
+        <v>33.268639038447546</v>
       </c>
       <c r="D27" s="160" t="str">
         <f>Market_currency</f>
@@ -18986,7 +18986,7 @@
       </c>
       <c r="C33" s="160">
         <f>IF(valuation_method="DCF",DCF!E77,DDM!E72)</f>
-        <v>32.141374144896901</v>
+        <v>32.196838111230072</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
@@ -19044,7 +19044,7 @@
       </c>
       <c r="C39" s="160">
         <f>IF(valuation_method="DCF",DCF!E75,DDM!E70)</f>
-        <v>34.312540509969253</v>
+        <v>34.371891474909965</v>
       </c>
       <c r="D39" t="str">
         <f>Market_currency</f>
@@ -19071,7 +19071,7 @@
       </c>
       <c r="C42" s="154">
         <f>C27*C28+C33*C34+C39*C40</f>
-        <v>33.217538736586938</v>
+        <v>33.274929340296531</v>
       </c>
       <c r="D42" t="str">
         <f>Market_currency</f>
@@ -19145,7 +19145,7 @@
       </c>
       <c r="C51" s="160">
         <f>IF(valuation_method="DCF",DCF!E78,DDM!E73)</f>
-        <v>31.61778738994807</v>
+        <v>31.672313988689261</v>
       </c>
       <c r="D51" t="str">
         <f>Market_currency</f>
@@ -19203,7 +19203,7 @@
       </c>
       <c r="C57" s="160">
         <f>IF(valuation_method="DCF",DCF!E74,DDM!E69)</f>
-        <v>41.37843701263477</v>
+        <v>41.450437920163381</v>
       </c>
       <c r="D57" t="str">
         <f>Market_currency</f>
@@ -19229,7 +19229,7 @@
       </c>
       <c r="C60" s="154">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
-        <v>33.545596083057383</v>
+        <v>33.603574001709504</v>
       </c>
       <c r="D60" t="str">
         <f>Market_currency</f>
@@ -19291,7 +19291,7 @@
       </c>
       <c r="C66" s="160">
         <f>IF(valuation_method="DCF",DCF!C18,DDM!C13)</f>
-        <v>32.873752096334002</v>
+        <v>32.930527225240084</v>
       </c>
       <c r="D66" s="160" t="str">
         <f>Market_currency</f>
@@ -19354,7 +19354,7 @@
       </c>
       <c r="F72" s="291">
         <f>BS!D89/C60</f>
-        <v>-4.8952627066889035E-2</v>
+        <v>-4.9017497128601116E-2</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="13.9">
@@ -19387,7 +19387,7 @@
       </c>
       <c r="C77" s="173">
         <f>Normalized_FCF!C90*(1-dividend_tax_rate)</f>
-        <v>1.5100817256000003</v>
+        <v>1.5127851967199999</v>
       </c>
       <c r="D77" t="str">
         <f>Market_currency</f>
@@ -19414,7 +19414,7 @@
       </c>
       <c r="C81" s="116">
         <f>PV(C80, C76, -C77, 0)</f>
-        <v>2.5609169334211259</v>
+        <v>2.5655016951945129</v>
       </c>
       <c r="D81" s="116"/>
       <c r="E81" s="100"/>
@@ -19426,7 +19426,7 @@
       </c>
       <c r="C82" s="116">
         <f>C60/(1+C80)^C76</f>
-        <v>13.634342766065082</v>
+        <v>13.657907433504851</v>
       </c>
       <c r="D82" s="116"/>
     </row>
@@ -19436,7 +19436,7 @@
       </c>
       <c r="C83" s="111">
         <f>C81+C82</f>
-        <v>16.195259699486208</v>
+        <v>16.223409128699366</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -19447,7 +19447,7 @@
       </c>
       <c r="F83" s="291">
         <f>(1-C83/C60)</f>
-        <v>0.51721651750091202</v>
+        <v>0.5172117963442211</v>
       </c>
     </row>
     <row r="84" spans="2:8">
@@ -19464,7 +19464,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>49.5</v>
+        <v>49.75</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19477,7 +19477,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>-8.6822328085409906E-2</v>
+        <v>-8.7863363504127934E-2</v>
       </c>
     </row>
     <row r="88" spans="2:8">
@@ -19503,7 +19503,7 @@
       </c>
       <c r="C91" s="116">
         <f>PV(C90, C76, -C77, 0)</f>
-        <v>2.947679528371201</v>
+        <v>2.9529567039974398</v>
       </c>
       <c r="D91" s="116"/>
       <c r="E91" s="100"/>
@@ -19515,7 +19515,7 @@
       </c>
       <c r="C92" s="116">
         <f>C60/(1+C90)^C76</f>
-        <v>17.175345194525381</v>
+        <v>17.205029888875266</v>
       </c>
       <c r="D92" s="116"/>
     </row>
@@ -19525,7 +19525,7 @@
       </c>
       <c r="C93" s="111">
         <f>C91+C92</f>
-        <v>20.123024722896581</v>
+        <v>20.157986592872707</v>
       </c>
       <c r="D93" t="str">
         <f>Market_currency</f>
@@ -19536,7 +19536,7 @@
       </c>
       <c r="F93" s="291">
         <f>(1-C93/C60)</f>
-        <v>0.40012916529869136</v>
+        <v>0.40012373112909905</v>
       </c>
     </row>
     <row r="95" spans="2:8" ht="13.15">
@@ -19563,7 +19563,7 @@
       </c>
       <c r="C97" s="116">
         <f>PV(C96, C76, -C77, 0)</f>
-        <v>3.9270063967330664</v>
+        <v>3.9340368429676258</v>
       </c>
       <c r="D97" s="116"/>
       <c r="G97" s="2"/>
@@ -19575,7 +19575,7 @@
       </c>
       <c r="C98" s="116">
         <f>C60/(1+C96)^C76</f>
-        <v>27.00288212755698</v>
+        <v>27.049552065974172</v>
       </c>
       <c r="D98" s="116"/>
       <c r="G98" s="2"/>
@@ -19587,7 +19587,7 @@
       </c>
       <c r="C99" s="111">
         <f>C97+C98</f>
-        <v>30.929888524290046</v>
+        <v>30.983588908941798</v>
       </c>
       <c r="D99" t="s">
         <v>393</v>
@@ -19597,7 +19597,7 @@
       </c>
       <c r="F99" s="291">
         <f>(1-C99/C60)</f>
-        <v>7.7974693080157587E-2</v>
+        <v>7.796745348082379E-2</v>
       </c>
     </row>
     <row r="100" spans="2:8">
@@ -19623,7 +19623,7 @@
       </c>
       <c r="C103" s="116">
         <f>PV(C102, C76, -C77, 0)</f>
-        <v>3.6432278916053904</v>
+        <v>3.6497502944803863</v>
       </c>
       <c r="D103" s="116"/>
     </row>
@@ -19633,7 +19633,7 @@
       </c>
       <c r="C104" s="116">
         <f>C60/(1+C102)^C76</f>
-        <v>24.044154632408034</v>
+        <v>24.085710908167307</v>
       </c>
       <c r="D104" s="116"/>
     </row>
@@ -19643,7 +19643,7 @@
       </c>
       <c r="C105" s="111">
         <f>C103+C104</f>
-        <v>27.687382524013426</v>
+        <v>27.735461202647695</v>
       </c>
       <c r="D105" t="s">
         <v>393</v>
@@ -19653,7 +19653,7 @@
       </c>
       <c r="F105" s="291">
         <f>(1-C105/C66)</f>
-        <v>0.15776627983086078</v>
+        <v>0.15775836162776513</v>
       </c>
     </row>
     <row r="106" spans="2:8">

--- a/financial_models/opportunities/1913.HK_Valuation.xlsx
+++ b/financial_models/opportunities/1913.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8B11AF7-60BB-43CA-A93C-62647ACA425B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADF8D3D8-D90E-417D-BBAF-A36EB3820BEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -20,6 +20,7 @@
     <sheet name="DCF" sheetId="8" r:id="rId5"/>
     <sheet name="DDM" sheetId="10" r:id="rId6"/>
     <sheet name="Scenarios" sheetId="9" r:id="rId7"/>
+    <sheet name="Breakdown" sheetId="11" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">DCF!$B$73:$H$73</definedName>
@@ -48,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="686" uniqueCount="466">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="687" uniqueCount="467">
   <si>
     <t>Number of Shares:</t>
   </si>
@@ -2444,6 +2445,9 @@
   </si>
   <si>
     <t>After-tax Dividend per share</t>
+  </si>
+  <si>
+    <t>Divisional Analysis (Optional)</t>
   </si>
   <si>
     <t>Y</t>
@@ -4246,7 +4250,7 @@
         <v>350</v>
       </c>
       <c r="F1" s="254" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="13.9">
@@ -4277,7 +4281,7 @@
         <v>312</v>
       </c>
       <c r="C5" s="294" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -4324,10 +4328,10 @@
         <v>413</v>
       </c>
       <c r="C11" s="49" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="D11" s="49" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="E11" s="34"/>
     </row>
@@ -4421,7 +4425,7 @@
         <v>435</v>
       </c>
       <c r="E21" s="308" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="22" spans="2:6">
@@ -4429,7 +4433,7 @@
         <v>56</v>
       </c>
       <c r="C22" s="48" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="D22" s="1" t="str">
         <f>IF(valuation_method="DDM","DDM Terminal Value","")</f>
@@ -4442,7 +4446,7 @@
         <v>430</v>
       </c>
       <c r="C23" s="262" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="24" spans="2:6">
@@ -4450,7 +4454,7 @@
         <v>431</v>
       </c>
       <c r="C24" s="262" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="25" spans="2:6">
@@ -4458,7 +4462,7 @@
         <v>344</v>
       </c>
       <c r="C25" s="48" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="D25" s="32" t="str">
         <f>IF(D11="","",Market_currency&amp;"/"&amp;D13&amp;":")</f>
@@ -6512,7 +6516,7 @@
         <v>28</v>
       </c>
       <c r="C27" s="97" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="28" spans="2:13">
@@ -12680,7 +12684,7 @@
       </c>
       <c r="D78" s="27"/>
       <c r="E78" s="266" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="F78" s="27"/>
       <c r="G78" s="6">
@@ -19703,4 +19707,27 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F820689B-F36D-4933-9EEF-92EBF45B6A8E}">
+  <dimension ref="B2:E2"/>
+  <sheetFormatPr defaultRowHeight="12.75"/>
+  <cols>
+    <col min="1" max="1" width="2.59765625" customWidth="1"/>
+    <col min="2" max="2" width="22.73046875" customWidth="1"/>
+    <col min="3" max="5" width="20.73046875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:5" ht="13.9">
+      <c r="B2" s="36" t="s">
+        <v>456</v>
+      </c>
+      <c r="C2" s="37"/>
+      <c r="D2" s="37"/>
+      <c r="E2" s="37"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/financial_models/opportunities/1913.HK_Valuation.xlsx
+++ b/financial_models/opportunities/1913.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADF8D3D8-D90E-417D-BBAF-A36EB3820BEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FD830A7-A327-472B-AA38-25ECA2301BF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,20 +20,33 @@
     <sheet name="DCF" sheetId="8" r:id="rId5"/>
     <sheet name="DDM" sheetId="10" r:id="rId6"/>
     <sheet name="Scenarios" sheetId="9" r:id="rId7"/>
-    <sheet name="Breakdown" sheetId="11" r:id="rId8"/>
+    <sheet name="Breakdown" sheetId="12" r:id="rId8"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId9"/>
+  </externalReferences>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">DCF!$B$73:$H$73</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">DDM!$B$68:$H$68</definedName>
+    <definedName name="Common_Shares" localSheetId="7">[1]Thesis!$C$6</definedName>
     <definedName name="Common_Shares">Thesis!$C$6</definedName>
+    <definedName name="dividend_tax_rate" localSheetId="7">[1]Normalized_FCF!$C$93</definedName>
     <definedName name="dividend_tax_rate">Normalized_FCF!$C$93</definedName>
+    <definedName name="Equity_Cost" localSheetId="7">[1]Thesis!$C$86</definedName>
     <definedName name="Equity_Cost">Thesis!$C$86</definedName>
+    <definedName name="Exchange_Rate" localSheetId="7">[1]Thesis!$C$16</definedName>
     <definedName name="Exchange_Rate">Thesis!$C$16</definedName>
+    <definedName name="Market_currency" localSheetId="7">[1]Thesis!$C$13</definedName>
     <definedName name="Market_currency">Thesis!$C$13</definedName>
+    <definedName name="Market_Price" localSheetId="7">[1]Thesis!$C$12</definedName>
     <definedName name="Market_Price">Thesis!$C$12</definedName>
+    <definedName name="Reporting_currency" localSheetId="7">[1]Thesis!$C$25</definedName>
     <definedName name="Reporting_currency">Thesis!$C$25</definedName>
+    <definedName name="scaling_factor" localSheetId="7">[1]Data!$C$3</definedName>
     <definedName name="scaling_factor">Data!$C$3</definedName>
+    <definedName name="Terminal_Growth" localSheetId="7">[1]Thesis!$C$92</definedName>
     <definedName name="Terminal_Growth">Thesis!$C$92</definedName>
+    <definedName name="valuation_method" localSheetId="7">[1]Thesis!$E$21</definedName>
     <definedName name="valuation_method">Thesis!$E$21</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -42,7 +55,7 @@
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
     <ext uri="GoogleSheetsCustomDataVersion1">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId9" roundtripDataSignature="AMtx7mi73Cg0ax9bLfpeUuF69nNRn7idDQ=="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId10" roundtripDataSignature="AMtx7mi73Cg0ax9bLfpeUuF69nNRn7idDQ=="/>
     </ext>
   </extLst>
 </workbook>
@@ -2504,7 +2517,7 @@
     <numFmt numFmtId="180" formatCode="0.000000000000000%"/>
     <numFmt numFmtId="181" formatCode="#,##0_);\(#,##0\);0;@"/>
   </numFmts>
-  <fonts count="59">
+  <fonts count="60">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -2944,6 +2957,12 @@
       <family val="2"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="10">
     <fill>
@@ -3147,11 +3166,12 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="1"/>
+    <xf numFmtId="0" fontId="59" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="370">
+  <cellXfs count="373">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -3936,9 +3956,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1"/>
+    <xf numFmtId="168" fontId="9" fillId="4" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="0" borderId="1" xfId="2"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="常规 2" xfId="2" xr:uid="{C34E3C06-C9E1-4D88-BB68-974148DC605C}"/>
     <cellStyle name="常规 2 2" xfId="1" xr:uid="{A35F4541-DCCE-4554-A311-39480A36979A}"/>
   </cellStyles>
   <dxfs count="8">
@@ -4023,6 +4049,89 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Thesis"/>
+      <sheetName val="Data"/>
+      <sheetName val="BS"/>
+      <sheetName val="Normalized_FCF"/>
+      <sheetName val="DCF"/>
+      <sheetName val="DDM"/>
+      <sheetName val="Scenarios"/>
+      <sheetName val="Breakdown"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="6">
+          <cell r="C6">
+            <v>2558824000</v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="C12">
+            <v>49.75</v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="C13" t="str">
+            <v>HKD</v>
+          </cell>
+        </row>
+        <row r="16">
+          <cell r="C16">
+            <v>9.2242999799999996</v>
+          </cell>
+        </row>
+        <row r="21">
+          <cell r="E21" t="str">
+            <v>DCF</v>
+          </cell>
+        </row>
+        <row r="25">
+          <cell r="C25" t="str">
+            <v>EUR</v>
+          </cell>
+        </row>
+        <row r="86">
+          <cell r="C86">
+            <v>7.4999999999999997E-2</v>
+          </cell>
+        </row>
+        <row r="92">
+          <cell r="C92">
+            <v>0</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1">
+        <row r="3">
+          <cell r="C3">
+            <v>1000</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3">
+        <row r="93">
+          <cell r="C93">
+            <v>0</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
+      <sheetData sheetId="6"/>
+      <sheetData sheetId="7"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -19710,22 +19819,23 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F820689B-F36D-4933-9EEF-92EBF45B6A8E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59270744-4D92-44FA-9D5B-2B99784DB263}">
   <dimension ref="B2:E2"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="2.59765625" customWidth="1"/>
-    <col min="2" max="2" width="22.73046875" customWidth="1"/>
-    <col min="3" max="5" width="20.73046875" customWidth="1"/>
+    <col min="1" max="1" width="2.59765625" style="372" customWidth="1"/>
+    <col min="2" max="2" width="22.73046875" style="372" customWidth="1"/>
+    <col min="3" max="5" width="20.73046875" style="372" customWidth="1"/>
+    <col min="6" max="16384" width="9.06640625" style="372"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:5" ht="13.9">
-      <c r="B2" s="36" t="s">
+      <c r="B2" s="370" t="s">
         <v>456</v>
       </c>
-      <c r="C2" s="37"/>
-      <c r="D2" s="37"/>
-      <c r="E2" s="37"/>
+      <c r="C2" s="371"/>
+      <c r="D2" s="371"/>
+      <c r="E2" s="371"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/financial_models/opportunities/1913.HK_Valuation.xlsx
+++ b/financial_models/opportunities/1913.HK_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3C48CE6-D95E-44B5-B498-0D4C359BF867}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{736763B1-A020-44AF-9ED1-276DB5D17713}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2205" yWindow="2205" windowWidth="12690" windowHeight="7642" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -4992,30 +4992,30 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5025,6 +5025,15 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -5034,16 +5043,7 @@
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5413,7 +5413,7 @@
         <v>350</v>
       </c>
       <c r="C8" s="47">
-        <v>42.4</v>
+        <v>41.88</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5431,14 +5431,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>108494.1376</v>
+        <v>107163.54912</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>528</v>
       </c>
       <c r="E10" s="303">
         <f>Scenarios!F34</f>
-        <v>0.15855740519921338</v>
+        <v>0.16319188190025868</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5446,13 +5446,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="462" t="s">
+      <c r="B12" s="460" t="s">
         <v>355</v>
       </c>
-      <c r="C12" s="462"/>
-      <c r="D12" s="462"/>
-      <c r="E12" s="462"/>
-      <c r="F12" s="462"/>
+      <c r="C12" s="460"/>
+      <c r="D12" s="460"/>
+      <c r="E12" s="460"/>
+      <c r="F12" s="460"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5487,7 +5487,7 @@
         <v>354</v>
       </c>
       <c r="E16" s="416">
-        <v>9.2841749332904815</v>
+        <v>9.2771663694858564</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -5511,7 +5511,7 @@
       </c>
       <c r="C18" s="252">
         <f>C125</f>
-        <v>60.922911775163712</v>
+        <v>60.876921461817851</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>347</v>
@@ -5561,7 +5561,7 @@
       </c>
       <c r="C22" s="255">
         <f>E140</f>
-        <v>30.695059697144316</v>
+        <v>30.673866004358207</v>
       </c>
       <c r="D22" s="38" t="s">
         <v>406</v>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="C23" s="256">
         <f>E141</f>
-        <v>38.202646604928695</v>
+        <v>38.176081802996066</v>
       </c>
       <c r="D23" s="38" t="s">
         <v>407</v>
@@ -5591,7 +5591,7 @@
       </c>
       <c r="C24" s="256">
         <f>E144</f>
-        <v>47.121500168497697</v>
+        <v>47.088536133429045</v>
       </c>
       <c r="D24" s="38" t="s">
         <v>408</v>
@@ -5606,7 +5606,7 @@
       </c>
       <c r="C25" s="256">
         <f>E145</f>
-        <v>53.124686702250834</v>
+        <v>53.087406825662384</v>
       </c>
       <c r="D25" s="38" t="s">
         <v>409</v>
@@ -5630,22 +5630,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="462" t="s">
+      <c r="B29" s="460" t="s">
         <v>356</v>
       </c>
-      <c r="C29" s="462"/>
-      <c r="D29" s="462"/>
-      <c r="E29" s="462"/>
-      <c r="F29" s="462"/>
+      <c r="C29" s="460"/>
+      <c r="D29" s="460"/>
+      <c r="E29" s="460"/>
+      <c r="F29" s="460"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="466" t="s">
+      <c r="B30" s="462" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="466"/>
-      <c r="D30" s="466"/>
-      <c r="E30" s="466"/>
-      <c r="F30" s="466"/>
+      <c r="C30" s="462"/>
+      <c r="D30" s="462"/>
+      <c r="E30" s="462"/>
+      <c r="F30" s="462"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5657,13 +5657,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="463" t="s">
+      <c r="B33" s="461" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="463"/>
-      <c r="D33" s="463"/>
-      <c r="E33" s="463"/>
-      <c r="F33" s="463"/>
+      <c r="C33" s="461"/>
+      <c r="D33" s="461"/>
+      <c r="E33" s="461"/>
+      <c r="F33" s="461"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5683,13 +5683,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="463" t="s">
+      <c r="B36" s="461" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="463"/>
-      <c r="D36" s="463"/>
-      <c r="E36" s="463"/>
-      <c r="F36" s="463"/>
+      <c r="C36" s="461"/>
+      <c r="D36" s="461"/>
+      <c r="E36" s="461"/>
+      <c r="F36" s="461"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5718,13 +5718,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="463" t="s">
+      <c r="B40" s="461" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="463"/>
-      <c r="D40" s="463"/>
-      <c r="E40" s="463"/>
-      <c r="F40" s="463"/>
+      <c r="C40" s="461"/>
+      <c r="D40" s="461"/>
+      <c r="E40" s="461"/>
+      <c r="F40" s="461"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5740,13 +5740,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="463" t="s">
+      <c r="B43" s="461" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="463"/>
-      <c r="D43" s="463"/>
-      <c r="E43" s="463"/>
-      <c r="F43" s="463"/>
+      <c r="C43" s="461"/>
+      <c r="D43" s="461"/>
+      <c r="E43" s="461"/>
+      <c r="F43" s="461"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5810,13 +5810,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="463" t="s">
+      <c r="B51" s="461" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="463"/>
-      <c r="D51" s="463"/>
-      <c r="E51" s="463"/>
-      <c r="F51" s="463"/>
+      <c r="C51" s="461"/>
+      <c r="D51" s="461"/>
+      <c r="E51" s="461"/>
+      <c r="F51" s="461"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5832,7 +5832,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="463" t="s">
+      <c r="B54" s="461" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="464"/>
@@ -5854,22 +5854,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="462" t="s">
+      <c r="B57" s="460" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="462"/>
-      <c r="D57" s="462"/>
-      <c r="E57" s="462"/>
-      <c r="F57" s="462"/>
+      <c r="C57" s="460"/>
+      <c r="D57" s="460"/>
+      <c r="E57" s="460"/>
+      <c r="F57" s="460"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="462" t="s">
+      <c r="B58" s="460" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="462"/>
-      <c r="D58" s="462"/>
-      <c r="E58" s="462"/>
-      <c r="F58" s="462"/>
+      <c r="C58" s="460"/>
+      <c r="D58" s="460"/>
+      <c r="E58" s="460"/>
+      <c r="F58" s="460"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5903,7 +5903,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>6.9312489962270629E-2</v>
+        <v>7.0120130272266309E-2</v>
       </c>
       <c r="F62" s="257"/>
     </row>
@@ -5913,7 +5913,7 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>3.3768915094339623E-2</v>
+        <v>3.4188204393505249E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>322</v>
@@ -6004,13 +6004,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="462" t="s">
+      <c r="B73" s="460" t="s">
         <v>478</v>
       </c>
-      <c r="C73" s="462"/>
-      <c r="D73" s="462"/>
-      <c r="E73" s="462"/>
-      <c r="F73" s="462"/>
+      <c r="C73" s="460"/>
+      <c r="D73" s="460"/>
+      <c r="E73" s="460"/>
+      <c r="F73" s="460"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6029,13 +6029,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="462" t="s">
+      <c r="B77" s="460" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="462"/>
-      <c r="D77" s="462"/>
-      <c r="E77" s="462"/>
-      <c r="F77" s="462"/>
+      <c r="C77" s="460"/>
+      <c r="D77" s="460"/>
+      <c r="E77" s="460"/>
+      <c r="F77" s="460"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6058,7 +6058,7 @@
       </c>
       <c r="C79" s="201">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-10.361928075499378</v>
+        <v>-10.354105922795677</v>
       </c>
       <c r="D79" s="1" t="str">
         <f>Market_currency</f>
@@ -6129,7 +6129,7 @@
       </c>
       <c r="C86" s="201">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-0.18857913052312023</v>
+        <v>-0.18843677335320597</v>
       </c>
       <c r="D86" s="1" t="str">
         <f>Market_currency</f>
@@ -6166,7 +6166,7 @@
       </c>
       <c r="C90" s="201">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>0.13285882389811524</v>
+        <v>0.13275852962845874</v>
       </c>
       <c r="D90" s="1" t="str">
         <f>Market_currency</f>
@@ -6183,7 +6183,7 @@
       </c>
       <c r="C92" s="216">
         <f>DCF!F8</f>
-        <v>-10.417648382124385</v>
+        <v>-10.409784166520426</v>
       </c>
       <c r="D92" s="44" t="str">
         <f>Market_currency</f>
@@ -6204,31 +6204,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="462" t="s">
+      <c r="B96" s="460" t="s">
         <v>485</v>
       </c>
-      <c r="C96" s="462"/>
-      <c r="D96" s="462"/>
-      <c r="E96" s="462"/>
-      <c r="F96" s="462"/>
+      <c r="C96" s="460"/>
+      <c r="D96" s="460"/>
+      <c r="E96" s="460"/>
+      <c r="F96" s="460"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="466" t="s">
+      <c r="B97" s="462" t="s">
         <v>484</v>
       </c>
-      <c r="C97" s="466"/>
-      <c r="D97" s="466"/>
-      <c r="E97" s="466"/>
-      <c r="F97" s="466"/>
+      <c r="C97" s="462"/>
+      <c r="D97" s="462"/>
+      <c r="E97" s="462"/>
+      <c r="F97" s="462"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="466" t="s">
+      <c r="B98" s="462" t="s">
         <v>483</v>
       </c>
-      <c r="C98" s="466"/>
-      <c r="D98" s="466"/>
-      <c r="E98" s="466"/>
-      <c r="F98" s="466"/>
+      <c r="C98" s="462"/>
+      <c r="D98" s="462"/>
+      <c r="E98" s="462"/>
+      <c r="F98" s="462"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6278,22 +6278,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="462" t="s">
+      <c r="B107" s="460" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="462"/>
-      <c r="D107" s="462"/>
-      <c r="E107" s="462"/>
-      <c r="F107" s="462"/>
+      <c r="C107" s="460"/>
+      <c r="D107" s="460"/>
+      <c r="E107" s="460"/>
+      <c r="F107" s="460"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="462" t="s">
+      <c r="B108" s="460" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="462"/>
-      <c r="D108" s="462"/>
-      <c r="E108" s="462"/>
-      <c r="F108" s="462"/>
+      <c r="C108" s="460"/>
+      <c r="D108" s="460"/>
+      <c r="E108" s="460"/>
+      <c r="F108" s="460"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6306,7 +6306,7 @@
       </c>
       <c r="C111" s="216">
         <f>BS!D47</f>
-        <v>-6.3382048349071285</v>
+        <v>-6.333420164937916</v>
       </c>
       <c r="D111" s="1" t="str">
         <f>Market_currency</f>
@@ -6319,7 +6319,7 @@
       </c>
       <c r="C112" s="216">
         <f>DCF!C11</f>
-        <v>46.680000491938102</v>
+        <v>46.644762060499836</v>
       </c>
       <c r="D112" s="1" t="str">
         <f>Market_currency</f>
@@ -6327,13 +6327,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="462" t="s">
+      <c r="B114" s="460" t="s">
         <v>491</v>
       </c>
-      <c r="C114" s="462"/>
-      <c r="D114" s="462"/>
-      <c r="E114" s="462"/>
-      <c r="F114" s="462"/>
+      <c r="C114" s="460"/>
+      <c r="D114" s="460"/>
+      <c r="E114" s="460"/>
+      <c r="F114" s="460"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6368,7 +6368,7 @@
       </c>
       <c r="D118" s="207" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>100.4 HKD</v>
+        <v>100.33 HKD</v>
       </c>
       <c r="E118" s="208">
         <f>DCF!F90</f>
@@ -6376,7 +6376,7 @@
       </c>
       <c r="F118" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E90,C$18)</f>
-        <v>-0.13643584359636657</v>
+        <v>-0.13642305620587292</v>
       </c>
     </row>
     <row r="119" spans="2:6">
@@ -6390,7 +6390,7 @@
       </c>
       <c r="D119" s="207" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>74.38 HKD</v>
+        <v>74.32 HKD</v>
       </c>
       <c r="E119" s="199">
         <f>DCF!F91</f>
@@ -6398,7 +6398,7 @@
       </c>
       <c r="F119" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E91,C$18)</f>
-        <v>-4.3756184430920858E-2</v>
+        <v>-4.3740647780984215E-2</v>
       </c>
     </row>
     <row r="120" spans="2:6">
@@ -6412,7 +6412,7 @@
       </c>
       <c r="D120" s="207" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>55.15 HKD</v>
+        <v>55.11 HKD</v>
       </c>
       <c r="E120" s="199">
         <f>DCF!F92</f>
@@ -6420,7 +6420,7 @@
       </c>
       <c r="F120" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E92,C$18)</f>
-        <v>5.8891628495255741E-2</v>
+        <v>5.891062916083515E-2</v>
       </c>
     </row>
     <row r="121" spans="2:6">
@@ -6434,7 +6434,7 @@
       </c>
       <c r="D121" s="207" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>40.91 HKD</v>
+        <v>40.88 HKD</v>
       </c>
       <c r="E121" s="199">
         <f>DCF!F93</f>
@@ -6442,7 +6442,7 @@
       </c>
       <c r="F121" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E93,C$18)</f>
-        <v>0.17288474334576429</v>
+        <v>0.17290814328575421</v>
       </c>
     </row>
     <row r="122" spans="2:6">
@@ -6456,7 +6456,7 @@
       </c>
       <c r="D122" s="207" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>30.32 HKD</v>
+        <v>30.3 HKD</v>
       </c>
       <c r="E122" s="199">
         <f>DCF!F94</f>
@@ -6464,17 +6464,17 @@
       </c>
       <c r="F122" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E94,C$18)</f>
-        <v>0.3001804223453835</v>
+        <v>0.30020947064812875</v>
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="463" t="s">
+      <c r="B124" s="461" t="s">
         <v>357</v>
       </c>
-      <c r="C124" s="463"/>
-      <c r="D124" s="463"/>
-      <c r="E124" s="463"/>
-      <c r="F124" s="463"/>
+      <c r="C124" s="461"/>
+      <c r="D124" s="461"/>
+      <c r="E124" s="461"/>
+      <c r="F124" s="461"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6482,7 +6482,7 @@
       </c>
       <c r="C125" s="197">
         <f>Scenarios!C36</f>
-        <v>60.922911775163712</v>
+        <v>60.876921461817851</v>
       </c>
       <c r="D125" s="194" t="str">
         <f>Market_currency</f>
@@ -6509,22 +6509,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="467" t="s">
+      <c r="B131" s="463" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="467"/>
-      <c r="D131" s="467"/>
-      <c r="E131" s="467"/>
-      <c r="F131" s="467"/>
+      <c r="C131" s="463"/>
+      <c r="D131" s="463"/>
+      <c r="E131" s="463"/>
+      <c r="F131" s="463"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="462" t="s">
+      <c r="B132" s="460" t="s">
         <v>359</v>
       </c>
-      <c r="C132" s="462"/>
-      <c r="D132" s="462"/>
-      <c r="E132" s="462"/>
-      <c r="F132" s="462"/>
+      <c r="C132" s="460"/>
+      <c r="D132" s="460"/>
+      <c r="E132" s="460"/>
+      <c r="F132" s="460"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6589,11 +6589,11 @@
       </c>
       <c r="D140" s="333">
         <f>Scenarios!D62</f>
-        <v>28.075074550766693</v>
+        <v>28.053880857980584</v>
       </c>
       <c r="E140" s="334">
         <f>Scenarios!E62</f>
-        <v>30.695059697144316</v>
+        <v>30.673866004358207</v>
       </c>
       <c r="F140" s="335">
         <f>E22</f>
@@ -6610,11 +6610,11 @@
       </c>
       <c r="D141" s="333">
         <f>Scenarios!D63</f>
-        <v>35.190129545220934</v>
+        <v>35.163564743288305</v>
       </c>
       <c r="E141" s="334">
         <f>Scenarios!E63</f>
-        <v>38.202646604928695</v>
+        <v>38.176081802996066</v>
       </c>
       <c r="F141" s="335">
         <f>Scenarios!F63</f>
@@ -6657,11 +6657,11 @@
       </c>
       <c r="D144" s="333">
         <f>Scenarios!D66</f>
-        <v>43.667130187572489</v>
+        <v>43.634166152503838</v>
       </c>
       <c r="E144" s="334">
         <f>Scenarios!E66</f>
-        <v>47.121500168497697</v>
+        <v>47.088536133429045</v>
       </c>
       <c r="F144" s="335">
         <f>E24</f>
@@ -6678,11 +6678,11 @@
       </c>
       <c r="D145" s="333">
         <f>Scenarios!D67</f>
-        <v>49.384282627234057</v>
+        <v>49.347002750645608</v>
       </c>
       <c r="E145" s="334">
         <f>Scenarios!E67</f>
-        <v>53.124686702250834</v>
+        <v>53.087406825662384</v>
       </c>
       <c r="F145" s="335">
         <f>Scenarios!F67</f>
@@ -6700,13 +6700,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="461" t="s">
+      <c r="B149" s="467" t="s">
         <v>360</v>
       </c>
-      <c r="C149" s="462"/>
-      <c r="D149" s="462"/>
-      <c r="E149" s="462"/>
-      <c r="F149" s="462"/>
+      <c r="C149" s="460"/>
+      <c r="D149" s="460"/>
+      <c r="E149" s="460"/>
+      <c r="F149" s="460"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6743,13 +6743,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="463" t="s">
+      <c r="B158" s="461" t="s">
         <v>438</v>
       </c>
-      <c r="C158" s="463"/>
-      <c r="D158" s="463"/>
-      <c r="E158" s="463"/>
-      <c r="F158" s="463"/>
+      <c r="C158" s="461"/>
+      <c r="D158" s="461"/>
+      <c r="E158" s="461"/>
+      <c r="F158" s="461"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6757,22 +6757,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="460" t="s">
+      <c r="B161" s="466" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="460"/>
-      <c r="D161" s="460"/>
-      <c r="E161" s="460"/>
-      <c r="F161" s="460"/>
+      <c r="C161" s="466"/>
+      <c r="D161" s="466"/>
+      <c r="E161" s="466"/>
+      <c r="F161" s="466"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="460" t="s">
+      <c r="B162" s="466" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="460"/>
-      <c r="D162" s="460"/>
-      <c r="E162" s="460"/>
-      <c r="F162" s="460"/>
+      <c r="C162" s="466"/>
+      <c r="D162" s="466"/>
+      <c r="E162" s="466"/>
+      <c r="F162" s="466"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6796,6 +6796,18 @@
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6812,18 +6824,6 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -9950,11 +9950,11 @@
       </c>
       <c r="C47" s="134">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>15.329114633835864</v>
+        <v>15.317542784021358</v>
       </c>
       <c r="D47" s="134">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>-6.3382048349071285</v>
+        <v>-6.333420164937916</v>
       </c>
       <c r="F47" s="223"/>
     </row>
@@ -10360,11 +10360,11 @@
       </c>
       <c r="C86" s="73">
         <f>DCF!F4*Exchange_Rate</f>
-        <v>-26514350.24586162</v>
+        <v>-26494334.733791724</v>
       </c>
       <c r="D86" s="201">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>-10.361928075499376</v>
+        <v>-10.354105922795677</v>
       </c>
       <c r="E86" s="214" t="str">
         <f>Market_currency</f>
@@ -10377,11 +10377,11 @@
       </c>
       <c r="C87" s="73">
         <f>DCF!F5*Exchange_Rate</f>
-        <v>-482540.80508169258</v>
+        <v>-482176.5381387439</v>
       </c>
       <c r="D87" s="201">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>-0.18857913052312023</v>
+        <v>-0.18843677335320597</v>
       </c>
       <c r="E87" s="214" t="str">
         <f>Market_currency</f>
@@ -10394,11 +10394,11 @@
       </c>
       <c r="C88" s="73">
         <f>DCF!F6*Exchange_Rate</f>
-        <v>339962.34720227082</v>
+        <v>339705.71181801136</v>
       </c>
       <c r="D88" s="201">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>0.13285882389811524</v>
+        <v>0.13275852962845874</v>
       </c>
       <c r="E88" s="214" t="str">
         <f>Market_currency</f>
@@ -10411,11 +10411,11 @@
       </c>
       <c r="C89" s="162">
         <f>SUM(C86:C88)</f>
-        <v>-26656928.70374104</v>
+        <v>-26636805.560112458</v>
       </c>
       <c r="D89" s="216">
         <f>SUM(D86:D88)</f>
-        <v>-10.417648382124382</v>
+        <v>-10.409784166520424</v>
       </c>
       <c r="E89" s="214" t="str">
         <f>Market_currency</f>
@@ -13998,16 +13998,16 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>3.3768915094339623E-2</v>
+        <v>3.4188204393505249E-2</v>
       </c>
       <c r="E92" s="237"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>3.3768915094339623E-2</v>
+        <v>3.4188204393505249E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>2.6742464622641512E-2</v>
+        <v>2.7074510506208214E-2</v>
       </c>
       <c r="I92" s="22" t="str">
         <f t="shared" si="38"/>
@@ -15162,18 +15162,18 @@
       </c>
       <c r="C123" s="159">
         <f>C14*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>2.9388495744002752</v>
+        <v>2.936631055802513</v>
       </c>
       <c r="D123" s="26"/>
       <c r="E123" s="234"/>
       <c r="F123" s="26"/>
       <c r="G123" s="159">
         <f t="shared" ref="G123:Q123" si="48">IF(G$4="","",G14*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>3.0438042400579008</v>
+        <v>3.0415064918596477</v>
       </c>
       <c r="H123" s="159">
         <f t="shared" si="48"/>
-        <v>2.4346820136071021</v>
+        <v>2.4328440878507536</v>
       </c>
       <c r="I123" s="159" t="str">
         <f t="shared" si="48"/>
@@ -15219,18 +15219,18 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>6.9312489962270629E-2</v>
+        <v>7.0120130272266309E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="234"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>7.1787835850422185E-2</v>
+        <v>7.2624319289867414E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>5.7421745603941088E-2</v>
+        <v>5.8090833043236707E-2</v>
       </c>
       <c r="I124" s="74" t="str">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
@@ -15276,11 +15276,11 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.7736919123637515E-3</v>
+        <v>7.8702133974265301E-3</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.2067132371952235E-3</v>
+        <v>6.2837784445338458E-3</v>
       </c>
       <c r="I125" s="22" t="str">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -16201,7 +16201,7 @@
       </c>
       <c r="F8" s="108">
         <f>FV_adjustments*scaling_factor/Common_Shares*Exchange_Rate</f>
-        <v>-10.417648382124385</v>
+        <v>-10.409784166520426</v>
       </c>
       <c r="G8" s="294" t="str">
         <f>Market_currency</f>
@@ -16226,7 +16226,7 @@
       </c>
       <c r="C9" s="190">
         <f>Exchange_Rate</f>
-        <v>9.2841749332904815</v>
+        <v>9.2771663694858564</v>
       </c>
       <c r="D9" t="str">
         <f>Thesis!E15</f>
@@ -16251,7 +16251,7 @@
       </c>
       <c r="C10" s="283">
         <f>C8*Exchange_Rate</f>
-        <v>119445905.57878302</v>
+        <v>119355736.63469642</v>
       </c>
       <c r="D10" t="str">
         <f>Market_currency</f>
@@ -16273,7 +16273,7 @@
       </c>
       <c r="C11" s="108">
         <f>(C10*scaling_factor)/Common_Shares</f>
-        <v>46.680000491938102</v>
+        <v>46.644762060499836</v>
       </c>
       <c r="D11" t="str">
         <f>Market_currency</f>
@@ -16396,7 +16396,7 @@
       </c>
       <c r="I18" s="129">
         <f>(L52+FV_adjustments)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>60.181801292913789</v>
+        <v>60.136370439093248</v>
       </c>
       <c r="J18" t="str">
         <f>Market_currency</f>
@@ -18584,23 +18584,23 @@
       </c>
       <c r="B73" s="119">
         <f>C11</f>
-        <v>46.680000491938102</v>
+        <v>46.644762060499836</v>
       </c>
       <c r="C73" s="119">
         <f>C11</f>
-        <v>46.680000491938102</v>
+        <v>46.644762060499836</v>
       </c>
       <c r="D73" s="119">
         <f>C11</f>
-        <v>46.680000491938102</v>
+        <v>46.644762060499836</v>
       </c>
       <c r="E73" s="119">
         <f>C11</f>
-        <v>46.680000491938102</v>
+        <v>46.644762060499836</v>
       </c>
       <c r="F73" s="119">
         <f>C11</f>
-        <v>46.680000491938102</v>
+        <v>46.644762060499836</v>
       </c>
       <c r="G73" s="296"/>
       <c r="H73" s="296"/>
@@ -18615,23 +18615,23 @@
       </c>
       <c r="B74" s="119">
         <f t="shared" ref="B74:F87" si="11">(B56+FV_adjustments)/Common_Shares*scaling_factor*Exchange_Rate</f>
-        <v>30.874121218805445</v>
+        <v>30.850814543734316</v>
       </c>
       <c r="C74" s="119">
         <f t="shared" si="11"/>
-        <v>31.699956610824032</v>
+        <v>31.676026517939402</v>
       </c>
       <c r="D74" s="119">
         <f t="shared" si="11"/>
-        <v>32.525792002842635</v>
+        <v>32.501238492144502</v>
       </c>
       <c r="E74" s="119">
         <f t="shared" si="11"/>
-        <v>33.351627394861225</v>
+        <v>33.326450466349584</v>
       </c>
       <c r="F74" s="119">
         <f t="shared" si="11"/>
-        <v>34.177462786879822</v>
+        <v>34.151662440554688</v>
       </c>
       <c r="G74" s="296"/>
       <c r="H74" s="296"/>
@@ -18646,23 +18646,23 @@
       </c>
       <c r="B75" s="119">
         <f t="shared" si="11"/>
-        <v>30.823022177623962</v>
+        <v>30.799754076889599</v>
       </c>
       <c r="C75" s="119">
         <f t="shared" si="11"/>
-        <v>32.433245472137308</v>
+        <v>32.408761824218587</v>
       </c>
       <c r="D75" s="119">
         <f t="shared" si="11"/>
-        <v>34.074269154231793</v>
+        <v>34.048546708114685</v>
       </c>
       <c r="E75" s="119">
         <f t="shared" si="11"/>
-        <v>35.746093223907366</v>
+        <v>35.719108728577844</v>
       </c>
       <c r="F75" s="119">
         <f t="shared" si="11"/>
-        <v>37.448717681164077</v>
+        <v>37.42044788560812</v>
       </c>
       <c r="G75" s="296"/>
       <c r="H75" s="296"/>
@@ -18677,23 +18677,23 @@
       </c>
       <c r="B76" s="119">
         <f t="shared" si="11"/>
-        <v>30.775377383981564</v>
+        <v>30.752145249994769</v>
       </c>
       <c r="C76" s="119">
         <f t="shared" si="11"/>
-        <v>33.130639074505183</v>
+        <v>33.105628968651935</v>
       </c>
       <c r="D76" s="119">
         <f t="shared" si="11"/>
-        <v>35.575822755578841</v>
+        <v>35.548966796328173</v>
       </c>
       <c r="E76" s="119">
         <f t="shared" si="11"/>
-        <v>38.112651525808438</v>
+        <v>38.083880530873365</v>
       </c>
       <c r="F76" s="119">
         <f t="shared" si="11"/>
-        <v>40.742848483799925</v>
+        <v>40.712091970137415</v>
       </c>
       <c r="G76" s="296"/>
       <c r="H76" s="296"/>
@@ -18708,23 +18708,23 @@
       </c>
       <c r="B77" s="119">
         <f t="shared" si="11"/>
-        <v>30.730953333965331</v>
+        <v>30.707754735407502</v>
       </c>
       <c r="C77" s="119">
         <f t="shared" si="11"/>
-        <v>33.793894528505398</v>
+        <v>33.768383735385747</v>
       </c>
       <c r="D77" s="119">
         <f t="shared" si="11"/>
-        <v>37.031874732642649</v>
+        <v>37.003919609141256</v>
       </c>
       <c r="E77" s="119">
         <f t="shared" si="11"/>
-        <v>40.451627563118578</v>
+        <v>40.421090890251669</v>
       </c>
       <c r="F77" s="119">
         <f t="shared" si="11"/>
-        <v>44.060015166174502</v>
+        <v>44.02675454476833</v>
       </c>
       <c r="G77" s="296"/>
       <c r="H77" s="296"/>
@@ -18739,23 +18739,23 @@
       </c>
       <c r="B78" s="119">
         <f t="shared" si="11"/>
-        <v>30.689532308309172</v>
+        <v>30.666364978216581</v>
       </c>
       <c r="C78" s="119">
         <f t="shared" si="11"/>
-        <v>34.424682932309793</v>
+        <v>34.398695961090631</v>
       </c>
       <c r="D78" s="119">
         <f t="shared" si="11"/>
-        <v>38.443803922522683</v>
+        <v>38.414782942778174</v>
       </c>
       <c r="E78" s="119">
         <f t="shared" si="11"/>
-        <v>42.763342807453078</v>
+        <v>42.731061035651216</v>
       </c>
       <c r="F78" s="119">
         <f t="shared" si="11"/>
-        <v>47.400378818355897</v>
+        <v>47.364596577963091</v>
       </c>
       <c r="G78" s="296"/>
       <c r="H78" s="296"/>
@@ -18770,23 +18770,23 @@
       </c>
       <c r="B79" s="119">
         <f t="shared" si="11"/>
-        <v>30.650911305366375</v>
+        <v>30.627773130019925</v>
       </c>
       <c r="C79" s="119">
         <f t="shared" si="11"/>
-        <v>35.024593582081806</v>
+        <v>34.998153742180591</v>
       </c>
       <c r="D79" s="119">
         <f t="shared" si="11"/>
-        <v>39.812947379376091</v>
+        <v>39.782892842062495</v>
       </c>
       <c r="E79" s="119">
         <f t="shared" si="11"/>
-        <v>45.048114983671802</v>
+        <v>45.014108452083406</v>
       </c>
       <c r="F79" s="119">
         <f t="shared" si="11"/>
-        <v>50.764101656916182</v>
+        <v>50.725780163837541</v>
       </c>
       <c r="G79" s="296"/>
       <c r="H79" s="296"/>
@@ -18802,23 +18802,23 @@
       </c>
       <c r="B80" s="119">
         <f t="shared" si="11"/>
-        <v>30.614901046212246</v>
+        <v>30.591790054778286</v>
       </c>
       <c r="C80" s="119">
         <f t="shared" si="11"/>
-        <v>35.595137976270578</v>
+        <v>35.568267436084334</v>
       </c>
       <c r="D80" s="119">
         <f t="shared" si="11"/>
-        <v>41.140601640567262</v>
+        <v>41.109544865610914</v>
       </c>
       <c r="E80" s="119">
         <f t="shared" si="11"/>
-        <v>47.306258113547635</v>
+        <v>47.270546924268125</v>
       </c>
       <c r="F80" s="119">
         <f t="shared" si="11"/>
-        <v>54.15134703280907</v>
+        <v>54.110468530032804</v>
       </c>
       <c r="G80" s="296"/>
       <c r="H80" s="296"/>
@@ -18833,23 +18833,23 @@
       </c>
       <c r="B81" s="119">
         <f t="shared" si="11"/>
-        <v>30.581325047000924</v>
+        <v>30.55823940187231</v>
       </c>
       <c r="C81" s="119">
         <f t="shared" si="11"/>
-        <v>36.137753623890667</v>
+        <v>36.110473466650127</v>
       </c>
       <c r="D81" s="119">
         <f t="shared" si="11"/>
-        <v>42.428023954449607</v>
+        <v>42.395995312688164</v>
       </c>
       <c r="E81" s="119">
         <f t="shared" si="11"/>
-        <v>49.538082558926099</v>
+        <v>49.500686579760725</v>
       </c>
       <c r="F81" s="119">
         <f t="shared" si="11"/>
-        <v>57.562279439302579</v>
+        <v>57.518826045641994</v>
       </c>
       <c r="G81" s="296"/>
       <c r="H81" s="296"/>
@@ -18865,23 +18865,23 @@
       </c>
       <c r="B82" s="119">
         <f t="shared" si="11"/>
-        <v>30.550018754030006</v>
+        <v>30.526956741820136</v>
       </c>
       <c r="C82" s="119">
         <f t="shared" si="11"/>
-        <v>36.653807666382505</v>
+        <v>36.626137943272141</v>
       </c>
       <c r="D82" s="119">
         <f t="shared" si="11"/>
-        <v>43.676433470941568</v>
+        <v>43.643462412884276</v>
       </c>
       <c r="E82" s="119">
         <f t="shared" si="11"/>
-        <v>51.743895064381739</v>
+        <v>51.70483393157626</v>
       </c>
       <c r="F82" s="119">
         <f t="shared" si="11"/>
-        <v>60.997064519967367</v>
+        <v>60.951018229192506</v>
       </c>
       <c r="G82" s="296"/>
       <c r="H82" s="296"/>
@@ -18897,23 +18897,23 @@
       </c>
       <c r="B83" s="119">
         <f t="shared" si="11"/>
-        <v>30.520828737273906</v>
+        <v>30.497788760419507</v>
       </c>
       <c r="C83" s="119">
         <f t="shared" si="11"/>
-        <v>37.144600322178938</v>
+        <v>37.116560102856717</v>
       </c>
       <c r="D83" s="119">
         <f t="shared" si="11"/>
-        <v>44.887012396024666</v>
+        <v>44.853127479741097</v>
       </c>
       <c r="E83" s="119">
         <f t="shared" si="11"/>
-        <v>53.9239987993775</v>
+        <v>53.883291920316999</v>
       </c>
       <c r="F83" s="119">
         <f t="shared" si="11"/>
-        <v>64.455869076720759</v>
+        <v>64.407211756683949</v>
       </c>
       <c r="G83" s="296"/>
       <c r="H83" s="296"/>
@@ -18929,23 +18929,23 @@
       </c>
       <c r="B84" s="119">
         <f t="shared" si="11"/>
-        <v>30.401940805666122</v>
+        <v>30.378990576544854</v>
       </c>
       <c r="C84" s="119">
         <f t="shared" si="11"/>
-        <v>39.260865414038022</v>
+        <v>39.231227639840938</v>
       </c>
       <c r="D84" s="119">
         <f t="shared" si="11"/>
-        <v>50.41137752980385</v>
+        <v>50.373322305894852</v>
       </c>
       <c r="E84" s="119">
         <f t="shared" si="11"/>
-        <v>64.449251800424292</v>
+        <v>64.400599475726722</v>
       </c>
       <c r="F84" s="119">
         <f t="shared" si="11"/>
-        <v>82.116104178599898</v>
+        <v>82.054115260935347</v>
       </c>
       <c r="G84" s="296"/>
       <c r="H84" s="296"/>
@@ -18961,23 +18961,23 @@
       </c>
       <c r="B85" s="119">
         <f t="shared" si="11"/>
-        <v>30.318158700786892</v>
+        <v>30.295271718236478</v>
       </c>
       <c r="C85" s="119">
         <f t="shared" si="11"/>
-        <v>40.907451430106995</v>
+        <v>40.876570658741464</v>
       </c>
       <c r="D85" s="119">
         <f t="shared" si="11"/>
-        <v>55.147932346681884</v>
+        <v>55.106301528076884</v>
       </c>
       <c r="E85" s="119">
         <f t="shared" si="11"/>
-        <v>74.375276831229229</v>
+        <v>74.319131414226234</v>
       </c>
       <c r="F85" s="119">
         <f t="shared" si="11"/>
-        <v>100.40252685710847</v>
+        <v>100.32673363685144</v>
       </c>
       <c r="G85" s="296"/>
       <c r="H85" s="296"/>
@@ -18993,23 +18993,23 @@
       </c>
       <c r="B86" s="119">
         <f t="shared" si="11"/>
-        <v>30.259116197455675</v>
+        <v>30.236273785710395</v>
       </c>
       <c r="C86" s="119">
         <f t="shared" si="11"/>
-        <v>42.188597879454761</v>
+        <v>42.156749978893821</v>
       </c>
       <c r="D86" s="119">
         <f t="shared" si="11"/>
-        <v>59.209023710123816</v>
+        <v>59.164327199829295</v>
       </c>
       <c r="E86" s="119">
         <f t="shared" si="11"/>
-        <v>83.736189381489723</v>
+        <v>83.672977471949764</v>
       </c>
       <c r="F86" s="119">
         <f t="shared" si="11"/>
-        <v>119.33734015081657</v>
+        <v>119.24725316207164</v>
       </c>
       <c r="G86" s="296"/>
       <c r="H86" s="296"/>
@@ -19025,23 +19025,23 @@
       </c>
       <c r="B87" s="119">
         <f t="shared" si="11"/>
-        <v>30.217508061629513</v>
+        <v>30.194697059597733</v>
       </c>
       <c r="C87" s="119">
         <f t="shared" si="11"/>
-        <v>43.185409590873824</v>
+        <v>43.152809203578101</v>
       </c>
       <c r="D87" s="119">
         <f t="shared" si="11"/>
-        <v>62.69097709182104</v>
+        <v>62.643652077365864</v>
       </c>
       <c r="E87" s="119">
         <f t="shared" si="11"/>
-        <v>92.564162664015129</v>
+        <v>92.494286574355698</v>
       </c>
       <c r="F87" s="119">
         <f t="shared" si="11"/>
-        <v>138.94353436227107</v>
+        <v>138.83864678391163</v>
       </c>
       <c r="G87" s="296"/>
       <c r="H87" s="296"/>
@@ -19088,7 +19088,7 @@
       </c>
       <c r="E90" s="127">
         <f>INDEX(B$73:F$87, MATCH(D90, A$73:A$87, 0), MATCH(C90, B$72:F$72, 0))</f>
-        <v>100.40252685710847</v>
+        <v>100.32673363685144</v>
       </c>
       <c r="F90" s="130">
         <f>Scenarios!F29</f>
@@ -19116,7 +19116,7 @@
       </c>
       <c r="E91" s="127">
         <f>INDEX(B$73:F$87, MATCH(D91, A$73:A$87, 0), MATCH(C91, B$72:F$72, 0))</f>
-        <v>74.375276831229229</v>
+        <v>74.319131414226234</v>
       </c>
       <c r="F91" s="130">
         <f>Scenarios!F22*(1-F$90-F$94)</f>
@@ -19144,7 +19144,7 @@
       </c>
       <c r="E92" s="127">
         <f>INDEX(B$73:F$87, MATCH(D92, A$73:A$87, 0), MATCH(C92, B$72:F$72, 0))</f>
-        <v>55.147932346681884</v>
+        <v>55.106301528076884</v>
       </c>
       <c r="F92" s="130">
         <f>Scenarios!F23*(1-F$90-F$94)</f>
@@ -19172,7 +19172,7 @@
       </c>
       <c r="E93" s="127">
         <f>INDEX(B$73:F$87, MATCH(D93, A$73:A$87, 0), MATCH(C93, B$72:F$72, 0))</f>
-        <v>40.907451430106995</v>
+        <v>40.876570658741464</v>
       </c>
       <c r="F93" s="130">
         <f>Scenarios!F24*(1-F$90-F$94)</f>
@@ -19200,7 +19200,7 @@
       </c>
       <c r="E94" s="127">
         <f>INDEX(B$73:F$87, MATCH(D94, A$73:A$87, 0), MATCH(C94, B$72:F$72, 0))</f>
-        <v>30.318158700786892</v>
+        <v>30.295271718236478</v>
       </c>
       <c r="F94" s="130">
         <f>Scenarios!F30</f>
@@ -19560,7 +19560,7 @@
       </c>
       <c r="E22" s="326">
         <f>DCF!E91</f>
-        <v>74.375276831229229</v>
+        <v>74.319131414226234</v>
       </c>
       <c r="F22" s="328">
         <f>1-F23-F24</f>
@@ -19584,7 +19584,7 @@
       </c>
       <c r="E23" s="326">
         <f>DCF!E92</f>
-        <v>55.147932346681884</v>
+        <v>55.106301528076884</v>
       </c>
       <c r="F23" s="327">
         <v>0.55000000000000004</v>
@@ -19607,7 +19607,7 @@
       </c>
       <c r="E24" s="326">
         <f>DCF!E93</f>
-        <v>40.907451430106995</v>
+        <v>40.876570658741464</v>
       </c>
       <c r="F24" s="327">
         <v>0.25</v>
@@ -19623,7 +19623,7 @@
       </c>
       <c r="C25" s="441">
         <f>E23*F23+E24*F24+E22*F22</f>
-        <v>55.43328101444763</v>
+        <v>55.391434787972898</v>
       </c>
       <c r="D25" s="141" t="str">
         <f>Market_currency</f>
@@ -19670,7 +19670,7 @@
       </c>
       <c r="E29" s="326">
         <f>DCF!E90</f>
-        <v>100.40252685710847</v>
+        <v>100.32673363685144</v>
       </c>
       <c r="F29" s="327">
         <v>0.15</v>
@@ -19693,7 +19693,7 @@
       </c>
       <c r="E30" s="326">
         <f>DCF!E94</f>
-        <v>30.318158700786892</v>
+        <v>30.295271718236478</v>
       </c>
       <c r="F30" s="327">
         <v>0.05</v>
@@ -19738,7 +19738,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>42.4</v>
+        <v>41.88</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19749,7 +19749,7 @@
       </c>
       <c r="F34" s="330">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.15855740519921338</v>
+        <v>0.16319188190025868</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -19758,7 +19758,7 @@
       </c>
       <c r="C35" s="320">
         <f>DCF!C11</f>
-        <v>46.680000491938102</v>
+        <v>46.644762060499836</v>
       </c>
       <c r="D35" s="97" t="str">
         <f>Market_currency</f>
@@ -19769,7 +19769,7 @@
       </c>
       <c r="F35" s="330">
         <f>RATE(Holding_Period,$C$33,-C35,$C$36)</f>
-        <v>0.12100678253457481</v>
+        <v>0.12102810582090839</v>
       </c>
     </row>
     <row r="36" spans="2:7">
@@ -19778,7 +19778,7 @@
       </c>
       <c r="C36" s="321">
         <f>E22*G22+E23*G23+E24*G24+E30*G30+E29*G29</f>
-        <v>60.922911775163712</v>
+        <v>60.876921461817851</v>
       </c>
       <c r="D36" t="str">
         <f>Market_currency</f>
@@ -19881,7 +19881,7 @@
       </c>
       <c r="C47" s="146">
         <f>DCF!I18</f>
-        <v>60.181801292913789</v>
+        <v>60.136370439093248</v>
       </c>
       <c r="D47" s="146" t="str">
         <f>Market_currency</f>
@@ -19948,7 +19948,7 @@
       </c>
       <c r="F53" s="249">
         <f>BS!D89/C36</f>
-        <v>-0.17099721727961331</v>
+        <v>-0.17099721727961334</v>
       </c>
     </row>
     <row r="55" spans="2:7" ht="13.9">
@@ -20026,11 +20026,11 @@
       </c>
       <c r="D62" s="119">
         <f>C36/(1+F62)^Holding_Period</f>
-        <v>28.075074550766693</v>
+        <v>28.053880857980584</v>
       </c>
       <c r="E62" s="332">
         <f>C62+D62</f>
-        <v>30.695059697144316</v>
+        <v>30.673866004358207</v>
       </c>
       <c r="F62" s="301">
         <f>Thesis!E22</f>
@@ -20038,7 +20038,7 @@
       </c>
       <c r="G62" s="440">
         <f>(1-E62/C36)</f>
-        <v>0.49616558364077257</v>
+        <v>0.49613309497595193</v>
       </c>
     </row>
     <row r="63" spans="2:7" ht="13.15">
@@ -20051,11 +20051,11 @@
       </c>
       <c r="D63" s="119">
         <f>C36/(1+F63)^Holding_Period</f>
-        <v>35.190129545220934</v>
+        <v>35.163564743288305</v>
       </c>
       <c r="E63" s="332">
         <f>C63+D63</f>
-        <v>38.202646604928695</v>
+        <v>38.176081802996066</v>
       </c>
       <c r="F63" s="301">
         <f>Thesis!E23</f>
@@ -20063,7 +20063,7 @@
       </c>
       <c r="G63" s="440">
         <f>(1-E63/C36)</f>
-        <v>0.37293465640782664</v>
+        <v>0.37289730022008105</v>
       </c>
     </row>
     <row r="65" spans="2:7" ht="13.15">
@@ -20097,11 +20097,11 @@
       </c>
       <c r="D66" s="119">
         <f>C36/(1+F66)^Holding_Period</f>
-        <v>43.667130187572489</v>
+        <v>43.634166152503838</v>
       </c>
       <c r="E66" s="332">
         <f>C66+D66</f>
-        <v>47.121500168497697</v>
+        <v>47.088536133429045</v>
       </c>
       <c r="F66" s="301">
         <f>Thesis!E24</f>
@@ -20109,7 +20109,7 @@
       </c>
       <c r="G66" s="440">
         <f>(1-E66/C36)</f>
-        <v>0.22653893591954677</v>
+        <v>0.22649610061239567</v>
       </c>
     </row>
     <row r="67" spans="2:7" ht="13.15">
@@ -20122,11 +20122,11 @@
       </c>
       <c r="D67" s="119">
         <f>C36/(1+F67)^Holding_Period</f>
-        <v>49.384282627234057</v>
+        <v>49.347002750645608</v>
       </c>
       <c r="E67" s="332">
         <f>C67+D67</f>
-        <v>53.124686702250834</v>
+        <v>53.087406825662384</v>
       </c>
       <c r="F67" s="301">
         <f>Thesis!E25</f>
@@ -20134,7 +20134,7 @@
       </c>
       <c r="G67" s="440">
         <f>(1-E67/C36)</f>
-        <v>0.12800151610763888</v>
+        <v>0.12795513388503177</v>
       </c>
     </row>
   </sheetData>
@@ -20245,7 +20245,7 @@
       </c>
       <c r="C8" s="356">
         <f>Market_Price</f>
-        <v>42.4</v>
+        <v>41.88</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20263,14 +20263,14 @@
       </c>
       <c r="C10" s="357">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>108494.1376</v>
+        <v>107163.54912</v>
       </c>
       <c r="D10" s="343" t="s">
         <v>529</v>
       </c>
       <c r="E10" s="360">
         <f>Scenarios!F34</f>
-        <v>0.15855740519921338</v>
+        <v>0.16319188190025868</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20278,13 +20278,13 @@
       <c r="E11" s="349"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="474" t="s">
+      <c r="B12" s="471" t="s">
         <v>498</v>
       </c>
-      <c r="C12" s="474"/>
-      <c r="D12" s="474"/>
-      <c r="E12" s="474"/>
-      <c r="F12" s="474"/>
+      <c r="C12" s="471"/>
+      <c r="D12" s="471"/>
+      <c r="E12" s="471"/>
+      <c r="F12" s="471"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="347" t="s">
@@ -20322,7 +20322,7 @@
       </c>
       <c r="E16" s="425">
         <f>Exchange_Rate</f>
-        <v>9.2841749332904815</v>
+        <v>9.2771663694858564</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -20348,7 +20348,7 @@
       </c>
       <c r="C18" s="359">
         <f>C125</f>
-        <v>60.922911775163712</v>
+        <v>60.876921461817851</v>
       </c>
       <c r="D18" s="350" t="s">
         <v>362</v>
@@ -20400,7 +20400,7 @@
       </c>
       <c r="C22" s="364">
         <f>E140</f>
-        <v>30.695059697144316</v>
+        <v>30.673866004358207</v>
       </c>
       <c r="D22" s="365" t="s">
         <v>440</v>
@@ -20416,7 +20416,7 @@
       </c>
       <c r="C23" s="367">
         <f>E141</f>
-        <v>38.202646604928695</v>
+        <v>38.176081802996066</v>
       </c>
       <c r="D23" s="365" t="s">
         <v>441</v>
@@ -20432,7 +20432,7 @@
       </c>
       <c r="C24" s="367">
         <f>E144</f>
-        <v>47.121500168497697</v>
+        <v>47.088536133429045</v>
       </c>
       <c r="D24" s="365" t="s">
         <v>443</v>
@@ -20448,7 +20448,7 @@
       </c>
       <c r="C25" s="367">
         <f>E145</f>
-        <v>53.124686702250834</v>
+        <v>53.087406825662384</v>
       </c>
       <c r="D25" s="365" t="s">
         <v>442</v>
@@ -20469,22 +20469,22 @@
       <c r="F27" s="345"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="474" t="s">
+      <c r="B29" s="471" t="s">
         <v>499</v>
       </c>
-      <c r="C29" s="474"/>
-      <c r="D29" s="474"/>
-      <c r="E29" s="474"/>
-      <c r="F29" s="474"/>
+      <c r="C29" s="471"/>
+      <c r="D29" s="471"/>
+      <c r="E29" s="471"/>
+      <c r="F29" s="471"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="477" t="s">
+      <c r="B30" s="472" t="s">
         <v>500</v>
       </c>
-      <c r="C30" s="477"/>
-      <c r="D30" s="477"/>
-      <c r="E30" s="477"/>
-      <c r="F30" s="477"/>
+      <c r="C30" s="472"/>
+      <c r="D30" s="472"/>
+      <c r="E30" s="472"/>
+      <c r="F30" s="472"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="369" t="s">
@@ -20674,10 +20674,10 @@
       <c r="B54" s="470" t="s">
         <v>507</v>
       </c>
-      <c r="C54" s="476"/>
-      <c r="D54" s="476"/>
-      <c r="E54" s="476"/>
-      <c r="F54" s="476"/>
+      <c r="C54" s="473"/>
+      <c r="D54" s="473"/>
+      <c r="E54" s="473"/>
+      <c r="F54" s="473"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="372" t="s">
@@ -20693,22 +20693,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="474" t="s">
+      <c r="B57" s="471" t="s">
         <v>508</v>
       </c>
-      <c r="C57" s="474"/>
-      <c r="D57" s="474"/>
-      <c r="E57" s="474"/>
-      <c r="F57" s="474"/>
+      <c r="C57" s="471"/>
+      <c r="D57" s="471"/>
+      <c r="E57" s="471"/>
+      <c r="F57" s="471"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="474" t="s">
+      <c r="B58" s="471" t="s">
         <v>509</v>
       </c>
-      <c r="C58" s="474"/>
-      <c r="D58" s="474"/>
-      <c r="E58" s="474"/>
-      <c r="F58" s="474"/>
+      <c r="C58" s="471"/>
+      <c r="D58" s="471"/>
+      <c r="E58" s="471"/>
+      <c r="F58" s="471"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="372" t="s">
@@ -20742,7 +20742,7 @@
       </c>
       <c r="C62" s="378">
         <f>Normalized_FCF!C124</f>
-        <v>6.9312489962270629E-2</v>
+        <v>7.0120130272266309E-2</v>
       </c>
       <c r="F62" s="379"/>
     </row>
@@ -20752,7 +20752,7 @@
       </c>
       <c r="C63" s="378">
         <f>Normalized_FCF!C92</f>
-        <v>3.3768915094339623E-2</v>
+        <v>3.4188204393505249E-2</v>
       </c>
       <c r="E63" s="372" t="s">
         <v>373</v>
@@ -20843,22 +20843,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="386"/>
-      <c r="B73" s="474" t="s">
+      <c r="B73" s="471" t="s">
         <v>510</v>
       </c>
-      <c r="C73" s="474"/>
-      <c r="D73" s="474"/>
-      <c r="E73" s="474"/>
-      <c r="F73" s="474"/>
+      <c r="C73" s="471"/>
+      <c r="D73" s="471"/>
+      <c r="E73" s="471"/>
+      <c r="F73" s="471"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="477" t="s">
+      <c r="B74" s="472" t="s">
         <v>479</v>
       </c>
-      <c r="C74" s="477"/>
-      <c r="D74" s="477"/>
-      <c r="E74" s="477"/>
-      <c r="F74" s="477"/>
+      <c r="C74" s="472"/>
+      <c r="D74" s="472"/>
+      <c r="E74" s="472"/>
+      <c r="F74" s="472"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="369" t="s">
@@ -20866,13 +20866,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="474" t="s">
+      <c r="B77" s="471" t="s">
         <v>511</v>
       </c>
-      <c r="C77" s="474"/>
-      <c r="D77" s="474"/>
-      <c r="E77" s="474"/>
-      <c r="F77" s="474"/>
+      <c r="C77" s="471"/>
+      <c r="D77" s="471"/>
+      <c r="E77" s="471"/>
+      <c r="F77" s="471"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="343" t="s">
@@ -20893,7 +20893,7 @@
       </c>
       <c r="C79" s="387">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-10.361928075499378</v>
+        <v>-10.354105922795677</v>
       </c>
       <c r="D79" s="343" t="str">
         <f>Market_currency</f>
@@ -20955,7 +20955,7 @@
       </c>
       <c r="C86" s="387">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-0.18857913052312023</v>
+        <v>-0.18843677335320597</v>
       </c>
       <c r="D86" s="343" t="str">
         <f>Market_currency</f>
@@ -20986,7 +20986,7 @@
       </c>
       <c r="C90" s="387">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>0.13285882389811524</v>
+        <v>0.13275852962845874</v>
       </c>
       <c r="D90" s="343" t="str">
         <f>Market_currency</f>
@@ -20999,7 +20999,7 @@
       </c>
       <c r="C92" s="387">
         <f>DCF!F8</f>
-        <v>-10.417648382124385</v>
+        <v>-10.409784166520426</v>
       </c>
       <c r="D92" s="343" t="str">
         <f>Market_currency</f>
@@ -21021,33 +21021,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="385"/>
-      <c r="B96" s="474" t="s">
+      <c r="B96" s="471" t="s">
         <v>514</v>
       </c>
-      <c r="C96" s="474"/>
-      <c r="D96" s="474"/>
-      <c r="E96" s="474"/>
-      <c r="F96" s="474"/>
+      <c r="C96" s="471"/>
+      <c r="D96" s="471"/>
+      <c r="E96" s="471"/>
+      <c r="F96" s="471"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="385"/>
-      <c r="B97" s="477" t="s">
+      <c r="B97" s="472" t="s">
         <v>515</v>
       </c>
-      <c r="C97" s="477"/>
-      <c r="D97" s="477"/>
-      <c r="E97" s="477"/>
-      <c r="F97" s="477"/>
+      <c r="C97" s="472"/>
+      <c r="D97" s="472"/>
+      <c r="E97" s="472"/>
+      <c r="F97" s="472"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="385"/>
-      <c r="B98" s="477" t="s">
+      <c r="B98" s="472" t="s">
         <v>516</v>
       </c>
-      <c r="C98" s="477"/>
-      <c r="D98" s="477"/>
-      <c r="E98" s="477"/>
-      <c r="F98" s="477"/>
+      <c r="C98" s="472"/>
+      <c r="D98" s="472"/>
+      <c r="E98" s="472"/>
+      <c r="F98" s="472"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="385"/>
@@ -21110,23 +21110,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="385"/>
-      <c r="B107" s="474" t="s">
+      <c r="B107" s="471" t="s">
         <v>517</v>
       </c>
-      <c r="C107" s="474"/>
-      <c r="D107" s="474"/>
-      <c r="E107" s="474"/>
-      <c r="F107" s="474"/>
+      <c r="C107" s="471"/>
+      <c r="D107" s="471"/>
+      <c r="E107" s="471"/>
+      <c r="F107" s="471"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="385"/>
-      <c r="B108" s="474" t="s">
+      <c r="B108" s="471" t="s">
         <v>536</v>
       </c>
-      <c r="C108" s="474"/>
-      <c r="D108" s="474"/>
-      <c r="E108" s="474"/>
-      <c r="F108" s="474"/>
+      <c r="C108" s="471"/>
+      <c r="D108" s="471"/>
+      <c r="E108" s="471"/>
+      <c r="F108" s="471"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="385"/>
@@ -21144,7 +21144,7 @@
       </c>
       <c r="C111" s="394">
         <f>BS!D47</f>
-        <v>-6.3382048349071285</v>
+        <v>-6.333420164937916</v>
       </c>
       <c r="D111" s="343" t="str">
         <f>Market_currency</f>
@@ -21158,7 +21158,7 @@
       </c>
       <c r="C112" s="394">
         <f>DCF!C11</f>
-        <v>46.680000491938102</v>
+        <v>46.644762060499836</v>
       </c>
       <c r="D112" s="343" t="str">
         <f>Market_currency</f>
@@ -21170,13 +21170,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="385"/>
-      <c r="B114" s="474" t="s">
+      <c r="B114" s="471" t="s">
         <v>518</v>
       </c>
-      <c r="C114" s="474"/>
-      <c r="D114" s="474"/>
-      <c r="E114" s="474"/>
-      <c r="F114" s="474"/>
+      <c r="C114" s="471"/>
+      <c r="D114" s="471"/>
+      <c r="E114" s="471"/>
+      <c r="F114" s="471"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="385"/>
@@ -21221,7 +21221,7 @@
       </c>
       <c r="E118" s="398" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>100.4 HKD</v>
+        <v>100.33 HKD</v>
       </c>
       <c r="F118" s="399">
         <f>DCF!F90</f>
@@ -21244,7 +21244,7 @@
       </c>
       <c r="E119" s="398" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>74.38 HKD</v>
+        <v>74.32 HKD</v>
       </c>
       <c r="F119" s="403">
         <f>DCF!F91</f>
@@ -21266,7 +21266,7 @@
       </c>
       <c r="E120" s="398" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>55.15 HKD</v>
+        <v>55.11 HKD</v>
       </c>
       <c r="F120" s="403">
         <f>DCF!F92</f>
@@ -21288,7 +21288,7 @@
       </c>
       <c r="E121" s="398" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>40.91 HKD</v>
+        <v>40.88 HKD</v>
       </c>
       <c r="F121" s="403">
         <f>DCF!F93</f>
@@ -21310,7 +21310,7 @@
       </c>
       <c r="E122" s="398" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>30.32 HKD</v>
+        <v>30.3 HKD</v>
       </c>
       <c r="F122" s="403">
         <f>DCF!F94</f>
@@ -21332,7 +21332,7 @@
       </c>
       <c r="C125" s="404">
         <f>Scenarios!C36</f>
-        <v>60.922911775163712</v>
+        <v>60.876921461817851</v>
       </c>
       <c r="D125" s="343" t="str">
         <f>Market_currency</f>
@@ -21340,13 +21340,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="472" t="s">
+      <c r="B127" s="475" t="s">
         <v>520</v>
       </c>
-      <c r="C127" s="472"/>
-      <c r="D127" s="472"/>
-      <c r="E127" s="472"/>
-      <c r="F127" s="472"/>
+      <c r="C127" s="475"/>
+      <c r="D127" s="475"/>
+      <c r="E127" s="475"/>
+      <c r="F127" s="475"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="345" t="s">
@@ -21359,22 +21359,22 @@
       <c r="F129" s="345"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="473" t="s">
+      <c r="B131" s="476" t="s">
         <v>521</v>
       </c>
-      <c r="C131" s="473"/>
-      <c r="D131" s="473"/>
-      <c r="E131" s="473"/>
-      <c r="F131" s="473"/>
+      <c r="C131" s="476"/>
+      <c r="D131" s="476"/>
+      <c r="E131" s="476"/>
+      <c r="F131" s="476"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="474" t="s">
+      <c r="B132" s="471" t="s">
         <v>522</v>
       </c>
-      <c r="C132" s="474"/>
-      <c r="D132" s="474"/>
-      <c r="E132" s="474"/>
-      <c r="F132" s="474"/>
+      <c r="C132" s="471"/>
+      <c r="D132" s="471"/>
+      <c r="E132" s="471"/>
+      <c r="F132" s="471"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="369" t="s">
@@ -21439,11 +21439,11 @@
       </c>
       <c r="D140" s="409">
         <f>Scenarios!D62</f>
-        <v>28.075074550766693</v>
+        <v>28.053880857980584</v>
       </c>
       <c r="E140" s="410">
         <f>Scenarios!E62</f>
-        <v>30.695059697144316</v>
+        <v>30.673866004358207</v>
       </c>
       <c r="F140" s="411">
         <f>E22</f>
@@ -21460,11 +21460,11 @@
       </c>
       <c r="D141" s="409">
         <f>Scenarios!D63</f>
-        <v>35.190129545220934</v>
+        <v>35.163564743288305</v>
       </c>
       <c r="E141" s="410">
         <f>Scenarios!E63</f>
-        <v>38.202646604928695</v>
+        <v>38.176081802996066</v>
       </c>
       <c r="F141" s="411">
         <f>Scenarios!F63</f>
@@ -21500,11 +21500,11 @@
       </c>
       <c r="D144" s="409">
         <f>Scenarios!D66</f>
-        <v>43.667130187572489</v>
+        <v>43.634166152503838</v>
       </c>
       <c r="E144" s="410">
         <f>Scenarios!E66</f>
-        <v>47.121500168497697</v>
+        <v>47.088536133429045</v>
       </c>
       <c r="F144" s="411">
         <f>E24</f>
@@ -21521,11 +21521,11 @@
       </c>
       <c r="D145" s="409">
         <f>Scenarios!D67</f>
-        <v>49.384282627234057</v>
+        <v>49.347002750645608</v>
       </c>
       <c r="E145" s="410">
         <f>Scenarios!E67</f>
-        <v>53.124686702250834</v>
+        <v>53.087406825662384</v>
       </c>
       <c r="F145" s="411">
         <f>Scenarios!F67</f>
@@ -21543,13 +21543,13 @@
       <c r="F147" s="345"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="475" t="s">
+      <c r="B149" s="477" t="s">
         <v>523</v>
       </c>
-      <c r="C149" s="474"/>
-      <c r="D149" s="474"/>
-      <c r="E149" s="474"/>
-      <c r="F149" s="474"/>
+      <c r="C149" s="471"/>
+      <c r="D149" s="471"/>
+      <c r="E149" s="471"/>
+      <c r="F149" s="471"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="369" t="s">
@@ -21557,13 +21557,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="476" t="s">
+      <c r="B152" s="473" t="s">
         <v>524</v>
       </c>
-      <c r="C152" s="476"/>
-      <c r="D152" s="476"/>
-      <c r="E152" s="476"/>
-      <c r="F152" s="476"/>
+      <c r="C152" s="473"/>
+      <c r="D152" s="473"/>
+      <c r="E152" s="473"/>
+      <c r="F152" s="473"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="412" t="s">
@@ -21600,22 +21600,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="471" t="s">
+      <c r="B161" s="474" t="s">
         <v>388</v>
       </c>
-      <c r="C161" s="471"/>
-      <c r="D161" s="471"/>
-      <c r="E161" s="471"/>
-      <c r="F161" s="471"/>
+      <c r="C161" s="474"/>
+      <c r="D161" s="474"/>
+      <c r="E161" s="474"/>
+      <c r="F161" s="474"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="471" t="s">
+      <c r="B162" s="474" t="s">
         <v>389</v>
       </c>
-      <c r="C162" s="471"/>
-      <c r="D162" s="471"/>
-      <c r="E162" s="471"/>
-      <c r="F162" s="471"/>
+      <c r="C162" s="474"/>
+      <c r="D162" s="474"/>
+      <c r="E162" s="474"/>
+      <c r="F162" s="474"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="343" t="s">
@@ -21639,12 +21639,15 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21659,15 +21662,12 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/1913.HK_Valuation.xlsx
+++ b/financial_models/opportunities/1913.HK_Valuation.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10209"/>
   <workbookPr showObjects="none" codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kamanl/PycharmProjects/Invest_Proc/financial_models/opportunities/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{736763B1-A020-44AF-9ED1-276DB5D17713}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFD32012-A231-7D44-8EE4-57DAC2DB80E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="17120" windowHeight="10760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -39,6 +39,17 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
     <ext uri="GoogleSheetsCustomDataVersion1">
       <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId10" roundtripDataSignature="AMtx7mi73Cg0ax9bLfpeUuF69nNRn7idDQ=="/>
@@ -3275,27 +3286,27 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="19">
-    <numFmt numFmtId="8" formatCode="&quot;$&quot;#,##0.00;[Red]\-&quot;$&quot;#,##0.00"/>
-    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="165" formatCode="#,##0&quot;mm&quot;"/>
-    <numFmt numFmtId="166" formatCode="#,##0.00&quot;x&quot;"/>
-    <numFmt numFmtId="167" formatCode="0.00\x"/>
-    <numFmt numFmtId="168" formatCode="yyyy\-mm\-dd;@"/>
-    <numFmt numFmtId="169" formatCode="#,##0.0000"/>
-    <numFmt numFmtId="170" formatCode="#,##0_ "/>
-    <numFmt numFmtId="171" formatCode="#,##0.0000_);\(#,##0.0000\)"/>
-    <numFmt numFmtId="172" formatCode="#,##0.0000_ "/>
-    <numFmt numFmtId="173" formatCode="&quot;in &quot;#,##0&quot;s&quot;"/>
-    <numFmt numFmtId="174" formatCode="#,##0.00_ "/>
-    <numFmt numFmtId="175" formatCode="0&quot; yrs&quot;"/>
-    <numFmt numFmtId="176" formatCode="0.000_ "/>
-    <numFmt numFmtId="177" formatCode="&quot;every&quot;\ 0\ &quot;Months&quot;"/>
-    <numFmt numFmtId="178" formatCode="0.0\x"/>
-    <numFmt numFmtId="179" formatCode="0\x"/>
-    <numFmt numFmtId="180" formatCode="0.000000000000000%"/>
-    <numFmt numFmtId="181" formatCode="#,##0_);\(#,##0\);0;@"/>
+    <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00;[Red]\-&quot;$&quot;#,##0.00"/>
+    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="166" formatCode="#,##0&quot;mm&quot;"/>
+    <numFmt numFmtId="167" formatCode="#,##0.00&quot;x&quot;"/>
+    <numFmt numFmtId="168" formatCode="0.00\x"/>
+    <numFmt numFmtId="169" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="170" formatCode="#,##0.0000"/>
+    <numFmt numFmtId="171" formatCode="#,##0_ "/>
+    <numFmt numFmtId="172" formatCode="#,##0.0000_);\(#,##0.0000\)"/>
+    <numFmt numFmtId="173" formatCode="#,##0.0000_ "/>
+    <numFmt numFmtId="174" formatCode="&quot;in &quot;#,##0&quot;s&quot;"/>
+    <numFmt numFmtId="175" formatCode="#,##0.00_ "/>
+    <numFmt numFmtId="176" formatCode="0&quot; yrs&quot;"/>
+    <numFmt numFmtId="177" formatCode="0.000_ "/>
+    <numFmt numFmtId="178" formatCode="&quot;every&quot;\ 0\ &quot;Months&quot;"/>
+    <numFmt numFmtId="179" formatCode="0.0\x"/>
+    <numFmt numFmtId="180" formatCode="0\x"/>
+    <numFmt numFmtId="181" formatCode="0.000000000000000%"/>
+    <numFmt numFmtId="182" formatCode="#,##0_);\(#,##0\);0;@"/>
   </numFmts>
-  <fonts count="72">
+  <fonts count="72" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -4047,7 +4058,7 @@
     <xf numFmtId="3" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
@@ -4089,17 +4100,17 @@
     <xf numFmtId="3" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="168" fontId="9" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="9" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="169" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4108,7 +4119,7 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="167" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4182,10 +4193,10 @@
     </xf>
     <xf numFmtId="10" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="171" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="172" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="170" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="171" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -4196,7 +4207,7 @@
     <xf numFmtId="10" fontId="11" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="168" fontId="9" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="9" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -4234,7 +4245,7 @@
     <xf numFmtId="10" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="8" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="8" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4244,7 +4255,7 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="168" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -4255,19 +4266,19 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="168" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="173" fontId="17" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="174" fontId="17" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="173" fontId="14" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="174" fontId="14" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="173" fontId="23" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="174" fontId="23" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
@@ -4275,8 +4286,8 @@
       <alignment horizontal="left" indent="1"/>
     </xf>
     <xf numFmtId="39" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="172" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="172" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="173" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="173" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="37" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="38" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -4299,29 +4310,29 @@
     </xf>
     <xf numFmtId="9" fontId="30" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="9" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="170" fontId="31" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="171" fontId="31" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="39" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="174" fontId="24" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="175" fontId="24" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="10" fontId="25" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="175" fontId="30" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="175" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="175" fontId="25" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="30" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="176" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="176" fontId="25" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="174" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="175" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="175" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="176" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -4338,15 +4349,15 @@
     </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="174" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="175" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="10" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="175" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="29" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="175" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="176" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -4357,11 +4368,11 @@
     <xf numFmtId="0" fontId="27" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="3" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="174" fontId="8" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="175" fontId="8" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="36" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4422,14 +4433,14 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="174" fontId="1" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="175" fontId="1" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="176" fontId="42" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="177" fontId="42" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
     <xf numFmtId="40" fontId="41" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -4442,7 +4453,7 @@
     </xf>
     <xf numFmtId="0" fontId="44" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="39" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="175" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="176" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="8" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -4479,7 +4490,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="175" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -4496,7 +4507,7 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="178" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="179" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
@@ -4542,7 +4553,7 @@
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="49" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="179" fontId="46" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="180" fontId="46" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -4557,13 +4568,13 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="174" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="175" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="174" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="175" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="180" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="181" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -4579,53 +4590,53 @@
     <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="181" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="181" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="181" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="182" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="182" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="182" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="181" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="181" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="182" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="181" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="181" fontId="3" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="181" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="181" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="181" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="181" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="181" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="181" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="181" fontId="47" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="181" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="3" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="182" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="182" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="182" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="182" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="182" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="182" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="182" fontId="47" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="182" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="181" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="181" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="181" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="181" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="181" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="181" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="182" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="182" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="182" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="181" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="181" fontId="17" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="17" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="181" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="181" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="181" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="182" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="182" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="3" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -4642,7 +4653,7 @@
       <alignment horizontal="left" indent="1"/>
     </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="181" fontId="8" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="8" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="25" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
@@ -4655,21 +4666,21 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="181" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="182" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="175" fontId="25" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="25" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="10" fontId="25" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="181" fontId="32" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="182" fontId="32" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
@@ -4679,14 +4690,14 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="181" fontId="24" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="24" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="174" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="175" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="40" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -4695,8 +4706,8 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="10" fontId="29" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="175" fontId="25" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="174" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="25" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="175" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="29" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="25" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="51" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4708,7 +4719,7 @@
     </xf>
     <xf numFmtId="39" fontId="24" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="39" fontId="42" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="174" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="175" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="42" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -4716,7 +4727,7 @@
     <xf numFmtId="9" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="178" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -4755,7 +4766,7 @@
     <xf numFmtId="4" fontId="56" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="165" fontId="56" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="56" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="56" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -4769,39 +4780,39 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="64" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="175" fontId="64" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="64" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="174" fontId="56" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="175" fontId="56" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="56" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="56" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="174" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="175" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="10" fontId="56" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="66" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="173" fontId="67" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="174" fontId="67" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="181" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="182" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="37" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="181" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
     <xf numFmtId="10" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="180" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="181" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -4812,7 +4823,7 @@
       <alignment horizontal="left" indent="1"/>
     </xf>
     <xf numFmtId="10" fontId="61" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="61" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="167" fontId="61" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -4823,10 +4834,10 @@
     <xf numFmtId="9" fontId="61" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="178" fontId="61" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="61" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="181" fontId="61" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="182" fontId="61" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="10" fontId="60" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -4835,7 +4846,7 @@
     <xf numFmtId="10" fontId="56" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="175" fontId="56" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="56" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="39" fontId="54" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4848,7 +4859,7 @@
     <xf numFmtId="10" fontId="56" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="175" fontId="56" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="56" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="10" fontId="54" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4857,8 +4868,8 @@
     <xf numFmtId="40" fontId="65" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="175" fontId="56" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="176" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="176" fontId="56" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="177" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="63" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -4866,10 +4877,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="39" fontId="54" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="174" fontId="65" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="175" fontId="65" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="54" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
-    <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="68" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="10" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4878,10 +4889,10 @@
     <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="177" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="69" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4898,16 +4909,16 @@
     <xf numFmtId="4" fontId="56" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="177" fontId="56" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="56" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="56" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="56" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4928,7 +4939,7 @@
     <xf numFmtId="0" fontId="59" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="56" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="56" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="56" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4946,7 +4957,7 @@
     <xf numFmtId="40" fontId="32" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="175" fontId="70" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="70" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="10" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -4956,10 +4967,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="173" fontId="14" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="174" fontId="14" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="181" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -4974,7 +4985,7 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="167" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="10" fontId="71" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4988,34 +4999,34 @@
     <xf numFmtId="10" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="181" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5025,30 +5036,30 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="常规 2 2" xfId="1" xr:uid="{A35F4541-DCCE-4554-A311-39480A36979A}"/>
   </cellStyles>
   <dxfs count="7">
@@ -5330,7 +5341,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:I167"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.65"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="2.6640625" style="1" customWidth="1"/>
     <col min="2" max="2" width="32.6640625" style="1" customWidth="1"/>
@@ -5339,7 +5350,7 @@
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:9" ht="13.9">
+    <row r="2" spans="1:9" ht="16" x14ac:dyDescent="0.25">
       <c r="A2" s="200" t="s">
         <v>225</v>
       </c>
@@ -5352,7 +5363,7 @@
       <c r="H2" s="21"/>
       <c r="I2" s="21"/>
     </row>
-    <row r="3" spans="1:9">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.15">
       <c r="E3" s="428" t="s">
         <v>538</v>
       </c>
@@ -5360,7 +5371,7 @@
         <v>46065</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="12.4">
+    <row r="4" spans="1:9" ht="14" x14ac:dyDescent="0.2">
       <c r="B4" s="421" t="s">
         <v>533</v>
       </c>
@@ -5374,7 +5385,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="5" spans="1:9">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.15">
       <c r="B5" s="1" t="s">
         <v>349</v>
       </c>
@@ -5388,7 +5399,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="6" spans="1:9">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.15">
       <c r="B6" s="2" t="s">
         <v>53</v>
       </c>
@@ -5398,7 +5409,7 @@
       <c r="D6" s="45"/>
       <c r="E6" s="45"/>
     </row>
-    <row r="7" spans="1:9">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.15">
       <c r="B7" s="1" t="s">
         <v>351</v>
       </c>
@@ -5408,16 +5419,16 @@
       <c r="D7" s="45"/>
       <c r="E7" s="45"/>
     </row>
-    <row r="8" spans="1:9">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.15">
       <c r="B8" s="4" t="s">
         <v>350</v>
       </c>
       <c r="C8" s="47">
-        <v>41.88</v>
+        <v>42.2</v>
       </c>
       <c r="E8" s="32"/>
     </row>
-    <row r="9" spans="1:9">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.15">
       <c r="B9" s="4" t="s">
         <v>346</v>
       </c>
@@ -5425,43 +5436,43 @@
         <v>2558824000</v>
       </c>
     </row>
-    <row r="10" spans="1:9">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.15">
       <c r="B10" s="4" t="s">
         <v>352</v>
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>107163.54912</v>
+        <v>107982.3728</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>528</v>
       </c>
       <c r="E10" s="303">
         <f>Scenarios!F34</f>
-        <v>0.16319188190025868</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9">
+        <v>0.15751340909520897</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.15">
       <c r="D11" s="5"/>
       <c r="E11" s="5"/>
     </row>
-    <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="460" t="s">
+    <row r="12" spans="1:9" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B12" s="462" t="s">
         <v>355</v>
       </c>
-      <c r="C12" s="460"/>
-      <c r="D12" s="460"/>
-      <c r="E12" s="460"/>
-      <c r="F12" s="460"/>
-    </row>
-    <row r="14" spans="1:9">
+      <c r="C12" s="462"/>
+      <c r="D12" s="462"/>
+      <c r="E12" s="462"/>
+      <c r="F12" s="462"/>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.15">
       <c r="B14" s="42" t="str">
         <f>Scenarios!B39&amp;" Valuation Conclusion"</f>
         <v>1-stage DCF Valuation Conclusion</v>
       </c>
       <c r="C14" s="43"/>
     </row>
-    <row r="15" spans="1:9">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.15">
       <c r="B15" s="1" t="s">
         <v>319</v>
       </c>
@@ -5476,7 +5487,7 @@
         <v>EUR/HKD</v>
       </c>
     </row>
-    <row r="16" spans="1:9">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.15">
       <c r="B16" s="1" t="s">
         <v>320</v>
       </c>
@@ -5487,10 +5498,10 @@
         <v>354</v>
       </c>
       <c r="E16" s="416">
-        <v>9.2771663694858564</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
+        <v>9.2105230273246779</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B17" s="1" t="s">
         <v>532</v>
       </c>
@@ -5504,14 +5515,14 @@
         <v>558</v>
       </c>
     </row>
-    <row r="18" spans="1:6">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B18" s="1" t="str">
         <f>"Expected Equity Value ("&amp;C7&amp;") :"</f>
         <v>Expected Equity Value (HKD) :</v>
       </c>
       <c r="C18" s="252">
         <f>C125</f>
-        <v>60.876921461817851</v>
+        <v>60.439606731746466</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>347</v>
@@ -5520,7 +5531,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="19" spans="1:6">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B19" s="2" t="s">
         <v>275</v>
       </c>
@@ -5536,11 +5547,11 @@
         <v>46081</v>
       </c>
     </row>
-    <row r="20" spans="1:6">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.15">
       <c r="D20" s="5"/>
       <c r="E20" s="5"/>
     </row>
-    <row r="21" spans="1:6">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B21" s="42" t="s">
         <v>404</v>
       </c>
@@ -5555,13 +5566,13 @@
         <v>3</v>
       </c>
     </row>
-    <row r="22" spans="1:6">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B22" s="1" t="s">
         <v>312</v>
       </c>
       <c r="C22" s="255">
         <f>E140</f>
-        <v>30.673866004358207</v>
+        <v>30.472338478979687</v>
       </c>
       <c r="D22" s="38" t="s">
         <v>406</v>
@@ -5570,13 +5581,13 @@
         <v>0.29465259038036606</v>
       </c>
     </row>
-    <row r="23" spans="1:6">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B23" s="1" t="s">
         <v>313</v>
       </c>
       <c r="C23" s="256">
         <f>E141</f>
-        <v>38.176081802996066</v>
+        <v>37.923481236889849</v>
       </c>
       <c r="D23" s="38" t="s">
         <v>407</v>
@@ -5585,13 +5596,13 @@
         <v>0.20075184365903009</v>
       </c>
     </row>
-    <row r="24" spans="1:6">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B24" s="1" t="s">
         <v>315</v>
       </c>
       <c r="C24" s="256">
         <f>E144</f>
-        <v>47.088536133429045</v>
+        <v>46.775086255631912</v>
       </c>
       <c r="D24" s="38" t="s">
         <v>408</v>
@@ -5600,13 +5611,13 @@
         <v>0.1174</v>
       </c>
     </row>
-    <row r="25" spans="1:6">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B25" s="1" t="s">
         <v>314</v>
       </c>
       <c r="C25" s="256">
         <f>E145</f>
-        <v>53.087406825662384</v>
+        <v>52.732918282721435</v>
       </c>
       <c r="D25" s="38" t="s">
         <v>409</v>
@@ -5615,11 +5626,11 @@
         <v>7.2499999999999995E-2</v>
       </c>
     </row>
-    <row r="26" spans="1:6">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.15">
       <c r="D26" s="5"/>
       <c r="E26" s="5"/>
     </row>
-    <row r="27" spans="1:6" ht="13.9">
+    <row r="27" spans="1:6" ht="16" x14ac:dyDescent="0.25">
       <c r="A27" s="200" t="s">
         <v>280</v>
       </c>
@@ -5629,25 +5640,25 @@
       <c r="E27" s="34"/>
       <c r="F27" s="34"/>
     </row>
-    <row r="29" spans="1:6">
-      <c r="B29" s="460" t="s">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="B29" s="462" t="s">
         <v>356</v>
       </c>
-      <c r="C29" s="460"/>
-      <c r="D29" s="460"/>
-      <c r="E29" s="460"/>
-      <c r="F29" s="460"/>
-    </row>
-    <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="462" t="s">
+      <c r="C29" s="462"/>
+      <c r="D29" s="462"/>
+      <c r="E29" s="462"/>
+      <c r="F29" s="462"/>
+    </row>
+    <row r="30" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B30" s="466" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="462"/>
-      <c r="D30" s="462"/>
-      <c r="E30" s="462"/>
-      <c r="F30" s="462"/>
-    </row>
-    <row r="32" spans="1:6">
+      <c r="C30" s="466"/>
+      <c r="D30" s="466"/>
+      <c r="E30" s="466"/>
+      <c r="F30" s="466"/>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B32" s="192" t="s">
         <v>195</v>
       </c>
@@ -5656,16 +5667,16 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="461" t="s">
+    <row r="33" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B33" s="463" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="461"/>
-      <c r="D33" s="461"/>
-      <c r="E33" s="461"/>
-      <c r="F33" s="461"/>
-    </row>
-    <row r="34" spans="2:6">
+      <c r="C33" s="463"/>
+      <c r="D33" s="463"/>
+      <c r="E33" s="463"/>
+      <c r="F33" s="463"/>
+    </row>
+    <row r="34" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B34" s="44" t="s">
         <v>197</v>
       </c>
@@ -5678,20 +5689,20 @@
         <v>EUR</v>
       </c>
     </row>
-    <row r="35" spans="2:6">
+    <row r="35" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B35" s="44"/>
       <c r="C35" s="73"/>
     </row>
-    <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="461" t="s">
+    <row r="36" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B36" s="463" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="461"/>
-      <c r="D36" s="461"/>
-      <c r="E36" s="461"/>
-      <c r="F36" s="461"/>
-    </row>
-    <row r="37" spans="2:6">
+      <c r="C36" s="463"/>
+      <c r="D36" s="463"/>
+      <c r="E36" s="463"/>
+      <c r="F36" s="463"/>
+    </row>
+    <row r="37" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B37" s="44" t="s">
         <v>199</v>
       </c>
@@ -5704,7 +5715,7 @@
         <v>EUR</v>
       </c>
     </row>
-    <row r="38" spans="2:6">
+    <row r="38" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B38" s="49" t="s">
         <v>200</v>
       </c>
@@ -5717,16 +5728,16 @@
         <v>EUR</v>
       </c>
     </row>
-    <row r="40" spans="2:6">
-      <c r="B40" s="461" t="s">
+    <row r="40" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="B40" s="463" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="461"/>
-      <c r="D40" s="461"/>
-      <c r="E40" s="461"/>
-      <c r="F40" s="461"/>
-    </row>
-    <row r="41" spans="2:6">
+      <c r="C40" s="463"/>
+      <c r="D40" s="463"/>
+      <c r="E40" s="463"/>
+      <c r="F40" s="463"/>
+    </row>
+    <row r="41" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B41" s="44" t="s">
         <v>202</v>
       </c>
@@ -5739,16 +5750,16 @@
         <v>EUR</v>
       </c>
     </row>
-    <row r="43" spans="2:6">
-      <c r="B43" s="461" t="s">
+    <row r="43" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="B43" s="463" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="461"/>
-      <c r="D43" s="461"/>
-      <c r="E43" s="461"/>
-      <c r="F43" s="461"/>
-    </row>
-    <row r="44" spans="2:6">
+      <c r="C43" s="463"/>
+      <c r="D43" s="463"/>
+      <c r="E43" s="463"/>
+      <c r="F43" s="463"/>
+    </row>
+    <row r="44" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B44" s="44" t="s">
         <v>267</v>
       </c>
@@ -5763,7 +5774,7 @@
       <c r="E44" s="244"/>
       <c r="F44" s="244"/>
     </row>
-    <row r="45" spans="2:6">
+    <row r="45" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B45" s="44" t="s">
         <v>268</v>
       </c>
@@ -5778,7 +5789,7 @@
       <c r="E45" s="244"/>
       <c r="F45" s="244"/>
     </row>
-    <row r="46" spans="2:6">
+    <row r="46" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B46" s="44" t="s">
         <v>203</v>
       </c>
@@ -5791,12 +5802,12 @@
         <v>EUR</v>
       </c>
     </row>
-    <row r="48" spans="2:6">
+    <row r="48" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B48" s="1" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="49" spans="2:6">
+    <row r="49" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B49" s="44" t="s">
         <v>223</v>
       </c>
@@ -5809,16 +5820,16 @@
         <v>EUR</v>
       </c>
     </row>
-    <row r="51" spans="2:6">
-      <c r="B51" s="461" t="s">
+    <row r="51" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="B51" s="463" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="461"/>
-      <c r="D51" s="461"/>
-      <c r="E51" s="461"/>
-      <c r="F51" s="461"/>
-    </row>
-    <row r="52" spans="2:6">
+      <c r="C51" s="463"/>
+      <c r="D51" s="463"/>
+      <c r="E51" s="463"/>
+      <c r="F51" s="463"/>
+    </row>
+    <row r="52" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B52" s="44" t="s">
         <v>204</v>
       </c>
@@ -5831,8 +5842,8 @@
         <v>EUR</v>
       </c>
     </row>
-    <row r="54" spans="2:6">
-      <c r="B54" s="461" t="s">
+    <row r="54" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="B54" s="463" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="464"/>
@@ -5840,7 +5851,7 @@
       <c r="E54" s="464"/>
       <c r="F54" s="464"/>
     </row>
-    <row r="55" spans="2:6">
+    <row r="55" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B55" s="44" t="s">
         <v>207</v>
       </c>
@@ -5853,25 +5864,25 @@
         <v>EUR</v>
       </c>
     </row>
-    <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="460" t="s">
+    <row r="57" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B57" s="462" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="460"/>
-      <c r="D57" s="460"/>
-      <c r="E57" s="460"/>
-      <c r="F57" s="460"/>
-    </row>
-    <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="460" t="s">
+      <c r="C57" s="462"/>
+      <c r="D57" s="462"/>
+      <c r="E57" s="462"/>
+      <c r="F57" s="462"/>
+    </row>
+    <row r="58" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B58" s="462" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="460"/>
-      <c r="D58" s="460"/>
-      <c r="E58" s="460"/>
-      <c r="F58" s="460"/>
-    </row>
-    <row r="60" spans="2:6">
+      <c r="C58" s="462"/>
+      <c r="D58" s="462"/>
+      <c r="E58" s="462"/>
+      <c r="F58" s="462"/>
+    </row>
+    <row r="60" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B60" s="44" t="s">
         <v>227</v>
       </c>
@@ -5884,7 +5895,7 @@
         <v>EUR</v>
       </c>
     </row>
-    <row r="61" spans="2:6">
+    <row r="61" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B61" s="44" t="s">
         <v>213</v>
       </c>
@@ -5897,23 +5908,23 @@
         <v>EUR</v>
       </c>
     </row>
-    <row r="62" spans="2:6">
+    <row r="62" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B62" s="204" t="s">
         <v>302</v>
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>7.0120130272266309E-2</v>
+        <v>6.9088519142746635E-2</v>
       </c>
       <c r="F62" s="257"/>
     </row>
-    <row r="63" spans="2:6">
+    <row r="63" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B63" s="204" t="s">
         <v>332</v>
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>3.4188204393505249E-2</v>
+        <v>3.392895734597156E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>322</v>
@@ -5923,7 +5934,7 @@
         <v>4.5232326123897897</v>
       </c>
     </row>
-    <row r="65" spans="1:6">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B65" s="192" t="s">
         <v>325</v>
       </c>
@@ -5934,7 +5945,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="66" spans="1:6">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B66" s="44" t="s">
         <v>326</v>
       </c>
@@ -5947,7 +5958,7 @@
         <v>0.28005991710273764</v>
       </c>
     </row>
-    <row r="67" spans="1:6">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B67" s="229" t="str">
         <f>Normalized_FCF!B116</f>
         <v>Pre-tax Profit/Sales</v>
@@ -5961,7 +5972,7 @@
         <v>0.21885492502426099</v>
       </c>
     </row>
-    <row r="68" spans="1:6">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B68" s="229" t="str">
         <f>Normalized_FCF!B117</f>
         <v>Sales/Total Assets</v>
@@ -5975,7 +5986,7 @@
         <v>0.65265738052043343</v>
       </c>
     </row>
-    <row r="69" spans="1:6">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B69" s="229" t="str">
         <f>Normalized_FCF!B118</f>
         <v>Total Assets/Equity</v>
@@ -5989,7 +6000,7 @@
         <v>1.9606920057834423</v>
       </c>
     </row>
-    <row r="71" spans="1:6" ht="13.9">
+    <row r="71" spans="1:6" ht="16" x14ac:dyDescent="0.25">
       <c r="A71" s="200" t="s">
         <v>477</v>
       </c>
@@ -5999,45 +6010,45 @@
       <c r="E71" s="34"/>
       <c r="F71" s="34"/>
     </row>
-    <row r="72" spans="1:6">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A72" s="191"/>
     </row>
-    <row r="73" spans="1:6">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A73" s="191"/>
-      <c r="B73" s="460" t="s">
+      <c r="B73" s="462" t="s">
         <v>478</v>
       </c>
-      <c r="C73" s="460"/>
-      <c r="D73" s="460"/>
-      <c r="E73" s="460"/>
-      <c r="F73" s="460"/>
-    </row>
-    <row r="74" spans="1:6">
+      <c r="C73" s="462"/>
+      <c r="D73" s="462"/>
+      <c r="E73" s="462"/>
+      <c r="F73" s="462"/>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A74" s="191"/>
       <c r="B74" s="1" t="s">
         <v>465</v>
       </c>
     </row>
-    <row r="75" spans="1:6">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A75" s="191"/>
     </row>
-    <row r="76" spans="1:6">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A76" s="191"/>
       <c r="B76" s="192" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="77" spans="1:6">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A77" s="191"/>
-      <c r="B77" s="460" t="s">
+      <c r="B77" s="462" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="460"/>
-      <c r="D77" s="460"/>
-      <c r="E77" s="460"/>
-      <c r="F77" s="460"/>
-    </row>
-    <row r="78" spans="1:6">
+      <c r="C77" s="462"/>
+      <c r="D77" s="462"/>
+      <c r="E77" s="462"/>
+      <c r="F77" s="462"/>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A78" s="191"/>
       <c r="B78" s="1" t="s">
         <v>215</v>
@@ -6051,21 +6062,21 @@
         <v>EUR</v>
       </c>
     </row>
-    <row r="79" spans="1:6">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A79" s="191"/>
       <c r="B79" s="44" t="s">
         <v>234</v>
       </c>
       <c r="C79" s="201">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-10.354105922795677</v>
+        <v>-10.279726290448499</v>
       </c>
       <c r="D79" s="1" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="80" spans="1:6">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A80" s="191"/>
       <c r="B80" s="229" t="s">
         <v>309</v>
@@ -6075,7 +6086,7 @@
         <v>0.67283405398617657</v>
       </c>
     </row>
-    <row r="81" spans="1:6">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A81" s="191"/>
       <c r="B81" s="229" t="s">
         <v>311</v>
@@ -6085,16 +6096,16 @@
         <v>2.2041306156151999</v>
       </c>
     </row>
-    <row r="82" spans="1:6">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A82" s="191"/>
     </row>
-    <row r="83" spans="1:6">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A83" s="191"/>
       <c r="B83" s="1" t="s">
         <v>466</v>
       </c>
     </row>
-    <row r="84" spans="1:6">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A84" s="191"/>
       <c r="B84" s="1" t="s">
         <v>224</v>
@@ -6108,7 +6119,7 @@
         <v>EUR</v>
       </c>
     </row>
-    <row r="85" spans="1:6">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A85" s="191"/>
       <c r="B85" s="229" t="s">
         <v>222</v>
@@ -6122,30 +6133,30 @@
         <v>EUR</v>
       </c>
     </row>
-    <row r="86" spans="1:6">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A86" s="191"/>
       <c r="B86" s="44" t="s">
         <v>235</v>
       </c>
       <c r="C86" s="201">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-0.18843677335320597</v>
+        <v>-0.1870831211859201</v>
       </c>
       <c r="D86" s="1" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="87" spans="1:6">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A87" s="191"/>
     </row>
-    <row r="88" spans="1:6">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A88" s="191"/>
       <c r="B88" s="1" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="89" spans="1:6">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A89" s="191"/>
       <c r="B89" s="1" t="s">
         <v>217</v>
@@ -6159,38 +6170,38 @@
         <v>EUR</v>
       </c>
     </row>
-    <row r="90" spans="1:6">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A90" s="191"/>
       <c r="B90" s="44" t="s">
         <v>236</v>
       </c>
       <c r="C90" s="201">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>0.13275852962845874</v>
+        <v>0.13180484703158896</v>
       </c>
       <c r="D90" s="1" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="91" spans="1:6">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A91" s="191"/>
     </row>
-    <row r="92" spans="1:6">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A92" s="191"/>
       <c r="B92" s="44" t="s">
         <v>469</v>
       </c>
       <c r="C92" s="216">
         <f>DCF!F8</f>
-        <v>-10.409784166520426</v>
+        <v>-10.335004564602832</v>
       </c>
       <c r="D92" s="44" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="94" spans="1:6" ht="13.9">
+    <row r="94" spans="1:6" ht="16" x14ac:dyDescent="0.25">
       <c r="A94" s="200" t="s">
         <v>470</v>
       </c>
@@ -6200,42 +6211,42 @@
       <c r="E94" s="34"/>
       <c r="F94" s="34"/>
     </row>
-    <row r="95" spans="1:6">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A95" s="191"/>
     </row>
-    <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="460" t="s">
+    <row r="96" spans="1:6" ht="11.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B96" s="462" t="s">
         <v>485</v>
       </c>
-      <c r="C96" s="460"/>
-      <c r="D96" s="460"/>
-      <c r="E96" s="460"/>
-      <c r="F96" s="460"/>
-    </row>
-    <row r="97" spans="2:6">
-      <c r="B97" s="462" t="s">
+      <c r="C96" s="462"/>
+      <c r="D96" s="462"/>
+      <c r="E96" s="462"/>
+      <c r="F96" s="462"/>
+    </row>
+    <row r="97" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="B97" s="466" t="s">
         <v>484</v>
       </c>
-      <c r="C97" s="462"/>
-      <c r="D97" s="462"/>
-      <c r="E97" s="462"/>
-      <c r="F97" s="462"/>
-    </row>
-    <row r="98" spans="2:6">
-      <c r="B98" s="462" t="s">
+      <c r="C97" s="466"/>
+      <c r="D97" s="466"/>
+      <c r="E97" s="466"/>
+      <c r="F97" s="466"/>
+    </row>
+    <row r="98" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="B98" s="466" t="s">
         <v>483</v>
       </c>
-      <c r="C98" s="462"/>
-      <c r="D98" s="462"/>
-      <c r="E98" s="462"/>
-      <c r="F98" s="462"/>
-    </row>
-    <row r="100" spans="2:6">
+      <c r="C98" s="466"/>
+      <c r="D98" s="466"/>
+      <c r="E98" s="466"/>
+      <c r="F98" s="466"/>
+    </row>
+    <row r="100" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B100" s="192" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="101" spans="2:6">
+    <row r="101" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B101" s="49" t="s">
         <v>467</v>
       </c>
@@ -6244,7 +6255,7 @@
         <v>7.2499999999999995E-2</v>
       </c>
     </row>
-    <row r="102" spans="2:6">
+    <row r="102" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B102" s="229" t="s">
         <v>318</v>
       </c>
@@ -6253,7 +6264,7 @@
         <v>7.2499999999999995E-2</v>
       </c>
     </row>
-    <row r="103" spans="2:6">
+    <row r="103" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B103" s="229" t="s">
         <v>317</v>
       </c>
@@ -6262,7 +6273,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="2:6">
+    <row r="104" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B104" s="44" t="s">
         <v>214</v>
       </c>
@@ -6271,76 +6282,76 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="106" spans="2:6">
+    <row r="106" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B106" s="250" t="s">
         <v>281</v>
       </c>
       <c r="C106" s="116"/>
     </row>
-    <row r="107" spans="2:6">
-      <c r="B107" s="460" t="s">
+    <row r="107" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="B107" s="462" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="460"/>
-      <c r="D107" s="460"/>
-      <c r="E107" s="460"/>
-      <c r="F107" s="460"/>
-    </row>
-    <row r="108" spans="2:6">
-      <c r="B108" s="460" t="s">
+      <c r="C107" s="462"/>
+      <c r="D107" s="462"/>
+      <c r="E107" s="462"/>
+      <c r="F107" s="462"/>
+    </row>
+    <row r="108" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="B108" s="462" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="460"/>
-      <c r="D108" s="460"/>
-      <c r="E108" s="460"/>
-      <c r="F108" s="460"/>
-    </row>
-    <row r="110" spans="2:6">
+      <c r="C108" s="462"/>
+      <c r="D108" s="462"/>
+      <c r="E108" s="462"/>
+      <c r="F108" s="462"/>
+    </row>
+    <row r="110" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B110" s="192" t="s">
         <v>487</v>
       </c>
     </row>
-    <row r="111" spans="2:6">
+    <row r="111" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B111" s="49" t="s">
         <v>468</v>
       </c>
       <c r="C111" s="216">
         <f>BS!D47</f>
-        <v>-6.333420164937916</v>
+        <v>-6.2879234830533743</v>
       </c>
       <c r="D111" s="1" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="112" spans="2:6">
+    <row r="112" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B112" s="44" t="s">
         <v>323</v>
       </c>
       <c r="C112" s="216">
         <f>DCF!C11</f>
-        <v>46.644762060499836</v>
+        <v>46.309685301690244</v>
       </c>
       <c r="D112" s="1" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="460" t="s">
+    <row r="114" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B114" s="462" t="s">
         <v>491</v>
       </c>
-      <c r="C114" s="460"/>
-      <c r="D114" s="460"/>
-      <c r="E114" s="460"/>
-      <c r="F114" s="460"/>
-    </row>
-    <row r="116" spans="2:6">
+      <c r="C114" s="462"/>
+      <c r="D114" s="462"/>
+      <c r="E114" s="462"/>
+      <c r="F114" s="462"/>
+    </row>
+    <row r="116" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B116" s="192" t="s">
         <v>488</v>
       </c>
     </row>
-    <row r="117" spans="2:6" ht="12.4">
+    <row r="117" spans="2:6" ht="14" x14ac:dyDescent="0.2">
       <c r="B117" s="342" t="s">
         <v>101</v>
       </c>
@@ -6357,7 +6368,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="118" spans="2:6">
+    <row r="118" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B118" s="205" t="str">
         <f>DCF!B90&amp;" ("&amp;DCF!D90&amp;"yrs)"</f>
         <v>Snowball Scenario (20yrs)</v>
@@ -6368,7 +6379,7 @@
       </c>
       <c r="D118" s="207" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>100.33 HKD</v>
+        <v>99.61 HKD</v>
       </c>
       <c r="E118" s="208">
         <f>DCF!F90</f>
@@ -6376,10 +6387,10 @@
       </c>
       <c r="F118" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E90,C$18)</f>
-        <v>-0.13642305620587292</v>
-      </c>
-    </row>
-    <row r="119" spans="2:6">
+        <v>-0.13630049268396624</v>
+      </c>
+    </row>
+    <row r="119" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B119" s="205" t="str">
         <f>DCF!B91&amp;" ("&amp;DCF!D91&amp;"yrs)"</f>
         <v>Optimistic (20yrs)</v>
@@ -6390,7 +6401,7 @@
       </c>
       <c r="D119" s="207" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>74.32 HKD</v>
+        <v>73.79 HKD</v>
       </c>
       <c r="E119" s="199">
         <f>DCF!F91</f>
@@ -6398,10 +6409,10 @@
       </c>
       <c r="F119" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E91,C$18)</f>
-        <v>-4.3740647780984215E-2</v>
-      </c>
-    </row>
-    <row r="120" spans="2:6">
+        <v>-4.3591731950928019E-2</v>
+      </c>
+    </row>
+    <row r="120" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B120" s="205" t="str">
         <f>DCF!B92&amp;" ("&amp;DCF!D92&amp;"yrs)"</f>
         <v>Base (20yrs)</v>
@@ -6412,7 +6423,7 @@
       </c>
       <c r="D120" s="207" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>55.11 HKD</v>
+        <v>54.71 HKD</v>
       </c>
       <c r="E120" s="199">
         <f>DCF!F92</f>
@@ -6420,10 +6431,10 @@
       </c>
       <c r="F120" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E92,C$18)</f>
-        <v>5.891062916083515E-2</v>
-      </c>
-    </row>
-    <row r="121" spans="2:6">
+        <v>5.9092749049236608E-2</v>
+      </c>
+    </row>
+    <row r="121" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B121" s="205" t="str">
         <f>DCF!B93&amp;" ("&amp;DCF!D93&amp;"yrs)"</f>
         <v>Pessimistic (20yrs)</v>
@@ -6434,7 +6445,7 @@
       </c>
       <c r="D121" s="207" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>40.88 HKD</v>
+        <v>40.58 HKD</v>
       </c>
       <c r="E121" s="199">
         <f>DCF!F93</f>
@@ -6442,10 +6453,10 @@
       </c>
       <c r="F121" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E93,C$18)</f>
-        <v>0.17290814328575421</v>
-      </c>
-    </row>
-    <row r="122" spans="2:6">
+        <v>0.17313243305898471</v>
+      </c>
+    </row>
+    <row r="122" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B122" s="205" t="str">
         <f>DCF!B94&amp;" ("&amp;DCF!D94&amp;"yrs)"</f>
         <v>Devil's advocate (20yrs)</v>
@@ -6456,7 +6467,7 @@
       </c>
       <c r="D122" s="207" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>30.3 HKD</v>
+        <v>30.08 HKD</v>
       </c>
       <c r="E122" s="199">
         <f>DCF!F94</f>
@@ -6464,32 +6475,32 @@
       </c>
       <c r="F122" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E94,C$18)</f>
-        <v>0.30020947064812875</v>
-      </c>
-    </row>
-    <row r="124" spans="2:6">
-      <c r="B124" s="461" t="s">
+        <v>0.30048790512722201</v>
+      </c>
+    </row>
+    <row r="124" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="B124" s="463" t="s">
         <v>357</v>
       </c>
-      <c r="C124" s="461"/>
-      <c r="D124" s="461"/>
-      <c r="E124" s="461"/>
-      <c r="F124" s="461"/>
-    </row>
-    <row r="125" spans="2:6">
+      <c r="C124" s="463"/>
+      <c r="D124" s="463"/>
+      <c r="E124" s="463"/>
+      <c r="F124" s="463"/>
+    </row>
+    <row r="125" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B125" s="193" t="s">
         <v>218</v>
       </c>
       <c r="C125" s="197">
         <f>Scenarios!C36</f>
-        <v>60.876921461817851</v>
+        <v>60.439606731746466</v>
       </c>
       <c r="D125" s="194" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="127" spans="2:6" ht="24.5" customHeight="1">
+    <row r="127" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B127" s="465" t="s">
         <v>358</v>
       </c>
@@ -6498,7 +6509,7 @@
       <c r="E127" s="465"/>
       <c r="F127" s="465"/>
     </row>
-    <row r="129" spans="1:6" ht="13.9">
+    <row r="129" spans="1:6" ht="16" x14ac:dyDescent="0.25">
       <c r="A129" s="200" t="s">
         <v>474</v>
       </c>
@@ -6508,30 +6519,30 @@
       <c r="E129" s="34"/>
       <c r="F129" s="34"/>
     </row>
-    <row r="131" spans="1:6">
-      <c r="B131" s="463" t="s">
+    <row r="131" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="B131" s="467" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="463"/>
-      <c r="D131" s="463"/>
-      <c r="E131" s="463"/>
-      <c r="F131" s="463"/>
-    </row>
-    <row r="132" spans="1:6">
-      <c r="B132" s="460" t="s">
+      <c r="C131" s="467"/>
+      <c r="D131" s="467"/>
+      <c r="E131" s="467"/>
+      <c r="F131" s="467"/>
+    </row>
+    <row r="132" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="B132" s="462" t="s">
         <v>359</v>
       </c>
-      <c r="C132" s="460"/>
-      <c r="D132" s="460"/>
-      <c r="E132" s="460"/>
-      <c r="F132" s="460"/>
-    </row>
-    <row r="134" spans="1:6">
+      <c r="C132" s="462"/>
+      <c r="D132" s="462"/>
+      <c r="E132" s="462"/>
+      <c r="F132" s="462"/>
+    </row>
+    <row r="134" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B134" s="192" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="135" spans="1:6">
+    <row r="135" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B135" s="1" t="s">
         <v>221</v>
       </c>
@@ -6540,7 +6551,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="136" spans="1:6">
+    <row r="136" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B136" s="194" t="s">
         <v>220</v>
       </c>
@@ -6553,14 +6564,14 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="138" spans="1:6">
+    <row r="138" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B138" s="192" t="s">
         <v>494</v>
       </c>
       <c r="C138" s="214"/>
       <c r="D138" s="215"/>
     </row>
-    <row r="139" spans="1:6" ht="12.4">
+    <row r="139" spans="1:6" ht="14" x14ac:dyDescent="0.2">
       <c r="B139" s="340" t="s">
         <v>462</v>
       </c>
@@ -6579,7 +6590,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="140" spans="1:6">
+    <row r="140" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B140" s="336" t="s">
         <v>312</v>
       </c>
@@ -6589,18 +6600,18 @@
       </c>
       <c r="D140" s="333">
         <f>Scenarios!D62</f>
-        <v>28.053880857980584</v>
+        <v>27.852353332602064</v>
       </c>
       <c r="E140" s="334">
         <f>Scenarios!E62</f>
-        <v>30.673866004358207</v>
+        <v>30.472338478979687</v>
       </c>
       <c r="F140" s="335">
         <f>E22</f>
         <v>0.29465259038036606</v>
       </c>
     </row>
-    <row r="141" spans="1:6">
+    <row r="141" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B141" s="336" t="s">
         <v>313</v>
       </c>
@@ -6610,25 +6621,25 @@
       </c>
       <c r="D141" s="333">
         <f>Scenarios!D63</f>
-        <v>35.163564743288305</v>
+        <v>34.910964177182088</v>
       </c>
       <c r="E141" s="334">
         <f>Scenarios!E63</f>
-        <v>38.176081802996066</v>
+        <v>37.923481236889849</v>
       </c>
       <c r="F141" s="335">
         <f>Scenarios!F63</f>
         <v>0.20075184365903009</v>
       </c>
     </row>
-    <row r="142" spans="1:6">
+    <row r="142" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B142" s="194"/>
       <c r="C142" s="194"/>
       <c r="D142" s="194"/>
       <c r="E142" s="194"/>
       <c r="F142" s="194"/>
     </row>
-    <row r="143" spans="1:6" ht="12.4">
+    <row r="143" spans="1:6" ht="14" x14ac:dyDescent="0.2">
       <c r="B143" s="340" t="s">
         <v>463</v>
       </c>
@@ -6647,7 +6658,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="144" spans="1:6">
+    <row r="144" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B144" s="336" t="s">
         <v>315</v>
       </c>
@@ -6657,18 +6668,18 @@
       </c>
       <c r="D144" s="333">
         <f>Scenarios!D66</f>
-        <v>43.634166152503838</v>
+        <v>43.320716274706704</v>
       </c>
       <c r="E144" s="334">
         <f>Scenarios!E66</f>
-        <v>47.088536133429045</v>
+        <v>46.775086255631912</v>
       </c>
       <c r="F144" s="335">
         <f>E24</f>
         <v>0.1174</v>
       </c>
     </row>
-    <row r="145" spans="1:6">
+    <row r="145" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B145" s="336" t="s">
         <v>314</v>
       </c>
@@ -6678,18 +6689,18 @@
       </c>
       <c r="D145" s="333">
         <f>Scenarios!D67</f>
-        <v>49.347002750645608</v>
+        <v>48.992514207704659</v>
       </c>
       <c r="E145" s="334">
         <f>Scenarios!E67</f>
-        <v>53.087406825662384</v>
+        <v>52.732918282721435</v>
       </c>
       <c r="F145" s="335">
         <f>Scenarios!F67</f>
         <v>7.2499999999999995E-2</v>
       </c>
     </row>
-    <row r="147" spans="1:6" ht="13.9">
+    <row r="147" spans="1:6" ht="16" x14ac:dyDescent="0.25">
       <c r="A147" s="200" t="s">
         <v>475</v>
       </c>
@@ -6699,21 +6710,21 @@
       <c r="E147" s="34"/>
       <c r="F147" s="34"/>
     </row>
-    <row r="149" spans="1:6">
-      <c r="B149" s="467" t="s">
+    <row r="149" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="B149" s="461" t="s">
         <v>360</v>
       </c>
-      <c r="C149" s="460"/>
-      <c r="D149" s="460"/>
-      <c r="E149" s="460"/>
-      <c r="F149" s="460"/>
-    </row>
-    <row r="151" spans="1:6">
+      <c r="C149" s="462"/>
+      <c r="D149" s="462"/>
+      <c r="E149" s="462"/>
+      <c r="F149" s="462"/>
+    </row>
+    <row r="151" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B151" s="192" t="s">
         <v>289</v>
       </c>
     </row>
-    <row r="152" spans="1:6">
+    <row r="152" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B152" s="464" t="s">
         <v>293</v>
       </c>
@@ -6722,92 +6733,80 @@
       <c r="E152" s="464"/>
       <c r="F152" s="464"/>
     </row>
-    <row r="153" spans="1:6">
+    <row r="153" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B153" s="196" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="154" spans="1:6">
+    <row r="154" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B154" s="196" t="s">
         <v>291</v>
       </c>
     </row>
-    <row r="155" spans="1:6">
+    <row r="155" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B155" s="196" t="s">
         <v>292</v>
       </c>
     </row>
-    <row r="157" spans="1:6">
+    <row r="157" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B157" s="1" t="s">
         <v>296</v>
       </c>
     </row>
-    <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="461" t="s">
+    <row r="158" spans="1:6" ht="34.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B158" s="463" t="s">
         <v>438</v>
       </c>
-      <c r="C158" s="461"/>
-      <c r="D158" s="461"/>
-      <c r="E158" s="461"/>
-      <c r="F158" s="461"/>
-    </row>
-    <row r="160" spans="1:6">
+      <c r="C158" s="463"/>
+      <c r="D158" s="463"/>
+      <c r="E158" s="463"/>
+      <c r="F158" s="463"/>
+    </row>
+    <row r="160" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B160" s="1" t="s">
         <v>297</v>
       </c>
     </row>
-    <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="466" t="s">
+    <row r="161" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B161" s="460" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="466"/>
-      <c r="D161" s="466"/>
-      <c r="E161" s="466"/>
-      <c r="F161" s="466"/>
-    </row>
-    <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="466" t="s">
+      <c r="C161" s="460"/>
+      <c r="D161" s="460"/>
+      <c r="E161" s="460"/>
+      <c r="F161" s="460"/>
+    </row>
+    <row r="162" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B162" s="460" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="466"/>
-      <c r="D162" s="466"/>
-      <c r="E162" s="466"/>
-      <c r="F162" s="466"/>
-    </row>
-    <row r="164" spans="2:6">
+      <c r="C162" s="460"/>
+      <c r="D162" s="460"/>
+      <c r="E162" s="460"/>
+      <c r="F162" s="460"/>
+    </row>
+    <row r="164" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B164" s="1" t="s">
         <v>301</v>
       </c>
     </row>
-    <row r="165" spans="2:6">
+    <row r="165" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B165" s="196" t="s">
         <v>298</v>
       </c>
     </row>
-    <row r="166" spans="2:6">
+    <row r="166" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B166" s="196" t="s">
         <v>299</v>
       </c>
     </row>
-    <row r="167" spans="2:6">
+    <row r="167" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B167" s="196" t="s">
         <v>300</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6824,6 +6823,18 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -6851,15 +6862,15 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:M80"/>
-  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="11.65"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="3" style="1" customWidth="1"/>
     <col min="2" max="2" width="27.33203125" style="1" customWidth="1"/>
     <col min="3" max="13" width="20.6640625" style="1" customWidth="1"/>
-    <col min="14" max="16384" width="8.796875" style="1"/>
+    <col min="14" max="16384" width="8.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:13">
+    <row r="1" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B1" s="87" t="str">
         <f>Thesis!E17</f>
         <v>EUR</v>
@@ -6908,7 +6919,7 @@
         <v>42004</v>
       </c>
     </row>
-    <row r="2" spans="2:13" ht="13.9">
+    <row r="2" spans="2:13" ht="16" x14ac:dyDescent="0.25">
       <c r="B2" s="34" t="s">
         <v>93</v>
       </c>
@@ -6924,7 +6935,7 @@
       <c r="L2" s="35"/>
       <c r="M2" s="35"/>
     </row>
-    <row r="3" spans="2:13">
+    <row r="3" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B3" s="16" t="s">
         <v>25</v>
       </c>
@@ -6932,7 +6943,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="4" spans="2:13">
+    <row r="4" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B4" s="31" t="s">
         <v>0</v>
       </c>
@@ -6952,7 +6963,7 @@
       <c r="L4" s="287"/>
       <c r="M4" s="287"/>
     </row>
-    <row r="5" spans="2:13">
+    <row r="5" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B5" s="38" t="s">
         <v>40</v>
       </c>
@@ -6972,7 +6983,7 @@
       <c r="L5" s="287"/>
       <c r="M5" s="287"/>
     </row>
-    <row r="6" spans="2:13">
+    <row r="6" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B6" s="38" t="s">
         <v>51</v>
       </c>
@@ -6992,7 +7003,7 @@
       <c r="L6" s="287"/>
       <c r="M6" s="287"/>
     </row>
-    <row r="7" spans="2:13">
+    <row r="7" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B7" s="66" t="s">
         <v>58</v>
       </c>
@@ -7008,7 +7019,7 @@
       <c r="L7" s="288"/>
       <c r="M7" s="288"/>
     </row>
-    <row r="8" spans="2:13">
+    <row r="8" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B8" s="38" t="s">
         <v>46</v>
       </c>
@@ -7024,7 +7035,7 @@
       <c r="L8" s="287"/>
       <c r="M8" s="287"/>
     </row>
-    <row r="9" spans="2:13">
+    <row r="9" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B9" s="38" t="s">
         <v>134</v>
       </c>
@@ -7040,7 +7051,7 @@
       <c r="L9" s="287"/>
       <c r="M9" s="287"/>
     </row>
-    <row r="10" spans="2:13">
+    <row r="10" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B10" s="38" t="s">
         <v>138</v>
       </c>
@@ -7060,7 +7071,7 @@
       <c r="L10" s="287"/>
       <c r="M10" s="287"/>
     </row>
-    <row r="11" spans="2:13">
+    <row r="11" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B11" s="38" t="s">
         <v>133</v>
       </c>
@@ -7076,7 +7087,7 @@
       <c r="L11" s="287"/>
       <c r="M11" s="287"/>
     </row>
-    <row r="12" spans="2:13">
+    <row r="12" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B12" s="38" t="s">
         <v>37</v>
       </c>
@@ -7098,7 +7109,7 @@
       <c r="L12" s="287"/>
       <c r="M12" s="287"/>
     </row>
-    <row r="13" spans="2:13">
+    <row r="13" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B13" s="38" t="s">
         <v>64</v>
       </c>
@@ -7114,7 +7125,7 @@
       <c r="L13" s="287"/>
       <c r="M13" s="287"/>
     </row>
-    <row r="14" spans="2:13">
+    <row r="14" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B14" s="38" t="s">
         <v>47</v>
       </c>
@@ -7134,7 +7145,7 @@
       <c r="L14" s="287"/>
       <c r="M14" s="287"/>
     </row>
-    <row r="15" spans="2:13">
+    <row r="15" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B15" s="41" t="s">
         <v>39</v>
       </c>
@@ -7154,7 +7165,7 @@
       <c r="L15" s="289"/>
       <c r="M15" s="289"/>
     </row>
-    <row r="16" spans="2:13">
+    <row r="16" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B16" s="27" t="s">
         <v>41</v>
       </c>
@@ -7174,13 +7185,13 @@
       <c r="L16" s="287"/>
       <c r="M16" s="287"/>
     </row>
-    <row r="18" spans="2:13">
+    <row r="18" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B18" s="16" t="s">
         <v>48</v>
       </c>
       <c r="C18" s="9"/>
     </row>
-    <row r="19" spans="2:13">
+    <row r="19" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B19" s="26" t="s">
         <v>44</v>
       </c>
@@ -7196,7 +7207,7 @@
       <c r="L19" s="287"/>
       <c r="M19" s="287"/>
     </row>
-    <row r="20" spans="2:13">
+    <row r="20" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B20" s="26" t="s">
         <v>50</v>
       </c>
@@ -7212,7 +7223,7 @@
       <c r="L20" s="287"/>
       <c r="M20" s="287"/>
     </row>
-    <row r="21" spans="2:13">
+    <row r="21" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B21" s="26" t="s">
         <v>49</v>
       </c>
@@ -7228,7 +7239,7 @@
       <c r="L21" s="287"/>
       <c r="M21" s="287"/>
     </row>
-    <row r="22" spans="2:13">
+    <row r="22" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B22" s="26" t="s">
         <v>286</v>
       </c>
@@ -7248,7 +7259,7 @@
       <c r="L22" s="287"/>
       <c r="M22" s="287"/>
     </row>
-    <row r="23" spans="2:13">
+    <row r="23" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B23" s="26" t="s">
         <v>288</v>
       </c>
@@ -7268,7 +7279,7 @@
       <c r="L23" s="287"/>
       <c r="M23" s="287"/>
     </row>
-    <row r="24" spans="2:13">
+    <row r="24" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B24" s="26" t="s">
         <v>287</v>
       </c>
@@ -7288,7 +7299,7 @@
       <c r="L24" s="287"/>
       <c r="M24" s="287"/>
     </row>
-    <row r="25" spans="2:13">
+    <row r="25" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B25" s="23" t="str">
         <f>"Dividend per share ("&amp;Market_currency&amp;")"</f>
         <v>Dividend per share (HKD)</v>
@@ -7309,7 +7320,7 @@
       <c r="L25" s="37"/>
       <c r="M25" s="37"/>
     </row>
-    <row r="27" spans="2:13">
+    <row r="27" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B27" s="16" t="s">
         <v>26</v>
       </c>
@@ -7317,7 +7328,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="28" spans="2:13">
+    <row r="28" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B28" s="25" t="s">
         <v>22</v>
       </c>
@@ -7338,7 +7349,7 @@
       <c r="L28" s="287"/>
       <c r="M28" s="287"/>
     </row>
-    <row r="29" spans="2:13">
+    <row r="29" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B29" s="25" t="s">
         <v>30</v>
       </c>
@@ -7359,7 +7370,7 @@
       <c r="L29" s="287"/>
       <c r="M29" s="287"/>
     </row>
-    <row r="30" spans="2:13">
+    <row r="30" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B30" s="28" t="s">
         <v>38</v>
       </c>
@@ -7380,7 +7391,7 @@
       <c r="L30" s="289"/>
       <c r="M30" s="289"/>
     </row>
-    <row r="31" spans="2:13">
+    <row r="31" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B31" s="28" t="s">
         <v>28</v>
       </c>
@@ -7401,7 +7412,7 @@
       <c r="L31" s="289"/>
       <c r="M31" s="289"/>
     </row>
-    <row r="32" spans="2:13">
+    <row r="32" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B32" s="25" t="s">
         <v>143</v>
       </c>
@@ -7422,7 +7433,7 @@
       <c r="L32" s="287"/>
       <c r="M32" s="287"/>
     </row>
-    <row r="34" spans="2:13" ht="13.9">
+    <row r="34" spans="2:13" ht="16" x14ac:dyDescent="0.25">
       <c r="B34" s="34" t="s">
         <v>78</v>
       </c>
@@ -7438,12 +7449,12 @@
       <c r="L34" s="35"/>
       <c r="M34" s="35"/>
     </row>
-    <row r="35" spans="2:13">
+    <row r="35" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B35" s="16" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="36" spans="2:13">
+    <row r="36" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B36" s="31" t="s">
         <v>0</v>
       </c>
@@ -7492,7 +7503,7 @@
         <v/>
       </c>
     </row>
-    <row r="37" spans="2:13">
+    <row r="37" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B37" s="38" t="s">
         <v>40</v>
       </c>
@@ -7541,7 +7552,7 @@
         <v/>
       </c>
     </row>
-    <row r="38" spans="2:13">
+    <row r="38" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B38" s="30" t="s">
         <v>55</v>
       </c>
@@ -7590,7 +7601,7 @@
         <v/>
       </c>
     </row>
-    <row r="39" spans="2:13">
+    <row r="39" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B39" s="38" t="s">
         <v>51</v>
       </c>
@@ -7639,7 +7650,7 @@
         <v/>
       </c>
     </row>
-    <row r="40" spans="2:13">
+    <row r="40" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B40" s="66" t="s">
         <v>58</v>
       </c>
@@ -7688,7 +7699,7 @@
         <v/>
       </c>
     </row>
-    <row r="41" spans="2:13">
+    <row r="41" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B41" s="66" t="s">
         <v>61</v>
       </c>
@@ -7737,7 +7748,7 @@
         <v/>
       </c>
     </row>
-    <row r="42" spans="2:13">
+    <row r="42" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B42" s="38" t="s">
         <v>46</v>
       </c>
@@ -7786,7 +7797,7 @@
         <v/>
       </c>
     </row>
-    <row r="43" spans="2:13">
+    <row r="43" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B43" s="41" t="s">
         <v>127</v>
       </c>
@@ -7835,7 +7846,7 @@
         <v/>
       </c>
     </row>
-    <row r="44" spans="2:13">
+    <row r="44" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B44" s="41" t="s">
         <v>139</v>
       </c>
@@ -7884,7 +7895,7 @@
         <v/>
       </c>
     </row>
-    <row r="45" spans="2:13">
+    <row r="45" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B45" s="38" t="s">
         <v>65</v>
       </c>
@@ -7933,7 +7944,7 @@
         <v/>
       </c>
     </row>
-    <row r="46" spans="2:13">
+    <row r="46" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B46" s="38" t="s">
         <v>47</v>
       </c>
@@ -7982,7 +7993,7 @@
         <v/>
       </c>
     </row>
-    <row r="47" spans="2:13">
+    <row r="47" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B47" s="41" t="s">
         <v>39</v>
       </c>
@@ -8031,7 +8042,7 @@
         <v/>
       </c>
     </row>
-    <row r="48" spans="2:13">
+    <row r="48" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B48" s="27" t="s">
         <v>41</v>
       </c>
@@ -8080,12 +8091,12 @@
         <v/>
       </c>
     </row>
-    <row r="50" spans="2:13">
+    <row r="50" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B50" s="16" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="51" spans="2:13">
+    <row r="51" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B51" s="38" t="s">
         <v>37</v>
       </c>
@@ -8134,7 +8145,7 @@
         <v/>
       </c>
     </row>
-    <row r="52" spans="2:13">
+    <row r="52" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B52" s="38" t="s">
         <v>64</v>
       </c>
@@ -8183,12 +8194,12 @@
         <v/>
       </c>
     </row>
-    <row r="54" spans="2:13">
+    <row r="54" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B54" s="156" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="55" spans="2:13">
+    <row r="55" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B55" s="38" t="s">
         <v>134</v>
       </c>
@@ -8237,7 +8248,7 @@
         <v/>
       </c>
     </row>
-    <row r="56" spans="2:13">
+    <row r="56" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B56" s="38" t="s">
         <v>138</v>
       </c>
@@ -8286,7 +8297,7 @@
         <v/>
       </c>
     </row>
-    <row r="57" spans="2:13">
+    <row r="57" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B57" s="38" t="s">
         <v>133</v>
       </c>
@@ -8335,7 +8346,7 @@
         <v/>
       </c>
     </row>
-    <row r="58" spans="2:13">
+    <row r="58" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B58" s="38" t="s">
         <v>135</v>
       </c>
@@ -8384,13 +8395,13 @@
         <v/>
       </c>
     </row>
-    <row r="60" spans="2:13">
+    <row r="60" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B60" s="16" t="s">
         <v>48</v>
       </c>
       <c r="C60" s="9"/>
     </row>
-    <row r="61" spans="2:13">
+    <row r="61" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B61" s="26" t="s">
         <v>44</v>
       </c>
@@ -8439,7 +8450,7 @@
         <v/>
       </c>
     </row>
-    <row r="62" spans="2:13">
+    <row r="62" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B62" s="26" t="s">
         <v>50</v>
       </c>
@@ -8488,7 +8499,7 @@
         <v/>
       </c>
     </row>
-    <row r="63" spans="2:13">
+    <row r="63" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B63" s="26" t="s">
         <v>49</v>
       </c>
@@ -8537,7 +8548,7 @@
         <v/>
       </c>
     </row>
-    <row r="64" spans="2:13">
+    <row r="64" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B64" s="26" t="s">
         <v>305</v>
       </c>
@@ -8586,7 +8597,7 @@
         <v/>
       </c>
     </row>
-    <row r="65" spans="2:13">
+    <row r="65" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B65" s="23" t="s">
         <v>34</v>
       </c>
@@ -8635,12 +8646,12 @@
         <v/>
       </c>
     </row>
-    <row r="67" spans="2:13">
+    <row r="67" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B67" s="88" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="68" spans="2:13">
+    <row r="68" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B68" s="1" t="str">
         <f>B36</f>
         <v>Sales</v>
@@ -8690,7 +8701,7 @@
         <v/>
       </c>
     </row>
-    <row r="69" spans="2:13">
+    <row r="69" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B69" s="30" t="s">
         <v>55</v>
       </c>
@@ -8739,7 +8750,7 @@
         <v/>
       </c>
     </row>
-    <row r="70" spans="2:13">
+    <row r="70" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B70" s="77" t="str">
         <f>B43</f>
         <v>Operating EBIT</v>
@@ -8789,7 +8800,7 @@
         <v/>
       </c>
     </row>
-    <row r="71" spans="2:13">
+    <row r="71" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B71" s="41" t="s">
         <v>139</v>
       </c>
@@ -8838,7 +8849,7 @@
         <v/>
       </c>
     </row>
-    <row r="72" spans="2:13">
+    <row r="72" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B72" s="77" t="str">
         <f>B47</f>
         <v>Reported Net Income</v>
@@ -8888,7 +8899,7 @@
         <v/>
       </c>
     </row>
-    <row r="74" spans="2:13" ht="13.9">
+    <row r="74" spans="2:13" ht="16" x14ac:dyDescent="0.25">
       <c r="B74" s="34" t="s">
         <v>79</v>
       </c>
@@ -8904,13 +8915,13 @@
       <c r="L74" s="35"/>
       <c r="M74" s="35"/>
     </row>
-    <row r="75" spans="2:13">
+    <row r="75" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B75" s="16" t="s">
         <v>26</v>
       </c>
       <c r="C75" s="9"/>
     </row>
-    <row r="76" spans="2:13">
+    <row r="76" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B76" s="25" t="s">
         <v>1</v>
       </c>
@@ -8959,7 +8970,7 @@
         <v/>
       </c>
     </row>
-    <row r="77" spans="2:13">
+    <row r="77" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B77" s="90" t="s">
         <v>82</v>
       </c>
@@ -8993,7 +9004,7 @@
       <c r="L77" s="291"/>
       <c r="M77" s="291"/>
     </row>
-    <row r="78" spans="2:13">
+    <row r="78" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B78" s="90" t="s">
         <v>83</v>
       </c>
@@ -9027,7 +9038,7 @@
       <c r="L78" s="291"/>
       <c r="M78" s="291"/>
     </row>
-    <row r="79" spans="2:13">
+    <row r="79" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B79" s="25" t="s">
         <v>38</v>
       </c>
@@ -9076,7 +9087,7 @@
         <v/>
       </c>
     </row>
-    <row r="80" spans="2:13">
+    <row r="80" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B80" s="25" t="s">
         <v>28</v>
       </c>
@@ -9157,7 +9168,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:H89"/>
-  <sheetFormatPr defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="2.33203125" style="1" customWidth="1"/>
     <col min="2" max="2" width="34" style="1" bestFit="1" customWidth="1"/>
@@ -9168,7 +9179,7 @@
     <col min="9" max="16384" width="12.33203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:8" ht="15" customHeight="1">
+    <row r="1" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B1" s="17" t="s">
         <v>35</v>
       </c>
@@ -9184,7 +9195,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="2" spans="2:8" ht="15" customHeight="1">
+    <row r="2" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B2" s="76" t="s">
         <v>131</v>
       </c>
@@ -9195,7 +9206,7 @@
       <c r="G2" s="35"/>
       <c r="H2" s="35"/>
     </row>
-    <row r="3" spans="2:8" ht="15" customHeight="1">
+    <row r="3" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B3" s="16" t="s">
         <v>154</v>
       </c>
@@ -9215,7 +9226,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="4" spans="2:8" ht="15" customHeight="1">
+    <row r="4" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B4" s="4" t="s">
         <v>22</v>
       </c>
@@ -9237,7 +9248,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="5" spans="2:8" ht="15" customHeight="1">
+    <row r="5" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B5" s="1" t="s">
         <v>31</v>
       </c>
@@ -9258,7 +9269,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="6" spans="2:8" ht="15" customHeight="1">
+    <row r="6" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B6" s="4" t="s">
         <v>8</v>
       </c>
@@ -9279,7 +9290,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="7" spans="2:8" ht="15" customHeight="1">
+    <row r="7" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B7" s="1" t="s">
         <v>66</v>
       </c>
@@ -9300,7 +9311,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="8" spans="2:8" ht="15" customHeight="1">
+    <row r="8" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B8" s="1" t="s">
         <v>144</v>
       </c>
@@ -9321,7 +9332,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="9" spans="2:8" ht="15" customHeight="1">
+    <row r="9" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B9" s="4" t="s">
         <v>23</v>
       </c>
@@ -9342,7 +9353,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="10" spans="2:8" ht="15" customHeight="1">
+    <row r="10" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B10" s="4" t="s">
         <v>9</v>
       </c>
@@ -9362,7 +9373,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="11" spans="2:8" ht="15" customHeight="1">
+    <row r="11" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B11" s="4" t="s">
         <v>10</v>
       </c>
@@ -9374,7 +9385,7 @@
       </c>
       <c r="H11" s="232"/>
     </row>
-    <row r="12" spans="2:8" ht="15" customHeight="1">
+    <row r="12" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B12" s="77" t="s">
         <v>69</v>
       </c>
@@ -9398,12 +9409,12 @@
         <v>567828</v>
       </c>
     </row>
-    <row r="13" spans="2:8" ht="15" customHeight="1">
+    <row r="13" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F13" s="77"/>
       <c r="G13" s="78"/>
       <c r="H13" s="19"/>
     </row>
-    <row r="14" spans="2:8" ht="15" customHeight="1">
+    <row r="14" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B14" s="16" t="s">
         <v>153</v>
       </c>
@@ -9423,7 +9434,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="15" spans="2:8" ht="15" customHeight="1">
+    <row r="15" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B15" s="4" t="s">
         <v>329</v>
       </c>
@@ -9443,7 +9454,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="16" spans="2:8" ht="15" customHeight="1">
+    <row r="16" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B16" s="1" t="s">
         <v>32</v>
       </c>
@@ -9463,7 +9474,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="17" spans="2:8" ht="15" customHeight="1">
+    <row r="17" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B17" s="1" t="s">
         <v>66</v>
       </c>
@@ -9483,7 +9494,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="18" spans="2:8" ht="15" customHeight="1">
+    <row r="18" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B18" s="4" t="s">
         <v>144</v>
       </c>
@@ -9503,7 +9514,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="19" spans="2:8" ht="15" customHeight="1">
+    <row r="19" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B19" s="4" t="s">
         <v>24</v>
       </c>
@@ -9524,7 +9535,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="20" spans="2:8" ht="15" customHeight="1">
+    <row r="20" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B20" s="4" t="s">
         <v>16</v>
       </c>
@@ -9544,7 +9555,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="21" spans="2:8" ht="15" customHeight="1">
+    <row r="21" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B21" s="4" t="s">
         <v>17</v>
       </c>
@@ -9564,7 +9575,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="22" spans="2:8" ht="15" customHeight="1">
+    <row r="22" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B22" s="4" t="s">
         <v>18</v>
       </c>
@@ -9576,7 +9587,7 @@
       </c>
       <c r="H22" s="232"/>
     </row>
-    <row r="23" spans="2:8" ht="15" customHeight="1">
+    <row r="23" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B23" s="4" t="s">
         <v>19</v>
       </c>
@@ -9588,7 +9599,7 @@
       </c>
       <c r="H23" s="232"/>
     </row>
-    <row r="24" spans="2:8" ht="15" customHeight="1">
+    <row r="24" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B24" s="77" t="s">
         <v>70</v>
       </c>
@@ -9612,7 +9623,7 @@
         <v>6982.2</v>
       </c>
     </row>
-    <row r="26" spans="2:8" ht="15" customHeight="1">
+    <row r="26" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B26" s="16" t="s">
         <v>169</v>
       </c>
@@ -9629,7 +9640,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="27" spans="2:8" ht="15" customHeight="1">
+    <row r="27" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B27" s="4" t="s">
         <v>3</v>
       </c>
@@ -9648,7 +9659,7 @@
         <v>-1727228.2000000002</v>
       </c>
     </row>
-    <row r="28" spans="2:8" ht="15" customHeight="1">
+    <row r="28" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B28" s="4" t="s">
         <v>4</v>
       </c>
@@ -9663,7 +9674,7 @@
       </c>
       <c r="H28" s="170"/>
     </row>
-    <row r="29" spans="2:8" ht="15" customHeight="1">
+    <row r="29" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B29" s="4" t="s">
         <v>5</v>
       </c>
@@ -9682,7 +9693,7 @@
         <v>-1746881.2000000002</v>
       </c>
     </row>
-    <row r="30" spans="2:8" ht="15" customHeight="1">
+    <row r="30" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B30" s="2" t="s">
         <v>6</v>
       </c>
@@ -9698,7 +9709,7 @@
       </c>
       <c r="H30" s="170"/>
     </row>
-    <row r="31" spans="2:8" ht="15" customHeight="1">
+    <row r="31" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B31" s="77" t="s">
         <v>172</v>
       </c>
@@ -9715,7 +9726,7 @@
       </c>
       <c r="H31" s="170"/>
     </row>
-    <row r="32" spans="2:8" ht="15" customHeight="1">
+    <row r="32" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B32" s="4" t="s">
         <v>7</v>
       </c>
@@ -9735,7 +9746,7 @@
         <v>2350458.7999999998</v>
       </c>
     </row>
-    <row r="33" spans="2:8" ht="15" customHeight="1">
+    <row r="33" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B33" s="80" t="s">
         <v>2</v>
       </c>
@@ -9746,7 +9757,7 @@
       <c r="G33" s="2"/>
       <c r="H33" s="177"/>
     </row>
-    <row r="34" spans="2:8" ht="15" customHeight="1">
+    <row r="34" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B34" s="80"/>
       <c r="C34" s="81"/>
       <c r="F34" s="178" t="s">
@@ -9759,7 +9770,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="35" spans="2:8" ht="15" customHeight="1">
+    <row r="35" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B35" s="16" t="s">
         <v>170</v>
       </c>
@@ -9778,7 +9789,7 @@
         <v>1775648.5999999999</v>
       </c>
     </row>
-    <row r="36" spans="2:8" ht="15" customHeight="1">
+    <row r="36" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B36" s="4" t="s">
         <v>11</v>
       </c>
@@ -9794,7 +9805,7 @@
       </c>
       <c r="H36" s="177"/>
     </row>
-    <row r="37" spans="2:8" ht="15" customHeight="1">
+    <row r="37" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B37" s="4" t="s">
         <v>12</v>
       </c>
@@ -9810,7 +9821,7 @@
       </c>
       <c r="H37" s="177"/>
     </row>
-    <row r="38" spans="2:8" ht="15" customHeight="1">
+    <row r="38" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B38" s="4" t="s">
         <v>13</v>
       </c>
@@ -9826,7 +9837,7 @@
       </c>
       <c r="H38" s="177"/>
     </row>
-    <row r="39" spans="2:8" ht="15" customHeight="1">
+    <row r="39" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B39" s="2" t="s">
         <v>14</v>
       </c>
@@ -9845,7 +9856,7 @@
         <v>468045.5</v>
       </c>
     </row>
-    <row r="40" spans="2:8" ht="15" customHeight="1">
+    <row r="40" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B40" s="77" t="s">
         <v>173</v>
       </c>
@@ -9865,7 +9876,7 @@
         <v>574810.19999999995</v>
       </c>
     </row>
-    <row r="41" spans="2:8" ht="15" customHeight="1">
+    <row r="41" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B41" s="4" t="s">
         <v>15</v>
       </c>
@@ -9885,7 +9896,7 @@
         <v>538192.79999999993</v>
       </c>
     </row>
-    <row r="42" spans="2:8" ht="15" customHeight="1">
+    <row r="42" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B42" s="80" t="s">
         <v>20</v>
       </c>
@@ -9904,7 +9915,7 @@
         <v>36617.399999999994</v>
       </c>
     </row>
-    <row r="44" spans="2:8" ht="15" customHeight="1">
+    <row r="44" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B44" s="76" t="s">
         <v>92</v>
       </c>
@@ -9915,7 +9926,7 @@
       <c r="G44" s="35"/>
       <c r="H44" s="35"/>
     </row>
-    <row r="45" spans="2:8" ht="15" customHeight="1">
+    <row r="45" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B45" s="16" t="s">
         <v>228</v>
       </c>
@@ -9929,7 +9940,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="46" spans="2:8" ht="15" customHeight="1">
+    <row r="46" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B46" s="1" t="s">
         <v>230</v>
       </c>
@@ -9943,25 +9954,25 @@
       </c>
       <c r="F46" s="223"/>
     </row>
-    <row r="47" spans="2:8" ht="15" customHeight="1">
+    <row r="47" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B47" s="1" t="str">
         <f>"Equity per share ("&amp;Market_currency&amp;")"</f>
         <v>Equity per share (HKD)</v>
       </c>
       <c r="C47" s="134">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>15.317542784021358</v>
+        <v>15.207507865580999</v>
       </c>
       <c r="D47" s="134">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>-6.333420164937916</v>
+        <v>-6.2879234830533743</v>
       </c>
       <c r="F47" s="223"/>
     </row>
-    <row r="48" spans="2:8" ht="15" customHeight="1">
+    <row r="48" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F48" s="223"/>
     </row>
-    <row r="49" spans="2:8" ht="15" customHeight="1">
+    <row r="49" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B49" s="143" t="s">
         <v>120</v>
       </c>
@@ -9974,7 +9985,7 @@
       <c r="E49" s="2"/>
       <c r="F49" s="223"/>
     </row>
-    <row r="50" spans="2:8" ht="15" customHeight="1">
+    <row r="50" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B50" s="8" t="s">
         <v>90</v>
       </c>
@@ -9988,7 +9999,7 @@
       </c>
       <c r="F50" s="223"/>
     </row>
-    <row r="51" spans="2:8" ht="15" customHeight="1">
+    <row r="51" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B51" s="1" t="s">
         <v>146</v>
       </c>
@@ -9999,10 +10010,10 @@
       </c>
       <c r="F51" s="223"/>
     </row>
-    <row r="52" spans="2:8" ht="15" customHeight="1">
+    <row r="52" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F52" s="223"/>
     </row>
-    <row r="53" spans="2:8" ht="15" customHeight="1">
+    <row r="53" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B53" s="143" t="s">
         <v>119</v>
       </c>
@@ -10014,7 +10025,7 @@
       </c>
       <c r="F53" s="223"/>
     </row>
-    <row r="54" spans="2:8" ht="15" customHeight="1">
+    <row r="54" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B54" s="1" t="s">
         <v>116</v>
       </c>
@@ -10028,7 +10039,7 @@
       </c>
       <c r="F54" s="223"/>
     </row>
-    <row r="55" spans="2:8" ht="15" customHeight="1">
+    <row r="55" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B55" s="1" t="s">
         <v>118</v>
       </c>
@@ -10042,10 +10053,10 @@
       </c>
       <c r="F55" s="223"/>
     </row>
-    <row r="56" spans="2:8" ht="15" customHeight="1">
+    <row r="56" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F56" s="223"/>
     </row>
-    <row r="57" spans="2:8" ht="15" customHeight="1">
+    <row r="57" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B57" s="143" t="s">
         <v>145</v>
       </c>
@@ -10057,7 +10068,7 @@
       </c>
       <c r="F57" s="223"/>
     </row>
-    <row r="58" spans="2:8" ht="15" customHeight="1">
+    <row r="58" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B58" s="2" t="s">
         <v>86</v>
       </c>
@@ -10068,7 +10079,7 @@
       </c>
       <c r="F58" s="5"/>
     </row>
-    <row r="59" spans="2:8" ht="15" customHeight="1">
+    <row r="59" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B59" s="1" t="s">
         <v>89</v>
       </c>
@@ -10079,10 +10090,10 @@
       </c>
       <c r="F59" s="223"/>
     </row>
-    <row r="60" spans="2:8" ht="15" customHeight="1">
+    <row r="60" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F60" s="223"/>
     </row>
-    <row r="61" spans="2:8" ht="15" customHeight="1">
+    <row r="61" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B61" s="143" t="s">
         <v>231</v>
       </c>
@@ -10094,7 +10105,7 @@
       </c>
       <c r="F61" s="223"/>
     </row>
-    <row r="62" spans="2:8" ht="15" customHeight="1">
+    <row r="62" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B62" s="1" t="s">
         <v>210</v>
       </c>
@@ -10110,7 +10121,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="64" spans="2:8" ht="15" customHeight="1">
+    <row r="64" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B64" s="76" t="s">
         <v>162</v>
       </c>
@@ -10121,7 +10132,7 @@
       <c r="G64" s="35"/>
       <c r="H64" s="35"/>
     </row>
-    <row r="65" spans="2:6" ht="15" customHeight="1">
+    <row r="65" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B65" s="16" t="s">
         <v>158</v>
       </c>
@@ -10135,7 +10146,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="66" spans="2:6" ht="15" customHeight="1">
+    <row r="66" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B66" s="102" t="s">
         <v>157</v>
       </c>
@@ -10151,7 +10162,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="67" spans="2:6" ht="15" customHeight="1">
+    <row r="67" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B67" s="102" t="s">
         <v>147</v>
       </c>
@@ -10161,7 +10172,7 @@
       </c>
       <c r="F67" s="223"/>
     </row>
-    <row r="68" spans="2:6" ht="15" customHeight="1">
+    <row r="68" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B68" s="102" t="s">
         <v>151</v>
       </c>
@@ -10171,7 +10182,7 @@
       </c>
       <c r="F68" s="223"/>
     </row>
-    <row r="69" spans="2:6" ht="15" customHeight="1">
+    <row r="69" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B69" s="102" t="s">
         <v>149</v>
       </c>
@@ -10181,7 +10192,7 @@
       </c>
       <c r="F69" s="223"/>
     </row>
-    <row r="70" spans="2:6" ht="15" customHeight="1">
+    <row r="70" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B70" s="77" t="s">
         <v>158</v>
       </c>
@@ -10191,10 +10202,10 @@
       </c>
       <c r="F70" s="223"/>
     </row>
-    <row r="71" spans="2:6" ht="15" customHeight="1">
+    <row r="71" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F71" s="223"/>
     </row>
-    <row r="72" spans="2:6" ht="15" customHeight="1">
+    <row r="72" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B72" s="225" t="s">
         <v>256</v>
       </c>
@@ -10206,7 +10217,7 @@
       </c>
       <c r="F72" s="223"/>
     </row>
-    <row r="73" spans="2:6" ht="15" customHeight="1">
+    <row r="73" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B73" s="102" t="s">
         <v>255</v>
       </c>
@@ -10222,7 +10233,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="74" spans="2:6" ht="15" customHeight="1">
+    <row r="74" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B74" s="227" t="s">
         <v>259</v>
       </c>
@@ -10238,7 +10249,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="75" spans="2:6" ht="15" customHeight="1">
+    <row r="75" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B75" s="77" t="s">
         <v>258</v>
       </c>
@@ -10251,7 +10262,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="76" spans="2:6" ht="15" customHeight="1">
+    <row r="76" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B76" s="229" t="s">
         <v>260</v>
       </c>
@@ -10264,10 +10275,10 @@
         <v>261</v>
       </c>
     </row>
-    <row r="77" spans="2:6" ht="15" customHeight="1">
+    <row r="77" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F77" s="223"/>
     </row>
-    <row r="78" spans="2:6" ht="15" customHeight="1">
+    <row r="78" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B78" s="16" t="s">
         <v>159</v>
       </c>
@@ -10279,7 +10290,7 @@
       </c>
       <c r="F78" s="223"/>
     </row>
-    <row r="79" spans="2:6" ht="15" customHeight="1">
+    <row r="79" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B79" s="102" t="s">
         <v>148</v>
       </c>
@@ -10293,7 +10304,7 @@
       </c>
       <c r="F79" s="223"/>
     </row>
-    <row r="80" spans="2:6" ht="15" customHeight="1">
+    <row r="80" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B80" s="102" t="s">
         <v>152</v>
       </c>
@@ -10307,7 +10318,7 @@
       </c>
       <c r="F80" s="223"/>
     </row>
-    <row r="81" spans="2:8" ht="15" customHeight="1">
+    <row r="81" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B81" s="102" t="s">
         <v>150</v>
       </c>
@@ -10321,7 +10332,7 @@
       </c>
       <c r="F81" s="223"/>
     </row>
-    <row r="82" spans="2:8" ht="15" customHeight="1">
+    <row r="82" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B82" s="77" t="s">
         <v>159</v>
       </c>
@@ -10335,7 +10346,7 @@
       </c>
       <c r="F82" s="223"/>
     </row>
-    <row r="84" spans="2:8" ht="15" customHeight="1">
+    <row r="84" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B84" s="76" t="s">
         <v>241</v>
       </c>
@@ -10346,7 +10357,7 @@
       <c r="G84" s="35"/>
       <c r="H84" s="35"/>
     </row>
-    <row r="85" spans="2:8" ht="15" customHeight="1">
+    <row r="85" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B85" s="16" t="s">
         <v>242</v>
       </c>
@@ -10354,68 +10365,68 @@
         <v>243</v>
       </c>
     </row>
-    <row r="86" spans="2:8" ht="15" customHeight="1">
+    <row r="86" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B86" s="212" t="s">
         <v>239</v>
       </c>
       <c r="C86" s="73">
         <f>DCF!F4*Exchange_Rate</f>
-        <v>-26494334.733791724</v>
+        <v>-26304010.34543059</v>
       </c>
       <c r="D86" s="201">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>-10.354105922795677</v>
+        <v>-10.279726290448499</v>
       </c>
       <c r="E86" s="214" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="87" spans="2:8" ht="15" customHeight="1">
+    <row r="87" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B87" s="212" t="s">
         <v>240</v>
       </c>
       <c r="C87" s="73">
         <f>DCF!F5*Exchange_Rate</f>
-        <v>-482176.5381387439</v>
+        <v>-478712.7804854408</v>
       </c>
       <c r="D87" s="201">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>-0.18843677335320597</v>
+        <v>-0.1870831211859201</v>
       </c>
       <c r="E87" s="214" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="88" spans="2:8" ht="15" customHeight="1">
+    <row r="88" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B88" s="213" t="s">
         <v>159</v>
       </c>
       <c r="C88" s="73">
         <f>DCF!F6*Exchange_Rate</f>
-        <v>339705.71181801136</v>
+        <v>337265.40590075863</v>
       </c>
       <c r="D88" s="201">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>0.13275852962845874</v>
+        <v>0.13180484703158898</v>
       </c>
       <c r="E88" s="214" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="89" spans="2:8" ht="15" customHeight="1">
+    <row r="89" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B89" s="77" t="s">
         <v>244</v>
       </c>
       <c r="C89" s="162">
         <f>SUM(C86:C88)</f>
-        <v>-26636805.560112458</v>
+        <v>-26445457.720015272</v>
       </c>
       <c r="D89" s="216">
         <f>SUM(D86:D88)</f>
-        <v>-10.409784166520424</v>
+        <v>-10.33500456460283</v>
       </c>
       <c r="E89" s="214" t="str">
         <f>Market_currency</f>
@@ -10441,19 +10452,19 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:Q807"/>
-  <sheetFormatPr defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="1.33203125" style="2" customWidth="1"/>
     <col min="2" max="2" width="26.33203125" style="2" customWidth="1"/>
     <col min="3" max="3" width="20.6640625" style="2" customWidth="1"/>
     <col min="4" max="4" width="2.6640625" style="2" customWidth="1"/>
-    <col min="5" max="5" width="25.1328125" style="2" customWidth="1"/>
+    <col min="5" max="5" width="25.1640625" style="2" customWidth="1"/>
     <col min="6" max="6" width="2.6640625" style="2" customWidth="1"/>
     <col min="7" max="17" width="20.6640625" style="2" customWidth="1"/>
     <col min="18" max="16384" width="12.33203125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="15.75" customHeight="1">
+    <row r="1" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="3"/>
       <c r="B1" s="87" t="str">
         <f>Thesis!E17</f>
@@ -10510,7 +10521,7 @@
         <v>42004</v>
       </c>
     </row>
-    <row r="2" spans="1:17" ht="15.75" customHeight="1">
+    <row r="2" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="51" t="s">
         <v>95</v>
@@ -10533,7 +10544,7 @@
       <c r="P2" s="35"/>
       <c r="Q2" s="35"/>
     </row>
-    <row r="3" spans="1:17" ht="15.75" customHeight="1">
+    <row r="3" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="10"/>
       <c r="B3" s="16" t="s">
         <v>393</v>
@@ -10553,7 +10564,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="4" spans="1:17" ht="15.75" customHeight="1">
+    <row r="4" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="10"/>
       <c r="B4" s="25" t="s">
         <v>0</v>
@@ -10610,7 +10621,7 @@
         <v/>
       </c>
     </row>
-    <row r="5" spans="1:17" ht="15.75" customHeight="1">
+    <row r="5" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="10"/>
       <c r="B5" s="2" t="s">
         <v>43</v>
@@ -10665,7 +10676,7 @@
         <v/>
       </c>
     </row>
-    <row r="6" spans="1:17" ht="15.75" customHeight="1">
+    <row r="6" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="10"/>
       <c r="B6" s="30" t="s">
         <v>45</v>
@@ -10720,7 +10731,7 @@
         <v/>
       </c>
     </row>
-    <row r="7" spans="1:17" ht="15.75" customHeight="1">
+    <row r="7" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="10"/>
       <c r="B7" s="8" t="s">
         <v>42</v>
@@ -10775,7 +10786,7 @@
         <v/>
       </c>
     </row>
-    <row r="8" spans="1:17" ht="15.75" customHeight="1">
+    <row r="8" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="10"/>
       <c r="B8" s="28" t="s">
         <v>127</v>
@@ -10832,7 +10843,7 @@
         <v/>
       </c>
     </row>
-    <row r="9" spans="1:17" ht="15.75" customHeight="1">
+    <row r="9" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="10"/>
       <c r="B9" s="26" t="s">
         <v>415</v>
@@ -10889,7 +10900,7 @@
         <v/>
       </c>
     </row>
-    <row r="10" spans="1:17" ht="15.75" customHeight="1">
+    <row r="10" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="10"/>
       <c r="B10" s="2" t="s">
         <v>65</v>
@@ -10944,7 +10955,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" spans="1:17" ht="15.75" customHeight="1">
+    <row r="11" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="10"/>
       <c r="B11" s="67" t="s">
         <v>137</v>
@@ -10999,7 +11010,7 @@
         <v/>
       </c>
     </row>
-    <row r="12" spans="1:17" ht="15.75" customHeight="1">
+    <row r="12" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="10"/>
       <c r="B12" s="2" t="s">
         <v>60</v>
@@ -11054,7 +11065,7 @@
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:17" ht="15.75" customHeight="1">
+    <row r="13" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="10"/>
       <c r="B13" s="38" t="s">
         <v>208</v>
@@ -11111,7 +11122,7 @@
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:17" ht="15.75" customHeight="1">
+    <row r="14" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="10"/>
       <c r="B14" s="39" t="s">
         <v>129</v>
@@ -11168,7 +11179,7 @@
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:17" ht="15.75" customHeight="1">
+    <row r="15" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="10"/>
       <c r="B15" s="2" t="s">
         <v>62</v>
@@ -11223,7 +11234,7 @@
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:17" ht="15.75" customHeight="1">
+    <row r="16" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="10"/>
       <c r="B16" s="2" t="s">
         <v>398</v>
@@ -11278,7 +11289,7 @@
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:17" ht="15.75" customHeight="1">
+    <row r="17" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="10"/>
       <c r="B17" s="26" t="s">
         <v>49</v>
@@ -11304,7 +11315,7 @@
       <c r="P17" s="272"/>
       <c r="Q17" s="272"/>
     </row>
-    <row r="18" spans="1:17" ht="15.75" customHeight="1">
+    <row r="18" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="10"/>
       <c r="B18" s="26" t="s">
         <v>94</v>
@@ -11329,7 +11340,7 @@
       <c r="P18" s="273"/>
       <c r="Q18" s="273"/>
     </row>
-    <row r="19" spans="1:17" ht="15.75" customHeight="1">
+    <row r="19" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="10"/>
       <c r="B19" s="30" t="s">
         <v>63</v>
@@ -11386,7 +11397,7 @@
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:17" ht="15.75" customHeight="1">
+    <row r="20" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="10"/>
       <c r="B20" s="26"/>
       <c r="C20" s="59"/>
@@ -11405,7 +11416,7 @@
       <c r="P20" s="12"/>
       <c r="Q20" s="12"/>
     </row>
-    <row r="21" spans="1:17" ht="15.75" customHeight="1">
+    <row r="21" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="10"/>
       <c r="B21" s="51" t="s">
         <v>174</v>
@@ -11428,7 +11439,7 @@
       <c r="P21" s="35"/>
       <c r="Q21" s="35"/>
     </row>
-    <row r="22" spans="1:17" ht="15.75" customHeight="1">
+    <row r="22" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="10"/>
       <c r="B22" s="61" t="s">
         <v>43</v>
@@ -11449,7 +11460,7 @@
       <c r="P22" s="12"/>
       <c r="Q22" s="12"/>
     </row>
-    <row r="23" spans="1:17" ht="15.75" customHeight="1">
+    <row r="23" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="10"/>
       <c r="B23" s="26" t="s">
         <v>40</v>
@@ -11506,7 +11517,7 @@
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:17" ht="15.75" customHeight="1">
+    <row r="24" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="10"/>
       <c r="B24" s="65" t="s">
         <v>59</v>
@@ -11563,7 +11574,7 @@
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:17" ht="15.75" customHeight="1">
+    <row r="25" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="10"/>
       <c r="B25" s="26" t="s">
         <v>46</v>
@@ -11620,7 +11631,7 @@
         <v/>
       </c>
     </row>
-    <row r="26" spans="1:17" ht="15.75" customHeight="1">
+    <row r="26" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" s="10"/>
       <c r="B26" s="67" t="s">
         <v>43</v>
@@ -11677,18 +11688,18 @@
         <v/>
       </c>
     </row>
-    <row r="27" spans="1:17" ht="15.75" customHeight="1">
+    <row r="27" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A27" s="10"/>
       <c r="E27" s="237"/>
     </row>
-    <row r="28" spans="1:17" ht="15.75" customHeight="1">
+    <row r="28" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="10"/>
       <c r="B28" s="61" t="s">
         <v>175</v>
       </c>
       <c r="E28" s="237"/>
     </row>
-    <row r="29" spans="1:17" ht="15.75" customHeight="1">
+    <row r="29" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A29" s="10"/>
       <c r="B29" s="25" t="s">
         <v>40</v>
@@ -11745,7 +11756,7 @@
         <v/>
       </c>
     </row>
-    <row r="30" spans="1:17" ht="15.75" customHeight="1">
+    <row r="30" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="10"/>
       <c r="B30" s="65" t="str">
         <f>B24</f>
@@ -11803,7 +11814,7 @@
         <v/>
       </c>
     </row>
-    <row r="31" spans="1:17" ht="15.75" customHeight="1">
+    <row r="31" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="10"/>
       <c r="B31" s="26" t="str">
         <f>B25</f>
@@ -11860,7 +11871,7 @@
         <v/>
       </c>
     </row>
-    <row r="32" spans="1:17" ht="15.75" customHeight="1">
+    <row r="32" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="10"/>
       <c r="B32" s="67" t="s">
         <v>43</v>
@@ -11915,18 +11926,18 @@
         <v/>
       </c>
     </row>
-    <row r="33" spans="1:17" ht="15.75" customHeight="1">
+    <row r="33" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="10"/>
       <c r="E33" s="237"/>
     </row>
-    <row r="34" spans="1:17" ht="15.75" customHeight="1">
+    <row r="34" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A34" s="10"/>
       <c r="B34" s="61" t="s">
         <v>42</v>
       </c>
       <c r="E34" s="237"/>
     </row>
-    <row r="35" spans="1:17" ht="15.75" customHeight="1">
+    <row r="35" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A35" s="10"/>
       <c r="B35" s="298" t="s">
         <v>396</v>
@@ -11983,18 +11994,18 @@
         <v/>
       </c>
     </row>
-    <row r="36" spans="1:17" ht="15.75" customHeight="1">
+    <row r="36" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A36" s="10"/>
       <c r="E36" s="237"/>
     </row>
-    <row r="37" spans="1:17" ht="15.75" customHeight="1">
+    <row r="37" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A37" s="10"/>
       <c r="B37" s="61" t="s">
         <v>176</v>
       </c>
       <c r="E37" s="237"/>
     </row>
-    <row r="38" spans="1:17" ht="15.75" customHeight="1">
+    <row r="38" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A38" s="10"/>
       <c r="B38" s="298" t="s">
         <v>396</v>
@@ -12049,18 +12060,18 @@
         <v/>
       </c>
     </row>
-    <row r="39" spans="1:17" ht="15.75" customHeight="1">
+    <row r="39" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A39" s="10"/>
       <c r="E39" s="237"/>
     </row>
-    <row r="40" spans="1:17" ht="15.75" customHeight="1">
+    <row r="40" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A40" s="10"/>
       <c r="B40" s="61" t="s">
         <v>177</v>
       </c>
       <c r="E40" s="237"/>
     </row>
-    <row r="41" spans="1:17" ht="15.75" customHeight="1">
+    <row r="41" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A41" s="10"/>
       <c r="B41" s="26" t="s">
         <v>142</v>
@@ -12118,10 +12129,10 @@
         <v/>
       </c>
     </row>
-    <row r="42" spans="1:17" ht="15.75" customHeight="1">
+    <row r="42" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A42" s="10"/>
     </row>
-    <row r="43" spans="1:17" ht="15.75" customHeight="1">
+    <row r="43" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="10"/>
       <c r="B43" s="51" t="s">
         <v>178</v>
@@ -12144,14 +12155,14 @@
       <c r="P43" s="35"/>
       <c r="Q43" s="35"/>
     </row>
-    <row r="44" spans="1:17" ht="15.75" customHeight="1">
+    <row r="44" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A44" s="10"/>
       <c r="B44" s="61" t="s">
         <v>57</v>
       </c>
       <c r="E44" s="237"/>
     </row>
-    <row r="45" spans="1:17" ht="15.75" customHeight="1">
+    <row r="45" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A45" s="10"/>
       <c r="B45" s="2" t="s">
         <v>37</v>
@@ -12206,7 +12217,7 @@
         <v/>
       </c>
     </row>
-    <row r="46" spans="1:17" ht="15.75" customHeight="1">
+    <row r="46" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A46" s="10"/>
       <c r="B46" s="2" t="s">
         <v>272</v>
@@ -12261,7 +12272,7 @@
         <v/>
       </c>
     </row>
-    <row r="47" spans="1:17" ht="15.75" customHeight="1">
+    <row r="47" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A47" s="10"/>
       <c r="B47" s="245" t="s">
         <v>269</v>
@@ -12318,7 +12329,7 @@
         <v/>
       </c>
     </row>
-    <row r="48" spans="1:17" ht="15.75" customHeight="1">
+    <row r="48" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A48" s="10"/>
       <c r="B48" s="67" t="s">
         <v>65</v>
@@ -12373,11 +12384,11 @@
         <v/>
       </c>
     </row>
-    <row r="49" spans="1:17" ht="15.75" customHeight="1">
+    <row r="49" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A49" s="10"/>
       <c r="E49" s="237"/>
     </row>
-    <row r="50" spans="1:17" ht="15.75" customHeight="1">
+    <row r="50" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A50" s="10"/>
       <c r="B50" s="69" t="s">
         <v>130</v>
@@ -12387,7 +12398,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="51" spans="1:17" ht="15.75" customHeight="1">
+    <row r="51" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A51" s="10"/>
       <c r="B51" s="8" t="s">
         <v>85</v>
@@ -12411,7 +12422,7 @@
       <c r="P51" s="151"/>
       <c r="Q51" s="151"/>
     </row>
-    <row r="52" spans="1:17" ht="15.75" customHeight="1">
+    <row r="52" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A52" s="10"/>
       <c r="B52" s="8" t="s">
         <v>84</v>
@@ -12435,7 +12446,7 @@
       <c r="P52" s="151"/>
       <c r="Q52" s="151"/>
     </row>
-    <row r="53" spans="1:17" ht="15.75" customHeight="1">
+    <row r="53" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A53" s="10"/>
       <c r="B53" s="25" t="s">
         <v>87</v>
@@ -12490,11 +12501,11 @@
         <v/>
       </c>
     </row>
-    <row r="54" spans="1:17" ht="15.75" customHeight="1">
+    <row r="54" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A54" s="10"/>
       <c r="E54" s="237"/>
     </row>
-    <row r="55" spans="1:17" ht="15.75" customHeight="1">
+    <row r="55" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A55" s="10"/>
       <c r="B55" s="61" t="s">
         <v>139</v>
@@ -12504,7 +12515,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="56" spans="1:17" ht="15.75" customHeight="1">
+    <row r="56" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A56" s="10"/>
       <c r="B56" s="38" t="s">
         <v>138</v>
@@ -12559,7 +12570,7 @@
         <v/>
       </c>
     </row>
-    <row r="57" spans="1:17" ht="15.75" customHeight="1">
+    <row r="57" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A57" s="10"/>
       <c r="B57" s="38" t="s">
         <v>134</v>
@@ -12614,7 +12625,7 @@
         <v/>
       </c>
     </row>
-    <row r="58" spans="1:17" ht="15.75" customHeight="1">
+    <row r="58" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A58" s="10"/>
       <c r="B58" s="38" t="s">
         <v>133</v>
@@ -12669,7 +12680,7 @@
         <v/>
       </c>
     </row>
-    <row r="59" spans="1:17" ht="15.75" customHeight="1">
+    <row r="59" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A59" s="10"/>
       <c r="B59" s="30" t="s">
         <v>163</v>
@@ -12724,7 +12735,7 @@
         <v/>
       </c>
     </row>
-    <row r="60" spans="1:17" ht="15.75" customHeight="1">
+    <row r="60" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A60" s="10"/>
       <c r="B60" s="38" t="s">
         <v>135</v>
@@ -12780,7 +12791,7 @@
         <v/>
       </c>
     </row>
-    <row r="61" spans="1:17" ht="15.75" customHeight="1">
+    <row r="61" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A61" s="10"/>
       <c r="B61" s="30" t="s">
         <v>164</v>
@@ -12835,11 +12846,11 @@
         <v/>
       </c>
     </row>
-    <row r="62" spans="1:17" ht="15.75" customHeight="1">
+    <row r="62" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A62" s="10"/>
       <c r="E62" s="237"/>
     </row>
-    <row r="63" spans="1:17" ht="15.75" customHeight="1">
+    <row r="63" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A63" s="10"/>
       <c r="B63" s="93" t="s">
         <v>140</v>
@@ -12849,7 +12860,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="64" spans="1:17" ht="15.75" customHeight="1">
+    <row r="64" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A64" s="10"/>
       <c r="B64" s="38" t="s">
         <v>138</v>
@@ -12874,7 +12885,7 @@
       <c r="P64" s="157"/>
       <c r="Q64" s="157"/>
     </row>
-    <row r="65" spans="1:17" ht="15.75" customHeight="1">
+    <row r="65" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A65" s="10"/>
       <c r="B65" s="102" t="s">
         <v>132</v>
@@ -12899,7 +12910,7 @@
       <c r="P65" s="157"/>
       <c r="Q65" s="157"/>
     </row>
-    <row r="66" spans="1:17" ht="15.75" customHeight="1">
+    <row r="66" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A66" s="10"/>
       <c r="B66" s="102" t="s">
         <v>133</v>
@@ -12924,7 +12935,7 @@
       <c r="P66" s="157"/>
       <c r="Q66" s="157"/>
     </row>
-    <row r="67" spans="1:17" ht="15.75" customHeight="1">
+    <row r="67" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A67" s="10"/>
       <c r="B67" s="30" t="s">
         <v>163</v>
@@ -12951,10 +12962,10 @@
       <c r="P67" s="157"/>
       <c r="Q67" s="157"/>
     </row>
-    <row r="68" spans="1:17" ht="15.75" customHeight="1">
+    <row r="68" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A68" s="10"/>
     </row>
-    <row r="69" spans="1:17" ht="15.75" customHeight="1">
+    <row r="69" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="10"/>
       <c r="B69" s="51" t="s">
         <v>181</v>
@@ -12977,7 +12988,7 @@
       <c r="P69" s="35"/>
       <c r="Q69" s="35"/>
     </row>
-    <row r="70" spans="1:17" ht="15.75" customHeight="1">
+    <row r="70" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A70" s="10"/>
       <c r="B70" s="69" t="s">
         <v>185</v>
@@ -12998,7 +13009,7 @@
       <c r="P70" s="12"/>
       <c r="Q70" s="12"/>
     </row>
-    <row r="71" spans="1:17" ht="15.75" customHeight="1">
+    <row r="71" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A71" s="10"/>
       <c r="B71" s="2" t="s">
         <v>43</v>
@@ -13055,7 +13066,7 @@
         <v/>
       </c>
     </row>
-    <row r="72" spans="1:17" ht="15.75" customHeight="1">
+    <row r="72" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A72" s="10"/>
       <c r="B72" s="30" t="s">
         <v>45</v>
@@ -13112,7 +13123,7 @@
         <v/>
       </c>
     </row>
-    <row r="73" spans="1:17" ht="15.75" customHeight="1">
+    <row r="73" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A73" s="10"/>
       <c r="B73" s="8" t="s">
         <v>42</v>
@@ -13169,7 +13180,7 @@
         <v/>
       </c>
     </row>
-    <row r="74" spans="1:17" ht="15.75" customHeight="1">
+    <row r="74" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A74" s="10"/>
       <c r="B74" s="28" t="s">
         <v>127</v>
@@ -13226,7 +13237,7 @@
         <v/>
       </c>
     </row>
-    <row r="75" spans="1:17" ht="15.75" customHeight="1">
+    <row r="75" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A75" s="10"/>
       <c r="B75" s="26" t="s">
         <v>128</v>
@@ -13283,7 +13294,7 @@
         <v/>
       </c>
     </row>
-    <row r="76" spans="1:17" ht="15.75" customHeight="1">
+    <row r="76" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A76" s="10"/>
       <c r="B76" s="2" t="s">
         <v>65</v>
@@ -13340,7 +13351,7 @@
         <v/>
       </c>
     </row>
-    <row r="77" spans="1:17" ht="15.75" customHeight="1">
+    <row r="77" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A77" s="10"/>
       <c r="B77" s="67" t="s">
         <v>137</v>
@@ -13397,7 +13408,7 @@
         <v/>
       </c>
     </row>
-    <row r="78" spans="1:17" ht="15.75" customHeight="1">
+    <row r="78" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A78" s="10"/>
       <c r="B78" s="2" t="s">
         <v>60</v>
@@ -13454,7 +13465,7 @@
         <v/>
       </c>
     </row>
-    <row r="79" spans="1:17" ht="15.75" customHeight="1">
+    <row r="79" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A79" s="10"/>
       <c r="B79" s="38" t="str">
         <f>B13</f>
@@ -13512,7 +13523,7 @@
         <v/>
       </c>
     </row>
-    <row r="80" spans="1:17" ht="15.75" customHeight="1">
+    <row r="80" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A80" s="10"/>
       <c r="B80" s="39" t="s">
         <v>129</v>
@@ -13569,7 +13580,7 @@
         <v/>
       </c>
     </row>
-    <row r="81" spans="1:17" ht="15.75" customHeight="1">
+    <row r="81" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A81" s="10"/>
       <c r="B81" s="2" t="s">
         <v>62</v>
@@ -13626,7 +13637,7 @@
         <v/>
       </c>
     </row>
-    <row r="82" spans="1:17" ht="15.75" customHeight="1">
+    <row r="82" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A82" s="10"/>
       <c r="B82" s="2" t="s">
         <v>77</v>
@@ -13685,7 +13696,7 @@
         <v/>
       </c>
     </row>
-    <row r="83" spans="1:17" ht="15.75" customHeight="1">
+    <row r="83" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A83" s="10"/>
       <c r="B83" s="26" t="s">
         <v>49</v>
@@ -13711,7 +13722,7 @@
       <c r="P83" s="203"/>
       <c r="Q83" s="203"/>
     </row>
-    <row r="84" spans="1:17" ht="15.75" customHeight="1">
+    <row r="84" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A84" s="10"/>
       <c r="B84" s="8" t="s">
         <v>94</v>
@@ -13735,7 +13746,7 @@
       <c r="P84" s="151"/>
       <c r="Q84" s="151"/>
     </row>
-    <row r="85" spans="1:17" ht="15.75" customHeight="1">
+    <row r="85" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A85" s="10"/>
       <c r="B85" s="30" t="s">
         <v>117</v>
@@ -13792,18 +13803,18 @@
         <v/>
       </c>
     </row>
-    <row r="86" spans="1:17" ht="15.75" customHeight="1">
+    <row r="86" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A86" s="10"/>
       <c r="E86" s="237"/>
     </row>
-    <row r="87" spans="1:17" ht="15.75" customHeight="1">
+    <row r="87" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A87" s="10"/>
       <c r="B87" s="61" t="s">
         <v>183</v>
       </c>
       <c r="E87" s="237"/>
     </row>
-    <row r="88" spans="1:17" ht="15.75" customHeight="1">
+    <row r="88" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A88" s="10"/>
       <c r="B88" s="2" t="str">
         <f>"Dividend per share ("&amp;Market_currency&amp;")"</f>
@@ -13859,7 +13870,7 @@
         <v/>
       </c>
     </row>
-    <row r="89" spans="1:17" ht="15.75" customHeight="1">
+    <row r="89" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A89" s="10"/>
       <c r="B89" s="2" t="str">
         <f>"Dividend ("&amp;Market_currency&amp;")"</f>
@@ -13915,7 +13926,7 @@
         <v/>
       </c>
     </row>
-    <row r="90" spans="1:17" ht="15.75" customHeight="1">
+    <row r="90" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A90" s="10"/>
       <c r="B90" s="2" t="s">
         <v>182</v>
@@ -13970,7 +13981,7 @@
         <v/>
       </c>
     </row>
-    <row r="91" spans="1:17" ht="15.75" customHeight="1">
+    <row r="91" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A91" s="10"/>
       <c r="B91" s="2" t="s">
         <v>331</v>
@@ -13991,23 +14002,23 @@
       <c r="P91" s="293"/>
       <c r="Q91" s="293"/>
     </row>
-    <row r="92" spans="1:17" ht="15.75" customHeight="1">
+    <row r="92" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A92" s="10"/>
       <c r="B92" s="2" t="s">
         <v>330</v>
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>3.4188204393505249E-2</v>
+        <v>3.392895734597156E-2</v>
       </c>
       <c r="E92" s="237"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>3.4188204393505249E-2</v>
+        <v>3.392895734597156E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>2.7074510506208214E-2</v>
+        <v>2.686920616113744E-2</v>
       </c>
       <c r="I92" s="22" t="str">
         <f t="shared" si="38"/>
@@ -14046,11 +14057,11 @@
         <v/>
       </c>
     </row>
-    <row r="93" spans="1:17" ht="15.75" customHeight="1">
+    <row r="93" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A93" s="10"/>
       <c r="E93" s="237"/>
     </row>
-    <row r="94" spans="1:17" ht="15.75" customHeight="1">
+    <row r="94" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A94" s="10"/>
       <c r="B94" s="143" t="s">
         <v>81</v>
@@ -14071,7 +14082,7 @@
       <c r="P94" s="12"/>
       <c r="Q94" s="12"/>
     </row>
-    <row r="95" spans="1:17" ht="15.75" customHeight="1">
+    <row r="95" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A95" s="10"/>
       <c r="B95" s="26" t="s">
         <v>121</v>
@@ -14128,7 +14139,7 @@
         <v/>
       </c>
     </row>
-    <row r="96" spans="1:17" ht="15.75" customHeight="1">
+    <row r="96" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A96" s="10"/>
       <c r="B96" s="67" t="s">
         <v>137</v>
@@ -14185,10 +14196,10 @@
         <v/>
       </c>
     </row>
-    <row r="97" spans="1:17" ht="15.75" customHeight="1">
+    <row r="97" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A97" s="10"/>
     </row>
-    <row r="98" spans="1:17" ht="15.75" customHeight="1">
+    <row r="98" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="3"/>
       <c r="B98" s="51" t="s">
         <v>184</v>
@@ -14211,7 +14222,7 @@
       <c r="P98" s="35"/>
       <c r="Q98" s="35"/>
     </row>
-    <row r="99" spans="1:17" ht="15.75" customHeight="1">
+    <row r="99" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A99" s="10"/>
       <c r="B99" s="61" t="s">
         <v>26</v>
@@ -14221,7 +14232,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="100" spans="1:17" ht="15.75" customHeight="1">
+    <row r="100" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A100" s="10"/>
       <c r="B100" s="25" t="s">
         <v>1</v>
@@ -14278,7 +14289,7 @@
         <v/>
       </c>
     </row>
-    <row r="101" spans="1:17" ht="15.75" customHeight="1">
+    <row r="101" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A101" s="10"/>
       <c r="B101" s="90" t="s">
         <v>179</v>
@@ -14335,7 +14346,7 @@
         <v/>
       </c>
     </row>
-    <row r="102" spans="1:17" ht="15.75" customHeight="1">
+    <row r="102" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A102" s="10"/>
       <c r="B102" s="90" t="s">
         <v>180</v>
@@ -14392,7 +14403,7 @@
         <v/>
       </c>
     </row>
-    <row r="103" spans="1:17" ht="15.75" customHeight="1">
+    <row r="103" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A103" s="10"/>
       <c r="B103" s="25" t="s">
         <v>38</v>
@@ -14449,7 +14460,7 @@
         <v/>
       </c>
     </row>
-    <row r="104" spans="1:17" ht="15.75" customHeight="1">
+    <row r="104" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A104" s="10"/>
       <c r="B104" s="25" t="s">
         <v>28</v>
@@ -14506,11 +14517,11 @@
         <v/>
       </c>
     </row>
-    <row r="105" spans="1:17" ht="15.75" customHeight="1">
+    <row r="105" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A105" s="10"/>
       <c r="E105" s="237"/>
     </row>
-    <row r="106" spans="1:17" ht="15.75" customHeight="1">
+    <row r="106" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A106" s="10"/>
       <c r="B106" s="88" t="s">
         <v>189</v>
@@ -14533,7 +14544,7 @@
       <c r="P106" s="12"/>
       <c r="Q106" s="12"/>
     </row>
-    <row r="107" spans="1:17" ht="15.75" customHeight="1">
+    <row r="107" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A107" s="10"/>
       <c r="B107" s="25" t="s">
         <v>186</v>
@@ -14590,7 +14601,7 @@
         <v/>
       </c>
     </row>
-    <row r="108" spans="1:17" ht="15.75" customHeight="1">
+    <row r="108" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A108" s="10"/>
       <c r="B108" s="25" t="s">
         <v>187</v>
@@ -14647,7 +14658,7 @@
         <v/>
       </c>
     </row>
-    <row r="109" spans="1:17" ht="15.75" customHeight="1">
+    <row r="109" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A109" s="10"/>
       <c r="B109" s="25" t="s">
         <v>66</v>
@@ -14674,18 +14685,18 @@
       <c r="P109" s="186"/>
       <c r="Q109" s="186"/>
     </row>
-    <row r="110" spans="1:17" ht="15.75" customHeight="1">
+    <row r="110" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A110" s="10"/>
       <c r="E110" s="237"/>
     </row>
-    <row r="111" spans="1:17" ht="15.75" customHeight="1">
+    <row r="111" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A111" s="10"/>
       <c r="B111" s="61" t="s">
         <v>48</v>
       </c>
       <c r="E111" s="237"/>
     </row>
-    <row r="112" spans="1:17" ht="15.75" customHeight="1">
+    <row r="112" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A112" s="10"/>
       <c r="B112" s="2" t="s">
         <v>303</v>
@@ -14739,7 +14750,7 @@
         <v/>
       </c>
     </row>
-    <row r="113" spans="1:17" ht="15.75" customHeight="1">
+    <row r="113" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A113" s="10"/>
       <c r="B113" s="2" t="s">
         <v>304</v>
@@ -14794,11 +14805,11 @@
         <v/>
       </c>
     </row>
-    <row r="114" spans="1:17" ht="15.75" customHeight="1">
+    <row r="114" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A114" s="10"/>
       <c r="E114" s="237"/>
     </row>
-    <row r="115" spans="1:17" ht="15.75" customHeight="1">
+    <row r="115" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A115" s="10"/>
       <c r="B115" s="88" t="s">
         <v>36</v>
@@ -14857,7 +14868,7 @@
         <v/>
       </c>
     </row>
-    <row r="116" spans="1:17" ht="15.75" customHeight="1">
+    <row r="116" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A116" s="10"/>
       <c r="B116" s="7" t="s">
         <v>190</v>
@@ -14915,7 +14926,7 @@
         <v/>
       </c>
     </row>
-    <row r="117" spans="1:17" ht="15.75" customHeight="1">
+    <row r="117" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B117" s="7" t="s">
         <v>80</v>
       </c>
@@ -14972,7 +14983,7 @@
         <v/>
       </c>
     </row>
-    <row r="118" spans="1:17" ht="15.75" customHeight="1">
+    <row r="118" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B118" s="7" t="s">
         <v>88</v>
       </c>
@@ -15031,7 +15042,7 @@
         <v/>
       </c>
     </row>
-    <row r="119" spans="1:17" ht="15.75" customHeight="1">
+    <row r="119" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A119" s="10"/>
       <c r="B119" s="67" t="s">
         <v>191</v>
@@ -15091,7 +15102,7 @@
         <v/>
       </c>
     </row>
-    <row r="120" spans="1:17" ht="15.75" customHeight="1">
+    <row r="120" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A120" s="10"/>
       <c r="B120" s="26"/>
       <c r="C120" s="59"/>
@@ -15110,7 +15121,7 @@
       <c r="P120" s="12"/>
       <c r="Q120" s="12"/>
     </row>
-    <row r="121" spans="1:17" ht="15.75" customHeight="1">
+    <row r="121" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="10"/>
       <c r="B121" s="51" t="s">
         <v>192</v>
@@ -15133,7 +15144,7 @@
       <c r="P121" s="35"/>
       <c r="Q121" s="35"/>
     </row>
-    <row r="122" spans="1:17" ht="15.75" customHeight="1">
+    <row r="122" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A122" s="10"/>
       <c r="B122" s="160" t="s">
         <v>141</v>
@@ -15154,7 +15165,7 @@
       <c r="P122" s="12"/>
       <c r="Q122" s="12"/>
     </row>
-    <row r="123" spans="1:17" ht="15.75" customHeight="1">
+    <row r="123" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A123" s="10"/>
       <c r="B123" s="26" t="str">
         <f>"FCFE per share ("&amp;Market_currency&amp;")"</f>
@@ -15162,18 +15173,18 @@
       </c>
       <c r="C123" s="159">
         <f>C14*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>2.936631055802513</v>
+        <v>2.915535507823908</v>
       </c>
       <c r="D123" s="26"/>
       <c r="E123" s="234"/>
       <c r="F123" s="26"/>
       <c r="G123" s="159">
         <f t="shared" ref="G123:Q123" si="48">IF(G$4="","",G14*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>3.0415064918596477</v>
+        <v>3.0196575619440273</v>
       </c>
       <c r="H123" s="159">
         <f t="shared" si="48"/>
-        <v>2.4328440878507536</v>
+        <v>2.4153675379524224</v>
       </c>
       <c r="I123" s="159" t="str">
         <f t="shared" si="48"/>
@@ -15212,25 +15223,25 @@
         <v/>
       </c>
     </row>
-    <row r="124" spans="1:17" ht="15.75" customHeight="1">
+    <row r="124" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A124" s="10"/>
       <c r="B124" s="26" t="s">
         <v>226</v>
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>7.0120130272266309E-2</v>
+        <v>6.9088519142746635E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="234"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>7.2624319289867414E-2</v>
+        <v>7.1555866396777898E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>5.8090833043236707E-2</v>
+        <v>5.7236197581810956E-2</v>
       </c>
       <c r="I124" s="74" t="str">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
@@ -15269,18 +15280,18 @@
         <v/>
       </c>
     </row>
-    <row r="125" spans="1:17" ht="15.75" customHeight="1">
+    <row r="125" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B125" s="2" t="s">
         <v>306</v>
       </c>
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.8702133974265301E-3</v>
+        <v>7.810534054128509E-3</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.2837784445338458E-3</v>
+        <v>6.2361289397411725E-3</v>
       </c>
       <c r="I125" s="22" t="str">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -15319,688 +15330,688 @@
         <v/>
       </c>
     </row>
-    <row r="126" spans="1:17" ht="15.75" customHeight="1"/>
-    <row r="127" spans="1:17" ht="15.75" customHeight="1"/>
-    <row r="128" spans="1:17" ht="15.75" customHeight="1"/>
-    <row r="129" ht="15.75" customHeight="1"/>
-    <row r="130" ht="15.75" customHeight="1"/>
-    <row r="131" ht="15.75" customHeight="1"/>
-    <row r="132" ht="15.75" customHeight="1"/>
-    <row r="133" ht="15.75" customHeight="1"/>
-    <row r="134" ht="15.75" customHeight="1"/>
-    <row r="135" ht="15.75" customHeight="1"/>
-    <row r="136" ht="15.75" customHeight="1"/>
-    <row r="137" ht="15.75" customHeight="1"/>
-    <row r="138" ht="15.75" customHeight="1"/>
-    <row r="139" ht="15.75" customHeight="1"/>
-    <row r="140" ht="15.75" customHeight="1"/>
-    <row r="141" ht="15.75" customHeight="1"/>
-    <row r="142" ht="15.75" customHeight="1"/>
-    <row r="143" ht="15.75" customHeight="1"/>
-    <row r="144" ht="15.75" customHeight="1"/>
-    <row r="145" ht="15.75" customHeight="1"/>
-    <row r="146" ht="15.75" customHeight="1"/>
-    <row r="147" ht="15.75" customHeight="1"/>
-    <row r="148" ht="15.75" customHeight="1"/>
-    <row r="149" ht="15.75" customHeight="1"/>
-    <row r="150" ht="15.75" customHeight="1"/>
-    <row r="151" ht="15.75" customHeight="1"/>
-    <row r="152" ht="15.75" customHeight="1"/>
-    <row r="153" ht="15.75" customHeight="1"/>
-    <row r="154" ht="15.75" customHeight="1"/>
-    <row r="155" ht="15.75" customHeight="1"/>
-    <row r="156" ht="15.75" customHeight="1"/>
-    <row r="157" ht="15.75" customHeight="1"/>
-    <row r="158" ht="15.75" customHeight="1"/>
-    <row r="159" ht="15.75" customHeight="1"/>
-    <row r="160" ht="15.75" customHeight="1"/>
-    <row r="161" ht="15.75" customHeight="1"/>
-    <row r="162" ht="15.75" customHeight="1"/>
-    <row r="163" ht="15.75" customHeight="1"/>
-    <row r="164" ht="15.75" customHeight="1"/>
-    <row r="165" ht="15.75" customHeight="1"/>
-    <row r="166" ht="15.75" customHeight="1"/>
-    <row r="167" ht="15.75" customHeight="1"/>
-    <row r="168" ht="15.75" customHeight="1"/>
-    <row r="169" ht="15.75" customHeight="1"/>
-    <row r="170" ht="15.75" customHeight="1"/>
-    <row r="171" ht="15.75" customHeight="1"/>
-    <row r="172" ht="15.75" customHeight="1"/>
-    <row r="173" ht="15.75" customHeight="1"/>
-    <row r="174" ht="15.75" customHeight="1"/>
-    <row r="175" ht="15.75" customHeight="1"/>
-    <row r="176" ht="15.75" customHeight="1"/>
-    <row r="177" ht="15.75" customHeight="1"/>
-    <row r="178" ht="15.75" customHeight="1"/>
-    <row r="179" ht="15.75" customHeight="1"/>
-    <row r="180" ht="15.75" customHeight="1"/>
-    <row r="181" ht="15.75" customHeight="1"/>
-    <row r="182" ht="15.75" customHeight="1"/>
-    <row r="183" ht="15.75" customHeight="1"/>
-    <row r="184" ht="15.75" customHeight="1"/>
-    <row r="185" ht="15.75" customHeight="1"/>
-    <row r="186" ht="15.75" customHeight="1"/>
-    <row r="187" ht="15.75" customHeight="1"/>
-    <row r="188" ht="15.75" customHeight="1"/>
-    <row r="189" ht="15.75" customHeight="1"/>
-    <row r="190" ht="15.75" customHeight="1"/>
-    <row r="191" ht="15.75" customHeight="1"/>
-    <row r="192" ht="15.75" customHeight="1"/>
-    <row r="193" ht="15.75" customHeight="1"/>
-    <row r="194" ht="15.75" customHeight="1"/>
-    <row r="195" ht="15.75" customHeight="1"/>
-    <row r="196" ht="15.75" customHeight="1"/>
-    <row r="197" ht="15.75" customHeight="1"/>
-    <row r="198" ht="15.75" customHeight="1"/>
-    <row r="199" ht="15.75" customHeight="1"/>
-    <row r="200" ht="15.75" customHeight="1"/>
-    <row r="201" ht="15.75" customHeight="1"/>
-    <row r="202" ht="15.75" customHeight="1"/>
-    <row r="203" ht="15.75" customHeight="1"/>
-    <row r="204" ht="15.75" customHeight="1"/>
-    <row r="205" ht="15.75" customHeight="1"/>
-    <row r="206" ht="15.75" customHeight="1"/>
-    <row r="207" ht="15.75" customHeight="1"/>
-    <row r="208" ht="15.75" customHeight="1"/>
-    <row r="209" ht="15.75" customHeight="1"/>
-    <row r="210" ht="15.75" customHeight="1"/>
-    <row r="211" ht="15.75" customHeight="1"/>
-    <row r="212" ht="15.75" customHeight="1"/>
-    <row r="213" ht="15.75" customHeight="1"/>
-    <row r="214" ht="15.75" customHeight="1"/>
-    <row r="215" ht="15.75" customHeight="1"/>
-    <row r="216" ht="15.75" customHeight="1"/>
-    <row r="217" ht="15.75" customHeight="1"/>
-    <row r="218" ht="15.75" customHeight="1"/>
-    <row r="219" ht="15.75" customHeight="1"/>
-    <row r="220" ht="15.75" customHeight="1"/>
-    <row r="221" ht="15.75" customHeight="1"/>
-    <row r="222" ht="15.75" customHeight="1"/>
-    <row r="223" ht="15.75" customHeight="1"/>
-    <row r="224" ht="15.75" customHeight="1"/>
-    <row r="225" ht="15.75" customHeight="1"/>
-    <row r="226" ht="15.75" customHeight="1"/>
-    <row r="227" ht="15.75" customHeight="1"/>
-    <row r="228" ht="15.75" customHeight="1"/>
-    <row r="229" ht="15.75" customHeight="1"/>
-    <row r="230" ht="15.75" customHeight="1"/>
-    <row r="231" ht="15.75" customHeight="1"/>
-    <row r="232" ht="15.75" customHeight="1"/>
-    <row r="233" ht="15.75" customHeight="1"/>
-    <row r="234" ht="15.75" customHeight="1"/>
-    <row r="235" ht="15.75" customHeight="1"/>
-    <row r="236" ht="15.75" customHeight="1"/>
-    <row r="237" ht="15.75" customHeight="1"/>
-    <row r="238" ht="15.75" customHeight="1"/>
-    <row r="239" ht="15.75" customHeight="1"/>
-    <row r="240" ht="15.75" customHeight="1"/>
-    <row r="241" ht="15.75" customHeight="1"/>
-    <row r="242" ht="15.75" customHeight="1"/>
-    <row r="243" ht="15.75" customHeight="1"/>
-    <row r="244" ht="15.75" customHeight="1"/>
-    <row r="245" ht="15.75" customHeight="1"/>
-    <row r="246" ht="15.75" customHeight="1"/>
-    <row r="247" ht="15.75" customHeight="1"/>
-    <row r="248" ht="15.75" customHeight="1"/>
-    <row r="249" ht="15.75" customHeight="1"/>
-    <row r="250" ht="15.75" customHeight="1"/>
-    <row r="251" ht="15.75" customHeight="1"/>
-    <row r="252" ht="15.75" customHeight="1"/>
-    <row r="253" ht="15.75" customHeight="1"/>
-    <row r="254" ht="15.75" customHeight="1"/>
-    <row r="255" ht="15.75" customHeight="1"/>
-    <row r="256" ht="15.75" customHeight="1"/>
-    <row r="257" ht="15.75" customHeight="1"/>
-    <row r="258" ht="15.75" customHeight="1"/>
-    <row r="259" ht="15.75" customHeight="1"/>
-    <row r="260" ht="15.75" customHeight="1"/>
-    <row r="261" ht="15.75" customHeight="1"/>
-    <row r="262" ht="15.75" customHeight="1"/>
-    <row r="263" ht="15.75" customHeight="1"/>
-    <row r="264" ht="15.75" customHeight="1"/>
-    <row r="265" ht="15.75" customHeight="1"/>
-    <row r="266" ht="15.75" customHeight="1"/>
-    <row r="267" ht="15.75" customHeight="1"/>
-    <row r="268" ht="15.75" customHeight="1"/>
-    <row r="269" ht="15.75" customHeight="1"/>
-    <row r="270" ht="15.75" customHeight="1"/>
-    <row r="271" ht="15.75" customHeight="1"/>
-    <row r="272" ht="15.75" customHeight="1"/>
-    <row r="273" ht="15.75" customHeight="1"/>
-    <row r="274" ht="15.75" customHeight="1"/>
-    <row r="275" ht="15.75" customHeight="1"/>
-    <row r="276" ht="15.75" customHeight="1"/>
-    <row r="277" ht="15.75" customHeight="1"/>
-    <row r="278" ht="15.75" customHeight="1"/>
-    <row r="279" ht="15.75" customHeight="1"/>
-    <row r="280" ht="15.75" customHeight="1"/>
-    <row r="281" ht="15.75" customHeight="1"/>
-    <row r="282" ht="15.75" customHeight="1"/>
-    <row r="283" ht="15.75" customHeight="1"/>
-    <row r="284" ht="15.75" customHeight="1"/>
-    <row r="285" ht="15.75" customHeight="1"/>
-    <row r="286" ht="15.75" customHeight="1"/>
-    <row r="287" ht="15.75" customHeight="1"/>
-    <row r="288" ht="15.75" customHeight="1"/>
-    <row r="289" ht="15.75" customHeight="1"/>
-    <row r="290" ht="15.75" customHeight="1"/>
-    <row r="291" ht="15.75" customHeight="1"/>
-    <row r="292" ht="15.75" customHeight="1"/>
-    <row r="293" ht="15.75" customHeight="1"/>
-    <row r="294" ht="15.75" customHeight="1"/>
-    <row r="295" ht="15.75" customHeight="1"/>
-    <row r="296" ht="15.75" customHeight="1"/>
-    <row r="297" ht="15.75" customHeight="1"/>
-    <row r="298" ht="15.75" customHeight="1"/>
-    <row r="299" ht="15.75" customHeight="1"/>
-    <row r="300" ht="15.75" customHeight="1"/>
-    <row r="301" ht="15.75" customHeight="1"/>
-    <row r="302" ht="15.75" customHeight="1"/>
-    <row r="303" ht="15.75" customHeight="1"/>
-    <row r="304" ht="15.75" customHeight="1"/>
-    <row r="305" ht="15.75" customHeight="1"/>
-    <row r="306" ht="15.75" customHeight="1"/>
-    <row r="307" ht="15.75" customHeight="1"/>
-    <row r="308" ht="15.75" customHeight="1"/>
-    <row r="309" ht="15.75" customHeight="1"/>
-    <row r="310" ht="15.75" customHeight="1"/>
-    <row r="311" ht="15.75" customHeight="1"/>
-    <row r="312" ht="15.75" customHeight="1"/>
-    <row r="313" ht="15.75" customHeight="1"/>
-    <row r="314" ht="15.75" customHeight="1"/>
-    <row r="315" ht="15.75" customHeight="1"/>
-    <row r="316" ht="15.75" customHeight="1"/>
-    <row r="317" ht="15.75" customHeight="1"/>
-    <row r="318" ht="15.75" customHeight="1"/>
-    <row r="319" ht="15.75" customHeight="1"/>
-    <row r="320" ht="15.75" customHeight="1"/>
-    <row r="321" ht="15.75" customHeight="1"/>
-    <row r="322" ht="15.75" customHeight="1"/>
-    <row r="323" ht="15.75" customHeight="1"/>
-    <row r="324" ht="15.75" customHeight="1"/>
-    <row r="325" ht="15.75" customHeight="1"/>
-    <row r="326" ht="15.75" customHeight="1"/>
-    <row r="327" ht="15.75" customHeight="1"/>
-    <row r="328" ht="15.75" customHeight="1"/>
-    <row r="329" ht="15.75" customHeight="1"/>
-    <row r="330" ht="15.75" customHeight="1"/>
-    <row r="331" ht="15.75" customHeight="1"/>
-    <row r="332" ht="15.75" customHeight="1"/>
-    <row r="333" ht="15.75" customHeight="1"/>
-    <row r="334" ht="15.75" customHeight="1"/>
-    <row r="335" ht="15.75" customHeight="1"/>
-    <row r="336" ht="15.75" customHeight="1"/>
-    <row r="337" ht="15.75" customHeight="1"/>
-    <row r="338" ht="15.75" customHeight="1"/>
-    <row r="339" ht="15.75" customHeight="1"/>
-    <row r="340" ht="15.75" customHeight="1"/>
-    <row r="341" ht="15.75" customHeight="1"/>
-    <row r="342" ht="15.75" customHeight="1"/>
-    <row r="343" ht="15.75" customHeight="1"/>
-    <row r="344" ht="15.75" customHeight="1"/>
-    <row r="345" ht="15.75" customHeight="1"/>
-    <row r="346" ht="15.75" customHeight="1"/>
-    <row r="347" ht="15.75" customHeight="1"/>
-    <row r="348" ht="15.75" customHeight="1"/>
-    <row r="349" ht="15.75" customHeight="1"/>
-    <row r="350" ht="15.75" customHeight="1"/>
-    <row r="351" ht="15.75" customHeight="1"/>
-    <row r="352" ht="15.75" customHeight="1"/>
-    <row r="353" ht="15.75" customHeight="1"/>
-    <row r="354" ht="15.75" customHeight="1"/>
-    <row r="355" ht="15.75" customHeight="1"/>
-    <row r="356" ht="15.75" customHeight="1"/>
-    <row r="357" ht="15.75" customHeight="1"/>
-    <row r="358" ht="15.75" customHeight="1"/>
-    <row r="359" ht="15.75" customHeight="1"/>
-    <row r="360" ht="15.75" customHeight="1"/>
-    <row r="361" ht="15.75" customHeight="1"/>
-    <row r="362" ht="15.75" customHeight="1"/>
-    <row r="363" ht="15.75" customHeight="1"/>
-    <row r="364" ht="15.75" customHeight="1"/>
-    <row r="365" ht="15.75" customHeight="1"/>
-    <row r="366" ht="15.75" customHeight="1"/>
-    <row r="367" ht="15.75" customHeight="1"/>
-    <row r="368" ht="15.75" customHeight="1"/>
-    <row r="369" ht="15.75" customHeight="1"/>
-    <row r="370" ht="15.75" customHeight="1"/>
-    <row r="371" ht="15.75" customHeight="1"/>
-    <row r="372" ht="15.75" customHeight="1"/>
-    <row r="373" ht="15.75" customHeight="1"/>
-    <row r="374" ht="15.75" customHeight="1"/>
-    <row r="375" ht="15.75" customHeight="1"/>
-    <row r="376" ht="15.75" customHeight="1"/>
-    <row r="377" ht="15.75" customHeight="1"/>
-    <row r="378" ht="15.75" customHeight="1"/>
-    <row r="379" ht="15.75" customHeight="1"/>
-    <row r="380" ht="15.75" customHeight="1"/>
-    <row r="381" ht="15.75" customHeight="1"/>
-    <row r="382" ht="15.75" customHeight="1"/>
-    <row r="383" ht="15.75" customHeight="1"/>
-    <row r="384" ht="15.75" customHeight="1"/>
-    <row r="385" ht="15.75" customHeight="1"/>
-    <row r="386" ht="15.75" customHeight="1"/>
-    <row r="387" ht="15.75" customHeight="1"/>
-    <row r="388" ht="15.75" customHeight="1"/>
-    <row r="389" ht="15.75" customHeight="1"/>
-    <row r="390" ht="15.75" customHeight="1"/>
-    <row r="391" ht="15.75" customHeight="1"/>
-    <row r="392" ht="15.75" customHeight="1"/>
-    <row r="393" ht="15.75" customHeight="1"/>
-    <row r="394" ht="15.75" customHeight="1"/>
-    <row r="395" ht="15.75" customHeight="1"/>
-    <row r="396" ht="15.75" customHeight="1"/>
-    <row r="397" ht="15.75" customHeight="1"/>
-    <row r="398" ht="15.75" customHeight="1"/>
-    <row r="399" ht="15.75" customHeight="1"/>
-    <row r="400" ht="15.75" customHeight="1"/>
-    <row r="401" ht="15.75" customHeight="1"/>
-    <row r="402" ht="15.75" customHeight="1"/>
-    <row r="403" ht="15.75" customHeight="1"/>
-    <row r="404" ht="15.75" customHeight="1"/>
-    <row r="405" ht="15.75" customHeight="1"/>
-    <row r="406" ht="15.75" customHeight="1"/>
-    <row r="407" ht="15.75" customHeight="1"/>
-    <row r="408" ht="15.75" customHeight="1"/>
-    <row r="409" ht="15.75" customHeight="1"/>
-    <row r="410" ht="15.75" customHeight="1"/>
-    <row r="411" ht="15.75" customHeight="1"/>
-    <row r="412" ht="15.75" customHeight="1"/>
-    <row r="413" ht="15.75" customHeight="1"/>
-    <row r="414" ht="15.75" customHeight="1"/>
-    <row r="415" ht="15.75" customHeight="1"/>
-    <row r="416" ht="15.75" customHeight="1"/>
-    <row r="417" ht="15.75" customHeight="1"/>
-    <row r="418" ht="15.75" customHeight="1"/>
-    <row r="419" ht="15.75" customHeight="1"/>
-    <row r="420" ht="15.75" customHeight="1"/>
-    <row r="421" ht="15.75" customHeight="1"/>
-    <row r="422" ht="15.75" customHeight="1"/>
-    <row r="423" ht="15.75" customHeight="1"/>
-    <row r="424" ht="15.75" customHeight="1"/>
-    <row r="425" ht="15.75" customHeight="1"/>
-    <row r="426" ht="15.75" customHeight="1"/>
-    <row r="427" ht="15.75" customHeight="1"/>
-    <row r="428" ht="15.75" customHeight="1"/>
-    <row r="429" ht="15.75" customHeight="1"/>
-    <row r="430" ht="15.75" customHeight="1"/>
-    <row r="431" ht="15.75" customHeight="1"/>
-    <row r="432" ht="15.75" customHeight="1"/>
-    <row r="433" ht="15.75" customHeight="1"/>
-    <row r="434" ht="15.75" customHeight="1"/>
-    <row r="435" ht="15.75" customHeight="1"/>
-    <row r="436" ht="15.75" customHeight="1"/>
-    <row r="437" ht="15.75" customHeight="1"/>
-    <row r="438" ht="15.75" customHeight="1"/>
-    <row r="439" ht="15.75" customHeight="1"/>
-    <row r="440" ht="15.75" customHeight="1"/>
-    <row r="441" ht="15.75" customHeight="1"/>
-    <row r="442" ht="15.75" customHeight="1"/>
-    <row r="443" ht="15.75" customHeight="1"/>
-    <row r="444" ht="15.75" customHeight="1"/>
-    <row r="445" ht="15.75" customHeight="1"/>
-    <row r="446" ht="15.75" customHeight="1"/>
-    <row r="447" ht="15.75" customHeight="1"/>
-    <row r="448" ht="15.75" customHeight="1"/>
-    <row r="449" ht="15.75" customHeight="1"/>
-    <row r="450" ht="15.75" customHeight="1"/>
-    <row r="451" ht="15.75" customHeight="1"/>
-    <row r="452" ht="15.75" customHeight="1"/>
-    <row r="453" ht="15.75" customHeight="1"/>
-    <row r="454" ht="15.75" customHeight="1"/>
-    <row r="455" ht="15.75" customHeight="1"/>
-    <row r="456" ht="15.75" customHeight="1"/>
-    <row r="457" ht="15.75" customHeight="1"/>
-    <row r="458" ht="15.75" customHeight="1"/>
-    <row r="459" ht="15.75" customHeight="1"/>
-    <row r="460" ht="15.75" customHeight="1"/>
-    <row r="461" ht="15.75" customHeight="1"/>
-    <row r="462" ht="15.75" customHeight="1"/>
-    <row r="463" ht="15.75" customHeight="1"/>
-    <row r="464" ht="15.75" customHeight="1"/>
-    <row r="465" ht="15.75" customHeight="1"/>
-    <row r="466" ht="15.75" customHeight="1"/>
-    <row r="467" ht="15.75" customHeight="1"/>
-    <row r="468" ht="15.75" customHeight="1"/>
-    <row r="469" ht="15.75" customHeight="1"/>
-    <row r="470" ht="15.75" customHeight="1"/>
-    <row r="471" ht="15.75" customHeight="1"/>
-    <row r="472" ht="15.75" customHeight="1"/>
-    <row r="473" ht="15.75" customHeight="1"/>
-    <row r="474" ht="15.75" customHeight="1"/>
-    <row r="475" ht="15.75" customHeight="1"/>
-    <row r="476" ht="15.75" customHeight="1"/>
-    <row r="477" ht="15.75" customHeight="1"/>
-    <row r="478" ht="15.75" customHeight="1"/>
-    <row r="479" ht="15.75" customHeight="1"/>
-    <row r="480" ht="15.75" customHeight="1"/>
-    <row r="481" ht="15.75" customHeight="1"/>
-    <row r="482" ht="15.75" customHeight="1"/>
-    <row r="483" ht="15.75" customHeight="1"/>
-    <row r="484" ht="15.75" customHeight="1"/>
-    <row r="485" ht="15.75" customHeight="1"/>
-    <row r="486" ht="15.75" customHeight="1"/>
-    <row r="487" ht="15.75" customHeight="1"/>
-    <row r="488" ht="15.75" customHeight="1"/>
-    <row r="489" ht="15.75" customHeight="1"/>
-    <row r="490" ht="15.75" customHeight="1"/>
-    <row r="491" ht="15.75" customHeight="1"/>
-    <row r="492" ht="15.75" customHeight="1"/>
-    <row r="493" ht="15.75" customHeight="1"/>
-    <row r="494" ht="15.75" customHeight="1"/>
-    <row r="495" ht="15.75" customHeight="1"/>
-    <row r="496" ht="15.75" customHeight="1"/>
-    <row r="497" ht="15.75" customHeight="1"/>
-    <row r="498" ht="15.75" customHeight="1"/>
-    <row r="499" ht="15.75" customHeight="1"/>
-    <row r="500" ht="15.75" customHeight="1"/>
-    <row r="501" ht="15.75" customHeight="1"/>
-    <row r="502" ht="15.75" customHeight="1"/>
-    <row r="503" ht="15.75" customHeight="1"/>
-    <row r="504" ht="15.75" customHeight="1"/>
-    <row r="505" ht="15.75" customHeight="1"/>
-    <row r="506" ht="15.75" customHeight="1"/>
-    <row r="507" ht="15.75" customHeight="1"/>
-    <row r="508" ht="15.75" customHeight="1"/>
-    <row r="509" ht="15.75" customHeight="1"/>
-    <row r="510" ht="15.75" customHeight="1"/>
-    <row r="511" ht="15.75" customHeight="1"/>
-    <row r="512" ht="15.75" customHeight="1"/>
-    <row r="513" ht="15.75" customHeight="1"/>
-    <row r="514" ht="15.75" customHeight="1"/>
-    <row r="515" ht="15.75" customHeight="1"/>
-    <row r="516" ht="15.75" customHeight="1"/>
-    <row r="517" ht="15.75" customHeight="1"/>
-    <row r="518" ht="15.75" customHeight="1"/>
-    <row r="519" ht="15.75" customHeight="1"/>
-    <row r="520" ht="15.75" customHeight="1"/>
-    <row r="521" ht="15.75" customHeight="1"/>
-    <row r="522" ht="15.75" customHeight="1"/>
-    <row r="523" ht="15.75" customHeight="1"/>
-    <row r="524" ht="15.75" customHeight="1"/>
-    <row r="525" ht="15.75" customHeight="1"/>
-    <row r="526" ht="15.75" customHeight="1"/>
-    <row r="527" ht="15.75" customHeight="1"/>
-    <row r="528" ht="15.75" customHeight="1"/>
-    <row r="529" ht="15.75" customHeight="1"/>
-    <row r="530" ht="15.75" customHeight="1"/>
-    <row r="531" ht="15.75" customHeight="1"/>
-    <row r="532" ht="15.75" customHeight="1"/>
-    <row r="533" ht="15.75" customHeight="1"/>
-    <row r="534" ht="15.75" customHeight="1"/>
-    <row r="535" ht="15.75" customHeight="1"/>
-    <row r="536" ht="15.75" customHeight="1"/>
-    <row r="537" ht="15.75" customHeight="1"/>
-    <row r="538" ht="15.75" customHeight="1"/>
-    <row r="539" ht="15.75" customHeight="1"/>
-    <row r="540" ht="15.75" customHeight="1"/>
-    <row r="541" ht="15.75" customHeight="1"/>
-    <row r="542" ht="15.75" customHeight="1"/>
-    <row r="543" ht="15.75" customHeight="1"/>
-    <row r="544" ht="15.75" customHeight="1"/>
-    <row r="545" ht="15.75" customHeight="1"/>
-    <row r="546" ht="15.75" customHeight="1"/>
-    <row r="547" ht="15.75" customHeight="1"/>
-    <row r="548" ht="15.75" customHeight="1"/>
-    <row r="549" ht="15.75" customHeight="1"/>
-    <row r="550" ht="15.75" customHeight="1"/>
-    <row r="551" ht="15.75" customHeight="1"/>
-    <row r="552" ht="15.75" customHeight="1"/>
-    <row r="553" ht="15.75" customHeight="1"/>
-    <row r="554" ht="15.75" customHeight="1"/>
-    <row r="555" ht="15.75" customHeight="1"/>
-    <row r="556" ht="15.75" customHeight="1"/>
-    <row r="557" ht="15.75" customHeight="1"/>
-    <row r="558" ht="15.75" customHeight="1"/>
-    <row r="559" ht="15.75" customHeight="1"/>
-    <row r="560" ht="15.75" customHeight="1"/>
-    <row r="561" ht="15.75" customHeight="1"/>
-    <row r="562" ht="15.75" customHeight="1"/>
-    <row r="563" ht="15.75" customHeight="1"/>
-    <row r="564" ht="15.75" customHeight="1"/>
-    <row r="565" ht="15.75" customHeight="1"/>
-    <row r="566" ht="15.75" customHeight="1"/>
-    <row r="567" ht="15.75" customHeight="1"/>
-    <row r="568" ht="15.75" customHeight="1"/>
-    <row r="569" ht="15.75" customHeight="1"/>
-    <row r="570" ht="15.75" customHeight="1"/>
-    <row r="571" ht="15.75" customHeight="1"/>
-    <row r="572" ht="15.75" customHeight="1"/>
-    <row r="573" ht="15.75" customHeight="1"/>
-    <row r="574" ht="15.75" customHeight="1"/>
-    <row r="575" ht="15.75" customHeight="1"/>
-    <row r="576" ht="15.75" customHeight="1"/>
-    <row r="577" ht="15.75" customHeight="1"/>
-    <row r="578" ht="15.75" customHeight="1"/>
-    <row r="579" ht="15.75" customHeight="1"/>
-    <row r="580" ht="15.75" customHeight="1"/>
-    <row r="581" ht="15.75" customHeight="1"/>
-    <row r="582" ht="15.75" customHeight="1"/>
-    <row r="583" ht="15.75" customHeight="1"/>
-    <row r="584" ht="15.75" customHeight="1"/>
-    <row r="585" ht="15.75" customHeight="1"/>
-    <row r="586" ht="15.75" customHeight="1"/>
-    <row r="587" ht="15.75" customHeight="1"/>
-    <row r="588" ht="15.75" customHeight="1"/>
-    <row r="589" ht="15.75" customHeight="1"/>
-    <row r="590" ht="15.75" customHeight="1"/>
-    <row r="591" ht="15.75" customHeight="1"/>
-    <row r="592" ht="15.75" customHeight="1"/>
-    <row r="593" ht="15.75" customHeight="1"/>
-    <row r="594" ht="15.75" customHeight="1"/>
-    <row r="595" ht="15.75" customHeight="1"/>
-    <row r="596" ht="15.75" customHeight="1"/>
-    <row r="597" ht="15.75" customHeight="1"/>
-    <row r="598" ht="15.75" customHeight="1"/>
-    <row r="599" ht="15.75" customHeight="1"/>
-    <row r="600" ht="15.75" customHeight="1"/>
-    <row r="601" ht="15.75" customHeight="1"/>
-    <row r="602" ht="15.75" customHeight="1"/>
-    <row r="603" ht="15.75" customHeight="1"/>
-    <row r="604" ht="15.75" customHeight="1"/>
-    <row r="605" ht="15.75" customHeight="1"/>
-    <row r="606" ht="15.75" customHeight="1"/>
-    <row r="607" ht="15.75" customHeight="1"/>
-    <row r="608" ht="15.75" customHeight="1"/>
-    <row r="609" ht="15.75" customHeight="1"/>
-    <row r="610" ht="15.75" customHeight="1"/>
-    <row r="611" ht="15.75" customHeight="1"/>
-    <row r="612" ht="15.75" customHeight="1"/>
-    <row r="613" ht="15.75" customHeight="1"/>
-    <row r="614" ht="15.75" customHeight="1"/>
-    <row r="615" ht="15.75" customHeight="1"/>
-    <row r="616" ht="15.75" customHeight="1"/>
-    <row r="617" ht="15.75" customHeight="1"/>
-    <row r="618" ht="15.75" customHeight="1"/>
-    <row r="619" ht="15.75" customHeight="1"/>
-    <row r="620" ht="15.75" customHeight="1"/>
-    <row r="621" ht="15.75" customHeight="1"/>
-    <row r="622" ht="15.75" customHeight="1"/>
-    <row r="623" ht="15.75" customHeight="1"/>
-    <row r="624" ht="15.75" customHeight="1"/>
-    <row r="625" ht="15.75" customHeight="1"/>
-    <row r="626" ht="15.75" customHeight="1"/>
-    <row r="627" ht="15.75" customHeight="1"/>
-    <row r="628" ht="15.75" customHeight="1"/>
-    <row r="629" ht="15.75" customHeight="1"/>
-    <row r="630" ht="15.75" customHeight="1"/>
-    <row r="631" ht="15.75" customHeight="1"/>
-    <row r="632" ht="15.75" customHeight="1"/>
-    <row r="633" ht="15.75" customHeight="1"/>
-    <row r="634" ht="15.75" customHeight="1"/>
-    <row r="635" ht="15.75" customHeight="1"/>
-    <row r="636" ht="15.75" customHeight="1"/>
-    <row r="637" ht="15.75" customHeight="1"/>
-    <row r="638" ht="15.75" customHeight="1"/>
-    <row r="639" ht="15.75" customHeight="1"/>
-    <row r="640" ht="15.75" customHeight="1"/>
-    <row r="641" ht="15.75" customHeight="1"/>
-    <row r="642" ht="15.75" customHeight="1"/>
-    <row r="643" ht="15.75" customHeight="1"/>
-    <row r="644" ht="15.75" customHeight="1"/>
-    <row r="645" ht="15.75" customHeight="1"/>
-    <row r="646" ht="15.75" customHeight="1"/>
-    <row r="647" ht="15.75" customHeight="1"/>
-    <row r="648" ht="15.75" customHeight="1"/>
-    <row r="649" ht="15.75" customHeight="1"/>
-    <row r="650" ht="15.75" customHeight="1"/>
-    <row r="651" ht="15.75" customHeight="1"/>
-    <row r="652" ht="15.75" customHeight="1"/>
-    <row r="653" ht="15.75" customHeight="1"/>
-    <row r="654" ht="15.75" customHeight="1"/>
-    <row r="655" ht="15.75" customHeight="1"/>
-    <row r="656" ht="15.75" customHeight="1"/>
-    <row r="657" ht="15.75" customHeight="1"/>
-    <row r="658" ht="15.75" customHeight="1"/>
-    <row r="659" ht="15.75" customHeight="1"/>
-    <row r="660" ht="15.75" customHeight="1"/>
-    <row r="661" ht="15.75" customHeight="1"/>
-    <row r="662" ht="15.75" customHeight="1"/>
-    <row r="663" ht="15.75" customHeight="1"/>
-    <row r="664" ht="15.75" customHeight="1"/>
-    <row r="665" ht="15.75" customHeight="1"/>
-    <row r="666" ht="15.75" customHeight="1"/>
-    <row r="667" ht="15.75" customHeight="1"/>
-    <row r="668" ht="15.75" customHeight="1"/>
-    <row r="669" ht="15.75" customHeight="1"/>
-    <row r="670" ht="15.75" customHeight="1"/>
-    <row r="671" ht="15.75" customHeight="1"/>
-    <row r="672" ht="15.75" customHeight="1"/>
-    <row r="673" ht="15.75" customHeight="1"/>
-    <row r="674" ht="15.75" customHeight="1"/>
-    <row r="675" ht="15.75" customHeight="1"/>
-    <row r="676" ht="15.75" customHeight="1"/>
-    <row r="677" ht="15.75" customHeight="1"/>
-    <row r="678" ht="15.75" customHeight="1"/>
-    <row r="679" ht="15.75" customHeight="1"/>
-    <row r="680" ht="15.75" customHeight="1"/>
-    <row r="681" ht="15.75" customHeight="1"/>
-    <row r="682" ht="15.75" customHeight="1"/>
-    <row r="683" ht="15.75" customHeight="1"/>
-    <row r="684" ht="15.75" customHeight="1"/>
-    <row r="685" ht="15.75" customHeight="1"/>
-    <row r="686" ht="15.75" customHeight="1"/>
-    <row r="687" ht="15.75" customHeight="1"/>
-    <row r="688" ht="15.75" customHeight="1"/>
-    <row r="689" ht="15.75" customHeight="1"/>
-    <row r="690" ht="15.75" customHeight="1"/>
-    <row r="691" ht="15.75" customHeight="1"/>
-    <row r="692" ht="15.75" customHeight="1"/>
-    <row r="693" ht="15.75" customHeight="1"/>
-    <row r="694" ht="15.75" customHeight="1"/>
-    <row r="695" ht="15.75" customHeight="1"/>
-    <row r="696" ht="15.75" customHeight="1"/>
-    <row r="697" ht="15.75" customHeight="1"/>
-    <row r="698" ht="15.75" customHeight="1"/>
-    <row r="699" ht="15.75" customHeight="1"/>
-    <row r="700" ht="15.75" customHeight="1"/>
-    <row r="701" ht="15.75" customHeight="1"/>
-    <row r="702" ht="15.75" customHeight="1"/>
-    <row r="703" ht="15.75" customHeight="1"/>
-    <row r="704" ht="15.75" customHeight="1"/>
-    <row r="705" ht="15.75" customHeight="1"/>
-    <row r="706" ht="15.75" customHeight="1"/>
-    <row r="707" ht="15.75" customHeight="1"/>
-    <row r="708" ht="15.75" customHeight="1"/>
-    <row r="709" ht="15.75" customHeight="1"/>
-    <row r="710" ht="15.75" customHeight="1"/>
-    <row r="711" ht="15.75" customHeight="1"/>
-    <row r="712" ht="15.75" customHeight="1"/>
-    <row r="713" ht="15.75" customHeight="1"/>
-    <row r="714" ht="15.75" customHeight="1"/>
-    <row r="715" ht="15.75" customHeight="1"/>
-    <row r="716" ht="15.75" customHeight="1"/>
-    <row r="717" ht="15.75" customHeight="1"/>
-    <row r="718" ht="15.75" customHeight="1"/>
-    <row r="719" ht="15.75" customHeight="1"/>
-    <row r="720" ht="15.75" customHeight="1"/>
-    <row r="721" ht="15.75" customHeight="1"/>
-    <row r="722" ht="15.75" customHeight="1"/>
-    <row r="723" ht="15.75" customHeight="1"/>
-    <row r="724" ht="15.75" customHeight="1"/>
-    <row r="725" ht="15.75" customHeight="1"/>
-    <row r="726" ht="15.75" customHeight="1"/>
-    <row r="727" ht="15.75" customHeight="1"/>
-    <row r="728" ht="15.75" customHeight="1"/>
-    <row r="729" ht="15.75" customHeight="1"/>
-    <row r="730" ht="15.75" customHeight="1"/>
-    <row r="731" ht="15.75" customHeight="1"/>
-    <row r="732" ht="15.75" customHeight="1"/>
-    <row r="733" ht="15.75" customHeight="1"/>
-    <row r="734" ht="15.75" customHeight="1"/>
-    <row r="735" ht="15.75" customHeight="1"/>
-    <row r="736" ht="15.75" customHeight="1"/>
-    <row r="737" ht="15.75" customHeight="1"/>
-    <row r="738" ht="15.75" customHeight="1"/>
-    <row r="739" ht="15.75" customHeight="1"/>
-    <row r="740" ht="15.75" customHeight="1"/>
-    <row r="741" ht="15.75" customHeight="1"/>
-    <row r="742" ht="15.75" customHeight="1"/>
-    <row r="743" ht="15.75" customHeight="1"/>
-    <row r="744" ht="15.75" customHeight="1"/>
-    <row r="745" ht="15.75" customHeight="1"/>
-    <row r="746" ht="15.75" customHeight="1"/>
-    <row r="747" ht="15.75" customHeight="1"/>
-    <row r="748" ht="15.75" customHeight="1"/>
-    <row r="749" ht="15.75" customHeight="1"/>
-    <row r="750" ht="15.75" customHeight="1"/>
-    <row r="751" ht="15.75" customHeight="1"/>
-    <row r="752" ht="15.75" customHeight="1"/>
-    <row r="753" ht="15.75" customHeight="1"/>
-    <row r="754" ht="15.75" customHeight="1"/>
-    <row r="755" ht="15.75" customHeight="1"/>
-    <row r="756" ht="15.75" customHeight="1"/>
-    <row r="757" ht="15.75" customHeight="1"/>
-    <row r="758" ht="15.75" customHeight="1"/>
-    <row r="759" ht="15.75" customHeight="1"/>
-    <row r="760" ht="15.75" customHeight="1"/>
-    <row r="761" ht="15.75" customHeight="1"/>
-    <row r="762" ht="15.75" customHeight="1"/>
-    <row r="763" ht="15.75" customHeight="1"/>
-    <row r="764" ht="15.75" customHeight="1"/>
-    <row r="765" ht="15.75" customHeight="1"/>
-    <row r="766" ht="15.75" customHeight="1"/>
-    <row r="767" ht="15.75" customHeight="1"/>
-    <row r="768" ht="15.75" customHeight="1"/>
-    <row r="769" ht="15.75" customHeight="1"/>
-    <row r="770" ht="15.75" customHeight="1"/>
-    <row r="771" ht="15.75" customHeight="1"/>
-    <row r="772" ht="15.75" customHeight="1"/>
-    <row r="773" ht="15.75" customHeight="1"/>
-    <row r="774" ht="15.75" customHeight="1"/>
-    <row r="775" ht="15.75" customHeight="1"/>
-    <row r="776" ht="15.75" customHeight="1"/>
-    <row r="777" ht="15.75" customHeight="1"/>
-    <row r="778" ht="15.75" customHeight="1"/>
-    <row r="779" ht="15.75" customHeight="1"/>
-    <row r="780" ht="15.75" customHeight="1"/>
-    <row r="781" ht="15.75" customHeight="1"/>
-    <row r="782" ht="15.75" customHeight="1"/>
-    <row r="783" ht="15.75" customHeight="1"/>
-    <row r="784" ht="15.75" customHeight="1"/>
-    <row r="785" ht="15.75" customHeight="1"/>
-    <row r="786" ht="15.75" customHeight="1"/>
-    <row r="787" ht="15.75" customHeight="1"/>
-    <row r="788" ht="15.75" customHeight="1"/>
-    <row r="789" ht="15.75" customHeight="1"/>
-    <row r="790" ht="15.75" customHeight="1"/>
-    <row r="791" ht="15.75" customHeight="1"/>
-    <row r="792" ht="15.75" customHeight="1"/>
-    <row r="793" ht="15.75" customHeight="1"/>
-    <row r="794" ht="15.75" customHeight="1"/>
-    <row r="795" ht="15.75" customHeight="1"/>
-    <row r="796" ht="15.75" customHeight="1"/>
-    <row r="797" ht="15.75" customHeight="1"/>
-    <row r="798" ht="15.75" customHeight="1"/>
-    <row r="799" ht="15.75" customHeight="1"/>
-    <row r="800" ht="15.75" customHeight="1"/>
-    <row r="801" ht="15.75" customHeight="1"/>
-    <row r="802" ht="15.75" customHeight="1"/>
-    <row r="803" ht="15.75" customHeight="1"/>
-    <row r="804" ht="15.75" customHeight="1"/>
-    <row r="805" ht="15.75" customHeight="1"/>
-    <row r="806" ht="15.75" customHeight="1"/>
-    <row r="807" ht="15.75" customHeight="1"/>
+    <row r="126" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="127" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="128" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="G4:Q11 G13:Q16 G23:Q25">
@@ -16022,16 +16033,16 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:U118"/>
-  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="6.1328125" customWidth="1"/>
+    <col min="1" max="1" width="6.1640625" customWidth="1"/>
     <col min="2" max="9" width="20.6640625" customWidth="1"/>
-    <col min="10" max="11" width="11.1328125" customWidth="1"/>
+    <col min="10" max="11" width="11.1640625" customWidth="1"/>
     <col min="12" max="12" width="20.6640625" customWidth="1"/>
     <col min="13" max="13" width="5.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:15" ht="13.9">
+    <row r="2" spans="2:15" ht="16" x14ac:dyDescent="0.25">
       <c r="B2" s="34" t="s">
         <v>52</v>
       </c>
@@ -16046,7 +16057,7 @@
       <c r="K2" s="35"/>
       <c r="L2" s="35"/>
     </row>
-    <row r="3" spans="2:15" ht="13.15">
+    <row r="3" spans="2:15" x14ac:dyDescent="0.15">
       <c r="B3" s="106" t="s">
         <v>136</v>
       </c>
@@ -16061,7 +16072,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="4" spans="2:15">
+    <row r="4" spans="2:15" x14ac:dyDescent="0.15">
       <c r="B4" s="97" t="s">
         <v>393</v>
       </c>
@@ -16093,7 +16104,7 @@
       </c>
       <c r="J4" s="305"/>
     </row>
-    <row r="5" spans="2:15">
+    <row r="5" spans="2:15" x14ac:dyDescent="0.15">
       <c r="B5" s="187" t="s">
         <v>105</v>
       </c>
@@ -16121,7 +16132,7 @@
       </c>
       <c r="J5" s="305"/>
     </row>
-    <row r="6" spans="2:15" ht="13.25" customHeight="1">
+    <row r="6" spans="2:15" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B6" s="136" t="s">
         <v>194</v>
       </c>
@@ -16154,7 +16165,7 @@
       <c r="J6" s="305"/>
       <c r="N6" s="135"/>
     </row>
-    <row r="7" spans="2:15" ht="12.75" customHeight="1">
+    <row r="7" spans="2:15" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B7" s="318" t="s">
         <v>430</v>
       </c>
@@ -16184,7 +16195,7 @@
       <c r="N7" s="304"/>
       <c r="O7" s="304"/>
     </row>
-    <row r="8" spans="2:15" ht="13.15">
+    <row r="8" spans="2:15" ht="14" x14ac:dyDescent="0.15">
       <c r="B8" s="136" t="s">
         <v>426</v>
       </c>
@@ -16201,7 +16212,7 @@
       </c>
       <c r="F8" s="108">
         <f>FV_adjustments*scaling_factor/Common_Shares*Exchange_Rate</f>
-        <v>-10.409784166520426</v>
+        <v>-10.335004564602832</v>
       </c>
       <c r="G8" s="294" t="str">
         <f>Market_currency</f>
@@ -16219,14 +16230,14 @@
       <c r="N8" s="304"/>
       <c r="O8" s="304"/>
     </row>
-    <row r="9" spans="2:15" ht="13.15" thickBot="1">
+    <row r="9" spans="2:15" ht="14" thickBot="1" x14ac:dyDescent="0.2">
       <c r="B9" s="189" t="str">
         <f>"*"&amp;Thesis!E15</f>
         <v>*EUR/HKD</v>
       </c>
       <c r="C9" s="190">
         <f>Exchange_Rate</f>
-        <v>9.2771663694858564</v>
+        <v>9.2105230273246779</v>
       </c>
       <c r="D9" t="str">
         <f>Thesis!E15</f>
@@ -16245,13 +16256,13 @@
       <c r="N9" s="304"/>
       <c r="O9" s="304"/>
     </row>
-    <row r="10" spans="2:15" ht="13.5" thickTop="1">
+    <row r="10" spans="2:15" ht="14" thickTop="1" x14ac:dyDescent="0.15">
       <c r="B10" s="107" t="s">
         <v>427</v>
       </c>
       <c r="C10" s="283">
         <f>C8*Exchange_Rate</f>
-        <v>119355736.63469642</v>
+        <v>118498334.18241224</v>
       </c>
       <c r="D10" t="str">
         <f>Market_currency</f>
@@ -16267,13 +16278,13 @@
       <c r="N10" s="304"/>
       <c r="O10" s="304"/>
     </row>
-    <row r="11" spans="2:15" ht="13.15">
+    <row r="11" spans="2:15" x14ac:dyDescent="0.15">
       <c r="B11" s="136" t="s">
         <v>425</v>
       </c>
       <c r="C11" s="108">
         <f>(C10*scaling_factor)/Common_Shares</f>
-        <v>46.644762060499836</v>
+        <v>46.309685301690244</v>
       </c>
       <c r="D11" t="str">
         <f>Market_currency</f>
@@ -16283,7 +16294,7 @@
       <c r="I11" s="307"/>
       <c r="J11" s="307"/>
     </row>
-    <row r="13" spans="2:15" ht="13.9">
+    <row r="13" spans="2:15" ht="16" x14ac:dyDescent="0.25">
       <c r="B13" s="34" t="s">
         <v>428</v>
       </c>
@@ -16298,7 +16309,7 @@
       <c r="K13" s="35"/>
       <c r="L13" s="35"/>
     </row>
-    <row r="14" spans="2:15" ht="13.15">
+    <row r="14" spans="2:15" x14ac:dyDescent="0.15">
       <c r="B14" s="106" t="s">
         <v>399</v>
       </c>
@@ -16316,7 +16327,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="15" spans="2:15">
+    <row r="15" spans="2:15" x14ac:dyDescent="0.15">
       <c r="B15" s="139" t="s">
         <v>421</v>
       </c>
@@ -16341,7 +16352,7 @@
       </c>
       <c r="J15" s="126"/>
     </row>
-    <row r="16" spans="2:15" ht="13.25" customHeight="1">
+    <row r="16" spans="2:15" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B16" s="114" t="s">
         <v>422</v>
       </c>
@@ -16357,7 +16368,7 @@
         <v>4.584597022756233E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:21" ht="13.25" customHeight="1">
+    <row r="17" spans="1:21" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B17" s="308" t="s">
         <v>550</v>
       </c>
@@ -16376,7 +16387,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="18" spans="1:21" ht="13.25" customHeight="1">
+    <row r="18" spans="1:21" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B18" s="308" t="s">
         <v>423</v>
       </c>
@@ -16396,17 +16407,17 @@
       </c>
       <c r="I18" s="129">
         <f>(L52+FV_adjustments)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>60.136370439093248</v>
+        <v>59.704375522554315</v>
       </c>
       <c r="J18" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="19" spans="1:21">
+    <row r="19" spans="1:21" x14ac:dyDescent="0.15">
       <c r="L19" s="275"/>
     </row>
-    <row r="20" spans="1:21" ht="13.15">
+    <row r="20" spans="1:21" ht="14" x14ac:dyDescent="0.2">
       <c r="A20" s="121" t="s">
         <v>399</v>
       </c>
@@ -16445,7 +16456,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="21" spans="1:21">
+    <row r="21" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A21" s="302" t="str">
         <f t="shared" ref="A21:A50" si="0">IF($C$15&lt;B21,"",IF(B21&gt;=$F$15,"II","I"))</f>
         <v>I</v>
@@ -16494,7 +16505,7 @@
         <v>789850.47609109606</v>
       </c>
     </row>
-    <row r="22" spans="1:21">
+    <row r="22" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A22" s="302" t="str">
         <f t="shared" si="0"/>
         <v>I</v>
@@ -16543,7 +16554,7 @@
         <v>770220.92074796697</v>
       </c>
     </row>
-    <row r="23" spans="1:21">
+    <row r="23" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A23" s="302" t="str">
         <f t="shared" si="0"/>
         <v>I</v>
@@ -16600,7 +16611,7 @@
       <c r="T23" s="275"/>
       <c r="U23" s="275"/>
     </row>
-    <row r="24" spans="1:21">
+    <row r="24" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A24" s="302" t="str">
         <f t="shared" si="0"/>
         <v>I</v>
@@ -16657,7 +16668,7 @@
       <c r="T24" s="275"/>
       <c r="U24" s="275"/>
     </row>
-    <row r="25" spans="1:21">
+    <row r="25" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A25" s="302" t="str">
         <f t="shared" si="0"/>
         <v>I</v>
@@ -16714,7 +16725,7 @@
       <c r="T25" s="275"/>
       <c r="U25" s="275"/>
     </row>
-    <row r="26" spans="1:21">
+    <row r="26" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A26" s="302" t="str">
         <f t="shared" si="0"/>
         <v>I</v>
@@ -16763,7 +16774,7 @@
         <v>696461.34425767313</v>
       </c>
     </row>
-    <row r="27" spans="1:21">
+    <row r="27" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A27" s="302" t="str">
         <f t="shared" si="0"/>
         <v>I</v>
@@ -16812,7 +16823,7 @@
         <v>679152.71823884244</v>
       </c>
     </row>
-    <row r="28" spans="1:21">
+    <row r="28" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A28" s="302" t="str">
         <f t="shared" si="0"/>
         <v>I</v>
@@ -16861,7 +16872,7 @@
         <v>662274.25038618979</v>
       </c>
     </row>
-    <row r="29" spans="1:21">
+    <row r="29" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A29" s="302" t="str">
         <f t="shared" si="0"/>
         <v>I</v>
@@ -16910,7 +16921,7 @@
         <v>645815.25030477962</v>
       </c>
     </row>
-    <row r="30" spans="1:21">
+    <row r="30" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A30" s="302" t="str">
         <f t="shared" si="0"/>
         <v>I</v>
@@ -16959,7 +16970,7 @@
         <v>629765.2932799611</v>
       </c>
     </row>
-    <row r="31" spans="1:21">
+    <row r="31" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A31" s="302" t="str">
         <f t="shared" si="0"/>
         <v>I</v>
@@ -17008,7 +17019,7 @@
         <v>614114.21367461688</v>
       </c>
     </row>
-    <row r="32" spans="1:21">
+    <row r="32" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A32" s="302" t="str">
         <f t="shared" si="0"/>
         <v>I</v>
@@ -17057,7 +17068,7 @@
         <v>598852.09849050455</v>
       </c>
     </row>
-    <row r="33" spans="1:21">
+    <row r="33" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A33" s="302" t="str">
         <f t="shared" si="0"/>
         <v>I</v>
@@ -17114,7 +17125,7 @@
       <c r="T33" s="275"/>
       <c r="U33" s="275"/>
     </row>
-    <row r="34" spans="1:21">
+    <row r="34" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A34" s="302" t="str">
         <f t="shared" si="0"/>
         <v>I</v>
@@ -17171,7 +17182,7 @@
       <c r="T34" s="275"/>
       <c r="U34" s="275"/>
     </row>
-    <row r="35" spans="1:21">
+    <row r="35" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A35" s="302" t="str">
         <f t="shared" si="0"/>
         <v>I</v>
@@ -17228,7 +17239,7 @@
       <c r="T35" s="275"/>
       <c r="U35" s="275"/>
     </row>
-    <row r="36" spans="1:21">
+    <row r="36" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A36" s="302" t="str">
         <f t="shared" si="0"/>
         <v>I</v>
@@ -17277,7 +17288,7 @@
         <v>541503.51709636569</v>
       </c>
     </row>
-    <row r="37" spans="1:21">
+    <row r="37" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A37" s="302" t="str">
         <f t="shared" si="0"/>
         <v>I</v>
@@ -17326,7 +17337,7 @@
         <v>528045.94053080282</v>
       </c>
     </row>
-    <row r="38" spans="1:21">
+    <row r="38" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A38" s="302" t="str">
         <f t="shared" si="0"/>
         <v>I</v>
@@ -17375,7 +17386,7 @@
         <v>514922.81491763471</v>
       </c>
     </row>
-    <row r="39" spans="1:21">
+    <row r="39" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A39" s="302" t="str">
         <f t="shared" si="0"/>
         <v>I</v>
@@ -17424,7 +17435,7 @@
         <v>502125.82840078446</v>
       </c>
     </row>
-    <row r="40" spans="1:21">
+    <row r="40" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A40" s="302" t="str">
         <f t="shared" si="0"/>
         <v>I</v>
@@ -17473,7 +17484,7 @@
         <v>489646.87569243525</v>
       </c>
     </row>
-    <row r="41" spans="1:21">
+    <row r="41" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A41" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17522,7 +17533,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:21">
+    <row r="42" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A42" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17571,7 +17582,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:21">
+    <row r="43" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A43" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17620,7 +17631,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:21">
+    <row r="44" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A44" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17669,7 +17680,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:21">
+    <row r="45" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A45" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17718,7 +17729,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:21">
+    <row r="46" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A46" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17767,7 +17778,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:21">
+    <row r="47" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A47" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17824,7 +17835,7 @@
       <c r="T47" s="275"/>
       <c r="U47" s="275"/>
     </row>
-    <row r="48" spans="1:21">
+    <row r="48" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A48" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17881,7 +17892,7 @@
       <c r="T48" s="275"/>
       <c r="U48" s="275"/>
     </row>
-    <row r="49" spans="1:21">
+    <row r="49" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A49" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17938,7 +17949,7 @@
       <c r="T49" s="275"/>
       <c r="U49" s="275"/>
     </row>
-    <row r="50" spans="1:21">
+    <row r="50" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A50" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17995,7 +18006,7 @@
       <c r="T50" s="275"/>
       <c r="U50" s="275"/>
     </row>
-    <row r="51" spans="1:21">
+    <row r="51" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A51" s="315" t="s">
         <v>418</v>
       </c>
@@ -18041,7 +18052,7 @@
         <v>6888825.0097418465</v>
       </c>
     </row>
-    <row r="52" spans="1:21" ht="13.15">
+    <row r="52" spans="1:21" x14ac:dyDescent="0.15">
       <c r="G52" s="111"/>
       <c r="H52" s="111"/>
       <c r="I52" s="111"/>
@@ -18054,10 +18065,10 @@
         <v>19458009.733047292</v>
       </c>
     </row>
-    <row r="53" spans="1:21">
+    <row r="53" spans="1:21" x14ac:dyDescent="0.15">
       <c r="C53" s="111"/>
     </row>
-    <row r="54" spans="1:21" ht="13.15">
+    <row r="54" spans="1:21" x14ac:dyDescent="0.15">
       <c r="B54" s="115" t="s">
         <v>108</v>
       </c>
@@ -18072,7 +18083,7 @@
       <c r="K54" s="113"/>
       <c r="L54" s="113"/>
     </row>
-    <row r="55" spans="1:21" ht="13.15">
+    <row r="55" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A55" s="125">
         <f>L52</f>
         <v>19458009.733047292</v>
@@ -18104,7 +18115,7 @@
       <c r="K55" s="123"/>
       <c r="L55" s="123"/>
     </row>
-    <row r="56" spans="1:21" ht="13.15">
+    <row r="56" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A56" s="131">
         <v>1</v>
       </c>
@@ -18131,7 +18142,7 @@
       <c r="K56" s="295"/>
       <c r="L56" s="295"/>
     </row>
-    <row r="57" spans="1:21" ht="13.15">
+    <row r="57" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A57" s="131">
         <v>2</v>
       </c>
@@ -18157,7 +18168,7 @@
       <c r="K57" s="295"/>
       <c r="L57" s="295"/>
     </row>
-    <row r="58" spans="1:21" ht="13.15">
+    <row r="58" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A58" s="131">
         <v>3</v>
       </c>
@@ -18183,7 +18194,7 @@
       <c r="K58" s="295"/>
       <c r="L58" s="295"/>
     </row>
-    <row r="59" spans="1:21" ht="13.15">
+    <row r="59" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A59" s="131">
         <v>4</v>
       </c>
@@ -18209,7 +18220,7 @@
       <c r="K59" s="295"/>
       <c r="L59" s="295"/>
     </row>
-    <row r="60" spans="1:21" ht="13.15">
+    <row r="60" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A60" s="131">
         <v>5</v>
       </c>
@@ -18235,7 +18246,7 @@
       <c r="K60" s="295"/>
       <c r="L60" s="295"/>
     </row>
-    <row r="61" spans="1:21" ht="13.15">
+    <row r="61" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A61" s="131">
         <v>6</v>
       </c>
@@ -18261,7 +18272,7 @@
       <c r="K61" s="295"/>
       <c r="L61" s="295"/>
     </row>
-    <row r="62" spans="1:21" ht="13.15">
+    <row r="62" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A62" s="131">
         <v>7</v>
       </c>
@@ -18287,7 +18298,7 @@
       <c r="K62" s="295"/>
       <c r="L62" s="295"/>
     </row>
-    <row r="63" spans="1:21" ht="13.15">
+    <row r="63" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A63" s="131">
         <v>8</v>
       </c>
@@ -18313,7 +18324,7 @@
       <c r="K63" s="295"/>
       <c r="L63" s="295"/>
     </row>
-    <row r="64" spans="1:21" ht="13.15">
+    <row r="64" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A64" s="131">
         <v>9</v>
       </c>
@@ -18339,7 +18350,7 @@
       <c r="K64" s="295"/>
       <c r="L64" s="295"/>
     </row>
-    <row r="65" spans="1:21" ht="13.15">
+    <row r="65" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A65" s="131">
         <v>10</v>
       </c>
@@ -18365,7 +18376,7 @@
       <c r="K65" s="295"/>
       <c r="L65" s="295"/>
     </row>
-    <row r="66" spans="1:21" ht="13.15">
+    <row r="66" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A66" s="131">
         <v>15</v>
       </c>
@@ -18400,7 +18411,7 @@
       <c r="T66" s="275"/>
       <c r="U66" s="275"/>
     </row>
-    <row r="67" spans="1:21" ht="13.15">
+    <row r="67" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A67" s="132">
         <v>20</v>
       </c>
@@ -18435,7 +18446,7 @@
       <c r="T67" s="275"/>
       <c r="U67" s="275"/>
     </row>
-    <row r="68" spans="1:21" ht="13.15">
+    <row r="68" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A68" s="132">
         <v>25</v>
       </c>
@@ -18470,7 +18481,7 @@
       <c r="T68" s="275"/>
       <c r="U68" s="275"/>
     </row>
-    <row r="69" spans="1:21" ht="13.15">
+    <row r="69" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A69" s="132">
         <v>30</v>
       </c>
@@ -18505,7 +18516,7 @@
       <c r="T69" s="275"/>
       <c r="U69" s="275"/>
     </row>
-    <row r="70" spans="1:21">
+    <row r="70" spans="1:21" x14ac:dyDescent="0.15">
       <c r="C70" s="275"/>
       <c r="D70" s="111"/>
       <c r="E70" s="111"/>
@@ -18526,7 +18537,7 @@
       <c r="T70" s="275"/>
       <c r="U70" s="275"/>
     </row>
-    <row r="71" spans="1:21" ht="13.15">
+    <row r="71" spans="1:21" x14ac:dyDescent="0.15">
       <c r="B71" s="115" t="s">
         <v>109</v>
       </c>
@@ -18550,7 +18561,7 @@
       <c r="T71" s="275"/>
       <c r="U71" s="275"/>
     </row>
-    <row r="72" spans="1:21" ht="13.15">
+    <row r="72" spans="1:21" x14ac:dyDescent="0.15">
       <c r="B72" s="124">
         <f>B55</f>
         <v>0</v>
@@ -18578,29 +18589,29 @@
       <c r="K72" s="124"/>
       <c r="L72" s="124"/>
     </row>
-    <row r="73" spans="1:21" ht="13.15">
+    <row r="73" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A73" s="131">
         <v>0</v>
       </c>
       <c r="B73" s="119">
         <f>C11</f>
-        <v>46.644762060499836</v>
+        <v>46.309685301690244</v>
       </c>
       <c r="C73" s="119">
         <f>C11</f>
-        <v>46.644762060499836</v>
+        <v>46.309685301690244</v>
       </c>
       <c r="D73" s="119">
         <f>C11</f>
-        <v>46.644762060499836</v>
+        <v>46.309685301690244</v>
       </c>
       <c r="E73" s="119">
         <f>C11</f>
-        <v>46.644762060499836</v>
+        <v>46.309685301690244</v>
       </c>
       <c r="F73" s="119">
         <f>C11</f>
-        <v>46.644762060499836</v>
+        <v>46.309685301690244</v>
       </c>
       <c r="G73" s="296"/>
       <c r="H73" s="296"/>
@@ -18609,29 +18620,29 @@
       <c r="K73" s="296"/>
       <c r="L73" s="296"/>
     </row>
-    <row r="74" spans="1:21" ht="13.15">
+    <row r="74" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A74" s="131">
         <v>1</v>
       </c>
       <c r="B74" s="119">
         <f t="shared" ref="B74:F87" si="11">(B56+FV_adjustments)/Common_Shares*scaling_factor*Exchange_Rate</f>
-        <v>30.850814543734316</v>
+        <v>30.6291949987457</v>
       </c>
       <c r="C74" s="119">
         <f t="shared" si="11"/>
-        <v>31.676026517939402</v>
+        <v>31.44847899001266</v>
       </c>
       <c r="D74" s="119">
         <f t="shared" si="11"/>
-        <v>32.501238492144502</v>
+        <v>32.267762981279638</v>
       </c>
       <c r="E74" s="119">
         <f t="shared" si="11"/>
-        <v>33.326450466349584</v>
+        <v>33.087046972546595</v>
       </c>
       <c r="F74" s="119">
         <f t="shared" si="11"/>
-        <v>34.151662440554688</v>
+        <v>33.906330963813573</v>
       </c>
       <c r="G74" s="296"/>
       <c r="H74" s="296"/>
@@ -18640,29 +18651,29 @@
       <c r="K74" s="296"/>
       <c r="L74" s="296"/>
     </row>
-    <row r="75" spans="1:21" ht="13.15">
+    <row r="75" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A75" s="131">
         <v>2</v>
       </c>
       <c r="B75" s="119">
         <f t="shared" si="11"/>
-        <v>30.799754076889599</v>
+        <v>30.578501329264242</v>
       </c>
       <c r="C75" s="119">
         <f t="shared" si="11"/>
-        <v>32.408761824218587</v>
+        <v>32.175950627647232</v>
       </c>
       <c r="D75" s="119">
         <f t="shared" si="11"/>
-        <v>34.048546708114685</v>
+        <v>33.80395597232458</v>
       </c>
       <c r="E75" s="119">
         <f t="shared" si="11"/>
-        <v>35.719108728577844</v>
+        <v>35.462517363296243</v>
       </c>
       <c r="F75" s="119">
         <f t="shared" si="11"/>
-        <v>37.42044788560812</v>
+        <v>37.15163480056227</v>
       </c>
       <c r="G75" s="296"/>
       <c r="H75" s="296"/>
@@ -18671,29 +18682,29 @@
       <c r="K75" s="296"/>
       <c r="L75" s="296"/>
     </row>
-    <row r="76" spans="1:21" ht="13.15">
+    <row r="76" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A76" s="131">
         <v>3</v>
       </c>
       <c r="B76" s="119">
         <f t="shared" si="11"/>
-        <v>30.752145249994769</v>
+        <v>30.531234504572918</v>
       </c>
       <c r="C76" s="119">
         <f t="shared" si="11"/>
-        <v>33.105628968651935</v>
+        <v>32.867811765537446</v>
       </c>
       <c r="D76" s="119">
         <f t="shared" si="11"/>
-        <v>35.548966796328173</v>
+        <v>35.293597660610565</v>
       </c>
       <c r="E76" s="119">
         <f t="shared" si="11"/>
-        <v>38.083880530873365</v>
+        <v>37.810301618955549</v>
       </c>
       <c r="F76" s="119">
         <f t="shared" si="11"/>
-        <v>40.712091970137415</v>
+        <v>40.419633069735738</v>
       </c>
       <c r="G76" s="296"/>
       <c r="H76" s="296"/>
@@ -18702,29 +18713,29 @@
       <c r="K76" s="296"/>
       <c r="L76" s="296"/>
     </row>
-    <row r="77" spans="1:21" ht="13.15">
+    <row r="77" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A77" s="131">
         <v>4</v>
       </c>
       <c r="B77" s="119">
         <f t="shared" si="11"/>
-        <v>30.707754735407502</v>
+        <v>30.487162873159082</v>
       </c>
       <c r="C77" s="119">
         <f t="shared" si="11"/>
-        <v>33.768383735385747</v>
+        <v>33.525805574999474</v>
       </c>
       <c r="D77" s="119">
         <f t="shared" si="11"/>
-        <v>37.003919609141256</v>
+        <v>36.738098691675766</v>
       </c>
       <c r="E77" s="119">
         <f t="shared" si="11"/>
-        <v>40.421090890251669</v>
+        <v>40.130722421751692</v>
       </c>
       <c r="F77" s="119">
         <f t="shared" si="11"/>
-        <v>44.02675454476833</v>
+        <v>43.710484473658688</v>
       </c>
       <c r="G77" s="296"/>
       <c r="H77" s="296"/>
@@ -18733,29 +18744,29 @@
       <c r="K77" s="296"/>
       <c r="L77" s="296"/>
     </row>
-    <row r="78" spans="1:21" ht="13.15">
+    <row r="78" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A78" s="131">
         <v>5</v>
       </c>
       <c r="B78" s="119">
         <f t="shared" si="11"/>
-        <v>30.666364978216581</v>
+        <v>30.446070442936396</v>
       </c>
       <c r="C78" s="119">
         <f t="shared" si="11"/>
-        <v>34.398695961090631</v>
+        <v>34.151589897285035</v>
       </c>
       <c r="D78" s="119">
         <f t="shared" si="11"/>
-        <v>38.414782942778174</v>
+        <v>38.138826964223824</v>
       </c>
       <c r="E78" s="119">
         <f t="shared" si="11"/>
-        <v>42.731061035651216</v>
+        <v>42.424098693046709</v>
       </c>
       <c r="F78" s="119">
         <f t="shared" si="11"/>
-        <v>47.364596577963091</v>
+        <v>47.024348824462223</v>
       </c>
       <c r="G78" s="296"/>
       <c r="H78" s="296"/>
@@ -18764,29 +18775,29 @@
       <c r="K78" s="296"/>
       <c r="L78" s="296"/>
     </row>
-    <row r="79" spans="1:21" ht="13.15">
+    <row r="79" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A79" s="131">
         <v>6</v>
       </c>
       <c r="B79" s="119">
         <f t="shared" si="11"/>
-        <v>30.627773130019925</v>
+        <v>30.407755822682148</v>
       </c>
       <c r="C79" s="119">
         <f t="shared" si="11"/>
-        <v>34.998153742180591</v>
+        <v>34.746741420577592</v>
       </c>
       <c r="D79" s="119">
         <f t="shared" si="11"/>
-        <v>39.782892842062495</v>
+        <v>39.497108925482586</v>
       </c>
       <c r="E79" s="119">
         <f t="shared" si="11"/>
-        <v>45.014108452083406</v>
+        <v>44.690745637170465</v>
       </c>
       <c r="F79" s="119">
         <f t="shared" si="11"/>
-        <v>50.725780163837541</v>
+        <v>50.361387051844801</v>
       </c>
       <c r="G79" s="296"/>
       <c r="H79" s="296"/>
@@ -18795,30 +18806,30 @@
       <c r="K79" s="296"/>
       <c r="L79" s="296"/>
     </row>
-    <row r="80" spans="1:21" ht="13.15">
+    <row r="80" spans="1:21" x14ac:dyDescent="0.15">
       <c r="A80" s="131">
         <f t="shared" ref="A80" si="12">A62</f>
         <v>7</v>
       </c>
       <c r="B80" s="119">
         <f t="shared" si="11"/>
-        <v>30.591790054778286</v>
+        <v>30.372031235032498</v>
       </c>
       <c r="C80" s="119">
         <f t="shared" si="11"/>
-        <v>35.568267436084334</v>
+        <v>35.312759652520178</v>
       </c>
       <c r="D80" s="119">
         <f t="shared" si="11"/>
-        <v>41.109544865610914</v>
+        <v>40.814230827309252</v>
       </c>
       <c r="E80" s="119">
         <f t="shared" si="11"/>
-        <v>47.270546924268125</v>
+        <v>46.930974784742652</v>
       </c>
       <c r="F80" s="119">
         <f t="shared" si="11"/>
-        <v>54.110468530032804</v>
+        <v>53.721761210887408</v>
       </c>
       <c r="G80" s="296"/>
       <c r="H80" s="296"/>
@@ -18827,29 +18838,29 @@
       <c r="K80" s="296"/>
       <c r="L80" s="296"/>
     </row>
-    <row r="81" spans="1:12" ht="13.15">
+    <row r="81" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A81" s="131">
         <v>8</v>
       </c>
       <c r="B81" s="119">
         <f t="shared" si="11"/>
-        <v>30.55823940187231</v>
+        <v>30.338721596198308</v>
       </c>
       <c r="C81" s="119">
         <f t="shared" si="11"/>
-        <v>36.110473466650127</v>
+        <v>35.851070698283749</v>
       </c>
       <c r="D81" s="119">
         <f t="shared" si="11"/>
-        <v>42.395995312688164</v>
+        <v>42.091439944232071</v>
       </c>
       <c r="E81" s="119">
         <f t="shared" si="11"/>
-        <v>49.500686579760725</v>
+        <v>49.145094035490004</v>
       </c>
       <c r="F81" s="119">
         <f t="shared" si="11"/>
-        <v>57.518826045641994</v>
+        <v>57.105634489923297</v>
       </c>
       <c r="G81" s="296"/>
       <c r="H81" s="296"/>
@@ -18858,30 +18869,30 @@
       <c r="K81" s="296"/>
       <c r="L81" s="296"/>
     </row>
-    <row r="82" spans="1:12" ht="13.15">
+    <row r="82" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A82" s="131">
         <f t="shared" ref="A82" si="13">A64</f>
         <v>9</v>
       </c>
       <c r="B82" s="119">
         <f t="shared" si="11"/>
-        <v>30.526956741820136</v>
+        <v>30.307663657891389</v>
       </c>
       <c r="C82" s="119">
         <f t="shared" si="11"/>
-        <v>36.626137943272141</v>
+        <v>36.363030853695257</v>
       </c>
       <c r="D82" s="119">
         <f t="shared" si="11"/>
-        <v>43.643462412884276</v>
+        <v>43.329945754581473</v>
       </c>
       <c r="E82" s="119">
         <f t="shared" si="11"/>
-        <v>51.70483393157626</v>
+        <v>51.333407700564308</v>
       </c>
       <c r="F82" s="119">
         <f t="shared" si="11"/>
-        <v>60.951018229192506</v>
+        <v>60.513171218462929</v>
       </c>
       <c r="G82" s="296"/>
       <c r="H82" s="296"/>
@@ -18890,30 +18901,30 @@
       <c r="K82" s="296"/>
       <c r="L82" s="296"/>
     </row>
-    <row r="83" spans="1:12" ht="13.15">
+    <row r="83" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A83" s="131">
         <f t="shared" ref="A83:A87" si="14">A65</f>
         <v>10</v>
       </c>
       <c r="B83" s="119">
         <f t="shared" si="11"/>
-        <v>30.497788760419507</v>
+        <v>30.278705207255562</v>
       </c>
       <c r="C83" s="119">
         <f t="shared" si="11"/>
-        <v>37.116560102856717</v>
+        <v>36.849930022478226</v>
       </c>
       <c r="D83" s="119">
         <f t="shared" si="11"/>
-        <v>44.853127479741097</v>
+        <v>44.530921085829355</v>
       </c>
       <c r="E83" s="119">
         <f t="shared" si="11"/>
-        <v>53.883291920316999</v>
+        <v>53.496216544367329</v>
       </c>
       <c r="F83" s="119">
         <f t="shared" si="11"/>
-        <v>64.407211756683949</v>
+        <v>63.944536875174201</v>
       </c>
       <c r="G83" s="296"/>
       <c r="H83" s="296"/>
@@ -18922,30 +18933,30 @@
       <c r="K83" s="296"/>
       <c r="L83" s="296"/>
     </row>
-    <row r="84" spans="1:12" ht="13.15">
+    <row r="84" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A84" s="131">
         <f t="shared" si="14"/>
         <v>15</v>
       </c>
       <c r="B84" s="119">
         <f t="shared" si="11"/>
-        <v>30.378990576544854</v>
+        <v>30.160760420603811</v>
       </c>
       <c r="C84" s="119">
         <f t="shared" si="11"/>
-        <v>39.231227639840938</v>
+        <v>38.949406658856425</v>
       </c>
       <c r="D84" s="119">
         <f t="shared" si="11"/>
-        <v>50.373322305894852</v>
+        <v>50.011461105984829</v>
       </c>
       <c r="E84" s="119">
         <f t="shared" si="11"/>
-        <v>64.400599475726722</v>
+        <v>63.937972094119921</v>
       </c>
       <c r="F84" s="119">
         <f t="shared" si="11"/>
-        <v>82.054115260935347</v>
+        <v>81.464672292977625</v>
       </c>
       <c r="G84" s="296"/>
       <c r="H84" s="296"/>
@@ -18954,30 +18965,30 @@
       <c r="K84" s="296"/>
       <c r="L84" s="296"/>
     </row>
-    <row r="85" spans="1:12" ht="13.15">
+    <row r="85" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A85" s="132">
         <f t="shared" si="14"/>
         <v>20</v>
       </c>
       <c r="B85" s="119">
         <f t="shared" si="11"/>
-        <v>30.295271718236478</v>
+        <v>30.07764296409178</v>
       </c>
       <c r="C85" s="119">
         <f t="shared" si="11"/>
-        <v>40.876570658741464</v>
+        <v>40.582930211185598</v>
       </c>
       <c r="D85" s="119">
         <f t="shared" si="11"/>
-        <v>55.106301528076884</v>
+        <v>54.710440554832722</v>
       </c>
       <c r="E85" s="119">
         <f t="shared" si="11"/>
-        <v>74.319131414226234</v>
+        <v>73.785253384373206</v>
       </c>
       <c r="F85" s="119">
         <f t="shared" si="11"/>
-        <v>100.32673363685144</v>
+        <v>99.606027704524323</v>
       </c>
       <c r="G85" s="296"/>
       <c r="H85" s="296"/>
@@ -18986,30 +18997,30 @@
       <c r="K85" s="296"/>
       <c r="L85" s="296"/>
     </row>
-    <row r="86" spans="1:12" ht="13.15">
+    <row r="86" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A86" s="132">
         <f t="shared" si="14"/>
         <v>25</v>
       </c>
       <c r="B86" s="119">
         <f t="shared" si="11"/>
-        <v>30.236273785710395</v>
+        <v>30.019068848413163</v>
       </c>
       <c r="C86" s="119">
         <f t="shared" si="11"/>
-        <v>42.156749978893821</v>
+        <v>41.853913250376422</v>
       </c>
       <c r="D86" s="119">
         <f t="shared" si="11"/>
-        <v>59.164327199829295</v>
+        <v>58.739315041560467</v>
       </c>
       <c r="E86" s="119">
         <f t="shared" si="11"/>
-        <v>83.672977471949764</v>
+        <v>83.071905264637735</v>
       </c>
       <c r="F86" s="119">
         <f t="shared" si="11"/>
-        <v>119.24725316207164</v>
+        <v>118.39063001037312</v>
       </c>
       <c r="G86" s="296"/>
       <c r="H86" s="296"/>
@@ -19018,30 +19029,30 @@
       <c r="K86" s="296"/>
       <c r="L86" s="296"/>
     </row>
-    <row r="87" spans="1:12" ht="13.15">
+    <row r="87" spans="1:12" x14ac:dyDescent="0.15">
       <c r="A87" s="132">
         <f t="shared" si="14"/>
         <v>30</v>
       </c>
       <c r="B87" s="119">
         <f t="shared" si="11"/>
-        <v>30.194697059597733</v>
+        <v>29.97779079237646</v>
       </c>
       <c r="C87" s="119">
         <f t="shared" si="11"/>
-        <v>43.152809203578101</v>
+        <v>42.842817195842933</v>
       </c>
       <c r="D87" s="119">
         <f t="shared" si="11"/>
-        <v>62.643652077365864</v>
+        <v>62.193645882225368</v>
       </c>
       <c r="E87" s="119">
         <f t="shared" si="11"/>
-        <v>92.494286574355698</v>
+        <v>91.829845715732773</v>
       </c>
       <c r="F87" s="119">
         <f t="shared" si="11"/>
-        <v>138.83864678391163</v>
+        <v>137.84128712964815</v>
       </c>
       <c r="G87" s="296"/>
       <c r="H87" s="296"/>
@@ -19050,7 +19061,7 @@
       <c r="K87" s="296"/>
       <c r="L87" s="296"/>
     </row>
-    <row r="89" spans="1:12" ht="13.15">
+    <row r="89" spans="1:12" ht="14" x14ac:dyDescent="0.2">
       <c r="B89" s="153" t="s">
         <v>101</v>
       </c>
@@ -19073,7 +19084,7 @@
       <c r="K89" s="323"/>
       <c r="L89" s="323"/>
     </row>
-    <row r="90" spans="1:12">
+    <row r="90" spans="1:12" x14ac:dyDescent="0.15">
       <c r="B90" s="120" t="str">
         <f>Scenarios!B29</f>
         <v>Snowball Scenario</v>
@@ -19088,7 +19099,7 @@
       </c>
       <c r="E90" s="127">
         <f>INDEX(B$73:F$87, MATCH(D90, A$73:A$87, 0), MATCH(C90, B$72:F$72, 0))</f>
-        <v>100.32673363685144</v>
+        <v>99.606027704524323</v>
       </c>
       <c r="F90" s="130">
         <f>Scenarios!F29</f>
@@ -19101,7 +19112,7 @@
       <c r="K90" s="297"/>
       <c r="L90" s="297"/>
     </row>
-    <row r="91" spans="1:12">
+    <row r="91" spans="1:12" x14ac:dyDescent="0.15">
       <c r="B91" s="120" t="str">
         <f>Scenarios!B22</f>
         <v>Optimistic</v>
@@ -19116,7 +19127,7 @@
       </c>
       <c r="E91" s="127">
         <f>INDEX(B$73:F$87, MATCH(D91, A$73:A$87, 0), MATCH(C91, B$72:F$72, 0))</f>
-        <v>74.319131414226234</v>
+        <v>73.785253384373206</v>
       </c>
       <c r="F91" s="130">
         <f>Scenarios!F22*(1-F$90-F$94)</f>
@@ -19129,7 +19140,7 @@
       <c r="K91" s="297"/>
       <c r="L91" s="297"/>
     </row>
-    <row r="92" spans="1:12">
+    <row r="92" spans="1:12" x14ac:dyDescent="0.15">
       <c r="B92" s="120" t="str">
         <f>Scenarios!B23</f>
         <v>Base</v>
@@ -19144,7 +19155,7 @@
       </c>
       <c r="E92" s="127">
         <f>INDEX(B$73:F$87, MATCH(D92, A$73:A$87, 0), MATCH(C92, B$72:F$72, 0))</f>
-        <v>55.106301528076884</v>
+        <v>54.710440554832722</v>
       </c>
       <c r="F92" s="130">
         <f>Scenarios!F23*(1-F$90-F$94)</f>
@@ -19157,7 +19168,7 @@
       <c r="K92" s="297"/>
       <c r="L92" s="297"/>
     </row>
-    <row r="93" spans="1:12">
+    <row r="93" spans="1:12" x14ac:dyDescent="0.15">
       <c r="B93" s="120" t="str">
         <f>Scenarios!B24</f>
         <v>Pessimistic</v>
@@ -19172,7 +19183,7 @@
       </c>
       <c r="E93" s="127">
         <f>INDEX(B$73:F$87, MATCH(D93, A$73:A$87, 0), MATCH(C93, B$72:F$72, 0))</f>
-        <v>40.876570658741464</v>
+        <v>40.582930211185598</v>
       </c>
       <c r="F93" s="130">
         <f>Scenarios!F24*(1-F$90-F$94)</f>
@@ -19185,7 +19196,7 @@
       <c r="K93" s="297"/>
       <c r="L93" s="297"/>
     </row>
-    <row r="94" spans="1:12">
+    <row r="94" spans="1:12" x14ac:dyDescent="0.15">
       <c r="B94" s="120" t="str">
         <f>Scenarios!B30</f>
         <v>Devil's advocate</v>
@@ -19200,7 +19211,7 @@
       </c>
       <c r="E94" s="127">
         <f>INDEX(B$73:F$87, MATCH(D94, A$73:A$87, 0), MATCH(C94, B$72:F$72, 0))</f>
-        <v>30.295271718236478</v>
+        <v>30.07764296409178</v>
       </c>
       <c r="F94" s="130">
         <f>Scenarios!F30</f>
@@ -19213,7 +19224,7 @@
       <c r="K94" s="297"/>
       <c r="L94" s="297"/>
     </row>
-    <row r="95" spans="1:12">
+    <row r="95" spans="1:12" x14ac:dyDescent="0.15">
       <c r="B95" s="141"/>
       <c r="C95" s="141"/>
       <c r="D95" s="141"/>
@@ -19226,16 +19237,16 @@
       <c r="K95" s="142"/>
       <c r="L95" s="142"/>
     </row>
-    <row r="105" spans="3:3">
+    <row r="105" spans="3:3" x14ac:dyDescent="0.15">
       <c r="C105" s="112"/>
     </row>
-    <row r="106" spans="3:3">
+    <row r="106" spans="3:3" x14ac:dyDescent="0.15">
       <c r="C106" s="112"/>
     </row>
-    <row r="107" spans="3:3">
+    <row r="107" spans="3:3" x14ac:dyDescent="0.15">
       <c r="C107" s="112"/>
     </row>
-    <row r="114" spans="3:21">
+    <row r="114" spans="3:21" x14ac:dyDescent="0.15">
       <c r="C114" s="275"/>
       <c r="M114" s="275"/>
       <c r="N114" s="275"/>
@@ -19247,7 +19258,7 @@
       <c r="T114" s="275"/>
       <c r="U114" s="275"/>
     </row>
-    <row r="115" spans="3:21">
+    <row r="115" spans="3:21" x14ac:dyDescent="0.15">
       <c r="C115" s="275"/>
       <c r="M115" s="275"/>
       <c r="N115" s="275"/>
@@ -19259,7 +19270,7 @@
       <c r="T115" s="275"/>
       <c r="U115" s="275"/>
     </row>
-    <row r="116" spans="3:21">
+    <row r="116" spans="3:21" x14ac:dyDescent="0.15">
       <c r="C116" s="275"/>
       <c r="M116" s="275"/>
       <c r="N116" s="275"/>
@@ -19271,7 +19282,7 @@
       <c r="T116" s="275"/>
       <c r="U116" s="275"/>
     </row>
-    <row r="117" spans="3:21">
+    <row r="117" spans="3:21" x14ac:dyDescent="0.15">
       <c r="C117" s="275"/>
       <c r="M117" s="275"/>
       <c r="N117" s="275"/>
@@ -19283,7 +19294,7 @@
       <c r="T117" s="275"/>
       <c r="U117" s="275"/>
     </row>
-    <row r="118" spans="3:21">
+    <row r="118" spans="3:21" x14ac:dyDescent="0.15">
       <c r="C118" s="275"/>
       <c r="M118" s="275"/>
       <c r="N118" s="275"/>
@@ -19323,14 +19334,14 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7DB08D6-06C8-485A-B381-9C0DCA9661D4}">
   <dimension ref="B2:G67"/>
-  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="2.6640625" customWidth="1"/>
     <col min="2" max="2" width="22.6640625" customWidth="1"/>
     <col min="3" max="7" width="20.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:7" ht="13.9">
+    <row r="2" spans="2:7" ht="16" x14ac:dyDescent="0.25">
       <c r="B2" s="34" t="s">
         <v>122</v>
       </c>
@@ -19340,7 +19351,7 @@
       <c r="F2" s="35"/>
       <c r="G2" s="35"/>
     </row>
-    <row r="3" spans="2:7" ht="13.15">
+    <row r="3" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B3" s="145" t="s">
         <v>125</v>
       </c>
@@ -19349,7 +19360,7 @@
       </c>
       <c r="E3" s="97"/>
     </row>
-    <row r="4" spans="2:7" ht="12.75" customHeight="1">
+    <row r="4" spans="2:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B4" s="139" t="s">
         <v>123</v>
       </c>
@@ -19370,14 +19381,14 @@
       <c r="F4" s="469"/>
       <c r="G4" s="469"/>
     </row>
-    <row r="5" spans="2:7">
+    <row r="5" spans="2:7" x14ac:dyDescent="0.15">
       <c r="C5" s="445"/>
       <c r="D5" s="469"/>
       <c r="E5" s="469"/>
       <c r="F5" s="469"/>
       <c r="G5" s="469"/>
     </row>
-    <row r="6" spans="2:7" ht="13.15">
+    <row r="6" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B6" s="145" t="s">
         <v>91</v>
       </c>
@@ -19390,7 +19401,7 @@
       <c r="F6" s="469"/>
       <c r="G6" s="469"/>
     </row>
-    <row r="7" spans="2:7" ht="12.75" customHeight="1">
+    <row r="7" spans="2:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B7" s="97" t="s">
         <v>232</v>
       </c>
@@ -19403,7 +19414,7 @@
       <c r="F7" s="469"/>
       <c r="G7" s="469"/>
     </row>
-    <row r="8" spans="2:7">
+    <row r="8" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B8" s="97" t="s">
         <v>63</v>
       </c>
@@ -19416,7 +19427,7 @@
       <c r="F8" s="469"/>
       <c r="G8" s="469"/>
     </row>
-    <row r="9" spans="2:7">
+    <row r="9" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B9" s="97" t="s">
         <v>54</v>
       </c>
@@ -19429,14 +19440,14 @@
       <c r="F9" s="469"/>
       <c r="G9" s="469"/>
     </row>
-    <row r="10" spans="2:7">
+    <row r="10" spans="2:7" x14ac:dyDescent="0.15">
       <c r="C10" s="448"/>
       <c r="D10" s="469"/>
       <c r="E10" s="469"/>
       <c r="F10" s="469"/>
       <c r="G10" s="469"/>
     </row>
-    <row r="11" spans="2:7" ht="13.15">
+    <row r="11" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B11" s="145" t="s">
         <v>321</v>
       </c>
@@ -19446,7 +19457,7 @@
       <c r="F11" s="469"/>
       <c r="G11" s="469"/>
     </row>
-    <row r="12" spans="2:7">
+    <row r="12" spans="2:7" ht="14" x14ac:dyDescent="0.15">
       <c r="B12" s="114" t="s">
         <v>121</v>
       </c>
@@ -19459,7 +19470,7 @@
       <c r="F12" s="469"/>
       <c r="G12" s="469"/>
     </row>
-    <row r="13" spans="2:7">
+    <row r="13" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B13" s="135" t="s">
         <v>127</v>
       </c>
@@ -19472,7 +19483,7 @@
       <c r="F13" s="469"/>
       <c r="G13" s="469"/>
     </row>
-    <row r="14" spans="2:7">
+    <row r="14" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B14" s="97" t="s">
         <v>63</v>
       </c>
@@ -19485,7 +19496,7 @@
       <c r="F14" s="469"/>
       <c r="G14" s="469"/>
     </row>
-    <row r="16" spans="2:7" ht="13.9">
+    <row r="16" spans="2:7" ht="16" x14ac:dyDescent="0.25">
       <c r="B16" s="34" t="s">
         <v>453</v>
       </c>
@@ -19495,7 +19506,7 @@
       <c r="F16" s="35"/>
       <c r="G16" s="35"/>
     </row>
-    <row r="17" spans="2:7" ht="13.15">
+    <row r="17" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B17" s="106" t="s">
         <v>126</v>
       </c>
@@ -19503,7 +19514,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="18" spans="2:7" ht="12.75" customHeight="1">
+    <row r="18" spans="2:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B18" s="139" t="s">
         <v>111</v>
       </c>
@@ -19515,18 +19526,18 @@
       </c>
       <c r="F18" s="319"/>
     </row>
-    <row r="19" spans="2:7">
+    <row r="19" spans="2:7" x14ac:dyDescent="0.15">
       <c r="E19" s="319"/>
       <c r="F19" s="319"/>
     </row>
-    <row r="20" spans="2:7" ht="13.15">
+    <row r="20" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B20" s="106" t="s">
         <v>450</v>
       </c>
       <c r="E20" s="319"/>
       <c r="F20" s="319"/>
     </row>
-    <row r="21" spans="2:7" ht="13.15">
+    <row r="21" spans="2:7" ht="14" x14ac:dyDescent="0.2">
       <c r="B21" s="153" t="s">
         <v>436</v>
       </c>
@@ -19547,7 +19558,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="22" spans="2:7">
+    <row r="22" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B22" s="302" t="s">
         <v>445</v>
       </c>
@@ -19560,7 +19571,7 @@
       </c>
       <c r="E22" s="326">
         <f>DCF!E91</f>
-        <v>74.319131414226234</v>
+        <v>73.785253384373206</v>
       </c>
       <c r="F22" s="328">
         <f>1-F23-F24</f>
@@ -19571,7 +19582,7 @@
         <v>0.15999999999999995</v>
       </c>
     </row>
-    <row r="23" spans="2:7">
+    <row r="23" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B23" s="302" t="s">
         <v>437</v>
       </c>
@@ -19584,7 +19595,7 @@
       </c>
       <c r="E23" s="326">
         <f>DCF!E92</f>
-        <v>55.106301528076884</v>
+        <v>54.710440554832722</v>
       </c>
       <c r="F23" s="327">
         <v>0.55000000000000004</v>
@@ -19594,7 +19605,7 @@
         <v>0.44</v>
       </c>
     </row>
-    <row r="24" spans="2:7">
+    <row r="24" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B24" s="302" t="s">
         <v>446</v>
       </c>
@@ -19607,7 +19618,7 @@
       </c>
       <c r="E24" s="326">
         <f>DCF!E93</f>
-        <v>40.876570658741464</v>
+        <v>40.582930211185598</v>
       </c>
       <c r="F24" s="327">
         <v>0.25</v>
@@ -19617,13 +19628,13 @@
         <v>0.19999999999999998</v>
       </c>
     </row>
-    <row r="25" spans="2:7">
+    <row r="25" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B25" s="141" t="s">
         <v>451</v>
       </c>
       <c r="C25" s="441">
         <f>E23*F23+E24*F24+E22*F22</f>
-        <v>55.391434787972898</v>
+        <v>54.993525534829033</v>
       </c>
       <c r="D25" s="141" t="str">
         <f>Market_currency</f>
@@ -19631,12 +19642,12 @@
       </c>
       <c r="G25" s="149"/>
     </row>
-    <row r="27" spans="2:7" ht="13.15">
+    <row r="27" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B27" s="106" t="s">
         <v>452</v>
       </c>
     </row>
-    <row r="28" spans="2:7" ht="13.15">
+    <row r="28" spans="2:7" ht="14" x14ac:dyDescent="0.2">
       <c r="B28" s="153" t="s">
         <v>436</v>
       </c>
@@ -19657,7 +19668,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="29" spans="2:7">
+    <row r="29" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B29" s="302" t="s">
         <v>444</v>
       </c>
@@ -19670,7 +19681,7 @@
       </c>
       <c r="E29" s="326">
         <f>DCF!E90</f>
-        <v>100.32673363685144</v>
+        <v>99.606027704524323</v>
       </c>
       <c r="F29" s="327">
         <v>0.15</v>
@@ -19680,7 +19691,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="30" spans="2:7">
+    <row r="30" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B30" s="315" t="s">
         <v>447</v>
       </c>
@@ -19693,7 +19704,7 @@
       </c>
       <c r="E30" s="326">
         <f>DCF!E94</f>
-        <v>30.295271718236478</v>
+        <v>30.07764296409178</v>
       </c>
       <c r="F30" s="327">
         <v>0.05</v>
@@ -19703,16 +19714,16 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="31" spans="2:7">
+    <row r="31" spans="2:7" x14ac:dyDescent="0.15">
       <c r="E31" s="329"/>
       <c r="F31" s="329"/>
     </row>
-    <row r="32" spans="2:7" ht="13.15">
+    <row r="32" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B32" s="145" t="s">
         <v>456</v>
       </c>
     </row>
-    <row r="33" spans="2:7">
+    <row r="33" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B33" s="97" t="s">
         <v>458</v>
       </c>
@@ -19732,13 +19743,13 @@
         <v>3</v>
       </c>
     </row>
-    <row r="34" spans="2:7">
+    <row r="34" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B34" s="97" t="s">
         <v>233</v>
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>41.88</v>
+        <v>42.2</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19749,16 +19760,16 @@
       </c>
       <c r="F34" s="330">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.16319188190025868</v>
-      </c>
-    </row>
-    <row r="35" spans="2:7">
+        <v>0.15751340909520897</v>
+      </c>
+    </row>
+    <row r="35" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B35" s="97" t="s">
         <v>434</v>
       </c>
       <c r="C35" s="320">
         <f>DCF!C11</f>
-        <v>46.644762060499836</v>
+        <v>46.309685301690244</v>
       </c>
       <c r="D35" s="97" t="str">
         <f>Market_currency</f>
@@ -19769,16 +19780,16 @@
       </c>
       <c r="F35" s="330">
         <f>RATE(Holding_Period,$C$33,-C35,$C$36)</f>
-        <v>0.12102810582090839</v>
-      </c>
-    </row>
-    <row r="36" spans="2:7">
+        <v>0.12123248939632798</v>
+      </c>
+    </row>
+    <row r="36" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B36" s="97" t="s">
         <v>435</v>
       </c>
       <c r="C36" s="321">
         <f>E22*G22+E23*G23+E24*G24+E30*G30+E29*G29</f>
-        <v>60.876921461817851</v>
+        <v>60.439606731746466</v>
       </c>
       <c r="D36" t="str">
         <f>Market_currency</f>
@@ -19791,7 +19802,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="38" spans="2:7" ht="13.9">
+    <row r="38" spans="2:7" ht="16" x14ac:dyDescent="0.25">
       <c r="B38" s="34" t="s">
         <v>411</v>
       </c>
@@ -19801,7 +19812,7 @@
       <c r="F38" s="35"/>
       <c r="G38" s="35"/>
     </row>
-    <row r="39" spans="2:7" ht="13.15">
+    <row r="39" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B39" s="414" t="str">
         <f>IF(DCF!F14="II","2","1")&amp;"-stage DCF"</f>
         <v>1-stage DCF</v>
@@ -19810,7 +19821,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="40" spans="2:7">
+    <row r="40" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B40" t="s">
         <v>551</v>
       </c>
@@ -19822,7 +19833,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="41" spans="2:7">
+    <row r="41" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B41" s="97" t="s">
         <v>400</v>
       </c>
@@ -19832,7 +19843,7 @@
       </c>
       <c r="E41" s="97"/>
     </row>
-    <row r="43" spans="2:7" ht="13.9">
+    <row r="43" spans="2:7" ht="16" x14ac:dyDescent="0.25">
       <c r="B43" s="34" t="s">
         <v>276</v>
       </c>
@@ -19842,7 +19853,7 @@
       <c r="F43" s="35"/>
       <c r="G43" s="35"/>
     </row>
-    <row r="44" spans="2:7" ht="13.15">
+    <row r="44" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B44" s="106" t="s">
         <v>249</v>
       </c>
@@ -19850,7 +19861,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="45" spans="2:7">
+    <row r="45" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B45" s="139" t="s">
         <v>111</v>
       </c>
@@ -19863,7 +19874,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="46" spans="2:7">
+    <row r="46" spans="2:7" ht="14" x14ac:dyDescent="0.15">
       <c r="B46" s="114" t="s">
         <v>112</v>
       </c>
@@ -19875,13 +19886,13 @@
         <v>252</v>
       </c>
     </row>
-    <row r="47" spans="2:7">
+    <row r="47" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B47" s="97" t="s">
         <v>96</v>
       </c>
       <c r="C47" s="146">
         <f>DCF!I18</f>
-        <v>60.136370439093248</v>
+        <v>59.704375522554315</v>
       </c>
       <c r="D47" s="146" t="str">
         <f>Market_currency</f>
@@ -19891,7 +19902,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="49" spans="2:7" ht="13.15">
+    <row r="49" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B49" s="106" t="s">
         <v>277</v>
       </c>
@@ -19903,7 +19914,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="50" spans="2:7">
+    <row r="50" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B50" s="97" t="s">
         <v>250</v>
       </c>
@@ -19913,7 +19924,7 @@
       </c>
       <c r="E50" s="126"/>
     </row>
-    <row r="51" spans="2:7">
+    <row r="51" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B51" s="97" t="s">
         <v>246</v>
       </c>
@@ -19925,7 +19936,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="52" spans="2:7">
+    <row r="52" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B52" s="97" t="s">
         <v>245</v>
       </c>
@@ -19935,7 +19946,7 @@
       </c>
       <c r="E52" s="221"/>
     </row>
-    <row r="53" spans="2:7">
+    <row r="53" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B53" s="97" t="s">
         <v>237</v>
       </c>
@@ -19948,10 +19959,10 @@
       </c>
       <c r="F53" s="249">
         <f>BS!D89/C36</f>
-        <v>-0.17099721727961334</v>
-      </c>
-    </row>
-    <row r="55" spans="2:7" ht="13.9">
+        <v>-0.17099721727961331</v>
+      </c>
+    </row>
+    <row r="55" spans="2:7" ht="16" x14ac:dyDescent="0.25">
       <c r="B55" s="34" t="s">
         <v>107</v>
       </c>
@@ -19961,12 +19972,12 @@
       <c r="F55" s="35"/>
       <c r="G55" s="35"/>
     </row>
-    <row r="56" spans="2:7" ht="13.15">
+    <row r="56" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B56" s="106" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="57" spans="2:7">
+    <row r="57" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B57" s="220" t="s">
         <v>248</v>
       </c>
@@ -19976,7 +19987,7 @@
       </c>
       <c r="D57" s="126"/>
     </row>
-    <row r="58" spans="2:7">
+    <row r="58" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B58" s="97" t="s">
         <v>333</v>
       </c>
@@ -19989,13 +20000,13 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="60" spans="2:7" ht="13.15">
+    <row r="60" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B60" s="106" t="s">
         <v>473</v>
       </c>
       <c r="E60" s="413"/>
     </row>
-    <row r="61" spans="2:7" ht="13.15">
+    <row r="61" spans="2:7" ht="14" x14ac:dyDescent="0.2">
       <c r="B61" s="153" t="s">
         <v>462</v>
       </c>
@@ -20016,7 +20027,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="62" spans="2:7" ht="13.15">
+    <row r="62" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B62" s="302" t="s">
         <v>312</v>
       </c>
@@ -20026,11 +20037,11 @@
       </c>
       <c r="D62" s="119">
         <f>C36/(1+F62)^Holding_Period</f>
-        <v>28.053880857980584</v>
+        <v>27.852353332602064</v>
       </c>
       <c r="E62" s="332">
         <f>C62+D62</f>
-        <v>30.673866004358207</v>
+        <v>30.472338478979687</v>
       </c>
       <c r="F62" s="301">
         <f>Thesis!E22</f>
@@ -20038,10 +20049,10 @@
       </c>
       <c r="G62" s="440">
         <f>(1-E62/C36)</f>
-        <v>0.49613309497595193</v>
-      </c>
-    </row>
-    <row r="63" spans="2:7" ht="13.15">
+        <v>0.49582169496523532</v>
+      </c>
+    </row>
+    <row r="63" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B63" s="302" t="s">
         <v>313</v>
       </c>
@@ -20051,11 +20062,11 @@
       </c>
       <c r="D63" s="119">
         <f>C36/(1+F63)^Holding_Period</f>
-        <v>35.163564743288305</v>
+        <v>34.910964177182088</v>
       </c>
       <c r="E63" s="332">
         <f>C63+D63</f>
-        <v>38.176081802996066</v>
+        <v>37.923481236889849</v>
       </c>
       <c r="F63" s="301">
         <f>Thesis!E23</f>
@@ -20063,10 +20074,10 @@
       </c>
       <c r="G63" s="440">
         <f>(1-E63/C36)</f>
-        <v>0.37289730022008105</v>
-      </c>
-    </row>
-    <row r="65" spans="2:7" ht="13.15">
+        <v>0.37253924557768192</v>
+      </c>
+    </row>
+    <row r="65" spans="2:7" ht="14" x14ac:dyDescent="0.2">
       <c r="B65" s="153" t="s">
         <v>463</v>
       </c>
@@ -20087,7 +20098,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="66" spans="2:7" ht="13.15">
+    <row r="66" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B66" s="302" t="s">
         <v>315</v>
       </c>
@@ -20097,11 +20108,11 @@
       </c>
       <c r="D66" s="119">
         <f>C36/(1+F66)^Holding_Period</f>
-        <v>43.634166152503838</v>
+        <v>43.320716274706704</v>
       </c>
       <c r="E66" s="332">
         <f>C66+D66</f>
-        <v>47.088536133429045</v>
+        <v>46.775086255631912</v>
       </c>
       <c r="F66" s="301">
         <f>Thesis!E24</f>
@@ -20109,10 +20120,10 @@
       </c>
       <c r="G66" s="440">
         <f>(1-E66/C36)</f>
-        <v>0.22649610061239567</v>
-      </c>
-    </row>
-    <row r="67" spans="2:7" ht="13.15">
+        <v>0.22608552925836856</v>
+      </c>
+    </row>
+    <row r="67" spans="2:7" x14ac:dyDescent="0.15">
       <c r="B67" s="302" t="s">
         <v>314</v>
       </c>
@@ -20122,11 +20133,11 @@
       </c>
       <c r="D67" s="119">
         <f>C36/(1+F67)^Holding_Period</f>
-        <v>49.347002750645608</v>
+        <v>48.992514207704659</v>
       </c>
       <c r="E67" s="332">
         <f>C67+D67</f>
-        <v>53.087406825662384</v>
+        <v>52.732918282721435</v>
       </c>
       <c r="F67" s="301">
         <f>Thesis!E25</f>
@@ -20134,7 +20145,7 @@
       </c>
       <c r="G67" s="440">
         <f>(1-E67/C36)</f>
-        <v>0.12795513388503177</v>
+        <v>0.12751056576576003</v>
       </c>
     </row>
   </sheetData>
@@ -20153,7 +20164,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:J167"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2.6640625" style="343" customWidth="1"/>
     <col min="2" max="2" width="32.6640625" style="343" customWidth="1"/>
@@ -20162,7 +20173,7 @@
     <col min="7" max="16384" width="9" style="343"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:10" ht="13.9">
+    <row r="2" spans="1:10" ht="16" x14ac:dyDescent="0.25">
       <c r="A2" s="345" t="s">
         <v>334</v>
       </c>
@@ -20176,7 +20187,7 @@
       <c r="I2" s="346"/>
       <c r="J2" s="346"/>
     </row>
-    <row r="3" spans="1:10">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="E3" s="435" t="s">
         <v>542</v>
       </c>
@@ -20185,7 +20196,7 @@
         <v>46065</v>
       </c>
     </row>
-    <row r="4" spans="1:10">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B4" s="422" t="s">
         <v>534</v>
       </c>
@@ -20202,7 +20213,7 @@
         <v>INT</v>
       </c>
     </row>
-    <row r="5" spans="1:10">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B5" s="343" t="s">
         <v>364</v>
       </c>
@@ -20218,7 +20229,7 @@
         <v>Y</v>
       </c>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B6" s="350" t="s">
         <v>336</v>
       </c>
@@ -20228,7 +20239,7 @@
       </c>
       <c r="E6" s="354"/>
     </row>
-    <row r="7" spans="1:10">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B7" s="343" t="s">
         <v>366</v>
       </c>
@@ -20239,16 +20250,16 @@
       <c r="D7" s="354"/>
       <c r="E7" s="354"/>
     </row>
-    <row r="8" spans="1:10">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B8" s="351" t="s">
         <v>365</v>
       </c>
       <c r="C8" s="356">
         <f>Market_Price</f>
-        <v>41.88</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10">
+        <v>42.2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B9" s="351" t="s">
         <v>361</v>
       </c>
@@ -20257,43 +20268,43 @@
         <v>2558824000</v>
       </c>
     </row>
-    <row r="10" spans="1:10">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B10" s="351" t="s">
         <v>367</v>
       </c>
       <c r="C10" s="357">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>107163.54912</v>
+        <v>107982.3728</v>
       </c>
       <c r="D10" s="343" t="s">
         <v>529</v>
       </c>
       <c r="E10" s="360">
         <f>Scenarios!F34</f>
-        <v>0.16319188190025868</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10">
+        <v>0.15751340909520897</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="D11" s="349"/>
       <c r="E11" s="349"/>
     </row>
-    <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="471" t="s">
+    <row r="12" spans="1:10" ht="24.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B12" s="474" t="s">
         <v>498</v>
       </c>
-      <c r="C12" s="471"/>
-      <c r="D12" s="471"/>
-      <c r="E12" s="471"/>
-      <c r="F12" s="471"/>
-    </row>
-    <row r="14" spans="1:10">
+      <c r="C12" s="474"/>
+      <c r="D12" s="474"/>
+      <c r="E12" s="474"/>
+      <c r="F12" s="474"/>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B14" s="347" t="s">
         <v>370</v>
       </c>
       <c r="C14" s="348"/>
       <c r="D14" s="349"/>
     </row>
-    <row r="15" spans="1:10">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B15" s="343" t="s">
         <v>337</v>
       </c>
@@ -20309,7 +20320,7 @@
         <v>EUR/HKD</v>
       </c>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B16" s="343" t="s">
         <v>338</v>
       </c>
@@ -20322,10 +20333,10 @@
       </c>
       <c r="E16" s="425">
         <f>Exchange_Rate</f>
-        <v>9.2771663694858564</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
+        <v>9.2105230273246779</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B17" s="343" t="s">
         <v>535</v>
       </c>
@@ -20341,14 +20352,14 @@
         <v>EUR</v>
       </c>
     </row>
-    <row r="18" spans="1:6">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B18" s="343" t="str">
         <f>"预期股权价值 ("&amp;C7&amp;") :"</f>
         <v>预期股权价值 (HKD) :</v>
       </c>
       <c r="C18" s="359">
         <f>C125</f>
-        <v>60.876921461817851</v>
+        <v>60.439606731746466</v>
       </c>
       <c r="D18" s="350" t="s">
         <v>362</v>
@@ -20358,7 +20369,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="19" spans="1:6">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B19" s="350" t="s">
         <v>335</v>
       </c>
@@ -20374,11 +20385,11 @@
         <v>46081</v>
       </c>
     </row>
-    <row r="20" spans="1:6">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
       <c r="D20" s="349"/>
       <c r="E20" s="349"/>
     </row>
-    <row r="21" spans="1:6">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B21" s="347" t="s">
         <v>493</v>
       </c>
@@ -20394,13 +20405,13 @@
         <v>3</v>
       </c>
     </row>
-    <row r="22" spans="1:6">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B22" s="343" t="s">
         <v>340</v>
       </c>
       <c r="C22" s="364">
         <f>E140</f>
-        <v>30.673866004358207</v>
+        <v>30.472338478979687</v>
       </c>
       <c r="D22" s="365" t="s">
         <v>440</v>
@@ -20410,13 +20421,13 @@
         <v>0.29465259038036606</v>
       </c>
     </row>
-    <row r="23" spans="1:6">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B23" s="343" t="s">
         <v>341</v>
       </c>
       <c r="C23" s="367">
         <f>E141</f>
-        <v>38.176081802996066</v>
+        <v>37.923481236889849</v>
       </c>
       <c r="D23" s="365" t="s">
         <v>441</v>
@@ -20426,13 +20437,13 @@
         <v>0.20075184365903009</v>
       </c>
     </row>
-    <row r="24" spans="1:6">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B24" s="343" t="s">
         <v>343</v>
       </c>
       <c r="C24" s="367">
         <f>E144</f>
-        <v>47.088536133429045</v>
+        <v>46.775086255631912</v>
       </c>
       <c r="D24" s="365" t="s">
         <v>443</v>
@@ -20442,13 +20453,13 @@
         <v>0.1174</v>
       </c>
     </row>
-    <row r="25" spans="1:6">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B25" s="343" t="s">
         <v>342</v>
       </c>
       <c r="C25" s="367">
         <f>E145</f>
-        <v>53.087406825662384</v>
+        <v>52.732918282721435</v>
       </c>
       <c r="D25" s="365" t="s">
         <v>442</v>
@@ -20458,7 +20469,7 @@
         <v>7.2499999999999995E-2</v>
       </c>
     </row>
-    <row r="27" spans="1:6" ht="13.9">
+    <row r="27" spans="1:6" ht="16" x14ac:dyDescent="0.25">
       <c r="A27" s="345" t="s">
         <v>345</v>
       </c>
@@ -20468,25 +20479,25 @@
       <c r="E27" s="345"/>
       <c r="F27" s="345"/>
     </row>
-    <row r="29" spans="1:6">
-      <c r="B29" s="471" t="s">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B29" s="474" t="s">
         <v>499</v>
       </c>
-      <c r="C29" s="471"/>
-      <c r="D29" s="471"/>
-      <c r="E29" s="471"/>
-      <c r="F29" s="471"/>
-    </row>
-    <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="472" t="s">
+      <c r="C29" s="474"/>
+      <c r="D29" s="474"/>
+      <c r="E29" s="474"/>
+      <c r="F29" s="474"/>
+    </row>
+    <row r="30" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B30" s="477" t="s">
         <v>500</v>
       </c>
-      <c r="C30" s="472"/>
-      <c r="D30" s="472"/>
-      <c r="E30" s="472"/>
-      <c r="F30" s="472"/>
-    </row>
-    <row r="32" spans="1:6">
+      <c r="C30" s="477"/>
+      <c r="D30" s="477"/>
+      <c r="E30" s="477"/>
+      <c r="F30" s="477"/>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B32" s="369" t="s">
         <v>371</v>
       </c>
@@ -20495,7 +20506,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="33" spans="2:6">
+    <row r="33" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B33" s="470" t="s">
         <v>501</v>
       </c>
@@ -20504,7 +20515,7 @@
       <c r="E33" s="470"/>
       <c r="F33" s="470"/>
     </row>
-    <row r="34" spans="2:6">
+    <row r="34" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B34" s="372" t="s">
         <v>197</v>
       </c>
@@ -20517,11 +20528,11 @@
         <v>EUR</v>
       </c>
     </row>
-    <row r="35" spans="2:6">
+    <row r="35" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B35" s="372"/>
       <c r="C35" s="374"/>
     </row>
-    <row r="36" spans="2:6" ht="24.5" customHeight="1">
+    <row r="36" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B36" s="470" t="s">
         <v>502</v>
       </c>
@@ -20530,7 +20541,7 @@
       <c r="E36" s="470"/>
       <c r="F36" s="470"/>
     </row>
-    <row r="37" spans="2:6">
+    <row r="37" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B37" s="372" t="s">
         <v>199</v>
       </c>
@@ -20543,7 +20554,7 @@
         <v>EUR</v>
       </c>
     </row>
-    <row r="38" spans="2:6">
+    <row r="38" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B38" s="375" t="s">
         <v>200</v>
       </c>
@@ -20556,7 +20567,7 @@
         <v>EUR</v>
       </c>
     </row>
-    <row r="40" spans="2:6">
+    <row r="40" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B40" s="470" t="s">
         <v>503</v>
       </c>
@@ -20565,7 +20576,7 @@
       <c r="E40" s="470"/>
       <c r="F40" s="470"/>
     </row>
-    <row r="41" spans="2:6">
+    <row r="41" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B41" s="372" t="s">
         <v>202</v>
       </c>
@@ -20578,7 +20589,7 @@
         <v>EUR</v>
       </c>
     </row>
-    <row r="43" spans="2:6">
+    <row r="43" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B43" s="470" t="s">
         <v>504</v>
       </c>
@@ -20587,7 +20598,7 @@
       <c r="E43" s="470"/>
       <c r="F43" s="470"/>
     </row>
-    <row r="44" spans="2:6">
+    <row r="44" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B44" s="372" t="s">
         <v>267</v>
       </c>
@@ -20602,7 +20613,7 @@
       <c r="E44" s="371"/>
       <c r="F44" s="371"/>
     </row>
-    <row r="45" spans="2:6">
+    <row r="45" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B45" s="372" t="s">
         <v>268</v>
       </c>
@@ -20617,7 +20628,7 @@
       <c r="E45" s="371"/>
       <c r="F45" s="371"/>
     </row>
-    <row r="46" spans="2:6">
+    <row r="46" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B46" s="372" t="s">
         <v>203</v>
       </c>
@@ -20630,12 +20641,12 @@
         <v>EUR</v>
       </c>
     </row>
-    <row r="48" spans="2:6">
+    <row r="48" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B48" s="343" t="s">
         <v>505</v>
       </c>
     </row>
-    <row r="49" spans="2:6">
+    <row r="49" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B49" s="372" t="s">
         <v>223</v>
       </c>
@@ -20648,7 +20659,7 @@
         <v>EUR</v>
       </c>
     </row>
-    <row r="51" spans="2:6">
+    <row r="51" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B51" s="470" t="s">
         <v>506</v>
       </c>
@@ -20657,7 +20668,7 @@
       <c r="E51" s="470"/>
       <c r="F51" s="470"/>
     </row>
-    <row r="52" spans="2:6">
+    <row r="52" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B52" s="372" t="s">
         <v>496</v>
       </c>
@@ -20670,16 +20681,16 @@
         <v>EUR</v>
       </c>
     </row>
-    <row r="54" spans="2:6">
+    <row r="54" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B54" s="470" t="s">
         <v>507</v>
       </c>
-      <c r="C54" s="473"/>
-      <c r="D54" s="473"/>
-      <c r="E54" s="473"/>
-      <c r="F54" s="473"/>
-    </row>
-    <row r="55" spans="2:6">
+      <c r="C54" s="476"/>
+      <c r="D54" s="476"/>
+      <c r="E54" s="476"/>
+      <c r="F54" s="476"/>
+    </row>
+    <row r="55" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B55" s="372" t="s">
         <v>207</v>
       </c>
@@ -20692,25 +20703,25 @@
         <v>EUR</v>
       </c>
     </row>
-    <row r="57" spans="2:6">
-      <c r="B57" s="471" t="s">
+    <row r="57" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B57" s="474" t="s">
         <v>508</v>
       </c>
-      <c r="C57" s="471"/>
-      <c r="D57" s="471"/>
-      <c r="E57" s="471"/>
-      <c r="F57" s="471"/>
-    </row>
-    <row r="58" spans="2:6">
-      <c r="B58" s="471" t="s">
+      <c r="C57" s="474"/>
+      <c r="D57" s="474"/>
+      <c r="E57" s="474"/>
+      <c r="F57" s="474"/>
+    </row>
+    <row r="58" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B58" s="474" t="s">
         <v>509</v>
       </c>
-      <c r="C58" s="471"/>
-      <c r="D58" s="471"/>
-      <c r="E58" s="471"/>
-      <c r="F58" s="471"/>
-    </row>
-    <row r="60" spans="2:6">
+      <c r="C58" s="474"/>
+      <c r="D58" s="474"/>
+      <c r="E58" s="474"/>
+      <c r="F58" s="474"/>
+    </row>
+    <row r="60" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B60" s="372" t="s">
         <v>372</v>
       </c>
@@ -20723,7 +20734,7 @@
         <v>EUR</v>
       </c>
     </row>
-    <row r="61" spans="2:6">
+    <row r="61" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B61" s="372" t="s">
         <v>213</v>
       </c>
@@ -20736,23 +20747,23 @@
         <v>EUR</v>
       </c>
     </row>
-    <row r="62" spans="2:6">
+    <row r="62" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B62" s="377" t="s">
         <v>302</v>
       </c>
       <c r="C62" s="378">
         <f>Normalized_FCF!C124</f>
-        <v>7.0120130272266309E-2</v>
+        <v>6.9088519142746635E-2</v>
       </c>
       <c r="F62" s="379"/>
     </row>
-    <row r="63" spans="2:6">
+    <row r="63" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B63" s="377" t="s">
         <v>332</v>
       </c>
       <c r="C63" s="378">
         <f>Normalized_FCF!C92</f>
-        <v>3.4188204393505249E-2</v>
+        <v>3.392895734597156E-2</v>
       </c>
       <c r="E63" s="372" t="s">
         <v>373</v>
@@ -20762,7 +20773,7 @@
         <v>4.5232326123897897</v>
       </c>
     </row>
-    <row r="65" spans="1:6">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B65" s="369" t="s">
         <v>376</v>
       </c>
@@ -20773,7 +20784,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="66" spans="1:6">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B66" s="372" t="s">
         <v>326</v>
       </c>
@@ -20786,7 +20797,7 @@
         <v>0.28005991710273764</v>
       </c>
     </row>
-    <row r="67" spans="1:6">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B67" s="382" t="str">
         <f>Normalized_FCF!B116</f>
         <v>Pre-tax Profit/Sales</v>
@@ -20800,7 +20811,7 @@
         <v>0.21885492502426099</v>
       </c>
     </row>
-    <row r="68" spans="1:6">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B68" s="382" t="str">
         <f>Normalized_FCF!B117</f>
         <v>Sales/Total Assets</v>
@@ -20814,7 +20825,7 @@
         <v>0.65265738052043343</v>
       </c>
     </row>
-    <row r="69" spans="1:6">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B69" s="382" t="str">
         <f>Normalized_FCF!B118</f>
         <v>Total Assets/Equity</v>
@@ -20828,7 +20839,7 @@
         <v>1.9606920057834423</v>
       </c>
     </row>
-    <row r="71" spans="1:6" ht="13.9">
+    <row r="71" spans="1:6" ht="16" x14ac:dyDescent="0.25">
       <c r="A71" s="345" t="s">
         <v>476</v>
       </c>
@@ -20838,43 +20849,43 @@
       <c r="E71" s="345"/>
       <c r="F71" s="345"/>
     </row>
-    <row r="72" spans="1:6">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A72" s="385"/>
     </row>
-    <row r="73" spans="1:6">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A73" s="386"/>
-      <c r="B73" s="471" t="s">
+      <c r="B73" s="474" t="s">
         <v>510</v>
       </c>
-      <c r="C73" s="471"/>
-      <c r="D73" s="471"/>
-      <c r="E73" s="471"/>
-      <c r="F73" s="471"/>
-    </row>
-    <row r="74" spans="1:6">
-      <c r="B74" s="472" t="s">
+      <c r="C73" s="474"/>
+      <c r="D73" s="474"/>
+      <c r="E73" s="474"/>
+      <c r="F73" s="474"/>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B74" s="477" t="s">
         <v>479</v>
       </c>
-      <c r="C74" s="472"/>
-      <c r="D74" s="472"/>
-      <c r="E74" s="472"/>
-      <c r="F74" s="472"/>
-    </row>
-    <row r="76" spans="1:6">
+      <c r="C74" s="477"/>
+      <c r="D74" s="477"/>
+      <c r="E74" s="477"/>
+      <c r="F74" s="477"/>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B76" s="369" t="s">
         <v>371</v>
       </c>
     </row>
-    <row r="77" spans="1:6">
-      <c r="B77" s="471" t="s">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B77" s="474" t="s">
         <v>511</v>
       </c>
-      <c r="C77" s="471"/>
-      <c r="D77" s="471"/>
-      <c r="E77" s="471"/>
-      <c r="F77" s="471"/>
-    </row>
-    <row r="78" spans="1:6">
+      <c r="C77" s="474"/>
+      <c r="D77" s="474"/>
+      <c r="E77" s="474"/>
+      <c r="F77" s="474"/>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B78" s="343" t="s">
         <v>215</v>
       </c>
@@ -20887,20 +20898,20 @@
         <v>EUR</v>
       </c>
     </row>
-    <row r="79" spans="1:6">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B79" s="372" t="s">
         <v>234</v>
       </c>
       <c r="C79" s="387">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-10.354105922795677</v>
+        <v>-10.279726290448499</v>
       </c>
       <c r="D79" s="343" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="80" spans="1:6">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B80" s="382" t="s">
         <v>309</v>
       </c>
@@ -20909,7 +20920,7 @@
         <v>0.67283405398617657</v>
       </c>
     </row>
-    <row r="81" spans="1:6">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B81" s="382" t="s">
         <v>311</v>
       </c>
@@ -20918,12 +20929,12 @@
         <v>2.2041306156151999</v>
       </c>
     </row>
-    <row r="83" spans="1:6">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B83" s="343" t="s">
         <v>512</v>
       </c>
     </row>
-    <row r="84" spans="1:6">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B84" s="343" t="s">
         <v>224</v>
       </c>
@@ -20936,7 +20947,7 @@
         <v>EUR</v>
       </c>
     </row>
-    <row r="85" spans="1:6">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B85" s="382" t="s">
         <v>481</v>
       </c>
@@ -20949,25 +20960,25 @@
         <v>EUR</v>
       </c>
     </row>
-    <row r="86" spans="1:6">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B86" s="372" t="s">
         <v>235</v>
       </c>
       <c r="C86" s="387">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-0.18843677335320597</v>
+        <v>-0.1870831211859201</v>
       </c>
       <c r="D86" s="343" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="88" spans="1:6">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B88" s="343" t="s">
         <v>513</v>
       </c>
     </row>
-    <row r="89" spans="1:6">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B89" s="343" t="s">
         <v>217</v>
       </c>
@@ -20980,33 +20991,33 @@
         <v>EUR</v>
       </c>
     </row>
-    <row r="90" spans="1:6">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B90" s="372" t="s">
         <v>236</v>
       </c>
       <c r="C90" s="387">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>0.13275852962845874</v>
+        <v>0.13180484703158896</v>
       </c>
       <c r="D90" s="343" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="92" spans="1:6">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B92" s="372" t="s">
         <v>480</v>
       </c>
       <c r="C92" s="387">
         <f>DCF!F8</f>
-        <v>-10.409784166520426</v>
+        <v>-10.335004564602832</v>
       </c>
       <c r="D92" s="343" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="94" spans="1:6" ht="13.9">
+    <row r="94" spans="1:6" ht="16" x14ac:dyDescent="0.25">
       <c r="A94" s="345" t="s">
         <v>482</v>
       </c>
@@ -21016,49 +21027,49 @@
       <c r="E94" s="345"/>
       <c r="F94" s="345"/>
     </row>
-    <row r="95" spans="1:6">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A95" s="385"/>
     </row>
-    <row r="96" spans="1:6">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A96" s="385"/>
-      <c r="B96" s="471" t="s">
+      <c r="B96" s="474" t="s">
         <v>514</v>
       </c>
-      <c r="C96" s="471"/>
-      <c r="D96" s="471"/>
-      <c r="E96" s="471"/>
-      <c r="F96" s="471"/>
-    </row>
-    <row r="97" spans="1:6">
+      <c r="C96" s="474"/>
+      <c r="D96" s="474"/>
+      <c r="E96" s="474"/>
+      <c r="F96" s="474"/>
+    </row>
+    <row r="97" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A97" s="385"/>
-      <c r="B97" s="472" t="s">
+      <c r="B97" s="477" t="s">
         <v>515</v>
       </c>
-      <c r="C97" s="472"/>
-      <c r="D97" s="472"/>
-      <c r="E97" s="472"/>
-      <c r="F97" s="472"/>
-    </row>
-    <row r="98" spans="1:6">
+      <c r="C97" s="477"/>
+      <c r="D97" s="477"/>
+      <c r="E97" s="477"/>
+      <c r="F97" s="477"/>
+    </row>
+    <row r="98" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A98" s="385"/>
-      <c r="B98" s="472" t="s">
+      <c r="B98" s="477" t="s">
         <v>516</v>
       </c>
-      <c r="C98" s="472"/>
-      <c r="D98" s="472"/>
-      <c r="E98" s="472"/>
-      <c r="F98" s="472"/>
-    </row>
-    <row r="99" spans="1:6">
+      <c r="C98" s="477"/>
+      <c r="D98" s="477"/>
+      <c r="E98" s="477"/>
+      <c r="F98" s="477"/>
+    </row>
+    <row r="99" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A99" s="385"/>
     </row>
-    <row r="100" spans="1:6">
+    <row r="100" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A100" s="385"/>
       <c r="B100" s="369" t="s">
         <v>371</v>
       </c>
     </row>
-    <row r="101" spans="1:6">
+    <row r="101" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A101" s="385"/>
       <c r="B101" s="372" t="s">
         <v>212</v>
@@ -21068,7 +21079,7 @@
         <v>7.2499999999999995E-2</v>
       </c>
     </row>
-    <row r="102" spans="1:6">
+    <row r="102" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A102" s="385"/>
       <c r="B102" s="382" t="s">
         <v>318</v>
@@ -21078,7 +21089,7 @@
         <v>7.2499999999999995E-2</v>
       </c>
     </row>
-    <row r="103" spans="1:6">
+    <row r="103" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A103" s="385"/>
       <c r="B103" s="382" t="s">
         <v>317</v>
@@ -21088,7 +21099,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:6">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A104" s="385"/>
       <c r="B104" s="372" t="s">
         <v>535</v>
@@ -21097,97 +21108,97 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:6">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A105" s="385"/>
       <c r="C105" s="392"/>
     </row>
-    <row r="106" spans="1:6">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A106" s="385"/>
       <c r="B106" s="393" t="s">
         <v>375</v>
       </c>
       <c r="C106" s="392"/>
     </row>
-    <row r="107" spans="1:6">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A107" s="385"/>
-      <c r="B107" s="471" t="s">
+      <c r="B107" s="474" t="s">
         <v>517</v>
       </c>
-      <c r="C107" s="471"/>
-      <c r="D107" s="471"/>
-      <c r="E107" s="471"/>
-      <c r="F107" s="471"/>
-    </row>
-    <row r="108" spans="1:6">
+      <c r="C107" s="474"/>
+      <c r="D107" s="474"/>
+      <c r="E107" s="474"/>
+      <c r="F107" s="474"/>
+    </row>
+    <row r="108" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A108" s="385"/>
-      <c r="B108" s="471" t="s">
+      <c r="B108" s="474" t="s">
         <v>536</v>
       </c>
-      <c r="C108" s="471"/>
-      <c r="D108" s="471"/>
-      <c r="E108" s="471"/>
-      <c r="F108" s="471"/>
-    </row>
-    <row r="109" spans="1:6">
+      <c r="C108" s="474"/>
+      <c r="D108" s="474"/>
+      <c r="E108" s="474"/>
+      <c r="F108" s="474"/>
+    </row>
+    <row r="109" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A109" s="385"/>
     </row>
-    <row r="110" spans="1:6">
+    <row r="110" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A110" s="385"/>
       <c r="B110" s="369" t="s">
         <v>489</v>
       </c>
     </row>
-    <row r="111" spans="1:6">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A111" s="385"/>
       <c r="B111" s="375" t="s">
         <v>486</v>
       </c>
       <c r="C111" s="394">
         <f>BS!D47</f>
-        <v>-6.333420164937916</v>
+        <v>-6.2879234830533743</v>
       </c>
       <c r="D111" s="343" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="112" spans="1:6">
+    <row r="112" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A112" s="385"/>
       <c r="B112" s="372" t="s">
         <v>377</v>
       </c>
       <c r="C112" s="394">
         <f>DCF!C11</f>
-        <v>46.644762060499836</v>
+        <v>46.309685301690244</v>
       </c>
       <c r="D112" s="343" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="113" spans="1:6">
+    <row r="113" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A113" s="385"/>
     </row>
-    <row r="114" spans="1:6">
+    <row r="114" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A114" s="385"/>
-      <c r="B114" s="471" t="s">
+      <c r="B114" s="474" t="s">
         <v>518</v>
       </c>
-      <c r="C114" s="471"/>
-      <c r="D114" s="471"/>
-      <c r="E114" s="471"/>
-      <c r="F114" s="471"/>
-    </row>
-    <row r="115" spans="1:6">
+      <c r="C114" s="474"/>
+      <c r="D114" s="474"/>
+      <c r="E114" s="474"/>
+      <c r="F114" s="474"/>
+    </row>
+    <row r="115" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A115" s="385"/>
     </row>
-    <row r="116" spans="1:6">
+    <row r="116" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A116" s="385"/>
       <c r="B116" s="369" t="s">
         <v>490</v>
       </c>
     </row>
-    <row r="117" spans="1:6">
+    <row r="117" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A117" s="385"/>
       <c r="B117" s="342" t="s">
         <v>378</v>
@@ -21205,7 +21216,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="118" spans="1:6">
+    <row r="118" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A118" s="385"/>
       <c r="B118" s="395" t="str">
         <f>DCF!B90</f>
@@ -21221,14 +21232,14 @@
       </c>
       <c r="E118" s="398" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>100.33 HKD</v>
+        <v>99.61 HKD</v>
       </c>
       <c r="F118" s="399">
         <f>DCF!F90</f>
         <v>0.15</v>
       </c>
     </row>
-    <row r="119" spans="1:6">
+    <row r="119" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A119" s="385"/>
       <c r="B119" s="400" t="str">
         <f>DCF!B91</f>
@@ -21244,14 +21255,14 @@
       </c>
       <c r="E119" s="398" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>74.32 HKD</v>
+        <v>73.79 HKD</v>
       </c>
       <c r="F119" s="403">
         <f>DCF!F91</f>
         <v>0.15999999999999995</v>
       </c>
     </row>
-    <row r="120" spans="1:6">
+    <row r="120" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B120" s="400" t="str">
         <f>DCF!B92</f>
         <v>Base</v>
@@ -21266,14 +21277,14 @@
       </c>
       <c r="E120" s="398" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>55.11 HKD</v>
+        <v>54.71 HKD</v>
       </c>
       <c r="F120" s="403">
         <f>DCF!F92</f>
         <v>0.44</v>
       </c>
     </row>
-    <row r="121" spans="1:6">
+    <row r="121" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B121" s="400" t="str">
         <f>DCF!B93</f>
         <v>Pessimistic</v>
@@ -21288,14 +21299,14 @@
       </c>
       <c r="E121" s="398" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>40.88 HKD</v>
+        <v>40.58 HKD</v>
       </c>
       <c r="F121" s="403">
         <f>DCF!F93</f>
         <v>0.19999999999999998</v>
       </c>
     </row>
-    <row r="122" spans="1:6">
+    <row r="122" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B122" s="400" t="str">
         <f>DCF!B94</f>
         <v>Devil's advocate</v>
@@ -21310,14 +21321,14 @@
       </c>
       <c r="E122" s="398" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>30.3 HKD</v>
+        <v>30.08 HKD</v>
       </c>
       <c r="F122" s="403">
         <f>DCF!F94</f>
         <v>0.05</v>
       </c>
     </row>
-    <row r="124" spans="1:6">
+    <row r="124" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B124" s="470" t="s">
         <v>519</v>
       </c>
@@ -21326,29 +21337,29 @@
       <c r="E124" s="470"/>
       <c r="F124" s="470"/>
     </row>
-    <row r="125" spans="1:6">
+    <row r="125" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B125" s="372" t="s">
         <v>218</v>
       </c>
       <c r="C125" s="404">
         <f>Scenarios!C36</f>
-        <v>60.876921461817851</v>
+        <v>60.439606731746466</v>
       </c>
       <c r="D125" s="343" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="127" spans="1:6">
-      <c r="B127" s="475" t="s">
+    <row r="127" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B127" s="472" t="s">
         <v>520</v>
       </c>
-      <c r="C127" s="475"/>
-      <c r="D127" s="475"/>
-      <c r="E127" s="475"/>
-      <c r="F127" s="475"/>
-    </row>
-    <row r="129" spans="1:6" ht="13.9">
+      <c r="C127" s="472"/>
+      <c r="D127" s="472"/>
+      <c r="E127" s="472"/>
+      <c r="F127" s="472"/>
+    </row>
+    <row r="129" spans="1:6" ht="16" x14ac:dyDescent="0.25">
       <c r="A129" s="345" t="s">
         <v>492</v>
       </c>
@@ -21358,30 +21369,30 @@
       <c r="E129" s="345"/>
       <c r="F129" s="345"/>
     </row>
-    <row r="131" spans="1:6">
-      <c r="B131" s="476" t="s">
+    <row r="131" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B131" s="473" t="s">
         <v>521</v>
       </c>
-      <c r="C131" s="476"/>
-      <c r="D131" s="476"/>
-      <c r="E131" s="476"/>
-      <c r="F131" s="476"/>
-    </row>
-    <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="471" t="s">
+      <c r="C131" s="473"/>
+      <c r="D131" s="473"/>
+      <c r="E131" s="473"/>
+      <c r="F131" s="473"/>
+    </row>
+    <row r="132" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B132" s="474" t="s">
         <v>522</v>
       </c>
-      <c r="C132" s="471"/>
-      <c r="D132" s="471"/>
-      <c r="E132" s="471"/>
-      <c r="F132" s="471"/>
-    </row>
-    <row r="134" spans="1:6">
+      <c r="C132" s="474"/>
+      <c r="D132" s="474"/>
+      <c r="E132" s="474"/>
+      <c r="F132" s="474"/>
+    </row>
+    <row r="134" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B134" s="369" t="s">
         <v>371</v>
       </c>
     </row>
-    <row r="135" spans="1:6">
+    <row r="135" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B135" s="343" t="s">
         <v>382</v>
       </c>
@@ -21390,7 +21401,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="136" spans="1:6">
+    <row r="136" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B136" s="343" t="s">
         <v>383</v>
       </c>
@@ -21403,14 +21414,14 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="138" spans="1:6">
+    <row r="138" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B138" s="369" t="s">
         <v>493</v>
       </c>
       <c r="C138" s="407"/>
       <c r="D138" s="407"/>
     </row>
-    <row r="139" spans="1:6">
+    <row r="139" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B139" s="340" t="s">
         <v>462</v>
       </c>
@@ -21429,7 +21440,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="140" spans="1:6">
+    <row r="140" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B140" s="408" t="s">
         <v>312</v>
       </c>
@@ -21439,18 +21450,18 @@
       </c>
       <c r="D140" s="409">
         <f>Scenarios!D62</f>
-        <v>28.053880857980584</v>
+        <v>27.852353332602064</v>
       </c>
       <c r="E140" s="410">
         <f>Scenarios!E62</f>
-        <v>30.673866004358207</v>
+        <v>30.472338478979687</v>
       </c>
       <c r="F140" s="411">
         <f>E22</f>
         <v>0.29465259038036606</v>
       </c>
     </row>
-    <row r="141" spans="1:6">
+    <row r="141" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B141" s="408" t="s">
         <v>313</v>
       </c>
@@ -21460,18 +21471,18 @@
       </c>
       <c r="D141" s="409">
         <f>Scenarios!D63</f>
-        <v>35.163564743288305</v>
+        <v>34.910964177182088</v>
       </c>
       <c r="E141" s="410">
         <f>Scenarios!E63</f>
-        <v>38.176081802996066</v>
+        <v>37.923481236889849</v>
       </c>
       <c r="F141" s="411">
         <f>Scenarios!F63</f>
         <v>0.20075184365903009</v>
       </c>
     </row>
-    <row r="143" spans="1:6">
+    <row r="143" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B143" s="340" t="s">
         <v>463</v>
       </c>
@@ -21490,7 +21501,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="144" spans="1:6">
+    <row r="144" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B144" s="408" t="s">
         <v>315</v>
       </c>
@@ -21500,18 +21511,18 @@
       </c>
       <c r="D144" s="409">
         <f>Scenarios!D66</f>
-        <v>43.634166152503838</v>
+        <v>43.320716274706704</v>
       </c>
       <c r="E144" s="410">
         <f>Scenarios!E66</f>
-        <v>47.088536133429045</v>
+        <v>46.775086255631912</v>
       </c>
       <c r="F144" s="411">
         <f>E24</f>
         <v>0.1174</v>
       </c>
     </row>
-    <row r="145" spans="1:6">
+    <row r="145" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B145" s="408" t="s">
         <v>314</v>
       </c>
@@ -21521,18 +21532,18 @@
       </c>
       <c r="D145" s="409">
         <f>Scenarios!D67</f>
-        <v>49.347002750645608</v>
+        <v>48.992514207704659</v>
       </c>
       <c r="E145" s="410">
         <f>Scenarios!E67</f>
-        <v>53.087406825662384</v>
+        <v>52.732918282721435</v>
       </c>
       <c r="F145" s="411">
         <f>Scenarios!F67</f>
         <v>7.2499999999999995E-2</v>
       </c>
     </row>
-    <row r="147" spans="1:6" ht="13.9">
+    <row r="147" spans="1:6" ht="16" x14ac:dyDescent="0.25">
       <c r="A147" s="345" t="s">
         <v>475</v>
       </c>
@@ -21542,50 +21553,50 @@
       <c r="E147" s="345"/>
       <c r="F147" s="345"/>
     </row>
-    <row r="149" spans="1:6">
-      <c r="B149" s="477" t="s">
+    <row r="149" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B149" s="475" t="s">
         <v>523</v>
       </c>
-      <c r="C149" s="471"/>
-      <c r="D149" s="471"/>
-      <c r="E149" s="471"/>
-      <c r="F149" s="471"/>
-    </row>
-    <row r="151" spans="1:6">
+      <c r="C149" s="474"/>
+      <c r="D149" s="474"/>
+      <c r="E149" s="474"/>
+      <c r="F149" s="474"/>
+    </row>
+    <row r="151" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B151" s="369" t="s">
         <v>384</v>
       </c>
     </row>
-    <row r="152" spans="1:6">
-      <c r="B152" s="473" t="s">
+    <row r="152" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B152" s="476" t="s">
         <v>524</v>
       </c>
-      <c r="C152" s="473"/>
-      <c r="D152" s="473"/>
-      <c r="E152" s="473"/>
-      <c r="F152" s="473"/>
-    </row>
-    <row r="153" spans="1:6">
+      <c r="C152" s="476"/>
+      <c r="D152" s="476"/>
+      <c r="E152" s="476"/>
+      <c r="F152" s="476"/>
+    </row>
+    <row r="153" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B153" s="412" t="s">
         <v>385</v>
       </c>
     </row>
-    <row r="154" spans="1:6">
+    <row r="154" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B154" s="412" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="155" spans="1:6">
+    <row r="155" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B155" s="412" t="s">
         <v>387</v>
       </c>
     </row>
-    <row r="157" spans="1:6">
+    <row r="157" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B157" s="343" t="s">
         <v>525</v>
       </c>
     </row>
-    <row r="158" spans="1:6" ht="24.5" customHeight="1">
+    <row r="158" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B158" s="470" t="s">
         <v>439</v>
       </c>
@@ -21594,60 +21605,57 @@
       <c r="E158" s="470"/>
       <c r="F158" s="470"/>
     </row>
-    <row r="160" spans="1:6">
+    <row r="160" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B160" s="343" t="s">
         <v>526</v>
       </c>
     </row>
-    <row r="161" spans="2:6">
-      <c r="B161" s="474" t="s">
+    <row r="161" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B161" s="471" t="s">
         <v>388</v>
       </c>
-      <c r="C161" s="474"/>
-      <c r="D161" s="474"/>
-      <c r="E161" s="474"/>
-      <c r="F161" s="474"/>
-    </row>
-    <row r="162" spans="2:6">
-      <c r="B162" s="474" t="s">
+      <c r="C161" s="471"/>
+      <c r="D161" s="471"/>
+      <c r="E161" s="471"/>
+      <c r="F161" s="471"/>
+    </row>
+    <row r="162" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B162" s="471" t="s">
         <v>389</v>
       </c>
-      <c r="C162" s="474"/>
-      <c r="D162" s="474"/>
-      <c r="E162" s="474"/>
-      <c r="F162" s="474"/>
-    </row>
-    <row r="164" spans="2:6">
+      <c r="C162" s="471"/>
+      <c r="D162" s="471"/>
+      <c r="E162" s="471"/>
+      <c r="F162" s="471"/>
+    </row>
+    <row r="164" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B164" s="343" t="s">
         <v>527</v>
       </c>
     </row>
-    <row r="165" spans="2:6">
+    <row r="165" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B165" s="412" t="s">
         <v>390</v>
       </c>
     </row>
-    <row r="166" spans="2:6">
+    <row r="166" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B166" s="412" t="s">
         <v>391</v>
       </c>
     </row>
-    <row r="167" spans="2:6">
+    <row r="167" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B167" s="412" t="s">
         <v>392</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21662,12 +21670,15 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/1913.HK_Valuation.xlsx
+++ b/financial_models/opportunities/1913.HK_Valuation.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10209"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr showObjects="none" codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kamanl/PycharmProjects/Invest_Proc/financial_models/opportunities/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFD32012-A231-7D44-8EE4-57DAC2DB80E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D439418A-9AAD-48B7-9A0A-EF91309388D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="17120" windowHeight="10760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -39,17 +39,6 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
     <ext uri="GoogleSheetsCustomDataVersion1">
       <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId10" roundtripDataSignature="AMtx7mi73Cg0ax9bLfpeUuF69nNRn7idDQ=="/>
@@ -3286,27 +3275,27 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="19">
-    <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00;[Red]\-&quot;$&quot;#,##0.00"/>
-    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="166" formatCode="#,##0&quot;mm&quot;"/>
-    <numFmt numFmtId="167" formatCode="#,##0.00&quot;x&quot;"/>
-    <numFmt numFmtId="168" formatCode="0.00\x"/>
-    <numFmt numFmtId="169" formatCode="yyyy\-mm\-dd;@"/>
-    <numFmt numFmtId="170" formatCode="#,##0.0000"/>
-    <numFmt numFmtId="171" formatCode="#,##0_ "/>
-    <numFmt numFmtId="172" formatCode="#,##0.0000_);\(#,##0.0000\)"/>
-    <numFmt numFmtId="173" formatCode="#,##0.0000_ "/>
-    <numFmt numFmtId="174" formatCode="&quot;in &quot;#,##0&quot;s&quot;"/>
-    <numFmt numFmtId="175" formatCode="#,##0.00_ "/>
-    <numFmt numFmtId="176" formatCode="0&quot; yrs&quot;"/>
-    <numFmt numFmtId="177" formatCode="0.000_ "/>
-    <numFmt numFmtId="178" formatCode="&quot;every&quot;\ 0\ &quot;Months&quot;"/>
-    <numFmt numFmtId="179" formatCode="0.0\x"/>
-    <numFmt numFmtId="180" formatCode="0\x"/>
-    <numFmt numFmtId="181" formatCode="0.000000000000000%"/>
-    <numFmt numFmtId="182" formatCode="#,##0_);\(#,##0\);0;@"/>
+    <numFmt numFmtId="8" formatCode="&quot;$&quot;#,##0.00;[Red]\-&quot;$&quot;#,##0.00"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="165" formatCode="#,##0&quot;mm&quot;"/>
+    <numFmt numFmtId="166" formatCode="#,##0.00&quot;x&quot;"/>
+    <numFmt numFmtId="167" formatCode="0.00\x"/>
+    <numFmt numFmtId="168" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="169" formatCode="#,##0.0000"/>
+    <numFmt numFmtId="170" formatCode="#,##0_ "/>
+    <numFmt numFmtId="171" formatCode="#,##0.0000_);\(#,##0.0000\)"/>
+    <numFmt numFmtId="172" formatCode="#,##0.0000_ "/>
+    <numFmt numFmtId="173" formatCode="&quot;in &quot;#,##0&quot;s&quot;"/>
+    <numFmt numFmtId="174" formatCode="#,##0.00_ "/>
+    <numFmt numFmtId="175" formatCode="0&quot; yrs&quot;"/>
+    <numFmt numFmtId="176" formatCode="0.000_ "/>
+    <numFmt numFmtId="177" formatCode="&quot;every&quot;\ 0\ &quot;Months&quot;"/>
+    <numFmt numFmtId="178" formatCode="0.0\x"/>
+    <numFmt numFmtId="179" formatCode="0\x"/>
+    <numFmt numFmtId="180" formatCode="0.000000000000000%"/>
+    <numFmt numFmtId="181" formatCode="#,##0_);\(#,##0\);0;@"/>
   </numFmts>
-  <fonts count="72" x14ac:knownFonts="1">
+  <fonts count="72">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -4058,7 +4047,7 @@
     <xf numFmtId="3" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
@@ -4100,17 +4089,17 @@
     <xf numFmtId="3" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="166" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="169" fontId="9" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="9" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="169" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="170" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4119,7 +4108,7 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="168" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4193,10 +4182,10 @@
     </xf>
     <xf numFmtId="10" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="172" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="171" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="171" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -4207,7 +4196,7 @@
     <xf numFmtId="10" fontId="11" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="169" fontId="9" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="9" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -4245,7 +4234,7 @@
     <xf numFmtId="10" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="168" fontId="8" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="8" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4255,7 +4244,7 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="169" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -4266,19 +4255,19 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="169" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="174" fontId="17" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="173" fontId="17" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="174" fontId="14" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="173" fontId="14" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="174" fontId="23" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="173" fontId="23" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
@@ -4286,8 +4275,8 @@
       <alignment horizontal="left" indent="1"/>
     </xf>
     <xf numFmtId="39" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="173" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="173" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="172" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="172" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="37" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="38" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -4310,29 +4299,29 @@
     </xf>
     <xf numFmtId="9" fontId="30" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="9" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="171" fontId="31" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="170" fontId="31" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="39" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="175" fontId="24" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="174" fontId="24" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="10" fontId="25" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="30" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="176" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="176" fontId="25" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="175" fontId="30" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="175" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="175" fontId="25" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="175" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="174" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="176" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="175" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -4349,15 +4338,15 @@
     </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="175" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="174" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="10" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="175" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="29" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="176" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="175" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -4368,11 +4357,11 @@
     <xf numFmtId="0" fontId="27" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="3" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="175" fontId="8" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="174" fontId="8" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="36" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4433,14 +4422,14 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="175" fontId="1" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="174" fontId="1" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="177" fontId="42" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="176" fontId="42" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
     <xf numFmtId="40" fontId="41" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -4453,7 +4442,7 @@
     </xf>
     <xf numFmtId="0" fontId="44" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="39" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="176" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="175" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="8" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -4490,7 +4479,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="176" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="175" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -4507,7 +4496,7 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="179" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="178" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
@@ -4553,7 +4542,7 @@
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="49" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="180" fontId="46" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="179" fontId="46" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -4568,13 +4557,13 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="175" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="174" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="175" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="174" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="181" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="180" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -4590,53 +4579,53 @@
     <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="167" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="182" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="182" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="182" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="181" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="182" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="182" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="182" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="182" fontId="3" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="182" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="182" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="182" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="182" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="182" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="182" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="182" fontId="47" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="182" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="3" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="181" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="47" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="182" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="182" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="182" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="182" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="182" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="182" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="181" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="181" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="182" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="182" fontId="17" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="17" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="182" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="182" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="182" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="181" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="181" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="3" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -4653,7 +4642,7 @@
       <alignment horizontal="left" indent="1"/>
     </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="182" fontId="8" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="8" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="25" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
@@ -4666,21 +4655,21 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="182" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="176" fontId="25" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="175" fontId="25" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="10" fontId="25" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="182" fontId="32" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="32" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
@@ -4690,14 +4679,14 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="182" fontId="24" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="24" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="175" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="174" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="40" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -4706,8 +4695,8 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="10" fontId="29" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="176" fontId="25" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="175" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="175" fontId="25" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="174" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="29" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="25" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="51" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4719,7 +4708,7 @@
     </xf>
     <xf numFmtId="39" fontId="24" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="39" fontId="42" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="175" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="174" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="42" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -4727,7 +4716,7 @@
     <xf numFmtId="9" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="179" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -4766,7 +4755,7 @@
     <xf numFmtId="4" fontId="56" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="166" fontId="56" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="56" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="56" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -4780,39 +4769,39 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="64" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="176" fontId="64" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="175" fontId="64" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="175" fontId="56" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="174" fontId="56" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="56" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="56" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="175" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="174" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="10" fontId="56" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="66" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="174" fontId="67" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="173" fontId="67" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="182" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="181" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="37" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="182" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
     <xf numFmtId="10" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="181" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="180" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -4823,7 +4812,7 @@
       <alignment horizontal="left" indent="1"/>
     </xf>
     <xf numFmtId="10" fontId="61" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="167" fontId="61" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="61" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -4834,10 +4823,10 @@
     <xf numFmtId="9" fontId="61" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="179" fontId="61" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="61" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="182" fontId="61" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="181" fontId="61" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="10" fontId="60" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -4846,7 +4835,7 @@
     <xf numFmtId="10" fontId="56" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="56" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="175" fontId="56" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="39" fontId="54" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4859,7 +4848,7 @@
     <xf numFmtId="10" fontId="56" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="56" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="175" fontId="56" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="10" fontId="54" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4868,8 +4857,8 @@
     <xf numFmtId="40" fontId="65" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="176" fontId="56" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="177" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="175" fontId="56" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="176" fontId="54" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="63" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -4877,10 +4866,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="39" fontId="54" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="175" fontId="65" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="174" fontId="65" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="54" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="68" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="10" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4889,10 +4878,10 @@
     <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="178" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="69" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4909,16 +4898,16 @@
     <xf numFmtId="4" fontId="56" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="178" fontId="56" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="56" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="56" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="56" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4939,7 +4928,7 @@
     <xf numFmtId="0" fontId="59" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="56" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="56" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="56" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4957,7 +4946,7 @@
     <xf numFmtId="40" fontId="32" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="176" fontId="70" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="175" fontId="70" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="10" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -4967,10 +4956,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="174" fontId="14" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="173" fontId="14" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="182" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -4985,7 +4974,7 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="168" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="10" fontId="71" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4999,34 +4988,34 @@
     <xf numFmtId="10" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="182" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5036,6 +5025,15 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -5045,21 +5043,12 @@
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
     <cellStyle name="常规 2 2" xfId="1" xr:uid="{A35F4541-DCCE-4554-A311-39480A36979A}"/>
   </cellStyles>
   <dxfs count="7">
@@ -5341,7 +5330,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:I167"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.65"/>
   <cols>
     <col min="1" max="1" width="2.6640625" style="1" customWidth="1"/>
     <col min="2" max="2" width="32.6640625" style="1" customWidth="1"/>
@@ -5350,7 +5339,7 @@
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:9" ht="16" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" ht="13.9">
       <c r="A2" s="200" t="s">
         <v>225</v>
       </c>
@@ -5363,7 +5352,7 @@
       <c r="H2" s="21"/>
       <c r="I2" s="21"/>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:9">
       <c r="E3" s="428" t="s">
         <v>538</v>
       </c>
@@ -5371,7 +5360,7 @@
         <v>46065</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="14" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:9" ht="12.4">
       <c r="B4" s="421" t="s">
         <v>533</v>
       </c>
@@ -5385,7 +5374,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:9">
       <c r="B5" s="1" t="s">
         <v>349</v>
       </c>
@@ -5399,7 +5388,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:9">
       <c r="B6" s="2" t="s">
         <v>53</v>
       </c>
@@ -5409,7 +5398,7 @@
       <c r="D6" s="45"/>
       <c r="E6" s="45"/>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:9">
       <c r="B7" s="1" t="s">
         <v>351</v>
       </c>
@@ -5419,16 +5408,16 @@
       <c r="D7" s="45"/>
       <c r="E7" s="45"/>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:9">
       <c r="B8" s="4" t="s">
         <v>350</v>
       </c>
       <c r="C8" s="47">
-        <v>42.2</v>
+        <v>44.5</v>
       </c>
       <c r="E8" s="32"/>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:9">
       <c r="B9" s="4" t="s">
         <v>346</v>
       </c>
@@ -5436,43 +5425,43 @@
         <v>2558824000</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:9">
       <c r="B10" s="4" t="s">
         <v>352</v>
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>107982.3728</v>
+        <v>113867.66800000001</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>528</v>
       </c>
       <c r="E10" s="303">
         <f>Scenarios!F34</f>
-        <v>0.15751340909520897</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.15">
+        <v>0.13797018670551686</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
       <c r="D11" s="5"/>
       <c r="E11" s="5"/>
     </row>
-    <row r="12" spans="1:9" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B12" s="462" t="s">
+    <row r="12" spans="1:9" ht="24.5" customHeight="1">
+      <c r="B12" s="460" t="s">
         <v>355</v>
       </c>
-      <c r="C12" s="462"/>
-      <c r="D12" s="462"/>
-      <c r="E12" s="462"/>
-      <c r="F12" s="462"/>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.15">
+      <c r="C12" s="460"/>
+      <c r="D12" s="460"/>
+      <c r="E12" s="460"/>
+      <c r="F12" s="460"/>
+    </row>
+    <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
         <f>Scenarios!B39&amp;" Valuation Conclusion"</f>
         <v>1-stage DCF Valuation Conclusion</v>
       </c>
       <c r="C14" s="43"/>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:9">
       <c r="B15" s="1" t="s">
         <v>319</v>
       </c>
@@ -5487,7 +5476,7 @@
         <v>EUR/HKD</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:9">
       <c r="B16" s="1" t="s">
         <v>320</v>
       </c>
@@ -5498,10 +5487,10 @@
         <v>354</v>
       </c>
       <c r="E16" s="416">
-        <v>9.2105230273246779</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.15">
+        <v>9.2443941400000007</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
       <c r="B17" s="1" t="s">
         <v>532</v>
       </c>
@@ -5515,14 +5504,14 @@
         <v>558</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:6">
       <c r="B18" s="1" t="str">
         <f>"Expected Equity Value ("&amp;C7&amp;") :"</f>
         <v>Expected Equity Value (HKD) :</v>
       </c>
       <c r="C18" s="252">
         <f>C125</f>
-        <v>60.439606731746466</v>
+        <v>60.661869541750846</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>347</v>
@@ -5531,7 +5520,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:6">
       <c r="B19" s="2" t="s">
         <v>275</v>
       </c>
@@ -5547,11 +5536,11 @@
         <v>46081</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:6">
       <c r="D20" s="5"/>
       <c r="E20" s="5"/>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:6">
       <c r="B21" s="42" t="s">
         <v>404</v>
       </c>
@@ -5566,13 +5555,13 @@
         <v>3</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:6">
       <c r="B22" s="1" t="s">
         <v>312</v>
       </c>
       <c r="C22" s="255">
         <f>E140</f>
-        <v>30.472338478979687</v>
+        <v>30.574763737046222</v>
       </c>
       <c r="D22" s="38" t="s">
         <v>406</v>
@@ -5581,13 +5570,13 @@
         <v>0.29465259038036606</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:6">
       <c r="B23" s="1" t="s">
         <v>313</v>
       </c>
       <c r="C23" s="256">
         <f>E141</f>
-        <v>37.923481236889849</v>
+        <v>38.051864087433898</v>
       </c>
       <c r="D23" s="38" t="s">
         <v>407</v>
@@ -5596,13 +5585,13 @@
         <v>0.20075184365903009</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:6">
       <c r="B24" s="1" t="s">
         <v>315</v>
       </c>
       <c r="C24" s="256">
         <f>E144</f>
-        <v>46.775086255631912</v>
+        <v>46.934395434683225</v>
       </c>
       <c r="D24" s="38" t="s">
         <v>408</v>
@@ -5611,13 +5600,13 @@
         <v>0.1174</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:6">
       <c r="B25" s="1" t="s">
         <v>314</v>
       </c>
       <c r="C25" s="256">
         <f>E145</f>
-        <v>52.732918282721435</v>
+        <v>52.913085137964458</v>
       </c>
       <c r="D25" s="38" t="s">
         <v>409</v>
@@ -5626,11 +5615,11 @@
         <v>7.2499999999999995E-2</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:6">
       <c r="D26" s="5"/>
       <c r="E26" s="5"/>
     </row>
-    <row r="27" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" ht="13.9">
       <c r="A27" s="200" t="s">
         <v>280</v>
       </c>
@@ -5640,25 +5629,25 @@
       <c r="E27" s="34"/>
       <c r="F27" s="34"/>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="B29" s="462" t="s">
+    <row r="29" spans="1:6">
+      <c r="B29" s="460" t="s">
         <v>356</v>
       </c>
-      <c r="C29" s="462"/>
-      <c r="D29" s="462"/>
-      <c r="E29" s="462"/>
-      <c r="F29" s="462"/>
-    </row>
-    <row r="30" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B30" s="466" t="s">
+      <c r="C29" s="460"/>
+      <c r="D29" s="460"/>
+      <c r="E29" s="460"/>
+      <c r="F29" s="460"/>
+    </row>
+    <row r="30" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B30" s="462" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="466"/>
-      <c r="D30" s="466"/>
-      <c r="E30" s="466"/>
-      <c r="F30" s="466"/>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C30" s="462"/>
+      <c r="D30" s="462"/>
+      <c r="E30" s="462"/>
+      <c r="F30" s="462"/>
+    </row>
+    <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
         <v>195</v>
       </c>
@@ -5667,16 +5656,16 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="33" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B33" s="463" t="s">
+    <row r="33" spans="2:6" ht="24.5" customHeight="1">
+      <c r="B33" s="461" t="s">
         <v>196</v>
       </c>
-      <c r="C33" s="463"/>
-      <c r="D33" s="463"/>
-      <c r="E33" s="463"/>
-      <c r="F33" s="463"/>
-    </row>
-    <row r="34" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="C33" s="461"/>
+      <c r="D33" s="461"/>
+      <c r="E33" s="461"/>
+      <c r="F33" s="461"/>
+    </row>
+    <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
         <v>197</v>
       </c>
@@ -5689,20 +5678,20 @@
         <v>EUR</v>
       </c>
     </row>
-    <row r="35" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="35" spans="2:6">
       <c r="B35" s="44"/>
       <c r="C35" s="73"/>
     </row>
-    <row r="36" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B36" s="463" t="s">
+    <row r="36" spans="2:6" ht="24.5" customHeight="1">
+      <c r="B36" s="461" t="s">
         <v>198</v>
       </c>
-      <c r="C36" s="463"/>
-      <c r="D36" s="463"/>
-      <c r="E36" s="463"/>
-      <c r="F36" s="463"/>
-    </row>
-    <row r="37" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="C36" s="461"/>
+      <c r="D36" s="461"/>
+      <c r="E36" s="461"/>
+      <c r="F36" s="461"/>
+    </row>
+    <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
         <v>199</v>
       </c>
@@ -5715,7 +5704,7 @@
         <v>EUR</v>
       </c>
     </row>
-    <row r="38" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="38" spans="2:6">
       <c r="B38" s="49" t="s">
         <v>200</v>
       </c>
@@ -5728,16 +5717,16 @@
         <v>EUR</v>
       </c>
     </row>
-    <row r="40" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B40" s="463" t="s">
+    <row r="40" spans="2:6">
+      <c r="B40" s="461" t="s">
         <v>201</v>
       </c>
-      <c r="C40" s="463"/>
-      <c r="D40" s="463"/>
-      <c r="E40" s="463"/>
-      <c r="F40" s="463"/>
-    </row>
-    <row r="41" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="C40" s="461"/>
+      <c r="D40" s="461"/>
+      <c r="E40" s="461"/>
+      <c r="F40" s="461"/>
+    </row>
+    <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
         <v>202</v>
       </c>
@@ -5750,16 +5739,16 @@
         <v>EUR</v>
       </c>
     </row>
-    <row r="43" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B43" s="463" t="s">
+    <row r="43" spans="2:6">
+      <c r="B43" s="461" t="s">
         <v>205</v>
       </c>
-      <c r="C43" s="463"/>
-      <c r="D43" s="463"/>
-      <c r="E43" s="463"/>
-      <c r="F43" s="463"/>
-    </row>
-    <row r="44" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="C43" s="461"/>
+      <c r="D43" s="461"/>
+      <c r="E43" s="461"/>
+      <c r="F43" s="461"/>
+    </row>
+    <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
         <v>267</v>
       </c>
@@ -5774,7 +5763,7 @@
       <c r="E44" s="244"/>
       <c r="F44" s="244"/>
     </row>
-    <row r="45" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="45" spans="2:6">
       <c r="B45" s="44" t="s">
         <v>268</v>
       </c>
@@ -5789,7 +5778,7 @@
       <c r="E45" s="244"/>
       <c r="F45" s="244"/>
     </row>
-    <row r="46" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="46" spans="2:6">
       <c r="B46" s="44" t="s">
         <v>203</v>
       </c>
@@ -5802,12 +5791,12 @@
         <v>EUR</v>
       </c>
     </row>
-    <row r="48" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="48" spans="2:6">
       <c r="B48" s="1" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="49" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="49" spans="2:6">
       <c r="B49" s="44" t="s">
         <v>223</v>
       </c>
@@ -5820,16 +5809,16 @@
         <v>EUR</v>
       </c>
     </row>
-    <row r="51" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B51" s="463" t="s">
+    <row r="51" spans="2:6">
+      <c r="B51" s="461" t="s">
         <v>206</v>
       </c>
-      <c r="C51" s="463"/>
-      <c r="D51" s="463"/>
-      <c r="E51" s="463"/>
-      <c r="F51" s="463"/>
-    </row>
-    <row r="52" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="C51" s="461"/>
+      <c r="D51" s="461"/>
+      <c r="E51" s="461"/>
+      <c r="F51" s="461"/>
+    </row>
+    <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
         <v>204</v>
       </c>
@@ -5842,8 +5831,8 @@
         <v>EUR</v>
       </c>
     </row>
-    <row r="54" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B54" s="463" t="s">
+    <row r="54" spans="2:6">
+      <c r="B54" s="461" t="s">
         <v>265</v>
       </c>
       <c r="C54" s="464"/>
@@ -5851,7 +5840,7 @@
       <c r="E54" s="464"/>
       <c r="F54" s="464"/>
     </row>
-    <row r="55" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="55" spans="2:6">
       <c r="B55" s="44" t="s">
         <v>207</v>
       </c>
@@ -5864,25 +5853,25 @@
         <v>EUR</v>
       </c>
     </row>
-    <row r="57" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B57" s="462" t="s">
+    <row r="57" spans="2:6" ht="24.5" customHeight="1">
+      <c r="B57" s="460" t="s">
         <v>270</v>
       </c>
-      <c r="C57" s="462"/>
-      <c r="D57" s="462"/>
-      <c r="E57" s="462"/>
-      <c r="F57" s="462"/>
-    </row>
-    <row r="58" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B58" s="462" t="s">
+      <c r="C57" s="460"/>
+      <c r="D57" s="460"/>
+      <c r="E57" s="460"/>
+      <c r="F57" s="460"/>
+    </row>
+    <row r="58" spans="2:6" ht="24.5" customHeight="1">
+      <c r="B58" s="460" t="s">
         <v>282</v>
       </c>
-      <c r="C58" s="462"/>
-      <c r="D58" s="462"/>
-      <c r="E58" s="462"/>
-      <c r="F58" s="462"/>
-    </row>
-    <row r="60" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="C58" s="460"/>
+      <c r="D58" s="460"/>
+      <c r="E58" s="460"/>
+      <c r="F58" s="460"/>
+    </row>
+    <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
         <v>227</v>
       </c>
@@ -5895,7 +5884,7 @@
         <v>EUR</v>
       </c>
     </row>
-    <row r="61" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="61" spans="2:6">
       <c r="B61" s="44" t="s">
         <v>213</v>
       </c>
@@ -5908,23 +5897,23 @@
         <v>EUR</v>
       </c>
     </row>
-    <row r="62" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="62" spans="2:6">
       <c r="B62" s="204" t="s">
         <v>302</v>
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>6.9088519142746635E-2</v>
+        <v>6.575858885923315E-2</v>
       </c>
       <c r="F62" s="257"/>
     </row>
-    <row r="63" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="63" spans="2:6">
       <c r="B63" s="204" t="s">
         <v>332</v>
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>3.392895734597156E-2</v>
+        <v>3.2175325842696632E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>322</v>
@@ -5934,7 +5923,7 @@
         <v>4.5232326123897897</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="65" spans="1:6">
       <c r="B65" s="192" t="s">
         <v>325</v>
       </c>
@@ -5945,7 +5934,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="66" spans="1:6">
       <c r="B66" s="44" t="s">
         <v>326</v>
       </c>
@@ -5958,7 +5947,7 @@
         <v>0.28005991710273764</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="67" spans="1:6">
       <c r="B67" s="229" t="str">
         <f>Normalized_FCF!B116</f>
         <v>Pre-tax Profit/Sales</v>
@@ -5972,7 +5961,7 @@
         <v>0.21885492502426099</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="68" spans="1:6">
       <c r="B68" s="229" t="str">
         <f>Normalized_FCF!B117</f>
         <v>Sales/Total Assets</v>
@@ -5986,7 +5975,7 @@
         <v>0.65265738052043343</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:6">
       <c r="B69" s="229" t="str">
         <f>Normalized_FCF!B118</f>
         <v>Total Assets/Equity</v>
@@ -6000,7 +5989,7 @@
         <v>1.9606920057834423</v>
       </c>
     </row>
-    <row r="71" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:6" ht="13.9">
       <c r="A71" s="200" t="s">
         <v>477</v>
       </c>
@@ -6010,45 +5999,45 @@
       <c r="E71" s="34"/>
       <c r="F71" s="34"/>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="72" spans="1:6">
       <c r="A72" s="191"/>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="462" t="s">
+      <c r="B73" s="460" t="s">
         <v>478</v>
       </c>
-      <c r="C73" s="462"/>
-      <c r="D73" s="462"/>
-      <c r="E73" s="462"/>
-      <c r="F73" s="462"/>
-    </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C73" s="460"/>
+      <c r="D73" s="460"/>
+      <c r="E73" s="460"/>
+      <c r="F73" s="460"/>
+    </row>
+    <row r="74" spans="1:6">
       <c r="A74" s="191"/>
       <c r="B74" s="1" t="s">
         <v>465</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:6">
       <c r="A75" s="191"/>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:6">
       <c r="A76" s="191"/>
       <c r="B76" s="192" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="462" t="s">
+      <c r="B77" s="460" t="s">
         <v>271</v>
       </c>
-      <c r="C77" s="462"/>
-      <c r="D77" s="462"/>
-      <c r="E77" s="462"/>
-      <c r="F77" s="462"/>
-    </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C77" s="460"/>
+      <c r="D77" s="460"/>
+      <c r="E77" s="460"/>
+      <c r="F77" s="460"/>
+    </row>
+    <row r="78" spans="1:6">
       <c r="A78" s="191"/>
       <c r="B78" s="1" t="s">
         <v>215</v>
@@ -6062,21 +6051,21 @@
         <v>EUR</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="79" spans="1:6">
       <c r="A79" s="191"/>
       <c r="B79" s="44" t="s">
         <v>234</v>
       </c>
       <c r="C79" s="201">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-10.279726290448499</v>
+        <v>-10.317529330126302</v>
       </c>
       <c r="D79" s="1" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="80" spans="1:6">
       <c r="A80" s="191"/>
       <c r="B80" s="229" t="s">
         <v>309</v>
@@ -6086,7 +6075,7 @@
         <v>0.67283405398617657</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="81" spans="1:6">
       <c r="A81" s="191"/>
       <c r="B81" s="229" t="s">
         <v>311</v>
@@ -6096,16 +6085,16 @@
         <v>2.2041306156151999</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="82" spans="1:6">
       <c r="A82" s="191"/>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="83" spans="1:6">
       <c r="A83" s="191"/>
       <c r="B83" s="1" t="s">
         <v>466</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="84" spans="1:6">
       <c r="A84" s="191"/>
       <c r="B84" s="1" t="s">
         <v>224</v>
@@ -6119,7 +6108,7 @@
         <v>EUR</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="85" spans="1:6">
       <c r="A85" s="191"/>
       <c r="B85" s="229" t="s">
         <v>222</v>
@@ -6133,30 +6122,30 @@
         <v>EUR</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="86" spans="1:6">
       <c r="A86" s="191"/>
       <c r="B86" s="44" t="s">
         <v>235</v>
       </c>
       <c r="C86" s="201">
         <f>C84*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-0.1870831211859201</v>
+        <v>-0.18777110746623668</v>
       </c>
       <c r="D86" s="1" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="87" spans="1:6">
       <c r="A87" s="191"/>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="88" spans="1:6">
       <c r="A88" s="191"/>
       <c r="B88" s="1" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="89" spans="1:6">
       <c r="A89" s="191"/>
       <c r="B89" s="1" t="s">
         <v>217</v>
@@ -6170,38 +6159,38 @@
         <v>EUR</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="90" spans="1:6">
       <c r="A90" s="191"/>
       <c r="B90" s="44" t="s">
         <v>236</v>
       </c>
       <c r="C90" s="201">
         <f>C89*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>0.13180484703158896</v>
+        <v>0.13228955097421158</v>
       </c>
       <c r="D90" s="1" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="91" spans="1:6">
       <c r="A91" s="191"/>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="92" spans="1:6">
       <c r="A92" s="191"/>
       <c r="B92" s="44" t="s">
         <v>469</v>
       </c>
       <c r="C92" s="216">
         <f>DCF!F8</f>
-        <v>-10.335004564602832</v>
+        <v>-10.373010886618328</v>
       </c>
       <c r="D92" s="44" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="94" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:6" ht="13.9">
       <c r="A94" s="200" t="s">
         <v>470</v>
       </c>
@@ -6211,42 +6200,42 @@
       <c r="E94" s="34"/>
       <c r="F94" s="34"/>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="95" spans="1:6">
       <c r="A95" s="191"/>
     </row>
-    <row r="96" spans="1:6" ht="11.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B96" s="462" t="s">
+    <row r="96" spans="1:6" ht="11.75" customHeight="1">
+      <c r="B96" s="460" t="s">
         <v>485</v>
       </c>
-      <c r="C96" s="462"/>
-      <c r="D96" s="462"/>
-      <c r="E96" s="462"/>
-      <c r="F96" s="462"/>
-    </row>
-    <row r="97" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B97" s="466" t="s">
+      <c r="C96" s="460"/>
+      <c r="D96" s="460"/>
+      <c r="E96" s="460"/>
+      <c r="F96" s="460"/>
+    </row>
+    <row r="97" spans="2:6">
+      <c r="B97" s="462" t="s">
         <v>484</v>
       </c>
-      <c r="C97" s="466"/>
-      <c r="D97" s="466"/>
-      <c r="E97" s="466"/>
-      <c r="F97" s="466"/>
-    </row>
-    <row r="98" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B98" s="466" t="s">
+      <c r="C97" s="462"/>
+      <c r="D97" s="462"/>
+      <c r="E97" s="462"/>
+      <c r="F97" s="462"/>
+    </row>
+    <row r="98" spans="2:6">
+      <c r="B98" s="462" t="s">
         <v>483</v>
       </c>
-      <c r="C98" s="466"/>
-      <c r="D98" s="466"/>
-      <c r="E98" s="466"/>
-      <c r="F98" s="466"/>
-    </row>
-    <row r="100" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="C98" s="462"/>
+      <c r="D98" s="462"/>
+      <c r="E98" s="462"/>
+      <c r="F98" s="462"/>
+    </row>
+    <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="101" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="101" spans="2:6">
       <c r="B101" s="49" t="s">
         <v>467</v>
       </c>
@@ -6255,7 +6244,7 @@
         <v>7.2499999999999995E-2</v>
       </c>
     </row>
-    <row r="102" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="102" spans="2:6">
       <c r="B102" s="229" t="s">
         <v>318</v>
       </c>
@@ -6264,7 +6253,7 @@
         <v>7.2499999999999995E-2</v>
       </c>
     </row>
-    <row r="103" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="103" spans="2:6">
       <c r="B103" s="229" t="s">
         <v>317</v>
       </c>
@@ -6273,7 +6262,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="104" spans="2:6">
       <c r="B104" s="44" t="s">
         <v>214</v>
       </c>
@@ -6282,76 +6271,76 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="106" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="106" spans="2:6">
       <c r="B106" s="250" t="s">
         <v>281</v>
       </c>
       <c r="C106" s="116"/>
     </row>
-    <row r="107" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B107" s="462" t="s">
+    <row r="107" spans="2:6">
+      <c r="B107" s="460" t="s">
         <v>283</v>
       </c>
-      <c r="C107" s="462"/>
-      <c r="D107" s="462"/>
-      <c r="E107" s="462"/>
-      <c r="F107" s="462"/>
-    </row>
-    <row r="108" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B108" s="462" t="s">
+      <c r="C107" s="460"/>
+      <c r="D107" s="460"/>
+      <c r="E107" s="460"/>
+      <c r="F107" s="460"/>
+    </row>
+    <row r="108" spans="2:6">
+      <c r="B108" s="460" t="s">
         <v>284</v>
       </c>
-      <c r="C108" s="462"/>
-      <c r="D108" s="462"/>
-      <c r="E108" s="462"/>
-      <c r="F108" s="462"/>
-    </row>
-    <row r="110" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="C108" s="460"/>
+      <c r="D108" s="460"/>
+      <c r="E108" s="460"/>
+      <c r="F108" s="460"/>
+    </row>
+    <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
         <v>487</v>
       </c>
     </row>
-    <row r="111" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="111" spans="2:6">
       <c r="B111" s="49" t="s">
         <v>468</v>
       </c>
       <c r="C111" s="216">
         <f>BS!D47</f>
-        <v>-6.2879234830533743</v>
+        <v>-6.3110469217719434</v>
       </c>
       <c r="D111" s="1" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="112" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="112" spans="2:6">
       <c r="B112" s="44" t="s">
         <v>323</v>
       </c>
       <c r="C112" s="216">
         <f>DCF!C11</f>
-        <v>46.309685301690244</v>
+        <v>46.479986224250105</v>
       </c>
       <c r="D112" s="1" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="114" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B114" s="462" t="s">
+    <row r="114" spans="2:6" ht="24.5" customHeight="1">
+      <c r="B114" s="460" t="s">
         <v>491</v>
       </c>
-      <c r="C114" s="462"/>
-      <c r="D114" s="462"/>
-      <c r="E114" s="462"/>
-      <c r="F114" s="462"/>
-    </row>
-    <row r="116" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="C114" s="460"/>
+      <c r="D114" s="460"/>
+      <c r="E114" s="460"/>
+      <c r="F114" s="460"/>
+    </row>
+    <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
         <v>488</v>
       </c>
     </row>
-    <row r="117" spans="2:6" ht="14" x14ac:dyDescent="0.2">
+    <row r="117" spans="2:6" ht="12.4">
       <c r="B117" s="342" t="s">
         <v>101</v>
       </c>
@@ -6368,7 +6357,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="118" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="118" spans="2:6">
       <c r="B118" s="205" t="str">
         <f>DCF!B90&amp;" ("&amp;DCF!D90&amp;"yrs)"</f>
         <v>Snowball Scenario (20yrs)</v>
@@ -6379,7 +6368,7 @@
       </c>
       <c r="D118" s="207" t="str">
         <f>ROUND(DCF!E90,2)&amp;" "&amp;Market_currency</f>
-        <v>99.61 HKD</v>
+        <v>99.97 HKD</v>
       </c>
       <c r="E118" s="208">
         <f>DCF!F90</f>
@@ -6387,10 +6376,10 @@
       </c>
       <c r="F118" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E90,C$18)</f>
-        <v>-0.13630049268396624</v>
-      </c>
-    </row>
-    <row r="119" spans="2:6" x14ac:dyDescent="0.15">
+        <v>-0.13636300527655298</v>
+      </c>
+    </row>
+    <row r="119" spans="2:6">
       <c r="B119" s="205" t="str">
         <f>DCF!B91&amp;" ("&amp;DCF!D91&amp;"yrs)"</f>
         <v>Optimistic (20yrs)</v>
@@ -6401,7 +6390,7 @@
       </c>
       <c r="D119" s="207" t="str">
         <f>ROUND(DCF!E91,2)&amp;" "&amp;Market_currency</f>
-        <v>73.79 HKD</v>
+        <v>74.06 HKD</v>
       </c>
       <c r="E119" s="199">
         <f>DCF!F91</f>
@@ -6409,10 +6398,10 @@
       </c>
       <c r="F119" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E91,C$18)</f>
-        <v>-4.3591731950928019E-2</v>
-      </c>
-    </row>
-    <row r="120" spans="2:6" x14ac:dyDescent="0.15">
+        <v>-4.3667685662394755E-2</v>
+      </c>
+    </row>
+    <row r="120" spans="2:6">
       <c r="B120" s="205" t="str">
         <f>DCF!B92&amp;" ("&amp;DCF!D92&amp;"yrs)"</f>
         <v>Base (20yrs)</v>
@@ -6423,7 +6412,7 @@
       </c>
       <c r="D120" s="207" t="str">
         <f>ROUND(DCF!E92,2)&amp;" "&amp;Market_currency</f>
-        <v>54.71 HKD</v>
+        <v>54.91 HKD</v>
       </c>
       <c r="E120" s="199">
         <f>DCF!F92</f>
@@ -6431,10 +6420,10 @@
       </c>
       <c r="F120" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E92,C$18)</f>
-        <v>5.9092749049236608E-2</v>
-      </c>
-    </row>
-    <row r="121" spans="2:6" x14ac:dyDescent="0.15">
+        <v>5.8999859306308793E-2</v>
+      </c>
+    </row>
+    <row r="121" spans="2:6">
       <c r="B121" s="205" t="str">
         <f>DCF!B93&amp;" ("&amp;DCF!D93&amp;"yrs)"</f>
         <v>Pessimistic (20yrs)</v>
@@ -6445,7 +6434,7 @@
       </c>
       <c r="D121" s="207" t="str">
         <f>ROUND(DCF!E93,2)&amp;" "&amp;Market_currency</f>
-        <v>40.58 HKD</v>
+        <v>40.73 HKD</v>
       </c>
       <c r="E121" s="199">
         <f>DCF!F93</f>
@@ -6453,10 +6442,10 @@
       </c>
       <c r="F121" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E93,C$18)</f>
-        <v>0.17313243305898471</v>
-      </c>
-    </row>
-    <row r="122" spans="2:6" x14ac:dyDescent="0.15">
+        <v>0.17301803396283413</v>
+      </c>
+    </row>
+    <row r="122" spans="2:6">
       <c r="B122" s="205" t="str">
         <f>DCF!B94&amp;" ("&amp;DCF!D94&amp;"yrs)"</f>
         <v>Devil's advocate (20yrs)</v>
@@ -6467,7 +6456,7 @@
       </c>
       <c r="D122" s="207" t="str">
         <f>ROUND(DCF!E94,2)&amp;" "&amp;Market_currency</f>
-        <v>30.08 HKD</v>
+        <v>30.19 HKD</v>
       </c>
       <c r="E122" s="199">
         <f>DCF!F94</f>
@@ -6475,32 +6464,32 @@
       </c>
       <c r="F122" s="208">
         <f>RATE(Holding_Period,Scenarios!C$58,-DCF!E94,C$18)</f>
-        <v>0.30048790512722201</v>
-      </c>
-    </row>
-    <row r="124" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B124" s="463" t="s">
+        <v>0.30034588840893967</v>
+      </c>
+    </row>
+    <row r="124" spans="2:6">
+      <c r="B124" s="461" t="s">
         <v>357</v>
       </c>
-      <c r="C124" s="463"/>
-      <c r="D124" s="463"/>
-      <c r="E124" s="463"/>
-      <c r="F124" s="463"/>
-    </row>
-    <row r="125" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="C124" s="461"/>
+      <c r="D124" s="461"/>
+      <c r="E124" s="461"/>
+      <c r="F124" s="461"/>
+    </row>
+    <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
         <v>218</v>
       </c>
       <c r="C125" s="197">
         <f>Scenarios!C36</f>
-        <v>60.439606731746466</v>
+        <v>60.661869541750846</v>
       </c>
       <c r="D125" s="194" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="127" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="127" spans="2:6" ht="24.5" customHeight="1">
       <c r="B127" s="465" t="s">
         <v>358</v>
       </c>
@@ -6509,7 +6498,7 @@
       <c r="E127" s="465"/>
       <c r="F127" s="465"/>
     </row>
-    <row r="129" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="200" t="s">
         <v>474</v>
       </c>
@@ -6519,30 +6508,30 @@
       <c r="E129" s="34"/>
       <c r="F129" s="34"/>
     </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="B131" s="467" t="s">
+    <row r="131" spans="1:6">
+      <c r="B131" s="463" t="s">
         <v>285</v>
       </c>
-      <c r="C131" s="467"/>
-      <c r="D131" s="467"/>
-      <c r="E131" s="467"/>
-      <c r="F131" s="467"/>
-    </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="B132" s="462" t="s">
+      <c r="C131" s="463"/>
+      <c r="D131" s="463"/>
+      <c r="E131" s="463"/>
+      <c r="F131" s="463"/>
+    </row>
+    <row r="132" spans="1:6">
+      <c r="B132" s="460" t="s">
         <v>359</v>
       </c>
-      <c r="C132" s="462"/>
-      <c r="D132" s="462"/>
-      <c r="E132" s="462"/>
-      <c r="F132" s="462"/>
-    </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C132" s="460"/>
+      <c r="D132" s="460"/>
+      <c r="E132" s="460"/>
+      <c r="F132" s="460"/>
+    </row>
+    <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="135" spans="1:6">
       <c r="B135" s="1" t="s">
         <v>221</v>
       </c>
@@ -6551,7 +6540,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="136" spans="1:6">
       <c r="B136" s="194" t="s">
         <v>220</v>
       </c>
@@ -6564,14 +6553,14 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="138" spans="1:6">
       <c r="B138" s="192" t="s">
         <v>494</v>
       </c>
       <c r="C138" s="214"/>
       <c r="D138" s="215"/>
     </row>
-    <row r="139" spans="1:6" ht="14" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:6" ht="12.4">
       <c r="B139" s="340" t="s">
         <v>462</v>
       </c>
@@ -6590,7 +6579,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="140" spans="1:6">
       <c r="B140" s="336" t="s">
         <v>312</v>
       </c>
@@ -6600,18 +6589,18 @@
       </c>
       <c r="D140" s="333">
         <f>Scenarios!D62</f>
-        <v>27.852353332602064</v>
+        <v>27.954778590668599</v>
       </c>
       <c r="E140" s="334">
         <f>Scenarios!E62</f>
-        <v>30.472338478979687</v>
+        <v>30.574763737046222</v>
       </c>
       <c r="F140" s="335">
         <f>E22</f>
         <v>0.29465259038036606</v>
       </c>
     </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="141" spans="1:6">
       <c r="B141" s="336" t="s">
         <v>313</v>
       </c>
@@ -6621,25 +6610,25 @@
       </c>
       <c r="D141" s="333">
         <f>Scenarios!D63</f>
-        <v>34.910964177182088</v>
+        <v>35.039347027726137</v>
       </c>
       <c r="E141" s="334">
         <f>Scenarios!E63</f>
-        <v>37.923481236889849</v>
+        <v>38.051864087433898</v>
       </c>
       <c r="F141" s="335">
         <f>Scenarios!F63</f>
         <v>0.20075184365903009</v>
       </c>
     </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="142" spans="1:6">
       <c r="B142" s="194"/>
       <c r="C142" s="194"/>
       <c r="D142" s="194"/>
       <c r="E142" s="194"/>
       <c r="F142" s="194"/>
     </row>
-    <row r="143" spans="1:6" ht="14" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:6" ht="12.4">
       <c r="B143" s="340" t="s">
         <v>463</v>
       </c>
@@ -6658,7 +6647,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="144" spans="1:6">
       <c r="B144" s="336" t="s">
         <v>315</v>
       </c>
@@ -6668,18 +6657,18 @@
       </c>
       <c r="D144" s="333">
         <f>Scenarios!D66</f>
-        <v>43.320716274706704</v>
+        <v>43.480025453758017</v>
       </c>
       <c r="E144" s="334">
         <f>Scenarios!E66</f>
-        <v>46.775086255631912</v>
+        <v>46.934395434683225</v>
       </c>
       <c r="F144" s="335">
         <f>E24</f>
         <v>0.1174</v>
       </c>
     </row>
-    <row r="145" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="145" spans="1:6">
       <c r="B145" s="336" t="s">
         <v>314</v>
       </c>
@@ -6689,18 +6678,18 @@
       </c>
       <c r="D145" s="333">
         <f>Scenarios!D67</f>
-        <v>48.992514207704659</v>
+        <v>49.172681062947682</v>
       </c>
       <c r="E145" s="334">
         <f>Scenarios!E67</f>
-        <v>52.732918282721435</v>
+        <v>52.913085137964458</v>
       </c>
       <c r="F145" s="335">
         <f>Scenarios!F67</f>
         <v>7.2499999999999995E-2</v>
       </c>
     </row>
-    <row r="147" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:6" ht="13.9">
       <c r="A147" s="200" t="s">
         <v>475</v>
       </c>
@@ -6710,21 +6699,21 @@
       <c r="E147" s="34"/>
       <c r="F147" s="34"/>
     </row>
-    <row r="149" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="B149" s="461" t="s">
+    <row r="149" spans="1:6">
+      <c r="B149" s="467" t="s">
         <v>360</v>
       </c>
-      <c r="C149" s="462"/>
-      <c r="D149" s="462"/>
-      <c r="E149" s="462"/>
-      <c r="F149" s="462"/>
-    </row>
-    <row r="151" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C149" s="460"/>
+      <c r="D149" s="460"/>
+      <c r="E149" s="460"/>
+      <c r="F149" s="460"/>
+    </row>
+    <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
         <v>289</v>
       </c>
     </row>
-    <row r="152" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="152" spans="1:6">
       <c r="B152" s="464" t="s">
         <v>293</v>
       </c>
@@ -6733,80 +6722,92 @@
       <c r="E152" s="464"/>
       <c r="F152" s="464"/>
     </row>
-    <row r="153" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="153" spans="1:6">
       <c r="B153" s="196" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="154" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="154" spans="1:6">
       <c r="B154" s="196" t="s">
         <v>291</v>
       </c>
     </row>
-    <row r="155" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="155" spans="1:6">
       <c r="B155" s="196" t="s">
         <v>292</v>
       </c>
     </row>
-    <row r="157" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="157" spans="1:6">
       <c r="B157" s="1" t="s">
         <v>296</v>
       </c>
     </row>
-    <row r="158" spans="1:6" ht="34.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B158" s="463" t="s">
+    <row r="158" spans="1:6" ht="34.25" customHeight="1">
+      <c r="B158" s="461" t="s">
         <v>438</v>
       </c>
-      <c r="C158" s="463"/>
-      <c r="D158" s="463"/>
-      <c r="E158" s="463"/>
-      <c r="F158" s="463"/>
-    </row>
-    <row r="160" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C158" s="461"/>
+      <c r="D158" s="461"/>
+      <c r="E158" s="461"/>
+      <c r="F158" s="461"/>
+    </row>
+    <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
         <v>297</v>
       </c>
     </row>
-    <row r="161" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B161" s="460" t="s">
+    <row r="161" spans="2:6" ht="24.5" customHeight="1">
+      <c r="B161" s="466" t="s">
         <v>294</v>
       </c>
-      <c r="C161" s="460"/>
-      <c r="D161" s="460"/>
-      <c r="E161" s="460"/>
-      <c r="F161" s="460"/>
-    </row>
-    <row r="162" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B162" s="460" t="s">
+      <c r="C161" s="466"/>
+      <c r="D161" s="466"/>
+      <c r="E161" s="466"/>
+      <c r="F161" s="466"/>
+    </row>
+    <row r="162" spans="2:6" ht="24.5" customHeight="1">
+      <c r="B162" s="466" t="s">
         <v>295</v>
       </c>
-      <c r="C162" s="460"/>
-      <c r="D162" s="460"/>
-      <c r="E162" s="460"/>
-      <c r="F162" s="460"/>
-    </row>
-    <row r="164" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="C162" s="466"/>
+      <c r="D162" s="466"/>
+      <c r="E162" s="466"/>
+      <c r="F162" s="466"/>
+    </row>
+    <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
         <v>301</v>
       </c>
     </row>
-    <row r="165" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="165" spans="2:6">
       <c r="B165" s="196" t="s">
         <v>298</v>
       </c>
     </row>
-    <row r="166" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="166" spans="2:6">
       <c r="B166" s="196" t="s">
         <v>299</v>
       </c>
     </row>
-    <row r="167" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="167" spans="2:6">
       <c r="B167" s="196" t="s">
         <v>300</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6823,18 +6824,6 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -6862,15 +6851,15 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:M80"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="11.65"/>
   <cols>
     <col min="1" max="1" width="3" style="1" customWidth="1"/>
     <col min="2" max="2" width="27.33203125" style="1" customWidth="1"/>
     <col min="3" max="13" width="20.6640625" style="1" customWidth="1"/>
-    <col min="14" max="16384" width="8.83203125" style="1"/>
+    <col min="14" max="16384" width="8.796875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="1" spans="2:13">
       <c r="B1" s="87" t="str">
         <f>Thesis!E17</f>
         <v>EUR</v>
@@ -6919,7 +6908,7 @@
         <v>42004</v>
       </c>
     </row>
-    <row r="2" spans="2:13" ht="16" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:13" ht="13.9">
       <c r="B2" s="34" t="s">
         <v>93</v>
       </c>
@@ -6935,7 +6924,7 @@
       <c r="L2" s="35"/>
       <c r="M2" s="35"/>
     </row>
-    <row r="3" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="3" spans="2:13">
       <c r="B3" s="16" t="s">
         <v>25</v>
       </c>
@@ -6943,7 +6932,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="4" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="4" spans="2:13">
       <c r="B4" s="31" t="s">
         <v>0</v>
       </c>
@@ -6963,7 +6952,7 @@
       <c r="L4" s="287"/>
       <c r="M4" s="287"/>
     </row>
-    <row r="5" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="5" spans="2:13">
       <c r="B5" s="38" t="s">
         <v>40</v>
       </c>
@@ -6983,7 +6972,7 @@
       <c r="L5" s="287"/>
       <c r="M5" s="287"/>
     </row>
-    <row r="6" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="6" spans="2:13">
       <c r="B6" s="38" t="s">
         <v>51</v>
       </c>
@@ -7003,7 +6992,7 @@
       <c r="L6" s="287"/>
       <c r="M6" s="287"/>
     </row>
-    <row r="7" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="7" spans="2:13">
       <c r="B7" s="66" t="s">
         <v>58</v>
       </c>
@@ -7019,7 +7008,7 @@
       <c r="L7" s="288"/>
       <c r="M7" s="288"/>
     </row>
-    <row r="8" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="8" spans="2:13">
       <c r="B8" s="38" t="s">
         <v>46</v>
       </c>
@@ -7035,7 +7024,7 @@
       <c r="L8" s="287"/>
       <c r="M8" s="287"/>
     </row>
-    <row r="9" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="9" spans="2:13">
       <c r="B9" s="38" t="s">
         <v>134</v>
       </c>
@@ -7051,7 +7040,7 @@
       <c r="L9" s="287"/>
       <c r="M9" s="287"/>
     </row>
-    <row r="10" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="10" spans="2:13">
       <c r="B10" s="38" t="s">
         <v>138</v>
       </c>
@@ -7071,7 +7060,7 @@
       <c r="L10" s="287"/>
       <c r="M10" s="287"/>
     </row>
-    <row r="11" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="11" spans="2:13">
       <c r="B11" s="38" t="s">
         <v>133</v>
       </c>
@@ -7087,7 +7076,7 @@
       <c r="L11" s="287"/>
       <c r="M11" s="287"/>
     </row>
-    <row r="12" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="12" spans="2:13">
       <c r="B12" s="38" t="s">
         <v>37</v>
       </c>
@@ -7109,7 +7098,7 @@
       <c r="L12" s="287"/>
       <c r="M12" s="287"/>
     </row>
-    <row r="13" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="13" spans="2:13">
       <c r="B13" s="38" t="s">
         <v>64</v>
       </c>
@@ -7125,7 +7114,7 @@
       <c r="L13" s="287"/>
       <c r="M13" s="287"/>
     </row>
-    <row r="14" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="14" spans="2:13">
       <c r="B14" s="38" t="s">
         <v>47</v>
       </c>
@@ -7145,7 +7134,7 @@
       <c r="L14" s="287"/>
       <c r="M14" s="287"/>
     </row>
-    <row r="15" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="15" spans="2:13">
       <c r="B15" s="41" t="s">
         <v>39</v>
       </c>
@@ -7165,7 +7154,7 @@
       <c r="L15" s="289"/>
       <c r="M15" s="289"/>
     </row>
-    <row r="16" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="16" spans="2:13">
       <c r="B16" s="27" t="s">
         <v>41</v>
       </c>
@@ -7185,13 +7174,13 @@
       <c r="L16" s="287"/>
       <c r="M16" s="287"/>
     </row>
-    <row r="18" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:13">
       <c r="B18" s="16" t="s">
         <v>48</v>
       </c>
       <c r="C18" s="9"/>
     </row>
-    <row r="19" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:13">
       <c r="B19" s="26" t="s">
         <v>44</v>
       </c>
@@ -7207,7 +7196,7 @@
       <c r="L19" s="287"/>
       <c r="M19" s="287"/>
     </row>
-    <row r="20" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="20" spans="2:13">
       <c r="B20" s="26" t="s">
         <v>50</v>
       </c>
@@ -7223,7 +7212,7 @@
       <c r="L20" s="287"/>
       <c r="M20" s="287"/>
     </row>
-    <row r="21" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:13">
       <c r="B21" s="26" t="s">
         <v>49</v>
       </c>
@@ -7239,7 +7228,7 @@
       <c r="L21" s="287"/>
       <c r="M21" s="287"/>
     </row>
-    <row r="22" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:13">
       <c r="B22" s="26" t="s">
         <v>286</v>
       </c>
@@ -7259,7 +7248,7 @@
       <c r="L22" s="287"/>
       <c r="M22" s="287"/>
     </row>
-    <row r="23" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="23" spans="2:13">
       <c r="B23" s="26" t="s">
         <v>288</v>
       </c>
@@ -7279,7 +7268,7 @@
       <c r="L23" s="287"/>
       <c r="M23" s="287"/>
     </row>
-    <row r="24" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:13">
       <c r="B24" s="26" t="s">
         <v>287</v>
       </c>
@@ -7299,7 +7288,7 @@
       <c r="L24" s="287"/>
       <c r="M24" s="287"/>
     </row>
-    <row r="25" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="25" spans="2:13">
       <c r="B25" s="23" t="str">
         <f>"Dividend per share ("&amp;Market_currency&amp;")"</f>
         <v>Dividend per share (HKD)</v>
@@ -7320,7 +7309,7 @@
       <c r="L25" s="37"/>
       <c r="M25" s="37"/>
     </row>
-    <row r="27" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="27" spans="2:13">
       <c r="B27" s="16" t="s">
         <v>26</v>
       </c>
@@ -7328,7 +7317,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="28" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:13">
       <c r="B28" s="25" t="s">
         <v>22</v>
       </c>
@@ -7349,7 +7338,7 @@
       <c r="L28" s="287"/>
       <c r="M28" s="287"/>
     </row>
-    <row r="29" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="29" spans="2:13">
       <c r="B29" s="25" t="s">
         <v>30</v>
       </c>
@@ -7370,7 +7359,7 @@
       <c r="L29" s="287"/>
       <c r="M29" s="287"/>
     </row>
-    <row r="30" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="30" spans="2:13">
       <c r="B30" s="28" t="s">
         <v>38</v>
       </c>
@@ -7391,7 +7380,7 @@
       <c r="L30" s="289"/>
       <c r="M30" s="289"/>
     </row>
-    <row r="31" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:13">
       <c r="B31" s="28" t="s">
         <v>28</v>
       </c>
@@ -7412,7 +7401,7 @@
       <c r="L31" s="289"/>
       <c r="M31" s="289"/>
     </row>
-    <row r="32" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="32" spans="2:13">
       <c r="B32" s="25" t="s">
         <v>143</v>
       </c>
@@ -7433,7 +7422,7 @@
       <c r="L32" s="287"/>
       <c r="M32" s="287"/>
     </row>
-    <row r="34" spans="2:13" ht="16" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:13" ht="13.9">
       <c r="B34" s="34" t="s">
         <v>78</v>
       </c>
@@ -7449,12 +7438,12 @@
       <c r="L34" s="35"/>
       <c r="M34" s="35"/>
     </row>
-    <row r="35" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="35" spans="2:13">
       <c r="B35" s="16" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="36" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="36" spans="2:13">
       <c r="B36" s="31" t="s">
         <v>0</v>
       </c>
@@ -7503,7 +7492,7 @@
         <v/>
       </c>
     </row>
-    <row r="37" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="37" spans="2:13">
       <c r="B37" s="38" t="s">
         <v>40</v>
       </c>
@@ -7552,7 +7541,7 @@
         <v/>
       </c>
     </row>
-    <row r="38" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="38" spans="2:13">
       <c r="B38" s="30" t="s">
         <v>55</v>
       </c>
@@ -7601,7 +7590,7 @@
         <v/>
       </c>
     </row>
-    <row r="39" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="39" spans="2:13">
       <c r="B39" s="38" t="s">
         <v>51</v>
       </c>
@@ -7650,7 +7639,7 @@
         <v/>
       </c>
     </row>
-    <row r="40" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="40" spans="2:13">
       <c r="B40" s="66" t="s">
         <v>58</v>
       </c>
@@ -7699,7 +7688,7 @@
         <v/>
       </c>
     </row>
-    <row r="41" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="41" spans="2:13">
       <c r="B41" s="66" t="s">
         <v>61</v>
       </c>
@@ -7748,7 +7737,7 @@
         <v/>
       </c>
     </row>
-    <row r="42" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="42" spans="2:13">
       <c r="B42" s="38" t="s">
         <v>46</v>
       </c>
@@ -7797,7 +7786,7 @@
         <v/>
       </c>
     </row>
-    <row r="43" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="43" spans="2:13">
       <c r="B43" s="41" t="s">
         <v>127</v>
       </c>
@@ -7846,7 +7835,7 @@
         <v/>
       </c>
     </row>
-    <row r="44" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="44" spans="2:13">
       <c r="B44" s="41" t="s">
         <v>139</v>
       </c>
@@ -7895,7 +7884,7 @@
         <v/>
       </c>
     </row>
-    <row r="45" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="45" spans="2:13">
       <c r="B45" s="38" t="s">
         <v>65</v>
       </c>
@@ -7944,7 +7933,7 @@
         <v/>
       </c>
     </row>
-    <row r="46" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="46" spans="2:13">
       <c r="B46" s="38" t="s">
         <v>47</v>
       </c>
@@ -7993,7 +7982,7 @@
         <v/>
       </c>
     </row>
-    <row r="47" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="47" spans="2:13">
       <c r="B47" s="41" t="s">
         <v>39</v>
       </c>
@@ -8042,7 +8031,7 @@
         <v/>
       </c>
     </row>
-    <row r="48" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="48" spans="2:13">
       <c r="B48" s="27" t="s">
         <v>41</v>
       </c>
@@ -8091,12 +8080,12 @@
         <v/>
       </c>
     </row>
-    <row r="50" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="50" spans="2:13">
       <c r="B50" s="16" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="51" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="51" spans="2:13">
       <c r="B51" s="38" t="s">
         <v>37</v>
       </c>
@@ -8145,7 +8134,7 @@
         <v/>
       </c>
     </row>
-    <row r="52" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="52" spans="2:13">
       <c r="B52" s="38" t="s">
         <v>64</v>
       </c>
@@ -8194,12 +8183,12 @@
         <v/>
       </c>
     </row>
-    <row r="54" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="54" spans="2:13">
       <c r="B54" s="156" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="55" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="55" spans="2:13">
       <c r="B55" s="38" t="s">
         <v>134</v>
       </c>
@@ -8248,7 +8237,7 @@
         <v/>
       </c>
     </row>
-    <row r="56" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="56" spans="2:13">
       <c r="B56" s="38" t="s">
         <v>138</v>
       </c>
@@ -8297,7 +8286,7 @@
         <v/>
       </c>
     </row>
-    <row r="57" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="57" spans="2:13">
       <c r="B57" s="38" t="s">
         <v>133</v>
       </c>
@@ -8346,7 +8335,7 @@
         <v/>
       </c>
     </row>
-    <row r="58" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="58" spans="2:13">
       <c r="B58" s="38" t="s">
         <v>135</v>
       </c>
@@ -8395,13 +8384,13 @@
         <v/>
       </c>
     </row>
-    <row r="60" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="60" spans="2:13">
       <c r="B60" s="16" t="s">
         <v>48</v>
       </c>
       <c r="C60" s="9"/>
     </row>
-    <row r="61" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="61" spans="2:13">
       <c r="B61" s="26" t="s">
         <v>44</v>
       </c>
@@ -8450,7 +8439,7 @@
         <v/>
       </c>
     </row>
-    <row r="62" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="62" spans="2:13">
       <c r="B62" s="26" t="s">
         <v>50</v>
       </c>
@@ -8499,7 +8488,7 @@
         <v/>
       </c>
     </row>
-    <row r="63" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="63" spans="2:13">
       <c r="B63" s="26" t="s">
         <v>49</v>
       </c>
@@ -8548,7 +8537,7 @@
         <v/>
       </c>
     </row>
-    <row r="64" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="64" spans="2:13">
       <c r="B64" s="26" t="s">
         <v>305</v>
       </c>
@@ -8597,7 +8586,7 @@
         <v/>
       </c>
     </row>
-    <row r="65" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="65" spans="2:13">
       <c r="B65" s="23" t="s">
         <v>34</v>
       </c>
@@ -8646,12 +8635,12 @@
         <v/>
       </c>
     </row>
-    <row r="67" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="67" spans="2:13">
       <c r="B67" s="88" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="68" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="68" spans="2:13">
       <c r="B68" s="1" t="str">
         <f>B36</f>
         <v>Sales</v>
@@ -8701,7 +8690,7 @@
         <v/>
       </c>
     </row>
-    <row r="69" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="69" spans="2:13">
       <c r="B69" s="30" t="s">
         <v>55</v>
       </c>
@@ -8750,7 +8739,7 @@
         <v/>
       </c>
     </row>
-    <row r="70" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="70" spans="2:13">
       <c r="B70" s="77" t="str">
         <f>B43</f>
         <v>Operating EBIT</v>
@@ -8800,7 +8789,7 @@
         <v/>
       </c>
     </row>
-    <row r="71" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="71" spans="2:13">
       <c r="B71" s="41" t="s">
         <v>139</v>
       </c>
@@ -8849,7 +8838,7 @@
         <v/>
       </c>
     </row>
-    <row r="72" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="72" spans="2:13">
       <c r="B72" s="77" t="str">
         <f>B47</f>
         <v>Reported Net Income</v>
@@ -8899,7 +8888,7 @@
         <v/>
       </c>
     </row>
-    <row r="74" spans="2:13" ht="16" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:13" ht="13.9">
       <c r="B74" s="34" t="s">
         <v>79</v>
       </c>
@@ -8915,13 +8904,13 @@
       <c r="L74" s="35"/>
       <c r="M74" s="35"/>
     </row>
-    <row r="75" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="75" spans="2:13">
       <c r="B75" s="16" t="s">
         <v>26</v>
       </c>
       <c r="C75" s="9"/>
     </row>
-    <row r="76" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="76" spans="2:13">
       <c r="B76" s="25" t="s">
         <v>1</v>
       </c>
@@ -8970,7 +8959,7 @@
         <v/>
       </c>
     </row>
-    <row r="77" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="77" spans="2:13">
       <c r="B77" s="90" t="s">
         <v>82</v>
       </c>
@@ -9004,7 +8993,7 @@
       <c r="L77" s="291"/>
       <c r="M77" s="291"/>
     </row>
-    <row r="78" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="78" spans="2:13">
       <c r="B78" s="90" t="s">
         <v>83</v>
       </c>
@@ -9038,7 +9027,7 @@
       <c r="L78" s="291"/>
       <c r="M78" s="291"/>
     </row>
-    <row r="79" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="79" spans="2:13">
       <c r="B79" s="25" t="s">
         <v>38</v>
       </c>
@@ -9087,7 +9076,7 @@
         <v/>
       </c>
     </row>
-    <row r="80" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="80" spans="2:13">
       <c r="B80" s="25" t="s">
         <v>28</v>
       </c>
@@ -9168,7 +9157,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:H89"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="2.33203125" style="1" customWidth="1"/>
     <col min="2" max="2" width="34" style="1" bestFit="1" customWidth="1"/>
@@ -9179,7 +9168,7 @@
     <col min="9" max="16384" width="12.33203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="2:8" ht="15" customHeight="1">
       <c r="B1" s="17" t="s">
         <v>35</v>
       </c>
@@ -9195,7 +9184,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="2" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="2:8" ht="15" customHeight="1">
       <c r="B2" s="76" t="s">
         <v>131</v>
       </c>
@@ -9206,7 +9195,7 @@
       <c r="G2" s="35"/>
       <c r="H2" s="35"/>
     </row>
-    <row r="3" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="2:8" ht="15" customHeight="1">
       <c r="B3" s="16" t="s">
         <v>154</v>
       </c>
@@ -9226,7 +9215,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="4" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="2:8" ht="15" customHeight="1">
       <c r="B4" s="4" t="s">
         <v>22</v>
       </c>
@@ -9248,7 +9237,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="5" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="2:8" ht="15" customHeight="1">
       <c r="B5" s="1" t="s">
         <v>31</v>
       </c>
@@ -9269,7 +9258,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="6" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="2:8" ht="15" customHeight="1">
       <c r="B6" s="4" t="s">
         <v>8</v>
       </c>
@@ -9290,7 +9279,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="7" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="2:8" ht="15" customHeight="1">
       <c r="B7" s="1" t="s">
         <v>66</v>
       </c>
@@ -9311,7 +9300,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="8" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="8" spans="2:8" ht="15" customHeight="1">
       <c r="B8" s="1" t="s">
         <v>144</v>
       </c>
@@ -9332,7 +9321,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="9" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" spans="2:8" ht="15" customHeight="1">
       <c r="B9" s="4" t="s">
         <v>23</v>
       </c>
@@ -9353,7 +9342,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="10" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="2:8" ht="15" customHeight="1">
       <c r="B10" s="4" t="s">
         <v>9</v>
       </c>
@@ -9373,7 +9362,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="11" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="2:8" ht="15" customHeight="1">
       <c r="B11" s="4" t="s">
         <v>10</v>
       </c>
@@ -9385,7 +9374,7 @@
       </c>
       <c r="H11" s="232"/>
     </row>
-    <row r="12" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="2:8" ht="15" customHeight="1">
       <c r="B12" s="77" t="s">
         <v>69</v>
       </c>
@@ -9409,12 +9398,12 @@
         <v>567828</v>
       </c>
     </row>
-    <row r="13" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="2:8" ht="15" customHeight="1">
       <c r="F13" s="77"/>
       <c r="G13" s="78"/>
       <c r="H13" s="19"/>
     </row>
-    <row r="14" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="14" spans="2:8" ht="15" customHeight="1">
       <c r="B14" s="16" t="s">
         <v>153</v>
       </c>
@@ -9434,7 +9423,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="15" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="15" spans="2:8" ht="15" customHeight="1">
       <c r="B15" s="4" t="s">
         <v>329</v>
       </c>
@@ -9454,7 +9443,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="16" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="16" spans="2:8" ht="15" customHeight="1">
       <c r="B16" s="1" t="s">
         <v>32</v>
       </c>
@@ -9474,7 +9463,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="17" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="2:8" ht="15" customHeight="1">
       <c r="B17" s="1" t="s">
         <v>66</v>
       </c>
@@ -9494,7 +9483,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="18" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:8" ht="15" customHeight="1">
       <c r="B18" s="4" t="s">
         <v>144</v>
       </c>
@@ -9514,7 +9503,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="19" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:8" ht="15" customHeight="1">
       <c r="B19" s="4" t="s">
         <v>24</v>
       </c>
@@ -9535,7 +9524,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="20" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="20" spans="2:8" ht="15" customHeight="1">
       <c r="B20" s="4" t="s">
         <v>16</v>
       </c>
@@ -9555,7 +9544,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="21" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:8" ht="15" customHeight="1">
       <c r="B21" s="4" t="s">
         <v>17</v>
       </c>
@@ -9575,7 +9564,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="22" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:8" ht="15" customHeight="1">
       <c r="B22" s="4" t="s">
         <v>18</v>
       </c>
@@ -9587,7 +9576,7 @@
       </c>
       <c r="H22" s="232"/>
     </row>
-    <row r="23" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="23" spans="2:8" ht="15" customHeight="1">
       <c r="B23" s="4" t="s">
         <v>19</v>
       </c>
@@ -9599,7 +9588,7 @@
       </c>
       <c r="H23" s="232"/>
     </row>
-    <row r="24" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:8" ht="15" customHeight="1">
       <c r="B24" s="77" t="s">
         <v>70</v>
       </c>
@@ -9623,7 +9612,7 @@
         <v>6982.2</v>
       </c>
     </row>
-    <row r="26" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="26" spans="2:8" ht="15" customHeight="1">
       <c r="B26" s="16" t="s">
         <v>169</v>
       </c>
@@ -9640,7 +9629,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="27" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="27" spans="2:8" ht="15" customHeight="1">
       <c r="B27" s="4" t="s">
         <v>3</v>
       </c>
@@ -9659,7 +9648,7 @@
         <v>-1727228.2000000002</v>
       </c>
     </row>
-    <row r="28" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:8" ht="15" customHeight="1">
       <c r="B28" s="4" t="s">
         <v>4</v>
       </c>
@@ -9674,7 +9663,7 @@
       </c>
       <c r="H28" s="170"/>
     </row>
-    <row r="29" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="29" spans="2:8" ht="15" customHeight="1">
       <c r="B29" s="4" t="s">
         <v>5</v>
       </c>
@@ -9693,7 +9682,7 @@
         <v>-1746881.2000000002</v>
       </c>
     </row>
-    <row r="30" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="30" spans="2:8" ht="15" customHeight="1">
       <c r="B30" s="2" t="s">
         <v>6</v>
       </c>
@@ -9709,7 +9698,7 @@
       </c>
       <c r="H30" s="170"/>
     </row>
-    <row r="31" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:8" ht="15" customHeight="1">
       <c r="B31" s="77" t="s">
         <v>172</v>
       </c>
@@ -9726,7 +9715,7 @@
       </c>
       <c r="H31" s="170"/>
     </row>
-    <row r="32" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="32" spans="2:8" ht="15" customHeight="1">
       <c r="B32" s="4" t="s">
         <v>7</v>
       </c>
@@ -9746,7 +9735,7 @@
         <v>2350458.7999999998</v>
       </c>
     </row>
-    <row r="33" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="33" spans="2:8" ht="15" customHeight="1">
       <c r="B33" s="80" t="s">
         <v>2</v>
       </c>
@@ -9757,7 +9746,7 @@
       <c r="G33" s="2"/>
       <c r="H33" s="177"/>
     </row>
-    <row r="34" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="34" spans="2:8" ht="15" customHeight="1">
       <c r="B34" s="80"/>
       <c r="C34" s="81"/>
       <c r="F34" s="178" t="s">
@@ -9770,7 +9759,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="35" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="35" spans="2:8" ht="15" customHeight="1">
       <c r="B35" s="16" t="s">
         <v>170</v>
       </c>
@@ -9789,7 +9778,7 @@
         <v>1775648.5999999999</v>
       </c>
     </row>
-    <row r="36" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="36" spans="2:8" ht="15" customHeight="1">
       <c r="B36" s="4" t="s">
         <v>11</v>
       </c>
@@ -9805,7 +9794,7 @@
       </c>
       <c r="H36" s="177"/>
     </row>
-    <row r="37" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="37" spans="2:8" ht="15" customHeight="1">
       <c r="B37" s="4" t="s">
         <v>12</v>
       </c>
@@ -9821,7 +9810,7 @@
       </c>
       <c r="H37" s="177"/>
     </row>
-    <row r="38" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="38" spans="2:8" ht="15" customHeight="1">
       <c r="B38" s="4" t="s">
         <v>13</v>
       </c>
@@ -9837,7 +9826,7 @@
       </c>
       <c r="H38" s="177"/>
     </row>
-    <row r="39" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="39" spans="2:8" ht="15" customHeight="1">
       <c r="B39" s="2" t="s">
         <v>14</v>
       </c>
@@ -9856,7 +9845,7 @@
         <v>468045.5</v>
       </c>
     </row>
-    <row r="40" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="40" spans="2:8" ht="15" customHeight="1">
       <c r="B40" s="77" t="s">
         <v>173</v>
       </c>
@@ -9876,7 +9865,7 @@
         <v>574810.19999999995</v>
       </c>
     </row>
-    <row r="41" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="41" spans="2:8" ht="15" customHeight="1">
       <c r="B41" s="4" t="s">
         <v>15</v>
       </c>
@@ -9896,7 +9885,7 @@
         <v>538192.79999999993</v>
       </c>
     </row>
-    <row r="42" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="42" spans="2:8" ht="15" customHeight="1">
       <c r="B42" s="80" t="s">
         <v>20</v>
       </c>
@@ -9915,7 +9904,7 @@
         <v>36617.399999999994</v>
       </c>
     </row>
-    <row r="44" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="44" spans="2:8" ht="15" customHeight="1">
       <c r="B44" s="76" t="s">
         <v>92</v>
       </c>
@@ -9926,7 +9915,7 @@
       <c r="G44" s="35"/>
       <c r="H44" s="35"/>
     </row>
-    <row r="45" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="45" spans="2:8" ht="15" customHeight="1">
       <c r="B45" s="16" t="s">
         <v>228</v>
       </c>
@@ -9940,7 +9929,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="46" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="46" spans="2:8" ht="15" customHeight="1">
       <c r="B46" s="1" t="s">
         <v>230</v>
       </c>
@@ -9954,25 +9943,25 @@
       </c>
       <c r="F46" s="223"/>
     </row>
-    <row r="47" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="47" spans="2:8" ht="15" customHeight="1">
       <c r="B47" s="1" t="str">
         <f>"Equity per share ("&amp;Market_currency&amp;")"</f>
         <v>Equity per share (HKD)</v>
       </c>
       <c r="C47" s="134">
         <f>C46*H1/Common_Shares*Exchange_Rate</f>
-        <v>15.207507865580999</v>
+        <v>15.263432508611348</v>
       </c>
       <c r="D47" s="134">
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
-        <v>-6.2879234830533743</v>
+        <v>-6.3110469217719434</v>
       </c>
       <c r="F47" s="223"/>
     </row>
-    <row r="48" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="48" spans="2:8" ht="15" customHeight="1">
       <c r="F48" s="223"/>
     </row>
-    <row r="49" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="49" spans="2:8" ht="15" customHeight="1">
       <c r="B49" s="143" t="s">
         <v>120</v>
       </c>
@@ -9985,7 +9974,7 @@
       <c r="E49" s="2"/>
       <c r="F49" s="223"/>
     </row>
-    <row r="50" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="50" spans="2:8" ht="15" customHeight="1">
       <c r="B50" s="8" t="s">
         <v>90</v>
       </c>
@@ -9999,7 +9988,7 @@
       </c>
       <c r="F50" s="223"/>
     </row>
-    <row r="51" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="51" spans="2:8" ht="15" customHeight="1">
       <c r="B51" s="1" t="s">
         <v>146</v>
       </c>
@@ -10010,10 +9999,10 @@
       </c>
       <c r="F51" s="223"/>
     </row>
-    <row r="52" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="52" spans="2:8" ht="15" customHeight="1">
       <c r="F52" s="223"/>
     </row>
-    <row r="53" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="53" spans="2:8" ht="15" customHeight="1">
       <c r="B53" s="143" t="s">
         <v>119</v>
       </c>
@@ -10025,7 +10014,7 @@
       </c>
       <c r="F53" s="223"/>
     </row>
-    <row r="54" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="54" spans="2:8" ht="15" customHeight="1">
       <c r="B54" s="1" t="s">
         <v>116</v>
       </c>
@@ -10039,7 +10028,7 @@
       </c>
       <c r="F54" s="223"/>
     </row>
-    <row r="55" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="55" spans="2:8" ht="15" customHeight="1">
       <c r="B55" s="1" t="s">
         <v>118</v>
       </c>
@@ -10053,10 +10042,10 @@
       </c>
       <c r="F55" s="223"/>
     </row>
-    <row r="56" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="56" spans="2:8" ht="15" customHeight="1">
       <c r="F56" s="223"/>
     </row>
-    <row r="57" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="57" spans="2:8" ht="15" customHeight="1">
       <c r="B57" s="143" t="s">
         <v>145</v>
       </c>
@@ -10068,7 +10057,7 @@
       </c>
       <c r="F57" s="223"/>
     </row>
-    <row r="58" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="58" spans="2:8" ht="15" customHeight="1">
       <c r="B58" s="2" t="s">
         <v>86</v>
       </c>
@@ -10079,7 +10068,7 @@
       </c>
       <c r="F58" s="5"/>
     </row>
-    <row r="59" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="59" spans="2:8" ht="15" customHeight="1">
       <c r="B59" s="1" t="s">
         <v>89</v>
       </c>
@@ -10090,10 +10079,10 @@
       </c>
       <c r="F59" s="223"/>
     </row>
-    <row r="60" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="60" spans="2:8" ht="15" customHeight="1">
       <c r="F60" s="223"/>
     </row>
-    <row r="61" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="61" spans="2:8" ht="15" customHeight="1">
       <c r="B61" s="143" t="s">
         <v>231</v>
       </c>
@@ -10105,7 +10094,7 @@
       </c>
       <c r="F61" s="223"/>
     </row>
-    <row r="62" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="62" spans="2:8" ht="15" customHeight="1">
       <c r="B62" s="1" t="s">
         <v>210</v>
       </c>
@@ -10121,7 +10110,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="64" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="64" spans="2:8" ht="15" customHeight="1">
       <c r="B64" s="76" t="s">
         <v>162</v>
       </c>
@@ -10132,7 +10121,7 @@
       <c r="G64" s="35"/>
       <c r="H64" s="35"/>
     </row>
-    <row r="65" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="65" spans="2:6" ht="15" customHeight="1">
       <c r="B65" s="16" t="s">
         <v>158</v>
       </c>
@@ -10146,7 +10135,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="66" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="66" spans="2:6" ht="15" customHeight="1">
       <c r="B66" s="102" t="s">
         <v>157</v>
       </c>
@@ -10162,7 +10151,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="67" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="67" spans="2:6" ht="15" customHeight="1">
       <c r="B67" s="102" t="s">
         <v>147</v>
       </c>
@@ -10172,7 +10161,7 @@
       </c>
       <c r="F67" s="223"/>
     </row>
-    <row r="68" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="68" spans="2:6" ht="15" customHeight="1">
       <c r="B68" s="102" t="s">
         <v>151</v>
       </c>
@@ -10182,7 +10171,7 @@
       </c>
       <c r="F68" s="223"/>
     </row>
-    <row r="69" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="69" spans="2:6" ht="15" customHeight="1">
       <c r="B69" s="102" t="s">
         <v>149</v>
       </c>
@@ -10192,7 +10181,7 @@
       </c>
       <c r="F69" s="223"/>
     </row>
-    <row r="70" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="70" spans="2:6" ht="15" customHeight="1">
       <c r="B70" s="77" t="s">
         <v>158</v>
       </c>
@@ -10202,10 +10191,10 @@
       </c>
       <c r="F70" s="223"/>
     </row>
-    <row r="71" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="71" spans="2:6" ht="15" customHeight="1">
       <c r="F71" s="223"/>
     </row>
-    <row r="72" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="72" spans="2:6" ht="15" customHeight="1">
       <c r="B72" s="225" t="s">
         <v>256</v>
       </c>
@@ -10217,7 +10206,7 @@
       </c>
       <c r="F72" s="223"/>
     </row>
-    <row r="73" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="73" spans="2:6" ht="15" customHeight="1">
       <c r="B73" s="102" t="s">
         <v>255</v>
       </c>
@@ -10233,7 +10222,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="74" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="74" spans="2:6" ht="15" customHeight="1">
       <c r="B74" s="227" t="s">
         <v>259</v>
       </c>
@@ -10249,7 +10238,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="75" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="75" spans="2:6" ht="15" customHeight="1">
       <c r="B75" s="77" t="s">
         <v>258</v>
       </c>
@@ -10262,7 +10251,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="76" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="76" spans="2:6" ht="15" customHeight="1">
       <c r="B76" s="229" t="s">
         <v>260</v>
       </c>
@@ -10275,10 +10264,10 @@
         <v>261</v>
       </c>
     </row>
-    <row r="77" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="77" spans="2:6" ht="15" customHeight="1">
       <c r="F77" s="223"/>
     </row>
-    <row r="78" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="78" spans="2:6" ht="15" customHeight="1">
       <c r="B78" s="16" t="s">
         <v>159</v>
       </c>
@@ -10290,7 +10279,7 @@
       </c>
       <c r="F78" s="223"/>
     </row>
-    <row r="79" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="79" spans="2:6" ht="15" customHeight="1">
       <c r="B79" s="102" t="s">
         <v>148</v>
       </c>
@@ -10304,7 +10293,7 @@
       </c>
       <c r="F79" s="223"/>
     </row>
-    <row r="80" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="80" spans="2:6" ht="15" customHeight="1">
       <c r="B80" s="102" t="s">
         <v>152</v>
       </c>
@@ -10318,7 +10307,7 @@
       </c>
       <c r="F80" s="223"/>
     </row>
-    <row r="81" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="81" spans="2:8" ht="15" customHeight="1">
       <c r="B81" s="102" t="s">
         <v>150</v>
       </c>
@@ -10332,7 +10321,7 @@
       </c>
       <c r="F81" s="223"/>
     </row>
-    <row r="82" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="82" spans="2:8" ht="15" customHeight="1">
       <c r="B82" s="77" t="s">
         <v>159</v>
       </c>
@@ -10346,7 +10335,7 @@
       </c>
       <c r="F82" s="223"/>
     </row>
-    <row r="84" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="84" spans="2:8" ht="15" customHeight="1">
       <c r="B84" s="76" t="s">
         <v>241</v>
       </c>
@@ -10357,7 +10346,7 @@
       <c r="G84" s="35"/>
       <c r="H84" s="35"/>
     </row>
-    <row r="85" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="85" spans="2:8" ht="15" customHeight="1">
       <c r="B85" s="16" t="s">
         <v>242</v>
       </c>
@@ -10365,68 +10354,68 @@
         <v>243</v>
       </c>
     </row>
-    <row r="86" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="86" spans="2:8" ht="15" customHeight="1">
       <c r="B86" s="212" t="s">
         <v>239</v>
       </c>
       <c r="C86" s="73">
         <f>DCF!F4*Exchange_Rate</f>
-        <v>-26304010.34543059</v>
+        <v>-26400741.670631103</v>
       </c>
       <c r="D86" s="201">
         <f>C86*scaling_factor/Common_Shares</f>
-        <v>-10.279726290448499</v>
+        <v>-10.317529330126302</v>
       </c>
       <c r="E86" s="214" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="87" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="87" spans="2:8" ht="15" customHeight="1">
       <c r="B87" s="212" t="s">
         <v>240</v>
       </c>
       <c r="C87" s="73">
         <f>DCF!F5*Exchange_Rate</f>
-        <v>-478712.7804854408</v>
+        <v>-480473.21629118564</v>
       </c>
       <c r="D87" s="201">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>-0.1870831211859201</v>
+        <v>-0.18777110746623668</v>
       </c>
       <c r="E87" s="214" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="88" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="88" spans="2:8" ht="15" customHeight="1">
       <c r="B88" s="213" t="s">
         <v>159</v>
       </c>
       <c r="C88" s="73">
         <f>DCF!F6*Exchange_Rate</f>
-        <v>337265.40590075863</v>
+        <v>338505.67798203597</v>
       </c>
       <c r="D88" s="201">
         <f>C88*scaling_factor/Common_Shares</f>
-        <v>0.13180484703158898</v>
+        <v>0.13228955097421158</v>
       </c>
       <c r="E88" s="214" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="89" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="89" spans="2:8" ht="15" customHeight="1">
       <c r="B89" s="77" t="s">
         <v>244</v>
       </c>
       <c r="C89" s="162">
         <f>SUM(C86:C88)</f>
-        <v>-26445457.720015272</v>
+        <v>-26542709.208940253</v>
       </c>
       <c r="D89" s="216">
         <f>SUM(D86:D88)</f>
-        <v>-10.33500456460283</v>
+        <v>-10.373010886618326</v>
       </c>
       <c r="E89" s="214" t="str">
         <f>Market_currency</f>
@@ -10452,19 +10441,19 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:Q807"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="1.33203125" style="2" customWidth="1"/>
     <col min="2" max="2" width="26.33203125" style="2" customWidth="1"/>
     <col min="3" max="3" width="20.6640625" style="2" customWidth="1"/>
     <col min="4" max="4" width="2.6640625" style="2" customWidth="1"/>
-    <col min="5" max="5" width="25.1640625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="25.1328125" style="2" customWidth="1"/>
     <col min="6" max="6" width="2.6640625" style="2" customWidth="1"/>
     <col min="7" max="17" width="20.6640625" style="2" customWidth="1"/>
     <col min="18" max="16384" width="12.33203125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:17" ht="15.75" customHeight="1">
       <c r="A1" s="3"/>
       <c r="B1" s="87" t="str">
         <f>Thesis!E17</f>
@@ -10521,7 +10510,7 @@
         <v>42004</v>
       </c>
     </row>
-    <row r="2" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:17" ht="15.75" customHeight="1">
       <c r="A2" s="3"/>
       <c r="B2" s="51" t="s">
         <v>95</v>
@@ -10544,7 +10533,7 @@
       <c r="P2" s="35"/>
       <c r="Q2" s="35"/>
     </row>
-    <row r="3" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:17" ht="15.75" customHeight="1">
       <c r="A3" s="10"/>
       <c r="B3" s="16" t="s">
         <v>393</v>
@@ -10564,7 +10553,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="4" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:17" ht="15.75" customHeight="1">
       <c r="A4" s="10"/>
       <c r="B4" s="25" t="s">
         <v>0</v>
@@ -10621,7 +10610,7 @@
         <v/>
       </c>
     </row>
-    <row r="5" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:17" ht="15.75" customHeight="1">
       <c r="A5" s="10"/>
       <c r="B5" s="2" t="s">
         <v>43</v>
@@ -10676,7 +10665,7 @@
         <v/>
       </c>
     </row>
-    <row r="6" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:17" ht="15.75" customHeight="1">
       <c r="A6" s="10"/>
       <c r="B6" s="30" t="s">
         <v>45</v>
@@ -10731,7 +10720,7 @@
         <v/>
       </c>
     </row>
-    <row r="7" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:17" ht="15.75" customHeight="1">
       <c r="A7" s="10"/>
       <c r="B7" s="8" t="s">
         <v>42</v>
@@ -10786,7 +10775,7 @@
         <v/>
       </c>
     </row>
-    <row r="8" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:17" ht="15.75" customHeight="1">
       <c r="A8" s="10"/>
       <c r="B8" s="28" t="s">
         <v>127</v>
@@ -10843,7 +10832,7 @@
         <v/>
       </c>
     </row>
-    <row r="9" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:17" ht="15.75" customHeight="1">
       <c r="A9" s="10"/>
       <c r="B9" s="26" t="s">
         <v>415</v>
@@ -10900,7 +10889,7 @@
         <v/>
       </c>
     </row>
-    <row r="10" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:17" ht="15.75" customHeight="1">
       <c r="A10" s="10"/>
       <c r="B10" s="2" t="s">
         <v>65</v>
@@ -10955,7 +10944,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:17" ht="15.75" customHeight="1">
       <c r="A11" s="10"/>
       <c r="B11" s="67" t="s">
         <v>137</v>
@@ -11010,7 +10999,7 @@
         <v/>
       </c>
     </row>
-    <row r="12" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:17" ht="15.75" customHeight="1">
       <c r="A12" s="10"/>
       <c r="B12" s="2" t="s">
         <v>60</v>
@@ -11065,7 +11054,7 @@
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:17" ht="15.75" customHeight="1">
       <c r="A13" s="10"/>
       <c r="B13" s="38" t="s">
         <v>208</v>
@@ -11122,7 +11111,7 @@
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:17" ht="15.75" customHeight="1">
       <c r="A14" s="10"/>
       <c r="B14" s="39" t="s">
         <v>129</v>
@@ -11179,7 +11168,7 @@
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:17" ht="15.75" customHeight="1">
       <c r="A15" s="10"/>
       <c r="B15" s="2" t="s">
         <v>62</v>
@@ -11234,7 +11223,7 @@
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:17" ht="15.75" customHeight="1">
       <c r="A16" s="10"/>
       <c r="B16" s="2" t="s">
         <v>398</v>
@@ -11289,7 +11278,7 @@
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:17" ht="15.75" customHeight="1">
       <c r="A17" s="10"/>
       <c r="B17" s="26" t="s">
         <v>49</v>
@@ -11315,7 +11304,7 @@
       <c r="P17" s="272"/>
       <c r="Q17" s="272"/>
     </row>
-    <row r="18" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:17" ht="15.75" customHeight="1">
       <c r="A18" s="10"/>
       <c r="B18" s="26" t="s">
         <v>94</v>
@@ -11340,7 +11329,7 @@
       <c r="P18" s="273"/>
       <c r="Q18" s="273"/>
     </row>
-    <row r="19" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:17" ht="15.75" customHeight="1">
       <c r="A19" s="10"/>
       <c r="B19" s="30" t="s">
         <v>63</v>
@@ -11397,7 +11386,7 @@
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:17" ht="15.75" customHeight="1">
       <c r="A20" s="10"/>
       <c r="B20" s="26"/>
       <c r="C20" s="59"/>
@@ -11416,7 +11405,7 @@
       <c r="P20" s="12"/>
       <c r="Q20" s="12"/>
     </row>
-    <row r="21" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:17" ht="15.75" customHeight="1">
       <c r="A21" s="10"/>
       <c r="B21" s="51" t="s">
         <v>174</v>
@@ -11439,7 +11428,7 @@
       <c r="P21" s="35"/>
       <c r="Q21" s="35"/>
     </row>
-    <row r="22" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:17" ht="15.75" customHeight="1">
       <c r="A22" s="10"/>
       <c r="B22" s="61" t="s">
         <v>43</v>
@@ -11460,7 +11449,7 @@
       <c r="P22" s="12"/>
       <c r="Q22" s="12"/>
     </row>
-    <row r="23" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:17" ht="15.75" customHeight="1">
       <c r="A23" s="10"/>
       <c r="B23" s="26" t="s">
         <v>40</v>
@@ -11517,7 +11506,7 @@
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:17" ht="15.75" customHeight="1">
       <c r="A24" s="10"/>
       <c r="B24" s="65" t="s">
         <v>59</v>
@@ -11574,7 +11563,7 @@
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:17" ht="15.75" customHeight="1">
       <c r="A25" s="10"/>
       <c r="B25" s="26" t="s">
         <v>46</v>
@@ -11631,7 +11620,7 @@
         <v/>
       </c>
     </row>
-    <row r="26" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:17" ht="15.75" customHeight="1">
       <c r="A26" s="10"/>
       <c r="B26" s="67" t="s">
         <v>43</v>
@@ -11688,18 +11677,18 @@
         <v/>
       </c>
     </row>
-    <row r="27" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:17" ht="15.75" customHeight="1">
       <c r="A27" s="10"/>
       <c r="E27" s="237"/>
     </row>
-    <row r="28" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:17" ht="15.75" customHeight="1">
       <c r="A28" s="10"/>
       <c r="B28" s="61" t="s">
         <v>175</v>
       </c>
       <c r="E28" s="237"/>
     </row>
-    <row r="29" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="29" spans="1:17" ht="15.75" customHeight="1">
       <c r="A29" s="10"/>
       <c r="B29" s="25" t="s">
         <v>40</v>
@@ -11756,7 +11745,7 @@
         <v/>
       </c>
     </row>
-    <row r="30" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:17" ht="15.75" customHeight="1">
       <c r="A30" s="10"/>
       <c r="B30" s="65" t="str">
         <f>B24</f>
@@ -11814,7 +11803,7 @@
         <v/>
       </c>
     </row>
-    <row r="31" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:17" ht="15.75" customHeight="1">
       <c r="A31" s="10"/>
       <c r="B31" s="26" t="str">
         <f>B25</f>
@@ -11871,7 +11860,7 @@
         <v/>
       </c>
     </row>
-    <row r="32" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:17" ht="15.75" customHeight="1">
       <c r="A32" s="10"/>
       <c r="B32" s="67" t="s">
         <v>43</v>
@@ -11926,18 +11915,18 @@
         <v/>
       </c>
     </row>
-    <row r="33" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:17" ht="15.75" customHeight="1">
       <c r="A33" s="10"/>
       <c r="E33" s="237"/>
     </row>
-    <row r="34" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:17" ht="15.75" customHeight="1">
       <c r="A34" s="10"/>
       <c r="B34" s="61" t="s">
         <v>42</v>
       </c>
       <c r="E34" s="237"/>
     </row>
-    <row r="35" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:17" ht="15.75" customHeight="1">
       <c r="A35" s="10"/>
       <c r="B35" s="298" t="s">
         <v>396</v>
@@ -11994,18 +11983,18 @@
         <v/>
       </c>
     </row>
-    <row r="36" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:17" ht="15.75" customHeight="1">
       <c r="A36" s="10"/>
       <c r="E36" s="237"/>
     </row>
-    <row r="37" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:17" ht="15.75" customHeight="1">
       <c r="A37" s="10"/>
       <c r="B37" s="61" t="s">
         <v>176</v>
       </c>
       <c r="E37" s="237"/>
     </row>
-    <row r="38" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="38" spans="1:17" ht="15.75" customHeight="1">
       <c r="A38" s="10"/>
       <c r="B38" s="298" t="s">
         <v>396</v>
@@ -12060,18 +12049,18 @@
         <v/>
       </c>
     </row>
-    <row r="39" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:17" ht="15.75" customHeight="1">
       <c r="A39" s="10"/>
       <c r="E39" s="237"/>
     </row>
-    <row r="40" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="40" spans="1:17" ht="15.75" customHeight="1">
       <c r="A40" s="10"/>
       <c r="B40" s="61" t="s">
         <v>177</v>
       </c>
       <c r="E40" s="237"/>
     </row>
-    <row r="41" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="41" spans="1:17" ht="15.75" customHeight="1">
       <c r="A41" s="10"/>
       <c r="B41" s="26" t="s">
         <v>142</v>
@@ -12129,10 +12118,10 @@
         <v/>
       </c>
     </row>
-    <row r="42" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="42" spans="1:17" ht="15.75" customHeight="1">
       <c r="A42" s="10"/>
     </row>
-    <row r="43" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:17" ht="15.75" customHeight="1">
       <c r="A43" s="10"/>
       <c r="B43" s="51" t="s">
         <v>178</v>
@@ -12155,14 +12144,14 @@
       <c r="P43" s="35"/>
       <c r="Q43" s="35"/>
     </row>
-    <row r="44" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="44" spans="1:17" ht="15.75" customHeight="1">
       <c r="A44" s="10"/>
       <c r="B44" s="61" t="s">
         <v>57</v>
       </c>
       <c r="E44" s="237"/>
     </row>
-    <row r="45" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="45" spans="1:17" ht="15.75" customHeight="1">
       <c r="A45" s="10"/>
       <c r="B45" s="2" t="s">
         <v>37</v>
@@ -12217,7 +12206,7 @@
         <v/>
       </c>
     </row>
-    <row r="46" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="46" spans="1:17" ht="15.75" customHeight="1">
       <c r="A46" s="10"/>
       <c r="B46" s="2" t="s">
         <v>272</v>
@@ -12272,7 +12261,7 @@
         <v/>
       </c>
     </row>
-    <row r="47" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="47" spans="1:17" ht="15.75" customHeight="1">
       <c r="A47" s="10"/>
       <c r="B47" s="245" t="s">
         <v>269</v>
@@ -12329,7 +12318,7 @@
         <v/>
       </c>
     </row>
-    <row r="48" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="48" spans="1:17" ht="15.75" customHeight="1">
       <c r="A48" s="10"/>
       <c r="B48" s="67" t="s">
         <v>65</v>
@@ -12384,11 +12373,11 @@
         <v/>
       </c>
     </row>
-    <row r="49" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="49" spans="1:17" ht="15.75" customHeight="1">
       <c r="A49" s="10"/>
       <c r="E49" s="237"/>
     </row>
-    <row r="50" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="50" spans="1:17" ht="15.75" customHeight="1">
       <c r="A50" s="10"/>
       <c r="B50" s="69" t="s">
         <v>130</v>
@@ -12398,7 +12387,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="51" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="51" spans="1:17" ht="15.75" customHeight="1">
       <c r="A51" s="10"/>
       <c r="B51" s="8" t="s">
         <v>85</v>
@@ -12422,7 +12411,7 @@
       <c r="P51" s="151"/>
       <c r="Q51" s="151"/>
     </row>
-    <row r="52" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="52" spans="1:17" ht="15.75" customHeight="1">
       <c r="A52" s="10"/>
       <c r="B52" s="8" t="s">
         <v>84</v>
@@ -12446,7 +12435,7 @@
       <c r="P52" s="151"/>
       <c r="Q52" s="151"/>
     </row>
-    <row r="53" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="53" spans="1:17" ht="15.75" customHeight="1">
       <c r="A53" s="10"/>
       <c r="B53" s="25" t="s">
         <v>87</v>
@@ -12501,11 +12490,11 @@
         <v/>
       </c>
     </row>
-    <row r="54" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="54" spans="1:17" ht="15.75" customHeight="1">
       <c r="A54" s="10"/>
       <c r="E54" s="237"/>
     </row>
-    <row r="55" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="55" spans="1:17" ht="15.75" customHeight="1">
       <c r="A55" s="10"/>
       <c r="B55" s="61" t="s">
         <v>139</v>
@@ -12515,7 +12504,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="56" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="56" spans="1:17" ht="15.75" customHeight="1">
       <c r="A56" s="10"/>
       <c r="B56" s="38" t="s">
         <v>138</v>
@@ -12570,7 +12559,7 @@
         <v/>
       </c>
     </row>
-    <row r="57" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="57" spans="1:17" ht="15.75" customHeight="1">
       <c r="A57" s="10"/>
       <c r="B57" s="38" t="s">
         <v>134</v>
@@ -12625,7 +12614,7 @@
         <v/>
       </c>
     </row>
-    <row r="58" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="58" spans="1:17" ht="15.75" customHeight="1">
       <c r="A58" s="10"/>
       <c r="B58" s="38" t="s">
         <v>133</v>
@@ -12680,7 +12669,7 @@
         <v/>
       </c>
     </row>
-    <row r="59" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="59" spans="1:17" ht="15.75" customHeight="1">
       <c r="A59" s="10"/>
       <c r="B59" s="30" t="s">
         <v>163</v>
@@ -12735,7 +12724,7 @@
         <v/>
       </c>
     </row>
-    <row r="60" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="60" spans="1:17" ht="15.75" customHeight="1">
       <c r="A60" s="10"/>
       <c r="B60" s="38" t="s">
         <v>135</v>
@@ -12791,7 +12780,7 @@
         <v/>
       </c>
     </row>
-    <row r="61" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="61" spans="1:17" ht="15.75" customHeight="1">
       <c r="A61" s="10"/>
       <c r="B61" s="30" t="s">
         <v>164</v>
@@ -12846,11 +12835,11 @@
         <v/>
       </c>
     </row>
-    <row r="62" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="62" spans="1:17" ht="15.75" customHeight="1">
       <c r="A62" s="10"/>
       <c r="E62" s="237"/>
     </row>
-    <row r="63" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="63" spans="1:17" ht="15.75" customHeight="1">
       <c r="A63" s="10"/>
       <c r="B63" s="93" t="s">
         <v>140</v>
@@ -12860,7 +12849,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="64" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="64" spans="1:17" ht="15.75" customHeight="1">
       <c r="A64" s="10"/>
       <c r="B64" s="38" t="s">
         <v>138</v>
@@ -12885,7 +12874,7 @@
       <c r="P64" s="157"/>
       <c r="Q64" s="157"/>
     </row>
-    <row r="65" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="65" spans="1:17" ht="15.75" customHeight="1">
       <c r="A65" s="10"/>
       <c r="B65" s="102" t="s">
         <v>132</v>
@@ -12910,7 +12899,7 @@
       <c r="P65" s="157"/>
       <c r="Q65" s="157"/>
     </row>
-    <row r="66" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="66" spans="1:17" ht="15.75" customHeight="1">
       <c r="A66" s="10"/>
       <c r="B66" s="102" t="s">
         <v>133</v>
@@ -12935,7 +12924,7 @@
       <c r="P66" s="157"/>
       <c r="Q66" s="157"/>
     </row>
-    <row r="67" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="67" spans="1:17" ht="15.75" customHeight="1">
       <c r="A67" s="10"/>
       <c r="B67" s="30" t="s">
         <v>163</v>
@@ -12962,10 +12951,10 @@
       <c r="P67" s="157"/>
       <c r="Q67" s="157"/>
     </row>
-    <row r="68" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="68" spans="1:17" ht="15.75" customHeight="1">
       <c r="A68" s="10"/>
     </row>
-    <row r="69" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:17" ht="15.75" customHeight="1">
       <c r="A69" s="10"/>
       <c r="B69" s="51" t="s">
         <v>181</v>
@@ -12988,7 +12977,7 @@
       <c r="P69" s="35"/>
       <c r="Q69" s="35"/>
     </row>
-    <row r="70" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:17" ht="15.75" customHeight="1">
       <c r="A70" s="10"/>
       <c r="B70" s="69" t="s">
         <v>185</v>
@@ -13009,7 +12998,7 @@
       <c r="P70" s="12"/>
       <c r="Q70" s="12"/>
     </row>
-    <row r="71" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="71" spans="1:17" ht="15.75" customHeight="1">
       <c r="A71" s="10"/>
       <c r="B71" s="2" t="s">
         <v>43</v>
@@ -13066,7 +13055,7 @@
         <v/>
       </c>
     </row>
-    <row r="72" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="72" spans="1:17" ht="15.75" customHeight="1">
       <c r="A72" s="10"/>
       <c r="B72" s="30" t="s">
         <v>45</v>
@@ -13123,7 +13112,7 @@
         <v/>
       </c>
     </row>
-    <row r="73" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="73" spans="1:17" ht="15.75" customHeight="1">
       <c r="A73" s="10"/>
       <c r="B73" s="8" t="s">
         <v>42</v>
@@ -13180,7 +13169,7 @@
         <v/>
       </c>
     </row>
-    <row r="74" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:17" ht="15.75" customHeight="1">
       <c r="A74" s="10"/>
       <c r="B74" s="28" t="s">
         <v>127</v>
@@ -13237,7 +13226,7 @@
         <v/>
       </c>
     </row>
-    <row r="75" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:17" ht="15.75" customHeight="1">
       <c r="A75" s="10"/>
       <c r="B75" s="26" t="s">
         <v>128</v>
@@ -13294,7 +13283,7 @@
         <v/>
       </c>
     </row>
-    <row r="76" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:17" ht="15.75" customHeight="1">
       <c r="A76" s="10"/>
       <c r="B76" s="2" t="s">
         <v>65</v>
@@ -13351,7 +13340,7 @@
         <v/>
       </c>
     </row>
-    <row r="77" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="77" spans="1:17" ht="15.75" customHeight="1">
       <c r="A77" s="10"/>
       <c r="B77" s="67" t="s">
         <v>137</v>
@@ -13408,7 +13397,7 @@
         <v/>
       </c>
     </row>
-    <row r="78" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="78" spans="1:17" ht="15.75" customHeight="1">
       <c r="A78" s="10"/>
       <c r="B78" s="2" t="s">
         <v>60</v>
@@ -13465,7 +13454,7 @@
         <v/>
       </c>
     </row>
-    <row r="79" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="79" spans="1:17" ht="15.75" customHeight="1">
       <c r="A79" s="10"/>
       <c r="B79" s="38" t="str">
         <f>B13</f>
@@ -13523,7 +13512,7 @@
         <v/>
       </c>
     </row>
-    <row r="80" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="80" spans="1:17" ht="15.75" customHeight="1">
       <c r="A80" s="10"/>
       <c r="B80" s="39" t="s">
         <v>129</v>
@@ -13580,7 +13569,7 @@
         <v/>
       </c>
     </row>
-    <row r="81" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="81" spans="1:17" ht="15.75" customHeight="1">
       <c r="A81" s="10"/>
       <c r="B81" s="2" t="s">
         <v>62</v>
@@ -13637,7 +13626,7 @@
         <v/>
       </c>
     </row>
-    <row r="82" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="82" spans="1:17" ht="15.75" customHeight="1">
       <c r="A82" s="10"/>
       <c r="B82" s="2" t="s">
         <v>77</v>
@@ -13696,7 +13685,7 @@
         <v/>
       </c>
     </row>
-    <row r="83" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="83" spans="1:17" ht="15.75" customHeight="1">
       <c r="A83" s="10"/>
       <c r="B83" s="26" t="s">
         <v>49</v>
@@ -13722,7 +13711,7 @@
       <c r="P83" s="203"/>
       <c r="Q83" s="203"/>
     </row>
-    <row r="84" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="84" spans="1:17" ht="15.75" customHeight="1">
       <c r="A84" s="10"/>
       <c r="B84" s="8" t="s">
         <v>94</v>
@@ -13746,7 +13735,7 @@
       <c r="P84" s="151"/>
       <c r="Q84" s="151"/>
     </row>
-    <row r="85" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="85" spans="1:17" ht="15.75" customHeight="1">
       <c r="A85" s="10"/>
       <c r="B85" s="30" t="s">
         <v>117</v>
@@ -13803,18 +13792,18 @@
         <v/>
       </c>
     </row>
-    <row r="86" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="86" spans="1:17" ht="15.75" customHeight="1">
       <c r="A86" s="10"/>
       <c r="E86" s="237"/>
     </row>
-    <row r="87" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="87" spans="1:17" ht="15.75" customHeight="1">
       <c r="A87" s="10"/>
       <c r="B87" s="61" t="s">
         <v>183</v>
       </c>
       <c r="E87" s="237"/>
     </row>
-    <row r="88" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="88" spans="1:17" ht="15.75" customHeight="1">
       <c r="A88" s="10"/>
       <c r="B88" s="2" t="str">
         <f>"Dividend per share ("&amp;Market_currency&amp;")"</f>
@@ -13870,7 +13859,7 @@
         <v/>
       </c>
     </row>
-    <row r="89" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="89" spans="1:17" ht="15.75" customHeight="1">
       <c r="A89" s="10"/>
       <c r="B89" s="2" t="str">
         <f>"Dividend ("&amp;Market_currency&amp;")"</f>
@@ -13926,7 +13915,7 @@
         <v/>
       </c>
     </row>
-    <row r="90" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="90" spans="1:17" ht="15.75" customHeight="1">
       <c r="A90" s="10"/>
       <c r="B90" s="2" t="s">
         <v>182</v>
@@ -13981,7 +13970,7 @@
         <v/>
       </c>
     </row>
-    <row r="91" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="91" spans="1:17" ht="15.75" customHeight="1">
       <c r="A91" s="10"/>
       <c r="B91" s="2" t="s">
         <v>331</v>
@@ -14002,23 +13991,23 @@
       <c r="P91" s="293"/>
       <c r="Q91" s="293"/>
     </row>
-    <row r="92" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="92" spans="1:17" ht="15.75" customHeight="1">
       <c r="A92" s="10"/>
       <c r="B92" s="2" t="s">
         <v>330</v>
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>3.392895734597156E-2</v>
+        <v>3.2175325842696632E-2</v>
       </c>
       <c r="E92" s="237"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>3.392895734597156E-2</v>
+        <v>3.2175325842696632E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>2.686920616113744E-2</v>
+        <v>2.5480460674157306E-2</v>
       </c>
       <c r="I92" s="22" t="str">
         <f t="shared" si="38"/>
@@ -14057,11 +14046,11 @@
         <v/>
       </c>
     </row>
-    <row r="93" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="93" spans="1:17" ht="15.75" customHeight="1">
       <c r="A93" s="10"/>
       <c r="E93" s="237"/>
     </row>
-    <row r="94" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="94" spans="1:17" ht="15.75" customHeight="1">
       <c r="A94" s="10"/>
       <c r="B94" s="143" t="s">
         <v>81</v>
@@ -14082,7 +14071,7 @@
       <c r="P94" s="12"/>
       <c r="Q94" s="12"/>
     </row>
-    <row r="95" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="95" spans="1:17" ht="15.75" customHeight="1">
       <c r="A95" s="10"/>
       <c r="B95" s="26" t="s">
         <v>121</v>
@@ -14139,7 +14128,7 @@
         <v/>
       </c>
     </row>
-    <row r="96" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="96" spans="1:17" ht="15.75" customHeight="1">
       <c r="A96" s="10"/>
       <c r="B96" s="67" t="s">
         <v>137</v>
@@ -14196,10 +14185,10 @@
         <v/>
       </c>
     </row>
-    <row r="97" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="97" spans="1:17" ht="15.75" customHeight="1">
       <c r="A97" s="10"/>
     </row>
-    <row r="98" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:17" ht="15.75" customHeight="1">
       <c r="A98" s="3"/>
       <c r="B98" s="51" t="s">
         <v>184</v>
@@ -14222,7 +14211,7 @@
       <c r="P98" s="35"/>
       <c r="Q98" s="35"/>
     </row>
-    <row r="99" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="99" spans="1:17" ht="15.75" customHeight="1">
       <c r="A99" s="10"/>
       <c r="B99" s="61" t="s">
         <v>26</v>
@@ -14232,7 +14221,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="100" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="100" spans="1:17" ht="15.75" customHeight="1">
       <c r="A100" s="10"/>
       <c r="B100" s="25" t="s">
         <v>1</v>
@@ -14289,7 +14278,7 @@
         <v/>
       </c>
     </row>
-    <row r="101" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="101" spans="1:17" ht="15.75" customHeight="1">
       <c r="A101" s="10"/>
       <c r="B101" s="90" t="s">
         <v>179</v>
@@ -14346,7 +14335,7 @@
         <v/>
       </c>
     </row>
-    <row r="102" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="102" spans="1:17" ht="15.75" customHeight="1">
       <c r="A102" s="10"/>
       <c r="B102" s="90" t="s">
         <v>180</v>
@@ -14403,7 +14392,7 @@
         <v/>
       </c>
     </row>
-    <row r="103" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="103" spans="1:17" ht="15.75" customHeight="1">
       <c r="A103" s="10"/>
       <c r="B103" s="25" t="s">
         <v>38</v>
@@ -14460,7 +14449,7 @@
         <v/>
       </c>
     </row>
-    <row r="104" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="104" spans="1:17" ht="15.75" customHeight="1">
       <c r="A104" s="10"/>
       <c r="B104" s="25" t="s">
         <v>28</v>
@@ -14517,11 +14506,11 @@
         <v/>
       </c>
     </row>
-    <row r="105" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="105" spans="1:17" ht="15.75" customHeight="1">
       <c r="A105" s="10"/>
       <c r="E105" s="237"/>
     </row>
-    <row r="106" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="106" spans="1:17" ht="15.75" customHeight="1">
       <c r="A106" s="10"/>
       <c r="B106" s="88" t="s">
         <v>189</v>
@@ -14544,7 +14533,7 @@
       <c r="P106" s="12"/>
       <c r="Q106" s="12"/>
     </row>
-    <row r="107" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="107" spans="1:17" ht="15.75" customHeight="1">
       <c r="A107" s="10"/>
       <c r="B107" s="25" t="s">
         <v>186</v>
@@ -14601,7 +14590,7 @@
         <v/>
       </c>
     </row>
-    <row r="108" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="108" spans="1:17" ht="15.75" customHeight="1">
       <c r="A108" s="10"/>
       <c r="B108" s="25" t="s">
         <v>187</v>
@@ -14658,7 +14647,7 @@
         <v/>
       </c>
     </row>
-    <row r="109" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="109" spans="1:17" ht="15.75" customHeight="1">
       <c r="A109" s="10"/>
       <c r="B109" s="25" t="s">
         <v>66</v>
@@ -14685,18 +14674,18 @@
       <c r="P109" s="186"/>
       <c r="Q109" s="186"/>
     </row>
-    <row r="110" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="110" spans="1:17" ht="15.75" customHeight="1">
       <c r="A110" s="10"/>
       <c r="E110" s="237"/>
     </row>
-    <row r="111" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="111" spans="1:17" ht="15.75" customHeight="1">
       <c r="A111" s="10"/>
       <c r="B111" s="61" t="s">
         <v>48</v>
       </c>
       <c r="E111" s="237"/>
     </row>
-    <row r="112" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="112" spans="1:17" ht="15.75" customHeight="1">
       <c r="A112" s="10"/>
       <c r="B112" s="2" t="s">
         <v>303</v>
@@ -14750,7 +14739,7 @@
         <v/>
       </c>
     </row>
-    <row r="113" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="113" spans="1:17" ht="15.75" customHeight="1">
       <c r="A113" s="10"/>
       <c r="B113" s="2" t="s">
         <v>304</v>
@@ -14805,11 +14794,11 @@
         <v/>
       </c>
     </row>
-    <row r="114" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="114" spans="1:17" ht="15.75" customHeight="1">
       <c r="A114" s="10"/>
       <c r="E114" s="237"/>
     </row>
-    <row r="115" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="115" spans="1:17" ht="15.75" customHeight="1">
       <c r="A115" s="10"/>
       <c r="B115" s="88" t="s">
         <v>36</v>
@@ -14868,7 +14857,7 @@
         <v/>
       </c>
     </row>
-    <row r="116" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="116" spans="1:17" ht="15.75" customHeight="1">
       <c r="A116" s="10"/>
       <c r="B116" s="7" t="s">
         <v>190</v>
@@ -14926,7 +14915,7 @@
         <v/>
       </c>
     </row>
-    <row r="117" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="117" spans="1:17" ht="15.75" customHeight="1">
       <c r="B117" s="7" t="s">
         <v>80</v>
       </c>
@@ -14983,7 +14972,7 @@
         <v/>
       </c>
     </row>
-    <row r="118" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="118" spans="1:17" ht="15.75" customHeight="1">
       <c r="B118" s="7" t="s">
         <v>88</v>
       </c>
@@ -15042,7 +15031,7 @@
         <v/>
       </c>
     </row>
-    <row r="119" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="119" spans="1:17" ht="15.75" customHeight="1">
       <c r="A119" s="10"/>
       <c r="B119" s="67" t="s">
         <v>191</v>
@@ -15102,7 +15091,7 @@
         <v/>
       </c>
     </row>
-    <row r="120" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="120" spans="1:17" ht="15.75" customHeight="1">
       <c r="A120" s="10"/>
       <c r="B120" s="26"/>
       <c r="C120" s="59"/>
@@ -15121,7 +15110,7 @@
       <c r="P120" s="12"/>
       <c r="Q120" s="12"/>
     </row>
-    <row r="121" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:17" ht="15.75" customHeight="1">
       <c r="A121" s="10"/>
       <c r="B121" s="51" t="s">
         <v>192</v>
@@ -15144,7 +15133,7 @@
       <c r="P121" s="35"/>
       <c r="Q121" s="35"/>
     </row>
-    <row r="122" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="122" spans="1:17" ht="15.75" customHeight="1">
       <c r="A122" s="10"/>
       <c r="B122" s="160" t="s">
         <v>141</v>
@@ -15165,7 +15154,7 @@
       <c r="P122" s="12"/>
       <c r="Q122" s="12"/>
     </row>
-    <row r="123" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="123" spans="1:17" ht="15.75" customHeight="1">
       <c r="A123" s="10"/>
       <c r="B123" s="26" t="str">
         <f>"FCFE per share ("&amp;Market_currency&amp;")"</f>
@@ -15173,18 +15162,18 @@
       </c>
       <c r="C123" s="159">
         <f>C14*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>2.915535507823908</v>
+        <v>2.9262572042358754</v>
       </c>
       <c r="D123" s="26"/>
       <c r="E123" s="234"/>
       <c r="F123" s="26"/>
       <c r="G123" s="159">
         <f t="shared" ref="G123:Q123" si="48">IF(G$4="","",G14*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>3.0196575619440273</v>
+        <v>3.0307621605882158</v>
       </c>
       <c r="H123" s="159">
         <f t="shared" si="48"/>
-        <v>2.4153675379524224</v>
+        <v>2.4242498984641543</v>
       </c>
       <c r="I123" s="159" t="str">
         <f t="shared" si="48"/>
@@ -15223,25 +15212,25 @@
         <v/>
       </c>
     </row>
-    <row r="124" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="124" spans="1:17" ht="15.75" customHeight="1">
       <c r="A124" s="10"/>
       <c r="B124" s="26" t="s">
         <v>226</v>
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>6.9088519142746635E-2</v>
+        <v>6.575858885923315E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="234"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>7.1555866396777898E-2</v>
+        <v>6.8107014844679001E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>5.7236197581810956E-2</v>
+        <v>5.4477525808183241E-2</v>
       </c>
       <c r="I124" s="74" t="str">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
@@ -15280,18 +15269,18 @@
         <v/>
       </c>
     </row>
-    <row r="125" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="125" spans="1:17" ht="15.75" customHeight="1">
       <c r="B125" s="2" t="s">
         <v>306</v>
       </c>
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.810534054128509E-3</v>
+        <v>7.4068435299825411E-3</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.2361289397411725E-3</v>
+        <v>5.913812163080393E-3</v>
       </c>
       <c r="I125" s="22" t="str">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -15330,688 +15319,688 @@
         <v/>
       </c>
     </row>
-    <row r="126" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="127" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="128" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="126" spans="1:17" ht="15.75" customHeight="1"/>
+    <row r="127" spans="1:17" ht="15.75" customHeight="1"/>
+    <row r="128" spans="1:17" ht="15.75" customHeight="1"/>
+    <row r="129" ht="15.75" customHeight="1"/>
+    <row r="130" ht="15.75" customHeight="1"/>
+    <row r="131" ht="15.75" customHeight="1"/>
+    <row r="132" ht="15.75" customHeight="1"/>
+    <row r="133" ht="15.75" customHeight="1"/>
+    <row r="134" ht="15.75" customHeight="1"/>
+    <row r="135" ht="15.75" customHeight="1"/>
+    <row r="136" ht="15.75" customHeight="1"/>
+    <row r="137" ht="15.75" customHeight="1"/>
+    <row r="138" ht="15.75" customHeight="1"/>
+    <row r="139" ht="15.75" customHeight="1"/>
+    <row r="140" ht="15.75" customHeight="1"/>
+    <row r="141" ht="15.75" customHeight="1"/>
+    <row r="142" ht="15.75" customHeight="1"/>
+    <row r="143" ht="15.75" customHeight="1"/>
+    <row r="144" ht="15.75" customHeight="1"/>
+    <row r="145" ht="15.75" customHeight="1"/>
+    <row r="146" ht="15.75" customHeight="1"/>
+    <row r="147" ht="15.75" customHeight="1"/>
+    <row r="148" ht="15.75" customHeight="1"/>
+    <row r="149" ht="15.75" customHeight="1"/>
+    <row r="150" ht="15.75" customHeight="1"/>
+    <row r="151" ht="15.75" customHeight="1"/>
+    <row r="152" ht="15.75" customHeight="1"/>
+    <row r="153" ht="15.75" customHeight="1"/>
+    <row r="154" ht="15.75" customHeight="1"/>
+    <row r="155" ht="15.75" customHeight="1"/>
+    <row r="156" ht="15.75" customHeight="1"/>
+    <row r="157" ht="15.75" customHeight="1"/>
+    <row r="158" ht="15.75" customHeight="1"/>
+    <row r="159" ht="15.75" customHeight="1"/>
+    <row r="160" ht="15.75" customHeight="1"/>
+    <row r="161" ht="15.75" customHeight="1"/>
+    <row r="162" ht="15.75" customHeight="1"/>
+    <row r="163" ht="15.75" customHeight="1"/>
+    <row r="164" ht="15.75" customHeight="1"/>
+    <row r="165" ht="15.75" customHeight="1"/>
+    <row r="166" ht="15.75" customHeight="1"/>
+    <row r="167" ht="15.75" customHeight="1"/>
+    <row r="168" ht="15.75" customHeight="1"/>
+    <row r="169" ht="15.75" customHeight="1"/>
+    <row r="170" ht="15.75" customHeight="1"/>
+    <row r="171" ht="15.75" customHeight="1"/>
+    <row r="172" ht="15.75" customHeight="1"/>
+    <row r="173" ht="15.75" customHeight="1"/>
+    <row r="174" ht="15.75" customHeight="1"/>
+    <row r="175" ht="15.75" customHeight="1"/>
+    <row r="176" ht="15.75" customHeight="1"/>
+    <row r="177" ht="15.75" customHeight="1"/>
+    <row r="178" ht="15.75" customHeight="1"/>
+    <row r="179" ht="15.75" customHeight="1"/>
+    <row r="180" ht="15.75" customHeight="1"/>
+    <row r="181" ht="15.75" customHeight="1"/>
+    <row r="182" ht="15.75" customHeight="1"/>
+    <row r="183" ht="15.75" customHeight="1"/>
+    <row r="184" ht="15.75" customHeight="1"/>
+    <row r="185" ht="15.75" customHeight="1"/>
+    <row r="186" ht="15.75" customHeight="1"/>
+    <row r="187" ht="15.75" customHeight="1"/>
+    <row r="188" ht="15.75" customHeight="1"/>
+    <row r="189" ht="15.75" customHeight="1"/>
+    <row r="190" ht="15.75" customHeight="1"/>
+    <row r="191" ht="15.75" customHeight="1"/>
+    <row r="192" ht="15.75" customHeight="1"/>
+    <row r="193" ht="15.75" customHeight="1"/>
+    <row r="194" ht="15.75" customHeight="1"/>
+    <row r="195" ht="15.75" customHeight="1"/>
+    <row r="196" ht="15.75" customHeight="1"/>
+    <row r="197" ht="15.75" customHeight="1"/>
+    <row r="198" ht="15.75" customHeight="1"/>
+    <row r="199" ht="15.75" customHeight="1"/>
+    <row r="200" ht="15.75" customHeight="1"/>
+    <row r="201" ht="15.75" customHeight="1"/>
+    <row r="202" ht="15.75" customHeight="1"/>
+    <row r="203" ht="15.75" customHeight="1"/>
+    <row r="204" ht="15.75" customHeight="1"/>
+    <row r="205" ht="15.75" customHeight="1"/>
+    <row r="206" ht="15.75" customHeight="1"/>
+    <row r="207" ht="15.75" customHeight="1"/>
+    <row r="208" ht="15.75" customHeight="1"/>
+    <row r="209" ht="15.75" customHeight="1"/>
+    <row r="210" ht="15.75" customHeight="1"/>
+    <row r="211" ht="15.75" customHeight="1"/>
+    <row r="212" ht="15.75" customHeight="1"/>
+    <row r="213" ht="15.75" customHeight="1"/>
+    <row r="214" ht="15.75" customHeight="1"/>
+    <row r="215" ht="15.75" customHeight="1"/>
+    <row r="216" ht="15.75" customHeight="1"/>
+    <row r="217" ht="15.75" customHeight="1"/>
+    <row r="218" ht="15.75" customHeight="1"/>
+    <row r="219" ht="15.75" customHeight="1"/>
+    <row r="220" ht="15.75" customHeight="1"/>
+    <row r="221" ht="15.75" customHeight="1"/>
+    <row r="222" ht="15.75" customHeight="1"/>
+    <row r="223" ht="15.75" customHeight="1"/>
+    <row r="224" ht="15.75" customHeight="1"/>
+    <row r="225" ht="15.75" customHeight="1"/>
+    <row r="226" ht="15.75" customHeight="1"/>
+    <row r="227" ht="15.75" customHeight="1"/>
+    <row r="228" ht="15.75" customHeight="1"/>
+    <row r="229" ht="15.75" customHeight="1"/>
+    <row r="230" ht="15.75" customHeight="1"/>
+    <row r="231" ht="15.75" customHeight="1"/>
+    <row r="232" ht="15.75" customHeight="1"/>
+    <row r="233" ht="15.75" customHeight="1"/>
+    <row r="234" ht="15.75" customHeight="1"/>
+    <row r="235" ht="15.75" customHeight="1"/>
+    <row r="236" ht="15.75" customHeight="1"/>
+    <row r="237" ht="15.75" customHeight="1"/>
+    <row r="238" ht="15.75" customHeight="1"/>
+    <row r="239" ht="15.75" customHeight="1"/>
+    <row r="240" ht="15.75" customHeight="1"/>
+    <row r="241" ht="15.75" customHeight="1"/>
+    <row r="242" ht="15.75" customHeight="1"/>
+    <row r="243" ht="15.75" customHeight="1"/>
+    <row r="244" ht="15.75" customHeight="1"/>
+    <row r="245" ht="15.75" customHeight="1"/>
+    <row r="246" ht="15.75" customHeight="1"/>
+    <row r="247" ht="15.75" customHeight="1"/>
+    <row r="248" ht="15.75" customHeight="1"/>
+    <row r="249" ht="15.75" customHeight="1"/>
+    <row r="250" ht="15.75" customHeight="1"/>
+    <row r="251" ht="15.75" customHeight="1"/>
+    <row r="252" ht="15.75" customHeight="1"/>
+    <row r="253" ht="15.75" customHeight="1"/>
+    <row r="254" ht="15.75" customHeight="1"/>
+    <row r="255" ht="15.75" customHeight="1"/>
+    <row r="256" ht="15.75" customHeight="1"/>
+    <row r="257" ht="15.75" customHeight="1"/>
+    <row r="258" ht="15.75" customHeight="1"/>
+    <row r="259" ht="15.75" customHeight="1"/>
+    <row r="260" ht="15.75" customHeight="1"/>
+    <row r="261" ht="15.75" customHeight="1"/>
+    <row r="262" ht="15.75" customHeight="1"/>
+    <row r="263" ht="15.75" customHeight="1"/>
+    <row r="264" ht="15.75" customHeight="1"/>
+    <row r="265" ht="15.75" customHeight="1"/>
+    <row r="266" ht="15.75" customHeight="1"/>
+    <row r="267" ht="15.75" customHeight="1"/>
+    <row r="268" ht="15.75" customHeight="1"/>
+    <row r="269" ht="15.75" customHeight="1"/>
+    <row r="270" ht="15.75" customHeight="1"/>
+    <row r="271" ht="15.75" customHeight="1"/>
+    <row r="272" ht="15.75" customHeight="1"/>
+    <row r="273" ht="15.75" customHeight="1"/>
+    <row r="274" ht="15.75" customHeight="1"/>
+    <row r="275" ht="15.75" customHeight="1"/>
+    <row r="276" ht="15.75" customHeight="1"/>
+    <row r="277" ht="15.75" customHeight="1"/>
+    <row r="278" ht="15.75" customHeight="1"/>
+    <row r="279" ht="15.75" customHeight="1"/>
+    <row r="280" ht="15.75" customHeight="1"/>
+    <row r="281" ht="15.75" customHeight="1"/>
+    <row r="282" ht="15.75" customHeight="1"/>
+    <row r="283" ht="15.75" customHeight="1"/>
+    <row r="284" ht="15.75" customHeight="1"/>
+    <row r="285" ht="15.75" customHeight="1"/>
+    <row r="286" ht="15.75" customHeight="1"/>
+    <row r="287" ht="15.75" customHeight="1"/>
+    <row r="288" ht="15.75" customHeight="1"/>
+    <row r="289" ht="15.75" customHeight="1"/>
+    <row r="290" ht="15.75" customHeight="1"/>
+    <row r="291" ht="15.75" customHeight="1"/>
+    <row r="292" ht="15.75" customHeight="1"/>
+    <row r="293" ht="15.75" customHeight="1"/>
+    <row r="294" ht="15.75" customHeight="1"/>
+    <row r="295" ht="15.75" customHeight="1"/>
+    <row r="296" ht="15.75" customHeight="1"/>
+    <row r="297" ht="15.75" customHeight="1"/>
+    <row r="298" ht="15.75" customHeight="1"/>
+    <row r="299" ht="15.75" customHeight="1"/>
+    <row r="300" ht="15.75" customHeight="1"/>
+    <row r="301" ht="15.75" customHeight="1"/>
+    <row r="302" ht="15.75" customHeight="1"/>
+    <row r="303" ht="15.75" customHeight="1"/>
+    <row r="304" ht="15.75" customHeight="1"/>
+    <row r="305" ht="15.75" customHeight="1"/>
+    <row r="306" ht="15.75" customHeight="1"/>
+    <row r="307" ht="15.75" customHeight="1"/>
+    <row r="308" ht="15.75" customHeight="1"/>
+    <row r="309" ht="15.75" customHeight="1"/>
+    <row r="310" ht="15.75" customHeight="1"/>
+    <row r="311" ht="15.75" customHeight="1"/>
+    <row r="312" ht="15.75" customHeight="1"/>
+    <row r="313" ht="15.75" customHeight="1"/>
+    <row r="314" ht="15.75" customHeight="1"/>
+    <row r="315" ht="15.75" customHeight="1"/>
+    <row r="316" ht="15.75" customHeight="1"/>
+    <row r="317" ht="15.75" customHeight="1"/>
+    <row r="318" ht="15.75" customHeight="1"/>
+    <row r="319" ht="15.75" customHeight="1"/>
+    <row r="320" ht="15.75" customHeight="1"/>
+    <row r="321" ht="15.75" customHeight="1"/>
+    <row r="322" ht="15.75" customHeight="1"/>
+    <row r="323" ht="15.75" customHeight="1"/>
+    <row r="324" ht="15.75" customHeight="1"/>
+    <row r="325" ht="15.75" customHeight="1"/>
+    <row r="326" ht="15.75" customHeight="1"/>
+    <row r="327" ht="15.75" customHeight="1"/>
+    <row r="328" ht="15.75" customHeight="1"/>
+    <row r="329" ht="15.75" customHeight="1"/>
+    <row r="330" ht="15.75" customHeight="1"/>
+    <row r="331" ht="15.75" customHeight="1"/>
+    <row r="332" ht="15.75" customHeight="1"/>
+    <row r="333" ht="15.75" customHeight="1"/>
+    <row r="334" ht="15.75" customHeight="1"/>
+    <row r="335" ht="15.75" customHeight="1"/>
+    <row r="336" ht="15.75" customHeight="1"/>
+    <row r="337" ht="15.75" customHeight="1"/>
+    <row r="338" ht="15.75" customHeight="1"/>
+    <row r="339" ht="15.75" customHeight="1"/>
+    <row r="340" ht="15.75" customHeight="1"/>
+    <row r="341" ht="15.75" customHeight="1"/>
+    <row r="342" ht="15.75" customHeight="1"/>
+    <row r="343" ht="15.75" customHeight="1"/>
+    <row r="344" ht="15.75" customHeight="1"/>
+    <row r="345" ht="15.75" customHeight="1"/>
+    <row r="346" ht="15.75" customHeight="1"/>
+    <row r="347" ht="15.75" customHeight="1"/>
+    <row r="348" ht="15.75" customHeight="1"/>
+    <row r="349" ht="15.75" customHeight="1"/>
+    <row r="350" ht="15.75" customHeight="1"/>
+    <row r="351" ht="15.75" customHeight="1"/>
+    <row r="352" ht="15.75" customHeight="1"/>
+    <row r="353" ht="15.75" customHeight="1"/>
+    <row r="354" ht="15.75" customHeight="1"/>
+    <row r="355" ht="15.75" customHeight="1"/>
+    <row r="356" ht="15.75" customHeight="1"/>
+    <row r="357" ht="15.75" customHeight="1"/>
+    <row r="358" ht="15.75" customHeight="1"/>
+    <row r="359" ht="15.75" customHeight="1"/>
+    <row r="360" ht="15.75" customHeight="1"/>
+    <row r="361" ht="15.75" customHeight="1"/>
+    <row r="362" ht="15.75" customHeight="1"/>
+    <row r="363" ht="15.75" customHeight="1"/>
+    <row r="364" ht="15.75" customHeight="1"/>
+    <row r="365" ht="15.75" customHeight="1"/>
+    <row r="366" ht="15.75" customHeight="1"/>
+    <row r="367" ht="15.75" customHeight="1"/>
+    <row r="368" ht="15.75" customHeight="1"/>
+    <row r="369" ht="15.75" customHeight="1"/>
+    <row r="370" ht="15.75" customHeight="1"/>
+    <row r="371" ht="15.75" customHeight="1"/>
+    <row r="372" ht="15.75" customHeight="1"/>
+    <row r="373" ht="15.75" customHeight="1"/>
+    <row r="374" ht="15.75" customHeight="1"/>
+    <row r="375" ht="15.75" customHeight="1"/>
+    <row r="376" ht="15.75" customHeight="1"/>
+    <row r="377" ht="15.75" customHeight="1"/>
+    <row r="378" ht="15.75" customHeight="1"/>
+    <row r="379" ht="15.75" customHeight="1"/>
+    <row r="380" ht="15.75" customHeight="1"/>
+    <row r="381" ht="15.75" customHeight="1"/>
+    <row r="382" ht="15.75" customHeight="1"/>
+    <row r="383" ht="15.75" customHeight="1"/>
+    <row r="384" ht="15.75" customHeight="1"/>
+    <row r="385" ht="15.75" customHeight="1"/>
+    <row r="386" ht="15.75" customHeight="1"/>
+    <row r="387" ht="15.75" customHeight="1"/>
+    <row r="388" ht="15.75" customHeight="1"/>
+    <row r="389" ht="15.75" customHeight="1"/>
+    <row r="390" ht="15.75" customHeight="1"/>
+    <row r="391" ht="15.75" customHeight="1"/>
+    <row r="392" ht="15.75" customHeight="1"/>
+    <row r="393" ht="15.75" customHeight="1"/>
+    <row r="394" ht="15.75" customHeight="1"/>
+    <row r="395" ht="15.75" customHeight="1"/>
+    <row r="396" ht="15.75" customHeight="1"/>
+    <row r="397" ht="15.75" customHeight="1"/>
+    <row r="398" ht="15.75" customHeight="1"/>
+    <row r="399" ht="15.75" customHeight="1"/>
+    <row r="400" ht="15.75" customHeight="1"/>
+    <row r="401" ht="15.75" customHeight="1"/>
+    <row r="402" ht="15.75" customHeight="1"/>
+    <row r="403" ht="15.75" customHeight="1"/>
+    <row r="404" ht="15.75" customHeight="1"/>
+    <row r="405" ht="15.75" customHeight="1"/>
+    <row r="406" ht="15.75" customHeight="1"/>
+    <row r="407" ht="15.75" customHeight="1"/>
+    <row r="408" ht="15.75" customHeight="1"/>
+    <row r="409" ht="15.75" customHeight="1"/>
+    <row r="410" ht="15.75" customHeight="1"/>
+    <row r="411" ht="15.75" customHeight="1"/>
+    <row r="412" ht="15.75" customHeight="1"/>
+    <row r="413" ht="15.75" customHeight="1"/>
+    <row r="414" ht="15.75" customHeight="1"/>
+    <row r="415" ht="15.75" customHeight="1"/>
+    <row r="416" ht="15.75" customHeight="1"/>
+    <row r="417" ht="15.75" customHeight="1"/>
+    <row r="418" ht="15.75" customHeight="1"/>
+    <row r="419" ht="15.75" customHeight="1"/>
+    <row r="420" ht="15.75" customHeight="1"/>
+    <row r="421" ht="15.75" customHeight="1"/>
+    <row r="422" ht="15.75" customHeight="1"/>
+    <row r="423" ht="15.75" customHeight="1"/>
+    <row r="424" ht="15.75" customHeight="1"/>
+    <row r="425" ht="15.75" customHeight="1"/>
+    <row r="426" ht="15.75" customHeight="1"/>
+    <row r="427" ht="15.75" customHeight="1"/>
+    <row r="428" ht="15.75" customHeight="1"/>
+    <row r="429" ht="15.75" customHeight="1"/>
+    <row r="430" ht="15.75" customHeight="1"/>
+    <row r="431" ht="15.75" customHeight="1"/>
+    <row r="432" ht="15.75" customHeight="1"/>
+    <row r="433" ht="15.75" customHeight="1"/>
+    <row r="434" ht="15.75" customHeight="1"/>
+    <row r="435" ht="15.75" customHeight="1"/>
+    <row r="436" ht="15.75" customHeight="1"/>
+    <row r="437" ht="15.75" customHeight="1"/>
+    <row r="438" ht="15.75" customHeight="1"/>
+    <row r="439" ht="15.75" customHeight="1"/>
+    <row r="440" ht="15.75" customHeight="1"/>
+    <row r="441" ht="15.75" customHeight="1"/>
+    <row r="442" ht="15.75" customHeight="1"/>
+    <row r="443" ht="15.75" customHeight="1"/>
+    <row r="444" ht="15.75" customHeight="1"/>
+    <row r="445" ht="15.75" customHeight="1"/>
+    <row r="446" ht="15.75" customHeight="1"/>
+    <row r="447" ht="15.75" customHeight="1"/>
+    <row r="448" ht="15.75" customHeight="1"/>
+    <row r="449" ht="15.75" customHeight="1"/>
+    <row r="450" ht="15.75" customHeight="1"/>
+    <row r="451" ht="15.75" customHeight="1"/>
+    <row r="452" ht="15.75" customHeight="1"/>
+    <row r="453" ht="15.75" customHeight="1"/>
+    <row r="454" ht="15.75" customHeight="1"/>
+    <row r="455" ht="15.75" customHeight="1"/>
+    <row r="456" ht="15.75" customHeight="1"/>
+    <row r="457" ht="15.75" customHeight="1"/>
+    <row r="458" ht="15.75" customHeight="1"/>
+    <row r="459" ht="15.75" customHeight="1"/>
+    <row r="460" ht="15.75" customHeight="1"/>
+    <row r="461" ht="15.75" customHeight="1"/>
+    <row r="462" ht="15.75" customHeight="1"/>
+    <row r="463" ht="15.75" customHeight="1"/>
+    <row r="464" ht="15.75" customHeight="1"/>
+    <row r="465" ht="15.75" customHeight="1"/>
+    <row r="466" ht="15.75" customHeight="1"/>
+    <row r="467" ht="15.75" customHeight="1"/>
+    <row r="468" ht="15.75" customHeight="1"/>
+    <row r="469" ht="15.75" customHeight="1"/>
+    <row r="470" ht="15.75" customHeight="1"/>
+    <row r="471" ht="15.75" customHeight="1"/>
+    <row r="472" ht="15.75" customHeight="1"/>
+    <row r="473" ht="15.75" customHeight="1"/>
+    <row r="474" ht="15.75" customHeight="1"/>
+    <row r="475" ht="15.75" customHeight="1"/>
+    <row r="476" ht="15.75" customHeight="1"/>
+    <row r="477" ht="15.75" customHeight="1"/>
+    <row r="478" ht="15.75" customHeight="1"/>
+    <row r="479" ht="15.75" customHeight="1"/>
+    <row r="480" ht="15.75" customHeight="1"/>
+    <row r="481" ht="15.75" customHeight="1"/>
+    <row r="482" ht="15.75" customHeight="1"/>
+    <row r="483" ht="15.75" customHeight="1"/>
+    <row r="484" ht="15.75" customHeight="1"/>
+    <row r="485" ht="15.75" customHeight="1"/>
+    <row r="486" ht="15.75" customHeight="1"/>
+    <row r="487" ht="15.75" customHeight="1"/>
+    <row r="488" ht="15.75" customHeight="1"/>
+    <row r="489" ht="15.75" customHeight="1"/>
+    <row r="490" ht="15.75" customHeight="1"/>
+    <row r="491" ht="15.75" customHeight="1"/>
+    <row r="492" ht="15.75" customHeight="1"/>
+    <row r="493" ht="15.75" customHeight="1"/>
+    <row r="494" ht="15.75" customHeight="1"/>
+    <row r="495" ht="15.75" customHeight="1"/>
+    <row r="496" ht="15.75" customHeight="1"/>
+    <row r="497" ht="15.75" customHeight="1"/>
+    <row r="498" ht="15.75" customHeight="1"/>
+    <row r="499" ht="15.75" customHeight="1"/>
+    <row r="500" ht="15.75" customHeight="1"/>
+    <row r="501" ht="15.75" customHeight="1"/>
+    <row r="502" ht="15.75" customHeight="1"/>
+    <row r="503" ht="15.75" customHeight="1"/>
+    <row r="504" ht="15.75" customHeight="1"/>
+    <row r="505" ht="15.75" customHeight="1"/>
+    <row r="506" ht="15.75" customHeight="1"/>
+    <row r="507" ht="15.75" customHeight="1"/>
+    <row r="508" ht="15.75" customHeight="1"/>
+    <row r="509" ht="15.75" customHeight="1"/>
+    <row r="510" ht="15.75" customHeight="1"/>
+    <row r="511" ht="15.75" customHeight="1"/>
+    <row r="512" ht="15.75" customHeight="1"/>
+    <row r="513" ht="15.75" customHeight="1"/>
+    <row r="514" ht="15.75" customHeight="1"/>
+    <row r="515" ht="15.75" customHeight="1"/>
+    <row r="516" ht="15.75" customHeight="1"/>
+    <row r="517" ht="15.75" customHeight="1"/>
+    <row r="518" ht="15.75" customHeight="1"/>
+    <row r="519" ht="15.75" customHeight="1"/>
+    <row r="520" ht="15.75" customHeight="1"/>
+    <row r="521" ht="15.75" customHeight="1"/>
+    <row r="522" ht="15.75" customHeight="1"/>
+    <row r="523" ht="15.75" customHeight="1"/>
+    <row r="524" ht="15.75" customHeight="1"/>
+    <row r="525" ht="15.75" customHeight="1"/>
+    <row r="526" ht="15.75" customHeight="1"/>
+    <row r="527" ht="15.75" customHeight="1"/>
+    <row r="528" ht="15.75" customHeight="1"/>
+    <row r="529" ht="15.75" customHeight="1"/>
+    <row r="530" ht="15.75" customHeight="1"/>
+    <row r="531" ht="15.75" customHeight="1"/>
+    <row r="532" ht="15.75" customHeight="1"/>
+    <row r="533" ht="15.75" customHeight="1"/>
+    <row r="534" ht="15.75" customHeight="1"/>
+    <row r="535" ht="15.75" customHeight="1"/>
+    <row r="536" ht="15.75" customHeight="1"/>
+    <row r="537" ht="15.75" customHeight="1"/>
+    <row r="538" ht="15.75" customHeight="1"/>
+    <row r="539" ht="15.75" customHeight="1"/>
+    <row r="540" ht="15.75" customHeight="1"/>
+    <row r="541" ht="15.75" customHeight="1"/>
+    <row r="542" ht="15.75" customHeight="1"/>
+    <row r="543" ht="15.75" customHeight="1"/>
+    <row r="544" ht="15.75" customHeight="1"/>
+    <row r="545" ht="15.75" customHeight="1"/>
+    <row r="546" ht="15.75" customHeight="1"/>
+    <row r="547" ht="15.75" customHeight="1"/>
+    <row r="548" ht="15.75" customHeight="1"/>
+    <row r="549" ht="15.75" customHeight="1"/>
+    <row r="550" ht="15.75" customHeight="1"/>
+    <row r="551" ht="15.75" customHeight="1"/>
+    <row r="552" ht="15.75" customHeight="1"/>
+    <row r="553" ht="15.75" customHeight="1"/>
+    <row r="554" ht="15.75" customHeight="1"/>
+    <row r="555" ht="15.75" customHeight="1"/>
+    <row r="556" ht="15.75" customHeight="1"/>
+    <row r="557" ht="15.75" customHeight="1"/>
+    <row r="558" ht="15.75" customHeight="1"/>
+    <row r="559" ht="15.75" customHeight="1"/>
+    <row r="560" ht="15.75" customHeight="1"/>
+    <row r="561" ht="15.75" customHeight="1"/>
+    <row r="562" ht="15.75" customHeight="1"/>
+    <row r="563" ht="15.75" customHeight="1"/>
+    <row r="564" ht="15.75" customHeight="1"/>
+    <row r="565" ht="15.75" customHeight="1"/>
+    <row r="566" ht="15.75" customHeight="1"/>
+    <row r="567" ht="15.75" customHeight="1"/>
+    <row r="568" ht="15.75" customHeight="1"/>
+    <row r="569" ht="15.75" customHeight="1"/>
+    <row r="570" ht="15.75" customHeight="1"/>
+    <row r="571" ht="15.75" customHeight="1"/>
+    <row r="572" ht="15.75" customHeight="1"/>
+    <row r="573" ht="15.75" customHeight="1"/>
+    <row r="574" ht="15.75" customHeight="1"/>
+    <row r="575" ht="15.75" customHeight="1"/>
+    <row r="576" ht="15.75" customHeight="1"/>
+    <row r="577" ht="15.75" customHeight="1"/>
+    <row r="578" ht="15.75" customHeight="1"/>
+    <row r="579" ht="15.75" customHeight="1"/>
+    <row r="580" ht="15.75" customHeight="1"/>
+    <row r="581" ht="15.75" customHeight="1"/>
+    <row r="582" ht="15.75" customHeight="1"/>
+    <row r="583" ht="15.75" customHeight="1"/>
+    <row r="584" ht="15.75" customHeight="1"/>
+    <row r="585" ht="15.75" customHeight="1"/>
+    <row r="586" ht="15.75" customHeight="1"/>
+    <row r="587" ht="15.75" customHeight="1"/>
+    <row r="588" ht="15.75" customHeight="1"/>
+    <row r="589" ht="15.75" customHeight="1"/>
+    <row r="590" ht="15.75" customHeight="1"/>
+    <row r="591" ht="15.75" customHeight="1"/>
+    <row r="592" ht="15.75" customHeight="1"/>
+    <row r="593" ht="15.75" customHeight="1"/>
+    <row r="594" ht="15.75" customHeight="1"/>
+    <row r="595" ht="15.75" customHeight="1"/>
+    <row r="596" ht="15.75" customHeight="1"/>
+    <row r="597" ht="15.75" customHeight="1"/>
+    <row r="598" ht="15.75" customHeight="1"/>
+    <row r="599" ht="15.75" customHeight="1"/>
+    <row r="600" ht="15.75" customHeight="1"/>
+    <row r="601" ht="15.75" customHeight="1"/>
+    <row r="602" ht="15.75" customHeight="1"/>
+    <row r="603" ht="15.75" customHeight="1"/>
+    <row r="604" ht="15.75" customHeight="1"/>
+    <row r="605" ht="15.75" customHeight="1"/>
+    <row r="606" ht="15.75" customHeight="1"/>
+    <row r="607" ht="15.75" customHeight="1"/>
+    <row r="608" ht="15.75" customHeight="1"/>
+    <row r="609" ht="15.75" customHeight="1"/>
+    <row r="610" ht="15.75" customHeight="1"/>
+    <row r="611" ht="15.75" customHeight="1"/>
+    <row r="612" ht="15.75" customHeight="1"/>
+    <row r="613" ht="15.75" customHeight="1"/>
+    <row r="614" ht="15.75" customHeight="1"/>
+    <row r="615" ht="15.75" customHeight="1"/>
+    <row r="616" ht="15.75" customHeight="1"/>
+    <row r="617" ht="15.75" customHeight="1"/>
+    <row r="618" ht="15.75" customHeight="1"/>
+    <row r="619" ht="15.75" customHeight="1"/>
+    <row r="620" ht="15.75" customHeight="1"/>
+    <row r="621" ht="15.75" customHeight="1"/>
+    <row r="622" ht="15.75" customHeight="1"/>
+    <row r="623" ht="15.75" customHeight="1"/>
+    <row r="624" ht="15.75" customHeight="1"/>
+    <row r="625" ht="15.75" customHeight="1"/>
+    <row r="626" ht="15.75" customHeight="1"/>
+    <row r="627" ht="15.75" customHeight="1"/>
+    <row r="628" ht="15.75" customHeight="1"/>
+    <row r="629" ht="15.75" customHeight="1"/>
+    <row r="630" ht="15.75" customHeight="1"/>
+    <row r="631" ht="15.75" customHeight="1"/>
+    <row r="632" ht="15.75" customHeight="1"/>
+    <row r="633" ht="15.75" customHeight="1"/>
+    <row r="634" ht="15.75" customHeight="1"/>
+    <row r="635" ht="15.75" customHeight="1"/>
+    <row r="636" ht="15.75" customHeight="1"/>
+    <row r="637" ht="15.75" customHeight="1"/>
+    <row r="638" ht="15.75" customHeight="1"/>
+    <row r="639" ht="15.75" customHeight="1"/>
+    <row r="640" ht="15.75" customHeight="1"/>
+    <row r="641" ht="15.75" customHeight="1"/>
+    <row r="642" ht="15.75" customHeight="1"/>
+    <row r="643" ht="15.75" customHeight="1"/>
+    <row r="644" ht="15.75" customHeight="1"/>
+    <row r="645" ht="15.75" customHeight="1"/>
+    <row r="646" ht="15.75" customHeight="1"/>
+    <row r="647" ht="15.75" customHeight="1"/>
+    <row r="648" ht="15.75" customHeight="1"/>
+    <row r="649" ht="15.75" customHeight="1"/>
+    <row r="650" ht="15.75" customHeight="1"/>
+    <row r="651" ht="15.75" customHeight="1"/>
+    <row r="652" ht="15.75" customHeight="1"/>
+    <row r="653" ht="15.75" customHeight="1"/>
+    <row r="654" ht="15.75" customHeight="1"/>
+    <row r="655" ht="15.75" customHeight="1"/>
+    <row r="656" ht="15.75" customHeight="1"/>
+    <row r="657" ht="15.75" customHeight="1"/>
+    <row r="658" ht="15.75" customHeight="1"/>
+    <row r="659" ht="15.75" customHeight="1"/>
+    <row r="660" ht="15.75" customHeight="1"/>
+    <row r="661" ht="15.75" customHeight="1"/>
+    <row r="662" ht="15.75" customHeight="1"/>
+    <row r="663" ht="15.75" customHeight="1"/>
+    <row r="664" ht="15.75" customHeight="1"/>
+    <row r="665" ht="15.75" customHeight="1"/>
+    <row r="666" ht="15.75" customHeight="1"/>
+    <row r="667" ht="15.75" customHeight="1"/>
+    <row r="668" ht="15.75" customHeight="1"/>
+    <row r="669" ht="15.75" customHeight="1"/>
+    <row r="670" ht="15.75" customHeight="1"/>
+    <row r="671" ht="15.75" customHeight="1"/>
+    <row r="672" ht="15.75" customHeight="1"/>
+    <row r="673" ht="15.75" customHeight="1"/>
+    <row r="674" ht="15.75" customHeight="1"/>
+    <row r="675" ht="15.75" customHeight="1"/>
+    <row r="676" ht="15.75" customHeight="1"/>
+    <row r="677" ht="15.75" customHeight="1"/>
+    <row r="678" ht="15.75" customHeight="1"/>
+    <row r="679" ht="15.75" customHeight="1"/>
+    <row r="680" ht="15.75" customHeight="1"/>
+    <row r="681" ht="15.75" customHeight="1"/>
+    <row r="682" ht="15.75" customHeight="1"/>
+    <row r="683" ht="15.75" customHeight="1"/>
+    <row r="684" ht="15.75" customHeight="1"/>
+    <row r="685" ht="15.75" customHeight="1"/>
+    <row r="686" ht="15.75" customHeight="1"/>
+    <row r="687" ht="15.75" customHeight="1"/>
+    <row r="688" ht="15.75" customHeight="1"/>
+    <row r="689" ht="15.75" customHeight="1"/>
+    <row r="690" ht="15.75" customHeight="1"/>
+    <row r="691" ht="15.75" customHeight="1"/>
+    <row r="692" ht="15.75" customHeight="1"/>
+    <row r="693" ht="15.75" customHeight="1"/>
+    <row r="694" ht="15.75" customHeight="1"/>
+    <row r="695" ht="15.75" customHeight="1"/>
+    <row r="696" ht="15.75" customHeight="1"/>
+    <row r="697" ht="15.75" customHeight="1"/>
+    <row r="698" ht="15.75" customHeight="1"/>
+    <row r="699" ht="15.75" customHeight="1"/>
+    <row r="700" ht="15.75" customHeight="1"/>
+    <row r="701" ht="15.75" customHeight="1"/>
+    <row r="702" ht="15.75" customHeight="1"/>
+    <row r="703" ht="15.75" customHeight="1"/>
+    <row r="704" ht="15.75" customHeight="1"/>
+    <row r="705" ht="15.75" customHeight="1"/>
+    <row r="706" ht="15.75" customHeight="1"/>
+    <row r="707" ht="15.75" customHeight="1"/>
+    <row r="708" ht="15.75" customHeight="1"/>
+    <row r="709" ht="15.75" customHeight="1"/>
+    <row r="710" ht="15.75" customHeight="1"/>
+    <row r="711" ht="15.75" customHeight="1"/>
+    <row r="712" ht="15.75" customHeight="1"/>
+    <row r="713" ht="15.75" customHeight="1"/>
+    <row r="714" ht="15.75" customHeight="1"/>
+    <row r="715" ht="15.75" customHeight="1"/>
+    <row r="716" ht="15.75" customHeight="1"/>
+    <row r="717" ht="15.75" customHeight="1"/>
+    <row r="718" ht="15.75" customHeight="1"/>
+    <row r="719" ht="15.75" customHeight="1"/>
+    <row r="720" ht="15.75" customHeight="1"/>
+    <row r="721" ht="15.75" customHeight="1"/>
+    <row r="722" ht="15.75" customHeight="1"/>
+    <row r="723" ht="15.75" customHeight="1"/>
+    <row r="724" ht="15.75" customHeight="1"/>
+    <row r="725" ht="15.75" customHeight="1"/>
+    <row r="726" ht="15.75" customHeight="1"/>
+    <row r="727" ht="15.75" customHeight="1"/>
+    <row r="728" ht="15.75" customHeight="1"/>
+    <row r="729" ht="15.75" customHeight="1"/>
+    <row r="730" ht="15.75" customHeight="1"/>
+    <row r="731" ht="15.75" customHeight="1"/>
+    <row r="732" ht="15.75" customHeight="1"/>
+    <row r="733" ht="15.75" customHeight="1"/>
+    <row r="734" ht="15.75" customHeight="1"/>
+    <row r="735" ht="15.75" customHeight="1"/>
+    <row r="736" ht="15.75" customHeight="1"/>
+    <row r="737" ht="15.75" customHeight="1"/>
+    <row r="738" ht="15.75" customHeight="1"/>
+    <row r="739" ht="15.75" customHeight="1"/>
+    <row r="740" ht="15.75" customHeight="1"/>
+    <row r="741" ht="15.75" customHeight="1"/>
+    <row r="742" ht="15.75" customHeight="1"/>
+    <row r="743" ht="15.75" customHeight="1"/>
+    <row r="744" ht="15.75" customHeight="1"/>
+    <row r="745" ht="15.75" customHeight="1"/>
+    <row r="746" ht="15.75" customHeight="1"/>
+    <row r="747" ht="15.75" customHeight="1"/>
+    <row r="748" ht="15.75" customHeight="1"/>
+    <row r="749" ht="15.75" customHeight="1"/>
+    <row r="750" ht="15.75" customHeight="1"/>
+    <row r="751" ht="15.75" customHeight="1"/>
+    <row r="752" ht="15.75" customHeight="1"/>
+    <row r="753" ht="15.75" customHeight="1"/>
+    <row r="754" ht="15.75" customHeight="1"/>
+    <row r="755" ht="15.75" customHeight="1"/>
+    <row r="756" ht="15.75" customHeight="1"/>
+    <row r="757" ht="15.75" customHeight="1"/>
+    <row r="758" ht="15.75" customHeight="1"/>
+    <row r="759" ht="15.75" customHeight="1"/>
+    <row r="760" ht="15.75" customHeight="1"/>
+    <row r="761" ht="15.75" customHeight="1"/>
+    <row r="762" ht="15.75" customHeight="1"/>
+    <row r="763" ht="15.75" customHeight="1"/>
+    <row r="764" ht="15.75" customHeight="1"/>
+    <row r="765" ht="15.75" customHeight="1"/>
+    <row r="766" ht="15.75" customHeight="1"/>
+    <row r="767" ht="15.75" customHeight="1"/>
+    <row r="768" ht="15.75" customHeight="1"/>
+    <row r="769" ht="15.75" customHeight="1"/>
+    <row r="770" ht="15.75" customHeight="1"/>
+    <row r="771" ht="15.75" customHeight="1"/>
+    <row r="772" ht="15.75" customHeight="1"/>
+    <row r="773" ht="15.75" customHeight="1"/>
+    <row r="774" ht="15.75" customHeight="1"/>
+    <row r="775" ht="15.75" customHeight="1"/>
+    <row r="776" ht="15.75" customHeight="1"/>
+    <row r="777" ht="15.75" customHeight="1"/>
+    <row r="778" ht="15.75" customHeight="1"/>
+    <row r="779" ht="15.75" customHeight="1"/>
+    <row r="780" ht="15.75" customHeight="1"/>
+    <row r="781" ht="15.75" customHeight="1"/>
+    <row r="782" ht="15.75" customHeight="1"/>
+    <row r="783" ht="15.75" customHeight="1"/>
+    <row r="784" ht="15.75" customHeight="1"/>
+    <row r="785" ht="15.75" customHeight="1"/>
+    <row r="786" ht="15.75" customHeight="1"/>
+    <row r="787" ht="15.75" customHeight="1"/>
+    <row r="788" ht="15.75" customHeight="1"/>
+    <row r="789" ht="15.75" customHeight="1"/>
+    <row r="790" ht="15.75" customHeight="1"/>
+    <row r="791" ht="15.75" customHeight="1"/>
+    <row r="792" ht="15.75" customHeight="1"/>
+    <row r="793" ht="15.75" customHeight="1"/>
+    <row r="794" ht="15.75" customHeight="1"/>
+    <row r="795" ht="15.75" customHeight="1"/>
+    <row r="796" ht="15.75" customHeight="1"/>
+    <row r="797" ht="15.75" customHeight="1"/>
+    <row r="798" ht="15.75" customHeight="1"/>
+    <row r="799" ht="15.75" customHeight="1"/>
+    <row r="800" ht="15.75" customHeight="1"/>
+    <row r="801" ht="15.75" customHeight="1"/>
+    <row r="802" ht="15.75" customHeight="1"/>
+    <row r="803" ht="15.75" customHeight="1"/>
+    <row r="804" ht="15.75" customHeight="1"/>
+    <row r="805" ht="15.75" customHeight="1"/>
+    <row r="806" ht="15.75" customHeight="1"/>
+    <row r="807" ht="15.75" customHeight="1"/>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="G4:Q11 G13:Q16 G23:Q25">
@@ -16033,16 +16022,16 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:U118"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="6.1640625" customWidth="1"/>
+    <col min="1" max="1" width="6.1328125" customWidth="1"/>
     <col min="2" max="9" width="20.6640625" customWidth="1"/>
-    <col min="10" max="11" width="11.1640625" customWidth="1"/>
+    <col min="10" max="11" width="11.1328125" customWidth="1"/>
     <col min="12" max="12" width="20.6640625" customWidth="1"/>
     <col min="13" max="13" width="5.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:15" ht="16" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:15" ht="13.9">
       <c r="B2" s="34" t="s">
         <v>52</v>
       </c>
@@ -16057,7 +16046,7 @@
       <c r="K2" s="35"/>
       <c r="L2" s="35"/>
     </row>
-    <row r="3" spans="2:15" x14ac:dyDescent="0.15">
+    <row r="3" spans="2:15" ht="13.15">
       <c r="B3" s="106" t="s">
         <v>136</v>
       </c>
@@ -16072,7 +16061,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="4" spans="2:15" x14ac:dyDescent="0.15">
+    <row r="4" spans="2:15">
       <c r="B4" s="97" t="s">
         <v>393</v>
       </c>
@@ -16104,7 +16093,7 @@
       </c>
       <c r="J4" s="305"/>
     </row>
-    <row r="5" spans="2:15" x14ac:dyDescent="0.15">
+    <row r="5" spans="2:15">
       <c r="B5" s="187" t="s">
         <v>105</v>
       </c>
@@ -16132,7 +16121,7 @@
       </c>
       <c r="J5" s="305"/>
     </row>
-    <row r="6" spans="2:15" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="2:15" ht="13.25" customHeight="1">
       <c r="B6" s="136" t="s">
         <v>194</v>
       </c>
@@ -16165,7 +16154,7 @@
       <c r="J6" s="305"/>
       <c r="N6" s="135"/>
     </row>
-    <row r="7" spans="2:15" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="2:15" ht="12.75" customHeight="1">
       <c r="B7" s="318" t="s">
         <v>430</v>
       </c>
@@ -16195,7 +16184,7 @@
       <c r="N7" s="304"/>
       <c r="O7" s="304"/>
     </row>
-    <row r="8" spans="2:15" ht="14" x14ac:dyDescent="0.15">
+    <row r="8" spans="2:15" ht="13.15">
       <c r="B8" s="136" t="s">
         <v>426</v>
       </c>
@@ -16212,7 +16201,7 @@
       </c>
       <c r="F8" s="108">
         <f>FV_adjustments*scaling_factor/Common_Shares*Exchange_Rate</f>
-        <v>-10.335004564602832</v>
+        <v>-10.373010886618328</v>
       </c>
       <c r="G8" s="294" t="str">
         <f>Market_currency</f>
@@ -16230,14 +16219,14 @@
       <c r="N8" s="304"/>
       <c r="O8" s="304"/>
     </row>
-    <row r="9" spans="2:15" ht="14" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="2:15" ht="13.15" thickBot="1">
       <c r="B9" s="189" t="str">
         <f>"*"&amp;Thesis!E15</f>
         <v>*EUR/HKD</v>
       </c>
       <c r="C9" s="190">
         <f>Exchange_Rate</f>
-        <v>9.2105230273246779</v>
+        <v>9.2443941400000007</v>
       </c>
       <c r="D9" t="str">
         <f>Thesis!E15</f>
@@ -16256,13 +16245,13 @@
       <c r="N9" s="304"/>
       <c r="O9" s="304"/>
     </row>
-    <row r="10" spans="2:15" ht="14" thickTop="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="2:15" ht="13.5" thickTop="1">
       <c r="B10" s="107" t="s">
         <v>427</v>
       </c>
       <c r="C10" s="283">
         <f>C8*Exchange_Rate</f>
-        <v>118498334.18241224</v>
+        <v>118934104.27028055</v>
       </c>
       <c r="D10" t="str">
         <f>Market_currency</f>
@@ -16278,13 +16267,13 @@
       <c r="N10" s="304"/>
       <c r="O10" s="304"/>
     </row>
-    <row r="11" spans="2:15" x14ac:dyDescent="0.15">
+    <row r="11" spans="2:15" ht="13.15">
       <c r="B11" s="136" t="s">
         <v>425</v>
       </c>
       <c r="C11" s="108">
         <f>(C10*scaling_factor)/Common_Shares</f>
-        <v>46.309685301690244</v>
+        <v>46.479986224250105</v>
       </c>
       <c r="D11" t="str">
         <f>Market_currency</f>
@@ -16294,7 +16283,7 @@
       <c r="I11" s="307"/>
       <c r="J11" s="307"/>
     </row>
-    <row r="13" spans="2:15" ht="16" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:15" ht="13.9">
       <c r="B13" s="34" t="s">
         <v>428</v>
       </c>
@@ -16309,7 +16298,7 @@
       <c r="K13" s="35"/>
       <c r="L13" s="35"/>
     </row>
-    <row r="14" spans="2:15" x14ac:dyDescent="0.15">
+    <row r="14" spans="2:15" ht="13.15">
       <c r="B14" s="106" t="s">
         <v>399</v>
       </c>
@@ -16327,7 +16316,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="15" spans="2:15" x14ac:dyDescent="0.15">
+    <row r="15" spans="2:15">
       <c r="B15" s="139" t="s">
         <v>421</v>
       </c>
@@ -16352,7 +16341,7 @@
       </c>
       <c r="J15" s="126"/>
     </row>
-    <row r="16" spans="2:15" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="16" spans="2:15" ht="13.25" customHeight="1">
       <c r="B16" s="114" t="s">
         <v>422</v>
       </c>
@@ -16368,7 +16357,7 @@
         <v>4.584597022756233E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:21" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:21" ht="13.25" customHeight="1">
       <c r="B17" s="308" t="s">
         <v>550</v>
       </c>
@@ -16387,7 +16376,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="18" spans="1:21" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:21" ht="13.25" customHeight="1">
       <c r="B18" s="308" t="s">
         <v>423</v>
       </c>
@@ -16407,17 +16396,17 @@
       </c>
       <c r="I18" s="129">
         <f>(L52+FV_adjustments)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>59.704375522554315</v>
+        <v>59.923934566545064</v>
       </c>
       <c r="J18" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="19" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:21">
       <c r="L19" s="275"/>
     </row>
-    <row r="20" spans="1:21" ht="14" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:21" ht="13.15">
       <c r="A20" s="121" t="s">
         <v>399</v>
       </c>
@@ -16456,7 +16445,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="21" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:21">
       <c r="A21" s="302" t="str">
         <f t="shared" ref="A21:A50" si="0">IF($C$15&lt;B21,"",IF(B21&gt;=$F$15,"II","I"))</f>
         <v>I</v>
@@ -16505,7 +16494,7 @@
         <v>789850.47609109606</v>
       </c>
     </row>
-    <row r="22" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:21">
       <c r="A22" s="302" t="str">
         <f t="shared" si="0"/>
         <v>I</v>
@@ -16554,7 +16543,7 @@
         <v>770220.92074796697</v>
       </c>
     </row>
-    <row r="23" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:21">
       <c r="A23" s="302" t="str">
         <f t="shared" si="0"/>
         <v>I</v>
@@ -16611,7 +16600,7 @@
       <c r="T23" s="275"/>
       <c r="U23" s="275"/>
     </row>
-    <row r="24" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:21">
       <c r="A24" s="302" t="str">
         <f t="shared" si="0"/>
         <v>I</v>
@@ -16668,7 +16657,7 @@
       <c r="T24" s="275"/>
       <c r="U24" s="275"/>
     </row>
-    <row r="25" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:21">
       <c r="A25" s="302" t="str">
         <f t="shared" si="0"/>
         <v>I</v>
@@ -16725,7 +16714,7 @@
       <c r="T25" s="275"/>
       <c r="U25" s="275"/>
     </row>
-    <row r="26" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:21">
       <c r="A26" s="302" t="str">
         <f t="shared" si="0"/>
         <v>I</v>
@@ -16774,7 +16763,7 @@
         <v>696461.34425767313</v>
       </c>
     </row>
-    <row r="27" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:21">
       <c r="A27" s="302" t="str">
         <f t="shared" si="0"/>
         <v>I</v>
@@ -16823,7 +16812,7 @@
         <v>679152.71823884244</v>
       </c>
     </row>
-    <row r="28" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:21">
       <c r="A28" s="302" t="str">
         <f t="shared" si="0"/>
         <v>I</v>
@@ -16872,7 +16861,7 @@
         <v>662274.25038618979</v>
       </c>
     </row>
-    <row r="29" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="29" spans="1:21">
       <c r="A29" s="302" t="str">
         <f t="shared" si="0"/>
         <v>I</v>
@@ -16921,7 +16910,7 @@
         <v>645815.25030477962</v>
       </c>
     </row>
-    <row r="30" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:21">
       <c r="A30" s="302" t="str">
         <f t="shared" si="0"/>
         <v>I</v>
@@ -16970,7 +16959,7 @@
         <v>629765.2932799611</v>
       </c>
     </row>
-    <row r="31" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:21">
       <c r="A31" s="302" t="str">
         <f t="shared" si="0"/>
         <v>I</v>
@@ -17019,7 +17008,7 @@
         <v>614114.21367461688</v>
       </c>
     </row>
-    <row r="32" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:21">
       <c r="A32" s="302" t="str">
         <f t="shared" si="0"/>
         <v>I</v>
@@ -17068,7 +17057,7 @@
         <v>598852.09849050455</v>
       </c>
     </row>
-    <row r="33" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:21">
       <c r="A33" s="302" t="str">
         <f t="shared" si="0"/>
         <v>I</v>
@@ -17125,7 +17114,7 @@
       <c r="T33" s="275"/>
       <c r="U33" s="275"/>
     </row>
-    <row r="34" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:21">
       <c r="A34" s="302" t="str">
         <f t="shared" si="0"/>
         <v>I</v>
@@ -17182,7 +17171,7 @@
       <c r="T34" s="275"/>
       <c r="U34" s="275"/>
     </row>
-    <row r="35" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:21">
       <c r="A35" s="302" t="str">
         <f t="shared" si="0"/>
         <v>I</v>
@@ -17239,7 +17228,7 @@
       <c r="T35" s="275"/>
       <c r="U35" s="275"/>
     </row>
-    <row r="36" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:21">
       <c r="A36" s="302" t="str">
         <f t="shared" si="0"/>
         <v>I</v>
@@ -17288,7 +17277,7 @@
         <v>541503.51709636569</v>
       </c>
     </row>
-    <row r="37" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:21">
       <c r="A37" s="302" t="str">
         <f t="shared" si="0"/>
         <v>I</v>
@@ -17337,7 +17326,7 @@
         <v>528045.94053080282</v>
       </c>
     </row>
-    <row r="38" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="38" spans="1:21">
       <c r="A38" s="302" t="str">
         <f t="shared" si="0"/>
         <v>I</v>
@@ -17386,7 +17375,7 @@
         <v>514922.81491763471</v>
       </c>
     </row>
-    <row r="39" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:21">
       <c r="A39" s="302" t="str">
         <f t="shared" si="0"/>
         <v>I</v>
@@ -17435,7 +17424,7 @@
         <v>502125.82840078446</v>
       </c>
     </row>
-    <row r="40" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="40" spans="1:21">
       <c r="A40" s="302" t="str">
         <f t="shared" si="0"/>
         <v>I</v>
@@ -17484,7 +17473,7 @@
         <v>489646.87569243525</v>
       </c>
     </row>
-    <row r="41" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="41" spans="1:21">
       <c r="A41" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17533,7 +17522,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="42" spans="1:21">
       <c r="A42" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17582,7 +17571,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="43" spans="1:21">
       <c r="A43" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17631,7 +17620,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="44" spans="1:21">
       <c r="A44" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17680,7 +17669,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="45" spans="1:21">
       <c r="A45" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17729,7 +17718,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="46" spans="1:21">
       <c r="A46" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17778,7 +17767,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="47" spans="1:21">
       <c r="A47" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17835,7 +17824,7 @@
       <c r="T47" s="275"/>
       <c r="U47" s="275"/>
     </row>
-    <row r="48" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="48" spans="1:21">
       <c r="A48" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17892,7 +17881,7 @@
       <c r="T48" s="275"/>
       <c r="U48" s="275"/>
     </row>
-    <row r="49" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="49" spans="1:21">
       <c r="A49" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -17949,7 +17938,7 @@
       <c r="T49" s="275"/>
       <c r="U49" s="275"/>
     </row>
-    <row r="50" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="50" spans="1:21">
       <c r="A50" s="302" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -18006,7 +17995,7 @@
       <c r="T50" s="275"/>
       <c r="U50" s="275"/>
     </row>
-    <row r="51" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="51" spans="1:21">
       <c r="A51" s="315" t="s">
         <v>418</v>
       </c>
@@ -18052,7 +18041,7 @@
         <v>6888825.0097418465</v>
       </c>
     </row>
-    <row r="52" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="52" spans="1:21" ht="13.15">
       <c r="G52" s="111"/>
       <c r="H52" s="111"/>
       <c r="I52" s="111"/>
@@ -18065,10 +18054,10 @@
         <v>19458009.733047292</v>
       </c>
     </row>
-    <row r="53" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="53" spans="1:21">
       <c r="C53" s="111"/>
     </row>
-    <row r="54" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="54" spans="1:21" ht="13.15">
       <c r="B54" s="115" t="s">
         <v>108</v>
       </c>
@@ -18083,7 +18072,7 @@
       <c r="K54" s="113"/>
       <c r="L54" s="113"/>
     </row>
-    <row r="55" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="55" spans="1:21" ht="13.15">
       <c r="A55" s="125">
         <f>L52</f>
         <v>19458009.733047292</v>
@@ -18115,7 +18104,7 @@
       <c r="K55" s="123"/>
       <c r="L55" s="123"/>
     </row>
-    <row r="56" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="56" spans="1:21" ht="13.15">
       <c r="A56" s="131">
         <v>1</v>
       </c>
@@ -18142,7 +18131,7 @@
       <c r="K56" s="295"/>
       <c r="L56" s="295"/>
     </row>
-    <row r="57" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="57" spans="1:21" ht="13.15">
       <c r="A57" s="131">
         <v>2</v>
       </c>
@@ -18168,7 +18157,7 @@
       <c r="K57" s="295"/>
       <c r="L57" s="295"/>
     </row>
-    <row r="58" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="58" spans="1:21" ht="13.15">
       <c r="A58" s="131">
         <v>3</v>
       </c>
@@ -18194,7 +18183,7 @@
       <c r="K58" s="295"/>
       <c r="L58" s="295"/>
     </row>
-    <row r="59" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="59" spans="1:21" ht="13.15">
       <c r="A59" s="131">
         <v>4</v>
       </c>
@@ -18220,7 +18209,7 @@
       <c r="K59" s="295"/>
       <c r="L59" s="295"/>
     </row>
-    <row r="60" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="60" spans="1:21" ht="13.15">
       <c r="A60" s="131">
         <v>5</v>
       </c>
@@ -18246,7 +18235,7 @@
       <c r="K60" s="295"/>
       <c r="L60" s="295"/>
     </row>
-    <row r="61" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="61" spans="1:21" ht="13.15">
       <c r="A61" s="131">
         <v>6</v>
       </c>
@@ -18272,7 +18261,7 @@
       <c r="K61" s="295"/>
       <c r="L61" s="295"/>
     </row>
-    <row r="62" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="62" spans="1:21" ht="13.15">
       <c r="A62" s="131">
         <v>7</v>
       </c>
@@ -18298,7 +18287,7 @@
       <c r="K62" s="295"/>
       <c r="L62" s="295"/>
     </row>
-    <row r="63" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="63" spans="1:21" ht="13.15">
       <c r="A63" s="131">
         <v>8</v>
       </c>
@@ -18324,7 +18313,7 @@
       <c r="K63" s="295"/>
       <c r="L63" s="295"/>
     </row>
-    <row r="64" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="64" spans="1:21" ht="13.15">
       <c r="A64" s="131">
         <v>9</v>
       </c>
@@ -18350,7 +18339,7 @@
       <c r="K64" s="295"/>
       <c r="L64" s="295"/>
     </row>
-    <row r="65" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="65" spans="1:21" ht="13.15">
       <c r="A65" s="131">
         <v>10</v>
       </c>
@@ -18376,7 +18365,7 @@
       <c r="K65" s="295"/>
       <c r="L65" s="295"/>
     </row>
-    <row r="66" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="66" spans="1:21" ht="13.15">
       <c r="A66" s="131">
         <v>15</v>
       </c>
@@ -18411,7 +18400,7 @@
       <c r="T66" s="275"/>
       <c r="U66" s="275"/>
     </row>
-    <row r="67" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="67" spans="1:21" ht="13.15">
       <c r="A67" s="132">
         <v>20</v>
       </c>
@@ -18446,7 +18435,7 @@
       <c r="T67" s="275"/>
       <c r="U67" s="275"/>
     </row>
-    <row r="68" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="68" spans="1:21" ht="13.15">
       <c r="A68" s="132">
         <v>25</v>
       </c>
@@ -18481,7 +18470,7 @@
       <c r="T68" s="275"/>
       <c r="U68" s="275"/>
     </row>
-    <row r="69" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:21" ht="13.15">
       <c r="A69" s="132">
         <v>30</v>
       </c>
@@ -18516,7 +18505,7 @@
       <c r="T69" s="275"/>
       <c r="U69" s="275"/>
     </row>
-    <row r="70" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:21">
       <c r="C70" s="275"/>
       <c r="D70" s="111"/>
       <c r="E70" s="111"/>
@@ -18537,7 +18526,7 @@
       <c r="T70" s="275"/>
       <c r="U70" s="275"/>
     </row>
-    <row r="71" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="71" spans="1:21" ht="13.15">
       <c r="B71" s="115" t="s">
         <v>109</v>
       </c>
@@ -18561,7 +18550,7 @@
       <c r="T71" s="275"/>
       <c r="U71" s="275"/>
     </row>
-    <row r="72" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="72" spans="1:21" ht="13.15">
       <c r="B72" s="124">
         <f>B55</f>
         <v>0</v>
@@ -18589,29 +18578,29 @@
       <c r="K72" s="124"/>
       <c r="L72" s="124"/>
     </row>
-    <row r="73" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="73" spans="1:21" ht="13.15">
       <c r="A73" s="131">
         <v>0</v>
       </c>
       <c r="B73" s="119">
         <f>C11</f>
-        <v>46.309685301690244</v>
+        <v>46.479986224250105</v>
       </c>
       <c r="C73" s="119">
         <f>C11</f>
-        <v>46.309685301690244</v>
+        <v>46.479986224250105</v>
       </c>
       <c r="D73" s="119">
         <f>C11</f>
-        <v>46.309685301690244</v>
+        <v>46.479986224250105</v>
       </c>
       <c r="E73" s="119">
         <f>C11</f>
-        <v>46.309685301690244</v>
+        <v>46.479986224250105</v>
       </c>
       <c r="F73" s="119">
         <f>C11</f>
-        <v>46.309685301690244</v>
+        <v>46.479986224250105</v>
       </c>
       <c r="G73" s="296"/>
       <c r="H73" s="296"/>
@@ -18620,29 +18609,29 @@
       <c r="K73" s="296"/>
       <c r="L73" s="296"/>
     </row>
-    <row r="74" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:21" ht="13.15">
       <c r="A74" s="131">
         <v>1</v>
       </c>
       <c r="B74" s="119">
         <f t="shared" ref="B74:F87" si="11">(B56+FV_adjustments)/Common_Shares*scaling_factor*Exchange_Rate</f>
-        <v>30.6291949987457</v>
+        <v>30.741831915441871</v>
       </c>
       <c r="C74" s="119">
         <f t="shared" si="11"/>
-        <v>31.44847899001266</v>
+        <v>31.564128771483066</v>
       </c>
       <c r="D74" s="119">
         <f t="shared" si="11"/>
-        <v>32.267762981279638</v>
+        <v>32.386425627524275</v>
       </c>
       <c r="E74" s="119">
         <f t="shared" si="11"/>
-        <v>33.087046972546595</v>
+        <v>33.208722483565474</v>
       </c>
       <c r="F74" s="119">
         <f t="shared" si="11"/>
-        <v>33.906330963813573</v>
+        <v>34.031019339606679</v>
       </c>
       <c r="G74" s="296"/>
       <c r="H74" s="296"/>
@@ -18651,29 +18640,29 @@
       <c r="K74" s="296"/>
       <c r="L74" s="296"/>
     </row>
-    <row r="75" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:21" ht="13.15">
       <c r="A75" s="131">
         <v>2</v>
       </c>
       <c r="B75" s="119">
         <f t="shared" si="11"/>
-        <v>30.578501329264242</v>
+        <v>30.690951823214842</v>
       </c>
       <c r="C75" s="119">
         <f t="shared" si="11"/>
-        <v>32.175950627647232</v>
+        <v>32.29427563980034</v>
       </c>
       <c r="D75" s="119">
         <f t="shared" si="11"/>
-        <v>33.80395597232458</v>
+        <v>33.928267870597182</v>
       </c>
       <c r="E75" s="119">
         <f t="shared" si="11"/>
-        <v>35.462517363296243</v>
+        <v>35.59292851560533</v>
       </c>
       <c r="F75" s="119">
         <f t="shared" si="11"/>
-        <v>37.15163480056227</v>
+        <v>37.288257574824826</v>
       </c>
       <c r="G75" s="296"/>
       <c r="H75" s="296"/>
@@ -18682,29 +18671,29 @@
       <c r="K75" s="296"/>
       <c r="L75" s="296"/>
     </row>
-    <row r="76" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:21" ht="13.15">
       <c r="A76" s="131">
         <v>3</v>
       </c>
       <c r="B76" s="119">
         <f t="shared" si="11"/>
-        <v>30.531234504572918</v>
+        <v>30.643511177781722</v>
       </c>
       <c r="C76" s="119">
         <f t="shared" si="11"/>
-        <v>32.867811765537446</v>
+        <v>32.988681053025154</v>
       </c>
       <c r="D76" s="119">
         <f t="shared" si="11"/>
-        <v>35.293597660610565</v>
+        <v>35.423387621455738</v>
       </c>
       <c r="E76" s="119">
         <f t="shared" si="11"/>
-        <v>37.810301618955549</v>
+        <v>37.949346598553802</v>
       </c>
       <c r="F76" s="119">
         <f t="shared" si="11"/>
-        <v>40.419633069735738</v>
+        <v>40.568273699799711</v>
       </c>
       <c r="G76" s="296"/>
       <c r="H76" s="296"/>
@@ -18713,29 +18702,29 @@
       <c r="K76" s="296"/>
       <c r="L76" s="296"/>
     </row>
-    <row r="77" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="77" spans="1:21" ht="13.15">
       <c r="A77" s="131">
         <v>4</v>
       </c>
       <c r="B77" s="119">
         <f t="shared" si="11"/>
-        <v>30.487162873159082</v>
+        <v>30.599277475746167</v>
       </c>
       <c r="C77" s="119">
         <f t="shared" si="11"/>
-        <v>33.525805574999474</v>
+        <v>33.649094592875322</v>
       </c>
       <c r="D77" s="119">
         <f t="shared" si="11"/>
-        <v>36.738098691675766</v>
+        <v>36.873200713197377</v>
       </c>
       <c r="E77" s="119">
         <f t="shared" si="11"/>
-        <v>40.130722421751692</v>
+        <v>40.278300601281423</v>
       </c>
       <c r="F77" s="119">
         <f t="shared" si="11"/>
-        <v>43.710484473658688</v>
+        <v>43.871227000473731</v>
       </c>
       <c r="G77" s="296"/>
       <c r="H77" s="296"/>
@@ -18744,29 +18733,29 @@
       <c r="K77" s="296"/>
       <c r="L77" s="296"/>
     </row>
-    <row r="78" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="78" spans="1:21" ht="13.15">
       <c r="A78" s="131">
         <v>5</v>
       </c>
       <c r="B78" s="119">
         <f t="shared" si="11"/>
-        <v>30.446070442936396</v>
+        <v>30.558033930724672</v>
       </c>
       <c r="C78" s="119">
         <f t="shared" si="11"/>
-        <v>34.151589897285035</v>
+        <v>34.277180197208359</v>
       </c>
       <c r="D78" s="119">
         <f t="shared" si="11"/>
-        <v>38.138826964223824</v>
+        <v>38.279080074886217</v>
       </c>
       <c r="E78" s="119">
         <f t="shared" si="11"/>
-        <v>42.424098693046709</v>
+        <v>42.580110617963264</v>
       </c>
       <c r="F78" s="119">
         <f t="shared" si="11"/>
-        <v>47.024348824462223</v>
+        <v>47.197277876676935</v>
       </c>
       <c r="G78" s="296"/>
       <c r="H78" s="296"/>
@@ -18775,29 +18764,29 @@
       <c r="K78" s="296"/>
       <c r="L78" s="296"/>
     </row>
-    <row r="79" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="79" spans="1:21" ht="13.15">
       <c r="A79" s="131">
         <v>6</v>
       </c>
       <c r="B79" s="119">
         <f t="shared" si="11"/>
-        <v>30.407755822682148</v>
+        <v>30.519578410891118</v>
       </c>
       <c r="C79" s="119">
         <f t="shared" si="11"/>
-        <v>34.746741420577592</v>
+        <v>34.874520352378227</v>
       </c>
       <c r="D79" s="119">
         <f t="shared" si="11"/>
-        <v>39.497108925482586</v>
+        <v>39.642357031675431</v>
       </c>
       <c r="E79" s="119">
         <f t="shared" si="11"/>
-        <v>44.690745637170465</v>
+        <v>44.85509301207307</v>
       </c>
       <c r="F79" s="119">
         <f t="shared" si="11"/>
-        <v>50.361387051844801</v>
+        <v>50.546587849916527</v>
       </c>
       <c r="G79" s="296"/>
       <c r="H79" s="296"/>
@@ -18806,30 +18795,30 @@
       <c r="K79" s="296"/>
       <c r="L79" s="296"/>
     </row>
-    <row r="80" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="80" spans="1:21" ht="13.15">
       <c r="A80" s="131">
         <f t="shared" ref="A80" si="12">A62</f>
         <v>7</v>
       </c>
       <c r="B80" s="119">
         <f t="shared" si="11"/>
-        <v>30.372031235032498</v>
+        <v>30.483722448342348</v>
       </c>
       <c r="C80" s="119">
         <f t="shared" si="11"/>
-        <v>35.312759652520178</v>
+        <v>35.44262008037196</v>
       </c>
       <c r="D80" s="119">
         <f t="shared" si="11"/>
-        <v>40.814230827309252</v>
+        <v>40.964322565531631</v>
       </c>
       <c r="E80" s="119">
         <f t="shared" si="11"/>
-        <v>46.930974784742652</v>
+        <v>47.103560459864568</v>
       </c>
       <c r="F80" s="119">
         <f t="shared" si="11"/>
-        <v>53.721761210887408</v>
+        <v>53.919319571220754</v>
       </c>
       <c r="G80" s="296"/>
       <c r="H80" s="296"/>
@@ -18838,29 +18827,29 @@
       <c r="K80" s="296"/>
       <c r="L80" s="296"/>
     </row>
-    <row r="81" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="81" spans="1:12" ht="13.15">
       <c r="A81" s="131">
         <v>8</v>
       </c>
       <c r="B81" s="119">
         <f t="shared" si="11"/>
-        <v>30.338721596198308</v>
+        <v>30.450290315429726</v>
       </c>
       <c r="C81" s="119">
         <f t="shared" si="11"/>
-        <v>35.851070698283749</v>
+        <v>35.982910730771593</v>
       </c>
       <c r="D81" s="119">
         <f t="shared" si="11"/>
-        <v>42.091439944232071</v>
+        <v>42.246228537755819</v>
       </c>
       <c r="E81" s="119">
         <f t="shared" si="11"/>
-        <v>49.145094035490004</v>
+        <v>49.325821993346153</v>
       </c>
       <c r="F81" s="119">
         <f t="shared" si="11"/>
-        <v>57.105634489923297</v>
+        <v>57.315636829037565</v>
       </c>
       <c r="G81" s="296"/>
       <c r="H81" s="296"/>
@@ -18869,30 +18858,30 @@
       <c r="K81" s="296"/>
       <c r="L81" s="296"/>
     </row>
-    <row r="82" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="82" spans="1:12" ht="13.15">
       <c r="A82" s="131">
         <f t="shared" ref="A82" si="13">A64</f>
         <v>9</v>
       </c>
       <c r="B82" s="119">
         <f t="shared" si="11"/>
-        <v>30.307663657891389</v>
+        <v>30.419118163529859</v>
       </c>
       <c r="C82" s="119">
         <f t="shared" si="11"/>
-        <v>36.363030853695257</v>
+        <v>36.496753587095718</v>
       </c>
       <c r="D82" s="119">
         <f t="shared" si="11"/>
-        <v>43.329945754581473</v>
+        <v>43.489288874458062</v>
       </c>
       <c r="E82" s="119">
         <f t="shared" si="11"/>
-        <v>51.333407700564308</v>
+        <v>51.522183042754527</v>
       </c>
       <c r="F82" s="119">
         <f t="shared" si="11"/>
-        <v>60.513171218462929</v>
+        <v>60.735704557188754</v>
       </c>
       <c r="G82" s="296"/>
       <c r="H82" s="296"/>
@@ -18901,30 +18890,30 @@
       <c r="K82" s="296"/>
       <c r="L82" s="296"/>
     </row>
-    <row r="83" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="83" spans="1:12" ht="13.15">
       <c r="A83" s="131">
         <f t="shared" ref="A83:A87" si="14">A65</f>
         <v>10</v>
       </c>
       <c r="B83" s="119">
         <f t="shared" si="11"/>
-        <v>30.278705207255562</v>
+        <v>30.390053220033479</v>
       </c>
       <c r="C83" s="119">
         <f t="shared" si="11"/>
-        <v>36.849930022478226</v>
+        <v>36.985443296606775</v>
       </c>
       <c r="D83" s="119">
         <f t="shared" si="11"/>
-        <v>44.530921085829355</v>
+        <v>44.694680716108692</v>
       </c>
       <c r="E83" s="119">
         <f t="shared" si="11"/>
-        <v>53.496216544367329</v>
+        <v>53.69294547853341</v>
       </c>
       <c r="F83" s="119">
         <f t="shared" si="11"/>
-        <v>63.944536875174201</v>
+        <v>64.1796888428795</v>
       </c>
       <c r="G83" s="296"/>
       <c r="H83" s="296"/>
@@ -18933,30 +18922,30 @@
       <c r="K83" s="296"/>
       <c r="L83" s="296"/>
     </row>
-    <row r="84" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="84" spans="1:12" ht="13.15">
       <c r="A84" s="131">
         <f t="shared" si="14"/>
         <v>15</v>
       </c>
       <c r="B84" s="119">
         <f t="shared" si="11"/>
-        <v>30.160760420603811</v>
+        <v>30.271674698929701</v>
       </c>
       <c r="C84" s="119">
         <f t="shared" si="11"/>
-        <v>38.949406658856425</v>
+        <v>39.092640624795742</v>
       </c>
       <c r="D84" s="119">
         <f t="shared" si="11"/>
-        <v>50.011461105984829</v>
+        <v>50.195375073644747</v>
       </c>
       <c r="E84" s="119">
         <f t="shared" si="11"/>
-        <v>63.937972094119921</v>
+        <v>64.173099920260384</v>
       </c>
       <c r="F84" s="119">
         <f t="shared" si="11"/>
-        <v>81.464672292977625</v>
+        <v>81.764253444461403</v>
       </c>
       <c r="G84" s="296"/>
       <c r="H84" s="296"/>
@@ -18965,30 +18954,30 @@
       <c r="K84" s="296"/>
       <c r="L84" s="296"/>
     </row>
-    <row r="85" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="85" spans="1:12" ht="13.15">
       <c r="A85" s="132">
         <f t="shared" si="14"/>
         <v>20</v>
       </c>
       <c r="B85" s="119">
         <f t="shared" si="11"/>
-        <v>30.07764296409178</v>
+        <v>30.18825158325733</v>
       </c>
       <c r="C85" s="119">
         <f t="shared" si="11"/>
-        <v>40.582930211185598</v>
+        <v>40.732171356102107</v>
       </c>
       <c r="D85" s="119">
         <f t="shared" si="11"/>
-        <v>54.710440554832722</v>
+        <v>54.911634720576807</v>
       </c>
       <c r="E85" s="119">
         <f t="shared" si="11"/>
-        <v>73.785253384373206</v>
+        <v>74.05659396120528</v>
       </c>
       <c r="F85" s="119">
         <f t="shared" si="11"/>
-        <v>99.606027704524323</v>
+        <v>99.972322536806104</v>
       </c>
       <c r="G85" s="296"/>
       <c r="H85" s="296"/>
@@ -18997,30 +18986,30 @@
       <c r="K85" s="296"/>
       <c r="L85" s="296"/>
     </row>
-    <row r="86" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="86" spans="1:12" ht="13.15">
       <c r="A86" s="132">
         <f t="shared" si="14"/>
         <v>25</v>
       </c>
       <c r="B86" s="119">
         <f t="shared" si="11"/>
-        <v>30.019068848413163</v>
+        <v>30.129462064993415</v>
       </c>
       <c r="C86" s="119">
         <f t="shared" si="11"/>
-        <v>41.853913250376422</v>
+        <v>42.0078283545894</v>
       </c>
       <c r="D86" s="119">
         <f t="shared" si="11"/>
-        <v>58.739315041560467</v>
+        <v>58.955325137006902</v>
       </c>
       <c r="E86" s="119">
         <f t="shared" si="11"/>
-        <v>83.071905264637735</v>
+        <v>83.377396913160283</v>
       </c>
       <c r="F86" s="119">
         <f t="shared" si="11"/>
-        <v>118.39063001037312</v>
+        <v>118.82600402299839</v>
       </c>
       <c r="G86" s="296"/>
       <c r="H86" s="296"/>
@@ -19029,30 +19018,30 @@
       <c r="K86" s="296"/>
       <c r="L86" s="296"/>
     </row>
-    <row r="87" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="87" spans="1:12" ht="13.15">
       <c r="A87" s="132">
         <f t="shared" si="14"/>
         <v>30</v>
       </c>
       <c r="B87" s="119">
         <f t="shared" si="11"/>
-        <v>29.97779079237646</v>
+        <v>30.088032211530781</v>
       </c>
       <c r="C87" s="119">
         <f t="shared" si="11"/>
-        <v>42.842817195842933</v>
+        <v>43.000368931424468</v>
       </c>
       <c r="D87" s="119">
         <f t="shared" si="11"/>
-        <v>62.193645882225368</v>
+        <v>62.42235905965476</v>
       </c>
       <c r="E87" s="119">
         <f t="shared" si="11"/>
-        <v>91.829845715732773</v>
+        <v>92.167544133289269</v>
       </c>
       <c r="F87" s="119">
         <f t="shared" si="11"/>
-        <v>137.84128712964815</v>
+        <v>138.34818969683451</v>
       </c>
       <c r="G87" s="296"/>
       <c r="H87" s="296"/>
@@ -19061,7 +19050,7 @@
       <c r="K87" s="296"/>
       <c r="L87" s="296"/>
     </row>
-    <row r="89" spans="1:12" ht="14" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:12" ht="13.15">
       <c r="B89" s="153" t="s">
         <v>101</v>
       </c>
@@ -19084,7 +19073,7 @@
       <c r="K89" s="323"/>
       <c r="L89" s="323"/>
     </row>
-    <row r="90" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="90" spans="1:12">
       <c r="B90" s="120" t="str">
         <f>Scenarios!B29</f>
         <v>Snowball Scenario</v>
@@ -19099,7 +19088,7 @@
       </c>
       <c r="E90" s="127">
         <f>INDEX(B$73:F$87, MATCH(D90, A$73:A$87, 0), MATCH(C90, B$72:F$72, 0))</f>
-        <v>99.606027704524323</v>
+        <v>99.972322536806104</v>
       </c>
       <c r="F90" s="130">
         <f>Scenarios!F29</f>
@@ -19112,7 +19101,7 @@
       <c r="K90" s="297"/>
       <c r="L90" s="297"/>
     </row>
-    <row r="91" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="91" spans="1:12">
       <c r="B91" s="120" t="str">
         <f>Scenarios!B22</f>
         <v>Optimistic</v>
@@ -19127,7 +19116,7 @@
       </c>
       <c r="E91" s="127">
         <f>INDEX(B$73:F$87, MATCH(D91, A$73:A$87, 0), MATCH(C91, B$72:F$72, 0))</f>
-        <v>73.785253384373206</v>
+        <v>74.05659396120528</v>
       </c>
       <c r="F91" s="130">
         <f>Scenarios!F22*(1-F$90-F$94)</f>
@@ -19140,7 +19129,7 @@
       <c r="K91" s="297"/>
       <c r="L91" s="297"/>
     </row>
-    <row r="92" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="92" spans="1:12">
       <c r="B92" s="120" t="str">
         <f>Scenarios!B23</f>
         <v>Base</v>
@@ -19155,7 +19144,7 @@
       </c>
       <c r="E92" s="127">
         <f>INDEX(B$73:F$87, MATCH(D92, A$73:A$87, 0), MATCH(C92, B$72:F$72, 0))</f>
-        <v>54.710440554832722</v>
+        <v>54.911634720576807</v>
       </c>
       <c r="F92" s="130">
         <f>Scenarios!F23*(1-F$90-F$94)</f>
@@ -19168,7 +19157,7 @@
       <c r="K92" s="297"/>
       <c r="L92" s="297"/>
     </row>
-    <row r="93" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="93" spans="1:12">
       <c r="B93" s="120" t="str">
         <f>Scenarios!B24</f>
         <v>Pessimistic</v>
@@ -19183,7 +19172,7 @@
       </c>
       <c r="E93" s="127">
         <f>INDEX(B$73:F$87, MATCH(D93, A$73:A$87, 0), MATCH(C93, B$72:F$72, 0))</f>
-        <v>40.582930211185598</v>
+        <v>40.732171356102107</v>
       </c>
       <c r="F93" s="130">
         <f>Scenarios!F24*(1-F$90-F$94)</f>
@@ -19196,7 +19185,7 @@
       <c r="K93" s="297"/>
       <c r="L93" s="297"/>
     </row>
-    <row r="94" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="94" spans="1:12">
       <c r="B94" s="120" t="str">
         <f>Scenarios!B30</f>
         <v>Devil's advocate</v>
@@ -19211,7 +19200,7 @@
       </c>
       <c r="E94" s="127">
         <f>INDEX(B$73:F$87, MATCH(D94, A$73:A$87, 0), MATCH(C94, B$72:F$72, 0))</f>
-        <v>30.07764296409178</v>
+        <v>30.18825158325733</v>
       </c>
       <c r="F94" s="130">
         <f>Scenarios!F30</f>
@@ -19224,7 +19213,7 @@
       <c r="K94" s="297"/>
       <c r="L94" s="297"/>
     </row>
-    <row r="95" spans="1:12" x14ac:dyDescent="0.15">
+    <row r="95" spans="1:12">
       <c r="B95" s="141"/>
       <c r="C95" s="141"/>
       <c r="D95" s="141"/>
@@ -19237,16 +19226,16 @@
       <c r="K95" s="142"/>
       <c r="L95" s="142"/>
     </row>
-    <row r="105" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="105" spans="3:3">
       <c r="C105" s="112"/>
     </row>
-    <row r="106" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="106" spans="3:3">
       <c r="C106" s="112"/>
     </row>
-    <row r="107" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="107" spans="3:3">
       <c r="C107" s="112"/>
     </row>
-    <row r="114" spans="3:21" x14ac:dyDescent="0.15">
+    <row r="114" spans="3:21">
       <c r="C114" s="275"/>
       <c r="M114" s="275"/>
       <c r="N114" s="275"/>
@@ -19258,7 +19247,7 @@
       <c r="T114" s="275"/>
       <c r="U114" s="275"/>
     </row>
-    <row r="115" spans="3:21" x14ac:dyDescent="0.15">
+    <row r="115" spans="3:21">
       <c r="C115" s="275"/>
       <c r="M115" s="275"/>
       <c r="N115" s="275"/>
@@ -19270,7 +19259,7 @@
       <c r="T115" s="275"/>
       <c r="U115" s="275"/>
     </row>
-    <row r="116" spans="3:21" x14ac:dyDescent="0.15">
+    <row r="116" spans="3:21">
       <c r="C116" s="275"/>
       <c r="M116" s="275"/>
       <c r="N116" s="275"/>
@@ -19282,7 +19271,7 @@
       <c r="T116" s="275"/>
       <c r="U116" s="275"/>
     </row>
-    <row r="117" spans="3:21" x14ac:dyDescent="0.15">
+    <row r="117" spans="3:21">
       <c r="C117" s="275"/>
       <c r="M117" s="275"/>
       <c r="N117" s="275"/>
@@ -19294,7 +19283,7 @@
       <c r="T117" s="275"/>
       <c r="U117" s="275"/>
     </row>
-    <row r="118" spans="3:21" x14ac:dyDescent="0.15">
+    <row r="118" spans="3:21">
       <c r="C118" s="275"/>
       <c r="M118" s="275"/>
       <c r="N118" s="275"/>
@@ -19334,14 +19323,14 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7DB08D6-06C8-485A-B381-9C0DCA9661D4}">
   <dimension ref="B2:G67"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="2.6640625" customWidth="1"/>
     <col min="2" max="2" width="22.6640625" customWidth="1"/>
     <col min="3" max="7" width="20.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:7" ht="16" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:7" ht="13.9">
       <c r="B2" s="34" t="s">
         <v>122</v>
       </c>
@@ -19351,7 +19340,7 @@
       <c r="F2" s="35"/>
       <c r="G2" s="35"/>
     </row>
-    <row r="3" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="3" spans="2:7" ht="13.15">
       <c r="B3" s="145" t="s">
         <v>125</v>
       </c>
@@ -19360,7 +19349,7 @@
       </c>
       <c r="E3" s="97"/>
     </row>
-    <row r="4" spans="2:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="2:7" ht="12.75" customHeight="1">
       <c r="B4" s="139" t="s">
         <v>123</v>
       </c>
@@ -19381,14 +19370,14 @@
       <c r="F4" s="469"/>
       <c r="G4" s="469"/>
     </row>
-    <row r="5" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="5" spans="2:7">
       <c r="C5" s="445"/>
       <c r="D5" s="469"/>
       <c r="E5" s="469"/>
       <c r="F5" s="469"/>
       <c r="G5" s="469"/>
     </row>
-    <row r="6" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="6" spans="2:7" ht="13.15">
       <c r="B6" s="145" t="s">
         <v>91</v>
       </c>
@@ -19401,7 +19390,7 @@
       <c r="F6" s="469"/>
       <c r="G6" s="469"/>
     </row>
-    <row r="7" spans="2:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="2:7" ht="12.75" customHeight="1">
       <c r="B7" s="97" t="s">
         <v>232</v>
       </c>
@@ -19414,7 +19403,7 @@
       <c r="F7" s="469"/>
       <c r="G7" s="469"/>
     </row>
-    <row r="8" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="8" spans="2:7">
       <c r="B8" s="97" t="s">
         <v>63</v>
       </c>
@@ -19427,7 +19416,7 @@
       <c r="F8" s="469"/>
       <c r="G8" s="469"/>
     </row>
-    <row r="9" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="9" spans="2:7">
       <c r="B9" s="97" t="s">
         <v>54</v>
       </c>
@@ -19440,14 +19429,14 @@
       <c r="F9" s="469"/>
       <c r="G9" s="469"/>
     </row>
-    <row r="10" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="10" spans="2:7">
       <c r="C10" s="448"/>
       <c r="D10" s="469"/>
       <c r="E10" s="469"/>
       <c r="F10" s="469"/>
       <c r="G10" s="469"/>
     </row>
-    <row r="11" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="11" spans="2:7" ht="13.15">
       <c r="B11" s="145" t="s">
         <v>321</v>
       </c>
@@ -19457,7 +19446,7 @@
       <c r="F11" s="469"/>
       <c r="G11" s="469"/>
     </row>
-    <row r="12" spans="2:7" ht="14" x14ac:dyDescent="0.15">
+    <row r="12" spans="2:7">
       <c r="B12" s="114" t="s">
         <v>121</v>
       </c>
@@ -19470,7 +19459,7 @@
       <c r="F12" s="469"/>
       <c r="G12" s="469"/>
     </row>
-    <row r="13" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="13" spans="2:7">
       <c r="B13" s="135" t="s">
         <v>127</v>
       </c>
@@ -19483,7 +19472,7 @@
       <c r="F13" s="469"/>
       <c r="G13" s="469"/>
     </row>
-    <row r="14" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="14" spans="2:7">
       <c r="B14" s="97" t="s">
         <v>63</v>
       </c>
@@ -19496,7 +19485,7 @@
       <c r="F14" s="469"/>
       <c r="G14" s="469"/>
     </row>
-    <row r="16" spans="2:7" ht="16" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:7" ht="13.9">
       <c r="B16" s="34" t="s">
         <v>453</v>
       </c>
@@ -19506,7 +19495,7 @@
       <c r="F16" s="35"/>
       <c r="G16" s="35"/>
     </row>
-    <row r="17" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="17" spans="2:7" ht="13.15">
       <c r="B17" s="106" t="s">
         <v>126</v>
       </c>
@@ -19514,7 +19503,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="18" spans="2:7" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:7" ht="12.75" customHeight="1">
       <c r="B18" s="139" t="s">
         <v>111</v>
       </c>
@@ -19526,18 +19515,18 @@
       </c>
       <c r="F18" s="319"/>
     </row>
-    <row r="19" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:7">
       <c r="E19" s="319"/>
       <c r="F19" s="319"/>
     </row>
-    <row r="20" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="20" spans="2:7" ht="13.15">
       <c r="B20" s="106" t="s">
         <v>450</v>
       </c>
       <c r="E20" s="319"/>
       <c r="F20" s="319"/>
     </row>
-    <row r="21" spans="2:7" ht="14" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:7" ht="13.15">
       <c r="B21" s="153" t="s">
         <v>436</v>
       </c>
@@ -19558,7 +19547,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="22" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:7">
       <c r="B22" s="302" t="s">
         <v>445</v>
       </c>
@@ -19571,7 +19560,7 @@
       </c>
       <c r="E22" s="326">
         <f>DCF!E91</f>
-        <v>73.785253384373206</v>
+        <v>74.05659396120528</v>
       </c>
       <c r="F22" s="328">
         <f>1-F23-F24</f>
@@ -19582,7 +19571,7 @@
         <v>0.15999999999999995</v>
       </c>
     </row>
-    <row r="23" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="23" spans="2:7">
       <c r="B23" s="302" t="s">
         <v>437</v>
       </c>
@@ -19595,7 +19584,7 @@
       </c>
       <c r="E23" s="326">
         <f>DCF!E92</f>
-        <v>54.710440554832722</v>
+        <v>54.911634720576807</v>
       </c>
       <c r="F23" s="327">
         <v>0.55000000000000004</v>
@@ -19605,7 +19594,7 @@
         <v>0.44</v>
       </c>
     </row>
-    <row r="24" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:7">
       <c r="B24" s="302" t="s">
         <v>446</v>
       </c>
@@ -19618,7 +19607,7 @@
       </c>
       <c r="E24" s="326">
         <f>DCF!E93</f>
-        <v>40.582930211185598</v>
+        <v>40.732171356102107</v>
       </c>
       <c r="F24" s="327">
         <v>0.25</v>
@@ -19628,13 +19617,13 @@
         <v>0.19999999999999998</v>
       </c>
     </row>
-    <row r="25" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="25" spans="2:7">
       <c r="B25" s="141" t="s">
         <v>451</v>
       </c>
       <c r="C25" s="441">
         <f>E23*F23+E24*F24+E22*F22</f>
-        <v>54.993525534829033</v>
+        <v>55.195760727583824</v>
       </c>
       <c r="D25" s="141" t="str">
         <f>Market_currency</f>
@@ -19642,12 +19631,12 @@
       </c>
       <c r="G25" s="149"/>
     </row>
-    <row r="27" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="27" spans="2:7" ht="13.15">
       <c r="B27" s="106" t="s">
         <v>452</v>
       </c>
     </row>
-    <row r="28" spans="2:7" ht="14" x14ac:dyDescent="0.2">
+    <row r="28" spans="2:7" ht="13.15">
       <c r="B28" s="153" t="s">
         <v>436</v>
       </c>
@@ -19668,7 +19657,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="29" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="29" spans="2:7">
       <c r="B29" s="302" t="s">
         <v>444</v>
       </c>
@@ -19681,7 +19670,7 @@
       </c>
       <c r="E29" s="326">
         <f>DCF!E90</f>
-        <v>99.606027704524323</v>
+        <v>99.972322536806104</v>
       </c>
       <c r="F29" s="327">
         <v>0.15</v>
@@ -19691,7 +19680,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="30" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="30" spans="2:7">
       <c r="B30" s="315" t="s">
         <v>447</v>
       </c>
@@ -19704,7 +19693,7 @@
       </c>
       <c r="E30" s="326">
         <f>DCF!E94</f>
-        <v>30.07764296409178</v>
+        <v>30.18825158325733</v>
       </c>
       <c r="F30" s="327">
         <v>0.05</v>
@@ -19714,16 +19703,16 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="31" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:7">
       <c r="E31" s="329"/>
       <c r="F31" s="329"/>
     </row>
-    <row r="32" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="32" spans="2:7" ht="13.15">
       <c r="B32" s="145" t="s">
         <v>456</v>
       </c>
     </row>
-    <row r="33" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="33" spans="2:7">
       <c r="B33" s="97" t="s">
         <v>458</v>
       </c>
@@ -19743,13 +19732,13 @@
         <v>3</v>
       </c>
     </row>
-    <row r="34" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="34" spans="2:7">
       <c r="B34" s="97" t="s">
         <v>233</v>
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>42.2</v>
+        <v>44.5</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19760,16 +19749,16 @@
       </c>
       <c r="F34" s="330">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.15751340909520897</v>
-      </c>
-    </row>
-    <row r="35" spans="2:7" x14ac:dyDescent="0.15">
+        <v>0.13797018670551686</v>
+      </c>
+    </row>
+    <row r="35" spans="2:7">
       <c r="B35" s="97" t="s">
         <v>434</v>
       </c>
       <c r="C35" s="320">
         <f>DCF!C11</f>
-        <v>46.309685301690244</v>
+        <v>46.479986224250105</v>
       </c>
       <c r="D35" s="97" t="str">
         <f>Market_currency</f>
@@ -19780,16 +19769,16 @@
       </c>
       <c r="F35" s="330">
         <f>RATE(Holding_Period,$C$33,-C35,$C$36)</f>
-        <v>0.12123248939632798</v>
-      </c>
-    </row>
-    <row r="36" spans="2:7" x14ac:dyDescent="0.15">
+        <v>0.12112824377112424</v>
+      </c>
+    </row>
+    <row r="36" spans="2:7">
       <c r="B36" s="97" t="s">
         <v>435</v>
       </c>
       <c r="C36" s="321">
         <f>E22*G22+E23*G23+E24*G24+E30*G30+E29*G29</f>
-        <v>60.439606731746466</v>
+        <v>60.661869541750846</v>
       </c>
       <c r="D36" t="str">
         <f>Market_currency</f>
@@ -19802,7 +19791,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="38" spans="2:7" ht="16" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:7" ht="13.9">
       <c r="B38" s="34" t="s">
         <v>411</v>
       </c>
@@ -19812,7 +19801,7 @@
       <c r="F38" s="35"/>
       <c r="G38" s="35"/>
     </row>
-    <row r="39" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="39" spans="2:7" ht="13.15">
       <c r="B39" s="414" t="str">
         <f>IF(DCF!F14="II","2","1")&amp;"-stage DCF"</f>
         <v>1-stage DCF</v>
@@ -19821,7 +19810,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="40" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="40" spans="2:7">
       <c r="B40" t="s">
         <v>551</v>
       </c>
@@ -19833,7 +19822,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="41" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="41" spans="2:7">
       <c r="B41" s="97" t="s">
         <v>400</v>
       </c>
@@ -19843,7 +19832,7 @@
       </c>
       <c r="E41" s="97"/>
     </row>
-    <row r="43" spans="2:7" ht="16" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:7" ht="13.9">
       <c r="B43" s="34" t="s">
         <v>276</v>
       </c>
@@ -19853,7 +19842,7 @@
       <c r="F43" s="35"/>
       <c r="G43" s="35"/>
     </row>
-    <row r="44" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="44" spans="2:7" ht="13.15">
       <c r="B44" s="106" t="s">
         <v>249</v>
       </c>
@@ -19861,7 +19850,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="45" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="45" spans="2:7">
       <c r="B45" s="139" t="s">
         <v>111</v>
       </c>
@@ -19874,7 +19863,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="46" spans="2:7" ht="14" x14ac:dyDescent="0.15">
+    <row r="46" spans="2:7">
       <c r="B46" s="114" t="s">
         <v>112</v>
       </c>
@@ -19886,13 +19875,13 @@
         <v>252</v>
       </c>
     </row>
-    <row r="47" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="47" spans="2:7">
       <c r="B47" s="97" t="s">
         <v>96</v>
       </c>
       <c r="C47" s="146">
         <f>DCF!I18</f>
-        <v>59.704375522554315</v>
+        <v>59.923934566545064</v>
       </c>
       <c r="D47" s="146" t="str">
         <f>Market_currency</f>
@@ -19902,7 +19891,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="49" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="49" spans="2:7" ht="13.15">
       <c r="B49" s="106" t="s">
         <v>277</v>
       </c>
@@ -19914,7 +19903,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="50" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="50" spans="2:7">
       <c r="B50" s="97" t="s">
         <v>250</v>
       </c>
@@ -19924,7 +19913,7 @@
       </c>
       <c r="E50" s="126"/>
     </row>
-    <row r="51" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="51" spans="2:7">
       <c r="B51" s="97" t="s">
         <v>246</v>
       </c>
@@ -19936,7 +19925,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="52" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="52" spans="2:7">
       <c r="B52" s="97" t="s">
         <v>245</v>
       </c>
@@ -19946,7 +19935,7 @@
       </c>
       <c r="E52" s="221"/>
     </row>
-    <row r="53" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="53" spans="2:7">
       <c r="B53" s="97" t="s">
         <v>237</v>
       </c>
@@ -19962,7 +19951,7 @@
         <v>-0.17099721727961331</v>
       </c>
     </row>
-    <row r="55" spans="2:7" ht="16" x14ac:dyDescent="0.25">
+    <row r="55" spans="2:7" ht="13.9">
       <c r="B55" s="34" t="s">
         <v>107</v>
       </c>
@@ -19972,12 +19961,12 @@
       <c r="F55" s="35"/>
       <c r="G55" s="35"/>
     </row>
-    <row r="56" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="56" spans="2:7" ht="13.15">
       <c r="B56" s="106" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="57" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="57" spans="2:7">
       <c r="B57" s="220" t="s">
         <v>248</v>
       </c>
@@ -19987,7 +19976,7 @@
       </c>
       <c r="D57" s="126"/>
     </row>
-    <row r="58" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="58" spans="2:7">
       <c r="B58" s="97" t="s">
         <v>333</v>
       </c>
@@ -20000,13 +19989,13 @@
         <v>HKD</v>
       </c>
     </row>
-    <row r="60" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="60" spans="2:7" ht="13.15">
       <c r="B60" s="106" t="s">
         <v>473</v>
       </c>
       <c r="E60" s="413"/>
     </row>
-    <row r="61" spans="2:7" ht="14" x14ac:dyDescent="0.2">
+    <row r="61" spans="2:7" ht="13.15">
       <c r="B61" s="153" t="s">
         <v>462</v>
       </c>
@@ -20027,7 +20016,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="62" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="62" spans="2:7" ht="13.15">
       <c r="B62" s="302" t="s">
         <v>312</v>
       </c>
@@ -20037,11 +20026,11 @@
       </c>
       <c r="D62" s="119">
         <f>C36/(1+F62)^Holding_Period</f>
-        <v>27.852353332602064</v>
+        <v>27.954778590668599</v>
       </c>
       <c r="E62" s="332">
         <f>C62+D62</f>
-        <v>30.472338478979687</v>
+        <v>30.574763737046222</v>
       </c>
       <c r="F62" s="301">
         <f>Thesis!E22</f>
@@ -20049,10 +20038,10 @@
       </c>
       <c r="G62" s="440">
         <f>(1-E62/C36)</f>
-        <v>0.49582169496523532</v>
-      </c>
-    </row>
-    <row r="63" spans="2:7" x14ac:dyDescent="0.15">
+        <v>0.49598052338293031</v>
+      </c>
+    </row>
+    <row r="63" spans="2:7" ht="13.15">
       <c r="B63" s="302" t="s">
         <v>313</v>
       </c>
@@ -20062,11 +20051,11 @@
       </c>
       <c r="D63" s="119">
         <f>C36/(1+F63)^Holding_Period</f>
-        <v>34.910964177182088</v>
+        <v>35.039347027726137</v>
       </c>
       <c r="E63" s="332">
         <f>C63+D63</f>
-        <v>37.923481236889849</v>
+        <v>38.051864087433898</v>
       </c>
       <c r="F63" s="301">
         <f>Thesis!E23</f>
@@ -20074,10 +20063,10 @@
       </c>
       <c r="G63" s="440">
         <f>(1-E63/C36)</f>
-        <v>0.37253924557768192</v>
-      </c>
-    </row>
-    <row r="65" spans="2:7" ht="14" x14ac:dyDescent="0.2">
+        <v>0.37272187001680679</v>
+      </c>
+    </row>
+    <row r="65" spans="2:7" ht="13.15">
       <c r="B65" s="153" t="s">
         <v>463</v>
       </c>
@@ -20098,7 +20087,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="66" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="66" spans="2:7" ht="13.15">
       <c r="B66" s="302" t="s">
         <v>315</v>
       </c>
@@ -20108,11 +20097,11 @@
       </c>
       <c r="D66" s="119">
         <f>C36/(1+F66)^Holding_Period</f>
-        <v>43.320716274706704</v>
+        <v>43.480025453758017</v>
       </c>
       <c r="E66" s="332">
         <f>C66+D66</f>
-        <v>46.775086255631912</v>
+        <v>46.934395434683225</v>
       </c>
       <c r="F66" s="301">
         <f>Thesis!E24</f>
@@ -20120,10 +20109,10 @@
       </c>
       <c r="G66" s="440">
         <f>(1-E66/C36)</f>
-        <v>0.22608552925836856</v>
-      </c>
-    </row>
-    <row r="67" spans="2:7" x14ac:dyDescent="0.15">
+        <v>0.22629493965100456</v>
+      </c>
+    </row>
+    <row r="67" spans="2:7" ht="13.15">
       <c r="B67" s="302" t="s">
         <v>314</v>
       </c>
@@ -20133,11 +20122,11 @@
       </c>
       <c r="D67" s="119">
         <f>C36/(1+F67)^Holding_Period</f>
-        <v>48.992514207704659</v>
+        <v>49.172681062947682</v>
       </c>
       <c r="E67" s="332">
         <f>C67+D67</f>
-        <v>52.732918282721435</v>
+        <v>52.913085137964458</v>
       </c>
       <c r="F67" s="301">
         <f>Thesis!E25</f>
@@ -20145,7 +20134,7 @@
       </c>
       <c r="G67" s="440">
         <f>(1-E67/C36)</f>
-        <v>0.12751056576576003</v>
+        <v>0.12773731608211059</v>
       </c>
     </row>
   </sheetData>
@@ -20164,7 +20153,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:J167"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.4"/>
   <cols>
     <col min="1" max="1" width="2.6640625" style="343" customWidth="1"/>
     <col min="2" max="2" width="32.6640625" style="343" customWidth="1"/>
@@ -20173,7 +20162,7 @@
     <col min="7" max="16384" width="9" style="343"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:10" ht="16" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" ht="13.9">
       <c r="A2" s="345" t="s">
         <v>334</v>
       </c>
@@ -20187,7 +20176,7 @@
       <c r="I2" s="346"/>
       <c r="J2" s="346"/>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:10">
       <c r="E3" s="435" t="s">
         <v>542</v>
       </c>
@@ -20196,7 +20185,7 @@
         <v>46065</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:10">
       <c r="B4" s="422" t="s">
         <v>534</v>
       </c>
@@ -20213,7 +20202,7 @@
         <v>INT</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:10">
       <c r="B5" s="343" t="s">
         <v>364</v>
       </c>
@@ -20229,7 +20218,7 @@
         <v>Y</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:10">
       <c r="B6" s="350" t="s">
         <v>336</v>
       </c>
@@ -20239,7 +20228,7 @@
       </c>
       <c r="E6" s="354"/>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:10">
       <c r="B7" s="343" t="s">
         <v>366</v>
       </c>
@@ -20250,16 +20239,16 @@
       <c r="D7" s="354"/>
       <c r="E7" s="354"/>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:10">
       <c r="B8" s="351" t="s">
         <v>365</v>
       </c>
       <c r="C8" s="356">
         <f>Market_Price</f>
-        <v>42.2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+        <v>44.5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
       <c r="B9" s="351" t="s">
         <v>361</v>
       </c>
@@ -20268,43 +20257,43 @@
         <v>2558824000</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:10">
       <c r="B10" s="351" t="s">
         <v>367</v>
       </c>
       <c r="C10" s="357">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>107982.3728</v>
+        <v>113867.66800000001</v>
       </c>
       <c r="D10" s="343" t="s">
         <v>529</v>
       </c>
       <c r="E10" s="360">
         <f>Scenarios!F34</f>
-        <v>0.15751340909520897</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
+        <v>0.13797018670551686</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
       <c r="D11" s="349"/>
       <c r="E11" s="349"/>
     </row>
-    <row r="12" spans="1:10" ht="24.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B12" s="474" t="s">
+    <row r="12" spans="1:10" ht="24.5" customHeight="1">
+      <c r="B12" s="471" t="s">
         <v>498</v>
       </c>
-      <c r="C12" s="474"/>
-      <c r="D12" s="474"/>
-      <c r="E12" s="474"/>
-      <c r="F12" s="474"/>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="C12" s="471"/>
+      <c r="D12" s="471"/>
+      <c r="E12" s="471"/>
+      <c r="F12" s="471"/>
+    </row>
+    <row r="14" spans="1:10">
       <c r="B14" s="347" t="s">
         <v>370</v>
       </c>
       <c r="C14" s="348"/>
       <c r="D14" s="349"/>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:10">
       <c r="B15" s="343" t="s">
         <v>337</v>
       </c>
@@ -20320,7 +20309,7 @@
         <v>EUR/HKD</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:10">
       <c r="B16" s="343" t="s">
         <v>338</v>
       </c>
@@ -20333,10 +20322,10 @@
       </c>
       <c r="E16" s="425">
         <f>Exchange_Rate</f>
-        <v>9.2105230273246779</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
+        <v>9.2443941400000007</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
       <c r="B17" s="343" t="s">
         <v>535</v>
       </c>
@@ -20352,14 +20341,14 @@
         <v>EUR</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:6">
       <c r="B18" s="343" t="str">
         <f>"预期股权价值 ("&amp;C7&amp;") :"</f>
         <v>预期股权价值 (HKD) :</v>
       </c>
       <c r="C18" s="359">
         <f>C125</f>
-        <v>60.439606731746466</v>
+        <v>60.661869541750846</v>
       </c>
       <c r="D18" s="350" t="s">
         <v>362</v>
@@ -20369,7 +20358,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:6">
       <c r="B19" s="350" t="s">
         <v>335</v>
       </c>
@@ -20385,11 +20374,11 @@
         <v>46081</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:6">
       <c r="D20" s="349"/>
       <c r="E20" s="349"/>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:6">
       <c r="B21" s="347" t="s">
         <v>493</v>
       </c>
@@ -20405,13 +20394,13 @@
         <v>3</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:6">
       <c r="B22" s="343" t="s">
         <v>340</v>
       </c>
       <c r="C22" s="364">
         <f>E140</f>
-        <v>30.472338478979687</v>
+        <v>30.574763737046222</v>
       </c>
       <c r="D22" s="365" t="s">
         <v>440</v>
@@ -20421,13 +20410,13 @@
         <v>0.29465259038036606</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:6">
       <c r="B23" s="343" t="s">
         <v>341</v>
       </c>
       <c r="C23" s="367">
         <f>E141</f>
-        <v>37.923481236889849</v>
+        <v>38.051864087433898</v>
       </c>
       <c r="D23" s="365" t="s">
         <v>441</v>
@@ -20437,13 +20426,13 @@
         <v>0.20075184365903009</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:6">
       <c r="B24" s="343" t="s">
         <v>343</v>
       </c>
       <c r="C24" s="367">
         <f>E144</f>
-        <v>46.775086255631912</v>
+        <v>46.934395434683225</v>
       </c>
       <c r="D24" s="365" t="s">
         <v>443</v>
@@ -20453,13 +20442,13 @@
         <v>0.1174</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:6">
       <c r="B25" s="343" t="s">
         <v>342</v>
       </c>
       <c r="C25" s="367">
         <f>E145</f>
-        <v>52.732918282721435</v>
+        <v>52.913085137964458</v>
       </c>
       <c r="D25" s="365" t="s">
         <v>442</v>
@@ -20469,7 +20458,7 @@
         <v>7.2499999999999995E-2</v>
       </c>
     </row>
-    <row r="27" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" ht="13.9">
       <c r="A27" s="345" t="s">
         <v>345</v>
       </c>
@@ -20479,25 +20468,25 @@
       <c r="E27" s="345"/>
       <c r="F27" s="345"/>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B29" s="474" t="s">
+    <row r="29" spans="1:6">
+      <c r="B29" s="471" t="s">
         <v>499</v>
       </c>
-      <c r="C29" s="474"/>
-      <c r="D29" s="474"/>
-      <c r="E29" s="474"/>
-      <c r="F29" s="474"/>
-    </row>
-    <row r="30" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B30" s="477" t="s">
+      <c r="C29" s="471"/>
+      <c r="D29" s="471"/>
+      <c r="E29" s="471"/>
+      <c r="F29" s="471"/>
+    </row>
+    <row r="30" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B30" s="472" t="s">
         <v>500</v>
       </c>
-      <c r="C30" s="477"/>
-      <c r="D30" s="477"/>
-      <c r="E30" s="477"/>
-      <c r="F30" s="477"/>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C30" s="472"/>
+      <c r="D30" s="472"/>
+      <c r="E30" s="472"/>
+      <c r="F30" s="472"/>
+    </row>
+    <row r="32" spans="1:6">
       <c r="B32" s="369" t="s">
         <v>371</v>
       </c>
@@ -20506,7 +20495,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="33" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:6">
       <c r="B33" s="470" t="s">
         <v>501</v>
       </c>
@@ -20515,7 +20504,7 @@
       <c r="E33" s="470"/>
       <c r="F33" s="470"/>
     </row>
-    <row r="34" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:6">
       <c r="B34" s="372" t="s">
         <v>197</v>
       </c>
@@ -20528,11 +20517,11 @@
         <v>EUR</v>
       </c>
     </row>
-    <row r="35" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:6">
       <c r="B35" s="372"/>
       <c r="C35" s="374"/>
     </row>
-    <row r="36" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="2:6" ht="24.5" customHeight="1">
       <c r="B36" s="470" t="s">
         <v>502</v>
       </c>
@@ -20541,7 +20530,7 @@
       <c r="E36" s="470"/>
       <c r="F36" s="470"/>
     </row>
-    <row r="37" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:6">
       <c r="B37" s="372" t="s">
         <v>199</v>
       </c>
@@ -20554,7 +20543,7 @@
         <v>EUR</v>
       </c>
     </row>
-    <row r="38" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:6">
       <c r="B38" s="375" t="s">
         <v>200</v>
       </c>
@@ -20567,7 +20556,7 @@
         <v>EUR</v>
       </c>
     </row>
-    <row r="40" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:6">
       <c r="B40" s="470" t="s">
         <v>503</v>
       </c>
@@ -20576,7 +20565,7 @@
       <c r="E40" s="470"/>
       <c r="F40" s="470"/>
     </row>
-    <row r="41" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:6">
       <c r="B41" s="372" t="s">
         <v>202</v>
       </c>
@@ -20589,7 +20578,7 @@
         <v>EUR</v>
       </c>
     </row>
-    <row r="43" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:6">
       <c r="B43" s="470" t="s">
         <v>504</v>
       </c>
@@ -20598,7 +20587,7 @@
       <c r="E43" s="470"/>
       <c r="F43" s="470"/>
     </row>
-    <row r="44" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:6">
       <c r="B44" s="372" t="s">
         <v>267</v>
       </c>
@@ -20613,7 +20602,7 @@
       <c r="E44" s="371"/>
       <c r="F44" s="371"/>
     </row>
-    <row r="45" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:6">
       <c r="B45" s="372" t="s">
         <v>268</v>
       </c>
@@ -20628,7 +20617,7 @@
       <c r="E45" s="371"/>
       <c r="F45" s="371"/>
     </row>
-    <row r="46" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:6">
       <c r="B46" s="372" t="s">
         <v>203</v>
       </c>
@@ -20641,12 +20630,12 @@
         <v>EUR</v>
       </c>
     </row>
-    <row r="48" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:6">
       <c r="B48" s="343" t="s">
         <v>505</v>
       </c>
     </row>
-    <row r="49" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="49" spans="2:6">
       <c r="B49" s="372" t="s">
         <v>223</v>
       </c>
@@ -20659,7 +20648,7 @@
         <v>EUR</v>
       </c>
     </row>
-    <row r="51" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="51" spans="2:6">
       <c r="B51" s="470" t="s">
         <v>506</v>
       </c>
@@ -20668,7 +20657,7 @@
       <c r="E51" s="470"/>
       <c r="F51" s="470"/>
     </row>
-    <row r="52" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="52" spans="2:6">
       <c r="B52" s="372" t="s">
         <v>496</v>
       </c>
@@ -20681,16 +20670,16 @@
         <v>EUR</v>
       </c>
     </row>
-    <row r="54" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="54" spans="2:6">
       <c r="B54" s="470" t="s">
         <v>507</v>
       </c>
-      <c r="C54" s="476"/>
-      <c r="D54" s="476"/>
-      <c r="E54" s="476"/>
-      <c r="F54" s="476"/>
-    </row>
-    <row r="55" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="C54" s="473"/>
+      <c r="D54" s="473"/>
+      <c r="E54" s="473"/>
+      <c r="F54" s="473"/>
+    </row>
+    <row r="55" spans="2:6">
       <c r="B55" s="372" t="s">
         <v>207</v>
       </c>
@@ -20703,25 +20692,25 @@
         <v>EUR</v>
       </c>
     </row>
-    <row r="57" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B57" s="474" t="s">
+    <row r="57" spans="2:6">
+      <c r="B57" s="471" t="s">
         <v>508</v>
       </c>
-      <c r="C57" s="474"/>
-      <c r="D57" s="474"/>
-      <c r="E57" s="474"/>
-      <c r="F57" s="474"/>
-    </row>
-    <row r="58" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B58" s="474" t="s">
+      <c r="C57" s="471"/>
+      <c r="D57" s="471"/>
+      <c r="E57" s="471"/>
+      <c r="F57" s="471"/>
+    </row>
+    <row r="58" spans="2:6">
+      <c r="B58" s="471" t="s">
         <v>509</v>
       </c>
-      <c r="C58" s="474"/>
-      <c r="D58" s="474"/>
-      <c r="E58" s="474"/>
-      <c r="F58" s="474"/>
-    </row>
-    <row r="60" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="C58" s="471"/>
+      <c r="D58" s="471"/>
+      <c r="E58" s="471"/>
+      <c r="F58" s="471"/>
+    </row>
+    <row r="60" spans="2:6">
       <c r="B60" s="372" t="s">
         <v>372</v>
       </c>
@@ -20734,7 +20723,7 @@
         <v>EUR</v>
       </c>
     </row>
-    <row r="61" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="61" spans="2:6">
       <c r="B61" s="372" t="s">
         <v>213</v>
       </c>
@@ -20747,23 +20736,23 @@
         <v>EUR</v>
       </c>
     </row>
-    <row r="62" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="62" spans="2:6">
       <c r="B62" s="377" t="s">
         <v>302</v>
       </c>
       <c r="C62" s="378">
         <f>Normalized_FCF!C124</f>
-        <v>6.9088519142746635E-2</v>
+        <v>6.575858885923315E-2</v>
       </c>
       <c r="F62" s="379"/>
     </row>
-    <row r="63" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="63" spans="2:6">
       <c r="B63" s="377" t="s">
         <v>332</v>
       </c>
       <c r="C63" s="378">
         <f>Normalized_FCF!C92</f>
-        <v>3.392895734597156E-2</v>
+        <v>3.2175325842696632E-2</v>
       </c>
       <c r="E63" s="372" t="s">
         <v>373</v>
@@ -20773,7 +20762,7 @@
         <v>4.5232326123897897</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:6">
       <c r="B65" s="369" t="s">
         <v>376</v>
       </c>
@@ -20784,7 +20773,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:6">
       <c r="B66" s="372" t="s">
         <v>326</v>
       </c>
@@ -20797,7 +20786,7 @@
         <v>0.28005991710273764</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:6">
       <c r="B67" s="382" t="str">
         <f>Normalized_FCF!B116</f>
         <v>Pre-tax Profit/Sales</v>
@@ -20811,7 +20800,7 @@
         <v>0.21885492502426099</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:6">
       <c r="B68" s="382" t="str">
         <f>Normalized_FCF!B117</f>
         <v>Sales/Total Assets</v>
@@ -20825,7 +20814,7 @@
         <v>0.65265738052043343</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:6">
       <c r="B69" s="382" t="str">
         <f>Normalized_FCF!B118</f>
         <v>Total Assets/Equity</v>
@@ -20839,7 +20828,7 @@
         <v>1.9606920057834423</v>
       </c>
     </row>
-    <row r="71" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:6" ht="13.9">
       <c r="A71" s="345" t="s">
         <v>476</v>
       </c>
@@ -20849,43 +20838,43 @@
       <c r="E71" s="345"/>
       <c r="F71" s="345"/>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:6">
       <c r="A72" s="385"/>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:6">
       <c r="A73" s="386"/>
-      <c r="B73" s="474" t="s">
+      <c r="B73" s="471" t="s">
         <v>510</v>
       </c>
-      <c r="C73" s="474"/>
-      <c r="D73" s="474"/>
-      <c r="E73" s="474"/>
-      <c r="F73" s="474"/>
-    </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B74" s="477" t="s">
+      <c r="C73" s="471"/>
+      <c r="D73" s="471"/>
+      <c r="E73" s="471"/>
+      <c r="F73" s="471"/>
+    </row>
+    <row r="74" spans="1:6">
+      <c r="B74" s="472" t="s">
         <v>479</v>
       </c>
-      <c r="C74" s="477"/>
-      <c r="D74" s="477"/>
-      <c r="E74" s="477"/>
-      <c r="F74" s="477"/>
-    </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C74" s="472"/>
+      <c r="D74" s="472"/>
+      <c r="E74" s="472"/>
+      <c r="F74" s="472"/>
+    </row>
+    <row r="76" spans="1:6">
       <c r="B76" s="369" t="s">
         <v>371</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B77" s="474" t="s">
+    <row r="77" spans="1:6">
+      <c r="B77" s="471" t="s">
         <v>511</v>
       </c>
-      <c r="C77" s="474"/>
-      <c r="D77" s="474"/>
-      <c r="E77" s="474"/>
-      <c r="F77" s="474"/>
-    </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C77" s="471"/>
+      <c r="D77" s="471"/>
+      <c r="E77" s="471"/>
+      <c r="F77" s="471"/>
+    </row>
+    <row r="78" spans="1:6">
       <c r="B78" s="343" t="s">
         <v>215</v>
       </c>
@@ -20898,20 +20887,20 @@
         <v>EUR</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:6">
       <c r="B79" s="372" t="s">
         <v>234</v>
       </c>
       <c r="C79" s="387">
         <f>C78*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>-10.279726290448499</v>
+        <v>-10.317529330126302</v>
       </c>
       <c r="D79" s="343" t="str">
         <f>Market_currency</f>
         <v>HKD</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:6">
       <c r="B80" s="382" t="s">
         <v>309</v>
       </c>
@@ -20920,7 +20909,7 @@
         <v>0.67283405398617657</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:6">
       <c r="B81" s="382" t="s">
         <v>311</v>
       </c>
@@ -20929,12 +20918,12 @@
         <v>2.2041306156151999</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:6">
       <c r="B83" s="343" t="s">
         <v>512</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:6">
       <c r="B84" s="343" t="s">